--- a/development/MS/spec/MSBB/Panel/MSBBP1210_SloReg.xlsx
+++ b/development/MS/spec/MSBB/Panel/MSBBP1210_SloReg.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\mcframeDEV\development\MS\spec\MSBB\Panel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC047C5F-CA1D-42CC-9C28-67871CC7329F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0045A7C3-E3D5-4F79-8ED2-4FFCB4B9C6A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-3330" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MSBBP1210" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9034" uniqueCount="2343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9034" uniqueCount="2344">
   <si>
     <t>検索</t>
     <rPh sb="0" eb="2">
@@ -9995,6 +9995,9 @@
   </si>
   <si>
     <t>Matching Expansion</t>
+  </si>
+  <si>
+    <t>stk_mng_typ</t>
   </si>
 </sst>
 </file>
@@ -11396,14 +11399,14 @@
     <xf numFmtId="0" fontId="27" fillId="24" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -11414,79 +11417,7 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11495,29 +11426,8 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -11548,6 +11458,99 @@
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -35703,7 +35706,7 @@
       <c r="B286" s="25"/>
       <c r="C286" s="25"/>
       <c r="D286" s="25" t="s">
-        <v>937</v>
+        <v>2343</v>
       </c>
       <c r="E286" s="37" t="s">
         <v>2061</v>
@@ -35736,38 +35739,38 @@
       <c r="W286" s="25"/>
       <c r="X286" s="25"/>
       <c r="Z286" s="25" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="AA286" s="25" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="AB286" s="25" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="AC286" s="25" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="AD286" s="25" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="AE286" s="25"/>
       <c r="AF286" s="25" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="AG286" s="25" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="AH286" s="25" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="AI286" s="25" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="AJ286" s="25" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="AK286" s="25" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="AM286" s="25"/>
       <c r="AN286" s="25" t="s">
@@ -64319,65 +64322,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:57" ht="38.25" customHeight="1" thickBot="1">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="101" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
-      <c r="H1" s="106"/>
-      <c r="I1" s="106"/>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
-      <c r="V1" s="106"/>
-      <c r="W1" s="106"/>
-      <c r="X1" s="106"/>
-      <c r="Y1" s="106"/>
-      <c r="Z1" s="106"/>
-      <c r="AA1" s="106"/>
-      <c r="AB1" s="106"/>
-      <c r="AC1" s="106"/>
-      <c r="AD1" s="106"/>
-      <c r="AE1" s="106"/>
-      <c r="AF1" s="106"/>
-      <c r="AG1" s="106"/>
-      <c r="AH1" s="106"/>
-      <c r="AI1" s="106"/>
-      <c r="AJ1" s="106"/>
-      <c r="AK1" s="106"/>
-      <c r="AL1" s="106"/>
-      <c r="AM1" s="106"/>
-      <c r="AN1" s="106"/>
-      <c r="AO1" s="106"/>
-      <c r="AP1" s="106"/>
-      <c r="AQ1" s="106"/>
-      <c r="AR1" s="106"/>
-      <c r="AS1" s="106"/>
-      <c r="AT1" s="106"/>
-      <c r="AU1" s="106"/>
-      <c r="AV1" s="106"/>
-      <c r="AW1" s="106"/>
-      <c r="AX1" s="106"/>
-      <c r="AY1" s="106"/>
-      <c r="AZ1" s="106"/>
-      <c r="BA1" s="106"/>
-      <c r="BB1" s="106"/>
-      <c r="BC1" s="106"/>
-      <c r="BD1" s="106"/>
-      <c r="BE1" s="107"/>
+      <c r="B1" s="102"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="102"/>
+      <c r="AG1" s="102"/>
+      <c r="AH1" s="102"/>
+      <c r="AI1" s="102"/>
+      <c r="AJ1" s="102"/>
+      <c r="AK1" s="102"/>
+      <c r="AL1" s="102"/>
+      <c r="AM1" s="102"/>
+      <c r="AN1" s="102"/>
+      <c r="AO1" s="102"/>
+      <c r="AP1" s="102"/>
+      <c r="AQ1" s="102"/>
+      <c r="AR1" s="102"/>
+      <c r="AS1" s="102"/>
+      <c r="AT1" s="102"/>
+      <c r="AU1" s="102"/>
+      <c r="AV1" s="102"/>
+      <c r="AW1" s="102"/>
+      <c r="AX1" s="102"/>
+      <c r="AY1" s="102"/>
+      <c r="AZ1" s="102"/>
+      <c r="BA1" s="102"/>
+      <c r="BB1" s="102"/>
+      <c r="BC1" s="102"/>
+      <c r="BD1" s="102"/>
+      <c r="BE1" s="103"/>
     </row>
     <row r="2" spans="1:57" ht="12" customHeight="1" thickBot="1">
       <c r="A2" s="14"/>
@@ -64424,145 +64427,145 @@
       <c r="AP2" s="14"/>
     </row>
     <row r="3" spans="1:57" ht="15" customHeight="1" thickBot="1">
-      <c r="A3" s="118" t="s">
+      <c r="A3" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="109"/>
-      <c r="C3" s="109"/>
-      <c r="D3" s="109"/>
-      <c r="E3" s="109"/>
-      <c r="F3" s="109"/>
-      <c r="G3" s="110"/>
-      <c r="H3" s="108" t="s">
+      <c r="B3" s="85"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="104" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="109"/>
-      <c r="J3" s="109"/>
-      <c r="K3" s="109"/>
-      <c r="L3" s="109"/>
-      <c r="M3" s="109"/>
-      <c r="N3" s="110"/>
-      <c r="O3" s="108" t="s">
+      <c r="I3" s="85"/>
+      <c r="J3" s="85"/>
+      <c r="K3" s="85"/>
+      <c r="L3" s="85"/>
+      <c r="M3" s="85"/>
+      <c r="N3" s="86"/>
+      <c r="O3" s="104" t="s">
         <v>9</v>
       </c>
-      <c r="P3" s="111"/>
-      <c r="Q3" s="111"/>
-      <c r="R3" s="111"/>
-      <c r="S3" s="111"/>
-      <c r="T3" s="111"/>
-      <c r="U3" s="111"/>
-      <c r="V3" s="111"/>
-      <c r="W3" s="111"/>
-      <c r="X3" s="111"/>
-      <c r="Y3" s="111"/>
-      <c r="Z3" s="111"/>
-      <c r="AA3" s="111"/>
-      <c r="AB3" s="111"/>
-      <c r="AC3" s="111"/>
-      <c r="AD3" s="111"/>
-      <c r="AE3" s="111"/>
-      <c r="AF3" s="111"/>
-      <c r="AG3" s="111"/>
-      <c r="AH3" s="111"/>
-      <c r="AI3" s="111"/>
-      <c r="AJ3" s="111"/>
-      <c r="AK3" s="111"/>
-      <c r="AL3" s="111"/>
-      <c r="AM3" s="111"/>
-      <c r="AN3" s="111"/>
-      <c r="AO3" s="111"/>
-      <c r="AP3" s="112"/>
-      <c r="AQ3" s="108" t="s">
+      <c r="P3" s="105"/>
+      <c r="Q3" s="105"/>
+      <c r="R3" s="105"/>
+      <c r="S3" s="105"/>
+      <c r="T3" s="105"/>
+      <c r="U3" s="105"/>
+      <c r="V3" s="105"/>
+      <c r="W3" s="105"/>
+      <c r="X3" s="105"/>
+      <c r="Y3" s="105"/>
+      <c r="Z3" s="105"/>
+      <c r="AA3" s="105"/>
+      <c r="AB3" s="105"/>
+      <c r="AC3" s="105"/>
+      <c r="AD3" s="105"/>
+      <c r="AE3" s="105"/>
+      <c r="AF3" s="105"/>
+      <c r="AG3" s="105"/>
+      <c r="AH3" s="105"/>
+      <c r="AI3" s="105"/>
+      <c r="AJ3" s="105"/>
+      <c r="AK3" s="105"/>
+      <c r="AL3" s="105"/>
+      <c r="AM3" s="105"/>
+      <c r="AN3" s="105"/>
+      <c r="AO3" s="105"/>
+      <c r="AP3" s="106"/>
+      <c r="AQ3" s="104" t="s">
         <v>10</v>
       </c>
-      <c r="AR3" s="113"/>
-      <c r="AS3" s="113"/>
-      <c r="AT3" s="113"/>
-      <c r="AU3" s="113"/>
-      <c r="AV3" s="113"/>
-      <c r="AW3" s="113"/>
-      <c r="AX3" s="113"/>
-      <c r="AY3" s="113"/>
-      <c r="AZ3" s="113"/>
-      <c r="BA3" s="113"/>
-      <c r="BB3" s="113"/>
-      <c r="BC3" s="113"/>
-      <c r="BD3" s="113"/>
-      <c r="BE3" s="114"/>
+      <c r="AR3" s="107"/>
+      <c r="AS3" s="107"/>
+      <c r="AT3" s="107"/>
+      <c r="AU3" s="107"/>
+      <c r="AV3" s="107"/>
+      <c r="AW3" s="107"/>
+      <c r="AX3" s="107"/>
+      <c r="AY3" s="107"/>
+      <c r="AZ3" s="107"/>
+      <c r="BA3" s="107"/>
+      <c r="BB3" s="107"/>
+      <c r="BC3" s="107"/>
+      <c r="BD3" s="107"/>
+      <c r="BE3" s="108"/>
     </row>
     <row r="4" spans="1:57" ht="15" customHeight="1">
-      <c r="A4" s="115">
+      <c r="A4" s="109">
         <v>1</v>
       </c>
-      <c r="B4" s="116"/>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="98"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="99"/>
-      <c r="K4" s="99"/>
-      <c r="L4" s="99"/>
-      <c r="M4" s="99"/>
-      <c r="N4" s="100"/>
-      <c r="O4" s="98" t="s">
+      <c r="B4" s="110"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="113"/>
+      <c r="L4" s="113"/>
+      <c r="M4" s="113"/>
+      <c r="N4" s="114"/>
+      <c r="O4" s="112" t="s">
         <v>11</v>
       </c>
-      <c r="P4" s="101"/>
-      <c r="Q4" s="101"/>
-      <c r="R4" s="101"/>
-      <c r="S4" s="101"/>
-      <c r="T4" s="101"/>
-      <c r="U4" s="101"/>
-      <c r="V4" s="101"/>
-      <c r="W4" s="101"/>
-      <c r="X4" s="101"/>
-      <c r="Y4" s="101"/>
-      <c r="Z4" s="101"/>
-      <c r="AA4" s="101"/>
-      <c r="AB4" s="101"/>
-      <c r="AC4" s="101"/>
-      <c r="AD4" s="101"/>
-      <c r="AE4" s="101"/>
-      <c r="AF4" s="101"/>
-      <c r="AG4" s="101"/>
-      <c r="AH4" s="101"/>
-      <c r="AI4" s="101"/>
-      <c r="AJ4" s="101"/>
-      <c r="AK4" s="101"/>
-      <c r="AL4" s="101"/>
-      <c r="AM4" s="101"/>
-      <c r="AN4" s="101"/>
-      <c r="AO4" s="101"/>
-      <c r="AP4" s="102"/>
-      <c r="AQ4" s="103"/>
-      <c r="AR4" s="101"/>
-      <c r="AS4" s="101"/>
-      <c r="AT4" s="101"/>
-      <c r="AU4" s="101"/>
-      <c r="AV4" s="101"/>
-      <c r="AW4" s="101"/>
-      <c r="AX4" s="101"/>
-      <c r="AY4" s="101"/>
-      <c r="AZ4" s="101"/>
-      <c r="BA4" s="101"/>
-      <c r="BB4" s="101"/>
-      <c r="BC4" s="101"/>
-      <c r="BD4" s="101"/>
-      <c r="BE4" s="104"/>
+      <c r="P4" s="115"/>
+      <c r="Q4" s="115"/>
+      <c r="R4" s="115"/>
+      <c r="S4" s="115"/>
+      <c r="T4" s="115"/>
+      <c r="U4" s="115"/>
+      <c r="V4" s="115"/>
+      <c r="W4" s="115"/>
+      <c r="X4" s="115"/>
+      <c r="Y4" s="115"/>
+      <c r="Z4" s="115"/>
+      <c r="AA4" s="115"/>
+      <c r="AB4" s="115"/>
+      <c r="AC4" s="115"/>
+      <c r="AD4" s="115"/>
+      <c r="AE4" s="115"/>
+      <c r="AF4" s="115"/>
+      <c r="AG4" s="115"/>
+      <c r="AH4" s="115"/>
+      <c r="AI4" s="115"/>
+      <c r="AJ4" s="115"/>
+      <c r="AK4" s="115"/>
+      <c r="AL4" s="115"/>
+      <c r="AM4" s="115"/>
+      <c r="AN4" s="115"/>
+      <c r="AO4" s="115"/>
+      <c r="AP4" s="116"/>
+      <c r="AQ4" s="117"/>
+      <c r="AR4" s="115"/>
+      <c r="AS4" s="115"/>
+      <c r="AT4" s="115"/>
+      <c r="AU4" s="115"/>
+      <c r="AV4" s="115"/>
+      <c r="AW4" s="115"/>
+      <c r="AX4" s="115"/>
+      <c r="AY4" s="115"/>
+      <c r="AZ4" s="115"/>
+      <c r="BA4" s="115"/>
+      <c r="BB4" s="115"/>
+      <c r="BC4" s="115"/>
+      <c r="BD4" s="115"/>
+      <c r="BE4" s="118"/>
     </row>
     <row r="5" spans="1:57" ht="105.75" customHeight="1">
-      <c r="A5" s="78">
+      <c r="A5" s="98">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B5" s="79"/>
-      <c r="C5" s="79"/>
-      <c r="D5" s="79"/>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="80"/>
+      <c r="B5" s="99"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="99"/>
+      <c r="E5" s="99"/>
+      <c r="F5" s="99"/>
+      <c r="G5" s="100"/>
       <c r="H5" s="81" t="s">
         <v>1816</v>
       </c>
@@ -64575,61 +64578,61 @@
       <c r="O5" s="81" t="s">
         <v>1818</v>
       </c>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
-      <c r="W5" s="84"/>
-      <c r="X5" s="84"/>
-      <c r="Y5" s="84"/>
-      <c r="Z5" s="84"/>
-      <c r="AA5" s="84"/>
-      <c r="AB5" s="84"/>
-      <c r="AC5" s="84"/>
-      <c r="AD5" s="84"/>
-      <c r="AE5" s="84"/>
-      <c r="AF5" s="84"/>
-      <c r="AG5" s="84"/>
-      <c r="AH5" s="84"/>
-      <c r="AI5" s="84"/>
-      <c r="AJ5" s="84"/>
-      <c r="AK5" s="84"/>
-      <c r="AL5" s="84"/>
-      <c r="AM5" s="84"/>
-      <c r="AN5" s="84"/>
-      <c r="AO5" s="84"/>
-      <c r="AP5" s="85"/>
-      <c r="AQ5" s="89" t="s">
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
+      <c r="W5" s="79"/>
+      <c r="X5" s="79"/>
+      <c r="Y5" s="79"/>
+      <c r="Z5" s="79"/>
+      <c r="AA5" s="79"/>
+      <c r="AB5" s="79"/>
+      <c r="AC5" s="79"/>
+      <c r="AD5" s="79"/>
+      <c r="AE5" s="79"/>
+      <c r="AF5" s="79"/>
+      <c r="AG5" s="79"/>
+      <c r="AH5" s="79"/>
+      <c r="AI5" s="79"/>
+      <c r="AJ5" s="79"/>
+      <c r="AK5" s="79"/>
+      <c r="AL5" s="79"/>
+      <c r="AM5" s="79"/>
+      <c r="AN5" s="79"/>
+      <c r="AO5" s="79"/>
+      <c r="AP5" s="87"/>
+      <c r="AQ5" s="78" t="s">
         <v>1817</v>
       </c>
-      <c r="AR5" s="84"/>
-      <c r="AS5" s="84"/>
-      <c r="AT5" s="84"/>
-      <c r="AU5" s="84"/>
-      <c r="AV5" s="84"/>
-      <c r="AW5" s="84"/>
-      <c r="AX5" s="84"/>
-      <c r="AY5" s="84"/>
-      <c r="AZ5" s="84"/>
-      <c r="BA5" s="84"/>
-      <c r="BB5" s="84"/>
-      <c r="BC5" s="84"/>
-      <c r="BD5" s="84"/>
-      <c r="BE5" s="90"/>
+      <c r="AR5" s="79"/>
+      <c r="AS5" s="79"/>
+      <c r="AT5" s="79"/>
+      <c r="AU5" s="79"/>
+      <c r="AV5" s="79"/>
+      <c r="AW5" s="79"/>
+      <c r="AX5" s="79"/>
+      <c r="AY5" s="79"/>
+      <c r="AZ5" s="79"/>
+      <c r="BA5" s="79"/>
+      <c r="BB5" s="79"/>
+      <c r="BC5" s="79"/>
+      <c r="BD5" s="79"/>
+      <c r="BE5" s="80"/>
     </row>
     <row r="6" spans="1:57" ht="36.6" customHeight="1">
-      <c r="A6" s="78">
+      <c r="A6" s="98">
         <v>1.2</v>
       </c>
-      <c r="B6" s="79"/>
-      <c r="C6" s="79"/>
-      <c r="D6" s="79"/>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="80"/>
+      <c r="B6" s="99"/>
+      <c r="C6" s="99"/>
+      <c r="D6" s="99"/>
+      <c r="E6" s="99"/>
+      <c r="F6" s="99"/>
+      <c r="G6" s="100"/>
       <c r="H6" s="81" t="s">
         <v>1844</v>
       </c>
@@ -64642,124 +64645,124 @@
       <c r="O6" s="81" t="s">
         <v>1843</v>
       </c>
-      <c r="P6" s="119"/>
-      <c r="Q6" s="119"/>
-      <c r="R6" s="119"/>
-      <c r="S6" s="119"/>
-      <c r="T6" s="119"/>
-      <c r="U6" s="119"/>
-      <c r="V6" s="119"/>
-      <c r="W6" s="119"/>
-      <c r="X6" s="119"/>
-      <c r="Y6" s="119"/>
-      <c r="Z6" s="119"/>
-      <c r="AA6" s="119"/>
-      <c r="AB6" s="119"/>
-      <c r="AC6" s="119"/>
-      <c r="AD6" s="119"/>
-      <c r="AE6" s="119"/>
-      <c r="AF6" s="119"/>
-      <c r="AG6" s="119"/>
-      <c r="AH6" s="119"/>
-      <c r="AI6" s="119"/>
-      <c r="AJ6" s="119"/>
-      <c r="AK6" s="119"/>
-      <c r="AL6" s="119"/>
-      <c r="AM6" s="119"/>
-      <c r="AN6" s="119"/>
-      <c r="AO6" s="119"/>
-      <c r="AP6" s="120"/>
-      <c r="AQ6" s="89" t="s">
+      <c r="P6" s="88"/>
+      <c r="Q6" s="88"/>
+      <c r="R6" s="88"/>
+      <c r="S6" s="88"/>
+      <c r="T6" s="88"/>
+      <c r="U6" s="88"/>
+      <c r="V6" s="88"/>
+      <c r="W6" s="88"/>
+      <c r="X6" s="88"/>
+      <c r="Y6" s="88"/>
+      <c r="Z6" s="88"/>
+      <c r="AA6" s="88"/>
+      <c r="AB6" s="88"/>
+      <c r="AC6" s="88"/>
+      <c r="AD6" s="88"/>
+      <c r="AE6" s="88"/>
+      <c r="AF6" s="88"/>
+      <c r="AG6" s="88"/>
+      <c r="AH6" s="88"/>
+      <c r="AI6" s="88"/>
+      <c r="AJ6" s="88"/>
+      <c r="AK6" s="88"/>
+      <c r="AL6" s="88"/>
+      <c r="AM6" s="88"/>
+      <c r="AN6" s="88"/>
+      <c r="AO6" s="88"/>
+      <c r="AP6" s="89"/>
+      <c r="AQ6" s="78" t="s">
         <v>1817</v>
       </c>
-      <c r="AR6" s="84"/>
-      <c r="AS6" s="84"/>
-      <c r="AT6" s="84"/>
-      <c r="AU6" s="84"/>
-      <c r="AV6" s="84"/>
-      <c r="AW6" s="84"/>
-      <c r="AX6" s="84"/>
-      <c r="AY6" s="84"/>
-      <c r="AZ6" s="84"/>
-      <c r="BA6" s="84"/>
-      <c r="BB6" s="84"/>
-      <c r="BC6" s="84"/>
-      <c r="BD6" s="84"/>
-      <c r="BE6" s="90"/>
+      <c r="AR6" s="79"/>
+      <c r="AS6" s="79"/>
+      <c r="AT6" s="79"/>
+      <c r="AU6" s="79"/>
+      <c r="AV6" s="79"/>
+      <c r="AW6" s="79"/>
+      <c r="AX6" s="79"/>
+      <c r="AY6" s="79"/>
+      <c r="AZ6" s="79"/>
+      <c r="BA6" s="79"/>
+      <c r="BB6" s="79"/>
+      <c r="BC6" s="79"/>
+      <c r="BD6" s="79"/>
+      <c r="BE6" s="80"/>
     </row>
     <row r="7" spans="1:57" ht="15" customHeight="1">
-      <c r="A7" s="78">
+      <c r="A7" s="98">
         <v>1.3</v>
       </c>
-      <c r="B7" s="79"/>
-      <c r="C7" s="79"/>
-      <c r="D7" s="79"/>
-      <c r="E7" s="79"/>
-      <c r="F7" s="79"/>
-      <c r="G7" s="80"/>
+      <c r="B7" s="99"/>
+      <c r="C7" s="99"/>
+      <c r="D7" s="99"/>
+      <c r="E7" s="99"/>
+      <c r="F7" s="99"/>
+      <c r="G7" s="100"/>
       <c r="H7" s="81"/>
-      <c r="I7" s="121"/>
-      <c r="J7" s="121"/>
-      <c r="K7" s="121"/>
-      <c r="L7" s="121"/>
-      <c r="M7" s="121"/>
-      <c r="N7" s="122"/>
-      <c r="O7" s="123" t="s">
+      <c r="I7" s="90"/>
+      <c r="J7" s="90"/>
+      <c r="K7" s="90"/>
+      <c r="L7" s="90"/>
+      <c r="M7" s="90"/>
+      <c r="N7" s="91"/>
+      <c r="O7" s="92" t="s">
         <v>2257</v>
       </c>
-      <c r="P7" s="124"/>
-      <c r="Q7" s="124"/>
-      <c r="R7" s="124"/>
-      <c r="S7" s="124"/>
-      <c r="T7" s="124"/>
-      <c r="U7" s="124"/>
-      <c r="V7" s="124"/>
-      <c r="W7" s="124"/>
-      <c r="X7" s="124"/>
-      <c r="Y7" s="124"/>
-      <c r="Z7" s="124"/>
-      <c r="AA7" s="124"/>
-      <c r="AB7" s="124"/>
-      <c r="AC7" s="124"/>
-      <c r="AD7" s="124"/>
-      <c r="AE7" s="124"/>
-      <c r="AF7" s="124"/>
-      <c r="AG7" s="124"/>
-      <c r="AH7" s="124"/>
-      <c r="AI7" s="124"/>
-      <c r="AJ7" s="124"/>
-      <c r="AK7" s="124"/>
-      <c r="AL7" s="124"/>
-      <c r="AM7" s="124"/>
-      <c r="AN7" s="124"/>
-      <c r="AO7" s="124"/>
-      <c r="AP7" s="125"/>
-      <c r="AQ7" s="126" t="s">
+      <c r="P7" s="93"/>
+      <c r="Q7" s="93"/>
+      <c r="R7" s="93"/>
+      <c r="S7" s="93"/>
+      <c r="T7" s="93"/>
+      <c r="U7" s="93"/>
+      <c r="V7" s="93"/>
+      <c r="W7" s="93"/>
+      <c r="X7" s="93"/>
+      <c r="Y7" s="93"/>
+      <c r="Z7" s="93"/>
+      <c r="AA7" s="93"/>
+      <c r="AB7" s="93"/>
+      <c r="AC7" s="93"/>
+      <c r="AD7" s="93"/>
+      <c r="AE7" s="93"/>
+      <c r="AF7" s="93"/>
+      <c r="AG7" s="93"/>
+      <c r="AH7" s="93"/>
+      <c r="AI7" s="93"/>
+      <c r="AJ7" s="93"/>
+      <c r="AK7" s="93"/>
+      <c r="AL7" s="93"/>
+      <c r="AM7" s="93"/>
+      <c r="AN7" s="93"/>
+      <c r="AO7" s="93"/>
+      <c r="AP7" s="94"/>
+      <c r="AQ7" s="95" t="s">
         <v>2258</v>
       </c>
-      <c r="AR7" s="127"/>
-      <c r="AS7" s="127"/>
-      <c r="AT7" s="127"/>
-      <c r="AU7" s="127"/>
-      <c r="AV7" s="127"/>
-      <c r="AW7" s="127"/>
-      <c r="AX7" s="127"/>
-      <c r="AY7" s="127"/>
-      <c r="AZ7" s="127"/>
-      <c r="BA7" s="127"/>
-      <c r="BB7" s="127"/>
-      <c r="BC7" s="127"/>
-      <c r="BD7" s="127"/>
-      <c r="BE7" s="128"/>
+      <c r="AR7" s="96"/>
+      <c r="AS7" s="96"/>
+      <c r="AT7" s="96"/>
+      <c r="AU7" s="96"/>
+      <c r="AV7" s="96"/>
+      <c r="AW7" s="96"/>
+      <c r="AX7" s="96"/>
+      <c r="AY7" s="96"/>
+      <c r="AZ7" s="96"/>
+      <c r="BA7" s="96"/>
+      <c r="BB7" s="96"/>
+      <c r="BC7" s="96"/>
+      <c r="BD7" s="96"/>
+      <c r="BE7" s="97"/>
     </row>
     <row r="8" spans="1:57" ht="15" customHeight="1">
-      <c r="A8" s="78"/>
-      <c r="B8" s="79"/>
-      <c r="C8" s="79"/>
-      <c r="D8" s="79"/>
-      <c r="E8" s="79"/>
-      <c r="F8" s="79"/>
-      <c r="G8" s="80"/>
+      <c r="A8" s="98"/>
+      <c r="B8" s="99"/>
+      <c r="C8" s="99"/>
+      <c r="D8" s="99"/>
+      <c r="E8" s="99"/>
+      <c r="F8" s="99"/>
+      <c r="G8" s="100"/>
       <c r="H8" s="81"/>
       <c r="I8" s="82"/>
       <c r="J8" s="82"/>
@@ -64768,57 +64771,57 @@
       <c r="M8" s="82"/>
       <c r="N8" s="83"/>
       <c r="O8" s="81"/>
-      <c r="P8" s="84"/>
-      <c r="Q8" s="84"/>
-      <c r="R8" s="84"/>
-      <c r="S8" s="84"/>
-      <c r="T8" s="84"/>
-      <c r="U8" s="84"/>
-      <c r="V8" s="84"/>
-      <c r="W8" s="84"/>
-      <c r="X8" s="84"/>
-      <c r="Y8" s="84"/>
-      <c r="Z8" s="84"/>
-      <c r="AA8" s="84"/>
-      <c r="AB8" s="84"/>
-      <c r="AC8" s="84"/>
-      <c r="AD8" s="84"/>
-      <c r="AE8" s="84"/>
-      <c r="AF8" s="84"/>
-      <c r="AG8" s="84"/>
-      <c r="AH8" s="84"/>
-      <c r="AI8" s="84"/>
-      <c r="AJ8" s="84"/>
-      <c r="AK8" s="84"/>
-      <c r="AL8" s="84"/>
-      <c r="AM8" s="84"/>
-      <c r="AN8" s="84"/>
-      <c r="AO8" s="84"/>
-      <c r="AP8" s="85"/>
-      <c r="AQ8" s="89"/>
-      <c r="AR8" s="84"/>
-      <c r="AS8" s="84"/>
-      <c r="AT8" s="84"/>
-      <c r="AU8" s="84"/>
-      <c r="AV8" s="84"/>
-      <c r="AW8" s="84"/>
-      <c r="AX8" s="84"/>
-      <c r="AY8" s="84"/>
-      <c r="AZ8" s="84"/>
-      <c r="BA8" s="84"/>
-      <c r="BB8" s="84"/>
-      <c r="BC8" s="84"/>
-      <c r="BD8" s="84"/>
-      <c r="BE8" s="90"/>
+      <c r="P8" s="79"/>
+      <c r="Q8" s="79"/>
+      <c r="R8" s="79"/>
+      <c r="S8" s="79"/>
+      <c r="T8" s="79"/>
+      <c r="U8" s="79"/>
+      <c r="V8" s="79"/>
+      <c r="W8" s="79"/>
+      <c r="X8" s="79"/>
+      <c r="Y8" s="79"/>
+      <c r="Z8" s="79"/>
+      <c r="AA8" s="79"/>
+      <c r="AB8" s="79"/>
+      <c r="AC8" s="79"/>
+      <c r="AD8" s="79"/>
+      <c r="AE8" s="79"/>
+      <c r="AF8" s="79"/>
+      <c r="AG8" s="79"/>
+      <c r="AH8" s="79"/>
+      <c r="AI8" s="79"/>
+      <c r="AJ8" s="79"/>
+      <c r="AK8" s="79"/>
+      <c r="AL8" s="79"/>
+      <c r="AM8" s="79"/>
+      <c r="AN8" s="79"/>
+      <c r="AO8" s="79"/>
+      <c r="AP8" s="87"/>
+      <c r="AQ8" s="78"/>
+      <c r="AR8" s="79"/>
+      <c r="AS8" s="79"/>
+      <c r="AT8" s="79"/>
+      <c r="AU8" s="79"/>
+      <c r="AV8" s="79"/>
+      <c r="AW8" s="79"/>
+      <c r="AX8" s="79"/>
+      <c r="AY8" s="79"/>
+      <c r="AZ8" s="79"/>
+      <c r="BA8" s="79"/>
+      <c r="BB8" s="79"/>
+      <c r="BC8" s="79"/>
+      <c r="BD8" s="79"/>
+      <c r="BE8" s="80"/>
     </row>
     <row r="9" spans="1:57" ht="15" customHeight="1">
-      <c r="A9" s="78"/>
-      <c r="B9" s="79"/>
-      <c r="C9" s="79"/>
-      <c r="D9" s="79"/>
-      <c r="E9" s="79"/>
-      <c r="F9" s="79"/>
-      <c r="G9" s="80"/>
+      <c r="A9" s="98"/>
+      <c r="B9" s="99"/>
+      <c r="C9" s="99"/>
+      <c r="D9" s="99"/>
+      <c r="E9" s="99"/>
+      <c r="F9" s="99"/>
+      <c r="G9" s="100"/>
       <c r="H9" s="81"/>
       <c r="I9" s="82"/>
       <c r="J9" s="82"/>
@@ -64827,57 +64830,57 @@
       <c r="M9" s="82"/>
       <c r="N9" s="83"/>
       <c r="O9" s="81"/>
-      <c r="P9" s="84"/>
-      <c r="Q9" s="84"/>
-      <c r="R9" s="84"/>
-      <c r="S9" s="84"/>
-      <c r="T9" s="84"/>
-      <c r="U9" s="84"/>
-      <c r="V9" s="84"/>
-      <c r="W9" s="84"/>
-      <c r="X9" s="84"/>
-      <c r="Y9" s="84"/>
-      <c r="Z9" s="84"/>
-      <c r="AA9" s="84"/>
-      <c r="AB9" s="84"/>
-      <c r="AC9" s="84"/>
-      <c r="AD9" s="84"/>
-      <c r="AE9" s="84"/>
-      <c r="AF9" s="84"/>
-      <c r="AG9" s="84"/>
-      <c r="AH9" s="84"/>
-      <c r="AI9" s="84"/>
-      <c r="AJ9" s="84"/>
-      <c r="AK9" s="84"/>
-      <c r="AL9" s="84"/>
-      <c r="AM9" s="84"/>
-      <c r="AN9" s="84"/>
-      <c r="AO9" s="84"/>
-      <c r="AP9" s="85"/>
-      <c r="AQ9" s="89"/>
-      <c r="AR9" s="84"/>
-      <c r="AS9" s="84"/>
-      <c r="AT9" s="84"/>
-      <c r="AU9" s="84"/>
-      <c r="AV9" s="84"/>
-      <c r="AW9" s="84"/>
-      <c r="AX9" s="84"/>
-      <c r="AY9" s="84"/>
-      <c r="AZ9" s="84"/>
-      <c r="BA9" s="84"/>
-      <c r="BB9" s="84"/>
-      <c r="BC9" s="84"/>
-      <c r="BD9" s="84"/>
-      <c r="BE9" s="90"/>
+      <c r="P9" s="79"/>
+      <c r="Q9" s="79"/>
+      <c r="R9" s="79"/>
+      <c r="S9" s="79"/>
+      <c r="T9" s="79"/>
+      <c r="U9" s="79"/>
+      <c r="V9" s="79"/>
+      <c r="W9" s="79"/>
+      <c r="X9" s="79"/>
+      <c r="Y9" s="79"/>
+      <c r="Z9" s="79"/>
+      <c r="AA9" s="79"/>
+      <c r="AB9" s="79"/>
+      <c r="AC9" s="79"/>
+      <c r="AD9" s="79"/>
+      <c r="AE9" s="79"/>
+      <c r="AF9" s="79"/>
+      <c r="AG9" s="79"/>
+      <c r="AH9" s="79"/>
+      <c r="AI9" s="79"/>
+      <c r="AJ9" s="79"/>
+      <c r="AK9" s="79"/>
+      <c r="AL9" s="79"/>
+      <c r="AM9" s="79"/>
+      <c r="AN9" s="79"/>
+      <c r="AO9" s="79"/>
+      <c r="AP9" s="87"/>
+      <c r="AQ9" s="78"/>
+      <c r="AR9" s="79"/>
+      <c r="AS9" s="79"/>
+      <c r="AT9" s="79"/>
+      <c r="AU9" s="79"/>
+      <c r="AV9" s="79"/>
+      <c r="AW9" s="79"/>
+      <c r="AX9" s="79"/>
+      <c r="AY9" s="79"/>
+      <c r="AZ9" s="79"/>
+      <c r="BA9" s="79"/>
+      <c r="BB9" s="79"/>
+      <c r="BC9" s="79"/>
+      <c r="BD9" s="79"/>
+      <c r="BE9" s="80"/>
     </row>
     <row r="10" spans="1:57" ht="15" customHeight="1">
-      <c r="A10" s="78"/>
-      <c r="B10" s="79"/>
-      <c r="C10" s="79"/>
-      <c r="D10" s="79"/>
-      <c r="E10" s="79"/>
-      <c r="F10" s="79"/>
-      <c r="G10" s="80"/>
+      <c r="A10" s="98"/>
+      <c r="B10" s="99"/>
+      <c r="C10" s="99"/>
+      <c r="D10" s="99"/>
+      <c r="E10" s="99"/>
+      <c r="F10" s="99"/>
+      <c r="G10" s="100"/>
       <c r="H10" s="81"/>
       <c r="I10" s="82"/>
       <c r="J10" s="82"/>
@@ -64886,57 +64889,57 @@
       <c r="M10" s="82"/>
       <c r="N10" s="83"/>
       <c r="O10" s="81"/>
-      <c r="P10" s="84"/>
-      <c r="Q10" s="84"/>
-      <c r="R10" s="84"/>
-      <c r="S10" s="84"/>
-      <c r="T10" s="84"/>
-      <c r="U10" s="84"/>
-      <c r="V10" s="84"/>
-      <c r="W10" s="84"/>
-      <c r="X10" s="84"/>
-      <c r="Y10" s="84"/>
-      <c r="Z10" s="84"/>
-      <c r="AA10" s="84"/>
-      <c r="AB10" s="84"/>
-      <c r="AC10" s="84"/>
-      <c r="AD10" s="84"/>
-      <c r="AE10" s="84"/>
-      <c r="AF10" s="84"/>
-      <c r="AG10" s="84"/>
-      <c r="AH10" s="84"/>
-      <c r="AI10" s="84"/>
-      <c r="AJ10" s="84"/>
-      <c r="AK10" s="84"/>
-      <c r="AL10" s="84"/>
-      <c r="AM10" s="84"/>
-      <c r="AN10" s="84"/>
-      <c r="AO10" s="84"/>
-      <c r="AP10" s="85"/>
-      <c r="AQ10" s="89"/>
-      <c r="AR10" s="84"/>
-      <c r="AS10" s="84"/>
-      <c r="AT10" s="84"/>
-      <c r="AU10" s="84"/>
-      <c r="AV10" s="84"/>
-      <c r="AW10" s="84"/>
-      <c r="AX10" s="84"/>
-      <c r="AY10" s="84"/>
-      <c r="AZ10" s="84"/>
-      <c r="BA10" s="84"/>
-      <c r="BB10" s="84"/>
-      <c r="BC10" s="84"/>
-      <c r="BD10" s="84"/>
-      <c r="BE10" s="90"/>
+      <c r="P10" s="79"/>
+      <c r="Q10" s="79"/>
+      <c r="R10" s="79"/>
+      <c r="S10" s="79"/>
+      <c r="T10" s="79"/>
+      <c r="U10" s="79"/>
+      <c r="V10" s="79"/>
+      <c r="W10" s="79"/>
+      <c r="X10" s="79"/>
+      <c r="Y10" s="79"/>
+      <c r="Z10" s="79"/>
+      <c r="AA10" s="79"/>
+      <c r="AB10" s="79"/>
+      <c r="AC10" s="79"/>
+      <c r="AD10" s="79"/>
+      <c r="AE10" s="79"/>
+      <c r="AF10" s="79"/>
+      <c r="AG10" s="79"/>
+      <c r="AH10" s="79"/>
+      <c r="AI10" s="79"/>
+      <c r="AJ10" s="79"/>
+      <c r="AK10" s="79"/>
+      <c r="AL10" s="79"/>
+      <c r="AM10" s="79"/>
+      <c r="AN10" s="79"/>
+      <c r="AO10" s="79"/>
+      <c r="AP10" s="87"/>
+      <c r="AQ10" s="78"/>
+      <c r="AR10" s="79"/>
+      <c r="AS10" s="79"/>
+      <c r="AT10" s="79"/>
+      <c r="AU10" s="79"/>
+      <c r="AV10" s="79"/>
+      <c r="AW10" s="79"/>
+      <c r="AX10" s="79"/>
+      <c r="AY10" s="79"/>
+      <c r="AZ10" s="79"/>
+      <c r="BA10" s="79"/>
+      <c r="BB10" s="79"/>
+      <c r="BC10" s="79"/>
+      <c r="BD10" s="79"/>
+      <c r="BE10" s="80"/>
     </row>
     <row r="11" spans="1:57" ht="15" customHeight="1">
-      <c r="A11" s="78"/>
-      <c r="B11" s="79"/>
-      <c r="C11" s="79"/>
-      <c r="D11" s="79"/>
-      <c r="E11" s="79"/>
-      <c r="F11" s="79"/>
-      <c r="G11" s="80"/>
+      <c r="A11" s="98"/>
+      <c r="B11" s="99"/>
+      <c r="C11" s="99"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="99"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="100"/>
       <c r="H11" s="81"/>
       <c r="I11" s="82"/>
       <c r="J11" s="82"/>
@@ -64945,57 +64948,57 @@
       <c r="M11" s="82"/>
       <c r="N11" s="83"/>
       <c r="O11" s="81"/>
-      <c r="P11" s="84"/>
-      <c r="Q11" s="84"/>
-      <c r="R11" s="84"/>
-      <c r="S11" s="84"/>
-      <c r="T11" s="84"/>
-      <c r="U11" s="84"/>
-      <c r="V11" s="84"/>
-      <c r="W11" s="84"/>
-      <c r="X11" s="84"/>
-      <c r="Y11" s="84"/>
-      <c r="Z11" s="84"/>
-      <c r="AA11" s="84"/>
-      <c r="AB11" s="84"/>
-      <c r="AC11" s="84"/>
-      <c r="AD11" s="84"/>
-      <c r="AE11" s="84"/>
-      <c r="AF11" s="84"/>
-      <c r="AG11" s="84"/>
-      <c r="AH11" s="84"/>
-      <c r="AI11" s="84"/>
-      <c r="AJ11" s="84"/>
-      <c r="AK11" s="84"/>
-      <c r="AL11" s="84"/>
-      <c r="AM11" s="84"/>
-      <c r="AN11" s="84"/>
-      <c r="AO11" s="84"/>
-      <c r="AP11" s="85"/>
-      <c r="AQ11" s="89"/>
-      <c r="AR11" s="84"/>
-      <c r="AS11" s="84"/>
-      <c r="AT11" s="84"/>
-      <c r="AU11" s="84"/>
-      <c r="AV11" s="84"/>
-      <c r="AW11" s="84"/>
-      <c r="AX11" s="84"/>
-      <c r="AY11" s="84"/>
-      <c r="AZ11" s="84"/>
-      <c r="BA11" s="84"/>
-      <c r="BB11" s="84"/>
-      <c r="BC11" s="84"/>
-      <c r="BD11" s="84"/>
-      <c r="BE11" s="90"/>
+      <c r="P11" s="79"/>
+      <c r="Q11" s="79"/>
+      <c r="R11" s="79"/>
+      <c r="S11" s="79"/>
+      <c r="T11" s="79"/>
+      <c r="U11" s="79"/>
+      <c r="V11" s="79"/>
+      <c r="W11" s="79"/>
+      <c r="X11" s="79"/>
+      <c r="Y11" s="79"/>
+      <c r="Z11" s="79"/>
+      <c r="AA11" s="79"/>
+      <c r="AB11" s="79"/>
+      <c r="AC11" s="79"/>
+      <c r="AD11" s="79"/>
+      <c r="AE11" s="79"/>
+      <c r="AF11" s="79"/>
+      <c r="AG11" s="79"/>
+      <c r="AH11" s="79"/>
+      <c r="AI11" s="79"/>
+      <c r="AJ11" s="79"/>
+      <c r="AK11" s="79"/>
+      <c r="AL11" s="79"/>
+      <c r="AM11" s="79"/>
+      <c r="AN11" s="79"/>
+      <c r="AO11" s="79"/>
+      <c r="AP11" s="87"/>
+      <c r="AQ11" s="78"/>
+      <c r="AR11" s="79"/>
+      <c r="AS11" s="79"/>
+      <c r="AT11" s="79"/>
+      <c r="AU11" s="79"/>
+      <c r="AV11" s="79"/>
+      <c r="AW11" s="79"/>
+      <c r="AX11" s="79"/>
+      <c r="AY11" s="79"/>
+      <c r="AZ11" s="79"/>
+      <c r="BA11" s="79"/>
+      <c r="BB11" s="79"/>
+      <c r="BC11" s="79"/>
+      <c r="BD11" s="79"/>
+      <c r="BE11" s="80"/>
     </row>
     <row r="12" spans="1:57" ht="15" customHeight="1">
-      <c r="A12" s="78"/>
-      <c r="B12" s="79"/>
-      <c r="C12" s="79"/>
-      <c r="D12" s="79"/>
-      <c r="E12" s="79"/>
-      <c r="F12" s="79"/>
-      <c r="G12" s="80"/>
+      <c r="A12" s="98"/>
+      <c r="B12" s="99"/>
+      <c r="C12" s="99"/>
+      <c r="D12" s="99"/>
+      <c r="E12" s="99"/>
+      <c r="F12" s="99"/>
+      <c r="G12" s="100"/>
       <c r="H12" s="81"/>
       <c r="I12" s="82"/>
       <c r="J12" s="82"/>
@@ -65004,57 +65007,57 @@
       <c r="M12" s="82"/>
       <c r="N12" s="83"/>
       <c r="O12" s="81"/>
-      <c r="P12" s="84"/>
-      <c r="Q12" s="84"/>
-      <c r="R12" s="84"/>
-      <c r="S12" s="84"/>
-      <c r="T12" s="84"/>
-      <c r="U12" s="84"/>
-      <c r="V12" s="84"/>
-      <c r="W12" s="84"/>
-      <c r="X12" s="84"/>
-      <c r="Y12" s="84"/>
-      <c r="Z12" s="84"/>
-      <c r="AA12" s="84"/>
-      <c r="AB12" s="84"/>
-      <c r="AC12" s="84"/>
-      <c r="AD12" s="84"/>
-      <c r="AE12" s="84"/>
-      <c r="AF12" s="84"/>
-      <c r="AG12" s="84"/>
-      <c r="AH12" s="84"/>
-      <c r="AI12" s="84"/>
-      <c r="AJ12" s="84"/>
-      <c r="AK12" s="84"/>
-      <c r="AL12" s="84"/>
-      <c r="AM12" s="84"/>
-      <c r="AN12" s="84"/>
-      <c r="AO12" s="84"/>
-      <c r="AP12" s="85"/>
-      <c r="AQ12" s="89"/>
-      <c r="AR12" s="84"/>
-      <c r="AS12" s="84"/>
-      <c r="AT12" s="84"/>
-      <c r="AU12" s="84"/>
-      <c r="AV12" s="84"/>
-      <c r="AW12" s="84"/>
-      <c r="AX12" s="84"/>
-      <c r="AY12" s="84"/>
-      <c r="AZ12" s="84"/>
-      <c r="BA12" s="84"/>
-      <c r="BB12" s="84"/>
-      <c r="BC12" s="84"/>
-      <c r="BD12" s="84"/>
-      <c r="BE12" s="90"/>
+      <c r="P12" s="79"/>
+      <c r="Q12" s="79"/>
+      <c r="R12" s="79"/>
+      <c r="S12" s="79"/>
+      <c r="T12" s="79"/>
+      <c r="U12" s="79"/>
+      <c r="V12" s="79"/>
+      <c r="W12" s="79"/>
+      <c r="X12" s="79"/>
+      <c r="Y12" s="79"/>
+      <c r="Z12" s="79"/>
+      <c r="AA12" s="79"/>
+      <c r="AB12" s="79"/>
+      <c r="AC12" s="79"/>
+      <c r="AD12" s="79"/>
+      <c r="AE12" s="79"/>
+      <c r="AF12" s="79"/>
+      <c r="AG12" s="79"/>
+      <c r="AH12" s="79"/>
+      <c r="AI12" s="79"/>
+      <c r="AJ12" s="79"/>
+      <c r="AK12" s="79"/>
+      <c r="AL12" s="79"/>
+      <c r="AM12" s="79"/>
+      <c r="AN12" s="79"/>
+      <c r="AO12" s="79"/>
+      <c r="AP12" s="87"/>
+      <c r="AQ12" s="78"/>
+      <c r="AR12" s="79"/>
+      <c r="AS12" s="79"/>
+      <c r="AT12" s="79"/>
+      <c r="AU12" s="79"/>
+      <c r="AV12" s="79"/>
+      <c r="AW12" s="79"/>
+      <c r="AX12" s="79"/>
+      <c r="AY12" s="79"/>
+      <c r="AZ12" s="79"/>
+      <c r="BA12" s="79"/>
+      <c r="BB12" s="79"/>
+      <c r="BC12" s="79"/>
+      <c r="BD12" s="79"/>
+      <c r="BE12" s="80"/>
     </row>
     <row r="13" spans="1:57" ht="15" customHeight="1">
-      <c r="A13" s="78"/>
-      <c r="B13" s="79"/>
-      <c r="C13" s="79"/>
-      <c r="D13" s="79"/>
-      <c r="E13" s="79"/>
-      <c r="F13" s="79"/>
-      <c r="G13" s="80"/>
+      <c r="A13" s="98"/>
+      <c r="B13" s="99"/>
+      <c r="C13" s="99"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="99"/>
+      <c r="F13" s="99"/>
+      <c r="G13" s="100"/>
       <c r="H13" s="81"/>
       <c r="I13" s="82"/>
       <c r="J13" s="82"/>
@@ -65063,57 +65066,57 @@
       <c r="M13" s="82"/>
       <c r="N13" s="83"/>
       <c r="O13" s="81"/>
-      <c r="P13" s="84"/>
-      <c r="Q13" s="84"/>
-      <c r="R13" s="84"/>
-      <c r="S13" s="84"/>
-      <c r="T13" s="84"/>
-      <c r="U13" s="84"/>
-      <c r="V13" s="84"/>
-      <c r="W13" s="84"/>
-      <c r="X13" s="84"/>
-      <c r="Y13" s="84"/>
-      <c r="Z13" s="84"/>
-      <c r="AA13" s="84"/>
-      <c r="AB13" s="84"/>
-      <c r="AC13" s="84"/>
-      <c r="AD13" s="84"/>
-      <c r="AE13" s="84"/>
-      <c r="AF13" s="84"/>
-      <c r="AG13" s="84"/>
-      <c r="AH13" s="84"/>
-      <c r="AI13" s="84"/>
-      <c r="AJ13" s="84"/>
-      <c r="AK13" s="84"/>
-      <c r="AL13" s="84"/>
-      <c r="AM13" s="84"/>
-      <c r="AN13" s="84"/>
-      <c r="AO13" s="84"/>
-      <c r="AP13" s="85"/>
-      <c r="AQ13" s="89"/>
-      <c r="AR13" s="84"/>
-      <c r="AS13" s="84"/>
-      <c r="AT13" s="84"/>
-      <c r="AU13" s="84"/>
-      <c r="AV13" s="84"/>
-      <c r="AW13" s="84"/>
-      <c r="AX13" s="84"/>
-      <c r="AY13" s="84"/>
-      <c r="AZ13" s="84"/>
-      <c r="BA13" s="84"/>
-      <c r="BB13" s="84"/>
-      <c r="BC13" s="84"/>
-      <c r="BD13" s="84"/>
-      <c r="BE13" s="90"/>
+      <c r="P13" s="79"/>
+      <c r="Q13" s="79"/>
+      <c r="R13" s="79"/>
+      <c r="S13" s="79"/>
+      <c r="T13" s="79"/>
+      <c r="U13" s="79"/>
+      <c r="V13" s="79"/>
+      <c r="W13" s="79"/>
+      <c r="X13" s="79"/>
+      <c r="Y13" s="79"/>
+      <c r="Z13" s="79"/>
+      <c r="AA13" s="79"/>
+      <c r="AB13" s="79"/>
+      <c r="AC13" s="79"/>
+      <c r="AD13" s="79"/>
+      <c r="AE13" s="79"/>
+      <c r="AF13" s="79"/>
+      <c r="AG13" s="79"/>
+      <c r="AH13" s="79"/>
+      <c r="AI13" s="79"/>
+      <c r="AJ13" s="79"/>
+      <c r="AK13" s="79"/>
+      <c r="AL13" s="79"/>
+      <c r="AM13" s="79"/>
+      <c r="AN13" s="79"/>
+      <c r="AO13" s="79"/>
+      <c r="AP13" s="87"/>
+      <c r="AQ13" s="78"/>
+      <c r="AR13" s="79"/>
+      <c r="AS13" s="79"/>
+      <c r="AT13" s="79"/>
+      <c r="AU13" s="79"/>
+      <c r="AV13" s="79"/>
+      <c r="AW13" s="79"/>
+      <c r="AX13" s="79"/>
+      <c r="AY13" s="79"/>
+      <c r="AZ13" s="79"/>
+      <c r="BA13" s="79"/>
+      <c r="BB13" s="79"/>
+      <c r="BC13" s="79"/>
+      <c r="BD13" s="79"/>
+      <c r="BE13" s="80"/>
     </row>
     <row r="14" spans="1:57" ht="15" customHeight="1">
-      <c r="A14" s="78"/>
-      <c r="B14" s="79"/>
-      <c r="C14" s="79"/>
-      <c r="D14" s="79"/>
-      <c r="E14" s="79"/>
-      <c r="F14" s="79"/>
-      <c r="G14" s="80"/>
+      <c r="A14" s="98"/>
+      <c r="B14" s="99"/>
+      <c r="C14" s="99"/>
+      <c r="D14" s="99"/>
+      <c r="E14" s="99"/>
+      <c r="F14" s="99"/>
+      <c r="G14" s="100"/>
       <c r="H14" s="81"/>
       <c r="I14" s="82"/>
       <c r="J14" s="82"/>
@@ -65122,57 +65125,57 @@
       <c r="M14" s="82"/>
       <c r="N14" s="83"/>
       <c r="O14" s="81"/>
-      <c r="P14" s="84"/>
-      <c r="Q14" s="84"/>
-      <c r="R14" s="84"/>
-      <c r="S14" s="84"/>
-      <c r="T14" s="84"/>
-      <c r="U14" s="84"/>
-      <c r="V14" s="84"/>
-      <c r="W14" s="84"/>
-      <c r="X14" s="84"/>
-      <c r="Y14" s="84"/>
-      <c r="Z14" s="84"/>
-      <c r="AA14" s="84"/>
-      <c r="AB14" s="84"/>
-      <c r="AC14" s="84"/>
-      <c r="AD14" s="84"/>
-      <c r="AE14" s="84"/>
-      <c r="AF14" s="84"/>
-      <c r="AG14" s="84"/>
-      <c r="AH14" s="84"/>
-      <c r="AI14" s="84"/>
-      <c r="AJ14" s="84"/>
-      <c r="AK14" s="84"/>
-      <c r="AL14" s="84"/>
-      <c r="AM14" s="84"/>
-      <c r="AN14" s="84"/>
-      <c r="AO14" s="84"/>
-      <c r="AP14" s="85"/>
-      <c r="AQ14" s="89"/>
-      <c r="AR14" s="84"/>
-      <c r="AS14" s="84"/>
-      <c r="AT14" s="84"/>
-      <c r="AU14" s="84"/>
-      <c r="AV14" s="84"/>
-      <c r="AW14" s="84"/>
-      <c r="AX14" s="84"/>
-      <c r="AY14" s="84"/>
-      <c r="AZ14" s="84"/>
-      <c r="BA14" s="84"/>
-      <c r="BB14" s="84"/>
-      <c r="BC14" s="84"/>
-      <c r="BD14" s="84"/>
-      <c r="BE14" s="90"/>
+      <c r="P14" s="79"/>
+      <c r="Q14" s="79"/>
+      <c r="R14" s="79"/>
+      <c r="S14" s="79"/>
+      <c r="T14" s="79"/>
+      <c r="U14" s="79"/>
+      <c r="V14" s="79"/>
+      <c r="W14" s="79"/>
+      <c r="X14" s="79"/>
+      <c r="Y14" s="79"/>
+      <c r="Z14" s="79"/>
+      <c r="AA14" s="79"/>
+      <c r="AB14" s="79"/>
+      <c r="AC14" s="79"/>
+      <c r="AD14" s="79"/>
+      <c r="AE14" s="79"/>
+      <c r="AF14" s="79"/>
+      <c r="AG14" s="79"/>
+      <c r="AH14" s="79"/>
+      <c r="AI14" s="79"/>
+      <c r="AJ14" s="79"/>
+      <c r="AK14" s="79"/>
+      <c r="AL14" s="79"/>
+      <c r="AM14" s="79"/>
+      <c r="AN14" s="79"/>
+      <c r="AO14" s="79"/>
+      <c r="AP14" s="87"/>
+      <c r="AQ14" s="78"/>
+      <c r="AR14" s="79"/>
+      <c r="AS14" s="79"/>
+      <c r="AT14" s="79"/>
+      <c r="AU14" s="79"/>
+      <c r="AV14" s="79"/>
+      <c r="AW14" s="79"/>
+      <c r="AX14" s="79"/>
+      <c r="AY14" s="79"/>
+      <c r="AZ14" s="79"/>
+      <c r="BA14" s="79"/>
+      <c r="BB14" s="79"/>
+      <c r="BC14" s="79"/>
+      <c r="BD14" s="79"/>
+      <c r="BE14" s="80"/>
     </row>
     <row r="15" spans="1:57" ht="15" customHeight="1">
-      <c r="A15" s="78"/>
-      <c r="B15" s="79"/>
-      <c r="C15" s="79"/>
-      <c r="D15" s="79"/>
-      <c r="E15" s="79"/>
-      <c r="F15" s="79"/>
-      <c r="G15" s="80"/>
+      <c r="A15" s="98"/>
+      <c r="B15" s="99"/>
+      <c r="C15" s="99"/>
+      <c r="D15" s="99"/>
+      <c r="E15" s="99"/>
+      <c r="F15" s="99"/>
+      <c r="G15" s="100"/>
       <c r="H15" s="81"/>
       <c r="I15" s="82"/>
       <c r="J15" s="82"/>
@@ -65181,57 +65184,57 @@
       <c r="M15" s="82"/>
       <c r="N15" s="83"/>
       <c r="O15" s="81"/>
-      <c r="P15" s="84"/>
-      <c r="Q15" s="84"/>
-      <c r="R15" s="84"/>
-      <c r="S15" s="84"/>
-      <c r="T15" s="84"/>
-      <c r="U15" s="84"/>
-      <c r="V15" s="84"/>
-      <c r="W15" s="84"/>
-      <c r="X15" s="84"/>
-      <c r="Y15" s="84"/>
-      <c r="Z15" s="84"/>
-      <c r="AA15" s="84"/>
-      <c r="AB15" s="84"/>
-      <c r="AC15" s="84"/>
-      <c r="AD15" s="84"/>
-      <c r="AE15" s="84"/>
-      <c r="AF15" s="84"/>
-      <c r="AG15" s="84"/>
-      <c r="AH15" s="84"/>
-      <c r="AI15" s="84"/>
-      <c r="AJ15" s="84"/>
-      <c r="AK15" s="84"/>
-      <c r="AL15" s="84"/>
-      <c r="AM15" s="84"/>
-      <c r="AN15" s="84"/>
-      <c r="AO15" s="84"/>
-      <c r="AP15" s="85"/>
-      <c r="AQ15" s="89"/>
-      <c r="AR15" s="84"/>
-      <c r="AS15" s="84"/>
-      <c r="AT15" s="84"/>
-      <c r="AU15" s="84"/>
-      <c r="AV15" s="84"/>
-      <c r="AW15" s="84"/>
-      <c r="AX15" s="84"/>
-      <c r="AY15" s="84"/>
-      <c r="AZ15" s="84"/>
-      <c r="BA15" s="84"/>
-      <c r="BB15" s="84"/>
-      <c r="BC15" s="84"/>
-      <c r="BD15" s="84"/>
-      <c r="BE15" s="90"/>
+      <c r="P15" s="79"/>
+      <c r="Q15" s="79"/>
+      <c r="R15" s="79"/>
+      <c r="S15" s="79"/>
+      <c r="T15" s="79"/>
+      <c r="U15" s="79"/>
+      <c r="V15" s="79"/>
+      <c r="W15" s="79"/>
+      <c r="X15" s="79"/>
+      <c r="Y15" s="79"/>
+      <c r="Z15" s="79"/>
+      <c r="AA15" s="79"/>
+      <c r="AB15" s="79"/>
+      <c r="AC15" s="79"/>
+      <c r="AD15" s="79"/>
+      <c r="AE15" s="79"/>
+      <c r="AF15" s="79"/>
+      <c r="AG15" s="79"/>
+      <c r="AH15" s="79"/>
+      <c r="AI15" s="79"/>
+      <c r="AJ15" s="79"/>
+      <c r="AK15" s="79"/>
+      <c r="AL15" s="79"/>
+      <c r="AM15" s="79"/>
+      <c r="AN15" s="79"/>
+      <c r="AO15" s="79"/>
+      <c r="AP15" s="87"/>
+      <c r="AQ15" s="78"/>
+      <c r="AR15" s="79"/>
+      <c r="AS15" s="79"/>
+      <c r="AT15" s="79"/>
+      <c r="AU15" s="79"/>
+      <c r="AV15" s="79"/>
+      <c r="AW15" s="79"/>
+      <c r="AX15" s="79"/>
+      <c r="AY15" s="79"/>
+      <c r="AZ15" s="79"/>
+      <c r="BA15" s="79"/>
+      <c r="BB15" s="79"/>
+      <c r="BC15" s="79"/>
+      <c r="BD15" s="79"/>
+      <c r="BE15" s="80"/>
     </row>
     <row r="16" spans="1:57" ht="15" customHeight="1">
-      <c r="A16" s="78"/>
-      <c r="B16" s="79"/>
-      <c r="C16" s="79"/>
-      <c r="D16" s="79"/>
-      <c r="E16" s="79"/>
-      <c r="F16" s="79"/>
-      <c r="G16" s="80"/>
+      <c r="A16" s="98"/>
+      <c r="B16" s="99"/>
+      <c r="C16" s="99"/>
+      <c r="D16" s="99"/>
+      <c r="E16" s="99"/>
+      <c r="F16" s="99"/>
+      <c r="G16" s="100"/>
       <c r="H16" s="81"/>
       <c r="I16" s="82"/>
       <c r="J16" s="82"/>
@@ -65240,57 +65243,57 @@
       <c r="M16" s="82"/>
       <c r="N16" s="83"/>
       <c r="O16" s="81"/>
-      <c r="P16" s="84"/>
-      <c r="Q16" s="84"/>
-      <c r="R16" s="84"/>
-      <c r="S16" s="84"/>
-      <c r="T16" s="84"/>
-      <c r="U16" s="84"/>
-      <c r="V16" s="84"/>
-      <c r="W16" s="84"/>
-      <c r="X16" s="84"/>
-      <c r="Y16" s="84"/>
-      <c r="Z16" s="84"/>
-      <c r="AA16" s="84"/>
-      <c r="AB16" s="84"/>
-      <c r="AC16" s="84"/>
-      <c r="AD16" s="84"/>
-      <c r="AE16" s="84"/>
-      <c r="AF16" s="84"/>
-      <c r="AG16" s="84"/>
-      <c r="AH16" s="84"/>
-      <c r="AI16" s="84"/>
-      <c r="AJ16" s="84"/>
-      <c r="AK16" s="84"/>
-      <c r="AL16" s="84"/>
-      <c r="AM16" s="84"/>
-      <c r="AN16" s="84"/>
-      <c r="AO16" s="84"/>
-      <c r="AP16" s="85"/>
-      <c r="AQ16" s="89"/>
-      <c r="AR16" s="84"/>
-      <c r="AS16" s="84"/>
-      <c r="AT16" s="84"/>
-      <c r="AU16" s="84"/>
-      <c r="AV16" s="84"/>
-      <c r="AW16" s="84"/>
-      <c r="AX16" s="84"/>
-      <c r="AY16" s="84"/>
-      <c r="AZ16" s="84"/>
-      <c r="BA16" s="84"/>
-      <c r="BB16" s="84"/>
-      <c r="BC16" s="84"/>
-      <c r="BD16" s="84"/>
-      <c r="BE16" s="90"/>
+      <c r="P16" s="79"/>
+      <c r="Q16" s="79"/>
+      <c r="R16" s="79"/>
+      <c r="S16" s="79"/>
+      <c r="T16" s="79"/>
+      <c r="U16" s="79"/>
+      <c r="V16" s="79"/>
+      <c r="W16" s="79"/>
+      <c r="X16" s="79"/>
+      <c r="Y16" s="79"/>
+      <c r="Z16" s="79"/>
+      <c r="AA16" s="79"/>
+      <c r="AB16" s="79"/>
+      <c r="AC16" s="79"/>
+      <c r="AD16" s="79"/>
+      <c r="AE16" s="79"/>
+      <c r="AF16" s="79"/>
+      <c r="AG16" s="79"/>
+      <c r="AH16" s="79"/>
+      <c r="AI16" s="79"/>
+      <c r="AJ16" s="79"/>
+      <c r="AK16" s="79"/>
+      <c r="AL16" s="79"/>
+      <c r="AM16" s="79"/>
+      <c r="AN16" s="79"/>
+      <c r="AO16" s="79"/>
+      <c r="AP16" s="87"/>
+      <c r="AQ16" s="78"/>
+      <c r="AR16" s="79"/>
+      <c r="AS16" s="79"/>
+      <c r="AT16" s="79"/>
+      <c r="AU16" s="79"/>
+      <c r="AV16" s="79"/>
+      <c r="AW16" s="79"/>
+      <c r="AX16" s="79"/>
+      <c r="AY16" s="79"/>
+      <c r="AZ16" s="79"/>
+      <c r="BA16" s="79"/>
+      <c r="BB16" s="79"/>
+      <c r="BC16" s="79"/>
+      <c r="BD16" s="79"/>
+      <c r="BE16" s="80"/>
     </row>
     <row r="17" spans="1:57" ht="15" customHeight="1">
-      <c r="A17" s="78"/>
-      <c r="B17" s="79"/>
-      <c r="C17" s="79"/>
-      <c r="D17" s="79"/>
-      <c r="E17" s="79"/>
-      <c r="F17" s="79"/>
-      <c r="G17" s="80"/>
+      <c r="A17" s="98"/>
+      <c r="B17" s="99"/>
+      <c r="C17" s="99"/>
+      <c r="D17" s="99"/>
+      <c r="E17" s="99"/>
+      <c r="F17" s="99"/>
+      <c r="G17" s="100"/>
       <c r="H17" s="81"/>
       <c r="I17" s="82"/>
       <c r="J17" s="82"/>
@@ -65299,57 +65302,57 @@
       <c r="M17" s="82"/>
       <c r="N17" s="83"/>
       <c r="O17" s="81"/>
-      <c r="P17" s="84"/>
-      <c r="Q17" s="84"/>
-      <c r="R17" s="84"/>
-      <c r="S17" s="84"/>
-      <c r="T17" s="84"/>
-      <c r="U17" s="84"/>
-      <c r="V17" s="84"/>
-      <c r="W17" s="84"/>
-      <c r="X17" s="84"/>
-      <c r="Y17" s="84"/>
-      <c r="Z17" s="84"/>
-      <c r="AA17" s="84"/>
-      <c r="AB17" s="84"/>
-      <c r="AC17" s="84"/>
-      <c r="AD17" s="84"/>
-      <c r="AE17" s="84"/>
-      <c r="AF17" s="84"/>
-      <c r="AG17" s="84"/>
-      <c r="AH17" s="84"/>
-      <c r="AI17" s="84"/>
-      <c r="AJ17" s="84"/>
-      <c r="AK17" s="84"/>
-      <c r="AL17" s="84"/>
-      <c r="AM17" s="84"/>
-      <c r="AN17" s="84"/>
-      <c r="AO17" s="84"/>
-      <c r="AP17" s="85"/>
-      <c r="AQ17" s="89"/>
-      <c r="AR17" s="84"/>
-      <c r="AS17" s="84"/>
-      <c r="AT17" s="84"/>
-      <c r="AU17" s="84"/>
-      <c r="AV17" s="84"/>
-      <c r="AW17" s="84"/>
-      <c r="AX17" s="84"/>
-      <c r="AY17" s="84"/>
-      <c r="AZ17" s="84"/>
-      <c r="BA17" s="84"/>
-      <c r="BB17" s="84"/>
-      <c r="BC17" s="84"/>
-      <c r="BD17" s="84"/>
-      <c r="BE17" s="90"/>
+      <c r="P17" s="79"/>
+      <c r="Q17" s="79"/>
+      <c r="R17" s="79"/>
+      <c r="S17" s="79"/>
+      <c r="T17" s="79"/>
+      <c r="U17" s="79"/>
+      <c r="V17" s="79"/>
+      <c r="W17" s="79"/>
+      <c r="X17" s="79"/>
+      <c r="Y17" s="79"/>
+      <c r="Z17" s="79"/>
+      <c r="AA17" s="79"/>
+      <c r="AB17" s="79"/>
+      <c r="AC17" s="79"/>
+      <c r="AD17" s="79"/>
+      <c r="AE17" s="79"/>
+      <c r="AF17" s="79"/>
+      <c r="AG17" s="79"/>
+      <c r="AH17" s="79"/>
+      <c r="AI17" s="79"/>
+      <c r="AJ17" s="79"/>
+      <c r="AK17" s="79"/>
+      <c r="AL17" s="79"/>
+      <c r="AM17" s="79"/>
+      <c r="AN17" s="79"/>
+      <c r="AO17" s="79"/>
+      <c r="AP17" s="87"/>
+      <c r="AQ17" s="78"/>
+      <c r="AR17" s="79"/>
+      <c r="AS17" s="79"/>
+      <c r="AT17" s="79"/>
+      <c r="AU17" s="79"/>
+      <c r="AV17" s="79"/>
+      <c r="AW17" s="79"/>
+      <c r="AX17" s="79"/>
+      <c r="AY17" s="79"/>
+      <c r="AZ17" s="79"/>
+      <c r="BA17" s="79"/>
+      <c r="BB17" s="79"/>
+      <c r="BC17" s="79"/>
+      <c r="BD17" s="79"/>
+      <c r="BE17" s="80"/>
     </row>
     <row r="18" spans="1:57" ht="15" customHeight="1">
-      <c r="A18" s="78"/>
-      <c r="B18" s="79"/>
-      <c r="C18" s="79"/>
-      <c r="D18" s="79"/>
-      <c r="E18" s="79"/>
-      <c r="F18" s="79"/>
-      <c r="G18" s="80"/>
+      <c r="A18" s="98"/>
+      <c r="B18" s="99"/>
+      <c r="C18" s="99"/>
+      <c r="D18" s="99"/>
+      <c r="E18" s="99"/>
+      <c r="F18" s="99"/>
+      <c r="G18" s="100"/>
       <c r="H18" s="81"/>
       <c r="I18" s="82"/>
       <c r="J18" s="82"/>
@@ -65358,57 +65361,57 @@
       <c r="M18" s="82"/>
       <c r="N18" s="83"/>
       <c r="O18" s="81"/>
-      <c r="P18" s="84"/>
-      <c r="Q18" s="84"/>
-      <c r="R18" s="84"/>
-      <c r="S18" s="84"/>
-      <c r="T18" s="84"/>
-      <c r="U18" s="84"/>
-      <c r="V18" s="84"/>
-      <c r="W18" s="84"/>
-      <c r="X18" s="84"/>
-      <c r="Y18" s="84"/>
-      <c r="Z18" s="84"/>
-      <c r="AA18" s="84"/>
-      <c r="AB18" s="84"/>
-      <c r="AC18" s="84"/>
-      <c r="AD18" s="84"/>
-      <c r="AE18" s="84"/>
-      <c r="AF18" s="84"/>
-      <c r="AG18" s="84"/>
-      <c r="AH18" s="84"/>
-      <c r="AI18" s="84"/>
-      <c r="AJ18" s="84"/>
-      <c r="AK18" s="84"/>
-      <c r="AL18" s="84"/>
-      <c r="AM18" s="84"/>
-      <c r="AN18" s="84"/>
-      <c r="AO18" s="84"/>
-      <c r="AP18" s="85"/>
-      <c r="AQ18" s="89"/>
-      <c r="AR18" s="84"/>
-      <c r="AS18" s="84"/>
-      <c r="AT18" s="84"/>
-      <c r="AU18" s="84"/>
-      <c r="AV18" s="84"/>
-      <c r="AW18" s="84"/>
-      <c r="AX18" s="84"/>
-      <c r="AY18" s="84"/>
-      <c r="AZ18" s="84"/>
-      <c r="BA18" s="84"/>
-      <c r="BB18" s="84"/>
-      <c r="BC18" s="84"/>
-      <c r="BD18" s="84"/>
-      <c r="BE18" s="90"/>
+      <c r="P18" s="79"/>
+      <c r="Q18" s="79"/>
+      <c r="R18" s="79"/>
+      <c r="S18" s="79"/>
+      <c r="T18" s="79"/>
+      <c r="U18" s="79"/>
+      <c r="V18" s="79"/>
+      <c r="W18" s="79"/>
+      <c r="X18" s="79"/>
+      <c r="Y18" s="79"/>
+      <c r="Z18" s="79"/>
+      <c r="AA18" s="79"/>
+      <c r="AB18" s="79"/>
+      <c r="AC18" s="79"/>
+      <c r="AD18" s="79"/>
+      <c r="AE18" s="79"/>
+      <c r="AF18" s="79"/>
+      <c r="AG18" s="79"/>
+      <c r="AH18" s="79"/>
+      <c r="AI18" s="79"/>
+      <c r="AJ18" s="79"/>
+      <c r="AK18" s="79"/>
+      <c r="AL18" s="79"/>
+      <c r="AM18" s="79"/>
+      <c r="AN18" s="79"/>
+      <c r="AO18" s="79"/>
+      <c r="AP18" s="87"/>
+      <c r="AQ18" s="78"/>
+      <c r="AR18" s="79"/>
+      <c r="AS18" s="79"/>
+      <c r="AT18" s="79"/>
+      <c r="AU18" s="79"/>
+      <c r="AV18" s="79"/>
+      <c r="AW18" s="79"/>
+      <c r="AX18" s="79"/>
+      <c r="AY18" s="79"/>
+      <c r="AZ18" s="79"/>
+      <c r="BA18" s="79"/>
+      <c r="BB18" s="79"/>
+      <c r="BC18" s="79"/>
+      <c r="BD18" s="79"/>
+      <c r="BE18" s="80"/>
     </row>
     <row r="19" spans="1:57" ht="15" customHeight="1">
-      <c r="A19" s="78"/>
-      <c r="B19" s="79"/>
-      <c r="C19" s="79"/>
-      <c r="D19" s="79"/>
-      <c r="E19" s="79"/>
-      <c r="F19" s="79"/>
-      <c r="G19" s="80"/>
+      <c r="A19" s="98"/>
+      <c r="B19" s="99"/>
+      <c r="C19" s="99"/>
+      <c r="D19" s="99"/>
+      <c r="E19" s="99"/>
+      <c r="F19" s="99"/>
+      <c r="G19" s="100"/>
       <c r="H19" s="81"/>
       <c r="I19" s="82"/>
       <c r="J19" s="82"/>
@@ -65417,57 +65420,57 @@
       <c r="M19" s="82"/>
       <c r="N19" s="83"/>
       <c r="O19" s="81"/>
-      <c r="P19" s="84"/>
-      <c r="Q19" s="84"/>
-      <c r="R19" s="84"/>
-      <c r="S19" s="84"/>
-      <c r="T19" s="84"/>
-      <c r="U19" s="84"/>
-      <c r="V19" s="84"/>
-      <c r="W19" s="84"/>
-      <c r="X19" s="84"/>
-      <c r="Y19" s="84"/>
-      <c r="Z19" s="84"/>
-      <c r="AA19" s="84"/>
-      <c r="AB19" s="84"/>
-      <c r="AC19" s="84"/>
-      <c r="AD19" s="84"/>
-      <c r="AE19" s="84"/>
-      <c r="AF19" s="84"/>
-      <c r="AG19" s="84"/>
-      <c r="AH19" s="84"/>
-      <c r="AI19" s="84"/>
-      <c r="AJ19" s="84"/>
-      <c r="AK19" s="84"/>
-      <c r="AL19" s="84"/>
-      <c r="AM19" s="84"/>
-      <c r="AN19" s="84"/>
-      <c r="AO19" s="84"/>
-      <c r="AP19" s="85"/>
-      <c r="AQ19" s="89"/>
-      <c r="AR19" s="84"/>
-      <c r="AS19" s="84"/>
-      <c r="AT19" s="84"/>
-      <c r="AU19" s="84"/>
-      <c r="AV19" s="84"/>
-      <c r="AW19" s="84"/>
-      <c r="AX19" s="84"/>
-      <c r="AY19" s="84"/>
-      <c r="AZ19" s="84"/>
-      <c r="BA19" s="84"/>
-      <c r="BB19" s="84"/>
-      <c r="BC19" s="84"/>
-      <c r="BD19" s="84"/>
-      <c r="BE19" s="90"/>
+      <c r="P19" s="79"/>
+      <c r="Q19" s="79"/>
+      <c r="R19" s="79"/>
+      <c r="S19" s="79"/>
+      <c r="T19" s="79"/>
+      <c r="U19" s="79"/>
+      <c r="V19" s="79"/>
+      <c r="W19" s="79"/>
+      <c r="X19" s="79"/>
+      <c r="Y19" s="79"/>
+      <c r="Z19" s="79"/>
+      <c r="AA19" s="79"/>
+      <c r="AB19" s="79"/>
+      <c r="AC19" s="79"/>
+      <c r="AD19" s="79"/>
+      <c r="AE19" s="79"/>
+      <c r="AF19" s="79"/>
+      <c r="AG19" s="79"/>
+      <c r="AH19" s="79"/>
+      <c r="AI19" s="79"/>
+      <c r="AJ19" s="79"/>
+      <c r="AK19" s="79"/>
+      <c r="AL19" s="79"/>
+      <c r="AM19" s="79"/>
+      <c r="AN19" s="79"/>
+      <c r="AO19" s="79"/>
+      <c r="AP19" s="87"/>
+      <c r="AQ19" s="78"/>
+      <c r="AR19" s="79"/>
+      <c r="AS19" s="79"/>
+      <c r="AT19" s="79"/>
+      <c r="AU19" s="79"/>
+      <c r="AV19" s="79"/>
+      <c r="AW19" s="79"/>
+      <c r="AX19" s="79"/>
+      <c r="AY19" s="79"/>
+      <c r="AZ19" s="79"/>
+      <c r="BA19" s="79"/>
+      <c r="BB19" s="79"/>
+      <c r="BC19" s="79"/>
+      <c r="BD19" s="79"/>
+      <c r="BE19" s="80"/>
     </row>
     <row r="20" spans="1:57" ht="15" customHeight="1">
-      <c r="A20" s="78"/>
-      <c r="B20" s="79"/>
-      <c r="C20" s="79"/>
-      <c r="D20" s="79"/>
-      <c r="E20" s="79"/>
-      <c r="F20" s="79"/>
-      <c r="G20" s="80"/>
+      <c r="A20" s="98"/>
+      <c r="B20" s="99"/>
+      <c r="C20" s="99"/>
+      <c r="D20" s="99"/>
+      <c r="E20" s="99"/>
+      <c r="F20" s="99"/>
+      <c r="G20" s="100"/>
       <c r="H20" s="81"/>
       <c r="I20" s="82"/>
       <c r="J20" s="82"/>
@@ -65476,57 +65479,57 @@
       <c r="M20" s="82"/>
       <c r="N20" s="83"/>
       <c r="O20" s="81"/>
-      <c r="P20" s="84"/>
-      <c r="Q20" s="84"/>
-      <c r="R20" s="84"/>
-      <c r="S20" s="84"/>
-      <c r="T20" s="84"/>
-      <c r="U20" s="84"/>
-      <c r="V20" s="84"/>
-      <c r="W20" s="84"/>
-      <c r="X20" s="84"/>
-      <c r="Y20" s="84"/>
-      <c r="Z20" s="84"/>
-      <c r="AA20" s="84"/>
-      <c r="AB20" s="84"/>
-      <c r="AC20" s="84"/>
-      <c r="AD20" s="84"/>
-      <c r="AE20" s="84"/>
-      <c r="AF20" s="84"/>
-      <c r="AG20" s="84"/>
-      <c r="AH20" s="84"/>
-      <c r="AI20" s="84"/>
-      <c r="AJ20" s="84"/>
-      <c r="AK20" s="84"/>
-      <c r="AL20" s="84"/>
-      <c r="AM20" s="84"/>
-      <c r="AN20" s="84"/>
-      <c r="AO20" s="84"/>
-      <c r="AP20" s="85"/>
-      <c r="AQ20" s="89"/>
-      <c r="AR20" s="84"/>
-      <c r="AS20" s="84"/>
-      <c r="AT20" s="84"/>
-      <c r="AU20" s="84"/>
-      <c r="AV20" s="84"/>
-      <c r="AW20" s="84"/>
-      <c r="AX20" s="84"/>
-      <c r="AY20" s="84"/>
-      <c r="AZ20" s="84"/>
-      <c r="BA20" s="84"/>
-      <c r="BB20" s="84"/>
-      <c r="BC20" s="84"/>
-      <c r="BD20" s="84"/>
-      <c r="BE20" s="90"/>
+      <c r="P20" s="79"/>
+      <c r="Q20" s="79"/>
+      <c r="R20" s="79"/>
+      <c r="S20" s="79"/>
+      <c r="T20" s="79"/>
+      <c r="U20" s="79"/>
+      <c r="V20" s="79"/>
+      <c r="W20" s="79"/>
+      <c r="X20" s="79"/>
+      <c r="Y20" s="79"/>
+      <c r="Z20" s="79"/>
+      <c r="AA20" s="79"/>
+      <c r="AB20" s="79"/>
+      <c r="AC20" s="79"/>
+      <c r="AD20" s="79"/>
+      <c r="AE20" s="79"/>
+      <c r="AF20" s="79"/>
+      <c r="AG20" s="79"/>
+      <c r="AH20" s="79"/>
+      <c r="AI20" s="79"/>
+      <c r="AJ20" s="79"/>
+      <c r="AK20" s="79"/>
+      <c r="AL20" s="79"/>
+      <c r="AM20" s="79"/>
+      <c r="AN20" s="79"/>
+      <c r="AO20" s="79"/>
+      <c r="AP20" s="87"/>
+      <c r="AQ20" s="78"/>
+      <c r="AR20" s="79"/>
+      <c r="AS20" s="79"/>
+      <c r="AT20" s="79"/>
+      <c r="AU20" s="79"/>
+      <c r="AV20" s="79"/>
+      <c r="AW20" s="79"/>
+      <c r="AX20" s="79"/>
+      <c r="AY20" s="79"/>
+      <c r="AZ20" s="79"/>
+      <c r="BA20" s="79"/>
+      <c r="BB20" s="79"/>
+      <c r="BC20" s="79"/>
+      <c r="BD20" s="79"/>
+      <c r="BE20" s="80"/>
     </row>
     <row r="21" spans="1:57" ht="15" customHeight="1">
-      <c r="A21" s="78"/>
-      <c r="B21" s="79"/>
-      <c r="C21" s="79"/>
-      <c r="D21" s="79"/>
-      <c r="E21" s="79"/>
-      <c r="F21" s="79"/>
-      <c r="G21" s="80"/>
+      <c r="A21" s="98"/>
+      <c r="B21" s="99"/>
+      <c r="C21" s="99"/>
+      <c r="D21" s="99"/>
+      <c r="E21" s="99"/>
+      <c r="F21" s="99"/>
+      <c r="G21" s="100"/>
       <c r="H21" s="81"/>
       <c r="I21" s="82"/>
       <c r="J21" s="82"/>
@@ -65535,57 +65538,57 @@
       <c r="M21" s="82"/>
       <c r="N21" s="83"/>
       <c r="O21" s="81"/>
-      <c r="P21" s="84"/>
-      <c r="Q21" s="84"/>
-      <c r="R21" s="84"/>
-      <c r="S21" s="84"/>
-      <c r="T21" s="84"/>
-      <c r="U21" s="84"/>
-      <c r="V21" s="84"/>
-      <c r="W21" s="84"/>
-      <c r="X21" s="84"/>
-      <c r="Y21" s="84"/>
-      <c r="Z21" s="84"/>
-      <c r="AA21" s="84"/>
-      <c r="AB21" s="84"/>
-      <c r="AC21" s="84"/>
-      <c r="AD21" s="84"/>
-      <c r="AE21" s="84"/>
-      <c r="AF21" s="84"/>
-      <c r="AG21" s="84"/>
-      <c r="AH21" s="84"/>
-      <c r="AI21" s="84"/>
-      <c r="AJ21" s="84"/>
-      <c r="AK21" s="84"/>
-      <c r="AL21" s="84"/>
-      <c r="AM21" s="84"/>
-      <c r="AN21" s="84"/>
-      <c r="AO21" s="84"/>
-      <c r="AP21" s="85"/>
-      <c r="AQ21" s="89"/>
-      <c r="AR21" s="84"/>
-      <c r="AS21" s="84"/>
-      <c r="AT21" s="84"/>
-      <c r="AU21" s="84"/>
-      <c r="AV21" s="84"/>
-      <c r="AW21" s="84"/>
-      <c r="AX21" s="84"/>
-      <c r="AY21" s="84"/>
-      <c r="AZ21" s="84"/>
-      <c r="BA21" s="84"/>
-      <c r="BB21" s="84"/>
-      <c r="BC21" s="84"/>
-      <c r="BD21" s="84"/>
-      <c r="BE21" s="90"/>
+      <c r="P21" s="79"/>
+      <c r="Q21" s="79"/>
+      <c r="R21" s="79"/>
+      <c r="S21" s="79"/>
+      <c r="T21" s="79"/>
+      <c r="U21" s="79"/>
+      <c r="V21" s="79"/>
+      <c r="W21" s="79"/>
+      <c r="X21" s="79"/>
+      <c r="Y21" s="79"/>
+      <c r="Z21" s="79"/>
+      <c r="AA21" s="79"/>
+      <c r="AB21" s="79"/>
+      <c r="AC21" s="79"/>
+      <c r="AD21" s="79"/>
+      <c r="AE21" s="79"/>
+      <c r="AF21" s="79"/>
+      <c r="AG21" s="79"/>
+      <c r="AH21" s="79"/>
+      <c r="AI21" s="79"/>
+      <c r="AJ21" s="79"/>
+      <c r="AK21" s="79"/>
+      <c r="AL21" s="79"/>
+      <c r="AM21" s="79"/>
+      <c r="AN21" s="79"/>
+      <c r="AO21" s="79"/>
+      <c r="AP21" s="87"/>
+      <c r="AQ21" s="78"/>
+      <c r="AR21" s="79"/>
+      <c r="AS21" s="79"/>
+      <c r="AT21" s="79"/>
+      <c r="AU21" s="79"/>
+      <c r="AV21" s="79"/>
+      <c r="AW21" s="79"/>
+      <c r="AX21" s="79"/>
+      <c r="AY21" s="79"/>
+      <c r="AZ21" s="79"/>
+      <c r="BA21" s="79"/>
+      <c r="BB21" s="79"/>
+      <c r="BC21" s="79"/>
+      <c r="BD21" s="79"/>
+      <c r="BE21" s="80"/>
     </row>
     <row r="22" spans="1:57" ht="15" customHeight="1">
-      <c r="A22" s="78"/>
-      <c r="B22" s="79"/>
-      <c r="C22" s="79"/>
-      <c r="D22" s="79"/>
-      <c r="E22" s="79"/>
-      <c r="F22" s="79"/>
-      <c r="G22" s="80"/>
+      <c r="A22" s="98"/>
+      <c r="B22" s="99"/>
+      <c r="C22" s="99"/>
+      <c r="D22" s="99"/>
+      <c r="E22" s="99"/>
+      <c r="F22" s="99"/>
+      <c r="G22" s="100"/>
       <c r="H22" s="81"/>
       <c r="I22" s="82"/>
       <c r="J22" s="82"/>
@@ -65594,57 +65597,57 @@
       <c r="M22" s="82"/>
       <c r="N22" s="83"/>
       <c r="O22" s="81"/>
-      <c r="P22" s="84"/>
-      <c r="Q22" s="84"/>
-      <c r="R22" s="84"/>
-      <c r="S22" s="84"/>
-      <c r="T22" s="84"/>
-      <c r="U22" s="84"/>
-      <c r="V22" s="84"/>
-      <c r="W22" s="84"/>
-      <c r="X22" s="84"/>
-      <c r="Y22" s="84"/>
-      <c r="Z22" s="84"/>
-      <c r="AA22" s="84"/>
-      <c r="AB22" s="84"/>
-      <c r="AC22" s="84"/>
-      <c r="AD22" s="84"/>
-      <c r="AE22" s="84"/>
-      <c r="AF22" s="84"/>
-      <c r="AG22" s="84"/>
-      <c r="AH22" s="84"/>
-      <c r="AI22" s="84"/>
-      <c r="AJ22" s="84"/>
-      <c r="AK22" s="84"/>
-      <c r="AL22" s="84"/>
-      <c r="AM22" s="84"/>
-      <c r="AN22" s="84"/>
-      <c r="AO22" s="84"/>
-      <c r="AP22" s="85"/>
-      <c r="AQ22" s="89"/>
-      <c r="AR22" s="84"/>
-      <c r="AS22" s="84"/>
-      <c r="AT22" s="84"/>
-      <c r="AU22" s="84"/>
-      <c r="AV22" s="84"/>
-      <c r="AW22" s="84"/>
-      <c r="AX22" s="84"/>
-      <c r="AY22" s="84"/>
-      <c r="AZ22" s="84"/>
-      <c r="BA22" s="84"/>
-      <c r="BB22" s="84"/>
-      <c r="BC22" s="84"/>
-      <c r="BD22" s="84"/>
-      <c r="BE22" s="90"/>
+      <c r="P22" s="79"/>
+      <c r="Q22" s="79"/>
+      <c r="R22" s="79"/>
+      <c r="S22" s="79"/>
+      <c r="T22" s="79"/>
+      <c r="U22" s="79"/>
+      <c r="V22" s="79"/>
+      <c r="W22" s="79"/>
+      <c r="X22" s="79"/>
+      <c r="Y22" s="79"/>
+      <c r="Z22" s="79"/>
+      <c r="AA22" s="79"/>
+      <c r="AB22" s="79"/>
+      <c r="AC22" s="79"/>
+      <c r="AD22" s="79"/>
+      <c r="AE22" s="79"/>
+      <c r="AF22" s="79"/>
+      <c r="AG22" s="79"/>
+      <c r="AH22" s="79"/>
+      <c r="AI22" s="79"/>
+      <c r="AJ22" s="79"/>
+      <c r="AK22" s="79"/>
+      <c r="AL22" s="79"/>
+      <c r="AM22" s="79"/>
+      <c r="AN22" s="79"/>
+      <c r="AO22" s="79"/>
+      <c r="AP22" s="87"/>
+      <c r="AQ22" s="78"/>
+      <c r="AR22" s="79"/>
+      <c r="AS22" s="79"/>
+      <c r="AT22" s="79"/>
+      <c r="AU22" s="79"/>
+      <c r="AV22" s="79"/>
+      <c r="AW22" s="79"/>
+      <c r="AX22" s="79"/>
+      <c r="AY22" s="79"/>
+      <c r="AZ22" s="79"/>
+      <c r="BA22" s="79"/>
+      <c r="BB22" s="79"/>
+      <c r="BC22" s="79"/>
+      <c r="BD22" s="79"/>
+      <c r="BE22" s="80"/>
     </row>
     <row r="23" spans="1:57" ht="15" customHeight="1">
-      <c r="A23" s="78"/>
-      <c r="B23" s="79"/>
-      <c r="C23" s="79"/>
-      <c r="D23" s="79"/>
-      <c r="E23" s="79"/>
-      <c r="F23" s="79"/>
-      <c r="G23" s="80"/>
+      <c r="A23" s="98"/>
+      <c r="B23" s="99"/>
+      <c r="C23" s="99"/>
+      <c r="D23" s="99"/>
+      <c r="E23" s="99"/>
+      <c r="F23" s="99"/>
+      <c r="G23" s="100"/>
       <c r="H23" s="81"/>
       <c r="I23" s="82"/>
       <c r="J23" s="82"/>
@@ -65653,57 +65656,57 @@
       <c r="M23" s="82"/>
       <c r="N23" s="83"/>
       <c r="O23" s="81"/>
-      <c r="P23" s="84"/>
-      <c r="Q23" s="84"/>
-      <c r="R23" s="84"/>
-      <c r="S23" s="84"/>
-      <c r="T23" s="84"/>
-      <c r="U23" s="84"/>
-      <c r="V23" s="84"/>
-      <c r="W23" s="84"/>
-      <c r="X23" s="84"/>
-      <c r="Y23" s="84"/>
-      <c r="Z23" s="84"/>
-      <c r="AA23" s="84"/>
-      <c r="AB23" s="84"/>
-      <c r="AC23" s="84"/>
-      <c r="AD23" s="84"/>
-      <c r="AE23" s="84"/>
-      <c r="AF23" s="84"/>
-      <c r="AG23" s="84"/>
-      <c r="AH23" s="84"/>
-      <c r="AI23" s="84"/>
-      <c r="AJ23" s="84"/>
-      <c r="AK23" s="84"/>
-      <c r="AL23" s="84"/>
-      <c r="AM23" s="84"/>
-      <c r="AN23" s="84"/>
-      <c r="AO23" s="84"/>
-      <c r="AP23" s="85"/>
-      <c r="AQ23" s="89"/>
-      <c r="AR23" s="84"/>
-      <c r="AS23" s="84"/>
-      <c r="AT23" s="84"/>
-      <c r="AU23" s="84"/>
-      <c r="AV23" s="84"/>
-      <c r="AW23" s="84"/>
-      <c r="AX23" s="84"/>
-      <c r="AY23" s="84"/>
-      <c r="AZ23" s="84"/>
-      <c r="BA23" s="84"/>
-      <c r="BB23" s="84"/>
-      <c r="BC23" s="84"/>
-      <c r="BD23" s="84"/>
-      <c r="BE23" s="90"/>
+      <c r="P23" s="79"/>
+      <c r="Q23" s="79"/>
+      <c r="R23" s="79"/>
+      <c r="S23" s="79"/>
+      <c r="T23" s="79"/>
+      <c r="U23" s="79"/>
+      <c r="V23" s="79"/>
+      <c r="W23" s="79"/>
+      <c r="X23" s="79"/>
+      <c r="Y23" s="79"/>
+      <c r="Z23" s="79"/>
+      <c r="AA23" s="79"/>
+      <c r="AB23" s="79"/>
+      <c r="AC23" s="79"/>
+      <c r="AD23" s="79"/>
+      <c r="AE23" s="79"/>
+      <c r="AF23" s="79"/>
+      <c r="AG23" s="79"/>
+      <c r="AH23" s="79"/>
+      <c r="AI23" s="79"/>
+      <c r="AJ23" s="79"/>
+      <c r="AK23" s="79"/>
+      <c r="AL23" s="79"/>
+      <c r="AM23" s="79"/>
+      <c r="AN23" s="79"/>
+      <c r="AO23" s="79"/>
+      <c r="AP23" s="87"/>
+      <c r="AQ23" s="78"/>
+      <c r="AR23" s="79"/>
+      <c r="AS23" s="79"/>
+      <c r="AT23" s="79"/>
+      <c r="AU23" s="79"/>
+      <c r="AV23" s="79"/>
+      <c r="AW23" s="79"/>
+      <c r="AX23" s="79"/>
+      <c r="AY23" s="79"/>
+      <c r="AZ23" s="79"/>
+      <c r="BA23" s="79"/>
+      <c r="BB23" s="79"/>
+      <c r="BC23" s="79"/>
+      <c r="BD23" s="79"/>
+      <c r="BE23" s="80"/>
     </row>
     <row r="24" spans="1:57" ht="15" customHeight="1">
-      <c r="A24" s="78"/>
-      <c r="B24" s="79"/>
-      <c r="C24" s="79"/>
-      <c r="D24" s="79"/>
-      <c r="E24" s="79"/>
-      <c r="F24" s="79"/>
-      <c r="G24" s="80"/>
+      <c r="A24" s="98"/>
+      <c r="B24" s="99"/>
+      <c r="C24" s="99"/>
+      <c r="D24" s="99"/>
+      <c r="E24" s="99"/>
+      <c r="F24" s="99"/>
+      <c r="G24" s="100"/>
       <c r="H24" s="81"/>
       <c r="I24" s="82"/>
       <c r="J24" s="82"/>
@@ -65712,57 +65715,57 @@
       <c r="M24" s="82"/>
       <c r="N24" s="83"/>
       <c r="O24" s="81"/>
-      <c r="P24" s="84"/>
-      <c r="Q24" s="84"/>
-      <c r="R24" s="84"/>
-      <c r="S24" s="84"/>
-      <c r="T24" s="84"/>
-      <c r="U24" s="84"/>
-      <c r="V24" s="84"/>
-      <c r="W24" s="84"/>
-      <c r="X24" s="84"/>
-      <c r="Y24" s="84"/>
-      <c r="Z24" s="84"/>
-      <c r="AA24" s="84"/>
-      <c r="AB24" s="84"/>
-      <c r="AC24" s="84"/>
-      <c r="AD24" s="84"/>
-      <c r="AE24" s="84"/>
-      <c r="AF24" s="84"/>
-      <c r="AG24" s="84"/>
-      <c r="AH24" s="84"/>
-      <c r="AI24" s="84"/>
-      <c r="AJ24" s="84"/>
-      <c r="AK24" s="84"/>
-      <c r="AL24" s="84"/>
-      <c r="AM24" s="84"/>
-      <c r="AN24" s="84"/>
-      <c r="AO24" s="84"/>
-      <c r="AP24" s="85"/>
-      <c r="AQ24" s="89"/>
-      <c r="AR24" s="84"/>
-      <c r="AS24" s="84"/>
-      <c r="AT24" s="84"/>
-      <c r="AU24" s="84"/>
-      <c r="AV24" s="84"/>
-      <c r="AW24" s="84"/>
-      <c r="AX24" s="84"/>
-      <c r="AY24" s="84"/>
-      <c r="AZ24" s="84"/>
-      <c r="BA24" s="84"/>
-      <c r="BB24" s="84"/>
-      <c r="BC24" s="84"/>
-      <c r="BD24" s="84"/>
-      <c r="BE24" s="90"/>
+      <c r="P24" s="79"/>
+      <c r="Q24" s="79"/>
+      <c r="R24" s="79"/>
+      <c r="S24" s="79"/>
+      <c r="T24" s="79"/>
+      <c r="U24" s="79"/>
+      <c r="V24" s="79"/>
+      <c r="W24" s="79"/>
+      <c r="X24" s="79"/>
+      <c r="Y24" s="79"/>
+      <c r="Z24" s="79"/>
+      <c r="AA24" s="79"/>
+      <c r="AB24" s="79"/>
+      <c r="AC24" s="79"/>
+      <c r="AD24" s="79"/>
+      <c r="AE24" s="79"/>
+      <c r="AF24" s="79"/>
+      <c r="AG24" s="79"/>
+      <c r="AH24" s="79"/>
+      <c r="AI24" s="79"/>
+      <c r="AJ24" s="79"/>
+      <c r="AK24" s="79"/>
+      <c r="AL24" s="79"/>
+      <c r="AM24" s="79"/>
+      <c r="AN24" s="79"/>
+      <c r="AO24" s="79"/>
+      <c r="AP24" s="87"/>
+      <c r="AQ24" s="78"/>
+      <c r="AR24" s="79"/>
+      <c r="AS24" s="79"/>
+      <c r="AT24" s="79"/>
+      <c r="AU24" s="79"/>
+      <c r="AV24" s="79"/>
+      <c r="AW24" s="79"/>
+      <c r="AX24" s="79"/>
+      <c r="AY24" s="79"/>
+      <c r="AZ24" s="79"/>
+      <c r="BA24" s="79"/>
+      <c r="BB24" s="79"/>
+      <c r="BC24" s="79"/>
+      <c r="BD24" s="79"/>
+      <c r="BE24" s="80"/>
     </row>
     <row r="25" spans="1:57" ht="15" customHeight="1">
-      <c r="A25" s="78"/>
-      <c r="B25" s="79"/>
-      <c r="C25" s="79"/>
-      <c r="D25" s="79"/>
-      <c r="E25" s="79"/>
-      <c r="F25" s="79"/>
-      <c r="G25" s="80"/>
+      <c r="A25" s="98"/>
+      <c r="B25" s="99"/>
+      <c r="C25" s="99"/>
+      <c r="D25" s="99"/>
+      <c r="E25" s="99"/>
+      <c r="F25" s="99"/>
+      <c r="G25" s="100"/>
       <c r="H25" s="81"/>
       <c r="I25" s="82"/>
       <c r="J25" s="82"/>
@@ -65771,57 +65774,57 @@
       <c r="M25" s="82"/>
       <c r="N25" s="83"/>
       <c r="O25" s="81"/>
-      <c r="P25" s="84"/>
-      <c r="Q25" s="84"/>
-      <c r="R25" s="84"/>
-      <c r="S25" s="84"/>
-      <c r="T25" s="84"/>
-      <c r="U25" s="84"/>
-      <c r="V25" s="84"/>
-      <c r="W25" s="84"/>
-      <c r="X25" s="84"/>
-      <c r="Y25" s="84"/>
-      <c r="Z25" s="84"/>
-      <c r="AA25" s="84"/>
-      <c r="AB25" s="84"/>
-      <c r="AC25" s="84"/>
-      <c r="AD25" s="84"/>
-      <c r="AE25" s="84"/>
-      <c r="AF25" s="84"/>
-      <c r="AG25" s="84"/>
-      <c r="AH25" s="84"/>
-      <c r="AI25" s="84"/>
-      <c r="AJ25" s="84"/>
-      <c r="AK25" s="84"/>
-      <c r="AL25" s="84"/>
-      <c r="AM25" s="84"/>
-      <c r="AN25" s="84"/>
-      <c r="AO25" s="84"/>
-      <c r="AP25" s="85"/>
-      <c r="AQ25" s="89"/>
-      <c r="AR25" s="84"/>
-      <c r="AS25" s="84"/>
-      <c r="AT25" s="84"/>
-      <c r="AU25" s="84"/>
-      <c r="AV25" s="84"/>
-      <c r="AW25" s="84"/>
-      <c r="AX25" s="84"/>
-      <c r="AY25" s="84"/>
-      <c r="AZ25" s="84"/>
-      <c r="BA25" s="84"/>
-      <c r="BB25" s="84"/>
-      <c r="BC25" s="84"/>
-      <c r="BD25" s="84"/>
-      <c r="BE25" s="90"/>
+      <c r="P25" s="79"/>
+      <c r="Q25" s="79"/>
+      <c r="R25" s="79"/>
+      <c r="S25" s="79"/>
+      <c r="T25" s="79"/>
+      <c r="U25" s="79"/>
+      <c r="V25" s="79"/>
+      <c r="W25" s="79"/>
+      <c r="X25" s="79"/>
+      <c r="Y25" s="79"/>
+      <c r="Z25" s="79"/>
+      <c r="AA25" s="79"/>
+      <c r="AB25" s="79"/>
+      <c r="AC25" s="79"/>
+      <c r="AD25" s="79"/>
+      <c r="AE25" s="79"/>
+      <c r="AF25" s="79"/>
+      <c r="AG25" s="79"/>
+      <c r="AH25" s="79"/>
+      <c r="AI25" s="79"/>
+      <c r="AJ25" s="79"/>
+      <c r="AK25" s="79"/>
+      <c r="AL25" s="79"/>
+      <c r="AM25" s="79"/>
+      <c r="AN25" s="79"/>
+      <c r="AO25" s="79"/>
+      <c r="AP25" s="87"/>
+      <c r="AQ25" s="78"/>
+      <c r="AR25" s="79"/>
+      <c r="AS25" s="79"/>
+      <c r="AT25" s="79"/>
+      <c r="AU25" s="79"/>
+      <c r="AV25" s="79"/>
+      <c r="AW25" s="79"/>
+      <c r="AX25" s="79"/>
+      <c r="AY25" s="79"/>
+      <c r="AZ25" s="79"/>
+      <c r="BA25" s="79"/>
+      <c r="BB25" s="79"/>
+      <c r="BC25" s="79"/>
+      <c r="BD25" s="79"/>
+      <c r="BE25" s="80"/>
     </row>
     <row r="26" spans="1:57" ht="15" customHeight="1">
-      <c r="A26" s="78"/>
-      <c r="B26" s="79"/>
-      <c r="C26" s="79"/>
-      <c r="D26" s="79"/>
-      <c r="E26" s="79"/>
-      <c r="F26" s="79"/>
-      <c r="G26" s="80"/>
+      <c r="A26" s="98"/>
+      <c r="B26" s="99"/>
+      <c r="C26" s="99"/>
+      <c r="D26" s="99"/>
+      <c r="E26" s="99"/>
+      <c r="F26" s="99"/>
+      <c r="G26" s="100"/>
       <c r="H26" s="81"/>
       <c r="I26" s="82"/>
       <c r="J26" s="82"/>
@@ -65830,57 +65833,57 @@
       <c r="M26" s="82"/>
       <c r="N26" s="83"/>
       <c r="O26" s="81"/>
-      <c r="P26" s="84"/>
-      <c r="Q26" s="84"/>
-      <c r="R26" s="84"/>
-      <c r="S26" s="84"/>
-      <c r="T26" s="84"/>
-      <c r="U26" s="84"/>
-      <c r="V26" s="84"/>
-      <c r="W26" s="84"/>
-      <c r="X26" s="84"/>
-      <c r="Y26" s="84"/>
-      <c r="Z26" s="84"/>
-      <c r="AA26" s="84"/>
-      <c r="AB26" s="84"/>
-      <c r="AC26" s="84"/>
-      <c r="AD26" s="84"/>
-      <c r="AE26" s="84"/>
-      <c r="AF26" s="84"/>
-      <c r="AG26" s="84"/>
-      <c r="AH26" s="84"/>
-      <c r="AI26" s="84"/>
-      <c r="AJ26" s="84"/>
-      <c r="AK26" s="84"/>
-      <c r="AL26" s="84"/>
-      <c r="AM26" s="84"/>
-      <c r="AN26" s="84"/>
-      <c r="AO26" s="84"/>
-      <c r="AP26" s="85"/>
-      <c r="AQ26" s="89"/>
-      <c r="AR26" s="84"/>
-      <c r="AS26" s="84"/>
-      <c r="AT26" s="84"/>
-      <c r="AU26" s="84"/>
-      <c r="AV26" s="84"/>
-      <c r="AW26" s="84"/>
-      <c r="AX26" s="84"/>
-      <c r="AY26" s="84"/>
-      <c r="AZ26" s="84"/>
-      <c r="BA26" s="84"/>
-      <c r="BB26" s="84"/>
-      <c r="BC26" s="84"/>
-      <c r="BD26" s="84"/>
-      <c r="BE26" s="90"/>
+      <c r="P26" s="79"/>
+      <c r="Q26" s="79"/>
+      <c r="R26" s="79"/>
+      <c r="S26" s="79"/>
+      <c r="T26" s="79"/>
+      <c r="U26" s="79"/>
+      <c r="V26" s="79"/>
+      <c r="W26" s="79"/>
+      <c r="X26" s="79"/>
+      <c r="Y26" s="79"/>
+      <c r="Z26" s="79"/>
+      <c r="AA26" s="79"/>
+      <c r="AB26" s="79"/>
+      <c r="AC26" s="79"/>
+      <c r="AD26" s="79"/>
+      <c r="AE26" s="79"/>
+      <c r="AF26" s="79"/>
+      <c r="AG26" s="79"/>
+      <c r="AH26" s="79"/>
+      <c r="AI26" s="79"/>
+      <c r="AJ26" s="79"/>
+      <c r="AK26" s="79"/>
+      <c r="AL26" s="79"/>
+      <c r="AM26" s="79"/>
+      <c r="AN26" s="79"/>
+      <c r="AO26" s="79"/>
+      <c r="AP26" s="87"/>
+      <c r="AQ26" s="78"/>
+      <c r="AR26" s="79"/>
+      <c r="AS26" s="79"/>
+      <c r="AT26" s="79"/>
+      <c r="AU26" s="79"/>
+      <c r="AV26" s="79"/>
+      <c r="AW26" s="79"/>
+      <c r="AX26" s="79"/>
+      <c r="AY26" s="79"/>
+      <c r="AZ26" s="79"/>
+      <c r="BA26" s="79"/>
+      <c r="BB26" s="79"/>
+      <c r="BC26" s="79"/>
+      <c r="BD26" s="79"/>
+      <c r="BE26" s="80"/>
     </row>
     <row r="27" spans="1:57" ht="15" customHeight="1">
-      <c r="A27" s="78"/>
-      <c r="B27" s="79"/>
-      <c r="C27" s="79"/>
-      <c r="D27" s="79"/>
-      <c r="E27" s="79"/>
-      <c r="F27" s="79"/>
-      <c r="G27" s="80"/>
+      <c r="A27" s="98"/>
+      <c r="B27" s="99"/>
+      <c r="C27" s="99"/>
+      <c r="D27" s="99"/>
+      <c r="E27" s="99"/>
+      <c r="F27" s="99"/>
+      <c r="G27" s="100"/>
       <c r="H27" s="81"/>
       <c r="I27" s="82"/>
       <c r="J27" s="82"/>
@@ -65889,57 +65892,57 @@
       <c r="M27" s="82"/>
       <c r="N27" s="83"/>
       <c r="O27" s="81"/>
-      <c r="P27" s="84"/>
-      <c r="Q27" s="84"/>
-      <c r="R27" s="84"/>
-      <c r="S27" s="84"/>
-      <c r="T27" s="84"/>
-      <c r="U27" s="84"/>
-      <c r="V27" s="84"/>
-      <c r="W27" s="84"/>
-      <c r="X27" s="84"/>
-      <c r="Y27" s="84"/>
-      <c r="Z27" s="84"/>
-      <c r="AA27" s="84"/>
-      <c r="AB27" s="84"/>
-      <c r="AC27" s="84"/>
-      <c r="AD27" s="84"/>
-      <c r="AE27" s="84"/>
-      <c r="AF27" s="84"/>
-      <c r="AG27" s="84"/>
-      <c r="AH27" s="84"/>
-      <c r="AI27" s="84"/>
-      <c r="AJ27" s="84"/>
-      <c r="AK27" s="84"/>
-      <c r="AL27" s="84"/>
-      <c r="AM27" s="84"/>
-      <c r="AN27" s="84"/>
-      <c r="AO27" s="84"/>
-      <c r="AP27" s="85"/>
-      <c r="AQ27" s="89"/>
-      <c r="AR27" s="84"/>
-      <c r="AS27" s="84"/>
-      <c r="AT27" s="84"/>
-      <c r="AU27" s="84"/>
-      <c r="AV27" s="84"/>
-      <c r="AW27" s="84"/>
-      <c r="AX27" s="84"/>
-      <c r="AY27" s="84"/>
-      <c r="AZ27" s="84"/>
-      <c r="BA27" s="84"/>
-      <c r="BB27" s="84"/>
-      <c r="BC27" s="84"/>
-      <c r="BD27" s="84"/>
-      <c r="BE27" s="90"/>
+      <c r="P27" s="79"/>
+      <c r="Q27" s="79"/>
+      <c r="R27" s="79"/>
+      <c r="S27" s="79"/>
+      <c r="T27" s="79"/>
+      <c r="U27" s="79"/>
+      <c r="V27" s="79"/>
+      <c r="W27" s="79"/>
+      <c r="X27" s="79"/>
+      <c r="Y27" s="79"/>
+      <c r="Z27" s="79"/>
+      <c r="AA27" s="79"/>
+      <c r="AB27" s="79"/>
+      <c r="AC27" s="79"/>
+      <c r="AD27" s="79"/>
+      <c r="AE27" s="79"/>
+      <c r="AF27" s="79"/>
+      <c r="AG27" s="79"/>
+      <c r="AH27" s="79"/>
+      <c r="AI27" s="79"/>
+      <c r="AJ27" s="79"/>
+      <c r="AK27" s="79"/>
+      <c r="AL27" s="79"/>
+      <c r="AM27" s="79"/>
+      <c r="AN27" s="79"/>
+      <c r="AO27" s="79"/>
+      <c r="AP27" s="87"/>
+      <c r="AQ27" s="78"/>
+      <c r="AR27" s="79"/>
+      <c r="AS27" s="79"/>
+      <c r="AT27" s="79"/>
+      <c r="AU27" s="79"/>
+      <c r="AV27" s="79"/>
+      <c r="AW27" s="79"/>
+      <c r="AX27" s="79"/>
+      <c r="AY27" s="79"/>
+      <c r="AZ27" s="79"/>
+      <c r="BA27" s="79"/>
+      <c r="BB27" s="79"/>
+      <c r="BC27" s="79"/>
+      <c r="BD27" s="79"/>
+      <c r="BE27" s="80"/>
     </row>
     <row r="28" spans="1:57" ht="15" customHeight="1">
-      <c r="A28" s="78"/>
-      <c r="B28" s="79"/>
-      <c r="C28" s="79"/>
-      <c r="D28" s="79"/>
-      <c r="E28" s="79"/>
-      <c r="F28" s="79"/>
-      <c r="G28" s="80"/>
+      <c r="A28" s="98"/>
+      <c r="B28" s="99"/>
+      <c r="C28" s="99"/>
+      <c r="D28" s="99"/>
+      <c r="E28" s="99"/>
+      <c r="F28" s="99"/>
+      <c r="G28" s="100"/>
       <c r="H28" s="81"/>
       <c r="I28" s="82"/>
       <c r="J28" s="82"/>
@@ -65948,57 +65951,57 @@
       <c r="M28" s="82"/>
       <c r="N28" s="83"/>
       <c r="O28" s="81"/>
-      <c r="P28" s="84"/>
-      <c r="Q28" s="84"/>
-      <c r="R28" s="84"/>
-      <c r="S28" s="84"/>
-      <c r="T28" s="84"/>
-      <c r="U28" s="84"/>
-      <c r="V28" s="84"/>
-      <c r="W28" s="84"/>
-      <c r="X28" s="84"/>
-      <c r="Y28" s="84"/>
-      <c r="Z28" s="84"/>
-      <c r="AA28" s="84"/>
-      <c r="AB28" s="84"/>
-      <c r="AC28" s="84"/>
-      <c r="AD28" s="84"/>
-      <c r="AE28" s="84"/>
-      <c r="AF28" s="84"/>
-      <c r="AG28" s="84"/>
-      <c r="AH28" s="84"/>
-      <c r="AI28" s="84"/>
-      <c r="AJ28" s="84"/>
-      <c r="AK28" s="84"/>
-      <c r="AL28" s="84"/>
-      <c r="AM28" s="84"/>
-      <c r="AN28" s="84"/>
-      <c r="AO28" s="84"/>
-      <c r="AP28" s="85"/>
-      <c r="AQ28" s="89"/>
-      <c r="AR28" s="84"/>
-      <c r="AS28" s="84"/>
-      <c r="AT28" s="84"/>
-      <c r="AU28" s="84"/>
-      <c r="AV28" s="84"/>
-      <c r="AW28" s="84"/>
-      <c r="AX28" s="84"/>
-      <c r="AY28" s="84"/>
-      <c r="AZ28" s="84"/>
-      <c r="BA28" s="84"/>
-      <c r="BB28" s="84"/>
-      <c r="BC28" s="84"/>
-      <c r="BD28" s="84"/>
-      <c r="BE28" s="90"/>
+      <c r="P28" s="79"/>
+      <c r="Q28" s="79"/>
+      <c r="R28" s="79"/>
+      <c r="S28" s="79"/>
+      <c r="T28" s="79"/>
+      <c r="U28" s="79"/>
+      <c r="V28" s="79"/>
+      <c r="W28" s="79"/>
+      <c r="X28" s="79"/>
+      <c r="Y28" s="79"/>
+      <c r="Z28" s="79"/>
+      <c r="AA28" s="79"/>
+      <c r="AB28" s="79"/>
+      <c r="AC28" s="79"/>
+      <c r="AD28" s="79"/>
+      <c r="AE28" s="79"/>
+      <c r="AF28" s="79"/>
+      <c r="AG28" s="79"/>
+      <c r="AH28" s="79"/>
+      <c r="AI28" s="79"/>
+      <c r="AJ28" s="79"/>
+      <c r="AK28" s="79"/>
+      <c r="AL28" s="79"/>
+      <c r="AM28" s="79"/>
+      <c r="AN28" s="79"/>
+      <c r="AO28" s="79"/>
+      <c r="AP28" s="87"/>
+      <c r="AQ28" s="78"/>
+      <c r="AR28" s="79"/>
+      <c r="AS28" s="79"/>
+      <c r="AT28" s="79"/>
+      <c r="AU28" s="79"/>
+      <c r="AV28" s="79"/>
+      <c r="AW28" s="79"/>
+      <c r="AX28" s="79"/>
+      <c r="AY28" s="79"/>
+      <c r="AZ28" s="79"/>
+      <c r="BA28" s="79"/>
+      <c r="BB28" s="79"/>
+      <c r="BC28" s="79"/>
+      <c r="BD28" s="79"/>
+      <c r="BE28" s="80"/>
     </row>
     <row r="29" spans="1:57" ht="15" customHeight="1">
-      <c r="A29" s="78"/>
-      <c r="B29" s="79"/>
-      <c r="C29" s="79"/>
-      <c r="D29" s="79"/>
-      <c r="E29" s="79"/>
-      <c r="F29" s="79"/>
-      <c r="G29" s="80"/>
+      <c r="A29" s="98"/>
+      <c r="B29" s="99"/>
+      <c r="C29" s="99"/>
+      <c r="D29" s="99"/>
+      <c r="E29" s="99"/>
+      <c r="F29" s="99"/>
+      <c r="G29" s="100"/>
       <c r="H29" s="81"/>
       <c r="I29" s="82"/>
       <c r="J29" s="82"/>
@@ -66007,57 +66010,57 @@
       <c r="M29" s="82"/>
       <c r="N29" s="83"/>
       <c r="O29" s="81"/>
-      <c r="P29" s="84"/>
-      <c r="Q29" s="84"/>
-      <c r="R29" s="84"/>
-      <c r="S29" s="84"/>
-      <c r="T29" s="84"/>
-      <c r="U29" s="84"/>
-      <c r="V29" s="84"/>
-      <c r="W29" s="84"/>
-      <c r="X29" s="84"/>
-      <c r="Y29" s="84"/>
-      <c r="Z29" s="84"/>
-      <c r="AA29" s="84"/>
-      <c r="AB29" s="84"/>
-      <c r="AC29" s="84"/>
-      <c r="AD29" s="84"/>
-      <c r="AE29" s="84"/>
-      <c r="AF29" s="84"/>
-      <c r="AG29" s="84"/>
-      <c r="AH29" s="84"/>
-      <c r="AI29" s="84"/>
-      <c r="AJ29" s="84"/>
-      <c r="AK29" s="84"/>
-      <c r="AL29" s="84"/>
-      <c r="AM29" s="84"/>
-      <c r="AN29" s="84"/>
-      <c r="AO29" s="84"/>
-      <c r="AP29" s="85"/>
-      <c r="AQ29" s="89"/>
-      <c r="AR29" s="84"/>
-      <c r="AS29" s="84"/>
-      <c r="AT29" s="84"/>
-      <c r="AU29" s="84"/>
-      <c r="AV29" s="84"/>
-      <c r="AW29" s="84"/>
-      <c r="AX29" s="84"/>
-      <c r="AY29" s="84"/>
-      <c r="AZ29" s="84"/>
-      <c r="BA29" s="84"/>
-      <c r="BB29" s="84"/>
-      <c r="BC29" s="84"/>
-      <c r="BD29" s="84"/>
-      <c r="BE29" s="90"/>
+      <c r="P29" s="79"/>
+      <c r="Q29" s="79"/>
+      <c r="R29" s="79"/>
+      <c r="S29" s="79"/>
+      <c r="T29" s="79"/>
+      <c r="U29" s="79"/>
+      <c r="V29" s="79"/>
+      <c r="W29" s="79"/>
+      <c r="X29" s="79"/>
+      <c r="Y29" s="79"/>
+      <c r="Z29" s="79"/>
+      <c r="AA29" s="79"/>
+      <c r="AB29" s="79"/>
+      <c r="AC29" s="79"/>
+      <c r="AD29" s="79"/>
+      <c r="AE29" s="79"/>
+      <c r="AF29" s="79"/>
+      <c r="AG29" s="79"/>
+      <c r="AH29" s="79"/>
+      <c r="AI29" s="79"/>
+      <c r="AJ29" s="79"/>
+      <c r="AK29" s="79"/>
+      <c r="AL29" s="79"/>
+      <c r="AM29" s="79"/>
+      <c r="AN29" s="79"/>
+      <c r="AO29" s="79"/>
+      <c r="AP29" s="87"/>
+      <c r="AQ29" s="78"/>
+      <c r="AR29" s="79"/>
+      <c r="AS29" s="79"/>
+      <c r="AT29" s="79"/>
+      <c r="AU29" s="79"/>
+      <c r="AV29" s="79"/>
+      <c r="AW29" s="79"/>
+      <c r="AX29" s="79"/>
+      <c r="AY29" s="79"/>
+      <c r="AZ29" s="79"/>
+      <c r="BA29" s="79"/>
+      <c r="BB29" s="79"/>
+      <c r="BC29" s="79"/>
+      <c r="BD29" s="79"/>
+      <c r="BE29" s="80"/>
     </row>
     <row r="30" spans="1:57" ht="15" customHeight="1">
-      <c r="A30" s="78"/>
-      <c r="B30" s="79"/>
-      <c r="C30" s="79"/>
-      <c r="D30" s="79"/>
-      <c r="E30" s="79"/>
-      <c r="F30" s="79"/>
-      <c r="G30" s="80"/>
+      <c r="A30" s="98"/>
+      <c r="B30" s="99"/>
+      <c r="C30" s="99"/>
+      <c r="D30" s="99"/>
+      <c r="E30" s="99"/>
+      <c r="F30" s="99"/>
+      <c r="G30" s="100"/>
       <c r="H30" s="81"/>
       <c r="I30" s="82"/>
       <c r="J30" s="82"/>
@@ -66066,57 +66069,57 @@
       <c r="M30" s="82"/>
       <c r="N30" s="83"/>
       <c r="O30" s="81"/>
-      <c r="P30" s="84"/>
-      <c r="Q30" s="84"/>
-      <c r="R30" s="84"/>
-      <c r="S30" s="84"/>
-      <c r="T30" s="84"/>
-      <c r="U30" s="84"/>
-      <c r="V30" s="84"/>
-      <c r="W30" s="84"/>
-      <c r="X30" s="84"/>
-      <c r="Y30" s="84"/>
-      <c r="Z30" s="84"/>
-      <c r="AA30" s="84"/>
-      <c r="AB30" s="84"/>
-      <c r="AC30" s="84"/>
-      <c r="AD30" s="84"/>
-      <c r="AE30" s="84"/>
-      <c r="AF30" s="84"/>
-      <c r="AG30" s="84"/>
-      <c r="AH30" s="84"/>
-      <c r="AI30" s="84"/>
-      <c r="AJ30" s="84"/>
-      <c r="AK30" s="84"/>
-      <c r="AL30" s="84"/>
-      <c r="AM30" s="84"/>
-      <c r="AN30" s="84"/>
-      <c r="AO30" s="84"/>
-      <c r="AP30" s="85"/>
-      <c r="AQ30" s="89"/>
-      <c r="AR30" s="84"/>
-      <c r="AS30" s="84"/>
-      <c r="AT30" s="84"/>
-      <c r="AU30" s="84"/>
-      <c r="AV30" s="84"/>
-      <c r="AW30" s="84"/>
-      <c r="AX30" s="84"/>
-      <c r="AY30" s="84"/>
-      <c r="AZ30" s="84"/>
-      <c r="BA30" s="84"/>
-      <c r="BB30" s="84"/>
-      <c r="BC30" s="84"/>
-      <c r="BD30" s="84"/>
-      <c r="BE30" s="90"/>
+      <c r="P30" s="79"/>
+      <c r="Q30" s="79"/>
+      <c r="R30" s="79"/>
+      <c r="S30" s="79"/>
+      <c r="T30" s="79"/>
+      <c r="U30" s="79"/>
+      <c r="V30" s="79"/>
+      <c r="W30" s="79"/>
+      <c r="X30" s="79"/>
+      <c r="Y30" s="79"/>
+      <c r="Z30" s="79"/>
+      <c r="AA30" s="79"/>
+      <c r="AB30" s="79"/>
+      <c r="AC30" s="79"/>
+      <c r="AD30" s="79"/>
+      <c r="AE30" s="79"/>
+      <c r="AF30" s="79"/>
+      <c r="AG30" s="79"/>
+      <c r="AH30" s="79"/>
+      <c r="AI30" s="79"/>
+      <c r="AJ30" s="79"/>
+      <c r="AK30" s="79"/>
+      <c r="AL30" s="79"/>
+      <c r="AM30" s="79"/>
+      <c r="AN30" s="79"/>
+      <c r="AO30" s="79"/>
+      <c r="AP30" s="87"/>
+      <c r="AQ30" s="78"/>
+      <c r="AR30" s="79"/>
+      <c r="AS30" s="79"/>
+      <c r="AT30" s="79"/>
+      <c r="AU30" s="79"/>
+      <c r="AV30" s="79"/>
+      <c r="AW30" s="79"/>
+      <c r="AX30" s="79"/>
+      <c r="AY30" s="79"/>
+      <c r="AZ30" s="79"/>
+      <c r="BA30" s="79"/>
+      <c r="BB30" s="79"/>
+      <c r="BC30" s="79"/>
+      <c r="BD30" s="79"/>
+      <c r="BE30" s="80"/>
     </row>
     <row r="31" spans="1:57" ht="15" customHeight="1">
-      <c r="A31" s="78"/>
-      <c r="B31" s="79"/>
-      <c r="C31" s="79"/>
-      <c r="D31" s="79"/>
-      <c r="E31" s="79"/>
-      <c r="F31" s="79"/>
-      <c r="G31" s="80"/>
+      <c r="A31" s="98"/>
+      <c r="B31" s="99"/>
+      <c r="C31" s="99"/>
+      <c r="D31" s="99"/>
+      <c r="E31" s="99"/>
+      <c r="F31" s="99"/>
+      <c r="G31" s="100"/>
       <c r="H31" s="81"/>
       <c r="I31" s="82"/>
       <c r="J31" s="82"/>
@@ -66125,57 +66128,57 @@
       <c r="M31" s="82"/>
       <c r="N31" s="83"/>
       <c r="O31" s="81"/>
-      <c r="P31" s="84"/>
-      <c r="Q31" s="84"/>
-      <c r="R31" s="84"/>
-      <c r="S31" s="84"/>
-      <c r="T31" s="84"/>
-      <c r="U31" s="84"/>
-      <c r="V31" s="84"/>
-      <c r="W31" s="84"/>
-      <c r="X31" s="84"/>
-      <c r="Y31" s="84"/>
-      <c r="Z31" s="84"/>
-      <c r="AA31" s="84"/>
-      <c r="AB31" s="84"/>
-      <c r="AC31" s="84"/>
-      <c r="AD31" s="84"/>
-      <c r="AE31" s="84"/>
-      <c r="AF31" s="84"/>
-      <c r="AG31" s="84"/>
-      <c r="AH31" s="84"/>
-      <c r="AI31" s="84"/>
-      <c r="AJ31" s="84"/>
-      <c r="AK31" s="84"/>
-      <c r="AL31" s="84"/>
-      <c r="AM31" s="84"/>
-      <c r="AN31" s="84"/>
-      <c r="AO31" s="84"/>
-      <c r="AP31" s="85"/>
-      <c r="AQ31" s="89"/>
-      <c r="AR31" s="84"/>
-      <c r="AS31" s="84"/>
-      <c r="AT31" s="84"/>
-      <c r="AU31" s="84"/>
-      <c r="AV31" s="84"/>
-      <c r="AW31" s="84"/>
-      <c r="AX31" s="84"/>
-      <c r="AY31" s="84"/>
-      <c r="AZ31" s="84"/>
-      <c r="BA31" s="84"/>
-      <c r="BB31" s="84"/>
-      <c r="BC31" s="84"/>
-      <c r="BD31" s="84"/>
-      <c r="BE31" s="90"/>
+      <c r="P31" s="79"/>
+      <c r="Q31" s="79"/>
+      <c r="R31" s="79"/>
+      <c r="S31" s="79"/>
+      <c r="T31" s="79"/>
+      <c r="U31" s="79"/>
+      <c r="V31" s="79"/>
+      <c r="W31" s="79"/>
+      <c r="X31" s="79"/>
+      <c r="Y31" s="79"/>
+      <c r="Z31" s="79"/>
+      <c r="AA31" s="79"/>
+      <c r="AB31" s="79"/>
+      <c r="AC31" s="79"/>
+      <c r="AD31" s="79"/>
+      <c r="AE31" s="79"/>
+      <c r="AF31" s="79"/>
+      <c r="AG31" s="79"/>
+      <c r="AH31" s="79"/>
+      <c r="AI31" s="79"/>
+      <c r="AJ31" s="79"/>
+      <c r="AK31" s="79"/>
+      <c r="AL31" s="79"/>
+      <c r="AM31" s="79"/>
+      <c r="AN31" s="79"/>
+      <c r="AO31" s="79"/>
+      <c r="AP31" s="87"/>
+      <c r="AQ31" s="78"/>
+      <c r="AR31" s="79"/>
+      <c r="AS31" s="79"/>
+      <c r="AT31" s="79"/>
+      <c r="AU31" s="79"/>
+      <c r="AV31" s="79"/>
+      <c r="AW31" s="79"/>
+      <c r="AX31" s="79"/>
+      <c r="AY31" s="79"/>
+      <c r="AZ31" s="79"/>
+      <c r="BA31" s="79"/>
+      <c r="BB31" s="79"/>
+      <c r="BC31" s="79"/>
+      <c r="BD31" s="79"/>
+      <c r="BE31" s="80"/>
     </row>
     <row r="32" spans="1:57" ht="15" customHeight="1">
-      <c r="A32" s="78"/>
-      <c r="B32" s="79"/>
-      <c r="C32" s="79"/>
-      <c r="D32" s="79"/>
-      <c r="E32" s="79"/>
-      <c r="F32" s="79"/>
-      <c r="G32" s="80"/>
+      <c r="A32" s="98"/>
+      <c r="B32" s="99"/>
+      <c r="C32" s="99"/>
+      <c r="D32" s="99"/>
+      <c r="E32" s="99"/>
+      <c r="F32" s="99"/>
+      <c r="G32" s="100"/>
       <c r="H32" s="81"/>
       <c r="I32" s="82"/>
       <c r="J32" s="82"/>
@@ -66184,57 +66187,57 @@
       <c r="M32" s="82"/>
       <c r="N32" s="83"/>
       <c r="O32" s="81"/>
-      <c r="P32" s="84"/>
-      <c r="Q32" s="84"/>
-      <c r="R32" s="84"/>
-      <c r="S32" s="84"/>
-      <c r="T32" s="84"/>
-      <c r="U32" s="84"/>
-      <c r="V32" s="84"/>
-      <c r="W32" s="84"/>
-      <c r="X32" s="84"/>
-      <c r="Y32" s="84"/>
-      <c r="Z32" s="84"/>
-      <c r="AA32" s="84"/>
-      <c r="AB32" s="84"/>
-      <c r="AC32" s="84"/>
-      <c r="AD32" s="84"/>
-      <c r="AE32" s="84"/>
-      <c r="AF32" s="84"/>
-      <c r="AG32" s="84"/>
-      <c r="AH32" s="84"/>
-      <c r="AI32" s="84"/>
-      <c r="AJ32" s="84"/>
-      <c r="AK32" s="84"/>
-      <c r="AL32" s="84"/>
-      <c r="AM32" s="84"/>
-      <c r="AN32" s="84"/>
-      <c r="AO32" s="84"/>
-      <c r="AP32" s="85"/>
-      <c r="AQ32" s="89"/>
-      <c r="AR32" s="84"/>
-      <c r="AS32" s="84"/>
-      <c r="AT32" s="84"/>
-      <c r="AU32" s="84"/>
-      <c r="AV32" s="84"/>
-      <c r="AW32" s="84"/>
-      <c r="AX32" s="84"/>
-      <c r="AY32" s="84"/>
-      <c r="AZ32" s="84"/>
-      <c r="BA32" s="84"/>
-      <c r="BB32" s="84"/>
-      <c r="BC32" s="84"/>
-      <c r="BD32" s="84"/>
-      <c r="BE32" s="90"/>
+      <c r="P32" s="79"/>
+      <c r="Q32" s="79"/>
+      <c r="R32" s="79"/>
+      <c r="S32" s="79"/>
+      <c r="T32" s="79"/>
+      <c r="U32" s="79"/>
+      <c r="V32" s="79"/>
+      <c r="W32" s="79"/>
+      <c r="X32" s="79"/>
+      <c r="Y32" s="79"/>
+      <c r="Z32" s="79"/>
+      <c r="AA32" s="79"/>
+      <c r="AB32" s="79"/>
+      <c r="AC32" s="79"/>
+      <c r="AD32" s="79"/>
+      <c r="AE32" s="79"/>
+      <c r="AF32" s="79"/>
+      <c r="AG32" s="79"/>
+      <c r="AH32" s="79"/>
+      <c r="AI32" s="79"/>
+      <c r="AJ32" s="79"/>
+      <c r="AK32" s="79"/>
+      <c r="AL32" s="79"/>
+      <c r="AM32" s="79"/>
+      <c r="AN32" s="79"/>
+      <c r="AO32" s="79"/>
+      <c r="AP32" s="87"/>
+      <c r="AQ32" s="78"/>
+      <c r="AR32" s="79"/>
+      <c r="AS32" s="79"/>
+      <c r="AT32" s="79"/>
+      <c r="AU32" s="79"/>
+      <c r="AV32" s="79"/>
+      <c r="AW32" s="79"/>
+      <c r="AX32" s="79"/>
+      <c r="AY32" s="79"/>
+      <c r="AZ32" s="79"/>
+      <c r="BA32" s="79"/>
+      <c r="BB32" s="79"/>
+      <c r="BC32" s="79"/>
+      <c r="BD32" s="79"/>
+      <c r="BE32" s="80"/>
     </row>
     <row r="33" spans="1:57" ht="15" customHeight="1">
-      <c r="A33" s="78"/>
-      <c r="B33" s="79"/>
-      <c r="C33" s="79"/>
-      <c r="D33" s="79"/>
-      <c r="E33" s="79"/>
-      <c r="F33" s="79"/>
-      <c r="G33" s="80"/>
+      <c r="A33" s="98"/>
+      <c r="B33" s="99"/>
+      <c r="C33" s="99"/>
+      <c r="D33" s="99"/>
+      <c r="E33" s="99"/>
+      <c r="F33" s="99"/>
+      <c r="G33" s="100"/>
       <c r="H33" s="81"/>
       <c r="I33" s="82"/>
       <c r="J33" s="82"/>
@@ -66243,57 +66246,57 @@
       <c r="M33" s="82"/>
       <c r="N33" s="83"/>
       <c r="O33" s="81"/>
-      <c r="P33" s="84"/>
-      <c r="Q33" s="84"/>
-      <c r="R33" s="84"/>
-      <c r="S33" s="84"/>
-      <c r="T33" s="84"/>
-      <c r="U33" s="84"/>
-      <c r="V33" s="84"/>
-      <c r="W33" s="84"/>
-      <c r="X33" s="84"/>
-      <c r="Y33" s="84"/>
-      <c r="Z33" s="84"/>
-      <c r="AA33" s="84"/>
-      <c r="AB33" s="84"/>
-      <c r="AC33" s="84"/>
-      <c r="AD33" s="84"/>
-      <c r="AE33" s="84"/>
-      <c r="AF33" s="84"/>
-      <c r="AG33" s="84"/>
-      <c r="AH33" s="84"/>
-      <c r="AI33" s="84"/>
-      <c r="AJ33" s="84"/>
-      <c r="AK33" s="84"/>
-      <c r="AL33" s="84"/>
-      <c r="AM33" s="84"/>
-      <c r="AN33" s="84"/>
-      <c r="AO33" s="84"/>
-      <c r="AP33" s="85"/>
-      <c r="AQ33" s="89"/>
-      <c r="AR33" s="84"/>
-      <c r="AS33" s="84"/>
-      <c r="AT33" s="84"/>
-      <c r="AU33" s="84"/>
-      <c r="AV33" s="84"/>
-      <c r="AW33" s="84"/>
-      <c r="AX33" s="84"/>
-      <c r="AY33" s="84"/>
-      <c r="AZ33" s="84"/>
-      <c r="BA33" s="84"/>
-      <c r="BB33" s="84"/>
-      <c r="BC33" s="84"/>
-      <c r="BD33" s="84"/>
-      <c r="BE33" s="90"/>
+      <c r="P33" s="79"/>
+      <c r="Q33" s="79"/>
+      <c r="R33" s="79"/>
+      <c r="S33" s="79"/>
+      <c r="T33" s="79"/>
+      <c r="U33" s="79"/>
+      <c r="V33" s="79"/>
+      <c r="W33" s="79"/>
+      <c r="X33" s="79"/>
+      <c r="Y33" s="79"/>
+      <c r="Z33" s="79"/>
+      <c r="AA33" s="79"/>
+      <c r="AB33" s="79"/>
+      <c r="AC33" s="79"/>
+      <c r="AD33" s="79"/>
+      <c r="AE33" s="79"/>
+      <c r="AF33" s="79"/>
+      <c r="AG33" s="79"/>
+      <c r="AH33" s="79"/>
+      <c r="AI33" s="79"/>
+      <c r="AJ33" s="79"/>
+      <c r="AK33" s="79"/>
+      <c r="AL33" s="79"/>
+      <c r="AM33" s="79"/>
+      <c r="AN33" s="79"/>
+      <c r="AO33" s="79"/>
+      <c r="AP33" s="87"/>
+      <c r="AQ33" s="78"/>
+      <c r="AR33" s="79"/>
+      <c r="AS33" s="79"/>
+      <c r="AT33" s="79"/>
+      <c r="AU33" s="79"/>
+      <c r="AV33" s="79"/>
+      <c r="AW33" s="79"/>
+      <c r="AX33" s="79"/>
+      <c r="AY33" s="79"/>
+      <c r="AZ33" s="79"/>
+      <c r="BA33" s="79"/>
+      <c r="BB33" s="79"/>
+      <c r="BC33" s="79"/>
+      <c r="BD33" s="79"/>
+      <c r="BE33" s="80"/>
     </row>
     <row r="34" spans="1:57" ht="15" customHeight="1">
-      <c r="A34" s="78"/>
-      <c r="B34" s="79"/>
-      <c r="C34" s="79"/>
-      <c r="D34" s="79"/>
-      <c r="E34" s="79"/>
-      <c r="F34" s="79"/>
-      <c r="G34" s="80"/>
+      <c r="A34" s="98"/>
+      <c r="B34" s="99"/>
+      <c r="C34" s="99"/>
+      <c r="D34" s="99"/>
+      <c r="E34" s="99"/>
+      <c r="F34" s="99"/>
+      <c r="G34" s="100"/>
       <c r="H34" s="81"/>
       <c r="I34" s="82"/>
       <c r="J34" s="82"/>
@@ -66302,110 +66305,219 @@
       <c r="M34" s="82"/>
       <c r="N34" s="83"/>
       <c r="O34" s="81"/>
-      <c r="P34" s="84"/>
-      <c r="Q34" s="84"/>
-      <c r="R34" s="84"/>
-      <c r="S34" s="84"/>
-      <c r="T34" s="84"/>
-      <c r="U34" s="84"/>
-      <c r="V34" s="84"/>
-      <c r="W34" s="84"/>
-      <c r="X34" s="84"/>
-      <c r="Y34" s="84"/>
-      <c r="Z34" s="84"/>
-      <c r="AA34" s="84"/>
-      <c r="AB34" s="84"/>
-      <c r="AC34" s="84"/>
-      <c r="AD34" s="84"/>
-      <c r="AE34" s="84"/>
-      <c r="AF34" s="84"/>
-      <c r="AG34" s="84"/>
-      <c r="AH34" s="84"/>
-      <c r="AI34" s="84"/>
-      <c r="AJ34" s="84"/>
-      <c r="AK34" s="84"/>
-      <c r="AL34" s="84"/>
-      <c r="AM34" s="84"/>
-      <c r="AN34" s="84"/>
-      <c r="AO34" s="84"/>
-      <c r="AP34" s="85"/>
-      <c r="AQ34" s="89"/>
-      <c r="AR34" s="84"/>
-      <c r="AS34" s="84"/>
-      <c r="AT34" s="84"/>
-      <c r="AU34" s="84"/>
-      <c r="AV34" s="84"/>
-      <c r="AW34" s="84"/>
-      <c r="AX34" s="84"/>
-      <c r="AY34" s="84"/>
-      <c r="AZ34" s="84"/>
-      <c r="BA34" s="84"/>
-      <c r="BB34" s="84"/>
-      <c r="BC34" s="84"/>
-      <c r="BD34" s="84"/>
-      <c r="BE34" s="90"/>
+      <c r="P34" s="79"/>
+      <c r="Q34" s="79"/>
+      <c r="R34" s="79"/>
+      <c r="S34" s="79"/>
+      <c r="T34" s="79"/>
+      <c r="U34" s="79"/>
+      <c r="V34" s="79"/>
+      <c r="W34" s="79"/>
+      <c r="X34" s="79"/>
+      <c r="Y34" s="79"/>
+      <c r="Z34" s="79"/>
+      <c r="AA34" s="79"/>
+      <c r="AB34" s="79"/>
+      <c r="AC34" s="79"/>
+      <c r="AD34" s="79"/>
+      <c r="AE34" s="79"/>
+      <c r="AF34" s="79"/>
+      <c r="AG34" s="79"/>
+      <c r="AH34" s="79"/>
+      <c r="AI34" s="79"/>
+      <c r="AJ34" s="79"/>
+      <c r="AK34" s="79"/>
+      <c r="AL34" s="79"/>
+      <c r="AM34" s="79"/>
+      <c r="AN34" s="79"/>
+      <c r="AO34" s="79"/>
+      <c r="AP34" s="87"/>
+      <c r="AQ34" s="78"/>
+      <c r="AR34" s="79"/>
+      <c r="AS34" s="79"/>
+      <c r="AT34" s="79"/>
+      <c r="AU34" s="79"/>
+      <c r="AV34" s="79"/>
+      <c r="AW34" s="79"/>
+      <c r="AX34" s="79"/>
+      <c r="AY34" s="79"/>
+      <c r="AZ34" s="79"/>
+      <c r="BA34" s="79"/>
+      <c r="BB34" s="79"/>
+      <c r="BC34" s="79"/>
+      <c r="BD34" s="79"/>
+      <c r="BE34" s="80"/>
     </row>
     <row r="35" spans="1:57" ht="15" customHeight="1" thickBot="1">
-      <c r="A35" s="95"/>
-      <c r="B35" s="96"/>
-      <c r="C35" s="96"/>
-      <c r="D35" s="96"/>
-      <c r="E35" s="96"/>
-      <c r="F35" s="96"/>
-      <c r="G35" s="97"/>
-      <c r="H35" s="91"/>
-      <c r="I35" s="92"/>
-      <c r="J35" s="92"/>
-      <c r="K35" s="92"/>
-      <c r="L35" s="92"/>
-      <c r="M35" s="92"/>
-      <c r="N35" s="93"/>
-      <c r="O35" s="91"/>
-      <c r="P35" s="87"/>
-      <c r="Q35" s="87"/>
-      <c r="R35" s="87"/>
-      <c r="S35" s="87"/>
-      <c r="T35" s="87"/>
-      <c r="U35" s="87"/>
-      <c r="V35" s="87"/>
-      <c r="W35" s="87"/>
-      <c r="X35" s="87"/>
-      <c r="Y35" s="87"/>
-      <c r="Z35" s="87"/>
-      <c r="AA35" s="87"/>
-      <c r="AB35" s="87"/>
-      <c r="AC35" s="87"/>
-      <c r="AD35" s="87"/>
-      <c r="AE35" s="87"/>
-      <c r="AF35" s="87"/>
-      <c r="AG35" s="87"/>
-      <c r="AH35" s="87"/>
-      <c r="AI35" s="87"/>
-      <c r="AJ35" s="87"/>
-      <c r="AK35" s="87"/>
-      <c r="AL35" s="87"/>
-      <c r="AM35" s="87"/>
-      <c r="AN35" s="87"/>
-      <c r="AO35" s="87"/>
-      <c r="AP35" s="94"/>
-      <c r="AQ35" s="86"/>
-      <c r="AR35" s="87"/>
-      <c r="AS35" s="87"/>
-      <c r="AT35" s="87"/>
-      <c r="AU35" s="87"/>
-      <c r="AV35" s="87"/>
-      <c r="AW35" s="87"/>
-      <c r="AX35" s="87"/>
-      <c r="AY35" s="87"/>
-      <c r="AZ35" s="87"/>
-      <c r="BA35" s="87"/>
-      <c r="BB35" s="87"/>
-      <c r="BC35" s="87"/>
-      <c r="BD35" s="87"/>
-      <c r="BE35" s="88"/>
+      <c r="A35" s="119"/>
+      <c r="B35" s="120"/>
+      <c r="C35" s="120"/>
+      <c r="D35" s="120"/>
+      <c r="E35" s="120"/>
+      <c r="F35" s="120"/>
+      <c r="G35" s="121"/>
+      <c r="H35" s="125"/>
+      <c r="I35" s="126"/>
+      <c r="J35" s="126"/>
+      <c r="K35" s="126"/>
+      <c r="L35" s="126"/>
+      <c r="M35" s="126"/>
+      <c r="N35" s="127"/>
+      <c r="O35" s="125"/>
+      <c r="P35" s="123"/>
+      <c r="Q35" s="123"/>
+      <c r="R35" s="123"/>
+      <c r="S35" s="123"/>
+      <c r="T35" s="123"/>
+      <c r="U35" s="123"/>
+      <c r="V35" s="123"/>
+      <c r="W35" s="123"/>
+      <c r="X35" s="123"/>
+      <c r="Y35" s="123"/>
+      <c r="Z35" s="123"/>
+      <c r="AA35" s="123"/>
+      <c r="AB35" s="123"/>
+      <c r="AC35" s="123"/>
+      <c r="AD35" s="123"/>
+      <c r="AE35" s="123"/>
+      <c r="AF35" s="123"/>
+      <c r="AG35" s="123"/>
+      <c r="AH35" s="123"/>
+      <c r="AI35" s="123"/>
+      <c r="AJ35" s="123"/>
+      <c r="AK35" s="123"/>
+      <c r="AL35" s="123"/>
+      <c r="AM35" s="123"/>
+      <c r="AN35" s="123"/>
+      <c r="AO35" s="123"/>
+      <c r="AP35" s="128"/>
+      <c r="AQ35" s="122"/>
+      <c r="AR35" s="123"/>
+      <c r="AS35" s="123"/>
+      <c r="AT35" s="123"/>
+      <c r="AU35" s="123"/>
+      <c r="AV35" s="123"/>
+      <c r="AW35" s="123"/>
+      <c r="AX35" s="123"/>
+      <c r="AY35" s="123"/>
+      <c r="AZ35" s="123"/>
+      <c r="BA35" s="123"/>
+      <c r="BB35" s="123"/>
+      <c r="BC35" s="123"/>
+      <c r="BD35" s="123"/>
+      <c r="BE35" s="124"/>
     </row>
   </sheetData>
   <mergeCells count="133">
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="O19:AP19"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AQ35:BE35"/>
+    <mergeCell ref="AQ33:BE33"/>
+    <mergeCell ref="AQ34:BE34"/>
+    <mergeCell ref="AQ32:BE32"/>
+    <mergeCell ref="AQ31:BE31"/>
+    <mergeCell ref="O27:AP27"/>
+    <mergeCell ref="AQ27:BE27"/>
+    <mergeCell ref="H30:N30"/>
+    <mergeCell ref="O30:AP30"/>
+    <mergeCell ref="AQ30:BE30"/>
+    <mergeCell ref="AQ28:BE28"/>
+    <mergeCell ref="H28:N28"/>
+    <mergeCell ref="O28:AP28"/>
+    <mergeCell ref="H35:N35"/>
+    <mergeCell ref="O35:AP35"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="H33:N33"/>
+    <mergeCell ref="H34:N34"/>
+    <mergeCell ref="O34:AP34"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="O33:AP33"/>
+    <mergeCell ref="O32:AP32"/>
+    <mergeCell ref="H31:N31"/>
+    <mergeCell ref="O31:AP31"/>
+    <mergeCell ref="H27:N27"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="H32:N32"/>
+    <mergeCell ref="H29:N29"/>
+    <mergeCell ref="O29:AP29"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:AP20"/>
+    <mergeCell ref="AQ17:BE17"/>
+    <mergeCell ref="H26:N26"/>
+    <mergeCell ref="O26:AP26"/>
+    <mergeCell ref="AQ26:BE26"/>
+    <mergeCell ref="AQ19:BE19"/>
+    <mergeCell ref="H25:N25"/>
+    <mergeCell ref="H24:N24"/>
+    <mergeCell ref="O24:AP24"/>
+    <mergeCell ref="O25:AP25"/>
+    <mergeCell ref="AQ25:BE25"/>
+    <mergeCell ref="H22:N22"/>
+    <mergeCell ref="AQ24:BE24"/>
+    <mergeCell ref="H23:N23"/>
+    <mergeCell ref="O23:AP23"/>
+    <mergeCell ref="AQ23:BE23"/>
+    <mergeCell ref="AQ20:BE20"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:AP21"/>
+    <mergeCell ref="AQ18:BE18"/>
+    <mergeCell ref="AQ21:BE21"/>
+    <mergeCell ref="O22:AP22"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="H4:N4"/>
+    <mergeCell ref="O4:AP4"/>
+    <mergeCell ref="AQ4:BE4"/>
+    <mergeCell ref="H13:N13"/>
+    <mergeCell ref="O13:AP13"/>
+    <mergeCell ref="AQ13:BE13"/>
+    <mergeCell ref="H14:N14"/>
+    <mergeCell ref="O14:AP14"/>
+    <mergeCell ref="AQ14:BE14"/>
+    <mergeCell ref="AQ16:BE16"/>
+    <mergeCell ref="H15:N15"/>
+    <mergeCell ref="O18:AP18"/>
+    <mergeCell ref="H9:N9"/>
+    <mergeCell ref="O9:AP9"/>
+    <mergeCell ref="AQ9:BE9"/>
+    <mergeCell ref="H10:N10"/>
+    <mergeCell ref="O10:AP10"/>
+    <mergeCell ref="AQ10:BE10"/>
+    <mergeCell ref="H11:N11"/>
+    <mergeCell ref="O11:AP11"/>
+    <mergeCell ref="AQ11:BE11"/>
+    <mergeCell ref="H16:N16"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="O15:AP15"/>
+    <mergeCell ref="A1:BE1"/>
+    <mergeCell ref="H3:N3"/>
+    <mergeCell ref="O3:AP3"/>
+    <mergeCell ref="AQ3:BE3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
     <mergeCell ref="AQ22:BE22"/>
     <mergeCell ref="AQ29:BE29"/>
     <mergeCell ref="H17:N17"/>
@@ -66430,115 +66542,6 @@
     <mergeCell ref="A9:G9"/>
     <mergeCell ref="O16:AP16"/>
     <mergeCell ref="O17:AP17"/>
-    <mergeCell ref="A1:BE1"/>
-    <mergeCell ref="H3:N3"/>
-    <mergeCell ref="O3:AP3"/>
-    <mergeCell ref="AQ3:BE3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="O15:AP15"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="H4:N4"/>
-    <mergeCell ref="O4:AP4"/>
-    <mergeCell ref="AQ4:BE4"/>
-    <mergeCell ref="H13:N13"/>
-    <mergeCell ref="O13:AP13"/>
-    <mergeCell ref="AQ13:BE13"/>
-    <mergeCell ref="H14:N14"/>
-    <mergeCell ref="O14:AP14"/>
-    <mergeCell ref="AQ14:BE14"/>
-    <mergeCell ref="AQ16:BE16"/>
-    <mergeCell ref="H15:N15"/>
-    <mergeCell ref="O18:AP18"/>
-    <mergeCell ref="H9:N9"/>
-    <mergeCell ref="O9:AP9"/>
-    <mergeCell ref="AQ9:BE9"/>
-    <mergeCell ref="H10:N10"/>
-    <mergeCell ref="O10:AP10"/>
-    <mergeCell ref="AQ10:BE10"/>
-    <mergeCell ref="H11:N11"/>
-    <mergeCell ref="O11:AP11"/>
-    <mergeCell ref="AQ11:BE11"/>
-    <mergeCell ref="H16:N16"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:AP20"/>
-    <mergeCell ref="AQ17:BE17"/>
-    <mergeCell ref="H26:N26"/>
-    <mergeCell ref="O26:AP26"/>
-    <mergeCell ref="AQ26:BE26"/>
-    <mergeCell ref="AQ19:BE19"/>
-    <mergeCell ref="H25:N25"/>
-    <mergeCell ref="H24:N24"/>
-    <mergeCell ref="O24:AP24"/>
-    <mergeCell ref="O25:AP25"/>
-    <mergeCell ref="AQ25:BE25"/>
-    <mergeCell ref="H22:N22"/>
-    <mergeCell ref="AQ24:BE24"/>
-    <mergeCell ref="H23:N23"/>
-    <mergeCell ref="O23:AP23"/>
-    <mergeCell ref="AQ23:BE23"/>
-    <mergeCell ref="AQ20:BE20"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:AP21"/>
-    <mergeCell ref="AQ18:BE18"/>
-    <mergeCell ref="AQ21:BE21"/>
-    <mergeCell ref="O22:AP22"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="H33:N33"/>
-    <mergeCell ref="H34:N34"/>
-    <mergeCell ref="O34:AP34"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="O33:AP33"/>
-    <mergeCell ref="O32:AP32"/>
-    <mergeCell ref="H31:N31"/>
-    <mergeCell ref="O31:AP31"/>
-    <mergeCell ref="H27:N27"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="H32:N32"/>
-    <mergeCell ref="H29:N29"/>
-    <mergeCell ref="O29:AP29"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="O19:AP19"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="AQ35:BE35"/>
-    <mergeCell ref="AQ33:BE33"/>
-    <mergeCell ref="AQ34:BE34"/>
-    <mergeCell ref="AQ32:BE32"/>
-    <mergeCell ref="AQ31:BE31"/>
-    <mergeCell ref="O27:AP27"/>
-    <mergeCell ref="AQ27:BE27"/>
-    <mergeCell ref="H30:N30"/>
-    <mergeCell ref="O30:AP30"/>
-    <mergeCell ref="AQ30:BE30"/>
-    <mergeCell ref="AQ28:BE28"/>
-    <mergeCell ref="H28:N28"/>
-    <mergeCell ref="O28:AP28"/>
-    <mergeCell ref="H35:N35"/>
-    <mergeCell ref="O35:AP35"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A20:G20"/>
   </mergeCells>
   <phoneticPr fontId="5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>

--- a/development/MS/spec/MSBB/Panel/MSBBP1210_SloReg.xlsx
+++ b/development/MS/spec/MSBB/Panel/MSBBP1210_SloReg.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\mcframeDEV\development\MS\spec\MSBB\Panel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A3ACB6-1E07-4F37-890D-C0C27F93F8B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60DC8AF2-4383-40FC-BF51-C81F69EE0BB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30855" yWindow="-795" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MSBBP1210" sheetId="1" r:id="rId1"/>
@@ -7272,10 +7272,6 @@
     <phoneticPr fontId="5"/>
   </si>
   <si>
-    <t>MS.MSUAP0030.SloItm</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
     <t>MS.MSUAP0030.SloItmSub1</t>
     <phoneticPr fontId="5"/>
   </si>
@@ -7512,10 +7508,6 @@
     <phoneticPr fontId="5"/>
   </si>
   <si>
-    <t>MAC_ITM_IS_SRCH_TYP.NOT_ASSET3;vmi_flg;trd_unit_qty;trd_cur_upri;tax_cd;tax_nm;tax_rate;tax_typ;inc_tax_flg;dscnt_rsn_cd;dscnt_rsn_nm;cost_upri;bill_crryovr_times;set_itm_grp_no;ship_rqst_dt;ship_rqst_hm;dlv_rqst_dt;dlv_rqst_hm;dlv_day_week_typ;dlv_day_week_typ_nm;sls_schd_dt;dlv_cd;dlv_nm;dlv_sundry_flg;pri_prnt_flg;dlv_lg_grp_cd;dlv_lg_grp_nm;dlv_cntry_cd;dlv_cntry_nm;dlv_zip_cd;dlv_addr1;dlv_addr2;dlv_addr3;dlv_addr4;dlv_tel;dlv_fax;dlv_cntct_dpt;dlv_cntct_psn;prnt_lcl_cd;tdlv_req_flg;dest_cd1;dest_nm1;dest_cd2;dest_nm2;dest_cd3;dest_nm3;tdlv_cd;tdlv_nm;tdlv_sundry_flg;tdlv_lg_grp_cd;tdlv_lg_grp_nm;tdlv_cntry_cd;tdlv_cntry_nm;tdlv_zip_cd;tdlv_addr1;tdlv_addr2;tdlv_addr3;tdlv_addr4;tdlv_tel;tdlv_fax;tdlv_cntct_dpt;tdlv_cntct_psn;via_dlv_typ;via_dlv_typ_nm;sls_cststk_flg;proc_typ;ship_schd_split_typ;alloc_scope_typ;alloc_typ;sls_upri_req_typ;from_slo_reg</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
     <t>itm_is_srch_typ;vmi_flg;trd_unit_qty;trd_cur_upri;tax_cd;tax_nm;tax_rate;tax_typ;inc_tax_flg;dscnt_rsn_cd;dscnt_rsn_nm;cost_upri;bill_crryovr_times;set_itm_grp_no;ship_rqst_dt;ship_rqst_hm;dlv_rqst_dt;dlv_rqst_hm;dlv_day_week_typ;dlv_day_week_typ_nm;sls_schd_dt;dlv_cd;dlv_nm;dlv_sundry_flg;pri_prnt_flg;dlv_lg_grp_cd;dlv_lg_grp_nm;dlv_cntry_cd;dlv_cntry_nm;dlv_zip_cd;dlv_addr1;dlv_addr2;dlv_addr3;dlv_addr4;dlv_tel;dlv_fax;dlv_cntct_dpt;dlv_cntct_psn;prnt_lcl_cd;tdlv_req_flg;dest_cd1;dest_nm1;dest_cd2;dest_nm2;dest_cd3;dest_nm3;tdlv_cd;tdlv_nm;tdlv_sundry_flg;tdlv_lg_grp_cd;tdlv_lg_grp_nm;tdlv_cntry_cd;tdlv_cntry_nm;tdlv_zip_cd;tdlv_addr1;tdlv_addr2;tdlv_addr3;tdlv_addr4;tdlv_tel;tdlv_fax;tdlv_cntct_dpt;tdlv_cntct_psn;via_dlv_typ;via_dlv_typ_nm;sls_cststk_flg;proc_typ;ship_schd_split_typ;alloc_scope_typ;alloc_typ;sls_upri_req_typ;from_slo_reg</t>
     <phoneticPr fontId="5"/>
   </si>
@@ -7789,38 +7781,6 @@
   </si>
   <si>
     <t>false</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>itm_sub1;itm_sub2;itm_sub3;itm_nm;stk_mng_typ;asset_mng_typ_nm;asset_mng_typ;sundry_itm_flg;dscnt_itm_flg;base_unit_cd;base_unit_nm;base_unit_dec_place;base_unit_rnd_typ;trd_unit_nm;trd_unit_cd;trd_unit_dec_place;lot_mng_typ;lot_no_typ;sublot_mng_typ;sublot_no_typ;sno1_mng_typ;slo_sno1_flg;sno1_num_typ;sno2_mng_typ;slo_sno2_flg;sno2_num_typ;sno3_mng_typ;slo_sno3_flg;sno3_num_typ;sno4_mng_typ;slo_sno4_flg;sno4_num_typ;cntry_org_cd;cntry_org_nm;itm_bill_crryovr_times;slo_proc_flg;ver_flg;sls_upri_cng_flg;cst_itm_cd;cst_itm_nm;vmi_flg;iv_itm_nm;trd_cur_upri;wtax_rate;tax_cd;tax_nm;tax_rate;tax_typ;inc_tax_flg;trd_unit_conv_base_qty;trd_unit_conv_qty;trd_unit_qty;dscnt_rsn_cd;dscnt_rsn_nm;cost_upri;bill_crryovr_times;dest_cd1;dest_nm1;dest_cd2;dest_nm2;dest_cd3;dest_nm3;dlv_rqst_dt;dlv_rqst_hm;ship_rqst_dt;ship_rqst_hm;dlv_day_week_typ_nm;dlv_day_week_typ;via_dlv_typ_nm;via_dlv_typ;sls_cststk_flg;gd_nm;gd_cd;ship_schd_split_typ;alloc_scope_typ;alloc_typ;sls_upri_req_typ;def_ship_inst_typ;ship_inst_typ;ship_term_cd;ship_term_nm;def_proc_typ;proc_typ;dlv_cd;dlv_nm;dlv_sundry_flg;pri_prnt_flg;dlv_lg_grp_cd;dlv_lg_grp_nm;dlv_cntry_cd;dlv_cntry_nm;dlv_zip_cd;dlv_addr1;dlv_addr2;dlv_addr3;dlv_addr4;dlv_tel;dlv_fax;dlv_cntct_dpt;dlv_cntct_psn;prnt_lcl_cd;tdlv_req_flg;tdlv_cd;tdlv_nm;tdlv_sundry_flg;tdlv_lg_grp_cd;tdlv_lg_grp_nm;tdlv_cntry_cd;tdlv_cntry_nm;tdlv_zip_cd;tdlv_addr1;tdlv_addr2;tdlv_addr3;tdlv_addr4;tdlv_tel;tdlv_fax;tdlv_cntct_dpt;tdlv_cntct_psn</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>itm_sub1;itm_sub2;itm_sub3;itm_nm;stk_mng_typ;asset_mng_typ_nm;asset_mng_typ;sundry_itm_flg;dscnt_itm_flg;unit_cd;unit_nm;dec_place;rnd_typ;ship_unit_nm;ship_unit_cd;ship_unit_dec_place;lot_mng_typ;lot_no_typ;sublot_mng_typ;sublot_no_typ;sno1_mng_typ;slo_sno1_flg;sno1_num_typ;sno2_mng_typ;slo_sno2_flg;sno2_num_typ;sno3_mng_typ;slo_sno3_flg;sno3_num_typ;sno4_mng_typ;slo_sno4_flg;sno4_num_typ;cntry_org_cd;cntry_org_nm;itm_bill_crryovr_times;slo_proc_flg;ver_flg;sls_upri_cng_flg;bp_itm_cd;bp_itm_nm;vmi_flg;iv_itm_nm;trd_cur_upri;wtax_rate;tax_cd;tax_nm;tax_rate;tax_typ;inc_tax_flg;ship_unit_conv_base_qty;ship_unit_conv_qty;ship_unit_qty;dscnt_rsn_cd;dscnt_rsn_nm;cost_upri;bill_crryovr_times;dest_cd1;dest_nm1;dest_cd2;dest_nm2;dest_cd3;dest_nm3;dlv_rqst_dt;dlv_rqst_hm;ship_rqst_dt;ship_rqst_hm;dlv_day_week_typ_nm;dlv_day_week_typ;via_dlv_typ_nm;via_dlv_typ;sls_cststk_flg;gd_nm;gd_cd;ship_schd_split_typ;alloc_scope_typ;alloc_typ;sls_upri_req_typ;def_ship_inst_typ;ship_inst_typ;ship_term_cd;ship_term_nm;slo_proc_typ;proc_typ;dlv_cd;dlv_nm;dlv_sundry_flg;pri_prnt_flg;dlv_lg_grp_cd;dlv_lg_grp_nm;dlv_cntry_cd;dlv_cntry_nm;dlv_zip_cd;dlv_addr1;dlv_addr2;dlv_addr3;dlv_addr4;dlv_tel;dlv_fax;dlv_cntct_dpt;dlv_cntct_psn;prnt_lcl_cd;tdlv_req_flg;tdlv_cd;tdlv_nm;tdlv_sundry_flg;tdlv_lg_grp_cd;tdlv_lg_grp_nm;tdlv_cntry_cd;tdlv_cntry_nm;tdlv_zip_cd;tdlv_addr1;tdlv_addr2;tdlv_addr3;tdlv_addr4;tdlv_tel;tdlv_fax;tdlv_cntct_dpt;tdlv_cntct_psn</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>itm_sub2;itm_sub3;itm_nm;stk_mng_typ;asset_mng_typ_nm;asset_mng_typ;sundry_itm_flg;dscnt_itm_flg;base_unit_cd;base_unit_nm;base_unit_dec_place;base_unit_rnd_typ;trd_unit_nm;trd_unit_cd;trd_unit_dec_place;lot_mng_typ;lot_no_typ;sublot_mng_typ;sublot_no_typ;sno1_mng_typ;slo_sno1_flg;sno1_num_typ;sno2_mng_typ;slo_sno2_flg;sno2_num_typ;sno3_mng_typ;slo_sno3_flg;sno3_num_typ;sno4_mng_typ;slo_sno4_flg;sno4_num_typ;cntry_org_cd;cntry_org_nm;itm_bill_crryovr_times;slo_proc_flg;ver_flg;sls_upri_cng_flg;cst_itm_cd;cst_itm_nm;vmi_flg;iv_itm_nm;trd_cur_upri;wtax_rate;tax_cd;tax_nm;tax_rate;tax_typ;inc_tax_flg;trd_unit_conv_base_qty;trd_unit_conv_qty;trd_unit_qty;dscnt_rsn_cd;dscnt_rsn_nm;cost_upri;bill_crryovr_times;dest_cd1;dest_nm1;dest_cd2;dest_nm2;dest_cd3;dest_nm3;dlv_rqst_dt;dlv_rqst_hm;ship_rqst_dt;ship_rqst_hm;dlv_day_week_typ_nm;dlv_day_week_typ;via_dlv_typ_nm;via_dlv_typ;sls_cststk_flg;gd_nm;gd_cd;ship_schd_split_typ;alloc_scope_typ;alloc_typ;sls_upri_req_typ;def_ship_inst_typ;ship_inst_typ;ship_term_cd;ship_term_nm;def_proc_typ;proc_typ;dlv_cd;dlv_nm;dlv_sundry_flg;pri_prnt_flg;dlv_lg_grp_cd;dlv_lg_grp_nm;dlv_cntry_cd;dlv_cntry_nm;dlv_zip_cd;dlv_addr1;dlv_addr2;dlv_addr3;dlv_addr4;dlv_tel;dlv_fax;dlv_cntct_dpt;dlv_cntct_psn;prnt_lcl_cd;tdlv_req_flg;tdlv_cd;tdlv_nm;tdlv_sundry_flg;tdlv_lg_grp_cd;tdlv_lg_grp_nm;tdlv_cntry_cd;tdlv_cntry_nm;tdlv_zip_cd;tdlv_addr1;tdlv_addr2;tdlv_addr3;tdlv_addr4;tdlv_tel;tdlv_fax;tdlv_cntct_dpt;tdlv_cntct_psn</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>itm_sub2;itm_sub3;itm_nm;stk_mng_typ;asset_mng_typ_nm;asset_mng_typ;sundry_itm_flg;dscnt_itm_flg;unit_cd;unit_nm;dec_place;rnd_typ;ship_unit_nm;ship_unit_cd;ship_unit_dec_place;lot_mng_typ;lot_no_typ;sublot_mng_typ;sublot_no_typ;sno1_mng_typ;slo_sno1_flg;sno1_num_typ;sno2_mng_typ;slo_sno2_flg;sno2_num_typ;sno3_mng_typ;slo_sno3_flg;sno3_num_typ;sno4_mng_typ;slo_sno4_flg;sno4_num_typ;cntry_org_cd;cntry_org_nm;itm_bill_crryovr_times;slo_proc_flg;ver_flg;sls_upri_cng_flg;bp_itm_cd;bp_itm_nm;vmi_flg;iv_itm_nm;trd_cur_upri;wtax_rate;tax_cd;tax_nm;tax_rate;tax_typ;inc_tax_flg;ship_unit_conv_base_qty;ship_unit_conv_qty;ship_unit_qty;dscnt_rsn_cd;dscnt_rsn_nm;cost_upri;bill_crryovr_times;dest_cd1;dest_nm1;dest_cd2;dest_nm2;dest_cd3;dest_nm3;dlv_rqst_dt;dlv_rqst_hm;ship_rqst_dt;ship_rqst_hm;dlv_day_week_typ_nm;dlv_day_week_typ;via_dlv_typ_nm;via_dlv_typ;sls_cststk_flg;gd_nm;gd_cd;ship_schd_split_typ;alloc_scope_typ;alloc_typ;sls_upri_req_typ;def_ship_inst_typ;ship_inst_typ;ship_term_cd;ship_term_nm;slo_proc_typ;proc_typ;dlv_cd;dlv_nm;dlv_sundry_flg;pri_prnt_flg;dlv_lg_grp_cd;dlv_lg_grp_nm;dlv_cntry_cd;dlv_cntry_nm;dlv_zip_cd;dlv_addr1;dlv_addr2;dlv_addr3;dlv_addr4;dlv_tel;dlv_fax;dlv_cntct_dpt;dlv_cntct_psn;prnt_lcl_cd;tdlv_req_flg;tdlv_cd;tdlv_nm;tdlv_sundry_flg;tdlv_lg_grp_cd;tdlv_lg_grp_nm;tdlv_cntry_cd;tdlv_cntry_nm;tdlv_zip_cd;tdlv_addr1;tdlv_addr2;tdlv_addr3;tdlv_addr4;tdlv_tel;tdlv_fax;tdlv_cntct_dpt;tdlv_cntct_psn</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>itm_sub3;itm_nm;stk_mng_typ;asset_mng_typ_nm;asset_mng_typ;sundry_itm_flg;dscnt_itm_flg;base_unit_cd;base_unit_nm;base_unit_dec_place;base_unit_rnd_typ;trd_unit_nm;trd_unit_cd;trd_unit_dec_place;lot_mng_typ;lot_no_typ;sublot_mng_typ;sublot_no_typ;sno1_mng_typ;slo_sno1_flg;sno1_num_typ;sno2_mng_typ;slo_sno2_flg;sno2_num_typ;sno3_mng_typ;slo_sno3_flg;sno3_num_typ;sno4_mng_typ;slo_sno4_flg;sno4_num_typ;cntry_org_cd;cntry_org_nm;itm_bill_crryovr_times;slo_proc_flg;ver_flg;sls_upri_cng_flg;cst_itm_cd;cst_itm_nm;vmi_flg;iv_itm_nm;trd_cur_upri;wtax_rate;tax_cd;tax_nm;tax_rate;tax_typ;inc_tax_flg;trd_unit_conv_base_qty;trd_unit_conv_qty;trd_unit_qty;dscnt_rsn_cd;dscnt_rsn_nm;cost_upri;bill_crryovr_times;dest_cd1;dest_nm1;dest_cd2;dest_nm2;dest_cd3;dest_nm3;dlv_rqst_dt;dlv_rqst_hm;ship_rqst_dt;ship_rqst_hm;dlv_day_week_typ_nm;dlv_day_week_typ;via_dlv_typ_nm;via_dlv_typ;sls_cststk_flg;gd_nm;gd_cd;ship_schd_split_typ;alloc_scope_typ;alloc_typ;sls_upri_req_typ;def_ship_inst_typ;ship_inst_typ;ship_term_cd;ship_term_nm;def_proc_typ;proc_typ;dlv_cd;dlv_nm;dlv_sundry_flg;pri_prnt_flg;dlv_lg_grp_cd;dlv_lg_grp_nm;dlv_cntry_cd;dlv_cntry_nm;dlv_zip_cd;dlv_addr1;dlv_addr2;dlv_addr3;dlv_addr4;dlv_tel;dlv_fax;dlv_cntct_dpt;dlv_cntct_psn;prnt_lcl_cd;tdlv_req_flg;tdlv_cd;tdlv_nm;tdlv_sundry_flg;tdlv_lg_grp_cd;tdlv_lg_grp_nm;tdlv_cntry_cd;tdlv_cntry_nm;tdlv_zip_cd;tdlv_addr1;tdlv_addr2;tdlv_addr3;tdlv_addr4;tdlv_tel;tdlv_fax;tdlv_cntct_dpt;tdlv_cntct_psn</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>itm_sub3;itm_nm;stk_mng_typ;asset_mng_typ_nm;asset_mng_typ;sundry_itm_flg;dscnt_itm_flg;unit_cd;unit_nm;dec_place;rnd_typ;ship_unit_nm;ship_unit_cd;ship_unit_dec_place;lot_mng_typ;lot_no_typ;sublot_mng_typ;sublot_no_typ;sno1_mng_typ;slo_sno1_flg;sno1_num_typ;sno2_mng_typ;slo_sno2_flg;sno2_num_typ;sno3_mng_typ;slo_sno3_flg;sno3_num_typ;sno4_mng_typ;slo_sno4_flg;sno4_num_typ;cntry_org_cd;cntry_org_nm;itm_bill_crryovr_times;slo_proc_flg;ver_flg;sls_upri_cng_flg;bp_itm_cd;bp_itm_nm;vmi_flg;iv_itm_nm;trd_cur_upri;wtax_rate;tax_cd;tax_nm;tax_rate;tax_typ;inc_tax_flg;ship_unit_conv_base_qty;ship_unit_conv_qty;ship_unit_qty;dscnt_rsn_cd;dscnt_rsn_nm;cost_upri;bill_crryovr_times;dest_cd1;dest_nm1;dest_cd2;dest_nm2;dest_cd3;dest_nm3;dlv_rqst_dt;dlv_rqst_hm;ship_rqst_dt;ship_rqst_hm;dlv_day_week_typ_nm;dlv_day_week_typ;via_dlv_typ_nm;via_dlv_typ;sls_cststk_flg;gd_nm;gd_cd;ship_schd_split_typ;alloc_scope_typ;alloc_typ;sls_upri_req_typ;def_ship_inst_typ;ship_inst_typ;ship_term_cd;ship_term_nm;slo_proc_typ;proc_typ;dlv_cd;dlv_nm;dlv_sundry_flg;pri_prnt_flg;dlv_lg_grp_cd;dlv_lg_grp_nm;dlv_cntry_cd;dlv_cntry_nm;dlv_zip_cd;dlv_addr1;dlv_addr2;dlv_addr3;dlv_addr4;dlv_tel;dlv_fax;dlv_cntct_dpt;dlv_cntct_psn;prnt_lcl_cd;tdlv_req_flg;tdlv_cd;tdlv_nm;tdlv_sundry_flg;tdlv_lg_grp_cd;tdlv_lg_grp_nm;tdlv_cntry_cd;tdlv_cntry_nm;tdlv_zip_cd;tdlv_addr1;tdlv_addr2;tdlv_addr3;tdlv_addr4;tdlv_tel;tdlv_fax;tdlv_cntct_dpt;tdlv_cntct_psn</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>itm_nm;stk_mng_typ;asset_mng_typ_nm;asset_mng_typ;sundry_itm_flg;dscnt_itm_flg;base_unit_cd;base_unit_nm;base_unit_dec_place;base_unit_rnd_typ;trd_unit_nm;trd_unit_cd;trd_unit_dec_place;lot_mng_typ;lot_no_typ;sublot_mng_typ;sublot_no_typ;sno1_mng_typ;slo_sno1_flg;sno1_num_typ;sno2_mng_typ;slo_sno2_flg;sno2_num_typ;sno3_mng_typ;slo_sno3_flg;sno3_num_typ;sno4_mng_typ;slo_sno4_flg;sno4_num_typ;cntry_org_cd;cntry_org_nm;itm_bill_crryovr_times;slo_proc_flg;ver_flg;sls_upri_cng_flg;cst_itm_cd;cst_itm_nm;vmi_flg;iv_itm_nm;trd_cur_upri;wtax_rate;tax_cd;tax_nm;tax_rate;tax_typ;inc_tax_flg;trd_unit_conv_base_qty;trd_unit_conv_qty;trd_unit_qty;dscnt_rsn_cd;dscnt_rsn_nm;cost_upri;bill_crryovr_times;dest_cd1;dest_nm1;dest_cd2;dest_nm2;dest_cd3;dest_nm3;dlv_rqst_dt;dlv_rqst_hm;ship_rqst_dt;ship_rqst_hm;dlv_day_week_typ_nm;dlv_day_week_typ;via_dlv_typ_nm;via_dlv_typ;sls_cststk_flg;gd_nm;gd_cd;ship_schd_split_typ;alloc_scope_typ;alloc_typ;sls_upri_req_typ;def_ship_inst_typ;ship_inst_typ;ship_term_cd;ship_term_nm;def_proc_typ;proc_typ;dlv_cd;dlv_nm;dlv_sundry_flg;pri_prnt_flg;dlv_lg_grp_cd;dlv_lg_grp_nm;dlv_cntry_cd;dlv_cntry_nm;dlv_zip_cd;dlv_addr1;dlv_addr2;dlv_addr3;dlv_addr4;dlv_tel;dlv_fax;dlv_cntct_dpt;dlv_cntct_psn;prnt_lcl_cd;tdlv_req_flg;tdlv_cd;tdlv_nm;tdlv_sundry_flg;tdlv_lg_grp_cd;tdlv_lg_grp_nm;tdlv_cntry_cd;tdlv_cntry_nm;tdlv_zip_cd;tdlv_addr1;tdlv_addr2;tdlv_addr3;tdlv_addr4;tdlv_tel;tdlv_fax;tdlv_cntct_dpt;tdlv_cntct_psn</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>itm_nm;stk_mng_typ;asset_mng_typ_nm;asset_mng_typ;sundry_itm_flg;dscnt_itm_flg;unit_cd;unit_nm;dec_place;rnd_typ;ship_unit_nm;ship_unit_cd;ship_unit_dec_place;lot_mng_typ;lot_no_typ;sublot_mng_typ;sublot_no_typ;sno1_mng_typ;slo_sno1_flg;sno1_num_typ;sno2_mng_typ;slo_sno2_flg;sno2_num_typ;sno3_mng_typ;slo_sno3_flg;sno3_num_typ;sno4_mng_typ;slo_sno4_flg;sno4_num_typ;cntry_org_cd;cntry_org_nm;itm_bill_crryovr_times;slo_proc_flg;ver_flg;sls_upri_cng_flg;bp_itm_cd;bp_itm_nm;vmi_flg;iv_itm_nm;trd_cur_upri;wtax_rate;tax_cd;tax_nm;tax_rate;tax_typ;inc_tax_flg;ship_unit_conv_base_qty;ship_unit_conv_qty;ship_unit_qty;dscnt_rsn_cd;dscnt_rsn_nm;cost_upri;bill_crryovr_times;dest_cd1;dest_nm1;dest_cd2;dest_nm2;dest_cd3;dest_nm3;dlv_rqst_dt;dlv_rqst_hm;ship_rqst_dt;ship_rqst_hm;dlv_day_week_typ_nm;dlv_day_week_typ;via_dlv_typ_nm;via_dlv_typ;sls_cststk_flg;gd_nm;gd_cd;ship_schd_split_typ;alloc_scope_typ;alloc_typ;sls_upri_req_typ;def_ship_inst_typ;ship_inst_typ;ship_term_cd;ship_term_nm;slo_proc_typ;proc_typ;dlv_cd;dlv_nm;dlv_sundry_flg;pri_prnt_flg;dlv_lg_grp_cd;dlv_lg_grp_nm;dlv_cntry_cd;dlv_cntry_nm;dlv_zip_cd;dlv_addr1;dlv_addr2;dlv_addr3;dlv_addr4;dlv_tel;dlv_fax;dlv_cntct_dpt;dlv_cntct_psn;prnt_lcl_cd;tdlv_req_flg;tdlv_cd;tdlv_nm;tdlv_sundry_flg;tdlv_lg_grp_cd;tdlv_lg_grp_nm;tdlv_cntry_cd;tdlv_cntry_nm;tdlv_zip_cd;tdlv_addr1;tdlv_addr2;tdlv_addr3;tdlv_addr4;tdlv_tel;tdlv_fax;tdlv_cntct_dpt;tdlv_cntct_psn</t>
     <phoneticPr fontId="5"/>
   </si>
   <si>
@@ -10049,6 +10009,36 @@
   </si>
   <si>
     <t>Unit price type</t>
+  </si>
+  <si>
+    <t>MAC_ITM_IS_SRCH_TYP.NOT_ASSET3;vmi_flg;trd_unit_qty;trd_cur_upri;tax_cd;tax_nm;tax_rate;tax_typ;inc_tax_flg;dscnt_rsn_cd;dscnt_rsn_nm;cost_upri;bill_crryovr_times;set_itm_grp_no;ship_rqst_dt;ship_rqst_hm;dlv_rqst_dt;dlv_rqst_hm;dlv_day_week_typ;dlv_day_week_typ_nm;sls_schd_dt;dlv_cd;dlv_nm;dlv_sundry_flg;pri_prnt_flg;dlv_lg_grp_cd;dlv_lg_grp_nm;dlv_cntry_cd;dlv_cntry_nm;dlv_zip_cd;dlv_addr1;dlv_addr2;dlv_addr3;dlv_addr4;dlv_tel;dlv_fax;dlv_cntct_dpt;dlv_cntct_psn;prnt_lcl_cd;tdlv_req_flg;dest_cd1;dest_nm1;dest_cd2;dest_nm2;dest_cd3;dest_nm3;tdlv_cd;tdlv_nm;tdlv_sundry_flg;tdlv_lg_grp_cd;tdlv_lg_grp_nm;tdlv_cntry_cd;tdlv_cntry_nm;tdlv_zip_cd;tdlv_addr1;tdlv_addr2;tdlv_addr3;tdlv_addr4;tdlv_tel;tdlv_fax;tdlv_cntct_dpt;tdlv_cntct_psn;via_dlv_typ;via_dlv_typ_nm;sls_cststk_flg;proc_typ;ship_schd_split_typ;alloc_scope_typ;alloc_typ;sls_upri_req_typ;from_slo_reg</t>
+  </si>
+  <si>
+    <t>MS.MSUAP0030.SloItm</t>
+  </si>
+  <si>
+    <t>itm_sub1;itm_sub2;itm_sub3;itm_nm;stk_mng_typ;asset_mng_typ_nm;asset_mng_typ;sundry_itm_flg;dscnt_itm_flg;base_unit_cd;base_unit_nm;base_unit_dec_place;base_unit_rnd_typ;trd_unit_nm;trd_unit_cd;trd_unit_dec_place;lot_mng_typ;lot_no_typ;sublot_mng_typ;sublot_no_typ;sno1_mng_typ;slo_sno1_flg;sno1_num_typ;sno2_mng_typ;slo_sno2_flg;sno2_num_typ;sno3_mng_typ;slo_sno3_flg;sno3_num_typ;sno4_mng_typ;slo_sno4_flg;sno4_num_typ;cntry_org_cd;cntry_org_nm;itm_bill_crryovr_times;slo_proc_flg;ver_flg;sls_upri_cng_flg;cst_itm_cd;cst_itm_nm;vmi_flg;iv_itm_nm;trd_cur_upri;wtax_rate;tax_cd;tax_nm;tax_rate;tax_typ;inc_tax_flg;trd_unit_conv_base_qty;trd_unit_conv_qty;trd_unit_qty;dscnt_rsn_cd;dscnt_rsn_nm;cost_upri;bill_crryovr_times;dest_cd1;dest_nm1;dest_cd2;dest_nm2;dest_cd3;dest_nm3;dlv_rqst_dt;dlv_rqst_hm;ship_rqst_dt;ship_rqst_hm;dlv_day_week_typ_nm;dlv_day_week_typ;via_dlv_typ_nm;via_dlv_typ;sls_cststk_flg;gd_nm;gd_cd;ship_schd_split_typ;alloc_scope_typ;alloc_typ;sls_upri_req_typ;def_ship_inst_typ;ship_inst_typ;ship_term_cd;ship_term_nm;def_proc_typ;proc_typ;dlv_cd;dlv_nm;dlv_sundry_flg;pri_prnt_flg;dlv_lg_grp_cd;dlv_lg_grp_nm;dlv_cntry_cd;dlv_cntry_nm;dlv_zip_cd;dlv_addr1;dlv_addr2;dlv_addr3;dlv_addr4;dlv_tel;dlv_fax;dlv_cntct_dpt;dlv_cntct_psn;prnt_lcl_cd;tdlv_req_flg;tdlv_cd;tdlv_nm;tdlv_sundry_flg;tdlv_lg_grp_cd;tdlv_lg_grp_nm;tdlv_cntry_cd;tdlv_cntry_nm;tdlv_zip_cd;tdlv_addr1;tdlv_addr2;tdlv_addr3;tdlv_addr4;tdlv_tel;tdlv_fax;tdlv_cntct_dpt;tdlv_cntct_psn;list_pri;wl_sale_upri;upri_typ;upri_rate</t>
+  </si>
+  <si>
+    <t>itm_sub2;itm_sub3;itm_nm;stk_mng_typ;asset_mng_typ_nm;asset_mng_typ;sundry_itm_flg;dscnt_itm_flg;base_unit_cd;base_unit_nm;base_unit_dec_place;base_unit_rnd_typ;trd_unit_nm;trd_unit_cd;trd_unit_dec_place;lot_mng_typ;lot_no_typ;sublot_mng_typ;sublot_no_typ;sno1_mng_typ;slo_sno1_flg;sno1_num_typ;sno2_mng_typ;slo_sno2_flg;sno2_num_typ;sno3_mng_typ;slo_sno3_flg;sno3_num_typ;sno4_mng_typ;slo_sno4_flg;sno4_num_typ;cntry_org_cd;cntry_org_nm;itm_bill_crryovr_times;slo_proc_flg;ver_flg;sls_upri_cng_flg;cst_itm_cd;cst_itm_nm;vmi_flg;iv_itm_nm;trd_cur_upri;wtax_rate;tax_cd;tax_nm;tax_rate;tax_typ;inc_tax_flg;trd_unit_conv_base_qty;trd_unit_conv_qty;trd_unit_qty;dscnt_rsn_cd;dscnt_rsn_nm;cost_upri;bill_crryovr_times;dest_cd1;dest_nm1;dest_cd2;dest_nm2;dest_cd3;dest_nm3;dlv_rqst_dt;dlv_rqst_hm;ship_rqst_dt;ship_rqst_hm;dlv_day_week_typ_nm;dlv_day_week_typ;via_dlv_typ_nm;via_dlv_typ;sls_cststk_flg;gd_nm;gd_cd;ship_schd_split_typ;alloc_scope_typ;alloc_typ;sls_upri_req_typ;def_ship_inst_typ;ship_inst_typ;ship_term_cd;ship_term_nm;def_proc_typ;proc_typ;dlv_cd;dlv_nm;dlv_sundry_flg;pri_prnt_flg;dlv_lg_grp_cd;dlv_lg_grp_nm;dlv_cntry_cd;dlv_cntry_nm;dlv_zip_cd;dlv_addr1;dlv_addr2;dlv_addr3;dlv_addr4;dlv_tel;dlv_fax;dlv_cntct_dpt;dlv_cntct_psn;prnt_lcl_cd;tdlv_req_flg;tdlv_cd;tdlv_nm;tdlv_sundry_flg;tdlv_lg_grp_cd;tdlv_lg_grp_nm;tdlv_cntry_cd;tdlv_cntry_nm;tdlv_zip_cd;tdlv_addr1;tdlv_addr2;tdlv_addr3;tdlv_addr4;tdlv_tel;tdlv_fax;tdlv_cntct_dpt;tdlv_cntct_psn;list_pri;wl_sale_upri;upri_typ;upri_rate</t>
+  </si>
+  <si>
+    <t>itm_sub3;itm_nm;stk_mng_typ;asset_mng_typ_nm;asset_mng_typ;sundry_itm_flg;dscnt_itm_flg;base_unit_cd;base_unit_nm;base_unit_dec_place;base_unit_rnd_typ;trd_unit_nm;trd_unit_cd;trd_unit_dec_place;lot_mng_typ;lot_no_typ;sublot_mng_typ;sublot_no_typ;sno1_mng_typ;slo_sno1_flg;sno1_num_typ;sno2_mng_typ;slo_sno2_flg;sno2_num_typ;sno3_mng_typ;slo_sno3_flg;sno3_num_typ;sno4_mng_typ;slo_sno4_flg;sno4_num_typ;cntry_org_cd;cntry_org_nm;itm_bill_crryovr_times;slo_proc_flg;ver_flg;sls_upri_cng_flg;cst_itm_cd;cst_itm_nm;vmi_flg;iv_itm_nm;trd_cur_upri;wtax_rate;tax_cd;tax_nm;tax_rate;tax_typ;inc_tax_flg;trd_unit_conv_base_qty;trd_unit_conv_qty;trd_unit_qty;dscnt_rsn_cd;dscnt_rsn_nm;cost_upri;bill_crryovr_times;dest_cd1;dest_nm1;dest_cd2;dest_nm2;dest_cd3;dest_nm3;dlv_rqst_dt;dlv_rqst_hm;ship_rqst_dt;ship_rqst_hm;dlv_day_week_typ_nm;dlv_day_week_typ;via_dlv_typ_nm;via_dlv_typ;sls_cststk_flg;gd_nm;gd_cd;ship_schd_split_typ;alloc_scope_typ;alloc_typ;sls_upri_req_typ;def_ship_inst_typ;ship_inst_typ;ship_term_cd;ship_term_nm;def_proc_typ;proc_typ;dlv_cd;dlv_nm;dlv_sundry_flg;pri_prnt_flg;dlv_lg_grp_cd;dlv_lg_grp_nm;dlv_cntry_cd;dlv_cntry_nm;dlv_zip_cd;dlv_addr1;dlv_addr2;dlv_addr3;dlv_addr4;dlv_tel;dlv_fax;dlv_cntct_dpt;dlv_cntct_psn;prnt_lcl_cd;tdlv_req_flg;tdlv_cd;tdlv_nm;tdlv_sundry_flg;tdlv_lg_grp_cd;tdlv_lg_grp_nm;tdlv_cntry_cd;tdlv_cntry_nm;tdlv_zip_cd;tdlv_addr1;tdlv_addr2;tdlv_addr3;tdlv_addr4;tdlv_tel;tdlv_fax;tdlv_cntct_dpt;tdlv_cntct_psn;list_pri;wl_sale_upri;upri_typ;upri_rate</t>
+  </si>
+  <si>
+    <t>itm_nm;stk_mng_typ;asset_mng_typ_nm;asset_mng_typ;sundry_itm_flg;dscnt_itm_flg;base_unit_cd;base_unit_nm;base_unit_dec_place;base_unit_rnd_typ;trd_unit_nm;trd_unit_cd;trd_unit_dec_place;lot_mng_typ;lot_no_typ;sublot_mng_typ;sublot_no_typ;sno1_mng_typ;slo_sno1_flg;sno1_num_typ;sno2_mng_typ;slo_sno2_flg;sno2_num_typ;sno3_mng_typ;slo_sno3_flg;sno3_num_typ;sno4_mng_typ;slo_sno4_flg;sno4_num_typ;cntry_org_cd;cntry_org_nm;itm_bill_crryovr_times;slo_proc_flg;ver_flg;sls_upri_cng_flg;cst_itm_cd;cst_itm_nm;vmi_flg;iv_itm_nm;trd_cur_upri;wtax_rate;tax_cd;tax_nm;tax_rate;tax_typ;inc_tax_flg;trd_unit_conv_base_qty;trd_unit_conv_qty;trd_unit_qty;dscnt_rsn_cd;dscnt_rsn_nm;cost_upri;bill_crryovr_times;dest_cd1;dest_nm1;dest_cd2;dest_nm2;dest_cd3;dest_nm3;dlv_rqst_dt;dlv_rqst_hm;ship_rqst_dt;ship_rqst_hm;dlv_day_week_typ_nm;dlv_day_week_typ;via_dlv_typ_nm;via_dlv_typ;sls_cststk_flg;gd_nm;gd_cd;ship_schd_split_typ;alloc_scope_typ;alloc_typ;sls_upri_req_typ;def_ship_inst_typ;ship_inst_typ;ship_term_cd;ship_term_nm;def_proc_typ;proc_typ;dlv_cd;dlv_nm;dlv_sundry_flg;pri_prnt_flg;dlv_lg_grp_cd;dlv_lg_grp_nm;dlv_cntry_cd;dlv_cntry_nm;dlv_zip_cd;dlv_addr1;dlv_addr2;dlv_addr3;dlv_addr4;dlv_tel;dlv_fax;dlv_cntct_dpt;dlv_cntct_psn;prnt_lcl_cd;tdlv_req_flg;tdlv_cd;tdlv_nm;tdlv_sundry_flg;tdlv_lg_grp_cd;tdlv_lg_grp_nm;tdlv_cntry_cd;tdlv_cntry_nm;tdlv_zip_cd;tdlv_addr1;tdlv_addr2;tdlv_addr3;tdlv_addr4;tdlv_tel;tdlv_fax;tdlv_cntct_dpt;tdlv_cntct_psn;list_pri;wl_sale_upri;upri_typ;upri_rate</t>
+  </si>
+  <si>
+    <t>itm_sub1;itm_sub2;itm_sub3;itm_nm;stk_mng_typ;asset_mng_typ_nm;asset_mng_typ;sundry_itm_flg;dscnt_itm_flg;unit_cd;unit_nm;dec_place;rnd_typ;ship_unit_nm;ship_unit_cd;ship_unit_dec_place;lot_mng_typ;lot_no_typ;sublot_mng_typ;sublot_no_typ;sno1_mng_typ;slo_sno1_flg;sno1_num_typ;sno2_mng_typ;slo_sno2_flg;sno2_num_typ;sno3_mng_typ;slo_sno3_flg;sno3_num_typ;sno4_mng_typ;slo_sno4_flg;sno4_num_typ;cntry_org_cd;cntry_org_nm;itm_bill_crryovr_times;slo_proc_flg;ver_flg;sls_upri_cng_flg;bp_itm_cd;bp_itm_nm;vmi_flg;iv_itm_nm;trd_cur_upri;wtax_rate;tax_cd;tax_nm;tax_rate;tax_typ;inc_tax_flg;ship_unit_conv_base_qty;ship_unit_conv_qty;ship_unit_qty;dscnt_rsn_cd;dscnt_rsn_nm;cost_upri;bill_crryovr_times;dest_cd1;dest_nm1;dest_cd2;dest_nm2;dest_cd3;dest_nm3;dlv_rqst_dt;dlv_rqst_hm;ship_rqst_dt;ship_rqst_hm;dlv_day_week_typ_nm;dlv_day_week_typ;via_dlv_typ_nm;via_dlv_typ;sls_cststk_flg;gd_nm;gd_cd;ship_schd_split_typ;alloc_scope_typ;alloc_typ;sls_upri_req_typ;def_ship_inst_typ;ship_inst_typ;ship_term_cd;ship_term_nm;slo_proc_typ;proc_typ;dlv_cd;dlv_nm;dlv_sundry_flg;pri_prnt_flg;dlv_lg_grp_cd;dlv_lg_grp_nm;dlv_cntry_cd;dlv_cntry_nm;dlv_zip_cd;dlv_addr1;dlv_addr2;dlv_addr3;dlv_addr4;dlv_tel;dlv_fax;dlv_cntct_dpt;dlv_cntct_psn;prnt_lcl_cd;tdlv_req_flg;tdlv_cd;tdlv_nm;tdlv_sundry_flg;tdlv_lg_grp_cd;tdlv_lg_grp_nm;tdlv_cntry_cd;tdlv_cntry_nm;tdlv_zip_cd;tdlv_addr1;tdlv_addr2;tdlv_addr3;tdlv_addr4;tdlv_tel;tdlv_fax;tdlv_cntct_dpt;tdlv_cntct_psn;list_pri;wl_sale_upri;upri_typ;upri_rate</t>
+  </si>
+  <si>
+    <t>itm_sub2;itm_sub3;itm_nm;stk_mng_typ;asset_mng_typ_nm;asset_mng_typ;sundry_itm_flg;dscnt_itm_flg;unit_cd;unit_nm;dec_place;rnd_typ;ship_unit_nm;ship_unit_cd;ship_unit_dec_place;lot_mng_typ;lot_no_typ;sublot_mng_typ;sublot_no_typ;sno1_mng_typ;slo_sno1_flg;sno1_num_typ;sno2_mng_typ;slo_sno2_flg;sno2_num_typ;sno3_mng_typ;slo_sno3_flg;sno3_num_typ;sno4_mng_typ;slo_sno4_flg;sno4_num_typ;cntry_org_cd;cntry_org_nm;itm_bill_crryovr_times;slo_proc_flg;ver_flg;sls_upri_cng_flg;bp_itm_cd;bp_itm_nm;vmi_flg;iv_itm_nm;trd_cur_upri;wtax_rate;tax_cd;tax_nm;tax_rate;tax_typ;inc_tax_flg;ship_unit_conv_base_qty;ship_unit_conv_qty;ship_unit_qty;dscnt_rsn_cd;dscnt_rsn_nm;cost_upri;bill_crryovr_times;dest_cd1;dest_nm1;dest_cd2;dest_nm2;dest_cd3;dest_nm3;dlv_rqst_dt;dlv_rqst_hm;ship_rqst_dt;ship_rqst_hm;dlv_day_week_typ_nm;dlv_day_week_typ;via_dlv_typ_nm;via_dlv_typ;sls_cststk_flg;gd_nm;gd_cd;ship_schd_split_typ;alloc_scope_typ;alloc_typ;sls_upri_req_typ;def_ship_inst_typ;ship_inst_typ;ship_term_cd;ship_term_nm;slo_proc_typ;proc_typ;dlv_cd;dlv_nm;dlv_sundry_flg;pri_prnt_flg;dlv_lg_grp_cd;dlv_lg_grp_nm;dlv_cntry_cd;dlv_cntry_nm;dlv_zip_cd;dlv_addr1;dlv_addr2;dlv_addr3;dlv_addr4;dlv_tel;dlv_fax;dlv_cntct_dpt;dlv_cntct_psn;prnt_lcl_cd;tdlv_req_flg;tdlv_cd;tdlv_nm;tdlv_sundry_flg;tdlv_lg_grp_cd;tdlv_lg_grp_nm;tdlv_cntry_cd;tdlv_cntry_nm;tdlv_zip_cd;tdlv_addr1;tdlv_addr2;tdlv_addr3;tdlv_addr4;tdlv_tel;tdlv_fax;tdlv_cntct_dpt;tdlv_cntct_psn;list_pri;wl_sale_upri;upri_typ;upri_rate</t>
+  </si>
+  <si>
+    <t>itm_sub3;itm_nm;stk_mng_typ;asset_mng_typ_nm;asset_mng_typ;sundry_itm_flg;dscnt_itm_flg;unit_cd;unit_nm;dec_place;rnd_typ;ship_unit_nm;ship_unit_cd;ship_unit_dec_place;lot_mng_typ;lot_no_typ;sublot_mng_typ;sublot_no_typ;sno1_mng_typ;slo_sno1_flg;sno1_num_typ;sno2_mng_typ;slo_sno2_flg;sno2_num_typ;sno3_mng_typ;slo_sno3_flg;sno3_num_typ;sno4_mng_typ;slo_sno4_flg;sno4_num_typ;cntry_org_cd;cntry_org_nm;itm_bill_crryovr_times;slo_proc_flg;ver_flg;sls_upri_cng_flg;bp_itm_cd;bp_itm_nm;vmi_flg;iv_itm_nm;trd_cur_upri;wtax_rate;tax_cd;tax_nm;tax_rate;tax_typ;inc_tax_flg;ship_unit_conv_base_qty;ship_unit_conv_qty;ship_unit_qty;dscnt_rsn_cd;dscnt_rsn_nm;cost_upri;bill_crryovr_times;dest_cd1;dest_nm1;dest_cd2;dest_nm2;dest_cd3;dest_nm3;dlv_rqst_dt;dlv_rqst_hm;ship_rqst_dt;ship_rqst_hm;dlv_day_week_typ_nm;dlv_day_week_typ;via_dlv_typ_nm;via_dlv_typ;sls_cststk_flg;gd_nm;gd_cd;ship_schd_split_typ;alloc_scope_typ;alloc_typ;sls_upri_req_typ;def_ship_inst_typ;ship_inst_typ;ship_term_cd;ship_term_nm;slo_proc_typ;proc_typ;dlv_cd;dlv_nm;dlv_sundry_flg;pri_prnt_flg;dlv_lg_grp_cd;dlv_lg_grp_nm;dlv_cntry_cd;dlv_cntry_nm;dlv_zip_cd;dlv_addr1;dlv_addr2;dlv_addr3;dlv_addr4;dlv_tel;dlv_fax;dlv_cntct_dpt;dlv_cntct_psn;prnt_lcl_cd;tdlv_req_flg;tdlv_cd;tdlv_nm;tdlv_sundry_flg;tdlv_lg_grp_cd;tdlv_lg_grp_nm;tdlv_cntry_cd;tdlv_cntry_nm;tdlv_zip_cd;tdlv_addr1;tdlv_addr2;tdlv_addr3;tdlv_addr4;tdlv_tel;tdlv_fax;tdlv_cntct_dpt;tdlv_cntct_psn;list_pri;wl_sale_upri;upri_typ;upri_rate</t>
+  </si>
+  <si>
+    <t>itm_nm;stk_mng_typ;asset_mng_typ_nm;asset_mng_typ;sundry_itm_flg;dscnt_itm_flg;unit_cd;unit_nm;dec_place;rnd_typ;ship_unit_nm;ship_unit_cd;ship_unit_dec_place;lot_mng_typ;lot_no_typ;sublot_mng_typ;sublot_no_typ;sno1_mng_typ;slo_sno1_flg;sno1_num_typ;sno2_mng_typ;slo_sno2_flg;sno2_num_typ;sno3_mng_typ;slo_sno3_flg;sno3_num_typ;sno4_mng_typ;slo_sno4_flg;sno4_num_typ;cntry_org_cd;cntry_org_nm;itm_bill_crryovr_times;slo_proc_flg;ver_flg;sls_upri_cng_flg;bp_itm_cd;bp_itm_nm;vmi_flg;iv_itm_nm;trd_cur_upri;wtax_rate;tax_cd;tax_nm;tax_rate;tax_typ;inc_tax_flg;ship_unit_conv_base_qty;ship_unit_conv_qty;ship_unit_qty;dscnt_rsn_cd;dscnt_rsn_nm;cost_upri;bill_crryovr_times;dest_cd1;dest_nm1;dest_cd2;dest_nm2;dest_cd3;dest_nm3;dlv_rqst_dt;dlv_rqst_hm;ship_rqst_dt;ship_rqst_hm;dlv_day_week_typ_nm;dlv_day_week_typ;via_dlv_typ_nm;via_dlv_typ;sls_cststk_flg;gd_nm;gd_cd;ship_schd_split_typ;alloc_scope_typ;alloc_typ;sls_upri_req_typ;def_ship_inst_typ;ship_inst_typ;ship_term_cd;ship_term_nm;slo_proc_typ;proc_typ;dlv_cd;dlv_nm;dlv_sundry_flg;pri_prnt_flg;dlv_lg_grp_cd;dlv_lg_grp_nm;dlv_cntry_cd;dlv_cntry_nm;dlv_zip_cd;dlv_addr1;dlv_addr2;dlv_addr3;dlv_addr4;dlv_tel;dlv_fax;dlv_cntct_dpt;dlv_cntct_psn;prnt_lcl_cd;tdlv_req_flg;tdlv_cd;tdlv_nm;tdlv_sundry_flg;tdlv_lg_grp_cd;tdlv_lg_grp_nm;tdlv_cntry_cd;tdlv_cntry_nm;tdlv_zip_cd;tdlv_addr1;tdlv_addr2;tdlv_addr3;tdlv_addr4;tdlv_tel;tdlv_fax;tdlv_cntct_dpt;tdlv_cntct_psn;list_pri;wl_sale_upri;upri_typ;upri_rate</t>
   </si>
 </sst>
 </file>
@@ -12294,7 +12284,7 @@
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="30" t="s">
-        <v>1845</v>
+        <v>1835</v>
       </c>
       <c r="E2" s="40" t="s">
         <v>1280</v>
@@ -12736,29 +12726,29 @@
       <c r="B8" s="25"/>
       <c r="C8" s="25"/>
       <c r="D8" s="40" t="s">
-        <v>1846</v>
+        <v>1836</v>
       </c>
       <c r="E8" s="40" t="s">
         <v>1501</v>
       </c>
       <c r="F8" s="40" t="s">
-        <v>1847</v>
+        <v>1837</v>
       </c>
       <c r="G8" s="46" t="s">
-        <v>1848</v>
+        <v>1838</v>
       </c>
       <c r="H8" s="40"/>
       <c r="I8" s="40" t="s">
-        <v>1849</v>
+        <v>1839</v>
       </c>
       <c r="J8" s="40" t="s">
-        <v>1850</v>
+        <v>1840</v>
       </c>
       <c r="K8" s="40" t="s">
-        <v>1851</v>
+        <v>1841</v>
       </c>
       <c r="L8" s="40" t="s">
-        <v>1852</v>
+        <v>1842</v>
       </c>
       <c r="M8" s="43" t="s">
         <v>1502</v>
@@ -12773,12 +12763,12 @@
         <v>1505</v>
       </c>
       <c r="Q8" s="66" t="s">
-        <v>1853</v>
+        <v>1843</v>
       </c>
       <c r="R8" s="67"/>
       <c r="S8" s="68"/>
       <c r="T8" s="7" t="s">
-        <v>1854</v>
+        <v>1844</v>
       </c>
       <c r="U8" s="25" t="s">
         <v>99</v>
@@ -12790,7 +12780,7 @@
         <v>101</v>
       </c>
       <c r="X8" s="25" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="Y8" s="19"/>
       <c r="Z8" s="25" t="s">
@@ -12868,7 +12858,7 @@
       </c>
       <c r="AY8" s="18"/>
       <c r="AZ8" s="19" t="s">
-        <v>1866</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="9" spans="1:52" s="59" customFormat="1" ht="60" customHeight="1">
@@ -12878,37 +12868,37 @@
       <c r="B9" s="25"/>
       <c r="C9" s="25"/>
       <c r="D9" s="40" t="s">
-        <v>1855</v>
+        <v>1845</v>
       </c>
       <c r="E9" s="46" t="s">
-        <v>1856</v>
+        <v>1846</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>1857</v>
+        <v>1847</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>1858</v>
+        <v>1848</v>
       </c>
       <c r="H9" s="58" t="s">
-        <v>1859</v>
+        <v>1849</v>
       </c>
       <c r="I9" s="40" t="s">
-        <v>1860</v>
+        <v>1850</v>
       </c>
       <c r="J9" s="58" t="s">
         <v>1506</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>1861</v>
+        <v>1851</v>
       </c>
       <c r="L9" s="40" t="s">
-        <v>1862</v>
+        <v>1852</v>
       </c>
       <c r="M9" s="40" t="s">
-        <v>1863</v>
+        <v>1853</v>
       </c>
       <c r="N9" s="40" t="s">
-        <v>1864</v>
+        <v>1854</v>
       </c>
       <c r="O9" s="40" t="s">
         <v>1277</v>
@@ -12981,10 +12971,10 @@
         <v>1299</v>
       </c>
       <c r="AY9" s="20" t="s">
-        <v>1865</v>
+        <v>1855</v>
       </c>
       <c r="AZ9" s="19" t="s">
-        <v>1867</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="10" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
@@ -13027,40 +13017,40 @@
       <c r="AK10" s="3"/>
       <c r="AL10" s="3"/>
       <c r="AM10" s="40" t="s">
-        <v>2255</v>
+        <v>2245</v>
       </c>
       <c r="AN10" s="40" t="s">
-        <v>2256</v>
+        <v>2246</v>
       </c>
       <c r="AO10" s="40" t="s">
-        <v>2255</v>
+        <v>2245</v>
       </c>
       <c r="AP10" s="40" t="s">
-        <v>2256</v>
+        <v>2246</v>
       </c>
       <c r="AQ10" s="40" t="s">
-        <v>2255</v>
+        <v>2245</v>
       </c>
       <c r="AR10" s="40" t="s">
-        <v>2256</v>
+        <v>2246</v>
       </c>
       <c r="AS10" s="40" t="s">
-        <v>2255</v>
+        <v>2245</v>
       </c>
       <c r="AT10" s="40" t="s">
-        <v>2256</v>
+        <v>2246</v>
       </c>
       <c r="AU10" s="40" t="s">
-        <v>2255</v>
+        <v>2245</v>
       </c>
       <c r="AV10" s="40" t="s">
-        <v>2256</v>
+        <v>2246</v>
       </c>
       <c r="AW10" s="40" t="s">
-        <v>2255</v>
+        <v>2245</v>
       </c>
       <c r="AX10" s="40" t="s">
-        <v>2256</v>
+        <v>2246</v>
       </c>
       <c r="AY10" s="7"/>
       <c r="AZ10" s="20"/>
@@ -13086,7 +13076,7 @@
         <v>31</v>
       </c>
       <c r="J11" s="33" t="s">
-        <v>1868</v>
+        <v>1858</v>
       </c>
       <c r="K11" s="33" t="s">
         <v>22</v>
@@ -13176,7 +13166,7 @@
         <v>31</v>
       </c>
       <c r="J13" s="33" t="s">
-        <v>1869</v>
+        <v>1859</v>
       </c>
       <c r="K13" s="33" t="s">
         <v>22</v>
@@ -13243,7 +13233,7 @@
         <v>55</v>
       </c>
       <c r="E14" s="28" t="s">
-        <v>1870</v>
+        <v>1860</v>
       </c>
       <c r="F14" s="27" t="s">
         <v>89</v>
@@ -13332,7 +13322,7 @@
         <v>860</v>
       </c>
       <c r="E15" s="37" t="s">
-        <v>1871</v>
+        <v>1861</v>
       </c>
       <c r="F15" s="25" t="s">
         <v>861</v>
@@ -13421,7 +13411,7 @@
         <v>862</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>1872</v>
+        <v>1862</v>
       </c>
       <c r="F16" s="25" t="s">
         <v>863</v>
@@ -13516,7 +13506,7 @@
         <v>865</v>
       </c>
       <c r="E17" s="37" t="s">
-        <v>1873</v>
+        <v>1863</v>
       </c>
       <c r="F17" s="25" t="s">
         <v>866</v>
@@ -13607,7 +13597,7 @@
         <v>867</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>1874</v>
+        <v>1864</v>
       </c>
       <c r="F18" s="25" t="s">
         <v>868</v>
@@ -13698,7 +13688,7 @@
         <v>636</v>
       </c>
       <c r="E19" s="37" t="s">
-        <v>1875</v>
+        <v>1865</v>
       </c>
       <c r="F19" s="25" t="s">
         <v>48</v>
@@ -13789,7 +13779,7 @@
         <v>455</v>
       </c>
       <c r="E20" s="37" t="s">
-        <v>1869</v>
+        <v>1859</v>
       </c>
       <c r="F20" s="25" t="s">
         <v>87</v>
@@ -13813,7 +13803,7 @@
       <c r="O20" s="25"/>
       <c r="P20" s="25"/>
       <c r="Q20" s="25" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="R20" s="25"/>
       <c r="S20" s="25"/>
@@ -13884,7 +13874,7 @@
         <v>456</v>
       </c>
       <c r="E21" s="37" t="s">
-        <v>1869</v>
+        <v>1859</v>
       </c>
       <c r="F21" s="25" t="s">
         <v>87</v>
@@ -13908,7 +13898,7 @@
       <c r="O21" s="25"/>
       <c r="P21" s="25"/>
       <c r="Q21" s="25" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="R21" s="25"/>
       <c r="S21" s="25"/>
@@ -14059,7 +14049,7 @@
         <v>94</v>
       </c>
       <c r="E24" s="28" t="s">
-        <v>1876</v>
+        <v>1866</v>
       </c>
       <c r="F24" s="27" t="s">
         <v>95</v>
@@ -14124,7 +14114,7 @@
         <v>96</v>
       </c>
       <c r="E25" s="37" t="s">
-        <v>1877</v>
+        <v>1867</v>
       </c>
       <c r="F25" s="25" t="s">
         <v>97</v>
@@ -14283,7 +14273,7 @@
         <v>57</v>
       </c>
       <c r="E28" s="28" t="s">
-        <v>1878</v>
+        <v>1868</v>
       </c>
       <c r="F28" s="27" t="s">
         <v>59</v>
@@ -14384,7 +14374,7 @@
         <v>58</v>
       </c>
       <c r="E29" s="37" t="s">
-        <v>1879</v>
+        <v>1869</v>
       </c>
       <c r="F29" s="25" t="s">
         <v>61</v>
@@ -14475,7 +14465,7 @@
         <v>672</v>
       </c>
       <c r="E30" s="37" t="s">
-        <v>1880</v>
+        <v>1870</v>
       </c>
       <c r="F30" s="25" t="s">
         <v>68</v>
@@ -14568,7 +14558,7 @@
         <v>1507</v>
       </c>
       <c r="E31" s="37" t="s">
-        <v>1873</v>
+        <v>1863</v>
       </c>
       <c r="F31" s="25" t="s">
         <v>1508</v>
@@ -14657,7 +14647,7 @@
         <v>354</v>
       </c>
       <c r="E32" s="37" t="s">
-        <v>1881</v>
+        <v>1871</v>
       </c>
       <c r="F32" s="25" t="s">
         <v>276</v>
@@ -14756,7 +14746,7 @@
         <v>355</v>
       </c>
       <c r="E33" s="37" t="s">
-        <v>1882</v>
+        <v>1872</v>
       </c>
       <c r="F33" s="25" t="s">
         <v>353</v>
@@ -14849,7 +14839,7 @@
         <v>636</v>
       </c>
       <c r="E34" s="37" t="s">
-        <v>1875</v>
+        <v>1865</v>
       </c>
       <c r="F34" s="25" t="s">
         <v>48</v>
@@ -14940,7 +14930,7 @@
         <v>598</v>
       </c>
       <c r="E35" s="37" t="s">
-        <v>1883</v>
+        <v>1873</v>
       </c>
       <c r="F35" s="25" t="s">
         <v>366</v>
@@ -15035,7 +15025,7 @@
         <v>668</v>
       </c>
       <c r="E36" s="37" t="s">
-        <v>1884</v>
+        <v>1874</v>
       </c>
       <c r="F36" s="25" t="s">
         <v>367</v>
@@ -15134,7 +15124,7 @@
         <v>369</v>
       </c>
       <c r="E37" s="37" t="s">
-        <v>1885</v>
+        <v>1875</v>
       </c>
       <c r="F37" s="25" t="s">
         <v>368</v>
@@ -15223,7 +15213,7 @@
         <v>148</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>1886</v>
+        <v>1876</v>
       </c>
       <c r="F38" s="25" t="s">
         <v>140</v>
@@ -15290,17 +15280,17 @@
       </c>
       <c r="AM38" s="25"/>
       <c r="AN38" s="25" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="AO38" s="25"/>
       <c r="AP38" s="25"/>
       <c r="AQ38" s="25"/>
       <c r="AR38" s="25" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="AS38" s="25"/>
       <c r="AT38" s="25" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="AU38" s="25"/>
       <c r="AV38" s="25"/>
@@ -15318,7 +15308,7 @@
         <v>1189</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>1887</v>
+        <v>1877</v>
       </c>
       <c r="F39" s="25" t="s">
         <v>141</v>
@@ -15409,7 +15399,7 @@
         <v>149</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>1888</v>
+        <v>1878</v>
       </c>
       <c r="F40" s="25" t="s">
         <v>142</v>
@@ -15476,17 +15466,17 @@
       </c>
       <c r="AM40" s="25"/>
       <c r="AN40" s="25" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="AO40" s="25"/>
       <c r="AP40" s="25"/>
       <c r="AQ40" s="25"/>
       <c r="AR40" s="25" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="AS40" s="25"/>
       <c r="AT40" s="25" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="AU40" s="25"/>
       <c r="AV40" s="25"/>
@@ -15504,7 +15494,7 @@
         <v>852</v>
       </c>
       <c r="E41" s="37" t="s">
-        <v>1889</v>
+        <v>1879</v>
       </c>
       <c r="F41" s="25" t="s">
         <v>143</v>
@@ -15599,7 +15589,7 @@
         <v>150</v>
       </c>
       <c r="E42" s="37" t="s">
-        <v>1890</v>
+        <v>1880</v>
       </c>
       <c r="F42" s="25" t="s">
         <v>144</v>
@@ -15664,17 +15654,17 @@
       </c>
       <c r="AM42" s="25"/>
       <c r="AN42" s="25" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="AO42" s="25"/>
       <c r="AP42" s="25"/>
       <c r="AQ42" s="25"/>
       <c r="AR42" s="25" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="AS42" s="25"/>
       <c r="AT42" s="25" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="AU42" s="25"/>
       <c r="AV42" s="25"/>
@@ -15692,7 +15682,7 @@
         <v>151</v>
       </c>
       <c r="E43" s="37" t="s">
-        <v>1891</v>
+        <v>1881</v>
       </c>
       <c r="F43" s="25" t="s">
         <v>154</v>
@@ -15759,17 +15749,17 @@
       </c>
       <c r="AM43" s="25"/>
       <c r="AN43" s="25" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="AO43" s="25"/>
       <c r="AP43" s="25"/>
       <c r="AQ43" s="25"/>
       <c r="AR43" s="25" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="AS43" s="25"/>
       <c r="AT43" s="25" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="AU43" s="25"/>
       <c r="AV43" s="25"/>
@@ -15787,7 +15777,7 @@
         <v>324</v>
       </c>
       <c r="E44" s="37" t="s">
-        <v>1892</v>
+        <v>1882</v>
       </c>
       <c r="F44" s="25" t="s">
         <v>155</v>
@@ -15882,7 +15872,7 @@
         <v>438</v>
       </c>
       <c r="E45" s="37" t="s">
-        <v>1893</v>
+        <v>1883</v>
       </c>
       <c r="F45" s="25" t="s">
         <v>713</v>
@@ -15949,7 +15939,7 @@
       </c>
       <c r="AM45" s="25"/>
       <c r="AN45" s="25" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="AO45" s="25"/>
       <c r="AP45" s="25"/>
@@ -17074,7 +17064,7 @@
         <v>1157</v>
       </c>
       <c r="E64" s="37" t="s">
-        <v>1894</v>
+        <v>1884</v>
       </c>
       <c r="F64" s="25" t="s">
         <v>1159</v>
@@ -17161,7 +17151,7 @@
         <v>1155</v>
       </c>
       <c r="E65" s="37" t="s">
-        <v>1895</v>
+        <v>1885</v>
       </c>
       <c r="F65" s="25" t="s">
         <v>900</v>
@@ -17248,7 +17238,7 @@
         <v>192</v>
       </c>
       <c r="E66" s="37" t="s">
-        <v>1896</v>
+        <v>1886</v>
       </c>
       <c r="F66" s="25" t="s">
         <v>176</v>
@@ -17287,7 +17277,7 @@
         <v>804</v>
       </c>
       <c r="X66" s="25" t="s">
-        <v>1662</v>
+        <v>1660</v>
       </c>
       <c r="Z66" s="25" t="s">
         <v>25</v>
@@ -17349,7 +17339,7 @@
         <v>193</v>
       </c>
       <c r="E67" s="37" t="s">
-        <v>1897</v>
+        <v>1887</v>
       </c>
       <c r="F67" s="25" t="s">
         <v>167</v>
@@ -17376,7 +17366,7 @@
       <c r="V67" s="25"/>
       <c r="W67" s="25"/>
       <c r="X67" s="25" t="s">
-        <v>1662</v>
+        <v>1660</v>
       </c>
       <c r="Z67" s="25" t="s">
         <v>25</v>
@@ -17438,7 +17428,7 @@
         <v>194</v>
       </c>
       <c r="E68" s="37" t="s">
-        <v>1898</v>
+        <v>1888</v>
       </c>
       <c r="F68" s="25" t="s">
         <v>177</v>
@@ -17477,7 +17467,7 @@
         <v>804</v>
       </c>
       <c r="X68" s="25" t="s">
-        <v>1663</v>
+        <v>1661</v>
       </c>
       <c r="Z68" s="25" t="s">
         <v>25</v>
@@ -17539,7 +17529,7 @@
         <v>195</v>
       </c>
       <c r="E69" s="37" t="s">
-        <v>1899</v>
+        <v>1889</v>
       </c>
       <c r="F69" s="25" t="s">
         <v>169</v>
@@ -17566,7 +17556,7 @@
       <c r="V69" s="25"/>
       <c r="W69" s="25"/>
       <c r="X69" s="25" t="s">
-        <v>1663</v>
+        <v>1661</v>
       </c>
       <c r="Z69" s="25" t="s">
         <v>25</v>
@@ -17628,7 +17618,7 @@
         <v>196</v>
       </c>
       <c r="E70" s="37" t="s">
-        <v>1900</v>
+        <v>1890</v>
       </c>
       <c r="F70" s="25" t="s">
         <v>178</v>
@@ -17667,7 +17657,7 @@
         <v>804</v>
       </c>
       <c r="X70" s="25" t="s">
-        <v>1664</v>
+        <v>1662</v>
       </c>
       <c r="Z70" s="25" t="s">
         <v>25</v>
@@ -17729,7 +17719,7 @@
         <v>197</v>
       </c>
       <c r="E71" s="37" t="s">
-        <v>1901</v>
+        <v>1891</v>
       </c>
       <c r="F71" s="25" t="s">
         <v>171</v>
@@ -17756,7 +17746,7 @@
       <c r="V71" s="25"/>
       <c r="W71" s="25"/>
       <c r="X71" s="25" t="s">
-        <v>1664</v>
+        <v>1662</v>
       </c>
       <c r="Z71" s="25" t="s">
         <v>25</v>
@@ -17906,7 +17896,7 @@
         <v>740</v>
       </c>
       <c r="E73" s="37" t="s">
-        <v>1902</v>
+        <v>1892</v>
       </c>
       <c r="F73" s="25" t="s">
         <v>758</v>
@@ -17981,7 +17971,7 @@
         <v>741</v>
       </c>
       <c r="E74" s="37" t="s">
-        <v>1903</v>
+        <v>1893</v>
       </c>
       <c r="F74" s="25" t="s">
         <v>759</v>
@@ -18044,7 +18034,7 @@
         <v>742</v>
       </c>
       <c r="E75" s="37" t="s">
-        <v>1904</v>
+        <v>1894</v>
       </c>
       <c r="F75" s="25" t="s">
         <v>797</v>
@@ -18192,7 +18182,7 @@
         <v>806</v>
       </c>
       <c r="E77" s="37" t="s">
-        <v>1905</v>
+        <v>1895</v>
       </c>
       <c r="F77" s="25" t="s">
         <v>760</v>
@@ -18255,7 +18245,7 @@
         <v>743</v>
       </c>
       <c r="E78" s="37" t="s">
-        <v>1906</v>
+        <v>1896</v>
       </c>
       <c r="F78" s="25" t="s">
         <v>768</v>
@@ -18320,7 +18310,7 @@
         <v>744</v>
       </c>
       <c r="E79" s="37" t="s">
-        <v>1907</v>
+        <v>1897</v>
       </c>
       <c r="F79" s="25" t="s">
         <v>769</v>
@@ -18383,7 +18373,7 @@
         <v>1146</v>
       </c>
       <c r="E80" s="37" t="s">
-        <v>1908</v>
+        <v>1898</v>
       </c>
       <c r="F80" s="25" t="s">
         <v>964</v>
@@ -18448,7 +18438,7 @@
         <v>1147</v>
       </c>
       <c r="E81" s="37" t="s">
-        <v>1909</v>
+        <v>1899</v>
       </c>
       <c r="F81" s="25" t="s">
         <v>965</v>
@@ -18511,7 +18501,7 @@
         <v>745</v>
       </c>
       <c r="E82" s="37" t="s">
-        <v>1910</v>
+        <v>1900</v>
       </c>
       <c r="F82" s="25" t="s">
         <v>761</v>
@@ -18576,7 +18566,7 @@
         <v>746</v>
       </c>
       <c r="E83" s="37" t="s">
-        <v>1911</v>
+        <v>1901</v>
       </c>
       <c r="F83" s="25" t="s">
         <v>762</v>
@@ -18641,7 +18631,7 @@
         <v>747</v>
       </c>
       <c r="E84" s="37" t="s">
-        <v>1912</v>
+        <v>1902</v>
       </c>
       <c r="F84" s="25" t="s">
         <v>763</v>
@@ -18706,7 +18696,7 @@
         <v>748</v>
       </c>
       <c r="E85" s="37" t="s">
-        <v>1913</v>
+        <v>1903</v>
       </c>
       <c r="F85" s="25" t="s">
         <v>764</v>
@@ -18771,7 +18761,7 @@
         <v>749</v>
       </c>
       <c r="E86" s="37" t="s">
-        <v>1914</v>
+        <v>1904</v>
       </c>
       <c r="F86" s="25" t="s">
         <v>765</v>
@@ -18836,7 +18826,7 @@
         <v>750</v>
       </c>
       <c r="E87" s="37" t="s">
-        <v>1915</v>
+        <v>1905</v>
       </c>
       <c r="F87" s="25" t="s">
         <v>375</v>
@@ -18901,7 +18891,7 @@
         <v>751</v>
       </c>
       <c r="E88" s="37" t="s">
-        <v>1916</v>
+        <v>1906</v>
       </c>
       <c r="F88" s="25" t="s">
         <v>376</v>
@@ -18966,7 +18956,7 @@
         <v>771</v>
       </c>
       <c r="E89" s="37" t="s">
-        <v>1917</v>
+        <v>1907</v>
       </c>
       <c r="F89" s="25" t="s">
         <v>766</v>
@@ -19031,7 +19021,7 @@
         <v>772</v>
       </c>
       <c r="E90" s="37" t="s">
-        <v>1918</v>
+        <v>1908</v>
       </c>
       <c r="F90" s="25" t="s">
         <v>767</v>
@@ -19096,7 +19086,7 @@
         <v>671</v>
       </c>
       <c r="E91" s="37" t="s">
-        <v>1919</v>
+        <v>1909</v>
       </c>
       <c r="F91" s="25" t="s">
         <v>374</v>
@@ -19189,7 +19179,7 @@
         <v>379</v>
       </c>
       <c r="E92" s="37" t="s">
-        <v>1920</v>
+        <v>1910</v>
       </c>
       <c r="F92" s="25" t="s">
         <v>380</v>
@@ -19273,10 +19263,10 @@
       <c r="B93" s="25"/>
       <c r="C93" s="25"/>
       <c r="D93" s="25" t="s">
-        <v>1687</v>
+        <v>1677</v>
       </c>
       <c r="E93" s="37" t="s">
-        <v>1921</v>
+        <v>1911</v>
       </c>
       <c r="F93" s="25" t="s">
         <v>156</v>
@@ -19302,11 +19292,11 @@
       </c>
       <c r="R93" s="25"/>
       <c r="S93" s="55" t="s">
-        <v>1819</v>
+        <v>1809</v>
       </c>
       <c r="T93" s="33"/>
       <c r="U93" s="55" t="s">
-        <v>1820</v>
+        <v>1810</v>
       </c>
       <c r="V93" s="25" t="s">
         <v>1153</v>
@@ -19383,7 +19373,7 @@
         <v>153</v>
       </c>
       <c r="E94" s="37" t="s">
-        <v>1922</v>
+        <v>1912</v>
       </c>
       <c r="F94" s="25" t="s">
         <v>157</v>
@@ -19448,11 +19438,11 @@
       </c>
       <c r="AM94" s="25"/>
       <c r="AN94" s="25" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="AO94" s="25"/>
       <c r="AP94" s="25" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="AQ94" s="25"/>
       <c r="AR94" s="25"/>
@@ -19474,7 +19464,7 @@
         <v>673</v>
       </c>
       <c r="E95" s="37" t="s">
-        <v>1923</v>
+        <v>1913</v>
       </c>
       <c r="F95" s="25" t="s">
         <v>384</v>
@@ -19575,7 +19565,7 @@
         <v>385</v>
       </c>
       <c r="E96" s="37" t="s">
-        <v>1924</v>
+        <v>1914</v>
       </c>
       <c r="F96" s="25" t="s">
         <v>386</v>
@@ -19663,13 +19653,13 @@
       <c r="B97" s="25"/>
       <c r="C97" s="25"/>
       <c r="D97" s="25" t="s">
-        <v>1701</v>
+        <v>1691</v>
       </c>
       <c r="E97" s="37" t="s">
-        <v>1925</v>
+        <v>1915</v>
       </c>
       <c r="F97" s="25" t="s">
-        <v>1702</v>
+        <v>1692</v>
       </c>
       <c r="G97" s="25"/>
       <c r="H97" s="25"/>
@@ -19682,7 +19672,7 @@
       </c>
       <c r="L97" s="25"/>
       <c r="M97" s="25" t="s">
-        <v>1703</v>
+        <v>1693</v>
       </c>
       <c r="N97" s="25"/>
       <c r="O97" s="25"/>
@@ -19733,7 +19723,7 @@
       </c>
       <c r="AM97" s="25"/>
       <c r="AN97" s="25" t="s">
-        <v>1701</v>
+        <v>1691</v>
       </c>
       <c r="AO97" s="25"/>
       <c r="AP97" s="25"/>
@@ -19754,22 +19744,22 @@
       <c r="B98" s="55"/>
       <c r="C98" s="55"/>
       <c r="D98" s="55" t="s">
-        <v>1821</v>
+        <v>1811</v>
       </c>
       <c r="E98" s="55"/>
       <c r="F98" s="55"/>
       <c r="G98" s="55"/>
       <c r="H98" s="55"/>
       <c r="I98" s="55" t="s">
-        <v>1822</v>
+        <v>1812</v>
       </c>
       <c r="J98" s="55"/>
       <c r="K98" s="55" t="s">
-        <v>1823</v>
+        <v>1813</v>
       </c>
       <c r="L98" s="55"/>
       <c r="M98" s="55" t="s">
-        <v>1824</v>
+        <v>1814</v>
       </c>
       <c r="N98" s="55"/>
       <c r="O98" s="55"/>
@@ -19784,49 +19774,49 @@
       <c r="X98" s="55"/>
       <c r="Y98" s="56"/>
       <c r="Z98" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AA98" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AB98" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AC98" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AD98" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AE98" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AF98" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AG98" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AH98" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AI98" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AJ98" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AK98" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AL98" s="56"/>
       <c r="AM98" s="55"/>
       <c r="AN98" s="55" t="s">
-        <v>1826</v>
+        <v>1816</v>
       </c>
       <c r="AO98" s="55"/>
       <c r="AP98" s="55" t="s">
-        <v>1826</v>
+        <v>1816</v>
       </c>
       <c r="AQ98" s="55"/>
       <c r="AR98" s="55"/>
@@ -19846,22 +19836,22 @@
       <c r="B99" s="55"/>
       <c r="C99" s="55"/>
       <c r="D99" s="55" t="s">
-        <v>1827</v>
+        <v>1817</v>
       </c>
       <c r="E99" s="55"/>
       <c r="F99" s="55"/>
       <c r="G99" s="55"/>
       <c r="H99" s="55"/>
       <c r="I99" s="55" t="s">
-        <v>1822</v>
+        <v>1812</v>
       </c>
       <c r="J99" s="55"/>
       <c r="K99" s="55" t="s">
-        <v>1823</v>
+        <v>1813</v>
       </c>
       <c r="L99" s="55"/>
       <c r="M99" s="55" t="s">
-        <v>1824</v>
+        <v>1814</v>
       </c>
       <c r="N99" s="55"/>
       <c r="O99" s="55"/>
@@ -19876,49 +19866,49 @@
       <c r="X99" s="55"/>
       <c r="Y99" s="56"/>
       <c r="Z99" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AA99" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AB99" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AC99" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AD99" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AE99" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AF99" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AG99" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AH99" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AI99" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AJ99" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AK99" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AL99" s="56"/>
       <c r="AM99" s="55"/>
       <c r="AN99" s="55" t="s">
-        <v>1828</v>
+        <v>1818</v>
       </c>
       <c r="AO99" s="55"/>
       <c r="AP99" s="55" t="s">
-        <v>1828</v>
+        <v>1818</v>
       </c>
       <c r="AQ99" s="55"/>
       <c r="AR99" s="55"/>
@@ -19938,22 +19928,22 @@
       <c r="B100" s="55"/>
       <c r="C100" s="55"/>
       <c r="D100" s="55" t="s">
-        <v>1829</v>
+        <v>1819</v>
       </c>
       <c r="E100" s="55"/>
       <c r="F100" s="55"/>
       <c r="G100" s="55"/>
       <c r="H100" s="55"/>
       <c r="I100" s="55" t="s">
-        <v>1822</v>
+        <v>1812</v>
       </c>
       <c r="J100" s="55"/>
       <c r="K100" s="55" t="s">
-        <v>1823</v>
+        <v>1813</v>
       </c>
       <c r="L100" s="55"/>
       <c r="M100" s="55" t="s">
-        <v>1824</v>
+        <v>1814</v>
       </c>
       <c r="N100" s="55"/>
       <c r="O100" s="55"/>
@@ -19968,49 +19958,49 @@
       <c r="X100" s="55"/>
       <c r="Y100" s="56"/>
       <c r="Z100" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AA100" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AB100" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AC100" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AD100" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AE100" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AF100" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AG100" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AH100" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AI100" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AJ100" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AK100" s="55" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AL100" s="56"/>
       <c r="AM100" s="55"/>
       <c r="AN100" s="55" t="s">
-        <v>1830</v>
+        <v>1820</v>
       </c>
       <c r="AO100" s="55"/>
       <c r="AP100" s="55" t="s">
-        <v>1830</v>
+        <v>1820</v>
       </c>
       <c r="AQ100" s="55"/>
       <c r="AR100" s="55"/>
@@ -20121,7 +20111,7 @@
         <v>1178</v>
       </c>
       <c r="E102" s="37" t="s">
-        <v>1926</v>
+        <v>1916</v>
       </c>
       <c r="F102" s="25" t="s">
         <v>179</v>
@@ -20202,7 +20192,7 @@
         <v>321</v>
       </c>
       <c r="E103" s="37" t="s">
-        <v>1927</v>
+        <v>1917</v>
       </c>
       <c r="F103" s="25" t="s">
         <v>161</v>
@@ -20269,7 +20259,7 @@
         <v>581</v>
       </c>
       <c r="E104" s="37" t="s">
-        <v>1928</v>
+        <v>1918</v>
       </c>
       <c r="F104" s="25" t="s">
         <v>180</v>
@@ -20352,7 +20342,7 @@
         <v>322</v>
       </c>
       <c r="E105" s="37" t="s">
-        <v>1929</v>
+        <v>1919</v>
       </c>
       <c r="F105" s="25" t="s">
         <v>162</v>
@@ -20443,7 +20433,7 @@
         <v>1168</v>
       </c>
       <c r="E106" s="37" t="s">
-        <v>1930</v>
+        <v>1920</v>
       </c>
       <c r="F106" s="25" t="s">
         <v>773</v>
@@ -20534,7 +20524,7 @@
         <v>1169</v>
       </c>
       <c r="E107" s="37" t="s">
-        <v>1931</v>
+        <v>1921</v>
       </c>
       <c r="F107" s="25" t="s">
         <v>774</v>
@@ -20625,7 +20615,7 @@
         <v>1171</v>
       </c>
       <c r="E108" s="37" t="s">
-        <v>1932</v>
+        <v>1922</v>
       </c>
       <c r="F108" s="25" t="s">
         <v>684</v>
@@ -20718,7 +20708,7 @@
         <v>1170</v>
       </c>
       <c r="E109" s="37" t="s">
-        <v>1933</v>
+        <v>1923</v>
       </c>
       <c r="F109" s="25" t="s">
         <v>775</v>
@@ -20809,7 +20799,7 @@
         <v>198</v>
       </c>
       <c r="E110" s="37" t="s">
-        <v>1934</v>
+        <v>1924</v>
       </c>
       <c r="F110" s="25" t="s">
         <v>181</v>
@@ -20838,7 +20828,7 @@
       <c r="V110" s="25"/>
       <c r="W110" s="25"/>
       <c r="X110" s="25" t="s">
-        <v>1669</v>
+        <v>1667</v>
       </c>
       <c r="Z110" s="25" t="s">
         <v>25</v>
@@ -20904,7 +20894,7 @@
         <v>199</v>
       </c>
       <c r="E111" s="37" t="s">
-        <v>1935</v>
+        <v>1925</v>
       </c>
       <c r="F111" s="25" t="s">
         <v>182</v>
@@ -20931,7 +20921,7 @@
       <c r="V111" s="25"/>
       <c r="W111" s="25"/>
       <c r="X111" s="25" t="s">
-        <v>1669</v>
+        <v>1667</v>
       </c>
       <c r="Z111" s="25" t="s">
         <v>25</v>
@@ -20971,11 +20961,11 @@
       </c>
       <c r="AM111" s="25"/>
       <c r="AN111" s="25" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="AO111" s="25"/>
       <c r="AP111" s="25" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="AQ111" s="25"/>
       <c r="AR111" s="25"/>
@@ -20997,7 +20987,7 @@
         <v>952</v>
       </c>
       <c r="E112" s="37" t="s">
-        <v>1936</v>
+        <v>1926</v>
       </c>
       <c r="F112" s="25" t="s">
         <v>315</v>
@@ -21100,7 +21090,7 @@
         <v>201</v>
       </c>
       <c r="E113" s="37" t="s">
-        <v>1937</v>
+        <v>1927</v>
       </c>
       <c r="F113" s="25" t="s">
         <v>316</v>
@@ -21165,11 +21155,11 @@
       </c>
       <c r="AM113" s="25"/>
       <c r="AN113" s="25" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="AO113" s="25"/>
       <c r="AP113" s="25" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="AQ113" s="25"/>
       <c r="AR113" s="25"/>
@@ -21279,7 +21269,7 @@
         <v>1260</v>
       </c>
       <c r="E115" s="37" t="s">
-        <v>1938</v>
+        <v>1928</v>
       </c>
       <c r="F115" s="25" t="s">
         <v>1261</v>
@@ -21308,7 +21298,7 @@
       <c r="V115" s="25"/>
       <c r="W115" s="25"/>
       <c r="X115" s="25" t="s">
-        <v>1665</v>
+        <v>1663</v>
       </c>
       <c r="Z115" s="25"/>
       <c r="AA115" s="25"/>
@@ -21354,7 +21344,7 @@
         <v>304</v>
       </c>
       <c r="E116" s="37" t="s">
-        <v>1939</v>
+        <v>1929</v>
       </c>
       <c r="F116" s="25" t="s">
         <v>709</v>
@@ -21447,7 +21437,7 @@
         <v>596</v>
       </c>
       <c r="E117" s="37" t="s">
-        <v>1940</v>
+        <v>1930</v>
       </c>
       <c r="F117" s="25" t="s">
         <v>708</v>
@@ -21540,7 +21530,7 @@
         <v>597</v>
       </c>
       <c r="E118" s="37" t="s">
-        <v>1941</v>
+        <v>1931</v>
       </c>
       <c r="F118" s="25" t="s">
         <v>184</v>
@@ -21569,7 +21559,7 @@
       <c r="V118" s="25"/>
       <c r="W118" s="25"/>
       <c r="X118" s="25" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="Z118" s="25" t="s">
         <v>25</v>
@@ -21635,7 +21625,7 @@
         <v>129</v>
       </c>
       <c r="E119" s="37" t="s">
-        <v>1942</v>
+        <v>1932</v>
       </c>
       <c r="F119" s="25" t="s">
         <v>130</v>
@@ -21662,7 +21652,7 @@
       <c r="V119" s="25"/>
       <c r="W119" s="25"/>
       <c r="X119" s="25" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="Z119" s="25" t="s">
         <v>25</v>
@@ -21702,11 +21692,11 @@
       </c>
       <c r="AM119" s="25"/>
       <c r="AN119" s="25" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="AO119" s="25"/>
       <c r="AP119" s="25" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="AQ119" s="25"/>
       <c r="AR119" s="25"/>
@@ -21728,7 +21718,7 @@
         <v>674</v>
       </c>
       <c r="E120" s="37" t="s">
-        <v>1943</v>
+        <v>1933</v>
       </c>
       <c r="F120" s="25" t="s">
         <v>393</v>
@@ -21757,7 +21747,7 @@
       <c r="V120" s="25"/>
       <c r="W120" s="25"/>
       <c r="X120" s="25" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="Z120" s="25" t="s">
         <v>25</v>
@@ -21938,7 +21928,7 @@
       <c r="V122" s="25"/>
       <c r="W122" s="25"/>
       <c r="X122" s="25" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="Z122" s="25"/>
       <c r="AA122" s="25"/>
@@ -21984,7 +21974,7 @@
         <v>689</v>
       </c>
       <c r="E123" s="37" t="s">
-        <v>1944</v>
+        <v>1934</v>
       </c>
       <c r="F123" s="25" t="s">
         <v>690</v>
@@ -22013,7 +22003,7 @@
       <c r="V123" s="25"/>
       <c r="W123" s="25"/>
       <c r="X123" s="25" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="Z123" s="25" t="s">
         <v>70</v>
@@ -22079,7 +22069,7 @@
         <v>306</v>
       </c>
       <c r="E124" s="37" t="s">
-        <v>1945</v>
+        <v>1935</v>
       </c>
       <c r="F124" s="25" t="s">
         <v>309</v>
@@ -22108,7 +22098,7 @@
       <c r="V124" s="25"/>
       <c r="W124" s="25"/>
       <c r="X124" s="25" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="Z124" s="25" t="s">
         <v>70</v>
@@ -22174,7 +22164,7 @@
         <v>307</v>
       </c>
       <c r="E125" s="37" t="s">
-        <v>1946</v>
+        <v>1936</v>
       </c>
       <c r="F125" s="25" t="s">
         <v>308</v>
@@ -22203,7 +22193,7 @@
       <c r="V125" s="25"/>
       <c r="W125" s="25"/>
       <c r="X125" s="25" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="Z125" s="25" t="s">
         <v>70</v>
@@ -22269,7 +22259,7 @@
         <v>595</v>
       </c>
       <c r="E126" s="37" t="s">
-        <v>1947</v>
+        <v>1937</v>
       </c>
       <c r="F126" s="25" t="s">
         <v>186</v>
@@ -22298,7 +22288,7 @@
       <c r="V126" s="25"/>
       <c r="W126" s="25"/>
       <c r="X126" s="25" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="Z126" s="25" t="s">
         <v>25</v>
@@ -22364,7 +22354,7 @@
         <v>202</v>
       </c>
       <c r="E127" s="37" t="s">
-        <v>1948</v>
+        <v>1938</v>
       </c>
       <c r="F127" s="25" t="s">
         <v>172</v>
@@ -22391,7 +22381,7 @@
       <c r="V127" s="25"/>
       <c r="W127" s="25"/>
       <c r="X127" s="25" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="Z127" s="25" t="s">
         <v>25</v>
@@ -22431,11 +22421,11 @@
       </c>
       <c r="AM127" s="25"/>
       <c r="AN127" s="25" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="AO127" s="25"/>
       <c r="AP127" s="25" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="AQ127" s="25"/>
       <c r="AR127" s="25"/>
@@ -22457,7 +22447,7 @@
         <v>1186</v>
       </c>
       <c r="E128" s="37" t="s">
-        <v>1949</v>
+        <v>1939</v>
       </c>
       <c r="F128" s="25" t="s">
         <v>557</v>
@@ -22486,7 +22476,7 @@
       <c r="V128" s="25"/>
       <c r="W128" s="25"/>
       <c r="X128" s="25" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="Z128" s="25" t="s">
         <v>25</v>
@@ -22642,7 +22632,7 @@
         <v>688</v>
       </c>
       <c r="E130" s="37" t="s">
-        <v>1950</v>
+        <v>1940</v>
       </c>
       <c r="F130" s="25" t="s">
         <v>173</v>
@@ -22671,7 +22661,7 @@
       <c r="V130" s="25"/>
       <c r="W130" s="25"/>
       <c r="X130" s="25" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="Z130" s="25"/>
       <c r="AA130" s="25"/>
@@ -22715,7 +22705,7 @@
         <v>310</v>
       </c>
       <c r="E131" s="37" t="s">
-        <v>1951</v>
+        <v>1941</v>
       </c>
       <c r="F131" s="25" t="s">
         <v>312</v>
@@ -22744,7 +22734,7 @@
       <c r="V131" s="25"/>
       <c r="W131" s="25"/>
       <c r="X131" s="25" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="Z131" s="25" t="s">
         <v>70</v>
@@ -22810,7 +22800,7 @@
         <v>311</v>
       </c>
       <c r="E132" s="37" t="s">
-        <v>1952</v>
+        <v>1942</v>
       </c>
       <c r="F132" s="25" t="s">
         <v>313</v>
@@ -22839,7 +22829,7 @@
       <c r="V132" s="25"/>
       <c r="W132" s="25"/>
       <c r="X132" s="25" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="Z132" s="25" t="s">
         <v>70</v>
@@ -22905,7 +22895,7 @@
         <v>801</v>
       </c>
       <c r="E133" s="37" t="s">
-        <v>1953</v>
+        <v>1943</v>
       </c>
       <c r="F133" s="25" t="s">
         <v>802</v>
@@ -22994,7 +22984,7 @@
         <v>1172</v>
       </c>
       <c r="E134" s="37" t="s">
-        <v>1954</v>
+        <v>1944</v>
       </c>
       <c r="F134" s="25" t="s">
         <v>776</v>
@@ -23087,7 +23077,7 @@
         <v>329</v>
       </c>
       <c r="E135" s="37" t="s">
-        <v>1955</v>
+        <v>1945</v>
       </c>
       <c r="F135" s="25" t="s">
         <v>330</v>
@@ -23180,7 +23170,7 @@
         <v>1173</v>
       </c>
       <c r="E136" s="37" t="s">
-        <v>1956</v>
+        <v>1946</v>
       </c>
       <c r="F136" s="25" t="s">
         <v>810</v>
@@ -23273,7 +23263,7 @@
         <v>1174</v>
       </c>
       <c r="E137" s="37" t="s">
-        <v>1957</v>
+        <v>1947</v>
       </c>
       <c r="F137" s="25" t="s">
         <v>718</v>
@@ -23366,7 +23356,7 @@
         <v>719</v>
       </c>
       <c r="E138" s="37" t="s">
-        <v>1958</v>
+        <v>1948</v>
       </c>
       <c r="F138" s="25" t="s">
         <v>717</v>
@@ -23459,7 +23449,7 @@
         <v>331</v>
       </c>
       <c r="E139" s="37" t="s">
-        <v>1959</v>
+        <v>1949</v>
       </c>
       <c r="F139" s="25" t="s">
         <v>1263</v>
@@ -23552,7 +23542,7 @@
         <v>676</v>
       </c>
       <c r="E140" s="37" t="s">
-        <v>1960</v>
+        <v>1950</v>
       </c>
       <c r="F140" s="25" t="s">
         <v>1264</v>
@@ -23645,7 +23635,7 @@
         <v>1175</v>
       </c>
       <c r="E141" s="37" t="s">
-        <v>1961</v>
+        <v>1951</v>
       </c>
       <c r="F141" s="25" t="s">
         <v>638</v>
@@ -23674,7 +23664,7 @@
       <c r="V141" s="25"/>
       <c r="W141" s="25"/>
       <c r="X141" s="25" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="Z141" s="25" t="s">
         <v>70</v>
@@ -23740,7 +23730,7 @@
         <v>637</v>
       </c>
       <c r="E142" s="37" t="s">
-        <v>1962</v>
+        <v>1952</v>
       </c>
       <c r="F142" s="25" t="s">
         <v>639</v>
@@ -23769,7 +23759,7 @@
       <c r="V142" s="25"/>
       <c r="W142" s="25"/>
       <c r="X142" s="25" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="Z142" s="25" t="s">
         <v>70</v>
@@ -23835,7 +23825,7 @@
         <v>356</v>
       </c>
       <c r="E143" s="37" t="s">
-        <v>1963</v>
+        <v>1953</v>
       </c>
       <c r="F143" s="25" t="s">
         <v>351</v>
@@ -23932,7 +23922,7 @@
         <v>357</v>
       </c>
       <c r="E144" s="37" t="s">
-        <v>1964</v>
+        <v>1954</v>
       </c>
       <c r="F144" s="25" t="s">
         <v>352</v>
@@ -24027,7 +24017,7 @@
         <v>1160</v>
       </c>
       <c r="E145" s="37" t="s">
-        <v>1965</v>
+        <v>1955</v>
       </c>
       <c r="F145" s="25" t="s">
         <v>1161</v>
@@ -24310,7 +24300,7 @@
         <v>635</v>
       </c>
       <c r="E149" s="37" t="s">
-        <v>1966</v>
+        <v>1956</v>
       </c>
       <c r="F149" s="25" t="s">
         <v>394</v>
@@ -24491,7 +24481,7 @@
         <v>1165</v>
       </c>
       <c r="E151" s="37" t="s">
-        <v>1967</v>
+        <v>1957</v>
       </c>
       <c r="F151" s="25" t="s">
         <v>395</v>
@@ -24648,7 +24638,7 @@
         <v>1166</v>
       </c>
       <c r="E153" s="37" t="s">
-        <v>1968</v>
+        <v>1958</v>
       </c>
       <c r="F153" s="25" t="s">
         <v>396</v>
@@ -24717,7 +24707,7 @@
         <v>879</v>
       </c>
       <c r="E154" s="37" t="s">
-        <v>1969</v>
+        <v>1959</v>
       </c>
       <c r="F154" s="25" t="s">
         <v>880</v>
@@ -24780,7 +24770,7 @@
         <v>876</v>
       </c>
       <c r="E155" s="37" t="s">
-        <v>1970</v>
+        <v>1960</v>
       </c>
       <c r="F155" s="25" t="s">
         <v>877</v>
@@ -24931,13 +24921,13 @@
         <v>1258</v>
       </c>
       <c r="E157" s="37" t="s">
-        <v>1971</v>
+        <v>1961</v>
       </c>
       <c r="F157" s="25" t="s">
         <v>884</v>
       </c>
       <c r="G157" s="25" t="s">
-        <v>2327</v>
+        <v>2317</v>
       </c>
       <c r="H157" s="25"/>
       <c r="I157" s="25" t="s">
@@ -25088,7 +25078,7 @@
         <v>883</v>
       </c>
       <c r="E159" s="37" t="s">
-        <v>1972</v>
+        <v>1962</v>
       </c>
       <c r="F159" s="25" t="s">
         <v>885</v>
@@ -25157,7 +25147,7 @@
         <v>935</v>
       </c>
       <c r="E160" s="37" t="s">
-        <v>1973</v>
+        <v>1963</v>
       </c>
       <c r="F160" s="25" t="s">
         <v>389</v>
@@ -25260,7 +25250,7 @@
         <v>390</v>
       </c>
       <c r="E161" s="37" t="s">
-        <v>1974</v>
+        <v>1964</v>
       </c>
       <c r="F161" s="25" t="s">
         <v>391</v>
@@ -25351,7 +25341,7 @@
         <v>955</v>
       </c>
       <c r="E162" s="37" t="s">
-        <v>1975</v>
+        <v>1965</v>
       </c>
       <c r="F162" s="25" t="s">
         <v>424</v>
@@ -25450,7 +25440,7 @@
         <v>450</v>
       </c>
       <c r="E163" s="37" t="s">
-        <v>1976</v>
+        <v>1966</v>
       </c>
       <c r="F163" s="25" t="s">
         <v>425</v>
@@ -25627,7 +25617,7 @@
         <v>1194</v>
       </c>
       <c r="E165" s="37" t="s">
-        <v>1977</v>
+        <v>1967</v>
       </c>
       <c r="F165" s="25" t="s">
         <v>1197</v>
@@ -25786,7 +25776,7 @@
         <v>1196</v>
       </c>
       <c r="E167" s="37" t="s">
-        <v>1978</v>
+        <v>1968</v>
       </c>
       <c r="F167" s="25" t="s">
         <v>426</v>
@@ -25853,7 +25843,7 @@
         <v>203</v>
       </c>
       <c r="E168" s="37" t="s">
-        <v>1979</v>
+        <v>1969</v>
       </c>
       <c r="F168" s="25" t="s">
         <v>174</v>
@@ -25920,16 +25910,16 @@
       </c>
       <c r="AM168" s="25"/>
       <c r="AN168" s="25" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="AO168" s="25"/>
       <c r="AP168" s="25"/>
       <c r="AQ168" s="25" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="AR168" s="25"/>
       <c r="AS168" s="25" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="AT168" s="25"/>
       <c r="AU168" s="25"/>
@@ -25948,7 +25938,7 @@
         <v>451</v>
       </c>
       <c r="E169" s="37" t="s">
-        <v>1980</v>
+        <v>1970</v>
       </c>
       <c r="F169" s="25" t="s">
         <v>427</v>
@@ -26041,7 +26031,7 @@
         <v>430</v>
       </c>
       <c r="E170" s="37" t="s">
-        <v>1981</v>
+        <v>1971</v>
       </c>
       <c r="F170" s="25" t="s">
         <v>428</v>
@@ -26108,16 +26098,16 @@
       </c>
       <c r="AM170" s="25"/>
       <c r="AN170" s="25" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="AO170" s="25"/>
       <c r="AP170" s="25"/>
       <c r="AQ170" s="25" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="AR170" s="25"/>
       <c r="AS170" s="25" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="AT170" s="25"/>
       <c r="AU170" s="25"/>
@@ -26136,7 +26126,7 @@
         <v>1233</v>
       </c>
       <c r="E171" s="37" t="s">
-        <v>1982</v>
+        <v>1972</v>
       </c>
       <c r="F171" s="25" t="s">
         <v>429</v>
@@ -26169,7 +26159,7 @@
         <v>633</v>
       </c>
       <c r="V171" s="52" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
       <c r="W171" s="25" t="s">
         <v>1232</v>
@@ -26241,7 +26231,7 @@
         <v>632</v>
       </c>
       <c r="E172" s="37" t="s">
-        <v>1983</v>
+        <v>1973</v>
       </c>
       <c r="F172" s="25" t="s">
         <v>457</v>
@@ -26330,7 +26320,7 @@
         <v>204</v>
       </c>
       <c r="E173" s="37" t="s">
-        <v>1984</v>
+        <v>1974</v>
       </c>
       <c r="F173" s="25" t="s">
         <v>188</v>
@@ -26397,11 +26387,11 @@
       </c>
       <c r="AM173" s="25"/>
       <c r="AN173" s="25" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="AO173" s="25"/>
       <c r="AP173" s="25" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="AQ173" s="25"/>
       <c r="AR173" s="25"/>
@@ -26423,7 +26413,7 @@
         <v>205</v>
       </c>
       <c r="E174" s="37" t="s">
-        <v>1985</v>
+        <v>1975</v>
       </c>
       <c r="F174" s="25" t="s">
         <v>165</v>
@@ -26488,11 +26478,11 @@
       </c>
       <c r="AM174" s="25"/>
       <c r="AN174" s="25" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="AO174" s="25"/>
       <c r="AP174" s="25" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="AQ174" s="25"/>
       <c r="AR174" s="25"/>
@@ -26514,7 +26504,7 @@
         <v>953</v>
       </c>
       <c r="E175" s="37" t="s">
-        <v>1933</v>
+        <v>1923</v>
       </c>
       <c r="F175" s="25" t="s">
         <v>190</v>
@@ -26621,7 +26611,7 @@
         <v>206</v>
       </c>
       <c r="E176" s="37" t="s">
-        <v>1986</v>
+        <v>1976</v>
       </c>
       <c r="F176" s="25" t="s">
         <v>175</v>
@@ -26712,7 +26702,7 @@
         <v>200</v>
       </c>
       <c r="E177" s="37" t="s">
-        <v>1987</v>
+        <v>1977</v>
       </c>
       <c r="F177" s="25" t="s">
         <v>183</v>
@@ -26779,21 +26769,21 @@
       </c>
       <c r="AM177" s="25"/>
       <c r="AN177" s="25" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="AO177" s="25"/>
       <c r="AP177" s="25"/>
       <c r="AQ177" s="25" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="AR177" s="25" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="AS177" s="25" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="AT177" s="25" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="AU177" s="25"/>
       <c r="AV177" s="25"/>
@@ -26811,7 +26801,7 @@
         <v>582</v>
       </c>
       <c r="E178" s="37" t="s">
-        <v>1988</v>
+        <v>1978</v>
       </c>
       <c r="F178" s="25" t="s">
         <v>164</v>
@@ -26825,7 +26815,7 @@
       </c>
       <c r="J178" s="25"/>
       <c r="K178" s="25" t="s">
-        <v>1823</v>
+        <v>1813</v>
       </c>
       <c r="L178" s="25"/>
       <c r="M178" s="25"/>
@@ -26906,7 +26896,7 @@
         <v>405</v>
       </c>
       <c r="E179" s="37" t="s">
-        <v>1989</v>
+        <v>1979</v>
       </c>
       <c r="F179" s="25" t="s">
         <v>397</v>
@@ -26977,18 +26967,18 @@
       </c>
       <c r="AM179" s="25"/>
       <c r="AN179" s="25" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="AO179" s="25"/>
       <c r="AP179" s="25" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="AQ179" s="25" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="AR179" s="25"/>
       <c r="AS179" s="25" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="AT179" s="25"/>
       <c r="AU179" s="25"/>
@@ -27007,7 +26997,7 @@
         <v>410</v>
       </c>
       <c r="E180" s="37" t="s">
-        <v>1990</v>
+        <v>1980</v>
       </c>
       <c r="F180" s="25" t="s">
         <v>411</v>
@@ -27098,7 +27088,7 @@
         <v>406</v>
       </c>
       <c r="E181" s="37" t="s">
-        <v>1991</v>
+        <v>1981</v>
       </c>
       <c r="F181" s="25" t="s">
         <v>398</v>
@@ -27165,16 +27155,16 @@
       </c>
       <c r="AM181" s="25"/>
       <c r="AN181" s="25" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="AO181" s="25"/>
       <c r="AP181" s="25"/>
       <c r="AQ181" s="25" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="AR181" s="25"/>
       <c r="AS181" s="25" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="AT181" s="25"/>
       <c r="AU181" s="25"/>
@@ -27193,7 +27183,7 @@
         <v>407</v>
       </c>
       <c r="E182" s="37" t="s">
-        <v>1992</v>
+        <v>1982</v>
       </c>
       <c r="F182" s="25" t="s">
         <v>399</v>
@@ -27266,16 +27256,16 @@
       </c>
       <c r="AM182" s="25"/>
       <c r="AN182" s="25" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="AO182" s="25"/>
       <c r="AP182" s="25"/>
       <c r="AQ182" s="25" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="AR182" s="25"/>
       <c r="AS182" s="25" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="AT182" s="25"/>
       <c r="AU182" s="25"/>
@@ -27294,7 +27284,7 @@
         <v>419</v>
       </c>
       <c r="E183" s="37" t="s">
-        <v>1993</v>
+        <v>1983</v>
       </c>
       <c r="F183" s="25" t="s">
         <v>414</v>
@@ -27383,7 +27373,7 @@
         <v>1181</v>
       </c>
       <c r="E184" s="37" t="s">
-        <v>1994</v>
+        <v>1984</v>
       </c>
       <c r="F184" s="25" t="s">
         <v>400</v>
@@ -27478,7 +27468,7 @@
         <v>408</v>
       </c>
       <c r="E185" s="37" t="s">
-        <v>1995</v>
+        <v>1985</v>
       </c>
       <c r="F185" s="25" t="s">
         <v>401</v>
@@ -27551,16 +27541,16 @@
       </c>
       <c r="AM185" s="25"/>
       <c r="AN185" s="25" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="AO185" s="25"/>
       <c r="AP185" s="25"/>
       <c r="AQ185" s="25" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="AR185" s="25"/>
       <c r="AS185" s="25" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="AT185" s="25"/>
       <c r="AU185" s="25"/>
@@ -27579,7 +27569,7 @@
         <v>420</v>
       </c>
       <c r="E186" s="37" t="s">
-        <v>1996</v>
+        <v>1986</v>
       </c>
       <c r="F186" s="25" t="s">
         <v>418</v>
@@ -27668,7 +27658,7 @@
         <v>1182</v>
       </c>
       <c r="E187" s="37" t="s">
-        <v>1997</v>
+        <v>1987</v>
       </c>
       <c r="F187" s="25" t="s">
         <v>402</v>
@@ -27763,7 +27753,7 @@
         <v>409</v>
       </c>
       <c r="E188" s="37" t="s">
-        <v>1998</v>
+        <v>1988</v>
       </c>
       <c r="F188" s="25" t="s">
         <v>403</v>
@@ -27836,16 +27826,16 @@
       </c>
       <c r="AM188" s="25"/>
       <c r="AN188" s="25" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="AO188" s="25"/>
       <c r="AP188" s="25"/>
       <c r="AQ188" s="25" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="AR188" s="25"/>
       <c r="AS188" s="25" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="AT188" s="25"/>
       <c r="AU188" s="25"/>
@@ -27864,7 +27854,7 @@
         <v>421</v>
       </c>
       <c r="E189" s="37" t="s">
-        <v>1999</v>
+        <v>1989</v>
       </c>
       <c r="F189" s="25" t="s">
         <v>417</v>
@@ -27953,7 +27943,7 @@
         <v>1183</v>
       </c>
       <c r="E190" s="37" t="s">
-        <v>2000</v>
+        <v>1990</v>
       </c>
       <c r="F190" s="25" t="s">
         <v>404</v>
@@ -28048,7 +28038,7 @@
         <v>227</v>
       </c>
       <c r="E191" s="37" t="s">
-        <v>2001</v>
+        <v>1991</v>
       </c>
       <c r="F191" s="25" t="s">
         <v>239</v>
@@ -28121,18 +28111,18 @@
       </c>
       <c r="AM191" s="25"/>
       <c r="AN191" s="25" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="AO191" s="25"/>
       <c r="AP191" s="25" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="AQ191" s="25" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="AR191" s="25"/>
       <c r="AS191" s="25" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="AT191" s="25"/>
       <c r="AU191" s="25"/>
@@ -28151,7 +28141,7 @@
         <v>228</v>
       </c>
       <c r="E192" s="37" t="s">
-        <v>2002</v>
+        <v>1992</v>
       </c>
       <c r="F192" s="25" t="s">
         <v>218</v>
@@ -28242,7 +28232,7 @@
         <v>229</v>
       </c>
       <c r="E193" s="37" t="s">
-        <v>2003</v>
+        <v>1993</v>
       </c>
       <c r="F193" s="25" t="s">
         <v>219</v>
@@ -28309,18 +28299,18 @@
       </c>
       <c r="AM193" s="25"/>
       <c r="AN193" s="25" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="AO193" s="25"/>
       <c r="AP193" s="25" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="AQ193" s="25" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="AR193" s="25"/>
       <c r="AS193" s="25" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="AT193" s="25"/>
       <c r="AU193" s="25"/>
@@ -28339,7 +28329,7 @@
         <v>230</v>
       </c>
       <c r="E194" s="37" t="s">
-        <v>2004</v>
+        <v>1994</v>
       </c>
       <c r="F194" s="25" t="s">
         <v>240</v>
@@ -28412,18 +28402,18 @@
       </c>
       <c r="AM194" s="25"/>
       <c r="AN194" s="25" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="AO194" s="25"/>
       <c r="AP194" s="25" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="AQ194" s="25" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="AR194" s="25"/>
       <c r="AS194" s="25" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="AT194" s="25"/>
       <c r="AU194" s="25"/>
@@ -28442,7 +28432,7 @@
         <v>231</v>
       </c>
       <c r="E195" s="37" t="s">
-        <v>2005</v>
+        <v>1995</v>
       </c>
       <c r="F195" s="25" t="s">
         <v>221</v>
@@ -28533,7 +28523,7 @@
         <v>232</v>
       </c>
       <c r="E196" s="37" t="s">
-        <v>2006</v>
+        <v>1996</v>
       </c>
       <c r="F196" s="25" t="s">
         <v>222</v>
@@ -28600,18 +28590,18 @@
       </c>
       <c r="AM196" s="25"/>
       <c r="AN196" s="25" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="AO196" s="25"/>
       <c r="AP196" s="25" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="AQ196" s="25" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="AR196" s="25"/>
       <c r="AS196" s="25" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="AT196" s="25"/>
       <c r="AU196" s="25"/>
@@ -28630,7 +28620,7 @@
         <v>233</v>
       </c>
       <c r="E197" s="37" t="s">
-        <v>2007</v>
+        <v>1997</v>
       </c>
       <c r="F197" s="25" t="s">
         <v>241</v>
@@ -28703,18 +28693,18 @@
       </c>
       <c r="AM197" s="25"/>
       <c r="AN197" s="25" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="AO197" s="25"/>
       <c r="AP197" s="25" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="AQ197" s="25" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="AR197" s="25"/>
       <c r="AS197" s="25" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="AT197" s="25"/>
       <c r="AU197" s="25"/>
@@ -28733,7 +28723,7 @@
         <v>234</v>
       </c>
       <c r="E198" s="37" t="s">
-        <v>2008</v>
+        <v>1998</v>
       </c>
       <c r="F198" s="25" t="s">
         <v>224</v>
@@ -28824,7 +28814,7 @@
         <v>235</v>
       </c>
       <c r="E199" s="37" t="s">
-        <v>2009</v>
+        <v>1999</v>
       </c>
       <c r="F199" s="25" t="s">
         <v>225</v>
@@ -28891,18 +28881,18 @@
       </c>
       <c r="AM199" s="25"/>
       <c r="AN199" s="25" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="AO199" s="25"/>
       <c r="AP199" s="25" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="AQ199" s="25" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="AR199" s="25"/>
       <c r="AS199" s="25" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="AT199" s="25"/>
       <c r="AU199" s="25"/>
@@ -28921,7 +28911,7 @@
         <v>432</v>
       </c>
       <c r="E200" s="37" t="s">
-        <v>2010</v>
+        <v>2000</v>
       </c>
       <c r="F200" s="25" t="s">
         <v>431</v>
@@ -28988,16 +28978,16 @@
       </c>
       <c r="AM200" s="25"/>
       <c r="AN200" s="25" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="AO200" s="25"/>
       <c r="AP200" s="25"/>
       <c r="AQ200" s="25" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="AR200" s="25"/>
       <c r="AS200" s="25" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="AT200" s="25"/>
       <c r="AU200" s="25"/>
@@ -29016,7 +29006,7 @@
         <v>236</v>
       </c>
       <c r="E201" s="37" t="s">
-        <v>2011</v>
+        <v>2001</v>
       </c>
       <c r="F201" s="25" t="s">
         <v>226</v>
@@ -29083,16 +29073,16 @@
       </c>
       <c r="AM201" s="25"/>
       <c r="AN201" s="25" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="AO201" s="25"/>
       <c r="AP201" s="25"/>
       <c r="AQ201" s="25" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="AR201" s="25"/>
       <c r="AS201" s="25" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="AT201" s="25"/>
       <c r="AU201" s="25"/>
@@ -29111,7 +29101,7 @@
         <v>237</v>
       </c>
       <c r="E202" s="37" t="s">
-        <v>2012</v>
+        <v>2002</v>
       </c>
       <c r="F202" s="25" t="s">
         <v>213</v>
@@ -29178,16 +29168,16 @@
       </c>
       <c r="AM202" s="25"/>
       <c r="AN202" s="25" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="AO202" s="25"/>
       <c r="AP202" s="25"/>
       <c r="AQ202" s="25" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="AR202" s="25"/>
       <c r="AS202" s="25" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="AT202" s="25"/>
       <c r="AU202" s="25"/>
@@ -29206,7 +29196,7 @@
         <v>238</v>
       </c>
       <c r="E203" s="37" t="s">
-        <v>2013</v>
+        <v>2003</v>
       </c>
       <c r="F203" s="25" t="s">
         <v>214</v>
@@ -29273,16 +29263,16 @@
       </c>
       <c r="AM203" s="25"/>
       <c r="AN203" s="25" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="AO203" s="25"/>
       <c r="AP203" s="25"/>
       <c r="AQ203" s="25" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="AR203" s="25"/>
       <c r="AS203" s="25" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="AT203" s="25"/>
       <c r="AU203" s="25"/>
@@ -29301,7 +29291,7 @@
         <v>91</v>
       </c>
       <c r="E204" s="37" t="s">
-        <v>2014</v>
+        <v>2004</v>
       </c>
       <c r="F204" s="25" t="s">
         <v>215</v>
@@ -29368,16 +29358,16 @@
       </c>
       <c r="AM204" s="25"/>
       <c r="AN204" s="25" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="AO204" s="25"/>
       <c r="AP204" s="25"/>
       <c r="AQ204" s="25" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="AR204" s="25"/>
       <c r="AS204" s="25" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="AT204" s="25"/>
       <c r="AU204" s="25"/>
@@ -29396,7 +29386,7 @@
         <v>92</v>
       </c>
       <c r="E205" s="37" t="s">
-        <v>2015</v>
+        <v>2005</v>
       </c>
       <c r="F205" s="25" t="s">
         <v>216</v>
@@ -29463,16 +29453,16 @@
       </c>
       <c r="AM205" s="25"/>
       <c r="AN205" s="25" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="AO205" s="25"/>
       <c r="AP205" s="25"/>
       <c r="AQ205" s="25" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="AR205" s="25"/>
       <c r="AS205" s="25" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="AT205" s="25"/>
       <c r="AU205" s="25"/>
@@ -29491,7 +29481,7 @@
         <v>1516</v>
       </c>
       <c r="E206" s="37" t="s">
-        <v>2016</v>
+        <v>2006</v>
       </c>
       <c r="F206" s="25" t="s">
         <v>1517</v>
@@ -29501,7 +29491,7 @@
       </c>
       <c r="H206" s="25"/>
       <c r="I206" s="25" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="J206" s="25"/>
       <c r="K206" s="25" t="s">
@@ -29558,16 +29548,16 @@
       </c>
       <c r="AM206" s="25"/>
       <c r="AN206" s="25" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="AO206" s="25"/>
       <c r="AP206" s="25"/>
       <c r="AQ206" s="25" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="AR206" s="25"/>
       <c r="AS206" s="25" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="AT206" s="25"/>
       <c r="AU206" s="25"/>
@@ -29586,7 +29576,7 @@
         <v>1518</v>
       </c>
       <c r="E207" s="37" t="s">
-        <v>2017</v>
+        <v>2007</v>
       </c>
       <c r="F207" s="25" t="s">
         <v>1519</v>
@@ -29596,7 +29586,7 @@
       </c>
       <c r="H207" s="25"/>
       <c r="I207" s="25" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="J207" s="25"/>
       <c r="K207" s="25" t="s">
@@ -29653,16 +29643,16 @@
       </c>
       <c r="AM207" s="25"/>
       <c r="AN207" s="25" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="AO207" s="25"/>
       <c r="AP207" s="25"/>
       <c r="AQ207" s="25" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="AR207" s="25"/>
       <c r="AS207" s="25" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="AT207" s="25"/>
       <c r="AU207" s="25"/>
@@ -29681,7 +29671,7 @@
         <v>1520</v>
       </c>
       <c r="E208" s="37" t="s">
-        <v>2018</v>
+        <v>2008</v>
       </c>
       <c r="F208" s="25" t="s">
         <v>1521</v>
@@ -29691,7 +29681,7 @@
       </c>
       <c r="H208" s="25"/>
       <c r="I208" s="25" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="J208" s="25"/>
       <c r="K208" s="25" t="s">
@@ -29748,16 +29738,16 @@
       </c>
       <c r="AM208" s="25"/>
       <c r="AN208" s="25" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="AO208" s="25"/>
       <c r="AP208" s="25"/>
       <c r="AQ208" s="25" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="AR208" s="25"/>
       <c r="AS208" s="25" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="AT208" s="25"/>
       <c r="AU208" s="25"/>
@@ -29776,7 +29766,7 @@
         <v>1522</v>
       </c>
       <c r="E209" s="37" t="s">
-        <v>2019</v>
+        <v>2009</v>
       </c>
       <c r="F209" s="25" t="s">
         <v>1523</v>
@@ -29786,7 +29776,7 @@
       </c>
       <c r="H209" s="25"/>
       <c r="I209" s="25" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="J209" s="25"/>
       <c r="K209" s="25" t="s">
@@ -29843,16 +29833,16 @@
       </c>
       <c r="AM209" s="25"/>
       <c r="AN209" s="25" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="AO209" s="25"/>
       <c r="AP209" s="25"/>
       <c r="AQ209" s="25" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="AR209" s="25"/>
       <c r="AS209" s="25" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="AT209" s="25"/>
       <c r="AU209" s="25"/>
@@ -29871,7 +29861,7 @@
         <v>1524</v>
       </c>
       <c r="E210" s="37" t="s">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="F210" s="25" t="s">
         <v>1525</v>
@@ -29881,7 +29871,7 @@
       </c>
       <c r="H210" s="25"/>
       <c r="I210" s="25" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="J210" s="25"/>
       <c r="K210" s="25" t="s">
@@ -29938,16 +29928,16 @@
       </c>
       <c r="AM210" s="25"/>
       <c r="AN210" s="25" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="AO210" s="25"/>
       <c r="AP210" s="25"/>
       <c r="AQ210" s="25" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="AR210" s="25"/>
       <c r="AS210" s="25" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="AT210" s="25"/>
       <c r="AU210" s="25"/>
@@ -29966,7 +29956,7 @@
         <v>1526</v>
       </c>
       <c r="E211" s="37" t="s">
-        <v>2021</v>
+        <v>2011</v>
       </c>
       <c r="F211" s="25" t="s">
         <v>1527</v>
@@ -29976,7 +29966,7 @@
       </c>
       <c r="H211" s="25"/>
       <c r="I211" s="25" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="J211" s="25"/>
       <c r="K211" s="25" t="s">
@@ -30033,16 +30023,16 @@
       </c>
       <c r="AM211" s="25"/>
       <c r="AN211" s="25" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="AO211" s="25"/>
       <c r="AP211" s="25"/>
       <c r="AQ211" s="25" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="AR211" s="25"/>
       <c r="AS211" s="25" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="AT211" s="25"/>
       <c r="AU211" s="25"/>
@@ -30061,7 +30051,7 @@
         <v>1528</v>
       </c>
       <c r="E212" s="37" t="s">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="F212" s="25" t="s">
         <v>1529</v>
@@ -30128,16 +30118,16 @@
       </c>
       <c r="AM212" s="25"/>
       <c r="AN212" s="25" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="AO212" s="25"/>
       <c r="AP212" s="25"/>
       <c r="AQ212" s="25" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="AR212" s="25"/>
       <c r="AS212" s="25" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="AT212" s="25"/>
       <c r="AU212" s="25"/>
@@ -30156,7 +30146,7 @@
         <v>435</v>
       </c>
       <c r="E213" s="37" t="s">
-        <v>2023</v>
+        <v>2013</v>
       </c>
       <c r="F213" s="25" t="s">
         <v>433</v>
@@ -30255,7 +30245,7 @@
         <v>459</v>
       </c>
       <c r="E214" s="37" t="s">
-        <v>2024</v>
+        <v>2014</v>
       </c>
       <c r="F214" s="25" t="s">
         <v>460</v>
@@ -30344,7 +30334,7 @@
         <v>436</v>
       </c>
       <c r="E215" s="37" t="s">
-        <v>2025</v>
+        <v>2015</v>
       </c>
       <c r="F215" s="25" t="s">
         <v>434</v>
@@ -30437,7 +30427,7 @@
         <v>443</v>
       </c>
       <c r="E216" s="37" t="s">
-        <v>2026</v>
+        <v>2016</v>
       </c>
       <c r="F216" s="25" t="s">
         <v>1210</v>
@@ -30478,7 +30468,7 @@
       <c r="AK216" s="25"/>
       <c r="AM216" s="25"/>
       <c r="AN216" s="25" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="AO216" s="25"/>
       <c r="AP216" s="25"/>
@@ -30502,7 +30492,7 @@
         <v>444</v>
       </c>
       <c r="E217" s="37" t="s">
-        <v>2027</v>
+        <v>2017</v>
       </c>
       <c r="F217" s="25" t="s">
         <v>439</v>
@@ -30543,7 +30533,7 @@
       <c r="AK217" s="25"/>
       <c r="AM217" s="25"/>
       <c r="AN217" s="25" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="AO217" s="25"/>
       <c r="AP217" s="25"/>
@@ -30567,7 +30557,7 @@
         <v>445</v>
       </c>
       <c r="E218" s="37" t="s">
-        <v>2028</v>
+        <v>2018</v>
       </c>
       <c r="F218" s="25" t="s">
         <v>440</v>
@@ -30608,7 +30598,7 @@
       <c r="AK218" s="25"/>
       <c r="AM218" s="25"/>
       <c r="AN218" s="25" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="AO218" s="25"/>
       <c r="AP218" s="25"/>
@@ -30632,7 +30622,7 @@
         <v>446</v>
       </c>
       <c r="E219" s="37" t="s">
-        <v>2029</v>
+        <v>2019</v>
       </c>
       <c r="F219" s="25" t="s">
         <v>1211</v>
@@ -30673,7 +30663,7 @@
       <c r="AK219" s="25"/>
       <c r="AM219" s="25"/>
       <c r="AN219" s="25" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="AO219" s="25"/>
       <c r="AP219" s="25"/>
@@ -30697,7 +30687,7 @@
         <v>447</v>
       </c>
       <c r="E220" s="37" t="s">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="F220" s="25" t="s">
         <v>1212</v>
@@ -30738,7 +30728,7 @@
       <c r="AK220" s="25"/>
       <c r="AM220" s="25"/>
       <c r="AN220" s="25" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="AO220" s="25"/>
       <c r="AP220" s="25"/>
@@ -30762,7 +30752,7 @@
         <v>102</v>
       </c>
       <c r="E221" s="37" t="s">
-        <v>2031</v>
+        <v>2021</v>
       </c>
       <c r="F221" s="25" t="s">
         <v>103</v>
@@ -30853,7 +30843,7 @@
         <v>104</v>
       </c>
       <c r="E222" s="37" t="s">
-        <v>2032</v>
+        <v>2022</v>
       </c>
       <c r="F222" s="25" t="s">
         <v>105</v>
@@ -30942,7 +30932,7 @@
         <v>106</v>
       </c>
       <c r="E223" s="37" t="s">
-        <v>2033</v>
+        <v>2023</v>
       </c>
       <c r="F223" s="25" t="s">
         <v>107</v>
@@ -31033,7 +31023,7 @@
         <v>136</v>
       </c>
       <c r="E224" s="37" t="s">
-        <v>2034</v>
+        <v>2024</v>
       </c>
       <c r="F224" s="25" t="s">
         <v>108</v>
@@ -31122,7 +31112,7 @@
         <v>110</v>
       </c>
       <c r="E225" s="37" t="s">
-        <v>2035</v>
+        <v>2025</v>
       </c>
       <c r="F225" s="25" t="s">
         <v>111</v>
@@ -31213,7 +31203,7 @@
         <v>112</v>
       </c>
       <c r="E226" s="37" t="s">
-        <v>2036</v>
+        <v>2026</v>
       </c>
       <c r="F226" s="25" t="s">
         <v>113</v>
@@ -31302,7 +31292,7 @@
         <v>114</v>
       </c>
       <c r="E227" s="37" t="s">
-        <v>2037</v>
+        <v>2027</v>
       </c>
       <c r="F227" s="25" t="s">
         <v>115</v>
@@ -31393,7 +31383,7 @@
         <v>116</v>
       </c>
       <c r="E228" s="37" t="s">
-        <v>2038</v>
+        <v>2028</v>
       </c>
       <c r="F228" s="25" t="s">
         <v>117</v>
@@ -31482,7 +31472,7 @@
         <v>122</v>
       </c>
       <c r="E229" s="37" t="s">
-        <v>2039</v>
+        <v>2029</v>
       </c>
       <c r="F229" s="25" t="s">
         <v>109</v>
@@ -31573,7 +31563,7 @@
         <v>118</v>
       </c>
       <c r="E230" s="37" t="s">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="F230" s="25" t="s">
         <v>119</v>
@@ -31664,7 +31654,7 @@
         <v>120</v>
       </c>
       <c r="E231" s="37" t="s">
-        <v>2041</v>
+        <v>2031</v>
       </c>
       <c r="F231" s="25" t="s">
         <v>121</v>
@@ -31755,7 +31745,7 @@
         <v>579</v>
       </c>
       <c r="E232" s="37" t="s">
-        <v>2042</v>
+        <v>2032</v>
       </c>
       <c r="F232" s="25" t="s">
         <v>441</v>
@@ -31824,7 +31814,7 @@
         <v>1176</v>
       </c>
       <c r="E233" s="37" t="s">
-        <v>2043</v>
+        <v>2033</v>
       </c>
       <c r="F233" s="25" t="s">
         <v>442</v>
@@ -31894,7 +31884,7 @@
       <c r="B234" s="50"/>
       <c r="C234" s="50"/>
       <c r="D234" s="25" t="s">
-        <v>2328</v>
+        <v>2318</v>
       </c>
       <c r="E234" s="50"/>
       <c r="F234" s="50"/>
@@ -31985,7 +31975,7 @@
         <v>888</v>
       </c>
       <c r="E235" s="37" t="s">
-        <v>2044</v>
+        <v>2034</v>
       </c>
       <c r="F235" s="25" t="s">
         <v>890</v>
@@ -32050,7 +32040,7 @@
         <v>889</v>
       </c>
       <c r="E236" s="37" t="s">
-        <v>2045</v>
+        <v>2035</v>
       </c>
       <c r="F236" s="25" t="s">
         <v>891</v>
@@ -32077,7 +32067,7 @@
       <c r="V236" s="25"/>
       <c r="W236" s="25"/>
       <c r="X236" s="25" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="Z236" s="25"/>
       <c r="AA236" s="25"/>
@@ -32203,7 +32193,7 @@
         <v>896</v>
       </c>
       <c r="E238" s="37" t="s">
-        <v>2046</v>
+        <v>2036</v>
       </c>
       <c r="F238" s="25" t="s">
         <v>892</v>
@@ -32268,7 +32258,7 @@
         <v>897</v>
       </c>
       <c r="E239" s="37" t="s">
-        <v>2047</v>
+        <v>2037</v>
       </c>
       <c r="F239" s="25" t="s">
         <v>893</v>
@@ -32295,7 +32285,7 @@
       <c r="V239" s="25"/>
       <c r="W239" s="25"/>
       <c r="X239" s="25" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="Z239" s="25"/>
       <c r="AA239" s="25"/>
@@ -32333,7 +32323,7 @@
         <v>1239</v>
       </c>
       <c r="E240" s="37" t="s">
-        <v>2048</v>
+        <v>2038</v>
       </c>
       <c r="F240" s="25" t="s">
         <v>382</v>
@@ -32422,7 +32412,7 @@
         <v>1546</v>
       </c>
       <c r="E241" s="37" t="s">
-        <v>2049</v>
+        <v>2039</v>
       </c>
       <c r="F241" s="25" t="s">
         <v>377</v>
@@ -32514,24 +32504,24 @@
       <c r="B242" s="61"/>
       <c r="C242" s="61"/>
       <c r="D242" s="61" t="s">
-        <v>2262</v>
+        <v>2252</v>
       </c>
       <c r="E242" s="62" t="s">
-        <v>2263</v>
+        <v>2253</v>
       </c>
       <c r="F242" s="61" t="s">
-        <v>2260</v>
+        <v>2250</v>
       </c>
       <c r="G242" s="61" t="s">
-        <v>2261</v>
+        <v>2251</v>
       </c>
       <c r="H242" s="61"/>
       <c r="I242" s="61" t="s">
-        <v>2259</v>
+        <v>2249</v>
       </c>
       <c r="J242" s="61"/>
       <c r="K242" s="61" t="s">
-        <v>2266</v>
+        <v>2256</v>
       </c>
       <c r="L242" s="61"/>
       <c r="M242" s="61"/>
@@ -32579,22 +32569,22 @@
       <c r="B243" s="61"/>
       <c r="C243" s="61"/>
       <c r="D243" s="61" t="s">
-        <v>2264</v>
+        <v>2254</v>
       </c>
       <c r="E243" s="62" t="s">
-        <v>2265</v>
+        <v>2255</v>
       </c>
       <c r="F243" s="61" t="s">
-        <v>2261</v>
+        <v>2251</v>
       </c>
       <c r="G243" s="61"/>
       <c r="H243" s="61"/>
       <c r="I243" s="61" t="s">
-        <v>2276</v>
+        <v>2266</v>
       </c>
       <c r="J243" s="61"/>
       <c r="K243" s="61" t="s">
-        <v>2266</v>
+        <v>2256</v>
       </c>
       <c r="L243" s="61"/>
       <c r="M243" s="61"/>
@@ -32642,24 +32632,24 @@
       <c r="B244" s="61"/>
       <c r="C244" s="61"/>
       <c r="D244" s="61" t="s">
-        <v>2267</v>
+        <v>2257</v>
       </c>
       <c r="E244" s="62" t="s">
-        <v>2271</v>
+        <v>2261</v>
       </c>
       <c r="F244" s="61" t="s">
-        <v>2273</v>
+        <v>2263</v>
       </c>
       <c r="G244" s="61" t="s">
-        <v>2269</v>
+        <v>2259</v>
       </c>
       <c r="H244" s="61"/>
       <c r="I244" s="61" t="s">
-        <v>2274</v>
+        <v>2264</v>
       </c>
       <c r="J244" s="61"/>
       <c r="K244" s="61" t="s">
-        <v>2266</v>
+        <v>2256</v>
       </c>
       <c r="L244" s="61"/>
       <c r="M244" s="61"/>
@@ -32707,22 +32697,22 @@
       <c r="B245" s="61"/>
       <c r="C245" s="61"/>
       <c r="D245" s="61" t="s">
-        <v>2268</v>
+        <v>2258</v>
       </c>
       <c r="E245" s="62" t="s">
-        <v>2272</v>
+        <v>2262</v>
       </c>
       <c r="F245" s="61" t="s">
-        <v>2270</v>
+        <v>2260</v>
       </c>
       <c r="G245" s="61"/>
       <c r="H245" s="61"/>
       <c r="I245" s="61" t="s">
-        <v>2275</v>
+        <v>2265</v>
       </c>
       <c r="J245" s="61"/>
       <c r="K245" s="61" t="s">
-        <v>2266</v>
+        <v>2256</v>
       </c>
       <c r="L245" s="61"/>
       <c r="M245" s="61"/>
@@ -32770,24 +32760,24 @@
       <c r="B246" s="61"/>
       <c r="C246" s="61"/>
       <c r="D246" s="61" t="s">
-        <v>2277</v>
+        <v>2267</v>
       </c>
       <c r="E246" s="62" t="s">
-        <v>2279</v>
+        <v>2269</v>
       </c>
       <c r="F246" s="61" t="s">
-        <v>2278</v>
+        <v>2268</v>
       </c>
       <c r="G246" s="61" t="s">
         <v>2</v>
       </c>
       <c r="H246" s="61"/>
       <c r="I246" s="61" t="s">
-        <v>2280</v>
+        <v>2270</v>
       </c>
       <c r="J246" s="61"/>
       <c r="K246" s="61" t="s">
-        <v>2266</v>
+        <v>2256</v>
       </c>
       <c r="L246" s="61"/>
       <c r="M246" s="61"/>
@@ -32835,22 +32825,22 @@
       <c r="B247" s="61"/>
       <c r="C247" s="61"/>
       <c r="D247" s="61" t="s">
-        <v>2281</v>
+        <v>2271</v>
       </c>
       <c r="E247" s="62"/>
       <c r="F247" s="61" t="s">
-        <v>2282</v>
+        <v>2272</v>
       </c>
       <c r="G247" s="61" t="s">
         <v>2</v>
       </c>
       <c r="H247" s="61"/>
       <c r="I247" s="61" t="s">
-        <v>1822</v>
+        <v>1812</v>
       </c>
       <c r="J247" s="61"/>
       <c r="K247" s="61" t="s">
-        <v>1823</v>
+        <v>1813</v>
       </c>
       <c r="L247" s="61"/>
       <c r="M247" s="61"/>
@@ -32898,22 +32888,22 @@
       <c r="B248" s="61"/>
       <c r="C248" s="61"/>
       <c r="D248" s="61" t="s">
-        <v>2283</v>
+        <v>2273</v>
       </c>
       <c r="E248" s="62"/>
       <c r="F248" s="61" t="s">
-        <v>2284</v>
+        <v>2274</v>
       </c>
       <c r="G248" s="61" t="s">
         <v>2</v>
       </c>
       <c r="H248" s="61"/>
       <c r="I248" s="61" t="s">
-        <v>2285</v>
+        <v>2275</v>
       </c>
       <c r="J248" s="61"/>
       <c r="K248" s="61" t="s">
-        <v>2266</v>
+        <v>2256</v>
       </c>
       <c r="L248" s="61"/>
       <c r="M248" s="61"/>
@@ -32961,22 +32951,22 @@
       <c r="B249" s="61"/>
       <c r="C249" s="61"/>
       <c r="D249" s="61" t="s">
-        <v>2296</v>
+        <v>2286</v>
       </c>
       <c r="E249" s="62"/>
       <c r="F249" s="61" t="s">
-        <v>2286</v>
+        <v>2276</v>
       </c>
       <c r="G249" s="61" t="s">
         <v>2</v>
       </c>
       <c r="H249" s="61"/>
       <c r="I249" s="61" t="s">
-        <v>2323</v>
+        <v>2313</v>
       </c>
       <c r="J249" s="61"/>
       <c r="K249" s="61" t="s">
-        <v>2266</v>
+        <v>2256</v>
       </c>
       <c r="L249" s="61"/>
       <c r="M249" s="61"/>
@@ -33024,22 +33014,22 @@
       <c r="B250" s="61"/>
       <c r="C250" s="61"/>
       <c r="D250" s="61" t="s">
-        <v>2297</v>
+        <v>2287</v>
       </c>
       <c r="E250" s="62"/>
       <c r="F250" s="61" t="s">
-        <v>2287</v>
+        <v>2277</v>
       </c>
       <c r="G250" s="61" t="s">
         <v>2</v>
       </c>
       <c r="H250" s="61"/>
       <c r="I250" s="61" t="s">
-        <v>1822</v>
+        <v>1812</v>
       </c>
       <c r="J250" s="61"/>
       <c r="K250" s="61" t="s">
-        <v>1823</v>
+        <v>1813</v>
       </c>
       <c r="L250" s="61"/>
       <c r="M250" s="61"/>
@@ -33087,21 +33077,21 @@
       <c r="B251" s="63"/>
       <c r="C251" s="63"/>
       <c r="D251" s="63" t="s">
-        <v>2299</v>
+        <v>2289</v>
       </c>
       <c r="E251" s="50"/>
       <c r="F251" s="50"/>
       <c r="G251" s="50"/>
       <c r="H251" s="50"/>
       <c r="I251" s="50" t="s">
-        <v>2308</v>
+        <v>2298</v>
       </c>
       <c r="J251" s="50"/>
       <c r="K251" s="50" t="s">
-        <v>2309</v>
+        <v>2299</v>
       </c>
       <c r="L251" s="50" t="s">
-        <v>2310</v>
+        <v>2300</v>
       </c>
       <c r="M251" s="50"/>
       <c r="N251" s="50"/>
@@ -33151,22 +33141,22 @@
       <c r="B252" s="61"/>
       <c r="C252" s="61"/>
       <c r="D252" s="61" t="s">
-        <v>2300</v>
+        <v>2290</v>
       </c>
       <c r="E252" s="62"/>
       <c r="F252" s="61" t="s">
-        <v>2288</v>
+        <v>2278</v>
       </c>
       <c r="G252" s="61" t="s">
-        <v>2288</v>
+        <v>2278</v>
       </c>
       <c r="H252" s="61"/>
       <c r="I252" s="61" t="s">
-        <v>2311</v>
+        <v>2301</v>
       </c>
       <c r="J252" s="61"/>
       <c r="K252" s="61" t="s">
-        <v>2312</v>
+        <v>2302</v>
       </c>
       <c r="L252" s="61"/>
       <c r="M252" s="61"/>
@@ -33174,7 +33164,7 @@
       <c r="O252" s="61"/>
       <c r="P252" s="61"/>
       <c r="Q252" s="61" t="s">
-        <v>2313</v>
+        <v>2303</v>
       </c>
       <c r="R252" s="61"/>
       <c r="S252" s="61"/>
@@ -33219,7 +33209,7 @@
       </c>
       <c r="AM252" s="33"/>
       <c r="AN252" s="33" t="s">
-        <v>2298</v>
+        <v>2288</v>
       </c>
       <c r="AO252" s="33"/>
       <c r="AP252" s="33"/>
@@ -33240,20 +33230,20 @@
       <c r="B253" s="61"/>
       <c r="C253" s="61"/>
       <c r="D253" s="61" t="s">
-        <v>2301</v>
+        <v>2291</v>
       </c>
       <c r="E253" s="62"/>
       <c r="F253" s="61" t="s">
-        <v>2289</v>
+        <v>2279</v>
       </c>
       <c r="G253" s="61"/>
       <c r="H253" s="61"/>
       <c r="I253" s="61" t="s">
-        <v>2311</v>
+        <v>2301</v>
       </c>
       <c r="J253" s="61"/>
       <c r="K253" s="61" t="s">
-        <v>2314</v>
+        <v>2304</v>
       </c>
       <c r="L253" s="61"/>
       <c r="M253" s="61"/>
@@ -33261,7 +33251,7 @@
       <c r="O253" s="61"/>
       <c r="P253" s="61"/>
       <c r="Q253" s="61" t="s">
-        <v>2315</v>
+        <v>2305</v>
       </c>
       <c r="R253" s="61"/>
       <c r="S253" s="61"/>
@@ -33306,7 +33296,7 @@
       </c>
       <c r="AM253" s="33"/>
       <c r="AN253" s="33" t="s">
-        <v>2319</v>
+        <v>2309</v>
       </c>
       <c r="AO253" s="33"/>
       <c r="AP253" s="33"/>
@@ -33327,20 +33317,20 @@
       <c r="B254" s="61"/>
       <c r="C254" s="61"/>
       <c r="D254" s="61" t="s">
-        <v>2302</v>
+        <v>2292</v>
       </c>
       <c r="E254" s="62"/>
       <c r="F254" s="61" t="s">
-        <v>2290</v>
+        <v>2280</v>
       </c>
       <c r="G254" s="61"/>
       <c r="H254" s="61"/>
       <c r="I254" s="61" t="s">
-        <v>2311</v>
+        <v>2301</v>
       </c>
       <c r="J254" s="61"/>
       <c r="K254" s="61" t="s">
-        <v>2314</v>
+        <v>2304</v>
       </c>
       <c r="L254" s="61"/>
       <c r="M254" s="61"/>
@@ -33348,7 +33338,7 @@
       <c r="O254" s="61"/>
       <c r="P254" s="61"/>
       <c r="Q254" s="61" t="s">
-        <v>2316</v>
+        <v>2306</v>
       </c>
       <c r="R254" s="61"/>
       <c r="S254" s="61"/>
@@ -33393,7 +33383,7 @@
       </c>
       <c r="AM254" s="33"/>
       <c r="AN254" s="33" t="s">
-        <v>2320</v>
+        <v>2310</v>
       </c>
       <c r="AO254" s="33"/>
       <c r="AP254" s="33"/>
@@ -33414,20 +33404,20 @@
       <c r="B255" s="61"/>
       <c r="C255" s="61"/>
       <c r="D255" s="61" t="s">
-        <v>2303</v>
+        <v>2293</v>
       </c>
       <c r="E255" s="62"/>
       <c r="F255" s="61" t="s">
-        <v>2291</v>
+        <v>2281</v>
       </c>
       <c r="G255" s="61"/>
       <c r="H255" s="61"/>
       <c r="I255" s="61" t="s">
-        <v>2311</v>
+        <v>2301</v>
       </c>
       <c r="J255" s="61"/>
       <c r="K255" s="61" t="s">
-        <v>2314</v>
+        <v>2304</v>
       </c>
       <c r="L255" s="61"/>
       <c r="M255" s="61"/>
@@ -33435,7 +33425,7 @@
       <c r="O255" s="61"/>
       <c r="P255" s="61"/>
       <c r="Q255" s="61" t="s">
-        <v>2317</v>
+        <v>2307</v>
       </c>
       <c r="R255" s="61"/>
       <c r="S255" s="61"/>
@@ -33480,7 +33470,7 @@
       </c>
       <c r="AM255" s="33"/>
       <c r="AN255" s="33" t="s">
-        <v>2321</v>
+        <v>2311</v>
       </c>
       <c r="AO255" s="33"/>
       <c r="AP255" s="33"/>
@@ -33501,22 +33491,22 @@
       <c r="B256" s="61"/>
       <c r="C256" s="61"/>
       <c r="D256" s="61" t="s">
-        <v>2304</v>
+        <v>2294</v>
       </c>
       <c r="E256" s="62"/>
       <c r="F256" s="61" t="s">
-        <v>2292</v>
+        <v>2282</v>
       </c>
       <c r="G256" s="61" t="s">
         <v>2</v>
       </c>
       <c r="H256" s="61"/>
       <c r="I256" s="61" t="s">
-        <v>2311</v>
+        <v>2301</v>
       </c>
       <c r="J256" s="61"/>
       <c r="K256" s="61" t="s">
-        <v>2318</v>
+        <v>2308</v>
       </c>
       <c r="L256" s="61"/>
       <c r="M256" s="61"/>
@@ -33567,7 +33557,7 @@
       </c>
       <c r="AM256" s="33"/>
       <c r="AN256" s="33" t="s">
-        <v>2322</v>
+        <v>2312</v>
       </c>
       <c r="AO256" s="33"/>
       <c r="AP256" s="33"/>
@@ -33588,22 +33578,22 @@
       <c r="B257" s="61"/>
       <c r="C257" s="61"/>
       <c r="D257" s="61" t="s">
-        <v>2335</v>
+        <v>2325</v>
       </c>
       <c r="E257" s="62"/>
       <c r="F257" s="61" t="s">
-        <v>2336</v>
+        <v>2326</v>
       </c>
       <c r="G257" s="61" t="s">
-        <v>2337</v>
+        <v>2327</v>
       </c>
       <c r="H257" s="61"/>
       <c r="I257" s="61" t="s">
-        <v>2338</v>
+        <v>2328</v>
       </c>
       <c r="J257" s="61"/>
       <c r="K257" s="61" t="s">
-        <v>2266</v>
+        <v>2256</v>
       </c>
       <c r="L257" s="61"/>
       <c r="M257" s="61"/>
@@ -33651,22 +33641,22 @@
       <c r="B258" s="61"/>
       <c r="C258" s="61"/>
       <c r="D258" s="61" t="s">
-        <v>2305</v>
+        <v>2295</v>
       </c>
       <c r="E258" s="62"/>
       <c r="F258" s="61" t="s">
-        <v>2293</v>
+        <v>2283</v>
       </c>
       <c r="G258" s="61" t="s">
         <v>2</v>
       </c>
       <c r="H258" s="61"/>
       <c r="I258" s="61" t="s">
-        <v>2324</v>
+        <v>2314</v>
       </c>
       <c r="J258" s="61"/>
       <c r="K258" s="61" t="s">
-        <v>2266</v>
+        <v>2256</v>
       </c>
       <c r="L258" s="61"/>
       <c r="M258" s="61"/>
@@ -33714,22 +33704,22 @@
       <c r="B259" s="61"/>
       <c r="C259" s="61"/>
       <c r="D259" s="61" t="s">
-        <v>2306</v>
+        <v>2296</v>
       </c>
       <c r="E259" s="62"/>
       <c r="F259" s="61" t="s">
-        <v>2294</v>
+        <v>2284</v>
       </c>
       <c r="G259" s="61" t="s">
         <v>2</v>
       </c>
       <c r="H259" s="61"/>
       <c r="I259" s="61" t="s">
-        <v>2325</v>
+        <v>2315</v>
       </c>
       <c r="J259" s="61"/>
       <c r="K259" s="61" t="s">
-        <v>2266</v>
+        <v>2256</v>
       </c>
       <c r="L259" s="61"/>
       <c r="M259" s="61"/>
@@ -33777,28 +33767,28 @@
       <c r="B260" s="25"/>
       <c r="C260" s="25"/>
       <c r="D260" s="61" t="s">
-        <v>2339</v>
+        <v>2329</v>
       </c>
       <c r="E260" s="64" t="s">
-        <v>2329</v>
+        <v>2319</v>
       </c>
       <c r="F260" s="65" t="s">
-        <v>2330</v>
+        <v>2320</v>
       </c>
       <c r="G260" s="65" t="s">
         <v>2</v>
       </c>
       <c r="H260" s="65"/>
       <c r="I260" s="65" t="s">
-        <v>2333</v>
+        <v>2323</v>
       </c>
       <c r="J260" s="65"/>
       <c r="K260" s="65" t="s">
-        <v>2331</v>
+        <v>2321</v>
       </c>
       <c r="L260" s="65"/>
       <c r="M260" s="65" t="s">
-        <v>2332</v>
+        <v>2322</v>
       </c>
       <c r="N260" s="25"/>
       <c r="O260" s="25"/>
@@ -33812,38 +33802,38 @@
       <c r="W260" s="25"/>
       <c r="X260" s="25"/>
       <c r="Z260" s="25" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AA260" s="25" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AB260" s="25" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AC260" s="25" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AD260" s="25" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AE260" s="25"/>
       <c r="AF260" s="25" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AG260" s="25" t="s">
-        <v>1834</v>
+        <v>1824</v>
       </c>
       <c r="AH260" s="25" t="s">
-        <v>1834</v>
+        <v>1824</v>
       </c>
       <c r="AI260" s="25" t="s">
-        <v>2334</v>
+        <v>2324</v>
       </c>
       <c r="AJ260" s="25" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AK260" s="25" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AM260" s="25"/>
       <c r="AN260" s="25"/>
@@ -33866,22 +33856,22 @@
       <c r="B261" s="61"/>
       <c r="C261" s="61"/>
       <c r="D261" s="61" t="s">
-        <v>2307</v>
+        <v>2297</v>
       </c>
       <c r="E261" s="62"/>
       <c r="F261" s="61" t="s">
-        <v>2295</v>
+        <v>2285</v>
       </c>
       <c r="G261" s="61" t="s">
         <v>2</v>
       </c>
       <c r="H261" s="61"/>
       <c r="I261" s="61" t="s">
-        <v>2326</v>
+        <v>2316</v>
       </c>
       <c r="J261" s="61"/>
       <c r="K261" s="61" t="s">
-        <v>2266</v>
+        <v>2256</v>
       </c>
       <c r="L261" s="61"/>
       <c r="M261" s="61"/>
@@ -33929,28 +33919,28 @@
       <c r="B262" s="25"/>
       <c r="C262" s="25"/>
       <c r="D262" s="61" t="s">
-        <v>2340</v>
+        <v>2330</v>
       </c>
       <c r="E262" s="64" t="s">
-        <v>2342</v>
+        <v>2332</v>
       </c>
       <c r="F262" s="65" t="s">
-        <v>2341</v>
+        <v>2331</v>
       </c>
       <c r="G262" s="65" t="s">
         <v>2</v>
       </c>
       <c r="H262" s="65"/>
       <c r="I262" s="65" t="s">
-        <v>2340</v>
+        <v>2330</v>
       </c>
       <c r="J262" s="65"/>
       <c r="K262" s="65" t="s">
-        <v>2331</v>
+        <v>2321</v>
       </c>
       <c r="L262" s="65"/>
       <c r="M262" s="65" t="s">
-        <v>2332</v>
+        <v>2322</v>
       </c>
       <c r="N262" s="25"/>
       <c r="O262" s="25"/>
@@ -33964,38 +33954,38 @@
       <c r="W262" s="25"/>
       <c r="X262" s="25"/>
       <c r="Z262" s="25" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AA262" s="25" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AB262" s="25" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AC262" s="25" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AD262" s="25" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AE262" s="25"/>
       <c r="AF262" s="25" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AG262" s="25" t="s">
-        <v>1834</v>
+        <v>1824</v>
       </c>
       <c r="AH262" s="25" t="s">
-        <v>1834</v>
+        <v>1824</v>
       </c>
       <c r="AI262" s="25" t="s">
-        <v>2334</v>
+        <v>2324</v>
       </c>
       <c r="AJ262" s="25" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AK262" s="25" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="AM262" s="25"/>
       <c r="AN262" s="25"/>
@@ -34172,40 +34162,40 @@
     <row r="267" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A267" s="9"/>
       <c r="AM267" s="40" t="s">
-        <v>2255</v>
+        <v>2245</v>
       </c>
       <c r="AN267" s="40" t="s">
-        <v>2256</v>
+        <v>2246</v>
       </c>
       <c r="AO267" s="40" t="s">
-        <v>2255</v>
+        <v>2245</v>
       </c>
       <c r="AP267" s="40" t="s">
-        <v>2256</v>
+        <v>2246</v>
       </c>
       <c r="AQ267" s="40" t="s">
-        <v>2255</v>
+        <v>2245</v>
       </c>
       <c r="AR267" s="40" t="s">
-        <v>2256</v>
+        <v>2246</v>
       </c>
       <c r="AS267" s="40" t="s">
-        <v>2255</v>
+        <v>2245</v>
       </c>
       <c r="AT267" s="40" t="s">
-        <v>2256</v>
+        <v>2246</v>
       </c>
       <c r="AU267" s="40" t="s">
-        <v>2255</v>
+        <v>2245</v>
       </c>
       <c r="AV267" s="40" t="s">
-        <v>2256</v>
+        <v>2246</v>
       </c>
       <c r="AW267" s="40" t="s">
-        <v>2255</v>
+        <v>2245</v>
       </c>
       <c r="AX267" s="40" t="s">
-        <v>2256</v>
+        <v>2246</v>
       </c>
       <c r="AZ267" s="13"/>
     </row>
@@ -34299,7 +34289,7 @@
         <v>849</v>
       </c>
       <c r="E269" s="28" t="s">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="F269" s="27" t="s">
         <v>463</v>
@@ -34390,7 +34380,7 @@
         <v>1237</v>
       </c>
       <c r="E270" s="37" t="s">
-        <v>2051</v>
+        <v>2041</v>
       </c>
       <c r="F270" s="25" t="s">
         <v>1238</v>
@@ -34455,7 +34445,7 @@
         <v>591</v>
       </c>
       <c r="E271" s="37" t="s">
-        <v>2052</v>
+        <v>2042</v>
       </c>
       <c r="F271" s="25" t="s">
         <v>594</v>
@@ -34548,7 +34538,7 @@
         <v>589</v>
       </c>
       <c r="E272" s="37" t="s">
-        <v>2053</v>
+        <v>2043</v>
       </c>
       <c r="F272" s="25" t="s">
         <v>590</v>
@@ -34613,17 +34603,17 @@
       </c>
       <c r="AM272" s="25"/>
       <c r="AN272" s="25" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="AO272" s="25"/>
       <c r="AP272" s="25"/>
       <c r="AQ272" s="25"/>
       <c r="AR272" s="25" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="AS272" s="25"/>
       <c r="AT272" s="25" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="AU272" s="25"/>
       <c r="AV272" s="25"/>
@@ -34641,7 +34631,7 @@
         <v>1265</v>
       </c>
       <c r="E273" s="37" t="s">
-        <v>2054</v>
+        <v>2044</v>
       </c>
       <c r="F273" s="25" t="s">
         <v>1266</v>
@@ -34734,7 +34724,7 @@
         <v>1269</v>
       </c>
       <c r="E274" s="37" t="s">
-        <v>2055</v>
+        <v>2045</v>
       </c>
       <c r="F274" s="25" t="s">
         <v>1270</v>
@@ -34827,7 +34817,7 @@
         <v>278</v>
       </c>
       <c r="E275" s="37" t="s">
-        <v>2056</v>
+        <v>2046</v>
       </c>
       <c r="F275" s="25" t="s">
         <v>277</v>
@@ -34892,22 +34882,22 @@
       </c>
       <c r="AM275" s="25"/>
       <c r="AN275" s="25" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="AO275" s="25"/>
       <c r="AP275" s="25"/>
       <c r="AQ275" s="25"/>
       <c r="AR275" s="25" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="AS275" s="25" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="AT275" s="25" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="AU275" s="25" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="AV275" s="25"/>
       <c r="AW275" s="25"/>
@@ -34921,10 +34911,10 @@
       <c r="B276" s="25"/>
       <c r="C276" s="25"/>
       <c r="D276" s="25" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="E276" s="37" t="s">
-        <v>2057</v>
+        <v>2047</v>
       </c>
       <c r="F276" s="25" t="s">
         <v>1208</v>
@@ -34938,7 +34928,7 @@
       </c>
       <c r="J276" s="25"/>
       <c r="K276" s="25" t="s">
-        <v>1811</v>
+        <v>1801</v>
       </c>
       <c r="L276" s="25"/>
       <c r="M276" s="25"/>
@@ -34946,21 +34936,21 @@
       <c r="O276" s="25"/>
       <c r="P276" s="25"/>
       <c r="Q276" s="25" t="s">
-        <v>1686</v>
+        <v>1676</v>
       </c>
       <c r="R276" s="25"/>
       <c r="S276" s="25" t="s">
-        <v>1694</v>
+        <v>1684</v>
       </c>
       <c r="T276" s="25"/>
       <c r="U276" s="25" t="s">
-        <v>1695</v>
+        <v>1685</v>
       </c>
       <c r="V276" s="25" t="s">
-        <v>1812</v>
+        <v>1802</v>
       </c>
       <c r="W276" s="25" t="s">
-        <v>1813</v>
+        <v>1803</v>
       </c>
       <c r="X276" s="25"/>
       <c r="Z276" s="25" t="s">
@@ -34999,18 +34989,18 @@
       </c>
       <c r="AM276" s="25"/>
       <c r="AN276" s="25" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="AO276" s="25"/>
       <c r="AP276" s="25" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="AQ276" s="25" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="AR276" s="25"/>
       <c r="AS276" s="25" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="AT276" s="25"/>
       <c r="AU276" s="25"/>
@@ -35026,13 +35016,13 @@
       <c r="B277" s="25"/>
       <c r="C277" s="25"/>
       <c r="D277" s="25" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="E277" s="37" t="s">
-        <v>2058</v>
+        <v>2048</v>
       </c>
       <c r="F277" s="25" t="s">
-        <v>1815</v>
+        <v>1805</v>
       </c>
       <c r="G277" s="25" t="s">
         <v>47</v>
@@ -35094,18 +35084,18 @@
       </c>
       <c r="AM277" s="25"/>
       <c r="AN277" s="25" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="AO277" s="25"/>
       <c r="AP277" s="25" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="AQ277" s="25" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="AR277" s="25"/>
       <c r="AS277" s="25" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="AT277" s="25"/>
       <c r="AU277" s="25"/>
@@ -35207,7 +35197,7 @@
       <c r="B279" s="25"/>
       <c r="C279" s="25"/>
       <c r="D279" s="25" t="s">
-        <v>1689</v>
+        <v>1679</v>
       </c>
       <c r="E279" s="37"/>
       <c r="F279" s="25"/>
@@ -35226,21 +35216,21 @@
       <c r="O279" s="25"/>
       <c r="P279" s="25"/>
       <c r="Q279" s="25" t="s">
-        <v>1548</v>
+        <v>2352</v>
       </c>
       <c r="R279" s="25"/>
       <c r="S279" s="25" t="s">
-        <v>1678</v>
+        <v>2353</v>
       </c>
       <c r="T279" s="25"/>
       <c r="U279" s="25" t="s">
-        <v>1679</v>
+        <v>2357</v>
       </c>
       <c r="V279" s="25" t="s">
-        <v>1608</v>
+        <v>2351</v>
       </c>
       <c r="W279" s="25" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="X279" s="25"/>
       <c r="Z279" s="25"/>
@@ -35284,7 +35274,7 @@
       <c r="B280" s="25"/>
       <c r="C280" s="25"/>
       <c r="D280" s="25" t="s">
-        <v>1690</v>
+        <v>1680</v>
       </c>
       <c r="E280" s="37"/>
       <c r="F280" s="25"/>
@@ -35303,21 +35293,21 @@
       <c r="O280" s="25"/>
       <c r="P280" s="25"/>
       <c r="Q280" s="25" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="R280" s="25"/>
       <c r="S280" s="25" t="s">
-        <v>1680</v>
+        <v>2354</v>
       </c>
       <c r="T280" s="25"/>
       <c r="U280" s="25" t="s">
-        <v>1681</v>
+        <v>2358</v>
       </c>
       <c r="V280" s="25" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="W280" s="25" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="X280" s="25"/>
       <c r="Z280" s="25"/>
@@ -35361,7 +35351,7 @@
       <c r="B281" s="25"/>
       <c r="C281" s="25"/>
       <c r="D281" s="25" t="s">
-        <v>1691</v>
+        <v>1681</v>
       </c>
       <c r="E281" s="37"/>
       <c r="F281" s="25"/>
@@ -35380,21 +35370,21 @@
       <c r="O281" s="25"/>
       <c r="P281" s="25"/>
       <c r="Q281" s="25" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="R281" s="25"/>
       <c r="S281" s="25" t="s">
-        <v>1682</v>
+        <v>2355</v>
       </c>
       <c r="T281" s="25"/>
       <c r="U281" s="25" t="s">
-        <v>1683</v>
+        <v>2359</v>
       </c>
       <c r="V281" s="25" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="W281" s="25" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="X281" s="25"/>
       <c r="Z281" s="25"/>
@@ -35438,7 +35428,7 @@
       <c r="B282" s="25"/>
       <c r="C282" s="25"/>
       <c r="D282" s="25" t="s">
-        <v>1692</v>
+        <v>1682</v>
       </c>
       <c r="E282" s="37"/>
       <c r="F282" s="25"/>
@@ -35457,21 +35447,21 @@
       <c r="O282" s="25"/>
       <c r="P282" s="25"/>
       <c r="Q282" s="25" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="R282" s="25"/>
       <c r="S282" s="25" t="s">
-        <v>1684</v>
+        <v>2356</v>
       </c>
       <c r="T282" s="25"/>
       <c r="U282" s="25" t="s">
-        <v>1685</v>
+        <v>2360</v>
       </c>
       <c r="V282" s="25" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="W282" s="25" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="X282" s="25"/>
       <c r="Z282" s="25"/>
@@ -35515,7 +35505,7 @@
       <c r="B283" s="25"/>
       <c r="C283" s="25"/>
       <c r="D283" s="25" t="s">
-        <v>1693</v>
+        <v>1683</v>
       </c>
       <c r="E283" s="37"/>
       <c r="F283" s="25"/>
@@ -35585,7 +35575,7 @@
         <v>599</v>
       </c>
       <c r="E284" s="37" t="s">
-        <v>2059</v>
+        <v>2049</v>
       </c>
       <c r="F284" s="25" t="s">
         <v>133</v>
@@ -35676,7 +35666,7 @@
         <v>242</v>
       </c>
       <c r="E285" s="37" t="s">
-        <v>2060</v>
+        <v>2050</v>
       </c>
       <c r="F285" s="25" t="s">
         <v>244</v>
@@ -35741,18 +35731,18 @@
       </c>
       <c r="AM285" s="25"/>
       <c r="AN285" s="25" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="AO285" s="25"/>
       <c r="AP285" s="25" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="AQ285" s="25" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="AR285" s="25"/>
       <c r="AS285" s="25" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="AT285" s="25"/>
       <c r="AU285" s="25"/>
@@ -35768,10 +35758,10 @@
       <c r="B286" s="25"/>
       <c r="C286" s="25"/>
       <c r="D286" s="25" t="s">
-        <v>2343</v>
+        <v>2333</v>
       </c>
       <c r="E286" s="37" t="s">
-        <v>2061</v>
+        <v>2051</v>
       </c>
       <c r="F286" s="25" t="s">
         <v>464</v>
@@ -35862,7 +35852,7 @@
         <v>317</v>
       </c>
       <c r="E287" s="37" t="s">
-        <v>2062</v>
+        <v>2052</v>
       </c>
       <c r="F287" s="25" t="s">
         <v>246</v>
@@ -35953,7 +35943,7 @@
         <v>243</v>
       </c>
       <c r="E288" s="37" t="s">
-        <v>2063</v>
+        <v>2053</v>
       </c>
       <c r="F288" s="25" t="s">
         <v>247</v>
@@ -36018,11 +36008,11 @@
       </c>
       <c r="AM288" s="25"/>
       <c r="AN288" s="25" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="AO288" s="25"/>
       <c r="AP288" s="25" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="AQ288" s="25"/>
       <c r="AR288" s="25"/>
@@ -36044,7 +36034,7 @@
         <v>601</v>
       </c>
       <c r="E289" s="37" t="s">
-        <v>2064</v>
+        <v>2054</v>
       </c>
       <c r="F289" s="25" t="s">
         <v>335</v>
@@ -36135,7 +36125,7 @@
         <v>123</v>
       </c>
       <c r="E290" s="37" t="s">
-        <v>2065</v>
+        <v>2055</v>
       </c>
       <c r="F290" s="25" t="s">
         <v>337</v>
@@ -36200,11 +36190,11 @@
       </c>
       <c r="AM290" s="25"/>
       <c r="AN290" s="25" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="AO290" s="25"/>
       <c r="AP290" s="25" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="AQ290" s="25"/>
       <c r="AR290" s="25"/>
@@ -36226,7 +36216,7 @@
         <v>602</v>
       </c>
       <c r="E291" s="37" t="s">
-        <v>2066</v>
+        <v>2056</v>
       </c>
       <c r="F291" s="25" t="s">
         <v>338</v>
@@ -36317,7 +36307,7 @@
         <v>124</v>
       </c>
       <c r="E292" s="37" t="s">
-        <v>2067</v>
+        <v>2057</v>
       </c>
       <c r="F292" s="25" t="s">
         <v>339</v>
@@ -36382,11 +36372,11 @@
       </c>
       <c r="AM292" s="25"/>
       <c r="AN292" s="25" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="AO292" s="25"/>
       <c r="AP292" s="25" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="AQ292" s="25"/>
       <c r="AR292" s="25"/>
@@ -36408,7 +36398,7 @@
         <v>125</v>
       </c>
       <c r="E293" s="37" t="s">
-        <v>2068</v>
+        <v>2058</v>
       </c>
       <c r="F293" s="25" t="s">
         <v>340</v>
@@ -36473,11 +36463,11 @@
       </c>
       <c r="AM293" s="25"/>
       <c r="AN293" s="25" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="AO293" s="25"/>
       <c r="AP293" s="25" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="AQ293" s="25"/>
       <c r="AR293" s="25"/>
@@ -36499,7 +36489,7 @@
         <v>126</v>
       </c>
       <c r="E294" s="37" t="s">
-        <v>2069</v>
+        <v>2059</v>
       </c>
       <c r="F294" s="25" t="s">
         <v>341</v>
@@ -36564,11 +36554,11 @@
       </c>
       <c r="AM294" s="25"/>
       <c r="AN294" s="25" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="AO294" s="25"/>
       <c r="AP294" s="25" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="AQ294" s="25"/>
       <c r="AR294" s="25"/>
@@ -36590,7 +36580,7 @@
         <v>127</v>
       </c>
       <c r="E295" s="37" t="s">
-        <v>2070</v>
+        <v>2060</v>
       </c>
       <c r="F295" s="25" t="s">
         <v>342</v>
@@ -36655,11 +36645,11 @@
       </c>
       <c r="AM295" s="25"/>
       <c r="AN295" s="25" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="AO295" s="25"/>
       <c r="AP295" s="25" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="AQ295" s="25"/>
       <c r="AR295" s="25"/>
@@ -36681,7 +36671,7 @@
         <v>128</v>
       </c>
       <c r="E296" s="37" t="s">
-        <v>2071</v>
+        <v>2061</v>
       </c>
       <c r="F296" s="25" t="s">
         <v>343</v>
@@ -36746,11 +36736,11 @@
       </c>
       <c r="AM296" s="25"/>
       <c r="AN296" s="25" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="AO296" s="25"/>
       <c r="AP296" s="25" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="AQ296" s="25"/>
       <c r="AR296" s="25"/>
@@ -36772,7 +36762,7 @@
         <v>699</v>
       </c>
       <c r="E297" s="37" t="s">
-        <v>2072</v>
+        <v>2062</v>
       </c>
       <c r="F297" s="25" t="s">
         <v>695</v>
@@ -36863,7 +36853,7 @@
         <v>700</v>
       </c>
       <c r="E298" s="37" t="s">
-        <v>2073</v>
+        <v>2063</v>
       </c>
       <c r="F298" s="25" t="s">
         <v>696</v>
@@ -36928,11 +36918,11 @@
       </c>
       <c r="AM298" s="25"/>
       <c r="AN298" s="25" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="AO298" s="25"/>
       <c r="AP298" s="25" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="AQ298" s="25"/>
       <c r="AR298" s="25"/>
@@ -36954,7 +36944,7 @@
         <v>701</v>
       </c>
       <c r="E299" s="37" t="s">
-        <v>2074</v>
+        <v>2064</v>
       </c>
       <c r="F299" s="25" t="s">
         <v>697</v>
@@ -37019,11 +37009,11 @@
       </c>
       <c r="AM299" s="25"/>
       <c r="AN299" s="25" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="AO299" s="25"/>
       <c r="AP299" s="25" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="AQ299" s="25"/>
       <c r="AR299" s="25"/>
@@ -37045,7 +37035,7 @@
         <v>702</v>
       </c>
       <c r="E300" s="37" t="s">
-        <v>2075</v>
+        <v>2065</v>
       </c>
       <c r="F300" s="25" t="s">
         <v>698</v>
@@ -37110,11 +37100,11 @@
       </c>
       <c r="AM300" s="25"/>
       <c r="AN300" s="25" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="AO300" s="25"/>
       <c r="AP300" s="25" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="AQ300" s="25"/>
       <c r="AR300" s="25"/>
@@ -37136,7 +37126,7 @@
         <v>707</v>
       </c>
       <c r="E301" s="37" t="s">
-        <v>2076</v>
+        <v>2066</v>
       </c>
       <c r="F301" s="25" t="s">
         <v>1213</v>
@@ -37201,11 +37191,11 @@
       </c>
       <c r="AM301" s="25"/>
       <c r="AN301" s="25" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="AO301" s="25"/>
       <c r="AP301" s="25" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="AQ301" s="25"/>
       <c r="AR301" s="25"/>
@@ -37227,7 +37217,7 @@
         <v>704</v>
       </c>
       <c r="E302" s="37" t="s">
-        <v>2077</v>
+        <v>2067</v>
       </c>
       <c r="F302" s="25" t="s">
         <v>1214</v>
@@ -37292,11 +37282,11 @@
       </c>
       <c r="AM302" s="25"/>
       <c r="AN302" s="25" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="AO302" s="25"/>
       <c r="AP302" s="25" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="AQ302" s="25"/>
       <c r="AR302" s="25"/>
@@ -37318,7 +37308,7 @@
         <v>705</v>
       </c>
       <c r="E303" s="37" t="s">
-        <v>2078</v>
+        <v>2068</v>
       </c>
       <c r="F303" s="25" t="s">
         <v>1215</v>
@@ -37383,11 +37373,11 @@
       </c>
       <c r="AM303" s="25"/>
       <c r="AN303" s="25" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="AO303" s="25"/>
       <c r="AP303" s="25" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="AQ303" s="25"/>
       <c r="AR303" s="25"/>
@@ -37409,7 +37399,7 @@
         <v>706</v>
       </c>
       <c r="E304" s="37" t="s">
-        <v>2079</v>
+        <v>2069</v>
       </c>
       <c r="F304" s="25" t="s">
         <v>1216</v>
@@ -37474,11 +37464,11 @@
       </c>
       <c r="AM304" s="25"/>
       <c r="AN304" s="25" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="AO304" s="25"/>
       <c r="AP304" s="25" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="AQ304" s="25"/>
       <c r="AR304" s="25"/>
@@ -37500,7 +37490,7 @@
         <v>811</v>
       </c>
       <c r="E305" s="37" t="s">
-        <v>1956</v>
+        <v>1946</v>
       </c>
       <c r="F305" s="25" t="s">
         <v>810</v>
@@ -37591,7 +37581,7 @@
         <v>938</v>
       </c>
       <c r="E306" s="37" t="s">
-        <v>2080</v>
+        <v>2070</v>
       </c>
       <c r="F306" s="25" t="s">
         <v>815</v>
@@ -37682,7 +37672,7 @@
         <v>929</v>
       </c>
       <c r="E307" s="37" t="s">
-        <v>2081</v>
+        <v>2071</v>
       </c>
       <c r="F307" s="25" t="s">
         <v>939</v>
@@ -37771,7 +37761,7 @@
         <v>1251</v>
       </c>
       <c r="E308" s="37" t="s">
-        <v>2082</v>
+        <v>2072</v>
       </c>
       <c r="F308" s="25" t="s">
         <v>1204</v>
@@ -37872,7 +37862,7 @@
         <v>588</v>
       </c>
       <c r="E309" s="37" t="s">
-        <v>2083</v>
+        <v>2073</v>
       </c>
       <c r="F309" s="25" t="s">
         <v>465</v>
@@ -37963,7 +37953,7 @@
         <v>681</v>
       </c>
       <c r="E310" s="37" t="s">
-        <v>2084</v>
+        <v>2074</v>
       </c>
       <c r="F310" s="25" t="s">
         <v>466</v>
@@ -38053,24 +38043,24 @@
       <c r="B311" s="61"/>
       <c r="C311" s="61"/>
       <c r="D311" s="61" t="s">
-        <v>2354</v>
+        <v>2344</v>
       </c>
       <c r="E311" s="62" t="s">
-        <v>2355</v>
+        <v>2345</v>
       </c>
       <c r="F311" s="61" t="s">
-        <v>2344</v>
+        <v>2334</v>
       </c>
       <c r="G311" s="61" t="s">
-        <v>2344</v>
+        <v>2334</v>
       </c>
       <c r="H311" s="61"/>
       <c r="I311" s="61" t="s">
-        <v>2348</v>
+        <v>2338</v>
       </c>
       <c r="J311" s="61"/>
       <c r="K311" s="61" t="s">
-        <v>2266</v>
+        <v>2256</v>
       </c>
       <c r="L311" s="61"/>
       <c r="M311" s="61"/>
@@ -38086,38 +38076,38 @@
       <c r="W311" s="61"/>
       <c r="X311" s="61"/>
       <c r="Z311" s="25" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AA311" s="25" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AB311" s="25" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="AC311" s="25" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="AD311" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE311" s="61"/>
+        <v>25</v>
+      </c>
+      <c r="AE311" s="25"/>
       <c r="AF311" s="25" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AG311" s="25" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="AH311" s="25" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="AI311" s="25" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AJ311" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AK311" s="61" t="s">
-        <v>1834</v>
+        <v>25</v>
+      </c>
+      <c r="AK311" s="25" t="s">
+        <v>25</v>
       </c>
       <c r="AM311" s="61"/>
       <c r="AN311" s="61"/>
@@ -38140,24 +38130,24 @@
       <c r="B312" s="61"/>
       <c r="C312" s="61"/>
       <c r="D312" s="61" t="s">
-        <v>2351</v>
+        <v>2341</v>
       </c>
       <c r="E312" s="62" t="s">
-        <v>2356</v>
+        <v>2346</v>
       </c>
       <c r="F312" s="61" t="s">
-        <v>2357</v>
+        <v>2347</v>
       </c>
       <c r="G312" s="61" t="s">
-        <v>2345</v>
+        <v>2335</v>
       </c>
       <c r="H312" s="61"/>
       <c r="I312" s="61" t="s">
-        <v>2348</v>
+        <v>2338</v>
       </c>
       <c r="J312" s="61"/>
       <c r="K312" s="61" t="s">
-        <v>2266</v>
+        <v>2256</v>
       </c>
       <c r="L312" s="61"/>
       <c r="M312" s="61"/>
@@ -38173,38 +38163,38 @@
       <c r="W312" s="61"/>
       <c r="X312" s="61"/>
       <c r="Z312" s="25" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AA312" s="25" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AB312" s="25" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="AC312" s="25" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="AD312" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE312" s="61"/>
+        <v>25</v>
+      </c>
+      <c r="AE312" s="25"/>
       <c r="AF312" s="25" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AG312" s="25" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="AH312" s="25" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="AI312" s="25" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AJ312" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AK312" s="61" t="s">
-        <v>1834</v>
+        <v>25</v>
+      </c>
+      <c r="AK312" s="25" t="s">
+        <v>25</v>
       </c>
       <c r="AM312" s="61"/>
       <c r="AN312" s="61"/>
@@ -38227,24 +38217,24 @@
       <c r="B313" s="61"/>
       <c r="C313" s="61"/>
       <c r="D313" s="61" t="s">
+        <v>2340</v>
+      </c>
+      <c r="E313" s="62" t="s">
         <v>2350</v>
       </c>
-      <c r="E313" s="62" t="s">
-        <v>2360</v>
-      </c>
       <c r="F313" s="61" t="s">
-        <v>2346</v>
+        <v>2336</v>
       </c>
       <c r="G313" s="61" t="s">
-        <v>2346</v>
+        <v>2336</v>
       </c>
       <c r="H313" s="61"/>
       <c r="I313" s="61" t="s">
-        <v>2349</v>
+        <v>2339</v>
       </c>
       <c r="J313" s="61"/>
       <c r="K313" s="61" t="s">
-        <v>2266</v>
+        <v>2256</v>
       </c>
       <c r="L313" s="61"/>
       <c r="M313" s="61"/>
@@ -38260,38 +38250,38 @@
       <c r="W313" s="61"/>
       <c r="X313" s="61"/>
       <c r="Z313" s="25" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AA313" s="25" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AB313" s="25" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="AC313" s="25" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="AD313" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE313" s="61"/>
+        <v>25</v>
+      </c>
+      <c r="AE313" s="25"/>
       <c r="AF313" s="25" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AG313" s="25" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="AH313" s="25" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="AI313" s="25" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AJ313" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AK313" s="61" t="s">
-        <v>1834</v>
+        <v>25</v>
+      </c>
+      <c r="AK313" s="25" t="s">
+        <v>25</v>
       </c>
       <c r="AM313" s="61"/>
       <c r="AN313" s="61"/>
@@ -38314,24 +38304,24 @@
       <c r="B314" s="61"/>
       <c r="C314" s="61"/>
       <c r="D314" s="61" t="s">
-        <v>2353</v>
+        <v>2343</v>
       </c>
       <c r="E314" s="62" t="s">
-        <v>2358</v>
+        <v>2348</v>
       </c>
       <c r="F314" s="61" t="s">
-        <v>2359</v>
+        <v>2349</v>
       </c>
       <c r="G314" s="61" t="s">
-        <v>2347</v>
+        <v>2337</v>
       </c>
       <c r="H314" s="61"/>
       <c r="I314" s="61" t="s">
-        <v>2352</v>
+        <v>2342</v>
       </c>
       <c r="J314" s="61"/>
       <c r="K314" s="61" t="s">
-        <v>2266</v>
+        <v>2256</v>
       </c>
       <c r="L314" s="61"/>
       <c r="M314" s="61"/>
@@ -38378,7 +38368,7 @@
         <v>19</v>
       </c>
       <c r="AK314" s="61" t="s">
-        <v>1834</v>
+        <v>1824</v>
       </c>
       <c r="AM314" s="61"/>
       <c r="AN314" s="61"/>
@@ -38404,7 +38394,7 @@
         <v>675</v>
       </c>
       <c r="E315" s="37" t="s">
-        <v>2085</v>
+        <v>2075</v>
       </c>
       <c r="F315" s="25" t="s">
         <v>326</v>
@@ -38509,7 +38499,7 @@
         <v>1164</v>
       </c>
       <c r="E316" s="37" t="s">
-        <v>2086</v>
+        <v>2076</v>
       </c>
       <c r="F316" s="25" t="s">
         <v>327</v>
@@ -38574,11 +38564,11 @@
       </c>
       <c r="AM316" s="25"/>
       <c r="AN316" s="25" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="AO316" s="25"/>
       <c r="AP316" s="25" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="AQ316" s="25"/>
       <c r="AR316" s="25"/>
@@ -38600,7 +38590,7 @@
         <v>295</v>
       </c>
       <c r="E317" s="37" t="s">
-        <v>2087</v>
+        <v>2077</v>
       </c>
       <c r="F317" s="25" t="s">
         <v>296</v>
@@ -38665,11 +38655,11 @@
       </c>
       <c r="AM317" s="25"/>
       <c r="AN317" s="25" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="AO317" s="25"/>
       <c r="AP317" s="25" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="AQ317" s="25"/>
       <c r="AR317" s="25"/>
@@ -38691,7 +38681,7 @@
         <v>323</v>
       </c>
       <c r="E318" s="37" t="s">
-        <v>2088</v>
+        <v>2078</v>
       </c>
       <c r="F318" s="25" t="s">
         <v>297</v>
@@ -38782,7 +38772,7 @@
         <v>298</v>
       </c>
       <c r="E319" s="37" t="s">
-        <v>2089</v>
+        <v>2079</v>
       </c>
       <c r="F319" s="25" t="s">
         <v>299</v>
@@ -38847,11 +38837,11 @@
       </c>
       <c r="AM319" s="25"/>
       <c r="AN319" s="25" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="AO319" s="25"/>
       <c r="AP319" s="25" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="AQ319" s="25"/>
       <c r="AR319" s="25"/>
@@ -38870,13 +38860,13 @@
       <c r="B320" s="25"/>
       <c r="C320" s="25"/>
       <c r="D320" s="25" t="s">
-        <v>1699</v>
+        <v>1689</v>
       </c>
       <c r="E320" s="37" t="s">
-        <v>2090</v>
+        <v>2080</v>
       </c>
       <c r="F320" s="25" t="s">
-        <v>1700</v>
+        <v>1690</v>
       </c>
       <c r="G320" s="25" t="s">
         <v>47</v>
@@ -38938,11 +38928,11 @@
       </c>
       <c r="AM320" s="25"/>
       <c r="AN320" s="25" t="s">
-        <v>1699</v>
+        <v>1689</v>
       </c>
       <c r="AO320" s="25"/>
       <c r="AP320" s="25" t="s">
-        <v>1699</v>
+        <v>1689</v>
       </c>
       <c r="AQ320" s="25"/>
       <c r="AR320" s="25"/>
@@ -38964,7 +38954,7 @@
         <v>1201</v>
       </c>
       <c r="E321" s="37" t="s">
-        <v>1954</v>
+        <v>1944</v>
       </c>
       <c r="F321" s="25" t="s">
         <v>777</v>
@@ -39053,7 +39043,7 @@
         <v>1202</v>
       </c>
       <c r="E322" s="37" t="s">
-        <v>2091</v>
+        <v>2081</v>
       </c>
       <c r="F322" s="25" t="s">
         <v>1203</v>
@@ -39228,7 +39218,7 @@
         <v>968</v>
       </c>
       <c r="E324" s="37" t="s">
-        <v>2092</v>
+        <v>2082</v>
       </c>
       <c r="F324" s="25" t="s">
         <v>325</v>
@@ -40474,7 +40464,7 @@
         <v>954</v>
       </c>
       <c r="E342" s="37" t="s">
-        <v>2093</v>
+        <v>2083</v>
       </c>
       <c r="F342" s="25" t="s">
         <v>859</v>
@@ -40633,7 +40623,7 @@
         <v>993</v>
       </c>
       <c r="E344" s="37" t="s">
-        <v>2094</v>
+        <v>2084</v>
       </c>
       <c r="F344" s="25" t="s">
         <v>872</v>
@@ -40788,7 +40778,7 @@
         <v>995</v>
       </c>
       <c r="E346" s="37" t="s">
-        <v>2095</v>
+        <v>2085</v>
       </c>
       <c r="F346" s="25" t="s">
         <v>887</v>
@@ -40947,7 +40937,7 @@
         <v>998</v>
       </c>
       <c r="E348" s="37" t="s">
-        <v>2096</v>
+        <v>2086</v>
       </c>
       <c r="F348" s="25" t="s">
         <v>999</v>
@@ -41016,7 +41006,7 @@
         <v>449</v>
       </c>
       <c r="E349" s="37" t="s">
-        <v>1966</v>
+        <v>1956</v>
       </c>
       <c r="F349" s="25" t="s">
         <v>394</v>
@@ -41107,7 +41097,7 @@
         <v>950</v>
       </c>
       <c r="E350" s="37" t="s">
-        <v>2097</v>
+        <v>2087</v>
       </c>
       <c r="F350" s="25" t="s">
         <v>285</v>
@@ -41136,7 +41126,7 @@
       <c r="V350" s="25"/>
       <c r="W350" s="25"/>
       <c r="X350" s="25" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="Z350" s="25" t="s">
         <v>25</v>
@@ -41290,7 +41280,7 @@
         <v>347</v>
       </c>
       <c r="E352" s="37" t="s">
-        <v>2098</v>
+        <v>2088</v>
       </c>
       <c r="F352" s="25" t="s">
         <v>1001</v>
@@ -41319,7 +41309,7 @@
       <c r="V352" s="25"/>
       <c r="W352" s="25"/>
       <c r="X352" s="25" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="Z352" s="25"/>
       <c r="AA352" s="25"/>
@@ -41447,7 +41437,7 @@
         <v>264</v>
       </c>
       <c r="E354" s="37" t="s">
-        <v>2099</v>
+        <v>2089</v>
       </c>
       <c r="F354" s="25" t="s">
         <v>261</v>
@@ -41476,7 +41466,7 @@
       <c r="V354" s="25"/>
       <c r="W354" s="25"/>
       <c r="X354" s="25" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="Z354" s="25"/>
       <c r="AA354" s="25"/>
@@ -41604,7 +41594,7 @@
         <v>1003</v>
       </c>
       <c r="E356" s="37" t="s">
-        <v>2100</v>
+        <v>2090</v>
       </c>
       <c r="F356" s="25" t="s">
         <v>262</v>
@@ -41633,7 +41623,7 @@
       <c r="V356" s="25"/>
       <c r="W356" s="25"/>
       <c r="X356" s="25" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="Z356" s="25"/>
       <c r="AA356" s="25"/>
@@ -41761,7 +41751,7 @@
         <v>1007</v>
       </c>
       <c r="E358" s="37" t="s">
-        <v>2101</v>
+        <v>2091</v>
       </c>
       <c r="F358" s="25" t="s">
         <v>1008</v>
@@ -41790,7 +41780,7 @@
       <c r="V358" s="25"/>
       <c r="W358" s="25"/>
       <c r="X358" s="25" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="Z358" s="25"/>
       <c r="AA358" s="25"/>
@@ -41918,7 +41908,7 @@
         <v>1011</v>
       </c>
       <c r="E360" s="37" t="s">
-        <v>2102</v>
+        <v>2092</v>
       </c>
       <c r="F360" s="25" t="s">
         <v>266</v>
@@ -41947,7 +41937,7 @@
       <c r="V360" s="25"/>
       <c r="W360" s="25"/>
       <c r="X360" s="25" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="Z360" s="25"/>
       <c r="AA360" s="25"/>
@@ -42075,7 +42065,7 @@
         <v>1014</v>
       </c>
       <c r="E362" s="37" t="s">
-        <v>2103</v>
+        <v>2093</v>
       </c>
       <c r="F362" s="25" t="s">
         <v>267</v>
@@ -42104,7 +42094,7 @@
       <c r="V362" s="25"/>
       <c r="W362" s="25"/>
       <c r="X362" s="25" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="Z362" s="25"/>
       <c r="AA362" s="25"/>
@@ -42232,7 +42222,7 @@
         <v>1017</v>
       </c>
       <c r="E364" s="37" t="s">
-        <v>2104</v>
+        <v>2094</v>
       </c>
       <c r="F364" s="25" t="s">
         <v>268</v>
@@ -42261,7 +42251,7 @@
       <c r="V364" s="25"/>
       <c r="W364" s="25"/>
       <c r="X364" s="25" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="Z364" s="25"/>
       <c r="AA364" s="25"/>
@@ -42389,7 +42379,7 @@
         <v>1020</v>
       </c>
       <c r="E366" s="37" t="s">
-        <v>2105</v>
+        <v>2095</v>
       </c>
       <c r="F366" s="25" t="s">
         <v>270</v>
@@ -42418,7 +42408,7 @@
       <c r="V366" s="25"/>
       <c r="W366" s="25"/>
       <c r="X366" s="25" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="Z366" s="25"/>
       <c r="AA366" s="25"/>
@@ -42546,7 +42536,7 @@
         <v>1023</v>
       </c>
       <c r="E368" s="37" t="s">
-        <v>2106</v>
+        <v>2096</v>
       </c>
       <c r="F368" s="25" t="s">
         <v>269</v>
@@ -42575,7 +42565,7 @@
       <c r="V368" s="25"/>
       <c r="W368" s="25"/>
       <c r="X368" s="25" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="Z368" s="25"/>
       <c r="AA368" s="25"/>
@@ -42617,7 +42607,7 @@
         <v>946</v>
       </c>
       <c r="E369" s="37" t="s">
-        <v>1956</v>
+        <v>1946</v>
       </c>
       <c r="F369" s="25" t="s">
         <v>273</v>
@@ -42712,7 +42702,7 @@
         <v>468</v>
       </c>
       <c r="E370" s="37" t="s">
-        <v>2107</v>
+        <v>2097</v>
       </c>
       <c r="F370" s="25" t="s">
         <v>1206</v>
@@ -42749,7 +42739,7 @@
         <v>1231</v>
       </c>
       <c r="X370" s="25" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="Z370" s="25" t="s">
         <v>25</v>
@@ -42817,7 +42807,7 @@
         <v>469</v>
       </c>
       <c r="E371" s="37" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
       <c r="F371" s="25" t="s">
         <v>467</v>
@@ -42846,7 +42836,7 @@
       <c r="V371" s="25"/>
       <c r="W371" s="25"/>
       <c r="X371" s="25" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="Z371" s="25" t="s">
         <v>25</v>
@@ -42910,7 +42900,7 @@
         <v>1187</v>
       </c>
       <c r="E372" s="37" t="s">
-        <v>2109</v>
+        <v>2099</v>
       </c>
       <c r="F372" s="25" t="s">
         <v>587</v>
@@ -42939,7 +42929,7 @@
       <c r="V372" s="25"/>
       <c r="W372" s="25"/>
       <c r="X372" s="25" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="Z372" s="25" t="s">
         <v>25</v>
@@ -43729,7 +43719,7 @@
         <v>936</v>
       </c>
       <c r="E382" s="37" t="s">
-        <v>2110</v>
+        <v>2100</v>
       </c>
       <c r="F382" s="25" t="s">
         <v>714</v>
@@ -43910,7 +43900,7 @@
         <v>780</v>
       </c>
       <c r="E384" s="37" t="s">
-        <v>2044</v>
+        <v>2034</v>
       </c>
       <c r="F384" s="25" t="s">
         <v>667</v>
@@ -43981,7 +43971,7 @@
         <v>781</v>
       </c>
       <c r="E385" s="37" t="s">
-        <v>2045</v>
+        <v>2035</v>
       </c>
       <c r="F385" s="25" t="s">
         <v>1036</v>
@@ -44134,7 +44124,7 @@
         <v>1038</v>
       </c>
       <c r="E387" s="37" t="s">
-        <v>2046</v>
+        <v>2036</v>
       </c>
       <c r="F387" s="25" t="s">
         <v>1039</v>
@@ -44205,7 +44195,7 @@
         <v>1042</v>
       </c>
       <c r="E388" s="37" t="s">
-        <v>2047</v>
+        <v>2037</v>
       </c>
       <c r="F388" s="25" t="s">
         <v>1043</v>
@@ -44272,7 +44262,7 @@
         <v>660</v>
       </c>
       <c r="E389" s="37" t="s">
-        <v>2048</v>
+        <v>2038</v>
       </c>
       <c r="F389" s="25" t="s">
         <v>382</v>
@@ -44365,7 +44355,7 @@
         <v>1547</v>
       </c>
       <c r="E390" s="37" t="s">
-        <v>2049</v>
+        <v>2039</v>
       </c>
       <c r="F390" s="25" t="s">
         <v>377</v>
@@ -44460,7 +44450,7 @@
         <v>947</v>
       </c>
       <c r="E391" s="37" t="s">
-        <v>2111</v>
+        <v>2101</v>
       </c>
       <c r="F391" s="25" t="s">
         <v>492</v>
@@ -44557,7 +44547,7 @@
         <v>470</v>
       </c>
       <c r="E392" s="37" t="s">
-        <v>2112</v>
+        <v>2102</v>
       </c>
       <c r="F392" s="25" t="s">
         <v>493</v>
@@ -44654,7 +44644,7 @@
         <v>925</v>
       </c>
       <c r="E393" s="37" t="s">
-        <v>2113</v>
+        <v>2103</v>
       </c>
       <c r="F393" s="25" t="s">
         <v>494</v>
@@ -44747,7 +44737,7 @@
         <v>926</v>
       </c>
       <c r="E394" s="37" t="s">
-        <v>2114</v>
+        <v>2104</v>
       </c>
       <c r="F394" s="25" t="s">
         <v>928</v>
@@ -44926,7 +44916,7 @@
         <v>784</v>
       </c>
       <c r="E396" s="37" t="s">
-        <v>2115</v>
+        <v>2105</v>
       </c>
       <c r="F396" s="25" t="s">
         <v>1045</v>
@@ -45001,7 +44991,7 @@
         <v>785</v>
       </c>
       <c r="E397" s="37" t="s">
-        <v>2116</v>
+        <v>2106</v>
       </c>
       <c r="F397" s="25" t="s">
         <v>1046</v>
@@ -45158,7 +45148,7 @@
         <v>789</v>
       </c>
       <c r="E399" s="37" t="s">
-        <v>2117</v>
+        <v>2107</v>
       </c>
       <c r="F399" s="25" t="s">
         <v>1047</v>
@@ -45233,7 +45223,7 @@
         <v>790</v>
       </c>
       <c r="E400" s="37" t="s">
-        <v>2118</v>
+        <v>2108</v>
       </c>
       <c r="F400" s="25" t="s">
         <v>1048</v>
@@ -45664,7 +45654,7 @@
         <v>1249</v>
       </c>
       <c r="E406" s="37" t="s">
-        <v>2119</v>
+        <v>2109</v>
       </c>
       <c r="F406" s="25" t="s">
         <v>1152</v>
@@ -46586,7 +46576,7 @@
         <v>899</v>
       </c>
       <c r="E420" s="37" t="s">
-        <v>1895</v>
+        <v>1885</v>
       </c>
       <c r="F420" s="25" t="s">
         <v>900</v>
@@ -46675,7 +46665,7 @@
         <v>902</v>
       </c>
       <c r="E421" s="37" t="s">
-        <v>1953</v>
+        <v>1943</v>
       </c>
       <c r="F421" s="25" t="s">
         <v>807</v>
@@ -46764,7 +46754,7 @@
         <v>1240</v>
       </c>
       <c r="E422" s="37" t="s">
-        <v>1896</v>
+        <v>1886</v>
       </c>
       <c r="F422" s="25" t="s">
         <v>661</v>
@@ -46803,7 +46793,7 @@
         <v>804</v>
       </c>
       <c r="X422" s="25" t="s">
-        <v>1662</v>
+        <v>1660</v>
       </c>
       <c r="Z422" s="25" t="s">
         <v>25</v>
@@ -46871,7 +46861,7 @@
         <v>654</v>
       </c>
       <c r="E423" s="37" t="s">
-        <v>1897</v>
+        <v>1887</v>
       </c>
       <c r="F423" s="25" t="s">
         <v>662</v>
@@ -46900,7 +46890,7 @@
       <c r="V423" s="25"/>
       <c r="W423" s="25"/>
       <c r="X423" s="25" t="s">
-        <v>1662</v>
+        <v>1660</v>
       </c>
       <c r="Z423" s="25" t="s">
         <v>25</v>
@@ -46964,7 +46954,7 @@
         <v>655</v>
       </c>
       <c r="E424" s="37" t="s">
-        <v>1898</v>
+        <v>1888</v>
       </c>
       <c r="F424" s="25" t="s">
         <v>663</v>
@@ -47003,7 +46993,7 @@
         <v>804</v>
       </c>
       <c r="X424" s="25" t="s">
-        <v>1663</v>
+        <v>1661</v>
       </c>
       <c r="Z424" s="25" t="s">
         <v>25</v>
@@ -47071,7 +47061,7 @@
         <v>656</v>
       </c>
       <c r="E425" s="37" t="s">
-        <v>1899</v>
+        <v>1889</v>
       </c>
       <c r="F425" s="25" t="s">
         <v>664</v>
@@ -47100,7 +47090,7 @@
       <c r="V425" s="25"/>
       <c r="W425" s="25"/>
       <c r="X425" s="25" t="s">
-        <v>1663</v>
+        <v>1661</v>
       </c>
       <c r="Z425" s="25" t="s">
         <v>25</v>
@@ -47164,7 +47154,7 @@
         <v>657</v>
       </c>
       <c r="E426" s="37" t="s">
-        <v>1900</v>
+        <v>1890</v>
       </c>
       <c r="F426" s="25" t="s">
         <v>665</v>
@@ -47203,7 +47193,7 @@
         <v>804</v>
       </c>
       <c r="X426" s="25" t="s">
-        <v>1664</v>
+        <v>1662</v>
       </c>
       <c r="Z426" s="25" t="s">
         <v>25</v>
@@ -47271,7 +47261,7 @@
         <v>658</v>
       </c>
       <c r="E427" s="37" t="s">
-        <v>1901</v>
+        <v>1891</v>
       </c>
       <c r="F427" s="25" t="s">
         <v>666</v>
@@ -47300,7 +47290,7 @@
       <c r="V427" s="25"/>
       <c r="W427" s="25"/>
       <c r="X427" s="25" t="s">
-        <v>1664</v>
+        <v>1662</v>
       </c>
       <c r="Z427" s="25" t="s">
         <v>25</v>
@@ -47450,7 +47440,7 @@
         <v>1241</v>
       </c>
       <c r="E429" s="37" t="s">
-        <v>1902</v>
+        <v>1892</v>
       </c>
       <c r="F429" s="25" t="s">
         <v>796</v>
@@ -47531,7 +47521,7 @@
         <v>1088</v>
       </c>
       <c r="E430" s="37" t="s">
-        <v>1903</v>
+        <v>1893</v>
       </c>
       <c r="F430" s="25" t="s">
         <v>759</v>
@@ -47602,7 +47592,7 @@
         <v>1090</v>
       </c>
       <c r="E431" s="37" t="s">
-        <v>1904</v>
+        <v>1894</v>
       </c>
       <c r="F431" s="25" t="s">
         <v>797</v>
@@ -47750,7 +47740,7 @@
         <v>1250</v>
       </c>
       <c r="E433" s="37" t="s">
-        <v>1905</v>
+        <v>1895</v>
       </c>
       <c r="F433" s="25" t="s">
         <v>800</v>
@@ -47813,7 +47803,7 @@
         <v>1092</v>
       </c>
       <c r="E434" s="37" t="s">
-        <v>1906</v>
+        <v>1896</v>
       </c>
       <c r="F434" s="25" t="s">
         <v>768</v>
@@ -47884,7 +47874,7 @@
         <v>1094</v>
       </c>
       <c r="E435" s="37" t="s">
-        <v>1907</v>
+        <v>1897</v>
       </c>
       <c r="F435" s="25" t="s">
         <v>769</v>
@@ -47951,7 +47941,7 @@
         <v>1096</v>
       </c>
       <c r="E436" s="37" t="s">
-        <v>1908</v>
+        <v>1898</v>
       </c>
       <c r="F436" s="25" t="s">
         <v>1084</v>
@@ -48018,7 +48008,7 @@
         <v>1097</v>
       </c>
       <c r="E437" s="37" t="s">
-        <v>1909</v>
+        <v>1899</v>
       </c>
       <c r="F437" s="25" t="s">
         <v>1085</v>
@@ -48085,7 +48075,7 @@
         <v>1098</v>
       </c>
       <c r="E438" s="37" t="s">
-        <v>1910</v>
+        <v>1900</v>
       </c>
       <c r="F438" s="25" t="s">
         <v>761</v>
@@ -48156,7 +48146,7 @@
         <v>1100</v>
       </c>
       <c r="E439" s="37" t="s">
-        <v>1911</v>
+        <v>1901</v>
       </c>
       <c r="F439" s="25" t="s">
         <v>762</v>
@@ -48227,7 +48217,7 @@
         <v>1102</v>
       </c>
       <c r="E440" s="37" t="s">
-        <v>1912</v>
+        <v>1902</v>
       </c>
       <c r="F440" s="25" t="s">
         <v>763</v>
@@ -48298,7 +48288,7 @@
         <v>1104</v>
       </c>
       <c r="E441" s="37" t="s">
-        <v>1913</v>
+        <v>1903</v>
       </c>
       <c r="F441" s="25" t="s">
         <v>764</v>
@@ -48369,7 +48359,7 @@
         <v>1106</v>
       </c>
       <c r="E442" s="37" t="s">
-        <v>1914</v>
+        <v>1904</v>
       </c>
       <c r="F442" s="25" t="s">
         <v>765</v>
@@ -48440,7 +48430,7 @@
         <v>1108</v>
       </c>
       <c r="E443" s="37" t="s">
-        <v>1915</v>
+        <v>1905</v>
       </c>
       <c r="F443" s="25" t="s">
         <v>1109</v>
@@ -48511,7 +48501,7 @@
         <v>1111</v>
       </c>
       <c r="E444" s="37" t="s">
-        <v>1916</v>
+        <v>1906</v>
       </c>
       <c r="F444" s="25" t="s">
         <v>1112</v>
@@ -48582,7 +48572,7 @@
         <v>1114</v>
       </c>
       <c r="E445" s="37" t="s">
-        <v>1917</v>
+        <v>1907</v>
       </c>
       <c r="F445" s="25" t="s">
         <v>766</v>
@@ -48653,7 +48643,7 @@
         <v>1116</v>
       </c>
       <c r="E446" s="37" t="s">
-        <v>1918</v>
+        <v>1908</v>
       </c>
       <c r="F446" s="25" t="s">
         <v>767</v>
@@ -48724,7 +48714,7 @@
         <v>671</v>
       </c>
       <c r="E447" s="37" t="s">
-        <v>1919</v>
+        <v>1909</v>
       </c>
       <c r="F447" s="25" t="s">
         <v>495</v>
@@ -48823,7 +48813,7 @@
         <v>659</v>
       </c>
       <c r="E448" s="37" t="s">
-        <v>1920</v>
+        <v>1910</v>
       </c>
       <c r="F448" s="25" t="s">
         <v>496</v>
@@ -48914,7 +48904,7 @@
         <v>683</v>
       </c>
       <c r="E449" s="37" t="s">
-        <v>2120</v>
+        <v>2110</v>
       </c>
       <c r="F449" s="25" t="s">
         <v>497</v>
@@ -49007,7 +48997,7 @@
         <v>940</v>
       </c>
       <c r="E450" s="37" t="s">
-        <v>2121</v>
+        <v>2111</v>
       </c>
       <c r="F450" s="25" t="s">
         <v>941</v>
@@ -49094,7 +49084,7 @@
         <v>943</v>
       </c>
       <c r="E451" s="37" t="s">
-        <v>2122</v>
+        <v>2112</v>
       </c>
       <c r="F451" s="25" t="s">
         <v>498</v>
@@ -49193,7 +49183,7 @@
         <v>472</v>
       </c>
       <c r="E452" s="37" t="s">
-        <v>2123</v>
+        <v>2113</v>
       </c>
       <c r="F452" s="25" t="s">
         <v>499</v>
@@ -49282,7 +49272,7 @@
         <v>1180</v>
       </c>
       <c r="E453" s="37" t="s">
-        <v>2124</v>
+        <v>2114</v>
       </c>
       <c r="F453" s="25" t="s">
         <v>962</v>
@@ -49369,7 +49359,7 @@
         <v>963</v>
       </c>
       <c r="E454" s="37" t="s">
-        <v>2125</v>
+        <v>2115</v>
       </c>
       <c r="F454" s="25" t="s">
         <v>500</v>
@@ -49466,7 +49456,7 @@
         <v>473</v>
       </c>
       <c r="E455" s="37" t="s">
-        <v>2126</v>
+        <v>2116</v>
       </c>
       <c r="F455" s="25" t="s">
         <v>501</v>
@@ -49555,7 +49545,7 @@
         <v>934</v>
       </c>
       <c r="E456" s="37" t="s">
-        <v>2127</v>
+        <v>2117</v>
       </c>
       <c r="F456" s="25" t="s">
         <v>502</v>
@@ -49654,7 +49644,7 @@
         <v>474</v>
       </c>
       <c r="E457" s="37" t="s">
-        <v>2128</v>
+        <v>2118</v>
       </c>
       <c r="F457" s="25" t="s">
         <v>503</v>
@@ -49745,7 +49735,7 @@
         <v>930</v>
       </c>
       <c r="E458" s="37" t="s">
-        <v>2129</v>
+        <v>2119</v>
       </c>
       <c r="F458" s="25" t="s">
         <v>504</v>
@@ -49846,7 +49836,7 @@
         <v>475</v>
       </c>
       <c r="E459" s="37" t="s">
-        <v>2130</v>
+        <v>2120</v>
       </c>
       <c r="F459" s="25" t="s">
         <v>505</v>
@@ -49936,20 +49926,20 @@
       <c r="B460" s="55"/>
       <c r="C460" s="55"/>
       <c r="D460" s="55" t="s">
-        <v>1831</v>
+        <v>1821</v>
       </c>
       <c r="E460" s="55" t="s">
-        <v>2131</v>
+        <v>2121</v>
       </c>
       <c r="F460" s="55" t="s">
-        <v>1832</v>
+        <v>1822</v>
       </c>
       <c r="G460" s="55" t="s">
         <v>47</v>
       </c>
       <c r="H460" s="55"/>
       <c r="I460" s="55" t="s">
-        <v>1822</v>
+        <v>1812</v>
       </c>
       <c r="J460" s="55"/>
       <c r="K460" s="55" t="s">
@@ -49968,56 +49958,56 @@
       <c r="V460" s="55"/>
       <c r="W460" s="55"/>
       <c r="X460" s="55" t="s">
-        <v>1842</v>
+        <v>1832</v>
       </c>
       <c r="Y460" s="56"/>
       <c r="Z460" s="55" t="s">
-        <v>1833</v>
+        <v>1823</v>
       </c>
       <c r="AA460" s="55" t="s">
-        <v>1833</v>
+        <v>1823</v>
       </c>
       <c r="AB460" s="55" t="s">
-        <v>1834</v>
+        <v>1824</v>
       </c>
       <c r="AC460" s="55" t="s">
-        <v>1834</v>
+        <v>1824</v>
       </c>
       <c r="AD460" s="55" t="s">
-        <v>1834</v>
+        <v>1824</v>
       </c>
       <c r="AE460" s="55"/>
       <c r="AF460" s="55" t="s">
-        <v>1833</v>
+        <v>1823</v>
       </c>
       <c r="AG460" s="55" t="s">
-        <v>1834</v>
+        <v>1824</v>
       </c>
       <c r="AH460" s="55" t="s">
-        <v>1834</v>
+        <v>1824</v>
       </c>
       <c r="AI460" s="55" t="s">
-        <v>1833</v>
+        <v>1823</v>
       </c>
       <c r="AJ460" s="55" t="s">
-        <v>1833</v>
+        <v>1823</v>
       </c>
       <c r="AK460" s="55" t="s">
-        <v>1833</v>
+        <v>1823</v>
       </c>
       <c r="AL460" s="56"/>
       <c r="AM460" s="55"/>
       <c r="AN460" s="55" t="s">
-        <v>1835</v>
+        <v>1825</v>
       </c>
       <c r="AO460" s="55"/>
       <c r="AP460" s="55"/>
       <c r="AQ460" s="55" t="s">
-        <v>1835</v>
+        <v>1825</v>
       </c>
       <c r="AR460" s="55"/>
       <c r="AS460" s="55" t="s">
-        <v>1835</v>
+        <v>1825</v>
       </c>
       <c r="AT460" s="55"/>
       <c r="AU460" s="55"/>
@@ -50037,7 +50027,7 @@
         <v>942</v>
       </c>
       <c r="E461" s="37" t="s">
-        <v>2132</v>
+        <v>2122</v>
       </c>
       <c r="F461" s="25" t="s">
         <v>506</v>
@@ -50138,7 +50128,7 @@
         <v>476</v>
       </c>
       <c r="E462" s="37" t="s">
-        <v>2133</v>
+        <v>2123</v>
       </c>
       <c r="F462" s="25" t="s">
         <v>507</v>
@@ -50231,7 +50221,7 @@
         <v>931</v>
       </c>
       <c r="E463" s="37" t="s">
-        <v>2134</v>
+        <v>2124</v>
       </c>
       <c r="F463" s="25" t="s">
         <v>904</v>
@@ -50264,7 +50254,7 @@
       <c r="V463" s="25"/>
       <c r="W463" s="25"/>
       <c r="X463" s="25" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
       <c r="Z463" s="25" t="s">
         <v>25</v>
@@ -50334,7 +50324,7 @@
         <v>482</v>
       </c>
       <c r="E464" s="37" t="s">
-        <v>2135</v>
+        <v>2125</v>
       </c>
       <c r="F464" s="25" t="s">
         <v>903</v>
@@ -50363,7 +50353,7 @@
       <c r="V464" s="25"/>
       <c r="W464" s="25"/>
       <c r="X464" s="25" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
       <c r="Z464" s="25" t="s">
         <v>25</v>
@@ -50429,7 +50419,7 @@
         <v>932</v>
       </c>
       <c r="E465" s="37" t="s">
-        <v>2136</v>
+        <v>2126</v>
       </c>
       <c r="F465" s="25" t="s">
         <v>548</v>
@@ -50464,7 +50454,7 @@
       <c r="V465" s="25"/>
       <c r="W465" s="25"/>
       <c r="X465" s="25" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
       <c r="Z465" s="25" t="s">
         <v>25</v>
@@ -50534,7 +50524,7 @@
         <v>483</v>
       </c>
       <c r="E466" s="37" t="s">
-        <v>2137</v>
+        <v>2127</v>
       </c>
       <c r="F466" s="25" t="s">
         <v>549</v>
@@ -50563,7 +50553,7 @@
       <c r="V466" s="25"/>
       <c r="W466" s="25"/>
       <c r="X466" s="25" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
       <c r="Z466" s="25" t="s">
         <v>25</v>
@@ -50629,7 +50619,7 @@
         <v>913</v>
       </c>
       <c r="E467" s="37" t="s">
-        <v>2138</v>
+        <v>2128</v>
       </c>
       <c r="F467" s="25" t="s">
         <v>550</v>
@@ -50722,7 +50712,7 @@
         <v>484</v>
       </c>
       <c r="E468" s="37" t="s">
-        <v>2139</v>
+        <v>2129</v>
       </c>
       <c r="F468" s="25" t="s">
         <v>520</v>
@@ -50787,17 +50777,17 @@
       </c>
       <c r="AM468" s="25"/>
       <c r="AN468" s="25" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="AO468" s="25"/>
       <c r="AP468" s="25"/>
       <c r="AQ468" s="25"/>
       <c r="AR468" s="25" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="AS468" s="25"/>
       <c r="AT468" s="25" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="AU468" s="25"/>
       <c r="AV468" s="25"/>
@@ -50815,7 +50805,7 @@
         <v>933</v>
       </c>
       <c r="E469" s="37" t="s">
-        <v>2140</v>
+        <v>2130</v>
       </c>
       <c r="F469" s="25" t="s">
         <v>552</v>
@@ -50916,7 +50906,7 @@
         <v>485</v>
       </c>
       <c r="E470" s="37" t="s">
-        <v>2141</v>
+        <v>2131</v>
       </c>
       <c r="F470" s="25" t="s">
         <v>521</v>
@@ -50981,17 +50971,17 @@
       </c>
       <c r="AM470" s="25"/>
       <c r="AN470" s="25" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="AO470" s="25"/>
       <c r="AP470" s="25"/>
       <c r="AQ470" s="25"/>
       <c r="AR470" s="25" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="AS470" s="25"/>
       <c r="AT470" s="25" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="AU470" s="25"/>
       <c r="AV470" s="25"/>
@@ -51009,7 +50999,7 @@
         <v>911</v>
       </c>
       <c r="E471" s="37" t="s">
-        <v>1934</v>
+        <v>1924</v>
       </c>
       <c r="F471" s="25" t="s">
         <v>914</v>
@@ -51036,7 +51026,7 @@
       <c r="V471" s="25"/>
       <c r="W471" s="25"/>
       <c r="X471" s="25" t="s">
-        <v>1669</v>
+        <v>1667</v>
       </c>
       <c r="Z471" s="25" t="s">
         <v>70</v>
@@ -51098,7 +51088,7 @@
         <v>1220</v>
       </c>
       <c r="E472" s="37" t="s">
-        <v>2142</v>
+        <v>2132</v>
       </c>
       <c r="F472" s="25" t="s">
         <v>1217</v>
@@ -51127,7 +51117,7 @@
       <c r="V472" s="25"/>
       <c r="W472" s="25"/>
       <c r="X472" s="25" t="s">
-        <v>1670</v>
+        <v>1668</v>
       </c>
       <c r="Z472" s="25" t="s">
         <v>70</v>
@@ -51923,20 +51913,20 @@
       <c r="B483" s="55"/>
       <c r="C483" s="55"/>
       <c r="D483" s="55" t="s">
-        <v>1836</v>
+        <v>1826</v>
       </c>
       <c r="E483" s="55" t="s">
-        <v>2143</v>
+        <v>2133</v>
       </c>
       <c r="F483" s="55" t="s">
-        <v>1837</v>
+        <v>1827</v>
       </c>
       <c r="G483" s="55" t="s">
         <v>47</v>
       </c>
       <c r="H483" s="55"/>
       <c r="I483" s="55" t="s">
-        <v>1822</v>
+        <v>1812</v>
       </c>
       <c r="J483" s="55"/>
       <c r="K483" s="55" t="s">
@@ -51957,52 +51947,52 @@
       <c r="X483" s="55"/>
       <c r="Y483" s="56"/>
       <c r="Z483" s="55" t="s">
-        <v>1833</v>
+        <v>1823</v>
       </c>
       <c r="AA483" s="55" t="s">
-        <v>1833</v>
+        <v>1823</v>
       </c>
       <c r="AB483" s="55" t="s">
-        <v>1834</v>
+        <v>1824</v>
       </c>
       <c r="AC483" s="55" t="s">
-        <v>1834</v>
+        <v>1824</v>
       </c>
       <c r="AD483" s="55" t="s">
-        <v>1834</v>
+        <v>1824</v>
       </c>
       <c r="AE483" s="55"/>
       <c r="AF483" s="55" t="s">
-        <v>1833</v>
+        <v>1823</v>
       </c>
       <c r="AG483" s="55" t="s">
-        <v>1834</v>
+        <v>1824</v>
       </c>
       <c r="AH483" s="55" t="s">
-        <v>1834</v>
+        <v>1824</v>
       </c>
       <c r="AI483" s="55" t="s">
-        <v>1833</v>
+        <v>1823</v>
       </c>
       <c r="AJ483" s="55" t="s">
-        <v>1833</v>
+        <v>1823</v>
       </c>
       <c r="AK483" s="55" t="s">
-        <v>1833</v>
+        <v>1823</v>
       </c>
       <c r="AL483" s="56"/>
       <c r="AM483" s="55"/>
       <c r="AN483" s="55" t="s">
-        <v>1838</v>
+        <v>1828</v>
       </c>
       <c r="AO483" s="55"/>
       <c r="AP483" s="55"/>
       <c r="AQ483" s="55" t="s">
-        <v>1838</v>
+        <v>1828</v>
       </c>
       <c r="AR483" s="55"/>
       <c r="AS483" s="55" t="s">
-        <v>1838</v>
+        <v>1828</v>
       </c>
       <c r="AT483" s="55"/>
       <c r="AU483" s="55"/>
@@ -52019,20 +52009,20 @@
       <c r="B484" s="55"/>
       <c r="C484" s="55"/>
       <c r="D484" s="55" t="s">
-        <v>1839</v>
+        <v>1829</v>
       </c>
       <c r="E484" s="55" t="s">
-        <v>2144</v>
+        <v>2134</v>
       </c>
       <c r="F484" s="55" t="s">
-        <v>1840</v>
+        <v>1830</v>
       </c>
       <c r="G484" s="55" t="s">
         <v>47</v>
       </c>
       <c r="H484" s="55"/>
       <c r="I484" s="55" t="s">
-        <v>1822</v>
+        <v>1812</v>
       </c>
       <c r="J484" s="55"/>
       <c r="K484" s="55" t="s">
@@ -52053,52 +52043,52 @@
       <c r="X484" s="55"/>
       <c r="Y484" s="56"/>
       <c r="Z484" s="55" t="s">
-        <v>1833</v>
+        <v>1823</v>
       </c>
       <c r="AA484" s="55" t="s">
-        <v>1833</v>
+        <v>1823</v>
       </c>
       <c r="AB484" s="55" t="s">
-        <v>1834</v>
+        <v>1824</v>
       </c>
       <c r="AC484" s="55" t="s">
-        <v>1834</v>
+        <v>1824</v>
       </c>
       <c r="AD484" s="55" t="s">
-        <v>1834</v>
+        <v>1824</v>
       </c>
       <c r="AE484" s="55"/>
       <c r="AF484" s="55" t="s">
-        <v>1833</v>
+        <v>1823</v>
       </c>
       <c r="AG484" s="55" t="s">
-        <v>1834</v>
+        <v>1824</v>
       </c>
       <c r="AH484" s="55" t="s">
-        <v>1834</v>
+        <v>1824</v>
       </c>
       <c r="AI484" s="55" t="s">
-        <v>1833</v>
+        <v>1823</v>
       </c>
       <c r="AJ484" s="55" t="s">
-        <v>1833</v>
+        <v>1823</v>
       </c>
       <c r="AK484" s="55" t="s">
-        <v>1833</v>
+        <v>1823</v>
       </c>
       <c r="AL484" s="56"/>
       <c r="AM484" s="55"/>
       <c r="AN484" s="55" t="s">
-        <v>1841</v>
+        <v>1831</v>
       </c>
       <c r="AO484" s="55"/>
       <c r="AP484" s="55"/>
       <c r="AQ484" s="55" t="s">
-        <v>1841</v>
+        <v>1831</v>
       </c>
       <c r="AR484" s="55"/>
       <c r="AS484" s="55" t="s">
-        <v>1841</v>
+        <v>1831</v>
       </c>
       <c r="AT484" s="55"/>
       <c r="AU484" s="55"/>
@@ -52118,7 +52108,7 @@
         <v>956</v>
       </c>
       <c r="E485" s="37" t="s">
-        <v>2145</v>
+        <v>2135</v>
       </c>
       <c r="F485" s="25" t="s">
         <v>544</v>
@@ -52221,7 +52211,7 @@
         <v>477</v>
       </c>
       <c r="E486" s="37" t="s">
-        <v>2146</v>
+        <v>2136</v>
       </c>
       <c r="F486" s="25" t="s">
         <v>508</v>
@@ -52314,7 +52304,7 @@
         <v>957</v>
       </c>
       <c r="E487" s="37" t="s">
-        <v>2147</v>
+        <v>2137</v>
       </c>
       <c r="F487" s="25" t="s">
         <v>546</v>
@@ -52417,7 +52407,7 @@
         <v>478</v>
       </c>
       <c r="E488" s="37" t="s">
-        <v>2148</v>
+        <v>2138</v>
       </c>
       <c r="F488" s="25" t="s">
         <v>510</v>
@@ -52510,7 +52500,7 @@
         <v>958</v>
       </c>
       <c r="E489" s="37" t="s">
-        <v>2149</v>
+        <v>2139</v>
       </c>
       <c r="F489" s="25" t="s">
         <v>547</v>
@@ -52545,7 +52535,7 @@
       <c r="V489" s="25"/>
       <c r="W489" s="25"/>
       <c r="X489" s="25" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
       <c r="Z489" s="25" t="s">
         <v>25</v>
@@ -52615,7 +52605,7 @@
         <v>479</v>
       </c>
       <c r="E490" s="37" t="s">
-        <v>2150</v>
+        <v>2140</v>
       </c>
       <c r="F490" s="25" t="s">
         <v>512</v>
@@ -52644,7 +52634,7 @@
       <c r="V490" s="25"/>
       <c r="W490" s="25"/>
       <c r="X490" s="25" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
       <c r="Z490" s="25" t="s">
         <v>25</v>
@@ -52710,7 +52700,7 @@
         <v>480</v>
       </c>
       <c r="E491" s="37" t="s">
-        <v>2151</v>
+        <v>2141</v>
       </c>
       <c r="F491" s="25" t="s">
         <v>513</v>
@@ -52775,17 +52765,17 @@
       </c>
       <c r="AM491" s="25"/>
       <c r="AN491" s="25" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="AO491" s="25"/>
       <c r="AP491" s="25"/>
       <c r="AQ491" s="25"/>
       <c r="AR491" s="25" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="AS491" s="25"/>
       <c r="AT491" s="25" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="AU491" s="25"/>
       <c r="AV491" s="25"/>
@@ -52803,7 +52793,7 @@
         <v>481</v>
       </c>
       <c r="E492" s="37" t="s">
-        <v>2152</v>
+        <v>2142</v>
       </c>
       <c r="F492" s="25" t="s">
         <v>514</v>
@@ -52868,17 +52858,17 @@
       </c>
       <c r="AM492" s="25"/>
       <c r="AN492" s="25" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="AO492" s="25"/>
       <c r="AP492" s="25"/>
       <c r="AQ492" s="25"/>
       <c r="AR492" s="25" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="AS492" s="25"/>
       <c r="AT492" s="25" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="AU492" s="25"/>
       <c r="AV492" s="25"/>
@@ -52896,7 +52886,7 @@
         <v>959</v>
       </c>
       <c r="E493" s="37" t="s">
-        <v>2153</v>
+        <v>2143</v>
       </c>
       <c r="F493" s="25" t="s">
         <v>515</v>
@@ -52989,7 +52979,7 @@
         <v>960</v>
       </c>
       <c r="E494" s="37" t="s">
-        <v>2154</v>
+        <v>2144</v>
       </c>
       <c r="F494" s="25" t="s">
         <v>554</v>
@@ -53088,7 +53078,7 @@
         <v>486</v>
       </c>
       <c r="E495" s="37" t="s">
-        <v>2155</v>
+        <v>2145</v>
       </c>
       <c r="F495" s="25" t="s">
         <v>523</v>
@@ -53179,7 +53169,7 @@
         <v>1184</v>
       </c>
       <c r="E496" s="37" t="s">
-        <v>2156</v>
+        <v>2146</v>
       </c>
       <c r="F496" s="25" t="s">
         <v>524</v>
@@ -53272,7 +53262,7 @@
         <v>961</v>
       </c>
       <c r="E497" s="37" t="s">
-        <v>2157</v>
+        <v>2147</v>
       </c>
       <c r="F497" s="25" t="s">
         <v>525</v>
@@ -53365,7 +53355,7 @@
         <v>272</v>
       </c>
       <c r="E498" s="37" t="s">
-        <v>2158</v>
+        <v>2148</v>
       </c>
       <c r="F498" s="25" t="s">
         <v>526</v>
@@ -53430,16 +53420,16 @@
       </c>
       <c r="AM498" s="25"/>
       <c r="AN498" s="25" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
       <c r="AO498" s="25"/>
       <c r="AP498" s="25"/>
       <c r="AQ498" s="25" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
       <c r="AR498" s="25"/>
       <c r="AS498" s="25" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
       <c r="AT498" s="25"/>
       <c r="AU498" s="25"/>
@@ -53458,7 +53448,7 @@
         <v>487</v>
       </c>
       <c r="E499" s="37" t="s">
-        <v>2159</v>
+        <v>2149</v>
       </c>
       <c r="F499" s="25" t="s">
         <v>527</v>
@@ -53523,16 +53513,16 @@
       </c>
       <c r="AM499" s="25"/>
       <c r="AN499" s="25" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="AO499" s="25"/>
       <c r="AP499" s="25"/>
       <c r="AQ499" s="25" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="AR499" s="25"/>
       <c r="AS499" s="25" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="AT499" s="25"/>
       <c r="AU499" s="25"/>
@@ -53551,7 +53541,7 @@
         <v>948</v>
       </c>
       <c r="E500" s="37" t="s">
-        <v>2160</v>
+        <v>2150</v>
       </c>
       <c r="F500" s="25" t="s">
         <v>555</v>
@@ -53650,7 +53640,7 @@
         <v>646</v>
       </c>
       <c r="E501" s="37" t="s">
-        <v>2161</v>
+        <v>2151</v>
       </c>
       <c r="F501" s="25" t="s">
         <v>529</v>
@@ -53739,7 +53729,7 @@
         <v>677</v>
       </c>
       <c r="E502" s="37" t="s">
-        <v>2162</v>
+        <v>2152</v>
       </c>
       <c r="F502" s="25" t="s">
         <v>1218</v>
@@ -53826,7 +53816,7 @@
         <v>679</v>
       </c>
       <c r="E503" s="37" t="s">
-        <v>2163</v>
+        <v>2153</v>
       </c>
       <c r="F503" s="25" t="s">
         <v>1219</v>
@@ -53929,7 +53919,7 @@
         <v>680</v>
       </c>
       <c r="E504" s="37" t="s">
-        <v>2164</v>
+        <v>2154</v>
       </c>
       <c r="F504" s="25" t="s">
         <v>531</v>
@@ -54018,7 +54008,7 @@
         <v>1227</v>
       </c>
       <c r="E505" s="37" t="s">
-        <v>1957</v>
+        <v>1947</v>
       </c>
       <c r="F505" s="25" t="s">
         <v>532</v>
@@ -54117,7 +54107,7 @@
         <v>488</v>
       </c>
       <c r="E506" s="37" t="s">
-        <v>2165</v>
+        <v>2155</v>
       </c>
       <c r="F506" s="25" t="s">
         <v>533</v>
@@ -54208,7 +54198,7 @@
         <v>287</v>
       </c>
       <c r="E507" s="37" t="s">
-        <v>2166</v>
+        <v>2156</v>
       </c>
       <c r="F507" s="25" t="s">
         <v>286</v>
@@ -54273,16 +54263,16 @@
       </c>
       <c r="AM507" s="25"/>
       <c r="AN507" s="25" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
       <c r="AO507" s="25"/>
       <c r="AP507" s="25"/>
       <c r="AQ507" s="25" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
       <c r="AR507" s="25"/>
       <c r="AS507" s="25" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
       <c r="AT507" s="25"/>
       <c r="AU507" s="25"/>
@@ -54301,7 +54291,7 @@
         <v>237</v>
       </c>
       <c r="E508" s="37" t="s">
-        <v>2167</v>
+        <v>2157</v>
       </c>
       <c r="F508" s="25" t="s">
         <v>534</v>
@@ -54366,16 +54356,16 @@
       </c>
       <c r="AM508" s="25"/>
       <c r="AN508" s="25" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="AO508" s="25"/>
       <c r="AP508" s="25"/>
       <c r="AQ508" s="25" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="AR508" s="25"/>
       <c r="AS508" s="25" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="AT508" s="25"/>
       <c r="AU508" s="25"/>
@@ -54391,10 +54381,10 @@
       <c r="B509" s="25"/>
       <c r="C509" s="25"/>
       <c r="D509" s="25" t="s">
-        <v>1688</v>
+        <v>1678</v>
       </c>
       <c r="E509" s="37" t="s">
-        <v>2013</v>
+        <v>2003</v>
       </c>
       <c r="F509" s="25" t="s">
         <v>214</v>
@@ -54459,16 +54449,16 @@
       </c>
       <c r="AM509" s="25"/>
       <c r="AN509" s="25" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="AO509" s="25"/>
       <c r="AP509" s="25"/>
       <c r="AQ509" s="25" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="AR509" s="25"/>
       <c r="AS509" s="25" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="AT509" s="25"/>
       <c r="AU509" s="25"/>
@@ -54487,7 +54477,7 @@
         <v>91</v>
       </c>
       <c r="E510" s="37" t="s">
-        <v>2014</v>
+        <v>2004</v>
       </c>
       <c r="F510" s="25" t="s">
         <v>215</v>
@@ -54552,16 +54542,16 @@
       </c>
       <c r="AM510" s="25"/>
       <c r="AN510" s="25" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="AO510" s="25"/>
       <c r="AP510" s="25"/>
       <c r="AQ510" s="25" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="AR510" s="25"/>
       <c r="AS510" s="25" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="AT510" s="25"/>
       <c r="AU510" s="25"/>
@@ -54580,7 +54570,7 @@
         <v>92</v>
       </c>
       <c r="E511" s="37" t="s">
-        <v>2015</v>
+        <v>2005</v>
       </c>
       <c r="F511" s="25" t="s">
         <v>216</v>
@@ -54645,16 +54635,16 @@
       </c>
       <c r="AM511" s="25"/>
       <c r="AN511" s="25" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="AO511" s="25"/>
       <c r="AP511" s="25"/>
       <c r="AQ511" s="25" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="AR511" s="25"/>
       <c r="AS511" s="25" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="AT511" s="25"/>
       <c r="AU511" s="25"/>
@@ -54673,7 +54663,7 @@
         <v>1530</v>
       </c>
       <c r="E512" s="37" t="s">
-        <v>2168</v>
+        <v>2158</v>
       </c>
       <c r="F512" s="25" t="s">
         <v>1531</v>
@@ -54683,7 +54673,7 @@
       </c>
       <c r="H512" s="25"/>
       <c r="I512" s="25" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="J512" s="25"/>
       <c r="K512" s="25" t="s">
@@ -54738,16 +54728,16 @@
       </c>
       <c r="AM512" s="25"/>
       <c r="AN512" s="25" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
       <c r="AO512" s="25"/>
       <c r="AP512" s="25"/>
       <c r="AQ512" s="25" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
       <c r="AR512" s="25"/>
       <c r="AS512" s="25" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
       <c r="AT512" s="25"/>
       <c r="AU512" s="25"/>
@@ -54766,7 +54756,7 @@
         <v>1532</v>
       </c>
       <c r="E513" s="37" t="s">
-        <v>2169</v>
+        <v>2159</v>
       </c>
       <c r="F513" s="25" t="s">
         <v>1533</v>
@@ -54776,7 +54766,7 @@
       </c>
       <c r="H513" s="25"/>
       <c r="I513" s="25" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="J513" s="25"/>
       <c r="K513" s="25" t="s">
@@ -54831,16 +54821,16 @@
       </c>
       <c r="AM513" s="25"/>
       <c r="AN513" s="25" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
       <c r="AO513" s="25"/>
       <c r="AP513" s="25"/>
       <c r="AQ513" s="25" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
       <c r="AR513" s="25"/>
       <c r="AS513" s="25" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
       <c r="AT513" s="25"/>
       <c r="AU513" s="25"/>
@@ -54859,7 +54849,7 @@
         <v>1535</v>
       </c>
       <c r="E514" s="37" t="s">
-        <v>2170</v>
+        <v>2160</v>
       </c>
       <c r="F514" s="25" t="s">
         <v>1536</v>
@@ -54869,7 +54859,7 @@
       </c>
       <c r="H514" s="25"/>
       <c r="I514" s="25" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="J514" s="25"/>
       <c r="K514" s="25" t="s">
@@ -54924,16 +54914,16 @@
       </c>
       <c r="AM514" s="25"/>
       <c r="AN514" s="25" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="AO514" s="25"/>
       <c r="AP514" s="25"/>
       <c r="AQ514" s="25" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="AR514" s="25"/>
       <c r="AS514" s="25" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="AT514" s="25"/>
       <c r="AU514" s="25"/>
@@ -54952,7 +54942,7 @@
         <v>1537</v>
       </c>
       <c r="E515" s="37" t="s">
-        <v>2171</v>
+        <v>2161</v>
       </c>
       <c r="F515" s="25" t="s">
         <v>1538</v>
@@ -54962,7 +54952,7 @@
       </c>
       <c r="H515" s="25"/>
       <c r="I515" s="25" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="J515" s="25"/>
       <c r="K515" s="25" t="s">
@@ -55017,16 +55007,16 @@
       </c>
       <c r="AM515" s="25"/>
       <c r="AN515" s="25" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="AO515" s="25"/>
       <c r="AP515" s="25"/>
       <c r="AQ515" s="25" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="AR515" s="25"/>
       <c r="AS515" s="25" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="AT515" s="25"/>
       <c r="AU515" s="25"/>
@@ -55045,7 +55035,7 @@
         <v>1539</v>
       </c>
       <c r="E516" s="37" t="s">
-        <v>2172</v>
+        <v>2162</v>
       </c>
       <c r="F516" s="25" t="s">
         <v>1540</v>
@@ -55055,7 +55045,7 @@
       </c>
       <c r="H516" s="25"/>
       <c r="I516" s="25" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="J516" s="25"/>
       <c r="K516" s="25" t="s">
@@ -55110,16 +55100,16 @@
       </c>
       <c r="AM516" s="25"/>
       <c r="AN516" s="25" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="AO516" s="25"/>
       <c r="AP516" s="25"/>
       <c r="AQ516" s="25" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="AR516" s="25"/>
       <c r="AS516" s="25" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="AT516" s="25"/>
       <c r="AU516" s="25"/>
@@ -55138,7 +55128,7 @@
         <v>1541</v>
       </c>
       <c r="E517" s="37" t="s">
-        <v>2173</v>
+        <v>2163</v>
       </c>
       <c r="F517" s="25" t="s">
         <v>1542</v>
@@ -55148,7 +55138,7 @@
       </c>
       <c r="H517" s="25"/>
       <c r="I517" s="25" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="J517" s="25"/>
       <c r="K517" s="25" t="s">
@@ -55203,16 +55193,16 @@
       </c>
       <c r="AM517" s="25"/>
       <c r="AN517" s="25" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="AO517" s="25"/>
       <c r="AP517" s="25"/>
       <c r="AQ517" s="25" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="AR517" s="25"/>
       <c r="AS517" s="25" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="AT517" s="25"/>
       <c r="AU517" s="25"/>
@@ -55231,7 +55221,7 @@
         <v>1543</v>
       </c>
       <c r="E518" s="37" t="s">
-        <v>2174</v>
+        <v>2164</v>
       </c>
       <c r="F518" s="25" t="s">
         <v>1544</v>
@@ -55296,16 +55286,16 @@
       </c>
       <c r="AM518" s="25"/>
       <c r="AN518" s="25" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="AO518" s="25"/>
       <c r="AP518" s="25"/>
       <c r="AQ518" s="25" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="AR518" s="25"/>
       <c r="AS518" s="25" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="AT518" s="25"/>
       <c r="AU518" s="25"/>
@@ -55324,7 +55314,7 @@
         <v>1234</v>
       </c>
       <c r="E519" s="37" t="s">
-        <v>2023</v>
+        <v>2013</v>
       </c>
       <c r="F519" s="25" t="s">
         <v>556</v>
@@ -55421,7 +55411,7 @@
         <v>489</v>
       </c>
       <c r="E520" s="37" t="s">
-        <v>2024</v>
+        <v>2014</v>
       </c>
       <c r="F520" s="25" t="s">
         <v>536</v>
@@ -55510,7 +55500,7 @@
         <v>490</v>
       </c>
       <c r="E521" s="37" t="s">
-        <v>2175</v>
+        <v>2165</v>
       </c>
       <c r="F521" s="25" t="s">
         <v>537</v>
@@ -55601,7 +55591,7 @@
         <v>592</v>
       </c>
       <c r="E522" s="37" t="s">
-        <v>2176</v>
+        <v>2166</v>
       </c>
       <c r="F522" s="25" t="s">
         <v>538</v>
@@ -55666,7 +55656,7 @@
       </c>
       <c r="AM522" s="25"/>
       <c r="AN522" s="25" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="AO522" s="25"/>
       <c r="AP522" s="25"/>
@@ -55690,7 +55680,7 @@
         <v>593</v>
       </c>
       <c r="E523" s="37" t="s">
-        <v>2177</v>
+        <v>2167</v>
       </c>
       <c r="F523" s="25" t="s">
         <v>539</v>
@@ -55755,7 +55745,7 @@
       </c>
       <c r="AM523" s="25"/>
       <c r="AN523" s="25" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="AO523" s="25"/>
       <c r="AP523" s="25"/>
@@ -55865,7 +55855,7 @@
         <v>1127</v>
       </c>
       <c r="E525" s="37" t="s">
-        <v>2178</v>
+        <v>2168</v>
       </c>
       <c r="F525" s="25" t="s">
         <v>259</v>
@@ -55894,7 +55884,7 @@
       <c r="V525" s="25"/>
       <c r="W525" s="25"/>
       <c r="X525" s="25" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="Z525" s="25"/>
       <c r="AA525" s="25"/>
@@ -55936,7 +55926,7 @@
         <v>253</v>
       </c>
       <c r="E526" s="37" t="s">
-        <v>2179</v>
+        <v>2169</v>
       </c>
       <c r="F526" s="25" t="s">
         <v>255</v>
@@ -55965,7 +55955,7 @@
       <c r="V526" s="25"/>
       <c r="W526" s="25"/>
       <c r="X526" s="25" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="Z526" s="25" t="s">
         <v>25</v>
@@ -56029,7 +56019,7 @@
         <v>254</v>
       </c>
       <c r="E527" s="37" t="s">
-        <v>2180</v>
+        <v>2170</v>
       </c>
       <c r="F527" s="25" t="s">
         <v>256</v>
@@ -56058,7 +56048,7 @@
       <c r="V527" s="25"/>
       <c r="W527" s="25"/>
       <c r="X527" s="25" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="Z527" s="25" t="s">
         <v>25</v>
@@ -56122,7 +56112,7 @@
         <v>300</v>
       </c>
       <c r="E528" s="37" t="s">
-        <v>2181</v>
+        <v>2171</v>
       </c>
       <c r="F528" s="25" t="s">
         <v>301</v>
@@ -56153,7 +56143,7 @@
       <c r="V528" s="25"/>
       <c r="W528" s="25"/>
       <c r="X528" s="25" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="Z528" s="25" t="s">
         <v>70</v>
@@ -56191,11 +56181,11 @@
       </c>
       <c r="AM528" s="25"/>
       <c r="AN528" s="25" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="AO528" s="25"/>
       <c r="AP528" s="25" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="AQ528" s="25"/>
       <c r="AR528" s="25"/>
@@ -56217,7 +56207,7 @@
         <v>302</v>
       </c>
       <c r="E529" s="37" t="s">
-        <v>2182</v>
+        <v>2172</v>
       </c>
       <c r="F529" s="25" t="s">
         <v>303</v>
@@ -56248,7 +56238,7 @@
       <c r="V529" s="25"/>
       <c r="W529" s="25"/>
       <c r="X529" s="25" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="Z529" s="25" t="s">
         <v>70</v>
@@ -56286,11 +56276,11 @@
       </c>
       <c r="AM529" s="25"/>
       <c r="AN529" s="25" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="AO529" s="25"/>
       <c r="AP529" s="25" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="AQ529" s="25"/>
       <c r="AR529" s="25"/>
@@ -56398,7 +56388,7 @@
         <v>822</v>
       </c>
       <c r="E531" s="37" t="s">
-        <v>2183</v>
+        <v>2173</v>
       </c>
       <c r="F531" s="25" t="s">
         <v>818</v>
@@ -56555,7 +56545,7 @@
         <v>824</v>
       </c>
       <c r="E533" s="37" t="s">
-        <v>2184</v>
+        <v>2174</v>
       </c>
       <c r="F533" s="25" t="s">
         <v>819</v>
@@ -56712,7 +56702,7 @@
         <v>826</v>
       </c>
       <c r="E535" s="37" t="s">
-        <v>2185</v>
+        <v>2175</v>
       </c>
       <c r="F535" s="25" t="s">
         <v>1130</v>
@@ -56869,7 +56859,7 @@
         <v>828</v>
       </c>
       <c r="E537" s="37" t="s">
-        <v>2186</v>
+        <v>2176</v>
       </c>
       <c r="F537" s="25" t="s">
         <v>820</v>
@@ -57026,7 +57016,7 @@
         <v>854</v>
       </c>
       <c r="E539" s="37" t="s">
-        <v>2187</v>
+        <v>2177</v>
       </c>
       <c r="F539" s="25" t="s">
         <v>1133</v>
@@ -57183,7 +57173,7 @@
         <v>856</v>
       </c>
       <c r="E541" s="37" t="s">
-        <v>2188</v>
+        <v>2178</v>
       </c>
       <c r="F541" s="25" t="s">
         <v>1135</v>
@@ -57340,7 +57330,7 @@
         <v>830</v>
       </c>
       <c r="E543" s="37" t="s">
-        <v>2189</v>
+        <v>2179</v>
       </c>
       <c r="F543" s="25" t="s">
         <v>922</v>
@@ -57497,7 +57487,7 @@
         <v>1244</v>
       </c>
       <c r="E545" s="37" t="s">
-        <v>2190</v>
+        <v>2180</v>
       </c>
       <c r="F545" s="25" t="s">
         <v>1245</v>
@@ -57654,7 +57644,7 @@
         <v>1247</v>
       </c>
       <c r="E547" s="37" t="s">
-        <v>2191</v>
+        <v>2181</v>
       </c>
       <c r="F547" s="25" t="s">
         <v>1248</v>
@@ -57811,7 +57801,7 @@
         <v>921</v>
       </c>
       <c r="E549" s="37" t="s">
-        <v>2192</v>
+        <v>2182</v>
       </c>
       <c r="F549" s="25" t="s">
         <v>1137</v>
@@ -57968,7 +57958,7 @@
         <v>920</v>
       </c>
       <c r="E551" s="37" t="s">
-        <v>2193</v>
+        <v>2183</v>
       </c>
       <c r="F551" s="25" t="s">
         <v>923</v>
@@ -58039,7 +58029,7 @@
         <v>491</v>
       </c>
       <c r="E552" s="37" t="s">
-        <v>2194</v>
+        <v>2184</v>
       </c>
       <c r="F552" s="25" t="s">
         <v>540</v>
@@ -58104,18 +58094,18 @@
       </c>
       <c r="AM552" s="25"/>
       <c r="AN552" s="25" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="AO552" s="25"/>
       <c r="AP552" s="25" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="AQ552" s="25" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="AR552" s="25"/>
       <c r="AS552" s="25" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="AT552" s="25"/>
       <c r="AU552" s="25"/>
@@ -58134,7 +58124,7 @@
         <v>66</v>
       </c>
       <c r="E553" s="37" t="s">
-        <v>2195</v>
+        <v>2185</v>
       </c>
       <c r="F553" s="25" t="s">
         <v>65</v>
@@ -58231,7 +58221,7 @@
         <v>586</v>
       </c>
       <c r="E554" s="37" t="s">
-        <v>2196</v>
+        <v>2186</v>
       </c>
       <c r="F554" s="25" t="s">
         <v>563</v>
@@ -58300,7 +58290,7 @@
         <v>568</v>
       </c>
       <c r="E555" s="37" t="s">
-        <v>2197</v>
+        <v>2187</v>
       </c>
       <c r="F555" s="25" t="s">
         <v>567</v>
@@ -58341,18 +58331,18 @@
       <c r="AK555" s="25"/>
       <c r="AM555" s="25"/>
       <c r="AN555" s="25" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="AO555" s="25"/>
       <c r="AP555" s="25"/>
       <c r="AQ555" s="25"/>
       <c r="AR555" s="25"/>
       <c r="AS555" s="25" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="AT555" s="25"/>
       <c r="AU555" s="25" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="AV555" s="25"/>
       <c r="AW555" s="25"/>
@@ -58369,7 +58359,7 @@
         <v>1254</v>
       </c>
       <c r="E556" s="37" t="s">
-        <v>2198</v>
+        <v>2188</v>
       </c>
       <c r="F556" s="25" t="s">
         <v>1255</v>
@@ -58412,11 +58402,11 @@
       <c r="AK556" s="25"/>
       <c r="AM556" s="25"/>
       <c r="AN556" s="25" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="AO556" s="25"/>
       <c r="AP556" s="25" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="AQ556" s="25"/>
       <c r="AR556" s="25"/>
@@ -58438,7 +58428,7 @@
         <v>1252</v>
       </c>
       <c r="E557" s="37" t="s">
-        <v>2199</v>
+        <v>2189</v>
       </c>
       <c r="F557" s="25" t="s">
         <v>1253</v>
@@ -58481,11 +58471,11 @@
       <c r="AK557" s="25"/>
       <c r="AM557" s="25"/>
       <c r="AN557" s="25" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="AO557" s="25"/>
       <c r="AP557" s="25" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="AQ557" s="25"/>
       <c r="AR557" s="25"/>
@@ -58507,7 +58497,7 @@
         <v>570</v>
       </c>
       <c r="E558" s="37" t="s">
-        <v>2200</v>
+        <v>2190</v>
       </c>
       <c r="F558" s="25" t="s">
         <v>569</v>
@@ -58548,14 +58538,14 @@
       <c r="AK558" s="25"/>
       <c r="AM558" s="25"/>
       <c r="AN558" s="25" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
       <c r="AO558" s="25"/>
       <c r="AP558" s="25"/>
       <c r="AQ558" s="25"/>
       <c r="AR558" s="25"/>
       <c r="AS558" s="25" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
       <c r="AT558" s="25"/>
       <c r="AU558" s="25"/>
@@ -58660,7 +58650,7 @@
         <v>1140</v>
       </c>
       <c r="E560" s="37" t="s">
-        <v>2201</v>
+        <v>2191</v>
       </c>
       <c r="F560" s="25" t="s">
         <v>1141</v>
@@ -58720,13 +58710,13 @@
       <c r="B561" s="25"/>
       <c r="C561" s="25"/>
       <c r="D561" s="25" t="s">
-        <v>1696</v>
+        <v>1686</v>
       </c>
       <c r="E561" s="37" t="s">
-        <v>2202</v>
+        <v>2192</v>
       </c>
       <c r="F561" s="25" t="s">
-        <v>1697</v>
+        <v>1687</v>
       </c>
       <c r="G561" s="25"/>
       <c r="H561" s="25"/>
@@ -58764,14 +58754,14 @@
       <c r="AK561" s="25"/>
       <c r="AM561" s="25"/>
       <c r="AN561" s="25" t="s">
-        <v>1696</v>
+        <v>1686</v>
       </c>
       <c r="AO561" s="25"/>
       <c r="AP561" s="25"/>
       <c r="AQ561" s="25"/>
       <c r="AR561" s="25"/>
       <c r="AS561" s="25" t="s">
-        <v>1696</v>
+        <v>1686</v>
       </c>
       <c r="AT561" s="25"/>
       <c r="AU561" s="25"/>
@@ -58787,13 +58777,13 @@
       <c r="B562" s="25"/>
       <c r="C562" s="25"/>
       <c r="D562" s="25" t="s">
-        <v>1698</v>
+        <v>1688</v>
       </c>
       <c r="E562" s="37" t="s">
-        <v>2203</v>
+        <v>2193</v>
       </c>
       <c r="F562" s="25" t="s">
-        <v>1814</v>
+        <v>1804</v>
       </c>
       <c r="G562" s="25"/>
       <c r="H562" s="25"/>
@@ -58831,14 +58821,14 @@
       <c r="AK562" s="25"/>
       <c r="AM562" s="25"/>
       <c r="AN562" s="25" t="s">
-        <v>1698</v>
+        <v>1688</v>
       </c>
       <c r="AO562" s="25"/>
       <c r="AP562" s="25"/>
       <c r="AQ562" s="25"/>
       <c r="AR562" s="25"/>
       <c r="AS562" s="25" t="s">
-        <v>1698</v>
+        <v>1688</v>
       </c>
       <c r="AT562" s="25"/>
       <c r="AU562" s="25"/>
@@ -58850,40 +58840,40 @@
     <row r="563" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A563" s="9"/>
       <c r="AM563" s="53" t="s">
-        <v>2255</v>
+        <v>2245</v>
       </c>
       <c r="AN563" s="53" t="s">
-        <v>2256</v>
+        <v>2246</v>
       </c>
       <c r="AO563" s="53" t="s">
-        <v>2255</v>
+        <v>2245</v>
       </c>
       <c r="AP563" s="53" t="s">
-        <v>2256</v>
+        <v>2246</v>
       </c>
       <c r="AQ563" s="53" t="s">
-        <v>2255</v>
+        <v>2245</v>
       </c>
       <c r="AR563" s="53" t="s">
-        <v>2256</v>
+        <v>2246</v>
       </c>
       <c r="AS563" s="53" t="s">
-        <v>2255</v>
+        <v>2245</v>
       </c>
       <c r="AT563" s="53" t="s">
-        <v>2256</v>
+        <v>2246</v>
       </c>
       <c r="AU563" s="53" t="s">
-        <v>2255</v>
+        <v>2245</v>
       </c>
       <c r="AV563" s="53" t="s">
-        <v>2256</v>
+        <v>2246</v>
       </c>
       <c r="AW563" s="53" t="s">
-        <v>2255</v>
+        <v>2245</v>
       </c>
       <c r="AX563" s="53" t="s">
-        <v>2256</v>
+        <v>2246</v>
       </c>
       <c r="AZ563" s="13"/>
     </row>
@@ -58896,7 +58886,7 @@
       </c>
       <c r="C564" s="33"/>
       <c r="D564" s="33" t="s">
-        <v>1704</v>
+        <v>1694</v>
       </c>
       <c r="E564" s="34"/>
       <c r="F564" s="33"/>
@@ -58940,11 +58930,11 @@
       <c r="AL564" s="49"/>
       <c r="AM564" s="33"/>
       <c r="AN564" s="33" t="s">
-        <v>1705</v>
+        <v>1695</v>
       </c>
       <c r="AO564" s="33"/>
       <c r="AP564" s="33" t="s">
-        <v>1705</v>
+        <v>1695</v>
       </c>
       <c r="AQ564" s="33"/>
       <c r="AR564" s="33"/>
@@ -58964,18 +58954,18 @@
       <c r="B565" s="27"/>
       <c r="C565" s="27"/>
       <c r="D565" s="27" t="s">
-        <v>1706</v>
+        <v>1696</v>
       </c>
       <c r="E565" s="28" t="s">
-        <v>2204</v>
+        <v>2194</v>
       </c>
       <c r="F565" s="27" t="s">
-        <v>1707</v>
+        <v>1697</v>
       </c>
       <c r="G565" s="27"/>
       <c r="H565" s="27"/>
       <c r="I565" s="27" t="s">
-        <v>1708</v>
+        <v>1698</v>
       </c>
       <c r="J565" s="27"/>
       <c r="K565" s="27" t="s">
@@ -59008,11 +58998,11 @@
       <c r="AK565" s="27"/>
       <c r="AM565" s="33"/>
       <c r="AN565" s="33" t="s">
-        <v>1709</v>
+        <v>1699</v>
       </c>
       <c r="AO565" s="33"/>
       <c r="AP565" s="33" t="s">
-        <v>1709</v>
+        <v>1699</v>
       </c>
       <c r="AQ565" s="33"/>
       <c r="AR565" s="33"/>
@@ -59031,18 +59021,18 @@
       <c r="B566" s="33"/>
       <c r="C566" s="33"/>
       <c r="D566" s="33" t="s">
-        <v>1710</v>
+        <v>1700</v>
       </c>
       <c r="E566" s="54" t="s">
-        <v>2205</v>
+        <v>2195</v>
       </c>
       <c r="F566" s="33" t="s">
-        <v>1711</v>
+        <v>1701</v>
       </c>
       <c r="G566" s="33"/>
       <c r="H566" s="33"/>
       <c r="I566" s="33" t="s">
-        <v>1712</v>
+        <v>1702</v>
       </c>
       <c r="J566" s="33"/>
       <c r="K566" s="33" t="s">
@@ -59075,11 +59065,11 @@
       <c r="AK566" s="33"/>
       <c r="AM566" s="33"/>
       <c r="AN566" s="33" t="s">
-        <v>1710</v>
+        <v>1700</v>
       </c>
       <c r="AO566" s="33"/>
       <c r="AP566" s="33" t="s">
-        <v>1710</v>
+        <v>1700</v>
       </c>
       <c r="AQ566" s="33"/>
       <c r="AR566" s="33"/>
@@ -59098,18 +59088,18 @@
       <c r="B567" s="33"/>
       <c r="C567" s="33"/>
       <c r="D567" s="33" t="s">
-        <v>1713</v>
+        <v>1703</v>
       </c>
       <c r="E567" s="54" t="s">
-        <v>2206</v>
+        <v>2196</v>
       </c>
       <c r="F567" s="33" t="s">
-        <v>1714</v>
+        <v>1704</v>
       </c>
       <c r="G567" s="33"/>
       <c r="H567" s="33"/>
       <c r="I567" s="33" t="s">
-        <v>1715</v>
+        <v>1705</v>
       </c>
       <c r="J567" s="33"/>
       <c r="K567" s="33" t="s">
@@ -59142,11 +59132,11 @@
       <c r="AK567" s="33"/>
       <c r="AM567" s="33"/>
       <c r="AN567" s="33" t="s">
-        <v>1716</v>
+        <v>1706</v>
       </c>
       <c r="AO567" s="33"/>
       <c r="AP567" s="33" t="s">
-        <v>1716</v>
+        <v>1706</v>
       </c>
       <c r="AQ567" s="33"/>
       <c r="AR567" s="33"/>
@@ -59165,18 +59155,18 @@
       <c r="B568" s="33"/>
       <c r="C568" s="33"/>
       <c r="D568" s="33" t="s">
-        <v>1717</v>
+        <v>1707</v>
       </c>
       <c r="E568" s="54" t="s">
-        <v>2207</v>
+        <v>2197</v>
       </c>
       <c r="F568" s="33" t="s">
-        <v>1718</v>
+        <v>1708</v>
       </c>
       <c r="G568" s="33"/>
       <c r="H568" s="33"/>
       <c r="I568" s="33" t="s">
-        <v>1719</v>
+        <v>1709</v>
       </c>
       <c r="J568" s="33"/>
       <c r="K568" s="33" t="s">
@@ -59209,11 +59199,11 @@
       <c r="AK568" s="33"/>
       <c r="AM568" s="33"/>
       <c r="AN568" s="33" t="s">
-        <v>1720</v>
+        <v>1710</v>
       </c>
       <c r="AO568" s="33"/>
       <c r="AP568" s="33" t="s">
-        <v>1720</v>
+        <v>1710</v>
       </c>
       <c r="AQ568" s="33"/>
       <c r="AR568" s="33"/>
@@ -59235,7 +59225,7 @@
         <v>278</v>
       </c>
       <c r="E569" s="54" t="s">
-        <v>2056</v>
+        <v>2046</v>
       </c>
       <c r="F569" s="33" t="s">
         <v>277</v>
@@ -59276,11 +59266,11 @@
       <c r="AK569" s="33"/>
       <c r="AM569" s="33"/>
       <c r="AN569" s="33" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="AO569" s="33"/>
       <c r="AP569" s="33" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="AQ569" s="33"/>
       <c r="AR569" s="33"/>
@@ -59302,10 +59292,10 @@
         <v>491</v>
       </c>
       <c r="E570" s="54" t="s">
-        <v>2194</v>
+        <v>2184</v>
       </c>
       <c r="F570" s="33" t="s">
-        <v>1721</v>
+        <v>1711</v>
       </c>
       <c r="G570" s="33"/>
       <c r="H570" s="33"/>
@@ -59343,11 +59333,11 @@
       <c r="AK570" s="33"/>
       <c r="AM570" s="33"/>
       <c r="AN570" s="33" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="AO570" s="33"/>
       <c r="AP570" s="33" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="AQ570" s="33"/>
       <c r="AR570" s="33"/>
@@ -59366,18 +59356,18 @@
       <c r="B571" s="33"/>
       <c r="C571" s="33"/>
       <c r="D571" s="33" t="s">
-        <v>1722</v>
+        <v>1712</v>
       </c>
       <c r="E571" s="54" t="s">
-        <v>2208</v>
+        <v>2198</v>
       </c>
       <c r="F571" s="33" t="s">
-        <v>1723</v>
+        <v>1713</v>
       </c>
       <c r="G571" s="33"/>
       <c r="H571" s="33"/>
       <c r="I571" s="33" t="s">
-        <v>1724</v>
+        <v>1714</v>
       </c>
       <c r="J571" s="33"/>
       <c r="K571" s="33" t="s">
@@ -59410,11 +59400,11 @@
       <c r="AK571" s="33"/>
       <c r="AM571" s="33"/>
       <c r="AN571" s="33" t="s">
-        <v>1725</v>
+        <v>1715</v>
       </c>
       <c r="AO571" s="33"/>
       <c r="AP571" s="33" t="s">
-        <v>1725</v>
+        <v>1715</v>
       </c>
       <c r="AQ571" s="33"/>
       <c r="AR571" s="33"/>
@@ -59433,13 +59423,13 @@
       <c r="B572" s="33"/>
       <c r="C572" s="33"/>
       <c r="D572" s="33" t="s">
-        <v>1726</v>
+        <v>1716</v>
       </c>
       <c r="E572" s="54" t="s">
-        <v>2209</v>
+        <v>2199</v>
       </c>
       <c r="F572" s="33" t="s">
-        <v>1727</v>
+        <v>1717</v>
       </c>
       <c r="G572" s="33"/>
       <c r="H572" s="33"/>
@@ -59477,11 +59467,11 @@
       <c r="AK572" s="33"/>
       <c r="AM572" s="33"/>
       <c r="AN572" s="33" t="s">
-        <v>1728</v>
+        <v>1718</v>
       </c>
       <c r="AO572" s="33"/>
       <c r="AP572" s="33" t="s">
-        <v>1728</v>
+        <v>1718</v>
       </c>
       <c r="AQ572" s="33"/>
       <c r="AR572" s="33"/>
@@ -59503,7 +59493,7 @@
         <v>5</v>
       </c>
       <c r="E573" s="54" t="s">
-        <v>2210</v>
+        <v>2200</v>
       </c>
       <c r="F573" s="33" t="s">
         <v>571</v>
@@ -59570,7 +59560,7 @@
         <v>82</v>
       </c>
       <c r="E574" s="54" t="s">
-        <v>2211</v>
+        <v>2201</v>
       </c>
       <c r="F574" s="33" t="s">
         <v>572</v>
@@ -59637,7 +59627,7 @@
         <v>79</v>
       </c>
       <c r="E575" s="54" t="s">
-        <v>2212</v>
+        <v>2202</v>
       </c>
       <c r="F575" s="33" t="s">
         <v>573</v>
@@ -59704,7 +59694,7 @@
         <v>80</v>
       </c>
       <c r="E576" s="54" t="s">
-        <v>2213</v>
+        <v>2203</v>
       </c>
       <c r="F576" s="33" t="s">
         <v>574</v>
@@ -59768,13 +59758,13 @@
       <c r="B577" s="33"/>
       <c r="C577" s="33"/>
       <c r="D577" s="33" t="s">
-        <v>1729</v>
+        <v>1719</v>
       </c>
       <c r="E577" s="54" t="s">
-        <v>2214</v>
+        <v>2204</v>
       </c>
       <c r="F577" s="33" t="s">
-        <v>1730</v>
+        <v>1720</v>
       </c>
       <c r="G577" s="33"/>
       <c r="H577" s="33"/>
@@ -59838,10 +59828,10 @@
         <v>248</v>
       </c>
       <c r="E578" s="54" t="s">
-        <v>2085</v>
+        <v>2075</v>
       </c>
       <c r="F578" s="33" t="s">
-        <v>1731</v>
+        <v>1721</v>
       </c>
       <c r="G578" s="33"/>
       <c r="H578" s="33"/>
@@ -59905,10 +59895,10 @@
         <v>575</v>
       </c>
       <c r="E579" s="54" t="s">
-        <v>2092</v>
+        <v>2082</v>
       </c>
       <c r="F579" s="33" t="s">
-        <v>1732</v>
+        <v>1722</v>
       </c>
       <c r="G579" s="33"/>
       <c r="H579" s="33"/>
@@ -59969,13 +59959,13 @@
       <c r="B580" s="33"/>
       <c r="C580" s="33"/>
       <c r="D580" s="33" t="s">
-        <v>1733</v>
+        <v>1723</v>
       </c>
       <c r="E580" s="54" t="s">
-        <v>2215</v>
+        <v>2205</v>
       </c>
       <c r="F580" s="33" t="s">
-        <v>1734</v>
+        <v>1724</v>
       </c>
       <c r="G580" s="33"/>
       <c r="H580" s="33"/>
@@ -60036,13 +60026,13 @@
       <c r="B581" s="33"/>
       <c r="C581" s="33"/>
       <c r="D581" s="33" t="s">
-        <v>1735</v>
+        <v>1725</v>
       </c>
       <c r="E581" s="54" t="s">
-        <v>2216</v>
+        <v>2206</v>
       </c>
       <c r="F581" s="33" t="s">
-        <v>1736</v>
+        <v>1726</v>
       </c>
       <c r="G581" s="33"/>
       <c r="H581" s="33"/>
@@ -60080,11 +60070,11 @@
       <c r="AK581" s="33"/>
       <c r="AM581" s="33"/>
       <c r="AN581" s="33" t="s">
-        <v>1737</v>
+        <v>1727</v>
       </c>
       <c r="AO581" s="33"/>
       <c r="AP581" s="33" t="s">
-        <v>1737</v>
+        <v>1727</v>
       </c>
       <c r="AQ581" s="33"/>
       <c r="AR581" s="33"/>
@@ -60103,13 +60093,13 @@
       <c r="B582" s="33"/>
       <c r="C582" s="33"/>
       <c r="D582" s="33" t="s">
-        <v>1738</v>
+        <v>1728</v>
       </c>
       <c r="E582" s="54" t="s">
-        <v>2217</v>
+        <v>2207</v>
       </c>
       <c r="F582" s="33" t="s">
-        <v>1739</v>
+        <v>1729</v>
       </c>
       <c r="G582" s="33"/>
       <c r="H582" s="33"/>
@@ -60147,11 +60137,11 @@
       <c r="AK582" s="33"/>
       <c r="AM582" s="33"/>
       <c r="AN582" s="33" t="s">
-        <v>1740</v>
+        <v>1730</v>
       </c>
       <c r="AO582" s="33"/>
       <c r="AP582" s="33" t="s">
-        <v>1740</v>
+        <v>1730</v>
       </c>
       <c r="AQ582" s="33"/>
       <c r="AR582" s="33"/>
@@ -60170,13 +60160,13 @@
       <c r="B583" s="33"/>
       <c r="C583" s="33"/>
       <c r="D583" s="33" t="s">
-        <v>1741</v>
+        <v>1731</v>
       </c>
       <c r="E583" s="54" t="s">
-        <v>2218</v>
+        <v>2208</v>
       </c>
       <c r="F583" s="33" t="s">
-        <v>1742</v>
+        <v>1732</v>
       </c>
       <c r="G583" s="33"/>
       <c r="H583" s="33"/>
@@ -60214,11 +60204,11 @@
       <c r="AK583" s="33"/>
       <c r="AM583" s="33"/>
       <c r="AN583" s="33" t="s">
-        <v>1743</v>
+        <v>1733</v>
       </c>
       <c r="AO583" s="33"/>
       <c r="AP583" s="33" t="s">
-        <v>1743</v>
+        <v>1733</v>
       </c>
       <c r="AQ583" s="33"/>
       <c r="AR583" s="33"/>
@@ -60237,18 +60227,18 @@
       <c r="B584" s="33"/>
       <c r="C584" s="33"/>
       <c r="D584" s="33" t="s">
-        <v>1744</v>
+        <v>1734</v>
       </c>
       <c r="E584" s="54" t="s">
-        <v>2219</v>
+        <v>2209</v>
       </c>
       <c r="F584" s="33" t="s">
-        <v>1745</v>
+        <v>1735</v>
       </c>
       <c r="G584" s="33"/>
       <c r="H584" s="33"/>
       <c r="I584" s="33" t="s">
-        <v>1746</v>
+        <v>1736</v>
       </c>
       <c r="J584" s="33"/>
       <c r="K584" s="33" t="s">
@@ -60281,11 +60271,11 @@
       <c r="AK584" s="33"/>
       <c r="AM584" s="33"/>
       <c r="AN584" s="33" t="s">
-        <v>1747</v>
+        <v>1737</v>
       </c>
       <c r="AO584" s="33"/>
       <c r="AP584" s="33" t="s">
-        <v>1747</v>
+        <v>1737</v>
       </c>
       <c r="AQ584" s="33"/>
       <c r="AR584" s="33"/>
@@ -60304,18 +60294,18 @@
       <c r="B585" s="33"/>
       <c r="C585" s="33"/>
       <c r="D585" s="33" t="s">
-        <v>1748</v>
+        <v>1738</v>
       </c>
       <c r="E585" s="54" t="s">
-        <v>2220</v>
+        <v>2210</v>
       </c>
       <c r="F585" s="33" t="s">
-        <v>1749</v>
+        <v>1739</v>
       </c>
       <c r="G585" s="33"/>
       <c r="H585" s="33"/>
       <c r="I585" s="33" t="s">
-        <v>1750</v>
+        <v>1740</v>
       </c>
       <c r="J585" s="33"/>
       <c r="K585" s="33" t="s">
@@ -60348,11 +60338,11 @@
       <c r="AK585" s="33"/>
       <c r="AM585" s="33"/>
       <c r="AN585" s="33" t="s">
-        <v>1751</v>
+        <v>1741</v>
       </c>
       <c r="AO585" s="33"/>
       <c r="AP585" s="33" t="s">
-        <v>1751</v>
+        <v>1741</v>
       </c>
       <c r="AQ585" s="33"/>
       <c r="AR585" s="33"/>
@@ -60371,18 +60361,18 @@
       <c r="B586" s="33"/>
       <c r="C586" s="33"/>
       <c r="D586" s="33" t="s">
-        <v>1752</v>
+        <v>1742</v>
       </c>
       <c r="E586" s="54" t="s">
-        <v>2221</v>
+        <v>2211</v>
       </c>
       <c r="F586" s="33" t="s">
-        <v>1753</v>
+        <v>1743</v>
       </c>
       <c r="G586" s="33"/>
       <c r="H586" s="33"/>
       <c r="I586" s="33" t="s">
-        <v>1754</v>
+        <v>1744</v>
       </c>
       <c r="J586" s="33"/>
       <c r="K586" s="33" t="s">
@@ -60415,11 +60405,11 @@
       <c r="AK586" s="33"/>
       <c r="AM586" s="33"/>
       <c r="AN586" s="33" t="s">
-        <v>1755</v>
+        <v>1745</v>
       </c>
       <c r="AO586" s="33"/>
       <c r="AP586" s="33" t="s">
-        <v>1755</v>
+        <v>1745</v>
       </c>
       <c r="AQ586" s="33"/>
       <c r="AR586" s="33"/>
@@ -60438,18 +60428,18 @@
       <c r="B587" s="33"/>
       <c r="C587" s="33"/>
       <c r="D587" s="33" t="s">
-        <v>1756</v>
+        <v>1746</v>
       </c>
       <c r="E587" s="54" t="s">
-        <v>2222</v>
+        <v>2212</v>
       </c>
       <c r="F587" s="33" t="s">
-        <v>1757</v>
+        <v>1747</v>
       </c>
       <c r="G587" s="33"/>
       <c r="H587" s="33"/>
       <c r="I587" s="33" t="s">
-        <v>1758</v>
+        <v>1748</v>
       </c>
       <c r="J587" s="33"/>
       <c r="K587" s="33" t="s">
@@ -60482,11 +60472,11 @@
       <c r="AK587" s="33"/>
       <c r="AM587" s="33"/>
       <c r="AN587" s="33" t="s">
-        <v>1759</v>
+        <v>1749</v>
       </c>
       <c r="AO587" s="33"/>
       <c r="AP587" s="33" t="s">
-        <v>1759</v>
+        <v>1749</v>
       </c>
       <c r="AQ587" s="33"/>
       <c r="AR587" s="33"/>
@@ -60505,18 +60495,18 @@
       <c r="B588" s="33"/>
       <c r="C588" s="33"/>
       <c r="D588" s="33" t="s">
-        <v>1760</v>
+        <v>1750</v>
       </c>
       <c r="E588" s="54" t="s">
-        <v>2223</v>
+        <v>2213</v>
       </c>
       <c r="F588" s="33" t="s">
-        <v>1761</v>
+        <v>1751</v>
       </c>
       <c r="G588" s="33"/>
       <c r="H588" s="33"/>
       <c r="I588" s="33" t="s">
-        <v>1746</v>
+        <v>1736</v>
       </c>
       <c r="J588" s="33"/>
       <c r="K588" s="33" t="s">
@@ -60549,11 +60539,11 @@
       <c r="AK588" s="33"/>
       <c r="AM588" s="33"/>
       <c r="AN588" s="33" t="s">
-        <v>1762</v>
+        <v>1752</v>
       </c>
       <c r="AO588" s="33"/>
       <c r="AP588" s="33" t="s">
-        <v>1762</v>
+        <v>1752</v>
       </c>
       <c r="AQ588" s="33"/>
       <c r="AR588" s="33"/>
@@ -60572,18 +60562,18 @@
       <c r="B589" s="33"/>
       <c r="C589" s="33"/>
       <c r="D589" s="33" t="s">
-        <v>1763</v>
+        <v>1753</v>
       </c>
       <c r="E589" s="54" t="s">
-        <v>2224</v>
+        <v>2214</v>
       </c>
       <c r="F589" s="33" t="s">
-        <v>1764</v>
+        <v>1754</v>
       </c>
       <c r="G589" s="33"/>
       <c r="H589" s="33"/>
       <c r="I589" s="33" t="s">
-        <v>1750</v>
+        <v>1740</v>
       </c>
       <c r="J589" s="33"/>
       <c r="K589" s="33" t="s">
@@ -60616,11 +60606,11 @@
       <c r="AK589" s="33"/>
       <c r="AM589" s="33"/>
       <c r="AN589" s="33" t="s">
-        <v>1765</v>
+        <v>1755</v>
       </c>
       <c r="AO589" s="33"/>
       <c r="AP589" s="33" t="s">
-        <v>1765</v>
+        <v>1755</v>
       </c>
       <c r="AQ589" s="33"/>
       <c r="AR589" s="33"/>
@@ -60639,18 +60629,18 @@
       <c r="B590" s="33"/>
       <c r="C590" s="33"/>
       <c r="D590" s="33" t="s">
-        <v>1766</v>
+        <v>1756</v>
       </c>
       <c r="E590" s="54" t="s">
-        <v>2225</v>
+        <v>2215</v>
       </c>
       <c r="F590" s="33" t="s">
-        <v>1767</v>
+        <v>1757</v>
       </c>
       <c r="G590" s="33"/>
       <c r="H590" s="33"/>
       <c r="I590" s="33" t="s">
-        <v>1754</v>
+        <v>1744</v>
       </c>
       <c r="J590" s="33"/>
       <c r="K590" s="33" t="s">
@@ -60683,11 +60673,11 @@
       <c r="AK590" s="33"/>
       <c r="AM590" s="33"/>
       <c r="AN590" s="33" t="s">
-        <v>1768</v>
+        <v>1758</v>
       </c>
       <c r="AO590" s="33"/>
       <c r="AP590" s="33" t="s">
-        <v>1768</v>
+        <v>1758</v>
       </c>
       <c r="AQ590" s="33"/>
       <c r="AR590" s="33"/>
@@ -60706,18 +60696,18 @@
       <c r="B591" s="33"/>
       <c r="C591" s="33"/>
       <c r="D591" s="33" t="s">
-        <v>1769</v>
+        <v>1759</v>
       </c>
       <c r="E591" s="54" t="s">
-        <v>2226</v>
+        <v>2216</v>
       </c>
       <c r="F591" s="33" t="s">
-        <v>1770</v>
+        <v>1760</v>
       </c>
       <c r="G591" s="33"/>
       <c r="H591" s="33"/>
       <c r="I591" s="33" t="s">
-        <v>1758</v>
+        <v>1748</v>
       </c>
       <c r="J591" s="33"/>
       <c r="K591" s="33" t="s">
@@ -60750,11 +60740,11 @@
       <c r="AK591" s="33"/>
       <c r="AM591" s="33"/>
       <c r="AN591" s="33" t="s">
-        <v>1771</v>
+        <v>1761</v>
       </c>
       <c r="AO591" s="33"/>
       <c r="AP591" s="33" t="s">
-        <v>1771</v>
+        <v>1761</v>
       </c>
       <c r="AQ591" s="33"/>
       <c r="AR591" s="33"/>
@@ -60773,18 +60763,18 @@
       <c r="B592" s="33"/>
       <c r="C592" s="33"/>
       <c r="D592" s="33" t="s">
-        <v>1772</v>
+        <v>1762</v>
       </c>
       <c r="E592" s="54" t="s">
-        <v>2227</v>
+        <v>2217</v>
       </c>
       <c r="F592" s="33" t="s">
-        <v>1773</v>
+        <v>1763</v>
       </c>
       <c r="G592" s="33"/>
       <c r="H592" s="33"/>
       <c r="I592" s="33" t="s">
-        <v>1746</v>
+        <v>1736</v>
       </c>
       <c r="J592" s="33"/>
       <c r="K592" s="33" t="s">
@@ -60817,11 +60807,11 @@
       <c r="AK592" s="33"/>
       <c r="AM592" s="33"/>
       <c r="AN592" s="33" t="s">
-        <v>1774</v>
+        <v>1764</v>
       </c>
       <c r="AO592" s="33"/>
       <c r="AP592" s="33" t="s">
-        <v>1774</v>
+        <v>1764</v>
       </c>
       <c r="AQ592" s="33"/>
       <c r="AR592" s="33"/>
@@ -60843,15 +60833,15 @@
         <v>238</v>
       </c>
       <c r="E593" s="54" t="s">
-        <v>2228</v>
+        <v>2218</v>
       </c>
       <c r="F593" s="33" t="s">
-        <v>1775</v>
+        <v>1765</v>
       </c>
       <c r="G593" s="33"/>
       <c r="H593" s="33"/>
       <c r="I593" s="33" t="s">
-        <v>1750</v>
+        <v>1740</v>
       </c>
       <c r="J593" s="33"/>
       <c r="K593" s="33" t="s">
@@ -60884,11 +60874,11 @@
       <c r="AK593" s="33"/>
       <c r="AM593" s="33"/>
       <c r="AN593" s="33" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="AO593" s="33"/>
       <c r="AP593" s="33" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="AQ593" s="33"/>
       <c r="AR593" s="33"/>
@@ -60910,15 +60900,15 @@
         <v>91</v>
       </c>
       <c r="E594" s="54" t="s">
-        <v>2229</v>
+        <v>2219</v>
       </c>
       <c r="F594" s="33" t="s">
-        <v>1776</v>
+        <v>1766</v>
       </c>
       <c r="G594" s="33"/>
       <c r="H594" s="33"/>
       <c r="I594" s="33" t="s">
-        <v>1754</v>
+        <v>1744</v>
       </c>
       <c r="J594" s="33"/>
       <c r="K594" s="33" t="s">
@@ -60951,11 +60941,11 @@
       <c r="AK594" s="33"/>
       <c r="AM594" s="33"/>
       <c r="AN594" s="33" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="AO594" s="33"/>
       <c r="AP594" s="33" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="AQ594" s="33"/>
       <c r="AR594" s="33"/>
@@ -60977,15 +60967,15 @@
         <v>92</v>
       </c>
       <c r="E595" s="54" t="s">
-        <v>2230</v>
+        <v>2220</v>
       </c>
       <c r="F595" s="33" t="s">
-        <v>1777</v>
+        <v>1767</v>
       </c>
       <c r="G595" s="33"/>
       <c r="H595" s="33"/>
       <c r="I595" s="33" t="s">
-        <v>1758</v>
+        <v>1748</v>
       </c>
       <c r="J595" s="33"/>
       <c r="K595" s="33" t="s">
@@ -61018,11 +61008,11 @@
       <c r="AK595" s="33"/>
       <c r="AM595" s="33"/>
       <c r="AN595" s="33" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="AO595" s="33"/>
       <c r="AP595" s="33" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="AQ595" s="33"/>
       <c r="AR595" s="33"/>
@@ -61037,40 +61027,40 @@
     <row r="596" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A596" s="9"/>
       <c r="AM596" s="53" t="s">
-        <v>2255</v>
+        <v>2245</v>
       </c>
       <c r="AN596" s="53" t="s">
-        <v>2256</v>
+        <v>2246</v>
       </c>
       <c r="AO596" s="53" t="s">
-        <v>2255</v>
+        <v>2245</v>
       </c>
       <c r="AP596" s="53" t="s">
-        <v>2256</v>
+        <v>2246</v>
       </c>
       <c r="AQ596" s="53" t="s">
-        <v>2255</v>
+        <v>2245</v>
       </c>
       <c r="AR596" s="53" t="s">
-        <v>2256</v>
+        <v>2246</v>
       </c>
       <c r="AS596" s="53" t="s">
-        <v>2255</v>
+        <v>2245</v>
       </c>
       <c r="AT596" s="53" t="s">
-        <v>2256</v>
+        <v>2246</v>
       </c>
       <c r="AU596" s="53" t="s">
-        <v>2255</v>
+        <v>2245</v>
       </c>
       <c r="AV596" s="53" t="s">
-        <v>2256</v>
+        <v>2246</v>
       </c>
       <c r="AW596" s="53" t="s">
-        <v>2255</v>
+        <v>2245</v>
       </c>
       <c r="AX596" s="53" t="s">
-        <v>2256</v>
+        <v>2246</v>
       </c>
       <c r="AZ596" s="13"/>
     </row>
@@ -61083,7 +61073,7 @@
       </c>
       <c r="C597" s="33"/>
       <c r="D597" s="33" t="s">
-        <v>1778</v>
+        <v>1768</v>
       </c>
       <c r="E597" s="34"/>
       <c r="F597" s="33"/>
@@ -61127,11 +61117,11 @@
       <c r="AL597" s="49"/>
       <c r="AM597" s="33"/>
       <c r="AN597" s="33" t="s">
-        <v>1779</v>
+        <v>1769</v>
       </c>
       <c r="AO597" s="33"/>
       <c r="AP597" s="33" t="s">
-        <v>1779</v>
+        <v>1769</v>
       </c>
       <c r="AQ597" s="33"/>
       <c r="AR597" s="33"/>
@@ -61151,18 +61141,18 @@
       <c r="B598" s="27"/>
       <c r="C598" s="27"/>
       <c r="D598" s="27" t="s">
-        <v>1780</v>
+        <v>1770</v>
       </c>
       <c r="E598" s="28" t="s">
-        <v>2231</v>
+        <v>2221</v>
       </c>
       <c r="F598" s="27" t="s">
-        <v>1781</v>
+        <v>1771</v>
       </c>
       <c r="G598" s="27"/>
       <c r="H598" s="27"/>
       <c r="I598" s="27" t="s">
-        <v>1782</v>
+        <v>1772</v>
       </c>
       <c r="J598" s="27"/>
       <c r="K598" s="27" t="s">
@@ -61195,11 +61185,11 @@
       <c r="AK598" s="27"/>
       <c r="AM598" s="33"/>
       <c r="AN598" s="33" t="s">
-        <v>1783</v>
+        <v>1773</v>
       </c>
       <c r="AO598" s="33"/>
       <c r="AP598" s="33" t="s">
-        <v>1783</v>
+        <v>1773</v>
       </c>
       <c r="AQ598" s="33"/>
       <c r="AR598" s="33"/>
@@ -61218,18 +61208,18 @@
       <c r="B599" s="33"/>
       <c r="C599" s="33"/>
       <c r="D599" s="33" t="s">
-        <v>1784</v>
+        <v>1774</v>
       </c>
       <c r="E599" s="54" t="s">
-        <v>2232</v>
+        <v>2222</v>
       </c>
       <c r="F599" s="33" t="s">
-        <v>1785</v>
+        <v>1775</v>
       </c>
       <c r="G599" s="33"/>
       <c r="H599" s="33"/>
       <c r="I599" s="33" t="s">
-        <v>1786</v>
+        <v>1776</v>
       </c>
       <c r="J599" s="33"/>
       <c r="K599" s="33" t="s">
@@ -61262,11 +61252,11 @@
       <c r="AK599" s="33"/>
       <c r="AM599" s="33"/>
       <c r="AN599" s="33" t="s">
-        <v>1787</v>
+        <v>1777</v>
       </c>
       <c r="AO599" s="33"/>
       <c r="AP599" s="33" t="s">
-        <v>1787</v>
+        <v>1777</v>
       </c>
       <c r="AQ599" s="33"/>
       <c r="AR599" s="33"/>
@@ -61285,18 +61275,18 @@
       <c r="B600" s="33"/>
       <c r="C600" s="33"/>
       <c r="D600" s="33" t="s">
-        <v>1788</v>
+        <v>1778</v>
       </c>
       <c r="E600" s="54" t="s">
-        <v>2205</v>
+        <v>2195</v>
       </c>
       <c r="F600" s="33" t="s">
-        <v>1711</v>
+        <v>1701</v>
       </c>
       <c r="G600" s="33"/>
       <c r="H600" s="33"/>
       <c r="I600" s="33" t="s">
-        <v>1712</v>
+        <v>1702</v>
       </c>
       <c r="J600" s="33"/>
       <c r="K600" s="33" t="s">
@@ -61329,11 +61319,11 @@
       <c r="AK600" s="33"/>
       <c r="AM600" s="33"/>
       <c r="AN600" s="33" t="s">
-        <v>1710</v>
+        <v>1700</v>
       </c>
       <c r="AO600" s="33"/>
       <c r="AP600" s="33" t="s">
-        <v>1710</v>
+        <v>1700</v>
       </c>
       <c r="AQ600" s="33"/>
       <c r="AR600" s="33"/>
@@ -61355,7 +61345,7 @@
         <v>278</v>
       </c>
       <c r="E601" s="54" t="s">
-        <v>2056</v>
+        <v>2046</v>
       </c>
       <c r="F601" s="33" t="s">
         <v>277</v>
@@ -61396,11 +61386,11 @@
       <c r="AK601" s="33"/>
       <c r="AM601" s="33"/>
       <c r="AN601" s="33" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="AO601" s="33"/>
       <c r="AP601" s="33" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="AQ601" s="33"/>
       <c r="AR601" s="33"/>
@@ -61419,18 +61409,18 @@
       <c r="B602" s="33"/>
       <c r="C602" s="33"/>
       <c r="D602" s="33" t="s">
-        <v>1789</v>
+        <v>1779</v>
       </c>
       <c r="E602" s="54" t="s">
-        <v>2233</v>
+        <v>2223</v>
       </c>
       <c r="F602" s="33" t="s">
-        <v>1790</v>
+        <v>1780</v>
       </c>
       <c r="G602" s="33"/>
       <c r="H602" s="33"/>
       <c r="I602" s="33" t="s">
-        <v>1791</v>
+        <v>1781</v>
       </c>
       <c r="J602" s="33"/>
       <c r="K602" s="33" t="s">
@@ -61463,11 +61453,11 @@
       <c r="AK602" s="33"/>
       <c r="AM602" s="33"/>
       <c r="AN602" s="33" t="s">
-        <v>1792</v>
+        <v>1782</v>
       </c>
       <c r="AO602" s="33"/>
       <c r="AP602" s="33" t="s">
-        <v>1792</v>
+        <v>1782</v>
       </c>
       <c r="AQ602" s="33"/>
       <c r="AR602" s="33"/>
@@ -61486,18 +61476,18 @@
       <c r="B603" s="33"/>
       <c r="C603" s="33"/>
       <c r="D603" s="33" t="s">
-        <v>1717</v>
+        <v>1707</v>
       </c>
       <c r="E603" s="54" t="s">
-        <v>2234</v>
+        <v>2224</v>
       </c>
       <c r="F603" s="33" t="s">
-        <v>1793</v>
+        <v>1783</v>
       </c>
       <c r="G603" s="33"/>
       <c r="H603" s="33"/>
       <c r="I603" s="33" t="s">
-        <v>1719</v>
+        <v>1709</v>
       </c>
       <c r="J603" s="33"/>
       <c r="K603" s="33" t="s">
@@ -61530,11 +61520,11 @@
       <c r="AK603" s="33"/>
       <c r="AM603" s="33"/>
       <c r="AN603" s="33" t="s">
-        <v>1720</v>
+        <v>1710</v>
       </c>
       <c r="AO603" s="33"/>
       <c r="AP603" s="33" t="s">
-        <v>1720</v>
+        <v>1710</v>
       </c>
       <c r="AQ603" s="33"/>
       <c r="AR603" s="33"/>
@@ -61556,7 +61546,7 @@
         <v>5</v>
       </c>
       <c r="E604" s="54" t="s">
-        <v>2210</v>
+        <v>2200</v>
       </c>
       <c r="F604" s="33" t="s">
         <v>571</v>
@@ -61620,13 +61610,13 @@
       <c r="B605" s="33"/>
       <c r="C605" s="33"/>
       <c r="D605" s="33" t="s">
-        <v>1729</v>
+        <v>1719</v>
       </c>
       <c r="E605" s="54" t="s">
-        <v>2214</v>
+        <v>2204</v>
       </c>
       <c r="F605" s="33" t="s">
-        <v>1730</v>
+        <v>1720</v>
       </c>
       <c r="G605" s="33"/>
       <c r="H605" s="33"/>
@@ -61687,18 +61677,18 @@
       <c r="B606" s="33"/>
       <c r="C606" s="33"/>
       <c r="D606" s="33" t="s">
-        <v>1794</v>
+        <v>1784</v>
       </c>
       <c r="E606" s="54" t="s">
-        <v>2235</v>
+        <v>2225</v>
       </c>
       <c r="F606" s="33" t="s">
-        <v>1795</v>
+        <v>1785</v>
       </c>
       <c r="G606" s="33"/>
       <c r="H606" s="33"/>
       <c r="I606" s="33" t="s">
-        <v>1796</v>
+        <v>1786</v>
       </c>
       <c r="J606" s="33"/>
       <c r="K606" s="33" t="s">
@@ -61731,11 +61721,11 @@
       <c r="AK606" s="33"/>
       <c r="AM606" s="33"/>
       <c r="AN606" s="33" t="s">
-        <v>1797</v>
+        <v>1787</v>
       </c>
       <c r="AO606" s="33"/>
       <c r="AP606" s="33" t="s">
-        <v>1797</v>
+        <v>1787</v>
       </c>
       <c r="AQ606" s="33"/>
       <c r="AR606" s="33"/>
@@ -61754,18 +61744,18 @@
       <c r="B607" s="33"/>
       <c r="C607" s="33"/>
       <c r="D607" s="33" t="s">
-        <v>1798</v>
+        <v>1788</v>
       </c>
       <c r="E607" s="54" t="s">
-        <v>2236</v>
+        <v>2226</v>
       </c>
       <c r="F607" s="33" t="s">
-        <v>1799</v>
+        <v>1789</v>
       </c>
       <c r="G607" s="33"/>
       <c r="H607" s="33"/>
       <c r="I607" s="33" t="s">
-        <v>1800</v>
+        <v>1790</v>
       </c>
       <c r="J607" s="33"/>
       <c r="K607" s="33" t="s">
@@ -61798,11 +61788,11 @@
       <c r="AK607" s="33"/>
       <c r="AM607" s="33"/>
       <c r="AN607" s="33" t="s">
-        <v>1801</v>
+        <v>1791</v>
       </c>
       <c r="AO607" s="33"/>
       <c r="AP607" s="33" t="s">
-        <v>1801</v>
+        <v>1791</v>
       </c>
       <c r="AQ607" s="33"/>
       <c r="AR607" s="33"/>
@@ -61821,18 +61811,18 @@
       <c r="B608" s="33"/>
       <c r="C608" s="33"/>
       <c r="D608" s="33" t="s">
-        <v>1772</v>
+        <v>1762</v>
       </c>
       <c r="E608" s="54" t="s">
-        <v>2237</v>
+        <v>2227</v>
       </c>
       <c r="F608" s="33" t="s">
-        <v>1802</v>
+        <v>1792</v>
       </c>
       <c r="G608" s="33"/>
       <c r="H608" s="33"/>
       <c r="I608" s="33" t="s">
-        <v>1803</v>
+        <v>1793</v>
       </c>
       <c r="J608" s="33"/>
       <c r="K608" s="33" t="s">
@@ -61865,11 +61855,11 @@
       <c r="AK608" s="33"/>
       <c r="AM608" s="33"/>
       <c r="AN608" s="33" t="s">
-        <v>1774</v>
+        <v>1764</v>
       </c>
       <c r="AO608" s="33"/>
       <c r="AP608" s="33" t="s">
-        <v>1774</v>
+        <v>1764</v>
       </c>
       <c r="AQ608" s="33"/>
       <c r="AR608" s="33"/>
@@ -61891,7 +61881,7 @@
         <v>238</v>
       </c>
       <c r="E609" s="54" t="s">
-        <v>2013</v>
+        <v>2003</v>
       </c>
       <c r="F609" s="33" t="s">
         <v>214</v>
@@ -61899,7 +61889,7 @@
       <c r="G609" s="33"/>
       <c r="H609" s="33"/>
       <c r="I609" s="33" t="s">
-        <v>1804</v>
+        <v>1794</v>
       </c>
       <c r="J609" s="33"/>
       <c r="K609" s="33" t="s">
@@ -61932,11 +61922,11 @@
       <c r="AK609" s="33"/>
       <c r="AM609" s="33"/>
       <c r="AN609" s="33" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="AO609" s="33"/>
       <c r="AP609" s="33" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="AQ609" s="33"/>
       <c r="AR609" s="33"/>
@@ -61958,7 +61948,7 @@
         <v>91</v>
       </c>
       <c r="E610" s="54" t="s">
-        <v>2014</v>
+        <v>2004</v>
       </c>
       <c r="F610" s="33" t="s">
         <v>215</v>
@@ -61966,7 +61956,7 @@
       <c r="G610" s="33"/>
       <c r="H610" s="33"/>
       <c r="I610" s="33" t="s">
-        <v>1805</v>
+        <v>1795</v>
       </c>
       <c r="J610" s="33"/>
       <c r="K610" s="33" t="s">
@@ -61999,11 +61989,11 @@
       <c r="AK610" s="33"/>
       <c r="AM610" s="33"/>
       <c r="AN610" s="33" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="AO610" s="33"/>
       <c r="AP610" s="33" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="AQ610" s="33"/>
       <c r="AR610" s="33"/>
@@ -62025,7 +62015,7 @@
         <v>92</v>
       </c>
       <c r="E611" s="54" t="s">
-        <v>2015</v>
+        <v>2005</v>
       </c>
       <c r="F611" s="33" t="s">
         <v>216</v>
@@ -62033,7 +62023,7 @@
       <c r="G611" s="33"/>
       <c r="H611" s="33"/>
       <c r="I611" s="33" t="s">
-        <v>1806</v>
+        <v>1796</v>
       </c>
       <c r="J611" s="33"/>
       <c r="K611" s="33" t="s">
@@ -62066,11 +62056,11 @@
       <c r="AK611" s="33"/>
       <c r="AM611" s="33"/>
       <c r="AN611" s="33" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="AO611" s="33"/>
       <c r="AP611" s="33" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="AQ611" s="33"/>
       <c r="AR611" s="33"/>
@@ -62089,18 +62079,18 @@
       <c r="B612" s="33"/>
       <c r="C612" s="33"/>
       <c r="D612" s="33" t="s">
-        <v>1807</v>
+        <v>1797</v>
       </c>
       <c r="E612" s="54" t="s">
-        <v>2238</v>
+        <v>2228</v>
       </c>
       <c r="F612" s="33" t="s">
-        <v>1808</v>
+        <v>1798</v>
       </c>
       <c r="G612" s="33"/>
       <c r="H612" s="33"/>
       <c r="I612" s="33" t="s">
-        <v>1809</v>
+        <v>1799</v>
       </c>
       <c r="J612" s="33"/>
       <c r="K612" s="33" t="s">
@@ -62133,11 +62123,11 @@
       <c r="AK612" s="33"/>
       <c r="AM612" s="33"/>
       <c r="AN612" s="33" t="s">
-        <v>1810</v>
+        <v>1800</v>
       </c>
       <c r="AO612" s="33"/>
       <c r="AP612" s="33" t="s">
-        <v>1810</v>
+        <v>1800</v>
       </c>
       <c r="AQ612" s="33"/>
       <c r="AR612" s="33"/>
@@ -62243,7 +62233,7 @@
         <v>542</v>
       </c>
       <c r="E615" s="28" t="s">
-        <v>2239</v>
+        <v>2229</v>
       </c>
       <c r="F615" s="27" t="s">
         <v>541</v>
@@ -62413,7 +62403,7 @@
         <v>640</v>
       </c>
       <c r="E617" s="37" t="s">
-        <v>2240</v>
+        <v>2230</v>
       </c>
       <c r="F617" s="25" t="s">
         <v>543</v>
@@ -62585,7 +62575,7 @@
         <v>1514</v>
       </c>
       <c r="E619" s="37" t="s">
-        <v>2241</v>
+        <v>2231</v>
       </c>
       <c r="F619" s="25" t="s">
         <v>33</v>
@@ -62678,7 +62668,7 @@
         <v>951</v>
       </c>
       <c r="E620" s="37" t="s">
-        <v>2242</v>
+        <v>2232</v>
       </c>
       <c r="F620" s="25" t="s">
         <v>36</v>
@@ -62773,7 +62763,7 @@
         <v>1513</v>
       </c>
       <c r="E621" s="37" t="s">
-        <v>2243</v>
+        <v>2233</v>
       </c>
       <c r="F621" s="25" t="s">
         <v>38</v>
@@ -62866,7 +62856,7 @@
         <v>641</v>
       </c>
       <c r="E622" s="37" t="s">
-        <v>2244</v>
+        <v>2234</v>
       </c>
       <c r="F622" s="25" t="s">
         <v>84</v>
@@ -62890,7 +62880,7 @@
       <c r="O622" s="25"/>
       <c r="P622" s="25"/>
       <c r="Q622" s="25" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
       <c r="R622" s="25"/>
       <c r="S622" s="25"/>
@@ -62959,7 +62949,7 @@
         <v>642</v>
       </c>
       <c r="E623" s="37" t="s">
-        <v>2244</v>
+        <v>2234</v>
       </c>
       <c r="F623" s="25" t="s">
         <v>84</v>
@@ -62983,7 +62973,7 @@
       <c r="O623" s="25"/>
       <c r="P623" s="25"/>
       <c r="Q623" s="25" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="R623" s="25"/>
       <c r="S623" s="25"/>
@@ -63052,7 +63042,7 @@
         <v>643</v>
       </c>
       <c r="E624" s="37" t="s">
-        <v>2245</v>
+        <v>2235</v>
       </c>
       <c r="F624" s="25" t="s">
         <v>85</v>
@@ -63076,7 +63066,7 @@
       <c r="O624" s="25"/>
       <c r="P624" s="25"/>
       <c r="Q624" s="25" t="s">
-        <v>1661</v>
+        <v>1659</v>
       </c>
       <c r="R624" s="25"/>
       <c r="S624" s="25"/>
@@ -63313,7 +63303,7 @@
         <v>5</v>
       </c>
       <c r="E629" s="28" t="s">
-        <v>2210</v>
+        <v>2200</v>
       </c>
       <c r="F629" s="27" t="s">
         <v>571</v>
@@ -63378,7 +63368,7 @@
         <v>82</v>
       </c>
       <c r="E630" s="37" t="s">
-        <v>2211</v>
+        <v>2201</v>
       </c>
       <c r="F630" s="25" t="s">
         <v>572</v>
@@ -63443,7 +63433,7 @@
         <v>79</v>
       </c>
       <c r="E631" s="37" t="s">
-        <v>2212</v>
+        <v>2202</v>
       </c>
       <c r="F631" s="25" t="s">
         <v>573</v>
@@ -63508,7 +63498,7 @@
         <v>80</v>
       </c>
       <c r="E632" s="37" t="s">
-        <v>2213</v>
+        <v>2203</v>
       </c>
       <c r="F632" s="25" t="s">
         <v>574</v>
@@ -63573,7 +63563,7 @@
         <v>152</v>
       </c>
       <c r="E633" s="37" t="s">
-        <v>1921</v>
+        <v>1911</v>
       </c>
       <c r="F633" s="25" t="s">
         <v>834</v>
@@ -63638,7 +63628,7 @@
         <v>471</v>
       </c>
       <c r="E634" s="37" t="s">
-        <v>2246</v>
+        <v>2236</v>
       </c>
       <c r="F634" s="25" t="s">
         <v>835</v>
@@ -63703,7 +63693,7 @@
         <v>192</v>
       </c>
       <c r="E635" s="37" t="s">
-        <v>2247</v>
+        <v>2237</v>
       </c>
       <c r="F635" s="25" t="s">
         <v>836</v>
@@ -63768,7 +63758,7 @@
         <v>194</v>
       </c>
       <c r="E636" s="37" t="s">
-        <v>2248</v>
+        <v>2238</v>
       </c>
       <c r="F636" s="25" t="s">
         <v>837</v>
@@ -63833,7 +63823,7 @@
         <v>196</v>
       </c>
       <c r="E637" s="37" t="s">
-        <v>2249</v>
+        <v>2239</v>
       </c>
       <c r="F637" s="25" t="s">
         <v>838</v>
@@ -63898,7 +63888,7 @@
         <v>248</v>
       </c>
       <c r="E638" s="37" t="s">
-        <v>2250</v>
+        <v>2240</v>
       </c>
       <c r="F638" s="25" t="s">
         <v>839</v>
@@ -63963,7 +63953,7 @@
         <v>575</v>
       </c>
       <c r="E639" s="37" t="s">
-        <v>2251</v>
+        <v>2241</v>
       </c>
       <c r="F639" s="25" t="s">
         <v>840</v>
@@ -64028,7 +64018,7 @@
         <v>841</v>
       </c>
       <c r="E640" s="37" t="s">
-        <v>1936</v>
+        <v>1926</v>
       </c>
       <c r="F640" s="25" t="s">
         <v>842</v>
@@ -64093,7 +64083,7 @@
         <v>843</v>
       </c>
       <c r="E641" s="37" t="s">
-        <v>2252</v>
+        <v>2242</v>
       </c>
       <c r="F641" s="25" t="s">
         <v>844</v>
@@ -64158,7 +64148,7 @@
         <v>198</v>
       </c>
       <c r="E642" s="37" t="s">
-        <v>1934</v>
+        <v>1924</v>
       </c>
       <c r="F642" s="25" t="s">
         <v>845</v>
@@ -64223,7 +64213,7 @@
         <v>846</v>
       </c>
       <c r="E643" s="37" t="s">
-        <v>2253</v>
+        <v>2243</v>
       </c>
       <c r="F643" s="25" t="s">
         <v>847</v>
@@ -64288,7 +64278,7 @@
         <v>857</v>
       </c>
       <c r="E644" s="37" t="s">
-        <v>2254</v>
+        <v>2244</v>
       </c>
       <c r="F644" s="25" t="s">
         <v>858</v>
@@ -64353,7 +64343,7 @@
         <v>669</v>
       </c>
       <c r="E645" s="37" t="s">
-        <v>2093</v>
+        <v>2083</v>
       </c>
       <c r="F645" s="25" t="s">
         <v>859</v>
@@ -64977,7 +64967,7 @@
       <c r="F5" s="79"/>
       <c r="G5" s="80"/>
       <c r="H5" s="81" t="s">
-        <v>1816</v>
+        <v>1806</v>
       </c>
       <c r="I5" s="82"/>
       <c r="J5" s="82"/>
@@ -64986,7 +64976,7 @@
       <c r="M5" s="82"/>
       <c r="N5" s="83"/>
       <c r="O5" s="81" t="s">
-        <v>1818</v>
+        <v>1808</v>
       </c>
       <c r="P5" s="84"/>
       <c r="Q5" s="84"/>
@@ -65016,7 +65006,7 @@
       <c r="AO5" s="84"/>
       <c r="AP5" s="85"/>
       <c r="AQ5" s="89" t="s">
-        <v>1817</v>
+        <v>1807</v>
       </c>
       <c r="AR5" s="84"/>
       <c r="AS5" s="84"/>
@@ -65044,7 +65034,7 @@
       <c r="F6" s="79"/>
       <c r="G6" s="80"/>
       <c r="H6" s="81" t="s">
-        <v>1844</v>
+        <v>1834</v>
       </c>
       <c r="I6" s="82"/>
       <c r="J6" s="82"/>
@@ -65053,7 +65043,7 @@
       <c r="M6" s="82"/>
       <c r="N6" s="83"/>
       <c r="O6" s="81" t="s">
-        <v>1843</v>
+        <v>1833</v>
       </c>
       <c r="P6" s="119"/>
       <c r="Q6" s="119"/>
@@ -65083,7 +65073,7 @@
       <c r="AO6" s="119"/>
       <c r="AP6" s="120"/>
       <c r="AQ6" s="89" t="s">
-        <v>1817</v>
+        <v>1807</v>
       </c>
       <c r="AR6" s="84"/>
       <c r="AS6" s="84"/>
@@ -65118,7 +65108,7 @@
       <c r="M7" s="121"/>
       <c r="N7" s="122"/>
       <c r="O7" s="123" t="s">
-        <v>2257</v>
+        <v>2247</v>
       </c>
       <c r="P7" s="124"/>
       <c r="Q7" s="124"/>
@@ -65148,7 +65138,7 @@
       <c r="AO7" s="124"/>
       <c r="AP7" s="125"/>
       <c r="AQ7" s="126" t="s">
-        <v>2258</v>
+        <v>2248</v>
       </c>
       <c r="AR7" s="127"/>
       <c r="AS7" s="127"/>

--- a/development/MS/spec/MSBB/Panel/MSBBP1210_SloReg.xlsx
+++ b/development/MS/spec/MSBB/Panel/MSBBP1210_SloReg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\mcframeDEV\development\MS\spec\MSBB\Panel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60DC8AF2-4383-40FC-BF51-C81F69EE0BB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62988139-3C5D-4D3B-9599-9FA19A3AD2AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11411,6 +11411,10 @@
     <xf numFmtId="0" fontId="33" fillId="24" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="25" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -11447,14 +11451,14 @@
     <xf numFmtId="0" fontId="27" fillId="24" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -11465,79 +11469,7 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11546,29 +11478,8 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -11600,9 +11511,98 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="33" fillId="25" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -12292,21 +12292,21 @@
       <c r="F2" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="66" t="s">
+      <c r="G2" s="68" t="s">
         <v>1274</v>
       </c>
-      <c r="H2" s="72"/>
-      <c r="I2" s="75" t="s">
+      <c r="H2" s="74"/>
+      <c r="I2" s="77" t="s">
         <v>348</v>
       </c>
-      <c r="J2" s="76"/>
-      <c r="K2" s="69" t="s">
+      <c r="J2" s="78"/>
+      <c r="K2" s="71" t="s">
         <v>1281</v>
       </c>
-      <c r="L2" s="70"/>
-      <c r="M2" s="70"/>
-      <c r="N2" s="70"/>
-      <c r="O2" s="66"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
+      <c r="N2" s="72"/>
+      <c r="O2" s="68"/>
       <c r="P2" s="41"/>
       <c r="Q2" s="42" t="s">
         <v>64</v>
@@ -12362,21 +12362,21 @@
       <c r="F3" s="25" t="s">
         <v>137</v>
       </c>
-      <c r="G3" s="73" t="s">
+      <c r="G3" s="75" t="s">
         <v>1284</v>
       </c>
-      <c r="H3" s="74"/>
-      <c r="I3" s="75" t="s">
+      <c r="H3" s="76"/>
+      <c r="I3" s="77" t="s">
         <v>350</v>
       </c>
-      <c r="J3" s="76"/>
-      <c r="K3" s="69" t="s">
+      <c r="J3" s="78"/>
+      <c r="K3" s="71" t="s">
         <v>1285</v>
       </c>
-      <c r="L3" s="70"/>
-      <c r="M3" s="70"/>
-      <c r="N3" s="70"/>
-      <c r="O3" s="66"/>
+      <c r="L3" s="72"/>
+      <c r="M3" s="72"/>
+      <c r="N3" s="72"/>
+      <c r="O3" s="68"/>
       <c r="P3" s="41"/>
       <c r="Q3" s="25"/>
       <c r="R3" s="40" t="s">
@@ -12432,21 +12432,21 @@
       <c r="F4" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="73" t="s">
+      <c r="G4" s="75" t="s">
         <v>1286</v>
       </c>
-      <c r="H4" s="74"/>
-      <c r="I4" s="75" t="s">
+      <c r="H4" s="76"/>
+      <c r="I4" s="77" t="s">
         <v>349</v>
       </c>
-      <c r="J4" s="76"/>
-      <c r="K4" s="70" t="s">
+      <c r="J4" s="78"/>
+      <c r="K4" s="72" t="s">
         <v>1275</v>
       </c>
-      <c r="L4" s="70"/>
-      <c r="M4" s="70"/>
-      <c r="N4" s="70"/>
-      <c r="O4" s="66"/>
+      <c r="L4" s="72"/>
+      <c r="M4" s="72"/>
+      <c r="N4" s="72"/>
+      <c r="O4" s="68"/>
       <c r="P4" s="41"/>
       <c r="Q4" s="25" t="s">
         <v>71</v>
@@ -12500,12 +12500,12 @@
       <c r="F5" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="G5" s="73" t="s">
+      <c r="G5" s="75" t="s">
         <v>1288</v>
       </c>
-      <c r="H5" s="74"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="K5" s="46"/>
       <c r="L5" s="46"/>
       <c r="M5" s="46"/>
@@ -12558,17 +12558,17 @@
       <c r="D6" s="3" t="s">
         <v>1289</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="71"/>
-      <c r="K6" s="71"/>
-      <c r="L6" s="71"/>
-      <c r="M6" s="71"/>
-      <c r="N6" s="71"/>
-      <c r="O6" s="71"/>
+      <c r="E6" s="73"/>
+      <c r="F6" s="73"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="73"/>
+      <c r="K6" s="73"/>
+      <c r="L6" s="73"/>
+      <c r="M6" s="73"/>
+      <c r="N6" s="73"/>
+      <c r="O6" s="73"/>
       <c r="P6" s="24"/>
       <c r="Q6" s="8"/>
       <c r="R6" s="8"/>
@@ -12762,11 +12762,11 @@
       <c r="P8" s="40" t="s">
         <v>1505</v>
       </c>
-      <c r="Q8" s="66" t="s">
+      <c r="Q8" s="68" t="s">
         <v>1843</v>
       </c>
-      <c r="R8" s="67"/>
-      <c r="S8" s="68"/>
+      <c r="R8" s="69"/>
+      <c r="S8" s="70"/>
       <c r="T8" s="7" t="s">
         <v>1844</v>
       </c>
@@ -38036,7 +38036,7 @@
       <c r="AX310" s="25"/>
       <c r="AZ310" s="26"/>
     </row>
-    <row r="311" spans="1:52" s="129" customFormat="1" ht="15.75" customHeight="1">
+    <row r="311" spans="1:52" s="66" customFormat="1" ht="15.75" customHeight="1">
       <c r="A311" s="65">
         <v>70</v>
       </c>
@@ -38082,10 +38082,10 @@
         <v>25</v>
       </c>
       <c r="AB311" s="25" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="AC311" s="25" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="AD311" s="25" t="s">
         <v>25</v>
@@ -38095,10 +38095,10 @@
         <v>25</v>
       </c>
       <c r="AG311" s="25" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="AH311" s="25" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="AI311" s="25" t="s">
         <v>25</v>
@@ -38121,9 +38121,9 @@
       <c r="AV311" s="61"/>
       <c r="AW311" s="61"/>
       <c r="AX311" s="61"/>
-      <c r="AZ311" s="130"/>
-    </row>
-    <row r="312" spans="1:52" s="129" customFormat="1" ht="15.75" customHeight="1">
+      <c r="AZ311" s="67"/>
+    </row>
+    <row r="312" spans="1:52" s="66" customFormat="1" ht="15.75" customHeight="1">
       <c r="A312" s="65">
         <v>70</v>
       </c>
@@ -38169,10 +38169,10 @@
         <v>25</v>
       </c>
       <c r="AB312" s="25" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="AC312" s="25" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="AD312" s="25" t="s">
         <v>25</v>
@@ -38182,10 +38182,10 @@
         <v>25</v>
       </c>
       <c r="AG312" s="25" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="AH312" s="25" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="AI312" s="25" t="s">
         <v>25</v>
@@ -38208,9 +38208,9 @@
       <c r="AV312" s="61"/>
       <c r="AW312" s="61"/>
       <c r="AX312" s="61"/>
-      <c r="AZ312" s="130"/>
-    </row>
-    <row r="313" spans="1:52" s="129" customFormat="1" ht="15.75" customHeight="1">
+      <c r="AZ312" s="67"/>
+    </row>
+    <row r="313" spans="1:52" s="66" customFormat="1" ht="15.75" customHeight="1">
       <c r="A313" s="65">
         <v>70</v>
       </c>
@@ -38256,10 +38256,10 @@
         <v>25</v>
       </c>
       <c r="AB313" s="25" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="AC313" s="25" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="AD313" s="25" t="s">
         <v>25</v>
@@ -38269,10 +38269,10 @@
         <v>25</v>
       </c>
       <c r="AG313" s="25" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="AH313" s="25" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="AI313" s="25" t="s">
         <v>25</v>
@@ -38295,9 +38295,9 @@
       <c r="AV313" s="61"/>
       <c r="AW313" s="61"/>
       <c r="AX313" s="61"/>
-      <c r="AZ313" s="130"/>
-    </row>
-    <row r="314" spans="1:52" s="129" customFormat="1" ht="15.75" customHeight="1">
+      <c r="AZ313" s="67"/>
+    </row>
+    <row r="314" spans="1:52" s="66" customFormat="1" ht="15.75" customHeight="1">
       <c r="A314" s="65">
         <v>70</v>
       </c>
@@ -38382,7 +38382,7 @@
       <c r="AV314" s="61"/>
       <c r="AW314" s="61"/>
       <c r="AX314" s="61"/>
-      <c r="AZ314" s="130"/>
+      <c r="AZ314" s="67"/>
     </row>
     <row r="315" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A315" s="25">
@@ -64722,65 +64722,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:57" ht="38.25" customHeight="1" thickBot="1">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="103" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
-      <c r="H1" s="106"/>
-      <c r="I1" s="106"/>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
-      <c r="V1" s="106"/>
-      <c r="W1" s="106"/>
-      <c r="X1" s="106"/>
-      <c r="Y1" s="106"/>
-      <c r="Z1" s="106"/>
-      <c r="AA1" s="106"/>
-      <c r="AB1" s="106"/>
-      <c r="AC1" s="106"/>
-      <c r="AD1" s="106"/>
-      <c r="AE1" s="106"/>
-      <c r="AF1" s="106"/>
-      <c r="AG1" s="106"/>
-      <c r="AH1" s="106"/>
-      <c r="AI1" s="106"/>
-      <c r="AJ1" s="106"/>
-      <c r="AK1" s="106"/>
-      <c r="AL1" s="106"/>
-      <c r="AM1" s="106"/>
-      <c r="AN1" s="106"/>
-      <c r="AO1" s="106"/>
-      <c r="AP1" s="106"/>
-      <c r="AQ1" s="106"/>
-      <c r="AR1" s="106"/>
-      <c r="AS1" s="106"/>
-      <c r="AT1" s="106"/>
-      <c r="AU1" s="106"/>
-      <c r="AV1" s="106"/>
-      <c r="AW1" s="106"/>
-      <c r="AX1" s="106"/>
-      <c r="AY1" s="106"/>
-      <c r="AZ1" s="106"/>
-      <c r="BA1" s="106"/>
-      <c r="BB1" s="106"/>
-      <c r="BC1" s="106"/>
-      <c r="BD1" s="106"/>
-      <c r="BE1" s="107"/>
+      <c r="B1" s="104"/>
+      <c r="C1" s="104"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
+      <c r="F1" s="104"/>
+      <c r="G1" s="104"/>
+      <c r="H1" s="104"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="104"/>
+      <c r="K1" s="104"/>
+      <c r="L1" s="104"/>
+      <c r="M1" s="104"/>
+      <c r="N1" s="104"/>
+      <c r="O1" s="104"/>
+      <c r="P1" s="104"/>
+      <c r="Q1" s="104"/>
+      <c r="R1" s="104"/>
+      <c r="S1" s="104"/>
+      <c r="T1" s="104"/>
+      <c r="U1" s="104"/>
+      <c r="V1" s="104"/>
+      <c r="W1" s="104"/>
+      <c r="X1" s="104"/>
+      <c r="Y1" s="104"/>
+      <c r="Z1" s="104"/>
+      <c r="AA1" s="104"/>
+      <c r="AB1" s="104"/>
+      <c r="AC1" s="104"/>
+      <c r="AD1" s="104"/>
+      <c r="AE1" s="104"/>
+      <c r="AF1" s="104"/>
+      <c r="AG1" s="104"/>
+      <c r="AH1" s="104"/>
+      <c r="AI1" s="104"/>
+      <c r="AJ1" s="104"/>
+      <c r="AK1" s="104"/>
+      <c r="AL1" s="104"/>
+      <c r="AM1" s="104"/>
+      <c r="AN1" s="104"/>
+      <c r="AO1" s="104"/>
+      <c r="AP1" s="104"/>
+      <c r="AQ1" s="104"/>
+      <c r="AR1" s="104"/>
+      <c r="AS1" s="104"/>
+      <c r="AT1" s="104"/>
+      <c r="AU1" s="104"/>
+      <c r="AV1" s="104"/>
+      <c r="AW1" s="104"/>
+      <c r="AX1" s="104"/>
+      <c r="AY1" s="104"/>
+      <c r="AZ1" s="104"/>
+      <c r="BA1" s="104"/>
+      <c r="BB1" s="104"/>
+      <c r="BC1" s="104"/>
+      <c r="BD1" s="104"/>
+      <c r="BE1" s="105"/>
     </row>
     <row r="2" spans="1:57" ht="12" customHeight="1" thickBot="1">
       <c r="A2" s="14"/>
@@ -64827,1988 +64827,2097 @@
       <c r="AP2" s="14"/>
     </row>
     <row r="3" spans="1:57" ht="15" customHeight="1" thickBot="1">
-      <c r="A3" s="118" t="s">
+      <c r="A3" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="109"/>
-      <c r="C3" s="109"/>
-      <c r="D3" s="109"/>
-      <c r="E3" s="109"/>
-      <c r="F3" s="109"/>
-      <c r="G3" s="110"/>
-      <c r="H3" s="108" t="s">
+      <c r="B3" s="87"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="109"/>
-      <c r="J3" s="109"/>
-      <c r="K3" s="109"/>
-      <c r="L3" s="109"/>
-      <c r="M3" s="109"/>
-      <c r="N3" s="110"/>
-      <c r="O3" s="108" t="s">
+      <c r="I3" s="87"/>
+      <c r="J3" s="87"/>
+      <c r="K3" s="87"/>
+      <c r="L3" s="87"/>
+      <c r="M3" s="87"/>
+      <c r="N3" s="88"/>
+      <c r="O3" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="P3" s="111"/>
-      <c r="Q3" s="111"/>
-      <c r="R3" s="111"/>
-      <c r="S3" s="111"/>
-      <c r="T3" s="111"/>
-      <c r="U3" s="111"/>
-      <c r="V3" s="111"/>
-      <c r="W3" s="111"/>
-      <c r="X3" s="111"/>
-      <c r="Y3" s="111"/>
-      <c r="Z3" s="111"/>
-      <c r="AA3" s="111"/>
-      <c r="AB3" s="111"/>
-      <c r="AC3" s="111"/>
-      <c r="AD3" s="111"/>
-      <c r="AE3" s="111"/>
-      <c r="AF3" s="111"/>
-      <c r="AG3" s="111"/>
-      <c r="AH3" s="111"/>
-      <c r="AI3" s="111"/>
-      <c r="AJ3" s="111"/>
-      <c r="AK3" s="111"/>
-      <c r="AL3" s="111"/>
-      <c r="AM3" s="111"/>
-      <c r="AN3" s="111"/>
-      <c r="AO3" s="111"/>
-      <c r="AP3" s="112"/>
-      <c r="AQ3" s="108" t="s">
+      <c r="P3" s="107"/>
+      <c r="Q3" s="107"/>
+      <c r="R3" s="107"/>
+      <c r="S3" s="107"/>
+      <c r="T3" s="107"/>
+      <c r="U3" s="107"/>
+      <c r="V3" s="107"/>
+      <c r="W3" s="107"/>
+      <c r="X3" s="107"/>
+      <c r="Y3" s="107"/>
+      <c r="Z3" s="107"/>
+      <c r="AA3" s="107"/>
+      <c r="AB3" s="107"/>
+      <c r="AC3" s="107"/>
+      <c r="AD3" s="107"/>
+      <c r="AE3" s="107"/>
+      <c r="AF3" s="107"/>
+      <c r="AG3" s="107"/>
+      <c r="AH3" s="107"/>
+      <c r="AI3" s="107"/>
+      <c r="AJ3" s="107"/>
+      <c r="AK3" s="107"/>
+      <c r="AL3" s="107"/>
+      <c r="AM3" s="107"/>
+      <c r="AN3" s="107"/>
+      <c r="AO3" s="107"/>
+      <c r="AP3" s="108"/>
+      <c r="AQ3" s="106" t="s">
         <v>10</v>
       </c>
-      <c r="AR3" s="113"/>
-      <c r="AS3" s="113"/>
-      <c r="AT3" s="113"/>
-      <c r="AU3" s="113"/>
-      <c r="AV3" s="113"/>
-      <c r="AW3" s="113"/>
-      <c r="AX3" s="113"/>
-      <c r="AY3" s="113"/>
-      <c r="AZ3" s="113"/>
-      <c r="BA3" s="113"/>
-      <c r="BB3" s="113"/>
-      <c r="BC3" s="113"/>
-      <c r="BD3" s="113"/>
-      <c r="BE3" s="114"/>
+      <c r="AR3" s="109"/>
+      <c r="AS3" s="109"/>
+      <c r="AT3" s="109"/>
+      <c r="AU3" s="109"/>
+      <c r="AV3" s="109"/>
+      <c r="AW3" s="109"/>
+      <c r="AX3" s="109"/>
+      <c r="AY3" s="109"/>
+      <c r="AZ3" s="109"/>
+      <c r="BA3" s="109"/>
+      <c r="BB3" s="109"/>
+      <c r="BC3" s="109"/>
+      <c r="BD3" s="109"/>
+      <c r="BE3" s="110"/>
     </row>
     <row r="4" spans="1:57" ht="15" customHeight="1">
-      <c r="A4" s="115">
+      <c r="A4" s="111">
         <v>1</v>
       </c>
-      <c r="B4" s="116"/>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="98"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="99"/>
-      <c r="K4" s="99"/>
-      <c r="L4" s="99"/>
-      <c r="M4" s="99"/>
-      <c r="N4" s="100"/>
-      <c r="O4" s="98" t="s">
+      <c r="B4" s="112"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="115"/>
+      <c r="L4" s="115"/>
+      <c r="M4" s="115"/>
+      <c r="N4" s="116"/>
+      <c r="O4" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="P4" s="101"/>
-      <c r="Q4" s="101"/>
-      <c r="R4" s="101"/>
-      <c r="S4" s="101"/>
-      <c r="T4" s="101"/>
-      <c r="U4" s="101"/>
-      <c r="V4" s="101"/>
-      <c r="W4" s="101"/>
-      <c r="X4" s="101"/>
-      <c r="Y4" s="101"/>
-      <c r="Z4" s="101"/>
-      <c r="AA4" s="101"/>
-      <c r="AB4" s="101"/>
-      <c r="AC4" s="101"/>
-      <c r="AD4" s="101"/>
-      <c r="AE4" s="101"/>
-      <c r="AF4" s="101"/>
-      <c r="AG4" s="101"/>
-      <c r="AH4" s="101"/>
-      <c r="AI4" s="101"/>
-      <c r="AJ4" s="101"/>
-      <c r="AK4" s="101"/>
-      <c r="AL4" s="101"/>
-      <c r="AM4" s="101"/>
-      <c r="AN4" s="101"/>
-      <c r="AO4" s="101"/>
-      <c r="AP4" s="102"/>
-      <c r="AQ4" s="103"/>
-      <c r="AR4" s="101"/>
-      <c r="AS4" s="101"/>
-      <c r="AT4" s="101"/>
-      <c r="AU4" s="101"/>
-      <c r="AV4" s="101"/>
-      <c r="AW4" s="101"/>
-      <c r="AX4" s="101"/>
-      <c r="AY4" s="101"/>
-      <c r="AZ4" s="101"/>
-      <c r="BA4" s="101"/>
-      <c r="BB4" s="101"/>
-      <c r="BC4" s="101"/>
-      <c r="BD4" s="101"/>
-      <c r="BE4" s="104"/>
+      <c r="P4" s="117"/>
+      <c r="Q4" s="117"/>
+      <c r="R4" s="117"/>
+      <c r="S4" s="117"/>
+      <c r="T4" s="117"/>
+      <c r="U4" s="117"/>
+      <c r="V4" s="117"/>
+      <c r="W4" s="117"/>
+      <c r="X4" s="117"/>
+      <c r="Y4" s="117"/>
+      <c r="Z4" s="117"/>
+      <c r="AA4" s="117"/>
+      <c r="AB4" s="117"/>
+      <c r="AC4" s="117"/>
+      <c r="AD4" s="117"/>
+      <c r="AE4" s="117"/>
+      <c r="AF4" s="117"/>
+      <c r="AG4" s="117"/>
+      <c r="AH4" s="117"/>
+      <c r="AI4" s="117"/>
+      <c r="AJ4" s="117"/>
+      <c r="AK4" s="117"/>
+      <c r="AL4" s="117"/>
+      <c r="AM4" s="117"/>
+      <c r="AN4" s="117"/>
+      <c r="AO4" s="117"/>
+      <c r="AP4" s="118"/>
+      <c r="AQ4" s="119"/>
+      <c r="AR4" s="117"/>
+      <c r="AS4" s="117"/>
+      <c r="AT4" s="117"/>
+      <c r="AU4" s="117"/>
+      <c r="AV4" s="117"/>
+      <c r="AW4" s="117"/>
+      <c r="AX4" s="117"/>
+      <c r="AY4" s="117"/>
+      <c r="AZ4" s="117"/>
+      <c r="BA4" s="117"/>
+      <c r="BB4" s="117"/>
+      <c r="BC4" s="117"/>
+      <c r="BD4" s="117"/>
+      <c r="BE4" s="120"/>
     </row>
     <row r="5" spans="1:57" ht="105.75" customHeight="1">
-      <c r="A5" s="78">
+      <c r="A5" s="100">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B5" s="79"/>
-      <c r="C5" s="79"/>
-      <c r="D5" s="79"/>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="81" t="s">
+      <c r="B5" s="101"/>
+      <c r="C5" s="101"/>
+      <c r="D5" s="101"/>
+      <c r="E5" s="101"/>
+      <c r="F5" s="101"/>
+      <c r="G5" s="102"/>
+      <c r="H5" s="83" t="s">
         <v>1806</v>
       </c>
-      <c r="I5" s="82"/>
-      <c r="J5" s="82"/>
-      <c r="K5" s="82"/>
-      <c r="L5" s="82"/>
-      <c r="M5" s="82"/>
-      <c r="N5" s="83"/>
-      <c r="O5" s="81" t="s">
+      <c r="I5" s="84"/>
+      <c r="J5" s="84"/>
+      <c r="K5" s="84"/>
+      <c r="L5" s="84"/>
+      <c r="M5" s="84"/>
+      <c r="N5" s="85"/>
+      <c r="O5" s="83" t="s">
         <v>1808</v>
       </c>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
-      <c r="W5" s="84"/>
-      <c r="X5" s="84"/>
-      <c r="Y5" s="84"/>
-      <c r="Z5" s="84"/>
-      <c r="AA5" s="84"/>
-      <c r="AB5" s="84"/>
-      <c r="AC5" s="84"/>
-      <c r="AD5" s="84"/>
-      <c r="AE5" s="84"/>
-      <c r="AF5" s="84"/>
-      <c r="AG5" s="84"/>
-      <c r="AH5" s="84"/>
-      <c r="AI5" s="84"/>
-      <c r="AJ5" s="84"/>
-      <c r="AK5" s="84"/>
-      <c r="AL5" s="84"/>
-      <c r="AM5" s="84"/>
-      <c r="AN5" s="84"/>
-      <c r="AO5" s="84"/>
-      <c r="AP5" s="85"/>
-      <c r="AQ5" s="89" t="s">
+      <c r="P5" s="81"/>
+      <c r="Q5" s="81"/>
+      <c r="R5" s="81"/>
+      <c r="S5" s="81"/>
+      <c r="T5" s="81"/>
+      <c r="U5" s="81"/>
+      <c r="V5" s="81"/>
+      <c r="W5" s="81"/>
+      <c r="X5" s="81"/>
+      <c r="Y5" s="81"/>
+      <c r="Z5" s="81"/>
+      <c r="AA5" s="81"/>
+      <c r="AB5" s="81"/>
+      <c r="AC5" s="81"/>
+      <c r="AD5" s="81"/>
+      <c r="AE5" s="81"/>
+      <c r="AF5" s="81"/>
+      <c r="AG5" s="81"/>
+      <c r="AH5" s="81"/>
+      <c r="AI5" s="81"/>
+      <c r="AJ5" s="81"/>
+      <c r="AK5" s="81"/>
+      <c r="AL5" s="81"/>
+      <c r="AM5" s="81"/>
+      <c r="AN5" s="81"/>
+      <c r="AO5" s="81"/>
+      <c r="AP5" s="89"/>
+      <c r="AQ5" s="80" t="s">
         <v>1807</v>
       </c>
-      <c r="AR5" s="84"/>
-      <c r="AS5" s="84"/>
-      <c r="AT5" s="84"/>
-      <c r="AU5" s="84"/>
-      <c r="AV5" s="84"/>
-      <c r="AW5" s="84"/>
-      <c r="AX5" s="84"/>
-      <c r="AY5" s="84"/>
-      <c r="AZ5" s="84"/>
-      <c r="BA5" s="84"/>
-      <c r="BB5" s="84"/>
-      <c r="BC5" s="84"/>
-      <c r="BD5" s="84"/>
-      <c r="BE5" s="90"/>
+      <c r="AR5" s="81"/>
+      <c r="AS5" s="81"/>
+      <c r="AT5" s="81"/>
+      <c r="AU5" s="81"/>
+      <c r="AV5" s="81"/>
+      <c r="AW5" s="81"/>
+      <c r="AX5" s="81"/>
+      <c r="AY5" s="81"/>
+      <c r="AZ5" s="81"/>
+      <c r="BA5" s="81"/>
+      <c r="BB5" s="81"/>
+      <c r="BC5" s="81"/>
+      <c r="BD5" s="81"/>
+      <c r="BE5" s="82"/>
     </row>
     <row r="6" spans="1:57" ht="36.6" customHeight="1">
-      <c r="A6" s="78">
+      <c r="A6" s="100">
         <v>1.2</v>
       </c>
-      <c r="B6" s="79"/>
-      <c r="C6" s="79"/>
-      <c r="D6" s="79"/>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="80"/>
-      <c r="H6" s="81" t="s">
+      <c r="B6" s="101"/>
+      <c r="C6" s="101"/>
+      <c r="D6" s="101"/>
+      <c r="E6" s="101"/>
+      <c r="F6" s="101"/>
+      <c r="G6" s="102"/>
+      <c r="H6" s="83" t="s">
         <v>1834</v>
       </c>
-      <c r="I6" s="82"/>
-      <c r="J6" s="82"/>
-      <c r="K6" s="82"/>
-      <c r="L6" s="82"/>
-      <c r="M6" s="82"/>
-      <c r="N6" s="83"/>
-      <c r="O6" s="81" t="s">
+      <c r="I6" s="84"/>
+      <c r="J6" s="84"/>
+      <c r="K6" s="84"/>
+      <c r="L6" s="84"/>
+      <c r="M6" s="84"/>
+      <c r="N6" s="85"/>
+      <c r="O6" s="83" t="s">
         <v>1833</v>
       </c>
-      <c r="P6" s="119"/>
-      <c r="Q6" s="119"/>
-      <c r="R6" s="119"/>
-      <c r="S6" s="119"/>
-      <c r="T6" s="119"/>
-      <c r="U6" s="119"/>
-      <c r="V6" s="119"/>
-      <c r="W6" s="119"/>
-      <c r="X6" s="119"/>
-      <c r="Y6" s="119"/>
-      <c r="Z6" s="119"/>
-      <c r="AA6" s="119"/>
-      <c r="AB6" s="119"/>
-      <c r="AC6" s="119"/>
-      <c r="AD6" s="119"/>
-      <c r="AE6" s="119"/>
-      <c r="AF6" s="119"/>
-      <c r="AG6" s="119"/>
-      <c r="AH6" s="119"/>
-      <c r="AI6" s="119"/>
-      <c r="AJ6" s="119"/>
-      <c r="AK6" s="119"/>
-      <c r="AL6" s="119"/>
-      <c r="AM6" s="119"/>
-      <c r="AN6" s="119"/>
-      <c r="AO6" s="119"/>
-      <c r="AP6" s="120"/>
-      <c r="AQ6" s="89" t="s">
+      <c r="P6" s="90"/>
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
+      <c r="V6" s="90"/>
+      <c r="W6" s="90"/>
+      <c r="X6" s="90"/>
+      <c r="Y6" s="90"/>
+      <c r="Z6" s="90"/>
+      <c r="AA6" s="90"/>
+      <c r="AB6" s="90"/>
+      <c r="AC6" s="90"/>
+      <c r="AD6" s="90"/>
+      <c r="AE6" s="90"/>
+      <c r="AF6" s="90"/>
+      <c r="AG6" s="90"/>
+      <c r="AH6" s="90"/>
+      <c r="AI6" s="90"/>
+      <c r="AJ6" s="90"/>
+      <c r="AK6" s="90"/>
+      <c r="AL6" s="90"/>
+      <c r="AM6" s="90"/>
+      <c r="AN6" s="90"/>
+      <c r="AO6" s="90"/>
+      <c r="AP6" s="91"/>
+      <c r="AQ6" s="80" t="s">
         <v>1807</v>
       </c>
-      <c r="AR6" s="84"/>
-      <c r="AS6" s="84"/>
-      <c r="AT6" s="84"/>
-      <c r="AU6" s="84"/>
-      <c r="AV6" s="84"/>
-      <c r="AW6" s="84"/>
-      <c r="AX6" s="84"/>
-      <c r="AY6" s="84"/>
-      <c r="AZ6" s="84"/>
-      <c r="BA6" s="84"/>
-      <c r="BB6" s="84"/>
-      <c r="BC6" s="84"/>
-      <c r="BD6" s="84"/>
-      <c r="BE6" s="90"/>
+      <c r="AR6" s="81"/>
+      <c r="AS6" s="81"/>
+      <c r="AT6" s="81"/>
+      <c r="AU6" s="81"/>
+      <c r="AV6" s="81"/>
+      <c r="AW6" s="81"/>
+      <c r="AX6" s="81"/>
+      <c r="AY6" s="81"/>
+      <c r="AZ6" s="81"/>
+      <c r="BA6" s="81"/>
+      <c r="BB6" s="81"/>
+      <c r="BC6" s="81"/>
+      <c r="BD6" s="81"/>
+      <c r="BE6" s="82"/>
     </row>
     <row r="7" spans="1:57" ht="15" customHeight="1">
-      <c r="A7" s="78">
+      <c r="A7" s="100">
         <v>1.3</v>
       </c>
-      <c r="B7" s="79"/>
-      <c r="C7" s="79"/>
-      <c r="D7" s="79"/>
-      <c r="E7" s="79"/>
-      <c r="F7" s="79"/>
-      <c r="G7" s="80"/>
-      <c r="H7" s="81"/>
-      <c r="I7" s="121"/>
-      <c r="J7" s="121"/>
-      <c r="K7" s="121"/>
-      <c r="L7" s="121"/>
-      <c r="M7" s="121"/>
-      <c r="N7" s="122"/>
-      <c r="O7" s="123" t="s">
+      <c r="B7" s="101"/>
+      <c r="C7" s="101"/>
+      <c r="D7" s="101"/>
+      <c r="E7" s="101"/>
+      <c r="F7" s="101"/>
+      <c r="G7" s="102"/>
+      <c r="H7" s="83"/>
+      <c r="I7" s="92"/>
+      <c r="J7" s="92"/>
+      <c r="K7" s="92"/>
+      <c r="L7" s="92"/>
+      <c r="M7" s="92"/>
+      <c r="N7" s="93"/>
+      <c r="O7" s="94" t="s">
         <v>2247</v>
       </c>
-      <c r="P7" s="124"/>
-      <c r="Q7" s="124"/>
-      <c r="R7" s="124"/>
-      <c r="S7" s="124"/>
-      <c r="T7" s="124"/>
-      <c r="U7" s="124"/>
-      <c r="V7" s="124"/>
-      <c r="W7" s="124"/>
-      <c r="X7" s="124"/>
-      <c r="Y7" s="124"/>
-      <c r="Z7" s="124"/>
-      <c r="AA7" s="124"/>
-      <c r="AB7" s="124"/>
-      <c r="AC7" s="124"/>
-      <c r="AD7" s="124"/>
-      <c r="AE7" s="124"/>
-      <c r="AF7" s="124"/>
-      <c r="AG7" s="124"/>
-      <c r="AH7" s="124"/>
-      <c r="AI7" s="124"/>
-      <c r="AJ7" s="124"/>
-      <c r="AK7" s="124"/>
-      <c r="AL7" s="124"/>
-      <c r="AM7" s="124"/>
-      <c r="AN7" s="124"/>
-      <c r="AO7" s="124"/>
-      <c r="AP7" s="125"/>
-      <c r="AQ7" s="126" t="s">
+      <c r="P7" s="95"/>
+      <c r="Q7" s="95"/>
+      <c r="R7" s="95"/>
+      <c r="S7" s="95"/>
+      <c r="T7" s="95"/>
+      <c r="U7" s="95"/>
+      <c r="V7" s="95"/>
+      <c r="W7" s="95"/>
+      <c r="X7" s="95"/>
+      <c r="Y7" s="95"/>
+      <c r="Z7" s="95"/>
+      <c r="AA7" s="95"/>
+      <c r="AB7" s="95"/>
+      <c r="AC7" s="95"/>
+      <c r="AD7" s="95"/>
+      <c r="AE7" s="95"/>
+      <c r="AF7" s="95"/>
+      <c r="AG7" s="95"/>
+      <c r="AH7" s="95"/>
+      <c r="AI7" s="95"/>
+      <c r="AJ7" s="95"/>
+      <c r="AK7" s="95"/>
+      <c r="AL7" s="95"/>
+      <c r="AM7" s="95"/>
+      <c r="AN7" s="95"/>
+      <c r="AO7" s="95"/>
+      <c r="AP7" s="96"/>
+      <c r="AQ7" s="97" t="s">
         <v>2248</v>
       </c>
-      <c r="AR7" s="127"/>
-      <c r="AS7" s="127"/>
-      <c r="AT7" s="127"/>
-      <c r="AU7" s="127"/>
-      <c r="AV7" s="127"/>
-      <c r="AW7" s="127"/>
-      <c r="AX7" s="127"/>
-      <c r="AY7" s="127"/>
-      <c r="AZ7" s="127"/>
-      <c r="BA7" s="127"/>
-      <c r="BB7" s="127"/>
-      <c r="BC7" s="127"/>
-      <c r="BD7" s="127"/>
-      <c r="BE7" s="128"/>
+      <c r="AR7" s="98"/>
+      <c r="AS7" s="98"/>
+      <c r="AT7" s="98"/>
+      <c r="AU7" s="98"/>
+      <c r="AV7" s="98"/>
+      <c r="AW7" s="98"/>
+      <c r="AX7" s="98"/>
+      <c r="AY7" s="98"/>
+      <c r="AZ7" s="98"/>
+      <c r="BA7" s="98"/>
+      <c r="BB7" s="98"/>
+      <c r="BC7" s="98"/>
+      <c r="BD7" s="98"/>
+      <c r="BE7" s="99"/>
     </row>
     <row r="8" spans="1:57" ht="15" customHeight="1">
-      <c r="A8" s="78"/>
-      <c r="B8" s="79"/>
-      <c r="C8" s="79"/>
-      <c r="D8" s="79"/>
-      <c r="E8" s="79"/>
-      <c r="F8" s="79"/>
-      <c r="G8" s="80"/>
-      <c r="H8" s="81"/>
-      <c r="I8" s="82"/>
-      <c r="J8" s="82"/>
-      <c r="K8" s="82"/>
-      <c r="L8" s="82"/>
-      <c r="M8" s="82"/>
-      <c r="N8" s="83"/>
-      <c r="O8" s="81"/>
-      <c r="P8" s="84"/>
-      <c r="Q8" s="84"/>
-      <c r="R8" s="84"/>
-      <c r="S8" s="84"/>
-      <c r="T8" s="84"/>
-      <c r="U8" s="84"/>
-      <c r="V8" s="84"/>
-      <c r="W8" s="84"/>
-      <c r="X8" s="84"/>
-      <c r="Y8" s="84"/>
-      <c r="Z8" s="84"/>
-      <c r="AA8" s="84"/>
-      <c r="AB8" s="84"/>
-      <c r="AC8" s="84"/>
-      <c r="AD8" s="84"/>
-      <c r="AE8" s="84"/>
-      <c r="AF8" s="84"/>
-      <c r="AG8" s="84"/>
-      <c r="AH8" s="84"/>
-      <c r="AI8" s="84"/>
-      <c r="AJ8" s="84"/>
-      <c r="AK8" s="84"/>
-      <c r="AL8" s="84"/>
-      <c r="AM8" s="84"/>
-      <c r="AN8" s="84"/>
-      <c r="AO8" s="84"/>
-      <c r="AP8" s="85"/>
-      <c r="AQ8" s="89"/>
-      <c r="AR8" s="84"/>
-      <c r="AS8" s="84"/>
-      <c r="AT8" s="84"/>
-      <c r="AU8" s="84"/>
-      <c r="AV8" s="84"/>
-      <c r="AW8" s="84"/>
-      <c r="AX8" s="84"/>
-      <c r="AY8" s="84"/>
-      <c r="AZ8" s="84"/>
-      <c r="BA8" s="84"/>
-      <c r="BB8" s="84"/>
-      <c r="BC8" s="84"/>
-      <c r="BD8" s="84"/>
-      <c r="BE8" s="90"/>
+      <c r="A8" s="100"/>
+      <c r="B8" s="101"/>
+      <c r="C8" s="101"/>
+      <c r="D8" s="101"/>
+      <c r="E8" s="101"/>
+      <c r="F8" s="101"/>
+      <c r="G8" s="102"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="84"/>
+      <c r="J8" s="84"/>
+      <c r="K8" s="84"/>
+      <c r="L8" s="84"/>
+      <c r="M8" s="84"/>
+      <c r="N8" s="85"/>
+      <c r="O8" s="83"/>
+      <c r="P8" s="81"/>
+      <c r="Q8" s="81"/>
+      <c r="R8" s="81"/>
+      <c r="S8" s="81"/>
+      <c r="T8" s="81"/>
+      <c r="U8" s="81"/>
+      <c r="V8" s="81"/>
+      <c r="W8" s="81"/>
+      <c r="X8" s="81"/>
+      <c r="Y8" s="81"/>
+      <c r="Z8" s="81"/>
+      <c r="AA8" s="81"/>
+      <c r="AB8" s="81"/>
+      <c r="AC8" s="81"/>
+      <c r="AD8" s="81"/>
+      <c r="AE8" s="81"/>
+      <c r="AF8" s="81"/>
+      <c r="AG8" s="81"/>
+      <c r="AH8" s="81"/>
+      <c r="AI8" s="81"/>
+      <c r="AJ8" s="81"/>
+      <c r="AK8" s="81"/>
+      <c r="AL8" s="81"/>
+      <c r="AM8" s="81"/>
+      <c r="AN8" s="81"/>
+      <c r="AO8" s="81"/>
+      <c r="AP8" s="89"/>
+      <c r="AQ8" s="80"/>
+      <c r="AR8" s="81"/>
+      <c r="AS8" s="81"/>
+      <c r="AT8" s="81"/>
+      <c r="AU8" s="81"/>
+      <c r="AV8" s="81"/>
+      <c r="AW8" s="81"/>
+      <c r="AX8" s="81"/>
+      <c r="AY8" s="81"/>
+      <c r="AZ8" s="81"/>
+      <c r="BA8" s="81"/>
+      <c r="BB8" s="81"/>
+      <c r="BC8" s="81"/>
+      <c r="BD8" s="81"/>
+      <c r="BE8" s="82"/>
     </row>
     <row r="9" spans="1:57" ht="15" customHeight="1">
-      <c r="A9" s="78"/>
-      <c r="B9" s="79"/>
-      <c r="C9" s="79"/>
-      <c r="D9" s="79"/>
-      <c r="E9" s="79"/>
-      <c r="F9" s="79"/>
-      <c r="G9" s="80"/>
-      <c r="H9" s="81"/>
-      <c r="I9" s="82"/>
-      <c r="J9" s="82"/>
-      <c r="K9" s="82"/>
-      <c r="L9" s="82"/>
-      <c r="M9" s="82"/>
-      <c r="N9" s="83"/>
-      <c r="O9" s="81"/>
-      <c r="P9" s="84"/>
-      <c r="Q9" s="84"/>
-      <c r="R9" s="84"/>
-      <c r="S9" s="84"/>
-      <c r="T9" s="84"/>
-      <c r="U9" s="84"/>
-      <c r="V9" s="84"/>
-      <c r="W9" s="84"/>
-      <c r="X9" s="84"/>
-      <c r="Y9" s="84"/>
-      <c r="Z9" s="84"/>
-      <c r="AA9" s="84"/>
-      <c r="AB9" s="84"/>
-      <c r="AC9" s="84"/>
-      <c r="AD9" s="84"/>
-      <c r="AE9" s="84"/>
-      <c r="AF9" s="84"/>
-      <c r="AG9" s="84"/>
-      <c r="AH9" s="84"/>
-      <c r="AI9" s="84"/>
-      <c r="AJ9" s="84"/>
-      <c r="AK9" s="84"/>
-      <c r="AL9" s="84"/>
-      <c r="AM9" s="84"/>
-      <c r="AN9" s="84"/>
-      <c r="AO9" s="84"/>
-      <c r="AP9" s="85"/>
-      <c r="AQ9" s="89"/>
-      <c r="AR9" s="84"/>
-      <c r="AS9" s="84"/>
-      <c r="AT9" s="84"/>
-      <c r="AU9" s="84"/>
-      <c r="AV9" s="84"/>
-      <c r="AW9" s="84"/>
-      <c r="AX9" s="84"/>
-      <c r="AY9" s="84"/>
-      <c r="AZ9" s="84"/>
-      <c r="BA9" s="84"/>
-      <c r="BB9" s="84"/>
-      <c r="BC9" s="84"/>
-      <c r="BD9" s="84"/>
-      <c r="BE9" s="90"/>
+      <c r="A9" s="100"/>
+      <c r="B9" s="101"/>
+      <c r="C9" s="101"/>
+      <c r="D9" s="101"/>
+      <c r="E9" s="101"/>
+      <c r="F9" s="101"/>
+      <c r="G9" s="102"/>
+      <c r="H9" s="83"/>
+      <c r="I9" s="84"/>
+      <c r="J9" s="84"/>
+      <c r="K9" s="84"/>
+      <c r="L9" s="84"/>
+      <c r="M9" s="84"/>
+      <c r="N9" s="85"/>
+      <c r="O9" s="83"/>
+      <c r="P9" s="81"/>
+      <c r="Q9" s="81"/>
+      <c r="R9" s="81"/>
+      <c r="S9" s="81"/>
+      <c r="T9" s="81"/>
+      <c r="U9" s="81"/>
+      <c r="V9" s="81"/>
+      <c r="W9" s="81"/>
+      <c r="X9" s="81"/>
+      <c r="Y9" s="81"/>
+      <c r="Z9" s="81"/>
+      <c r="AA9" s="81"/>
+      <c r="AB9" s="81"/>
+      <c r="AC9" s="81"/>
+      <c r="AD9" s="81"/>
+      <c r="AE9" s="81"/>
+      <c r="AF9" s="81"/>
+      <c r="AG9" s="81"/>
+      <c r="AH9" s="81"/>
+      <c r="AI9" s="81"/>
+      <c r="AJ9" s="81"/>
+      <c r="AK9" s="81"/>
+      <c r="AL9" s="81"/>
+      <c r="AM9" s="81"/>
+      <c r="AN9" s="81"/>
+      <c r="AO9" s="81"/>
+      <c r="AP9" s="89"/>
+      <c r="AQ9" s="80"/>
+      <c r="AR9" s="81"/>
+      <c r="AS9" s="81"/>
+      <c r="AT9" s="81"/>
+      <c r="AU9" s="81"/>
+      <c r="AV9" s="81"/>
+      <c r="AW9" s="81"/>
+      <c r="AX9" s="81"/>
+      <c r="AY9" s="81"/>
+      <c r="AZ9" s="81"/>
+      <c r="BA9" s="81"/>
+      <c r="BB9" s="81"/>
+      <c r="BC9" s="81"/>
+      <c r="BD9" s="81"/>
+      <c r="BE9" s="82"/>
     </row>
     <row r="10" spans="1:57" ht="15" customHeight="1">
-      <c r="A10" s="78"/>
-      <c r="B10" s="79"/>
-      <c r="C10" s="79"/>
-      <c r="D10" s="79"/>
-      <c r="E10" s="79"/>
-      <c r="F10" s="79"/>
-      <c r="G10" s="80"/>
-      <c r="H10" s="81"/>
-      <c r="I10" s="82"/>
-      <c r="J10" s="82"/>
-      <c r="K10" s="82"/>
-      <c r="L10" s="82"/>
-      <c r="M10" s="82"/>
-      <c r="N10" s="83"/>
-      <c r="O10" s="81"/>
-      <c r="P10" s="84"/>
-      <c r="Q10" s="84"/>
-      <c r="R10" s="84"/>
-      <c r="S10" s="84"/>
-      <c r="T10" s="84"/>
-      <c r="U10" s="84"/>
-      <c r="V10" s="84"/>
-      <c r="W10" s="84"/>
-      <c r="X10" s="84"/>
-      <c r="Y10" s="84"/>
-      <c r="Z10" s="84"/>
-      <c r="AA10" s="84"/>
-      <c r="AB10" s="84"/>
-      <c r="AC10" s="84"/>
-      <c r="AD10" s="84"/>
-      <c r="AE10" s="84"/>
-      <c r="AF10" s="84"/>
-      <c r="AG10" s="84"/>
-      <c r="AH10" s="84"/>
-      <c r="AI10" s="84"/>
-      <c r="AJ10" s="84"/>
-      <c r="AK10" s="84"/>
-      <c r="AL10" s="84"/>
-      <c r="AM10" s="84"/>
-      <c r="AN10" s="84"/>
-      <c r="AO10" s="84"/>
-      <c r="AP10" s="85"/>
-      <c r="AQ10" s="89"/>
-      <c r="AR10" s="84"/>
-      <c r="AS10" s="84"/>
-      <c r="AT10" s="84"/>
-      <c r="AU10" s="84"/>
-      <c r="AV10" s="84"/>
-      <c r="AW10" s="84"/>
-      <c r="AX10" s="84"/>
-      <c r="AY10" s="84"/>
-      <c r="AZ10" s="84"/>
-      <c r="BA10" s="84"/>
-      <c r="BB10" s="84"/>
-      <c r="BC10" s="84"/>
-      <c r="BD10" s="84"/>
-      <c r="BE10" s="90"/>
+      <c r="A10" s="100"/>
+      <c r="B10" s="101"/>
+      <c r="C10" s="101"/>
+      <c r="D10" s="101"/>
+      <c r="E10" s="101"/>
+      <c r="F10" s="101"/>
+      <c r="G10" s="102"/>
+      <c r="H10" s="83"/>
+      <c r="I10" s="84"/>
+      <c r="J10" s="84"/>
+      <c r="K10" s="84"/>
+      <c r="L10" s="84"/>
+      <c r="M10" s="84"/>
+      <c r="N10" s="85"/>
+      <c r="O10" s="83"/>
+      <c r="P10" s="81"/>
+      <c r="Q10" s="81"/>
+      <c r="R10" s="81"/>
+      <c r="S10" s="81"/>
+      <c r="T10" s="81"/>
+      <c r="U10" s="81"/>
+      <c r="V10" s="81"/>
+      <c r="W10" s="81"/>
+      <c r="X10" s="81"/>
+      <c r="Y10" s="81"/>
+      <c r="Z10" s="81"/>
+      <c r="AA10" s="81"/>
+      <c r="AB10" s="81"/>
+      <c r="AC10" s="81"/>
+      <c r="AD10" s="81"/>
+      <c r="AE10" s="81"/>
+      <c r="AF10" s="81"/>
+      <c r="AG10" s="81"/>
+      <c r="AH10" s="81"/>
+      <c r="AI10" s="81"/>
+      <c r="AJ10" s="81"/>
+      <c r="AK10" s="81"/>
+      <c r="AL10" s="81"/>
+      <c r="AM10" s="81"/>
+      <c r="AN10" s="81"/>
+      <c r="AO10" s="81"/>
+      <c r="AP10" s="89"/>
+      <c r="AQ10" s="80"/>
+      <c r="AR10" s="81"/>
+      <c r="AS10" s="81"/>
+      <c r="AT10" s="81"/>
+      <c r="AU10" s="81"/>
+      <c r="AV10" s="81"/>
+      <c r="AW10" s="81"/>
+      <c r="AX10" s="81"/>
+      <c r="AY10" s="81"/>
+      <c r="AZ10" s="81"/>
+      <c r="BA10" s="81"/>
+      <c r="BB10" s="81"/>
+      <c r="BC10" s="81"/>
+      <c r="BD10" s="81"/>
+      <c r="BE10" s="82"/>
     </row>
     <row r="11" spans="1:57" ht="15" customHeight="1">
-      <c r="A11" s="78"/>
-      <c r="B11" s="79"/>
-      <c r="C11" s="79"/>
-      <c r="D11" s="79"/>
-      <c r="E11" s="79"/>
-      <c r="F11" s="79"/>
-      <c r="G11" s="80"/>
-      <c r="H11" s="81"/>
-      <c r="I11" s="82"/>
-      <c r="J11" s="82"/>
-      <c r="K11" s="82"/>
-      <c r="L11" s="82"/>
-      <c r="M11" s="82"/>
-      <c r="N11" s="83"/>
-      <c r="O11" s="81"/>
-      <c r="P11" s="84"/>
-      <c r="Q11" s="84"/>
-      <c r="R11" s="84"/>
-      <c r="S11" s="84"/>
-      <c r="T11" s="84"/>
-      <c r="U11" s="84"/>
-      <c r="V11" s="84"/>
-      <c r="W11" s="84"/>
-      <c r="X11" s="84"/>
-      <c r="Y11" s="84"/>
-      <c r="Z11" s="84"/>
-      <c r="AA11" s="84"/>
-      <c r="AB11" s="84"/>
-      <c r="AC11" s="84"/>
-      <c r="AD11" s="84"/>
-      <c r="AE11" s="84"/>
-      <c r="AF11" s="84"/>
-      <c r="AG11" s="84"/>
-      <c r="AH11" s="84"/>
-      <c r="AI11" s="84"/>
-      <c r="AJ11" s="84"/>
-      <c r="AK11" s="84"/>
-      <c r="AL11" s="84"/>
-      <c r="AM11" s="84"/>
-      <c r="AN11" s="84"/>
-      <c r="AO11" s="84"/>
-      <c r="AP11" s="85"/>
-      <c r="AQ11" s="89"/>
-      <c r="AR11" s="84"/>
-      <c r="AS11" s="84"/>
-      <c r="AT11" s="84"/>
-      <c r="AU11" s="84"/>
-      <c r="AV11" s="84"/>
-      <c r="AW11" s="84"/>
-      <c r="AX11" s="84"/>
-      <c r="AY11" s="84"/>
-      <c r="AZ11" s="84"/>
-      <c r="BA11" s="84"/>
-      <c r="BB11" s="84"/>
-      <c r="BC11" s="84"/>
-      <c r="BD11" s="84"/>
-      <c r="BE11" s="90"/>
+      <c r="A11" s="100"/>
+      <c r="B11" s="101"/>
+      <c r="C11" s="101"/>
+      <c r="D11" s="101"/>
+      <c r="E11" s="101"/>
+      <c r="F11" s="101"/>
+      <c r="G11" s="102"/>
+      <c r="H11" s="83"/>
+      <c r="I11" s="84"/>
+      <c r="J11" s="84"/>
+      <c r="K11" s="84"/>
+      <c r="L11" s="84"/>
+      <c r="M11" s="84"/>
+      <c r="N11" s="85"/>
+      <c r="O11" s="83"/>
+      <c r="P11" s="81"/>
+      <c r="Q11" s="81"/>
+      <c r="R11" s="81"/>
+      <c r="S11" s="81"/>
+      <c r="T11" s="81"/>
+      <c r="U11" s="81"/>
+      <c r="V11" s="81"/>
+      <c r="W11" s="81"/>
+      <c r="X11" s="81"/>
+      <c r="Y11" s="81"/>
+      <c r="Z11" s="81"/>
+      <c r="AA11" s="81"/>
+      <c r="AB11" s="81"/>
+      <c r="AC11" s="81"/>
+      <c r="AD11" s="81"/>
+      <c r="AE11" s="81"/>
+      <c r="AF11" s="81"/>
+      <c r="AG11" s="81"/>
+      <c r="AH11" s="81"/>
+      <c r="AI11" s="81"/>
+      <c r="AJ11" s="81"/>
+      <c r="AK11" s="81"/>
+      <c r="AL11" s="81"/>
+      <c r="AM11" s="81"/>
+      <c r="AN11" s="81"/>
+      <c r="AO11" s="81"/>
+      <c r="AP11" s="89"/>
+      <c r="AQ11" s="80"/>
+      <c r="AR11" s="81"/>
+      <c r="AS11" s="81"/>
+      <c r="AT11" s="81"/>
+      <c r="AU11" s="81"/>
+      <c r="AV11" s="81"/>
+      <c r="AW11" s="81"/>
+      <c r="AX11" s="81"/>
+      <c r="AY11" s="81"/>
+      <c r="AZ11" s="81"/>
+      <c r="BA11" s="81"/>
+      <c r="BB11" s="81"/>
+      <c r="BC11" s="81"/>
+      <c r="BD11" s="81"/>
+      <c r="BE11" s="82"/>
     </row>
     <row r="12" spans="1:57" ht="15" customHeight="1">
-      <c r="A12" s="78"/>
-      <c r="B12" s="79"/>
-      <c r="C12" s="79"/>
-      <c r="D12" s="79"/>
-      <c r="E12" s="79"/>
-      <c r="F12" s="79"/>
-      <c r="G12" s="80"/>
-      <c r="H12" s="81"/>
-      <c r="I12" s="82"/>
-      <c r="J12" s="82"/>
-      <c r="K12" s="82"/>
-      <c r="L12" s="82"/>
-      <c r="M12" s="82"/>
-      <c r="N12" s="83"/>
-      <c r="O12" s="81"/>
-      <c r="P12" s="84"/>
-      <c r="Q12" s="84"/>
-      <c r="R12" s="84"/>
-      <c r="S12" s="84"/>
-      <c r="T12" s="84"/>
-      <c r="U12" s="84"/>
-      <c r="V12" s="84"/>
-      <c r="W12" s="84"/>
-      <c r="X12" s="84"/>
-      <c r="Y12" s="84"/>
-      <c r="Z12" s="84"/>
-      <c r="AA12" s="84"/>
-      <c r="AB12" s="84"/>
-      <c r="AC12" s="84"/>
-      <c r="AD12" s="84"/>
-      <c r="AE12" s="84"/>
-      <c r="AF12" s="84"/>
-      <c r="AG12" s="84"/>
-      <c r="AH12" s="84"/>
-      <c r="AI12" s="84"/>
-      <c r="AJ12" s="84"/>
-      <c r="AK12" s="84"/>
-      <c r="AL12" s="84"/>
-      <c r="AM12" s="84"/>
-      <c r="AN12" s="84"/>
-      <c r="AO12" s="84"/>
-      <c r="AP12" s="85"/>
-      <c r="AQ12" s="89"/>
-      <c r="AR12" s="84"/>
-      <c r="AS12" s="84"/>
-      <c r="AT12" s="84"/>
-      <c r="AU12" s="84"/>
-      <c r="AV12" s="84"/>
-      <c r="AW12" s="84"/>
-      <c r="AX12" s="84"/>
-      <c r="AY12" s="84"/>
-      <c r="AZ12" s="84"/>
-      <c r="BA12" s="84"/>
-      <c r="BB12" s="84"/>
-      <c r="BC12" s="84"/>
-      <c r="BD12" s="84"/>
-      <c r="BE12" s="90"/>
+      <c r="A12" s="100"/>
+      <c r="B12" s="101"/>
+      <c r="C12" s="101"/>
+      <c r="D12" s="101"/>
+      <c r="E12" s="101"/>
+      <c r="F12" s="101"/>
+      <c r="G12" s="102"/>
+      <c r="H12" s="83"/>
+      <c r="I12" s="84"/>
+      <c r="J12" s="84"/>
+      <c r="K12" s="84"/>
+      <c r="L12" s="84"/>
+      <c r="M12" s="84"/>
+      <c r="N12" s="85"/>
+      <c r="O12" s="83"/>
+      <c r="P12" s="81"/>
+      <c r="Q12" s="81"/>
+      <c r="R12" s="81"/>
+      <c r="S12" s="81"/>
+      <c r="T12" s="81"/>
+      <c r="U12" s="81"/>
+      <c r="V12" s="81"/>
+      <c r="W12" s="81"/>
+      <c r="X12" s="81"/>
+      <c r="Y12" s="81"/>
+      <c r="Z12" s="81"/>
+      <c r="AA12" s="81"/>
+      <c r="AB12" s="81"/>
+      <c r="AC12" s="81"/>
+      <c r="AD12" s="81"/>
+      <c r="AE12" s="81"/>
+      <c r="AF12" s="81"/>
+      <c r="AG12" s="81"/>
+      <c r="AH12" s="81"/>
+      <c r="AI12" s="81"/>
+      <c r="AJ12" s="81"/>
+      <c r="AK12" s="81"/>
+      <c r="AL12" s="81"/>
+      <c r="AM12" s="81"/>
+      <c r="AN12" s="81"/>
+      <c r="AO12" s="81"/>
+      <c r="AP12" s="89"/>
+      <c r="AQ12" s="80"/>
+      <c r="AR12" s="81"/>
+      <c r="AS12" s="81"/>
+      <c r="AT12" s="81"/>
+      <c r="AU12" s="81"/>
+      <c r="AV12" s="81"/>
+      <c r="AW12" s="81"/>
+      <c r="AX12" s="81"/>
+      <c r="AY12" s="81"/>
+      <c r="AZ12" s="81"/>
+      <c r="BA12" s="81"/>
+      <c r="BB12" s="81"/>
+      <c r="BC12" s="81"/>
+      <c r="BD12" s="81"/>
+      <c r="BE12" s="82"/>
     </row>
     <row r="13" spans="1:57" ht="15" customHeight="1">
-      <c r="A13" s="78"/>
-      <c r="B13" s="79"/>
-      <c r="C13" s="79"/>
-      <c r="D13" s="79"/>
-      <c r="E13" s="79"/>
-      <c r="F13" s="79"/>
-      <c r="G13" s="80"/>
-      <c r="H13" s="81"/>
-      <c r="I13" s="82"/>
-      <c r="J13" s="82"/>
-      <c r="K13" s="82"/>
-      <c r="L13" s="82"/>
-      <c r="M13" s="82"/>
-      <c r="N13" s="83"/>
-      <c r="O13" s="81"/>
-      <c r="P13" s="84"/>
-      <c r="Q13" s="84"/>
-      <c r="R13" s="84"/>
-      <c r="S13" s="84"/>
-      <c r="T13" s="84"/>
-      <c r="U13" s="84"/>
-      <c r="V13" s="84"/>
-      <c r="W13" s="84"/>
-      <c r="X13" s="84"/>
-      <c r="Y13" s="84"/>
-      <c r="Z13" s="84"/>
-      <c r="AA13" s="84"/>
-      <c r="AB13" s="84"/>
-      <c r="AC13" s="84"/>
-      <c r="AD13" s="84"/>
-      <c r="AE13" s="84"/>
-      <c r="AF13" s="84"/>
-      <c r="AG13" s="84"/>
-      <c r="AH13" s="84"/>
-      <c r="AI13" s="84"/>
-      <c r="AJ13" s="84"/>
-      <c r="AK13" s="84"/>
-      <c r="AL13" s="84"/>
-      <c r="AM13" s="84"/>
-      <c r="AN13" s="84"/>
-      <c r="AO13" s="84"/>
-      <c r="AP13" s="85"/>
-      <c r="AQ13" s="89"/>
-      <c r="AR13" s="84"/>
-      <c r="AS13" s="84"/>
-      <c r="AT13" s="84"/>
-      <c r="AU13" s="84"/>
-      <c r="AV13" s="84"/>
-      <c r="AW13" s="84"/>
-      <c r="AX13" s="84"/>
-      <c r="AY13" s="84"/>
-      <c r="AZ13" s="84"/>
-      <c r="BA13" s="84"/>
-      <c r="BB13" s="84"/>
-      <c r="BC13" s="84"/>
-      <c r="BD13" s="84"/>
-      <c r="BE13" s="90"/>
+      <c r="A13" s="100"/>
+      <c r="B13" s="101"/>
+      <c r="C13" s="101"/>
+      <c r="D13" s="101"/>
+      <c r="E13" s="101"/>
+      <c r="F13" s="101"/>
+      <c r="G13" s="102"/>
+      <c r="H13" s="83"/>
+      <c r="I13" s="84"/>
+      <c r="J13" s="84"/>
+      <c r="K13" s="84"/>
+      <c r="L13" s="84"/>
+      <c r="M13" s="84"/>
+      <c r="N13" s="85"/>
+      <c r="O13" s="83"/>
+      <c r="P13" s="81"/>
+      <c r="Q13" s="81"/>
+      <c r="R13" s="81"/>
+      <c r="S13" s="81"/>
+      <c r="T13" s="81"/>
+      <c r="U13" s="81"/>
+      <c r="V13" s="81"/>
+      <c r="W13" s="81"/>
+      <c r="X13" s="81"/>
+      <c r="Y13" s="81"/>
+      <c r="Z13" s="81"/>
+      <c r="AA13" s="81"/>
+      <c r="AB13" s="81"/>
+      <c r="AC13" s="81"/>
+      <c r="AD13" s="81"/>
+      <c r="AE13" s="81"/>
+      <c r="AF13" s="81"/>
+      <c r="AG13" s="81"/>
+      <c r="AH13" s="81"/>
+      <c r="AI13" s="81"/>
+      <c r="AJ13" s="81"/>
+      <c r="AK13" s="81"/>
+      <c r="AL13" s="81"/>
+      <c r="AM13" s="81"/>
+      <c r="AN13" s="81"/>
+      <c r="AO13" s="81"/>
+      <c r="AP13" s="89"/>
+      <c r="AQ13" s="80"/>
+      <c r="AR13" s="81"/>
+      <c r="AS13" s="81"/>
+      <c r="AT13" s="81"/>
+      <c r="AU13" s="81"/>
+      <c r="AV13" s="81"/>
+      <c r="AW13" s="81"/>
+      <c r="AX13" s="81"/>
+      <c r="AY13" s="81"/>
+      <c r="AZ13" s="81"/>
+      <c r="BA13" s="81"/>
+      <c r="BB13" s="81"/>
+      <c r="BC13" s="81"/>
+      <c r="BD13" s="81"/>
+      <c r="BE13" s="82"/>
     </row>
     <row r="14" spans="1:57" ht="15" customHeight="1">
-      <c r="A14" s="78"/>
-      <c r="B14" s="79"/>
-      <c r="C14" s="79"/>
-      <c r="D14" s="79"/>
-      <c r="E14" s="79"/>
-      <c r="F14" s="79"/>
-      <c r="G14" s="80"/>
-      <c r="H14" s="81"/>
-      <c r="I14" s="82"/>
-      <c r="J14" s="82"/>
-      <c r="K14" s="82"/>
-      <c r="L14" s="82"/>
-      <c r="M14" s="82"/>
-      <c r="N14" s="83"/>
-      <c r="O14" s="81"/>
-      <c r="P14" s="84"/>
-      <c r="Q14" s="84"/>
-      <c r="R14" s="84"/>
-      <c r="S14" s="84"/>
-      <c r="T14" s="84"/>
-      <c r="U14" s="84"/>
-      <c r="V14" s="84"/>
-      <c r="W14" s="84"/>
-      <c r="X14" s="84"/>
-      <c r="Y14" s="84"/>
-      <c r="Z14" s="84"/>
-      <c r="AA14" s="84"/>
-      <c r="AB14" s="84"/>
-      <c r="AC14" s="84"/>
-      <c r="AD14" s="84"/>
-      <c r="AE14" s="84"/>
-      <c r="AF14" s="84"/>
-      <c r="AG14" s="84"/>
-      <c r="AH14" s="84"/>
-      <c r="AI14" s="84"/>
-      <c r="AJ14" s="84"/>
-      <c r="AK14" s="84"/>
-      <c r="AL14" s="84"/>
-      <c r="AM14" s="84"/>
-      <c r="AN14" s="84"/>
-      <c r="AO14" s="84"/>
-      <c r="AP14" s="85"/>
-      <c r="AQ14" s="89"/>
-      <c r="AR14" s="84"/>
-      <c r="AS14" s="84"/>
-      <c r="AT14" s="84"/>
-      <c r="AU14" s="84"/>
-      <c r="AV14" s="84"/>
-      <c r="AW14" s="84"/>
-      <c r="AX14" s="84"/>
-      <c r="AY14" s="84"/>
-      <c r="AZ14" s="84"/>
-      <c r="BA14" s="84"/>
-      <c r="BB14" s="84"/>
-      <c r="BC14" s="84"/>
-      <c r="BD14" s="84"/>
-      <c r="BE14" s="90"/>
+      <c r="A14" s="100"/>
+      <c r="B14" s="101"/>
+      <c r="C14" s="101"/>
+      <c r="D14" s="101"/>
+      <c r="E14" s="101"/>
+      <c r="F14" s="101"/>
+      <c r="G14" s="102"/>
+      <c r="H14" s="83"/>
+      <c r="I14" s="84"/>
+      <c r="J14" s="84"/>
+      <c r="K14" s="84"/>
+      <c r="L14" s="84"/>
+      <c r="M14" s="84"/>
+      <c r="N14" s="85"/>
+      <c r="O14" s="83"/>
+      <c r="P14" s="81"/>
+      <c r="Q14" s="81"/>
+      <c r="R14" s="81"/>
+      <c r="S14" s="81"/>
+      <c r="T14" s="81"/>
+      <c r="U14" s="81"/>
+      <c r="V14" s="81"/>
+      <c r="W14" s="81"/>
+      <c r="X14" s="81"/>
+      <c r="Y14" s="81"/>
+      <c r="Z14" s="81"/>
+      <c r="AA14" s="81"/>
+      <c r="AB14" s="81"/>
+      <c r="AC14" s="81"/>
+      <c r="AD14" s="81"/>
+      <c r="AE14" s="81"/>
+      <c r="AF14" s="81"/>
+      <c r="AG14" s="81"/>
+      <c r="AH14" s="81"/>
+      <c r="AI14" s="81"/>
+      <c r="AJ14" s="81"/>
+      <c r="AK14" s="81"/>
+      <c r="AL14" s="81"/>
+      <c r="AM14" s="81"/>
+      <c r="AN14" s="81"/>
+      <c r="AO14" s="81"/>
+      <c r="AP14" s="89"/>
+      <c r="AQ14" s="80"/>
+      <c r="AR14" s="81"/>
+      <c r="AS14" s="81"/>
+      <c r="AT14" s="81"/>
+      <c r="AU14" s="81"/>
+      <c r="AV14" s="81"/>
+      <c r="AW14" s="81"/>
+      <c r="AX14" s="81"/>
+      <c r="AY14" s="81"/>
+      <c r="AZ14" s="81"/>
+      <c r="BA14" s="81"/>
+      <c r="BB14" s="81"/>
+      <c r="BC14" s="81"/>
+      <c r="BD14" s="81"/>
+      <c r="BE14" s="82"/>
     </row>
     <row r="15" spans="1:57" ht="15" customHeight="1">
-      <c r="A15" s="78"/>
-      <c r="B15" s="79"/>
-      <c r="C15" s="79"/>
-      <c r="D15" s="79"/>
-      <c r="E15" s="79"/>
-      <c r="F15" s="79"/>
-      <c r="G15" s="80"/>
-      <c r="H15" s="81"/>
-      <c r="I15" s="82"/>
-      <c r="J15" s="82"/>
-      <c r="K15" s="82"/>
-      <c r="L15" s="82"/>
-      <c r="M15" s="82"/>
-      <c r="N15" s="83"/>
-      <c r="O15" s="81"/>
-      <c r="P15" s="84"/>
-      <c r="Q15" s="84"/>
-      <c r="R15" s="84"/>
-      <c r="S15" s="84"/>
-      <c r="T15" s="84"/>
-      <c r="U15" s="84"/>
-      <c r="V15" s="84"/>
-      <c r="W15" s="84"/>
-      <c r="X15" s="84"/>
-      <c r="Y15" s="84"/>
-      <c r="Z15" s="84"/>
-      <c r="AA15" s="84"/>
-      <c r="AB15" s="84"/>
-      <c r="AC15" s="84"/>
-      <c r="AD15" s="84"/>
-      <c r="AE15" s="84"/>
-      <c r="AF15" s="84"/>
-      <c r="AG15" s="84"/>
-      <c r="AH15" s="84"/>
-      <c r="AI15" s="84"/>
-      <c r="AJ15" s="84"/>
-      <c r="AK15" s="84"/>
-      <c r="AL15" s="84"/>
-      <c r="AM15" s="84"/>
-      <c r="AN15" s="84"/>
-      <c r="AO15" s="84"/>
-      <c r="AP15" s="85"/>
-      <c r="AQ15" s="89"/>
-      <c r="AR15" s="84"/>
-      <c r="AS15" s="84"/>
-      <c r="AT15" s="84"/>
-      <c r="AU15" s="84"/>
-      <c r="AV15" s="84"/>
-      <c r="AW15" s="84"/>
-      <c r="AX15" s="84"/>
-      <c r="AY15" s="84"/>
-      <c r="AZ15" s="84"/>
-      <c r="BA15" s="84"/>
-      <c r="BB15" s="84"/>
-      <c r="BC15" s="84"/>
-      <c r="BD15" s="84"/>
-      <c r="BE15" s="90"/>
+      <c r="A15" s="100"/>
+      <c r="B15" s="101"/>
+      <c r="C15" s="101"/>
+      <c r="D15" s="101"/>
+      <c r="E15" s="101"/>
+      <c r="F15" s="101"/>
+      <c r="G15" s="102"/>
+      <c r="H15" s="83"/>
+      <c r="I15" s="84"/>
+      <c r="J15" s="84"/>
+      <c r="K15" s="84"/>
+      <c r="L15" s="84"/>
+      <c r="M15" s="84"/>
+      <c r="N15" s="85"/>
+      <c r="O15" s="83"/>
+      <c r="P15" s="81"/>
+      <c r="Q15" s="81"/>
+      <c r="R15" s="81"/>
+      <c r="S15" s="81"/>
+      <c r="T15" s="81"/>
+      <c r="U15" s="81"/>
+      <c r="V15" s="81"/>
+      <c r="W15" s="81"/>
+      <c r="X15" s="81"/>
+      <c r="Y15" s="81"/>
+      <c r="Z15" s="81"/>
+      <c r="AA15" s="81"/>
+      <c r="AB15" s="81"/>
+      <c r="AC15" s="81"/>
+      <c r="AD15" s="81"/>
+      <c r="AE15" s="81"/>
+      <c r="AF15" s="81"/>
+      <c r="AG15" s="81"/>
+      <c r="AH15" s="81"/>
+      <c r="AI15" s="81"/>
+      <c r="AJ15" s="81"/>
+      <c r="AK15" s="81"/>
+      <c r="AL15" s="81"/>
+      <c r="AM15" s="81"/>
+      <c r="AN15" s="81"/>
+      <c r="AO15" s="81"/>
+      <c r="AP15" s="89"/>
+      <c r="AQ15" s="80"/>
+      <c r="AR15" s="81"/>
+      <c r="AS15" s="81"/>
+      <c r="AT15" s="81"/>
+      <c r="AU15" s="81"/>
+      <c r="AV15" s="81"/>
+      <c r="AW15" s="81"/>
+      <c r="AX15" s="81"/>
+      <c r="AY15" s="81"/>
+      <c r="AZ15" s="81"/>
+      <c r="BA15" s="81"/>
+      <c r="BB15" s="81"/>
+      <c r="BC15" s="81"/>
+      <c r="BD15" s="81"/>
+      <c r="BE15" s="82"/>
     </row>
     <row r="16" spans="1:57" ht="15" customHeight="1">
-      <c r="A16" s="78"/>
-      <c r="B16" s="79"/>
-      <c r="C16" s="79"/>
-      <c r="D16" s="79"/>
-      <c r="E16" s="79"/>
-      <c r="F16" s="79"/>
-      <c r="G16" s="80"/>
-      <c r="H16" s="81"/>
-      <c r="I16" s="82"/>
-      <c r="J16" s="82"/>
-      <c r="K16" s="82"/>
-      <c r="L16" s="82"/>
-      <c r="M16" s="82"/>
-      <c r="N16" s="83"/>
-      <c r="O16" s="81"/>
-      <c r="P16" s="84"/>
-      <c r="Q16" s="84"/>
-      <c r="R16" s="84"/>
-      <c r="S16" s="84"/>
-      <c r="T16" s="84"/>
-      <c r="U16" s="84"/>
-      <c r="V16" s="84"/>
-      <c r="W16" s="84"/>
-      <c r="X16" s="84"/>
-      <c r="Y16" s="84"/>
-      <c r="Z16" s="84"/>
-      <c r="AA16" s="84"/>
-      <c r="AB16" s="84"/>
-      <c r="AC16" s="84"/>
-      <c r="AD16" s="84"/>
-      <c r="AE16" s="84"/>
-      <c r="AF16" s="84"/>
-      <c r="AG16" s="84"/>
-      <c r="AH16" s="84"/>
-      <c r="AI16" s="84"/>
-      <c r="AJ16" s="84"/>
-      <c r="AK16" s="84"/>
-      <c r="AL16" s="84"/>
-      <c r="AM16" s="84"/>
-      <c r="AN16" s="84"/>
-      <c r="AO16" s="84"/>
-      <c r="AP16" s="85"/>
-      <c r="AQ16" s="89"/>
-      <c r="AR16" s="84"/>
-      <c r="AS16" s="84"/>
-      <c r="AT16" s="84"/>
-      <c r="AU16" s="84"/>
-      <c r="AV16" s="84"/>
-      <c r="AW16" s="84"/>
-      <c r="AX16" s="84"/>
-      <c r="AY16" s="84"/>
-      <c r="AZ16" s="84"/>
-      <c r="BA16" s="84"/>
-      <c r="BB16" s="84"/>
-      <c r="BC16" s="84"/>
-      <c r="BD16" s="84"/>
-      <c r="BE16" s="90"/>
+      <c r="A16" s="100"/>
+      <c r="B16" s="101"/>
+      <c r="C16" s="101"/>
+      <c r="D16" s="101"/>
+      <c r="E16" s="101"/>
+      <c r="F16" s="101"/>
+      <c r="G16" s="102"/>
+      <c r="H16" s="83"/>
+      <c r="I16" s="84"/>
+      <c r="J16" s="84"/>
+      <c r="K16" s="84"/>
+      <c r="L16" s="84"/>
+      <c r="M16" s="84"/>
+      <c r="N16" s="85"/>
+      <c r="O16" s="83"/>
+      <c r="P16" s="81"/>
+      <c r="Q16" s="81"/>
+      <c r="R16" s="81"/>
+      <c r="S16" s="81"/>
+      <c r="T16" s="81"/>
+      <c r="U16" s="81"/>
+      <c r="V16" s="81"/>
+      <c r="W16" s="81"/>
+      <c r="X16" s="81"/>
+      <c r="Y16" s="81"/>
+      <c r="Z16" s="81"/>
+      <c r="AA16" s="81"/>
+      <c r="AB16" s="81"/>
+      <c r="AC16" s="81"/>
+      <c r="AD16" s="81"/>
+      <c r="AE16" s="81"/>
+      <c r="AF16" s="81"/>
+      <c r="AG16" s="81"/>
+      <c r="AH16" s="81"/>
+      <c r="AI16" s="81"/>
+      <c r="AJ16" s="81"/>
+      <c r="AK16" s="81"/>
+      <c r="AL16" s="81"/>
+      <c r="AM16" s="81"/>
+      <c r="AN16" s="81"/>
+      <c r="AO16" s="81"/>
+      <c r="AP16" s="89"/>
+      <c r="AQ16" s="80"/>
+      <c r="AR16" s="81"/>
+      <c r="AS16" s="81"/>
+      <c r="AT16" s="81"/>
+      <c r="AU16" s="81"/>
+      <c r="AV16" s="81"/>
+      <c r="AW16" s="81"/>
+      <c r="AX16" s="81"/>
+      <c r="AY16" s="81"/>
+      <c r="AZ16" s="81"/>
+      <c r="BA16" s="81"/>
+      <c r="BB16" s="81"/>
+      <c r="BC16" s="81"/>
+      <c r="BD16" s="81"/>
+      <c r="BE16" s="82"/>
     </row>
     <row r="17" spans="1:57" ht="15" customHeight="1">
-      <c r="A17" s="78"/>
-      <c r="B17" s="79"/>
-      <c r="C17" s="79"/>
-      <c r="D17" s="79"/>
-      <c r="E17" s="79"/>
-      <c r="F17" s="79"/>
-      <c r="G17" s="80"/>
-      <c r="H17" s="81"/>
-      <c r="I17" s="82"/>
-      <c r="J17" s="82"/>
-      <c r="K17" s="82"/>
-      <c r="L17" s="82"/>
-      <c r="M17" s="82"/>
-      <c r="N17" s="83"/>
-      <c r="O17" s="81"/>
-      <c r="P17" s="84"/>
-      <c r="Q17" s="84"/>
-      <c r="R17" s="84"/>
-      <c r="S17" s="84"/>
-      <c r="T17" s="84"/>
-      <c r="U17" s="84"/>
-      <c r="V17" s="84"/>
-      <c r="W17" s="84"/>
-      <c r="X17" s="84"/>
-      <c r="Y17" s="84"/>
-      <c r="Z17" s="84"/>
-      <c r="AA17" s="84"/>
-      <c r="AB17" s="84"/>
-      <c r="AC17" s="84"/>
-      <c r="AD17" s="84"/>
-      <c r="AE17" s="84"/>
-      <c r="AF17" s="84"/>
-      <c r="AG17" s="84"/>
-      <c r="AH17" s="84"/>
-      <c r="AI17" s="84"/>
-      <c r="AJ17" s="84"/>
-      <c r="AK17" s="84"/>
-      <c r="AL17" s="84"/>
-      <c r="AM17" s="84"/>
-      <c r="AN17" s="84"/>
-      <c r="AO17" s="84"/>
-      <c r="AP17" s="85"/>
-      <c r="AQ17" s="89"/>
-      <c r="AR17" s="84"/>
-      <c r="AS17" s="84"/>
-      <c r="AT17" s="84"/>
-      <c r="AU17" s="84"/>
-      <c r="AV17" s="84"/>
-      <c r="AW17" s="84"/>
-      <c r="AX17" s="84"/>
-      <c r="AY17" s="84"/>
-      <c r="AZ17" s="84"/>
-      <c r="BA17" s="84"/>
-      <c r="BB17" s="84"/>
-      <c r="BC17" s="84"/>
-      <c r="BD17" s="84"/>
-      <c r="BE17" s="90"/>
+      <c r="A17" s="100"/>
+      <c r="B17" s="101"/>
+      <c r="C17" s="101"/>
+      <c r="D17" s="101"/>
+      <c r="E17" s="101"/>
+      <c r="F17" s="101"/>
+      <c r="G17" s="102"/>
+      <c r="H17" s="83"/>
+      <c r="I17" s="84"/>
+      <c r="J17" s="84"/>
+      <c r="K17" s="84"/>
+      <c r="L17" s="84"/>
+      <c r="M17" s="84"/>
+      <c r="N17" s="85"/>
+      <c r="O17" s="83"/>
+      <c r="P17" s="81"/>
+      <c r="Q17" s="81"/>
+      <c r="R17" s="81"/>
+      <c r="S17" s="81"/>
+      <c r="T17" s="81"/>
+      <c r="U17" s="81"/>
+      <c r="V17" s="81"/>
+      <c r="W17" s="81"/>
+      <c r="X17" s="81"/>
+      <c r="Y17" s="81"/>
+      <c r="Z17" s="81"/>
+      <c r="AA17" s="81"/>
+      <c r="AB17" s="81"/>
+      <c r="AC17" s="81"/>
+      <c r="AD17" s="81"/>
+      <c r="AE17" s="81"/>
+      <c r="AF17" s="81"/>
+      <c r="AG17" s="81"/>
+      <c r="AH17" s="81"/>
+      <c r="AI17" s="81"/>
+      <c r="AJ17" s="81"/>
+      <c r="AK17" s="81"/>
+      <c r="AL17" s="81"/>
+      <c r="AM17" s="81"/>
+      <c r="AN17" s="81"/>
+      <c r="AO17" s="81"/>
+      <c r="AP17" s="89"/>
+      <c r="AQ17" s="80"/>
+      <c r="AR17" s="81"/>
+      <c r="AS17" s="81"/>
+      <c r="AT17" s="81"/>
+      <c r="AU17" s="81"/>
+      <c r="AV17" s="81"/>
+      <c r="AW17" s="81"/>
+      <c r="AX17" s="81"/>
+      <c r="AY17" s="81"/>
+      <c r="AZ17" s="81"/>
+      <c r="BA17" s="81"/>
+      <c r="BB17" s="81"/>
+      <c r="BC17" s="81"/>
+      <c r="BD17" s="81"/>
+      <c r="BE17" s="82"/>
     </row>
     <row r="18" spans="1:57" ht="15" customHeight="1">
-      <c r="A18" s="78"/>
-      <c r="B18" s="79"/>
-      <c r="C18" s="79"/>
-      <c r="D18" s="79"/>
-      <c r="E18" s="79"/>
-      <c r="F18" s="79"/>
-      <c r="G18" s="80"/>
-      <c r="H18" s="81"/>
-      <c r="I18" s="82"/>
-      <c r="J18" s="82"/>
-      <c r="K18" s="82"/>
-      <c r="L18" s="82"/>
-      <c r="M18" s="82"/>
-      <c r="N18" s="83"/>
-      <c r="O18" s="81"/>
-      <c r="P18" s="84"/>
-      <c r="Q18" s="84"/>
-      <c r="R18" s="84"/>
-      <c r="S18" s="84"/>
-      <c r="T18" s="84"/>
-      <c r="U18" s="84"/>
-      <c r="V18" s="84"/>
-      <c r="W18" s="84"/>
-      <c r="X18" s="84"/>
-      <c r="Y18" s="84"/>
-      <c r="Z18" s="84"/>
-      <c r="AA18" s="84"/>
-      <c r="AB18" s="84"/>
-      <c r="AC18" s="84"/>
-      <c r="AD18" s="84"/>
-      <c r="AE18" s="84"/>
-      <c r="AF18" s="84"/>
-      <c r="AG18" s="84"/>
-      <c r="AH18" s="84"/>
-      <c r="AI18" s="84"/>
-      <c r="AJ18" s="84"/>
-      <c r="AK18" s="84"/>
-      <c r="AL18" s="84"/>
-      <c r="AM18" s="84"/>
-      <c r="AN18" s="84"/>
-      <c r="AO18" s="84"/>
-      <c r="AP18" s="85"/>
-      <c r="AQ18" s="89"/>
-      <c r="AR18" s="84"/>
-      <c r="AS18" s="84"/>
-      <c r="AT18" s="84"/>
-      <c r="AU18" s="84"/>
-      <c r="AV18" s="84"/>
-      <c r="AW18" s="84"/>
-      <c r="AX18" s="84"/>
-      <c r="AY18" s="84"/>
-      <c r="AZ18" s="84"/>
-      <c r="BA18" s="84"/>
-      <c r="BB18" s="84"/>
-      <c r="BC18" s="84"/>
-      <c r="BD18" s="84"/>
-      <c r="BE18" s="90"/>
+      <c r="A18" s="100"/>
+      <c r="B18" s="101"/>
+      <c r="C18" s="101"/>
+      <c r="D18" s="101"/>
+      <c r="E18" s="101"/>
+      <c r="F18" s="101"/>
+      <c r="G18" s="102"/>
+      <c r="H18" s="83"/>
+      <c r="I18" s="84"/>
+      <c r="J18" s="84"/>
+      <c r="K18" s="84"/>
+      <c r="L18" s="84"/>
+      <c r="M18" s="84"/>
+      <c r="N18" s="85"/>
+      <c r="O18" s="83"/>
+      <c r="P18" s="81"/>
+      <c r="Q18" s="81"/>
+      <c r="R18" s="81"/>
+      <c r="S18" s="81"/>
+      <c r="T18" s="81"/>
+      <c r="U18" s="81"/>
+      <c r="V18" s="81"/>
+      <c r="W18" s="81"/>
+      <c r="X18" s="81"/>
+      <c r="Y18" s="81"/>
+      <c r="Z18" s="81"/>
+      <c r="AA18" s="81"/>
+      <c r="AB18" s="81"/>
+      <c r="AC18" s="81"/>
+      <c r="AD18" s="81"/>
+      <c r="AE18" s="81"/>
+      <c r="AF18" s="81"/>
+      <c r="AG18" s="81"/>
+      <c r="AH18" s="81"/>
+      <c r="AI18" s="81"/>
+      <c r="AJ18" s="81"/>
+      <c r="AK18" s="81"/>
+      <c r="AL18" s="81"/>
+      <c r="AM18" s="81"/>
+      <c r="AN18" s="81"/>
+      <c r="AO18" s="81"/>
+      <c r="AP18" s="89"/>
+      <c r="AQ18" s="80"/>
+      <c r="AR18" s="81"/>
+      <c r="AS18" s="81"/>
+      <c r="AT18" s="81"/>
+      <c r="AU18" s="81"/>
+      <c r="AV18" s="81"/>
+      <c r="AW18" s="81"/>
+      <c r="AX18" s="81"/>
+      <c r="AY18" s="81"/>
+      <c r="AZ18" s="81"/>
+      <c r="BA18" s="81"/>
+      <c r="BB18" s="81"/>
+      <c r="BC18" s="81"/>
+      <c r="BD18" s="81"/>
+      <c r="BE18" s="82"/>
     </row>
     <row r="19" spans="1:57" ht="15" customHeight="1">
-      <c r="A19" s="78"/>
-      <c r="B19" s="79"/>
-      <c r="C19" s="79"/>
-      <c r="D19" s="79"/>
-      <c r="E19" s="79"/>
-      <c r="F19" s="79"/>
-      <c r="G19" s="80"/>
-      <c r="H19" s="81"/>
-      <c r="I19" s="82"/>
-      <c r="J19" s="82"/>
-      <c r="K19" s="82"/>
-      <c r="L19" s="82"/>
-      <c r="M19" s="82"/>
-      <c r="N19" s="83"/>
-      <c r="O19" s="81"/>
-      <c r="P19" s="84"/>
-      <c r="Q19" s="84"/>
-      <c r="R19" s="84"/>
-      <c r="S19" s="84"/>
-      <c r="T19" s="84"/>
-      <c r="U19" s="84"/>
-      <c r="V19" s="84"/>
-      <c r="W19" s="84"/>
-      <c r="X19" s="84"/>
-      <c r="Y19" s="84"/>
-      <c r="Z19" s="84"/>
-      <c r="AA19" s="84"/>
-      <c r="AB19" s="84"/>
-      <c r="AC19" s="84"/>
-      <c r="AD19" s="84"/>
-      <c r="AE19" s="84"/>
-      <c r="AF19" s="84"/>
-      <c r="AG19" s="84"/>
-      <c r="AH19" s="84"/>
-      <c r="AI19" s="84"/>
-      <c r="AJ19" s="84"/>
-      <c r="AK19" s="84"/>
-      <c r="AL19" s="84"/>
-      <c r="AM19" s="84"/>
-      <c r="AN19" s="84"/>
-      <c r="AO19" s="84"/>
-      <c r="AP19" s="85"/>
-      <c r="AQ19" s="89"/>
-      <c r="AR19" s="84"/>
-      <c r="AS19" s="84"/>
-      <c r="AT19" s="84"/>
-      <c r="AU19" s="84"/>
-      <c r="AV19" s="84"/>
-      <c r="AW19" s="84"/>
-      <c r="AX19" s="84"/>
-      <c r="AY19" s="84"/>
-      <c r="AZ19" s="84"/>
-      <c r="BA19" s="84"/>
-      <c r="BB19" s="84"/>
-      <c r="BC19" s="84"/>
-      <c r="BD19" s="84"/>
-      <c r="BE19" s="90"/>
+      <c r="A19" s="100"/>
+      <c r="B19" s="101"/>
+      <c r="C19" s="101"/>
+      <c r="D19" s="101"/>
+      <c r="E19" s="101"/>
+      <c r="F19" s="101"/>
+      <c r="G19" s="102"/>
+      <c r="H19" s="83"/>
+      <c r="I19" s="84"/>
+      <c r="J19" s="84"/>
+      <c r="K19" s="84"/>
+      <c r="L19" s="84"/>
+      <c r="M19" s="84"/>
+      <c r="N19" s="85"/>
+      <c r="O19" s="83"/>
+      <c r="P19" s="81"/>
+      <c r="Q19" s="81"/>
+      <c r="R19" s="81"/>
+      <c r="S19" s="81"/>
+      <c r="T19" s="81"/>
+      <c r="U19" s="81"/>
+      <c r="V19" s="81"/>
+      <c r="W19" s="81"/>
+      <c r="X19" s="81"/>
+      <c r="Y19" s="81"/>
+      <c r="Z19" s="81"/>
+      <c r="AA19" s="81"/>
+      <c r="AB19" s="81"/>
+      <c r="AC19" s="81"/>
+      <c r="AD19" s="81"/>
+      <c r="AE19" s="81"/>
+      <c r="AF19" s="81"/>
+      <c r="AG19" s="81"/>
+      <c r="AH19" s="81"/>
+      <c r="AI19" s="81"/>
+      <c r="AJ19" s="81"/>
+      <c r="AK19" s="81"/>
+      <c r="AL19" s="81"/>
+      <c r="AM19" s="81"/>
+      <c r="AN19" s="81"/>
+      <c r="AO19" s="81"/>
+      <c r="AP19" s="89"/>
+      <c r="AQ19" s="80"/>
+      <c r="AR19" s="81"/>
+      <c r="AS19" s="81"/>
+      <c r="AT19" s="81"/>
+      <c r="AU19" s="81"/>
+      <c r="AV19" s="81"/>
+      <c r="AW19" s="81"/>
+      <c r="AX19" s="81"/>
+      <c r="AY19" s="81"/>
+      <c r="AZ19" s="81"/>
+      <c r="BA19" s="81"/>
+      <c r="BB19" s="81"/>
+      <c r="BC19" s="81"/>
+      <c r="BD19" s="81"/>
+      <c r="BE19" s="82"/>
     </row>
     <row r="20" spans="1:57" ht="15" customHeight="1">
-      <c r="A20" s="78"/>
-      <c r="B20" s="79"/>
-      <c r="C20" s="79"/>
-      <c r="D20" s="79"/>
-      <c r="E20" s="79"/>
-      <c r="F20" s="79"/>
-      <c r="G20" s="80"/>
-      <c r="H20" s="81"/>
-      <c r="I20" s="82"/>
-      <c r="J20" s="82"/>
-      <c r="K20" s="82"/>
-      <c r="L20" s="82"/>
-      <c r="M20" s="82"/>
-      <c r="N20" s="83"/>
-      <c r="O20" s="81"/>
-      <c r="P20" s="84"/>
-      <c r="Q20" s="84"/>
-      <c r="R20" s="84"/>
-      <c r="S20" s="84"/>
-      <c r="T20" s="84"/>
-      <c r="U20" s="84"/>
-      <c r="V20" s="84"/>
-      <c r="W20" s="84"/>
-      <c r="X20" s="84"/>
-      <c r="Y20" s="84"/>
-      <c r="Z20" s="84"/>
-      <c r="AA20" s="84"/>
-      <c r="AB20" s="84"/>
-      <c r="AC20" s="84"/>
-      <c r="AD20" s="84"/>
-      <c r="AE20" s="84"/>
-      <c r="AF20" s="84"/>
-      <c r="AG20" s="84"/>
-      <c r="AH20" s="84"/>
-      <c r="AI20" s="84"/>
-      <c r="AJ20" s="84"/>
-      <c r="AK20" s="84"/>
-      <c r="AL20" s="84"/>
-      <c r="AM20" s="84"/>
-      <c r="AN20" s="84"/>
-      <c r="AO20" s="84"/>
-      <c r="AP20" s="85"/>
-      <c r="AQ20" s="89"/>
-      <c r="AR20" s="84"/>
-      <c r="AS20" s="84"/>
-      <c r="AT20" s="84"/>
-      <c r="AU20" s="84"/>
-      <c r="AV20" s="84"/>
-      <c r="AW20" s="84"/>
-      <c r="AX20" s="84"/>
-      <c r="AY20" s="84"/>
-      <c r="AZ20" s="84"/>
-      <c r="BA20" s="84"/>
-      <c r="BB20" s="84"/>
-      <c r="BC20" s="84"/>
-      <c r="BD20" s="84"/>
-      <c r="BE20" s="90"/>
+      <c r="A20" s="100"/>
+      <c r="B20" s="101"/>
+      <c r="C20" s="101"/>
+      <c r="D20" s="101"/>
+      <c r="E20" s="101"/>
+      <c r="F20" s="101"/>
+      <c r="G20" s="102"/>
+      <c r="H20" s="83"/>
+      <c r="I20" s="84"/>
+      <c r="J20" s="84"/>
+      <c r="K20" s="84"/>
+      <c r="L20" s="84"/>
+      <c r="M20" s="84"/>
+      <c r="N20" s="85"/>
+      <c r="O20" s="83"/>
+      <c r="P20" s="81"/>
+      <c r="Q20" s="81"/>
+      <c r="R20" s="81"/>
+      <c r="S20" s="81"/>
+      <c r="T20" s="81"/>
+      <c r="U20" s="81"/>
+      <c r="V20" s="81"/>
+      <c r="W20" s="81"/>
+      <c r="X20" s="81"/>
+      <c r="Y20" s="81"/>
+      <c r="Z20" s="81"/>
+      <c r="AA20" s="81"/>
+      <c r="AB20" s="81"/>
+      <c r="AC20" s="81"/>
+      <c r="AD20" s="81"/>
+      <c r="AE20" s="81"/>
+      <c r="AF20" s="81"/>
+      <c r="AG20" s="81"/>
+      <c r="AH20" s="81"/>
+      <c r="AI20" s="81"/>
+      <c r="AJ20" s="81"/>
+      <c r="AK20" s="81"/>
+      <c r="AL20" s="81"/>
+      <c r="AM20" s="81"/>
+      <c r="AN20" s="81"/>
+      <c r="AO20" s="81"/>
+      <c r="AP20" s="89"/>
+      <c r="AQ20" s="80"/>
+      <c r="AR20" s="81"/>
+      <c r="AS20" s="81"/>
+      <c r="AT20" s="81"/>
+      <c r="AU20" s="81"/>
+      <c r="AV20" s="81"/>
+      <c r="AW20" s="81"/>
+      <c r="AX20" s="81"/>
+      <c r="AY20" s="81"/>
+      <c r="AZ20" s="81"/>
+      <c r="BA20" s="81"/>
+      <c r="BB20" s="81"/>
+      <c r="BC20" s="81"/>
+      <c r="BD20" s="81"/>
+      <c r="BE20" s="82"/>
     </row>
     <row r="21" spans="1:57" ht="15" customHeight="1">
-      <c r="A21" s="78"/>
-      <c r="B21" s="79"/>
-      <c r="C21" s="79"/>
-      <c r="D21" s="79"/>
-      <c r="E21" s="79"/>
-      <c r="F21" s="79"/>
-      <c r="G21" s="80"/>
-      <c r="H21" s="81"/>
-      <c r="I21" s="82"/>
-      <c r="J21" s="82"/>
-      <c r="K21" s="82"/>
-      <c r="L21" s="82"/>
-      <c r="M21" s="82"/>
-      <c r="N21" s="83"/>
-      <c r="O21" s="81"/>
-      <c r="P21" s="84"/>
-      <c r="Q21" s="84"/>
-      <c r="R21" s="84"/>
-      <c r="S21" s="84"/>
-      <c r="T21" s="84"/>
-      <c r="U21" s="84"/>
-      <c r="V21" s="84"/>
-      <c r="W21" s="84"/>
-      <c r="X21" s="84"/>
-      <c r="Y21" s="84"/>
-      <c r="Z21" s="84"/>
-      <c r="AA21" s="84"/>
-      <c r="AB21" s="84"/>
-      <c r="AC21" s="84"/>
-      <c r="AD21" s="84"/>
-      <c r="AE21" s="84"/>
-      <c r="AF21" s="84"/>
-      <c r="AG21" s="84"/>
-      <c r="AH21" s="84"/>
-      <c r="AI21" s="84"/>
-      <c r="AJ21" s="84"/>
-      <c r="AK21" s="84"/>
-      <c r="AL21" s="84"/>
-      <c r="AM21" s="84"/>
-      <c r="AN21" s="84"/>
-      <c r="AO21" s="84"/>
-      <c r="AP21" s="85"/>
-      <c r="AQ21" s="89"/>
-      <c r="AR21" s="84"/>
-      <c r="AS21" s="84"/>
-      <c r="AT21" s="84"/>
-      <c r="AU21" s="84"/>
-      <c r="AV21" s="84"/>
-      <c r="AW21" s="84"/>
-      <c r="AX21" s="84"/>
-      <c r="AY21" s="84"/>
-      <c r="AZ21" s="84"/>
-      <c r="BA21" s="84"/>
-      <c r="BB21" s="84"/>
-      <c r="BC21" s="84"/>
-      <c r="BD21" s="84"/>
-      <c r="BE21" s="90"/>
+      <c r="A21" s="100"/>
+      <c r="B21" s="101"/>
+      <c r="C21" s="101"/>
+      <c r="D21" s="101"/>
+      <c r="E21" s="101"/>
+      <c r="F21" s="101"/>
+      <c r="G21" s="102"/>
+      <c r="H21" s="83"/>
+      <c r="I21" s="84"/>
+      <c r="J21" s="84"/>
+      <c r="K21" s="84"/>
+      <c r="L21" s="84"/>
+      <c r="M21" s="84"/>
+      <c r="N21" s="85"/>
+      <c r="O21" s="83"/>
+      <c r="P21" s="81"/>
+      <c r="Q21" s="81"/>
+      <c r="R21" s="81"/>
+      <c r="S21" s="81"/>
+      <c r="T21" s="81"/>
+      <c r="U21" s="81"/>
+      <c r="V21" s="81"/>
+      <c r="W21" s="81"/>
+      <c r="X21" s="81"/>
+      <c r="Y21" s="81"/>
+      <c r="Z21" s="81"/>
+      <c r="AA21" s="81"/>
+      <c r="AB21" s="81"/>
+      <c r="AC21" s="81"/>
+      <c r="AD21" s="81"/>
+      <c r="AE21" s="81"/>
+      <c r="AF21" s="81"/>
+      <c r="AG21" s="81"/>
+      <c r="AH21" s="81"/>
+      <c r="AI21" s="81"/>
+      <c r="AJ21" s="81"/>
+      <c r="AK21" s="81"/>
+      <c r="AL21" s="81"/>
+      <c r="AM21" s="81"/>
+      <c r="AN21" s="81"/>
+      <c r="AO21" s="81"/>
+      <c r="AP21" s="89"/>
+      <c r="AQ21" s="80"/>
+      <c r="AR21" s="81"/>
+      <c r="AS21" s="81"/>
+      <c r="AT21" s="81"/>
+      <c r="AU21" s="81"/>
+      <c r="AV21" s="81"/>
+      <c r="AW21" s="81"/>
+      <c r="AX21" s="81"/>
+      <c r="AY21" s="81"/>
+      <c r="AZ21" s="81"/>
+      <c r="BA21" s="81"/>
+      <c r="BB21" s="81"/>
+      <c r="BC21" s="81"/>
+      <c r="BD21" s="81"/>
+      <c r="BE21" s="82"/>
     </row>
     <row r="22" spans="1:57" ht="15" customHeight="1">
-      <c r="A22" s="78"/>
-      <c r="B22" s="79"/>
-      <c r="C22" s="79"/>
-      <c r="D22" s="79"/>
-      <c r="E22" s="79"/>
-      <c r="F22" s="79"/>
-      <c r="G22" s="80"/>
-      <c r="H22" s="81"/>
-      <c r="I22" s="82"/>
-      <c r="J22" s="82"/>
-      <c r="K22" s="82"/>
-      <c r="L22" s="82"/>
-      <c r="M22" s="82"/>
-      <c r="N22" s="83"/>
-      <c r="O22" s="81"/>
-      <c r="P22" s="84"/>
-      <c r="Q22" s="84"/>
-      <c r="R22" s="84"/>
-      <c r="S22" s="84"/>
-      <c r="T22" s="84"/>
-      <c r="U22" s="84"/>
-      <c r="V22" s="84"/>
-      <c r="W22" s="84"/>
-      <c r="X22" s="84"/>
-      <c r="Y22" s="84"/>
-      <c r="Z22" s="84"/>
-      <c r="AA22" s="84"/>
-      <c r="AB22" s="84"/>
-      <c r="AC22" s="84"/>
-      <c r="AD22" s="84"/>
-      <c r="AE22" s="84"/>
-      <c r="AF22" s="84"/>
-      <c r="AG22" s="84"/>
-      <c r="AH22" s="84"/>
-      <c r="AI22" s="84"/>
-      <c r="AJ22" s="84"/>
-      <c r="AK22" s="84"/>
-      <c r="AL22" s="84"/>
-      <c r="AM22" s="84"/>
-      <c r="AN22" s="84"/>
-      <c r="AO22" s="84"/>
-      <c r="AP22" s="85"/>
-      <c r="AQ22" s="89"/>
-      <c r="AR22" s="84"/>
-      <c r="AS22" s="84"/>
-      <c r="AT22" s="84"/>
-      <c r="AU22" s="84"/>
-      <c r="AV22" s="84"/>
-      <c r="AW22" s="84"/>
-      <c r="AX22" s="84"/>
-      <c r="AY22" s="84"/>
-      <c r="AZ22" s="84"/>
-      <c r="BA22" s="84"/>
-      <c r="BB22" s="84"/>
-      <c r="BC22" s="84"/>
-      <c r="BD22" s="84"/>
-      <c r="BE22" s="90"/>
+      <c r="A22" s="100"/>
+      <c r="B22" s="101"/>
+      <c r="C22" s="101"/>
+      <c r="D22" s="101"/>
+      <c r="E22" s="101"/>
+      <c r="F22" s="101"/>
+      <c r="G22" s="102"/>
+      <c r="H22" s="83"/>
+      <c r="I22" s="84"/>
+      <c r="J22" s="84"/>
+      <c r="K22" s="84"/>
+      <c r="L22" s="84"/>
+      <c r="M22" s="84"/>
+      <c r="N22" s="85"/>
+      <c r="O22" s="83"/>
+      <c r="P22" s="81"/>
+      <c r="Q22" s="81"/>
+      <c r="R22" s="81"/>
+      <c r="S22" s="81"/>
+      <c r="T22" s="81"/>
+      <c r="U22" s="81"/>
+      <c r="V22" s="81"/>
+      <c r="W22" s="81"/>
+      <c r="X22" s="81"/>
+      <c r="Y22" s="81"/>
+      <c r="Z22" s="81"/>
+      <c r="AA22" s="81"/>
+      <c r="AB22" s="81"/>
+      <c r="AC22" s="81"/>
+      <c r="AD22" s="81"/>
+      <c r="AE22" s="81"/>
+      <c r="AF22" s="81"/>
+      <c r="AG22" s="81"/>
+      <c r="AH22" s="81"/>
+      <c r="AI22" s="81"/>
+      <c r="AJ22" s="81"/>
+      <c r="AK22" s="81"/>
+      <c r="AL22" s="81"/>
+      <c r="AM22" s="81"/>
+      <c r="AN22" s="81"/>
+      <c r="AO22" s="81"/>
+      <c r="AP22" s="89"/>
+      <c r="AQ22" s="80"/>
+      <c r="AR22" s="81"/>
+      <c r="AS22" s="81"/>
+      <c r="AT22" s="81"/>
+      <c r="AU22" s="81"/>
+      <c r="AV22" s="81"/>
+      <c r="AW22" s="81"/>
+      <c r="AX22" s="81"/>
+      <c r="AY22" s="81"/>
+      <c r="AZ22" s="81"/>
+      <c r="BA22" s="81"/>
+      <c r="BB22" s="81"/>
+      <c r="BC22" s="81"/>
+      <c r="BD22" s="81"/>
+      <c r="BE22" s="82"/>
     </row>
     <row r="23" spans="1:57" ht="15" customHeight="1">
-      <c r="A23" s="78"/>
-      <c r="B23" s="79"/>
-      <c r="C23" s="79"/>
-      <c r="D23" s="79"/>
-      <c r="E23" s="79"/>
-      <c r="F23" s="79"/>
-      <c r="G23" s="80"/>
-      <c r="H23" s="81"/>
-      <c r="I23" s="82"/>
-      <c r="J23" s="82"/>
-      <c r="K23" s="82"/>
-      <c r="L23" s="82"/>
-      <c r="M23" s="82"/>
-      <c r="N23" s="83"/>
-      <c r="O23" s="81"/>
-      <c r="P23" s="84"/>
-      <c r="Q23" s="84"/>
-      <c r="R23" s="84"/>
-      <c r="S23" s="84"/>
-      <c r="T23" s="84"/>
-      <c r="U23" s="84"/>
-      <c r="V23" s="84"/>
-      <c r="W23" s="84"/>
-      <c r="X23" s="84"/>
-      <c r="Y23" s="84"/>
-      <c r="Z23" s="84"/>
-      <c r="AA23" s="84"/>
-      <c r="AB23" s="84"/>
-      <c r="AC23" s="84"/>
-      <c r="AD23" s="84"/>
-      <c r="AE23" s="84"/>
-      <c r="AF23" s="84"/>
-      <c r="AG23" s="84"/>
-      <c r="AH23" s="84"/>
-      <c r="AI23" s="84"/>
-      <c r="AJ23" s="84"/>
-      <c r="AK23" s="84"/>
-      <c r="AL23" s="84"/>
-      <c r="AM23" s="84"/>
-      <c r="AN23" s="84"/>
-      <c r="AO23" s="84"/>
-      <c r="AP23" s="85"/>
-      <c r="AQ23" s="89"/>
-      <c r="AR23" s="84"/>
-      <c r="AS23" s="84"/>
-      <c r="AT23" s="84"/>
-      <c r="AU23" s="84"/>
-      <c r="AV23" s="84"/>
-      <c r="AW23" s="84"/>
-      <c r="AX23" s="84"/>
-      <c r="AY23" s="84"/>
-      <c r="AZ23" s="84"/>
-      <c r="BA23" s="84"/>
-      <c r="BB23" s="84"/>
-      <c r="BC23" s="84"/>
-      <c r="BD23" s="84"/>
-      <c r="BE23" s="90"/>
+      <c r="A23" s="100"/>
+      <c r="B23" s="101"/>
+      <c r="C23" s="101"/>
+      <c r="D23" s="101"/>
+      <c r="E23" s="101"/>
+      <c r="F23" s="101"/>
+      <c r="G23" s="102"/>
+      <c r="H23" s="83"/>
+      <c r="I23" s="84"/>
+      <c r="J23" s="84"/>
+      <c r="K23" s="84"/>
+      <c r="L23" s="84"/>
+      <c r="M23" s="84"/>
+      <c r="N23" s="85"/>
+      <c r="O23" s="83"/>
+      <c r="P23" s="81"/>
+      <c r="Q23" s="81"/>
+      <c r="R23" s="81"/>
+      <c r="S23" s="81"/>
+      <c r="T23" s="81"/>
+      <c r="U23" s="81"/>
+      <c r="V23" s="81"/>
+      <c r="W23" s="81"/>
+      <c r="X23" s="81"/>
+      <c r="Y23" s="81"/>
+      <c r="Z23" s="81"/>
+      <c r="AA23" s="81"/>
+      <c r="AB23" s="81"/>
+      <c r="AC23" s="81"/>
+      <c r="AD23" s="81"/>
+      <c r="AE23" s="81"/>
+      <c r="AF23" s="81"/>
+      <c r="AG23" s="81"/>
+      <c r="AH23" s="81"/>
+      <c r="AI23" s="81"/>
+      <c r="AJ23" s="81"/>
+      <c r="AK23" s="81"/>
+      <c r="AL23" s="81"/>
+      <c r="AM23" s="81"/>
+      <c r="AN23" s="81"/>
+      <c r="AO23" s="81"/>
+      <c r="AP23" s="89"/>
+      <c r="AQ23" s="80"/>
+      <c r="AR23" s="81"/>
+      <c r="AS23" s="81"/>
+      <c r="AT23" s="81"/>
+      <c r="AU23" s="81"/>
+      <c r="AV23" s="81"/>
+      <c r="AW23" s="81"/>
+      <c r="AX23" s="81"/>
+      <c r="AY23" s="81"/>
+      <c r="AZ23" s="81"/>
+      <c r="BA23" s="81"/>
+      <c r="BB23" s="81"/>
+      <c r="BC23" s="81"/>
+      <c r="BD23" s="81"/>
+      <c r="BE23" s="82"/>
     </row>
     <row r="24" spans="1:57" ht="15" customHeight="1">
-      <c r="A24" s="78"/>
-      <c r="B24" s="79"/>
-      <c r="C24" s="79"/>
-      <c r="D24" s="79"/>
-      <c r="E24" s="79"/>
-      <c r="F24" s="79"/>
-      <c r="G24" s="80"/>
-      <c r="H24" s="81"/>
-      <c r="I24" s="82"/>
-      <c r="J24" s="82"/>
-      <c r="K24" s="82"/>
-      <c r="L24" s="82"/>
-      <c r="M24" s="82"/>
-      <c r="N24" s="83"/>
-      <c r="O24" s="81"/>
-      <c r="P24" s="84"/>
-      <c r="Q24" s="84"/>
-      <c r="R24" s="84"/>
-      <c r="S24" s="84"/>
-      <c r="T24" s="84"/>
-      <c r="U24" s="84"/>
-      <c r="V24" s="84"/>
-      <c r="W24" s="84"/>
-      <c r="X24" s="84"/>
-      <c r="Y24" s="84"/>
-      <c r="Z24" s="84"/>
-      <c r="AA24" s="84"/>
-      <c r="AB24" s="84"/>
-      <c r="AC24" s="84"/>
-      <c r="AD24" s="84"/>
-      <c r="AE24" s="84"/>
-      <c r="AF24" s="84"/>
-      <c r="AG24" s="84"/>
-      <c r="AH24" s="84"/>
-      <c r="AI24" s="84"/>
-      <c r="AJ24" s="84"/>
-      <c r="AK24" s="84"/>
-      <c r="AL24" s="84"/>
-      <c r="AM24" s="84"/>
-      <c r="AN24" s="84"/>
-      <c r="AO24" s="84"/>
-      <c r="AP24" s="85"/>
-      <c r="AQ24" s="89"/>
-      <c r="AR24" s="84"/>
-      <c r="AS24" s="84"/>
-      <c r="AT24" s="84"/>
-      <c r="AU24" s="84"/>
-      <c r="AV24" s="84"/>
-      <c r="AW24" s="84"/>
-      <c r="AX24" s="84"/>
-      <c r="AY24" s="84"/>
-      <c r="AZ24" s="84"/>
-      <c r="BA24" s="84"/>
-      <c r="BB24" s="84"/>
-      <c r="BC24" s="84"/>
-      <c r="BD24" s="84"/>
-      <c r="BE24" s="90"/>
+      <c r="A24" s="100"/>
+      <c r="B24" s="101"/>
+      <c r="C24" s="101"/>
+      <c r="D24" s="101"/>
+      <c r="E24" s="101"/>
+      <c r="F24" s="101"/>
+      <c r="G24" s="102"/>
+      <c r="H24" s="83"/>
+      <c r="I24" s="84"/>
+      <c r="J24" s="84"/>
+      <c r="K24" s="84"/>
+      <c r="L24" s="84"/>
+      <c r="M24" s="84"/>
+      <c r="N24" s="85"/>
+      <c r="O24" s="83"/>
+      <c r="P24" s="81"/>
+      <c r="Q24" s="81"/>
+      <c r="R24" s="81"/>
+      <c r="S24" s="81"/>
+      <c r="T24" s="81"/>
+      <c r="U24" s="81"/>
+      <c r="V24" s="81"/>
+      <c r="W24" s="81"/>
+      <c r="X24" s="81"/>
+      <c r="Y24" s="81"/>
+      <c r="Z24" s="81"/>
+      <c r="AA24" s="81"/>
+      <c r="AB24" s="81"/>
+      <c r="AC24" s="81"/>
+      <c r="AD24" s="81"/>
+      <c r="AE24" s="81"/>
+      <c r="AF24" s="81"/>
+      <c r="AG24" s="81"/>
+      <c r="AH24" s="81"/>
+      <c r="AI24" s="81"/>
+      <c r="AJ24" s="81"/>
+      <c r="AK24" s="81"/>
+      <c r="AL24" s="81"/>
+      <c r="AM24" s="81"/>
+      <c r="AN24" s="81"/>
+      <c r="AO24" s="81"/>
+      <c r="AP24" s="89"/>
+      <c r="AQ24" s="80"/>
+      <c r="AR24" s="81"/>
+      <c r="AS24" s="81"/>
+      <c r="AT24" s="81"/>
+      <c r="AU24" s="81"/>
+      <c r="AV24" s="81"/>
+      <c r="AW24" s="81"/>
+      <c r="AX24" s="81"/>
+      <c r="AY24" s="81"/>
+      <c r="AZ24" s="81"/>
+      <c r="BA24" s="81"/>
+      <c r="BB24" s="81"/>
+      <c r="BC24" s="81"/>
+      <c r="BD24" s="81"/>
+      <c r="BE24" s="82"/>
     </row>
     <row r="25" spans="1:57" ht="15" customHeight="1">
-      <c r="A25" s="78"/>
-      <c r="B25" s="79"/>
-      <c r="C25" s="79"/>
-      <c r="D25" s="79"/>
-      <c r="E25" s="79"/>
-      <c r="F25" s="79"/>
-      <c r="G25" s="80"/>
-      <c r="H25" s="81"/>
-      <c r="I25" s="82"/>
-      <c r="J25" s="82"/>
-      <c r="K25" s="82"/>
-      <c r="L25" s="82"/>
-      <c r="M25" s="82"/>
-      <c r="N25" s="83"/>
-      <c r="O25" s="81"/>
-      <c r="P25" s="84"/>
-      <c r="Q25" s="84"/>
-      <c r="R25" s="84"/>
-      <c r="S25" s="84"/>
-      <c r="T25" s="84"/>
-      <c r="U25" s="84"/>
-      <c r="V25" s="84"/>
-      <c r="W25" s="84"/>
-      <c r="X25" s="84"/>
-      <c r="Y25" s="84"/>
-      <c r="Z25" s="84"/>
-      <c r="AA25" s="84"/>
-      <c r="AB25" s="84"/>
-      <c r="AC25" s="84"/>
-      <c r="AD25" s="84"/>
-      <c r="AE25" s="84"/>
-      <c r="AF25" s="84"/>
-      <c r="AG25" s="84"/>
-      <c r="AH25" s="84"/>
-      <c r="AI25" s="84"/>
-      <c r="AJ25" s="84"/>
-      <c r="AK25" s="84"/>
-      <c r="AL25" s="84"/>
-      <c r="AM25" s="84"/>
-      <c r="AN25" s="84"/>
-      <c r="AO25" s="84"/>
-      <c r="AP25" s="85"/>
-      <c r="AQ25" s="89"/>
-      <c r="AR25" s="84"/>
-      <c r="AS25" s="84"/>
-      <c r="AT25" s="84"/>
-      <c r="AU25" s="84"/>
-      <c r="AV25" s="84"/>
-      <c r="AW25" s="84"/>
-      <c r="AX25" s="84"/>
-      <c r="AY25" s="84"/>
-      <c r="AZ25" s="84"/>
-      <c r="BA25" s="84"/>
-      <c r="BB25" s="84"/>
-      <c r="BC25" s="84"/>
-      <c r="BD25" s="84"/>
-      <c r="BE25" s="90"/>
+      <c r="A25" s="100"/>
+      <c r="B25" s="101"/>
+      <c r="C25" s="101"/>
+      <c r="D25" s="101"/>
+      <c r="E25" s="101"/>
+      <c r="F25" s="101"/>
+      <c r="G25" s="102"/>
+      <c r="H25" s="83"/>
+      <c r="I25" s="84"/>
+      <c r="J25" s="84"/>
+      <c r="K25" s="84"/>
+      <c r="L25" s="84"/>
+      <c r="M25" s="84"/>
+      <c r="N25" s="85"/>
+      <c r="O25" s="83"/>
+      <c r="P25" s="81"/>
+      <c r="Q25" s="81"/>
+      <c r="R25" s="81"/>
+      <c r="S25" s="81"/>
+      <c r="T25" s="81"/>
+      <c r="U25" s="81"/>
+      <c r="V25" s="81"/>
+      <c r="W25" s="81"/>
+      <c r="X25" s="81"/>
+      <c r="Y25" s="81"/>
+      <c r="Z25" s="81"/>
+      <c r="AA25" s="81"/>
+      <c r="AB25" s="81"/>
+      <c r="AC25" s="81"/>
+      <c r="AD25" s="81"/>
+      <c r="AE25" s="81"/>
+      <c r="AF25" s="81"/>
+      <c r="AG25" s="81"/>
+      <c r="AH25" s="81"/>
+      <c r="AI25" s="81"/>
+      <c r="AJ25" s="81"/>
+      <c r="AK25" s="81"/>
+      <c r="AL25" s="81"/>
+      <c r="AM25" s="81"/>
+      <c r="AN25" s="81"/>
+      <c r="AO25" s="81"/>
+      <c r="AP25" s="89"/>
+      <c r="AQ25" s="80"/>
+      <c r="AR25" s="81"/>
+      <c r="AS25" s="81"/>
+      <c r="AT25" s="81"/>
+      <c r="AU25" s="81"/>
+      <c r="AV25" s="81"/>
+      <c r="AW25" s="81"/>
+      <c r="AX25" s="81"/>
+      <c r="AY25" s="81"/>
+      <c r="AZ25" s="81"/>
+      <c r="BA25" s="81"/>
+      <c r="BB25" s="81"/>
+      <c r="BC25" s="81"/>
+      <c r="BD25" s="81"/>
+      <c r="BE25" s="82"/>
     </row>
     <row r="26" spans="1:57" ht="15" customHeight="1">
-      <c r="A26" s="78"/>
-      <c r="B26" s="79"/>
-      <c r="C26" s="79"/>
-      <c r="D26" s="79"/>
-      <c r="E26" s="79"/>
-      <c r="F26" s="79"/>
-      <c r="G26" s="80"/>
-      <c r="H26" s="81"/>
-      <c r="I26" s="82"/>
-      <c r="J26" s="82"/>
-      <c r="K26" s="82"/>
-      <c r="L26" s="82"/>
-      <c r="M26" s="82"/>
-      <c r="N26" s="83"/>
-      <c r="O26" s="81"/>
-      <c r="P26" s="84"/>
-      <c r="Q26" s="84"/>
-      <c r="R26" s="84"/>
-      <c r="S26" s="84"/>
-      <c r="T26" s="84"/>
-      <c r="U26" s="84"/>
-      <c r="V26" s="84"/>
-      <c r="W26" s="84"/>
-      <c r="X26" s="84"/>
-      <c r="Y26" s="84"/>
-      <c r="Z26" s="84"/>
-      <c r="AA26" s="84"/>
-      <c r="AB26" s="84"/>
-      <c r="AC26" s="84"/>
-      <c r="AD26" s="84"/>
-      <c r="AE26" s="84"/>
-      <c r="AF26" s="84"/>
-      <c r="AG26" s="84"/>
-      <c r="AH26" s="84"/>
-      <c r="AI26" s="84"/>
-      <c r="AJ26" s="84"/>
-      <c r="AK26" s="84"/>
-      <c r="AL26" s="84"/>
-      <c r="AM26" s="84"/>
-      <c r="AN26" s="84"/>
-      <c r="AO26" s="84"/>
-      <c r="AP26" s="85"/>
-      <c r="AQ26" s="89"/>
-      <c r="AR26" s="84"/>
-      <c r="AS26" s="84"/>
-      <c r="AT26" s="84"/>
-      <c r="AU26" s="84"/>
-      <c r="AV26" s="84"/>
-      <c r="AW26" s="84"/>
-      <c r="AX26" s="84"/>
-      <c r="AY26" s="84"/>
-      <c r="AZ26" s="84"/>
-      <c r="BA26" s="84"/>
-      <c r="BB26" s="84"/>
-      <c r="BC26" s="84"/>
-      <c r="BD26" s="84"/>
-      <c r="BE26" s="90"/>
+      <c r="A26" s="100"/>
+      <c r="B26" s="101"/>
+      <c r="C26" s="101"/>
+      <c r="D26" s="101"/>
+      <c r="E26" s="101"/>
+      <c r="F26" s="101"/>
+      <c r="G26" s="102"/>
+      <c r="H26" s="83"/>
+      <c r="I26" s="84"/>
+      <c r="J26" s="84"/>
+      <c r="K26" s="84"/>
+      <c r="L26" s="84"/>
+      <c r="M26" s="84"/>
+      <c r="N26" s="85"/>
+      <c r="O26" s="83"/>
+      <c r="P26" s="81"/>
+      <c r="Q26" s="81"/>
+      <c r="R26" s="81"/>
+      <c r="S26" s="81"/>
+      <c r="T26" s="81"/>
+      <c r="U26" s="81"/>
+      <c r="V26" s="81"/>
+      <c r="W26" s="81"/>
+      <c r="X26" s="81"/>
+      <c r="Y26" s="81"/>
+      <c r="Z26" s="81"/>
+      <c r="AA26" s="81"/>
+      <c r="AB26" s="81"/>
+      <c r="AC26" s="81"/>
+      <c r="AD26" s="81"/>
+      <c r="AE26" s="81"/>
+      <c r="AF26" s="81"/>
+      <c r="AG26" s="81"/>
+      <c r="AH26" s="81"/>
+      <c r="AI26" s="81"/>
+      <c r="AJ26" s="81"/>
+      <c r="AK26" s="81"/>
+      <c r="AL26" s="81"/>
+      <c r="AM26" s="81"/>
+      <c r="AN26" s="81"/>
+      <c r="AO26" s="81"/>
+      <c r="AP26" s="89"/>
+      <c r="AQ26" s="80"/>
+      <c r="AR26" s="81"/>
+      <c r="AS26" s="81"/>
+      <c r="AT26" s="81"/>
+      <c r="AU26" s="81"/>
+      <c r="AV26" s="81"/>
+      <c r="AW26" s="81"/>
+      <c r="AX26" s="81"/>
+      <c r="AY26" s="81"/>
+      <c r="AZ26" s="81"/>
+      <c r="BA26" s="81"/>
+      <c r="BB26" s="81"/>
+      <c r="BC26" s="81"/>
+      <c r="BD26" s="81"/>
+      <c r="BE26" s="82"/>
     </row>
     <row r="27" spans="1:57" ht="15" customHeight="1">
-      <c r="A27" s="78"/>
-      <c r="B27" s="79"/>
-      <c r="C27" s="79"/>
-      <c r="D27" s="79"/>
-      <c r="E27" s="79"/>
-      <c r="F27" s="79"/>
-      <c r="G27" s="80"/>
-      <c r="H27" s="81"/>
-      <c r="I27" s="82"/>
-      <c r="J27" s="82"/>
-      <c r="K27" s="82"/>
-      <c r="L27" s="82"/>
-      <c r="M27" s="82"/>
-      <c r="N27" s="83"/>
-      <c r="O27" s="81"/>
-      <c r="P27" s="84"/>
-      <c r="Q27" s="84"/>
-      <c r="R27" s="84"/>
-      <c r="S27" s="84"/>
-      <c r="T27" s="84"/>
-      <c r="U27" s="84"/>
-      <c r="V27" s="84"/>
-      <c r="W27" s="84"/>
-      <c r="X27" s="84"/>
-      <c r="Y27" s="84"/>
-      <c r="Z27" s="84"/>
-      <c r="AA27" s="84"/>
-      <c r="AB27" s="84"/>
-      <c r="AC27" s="84"/>
-      <c r="AD27" s="84"/>
-      <c r="AE27" s="84"/>
-      <c r="AF27" s="84"/>
-      <c r="AG27" s="84"/>
-      <c r="AH27" s="84"/>
-      <c r="AI27" s="84"/>
-      <c r="AJ27" s="84"/>
-      <c r="AK27" s="84"/>
-      <c r="AL27" s="84"/>
-      <c r="AM27" s="84"/>
-      <c r="AN27" s="84"/>
-      <c r="AO27" s="84"/>
-      <c r="AP27" s="85"/>
-      <c r="AQ27" s="89"/>
-      <c r="AR27" s="84"/>
-      <c r="AS27" s="84"/>
-      <c r="AT27" s="84"/>
-      <c r="AU27" s="84"/>
-      <c r="AV27" s="84"/>
-      <c r="AW27" s="84"/>
-      <c r="AX27" s="84"/>
-      <c r="AY27" s="84"/>
-      <c r="AZ27" s="84"/>
-      <c r="BA27" s="84"/>
-      <c r="BB27" s="84"/>
-      <c r="BC27" s="84"/>
-      <c r="BD27" s="84"/>
-      <c r="BE27" s="90"/>
+      <c r="A27" s="100"/>
+      <c r="B27" s="101"/>
+      <c r="C27" s="101"/>
+      <c r="D27" s="101"/>
+      <c r="E27" s="101"/>
+      <c r="F27" s="101"/>
+      <c r="G27" s="102"/>
+      <c r="H27" s="83"/>
+      <c r="I27" s="84"/>
+      <c r="J27" s="84"/>
+      <c r="K27" s="84"/>
+      <c r="L27" s="84"/>
+      <c r="M27" s="84"/>
+      <c r="N27" s="85"/>
+      <c r="O27" s="83"/>
+      <c r="P27" s="81"/>
+      <c r="Q27" s="81"/>
+      <c r="R27" s="81"/>
+      <c r="S27" s="81"/>
+      <c r="T27" s="81"/>
+      <c r="U27" s="81"/>
+      <c r="V27" s="81"/>
+      <c r="W27" s="81"/>
+      <c r="X27" s="81"/>
+      <c r="Y27" s="81"/>
+      <c r="Z27" s="81"/>
+      <c r="AA27" s="81"/>
+      <c r="AB27" s="81"/>
+      <c r="AC27" s="81"/>
+      <c r="AD27" s="81"/>
+      <c r="AE27" s="81"/>
+      <c r="AF27" s="81"/>
+      <c r="AG27" s="81"/>
+      <c r="AH27" s="81"/>
+      <c r="AI27" s="81"/>
+      <c r="AJ27" s="81"/>
+      <c r="AK27" s="81"/>
+      <c r="AL27" s="81"/>
+      <c r="AM27" s="81"/>
+      <c r="AN27" s="81"/>
+      <c r="AO27" s="81"/>
+      <c r="AP27" s="89"/>
+      <c r="AQ27" s="80"/>
+      <c r="AR27" s="81"/>
+      <c r="AS27" s="81"/>
+      <c r="AT27" s="81"/>
+      <c r="AU27" s="81"/>
+      <c r="AV27" s="81"/>
+      <c r="AW27" s="81"/>
+      <c r="AX27" s="81"/>
+      <c r="AY27" s="81"/>
+      <c r="AZ27" s="81"/>
+      <c r="BA27" s="81"/>
+      <c r="BB27" s="81"/>
+      <c r="BC27" s="81"/>
+      <c r="BD27" s="81"/>
+      <c r="BE27" s="82"/>
     </row>
     <row r="28" spans="1:57" ht="15" customHeight="1">
-      <c r="A28" s="78"/>
-      <c r="B28" s="79"/>
-      <c r="C28" s="79"/>
-      <c r="D28" s="79"/>
-      <c r="E28" s="79"/>
-      <c r="F28" s="79"/>
-      <c r="G28" s="80"/>
-      <c r="H28" s="81"/>
-      <c r="I28" s="82"/>
-      <c r="J28" s="82"/>
-      <c r="K28" s="82"/>
-      <c r="L28" s="82"/>
-      <c r="M28" s="82"/>
-      <c r="N28" s="83"/>
-      <c r="O28" s="81"/>
-      <c r="P28" s="84"/>
-      <c r="Q28" s="84"/>
-      <c r="R28" s="84"/>
-      <c r="S28" s="84"/>
-      <c r="T28" s="84"/>
-      <c r="U28" s="84"/>
-      <c r="V28" s="84"/>
-      <c r="W28" s="84"/>
-      <c r="X28" s="84"/>
-      <c r="Y28" s="84"/>
-      <c r="Z28" s="84"/>
-      <c r="AA28" s="84"/>
-      <c r="AB28" s="84"/>
-      <c r="AC28" s="84"/>
-      <c r="AD28" s="84"/>
-      <c r="AE28" s="84"/>
-      <c r="AF28" s="84"/>
-      <c r="AG28" s="84"/>
-      <c r="AH28" s="84"/>
-      <c r="AI28" s="84"/>
-      <c r="AJ28" s="84"/>
-      <c r="AK28" s="84"/>
-      <c r="AL28" s="84"/>
-      <c r="AM28" s="84"/>
-      <c r="AN28" s="84"/>
-      <c r="AO28" s="84"/>
-      <c r="AP28" s="85"/>
-      <c r="AQ28" s="89"/>
-      <c r="AR28" s="84"/>
-      <c r="AS28" s="84"/>
-      <c r="AT28" s="84"/>
-      <c r="AU28" s="84"/>
-      <c r="AV28" s="84"/>
-      <c r="AW28" s="84"/>
-      <c r="AX28" s="84"/>
-      <c r="AY28" s="84"/>
-      <c r="AZ28" s="84"/>
-      <c r="BA28" s="84"/>
-      <c r="BB28" s="84"/>
-      <c r="BC28" s="84"/>
-      <c r="BD28" s="84"/>
-      <c r="BE28" s="90"/>
+      <c r="A28" s="100"/>
+      <c r="B28" s="101"/>
+      <c r="C28" s="101"/>
+      <c r="D28" s="101"/>
+      <c r="E28" s="101"/>
+      <c r="F28" s="101"/>
+      <c r="G28" s="102"/>
+      <c r="H28" s="83"/>
+      <c r="I28" s="84"/>
+      <c r="J28" s="84"/>
+      <c r="K28" s="84"/>
+      <c r="L28" s="84"/>
+      <c r="M28" s="84"/>
+      <c r="N28" s="85"/>
+      <c r="O28" s="83"/>
+      <c r="P28" s="81"/>
+      <c r="Q28" s="81"/>
+      <c r="R28" s="81"/>
+      <c r="S28" s="81"/>
+      <c r="T28" s="81"/>
+      <c r="U28" s="81"/>
+      <c r="V28" s="81"/>
+      <c r="W28" s="81"/>
+      <c r="X28" s="81"/>
+      <c r="Y28" s="81"/>
+      <c r="Z28" s="81"/>
+      <c r="AA28" s="81"/>
+      <c r="AB28" s="81"/>
+      <c r="AC28" s="81"/>
+      <c r="AD28" s="81"/>
+      <c r="AE28" s="81"/>
+      <c r="AF28" s="81"/>
+      <c r="AG28" s="81"/>
+      <c r="AH28" s="81"/>
+      <c r="AI28" s="81"/>
+      <c r="AJ28" s="81"/>
+      <c r="AK28" s="81"/>
+      <c r="AL28" s="81"/>
+      <c r="AM28" s="81"/>
+      <c r="AN28" s="81"/>
+      <c r="AO28" s="81"/>
+      <c r="AP28" s="89"/>
+      <c r="AQ28" s="80"/>
+      <c r="AR28" s="81"/>
+      <c r="AS28" s="81"/>
+      <c r="AT28" s="81"/>
+      <c r="AU28" s="81"/>
+      <c r="AV28" s="81"/>
+      <c r="AW28" s="81"/>
+      <c r="AX28" s="81"/>
+      <c r="AY28" s="81"/>
+      <c r="AZ28" s="81"/>
+      <c r="BA28" s="81"/>
+      <c r="BB28" s="81"/>
+      <c r="BC28" s="81"/>
+      <c r="BD28" s="81"/>
+      <c r="BE28" s="82"/>
     </row>
     <row r="29" spans="1:57" ht="15" customHeight="1">
-      <c r="A29" s="78"/>
-      <c r="B29" s="79"/>
-      <c r="C29" s="79"/>
-      <c r="D29" s="79"/>
-      <c r="E29" s="79"/>
-      <c r="F29" s="79"/>
-      <c r="G29" s="80"/>
-      <c r="H29" s="81"/>
-      <c r="I29" s="82"/>
-      <c r="J29" s="82"/>
-      <c r="K29" s="82"/>
-      <c r="L29" s="82"/>
-      <c r="M29" s="82"/>
-      <c r="N29" s="83"/>
-      <c r="O29" s="81"/>
-      <c r="P29" s="84"/>
-      <c r="Q29" s="84"/>
-      <c r="R29" s="84"/>
-      <c r="S29" s="84"/>
-      <c r="T29" s="84"/>
-      <c r="U29" s="84"/>
-      <c r="V29" s="84"/>
-      <c r="W29" s="84"/>
-      <c r="X29" s="84"/>
-      <c r="Y29" s="84"/>
-      <c r="Z29" s="84"/>
-      <c r="AA29" s="84"/>
-      <c r="AB29" s="84"/>
-      <c r="AC29" s="84"/>
-      <c r="AD29" s="84"/>
-      <c r="AE29" s="84"/>
-      <c r="AF29" s="84"/>
-      <c r="AG29" s="84"/>
-      <c r="AH29" s="84"/>
-      <c r="AI29" s="84"/>
-      <c r="AJ29" s="84"/>
-      <c r="AK29" s="84"/>
-      <c r="AL29" s="84"/>
-      <c r="AM29" s="84"/>
-      <c r="AN29" s="84"/>
-      <c r="AO29" s="84"/>
-      <c r="AP29" s="85"/>
-      <c r="AQ29" s="89"/>
-      <c r="AR29" s="84"/>
-      <c r="AS29" s="84"/>
-      <c r="AT29" s="84"/>
-      <c r="AU29" s="84"/>
-      <c r="AV29" s="84"/>
-      <c r="AW29" s="84"/>
-      <c r="AX29" s="84"/>
-      <c r="AY29" s="84"/>
-      <c r="AZ29" s="84"/>
-      <c r="BA29" s="84"/>
-      <c r="BB29" s="84"/>
-      <c r="BC29" s="84"/>
-      <c r="BD29" s="84"/>
-      <c r="BE29" s="90"/>
+      <c r="A29" s="100"/>
+      <c r="B29" s="101"/>
+      <c r="C29" s="101"/>
+      <c r="D29" s="101"/>
+      <c r="E29" s="101"/>
+      <c r="F29" s="101"/>
+      <c r="G29" s="102"/>
+      <c r="H29" s="83"/>
+      <c r="I29" s="84"/>
+      <c r="J29" s="84"/>
+      <c r="K29" s="84"/>
+      <c r="L29" s="84"/>
+      <c r="M29" s="84"/>
+      <c r="N29" s="85"/>
+      <c r="O29" s="83"/>
+      <c r="P29" s="81"/>
+      <c r="Q29" s="81"/>
+      <c r="R29" s="81"/>
+      <c r="S29" s="81"/>
+      <c r="T29" s="81"/>
+      <c r="U29" s="81"/>
+      <c r="V29" s="81"/>
+      <c r="W29" s="81"/>
+      <c r="X29" s="81"/>
+      <c r="Y29" s="81"/>
+      <c r="Z29" s="81"/>
+      <c r="AA29" s="81"/>
+      <c r="AB29" s="81"/>
+      <c r="AC29" s="81"/>
+      <c r="AD29" s="81"/>
+      <c r="AE29" s="81"/>
+      <c r="AF29" s="81"/>
+      <c r="AG29" s="81"/>
+      <c r="AH29" s="81"/>
+      <c r="AI29" s="81"/>
+      <c r="AJ29" s="81"/>
+      <c r="AK29" s="81"/>
+      <c r="AL29" s="81"/>
+      <c r="AM29" s="81"/>
+      <c r="AN29" s="81"/>
+      <c r="AO29" s="81"/>
+      <c r="AP29" s="89"/>
+      <c r="AQ29" s="80"/>
+      <c r="AR29" s="81"/>
+      <c r="AS29" s="81"/>
+      <c r="AT29" s="81"/>
+      <c r="AU29" s="81"/>
+      <c r="AV29" s="81"/>
+      <c r="AW29" s="81"/>
+      <c r="AX29" s="81"/>
+      <c r="AY29" s="81"/>
+      <c r="AZ29" s="81"/>
+      <c r="BA29" s="81"/>
+      <c r="BB29" s="81"/>
+      <c r="BC29" s="81"/>
+      <c r="BD29" s="81"/>
+      <c r="BE29" s="82"/>
     </row>
     <row r="30" spans="1:57" ht="15" customHeight="1">
-      <c r="A30" s="78"/>
-      <c r="B30" s="79"/>
-      <c r="C30" s="79"/>
-      <c r="D30" s="79"/>
-      <c r="E30" s="79"/>
-      <c r="F30" s="79"/>
-      <c r="G30" s="80"/>
-      <c r="H30" s="81"/>
-      <c r="I30" s="82"/>
-      <c r="J30" s="82"/>
-      <c r="K30" s="82"/>
-      <c r="L30" s="82"/>
-      <c r="M30" s="82"/>
-      <c r="N30" s="83"/>
-      <c r="O30" s="81"/>
-      <c r="P30" s="84"/>
-      <c r="Q30" s="84"/>
-      <c r="R30" s="84"/>
-      <c r="S30" s="84"/>
-      <c r="T30" s="84"/>
-      <c r="U30" s="84"/>
-      <c r="V30" s="84"/>
-      <c r="W30" s="84"/>
-      <c r="X30" s="84"/>
-      <c r="Y30" s="84"/>
-      <c r="Z30" s="84"/>
-      <c r="AA30" s="84"/>
-      <c r="AB30" s="84"/>
-      <c r="AC30" s="84"/>
-      <c r="AD30" s="84"/>
-      <c r="AE30" s="84"/>
-      <c r="AF30" s="84"/>
-      <c r="AG30" s="84"/>
-      <c r="AH30" s="84"/>
-      <c r="AI30" s="84"/>
-      <c r="AJ30" s="84"/>
-      <c r="AK30" s="84"/>
-      <c r="AL30" s="84"/>
-      <c r="AM30" s="84"/>
-      <c r="AN30" s="84"/>
-      <c r="AO30" s="84"/>
-      <c r="AP30" s="85"/>
-      <c r="AQ30" s="89"/>
-      <c r="AR30" s="84"/>
-      <c r="AS30" s="84"/>
-      <c r="AT30" s="84"/>
-      <c r="AU30" s="84"/>
-      <c r="AV30" s="84"/>
-      <c r="AW30" s="84"/>
-      <c r="AX30" s="84"/>
-      <c r="AY30" s="84"/>
-      <c r="AZ30" s="84"/>
-      <c r="BA30" s="84"/>
-      <c r="BB30" s="84"/>
-      <c r="BC30" s="84"/>
-      <c r="BD30" s="84"/>
-      <c r="BE30" s="90"/>
+      <c r="A30" s="100"/>
+      <c r="B30" s="101"/>
+      <c r="C30" s="101"/>
+      <c r="D30" s="101"/>
+      <c r="E30" s="101"/>
+      <c r="F30" s="101"/>
+      <c r="G30" s="102"/>
+      <c r="H30" s="83"/>
+      <c r="I30" s="84"/>
+      <c r="J30" s="84"/>
+      <c r="K30" s="84"/>
+      <c r="L30" s="84"/>
+      <c r="M30" s="84"/>
+      <c r="N30" s="85"/>
+      <c r="O30" s="83"/>
+      <c r="P30" s="81"/>
+      <c r="Q30" s="81"/>
+      <c r="R30" s="81"/>
+      <c r="S30" s="81"/>
+      <c r="T30" s="81"/>
+      <c r="U30" s="81"/>
+      <c r="V30" s="81"/>
+      <c r="W30" s="81"/>
+      <c r="X30" s="81"/>
+      <c r="Y30" s="81"/>
+      <c r="Z30" s="81"/>
+      <c r="AA30" s="81"/>
+      <c r="AB30" s="81"/>
+      <c r="AC30" s="81"/>
+      <c r="AD30" s="81"/>
+      <c r="AE30" s="81"/>
+      <c r="AF30" s="81"/>
+      <c r="AG30" s="81"/>
+      <c r="AH30" s="81"/>
+      <c r="AI30" s="81"/>
+      <c r="AJ30" s="81"/>
+      <c r="AK30" s="81"/>
+      <c r="AL30" s="81"/>
+      <c r="AM30" s="81"/>
+      <c r="AN30" s="81"/>
+      <c r="AO30" s="81"/>
+      <c r="AP30" s="89"/>
+      <c r="AQ30" s="80"/>
+      <c r="AR30" s="81"/>
+      <c r="AS30" s="81"/>
+      <c r="AT30" s="81"/>
+      <c r="AU30" s="81"/>
+      <c r="AV30" s="81"/>
+      <c r="AW30" s="81"/>
+      <c r="AX30" s="81"/>
+      <c r="AY30" s="81"/>
+      <c r="AZ30" s="81"/>
+      <c r="BA30" s="81"/>
+      <c r="BB30" s="81"/>
+      <c r="BC30" s="81"/>
+      <c r="BD30" s="81"/>
+      <c r="BE30" s="82"/>
     </row>
     <row r="31" spans="1:57" ht="15" customHeight="1">
-      <c r="A31" s="78"/>
-      <c r="B31" s="79"/>
-      <c r="C31" s="79"/>
-      <c r="D31" s="79"/>
-      <c r="E31" s="79"/>
-      <c r="F31" s="79"/>
-      <c r="G31" s="80"/>
-      <c r="H31" s="81"/>
-      <c r="I31" s="82"/>
-      <c r="J31" s="82"/>
-      <c r="K31" s="82"/>
-      <c r="L31" s="82"/>
-      <c r="M31" s="82"/>
-      <c r="N31" s="83"/>
-      <c r="O31" s="81"/>
-      <c r="P31" s="84"/>
-      <c r="Q31" s="84"/>
-      <c r="R31" s="84"/>
-      <c r="S31" s="84"/>
-      <c r="T31" s="84"/>
-      <c r="U31" s="84"/>
-      <c r="V31" s="84"/>
-      <c r="W31" s="84"/>
-      <c r="X31" s="84"/>
-      <c r="Y31" s="84"/>
-      <c r="Z31" s="84"/>
-      <c r="AA31" s="84"/>
-      <c r="AB31" s="84"/>
-      <c r="AC31" s="84"/>
-      <c r="AD31" s="84"/>
-      <c r="AE31" s="84"/>
-      <c r="AF31" s="84"/>
-      <c r="AG31" s="84"/>
-      <c r="AH31" s="84"/>
-      <c r="AI31" s="84"/>
-      <c r="AJ31" s="84"/>
-      <c r="AK31" s="84"/>
-      <c r="AL31" s="84"/>
-      <c r="AM31" s="84"/>
-      <c r="AN31" s="84"/>
-      <c r="AO31" s="84"/>
-      <c r="AP31" s="85"/>
-      <c r="AQ31" s="89"/>
-      <c r="AR31" s="84"/>
-      <c r="AS31" s="84"/>
-      <c r="AT31" s="84"/>
-      <c r="AU31" s="84"/>
-      <c r="AV31" s="84"/>
-      <c r="AW31" s="84"/>
-      <c r="AX31" s="84"/>
-      <c r="AY31" s="84"/>
-      <c r="AZ31" s="84"/>
-      <c r="BA31" s="84"/>
-      <c r="BB31" s="84"/>
-      <c r="BC31" s="84"/>
-      <c r="BD31" s="84"/>
-      <c r="BE31" s="90"/>
+      <c r="A31" s="100"/>
+      <c r="B31" s="101"/>
+      <c r="C31" s="101"/>
+      <c r="D31" s="101"/>
+      <c r="E31" s="101"/>
+      <c r="F31" s="101"/>
+      <c r="G31" s="102"/>
+      <c r="H31" s="83"/>
+      <c r="I31" s="84"/>
+      <c r="J31" s="84"/>
+      <c r="K31" s="84"/>
+      <c r="L31" s="84"/>
+      <c r="M31" s="84"/>
+      <c r="N31" s="85"/>
+      <c r="O31" s="83"/>
+      <c r="P31" s="81"/>
+      <c r="Q31" s="81"/>
+      <c r="R31" s="81"/>
+      <c r="S31" s="81"/>
+      <c r="T31" s="81"/>
+      <c r="U31" s="81"/>
+      <c r="V31" s="81"/>
+      <c r="W31" s="81"/>
+      <c r="X31" s="81"/>
+      <c r="Y31" s="81"/>
+      <c r="Z31" s="81"/>
+      <c r="AA31" s="81"/>
+      <c r="AB31" s="81"/>
+      <c r="AC31" s="81"/>
+      <c r="AD31" s="81"/>
+      <c r="AE31" s="81"/>
+      <c r="AF31" s="81"/>
+      <c r="AG31" s="81"/>
+      <c r="AH31" s="81"/>
+      <c r="AI31" s="81"/>
+      <c r="AJ31" s="81"/>
+      <c r="AK31" s="81"/>
+      <c r="AL31" s="81"/>
+      <c r="AM31" s="81"/>
+      <c r="AN31" s="81"/>
+      <c r="AO31" s="81"/>
+      <c r="AP31" s="89"/>
+      <c r="AQ31" s="80"/>
+      <c r="AR31" s="81"/>
+      <c r="AS31" s="81"/>
+      <c r="AT31" s="81"/>
+      <c r="AU31" s="81"/>
+      <c r="AV31" s="81"/>
+      <c r="AW31" s="81"/>
+      <c r="AX31" s="81"/>
+      <c r="AY31" s="81"/>
+      <c r="AZ31" s="81"/>
+      <c r="BA31" s="81"/>
+      <c r="BB31" s="81"/>
+      <c r="BC31" s="81"/>
+      <c r="BD31" s="81"/>
+      <c r="BE31" s="82"/>
     </row>
     <row r="32" spans="1:57" ht="15" customHeight="1">
-      <c r="A32" s="78"/>
-      <c r="B32" s="79"/>
-      <c r="C32" s="79"/>
-      <c r="D32" s="79"/>
-      <c r="E32" s="79"/>
-      <c r="F32" s="79"/>
-      <c r="G32" s="80"/>
-      <c r="H32" s="81"/>
-      <c r="I32" s="82"/>
-      <c r="J32" s="82"/>
-      <c r="K32" s="82"/>
-      <c r="L32" s="82"/>
-      <c r="M32" s="82"/>
-      <c r="N32" s="83"/>
-      <c r="O32" s="81"/>
-      <c r="P32" s="84"/>
-      <c r="Q32" s="84"/>
-      <c r="R32" s="84"/>
-      <c r="S32" s="84"/>
-      <c r="T32" s="84"/>
-      <c r="U32" s="84"/>
-      <c r="V32" s="84"/>
-      <c r="W32" s="84"/>
-      <c r="X32" s="84"/>
-      <c r="Y32" s="84"/>
-      <c r="Z32" s="84"/>
-      <c r="AA32" s="84"/>
-      <c r="AB32" s="84"/>
-      <c r="AC32" s="84"/>
-      <c r="AD32" s="84"/>
-      <c r="AE32" s="84"/>
-      <c r="AF32" s="84"/>
-      <c r="AG32" s="84"/>
-      <c r="AH32" s="84"/>
-      <c r="AI32" s="84"/>
-      <c r="AJ32" s="84"/>
-      <c r="AK32" s="84"/>
-      <c r="AL32" s="84"/>
-      <c r="AM32" s="84"/>
-      <c r="AN32" s="84"/>
-      <c r="AO32" s="84"/>
-      <c r="AP32" s="85"/>
-      <c r="AQ32" s="89"/>
-      <c r="AR32" s="84"/>
-      <c r="AS32" s="84"/>
-      <c r="AT32" s="84"/>
-      <c r="AU32" s="84"/>
-      <c r="AV32" s="84"/>
-      <c r="AW32" s="84"/>
-      <c r="AX32" s="84"/>
-      <c r="AY32" s="84"/>
-      <c r="AZ32" s="84"/>
-      <c r="BA32" s="84"/>
-      <c r="BB32" s="84"/>
-      <c r="BC32" s="84"/>
-      <c r="BD32" s="84"/>
-      <c r="BE32" s="90"/>
+      <c r="A32" s="100"/>
+      <c r="B32" s="101"/>
+      <c r="C32" s="101"/>
+      <c r="D32" s="101"/>
+      <c r="E32" s="101"/>
+      <c r="F32" s="101"/>
+      <c r="G32" s="102"/>
+      <c r="H32" s="83"/>
+      <c r="I32" s="84"/>
+      <c r="J32" s="84"/>
+      <c r="K32" s="84"/>
+      <c r="L32" s="84"/>
+      <c r="M32" s="84"/>
+      <c r="N32" s="85"/>
+      <c r="O32" s="83"/>
+      <c r="P32" s="81"/>
+      <c r="Q32" s="81"/>
+      <c r="R32" s="81"/>
+      <c r="S32" s="81"/>
+      <c r="T32" s="81"/>
+      <c r="U32" s="81"/>
+      <c r="V32" s="81"/>
+      <c r="W32" s="81"/>
+      <c r="X32" s="81"/>
+      <c r="Y32" s="81"/>
+      <c r="Z32" s="81"/>
+      <c r="AA32" s="81"/>
+      <c r="AB32" s="81"/>
+      <c r="AC32" s="81"/>
+      <c r="AD32" s="81"/>
+      <c r="AE32" s="81"/>
+      <c r="AF32" s="81"/>
+      <c r="AG32" s="81"/>
+      <c r="AH32" s="81"/>
+      <c r="AI32" s="81"/>
+      <c r="AJ32" s="81"/>
+      <c r="AK32" s="81"/>
+      <c r="AL32" s="81"/>
+      <c r="AM32" s="81"/>
+      <c r="AN32" s="81"/>
+      <c r="AO32" s="81"/>
+      <c r="AP32" s="89"/>
+      <c r="AQ32" s="80"/>
+      <c r="AR32" s="81"/>
+      <c r="AS32" s="81"/>
+      <c r="AT32" s="81"/>
+      <c r="AU32" s="81"/>
+      <c r="AV32" s="81"/>
+      <c r="AW32" s="81"/>
+      <c r="AX32" s="81"/>
+      <c r="AY32" s="81"/>
+      <c r="AZ32" s="81"/>
+      <c r="BA32" s="81"/>
+      <c r="BB32" s="81"/>
+      <c r="BC32" s="81"/>
+      <c r="BD32" s="81"/>
+      <c r="BE32" s="82"/>
     </row>
     <row r="33" spans="1:57" ht="15" customHeight="1">
-      <c r="A33" s="78"/>
-      <c r="B33" s="79"/>
-      <c r="C33" s="79"/>
-      <c r="D33" s="79"/>
-      <c r="E33" s="79"/>
-      <c r="F33" s="79"/>
-      <c r="G33" s="80"/>
-      <c r="H33" s="81"/>
-      <c r="I33" s="82"/>
-      <c r="J33" s="82"/>
-      <c r="K33" s="82"/>
-      <c r="L33" s="82"/>
-      <c r="M33" s="82"/>
-      <c r="N33" s="83"/>
-      <c r="O33" s="81"/>
-      <c r="P33" s="84"/>
-      <c r="Q33" s="84"/>
-      <c r="R33" s="84"/>
-      <c r="S33" s="84"/>
-      <c r="T33" s="84"/>
-      <c r="U33" s="84"/>
-      <c r="V33" s="84"/>
-      <c r="W33" s="84"/>
-      <c r="X33" s="84"/>
-      <c r="Y33" s="84"/>
-      <c r="Z33" s="84"/>
-      <c r="AA33" s="84"/>
-      <c r="AB33" s="84"/>
-      <c r="AC33" s="84"/>
-      <c r="AD33" s="84"/>
-      <c r="AE33" s="84"/>
-      <c r="AF33" s="84"/>
-      <c r="AG33" s="84"/>
-      <c r="AH33" s="84"/>
-      <c r="AI33" s="84"/>
-      <c r="AJ33" s="84"/>
-      <c r="AK33" s="84"/>
-      <c r="AL33" s="84"/>
-      <c r="AM33" s="84"/>
-      <c r="AN33" s="84"/>
-      <c r="AO33" s="84"/>
-      <c r="AP33" s="85"/>
-      <c r="AQ33" s="89"/>
-      <c r="AR33" s="84"/>
-      <c r="AS33" s="84"/>
-      <c r="AT33" s="84"/>
-      <c r="AU33" s="84"/>
-      <c r="AV33" s="84"/>
-      <c r="AW33" s="84"/>
-      <c r="AX33" s="84"/>
-      <c r="AY33" s="84"/>
-      <c r="AZ33" s="84"/>
-      <c r="BA33" s="84"/>
-      <c r="BB33" s="84"/>
-      <c r="BC33" s="84"/>
-      <c r="BD33" s="84"/>
-      <c r="BE33" s="90"/>
+      <c r="A33" s="100"/>
+      <c r="B33" s="101"/>
+      <c r="C33" s="101"/>
+      <c r="D33" s="101"/>
+      <c r="E33" s="101"/>
+      <c r="F33" s="101"/>
+      <c r="G33" s="102"/>
+      <c r="H33" s="83"/>
+      <c r="I33" s="84"/>
+      <c r="J33" s="84"/>
+      <c r="K33" s="84"/>
+      <c r="L33" s="84"/>
+      <c r="M33" s="84"/>
+      <c r="N33" s="85"/>
+      <c r="O33" s="83"/>
+      <c r="P33" s="81"/>
+      <c r="Q33" s="81"/>
+      <c r="R33" s="81"/>
+      <c r="S33" s="81"/>
+      <c r="T33" s="81"/>
+      <c r="U33" s="81"/>
+      <c r="V33" s="81"/>
+      <c r="W33" s="81"/>
+      <c r="X33" s="81"/>
+      <c r="Y33" s="81"/>
+      <c r="Z33" s="81"/>
+      <c r="AA33" s="81"/>
+      <c r="AB33" s="81"/>
+      <c r="AC33" s="81"/>
+      <c r="AD33" s="81"/>
+      <c r="AE33" s="81"/>
+      <c r="AF33" s="81"/>
+      <c r="AG33" s="81"/>
+      <c r="AH33" s="81"/>
+      <c r="AI33" s="81"/>
+      <c r="AJ33" s="81"/>
+      <c r="AK33" s="81"/>
+      <c r="AL33" s="81"/>
+      <c r="AM33" s="81"/>
+      <c r="AN33" s="81"/>
+      <c r="AO33" s="81"/>
+      <c r="AP33" s="89"/>
+      <c r="AQ33" s="80"/>
+      <c r="AR33" s="81"/>
+      <c r="AS33" s="81"/>
+      <c r="AT33" s="81"/>
+      <c r="AU33" s="81"/>
+      <c r="AV33" s="81"/>
+      <c r="AW33" s="81"/>
+      <c r="AX33" s="81"/>
+      <c r="AY33" s="81"/>
+      <c r="AZ33" s="81"/>
+      <c r="BA33" s="81"/>
+      <c r="BB33" s="81"/>
+      <c r="BC33" s="81"/>
+      <c r="BD33" s="81"/>
+      <c r="BE33" s="82"/>
     </row>
     <row r="34" spans="1:57" ht="15" customHeight="1">
-      <c r="A34" s="78"/>
-      <c r="B34" s="79"/>
-      <c r="C34" s="79"/>
-      <c r="D34" s="79"/>
-      <c r="E34" s="79"/>
-      <c r="F34" s="79"/>
-      <c r="G34" s="80"/>
-      <c r="H34" s="81"/>
-      <c r="I34" s="82"/>
-      <c r="J34" s="82"/>
-      <c r="K34" s="82"/>
-      <c r="L34" s="82"/>
-      <c r="M34" s="82"/>
-      <c r="N34" s="83"/>
-      <c r="O34" s="81"/>
-      <c r="P34" s="84"/>
-      <c r="Q34" s="84"/>
-      <c r="R34" s="84"/>
-      <c r="S34" s="84"/>
-      <c r="T34" s="84"/>
-      <c r="U34" s="84"/>
-      <c r="V34" s="84"/>
-      <c r="W34" s="84"/>
-      <c r="X34" s="84"/>
-      <c r="Y34" s="84"/>
-      <c r="Z34" s="84"/>
-      <c r="AA34" s="84"/>
-      <c r="AB34" s="84"/>
-      <c r="AC34" s="84"/>
-      <c r="AD34" s="84"/>
-      <c r="AE34" s="84"/>
-      <c r="AF34" s="84"/>
-      <c r="AG34" s="84"/>
-      <c r="AH34" s="84"/>
-      <c r="AI34" s="84"/>
-      <c r="AJ34" s="84"/>
-      <c r="AK34" s="84"/>
-      <c r="AL34" s="84"/>
-      <c r="AM34" s="84"/>
-      <c r="AN34" s="84"/>
-      <c r="AO34" s="84"/>
-      <c r="AP34" s="85"/>
-      <c r="AQ34" s="89"/>
-      <c r="AR34" s="84"/>
-      <c r="AS34" s="84"/>
-      <c r="AT34" s="84"/>
-      <c r="AU34" s="84"/>
-      <c r="AV34" s="84"/>
-      <c r="AW34" s="84"/>
-      <c r="AX34" s="84"/>
-      <c r="AY34" s="84"/>
-      <c r="AZ34" s="84"/>
-      <c r="BA34" s="84"/>
-      <c r="BB34" s="84"/>
-      <c r="BC34" s="84"/>
-      <c r="BD34" s="84"/>
-      <c r="BE34" s="90"/>
+      <c r="A34" s="100"/>
+      <c r="B34" s="101"/>
+      <c r="C34" s="101"/>
+      <c r="D34" s="101"/>
+      <c r="E34" s="101"/>
+      <c r="F34" s="101"/>
+      <c r="G34" s="102"/>
+      <c r="H34" s="83"/>
+      <c r="I34" s="84"/>
+      <c r="J34" s="84"/>
+      <c r="K34" s="84"/>
+      <c r="L34" s="84"/>
+      <c r="M34" s="84"/>
+      <c r="N34" s="85"/>
+      <c r="O34" s="83"/>
+      <c r="P34" s="81"/>
+      <c r="Q34" s="81"/>
+      <c r="R34" s="81"/>
+      <c r="S34" s="81"/>
+      <c r="T34" s="81"/>
+      <c r="U34" s="81"/>
+      <c r="V34" s="81"/>
+      <c r="W34" s="81"/>
+      <c r="X34" s="81"/>
+      <c r="Y34" s="81"/>
+      <c r="Z34" s="81"/>
+      <c r="AA34" s="81"/>
+      <c r="AB34" s="81"/>
+      <c r="AC34" s="81"/>
+      <c r="AD34" s="81"/>
+      <c r="AE34" s="81"/>
+      <c r="AF34" s="81"/>
+      <c r="AG34" s="81"/>
+      <c r="AH34" s="81"/>
+      <c r="AI34" s="81"/>
+      <c r="AJ34" s="81"/>
+      <c r="AK34" s="81"/>
+      <c r="AL34" s="81"/>
+      <c r="AM34" s="81"/>
+      <c r="AN34" s="81"/>
+      <c r="AO34" s="81"/>
+      <c r="AP34" s="89"/>
+      <c r="AQ34" s="80"/>
+      <c r="AR34" s="81"/>
+      <c r="AS34" s="81"/>
+      <c r="AT34" s="81"/>
+      <c r="AU34" s="81"/>
+      <c r="AV34" s="81"/>
+      <c r="AW34" s="81"/>
+      <c r="AX34" s="81"/>
+      <c r="AY34" s="81"/>
+      <c r="AZ34" s="81"/>
+      <c r="BA34" s="81"/>
+      <c r="BB34" s="81"/>
+      <c r="BC34" s="81"/>
+      <c r="BD34" s="81"/>
+      <c r="BE34" s="82"/>
     </row>
     <row r="35" spans="1:57" ht="15" customHeight="1" thickBot="1">
-      <c r="A35" s="95"/>
-      <c r="B35" s="96"/>
-      <c r="C35" s="96"/>
-      <c r="D35" s="96"/>
-      <c r="E35" s="96"/>
-      <c r="F35" s="96"/>
-      <c r="G35" s="97"/>
-      <c r="H35" s="91"/>
-      <c r="I35" s="92"/>
-      <c r="J35" s="92"/>
-      <c r="K35" s="92"/>
-      <c r="L35" s="92"/>
-      <c r="M35" s="92"/>
-      <c r="N35" s="93"/>
-      <c r="O35" s="91"/>
-      <c r="P35" s="87"/>
-      <c r="Q35" s="87"/>
-      <c r="R35" s="87"/>
-      <c r="S35" s="87"/>
-      <c r="T35" s="87"/>
-      <c r="U35" s="87"/>
-      <c r="V35" s="87"/>
-      <c r="W35" s="87"/>
-      <c r="X35" s="87"/>
-      <c r="Y35" s="87"/>
-      <c r="Z35" s="87"/>
-      <c r="AA35" s="87"/>
-      <c r="AB35" s="87"/>
-      <c r="AC35" s="87"/>
-      <c r="AD35" s="87"/>
-      <c r="AE35" s="87"/>
-      <c r="AF35" s="87"/>
-      <c r="AG35" s="87"/>
-      <c r="AH35" s="87"/>
-      <c r="AI35" s="87"/>
-      <c r="AJ35" s="87"/>
-      <c r="AK35" s="87"/>
-      <c r="AL35" s="87"/>
-      <c r="AM35" s="87"/>
-      <c r="AN35" s="87"/>
-      <c r="AO35" s="87"/>
-      <c r="AP35" s="94"/>
-      <c r="AQ35" s="86"/>
-      <c r="AR35" s="87"/>
-      <c r="AS35" s="87"/>
-      <c r="AT35" s="87"/>
-      <c r="AU35" s="87"/>
-      <c r="AV35" s="87"/>
-      <c r="AW35" s="87"/>
-      <c r="AX35" s="87"/>
-      <c r="AY35" s="87"/>
-      <c r="AZ35" s="87"/>
-      <c r="BA35" s="87"/>
-      <c r="BB35" s="87"/>
-      <c r="BC35" s="87"/>
-      <c r="BD35" s="87"/>
-      <c r="BE35" s="88"/>
+      <c r="A35" s="121"/>
+      <c r="B35" s="122"/>
+      <c r="C35" s="122"/>
+      <c r="D35" s="122"/>
+      <c r="E35" s="122"/>
+      <c r="F35" s="122"/>
+      <c r="G35" s="123"/>
+      <c r="H35" s="127"/>
+      <c r="I35" s="128"/>
+      <c r="J35" s="128"/>
+      <c r="K35" s="128"/>
+      <c r="L35" s="128"/>
+      <c r="M35" s="128"/>
+      <c r="N35" s="129"/>
+      <c r="O35" s="127"/>
+      <c r="P35" s="125"/>
+      <c r="Q35" s="125"/>
+      <c r="R35" s="125"/>
+      <c r="S35" s="125"/>
+      <c r="T35" s="125"/>
+      <c r="U35" s="125"/>
+      <c r="V35" s="125"/>
+      <c r="W35" s="125"/>
+      <c r="X35" s="125"/>
+      <c r="Y35" s="125"/>
+      <c r="Z35" s="125"/>
+      <c r="AA35" s="125"/>
+      <c r="AB35" s="125"/>
+      <c r="AC35" s="125"/>
+      <c r="AD35" s="125"/>
+      <c r="AE35" s="125"/>
+      <c r="AF35" s="125"/>
+      <c r="AG35" s="125"/>
+      <c r="AH35" s="125"/>
+      <c r="AI35" s="125"/>
+      <c r="AJ35" s="125"/>
+      <c r="AK35" s="125"/>
+      <c r="AL35" s="125"/>
+      <c r="AM35" s="125"/>
+      <c r="AN35" s="125"/>
+      <c r="AO35" s="125"/>
+      <c r="AP35" s="130"/>
+      <c r="AQ35" s="124"/>
+      <c r="AR35" s="125"/>
+      <c r="AS35" s="125"/>
+      <c r="AT35" s="125"/>
+      <c r="AU35" s="125"/>
+      <c r="AV35" s="125"/>
+      <c r="AW35" s="125"/>
+      <c r="AX35" s="125"/>
+      <c r="AY35" s="125"/>
+      <c r="AZ35" s="125"/>
+      <c r="BA35" s="125"/>
+      <c r="BB35" s="125"/>
+      <c r="BC35" s="125"/>
+      <c r="BD35" s="125"/>
+      <c r="BE35" s="126"/>
     </row>
   </sheetData>
   <mergeCells count="133">
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="O19:AP19"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AQ35:BE35"/>
+    <mergeCell ref="AQ33:BE33"/>
+    <mergeCell ref="AQ34:BE34"/>
+    <mergeCell ref="AQ32:BE32"/>
+    <mergeCell ref="AQ31:BE31"/>
+    <mergeCell ref="O27:AP27"/>
+    <mergeCell ref="AQ27:BE27"/>
+    <mergeCell ref="H30:N30"/>
+    <mergeCell ref="O30:AP30"/>
+    <mergeCell ref="AQ30:BE30"/>
+    <mergeCell ref="AQ28:BE28"/>
+    <mergeCell ref="H28:N28"/>
+    <mergeCell ref="O28:AP28"/>
+    <mergeCell ref="H35:N35"/>
+    <mergeCell ref="O35:AP35"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="H33:N33"/>
+    <mergeCell ref="H34:N34"/>
+    <mergeCell ref="O34:AP34"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="O33:AP33"/>
+    <mergeCell ref="O32:AP32"/>
+    <mergeCell ref="H31:N31"/>
+    <mergeCell ref="O31:AP31"/>
+    <mergeCell ref="H27:N27"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="H32:N32"/>
+    <mergeCell ref="H29:N29"/>
+    <mergeCell ref="O29:AP29"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:AP20"/>
+    <mergeCell ref="AQ17:BE17"/>
+    <mergeCell ref="H26:N26"/>
+    <mergeCell ref="O26:AP26"/>
+    <mergeCell ref="AQ26:BE26"/>
+    <mergeCell ref="AQ19:BE19"/>
+    <mergeCell ref="H25:N25"/>
+    <mergeCell ref="H24:N24"/>
+    <mergeCell ref="O24:AP24"/>
+    <mergeCell ref="O25:AP25"/>
+    <mergeCell ref="AQ25:BE25"/>
+    <mergeCell ref="H22:N22"/>
+    <mergeCell ref="AQ24:BE24"/>
+    <mergeCell ref="H23:N23"/>
+    <mergeCell ref="O23:AP23"/>
+    <mergeCell ref="AQ23:BE23"/>
+    <mergeCell ref="AQ20:BE20"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:AP21"/>
+    <mergeCell ref="AQ18:BE18"/>
+    <mergeCell ref="AQ21:BE21"/>
+    <mergeCell ref="O22:AP22"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="H4:N4"/>
+    <mergeCell ref="O4:AP4"/>
+    <mergeCell ref="AQ4:BE4"/>
+    <mergeCell ref="H13:N13"/>
+    <mergeCell ref="O13:AP13"/>
+    <mergeCell ref="AQ13:BE13"/>
+    <mergeCell ref="H14:N14"/>
+    <mergeCell ref="O14:AP14"/>
+    <mergeCell ref="AQ14:BE14"/>
+    <mergeCell ref="AQ16:BE16"/>
+    <mergeCell ref="H15:N15"/>
+    <mergeCell ref="O18:AP18"/>
+    <mergeCell ref="H9:N9"/>
+    <mergeCell ref="O9:AP9"/>
+    <mergeCell ref="AQ9:BE9"/>
+    <mergeCell ref="H10:N10"/>
+    <mergeCell ref="O10:AP10"/>
+    <mergeCell ref="AQ10:BE10"/>
+    <mergeCell ref="H11:N11"/>
+    <mergeCell ref="O11:AP11"/>
+    <mergeCell ref="AQ11:BE11"/>
+    <mergeCell ref="H16:N16"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="O15:AP15"/>
+    <mergeCell ref="A1:BE1"/>
+    <mergeCell ref="H3:N3"/>
+    <mergeCell ref="O3:AP3"/>
+    <mergeCell ref="AQ3:BE3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
     <mergeCell ref="AQ22:BE22"/>
     <mergeCell ref="AQ29:BE29"/>
     <mergeCell ref="H17:N17"/>
@@ -66833,115 +66942,6 @@
     <mergeCell ref="A9:G9"/>
     <mergeCell ref="O16:AP16"/>
     <mergeCell ref="O17:AP17"/>
-    <mergeCell ref="A1:BE1"/>
-    <mergeCell ref="H3:N3"/>
-    <mergeCell ref="O3:AP3"/>
-    <mergeCell ref="AQ3:BE3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="O15:AP15"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="H4:N4"/>
-    <mergeCell ref="O4:AP4"/>
-    <mergeCell ref="AQ4:BE4"/>
-    <mergeCell ref="H13:N13"/>
-    <mergeCell ref="O13:AP13"/>
-    <mergeCell ref="AQ13:BE13"/>
-    <mergeCell ref="H14:N14"/>
-    <mergeCell ref="O14:AP14"/>
-    <mergeCell ref="AQ14:BE14"/>
-    <mergeCell ref="AQ16:BE16"/>
-    <mergeCell ref="H15:N15"/>
-    <mergeCell ref="O18:AP18"/>
-    <mergeCell ref="H9:N9"/>
-    <mergeCell ref="O9:AP9"/>
-    <mergeCell ref="AQ9:BE9"/>
-    <mergeCell ref="H10:N10"/>
-    <mergeCell ref="O10:AP10"/>
-    <mergeCell ref="AQ10:BE10"/>
-    <mergeCell ref="H11:N11"/>
-    <mergeCell ref="O11:AP11"/>
-    <mergeCell ref="AQ11:BE11"/>
-    <mergeCell ref="H16:N16"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:AP20"/>
-    <mergeCell ref="AQ17:BE17"/>
-    <mergeCell ref="H26:N26"/>
-    <mergeCell ref="O26:AP26"/>
-    <mergeCell ref="AQ26:BE26"/>
-    <mergeCell ref="AQ19:BE19"/>
-    <mergeCell ref="H25:N25"/>
-    <mergeCell ref="H24:N24"/>
-    <mergeCell ref="O24:AP24"/>
-    <mergeCell ref="O25:AP25"/>
-    <mergeCell ref="AQ25:BE25"/>
-    <mergeCell ref="H22:N22"/>
-    <mergeCell ref="AQ24:BE24"/>
-    <mergeCell ref="H23:N23"/>
-    <mergeCell ref="O23:AP23"/>
-    <mergeCell ref="AQ23:BE23"/>
-    <mergeCell ref="AQ20:BE20"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:AP21"/>
-    <mergeCell ref="AQ18:BE18"/>
-    <mergeCell ref="AQ21:BE21"/>
-    <mergeCell ref="O22:AP22"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="H33:N33"/>
-    <mergeCell ref="H34:N34"/>
-    <mergeCell ref="O34:AP34"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="O33:AP33"/>
-    <mergeCell ref="O32:AP32"/>
-    <mergeCell ref="H31:N31"/>
-    <mergeCell ref="O31:AP31"/>
-    <mergeCell ref="H27:N27"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="H32:N32"/>
-    <mergeCell ref="H29:N29"/>
-    <mergeCell ref="O29:AP29"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="O19:AP19"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="AQ35:BE35"/>
-    <mergeCell ref="AQ33:BE33"/>
-    <mergeCell ref="AQ34:BE34"/>
-    <mergeCell ref="AQ32:BE32"/>
-    <mergeCell ref="AQ31:BE31"/>
-    <mergeCell ref="O27:AP27"/>
-    <mergeCell ref="AQ27:BE27"/>
-    <mergeCell ref="H30:N30"/>
-    <mergeCell ref="O30:AP30"/>
-    <mergeCell ref="AQ30:BE30"/>
-    <mergeCell ref="AQ28:BE28"/>
-    <mergeCell ref="H28:N28"/>
-    <mergeCell ref="O28:AP28"/>
-    <mergeCell ref="H35:N35"/>
-    <mergeCell ref="O35:AP35"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A20:G20"/>
   </mergeCells>
   <phoneticPr fontId="5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>

--- a/development/MS/spec/MSBB/Panel/MSBBP1210_SloReg.xlsx
+++ b/development/MS/spec/MSBB/Panel/MSBBP1210_SloReg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\mcframeDEV\development\MS\spec\MSBB\Panel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E01F8192-AD82-44AA-9D79-94DB2661DA05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE7E130-9C52-4E46-8C6A-EF9E78616819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-3330" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11461,14 +11461,14 @@
     <xf numFmtId="0" fontId="27" fillId="24" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -11479,7 +11479,79 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11488,8 +11560,29 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -11520,99 +11613,6 @@
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -64819,65 +64819,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:57" ht="38.25" customHeight="1" thickBot="1">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="107" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="104"/>
-      <c r="C1" s="104"/>
-      <c r="D1" s="104"/>
-      <c r="E1" s="104"/>
-      <c r="F1" s="104"/>
-      <c r="G1" s="104"/>
-      <c r="H1" s="104"/>
-      <c r="I1" s="104"/>
-      <c r="J1" s="104"/>
-      <c r="K1" s="104"/>
-      <c r="L1" s="104"/>
-      <c r="M1" s="104"/>
-      <c r="N1" s="104"/>
-      <c r="O1" s="104"/>
-      <c r="P1" s="104"/>
-      <c r="Q1" s="104"/>
-      <c r="R1" s="104"/>
-      <c r="S1" s="104"/>
-      <c r="T1" s="104"/>
-      <c r="U1" s="104"/>
-      <c r="V1" s="104"/>
-      <c r="W1" s="104"/>
-      <c r="X1" s="104"/>
-      <c r="Y1" s="104"/>
-      <c r="Z1" s="104"/>
-      <c r="AA1" s="104"/>
-      <c r="AB1" s="104"/>
-      <c r="AC1" s="104"/>
-      <c r="AD1" s="104"/>
-      <c r="AE1" s="104"/>
-      <c r="AF1" s="104"/>
-      <c r="AG1" s="104"/>
-      <c r="AH1" s="104"/>
-      <c r="AI1" s="104"/>
-      <c r="AJ1" s="104"/>
-      <c r="AK1" s="104"/>
-      <c r="AL1" s="104"/>
-      <c r="AM1" s="104"/>
-      <c r="AN1" s="104"/>
-      <c r="AO1" s="104"/>
-      <c r="AP1" s="104"/>
-      <c r="AQ1" s="104"/>
-      <c r="AR1" s="104"/>
-      <c r="AS1" s="104"/>
-      <c r="AT1" s="104"/>
-      <c r="AU1" s="104"/>
-      <c r="AV1" s="104"/>
-      <c r="AW1" s="104"/>
-      <c r="AX1" s="104"/>
-      <c r="AY1" s="104"/>
-      <c r="AZ1" s="104"/>
-      <c r="BA1" s="104"/>
-      <c r="BB1" s="104"/>
-      <c r="BC1" s="104"/>
-      <c r="BD1" s="104"/>
-      <c r="BE1" s="105"/>
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="108"/>
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
+      <c r="V1" s="108"/>
+      <c r="W1" s="108"/>
+      <c r="X1" s="108"/>
+      <c r="Y1" s="108"/>
+      <c r="Z1" s="108"/>
+      <c r="AA1" s="108"/>
+      <c r="AB1" s="108"/>
+      <c r="AC1" s="108"/>
+      <c r="AD1" s="108"/>
+      <c r="AE1" s="108"/>
+      <c r="AF1" s="108"/>
+      <c r="AG1" s="108"/>
+      <c r="AH1" s="108"/>
+      <c r="AI1" s="108"/>
+      <c r="AJ1" s="108"/>
+      <c r="AK1" s="108"/>
+      <c r="AL1" s="108"/>
+      <c r="AM1" s="108"/>
+      <c r="AN1" s="108"/>
+      <c r="AO1" s="108"/>
+      <c r="AP1" s="108"/>
+      <c r="AQ1" s="108"/>
+      <c r="AR1" s="108"/>
+      <c r="AS1" s="108"/>
+      <c r="AT1" s="108"/>
+      <c r="AU1" s="108"/>
+      <c r="AV1" s="108"/>
+      <c r="AW1" s="108"/>
+      <c r="AX1" s="108"/>
+      <c r="AY1" s="108"/>
+      <c r="AZ1" s="108"/>
+      <c r="BA1" s="108"/>
+      <c r="BB1" s="108"/>
+      <c r="BC1" s="108"/>
+      <c r="BD1" s="108"/>
+      <c r="BE1" s="109"/>
     </row>
     <row r="2" spans="1:57" ht="12" customHeight="1" thickBot="1">
       <c r="A2" s="14"/>
@@ -64924,145 +64924,145 @@
       <c r="AP2" s="14"/>
     </row>
     <row r="3" spans="1:57" ht="15" customHeight="1" thickBot="1">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="120" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="87"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="106" t="s">
+      <c r="B3" s="111"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="111"/>
+      <c r="F3" s="111"/>
+      <c r="G3" s="112"/>
+      <c r="H3" s="110" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="87"/>
-      <c r="J3" s="87"/>
-      <c r="K3" s="87"/>
-      <c r="L3" s="87"/>
-      <c r="M3" s="87"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="106" t="s">
+      <c r="I3" s="111"/>
+      <c r="J3" s="111"/>
+      <c r="K3" s="111"/>
+      <c r="L3" s="111"/>
+      <c r="M3" s="111"/>
+      <c r="N3" s="112"/>
+      <c r="O3" s="110" t="s">
         <v>9</v>
       </c>
-      <c r="P3" s="107"/>
-      <c r="Q3" s="107"/>
-      <c r="R3" s="107"/>
-      <c r="S3" s="107"/>
-      <c r="T3" s="107"/>
-      <c r="U3" s="107"/>
-      <c r="V3" s="107"/>
-      <c r="W3" s="107"/>
-      <c r="X3" s="107"/>
-      <c r="Y3" s="107"/>
-      <c r="Z3" s="107"/>
-      <c r="AA3" s="107"/>
-      <c r="AB3" s="107"/>
-      <c r="AC3" s="107"/>
-      <c r="AD3" s="107"/>
-      <c r="AE3" s="107"/>
-      <c r="AF3" s="107"/>
-      <c r="AG3" s="107"/>
-      <c r="AH3" s="107"/>
-      <c r="AI3" s="107"/>
-      <c r="AJ3" s="107"/>
-      <c r="AK3" s="107"/>
-      <c r="AL3" s="107"/>
-      <c r="AM3" s="107"/>
-      <c r="AN3" s="107"/>
-      <c r="AO3" s="107"/>
-      <c r="AP3" s="108"/>
-      <c r="AQ3" s="106" t="s">
+      <c r="P3" s="113"/>
+      <c r="Q3" s="113"/>
+      <c r="R3" s="113"/>
+      <c r="S3" s="113"/>
+      <c r="T3" s="113"/>
+      <c r="U3" s="113"/>
+      <c r="V3" s="113"/>
+      <c r="W3" s="113"/>
+      <c r="X3" s="113"/>
+      <c r="Y3" s="113"/>
+      <c r="Z3" s="113"/>
+      <c r="AA3" s="113"/>
+      <c r="AB3" s="113"/>
+      <c r="AC3" s="113"/>
+      <c r="AD3" s="113"/>
+      <c r="AE3" s="113"/>
+      <c r="AF3" s="113"/>
+      <c r="AG3" s="113"/>
+      <c r="AH3" s="113"/>
+      <c r="AI3" s="113"/>
+      <c r="AJ3" s="113"/>
+      <c r="AK3" s="113"/>
+      <c r="AL3" s="113"/>
+      <c r="AM3" s="113"/>
+      <c r="AN3" s="113"/>
+      <c r="AO3" s="113"/>
+      <c r="AP3" s="114"/>
+      <c r="AQ3" s="110" t="s">
         <v>10</v>
       </c>
-      <c r="AR3" s="109"/>
-      <c r="AS3" s="109"/>
-      <c r="AT3" s="109"/>
-      <c r="AU3" s="109"/>
-      <c r="AV3" s="109"/>
-      <c r="AW3" s="109"/>
-      <c r="AX3" s="109"/>
-      <c r="AY3" s="109"/>
-      <c r="AZ3" s="109"/>
-      <c r="BA3" s="109"/>
-      <c r="BB3" s="109"/>
-      <c r="BC3" s="109"/>
-      <c r="BD3" s="109"/>
-      <c r="BE3" s="110"/>
+      <c r="AR3" s="115"/>
+      <c r="AS3" s="115"/>
+      <c r="AT3" s="115"/>
+      <c r="AU3" s="115"/>
+      <c r="AV3" s="115"/>
+      <c r="AW3" s="115"/>
+      <c r="AX3" s="115"/>
+      <c r="AY3" s="115"/>
+      <c r="AZ3" s="115"/>
+      <c r="BA3" s="115"/>
+      <c r="BB3" s="115"/>
+      <c r="BC3" s="115"/>
+      <c r="BD3" s="115"/>
+      <c r="BE3" s="116"/>
     </row>
     <row r="4" spans="1:57" ht="15" customHeight="1">
-      <c r="A4" s="111">
+      <c r="A4" s="117">
         <v>1</v>
       </c>
-      <c r="B4" s="112"/>
-      <c r="C4" s="112"/>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="115"/>
-      <c r="L4" s="115"/>
-      <c r="M4" s="115"/>
-      <c r="N4" s="116"/>
-      <c r="O4" s="114" t="s">
+      <c r="B4" s="118"/>
+      <c r="C4" s="118"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="100"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="101"/>
+      <c r="K4" s="101"/>
+      <c r="L4" s="101"/>
+      <c r="M4" s="101"/>
+      <c r="N4" s="102"/>
+      <c r="O4" s="100" t="s">
         <v>11</v>
       </c>
-      <c r="P4" s="117"/>
-      <c r="Q4" s="117"/>
-      <c r="R4" s="117"/>
-      <c r="S4" s="117"/>
-      <c r="T4" s="117"/>
-      <c r="U4" s="117"/>
-      <c r="V4" s="117"/>
-      <c r="W4" s="117"/>
-      <c r="X4" s="117"/>
-      <c r="Y4" s="117"/>
-      <c r="Z4" s="117"/>
-      <c r="AA4" s="117"/>
-      <c r="AB4" s="117"/>
-      <c r="AC4" s="117"/>
-      <c r="AD4" s="117"/>
-      <c r="AE4" s="117"/>
-      <c r="AF4" s="117"/>
-      <c r="AG4" s="117"/>
-      <c r="AH4" s="117"/>
-      <c r="AI4" s="117"/>
-      <c r="AJ4" s="117"/>
-      <c r="AK4" s="117"/>
-      <c r="AL4" s="117"/>
-      <c r="AM4" s="117"/>
-      <c r="AN4" s="117"/>
-      <c r="AO4" s="117"/>
-      <c r="AP4" s="118"/>
-      <c r="AQ4" s="119"/>
-      <c r="AR4" s="117"/>
-      <c r="AS4" s="117"/>
-      <c r="AT4" s="117"/>
-      <c r="AU4" s="117"/>
-      <c r="AV4" s="117"/>
-      <c r="AW4" s="117"/>
-      <c r="AX4" s="117"/>
-      <c r="AY4" s="117"/>
-      <c r="AZ4" s="117"/>
-      <c r="BA4" s="117"/>
-      <c r="BB4" s="117"/>
-      <c r="BC4" s="117"/>
-      <c r="BD4" s="117"/>
-      <c r="BE4" s="120"/>
+      <c r="P4" s="103"/>
+      <c r="Q4" s="103"/>
+      <c r="R4" s="103"/>
+      <c r="S4" s="103"/>
+      <c r="T4" s="103"/>
+      <c r="U4" s="103"/>
+      <c r="V4" s="103"/>
+      <c r="W4" s="103"/>
+      <c r="X4" s="103"/>
+      <c r="Y4" s="103"/>
+      <c r="Z4" s="103"/>
+      <c r="AA4" s="103"/>
+      <c r="AB4" s="103"/>
+      <c r="AC4" s="103"/>
+      <c r="AD4" s="103"/>
+      <c r="AE4" s="103"/>
+      <c r="AF4" s="103"/>
+      <c r="AG4" s="103"/>
+      <c r="AH4" s="103"/>
+      <c r="AI4" s="103"/>
+      <c r="AJ4" s="103"/>
+      <c r="AK4" s="103"/>
+      <c r="AL4" s="103"/>
+      <c r="AM4" s="103"/>
+      <c r="AN4" s="103"/>
+      <c r="AO4" s="103"/>
+      <c r="AP4" s="104"/>
+      <c r="AQ4" s="105"/>
+      <c r="AR4" s="103"/>
+      <c r="AS4" s="103"/>
+      <c r="AT4" s="103"/>
+      <c r="AU4" s="103"/>
+      <c r="AV4" s="103"/>
+      <c r="AW4" s="103"/>
+      <c r="AX4" s="103"/>
+      <c r="AY4" s="103"/>
+      <c r="AZ4" s="103"/>
+      <c r="BA4" s="103"/>
+      <c r="BB4" s="103"/>
+      <c r="BC4" s="103"/>
+      <c r="BD4" s="103"/>
+      <c r="BE4" s="106"/>
     </row>
     <row r="5" spans="1:57" ht="105.75" customHeight="1">
-      <c r="A5" s="100">
+      <c r="A5" s="80">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B5" s="101"/>
-      <c r="C5" s="101"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="101"/>
-      <c r="F5" s="101"/>
-      <c r="G5" s="102"/>
+      <c r="B5" s="81"/>
+      <c r="C5" s="81"/>
+      <c r="D5" s="81"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="82"/>
       <c r="H5" s="83" t="s">
         <v>1804</v>
       </c>
@@ -65075,61 +65075,61 @@
       <c r="O5" s="83" t="s">
         <v>1806</v>
       </c>
-      <c r="P5" s="81"/>
-      <c r="Q5" s="81"/>
-      <c r="R5" s="81"/>
-      <c r="S5" s="81"/>
-      <c r="T5" s="81"/>
-      <c r="U5" s="81"/>
-      <c r="V5" s="81"/>
-      <c r="W5" s="81"/>
-      <c r="X5" s="81"/>
-      <c r="Y5" s="81"/>
-      <c r="Z5" s="81"/>
-      <c r="AA5" s="81"/>
-      <c r="AB5" s="81"/>
-      <c r="AC5" s="81"/>
-      <c r="AD5" s="81"/>
-      <c r="AE5" s="81"/>
-      <c r="AF5" s="81"/>
-      <c r="AG5" s="81"/>
-      <c r="AH5" s="81"/>
-      <c r="AI5" s="81"/>
-      <c r="AJ5" s="81"/>
-      <c r="AK5" s="81"/>
-      <c r="AL5" s="81"/>
-      <c r="AM5" s="81"/>
-      <c r="AN5" s="81"/>
-      <c r="AO5" s="81"/>
-      <c r="AP5" s="89"/>
-      <c r="AQ5" s="80" t="s">
+      <c r="P5" s="86"/>
+      <c r="Q5" s="86"/>
+      <c r="R5" s="86"/>
+      <c r="S5" s="86"/>
+      <c r="T5" s="86"/>
+      <c r="U5" s="86"/>
+      <c r="V5" s="86"/>
+      <c r="W5" s="86"/>
+      <c r="X5" s="86"/>
+      <c r="Y5" s="86"/>
+      <c r="Z5" s="86"/>
+      <c r="AA5" s="86"/>
+      <c r="AB5" s="86"/>
+      <c r="AC5" s="86"/>
+      <c r="AD5" s="86"/>
+      <c r="AE5" s="86"/>
+      <c r="AF5" s="86"/>
+      <c r="AG5" s="86"/>
+      <c r="AH5" s="86"/>
+      <c r="AI5" s="86"/>
+      <c r="AJ5" s="86"/>
+      <c r="AK5" s="86"/>
+      <c r="AL5" s="86"/>
+      <c r="AM5" s="86"/>
+      <c r="AN5" s="86"/>
+      <c r="AO5" s="86"/>
+      <c r="AP5" s="87"/>
+      <c r="AQ5" s="91" t="s">
         <v>1805</v>
       </c>
-      <c r="AR5" s="81"/>
-      <c r="AS5" s="81"/>
-      <c r="AT5" s="81"/>
-      <c r="AU5" s="81"/>
-      <c r="AV5" s="81"/>
-      <c r="AW5" s="81"/>
-      <c r="AX5" s="81"/>
-      <c r="AY5" s="81"/>
-      <c r="AZ5" s="81"/>
-      <c r="BA5" s="81"/>
-      <c r="BB5" s="81"/>
-      <c r="BC5" s="81"/>
-      <c r="BD5" s="81"/>
-      <c r="BE5" s="82"/>
+      <c r="AR5" s="86"/>
+      <c r="AS5" s="86"/>
+      <c r="AT5" s="86"/>
+      <c r="AU5" s="86"/>
+      <c r="AV5" s="86"/>
+      <c r="AW5" s="86"/>
+      <c r="AX5" s="86"/>
+      <c r="AY5" s="86"/>
+      <c r="AZ5" s="86"/>
+      <c r="BA5" s="86"/>
+      <c r="BB5" s="86"/>
+      <c r="BC5" s="86"/>
+      <c r="BD5" s="86"/>
+      <c r="BE5" s="92"/>
     </row>
     <row r="6" spans="1:57" ht="36.6" customHeight="1">
-      <c r="A6" s="100">
+      <c r="A6" s="80">
         <v>1.2</v>
       </c>
-      <c r="B6" s="101"/>
-      <c r="C6" s="101"/>
-      <c r="D6" s="101"/>
-      <c r="E6" s="101"/>
-      <c r="F6" s="101"/>
-      <c r="G6" s="102"/>
+      <c r="B6" s="81"/>
+      <c r="C6" s="81"/>
+      <c r="D6" s="81"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="82"/>
       <c r="H6" s="83" t="s">
         <v>1832</v>
       </c>
@@ -65142,124 +65142,124 @@
       <c r="O6" s="83" t="s">
         <v>1831</v>
       </c>
-      <c r="P6" s="90"/>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90"/>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
-      <c r="V6" s="90"/>
-      <c r="W6" s="90"/>
-      <c r="X6" s="90"/>
-      <c r="Y6" s="90"/>
-      <c r="Z6" s="90"/>
-      <c r="AA6" s="90"/>
-      <c r="AB6" s="90"/>
-      <c r="AC6" s="90"/>
-      <c r="AD6" s="90"/>
-      <c r="AE6" s="90"/>
-      <c r="AF6" s="90"/>
-      <c r="AG6" s="90"/>
-      <c r="AH6" s="90"/>
-      <c r="AI6" s="90"/>
-      <c r="AJ6" s="90"/>
-      <c r="AK6" s="90"/>
-      <c r="AL6" s="90"/>
-      <c r="AM6" s="90"/>
-      <c r="AN6" s="90"/>
-      <c r="AO6" s="90"/>
-      <c r="AP6" s="91"/>
-      <c r="AQ6" s="80" t="s">
+      <c r="P6" s="121"/>
+      <c r="Q6" s="121"/>
+      <c r="R6" s="121"/>
+      <c r="S6" s="121"/>
+      <c r="T6" s="121"/>
+      <c r="U6" s="121"/>
+      <c r="V6" s="121"/>
+      <c r="W6" s="121"/>
+      <c r="X6" s="121"/>
+      <c r="Y6" s="121"/>
+      <c r="Z6" s="121"/>
+      <c r="AA6" s="121"/>
+      <c r="AB6" s="121"/>
+      <c r="AC6" s="121"/>
+      <c r="AD6" s="121"/>
+      <c r="AE6" s="121"/>
+      <c r="AF6" s="121"/>
+      <c r="AG6" s="121"/>
+      <c r="AH6" s="121"/>
+      <c r="AI6" s="121"/>
+      <c r="AJ6" s="121"/>
+      <c r="AK6" s="121"/>
+      <c r="AL6" s="121"/>
+      <c r="AM6" s="121"/>
+      <c r="AN6" s="121"/>
+      <c r="AO6" s="121"/>
+      <c r="AP6" s="122"/>
+      <c r="AQ6" s="91" t="s">
         <v>1805</v>
       </c>
-      <c r="AR6" s="81"/>
-      <c r="AS6" s="81"/>
-      <c r="AT6" s="81"/>
-      <c r="AU6" s="81"/>
-      <c r="AV6" s="81"/>
-      <c r="AW6" s="81"/>
-      <c r="AX6" s="81"/>
-      <c r="AY6" s="81"/>
-      <c r="AZ6" s="81"/>
-      <c r="BA6" s="81"/>
-      <c r="BB6" s="81"/>
-      <c r="BC6" s="81"/>
-      <c r="BD6" s="81"/>
-      <c r="BE6" s="82"/>
+      <c r="AR6" s="86"/>
+      <c r="AS6" s="86"/>
+      <c r="AT6" s="86"/>
+      <c r="AU6" s="86"/>
+      <c r="AV6" s="86"/>
+      <c r="AW6" s="86"/>
+      <c r="AX6" s="86"/>
+      <c r="AY6" s="86"/>
+      <c r="AZ6" s="86"/>
+      <c r="BA6" s="86"/>
+      <c r="BB6" s="86"/>
+      <c r="BC6" s="86"/>
+      <c r="BD6" s="86"/>
+      <c r="BE6" s="92"/>
     </row>
     <row r="7" spans="1:57" ht="15" customHeight="1">
-      <c r="A7" s="100">
+      <c r="A7" s="80">
         <v>1.3</v>
       </c>
-      <c r="B7" s="101"/>
-      <c r="C7" s="101"/>
-      <c r="D7" s="101"/>
-      <c r="E7" s="101"/>
-      <c r="F7" s="101"/>
-      <c r="G7" s="102"/>
+      <c r="B7" s="81"/>
+      <c r="C7" s="81"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="82"/>
       <c r="H7" s="83"/>
-      <c r="I7" s="92"/>
-      <c r="J7" s="92"/>
-      <c r="K7" s="92"/>
-      <c r="L7" s="92"/>
-      <c r="M7" s="92"/>
-      <c r="N7" s="93"/>
-      <c r="O7" s="94" t="s">
+      <c r="I7" s="123"/>
+      <c r="J7" s="123"/>
+      <c r="K7" s="123"/>
+      <c r="L7" s="123"/>
+      <c r="M7" s="123"/>
+      <c r="N7" s="124"/>
+      <c r="O7" s="125" t="s">
         <v>2245</v>
       </c>
-      <c r="P7" s="95"/>
-      <c r="Q7" s="95"/>
-      <c r="R7" s="95"/>
-      <c r="S7" s="95"/>
-      <c r="T7" s="95"/>
-      <c r="U7" s="95"/>
-      <c r="V7" s="95"/>
-      <c r="W7" s="95"/>
-      <c r="X7" s="95"/>
-      <c r="Y7" s="95"/>
-      <c r="Z7" s="95"/>
-      <c r="AA7" s="95"/>
-      <c r="AB7" s="95"/>
-      <c r="AC7" s="95"/>
-      <c r="AD7" s="95"/>
-      <c r="AE7" s="95"/>
-      <c r="AF7" s="95"/>
-      <c r="AG7" s="95"/>
-      <c r="AH7" s="95"/>
-      <c r="AI7" s="95"/>
-      <c r="AJ7" s="95"/>
-      <c r="AK7" s="95"/>
-      <c r="AL7" s="95"/>
-      <c r="AM7" s="95"/>
-      <c r="AN7" s="95"/>
-      <c r="AO7" s="95"/>
-      <c r="AP7" s="96"/>
-      <c r="AQ7" s="97" t="s">
+      <c r="P7" s="126"/>
+      <c r="Q7" s="126"/>
+      <c r="R7" s="126"/>
+      <c r="S7" s="126"/>
+      <c r="T7" s="126"/>
+      <c r="U7" s="126"/>
+      <c r="V7" s="126"/>
+      <c r="W7" s="126"/>
+      <c r="X7" s="126"/>
+      <c r="Y7" s="126"/>
+      <c r="Z7" s="126"/>
+      <c r="AA7" s="126"/>
+      <c r="AB7" s="126"/>
+      <c r="AC7" s="126"/>
+      <c r="AD7" s="126"/>
+      <c r="AE7" s="126"/>
+      <c r="AF7" s="126"/>
+      <c r="AG7" s="126"/>
+      <c r="AH7" s="126"/>
+      <c r="AI7" s="126"/>
+      <c r="AJ7" s="126"/>
+      <c r="AK7" s="126"/>
+      <c r="AL7" s="126"/>
+      <c r="AM7" s="126"/>
+      <c r="AN7" s="126"/>
+      <c r="AO7" s="126"/>
+      <c r="AP7" s="127"/>
+      <c r="AQ7" s="128" t="s">
         <v>2246</v>
       </c>
-      <c r="AR7" s="98"/>
-      <c r="AS7" s="98"/>
-      <c r="AT7" s="98"/>
-      <c r="AU7" s="98"/>
-      <c r="AV7" s="98"/>
-      <c r="AW7" s="98"/>
-      <c r="AX7" s="98"/>
-      <c r="AY7" s="98"/>
-      <c r="AZ7" s="98"/>
-      <c r="BA7" s="98"/>
-      <c r="BB7" s="98"/>
-      <c r="BC7" s="98"/>
-      <c r="BD7" s="98"/>
-      <c r="BE7" s="99"/>
+      <c r="AR7" s="129"/>
+      <c r="AS7" s="129"/>
+      <c r="AT7" s="129"/>
+      <c r="AU7" s="129"/>
+      <c r="AV7" s="129"/>
+      <c r="AW7" s="129"/>
+      <c r="AX7" s="129"/>
+      <c r="AY7" s="129"/>
+      <c r="AZ7" s="129"/>
+      <c r="BA7" s="129"/>
+      <c r="BB7" s="129"/>
+      <c r="BC7" s="129"/>
+      <c r="BD7" s="129"/>
+      <c r="BE7" s="130"/>
     </row>
     <row r="8" spans="1:57" ht="15" customHeight="1">
-      <c r="A8" s="100"/>
-      <c r="B8" s="101"/>
-      <c r="C8" s="101"/>
-      <c r="D8" s="101"/>
-      <c r="E8" s="101"/>
-      <c r="F8" s="101"/>
-      <c r="G8" s="102"/>
+      <c r="A8" s="80"/>
+      <c r="B8" s="81"/>
+      <c r="C8" s="81"/>
+      <c r="D8" s="81"/>
+      <c r="E8" s="81"/>
+      <c r="F8" s="81"/>
+      <c r="G8" s="82"/>
       <c r="H8" s="83"/>
       <c r="I8" s="84"/>
       <c r="J8" s="84"/>
@@ -65268,57 +65268,57 @@
       <c r="M8" s="84"/>
       <c r="N8" s="85"/>
       <c r="O8" s="83"/>
-      <c r="P8" s="81"/>
-      <c r="Q8" s="81"/>
-      <c r="R8" s="81"/>
-      <c r="S8" s="81"/>
-      <c r="T8" s="81"/>
-      <c r="U8" s="81"/>
-      <c r="V8" s="81"/>
-      <c r="W8" s="81"/>
-      <c r="X8" s="81"/>
-      <c r="Y8" s="81"/>
-      <c r="Z8" s="81"/>
-      <c r="AA8" s="81"/>
-      <c r="AB8" s="81"/>
-      <c r="AC8" s="81"/>
-      <c r="AD8" s="81"/>
-      <c r="AE8" s="81"/>
-      <c r="AF8" s="81"/>
-      <c r="AG8" s="81"/>
-      <c r="AH8" s="81"/>
-      <c r="AI8" s="81"/>
-      <c r="AJ8" s="81"/>
-      <c r="AK8" s="81"/>
-      <c r="AL8" s="81"/>
-      <c r="AM8" s="81"/>
-      <c r="AN8" s="81"/>
-      <c r="AO8" s="81"/>
-      <c r="AP8" s="89"/>
-      <c r="AQ8" s="80"/>
-      <c r="AR8" s="81"/>
-      <c r="AS8" s="81"/>
-      <c r="AT8" s="81"/>
-      <c r="AU8" s="81"/>
-      <c r="AV8" s="81"/>
-      <c r="AW8" s="81"/>
-      <c r="AX8" s="81"/>
-      <c r="AY8" s="81"/>
-      <c r="AZ8" s="81"/>
-      <c r="BA8" s="81"/>
-      <c r="BB8" s="81"/>
-      <c r="BC8" s="81"/>
-      <c r="BD8" s="81"/>
-      <c r="BE8" s="82"/>
+      <c r="P8" s="86"/>
+      <c r="Q8" s="86"/>
+      <c r="R8" s="86"/>
+      <c r="S8" s="86"/>
+      <c r="T8" s="86"/>
+      <c r="U8" s="86"/>
+      <c r="V8" s="86"/>
+      <c r="W8" s="86"/>
+      <c r="X8" s="86"/>
+      <c r="Y8" s="86"/>
+      <c r="Z8" s="86"/>
+      <c r="AA8" s="86"/>
+      <c r="AB8" s="86"/>
+      <c r="AC8" s="86"/>
+      <c r="AD8" s="86"/>
+      <c r="AE8" s="86"/>
+      <c r="AF8" s="86"/>
+      <c r="AG8" s="86"/>
+      <c r="AH8" s="86"/>
+      <c r="AI8" s="86"/>
+      <c r="AJ8" s="86"/>
+      <c r="AK8" s="86"/>
+      <c r="AL8" s="86"/>
+      <c r="AM8" s="86"/>
+      <c r="AN8" s="86"/>
+      <c r="AO8" s="86"/>
+      <c r="AP8" s="87"/>
+      <c r="AQ8" s="91"/>
+      <c r="AR8" s="86"/>
+      <c r="AS8" s="86"/>
+      <c r="AT8" s="86"/>
+      <c r="AU8" s="86"/>
+      <c r="AV8" s="86"/>
+      <c r="AW8" s="86"/>
+      <c r="AX8" s="86"/>
+      <c r="AY8" s="86"/>
+      <c r="AZ8" s="86"/>
+      <c r="BA8" s="86"/>
+      <c r="BB8" s="86"/>
+      <c r="BC8" s="86"/>
+      <c r="BD8" s="86"/>
+      <c r="BE8" s="92"/>
     </row>
     <row r="9" spans="1:57" ht="15" customHeight="1">
-      <c r="A9" s="100"/>
-      <c r="B9" s="101"/>
-      <c r="C9" s="101"/>
-      <c r="D9" s="101"/>
-      <c r="E9" s="101"/>
-      <c r="F9" s="101"/>
-      <c r="G9" s="102"/>
+      <c r="A9" s="80"/>
+      <c r="B9" s="81"/>
+      <c r="C9" s="81"/>
+      <c r="D9" s="81"/>
+      <c r="E9" s="81"/>
+      <c r="F9" s="81"/>
+      <c r="G9" s="82"/>
       <c r="H9" s="83"/>
       <c r="I9" s="84"/>
       <c r="J9" s="84"/>
@@ -65327,57 +65327,57 @@
       <c r="M9" s="84"/>
       <c r="N9" s="85"/>
       <c r="O9" s="83"/>
-      <c r="P9" s="81"/>
-      <c r="Q9" s="81"/>
-      <c r="R9" s="81"/>
-      <c r="S9" s="81"/>
-      <c r="T9" s="81"/>
-      <c r="U9" s="81"/>
-      <c r="V9" s="81"/>
-      <c r="W9" s="81"/>
-      <c r="X9" s="81"/>
-      <c r="Y9" s="81"/>
-      <c r="Z9" s="81"/>
-      <c r="AA9" s="81"/>
-      <c r="AB9" s="81"/>
-      <c r="AC9" s="81"/>
-      <c r="AD9" s="81"/>
-      <c r="AE9" s="81"/>
-      <c r="AF9" s="81"/>
-      <c r="AG9" s="81"/>
-      <c r="AH9" s="81"/>
-      <c r="AI9" s="81"/>
-      <c r="AJ9" s="81"/>
-      <c r="AK9" s="81"/>
-      <c r="AL9" s="81"/>
-      <c r="AM9" s="81"/>
-      <c r="AN9" s="81"/>
-      <c r="AO9" s="81"/>
-      <c r="AP9" s="89"/>
-      <c r="AQ9" s="80"/>
-      <c r="AR9" s="81"/>
-      <c r="AS9" s="81"/>
-      <c r="AT9" s="81"/>
-      <c r="AU9" s="81"/>
-      <c r="AV9" s="81"/>
-      <c r="AW9" s="81"/>
-      <c r="AX9" s="81"/>
-      <c r="AY9" s="81"/>
-      <c r="AZ9" s="81"/>
-      <c r="BA9" s="81"/>
-      <c r="BB9" s="81"/>
-      <c r="BC9" s="81"/>
-      <c r="BD9" s="81"/>
-      <c r="BE9" s="82"/>
+      <c r="P9" s="86"/>
+      <c r="Q9" s="86"/>
+      <c r="R9" s="86"/>
+      <c r="S9" s="86"/>
+      <c r="T9" s="86"/>
+      <c r="U9" s="86"/>
+      <c r="V9" s="86"/>
+      <c r="W9" s="86"/>
+      <c r="X9" s="86"/>
+      <c r="Y9" s="86"/>
+      <c r="Z9" s="86"/>
+      <c r="AA9" s="86"/>
+      <c r="AB9" s="86"/>
+      <c r="AC9" s="86"/>
+      <c r="AD9" s="86"/>
+      <c r="AE9" s="86"/>
+      <c r="AF9" s="86"/>
+      <c r="AG9" s="86"/>
+      <c r="AH9" s="86"/>
+      <c r="AI9" s="86"/>
+      <c r="AJ9" s="86"/>
+      <c r="AK9" s="86"/>
+      <c r="AL9" s="86"/>
+      <c r="AM9" s="86"/>
+      <c r="AN9" s="86"/>
+      <c r="AO9" s="86"/>
+      <c r="AP9" s="87"/>
+      <c r="AQ9" s="91"/>
+      <c r="AR9" s="86"/>
+      <c r="AS9" s="86"/>
+      <c r="AT9" s="86"/>
+      <c r="AU9" s="86"/>
+      <c r="AV9" s="86"/>
+      <c r="AW9" s="86"/>
+      <c r="AX9" s="86"/>
+      <c r="AY9" s="86"/>
+      <c r="AZ9" s="86"/>
+      <c r="BA9" s="86"/>
+      <c r="BB9" s="86"/>
+      <c r="BC9" s="86"/>
+      <c r="BD9" s="86"/>
+      <c r="BE9" s="92"/>
     </row>
     <row r="10" spans="1:57" ht="15" customHeight="1">
-      <c r="A10" s="100"/>
-      <c r="B10" s="101"/>
-      <c r="C10" s="101"/>
-      <c r="D10" s="101"/>
-      <c r="E10" s="101"/>
-      <c r="F10" s="101"/>
-      <c r="G10" s="102"/>
+      <c r="A10" s="80"/>
+      <c r="B10" s="81"/>
+      <c r="C10" s="81"/>
+      <c r="D10" s="81"/>
+      <c r="E10" s="81"/>
+      <c r="F10" s="81"/>
+      <c r="G10" s="82"/>
       <c r="H10" s="83"/>
       <c r="I10" s="84"/>
       <c r="J10" s="84"/>
@@ -65386,57 +65386,57 @@
       <c r="M10" s="84"/>
       <c r="N10" s="85"/>
       <c r="O10" s="83"/>
-      <c r="P10" s="81"/>
-      <c r="Q10" s="81"/>
-      <c r="R10" s="81"/>
-      <c r="S10" s="81"/>
-      <c r="T10" s="81"/>
-      <c r="U10" s="81"/>
-      <c r="V10" s="81"/>
-      <c r="W10" s="81"/>
-      <c r="X10" s="81"/>
-      <c r="Y10" s="81"/>
-      <c r="Z10" s="81"/>
-      <c r="AA10" s="81"/>
-      <c r="AB10" s="81"/>
-      <c r="AC10" s="81"/>
-      <c r="AD10" s="81"/>
-      <c r="AE10" s="81"/>
-      <c r="AF10" s="81"/>
-      <c r="AG10" s="81"/>
-      <c r="AH10" s="81"/>
-      <c r="AI10" s="81"/>
-      <c r="AJ10" s="81"/>
-      <c r="AK10" s="81"/>
-      <c r="AL10" s="81"/>
-      <c r="AM10" s="81"/>
-      <c r="AN10" s="81"/>
-      <c r="AO10" s="81"/>
-      <c r="AP10" s="89"/>
-      <c r="AQ10" s="80"/>
-      <c r="AR10" s="81"/>
-      <c r="AS10" s="81"/>
-      <c r="AT10" s="81"/>
-      <c r="AU10" s="81"/>
-      <c r="AV10" s="81"/>
-      <c r="AW10" s="81"/>
-      <c r="AX10" s="81"/>
-      <c r="AY10" s="81"/>
-      <c r="AZ10" s="81"/>
-      <c r="BA10" s="81"/>
-      <c r="BB10" s="81"/>
-      <c r="BC10" s="81"/>
-      <c r="BD10" s="81"/>
-      <c r="BE10" s="82"/>
+      <c r="P10" s="86"/>
+      <c r="Q10" s="86"/>
+      <c r="R10" s="86"/>
+      <c r="S10" s="86"/>
+      <c r="T10" s="86"/>
+      <c r="U10" s="86"/>
+      <c r="V10" s="86"/>
+      <c r="W10" s="86"/>
+      <c r="X10" s="86"/>
+      <c r="Y10" s="86"/>
+      <c r="Z10" s="86"/>
+      <c r="AA10" s="86"/>
+      <c r="AB10" s="86"/>
+      <c r="AC10" s="86"/>
+      <c r="AD10" s="86"/>
+      <c r="AE10" s="86"/>
+      <c r="AF10" s="86"/>
+      <c r="AG10" s="86"/>
+      <c r="AH10" s="86"/>
+      <c r="AI10" s="86"/>
+      <c r="AJ10" s="86"/>
+      <c r="AK10" s="86"/>
+      <c r="AL10" s="86"/>
+      <c r="AM10" s="86"/>
+      <c r="AN10" s="86"/>
+      <c r="AO10" s="86"/>
+      <c r="AP10" s="87"/>
+      <c r="AQ10" s="91"/>
+      <c r="AR10" s="86"/>
+      <c r="AS10" s="86"/>
+      <c r="AT10" s="86"/>
+      <c r="AU10" s="86"/>
+      <c r="AV10" s="86"/>
+      <c r="AW10" s="86"/>
+      <c r="AX10" s="86"/>
+      <c r="AY10" s="86"/>
+      <c r="AZ10" s="86"/>
+      <c r="BA10" s="86"/>
+      <c r="BB10" s="86"/>
+      <c r="BC10" s="86"/>
+      <c r="BD10" s="86"/>
+      <c r="BE10" s="92"/>
     </row>
     <row r="11" spans="1:57" ht="15" customHeight="1">
-      <c r="A11" s="100"/>
-      <c r="B11" s="101"/>
-      <c r="C11" s="101"/>
-      <c r="D11" s="101"/>
-      <c r="E11" s="101"/>
-      <c r="F11" s="101"/>
-      <c r="G11" s="102"/>
+      <c r="A11" s="80"/>
+      <c r="B11" s="81"/>
+      <c r="C11" s="81"/>
+      <c r="D11" s="81"/>
+      <c r="E11" s="81"/>
+      <c r="F11" s="81"/>
+      <c r="G11" s="82"/>
       <c r="H11" s="83"/>
       <c r="I11" s="84"/>
       <c r="J11" s="84"/>
@@ -65445,57 +65445,57 @@
       <c r="M11" s="84"/>
       <c r="N11" s="85"/>
       <c r="O11" s="83"/>
-      <c r="P11" s="81"/>
-      <c r="Q11" s="81"/>
-      <c r="R11" s="81"/>
-      <c r="S11" s="81"/>
-      <c r="T11" s="81"/>
-      <c r="U11" s="81"/>
-      <c r="V11" s="81"/>
-      <c r="W11" s="81"/>
-      <c r="X11" s="81"/>
-      <c r="Y11" s="81"/>
-      <c r="Z11" s="81"/>
-      <c r="AA11" s="81"/>
-      <c r="AB11" s="81"/>
-      <c r="AC11" s="81"/>
-      <c r="AD11" s="81"/>
-      <c r="AE11" s="81"/>
-      <c r="AF11" s="81"/>
-      <c r="AG11" s="81"/>
-      <c r="AH11" s="81"/>
-      <c r="AI11" s="81"/>
-      <c r="AJ11" s="81"/>
-      <c r="AK11" s="81"/>
-      <c r="AL11" s="81"/>
-      <c r="AM11" s="81"/>
-      <c r="AN11" s="81"/>
-      <c r="AO11" s="81"/>
-      <c r="AP11" s="89"/>
-      <c r="AQ11" s="80"/>
-      <c r="AR11" s="81"/>
-      <c r="AS11" s="81"/>
-      <c r="AT11" s="81"/>
-      <c r="AU11" s="81"/>
-      <c r="AV11" s="81"/>
-      <c r="AW11" s="81"/>
-      <c r="AX11" s="81"/>
-      <c r="AY11" s="81"/>
-      <c r="AZ11" s="81"/>
-      <c r="BA11" s="81"/>
-      <c r="BB11" s="81"/>
-      <c r="BC11" s="81"/>
-      <c r="BD11" s="81"/>
-      <c r="BE11" s="82"/>
+      <c r="P11" s="86"/>
+      <c r="Q11" s="86"/>
+      <c r="R11" s="86"/>
+      <c r="S11" s="86"/>
+      <c r="T11" s="86"/>
+      <c r="U11" s="86"/>
+      <c r="V11" s="86"/>
+      <c r="W11" s="86"/>
+      <c r="X11" s="86"/>
+      <c r="Y11" s="86"/>
+      <c r="Z11" s="86"/>
+      <c r="AA11" s="86"/>
+      <c r="AB11" s="86"/>
+      <c r="AC11" s="86"/>
+      <c r="AD11" s="86"/>
+      <c r="AE11" s="86"/>
+      <c r="AF11" s="86"/>
+      <c r="AG11" s="86"/>
+      <c r="AH11" s="86"/>
+      <c r="AI11" s="86"/>
+      <c r="AJ11" s="86"/>
+      <c r="AK11" s="86"/>
+      <c r="AL11" s="86"/>
+      <c r="AM11" s="86"/>
+      <c r="AN11" s="86"/>
+      <c r="AO11" s="86"/>
+      <c r="AP11" s="87"/>
+      <c r="AQ11" s="91"/>
+      <c r="AR11" s="86"/>
+      <c r="AS11" s="86"/>
+      <c r="AT11" s="86"/>
+      <c r="AU11" s="86"/>
+      <c r="AV11" s="86"/>
+      <c r="AW11" s="86"/>
+      <c r="AX11" s="86"/>
+      <c r="AY11" s="86"/>
+      <c r="AZ11" s="86"/>
+      <c r="BA11" s="86"/>
+      <c r="BB11" s="86"/>
+      <c r="BC11" s="86"/>
+      <c r="BD11" s="86"/>
+      <c r="BE11" s="92"/>
     </row>
     <row r="12" spans="1:57" ht="15" customHeight="1">
-      <c r="A12" s="100"/>
-      <c r="B12" s="101"/>
-      <c r="C12" s="101"/>
-      <c r="D12" s="101"/>
-      <c r="E12" s="101"/>
-      <c r="F12" s="101"/>
-      <c r="G12" s="102"/>
+      <c r="A12" s="80"/>
+      <c r="B12" s="81"/>
+      <c r="C12" s="81"/>
+      <c r="D12" s="81"/>
+      <c r="E12" s="81"/>
+      <c r="F12" s="81"/>
+      <c r="G12" s="82"/>
       <c r="H12" s="83"/>
       <c r="I12" s="84"/>
       <c r="J12" s="84"/>
@@ -65504,57 +65504,57 @@
       <c r="M12" s="84"/>
       <c r="N12" s="85"/>
       <c r="O12" s="83"/>
-      <c r="P12" s="81"/>
-      <c r="Q12" s="81"/>
-      <c r="R12" s="81"/>
-      <c r="S12" s="81"/>
-      <c r="T12" s="81"/>
-      <c r="U12" s="81"/>
-      <c r="V12" s="81"/>
-      <c r="W12" s="81"/>
-      <c r="X12" s="81"/>
-      <c r="Y12" s="81"/>
-      <c r="Z12" s="81"/>
-      <c r="AA12" s="81"/>
-      <c r="AB12" s="81"/>
-      <c r="AC12" s="81"/>
-      <c r="AD12" s="81"/>
-      <c r="AE12" s="81"/>
-      <c r="AF12" s="81"/>
-      <c r="AG12" s="81"/>
-      <c r="AH12" s="81"/>
-      <c r="AI12" s="81"/>
-      <c r="AJ12" s="81"/>
-      <c r="AK12" s="81"/>
-      <c r="AL12" s="81"/>
-      <c r="AM12" s="81"/>
-      <c r="AN12" s="81"/>
-      <c r="AO12" s="81"/>
-      <c r="AP12" s="89"/>
-      <c r="AQ12" s="80"/>
-      <c r="AR12" s="81"/>
-      <c r="AS12" s="81"/>
-      <c r="AT12" s="81"/>
-      <c r="AU12" s="81"/>
-      <c r="AV12" s="81"/>
-      <c r="AW12" s="81"/>
-      <c r="AX12" s="81"/>
-      <c r="AY12" s="81"/>
-      <c r="AZ12" s="81"/>
-      <c r="BA12" s="81"/>
-      <c r="BB12" s="81"/>
-      <c r="BC12" s="81"/>
-      <c r="BD12" s="81"/>
-      <c r="BE12" s="82"/>
+      <c r="P12" s="86"/>
+      <c r="Q12" s="86"/>
+      <c r="R12" s="86"/>
+      <c r="S12" s="86"/>
+      <c r="T12" s="86"/>
+      <c r="U12" s="86"/>
+      <c r="V12" s="86"/>
+      <c r="W12" s="86"/>
+      <c r="X12" s="86"/>
+      <c r="Y12" s="86"/>
+      <c r="Z12" s="86"/>
+      <c r="AA12" s="86"/>
+      <c r="AB12" s="86"/>
+      <c r="AC12" s="86"/>
+      <c r="AD12" s="86"/>
+      <c r="AE12" s="86"/>
+      <c r="AF12" s="86"/>
+      <c r="AG12" s="86"/>
+      <c r="AH12" s="86"/>
+      <c r="AI12" s="86"/>
+      <c r="AJ12" s="86"/>
+      <c r="AK12" s="86"/>
+      <c r="AL12" s="86"/>
+      <c r="AM12" s="86"/>
+      <c r="AN12" s="86"/>
+      <c r="AO12" s="86"/>
+      <c r="AP12" s="87"/>
+      <c r="AQ12" s="91"/>
+      <c r="AR12" s="86"/>
+      <c r="AS12" s="86"/>
+      <c r="AT12" s="86"/>
+      <c r="AU12" s="86"/>
+      <c r="AV12" s="86"/>
+      <c r="AW12" s="86"/>
+      <c r="AX12" s="86"/>
+      <c r="AY12" s="86"/>
+      <c r="AZ12" s="86"/>
+      <c r="BA12" s="86"/>
+      <c r="BB12" s="86"/>
+      <c r="BC12" s="86"/>
+      <c r="BD12" s="86"/>
+      <c r="BE12" s="92"/>
     </row>
     <row r="13" spans="1:57" ht="15" customHeight="1">
-      <c r="A13" s="100"/>
-      <c r="B13" s="101"/>
-      <c r="C13" s="101"/>
-      <c r="D13" s="101"/>
-      <c r="E13" s="101"/>
-      <c r="F13" s="101"/>
-      <c r="G13" s="102"/>
+      <c r="A13" s="80"/>
+      <c r="B13" s="81"/>
+      <c r="C13" s="81"/>
+      <c r="D13" s="81"/>
+      <c r="E13" s="81"/>
+      <c r="F13" s="81"/>
+      <c r="G13" s="82"/>
       <c r="H13" s="83"/>
       <c r="I13" s="84"/>
       <c r="J13" s="84"/>
@@ -65563,57 +65563,57 @@
       <c r="M13" s="84"/>
       <c r="N13" s="85"/>
       <c r="O13" s="83"/>
-      <c r="P13" s="81"/>
-      <c r="Q13" s="81"/>
-      <c r="R13" s="81"/>
-      <c r="S13" s="81"/>
-      <c r="T13" s="81"/>
-      <c r="U13" s="81"/>
-      <c r="V13" s="81"/>
-      <c r="W13" s="81"/>
-      <c r="X13" s="81"/>
-      <c r="Y13" s="81"/>
-      <c r="Z13" s="81"/>
-      <c r="AA13" s="81"/>
-      <c r="AB13" s="81"/>
-      <c r="AC13" s="81"/>
-      <c r="AD13" s="81"/>
-      <c r="AE13" s="81"/>
-      <c r="AF13" s="81"/>
-      <c r="AG13" s="81"/>
-      <c r="AH13" s="81"/>
-      <c r="AI13" s="81"/>
-      <c r="AJ13" s="81"/>
-      <c r="AK13" s="81"/>
-      <c r="AL13" s="81"/>
-      <c r="AM13" s="81"/>
-      <c r="AN13" s="81"/>
-      <c r="AO13" s="81"/>
-      <c r="AP13" s="89"/>
-      <c r="AQ13" s="80"/>
-      <c r="AR13" s="81"/>
-      <c r="AS13" s="81"/>
-      <c r="AT13" s="81"/>
-      <c r="AU13" s="81"/>
-      <c r="AV13" s="81"/>
-      <c r="AW13" s="81"/>
-      <c r="AX13" s="81"/>
-      <c r="AY13" s="81"/>
-      <c r="AZ13" s="81"/>
-      <c r="BA13" s="81"/>
-      <c r="BB13" s="81"/>
-      <c r="BC13" s="81"/>
-      <c r="BD13" s="81"/>
-      <c r="BE13" s="82"/>
+      <c r="P13" s="86"/>
+      <c r="Q13" s="86"/>
+      <c r="R13" s="86"/>
+      <c r="S13" s="86"/>
+      <c r="T13" s="86"/>
+      <c r="U13" s="86"/>
+      <c r="V13" s="86"/>
+      <c r="W13" s="86"/>
+      <c r="X13" s="86"/>
+      <c r="Y13" s="86"/>
+      <c r="Z13" s="86"/>
+      <c r="AA13" s="86"/>
+      <c r="AB13" s="86"/>
+      <c r="AC13" s="86"/>
+      <c r="AD13" s="86"/>
+      <c r="AE13" s="86"/>
+      <c r="AF13" s="86"/>
+      <c r="AG13" s="86"/>
+      <c r="AH13" s="86"/>
+      <c r="AI13" s="86"/>
+      <c r="AJ13" s="86"/>
+      <c r="AK13" s="86"/>
+      <c r="AL13" s="86"/>
+      <c r="AM13" s="86"/>
+      <c r="AN13" s="86"/>
+      <c r="AO13" s="86"/>
+      <c r="AP13" s="87"/>
+      <c r="AQ13" s="91"/>
+      <c r="AR13" s="86"/>
+      <c r="AS13" s="86"/>
+      <c r="AT13" s="86"/>
+      <c r="AU13" s="86"/>
+      <c r="AV13" s="86"/>
+      <c r="AW13" s="86"/>
+      <c r="AX13" s="86"/>
+      <c r="AY13" s="86"/>
+      <c r="AZ13" s="86"/>
+      <c r="BA13" s="86"/>
+      <c r="BB13" s="86"/>
+      <c r="BC13" s="86"/>
+      <c r="BD13" s="86"/>
+      <c r="BE13" s="92"/>
     </row>
     <row r="14" spans="1:57" ht="15" customHeight="1">
-      <c r="A14" s="100"/>
-      <c r="B14" s="101"/>
-      <c r="C14" s="101"/>
-      <c r="D14" s="101"/>
-      <c r="E14" s="101"/>
-      <c r="F14" s="101"/>
-      <c r="G14" s="102"/>
+      <c r="A14" s="80"/>
+      <c r="B14" s="81"/>
+      <c r="C14" s="81"/>
+      <c r="D14" s="81"/>
+      <c r="E14" s="81"/>
+      <c r="F14" s="81"/>
+      <c r="G14" s="82"/>
       <c r="H14" s="83"/>
       <c r="I14" s="84"/>
       <c r="J14" s="84"/>
@@ -65622,57 +65622,57 @@
       <c r="M14" s="84"/>
       <c r="N14" s="85"/>
       <c r="O14" s="83"/>
-      <c r="P14" s="81"/>
-      <c r="Q14" s="81"/>
-      <c r="R14" s="81"/>
-      <c r="S14" s="81"/>
-      <c r="T14" s="81"/>
-      <c r="U14" s="81"/>
-      <c r="V14" s="81"/>
-      <c r="W14" s="81"/>
-      <c r="X14" s="81"/>
-      <c r="Y14" s="81"/>
-      <c r="Z14" s="81"/>
-      <c r="AA14" s="81"/>
-      <c r="AB14" s="81"/>
-      <c r="AC14" s="81"/>
-      <c r="AD14" s="81"/>
-      <c r="AE14" s="81"/>
-      <c r="AF14" s="81"/>
-      <c r="AG14" s="81"/>
-      <c r="AH14" s="81"/>
-      <c r="AI14" s="81"/>
-      <c r="AJ14" s="81"/>
-      <c r="AK14" s="81"/>
-      <c r="AL14" s="81"/>
-      <c r="AM14" s="81"/>
-      <c r="AN14" s="81"/>
-      <c r="AO14" s="81"/>
-      <c r="AP14" s="89"/>
-      <c r="AQ14" s="80"/>
-      <c r="AR14" s="81"/>
-      <c r="AS14" s="81"/>
-      <c r="AT14" s="81"/>
-      <c r="AU14" s="81"/>
-      <c r="AV14" s="81"/>
-      <c r="AW14" s="81"/>
-      <c r="AX14" s="81"/>
-      <c r="AY14" s="81"/>
-      <c r="AZ14" s="81"/>
-      <c r="BA14" s="81"/>
-      <c r="BB14" s="81"/>
-      <c r="BC14" s="81"/>
-      <c r="BD14" s="81"/>
-      <c r="BE14" s="82"/>
+      <c r="P14" s="86"/>
+      <c r="Q14" s="86"/>
+      <c r="R14" s="86"/>
+      <c r="S14" s="86"/>
+      <c r="T14" s="86"/>
+      <c r="U14" s="86"/>
+      <c r="V14" s="86"/>
+      <c r="W14" s="86"/>
+      <c r="X14" s="86"/>
+      <c r="Y14" s="86"/>
+      <c r="Z14" s="86"/>
+      <c r="AA14" s="86"/>
+      <c r="AB14" s="86"/>
+      <c r="AC14" s="86"/>
+      <c r="AD14" s="86"/>
+      <c r="AE14" s="86"/>
+      <c r="AF14" s="86"/>
+      <c r="AG14" s="86"/>
+      <c r="AH14" s="86"/>
+      <c r="AI14" s="86"/>
+      <c r="AJ14" s="86"/>
+      <c r="AK14" s="86"/>
+      <c r="AL14" s="86"/>
+      <c r="AM14" s="86"/>
+      <c r="AN14" s="86"/>
+      <c r="AO14" s="86"/>
+      <c r="AP14" s="87"/>
+      <c r="AQ14" s="91"/>
+      <c r="AR14" s="86"/>
+      <c r="AS14" s="86"/>
+      <c r="AT14" s="86"/>
+      <c r="AU14" s="86"/>
+      <c r="AV14" s="86"/>
+      <c r="AW14" s="86"/>
+      <c r="AX14" s="86"/>
+      <c r="AY14" s="86"/>
+      <c r="AZ14" s="86"/>
+      <c r="BA14" s="86"/>
+      <c r="BB14" s="86"/>
+      <c r="BC14" s="86"/>
+      <c r="BD14" s="86"/>
+      <c r="BE14" s="92"/>
     </row>
     <row r="15" spans="1:57" ht="15" customHeight="1">
-      <c r="A15" s="100"/>
-      <c r="B15" s="101"/>
-      <c r="C15" s="101"/>
-      <c r="D15" s="101"/>
-      <c r="E15" s="101"/>
-      <c r="F15" s="101"/>
-      <c r="G15" s="102"/>
+      <c r="A15" s="80"/>
+      <c r="B15" s="81"/>
+      <c r="C15" s="81"/>
+      <c r="D15" s="81"/>
+      <c r="E15" s="81"/>
+      <c r="F15" s="81"/>
+      <c r="G15" s="82"/>
       <c r="H15" s="83"/>
       <c r="I15" s="84"/>
       <c r="J15" s="84"/>
@@ -65681,57 +65681,57 @@
       <c r="M15" s="84"/>
       <c r="N15" s="85"/>
       <c r="O15" s="83"/>
-      <c r="P15" s="81"/>
-      <c r="Q15" s="81"/>
-      <c r="R15" s="81"/>
-      <c r="S15" s="81"/>
-      <c r="T15" s="81"/>
-      <c r="U15" s="81"/>
-      <c r="V15" s="81"/>
-      <c r="W15" s="81"/>
-      <c r="X15" s="81"/>
-      <c r="Y15" s="81"/>
-      <c r="Z15" s="81"/>
-      <c r="AA15" s="81"/>
-      <c r="AB15" s="81"/>
-      <c r="AC15" s="81"/>
-      <c r="AD15" s="81"/>
-      <c r="AE15" s="81"/>
-      <c r="AF15" s="81"/>
-      <c r="AG15" s="81"/>
-      <c r="AH15" s="81"/>
-      <c r="AI15" s="81"/>
-      <c r="AJ15" s="81"/>
-      <c r="AK15" s="81"/>
-      <c r="AL15" s="81"/>
-      <c r="AM15" s="81"/>
-      <c r="AN15" s="81"/>
-      <c r="AO15" s="81"/>
-      <c r="AP15" s="89"/>
-      <c r="AQ15" s="80"/>
-      <c r="AR15" s="81"/>
-      <c r="AS15" s="81"/>
-      <c r="AT15" s="81"/>
-      <c r="AU15" s="81"/>
-      <c r="AV15" s="81"/>
-      <c r="AW15" s="81"/>
-      <c r="AX15" s="81"/>
-      <c r="AY15" s="81"/>
-      <c r="AZ15" s="81"/>
-      <c r="BA15" s="81"/>
-      <c r="BB15" s="81"/>
-      <c r="BC15" s="81"/>
-      <c r="BD15" s="81"/>
-      <c r="BE15" s="82"/>
+      <c r="P15" s="86"/>
+      <c r="Q15" s="86"/>
+      <c r="R15" s="86"/>
+      <c r="S15" s="86"/>
+      <c r="T15" s="86"/>
+      <c r="U15" s="86"/>
+      <c r="V15" s="86"/>
+      <c r="W15" s="86"/>
+      <c r="X15" s="86"/>
+      <c r="Y15" s="86"/>
+      <c r="Z15" s="86"/>
+      <c r="AA15" s="86"/>
+      <c r="AB15" s="86"/>
+      <c r="AC15" s="86"/>
+      <c r="AD15" s="86"/>
+      <c r="AE15" s="86"/>
+      <c r="AF15" s="86"/>
+      <c r="AG15" s="86"/>
+      <c r="AH15" s="86"/>
+      <c r="AI15" s="86"/>
+      <c r="AJ15" s="86"/>
+      <c r="AK15" s="86"/>
+      <c r="AL15" s="86"/>
+      <c r="AM15" s="86"/>
+      <c r="AN15" s="86"/>
+      <c r="AO15" s="86"/>
+      <c r="AP15" s="87"/>
+      <c r="AQ15" s="91"/>
+      <c r="AR15" s="86"/>
+      <c r="AS15" s="86"/>
+      <c r="AT15" s="86"/>
+      <c r="AU15" s="86"/>
+      <c r="AV15" s="86"/>
+      <c r="AW15" s="86"/>
+      <c r="AX15" s="86"/>
+      <c r="AY15" s="86"/>
+      <c r="AZ15" s="86"/>
+      <c r="BA15" s="86"/>
+      <c r="BB15" s="86"/>
+      <c r="BC15" s="86"/>
+      <c r="BD15" s="86"/>
+      <c r="BE15" s="92"/>
     </row>
     <row r="16" spans="1:57" ht="15" customHeight="1">
-      <c r="A16" s="100"/>
-      <c r="B16" s="101"/>
-      <c r="C16" s="101"/>
-      <c r="D16" s="101"/>
-      <c r="E16" s="101"/>
-      <c r="F16" s="101"/>
-      <c r="G16" s="102"/>
+      <c r="A16" s="80"/>
+      <c r="B16" s="81"/>
+      <c r="C16" s="81"/>
+      <c r="D16" s="81"/>
+      <c r="E16" s="81"/>
+      <c r="F16" s="81"/>
+      <c r="G16" s="82"/>
       <c r="H16" s="83"/>
       <c r="I16" s="84"/>
       <c r="J16" s="84"/>
@@ -65740,57 +65740,57 @@
       <c r="M16" s="84"/>
       <c r="N16" s="85"/>
       <c r="O16" s="83"/>
-      <c r="P16" s="81"/>
-      <c r="Q16" s="81"/>
-      <c r="R16" s="81"/>
-      <c r="S16" s="81"/>
-      <c r="T16" s="81"/>
-      <c r="U16" s="81"/>
-      <c r="V16" s="81"/>
-      <c r="W16" s="81"/>
-      <c r="X16" s="81"/>
-      <c r="Y16" s="81"/>
-      <c r="Z16" s="81"/>
-      <c r="AA16" s="81"/>
-      <c r="AB16" s="81"/>
-      <c r="AC16" s="81"/>
-      <c r="AD16" s="81"/>
-      <c r="AE16" s="81"/>
-      <c r="AF16" s="81"/>
-      <c r="AG16" s="81"/>
-      <c r="AH16" s="81"/>
-      <c r="AI16" s="81"/>
-      <c r="AJ16" s="81"/>
-      <c r="AK16" s="81"/>
-      <c r="AL16" s="81"/>
-      <c r="AM16" s="81"/>
-      <c r="AN16" s="81"/>
-      <c r="AO16" s="81"/>
-      <c r="AP16" s="89"/>
-      <c r="AQ16" s="80"/>
-      <c r="AR16" s="81"/>
-      <c r="AS16" s="81"/>
-      <c r="AT16" s="81"/>
-      <c r="AU16" s="81"/>
-      <c r="AV16" s="81"/>
-      <c r="AW16" s="81"/>
-      <c r="AX16" s="81"/>
-      <c r="AY16" s="81"/>
-      <c r="AZ16" s="81"/>
-      <c r="BA16" s="81"/>
-      <c r="BB16" s="81"/>
-      <c r="BC16" s="81"/>
-      <c r="BD16" s="81"/>
-      <c r="BE16" s="82"/>
+      <c r="P16" s="86"/>
+      <c r="Q16" s="86"/>
+      <c r="R16" s="86"/>
+      <c r="S16" s="86"/>
+      <c r="T16" s="86"/>
+      <c r="U16" s="86"/>
+      <c r="V16" s="86"/>
+      <c r="W16" s="86"/>
+      <c r="X16" s="86"/>
+      <c r="Y16" s="86"/>
+      <c r="Z16" s="86"/>
+      <c r="AA16" s="86"/>
+      <c r="AB16" s="86"/>
+      <c r="AC16" s="86"/>
+      <c r="AD16" s="86"/>
+      <c r="AE16" s="86"/>
+      <c r="AF16" s="86"/>
+      <c r="AG16" s="86"/>
+      <c r="AH16" s="86"/>
+      <c r="AI16" s="86"/>
+      <c r="AJ16" s="86"/>
+      <c r="AK16" s="86"/>
+      <c r="AL16" s="86"/>
+      <c r="AM16" s="86"/>
+      <c r="AN16" s="86"/>
+      <c r="AO16" s="86"/>
+      <c r="AP16" s="87"/>
+      <c r="AQ16" s="91"/>
+      <c r="AR16" s="86"/>
+      <c r="AS16" s="86"/>
+      <c r="AT16" s="86"/>
+      <c r="AU16" s="86"/>
+      <c r="AV16" s="86"/>
+      <c r="AW16" s="86"/>
+      <c r="AX16" s="86"/>
+      <c r="AY16" s="86"/>
+      <c r="AZ16" s="86"/>
+      <c r="BA16" s="86"/>
+      <c r="BB16" s="86"/>
+      <c r="BC16" s="86"/>
+      <c r="BD16" s="86"/>
+      <c r="BE16" s="92"/>
     </row>
     <row r="17" spans="1:57" ht="15" customHeight="1">
-      <c r="A17" s="100"/>
-      <c r="B17" s="101"/>
-      <c r="C17" s="101"/>
-      <c r="D17" s="101"/>
-      <c r="E17" s="101"/>
-      <c r="F17" s="101"/>
-      <c r="G17" s="102"/>
+      <c r="A17" s="80"/>
+      <c r="B17" s="81"/>
+      <c r="C17" s="81"/>
+      <c r="D17" s="81"/>
+      <c r="E17" s="81"/>
+      <c r="F17" s="81"/>
+      <c r="G17" s="82"/>
       <c r="H17" s="83"/>
       <c r="I17" s="84"/>
       <c r="J17" s="84"/>
@@ -65799,57 +65799,57 @@
       <c r="M17" s="84"/>
       <c r="N17" s="85"/>
       <c r="O17" s="83"/>
-      <c r="P17" s="81"/>
-      <c r="Q17" s="81"/>
-      <c r="R17" s="81"/>
-      <c r="S17" s="81"/>
-      <c r="T17" s="81"/>
-      <c r="U17" s="81"/>
-      <c r="V17" s="81"/>
-      <c r="W17" s="81"/>
-      <c r="X17" s="81"/>
-      <c r="Y17" s="81"/>
-      <c r="Z17" s="81"/>
-      <c r="AA17" s="81"/>
-      <c r="AB17" s="81"/>
-      <c r="AC17" s="81"/>
-      <c r="AD17" s="81"/>
-      <c r="AE17" s="81"/>
-      <c r="AF17" s="81"/>
-      <c r="AG17" s="81"/>
-      <c r="AH17" s="81"/>
-      <c r="AI17" s="81"/>
-      <c r="AJ17" s="81"/>
-      <c r="AK17" s="81"/>
-      <c r="AL17" s="81"/>
-      <c r="AM17" s="81"/>
-      <c r="AN17" s="81"/>
-      <c r="AO17" s="81"/>
-      <c r="AP17" s="89"/>
-      <c r="AQ17" s="80"/>
-      <c r="AR17" s="81"/>
-      <c r="AS17" s="81"/>
-      <c r="AT17" s="81"/>
-      <c r="AU17" s="81"/>
-      <c r="AV17" s="81"/>
-      <c r="AW17" s="81"/>
-      <c r="AX17" s="81"/>
-      <c r="AY17" s="81"/>
-      <c r="AZ17" s="81"/>
-      <c r="BA17" s="81"/>
-      <c r="BB17" s="81"/>
-      <c r="BC17" s="81"/>
-      <c r="BD17" s="81"/>
-      <c r="BE17" s="82"/>
+      <c r="P17" s="86"/>
+      <c r="Q17" s="86"/>
+      <c r="R17" s="86"/>
+      <c r="S17" s="86"/>
+      <c r="T17" s="86"/>
+      <c r="U17" s="86"/>
+      <c r="V17" s="86"/>
+      <c r="W17" s="86"/>
+      <c r="X17" s="86"/>
+      <c r="Y17" s="86"/>
+      <c r="Z17" s="86"/>
+      <c r="AA17" s="86"/>
+      <c r="AB17" s="86"/>
+      <c r="AC17" s="86"/>
+      <c r="AD17" s="86"/>
+      <c r="AE17" s="86"/>
+      <c r="AF17" s="86"/>
+      <c r="AG17" s="86"/>
+      <c r="AH17" s="86"/>
+      <c r="AI17" s="86"/>
+      <c r="AJ17" s="86"/>
+      <c r="AK17" s="86"/>
+      <c r="AL17" s="86"/>
+      <c r="AM17" s="86"/>
+      <c r="AN17" s="86"/>
+      <c r="AO17" s="86"/>
+      <c r="AP17" s="87"/>
+      <c r="AQ17" s="91"/>
+      <c r="AR17" s="86"/>
+      <c r="AS17" s="86"/>
+      <c r="AT17" s="86"/>
+      <c r="AU17" s="86"/>
+      <c r="AV17" s="86"/>
+      <c r="AW17" s="86"/>
+      <c r="AX17" s="86"/>
+      <c r="AY17" s="86"/>
+      <c r="AZ17" s="86"/>
+      <c r="BA17" s="86"/>
+      <c r="BB17" s="86"/>
+      <c r="BC17" s="86"/>
+      <c r="BD17" s="86"/>
+      <c r="BE17" s="92"/>
     </row>
     <row r="18" spans="1:57" ht="15" customHeight="1">
-      <c r="A18" s="100"/>
-      <c r="B18" s="101"/>
-      <c r="C18" s="101"/>
-      <c r="D18" s="101"/>
-      <c r="E18" s="101"/>
-      <c r="F18" s="101"/>
-      <c r="G18" s="102"/>
+      <c r="A18" s="80"/>
+      <c r="B18" s="81"/>
+      <c r="C18" s="81"/>
+      <c r="D18" s="81"/>
+      <c r="E18" s="81"/>
+      <c r="F18" s="81"/>
+      <c r="G18" s="82"/>
       <c r="H18" s="83"/>
       <c r="I18" s="84"/>
       <c r="J18" s="84"/>
@@ -65858,57 +65858,57 @@
       <c r="M18" s="84"/>
       <c r="N18" s="85"/>
       <c r="O18" s="83"/>
-      <c r="P18" s="81"/>
-      <c r="Q18" s="81"/>
-      <c r="R18" s="81"/>
-      <c r="S18" s="81"/>
-      <c r="T18" s="81"/>
-      <c r="U18" s="81"/>
-      <c r="V18" s="81"/>
-      <c r="W18" s="81"/>
-      <c r="X18" s="81"/>
-      <c r="Y18" s="81"/>
-      <c r="Z18" s="81"/>
-      <c r="AA18" s="81"/>
-      <c r="AB18" s="81"/>
-      <c r="AC18" s="81"/>
-      <c r="AD18" s="81"/>
-      <c r="AE18" s="81"/>
-      <c r="AF18" s="81"/>
-      <c r="AG18" s="81"/>
-      <c r="AH18" s="81"/>
-      <c r="AI18" s="81"/>
-      <c r="AJ18" s="81"/>
-      <c r="AK18" s="81"/>
-      <c r="AL18" s="81"/>
-      <c r="AM18" s="81"/>
-      <c r="AN18" s="81"/>
-      <c r="AO18" s="81"/>
-      <c r="AP18" s="89"/>
-      <c r="AQ18" s="80"/>
-      <c r="AR18" s="81"/>
-      <c r="AS18" s="81"/>
-      <c r="AT18" s="81"/>
-      <c r="AU18" s="81"/>
-      <c r="AV18" s="81"/>
-      <c r="AW18" s="81"/>
-      <c r="AX18" s="81"/>
-      <c r="AY18" s="81"/>
-      <c r="AZ18" s="81"/>
-      <c r="BA18" s="81"/>
-      <c r="BB18" s="81"/>
-      <c r="BC18" s="81"/>
-      <c r="BD18" s="81"/>
-      <c r="BE18" s="82"/>
+      <c r="P18" s="86"/>
+      <c r="Q18" s="86"/>
+      <c r="R18" s="86"/>
+      <c r="S18" s="86"/>
+      <c r="T18" s="86"/>
+      <c r="U18" s="86"/>
+      <c r="V18" s="86"/>
+      <c r="W18" s="86"/>
+      <c r="X18" s="86"/>
+      <c r="Y18" s="86"/>
+      <c r="Z18" s="86"/>
+      <c r="AA18" s="86"/>
+      <c r="AB18" s="86"/>
+      <c r="AC18" s="86"/>
+      <c r="AD18" s="86"/>
+      <c r="AE18" s="86"/>
+      <c r="AF18" s="86"/>
+      <c r="AG18" s="86"/>
+      <c r="AH18" s="86"/>
+      <c r="AI18" s="86"/>
+      <c r="AJ18" s="86"/>
+      <c r="AK18" s="86"/>
+      <c r="AL18" s="86"/>
+      <c r="AM18" s="86"/>
+      <c r="AN18" s="86"/>
+      <c r="AO18" s="86"/>
+      <c r="AP18" s="87"/>
+      <c r="AQ18" s="91"/>
+      <c r="AR18" s="86"/>
+      <c r="AS18" s="86"/>
+      <c r="AT18" s="86"/>
+      <c r="AU18" s="86"/>
+      <c r="AV18" s="86"/>
+      <c r="AW18" s="86"/>
+      <c r="AX18" s="86"/>
+      <c r="AY18" s="86"/>
+      <c r="AZ18" s="86"/>
+      <c r="BA18" s="86"/>
+      <c r="BB18" s="86"/>
+      <c r="BC18" s="86"/>
+      <c r="BD18" s="86"/>
+      <c r="BE18" s="92"/>
     </row>
     <row r="19" spans="1:57" ht="15" customHeight="1">
-      <c r="A19" s="100"/>
-      <c r="B19" s="101"/>
-      <c r="C19" s="101"/>
-      <c r="D19" s="101"/>
-      <c r="E19" s="101"/>
-      <c r="F19" s="101"/>
-      <c r="G19" s="102"/>
+      <c r="A19" s="80"/>
+      <c r="B19" s="81"/>
+      <c r="C19" s="81"/>
+      <c r="D19" s="81"/>
+      <c r="E19" s="81"/>
+      <c r="F19" s="81"/>
+      <c r="G19" s="82"/>
       <c r="H19" s="83"/>
       <c r="I19" s="84"/>
       <c r="J19" s="84"/>
@@ -65917,57 +65917,57 @@
       <c r="M19" s="84"/>
       <c r="N19" s="85"/>
       <c r="O19" s="83"/>
-      <c r="P19" s="81"/>
-      <c r="Q19" s="81"/>
-      <c r="R19" s="81"/>
-      <c r="S19" s="81"/>
-      <c r="T19" s="81"/>
-      <c r="U19" s="81"/>
-      <c r="V19" s="81"/>
-      <c r="W19" s="81"/>
-      <c r="X19" s="81"/>
-      <c r="Y19" s="81"/>
-      <c r="Z19" s="81"/>
-      <c r="AA19" s="81"/>
-      <c r="AB19" s="81"/>
-      <c r="AC19" s="81"/>
-      <c r="AD19" s="81"/>
-      <c r="AE19" s="81"/>
-      <c r="AF19" s="81"/>
-      <c r="AG19" s="81"/>
-      <c r="AH19" s="81"/>
-      <c r="AI19" s="81"/>
-      <c r="AJ19" s="81"/>
-      <c r="AK19" s="81"/>
-      <c r="AL19" s="81"/>
-      <c r="AM19" s="81"/>
-      <c r="AN19" s="81"/>
-      <c r="AO19" s="81"/>
-      <c r="AP19" s="89"/>
-      <c r="AQ19" s="80"/>
-      <c r="AR19" s="81"/>
-      <c r="AS19" s="81"/>
-      <c r="AT19" s="81"/>
-      <c r="AU19" s="81"/>
-      <c r="AV19" s="81"/>
-      <c r="AW19" s="81"/>
-      <c r="AX19" s="81"/>
-      <c r="AY19" s="81"/>
-      <c r="AZ19" s="81"/>
-      <c r="BA19" s="81"/>
-      <c r="BB19" s="81"/>
-      <c r="BC19" s="81"/>
-      <c r="BD19" s="81"/>
-      <c r="BE19" s="82"/>
+      <c r="P19" s="86"/>
+      <c r="Q19" s="86"/>
+      <c r="R19" s="86"/>
+      <c r="S19" s="86"/>
+      <c r="T19" s="86"/>
+      <c r="U19" s="86"/>
+      <c r="V19" s="86"/>
+      <c r="W19" s="86"/>
+      <c r="X19" s="86"/>
+      <c r="Y19" s="86"/>
+      <c r="Z19" s="86"/>
+      <c r="AA19" s="86"/>
+      <c r="AB19" s="86"/>
+      <c r="AC19" s="86"/>
+      <c r="AD19" s="86"/>
+      <c r="AE19" s="86"/>
+      <c r="AF19" s="86"/>
+      <c r="AG19" s="86"/>
+      <c r="AH19" s="86"/>
+      <c r="AI19" s="86"/>
+      <c r="AJ19" s="86"/>
+      <c r="AK19" s="86"/>
+      <c r="AL19" s="86"/>
+      <c r="AM19" s="86"/>
+      <c r="AN19" s="86"/>
+      <c r="AO19" s="86"/>
+      <c r="AP19" s="87"/>
+      <c r="AQ19" s="91"/>
+      <c r="AR19" s="86"/>
+      <c r="AS19" s="86"/>
+      <c r="AT19" s="86"/>
+      <c r="AU19" s="86"/>
+      <c r="AV19" s="86"/>
+      <c r="AW19" s="86"/>
+      <c r="AX19" s="86"/>
+      <c r="AY19" s="86"/>
+      <c r="AZ19" s="86"/>
+      <c r="BA19" s="86"/>
+      <c r="BB19" s="86"/>
+      <c r="BC19" s="86"/>
+      <c r="BD19" s="86"/>
+      <c r="BE19" s="92"/>
     </row>
     <row r="20" spans="1:57" ht="15" customHeight="1">
-      <c r="A20" s="100"/>
-      <c r="B20" s="101"/>
-      <c r="C20" s="101"/>
-      <c r="D20" s="101"/>
-      <c r="E20" s="101"/>
-      <c r="F20" s="101"/>
-      <c r="G20" s="102"/>
+      <c r="A20" s="80"/>
+      <c r="B20" s="81"/>
+      <c r="C20" s="81"/>
+      <c r="D20" s="81"/>
+      <c r="E20" s="81"/>
+      <c r="F20" s="81"/>
+      <c r="G20" s="82"/>
       <c r="H20" s="83"/>
       <c r="I20" s="84"/>
       <c r="J20" s="84"/>
@@ -65976,57 +65976,57 @@
       <c r="M20" s="84"/>
       <c r="N20" s="85"/>
       <c r="O20" s="83"/>
-      <c r="P20" s="81"/>
-      <c r="Q20" s="81"/>
-      <c r="R20" s="81"/>
-      <c r="S20" s="81"/>
-      <c r="T20" s="81"/>
-      <c r="U20" s="81"/>
-      <c r="V20" s="81"/>
-      <c r="W20" s="81"/>
-      <c r="X20" s="81"/>
-      <c r="Y20" s="81"/>
-      <c r="Z20" s="81"/>
-      <c r="AA20" s="81"/>
-      <c r="AB20" s="81"/>
-      <c r="AC20" s="81"/>
-      <c r="AD20" s="81"/>
-      <c r="AE20" s="81"/>
-      <c r="AF20" s="81"/>
-      <c r="AG20" s="81"/>
-      <c r="AH20" s="81"/>
-      <c r="AI20" s="81"/>
-      <c r="AJ20" s="81"/>
-      <c r="AK20" s="81"/>
-      <c r="AL20" s="81"/>
-      <c r="AM20" s="81"/>
-      <c r="AN20" s="81"/>
-      <c r="AO20" s="81"/>
-      <c r="AP20" s="89"/>
-      <c r="AQ20" s="80"/>
-      <c r="AR20" s="81"/>
-      <c r="AS20" s="81"/>
-      <c r="AT20" s="81"/>
-      <c r="AU20" s="81"/>
-      <c r="AV20" s="81"/>
-      <c r="AW20" s="81"/>
-      <c r="AX20" s="81"/>
-      <c r="AY20" s="81"/>
-      <c r="AZ20" s="81"/>
-      <c r="BA20" s="81"/>
-      <c r="BB20" s="81"/>
-      <c r="BC20" s="81"/>
-      <c r="BD20" s="81"/>
-      <c r="BE20" s="82"/>
+      <c r="P20" s="86"/>
+      <c r="Q20" s="86"/>
+      <c r="R20" s="86"/>
+      <c r="S20" s="86"/>
+      <c r="T20" s="86"/>
+      <c r="U20" s="86"/>
+      <c r="V20" s="86"/>
+      <c r="W20" s="86"/>
+      <c r="X20" s="86"/>
+      <c r="Y20" s="86"/>
+      <c r="Z20" s="86"/>
+      <c r="AA20" s="86"/>
+      <c r="AB20" s="86"/>
+      <c r="AC20" s="86"/>
+      <c r="AD20" s="86"/>
+      <c r="AE20" s="86"/>
+      <c r="AF20" s="86"/>
+      <c r="AG20" s="86"/>
+      <c r="AH20" s="86"/>
+      <c r="AI20" s="86"/>
+      <c r="AJ20" s="86"/>
+      <c r="AK20" s="86"/>
+      <c r="AL20" s="86"/>
+      <c r="AM20" s="86"/>
+      <c r="AN20" s="86"/>
+      <c r="AO20" s="86"/>
+      <c r="AP20" s="87"/>
+      <c r="AQ20" s="91"/>
+      <c r="AR20" s="86"/>
+      <c r="AS20" s="86"/>
+      <c r="AT20" s="86"/>
+      <c r="AU20" s="86"/>
+      <c r="AV20" s="86"/>
+      <c r="AW20" s="86"/>
+      <c r="AX20" s="86"/>
+      <c r="AY20" s="86"/>
+      <c r="AZ20" s="86"/>
+      <c r="BA20" s="86"/>
+      <c r="BB20" s="86"/>
+      <c r="BC20" s="86"/>
+      <c r="BD20" s="86"/>
+      <c r="BE20" s="92"/>
     </row>
     <row r="21" spans="1:57" ht="15" customHeight="1">
-      <c r="A21" s="100"/>
-      <c r="B21" s="101"/>
-      <c r="C21" s="101"/>
-      <c r="D21" s="101"/>
-      <c r="E21" s="101"/>
-      <c r="F21" s="101"/>
-      <c r="G21" s="102"/>
+      <c r="A21" s="80"/>
+      <c r="B21" s="81"/>
+      <c r="C21" s="81"/>
+      <c r="D21" s="81"/>
+      <c r="E21" s="81"/>
+      <c r="F21" s="81"/>
+      <c r="G21" s="82"/>
       <c r="H21" s="83"/>
       <c r="I21" s="84"/>
       <c r="J21" s="84"/>
@@ -66035,57 +66035,57 @@
       <c r="M21" s="84"/>
       <c r="N21" s="85"/>
       <c r="O21" s="83"/>
-      <c r="P21" s="81"/>
-      <c r="Q21" s="81"/>
-      <c r="R21" s="81"/>
-      <c r="S21" s="81"/>
-      <c r="T21" s="81"/>
-      <c r="U21" s="81"/>
-      <c r="V21" s="81"/>
-      <c r="W21" s="81"/>
-      <c r="X21" s="81"/>
-      <c r="Y21" s="81"/>
-      <c r="Z21" s="81"/>
-      <c r="AA21" s="81"/>
-      <c r="AB21" s="81"/>
-      <c r="AC21" s="81"/>
-      <c r="AD21" s="81"/>
-      <c r="AE21" s="81"/>
-      <c r="AF21" s="81"/>
-      <c r="AG21" s="81"/>
-      <c r="AH21" s="81"/>
-      <c r="AI21" s="81"/>
-      <c r="AJ21" s="81"/>
-      <c r="AK21" s="81"/>
-      <c r="AL21" s="81"/>
-      <c r="AM21" s="81"/>
-      <c r="AN21" s="81"/>
-      <c r="AO21" s="81"/>
-      <c r="AP21" s="89"/>
-      <c r="AQ21" s="80"/>
-      <c r="AR21" s="81"/>
-      <c r="AS21" s="81"/>
-      <c r="AT21" s="81"/>
-      <c r="AU21" s="81"/>
-      <c r="AV21" s="81"/>
-      <c r="AW21" s="81"/>
-      <c r="AX21" s="81"/>
-      <c r="AY21" s="81"/>
-      <c r="AZ21" s="81"/>
-      <c r="BA21" s="81"/>
-      <c r="BB21" s="81"/>
-      <c r="BC21" s="81"/>
-      <c r="BD21" s="81"/>
-      <c r="BE21" s="82"/>
+      <c r="P21" s="86"/>
+      <c r="Q21" s="86"/>
+      <c r="R21" s="86"/>
+      <c r="S21" s="86"/>
+      <c r="T21" s="86"/>
+      <c r="U21" s="86"/>
+      <c r="V21" s="86"/>
+      <c r="W21" s="86"/>
+      <c r="X21" s="86"/>
+      <c r="Y21" s="86"/>
+      <c r="Z21" s="86"/>
+      <c r="AA21" s="86"/>
+      <c r="AB21" s="86"/>
+      <c r="AC21" s="86"/>
+      <c r="AD21" s="86"/>
+      <c r="AE21" s="86"/>
+      <c r="AF21" s="86"/>
+      <c r="AG21" s="86"/>
+      <c r="AH21" s="86"/>
+      <c r="AI21" s="86"/>
+      <c r="AJ21" s="86"/>
+      <c r="AK21" s="86"/>
+      <c r="AL21" s="86"/>
+      <c r="AM21" s="86"/>
+      <c r="AN21" s="86"/>
+      <c r="AO21" s="86"/>
+      <c r="AP21" s="87"/>
+      <c r="AQ21" s="91"/>
+      <c r="AR21" s="86"/>
+      <c r="AS21" s="86"/>
+      <c r="AT21" s="86"/>
+      <c r="AU21" s="86"/>
+      <c r="AV21" s="86"/>
+      <c r="AW21" s="86"/>
+      <c r="AX21" s="86"/>
+      <c r="AY21" s="86"/>
+      <c r="AZ21" s="86"/>
+      <c r="BA21" s="86"/>
+      <c r="BB21" s="86"/>
+      <c r="BC21" s="86"/>
+      <c r="BD21" s="86"/>
+      <c r="BE21" s="92"/>
     </row>
     <row r="22" spans="1:57" ht="15" customHeight="1">
-      <c r="A22" s="100"/>
-      <c r="B22" s="101"/>
-      <c r="C22" s="101"/>
-      <c r="D22" s="101"/>
-      <c r="E22" s="101"/>
-      <c r="F22" s="101"/>
-      <c r="G22" s="102"/>
+      <c r="A22" s="80"/>
+      <c r="B22" s="81"/>
+      <c r="C22" s="81"/>
+      <c r="D22" s="81"/>
+      <c r="E22" s="81"/>
+      <c r="F22" s="81"/>
+      <c r="G22" s="82"/>
       <c r="H22" s="83"/>
       <c r="I22" s="84"/>
       <c r="J22" s="84"/>
@@ -66094,57 +66094,57 @@
       <c r="M22" s="84"/>
       <c r="N22" s="85"/>
       <c r="O22" s="83"/>
-      <c r="P22" s="81"/>
-      <c r="Q22" s="81"/>
-      <c r="R22" s="81"/>
-      <c r="S22" s="81"/>
-      <c r="T22" s="81"/>
-      <c r="U22" s="81"/>
-      <c r="V22" s="81"/>
-      <c r="W22" s="81"/>
-      <c r="X22" s="81"/>
-      <c r="Y22" s="81"/>
-      <c r="Z22" s="81"/>
-      <c r="AA22" s="81"/>
-      <c r="AB22" s="81"/>
-      <c r="AC22" s="81"/>
-      <c r="AD22" s="81"/>
-      <c r="AE22" s="81"/>
-      <c r="AF22" s="81"/>
-      <c r="AG22" s="81"/>
-      <c r="AH22" s="81"/>
-      <c r="AI22" s="81"/>
-      <c r="AJ22" s="81"/>
-      <c r="AK22" s="81"/>
-      <c r="AL22" s="81"/>
-      <c r="AM22" s="81"/>
-      <c r="AN22" s="81"/>
-      <c r="AO22" s="81"/>
-      <c r="AP22" s="89"/>
-      <c r="AQ22" s="80"/>
-      <c r="AR22" s="81"/>
-      <c r="AS22" s="81"/>
-      <c r="AT22" s="81"/>
-      <c r="AU22" s="81"/>
-      <c r="AV22" s="81"/>
-      <c r="AW22" s="81"/>
-      <c r="AX22" s="81"/>
-      <c r="AY22" s="81"/>
-      <c r="AZ22" s="81"/>
-      <c r="BA22" s="81"/>
-      <c r="BB22" s="81"/>
-      <c r="BC22" s="81"/>
-      <c r="BD22" s="81"/>
-      <c r="BE22" s="82"/>
+      <c r="P22" s="86"/>
+      <c r="Q22" s="86"/>
+      <c r="R22" s="86"/>
+      <c r="S22" s="86"/>
+      <c r="T22" s="86"/>
+      <c r="U22" s="86"/>
+      <c r="V22" s="86"/>
+      <c r="W22" s="86"/>
+      <c r="X22" s="86"/>
+      <c r="Y22" s="86"/>
+      <c r="Z22" s="86"/>
+      <c r="AA22" s="86"/>
+      <c r="AB22" s="86"/>
+      <c r="AC22" s="86"/>
+      <c r="AD22" s="86"/>
+      <c r="AE22" s="86"/>
+      <c r="AF22" s="86"/>
+      <c r="AG22" s="86"/>
+      <c r="AH22" s="86"/>
+      <c r="AI22" s="86"/>
+      <c r="AJ22" s="86"/>
+      <c r="AK22" s="86"/>
+      <c r="AL22" s="86"/>
+      <c r="AM22" s="86"/>
+      <c r="AN22" s="86"/>
+      <c r="AO22" s="86"/>
+      <c r="AP22" s="87"/>
+      <c r="AQ22" s="91"/>
+      <c r="AR22" s="86"/>
+      <c r="AS22" s="86"/>
+      <c r="AT22" s="86"/>
+      <c r="AU22" s="86"/>
+      <c r="AV22" s="86"/>
+      <c r="AW22" s="86"/>
+      <c r="AX22" s="86"/>
+      <c r="AY22" s="86"/>
+      <c r="AZ22" s="86"/>
+      <c r="BA22" s="86"/>
+      <c r="BB22" s="86"/>
+      <c r="BC22" s="86"/>
+      <c r="BD22" s="86"/>
+      <c r="BE22" s="92"/>
     </row>
     <row r="23" spans="1:57" ht="15" customHeight="1">
-      <c r="A23" s="100"/>
-      <c r="B23" s="101"/>
-      <c r="C23" s="101"/>
-      <c r="D23" s="101"/>
-      <c r="E23" s="101"/>
-      <c r="F23" s="101"/>
-      <c r="G23" s="102"/>
+      <c r="A23" s="80"/>
+      <c r="B23" s="81"/>
+      <c r="C23" s="81"/>
+      <c r="D23" s="81"/>
+      <c r="E23" s="81"/>
+      <c r="F23" s="81"/>
+      <c r="G23" s="82"/>
       <c r="H23" s="83"/>
       <c r="I23" s="84"/>
       <c r="J23" s="84"/>
@@ -66153,57 +66153,57 @@
       <c r="M23" s="84"/>
       <c r="N23" s="85"/>
       <c r="O23" s="83"/>
-      <c r="P23" s="81"/>
-      <c r="Q23" s="81"/>
-      <c r="R23" s="81"/>
-      <c r="S23" s="81"/>
-      <c r="T23" s="81"/>
-      <c r="U23" s="81"/>
-      <c r="V23" s="81"/>
-      <c r="W23" s="81"/>
-      <c r="X23" s="81"/>
-      <c r="Y23" s="81"/>
-      <c r="Z23" s="81"/>
-      <c r="AA23" s="81"/>
-      <c r="AB23" s="81"/>
-      <c r="AC23" s="81"/>
-      <c r="AD23" s="81"/>
-      <c r="AE23" s="81"/>
-      <c r="AF23" s="81"/>
-      <c r="AG23" s="81"/>
-      <c r="AH23" s="81"/>
-      <c r="AI23" s="81"/>
-      <c r="AJ23" s="81"/>
-      <c r="AK23" s="81"/>
-      <c r="AL23" s="81"/>
-      <c r="AM23" s="81"/>
-      <c r="AN23" s="81"/>
-      <c r="AO23" s="81"/>
-      <c r="AP23" s="89"/>
-      <c r="AQ23" s="80"/>
-      <c r="AR23" s="81"/>
-      <c r="AS23" s="81"/>
-      <c r="AT23" s="81"/>
-      <c r="AU23" s="81"/>
-      <c r="AV23" s="81"/>
-      <c r="AW23" s="81"/>
-      <c r="AX23" s="81"/>
-      <c r="AY23" s="81"/>
-      <c r="AZ23" s="81"/>
-      <c r="BA23" s="81"/>
-      <c r="BB23" s="81"/>
-      <c r="BC23" s="81"/>
-      <c r="BD23" s="81"/>
-      <c r="BE23" s="82"/>
+      <c r="P23" s="86"/>
+      <c r="Q23" s="86"/>
+      <c r="R23" s="86"/>
+      <c r="S23" s="86"/>
+      <c r="T23" s="86"/>
+      <c r="U23" s="86"/>
+      <c r="V23" s="86"/>
+      <c r="W23" s="86"/>
+      <c r="X23" s="86"/>
+      <c r="Y23" s="86"/>
+      <c r="Z23" s="86"/>
+      <c r="AA23" s="86"/>
+      <c r="AB23" s="86"/>
+      <c r="AC23" s="86"/>
+      <c r="AD23" s="86"/>
+      <c r="AE23" s="86"/>
+      <c r="AF23" s="86"/>
+      <c r="AG23" s="86"/>
+      <c r="AH23" s="86"/>
+      <c r="AI23" s="86"/>
+      <c r="AJ23" s="86"/>
+      <c r="AK23" s="86"/>
+      <c r="AL23" s="86"/>
+      <c r="AM23" s="86"/>
+      <c r="AN23" s="86"/>
+      <c r="AO23" s="86"/>
+      <c r="AP23" s="87"/>
+      <c r="AQ23" s="91"/>
+      <c r="AR23" s="86"/>
+      <c r="AS23" s="86"/>
+      <c r="AT23" s="86"/>
+      <c r="AU23" s="86"/>
+      <c r="AV23" s="86"/>
+      <c r="AW23" s="86"/>
+      <c r="AX23" s="86"/>
+      <c r="AY23" s="86"/>
+      <c r="AZ23" s="86"/>
+      <c r="BA23" s="86"/>
+      <c r="BB23" s="86"/>
+      <c r="BC23" s="86"/>
+      <c r="BD23" s="86"/>
+      <c r="BE23" s="92"/>
     </row>
     <row r="24" spans="1:57" ht="15" customHeight="1">
-      <c r="A24" s="100"/>
-      <c r="B24" s="101"/>
-      <c r="C24" s="101"/>
-      <c r="D24" s="101"/>
-      <c r="E24" s="101"/>
-      <c r="F24" s="101"/>
-      <c r="G24" s="102"/>
+      <c r="A24" s="80"/>
+      <c r="B24" s="81"/>
+      <c r="C24" s="81"/>
+      <c r="D24" s="81"/>
+      <c r="E24" s="81"/>
+      <c r="F24" s="81"/>
+      <c r="G24" s="82"/>
       <c r="H24" s="83"/>
       <c r="I24" s="84"/>
       <c r="J24" s="84"/>
@@ -66212,57 +66212,57 @@
       <c r="M24" s="84"/>
       <c r="N24" s="85"/>
       <c r="O24" s="83"/>
-      <c r="P24" s="81"/>
-      <c r="Q24" s="81"/>
-      <c r="R24" s="81"/>
-      <c r="S24" s="81"/>
-      <c r="T24" s="81"/>
-      <c r="U24" s="81"/>
-      <c r="V24" s="81"/>
-      <c r="W24" s="81"/>
-      <c r="X24" s="81"/>
-      <c r="Y24" s="81"/>
-      <c r="Z24" s="81"/>
-      <c r="AA24" s="81"/>
-      <c r="AB24" s="81"/>
-      <c r="AC24" s="81"/>
-      <c r="AD24" s="81"/>
-      <c r="AE24" s="81"/>
-      <c r="AF24" s="81"/>
-      <c r="AG24" s="81"/>
-      <c r="AH24" s="81"/>
-      <c r="AI24" s="81"/>
-      <c r="AJ24" s="81"/>
-      <c r="AK24" s="81"/>
-      <c r="AL24" s="81"/>
-      <c r="AM24" s="81"/>
-      <c r="AN24" s="81"/>
-      <c r="AO24" s="81"/>
-      <c r="AP24" s="89"/>
-      <c r="AQ24" s="80"/>
-      <c r="AR24" s="81"/>
-      <c r="AS24" s="81"/>
-      <c r="AT24" s="81"/>
-      <c r="AU24" s="81"/>
-      <c r="AV24" s="81"/>
-      <c r="AW24" s="81"/>
-      <c r="AX24" s="81"/>
-      <c r="AY24" s="81"/>
-      <c r="AZ24" s="81"/>
-      <c r="BA24" s="81"/>
-      <c r="BB24" s="81"/>
-      <c r="BC24" s="81"/>
-      <c r="BD24" s="81"/>
-      <c r="BE24" s="82"/>
+      <c r="P24" s="86"/>
+      <c r="Q24" s="86"/>
+      <c r="R24" s="86"/>
+      <c r="S24" s="86"/>
+      <c r="T24" s="86"/>
+      <c r="U24" s="86"/>
+      <c r="V24" s="86"/>
+      <c r="W24" s="86"/>
+      <c r="X24" s="86"/>
+      <c r="Y24" s="86"/>
+      <c r="Z24" s="86"/>
+      <c r="AA24" s="86"/>
+      <c r="AB24" s="86"/>
+      <c r="AC24" s="86"/>
+      <c r="AD24" s="86"/>
+      <c r="AE24" s="86"/>
+      <c r="AF24" s="86"/>
+      <c r="AG24" s="86"/>
+      <c r="AH24" s="86"/>
+      <c r="AI24" s="86"/>
+      <c r="AJ24" s="86"/>
+      <c r="AK24" s="86"/>
+      <c r="AL24" s="86"/>
+      <c r="AM24" s="86"/>
+      <c r="AN24" s="86"/>
+      <c r="AO24" s="86"/>
+      <c r="AP24" s="87"/>
+      <c r="AQ24" s="91"/>
+      <c r="AR24" s="86"/>
+      <c r="AS24" s="86"/>
+      <c r="AT24" s="86"/>
+      <c r="AU24" s="86"/>
+      <c r="AV24" s="86"/>
+      <c r="AW24" s="86"/>
+      <c r="AX24" s="86"/>
+      <c r="AY24" s="86"/>
+      <c r="AZ24" s="86"/>
+      <c r="BA24" s="86"/>
+      <c r="BB24" s="86"/>
+      <c r="BC24" s="86"/>
+      <c r="BD24" s="86"/>
+      <c r="BE24" s="92"/>
     </row>
     <row r="25" spans="1:57" ht="15" customHeight="1">
-      <c r="A25" s="100"/>
-      <c r="B25" s="101"/>
-      <c r="C25" s="101"/>
-      <c r="D25" s="101"/>
-      <c r="E25" s="101"/>
-      <c r="F25" s="101"/>
-      <c r="G25" s="102"/>
+      <c r="A25" s="80"/>
+      <c r="B25" s="81"/>
+      <c r="C25" s="81"/>
+      <c r="D25" s="81"/>
+      <c r="E25" s="81"/>
+      <c r="F25" s="81"/>
+      <c r="G25" s="82"/>
       <c r="H25" s="83"/>
       <c r="I25" s="84"/>
       <c r="J25" s="84"/>
@@ -66271,57 +66271,57 @@
       <c r="M25" s="84"/>
       <c r="N25" s="85"/>
       <c r="O25" s="83"/>
-      <c r="P25" s="81"/>
-      <c r="Q25" s="81"/>
-      <c r="R25" s="81"/>
-      <c r="S25" s="81"/>
-      <c r="T25" s="81"/>
-      <c r="U25" s="81"/>
-      <c r="V25" s="81"/>
-      <c r="W25" s="81"/>
-      <c r="X25" s="81"/>
-      <c r="Y25" s="81"/>
-      <c r="Z25" s="81"/>
-      <c r="AA25" s="81"/>
-      <c r="AB25" s="81"/>
-      <c r="AC25" s="81"/>
-      <c r="AD25" s="81"/>
-      <c r="AE25" s="81"/>
-      <c r="AF25" s="81"/>
-      <c r="AG25" s="81"/>
-      <c r="AH25" s="81"/>
-      <c r="AI25" s="81"/>
-      <c r="AJ25" s="81"/>
-      <c r="AK25" s="81"/>
-      <c r="AL25" s="81"/>
-      <c r="AM25" s="81"/>
-      <c r="AN25" s="81"/>
-      <c r="AO25" s="81"/>
-      <c r="AP25" s="89"/>
-      <c r="AQ25" s="80"/>
-      <c r="AR25" s="81"/>
-      <c r="AS25" s="81"/>
-      <c r="AT25" s="81"/>
-      <c r="AU25" s="81"/>
-      <c r="AV25" s="81"/>
-      <c r="AW25" s="81"/>
-      <c r="AX25" s="81"/>
-      <c r="AY25" s="81"/>
-      <c r="AZ25" s="81"/>
-      <c r="BA25" s="81"/>
-      <c r="BB25" s="81"/>
-      <c r="BC25" s="81"/>
-      <c r="BD25" s="81"/>
-      <c r="BE25" s="82"/>
+      <c r="P25" s="86"/>
+      <c r="Q25" s="86"/>
+      <c r="R25" s="86"/>
+      <c r="S25" s="86"/>
+      <c r="T25" s="86"/>
+      <c r="U25" s="86"/>
+      <c r="V25" s="86"/>
+      <c r="W25" s="86"/>
+      <c r="X25" s="86"/>
+      <c r="Y25" s="86"/>
+      <c r="Z25" s="86"/>
+      <c r="AA25" s="86"/>
+      <c r="AB25" s="86"/>
+      <c r="AC25" s="86"/>
+      <c r="AD25" s="86"/>
+      <c r="AE25" s="86"/>
+      <c r="AF25" s="86"/>
+      <c r="AG25" s="86"/>
+      <c r="AH25" s="86"/>
+      <c r="AI25" s="86"/>
+      <c r="AJ25" s="86"/>
+      <c r="AK25" s="86"/>
+      <c r="AL25" s="86"/>
+      <c r="AM25" s="86"/>
+      <c r="AN25" s="86"/>
+      <c r="AO25" s="86"/>
+      <c r="AP25" s="87"/>
+      <c r="AQ25" s="91"/>
+      <c r="AR25" s="86"/>
+      <c r="AS25" s="86"/>
+      <c r="AT25" s="86"/>
+      <c r="AU25" s="86"/>
+      <c r="AV25" s="86"/>
+      <c r="AW25" s="86"/>
+      <c r="AX25" s="86"/>
+      <c r="AY25" s="86"/>
+      <c r="AZ25" s="86"/>
+      <c r="BA25" s="86"/>
+      <c r="BB25" s="86"/>
+      <c r="BC25" s="86"/>
+      <c r="BD25" s="86"/>
+      <c r="BE25" s="92"/>
     </row>
     <row r="26" spans="1:57" ht="15" customHeight="1">
-      <c r="A26" s="100"/>
-      <c r="B26" s="101"/>
-      <c r="C26" s="101"/>
-      <c r="D26" s="101"/>
-      <c r="E26" s="101"/>
-      <c r="F26" s="101"/>
-      <c r="G26" s="102"/>
+      <c r="A26" s="80"/>
+      <c r="B26" s="81"/>
+      <c r="C26" s="81"/>
+      <c r="D26" s="81"/>
+      <c r="E26" s="81"/>
+      <c r="F26" s="81"/>
+      <c r="G26" s="82"/>
       <c r="H26" s="83"/>
       <c r="I26" s="84"/>
       <c r="J26" s="84"/>
@@ -66330,57 +66330,57 @@
       <c r="M26" s="84"/>
       <c r="N26" s="85"/>
       <c r="O26" s="83"/>
-      <c r="P26" s="81"/>
-      <c r="Q26" s="81"/>
-      <c r="R26" s="81"/>
-      <c r="S26" s="81"/>
-      <c r="T26" s="81"/>
-      <c r="U26" s="81"/>
-      <c r="V26" s="81"/>
-      <c r="W26" s="81"/>
-      <c r="X26" s="81"/>
-      <c r="Y26" s="81"/>
-      <c r="Z26" s="81"/>
-      <c r="AA26" s="81"/>
-      <c r="AB26" s="81"/>
-      <c r="AC26" s="81"/>
-      <c r="AD26" s="81"/>
-      <c r="AE26" s="81"/>
-      <c r="AF26" s="81"/>
-      <c r="AG26" s="81"/>
-      <c r="AH26" s="81"/>
-      <c r="AI26" s="81"/>
-      <c r="AJ26" s="81"/>
-      <c r="AK26" s="81"/>
-      <c r="AL26" s="81"/>
-      <c r="AM26" s="81"/>
-      <c r="AN26" s="81"/>
-      <c r="AO26" s="81"/>
-      <c r="AP26" s="89"/>
-      <c r="AQ26" s="80"/>
-      <c r="AR26" s="81"/>
-      <c r="AS26" s="81"/>
-      <c r="AT26" s="81"/>
-      <c r="AU26" s="81"/>
-      <c r="AV26" s="81"/>
-      <c r="AW26" s="81"/>
-      <c r="AX26" s="81"/>
-      <c r="AY26" s="81"/>
-      <c r="AZ26" s="81"/>
-      <c r="BA26" s="81"/>
-      <c r="BB26" s="81"/>
-      <c r="BC26" s="81"/>
-      <c r="BD26" s="81"/>
-      <c r="BE26" s="82"/>
+      <c r="P26" s="86"/>
+      <c r="Q26" s="86"/>
+      <c r="R26" s="86"/>
+      <c r="S26" s="86"/>
+      <c r="T26" s="86"/>
+      <c r="U26" s="86"/>
+      <c r="V26" s="86"/>
+      <c r="W26" s="86"/>
+      <c r="X26" s="86"/>
+      <c r="Y26" s="86"/>
+      <c r="Z26" s="86"/>
+      <c r="AA26" s="86"/>
+      <c r="AB26" s="86"/>
+      <c r="AC26" s="86"/>
+      <c r="AD26" s="86"/>
+      <c r="AE26" s="86"/>
+      <c r="AF26" s="86"/>
+      <c r="AG26" s="86"/>
+      <c r="AH26" s="86"/>
+      <c r="AI26" s="86"/>
+      <c r="AJ26" s="86"/>
+      <c r="AK26" s="86"/>
+      <c r="AL26" s="86"/>
+      <c r="AM26" s="86"/>
+      <c r="AN26" s="86"/>
+      <c r="AO26" s="86"/>
+      <c r="AP26" s="87"/>
+      <c r="AQ26" s="91"/>
+      <c r="AR26" s="86"/>
+      <c r="AS26" s="86"/>
+      <c r="AT26" s="86"/>
+      <c r="AU26" s="86"/>
+      <c r="AV26" s="86"/>
+      <c r="AW26" s="86"/>
+      <c r="AX26" s="86"/>
+      <c r="AY26" s="86"/>
+      <c r="AZ26" s="86"/>
+      <c r="BA26" s="86"/>
+      <c r="BB26" s="86"/>
+      <c r="BC26" s="86"/>
+      <c r="BD26" s="86"/>
+      <c r="BE26" s="92"/>
     </row>
     <row r="27" spans="1:57" ht="15" customHeight="1">
-      <c r="A27" s="100"/>
-      <c r="B27" s="101"/>
-      <c r="C27" s="101"/>
-      <c r="D27" s="101"/>
-      <c r="E27" s="101"/>
-      <c r="F27" s="101"/>
-      <c r="G27" s="102"/>
+      <c r="A27" s="80"/>
+      <c r="B27" s="81"/>
+      <c r="C27" s="81"/>
+      <c r="D27" s="81"/>
+      <c r="E27" s="81"/>
+      <c r="F27" s="81"/>
+      <c r="G27" s="82"/>
       <c r="H27" s="83"/>
       <c r="I27" s="84"/>
       <c r="J27" s="84"/>
@@ -66389,57 +66389,57 @@
       <c r="M27" s="84"/>
       <c r="N27" s="85"/>
       <c r="O27" s="83"/>
-      <c r="P27" s="81"/>
-      <c r="Q27" s="81"/>
-      <c r="R27" s="81"/>
-      <c r="S27" s="81"/>
-      <c r="T27" s="81"/>
-      <c r="U27" s="81"/>
-      <c r="V27" s="81"/>
-      <c r="W27" s="81"/>
-      <c r="X27" s="81"/>
-      <c r="Y27" s="81"/>
-      <c r="Z27" s="81"/>
-      <c r="AA27" s="81"/>
-      <c r="AB27" s="81"/>
-      <c r="AC27" s="81"/>
-      <c r="AD27" s="81"/>
-      <c r="AE27" s="81"/>
-      <c r="AF27" s="81"/>
-      <c r="AG27" s="81"/>
-      <c r="AH27" s="81"/>
-      <c r="AI27" s="81"/>
-      <c r="AJ27" s="81"/>
-      <c r="AK27" s="81"/>
-      <c r="AL27" s="81"/>
-      <c r="AM27" s="81"/>
-      <c r="AN27" s="81"/>
-      <c r="AO27" s="81"/>
-      <c r="AP27" s="89"/>
-      <c r="AQ27" s="80"/>
-      <c r="AR27" s="81"/>
-      <c r="AS27" s="81"/>
-      <c r="AT27" s="81"/>
-      <c r="AU27" s="81"/>
-      <c r="AV27" s="81"/>
-      <c r="AW27" s="81"/>
-      <c r="AX27" s="81"/>
-      <c r="AY27" s="81"/>
-      <c r="AZ27" s="81"/>
-      <c r="BA27" s="81"/>
-      <c r="BB27" s="81"/>
-      <c r="BC27" s="81"/>
-      <c r="BD27" s="81"/>
-      <c r="BE27" s="82"/>
+      <c r="P27" s="86"/>
+      <c r="Q27" s="86"/>
+      <c r="R27" s="86"/>
+      <c r="S27" s="86"/>
+      <c r="T27" s="86"/>
+      <c r="U27" s="86"/>
+      <c r="V27" s="86"/>
+      <c r="W27" s="86"/>
+      <c r="X27" s="86"/>
+      <c r="Y27" s="86"/>
+      <c r="Z27" s="86"/>
+      <c r="AA27" s="86"/>
+      <c r="AB27" s="86"/>
+      <c r="AC27" s="86"/>
+      <c r="AD27" s="86"/>
+      <c r="AE27" s="86"/>
+      <c r="AF27" s="86"/>
+      <c r="AG27" s="86"/>
+      <c r="AH27" s="86"/>
+      <c r="AI27" s="86"/>
+      <c r="AJ27" s="86"/>
+      <c r="AK27" s="86"/>
+      <c r="AL27" s="86"/>
+      <c r="AM27" s="86"/>
+      <c r="AN27" s="86"/>
+      <c r="AO27" s="86"/>
+      <c r="AP27" s="87"/>
+      <c r="AQ27" s="91"/>
+      <c r="AR27" s="86"/>
+      <c r="AS27" s="86"/>
+      <c r="AT27" s="86"/>
+      <c r="AU27" s="86"/>
+      <c r="AV27" s="86"/>
+      <c r="AW27" s="86"/>
+      <c r="AX27" s="86"/>
+      <c r="AY27" s="86"/>
+      <c r="AZ27" s="86"/>
+      <c r="BA27" s="86"/>
+      <c r="BB27" s="86"/>
+      <c r="BC27" s="86"/>
+      <c r="BD27" s="86"/>
+      <c r="BE27" s="92"/>
     </row>
     <row r="28" spans="1:57" ht="15" customHeight="1">
-      <c r="A28" s="100"/>
-      <c r="B28" s="101"/>
-      <c r="C28" s="101"/>
-      <c r="D28" s="101"/>
-      <c r="E28" s="101"/>
-      <c r="F28" s="101"/>
-      <c r="G28" s="102"/>
+      <c r="A28" s="80"/>
+      <c r="B28" s="81"/>
+      <c r="C28" s="81"/>
+      <c r="D28" s="81"/>
+      <c r="E28" s="81"/>
+      <c r="F28" s="81"/>
+      <c r="G28" s="82"/>
       <c r="H28" s="83"/>
       <c r="I28" s="84"/>
       <c r="J28" s="84"/>
@@ -66448,57 +66448,57 @@
       <c r="M28" s="84"/>
       <c r="N28" s="85"/>
       <c r="O28" s="83"/>
-      <c r="P28" s="81"/>
-      <c r="Q28" s="81"/>
-      <c r="R28" s="81"/>
-      <c r="S28" s="81"/>
-      <c r="T28" s="81"/>
-      <c r="U28" s="81"/>
-      <c r="V28" s="81"/>
-      <c r="W28" s="81"/>
-      <c r="X28" s="81"/>
-      <c r="Y28" s="81"/>
-      <c r="Z28" s="81"/>
-      <c r="AA28" s="81"/>
-      <c r="AB28" s="81"/>
-      <c r="AC28" s="81"/>
-      <c r="AD28" s="81"/>
-      <c r="AE28" s="81"/>
-      <c r="AF28" s="81"/>
-      <c r="AG28" s="81"/>
-      <c r="AH28" s="81"/>
-      <c r="AI28" s="81"/>
-      <c r="AJ28" s="81"/>
-      <c r="AK28" s="81"/>
-      <c r="AL28" s="81"/>
-      <c r="AM28" s="81"/>
-      <c r="AN28" s="81"/>
-      <c r="AO28" s="81"/>
-      <c r="AP28" s="89"/>
-      <c r="AQ28" s="80"/>
-      <c r="AR28" s="81"/>
-      <c r="AS28" s="81"/>
-      <c r="AT28" s="81"/>
-      <c r="AU28" s="81"/>
-      <c r="AV28" s="81"/>
-      <c r="AW28" s="81"/>
-      <c r="AX28" s="81"/>
-      <c r="AY28" s="81"/>
-      <c r="AZ28" s="81"/>
-      <c r="BA28" s="81"/>
-      <c r="BB28" s="81"/>
-      <c r="BC28" s="81"/>
-      <c r="BD28" s="81"/>
-      <c r="BE28" s="82"/>
+      <c r="P28" s="86"/>
+      <c r="Q28" s="86"/>
+      <c r="R28" s="86"/>
+      <c r="S28" s="86"/>
+      <c r="T28" s="86"/>
+      <c r="U28" s="86"/>
+      <c r="V28" s="86"/>
+      <c r="W28" s="86"/>
+      <c r="X28" s="86"/>
+      <c r="Y28" s="86"/>
+      <c r="Z28" s="86"/>
+      <c r="AA28" s="86"/>
+      <c r="AB28" s="86"/>
+      <c r="AC28" s="86"/>
+      <c r="AD28" s="86"/>
+      <c r="AE28" s="86"/>
+      <c r="AF28" s="86"/>
+      <c r="AG28" s="86"/>
+      <c r="AH28" s="86"/>
+      <c r="AI28" s="86"/>
+      <c r="AJ28" s="86"/>
+      <c r="AK28" s="86"/>
+      <c r="AL28" s="86"/>
+      <c r="AM28" s="86"/>
+      <c r="AN28" s="86"/>
+      <c r="AO28" s="86"/>
+      <c r="AP28" s="87"/>
+      <c r="AQ28" s="91"/>
+      <c r="AR28" s="86"/>
+      <c r="AS28" s="86"/>
+      <c r="AT28" s="86"/>
+      <c r="AU28" s="86"/>
+      <c r="AV28" s="86"/>
+      <c r="AW28" s="86"/>
+      <c r="AX28" s="86"/>
+      <c r="AY28" s="86"/>
+      <c r="AZ28" s="86"/>
+      <c r="BA28" s="86"/>
+      <c r="BB28" s="86"/>
+      <c r="BC28" s="86"/>
+      <c r="BD28" s="86"/>
+      <c r="BE28" s="92"/>
     </row>
     <row r="29" spans="1:57" ht="15" customHeight="1">
-      <c r="A29" s="100"/>
-      <c r="B29" s="101"/>
-      <c r="C29" s="101"/>
-      <c r="D29" s="101"/>
-      <c r="E29" s="101"/>
-      <c r="F29" s="101"/>
-      <c r="G29" s="102"/>
+      <c r="A29" s="80"/>
+      <c r="B29" s="81"/>
+      <c r="C29" s="81"/>
+      <c r="D29" s="81"/>
+      <c r="E29" s="81"/>
+      <c r="F29" s="81"/>
+      <c r="G29" s="82"/>
       <c r="H29" s="83"/>
       <c r="I29" s="84"/>
       <c r="J29" s="84"/>
@@ -66507,57 +66507,57 @@
       <c r="M29" s="84"/>
       <c r="N29" s="85"/>
       <c r="O29" s="83"/>
-      <c r="P29" s="81"/>
-      <c r="Q29" s="81"/>
-      <c r="R29" s="81"/>
-      <c r="S29" s="81"/>
-      <c r="T29" s="81"/>
-      <c r="U29" s="81"/>
-      <c r="V29" s="81"/>
-      <c r="W29" s="81"/>
-      <c r="X29" s="81"/>
-      <c r="Y29" s="81"/>
-      <c r="Z29" s="81"/>
-      <c r="AA29" s="81"/>
-      <c r="AB29" s="81"/>
-      <c r="AC29" s="81"/>
-      <c r="AD29" s="81"/>
-      <c r="AE29" s="81"/>
-      <c r="AF29" s="81"/>
-      <c r="AG29" s="81"/>
-      <c r="AH29" s="81"/>
-      <c r="AI29" s="81"/>
-      <c r="AJ29" s="81"/>
-      <c r="AK29" s="81"/>
-      <c r="AL29" s="81"/>
-      <c r="AM29" s="81"/>
-      <c r="AN29" s="81"/>
-      <c r="AO29" s="81"/>
-      <c r="AP29" s="89"/>
-      <c r="AQ29" s="80"/>
-      <c r="AR29" s="81"/>
-      <c r="AS29" s="81"/>
-      <c r="AT29" s="81"/>
-      <c r="AU29" s="81"/>
-      <c r="AV29" s="81"/>
-      <c r="AW29" s="81"/>
-      <c r="AX29" s="81"/>
-      <c r="AY29" s="81"/>
-      <c r="AZ29" s="81"/>
-      <c r="BA29" s="81"/>
-      <c r="BB29" s="81"/>
-      <c r="BC29" s="81"/>
-      <c r="BD29" s="81"/>
-      <c r="BE29" s="82"/>
+      <c r="P29" s="86"/>
+      <c r="Q29" s="86"/>
+      <c r="R29" s="86"/>
+      <c r="S29" s="86"/>
+      <c r="T29" s="86"/>
+      <c r="U29" s="86"/>
+      <c r="V29" s="86"/>
+      <c r="W29" s="86"/>
+      <c r="X29" s="86"/>
+      <c r="Y29" s="86"/>
+      <c r="Z29" s="86"/>
+      <c r="AA29" s="86"/>
+      <c r="AB29" s="86"/>
+      <c r="AC29" s="86"/>
+      <c r="AD29" s="86"/>
+      <c r="AE29" s="86"/>
+      <c r="AF29" s="86"/>
+      <c r="AG29" s="86"/>
+      <c r="AH29" s="86"/>
+      <c r="AI29" s="86"/>
+      <c r="AJ29" s="86"/>
+      <c r="AK29" s="86"/>
+      <c r="AL29" s="86"/>
+      <c r="AM29" s="86"/>
+      <c r="AN29" s="86"/>
+      <c r="AO29" s="86"/>
+      <c r="AP29" s="87"/>
+      <c r="AQ29" s="91"/>
+      <c r="AR29" s="86"/>
+      <c r="AS29" s="86"/>
+      <c r="AT29" s="86"/>
+      <c r="AU29" s="86"/>
+      <c r="AV29" s="86"/>
+      <c r="AW29" s="86"/>
+      <c r="AX29" s="86"/>
+      <c r="AY29" s="86"/>
+      <c r="AZ29" s="86"/>
+      <c r="BA29" s="86"/>
+      <c r="BB29" s="86"/>
+      <c r="BC29" s="86"/>
+      <c r="BD29" s="86"/>
+      <c r="BE29" s="92"/>
     </row>
     <row r="30" spans="1:57" ht="15" customHeight="1">
-      <c r="A30" s="100"/>
-      <c r="B30" s="101"/>
-      <c r="C30" s="101"/>
-      <c r="D30" s="101"/>
-      <c r="E30" s="101"/>
-      <c r="F30" s="101"/>
-      <c r="G30" s="102"/>
+      <c r="A30" s="80"/>
+      <c r="B30" s="81"/>
+      <c r="C30" s="81"/>
+      <c r="D30" s="81"/>
+      <c r="E30" s="81"/>
+      <c r="F30" s="81"/>
+      <c r="G30" s="82"/>
       <c r="H30" s="83"/>
       <c r="I30" s="84"/>
       <c r="J30" s="84"/>
@@ -66566,57 +66566,57 @@
       <c r="M30" s="84"/>
       <c r="N30" s="85"/>
       <c r="O30" s="83"/>
-      <c r="P30" s="81"/>
-      <c r="Q30" s="81"/>
-      <c r="R30" s="81"/>
-      <c r="S30" s="81"/>
-      <c r="T30" s="81"/>
-      <c r="U30" s="81"/>
-      <c r="V30" s="81"/>
-      <c r="W30" s="81"/>
-      <c r="X30" s="81"/>
-      <c r="Y30" s="81"/>
-      <c r="Z30" s="81"/>
-      <c r="AA30" s="81"/>
-      <c r="AB30" s="81"/>
-      <c r="AC30" s="81"/>
-      <c r="AD30" s="81"/>
-      <c r="AE30" s="81"/>
-      <c r="AF30" s="81"/>
-      <c r="AG30" s="81"/>
-      <c r="AH30" s="81"/>
-      <c r="AI30" s="81"/>
-      <c r="AJ30" s="81"/>
-      <c r="AK30" s="81"/>
-      <c r="AL30" s="81"/>
-      <c r="AM30" s="81"/>
-      <c r="AN30" s="81"/>
-      <c r="AO30" s="81"/>
-      <c r="AP30" s="89"/>
-      <c r="AQ30" s="80"/>
-      <c r="AR30" s="81"/>
-      <c r="AS30" s="81"/>
-      <c r="AT30" s="81"/>
-      <c r="AU30" s="81"/>
-      <c r="AV30" s="81"/>
-      <c r="AW30" s="81"/>
-      <c r="AX30" s="81"/>
-      <c r="AY30" s="81"/>
-      <c r="AZ30" s="81"/>
-      <c r="BA30" s="81"/>
-      <c r="BB30" s="81"/>
-      <c r="BC30" s="81"/>
-      <c r="BD30" s="81"/>
-      <c r="BE30" s="82"/>
+      <c r="P30" s="86"/>
+      <c r="Q30" s="86"/>
+      <c r="R30" s="86"/>
+      <c r="S30" s="86"/>
+      <c r="T30" s="86"/>
+      <c r="U30" s="86"/>
+      <c r="V30" s="86"/>
+      <c r="W30" s="86"/>
+      <c r="X30" s="86"/>
+      <c r="Y30" s="86"/>
+      <c r="Z30" s="86"/>
+      <c r="AA30" s="86"/>
+      <c r="AB30" s="86"/>
+      <c r="AC30" s="86"/>
+      <c r="AD30" s="86"/>
+      <c r="AE30" s="86"/>
+      <c r="AF30" s="86"/>
+      <c r="AG30" s="86"/>
+      <c r="AH30" s="86"/>
+      <c r="AI30" s="86"/>
+      <c r="AJ30" s="86"/>
+      <c r="AK30" s="86"/>
+      <c r="AL30" s="86"/>
+      <c r="AM30" s="86"/>
+      <c r="AN30" s="86"/>
+      <c r="AO30" s="86"/>
+      <c r="AP30" s="87"/>
+      <c r="AQ30" s="91"/>
+      <c r="AR30" s="86"/>
+      <c r="AS30" s="86"/>
+      <c r="AT30" s="86"/>
+      <c r="AU30" s="86"/>
+      <c r="AV30" s="86"/>
+      <c r="AW30" s="86"/>
+      <c r="AX30" s="86"/>
+      <c r="AY30" s="86"/>
+      <c r="AZ30" s="86"/>
+      <c r="BA30" s="86"/>
+      <c r="BB30" s="86"/>
+      <c r="BC30" s="86"/>
+      <c r="BD30" s="86"/>
+      <c r="BE30" s="92"/>
     </row>
     <row r="31" spans="1:57" ht="15" customHeight="1">
-      <c r="A31" s="100"/>
-      <c r="B31" s="101"/>
-      <c r="C31" s="101"/>
-      <c r="D31" s="101"/>
-      <c r="E31" s="101"/>
-      <c r="F31" s="101"/>
-      <c r="G31" s="102"/>
+      <c r="A31" s="80"/>
+      <c r="B31" s="81"/>
+      <c r="C31" s="81"/>
+      <c r="D31" s="81"/>
+      <c r="E31" s="81"/>
+      <c r="F31" s="81"/>
+      <c r="G31" s="82"/>
       <c r="H31" s="83"/>
       <c r="I31" s="84"/>
       <c r="J31" s="84"/>
@@ -66625,57 +66625,57 @@
       <c r="M31" s="84"/>
       <c r="N31" s="85"/>
       <c r="O31" s="83"/>
-      <c r="P31" s="81"/>
-      <c r="Q31" s="81"/>
-      <c r="R31" s="81"/>
-      <c r="S31" s="81"/>
-      <c r="T31" s="81"/>
-      <c r="U31" s="81"/>
-      <c r="V31" s="81"/>
-      <c r="W31" s="81"/>
-      <c r="X31" s="81"/>
-      <c r="Y31" s="81"/>
-      <c r="Z31" s="81"/>
-      <c r="AA31" s="81"/>
-      <c r="AB31" s="81"/>
-      <c r="AC31" s="81"/>
-      <c r="AD31" s="81"/>
-      <c r="AE31" s="81"/>
-      <c r="AF31" s="81"/>
-      <c r="AG31" s="81"/>
-      <c r="AH31" s="81"/>
-      <c r="AI31" s="81"/>
-      <c r="AJ31" s="81"/>
-      <c r="AK31" s="81"/>
-      <c r="AL31" s="81"/>
-      <c r="AM31" s="81"/>
-      <c r="AN31" s="81"/>
-      <c r="AO31" s="81"/>
-      <c r="AP31" s="89"/>
-      <c r="AQ31" s="80"/>
-      <c r="AR31" s="81"/>
-      <c r="AS31" s="81"/>
-      <c r="AT31" s="81"/>
-      <c r="AU31" s="81"/>
-      <c r="AV31" s="81"/>
-      <c r="AW31" s="81"/>
-      <c r="AX31" s="81"/>
-      <c r="AY31" s="81"/>
-      <c r="AZ31" s="81"/>
-      <c r="BA31" s="81"/>
-      <c r="BB31" s="81"/>
-      <c r="BC31" s="81"/>
-      <c r="BD31" s="81"/>
-      <c r="BE31" s="82"/>
+      <c r="P31" s="86"/>
+      <c r="Q31" s="86"/>
+      <c r="R31" s="86"/>
+      <c r="S31" s="86"/>
+      <c r="T31" s="86"/>
+      <c r="U31" s="86"/>
+      <c r="V31" s="86"/>
+      <c r="W31" s="86"/>
+      <c r="X31" s="86"/>
+      <c r="Y31" s="86"/>
+      <c r="Z31" s="86"/>
+      <c r="AA31" s="86"/>
+      <c r="AB31" s="86"/>
+      <c r="AC31" s="86"/>
+      <c r="AD31" s="86"/>
+      <c r="AE31" s="86"/>
+      <c r="AF31" s="86"/>
+      <c r="AG31" s="86"/>
+      <c r="AH31" s="86"/>
+      <c r="AI31" s="86"/>
+      <c r="AJ31" s="86"/>
+      <c r="AK31" s="86"/>
+      <c r="AL31" s="86"/>
+      <c r="AM31" s="86"/>
+      <c r="AN31" s="86"/>
+      <c r="AO31" s="86"/>
+      <c r="AP31" s="87"/>
+      <c r="AQ31" s="91"/>
+      <c r="AR31" s="86"/>
+      <c r="AS31" s="86"/>
+      <c r="AT31" s="86"/>
+      <c r="AU31" s="86"/>
+      <c r="AV31" s="86"/>
+      <c r="AW31" s="86"/>
+      <c r="AX31" s="86"/>
+      <c r="AY31" s="86"/>
+      <c r="AZ31" s="86"/>
+      <c r="BA31" s="86"/>
+      <c r="BB31" s="86"/>
+      <c r="BC31" s="86"/>
+      <c r="BD31" s="86"/>
+      <c r="BE31" s="92"/>
     </row>
     <row r="32" spans="1:57" ht="15" customHeight="1">
-      <c r="A32" s="100"/>
-      <c r="B32" s="101"/>
-      <c r="C32" s="101"/>
-      <c r="D32" s="101"/>
-      <c r="E32" s="101"/>
-      <c r="F32" s="101"/>
-      <c r="G32" s="102"/>
+      <c r="A32" s="80"/>
+      <c r="B32" s="81"/>
+      <c r="C32" s="81"/>
+      <c r="D32" s="81"/>
+      <c r="E32" s="81"/>
+      <c r="F32" s="81"/>
+      <c r="G32" s="82"/>
       <c r="H32" s="83"/>
       <c r="I32" s="84"/>
       <c r="J32" s="84"/>
@@ -66684,57 +66684,57 @@
       <c r="M32" s="84"/>
       <c r="N32" s="85"/>
       <c r="O32" s="83"/>
-      <c r="P32" s="81"/>
-      <c r="Q32" s="81"/>
-      <c r="R32" s="81"/>
-      <c r="S32" s="81"/>
-      <c r="T32" s="81"/>
-      <c r="U32" s="81"/>
-      <c r="V32" s="81"/>
-      <c r="W32" s="81"/>
-      <c r="X32" s="81"/>
-      <c r="Y32" s="81"/>
-      <c r="Z32" s="81"/>
-      <c r="AA32" s="81"/>
-      <c r="AB32" s="81"/>
-      <c r="AC32" s="81"/>
-      <c r="AD32" s="81"/>
-      <c r="AE32" s="81"/>
-      <c r="AF32" s="81"/>
-      <c r="AG32" s="81"/>
-      <c r="AH32" s="81"/>
-      <c r="AI32" s="81"/>
-      <c r="AJ32" s="81"/>
-      <c r="AK32" s="81"/>
-      <c r="AL32" s="81"/>
-      <c r="AM32" s="81"/>
-      <c r="AN32" s="81"/>
-      <c r="AO32" s="81"/>
-      <c r="AP32" s="89"/>
-      <c r="AQ32" s="80"/>
-      <c r="AR32" s="81"/>
-      <c r="AS32" s="81"/>
-      <c r="AT32" s="81"/>
-      <c r="AU32" s="81"/>
-      <c r="AV32" s="81"/>
-      <c r="AW32" s="81"/>
-      <c r="AX32" s="81"/>
-      <c r="AY32" s="81"/>
-      <c r="AZ32" s="81"/>
-      <c r="BA32" s="81"/>
-      <c r="BB32" s="81"/>
-      <c r="BC32" s="81"/>
-      <c r="BD32" s="81"/>
-      <c r="BE32" s="82"/>
+      <c r="P32" s="86"/>
+      <c r="Q32" s="86"/>
+      <c r="R32" s="86"/>
+      <c r="S32" s="86"/>
+      <c r="T32" s="86"/>
+      <c r="U32" s="86"/>
+      <c r="V32" s="86"/>
+      <c r="W32" s="86"/>
+      <c r="X32" s="86"/>
+      <c r="Y32" s="86"/>
+      <c r="Z32" s="86"/>
+      <c r="AA32" s="86"/>
+      <c r="AB32" s="86"/>
+      <c r="AC32" s="86"/>
+      <c r="AD32" s="86"/>
+      <c r="AE32" s="86"/>
+      <c r="AF32" s="86"/>
+      <c r="AG32" s="86"/>
+      <c r="AH32" s="86"/>
+      <c r="AI32" s="86"/>
+      <c r="AJ32" s="86"/>
+      <c r="AK32" s="86"/>
+      <c r="AL32" s="86"/>
+      <c r="AM32" s="86"/>
+      <c r="AN32" s="86"/>
+      <c r="AO32" s="86"/>
+      <c r="AP32" s="87"/>
+      <c r="AQ32" s="91"/>
+      <c r="AR32" s="86"/>
+      <c r="AS32" s="86"/>
+      <c r="AT32" s="86"/>
+      <c r="AU32" s="86"/>
+      <c r="AV32" s="86"/>
+      <c r="AW32" s="86"/>
+      <c r="AX32" s="86"/>
+      <c r="AY32" s="86"/>
+      <c r="AZ32" s="86"/>
+      <c r="BA32" s="86"/>
+      <c r="BB32" s="86"/>
+      <c r="BC32" s="86"/>
+      <c r="BD32" s="86"/>
+      <c r="BE32" s="92"/>
     </row>
     <row r="33" spans="1:57" ht="15" customHeight="1">
-      <c r="A33" s="100"/>
-      <c r="B33" s="101"/>
-      <c r="C33" s="101"/>
-      <c r="D33" s="101"/>
-      <c r="E33" s="101"/>
-      <c r="F33" s="101"/>
-      <c r="G33" s="102"/>
+      <c r="A33" s="80"/>
+      <c r="B33" s="81"/>
+      <c r="C33" s="81"/>
+      <c r="D33" s="81"/>
+      <c r="E33" s="81"/>
+      <c r="F33" s="81"/>
+      <c r="G33" s="82"/>
       <c r="H33" s="83"/>
       <c r="I33" s="84"/>
       <c r="J33" s="84"/>
@@ -66743,57 +66743,57 @@
       <c r="M33" s="84"/>
       <c r="N33" s="85"/>
       <c r="O33" s="83"/>
-      <c r="P33" s="81"/>
-      <c r="Q33" s="81"/>
-      <c r="R33" s="81"/>
-      <c r="S33" s="81"/>
-      <c r="T33" s="81"/>
-      <c r="U33" s="81"/>
-      <c r="V33" s="81"/>
-      <c r="W33" s="81"/>
-      <c r="X33" s="81"/>
-      <c r="Y33" s="81"/>
-      <c r="Z33" s="81"/>
-      <c r="AA33" s="81"/>
-      <c r="AB33" s="81"/>
-      <c r="AC33" s="81"/>
-      <c r="AD33" s="81"/>
-      <c r="AE33" s="81"/>
-      <c r="AF33" s="81"/>
-      <c r="AG33" s="81"/>
-      <c r="AH33" s="81"/>
-      <c r="AI33" s="81"/>
-      <c r="AJ33" s="81"/>
-      <c r="AK33" s="81"/>
-      <c r="AL33" s="81"/>
-      <c r="AM33" s="81"/>
-      <c r="AN33" s="81"/>
-      <c r="AO33" s="81"/>
-      <c r="AP33" s="89"/>
-      <c r="AQ33" s="80"/>
-      <c r="AR33" s="81"/>
-      <c r="AS33" s="81"/>
-      <c r="AT33" s="81"/>
-      <c r="AU33" s="81"/>
-      <c r="AV33" s="81"/>
-      <c r="AW33" s="81"/>
-      <c r="AX33" s="81"/>
-      <c r="AY33" s="81"/>
-      <c r="AZ33" s="81"/>
-      <c r="BA33" s="81"/>
-      <c r="BB33" s="81"/>
-      <c r="BC33" s="81"/>
-      <c r="BD33" s="81"/>
-      <c r="BE33" s="82"/>
+      <c r="P33" s="86"/>
+      <c r="Q33" s="86"/>
+      <c r="R33" s="86"/>
+      <c r="S33" s="86"/>
+      <c r="T33" s="86"/>
+      <c r="U33" s="86"/>
+      <c r="V33" s="86"/>
+      <c r="W33" s="86"/>
+      <c r="X33" s="86"/>
+      <c r="Y33" s="86"/>
+      <c r="Z33" s="86"/>
+      <c r="AA33" s="86"/>
+      <c r="AB33" s="86"/>
+      <c r="AC33" s="86"/>
+      <c r="AD33" s="86"/>
+      <c r="AE33" s="86"/>
+      <c r="AF33" s="86"/>
+      <c r="AG33" s="86"/>
+      <c r="AH33" s="86"/>
+      <c r="AI33" s="86"/>
+      <c r="AJ33" s="86"/>
+      <c r="AK33" s="86"/>
+      <c r="AL33" s="86"/>
+      <c r="AM33" s="86"/>
+      <c r="AN33" s="86"/>
+      <c r="AO33" s="86"/>
+      <c r="AP33" s="87"/>
+      <c r="AQ33" s="91"/>
+      <c r="AR33" s="86"/>
+      <c r="AS33" s="86"/>
+      <c r="AT33" s="86"/>
+      <c r="AU33" s="86"/>
+      <c r="AV33" s="86"/>
+      <c r="AW33" s="86"/>
+      <c r="AX33" s="86"/>
+      <c r="AY33" s="86"/>
+      <c r="AZ33" s="86"/>
+      <c r="BA33" s="86"/>
+      <c r="BB33" s="86"/>
+      <c r="BC33" s="86"/>
+      <c r="BD33" s="86"/>
+      <c r="BE33" s="92"/>
     </row>
     <row r="34" spans="1:57" ht="15" customHeight="1">
-      <c r="A34" s="100"/>
-      <c r="B34" s="101"/>
-      <c r="C34" s="101"/>
-      <c r="D34" s="101"/>
-      <c r="E34" s="101"/>
-      <c r="F34" s="101"/>
-      <c r="G34" s="102"/>
+      <c r="A34" s="80"/>
+      <c r="B34" s="81"/>
+      <c r="C34" s="81"/>
+      <c r="D34" s="81"/>
+      <c r="E34" s="81"/>
+      <c r="F34" s="81"/>
+      <c r="G34" s="82"/>
       <c r="H34" s="83"/>
       <c r="I34" s="84"/>
       <c r="J34" s="84"/>
@@ -66802,110 +66802,219 @@
       <c r="M34" s="84"/>
       <c r="N34" s="85"/>
       <c r="O34" s="83"/>
-      <c r="P34" s="81"/>
-      <c r="Q34" s="81"/>
-      <c r="R34" s="81"/>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="81"/>
-      <c r="V34" s="81"/>
-      <c r="W34" s="81"/>
-      <c r="X34" s="81"/>
-      <c r="Y34" s="81"/>
-      <c r="Z34" s="81"/>
-      <c r="AA34" s="81"/>
-      <c r="AB34" s="81"/>
-      <c r="AC34" s="81"/>
-      <c r="AD34" s="81"/>
-      <c r="AE34" s="81"/>
-      <c r="AF34" s="81"/>
-      <c r="AG34" s="81"/>
-      <c r="AH34" s="81"/>
-      <c r="AI34" s="81"/>
-      <c r="AJ34" s="81"/>
-      <c r="AK34" s="81"/>
-      <c r="AL34" s="81"/>
-      <c r="AM34" s="81"/>
-      <c r="AN34" s="81"/>
-      <c r="AO34" s="81"/>
-      <c r="AP34" s="89"/>
-      <c r="AQ34" s="80"/>
-      <c r="AR34" s="81"/>
-      <c r="AS34" s="81"/>
-      <c r="AT34" s="81"/>
-      <c r="AU34" s="81"/>
-      <c r="AV34" s="81"/>
-      <c r="AW34" s="81"/>
-      <c r="AX34" s="81"/>
-      <c r="AY34" s="81"/>
-      <c r="AZ34" s="81"/>
-      <c r="BA34" s="81"/>
-      <c r="BB34" s="81"/>
-      <c r="BC34" s="81"/>
-      <c r="BD34" s="81"/>
-      <c r="BE34" s="82"/>
+      <c r="P34" s="86"/>
+      <c r="Q34" s="86"/>
+      <c r="R34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="86"/>
+      <c r="V34" s="86"/>
+      <c r="W34" s="86"/>
+      <c r="X34" s="86"/>
+      <c r="Y34" s="86"/>
+      <c r="Z34" s="86"/>
+      <c r="AA34" s="86"/>
+      <c r="AB34" s="86"/>
+      <c r="AC34" s="86"/>
+      <c r="AD34" s="86"/>
+      <c r="AE34" s="86"/>
+      <c r="AF34" s="86"/>
+      <c r="AG34" s="86"/>
+      <c r="AH34" s="86"/>
+      <c r="AI34" s="86"/>
+      <c r="AJ34" s="86"/>
+      <c r="AK34" s="86"/>
+      <c r="AL34" s="86"/>
+      <c r="AM34" s="86"/>
+      <c r="AN34" s="86"/>
+      <c r="AO34" s="86"/>
+      <c r="AP34" s="87"/>
+      <c r="AQ34" s="91"/>
+      <c r="AR34" s="86"/>
+      <c r="AS34" s="86"/>
+      <c r="AT34" s="86"/>
+      <c r="AU34" s="86"/>
+      <c r="AV34" s="86"/>
+      <c r="AW34" s="86"/>
+      <c r="AX34" s="86"/>
+      <c r="AY34" s="86"/>
+      <c r="AZ34" s="86"/>
+      <c r="BA34" s="86"/>
+      <c r="BB34" s="86"/>
+      <c r="BC34" s="86"/>
+      <c r="BD34" s="86"/>
+      <c r="BE34" s="92"/>
     </row>
     <row r="35" spans="1:57" ht="15" customHeight="1" thickBot="1">
-      <c r="A35" s="121"/>
-      <c r="B35" s="122"/>
-      <c r="C35" s="122"/>
-      <c r="D35" s="122"/>
-      <c r="E35" s="122"/>
-      <c r="F35" s="122"/>
-      <c r="G35" s="123"/>
-      <c r="H35" s="127"/>
-      <c r="I35" s="128"/>
-      <c r="J35" s="128"/>
-      <c r="K35" s="128"/>
-      <c r="L35" s="128"/>
-      <c r="M35" s="128"/>
-      <c r="N35" s="129"/>
-      <c r="O35" s="127"/>
-      <c r="P35" s="125"/>
-      <c r="Q35" s="125"/>
-      <c r="R35" s="125"/>
-      <c r="S35" s="125"/>
-      <c r="T35" s="125"/>
-      <c r="U35" s="125"/>
-      <c r="V35" s="125"/>
-      <c r="W35" s="125"/>
-      <c r="X35" s="125"/>
-      <c r="Y35" s="125"/>
-      <c r="Z35" s="125"/>
-      <c r="AA35" s="125"/>
-      <c r="AB35" s="125"/>
-      <c r="AC35" s="125"/>
-      <c r="AD35" s="125"/>
-      <c r="AE35" s="125"/>
-      <c r="AF35" s="125"/>
-      <c r="AG35" s="125"/>
-      <c r="AH35" s="125"/>
-      <c r="AI35" s="125"/>
-      <c r="AJ35" s="125"/>
-      <c r="AK35" s="125"/>
-      <c r="AL35" s="125"/>
-      <c r="AM35" s="125"/>
-      <c r="AN35" s="125"/>
-      <c r="AO35" s="125"/>
-      <c r="AP35" s="130"/>
-      <c r="AQ35" s="124"/>
-      <c r="AR35" s="125"/>
-      <c r="AS35" s="125"/>
-      <c r="AT35" s="125"/>
-      <c r="AU35" s="125"/>
-      <c r="AV35" s="125"/>
-      <c r="AW35" s="125"/>
-      <c r="AX35" s="125"/>
-      <c r="AY35" s="125"/>
-      <c r="AZ35" s="125"/>
-      <c r="BA35" s="125"/>
-      <c r="BB35" s="125"/>
-      <c r="BC35" s="125"/>
-      <c r="BD35" s="125"/>
-      <c r="BE35" s="126"/>
+      <c r="A35" s="97"/>
+      <c r="B35" s="98"/>
+      <c r="C35" s="98"/>
+      <c r="D35" s="98"/>
+      <c r="E35" s="98"/>
+      <c r="F35" s="98"/>
+      <c r="G35" s="99"/>
+      <c r="H35" s="93"/>
+      <c r="I35" s="94"/>
+      <c r="J35" s="94"/>
+      <c r="K35" s="94"/>
+      <c r="L35" s="94"/>
+      <c r="M35" s="94"/>
+      <c r="N35" s="95"/>
+      <c r="O35" s="93"/>
+      <c r="P35" s="89"/>
+      <c r="Q35" s="89"/>
+      <c r="R35" s="89"/>
+      <c r="S35" s="89"/>
+      <c r="T35" s="89"/>
+      <c r="U35" s="89"/>
+      <c r="V35" s="89"/>
+      <c r="W35" s="89"/>
+      <c r="X35" s="89"/>
+      <c r="Y35" s="89"/>
+      <c r="Z35" s="89"/>
+      <c r="AA35" s="89"/>
+      <c r="AB35" s="89"/>
+      <c r="AC35" s="89"/>
+      <c r="AD35" s="89"/>
+      <c r="AE35" s="89"/>
+      <c r="AF35" s="89"/>
+      <c r="AG35" s="89"/>
+      <c r="AH35" s="89"/>
+      <c r="AI35" s="89"/>
+      <c r="AJ35" s="89"/>
+      <c r="AK35" s="89"/>
+      <c r="AL35" s="89"/>
+      <c r="AM35" s="89"/>
+      <c r="AN35" s="89"/>
+      <c r="AO35" s="89"/>
+      <c r="AP35" s="96"/>
+      <c r="AQ35" s="88"/>
+      <c r="AR35" s="89"/>
+      <c r="AS35" s="89"/>
+      <c r="AT35" s="89"/>
+      <c r="AU35" s="89"/>
+      <c r="AV35" s="89"/>
+      <c r="AW35" s="89"/>
+      <c r="AX35" s="89"/>
+      <c r="AY35" s="89"/>
+      <c r="AZ35" s="89"/>
+      <c r="BA35" s="89"/>
+      <c r="BB35" s="89"/>
+      <c r="BC35" s="89"/>
+      <c r="BD35" s="89"/>
+      <c r="BE35" s="90"/>
     </row>
   </sheetData>
   <mergeCells count="133">
+    <mergeCell ref="AQ22:BE22"/>
+    <mergeCell ref="AQ29:BE29"/>
+    <mergeCell ref="H17:N17"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="H12:N12"/>
+    <mergeCell ref="O12:AP12"/>
+    <mergeCell ref="AQ12:BE12"/>
+    <mergeCell ref="H8:N8"/>
+    <mergeCell ref="AQ6:BE6"/>
+    <mergeCell ref="H5:N5"/>
+    <mergeCell ref="O8:AP8"/>
+    <mergeCell ref="AQ8:BE8"/>
+    <mergeCell ref="O5:AP5"/>
+    <mergeCell ref="AQ5:BE5"/>
+    <mergeCell ref="H6:N6"/>
+    <mergeCell ref="O6:AP6"/>
+    <mergeCell ref="H7:N7"/>
+    <mergeCell ref="O7:AP7"/>
+    <mergeCell ref="AQ7:BE7"/>
+    <mergeCell ref="AQ15:BE15"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="O16:AP16"/>
+    <mergeCell ref="O17:AP17"/>
+    <mergeCell ref="A1:BE1"/>
+    <mergeCell ref="H3:N3"/>
+    <mergeCell ref="O3:AP3"/>
+    <mergeCell ref="AQ3:BE3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="O15:AP15"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="H4:N4"/>
+    <mergeCell ref="O4:AP4"/>
+    <mergeCell ref="AQ4:BE4"/>
+    <mergeCell ref="H13:N13"/>
+    <mergeCell ref="O13:AP13"/>
+    <mergeCell ref="AQ13:BE13"/>
+    <mergeCell ref="H14:N14"/>
+    <mergeCell ref="O14:AP14"/>
+    <mergeCell ref="AQ14:BE14"/>
+    <mergeCell ref="AQ16:BE16"/>
+    <mergeCell ref="H15:N15"/>
+    <mergeCell ref="O18:AP18"/>
+    <mergeCell ref="H9:N9"/>
+    <mergeCell ref="O9:AP9"/>
+    <mergeCell ref="AQ9:BE9"/>
+    <mergeCell ref="H10:N10"/>
+    <mergeCell ref="O10:AP10"/>
+    <mergeCell ref="AQ10:BE10"/>
+    <mergeCell ref="H11:N11"/>
+    <mergeCell ref="O11:AP11"/>
+    <mergeCell ref="AQ11:BE11"/>
+    <mergeCell ref="H16:N16"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:AP20"/>
+    <mergeCell ref="AQ17:BE17"/>
+    <mergeCell ref="H26:N26"/>
+    <mergeCell ref="O26:AP26"/>
+    <mergeCell ref="AQ26:BE26"/>
+    <mergeCell ref="AQ19:BE19"/>
+    <mergeCell ref="H25:N25"/>
+    <mergeCell ref="H24:N24"/>
+    <mergeCell ref="O24:AP24"/>
+    <mergeCell ref="O25:AP25"/>
+    <mergeCell ref="AQ25:BE25"/>
+    <mergeCell ref="H22:N22"/>
+    <mergeCell ref="AQ24:BE24"/>
+    <mergeCell ref="H23:N23"/>
+    <mergeCell ref="O23:AP23"/>
+    <mergeCell ref="AQ23:BE23"/>
+    <mergeCell ref="AQ20:BE20"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:AP21"/>
+    <mergeCell ref="AQ18:BE18"/>
+    <mergeCell ref="AQ21:BE21"/>
+    <mergeCell ref="O22:AP22"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="H33:N33"/>
+    <mergeCell ref="H34:N34"/>
+    <mergeCell ref="O34:AP34"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="O33:AP33"/>
+    <mergeCell ref="O32:AP32"/>
+    <mergeCell ref="H31:N31"/>
+    <mergeCell ref="O31:AP31"/>
+    <mergeCell ref="H27:N27"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="H32:N32"/>
+    <mergeCell ref="H29:N29"/>
+    <mergeCell ref="O29:AP29"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A24:G24"/>
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="H19:N19"/>
     <mergeCell ref="O19:AP19"/>
@@ -66930,115 +67039,6 @@
     <mergeCell ref="A31:G31"/>
     <mergeCell ref="A25:G25"/>
     <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="H33:N33"/>
-    <mergeCell ref="H34:N34"/>
-    <mergeCell ref="O34:AP34"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="O33:AP33"/>
-    <mergeCell ref="O32:AP32"/>
-    <mergeCell ref="H31:N31"/>
-    <mergeCell ref="O31:AP31"/>
-    <mergeCell ref="H27:N27"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="H32:N32"/>
-    <mergeCell ref="H29:N29"/>
-    <mergeCell ref="O29:AP29"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:AP20"/>
-    <mergeCell ref="AQ17:BE17"/>
-    <mergeCell ref="H26:N26"/>
-    <mergeCell ref="O26:AP26"/>
-    <mergeCell ref="AQ26:BE26"/>
-    <mergeCell ref="AQ19:BE19"/>
-    <mergeCell ref="H25:N25"/>
-    <mergeCell ref="H24:N24"/>
-    <mergeCell ref="O24:AP24"/>
-    <mergeCell ref="O25:AP25"/>
-    <mergeCell ref="AQ25:BE25"/>
-    <mergeCell ref="H22:N22"/>
-    <mergeCell ref="AQ24:BE24"/>
-    <mergeCell ref="H23:N23"/>
-    <mergeCell ref="O23:AP23"/>
-    <mergeCell ref="AQ23:BE23"/>
-    <mergeCell ref="AQ20:BE20"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:AP21"/>
-    <mergeCell ref="AQ18:BE18"/>
-    <mergeCell ref="AQ21:BE21"/>
-    <mergeCell ref="O22:AP22"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="H4:N4"/>
-    <mergeCell ref="O4:AP4"/>
-    <mergeCell ref="AQ4:BE4"/>
-    <mergeCell ref="H13:N13"/>
-    <mergeCell ref="O13:AP13"/>
-    <mergeCell ref="AQ13:BE13"/>
-    <mergeCell ref="H14:N14"/>
-    <mergeCell ref="O14:AP14"/>
-    <mergeCell ref="AQ14:BE14"/>
-    <mergeCell ref="AQ16:BE16"/>
-    <mergeCell ref="H15:N15"/>
-    <mergeCell ref="O18:AP18"/>
-    <mergeCell ref="H9:N9"/>
-    <mergeCell ref="O9:AP9"/>
-    <mergeCell ref="AQ9:BE9"/>
-    <mergeCell ref="H10:N10"/>
-    <mergeCell ref="O10:AP10"/>
-    <mergeCell ref="AQ10:BE10"/>
-    <mergeCell ref="H11:N11"/>
-    <mergeCell ref="O11:AP11"/>
-    <mergeCell ref="AQ11:BE11"/>
-    <mergeCell ref="H16:N16"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="O15:AP15"/>
-    <mergeCell ref="A1:BE1"/>
-    <mergeCell ref="H3:N3"/>
-    <mergeCell ref="O3:AP3"/>
-    <mergeCell ref="AQ3:BE3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="AQ22:BE22"/>
-    <mergeCell ref="AQ29:BE29"/>
-    <mergeCell ref="H17:N17"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="H12:N12"/>
-    <mergeCell ref="O12:AP12"/>
-    <mergeCell ref="AQ12:BE12"/>
-    <mergeCell ref="H8:N8"/>
-    <mergeCell ref="AQ6:BE6"/>
-    <mergeCell ref="H5:N5"/>
-    <mergeCell ref="O8:AP8"/>
-    <mergeCell ref="AQ8:BE8"/>
-    <mergeCell ref="O5:AP5"/>
-    <mergeCell ref="AQ5:BE5"/>
-    <mergeCell ref="H6:N6"/>
-    <mergeCell ref="O6:AP6"/>
-    <mergeCell ref="H7:N7"/>
-    <mergeCell ref="O7:AP7"/>
-    <mergeCell ref="AQ7:BE7"/>
-    <mergeCell ref="AQ15:BE15"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="O16:AP16"/>
-    <mergeCell ref="O17:AP17"/>
   </mergeCells>
   <phoneticPr fontId="5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>

--- a/development/MS/spec/MSBB/Panel/MSBBP1210_SloReg.xlsx
+++ b/development/MS/spec/MSBB/Panel/MSBBP1210_SloReg.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\PJ\TK\dev\development\MS\spec\MSBB\Panel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\mcframeDEV\development\MS\spec\MSBB\Panel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20AF0756-7B07-43A6-BF50-D4C4C17E8AB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A30C42AE-E223-41D0-9916-2027258F96EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MSBBP1210" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9122" uniqueCount="2367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9144" uniqueCount="2367">
   <si>
     <t>検索</t>
     <rPh sb="0" eb="2">
@@ -11428,6 +11428,9 @@
     <xf numFmtId="0" fontId="33" fillId="25" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="33" fillId="25" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -11617,64 +11620,54 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="25" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="44">
-    <cellStyle name="20% - アクセント 1" xfId="1" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - アクセント 2" xfId="2" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - アクセント 3" xfId="3" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - アクセント 4" xfId="4" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - アクセント 5" xfId="5" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - アクセント 6" xfId="6" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - アクセント 1" xfId="7" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - アクセント 2" xfId="8" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - アクセント 3" xfId="9" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - アクセント 4" xfId="10" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - アクセント 5" xfId="11" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - アクセント 6" xfId="12" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - アクセント 1" xfId="13" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - アクセント 2" xfId="14" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - アクセント 3" xfId="15" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - アクセント 4" xfId="16" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - アクセント 5" xfId="17" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - アクセント 6" xfId="18" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="20% - Accent1" xfId="1" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="2" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="3" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="4" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="5" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="6" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="7" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="8" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="9" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="10" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="11" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="12" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="13" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="14" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="15" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="16" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="17" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="18" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="19" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="20" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="21" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="22" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="23" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="24" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="30" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="31" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="26" builtinId="23" customBuiltin="1"/>
     <cellStyle name="Comma [0]" xfId="42" hidden="1" xr:uid="{00000000-0005-0000-0000-00006D000000}"/>
     <cellStyle name="Currency [0]" xfId="43" hidden="1" xr:uid="{00000000-0005-0000-0000-000071000000}"/>
-    <cellStyle name="アクセント 1" xfId="19" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="アクセント 2" xfId="20" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="アクセント 3" xfId="21" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="アクセント 4" xfId="22" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="アクセント 5" xfId="23" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="アクセント 6" xfId="24" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="タイトル" xfId="25" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="チェック セル" xfId="26" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="どちらでもない" xfId="27" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="メモ" xfId="28" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="リンク セル" xfId="29" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="悪い" xfId="30" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="計算" xfId="31" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="警告文" xfId="32" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="見出し 1" xfId="33" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="見出し 2" xfId="34" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="見出し 3" xfId="35" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="見出し 4" xfId="36" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="集計" xfId="37" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="出力" xfId="38" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="説明文" xfId="39" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="入力" xfId="40" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
-    <cellStyle name="良い" xfId="41" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="39" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="41" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="33" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="34" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="35" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="36" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="40" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="29" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="27" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="28" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="38" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="25" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="37" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="32" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="28">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="27">
     <dxf>
       <fill>
         <patternFill>
@@ -12301,21 +12294,21 @@
       <c r="F2" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="68" t="s">
+      <c r="G2" s="69" t="s">
         <v>1269</v>
       </c>
-      <c r="H2" s="74"/>
-      <c r="I2" s="77" t="s">
+      <c r="H2" s="75"/>
+      <c r="I2" s="78" t="s">
         <v>348</v>
       </c>
-      <c r="J2" s="78"/>
-      <c r="K2" s="71" t="s">
+      <c r="J2" s="79"/>
+      <c r="K2" s="72" t="s">
         <v>1276</v>
       </c>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
-      <c r="N2" s="72"/>
-      <c r="O2" s="68"/>
+      <c r="L2" s="73"/>
+      <c r="M2" s="73"/>
+      <c r="N2" s="73"/>
+      <c r="O2" s="69"/>
       <c r="P2" s="41"/>
       <c r="Q2" s="42" t="s">
         <v>64</v>
@@ -12371,21 +12364,21 @@
       <c r="F3" s="25" t="s">
         <v>137</v>
       </c>
-      <c r="G3" s="75" t="s">
+      <c r="G3" s="76" t="s">
         <v>1279</v>
       </c>
-      <c r="H3" s="76"/>
-      <c r="I3" s="77" t="s">
+      <c r="H3" s="77"/>
+      <c r="I3" s="78" t="s">
         <v>350</v>
       </c>
-      <c r="J3" s="78"/>
-      <c r="K3" s="71" t="s">
+      <c r="J3" s="79"/>
+      <c r="K3" s="72" t="s">
         <v>1280</v>
       </c>
-      <c r="L3" s="72"/>
-      <c r="M3" s="72"/>
-      <c r="N3" s="72"/>
-      <c r="O3" s="68"/>
+      <c r="L3" s="73"/>
+      <c r="M3" s="73"/>
+      <c r="N3" s="73"/>
+      <c r="O3" s="69"/>
       <c r="P3" s="41"/>
       <c r="Q3" s="25"/>
       <c r="R3" s="40" t="s">
@@ -12441,21 +12434,21 @@
       <c r="F4" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="75" t="s">
+      <c r="G4" s="76" t="s">
         <v>1281</v>
       </c>
-      <c r="H4" s="76"/>
-      <c r="I4" s="77" t="s">
+      <c r="H4" s="77"/>
+      <c r="I4" s="78" t="s">
         <v>349</v>
       </c>
-      <c r="J4" s="78"/>
-      <c r="K4" s="72" t="s">
+      <c r="J4" s="79"/>
+      <c r="K4" s="73" t="s">
         <v>1270</v>
       </c>
-      <c r="L4" s="72"/>
-      <c r="M4" s="72"/>
-      <c r="N4" s="72"/>
-      <c r="O4" s="68"/>
+      <c r="L4" s="73"/>
+      <c r="M4" s="73"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="69"/>
       <c r="P4" s="41"/>
       <c r="Q4" s="25" t="s">
         <v>71</v>
@@ -12509,12 +12502,12 @@
       <c r="F5" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="G5" s="75" t="s">
+      <c r="G5" s="76" t="s">
         <v>1283</v>
       </c>
-      <c r="H5" s="76"/>
-      <c r="I5" s="79"/>
-      <c r="J5" s="79"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="80"/>
       <c r="K5" s="46"/>
       <c r="L5" s="46"/>
       <c r="M5" s="46"/>
@@ -12567,17 +12560,17 @@
       <c r="D6" s="3" t="s">
         <v>1284</v>
       </c>
-      <c r="E6" s="73"/>
-      <c r="F6" s="73"/>
-      <c r="G6" s="73"/>
-      <c r="H6" s="73"/>
-      <c r="I6" s="73"/>
-      <c r="J6" s="73"/>
-      <c r="K6" s="73"/>
-      <c r="L6" s="73"/>
-      <c r="M6" s="73"/>
-      <c r="N6" s="73"/>
-      <c r="O6" s="73"/>
+      <c r="E6" s="74"/>
+      <c r="F6" s="74"/>
+      <c r="G6" s="74"/>
+      <c r="H6" s="74"/>
+      <c r="I6" s="74"/>
+      <c r="J6" s="74"/>
+      <c r="K6" s="74"/>
+      <c r="L6" s="74"/>
+      <c r="M6" s="74"/>
+      <c r="N6" s="74"/>
+      <c r="O6" s="74"/>
       <c r="P6" s="24"/>
       <c r="Q6" s="8"/>
       <c r="R6" s="8"/>
@@ -12771,11 +12764,11 @@
       <c r="P8" s="40" t="s">
         <v>1500</v>
       </c>
-      <c r="Q8" s="68" t="s">
+      <c r="Q8" s="69" t="s">
         <v>1838</v>
       </c>
-      <c r="R8" s="69"/>
-      <c r="S8" s="70"/>
+      <c r="R8" s="70"/>
+      <c r="S8" s="71"/>
       <c r="T8" s="7" t="s">
         <v>1839</v>
       </c>
@@ -39377,125 +39370,110 @@
       <c r="AX325" s="25"/>
       <c r="AZ325" s="26"/>
     </row>
-    <row r="326" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A326" s="50">
-        <v>70</v>
-      </c>
-      <c r="B326" s="50"/>
-      <c r="C326" s="50"/>
-      <c r="D326" s="50" t="s">
-        <v>812</v>
-      </c>
-      <c r="E326" s="50"/>
-      <c r="F326" s="50"/>
-      <c r="G326" s="50"/>
-      <c r="H326" s="50"/>
-      <c r="I326" s="50" t="s">
-        <v>31</v>
-      </c>
-      <c r="J326" s="50"/>
-      <c r="K326" s="50" t="s">
-        <v>250</v>
-      </c>
-      <c r="L326" s="50" t="s">
-        <v>1158</v>
-      </c>
-      <c r="M326" s="50"/>
-      <c r="N326" s="50"/>
-      <c r="O326" s="50"/>
-      <c r="P326" s="50"/>
-      <c r="Q326" s="50"/>
-      <c r="R326" s="50"/>
-      <c r="S326" s="50"/>
-      <c r="T326" s="50"/>
-      <c r="U326" s="50"/>
-      <c r="V326" s="50"/>
-      <c r="W326" s="50"/>
-      <c r="X326" s="50"/>
-      <c r="Y326" s="50"/>
-      <c r="Z326" s="50" t="s">
-        <v>81</v>
-      </c>
-      <c r="AA326" s="50" t="s">
-        <v>81</v>
-      </c>
-      <c r="AB326" s="50" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC326" s="50" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD326" s="50" t="s">
-        <v>81</v>
-      </c>
-      <c r="AE326" s="50"/>
-      <c r="AF326" s="50" t="s">
-        <v>81</v>
-      </c>
-      <c r="AG326" s="50" t="s">
-        <v>30</v>
-      </c>
-      <c r="AH326" s="50" t="s">
-        <v>30</v>
-      </c>
-      <c r="AI326" s="50" t="s">
-        <v>81</v>
-      </c>
-      <c r="AJ326" s="50" t="s">
-        <v>81</v>
-      </c>
-      <c r="AK326" s="50" t="s">
-        <v>81</v>
-      </c>
-      <c r="AL326" s="50"/>
-      <c r="AM326" s="50"/>
-      <c r="AN326" s="50"/>
-      <c r="AO326" s="50"/>
-      <c r="AP326" s="50"/>
-      <c r="AQ326" s="50"/>
-      <c r="AR326" s="50"/>
-      <c r="AS326" s="50"/>
-      <c r="AT326" s="50"/>
-      <c r="AU326" s="50"/>
-      <c r="AV326" s="50"/>
-      <c r="AW326" s="50"/>
-      <c r="AX326" s="50"/>
-      <c r="AY326" s="50"/>
-      <c r="AZ326" s="50"/>
-    </row>
-    <row r="327" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A327" s="50">
-        <v>70</v>
-      </c>
-      <c r="B327" s="25"/>
-      <c r="C327" s="25"/>
-      <c r="D327" s="25" t="s">
-        <v>949</v>
-      </c>
-      <c r="E327" s="37"/>
-      <c r="F327" s="25"/>
-      <c r="G327" s="25"/>
-      <c r="H327" s="25"/>
-      <c r="I327" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="J327" s="25"/>
-      <c r="K327" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="L327" s="25"/>
-      <c r="M327" s="25"/>
-      <c r="N327" s="25"/>
-      <c r="O327" s="25"/>
-      <c r="P327" s="25"/>
-      <c r="Q327" s="25"/>
-      <c r="R327" s="25"/>
-      <c r="S327" s="25"/>
-      <c r="T327" s="25"/>
-      <c r="U327" s="25"/>
-      <c r="V327" s="25"/>
-      <c r="W327" s="25"/>
-      <c r="X327" s="25"/>
+    <row r="326" spans="1:52" s="66" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A326" s="63">
+        <v>70</v>
+      </c>
+      <c r="B326" s="65"/>
+      <c r="C326" s="65"/>
+      <c r="D326" s="65" t="s">
+        <v>1718</v>
+      </c>
+      <c r="E326" s="64"/>
+      <c r="F326" s="65"/>
+      <c r="G326" s="65" t="s">
+        <v>2366</v>
+      </c>
+      <c r="H326" s="65"/>
+      <c r="I326" s="65" t="s">
+        <v>2333</v>
+      </c>
+      <c r="J326" s="65"/>
+      <c r="K326" s="65" t="s">
+        <v>2251</v>
+      </c>
+      <c r="L326" s="65"/>
+      <c r="M326" s="65"/>
+      <c r="N326" s="65"/>
+      <c r="O326" s="65"/>
+      <c r="P326" s="65"/>
+      <c r="Q326" s="65"/>
+      <c r="R326" s="65"/>
+      <c r="S326" s="65"/>
+      <c r="T326" s="65"/>
+      <c r="U326" s="65"/>
+      <c r="V326" s="65"/>
+      <c r="W326" s="65"/>
+      <c r="X326" s="65"/>
+      <c r="Z326" s="65"/>
+      <c r="AA326" s="65"/>
+      <c r="AB326" s="65"/>
+      <c r="AC326" s="65"/>
+      <c r="AD326" s="65"/>
+      <c r="AE326" s="65"/>
+      <c r="AF326" s="65"/>
+      <c r="AG326" s="65"/>
+      <c r="AH326" s="65"/>
+      <c r="AI326" s="65"/>
+      <c r="AJ326" s="65"/>
+      <c r="AK326" s="65"/>
+      <c r="AM326" s="65"/>
+      <c r="AN326" s="65" t="s">
+        <v>968</v>
+      </c>
+      <c r="AO326" s="65"/>
+      <c r="AP326" s="65" t="s">
+        <v>968</v>
+      </c>
+      <c r="AQ326" s="65" t="s">
+        <v>968</v>
+      </c>
+      <c r="AR326" s="65"/>
+      <c r="AS326" s="65" t="s">
+        <v>968</v>
+      </c>
+      <c r="AT326" s="65"/>
+      <c r="AU326" s="65"/>
+      <c r="AV326" s="65"/>
+      <c r="AW326" s="65"/>
+      <c r="AX326" s="65"/>
+      <c r="AZ326" s="68"/>
+    </row>
+    <row r="327" spans="1:52" s="66" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A327" s="63">
+        <v>70</v>
+      </c>
+      <c r="B327" s="65"/>
+      <c r="C327" s="65"/>
+      <c r="D327" s="65" t="s">
+        <v>2362</v>
+      </c>
+      <c r="E327" s="64"/>
+      <c r="F327" s="65"/>
+      <c r="G327" s="65" t="s">
+        <v>2363</v>
+      </c>
+      <c r="H327" s="65"/>
+      <c r="I327" s="65" t="s">
+        <v>2333</v>
+      </c>
+      <c r="J327" s="65"/>
+      <c r="K327" s="65" t="s">
+        <v>2251</v>
+      </c>
+      <c r="L327" s="65"/>
+      <c r="M327" s="65"/>
+      <c r="N327" s="65"/>
+      <c r="O327" s="65"/>
+      <c r="P327" s="65"/>
+      <c r="Q327" s="65"/>
+      <c r="R327" s="65"/>
+      <c r="S327" s="65"/>
+      <c r="T327" s="65"/>
+      <c r="U327" s="65"/>
+      <c r="V327" s="65"/>
+      <c r="W327" s="65"/>
+      <c r="X327" s="65"/>
       <c r="Z327" s="25" t="s">
         <v>25</v>
       </c>
@@ -39503,23 +39481,23 @@
         <v>25</v>
       </c>
       <c r="AB327" s="25" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="AC327" s="25" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="AD327" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="AE327" s="25"/>
+      <c r="AE327" s="65"/>
       <c r="AF327" s="25" t="s">
         <v>25</v>
       </c>
       <c r="AG327" s="25" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="AH327" s="25" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="AI327" s="25" t="s">
         <v>25</v>
@@ -39530,157 +39508,200 @@
       <c r="AK327" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="AM327" s="25"/>
-      <c r="AN327" s="25" t="s">
-        <v>682</v>
-      </c>
-      <c r="AO327" s="25"/>
-      <c r="AP327" s="25" t="s">
-        <v>682</v>
-      </c>
-      <c r="AQ327" s="25" t="s">
-        <v>682</v>
-      </c>
-      <c r="AR327" s="25"/>
-      <c r="AS327" s="25" t="s">
-        <v>682</v>
-      </c>
-      <c r="AT327" s="25"/>
-      <c r="AU327" s="25"/>
-      <c r="AV327" s="25"/>
-      <c r="AW327" s="25"/>
-      <c r="AX327" s="25"/>
-      <c r="AZ327" s="26"/>
-    </row>
-    <row r="328" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A328" s="50">
-        <v>70</v>
-      </c>
-      <c r="B328" s="25"/>
-      <c r="C328" s="25"/>
-      <c r="D328" s="25" t="s">
-        <v>969</v>
-      </c>
-      <c r="E328" s="37"/>
-      <c r="F328" s="25"/>
-      <c r="G328" s="25"/>
-      <c r="H328" s="25"/>
-      <c r="I328" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="J328" s="25"/>
-      <c r="K328" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="L328" s="25"/>
-      <c r="M328" s="25"/>
-      <c r="N328" s="25"/>
-      <c r="O328" s="25"/>
-      <c r="P328" s="25"/>
-      <c r="Q328" s="25"/>
-      <c r="R328" s="25"/>
-      <c r="S328" s="25"/>
-      <c r="T328" s="25"/>
-      <c r="U328" s="25"/>
-      <c r="V328" s="25"/>
-      <c r="W328" s="25"/>
-      <c r="X328" s="25"/>
-      <c r="Z328" s="25"/>
-      <c r="AA328" s="25"/>
-      <c r="AB328" s="25"/>
-      <c r="AC328" s="25"/>
-      <c r="AD328" s="25"/>
-      <c r="AE328" s="25"/>
-      <c r="AF328" s="25"/>
-      <c r="AG328" s="25"/>
-      <c r="AH328" s="25"/>
-      <c r="AI328" s="25"/>
-      <c r="AJ328" s="25"/>
-      <c r="AK328" s="25"/>
-      <c r="AM328" s="25"/>
-      <c r="AN328" s="25" t="s">
-        <v>857</v>
-      </c>
-      <c r="AO328" s="25"/>
-      <c r="AP328" s="25" t="s">
-        <v>857</v>
-      </c>
-      <c r="AQ328" s="25" t="s">
-        <v>857</v>
-      </c>
-      <c r="AR328" s="25"/>
-      <c r="AS328" s="25" t="s">
-        <v>857</v>
-      </c>
-      <c r="AT328" s="25"/>
-      <c r="AU328" s="25"/>
-      <c r="AV328" s="25"/>
-      <c r="AW328" s="25"/>
-      <c r="AX328" s="25"/>
-      <c r="AZ328" s="26"/>
+      <c r="AM327" s="65"/>
+      <c r="AN327" s="65" t="s">
+        <v>886</v>
+      </c>
+      <c r="AO327" s="65"/>
+      <c r="AP327" s="65" t="s">
+        <v>886</v>
+      </c>
+      <c r="AQ327" s="65"/>
+      <c r="AR327" s="65"/>
+      <c r="AS327" s="65"/>
+      <c r="AT327" s="65"/>
+      <c r="AU327" s="65"/>
+      <c r="AV327" s="65"/>
+      <c r="AW327" s="65"/>
+      <c r="AX327" s="65"/>
+      <c r="AZ327" s="68"/>
+    </row>
+    <row r="328" spans="1:52" s="66" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A328" s="63">
+        <v>70</v>
+      </c>
+      <c r="B328" s="65"/>
+      <c r="C328" s="65"/>
+      <c r="D328" s="65" t="s">
+        <v>2364</v>
+      </c>
+      <c r="E328" s="64"/>
+      <c r="F328" s="65"/>
+      <c r="G328" s="65" t="s">
+        <v>2365</v>
+      </c>
+      <c r="H328" s="65"/>
+      <c r="I328" s="65" t="s">
+        <v>2333</v>
+      </c>
+      <c r="J328" s="65"/>
+      <c r="K328" s="65" t="s">
+        <v>2251</v>
+      </c>
+      <c r="L328" s="65"/>
+      <c r="M328" s="65"/>
+      <c r="N328" s="65"/>
+      <c r="O328" s="65"/>
+      <c r="P328" s="65"/>
+      <c r="Q328" s="65"/>
+      <c r="R328" s="65"/>
+      <c r="S328" s="65"/>
+      <c r="T328" s="65"/>
+      <c r="U328" s="65"/>
+      <c r="V328" s="65"/>
+      <c r="W328" s="65"/>
+      <c r="X328" s="65"/>
+      <c r="Z328" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA328" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB328" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC328" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD328" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE328" s="65"/>
+      <c r="AF328" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG328" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH328" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI328" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ328" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK328" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM328" s="65"/>
+      <c r="AN328" s="65" t="s">
+        <v>985</v>
+      </c>
+      <c r="AO328" s="65"/>
+      <c r="AP328" s="65" t="s">
+        <v>985</v>
+      </c>
+      <c r="AQ328" s="65" t="s">
+        <v>985</v>
+      </c>
+      <c r="AR328" s="65"/>
+      <c r="AS328" s="65" t="s">
+        <v>985</v>
+      </c>
+      <c r="AT328" s="65"/>
+      <c r="AU328" s="65"/>
+      <c r="AV328" s="65"/>
+      <c r="AW328" s="65"/>
+      <c r="AX328" s="65"/>
+      <c r="AZ328" s="68"/>
     </row>
     <row r="329" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A329" s="50">
         <v>70</v>
       </c>
-      <c r="B329" s="25"/>
-      <c r="C329" s="25"/>
-      <c r="D329" s="25" t="s">
-        <v>970</v>
-      </c>
-      <c r="E329" s="37"/>
-      <c r="F329" s="25"/>
-      <c r="G329" s="25"/>
-      <c r="H329" s="25"/>
-      <c r="I329" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="J329" s="25"/>
-      <c r="K329" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="L329" s="25"/>
-      <c r="M329" s="25"/>
-      <c r="N329" s="25"/>
-      <c r="O329" s="25"/>
-      <c r="P329" s="25"/>
-      <c r="Q329" s="25"/>
-      <c r="R329" s="25"/>
-      <c r="S329" s="25"/>
-      <c r="T329" s="25"/>
-      <c r="U329" s="25"/>
-      <c r="V329" s="25"/>
-      <c r="W329" s="25"/>
-      <c r="X329" s="25"/>
-      <c r="Z329" s="25"/>
-      <c r="AA329" s="25"/>
-      <c r="AB329" s="25"/>
-      <c r="AC329" s="25"/>
-      <c r="AD329" s="25"/>
-      <c r="AE329" s="25"/>
-      <c r="AF329" s="25"/>
-      <c r="AG329" s="25"/>
-      <c r="AH329" s="25"/>
-      <c r="AI329" s="25"/>
-      <c r="AJ329" s="25"/>
-      <c r="AK329" s="25"/>
-      <c r="AM329" s="25"/>
-      <c r="AN329" s="25" t="s">
-        <v>971</v>
-      </c>
-      <c r="AO329" s="25"/>
-      <c r="AP329" s="25" t="s">
-        <v>971</v>
-      </c>
-      <c r="AQ329" s="25"/>
-      <c r="AR329" s="25"/>
-      <c r="AS329" s="25"/>
-      <c r="AT329" s="25"/>
-      <c r="AU329" s="25"/>
-      <c r="AV329" s="25"/>
-      <c r="AW329" s="25"/>
-      <c r="AX329" s="25"/>
-      <c r="AZ329" s="26"/>
+      <c r="B329" s="50"/>
+      <c r="C329" s="50"/>
+      <c r="D329" s="50" t="s">
+        <v>812</v>
+      </c>
+      <c r="E329" s="50"/>
+      <c r="F329" s="50"/>
+      <c r="G329" s="50"/>
+      <c r="H329" s="50"/>
+      <c r="I329" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="J329" s="50"/>
+      <c r="K329" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="L329" s="50" t="s">
+        <v>1158</v>
+      </c>
+      <c r="M329" s="50"/>
+      <c r="N329" s="50"/>
+      <c r="O329" s="50"/>
+      <c r="P329" s="50"/>
+      <c r="Q329" s="50"/>
+      <c r="R329" s="50"/>
+      <c r="S329" s="50"/>
+      <c r="T329" s="50"/>
+      <c r="U329" s="50"/>
+      <c r="V329" s="50"/>
+      <c r="W329" s="50"/>
+      <c r="X329" s="50"/>
+      <c r="Y329" s="50"/>
+      <c r="Z329" s="50" t="s">
+        <v>81</v>
+      </c>
+      <c r="AA329" s="50" t="s">
+        <v>81</v>
+      </c>
+      <c r="AB329" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC329" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD329" s="50" t="s">
+        <v>81</v>
+      </c>
+      <c r="AE329" s="50"/>
+      <c r="AF329" s="50" t="s">
+        <v>81</v>
+      </c>
+      <c r="AG329" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="AH329" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="AI329" s="50" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ329" s="50" t="s">
+        <v>81</v>
+      </c>
+      <c r="AK329" s="50" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL329" s="50"/>
+      <c r="AM329" s="50"/>
+      <c r="AN329" s="50"/>
+      <c r="AO329" s="50"/>
+      <c r="AP329" s="50"/>
+      <c r="AQ329" s="50"/>
+      <c r="AR329" s="50"/>
+      <c r="AS329" s="50"/>
+      <c r="AT329" s="50"/>
+      <c r="AU329" s="50"/>
+      <c r="AV329" s="50"/>
+      <c r="AW329" s="50"/>
+      <c r="AX329" s="50"/>
+      <c r="AY329" s="50"/>
+      <c r="AZ329" s="50"/>
     </row>
     <row r="330" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A330" s="50">
@@ -39689,7 +39710,7 @@
       <c r="B330" s="25"/>
       <c r="C330" s="25"/>
       <c r="D330" s="25" t="s">
-        <v>972</v>
+        <v>949</v>
       </c>
       <c r="E330" s="37"/>
       <c r="F330" s="25"/>
@@ -39715,32 +39736,54 @@
       <c r="V330" s="25"/>
       <c r="W330" s="25"/>
       <c r="X330" s="25"/>
-      <c r="Z330" s="25"/>
-      <c r="AA330" s="25"/>
-      <c r="AB330" s="25"/>
-      <c r="AC330" s="25"/>
-      <c r="AD330" s="25"/>
+      <c r="Z330" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA330" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB330" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC330" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD330" s="25" t="s">
+        <v>25</v>
+      </c>
       <c r="AE330" s="25"/>
-      <c r="AF330" s="25"/>
-      <c r="AG330" s="25"/>
-      <c r="AH330" s="25"/>
-      <c r="AI330" s="25"/>
-      <c r="AJ330" s="25"/>
-      <c r="AK330" s="25"/>
+      <c r="AF330" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG330" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH330" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI330" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ330" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK330" s="25" t="s">
+        <v>25</v>
+      </c>
       <c r="AM330" s="25"/>
       <c r="AN330" s="25" t="s">
-        <v>973</v>
+        <v>682</v>
       </c>
       <c r="AO330" s="25"/>
       <c r="AP330" s="25" t="s">
-        <v>973</v>
+        <v>682</v>
       </c>
       <c r="AQ330" s="25" t="s">
-        <v>973</v>
+        <v>682</v>
       </c>
       <c r="AR330" s="25"/>
       <c r="AS330" s="25" t="s">
-        <v>973</v>
+        <v>682</v>
       </c>
       <c r="AT330" s="25"/>
       <c r="AU330" s="25"/>
@@ -39756,7 +39799,7 @@
       <c r="B331" s="25"/>
       <c r="C331" s="25"/>
       <c r="D331" s="25" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="E331" s="37"/>
       <c r="F331" s="25"/>
@@ -39774,13 +39817,9 @@
       <c r="N331" s="25"/>
       <c r="O331" s="25"/>
       <c r="P331" s="25"/>
-      <c r="Q331" s="25" t="s">
-        <v>611</v>
-      </c>
+      <c r="Q331" s="25"/>
       <c r="R331" s="25"/>
-      <c r="S331" s="25" t="s">
-        <v>813</v>
-      </c>
+      <c r="S331" s="25"/>
       <c r="T331" s="25"/>
       <c r="U331" s="25"/>
       <c r="V331" s="25"/>
@@ -39800,18 +39839,18 @@
       <c r="AK331" s="25"/>
       <c r="AM331" s="25"/>
       <c r="AN331" s="25" t="s">
-        <v>975</v>
+        <v>857</v>
       </c>
       <c r="AO331" s="25"/>
       <c r="AP331" s="25" t="s">
-        <v>975</v>
+        <v>857</v>
       </c>
       <c r="AQ331" s="25" t="s">
-        <v>975</v>
+        <v>857</v>
       </c>
       <c r="AR331" s="25"/>
       <c r="AS331" s="25" t="s">
-        <v>975</v>
+        <v>857</v>
       </c>
       <c r="AT331" s="25"/>
       <c r="AU331" s="25"/>
@@ -39827,7 +39866,7 @@
       <c r="B332" s="25"/>
       <c r="C332" s="25"/>
       <c r="D332" s="25" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="E332" s="37"/>
       <c r="F332" s="25"/>
@@ -39867,11 +39906,11 @@
       <c r="AK332" s="25"/>
       <c r="AM332" s="25"/>
       <c r="AN332" s="25" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
       <c r="AO332" s="25"/>
       <c r="AP332" s="25" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
       <c r="AQ332" s="25"/>
       <c r="AR332" s="25"/>
@@ -39890,7 +39929,7 @@
       <c r="B333" s="25"/>
       <c r="C333" s="25"/>
       <c r="D333" s="25" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="E333" s="37"/>
       <c r="F333" s="25"/>
@@ -39930,15 +39969,19 @@
       <c r="AK333" s="25"/>
       <c r="AM333" s="25"/>
       <c r="AN333" s="25" t="s">
-        <v>979</v>
+        <v>973</v>
       </c>
       <c r="AO333" s="25"/>
       <c r="AP333" s="25" t="s">
-        <v>979</v>
-      </c>
-      <c r="AQ333" s="25"/>
+        <v>973</v>
+      </c>
+      <c r="AQ333" s="25" t="s">
+        <v>973</v>
+      </c>
       <c r="AR333" s="25"/>
-      <c r="AS333" s="25"/>
+      <c r="AS333" s="25" t="s">
+        <v>973</v>
+      </c>
       <c r="AT333" s="25"/>
       <c r="AU333" s="25"/>
       <c r="AV333" s="25"/>
@@ -39953,7 +39996,7 @@
       <c r="B334" s="25"/>
       <c r="C334" s="25"/>
       <c r="D334" s="25" t="s">
-        <v>980</v>
+        <v>974</v>
       </c>
       <c r="E334" s="37"/>
       <c r="F334" s="25"/>
@@ -39971,9 +40014,13 @@
       <c r="N334" s="25"/>
       <c r="O334" s="25"/>
       <c r="P334" s="25"/>
-      <c r="Q334" s="25"/>
+      <c r="Q334" s="25" t="s">
+        <v>611</v>
+      </c>
       <c r="R334" s="25"/>
-      <c r="S334" s="25"/>
+      <c r="S334" s="25" t="s">
+        <v>813</v>
+      </c>
       <c r="T334" s="25"/>
       <c r="U334" s="25"/>
       <c r="V334" s="25"/>
@@ -39992,12 +40039,20 @@
       <c r="AJ334" s="25"/>
       <c r="AK334" s="25"/>
       <c r="AM334" s="25"/>
-      <c r="AN334" s="25"/>
+      <c r="AN334" s="25" t="s">
+        <v>975</v>
+      </c>
       <c r="AO334" s="25"/>
-      <c r="AP334" s="25"/>
-      <c r="AQ334" s="25"/>
+      <c r="AP334" s="25" t="s">
+        <v>975</v>
+      </c>
+      <c r="AQ334" s="25" t="s">
+        <v>975</v>
+      </c>
       <c r="AR334" s="25"/>
-      <c r="AS334" s="25"/>
+      <c r="AS334" s="25" t="s">
+        <v>975</v>
+      </c>
       <c r="AT334" s="25"/>
       <c r="AU334" s="25"/>
       <c r="AV334" s="25"/>
@@ -40012,7 +40067,7 @@
       <c r="B335" s="25"/>
       <c r="C335" s="25"/>
       <c r="D335" s="25" t="s">
-        <v>981</v>
+        <v>976</v>
       </c>
       <c r="E335" s="37"/>
       <c r="F335" s="25"/>
@@ -40052,11 +40107,11 @@
       <c r="AK335" s="25"/>
       <c r="AM335" s="25"/>
       <c r="AN335" s="25" t="s">
-        <v>982</v>
+        <v>977</v>
       </c>
       <c r="AO335" s="25"/>
       <c r="AP335" s="25" t="s">
-        <v>982</v>
+        <v>977</v>
       </c>
       <c r="AQ335" s="25"/>
       <c r="AR335" s="25"/>
@@ -40075,7 +40130,7 @@
       <c r="B336" s="25"/>
       <c r="C336" s="25"/>
       <c r="D336" s="25" t="s">
-        <v>983</v>
+        <v>978</v>
       </c>
       <c r="E336" s="37"/>
       <c r="F336" s="25"/>
@@ -40115,11 +40170,11 @@
       <c r="AK336" s="25"/>
       <c r="AM336" s="25"/>
       <c r="AN336" s="25" t="s">
-        <v>984</v>
+        <v>979</v>
       </c>
       <c r="AO336" s="25"/>
       <c r="AP336" s="25" t="s">
-        <v>984</v>
+        <v>979</v>
       </c>
       <c r="AQ336" s="25"/>
       <c r="AR336" s="25"/>
@@ -40138,7 +40193,7 @@
       <c r="B337" s="25"/>
       <c r="C337" s="25"/>
       <c r="D337" s="25" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="E337" s="37"/>
       <c r="F337" s="25"/>
@@ -40156,17 +40211,11 @@
       <c r="N337" s="25"/>
       <c r="O337" s="25"/>
       <c r="P337" s="25"/>
-      <c r="Q337" s="25" t="s">
-        <v>1410</v>
-      </c>
+      <c r="Q337" s="25"/>
       <c r="R337" s="25"/>
-      <c r="S337" s="25" t="s">
-        <v>814</v>
-      </c>
+      <c r="S337" s="25"/>
       <c r="T337" s="25"/>
-      <c r="U337" s="25" t="s">
-        <v>271</v>
-      </c>
+      <c r="U337" s="25"/>
       <c r="V337" s="25"/>
       <c r="W337" s="25"/>
       <c r="X337" s="25"/>
@@ -40183,20 +40232,12 @@
       <c r="AJ337" s="25"/>
       <c r="AK337" s="25"/>
       <c r="AM337" s="25"/>
-      <c r="AN337" s="25" t="s">
-        <v>987</v>
-      </c>
+      <c r="AN337" s="25"/>
       <c r="AO337" s="25"/>
-      <c r="AP337" s="25" t="s">
-        <v>987</v>
-      </c>
-      <c r="AQ337" s="25" t="s">
-        <v>987</v>
-      </c>
+      <c r="AP337" s="25"/>
+      <c r="AQ337" s="25"/>
       <c r="AR337" s="25"/>
-      <c r="AS337" s="25" t="s">
-        <v>987</v>
-      </c>
+      <c r="AS337" s="25"/>
       <c r="AT337" s="25"/>
       <c r="AU337" s="25"/>
       <c r="AV337" s="25"/>
@@ -40211,7 +40252,7 @@
       <c r="B338" s="25"/>
       <c r="C338" s="25"/>
       <c r="D338" s="25" t="s">
-        <v>988</v>
+        <v>981</v>
       </c>
       <c r="E338" s="37"/>
       <c r="F338" s="25"/>
@@ -40251,11 +40292,11 @@
       <c r="AK338" s="25"/>
       <c r="AM338" s="25"/>
       <c r="AN338" s="25" t="s">
-        <v>814</v>
+        <v>982</v>
       </c>
       <c r="AO338" s="25"/>
       <c r="AP338" s="25" t="s">
-        <v>814</v>
+        <v>982</v>
       </c>
       <c r="AQ338" s="25"/>
       <c r="AR338" s="25"/>
@@ -40267,208 +40308,204 @@
       <c r="AX338" s="25"/>
       <c r="AZ338" s="26"/>
     </row>
-    <row r="339" spans="1:52" s="66" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A339" s="63">
-        <v>70</v>
-      </c>
-      <c r="B339" s="65"/>
-      <c r="C339" s="65"/>
-      <c r="D339" s="65" t="s">
-        <v>1718</v>
-      </c>
-      <c r="E339" s="64"/>
-      <c r="F339" s="65"/>
-      <c r="G339" s="65" t="s">
-        <v>2366</v>
-      </c>
-      <c r="H339" s="65"/>
-      <c r="I339" s="65" t="s">
-        <v>2333</v>
-      </c>
-      <c r="J339" s="65"/>
-      <c r="K339" s="65" t="s">
-        <v>2251</v>
-      </c>
-      <c r="L339" s="65"/>
-      <c r="M339" s="65"/>
-      <c r="N339" s="65"/>
-      <c r="O339" s="65"/>
-      <c r="P339" s="65"/>
-      <c r="Q339" s="65"/>
-      <c r="R339" s="65"/>
-      <c r="S339" s="65"/>
-      <c r="T339" s="65"/>
-      <c r="U339" s="65"/>
-      <c r="V339" s="65"/>
-      <c r="W339" s="65"/>
-      <c r="X339" s="65"/>
-      <c r="Z339" s="65"/>
-      <c r="AA339" s="65"/>
-      <c r="AB339" s="65"/>
-      <c r="AC339" s="65"/>
-      <c r="AD339" s="65"/>
-      <c r="AE339" s="65"/>
-      <c r="AF339" s="65"/>
-      <c r="AG339" s="65"/>
-      <c r="AH339" s="65"/>
-      <c r="AI339" s="65"/>
-      <c r="AJ339" s="65"/>
-      <c r="AK339" s="65"/>
-      <c r="AM339" s="65"/>
-      <c r="AN339" s="65" t="s">
-        <v>968</v>
-      </c>
-      <c r="AO339" s="65"/>
-      <c r="AP339" s="65" t="s">
-        <v>968</v>
-      </c>
-      <c r="AQ339" s="65" t="s">
-        <v>968</v>
-      </c>
-      <c r="AR339" s="65"/>
-      <c r="AS339" s="65" t="s">
-        <v>968</v>
-      </c>
-      <c r="AT339" s="65"/>
-      <c r="AU339" s="65"/>
-      <c r="AV339" s="65"/>
-      <c r="AW339" s="65"/>
-      <c r="AX339" s="65"/>
-      <c r="AZ339" s="131"/>
-    </row>
-    <row r="340" spans="1:52" s="66" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A340" s="63">
-        <v>70</v>
-      </c>
-      <c r="B340" s="65"/>
-      <c r="C340" s="65"/>
-      <c r="D340" s="65" t="s">
-        <v>2364</v>
-      </c>
-      <c r="E340" s="64"/>
-      <c r="F340" s="65"/>
-      <c r="G340" s="65" t="s">
-        <v>2365</v>
-      </c>
-      <c r="H340" s="65"/>
-      <c r="I340" s="65" t="s">
-        <v>2333</v>
-      </c>
-      <c r="J340" s="65"/>
-      <c r="K340" s="65" t="s">
-        <v>2251</v>
-      </c>
-      <c r="L340" s="65"/>
-      <c r="M340" s="65"/>
-      <c r="N340" s="65"/>
-      <c r="O340" s="65"/>
-      <c r="P340" s="65"/>
-      <c r="Q340" s="65"/>
-      <c r="R340" s="65"/>
-      <c r="S340" s="65"/>
-      <c r="T340" s="65"/>
-      <c r="U340" s="65"/>
-      <c r="V340" s="65"/>
-      <c r="W340" s="65"/>
-      <c r="X340" s="65"/>
-      <c r="Z340" s="65"/>
-      <c r="AA340" s="65"/>
-      <c r="AB340" s="65"/>
-      <c r="AC340" s="65"/>
-      <c r="AD340" s="65"/>
-      <c r="AE340" s="65"/>
-      <c r="AF340" s="65"/>
-      <c r="AG340" s="65"/>
-      <c r="AH340" s="65"/>
-      <c r="AI340" s="65"/>
-      <c r="AJ340" s="65"/>
-      <c r="AK340" s="65"/>
-      <c r="AM340" s="65"/>
-      <c r="AN340" s="65" t="s">
-        <v>985</v>
-      </c>
-      <c r="AO340" s="65"/>
-      <c r="AP340" s="65" t="s">
-        <v>985</v>
-      </c>
-      <c r="AQ340" s="65" t="s">
-        <v>985</v>
-      </c>
-      <c r="AR340" s="65"/>
-      <c r="AS340" s="65" t="s">
-        <v>985</v>
-      </c>
-      <c r="AT340" s="65"/>
-      <c r="AU340" s="65"/>
-      <c r="AV340" s="65"/>
-      <c r="AW340" s="65"/>
-      <c r="AX340" s="65"/>
-      <c r="AZ340" s="131"/>
-    </row>
-    <row r="341" spans="1:52" s="66" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A341" s="63">
-        <v>70</v>
-      </c>
-      <c r="B341" s="65"/>
-      <c r="C341" s="65"/>
-      <c r="D341" s="65" t="s">
-        <v>2362</v>
-      </c>
-      <c r="E341" s="64"/>
-      <c r="F341" s="65"/>
-      <c r="G341" s="65" t="s">
-        <v>2363</v>
-      </c>
-      <c r="H341" s="65"/>
-      <c r="I341" s="65" t="s">
-        <v>2333</v>
-      </c>
-      <c r="J341" s="65"/>
-      <c r="K341" s="65" t="s">
-        <v>2251</v>
-      </c>
-      <c r="L341" s="65"/>
-      <c r="M341" s="65"/>
-      <c r="N341" s="65"/>
-      <c r="O341" s="65"/>
-      <c r="P341" s="65"/>
-      <c r="Q341" s="65"/>
-      <c r="R341" s="65"/>
-      <c r="S341" s="65"/>
-      <c r="T341" s="65"/>
-      <c r="U341" s="65"/>
-      <c r="V341" s="65"/>
-      <c r="W341" s="65"/>
-      <c r="X341" s="65"/>
-      <c r="Z341" s="65"/>
-      <c r="AA341" s="65"/>
-      <c r="AB341" s="65"/>
-      <c r="AC341" s="65"/>
-      <c r="AD341" s="65"/>
-      <c r="AE341" s="65"/>
-      <c r="AF341" s="65"/>
-      <c r="AG341" s="65"/>
-      <c r="AH341" s="65"/>
-      <c r="AI341" s="65"/>
-      <c r="AJ341" s="65"/>
-      <c r="AK341" s="65"/>
-      <c r="AM341" s="65"/>
-      <c r="AN341" s="65" t="s">
-        <v>886</v>
-      </c>
-      <c r="AO341" s="65"/>
-      <c r="AP341" s="65" t="s">
-        <v>886</v>
-      </c>
-      <c r="AQ341" s="65"/>
-      <c r="AR341" s="65"/>
-      <c r="AS341" s="65"/>
-      <c r="AT341" s="65"/>
-      <c r="AU341" s="65"/>
-      <c r="AV341" s="65"/>
-      <c r="AW341" s="65"/>
-      <c r="AX341" s="65"/>
-      <c r="AZ341" s="131"/>
+    <row r="339" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A339" s="50">
+        <v>70</v>
+      </c>
+      <c r="B339" s="25"/>
+      <c r="C339" s="25"/>
+      <c r="D339" s="25" t="s">
+        <v>983</v>
+      </c>
+      <c r="E339" s="37"/>
+      <c r="F339" s="25"/>
+      <c r="G339" s="25"/>
+      <c r="H339" s="25"/>
+      <c r="I339" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="J339" s="25"/>
+      <c r="K339" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L339" s="25"/>
+      <c r="M339" s="25"/>
+      <c r="N339" s="25"/>
+      <c r="O339" s="25"/>
+      <c r="P339" s="25"/>
+      <c r="Q339" s="25"/>
+      <c r="R339" s="25"/>
+      <c r="S339" s="25"/>
+      <c r="T339" s="25"/>
+      <c r="U339" s="25"/>
+      <c r="V339" s="25"/>
+      <c r="W339" s="25"/>
+      <c r="X339" s="25"/>
+      <c r="Z339" s="25"/>
+      <c r="AA339" s="25"/>
+      <c r="AB339" s="25"/>
+      <c r="AC339" s="25"/>
+      <c r="AD339" s="25"/>
+      <c r="AE339" s="25"/>
+      <c r="AF339" s="25"/>
+      <c r="AG339" s="25"/>
+      <c r="AH339" s="25"/>
+      <c r="AI339" s="25"/>
+      <c r="AJ339" s="25"/>
+      <c r="AK339" s="25"/>
+      <c r="AM339" s="25"/>
+      <c r="AN339" s="25" t="s">
+        <v>984</v>
+      </c>
+      <c r="AO339" s="25"/>
+      <c r="AP339" s="25" t="s">
+        <v>984</v>
+      </c>
+      <c r="AQ339" s="25"/>
+      <c r="AR339" s="25"/>
+      <c r="AS339" s="25"/>
+      <c r="AT339" s="25"/>
+      <c r="AU339" s="25"/>
+      <c r="AV339" s="25"/>
+      <c r="AW339" s="25"/>
+      <c r="AX339" s="25"/>
+      <c r="AZ339" s="26"/>
+    </row>
+    <row r="340" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A340" s="50">
+        <v>70</v>
+      </c>
+      <c r="B340" s="25"/>
+      <c r="C340" s="25"/>
+      <c r="D340" s="25" t="s">
+        <v>986</v>
+      </c>
+      <c r="E340" s="37"/>
+      <c r="F340" s="25"/>
+      <c r="G340" s="25"/>
+      <c r="H340" s="25"/>
+      <c r="I340" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="J340" s="25"/>
+      <c r="K340" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L340" s="25"/>
+      <c r="M340" s="25"/>
+      <c r="N340" s="25"/>
+      <c r="O340" s="25"/>
+      <c r="P340" s="25"/>
+      <c r="Q340" s="25" t="s">
+        <v>1410</v>
+      </c>
+      <c r="R340" s="25"/>
+      <c r="S340" s="25" t="s">
+        <v>814</v>
+      </c>
+      <c r="T340" s="25"/>
+      <c r="U340" s="25" t="s">
+        <v>271</v>
+      </c>
+      <c r="V340" s="25"/>
+      <c r="W340" s="25"/>
+      <c r="X340" s="25"/>
+      <c r="Z340" s="25"/>
+      <c r="AA340" s="25"/>
+      <c r="AB340" s="25"/>
+      <c r="AC340" s="25"/>
+      <c r="AD340" s="25"/>
+      <c r="AE340" s="25"/>
+      <c r="AF340" s="25"/>
+      <c r="AG340" s="25"/>
+      <c r="AH340" s="25"/>
+      <c r="AI340" s="25"/>
+      <c r="AJ340" s="25"/>
+      <c r="AK340" s="25"/>
+      <c r="AM340" s="25"/>
+      <c r="AN340" s="25" t="s">
+        <v>987</v>
+      </c>
+      <c r="AO340" s="25"/>
+      <c r="AP340" s="25" t="s">
+        <v>987</v>
+      </c>
+      <c r="AQ340" s="25" t="s">
+        <v>987</v>
+      </c>
+      <c r="AR340" s="25"/>
+      <c r="AS340" s="25" t="s">
+        <v>987</v>
+      </c>
+      <c r="AT340" s="25"/>
+      <c r="AU340" s="25"/>
+      <c r="AV340" s="25"/>
+      <c r="AW340" s="25"/>
+      <c r="AX340" s="25"/>
+      <c r="AZ340" s="26"/>
+    </row>
+    <row r="341" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A341" s="50">
+        <v>70</v>
+      </c>
+      <c r="B341" s="25"/>
+      <c r="C341" s="25"/>
+      <c r="D341" s="25" t="s">
+        <v>988</v>
+      </c>
+      <c r="E341" s="37"/>
+      <c r="F341" s="25"/>
+      <c r="G341" s="25"/>
+      <c r="H341" s="25"/>
+      <c r="I341" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="J341" s="25"/>
+      <c r="K341" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L341" s="25"/>
+      <c r="M341" s="25"/>
+      <c r="N341" s="25"/>
+      <c r="O341" s="25"/>
+      <c r="P341" s="25"/>
+      <c r="Q341" s="25"/>
+      <c r="R341" s="25"/>
+      <c r="S341" s="25"/>
+      <c r="T341" s="25"/>
+      <c r="U341" s="25"/>
+      <c r="V341" s="25"/>
+      <c r="W341" s="25"/>
+      <c r="X341" s="25"/>
+      <c r="Z341" s="25"/>
+      <c r="AA341" s="25"/>
+      <c r="AB341" s="25"/>
+      <c r="AC341" s="25"/>
+      <c r="AD341" s="25"/>
+      <c r="AE341" s="25"/>
+      <c r="AF341" s="25"/>
+      <c r="AG341" s="25"/>
+      <c r="AH341" s="25"/>
+      <c r="AI341" s="25"/>
+      <c r="AJ341" s="25"/>
+      <c r="AK341" s="25"/>
+      <c r="AM341" s="25"/>
+      <c r="AN341" s="25" t="s">
+        <v>814</v>
+      </c>
+      <c r="AO341" s="25"/>
+      <c r="AP341" s="25" t="s">
+        <v>814</v>
+      </c>
+      <c r="AQ341" s="25"/>
+      <c r="AR341" s="25"/>
+      <c r="AS341" s="25"/>
+      <c r="AT341" s="25"/>
+      <c r="AU341" s="25"/>
+      <c r="AV341" s="25"/>
+      <c r="AW341" s="25"/>
+      <c r="AX341" s="25"/>
+      <c r="AZ341" s="26"/>
     </row>
     <row r="342" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A342" s="50">
@@ -64651,14 +64688,9 @@
     <mergeCell ref="I5:J5"/>
   </mergeCells>
   <phoneticPr fontId="5"/>
-  <conditionalFormatting sqref="V279:X282 V327:X341">
-    <cfRule type="expression" dxfId="27" priority="44">
+  <conditionalFormatting sqref="V279:X282 V330:X341 V325:X328">
+    <cfRule type="expression" dxfId="26" priority="44">
       <formula>$A279=""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V325:X325">
-    <cfRule type="expression" dxfId="26" priority="43">
-      <formula>$A325=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V343:X343">
@@ -64819,65 +64851,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:57" ht="38.25" customHeight="1" thickBot="1">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="104" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="104"/>
-      <c r="C1" s="104"/>
-      <c r="D1" s="104"/>
-      <c r="E1" s="104"/>
-      <c r="F1" s="104"/>
-      <c r="G1" s="104"/>
-      <c r="H1" s="104"/>
-      <c r="I1" s="104"/>
-      <c r="J1" s="104"/>
-      <c r="K1" s="104"/>
-      <c r="L1" s="104"/>
-      <c r="M1" s="104"/>
-      <c r="N1" s="104"/>
-      <c r="O1" s="104"/>
-      <c r="P1" s="104"/>
-      <c r="Q1" s="104"/>
-      <c r="R1" s="104"/>
-      <c r="S1" s="104"/>
-      <c r="T1" s="104"/>
-      <c r="U1" s="104"/>
-      <c r="V1" s="104"/>
-      <c r="W1" s="104"/>
-      <c r="X1" s="104"/>
-      <c r="Y1" s="104"/>
-      <c r="Z1" s="104"/>
-      <c r="AA1" s="104"/>
-      <c r="AB1" s="104"/>
-      <c r="AC1" s="104"/>
-      <c r="AD1" s="104"/>
-      <c r="AE1" s="104"/>
-      <c r="AF1" s="104"/>
-      <c r="AG1" s="104"/>
-      <c r="AH1" s="104"/>
-      <c r="AI1" s="104"/>
-      <c r="AJ1" s="104"/>
-      <c r="AK1" s="104"/>
-      <c r="AL1" s="104"/>
-      <c r="AM1" s="104"/>
-      <c r="AN1" s="104"/>
-      <c r="AO1" s="104"/>
-      <c r="AP1" s="104"/>
-      <c r="AQ1" s="104"/>
-      <c r="AR1" s="104"/>
-      <c r="AS1" s="104"/>
-      <c r="AT1" s="104"/>
-      <c r="AU1" s="104"/>
-      <c r="AV1" s="104"/>
-      <c r="AW1" s="104"/>
-      <c r="AX1" s="104"/>
-      <c r="AY1" s="104"/>
-      <c r="AZ1" s="104"/>
-      <c r="BA1" s="104"/>
-      <c r="BB1" s="104"/>
-      <c r="BC1" s="104"/>
-      <c r="BD1" s="104"/>
-      <c r="BE1" s="105"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="105"/>
+      <c r="H1" s="105"/>
+      <c r="I1" s="105"/>
+      <c r="J1" s="105"/>
+      <c r="K1" s="105"/>
+      <c r="L1" s="105"/>
+      <c r="M1" s="105"/>
+      <c r="N1" s="105"/>
+      <c r="O1" s="105"/>
+      <c r="P1" s="105"/>
+      <c r="Q1" s="105"/>
+      <c r="R1" s="105"/>
+      <c r="S1" s="105"/>
+      <c r="T1" s="105"/>
+      <c r="U1" s="105"/>
+      <c r="V1" s="105"/>
+      <c r="W1" s="105"/>
+      <c r="X1" s="105"/>
+      <c r="Y1" s="105"/>
+      <c r="Z1" s="105"/>
+      <c r="AA1" s="105"/>
+      <c r="AB1" s="105"/>
+      <c r="AC1" s="105"/>
+      <c r="AD1" s="105"/>
+      <c r="AE1" s="105"/>
+      <c r="AF1" s="105"/>
+      <c r="AG1" s="105"/>
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="106"/>
     </row>
     <row r="2" spans="1:57" ht="12" customHeight="1" thickBot="1">
       <c r="A2" s="14"/>
@@ -64924,1985 +64956,1985 @@
       <c r="AP2" s="14"/>
     </row>
     <row r="3" spans="1:57" ht="15" customHeight="1" thickBot="1">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="87" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="87"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="106" t="s">
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="107" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="87"/>
-      <c r="J3" s="87"/>
-      <c r="K3" s="87"/>
-      <c r="L3" s="87"/>
-      <c r="M3" s="87"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="106" t="s">
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
+      <c r="K3" s="88"/>
+      <c r="L3" s="88"/>
+      <c r="M3" s="88"/>
+      <c r="N3" s="89"/>
+      <c r="O3" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="P3" s="107"/>
-      <c r="Q3" s="107"/>
-      <c r="R3" s="107"/>
-      <c r="S3" s="107"/>
-      <c r="T3" s="107"/>
-      <c r="U3" s="107"/>
-      <c r="V3" s="107"/>
-      <c r="W3" s="107"/>
-      <c r="X3" s="107"/>
-      <c r="Y3" s="107"/>
-      <c r="Z3" s="107"/>
-      <c r="AA3" s="107"/>
-      <c r="AB3" s="107"/>
-      <c r="AC3" s="107"/>
-      <c r="AD3" s="107"/>
-      <c r="AE3" s="107"/>
-      <c r="AF3" s="107"/>
-      <c r="AG3" s="107"/>
-      <c r="AH3" s="107"/>
-      <c r="AI3" s="107"/>
-      <c r="AJ3" s="107"/>
-      <c r="AK3" s="107"/>
-      <c r="AL3" s="107"/>
-      <c r="AM3" s="107"/>
-      <c r="AN3" s="107"/>
-      <c r="AO3" s="107"/>
-      <c r="AP3" s="108"/>
-      <c r="AQ3" s="106" t="s">
+      <c r="P3" s="108"/>
+      <c r="Q3" s="108"/>
+      <c r="R3" s="108"/>
+      <c r="S3" s="108"/>
+      <c r="T3" s="108"/>
+      <c r="U3" s="108"/>
+      <c r="V3" s="108"/>
+      <c r="W3" s="108"/>
+      <c r="X3" s="108"/>
+      <c r="Y3" s="108"/>
+      <c r="Z3" s="108"/>
+      <c r="AA3" s="108"/>
+      <c r="AB3" s="108"/>
+      <c r="AC3" s="108"/>
+      <c r="AD3" s="108"/>
+      <c r="AE3" s="108"/>
+      <c r="AF3" s="108"/>
+      <c r="AG3" s="108"/>
+      <c r="AH3" s="108"/>
+      <c r="AI3" s="108"/>
+      <c r="AJ3" s="108"/>
+      <c r="AK3" s="108"/>
+      <c r="AL3" s="108"/>
+      <c r="AM3" s="108"/>
+      <c r="AN3" s="108"/>
+      <c r="AO3" s="108"/>
+      <c r="AP3" s="109"/>
+      <c r="AQ3" s="107" t="s">
         <v>10</v>
       </c>
-      <c r="AR3" s="109"/>
-      <c r="AS3" s="109"/>
-      <c r="AT3" s="109"/>
-      <c r="AU3" s="109"/>
-      <c r="AV3" s="109"/>
-      <c r="AW3" s="109"/>
-      <c r="AX3" s="109"/>
-      <c r="AY3" s="109"/>
-      <c r="AZ3" s="109"/>
-      <c r="BA3" s="109"/>
-      <c r="BB3" s="109"/>
-      <c r="BC3" s="109"/>
-      <c r="BD3" s="109"/>
-      <c r="BE3" s="110"/>
+      <c r="AR3" s="110"/>
+      <c r="AS3" s="110"/>
+      <c r="AT3" s="110"/>
+      <c r="AU3" s="110"/>
+      <c r="AV3" s="110"/>
+      <c r="AW3" s="110"/>
+      <c r="AX3" s="110"/>
+      <c r="AY3" s="110"/>
+      <c r="AZ3" s="110"/>
+      <c r="BA3" s="110"/>
+      <c r="BB3" s="110"/>
+      <c r="BC3" s="110"/>
+      <c r="BD3" s="110"/>
+      <c r="BE3" s="111"/>
     </row>
     <row r="4" spans="1:57" ht="15" customHeight="1">
-      <c r="A4" s="111">
+      <c r="A4" s="112">
         <v>1</v>
       </c>
-      <c r="B4" s="112"/>
-      <c r="C4" s="112"/>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="115"/>
-      <c r="L4" s="115"/>
-      <c r="M4" s="115"/>
-      <c r="N4" s="116"/>
-      <c r="O4" s="114" t="s">
+      <c r="B4" s="113"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="116"/>
+      <c r="L4" s="116"/>
+      <c r="M4" s="116"/>
+      <c r="N4" s="117"/>
+      <c r="O4" s="115" t="s">
         <v>11</v>
       </c>
-      <c r="P4" s="117"/>
-      <c r="Q4" s="117"/>
-      <c r="R4" s="117"/>
-      <c r="S4" s="117"/>
-      <c r="T4" s="117"/>
-      <c r="U4" s="117"/>
-      <c r="V4" s="117"/>
-      <c r="W4" s="117"/>
-      <c r="X4" s="117"/>
-      <c r="Y4" s="117"/>
-      <c r="Z4" s="117"/>
-      <c r="AA4" s="117"/>
-      <c r="AB4" s="117"/>
-      <c r="AC4" s="117"/>
-      <c r="AD4" s="117"/>
-      <c r="AE4" s="117"/>
-      <c r="AF4" s="117"/>
-      <c r="AG4" s="117"/>
-      <c r="AH4" s="117"/>
-      <c r="AI4" s="117"/>
-      <c r="AJ4" s="117"/>
-      <c r="AK4" s="117"/>
-      <c r="AL4" s="117"/>
-      <c r="AM4" s="117"/>
-      <c r="AN4" s="117"/>
-      <c r="AO4" s="117"/>
-      <c r="AP4" s="118"/>
-      <c r="AQ4" s="119"/>
-      <c r="AR4" s="117"/>
-      <c r="AS4" s="117"/>
-      <c r="AT4" s="117"/>
-      <c r="AU4" s="117"/>
-      <c r="AV4" s="117"/>
-      <c r="AW4" s="117"/>
-      <c r="AX4" s="117"/>
-      <c r="AY4" s="117"/>
-      <c r="AZ4" s="117"/>
-      <c r="BA4" s="117"/>
-      <c r="BB4" s="117"/>
-      <c r="BC4" s="117"/>
-      <c r="BD4" s="117"/>
-      <c r="BE4" s="120"/>
+      <c r="P4" s="118"/>
+      <c r="Q4" s="118"/>
+      <c r="R4" s="118"/>
+      <c r="S4" s="118"/>
+      <c r="T4" s="118"/>
+      <c r="U4" s="118"/>
+      <c r="V4" s="118"/>
+      <c r="W4" s="118"/>
+      <c r="X4" s="118"/>
+      <c r="Y4" s="118"/>
+      <c r="Z4" s="118"/>
+      <c r="AA4" s="118"/>
+      <c r="AB4" s="118"/>
+      <c r="AC4" s="118"/>
+      <c r="AD4" s="118"/>
+      <c r="AE4" s="118"/>
+      <c r="AF4" s="118"/>
+      <c r="AG4" s="118"/>
+      <c r="AH4" s="118"/>
+      <c r="AI4" s="118"/>
+      <c r="AJ4" s="118"/>
+      <c r="AK4" s="118"/>
+      <c r="AL4" s="118"/>
+      <c r="AM4" s="118"/>
+      <c r="AN4" s="118"/>
+      <c r="AO4" s="118"/>
+      <c r="AP4" s="119"/>
+      <c r="AQ4" s="120"/>
+      <c r="AR4" s="118"/>
+      <c r="AS4" s="118"/>
+      <c r="AT4" s="118"/>
+      <c r="AU4" s="118"/>
+      <c r="AV4" s="118"/>
+      <c r="AW4" s="118"/>
+      <c r="AX4" s="118"/>
+      <c r="AY4" s="118"/>
+      <c r="AZ4" s="118"/>
+      <c r="BA4" s="118"/>
+      <c r="BB4" s="118"/>
+      <c r="BC4" s="118"/>
+      <c r="BD4" s="118"/>
+      <c r="BE4" s="121"/>
     </row>
     <row r="5" spans="1:57" ht="105.75" customHeight="1">
-      <c r="A5" s="100">
+      <c r="A5" s="101">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B5" s="101"/>
-      <c r="C5" s="101"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="101"/>
-      <c r="F5" s="101"/>
-      <c r="G5" s="102"/>
-      <c r="H5" s="83" t="s">
+      <c r="B5" s="102"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="102"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="102"/>
+      <c r="G5" s="103"/>
+      <c r="H5" s="84" t="s">
         <v>1801</v>
       </c>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
-      <c r="K5" s="84"/>
-      <c r="L5" s="84"/>
-      <c r="M5" s="84"/>
-      <c r="N5" s="85"/>
-      <c r="O5" s="83" t="s">
+      <c r="I5" s="85"/>
+      <c r="J5" s="85"/>
+      <c r="K5" s="85"/>
+      <c r="L5" s="85"/>
+      <c r="M5" s="85"/>
+      <c r="N5" s="86"/>
+      <c r="O5" s="84" t="s">
         <v>1803</v>
       </c>
-      <c r="P5" s="81"/>
-      <c r="Q5" s="81"/>
-      <c r="R5" s="81"/>
-      <c r="S5" s="81"/>
-      <c r="T5" s="81"/>
-      <c r="U5" s="81"/>
-      <c r="V5" s="81"/>
-      <c r="W5" s="81"/>
-      <c r="X5" s="81"/>
-      <c r="Y5" s="81"/>
-      <c r="Z5" s="81"/>
-      <c r="AA5" s="81"/>
-      <c r="AB5" s="81"/>
-      <c r="AC5" s="81"/>
-      <c r="AD5" s="81"/>
-      <c r="AE5" s="81"/>
-      <c r="AF5" s="81"/>
-      <c r="AG5" s="81"/>
-      <c r="AH5" s="81"/>
-      <c r="AI5" s="81"/>
-      <c r="AJ5" s="81"/>
-      <c r="AK5" s="81"/>
-      <c r="AL5" s="81"/>
-      <c r="AM5" s="81"/>
-      <c r="AN5" s="81"/>
-      <c r="AO5" s="81"/>
-      <c r="AP5" s="89"/>
-      <c r="AQ5" s="80" t="s">
+      <c r="P5" s="82"/>
+      <c r="Q5" s="82"/>
+      <c r="R5" s="82"/>
+      <c r="S5" s="82"/>
+      <c r="T5" s="82"/>
+      <c r="U5" s="82"/>
+      <c r="V5" s="82"/>
+      <c r="W5" s="82"/>
+      <c r="X5" s="82"/>
+      <c r="Y5" s="82"/>
+      <c r="Z5" s="82"/>
+      <c r="AA5" s="82"/>
+      <c r="AB5" s="82"/>
+      <c r="AC5" s="82"/>
+      <c r="AD5" s="82"/>
+      <c r="AE5" s="82"/>
+      <c r="AF5" s="82"/>
+      <c r="AG5" s="82"/>
+      <c r="AH5" s="82"/>
+      <c r="AI5" s="82"/>
+      <c r="AJ5" s="82"/>
+      <c r="AK5" s="82"/>
+      <c r="AL5" s="82"/>
+      <c r="AM5" s="82"/>
+      <c r="AN5" s="82"/>
+      <c r="AO5" s="82"/>
+      <c r="AP5" s="90"/>
+      <c r="AQ5" s="81" t="s">
         <v>1802</v>
       </c>
-      <c r="AR5" s="81"/>
-      <c r="AS5" s="81"/>
-      <c r="AT5" s="81"/>
-      <c r="AU5" s="81"/>
-      <c r="AV5" s="81"/>
-      <c r="AW5" s="81"/>
-      <c r="AX5" s="81"/>
-      <c r="AY5" s="81"/>
-      <c r="AZ5" s="81"/>
-      <c r="BA5" s="81"/>
-      <c r="BB5" s="81"/>
-      <c r="BC5" s="81"/>
-      <c r="BD5" s="81"/>
-      <c r="BE5" s="82"/>
+      <c r="AR5" s="82"/>
+      <c r="AS5" s="82"/>
+      <c r="AT5" s="82"/>
+      <c r="AU5" s="82"/>
+      <c r="AV5" s="82"/>
+      <c r="AW5" s="82"/>
+      <c r="AX5" s="82"/>
+      <c r="AY5" s="82"/>
+      <c r="AZ5" s="82"/>
+      <c r="BA5" s="82"/>
+      <c r="BB5" s="82"/>
+      <c r="BC5" s="82"/>
+      <c r="BD5" s="82"/>
+      <c r="BE5" s="83"/>
     </row>
     <row r="6" spans="1:57" ht="36.6" customHeight="1">
-      <c r="A6" s="100">
+      <c r="A6" s="101">
         <v>1.2</v>
       </c>
-      <c r="B6" s="101"/>
-      <c r="C6" s="101"/>
-      <c r="D6" s="101"/>
-      <c r="E6" s="101"/>
-      <c r="F6" s="101"/>
-      <c r="G6" s="102"/>
-      <c r="H6" s="83" t="s">
+      <c r="B6" s="102"/>
+      <c r="C6" s="102"/>
+      <c r="D6" s="102"/>
+      <c r="E6" s="102"/>
+      <c r="F6" s="102"/>
+      <c r="G6" s="103"/>
+      <c r="H6" s="84" t="s">
         <v>1829</v>
       </c>
-      <c r="I6" s="84"/>
-      <c r="J6" s="84"/>
-      <c r="K6" s="84"/>
-      <c r="L6" s="84"/>
-      <c r="M6" s="84"/>
-      <c r="N6" s="85"/>
-      <c r="O6" s="83" t="s">
+      <c r="I6" s="85"/>
+      <c r="J6" s="85"/>
+      <c r="K6" s="85"/>
+      <c r="L6" s="85"/>
+      <c r="M6" s="85"/>
+      <c r="N6" s="86"/>
+      <c r="O6" s="84" t="s">
         <v>1828</v>
       </c>
-      <c r="P6" s="90"/>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90"/>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
-      <c r="V6" s="90"/>
-      <c r="W6" s="90"/>
-      <c r="X6" s="90"/>
-      <c r="Y6" s="90"/>
-      <c r="Z6" s="90"/>
-      <c r="AA6" s="90"/>
-      <c r="AB6" s="90"/>
-      <c r="AC6" s="90"/>
-      <c r="AD6" s="90"/>
-      <c r="AE6" s="90"/>
-      <c r="AF6" s="90"/>
-      <c r="AG6" s="90"/>
-      <c r="AH6" s="90"/>
-      <c r="AI6" s="90"/>
-      <c r="AJ6" s="90"/>
-      <c r="AK6" s="90"/>
-      <c r="AL6" s="90"/>
-      <c r="AM6" s="90"/>
-      <c r="AN6" s="90"/>
-      <c r="AO6" s="90"/>
-      <c r="AP6" s="91"/>
-      <c r="AQ6" s="80" t="s">
+      <c r="P6" s="91"/>
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
+      <c r="V6" s="91"/>
+      <c r="W6" s="91"/>
+      <c r="X6" s="91"/>
+      <c r="Y6" s="91"/>
+      <c r="Z6" s="91"/>
+      <c r="AA6" s="91"/>
+      <c r="AB6" s="91"/>
+      <c r="AC6" s="91"/>
+      <c r="AD6" s="91"/>
+      <c r="AE6" s="91"/>
+      <c r="AF6" s="91"/>
+      <c r="AG6" s="91"/>
+      <c r="AH6" s="91"/>
+      <c r="AI6" s="91"/>
+      <c r="AJ6" s="91"/>
+      <c r="AK6" s="91"/>
+      <c r="AL6" s="91"/>
+      <c r="AM6" s="91"/>
+      <c r="AN6" s="91"/>
+      <c r="AO6" s="91"/>
+      <c r="AP6" s="92"/>
+      <c r="AQ6" s="81" t="s">
         <v>1802</v>
       </c>
-      <c r="AR6" s="81"/>
-      <c r="AS6" s="81"/>
-      <c r="AT6" s="81"/>
-      <c r="AU6" s="81"/>
-      <c r="AV6" s="81"/>
-      <c r="AW6" s="81"/>
-      <c r="AX6" s="81"/>
-      <c r="AY6" s="81"/>
-      <c r="AZ6" s="81"/>
-      <c r="BA6" s="81"/>
-      <c r="BB6" s="81"/>
-      <c r="BC6" s="81"/>
-      <c r="BD6" s="81"/>
-      <c r="BE6" s="82"/>
+      <c r="AR6" s="82"/>
+      <c r="AS6" s="82"/>
+      <c r="AT6" s="82"/>
+      <c r="AU6" s="82"/>
+      <c r="AV6" s="82"/>
+      <c r="AW6" s="82"/>
+      <c r="AX6" s="82"/>
+      <c r="AY6" s="82"/>
+      <c r="AZ6" s="82"/>
+      <c r="BA6" s="82"/>
+      <c r="BB6" s="82"/>
+      <c r="BC6" s="82"/>
+      <c r="BD6" s="82"/>
+      <c r="BE6" s="83"/>
     </row>
     <row r="7" spans="1:57" ht="15" customHeight="1">
-      <c r="A7" s="100">
+      <c r="A7" s="101">
         <v>1.3</v>
       </c>
-      <c r="B7" s="101"/>
-      <c r="C7" s="101"/>
-      <c r="D7" s="101"/>
-      <c r="E7" s="101"/>
-      <c r="F7" s="101"/>
-      <c r="G7" s="102"/>
-      <c r="H7" s="83"/>
-      <c r="I7" s="92"/>
-      <c r="J7" s="92"/>
-      <c r="K7" s="92"/>
-      <c r="L7" s="92"/>
-      <c r="M7" s="92"/>
-      <c r="N7" s="93"/>
-      <c r="O7" s="94" t="s">
+      <c r="B7" s="102"/>
+      <c r="C7" s="102"/>
+      <c r="D7" s="102"/>
+      <c r="E7" s="102"/>
+      <c r="F7" s="102"/>
+      <c r="G7" s="103"/>
+      <c r="H7" s="84"/>
+      <c r="I7" s="93"/>
+      <c r="J7" s="93"/>
+      <c r="K7" s="93"/>
+      <c r="L7" s="93"/>
+      <c r="M7" s="93"/>
+      <c r="N7" s="94"/>
+      <c r="O7" s="95" t="s">
         <v>2242</v>
       </c>
-      <c r="P7" s="95"/>
-      <c r="Q7" s="95"/>
-      <c r="R7" s="95"/>
-      <c r="S7" s="95"/>
-      <c r="T7" s="95"/>
-      <c r="U7" s="95"/>
-      <c r="V7" s="95"/>
-      <c r="W7" s="95"/>
-      <c r="X7" s="95"/>
-      <c r="Y7" s="95"/>
-      <c r="Z7" s="95"/>
-      <c r="AA7" s="95"/>
-      <c r="AB7" s="95"/>
-      <c r="AC7" s="95"/>
-      <c r="AD7" s="95"/>
-      <c r="AE7" s="95"/>
-      <c r="AF7" s="95"/>
-      <c r="AG7" s="95"/>
-      <c r="AH7" s="95"/>
-      <c r="AI7" s="95"/>
-      <c r="AJ7" s="95"/>
-      <c r="AK7" s="95"/>
-      <c r="AL7" s="95"/>
-      <c r="AM7" s="95"/>
-      <c r="AN7" s="95"/>
-      <c r="AO7" s="95"/>
-      <c r="AP7" s="96"/>
-      <c r="AQ7" s="97" t="s">
+      <c r="P7" s="96"/>
+      <c r="Q7" s="96"/>
+      <c r="R7" s="96"/>
+      <c r="S7" s="96"/>
+      <c r="T7" s="96"/>
+      <c r="U7" s="96"/>
+      <c r="V7" s="96"/>
+      <c r="W7" s="96"/>
+      <c r="X7" s="96"/>
+      <c r="Y7" s="96"/>
+      <c r="Z7" s="96"/>
+      <c r="AA7" s="96"/>
+      <c r="AB7" s="96"/>
+      <c r="AC7" s="96"/>
+      <c r="AD7" s="96"/>
+      <c r="AE7" s="96"/>
+      <c r="AF7" s="96"/>
+      <c r="AG7" s="96"/>
+      <c r="AH7" s="96"/>
+      <c r="AI7" s="96"/>
+      <c r="AJ7" s="96"/>
+      <c r="AK7" s="96"/>
+      <c r="AL7" s="96"/>
+      <c r="AM7" s="96"/>
+      <c r="AN7" s="96"/>
+      <c r="AO7" s="96"/>
+      <c r="AP7" s="97"/>
+      <c r="AQ7" s="98" t="s">
         <v>2243</v>
       </c>
-      <c r="AR7" s="98"/>
-      <c r="AS7" s="98"/>
-      <c r="AT7" s="98"/>
-      <c r="AU7" s="98"/>
-      <c r="AV7" s="98"/>
-      <c r="AW7" s="98"/>
-      <c r="AX7" s="98"/>
-      <c r="AY7" s="98"/>
-      <c r="AZ7" s="98"/>
-      <c r="BA7" s="98"/>
-      <c r="BB7" s="98"/>
-      <c r="BC7" s="98"/>
-      <c r="BD7" s="98"/>
-      <c r="BE7" s="99"/>
+      <c r="AR7" s="99"/>
+      <c r="AS7" s="99"/>
+      <c r="AT7" s="99"/>
+      <c r="AU7" s="99"/>
+      <c r="AV7" s="99"/>
+      <c r="AW7" s="99"/>
+      <c r="AX7" s="99"/>
+      <c r="AY7" s="99"/>
+      <c r="AZ7" s="99"/>
+      <c r="BA7" s="99"/>
+      <c r="BB7" s="99"/>
+      <c r="BC7" s="99"/>
+      <c r="BD7" s="99"/>
+      <c r="BE7" s="100"/>
     </row>
     <row r="8" spans="1:57" ht="15" customHeight="1">
-      <c r="A8" s="100"/>
-      <c r="B8" s="101"/>
-      <c r="C8" s="101"/>
-      <c r="D8" s="101"/>
-      <c r="E8" s="101"/>
-      <c r="F8" s="101"/>
-      <c r="G8" s="102"/>
-      <c r="H8" s="83"/>
-      <c r="I8" s="84"/>
-      <c r="J8" s="84"/>
-      <c r="K8" s="84"/>
-      <c r="L8" s="84"/>
-      <c r="M8" s="84"/>
-      <c r="N8" s="85"/>
-      <c r="O8" s="83"/>
-      <c r="P8" s="81"/>
-      <c r="Q8" s="81"/>
-      <c r="R8" s="81"/>
-      <c r="S8" s="81"/>
-      <c r="T8" s="81"/>
-      <c r="U8" s="81"/>
-      <c r="V8" s="81"/>
-      <c r="W8" s="81"/>
-      <c r="X8" s="81"/>
-      <c r="Y8" s="81"/>
-      <c r="Z8" s="81"/>
-      <c r="AA8" s="81"/>
-      <c r="AB8" s="81"/>
-      <c r="AC8" s="81"/>
-      <c r="AD8" s="81"/>
-      <c r="AE8" s="81"/>
-      <c r="AF8" s="81"/>
-      <c r="AG8" s="81"/>
-      <c r="AH8" s="81"/>
-      <c r="AI8" s="81"/>
-      <c r="AJ8" s="81"/>
-      <c r="AK8" s="81"/>
-      <c r="AL8" s="81"/>
-      <c r="AM8" s="81"/>
-      <c r="AN8" s="81"/>
-      <c r="AO8" s="81"/>
-      <c r="AP8" s="89"/>
-      <c r="AQ8" s="80"/>
-      <c r="AR8" s="81"/>
-      <c r="AS8" s="81"/>
-      <c r="AT8" s="81"/>
-      <c r="AU8" s="81"/>
-      <c r="AV8" s="81"/>
-      <c r="AW8" s="81"/>
-      <c r="AX8" s="81"/>
-      <c r="AY8" s="81"/>
-      <c r="AZ8" s="81"/>
-      <c r="BA8" s="81"/>
-      <c r="BB8" s="81"/>
-      <c r="BC8" s="81"/>
-      <c r="BD8" s="81"/>
-      <c r="BE8" s="82"/>
+      <c r="A8" s="101"/>
+      <c r="B8" s="102"/>
+      <c r="C8" s="102"/>
+      <c r="D8" s="102"/>
+      <c r="E8" s="102"/>
+      <c r="F8" s="102"/>
+      <c r="G8" s="103"/>
+      <c r="H8" s="84"/>
+      <c r="I8" s="85"/>
+      <c r="J8" s="85"/>
+      <c r="K8" s="85"/>
+      <c r="L8" s="85"/>
+      <c r="M8" s="85"/>
+      <c r="N8" s="86"/>
+      <c r="O8" s="84"/>
+      <c r="P8" s="82"/>
+      <c r="Q8" s="82"/>
+      <c r="R8" s="82"/>
+      <c r="S8" s="82"/>
+      <c r="T8" s="82"/>
+      <c r="U8" s="82"/>
+      <c r="V8" s="82"/>
+      <c r="W8" s="82"/>
+      <c r="X8" s="82"/>
+      <c r="Y8" s="82"/>
+      <c r="Z8" s="82"/>
+      <c r="AA8" s="82"/>
+      <c r="AB8" s="82"/>
+      <c r="AC8" s="82"/>
+      <c r="AD8" s="82"/>
+      <c r="AE8" s="82"/>
+      <c r="AF8" s="82"/>
+      <c r="AG8" s="82"/>
+      <c r="AH8" s="82"/>
+      <c r="AI8" s="82"/>
+      <c r="AJ8" s="82"/>
+      <c r="AK8" s="82"/>
+      <c r="AL8" s="82"/>
+      <c r="AM8" s="82"/>
+      <c r="AN8" s="82"/>
+      <c r="AO8" s="82"/>
+      <c r="AP8" s="90"/>
+      <c r="AQ8" s="81"/>
+      <c r="AR8" s="82"/>
+      <c r="AS8" s="82"/>
+      <c r="AT8" s="82"/>
+      <c r="AU8" s="82"/>
+      <c r="AV8" s="82"/>
+      <c r="AW8" s="82"/>
+      <c r="AX8" s="82"/>
+      <c r="AY8" s="82"/>
+      <c r="AZ8" s="82"/>
+      <c r="BA8" s="82"/>
+      <c r="BB8" s="82"/>
+      <c r="BC8" s="82"/>
+      <c r="BD8" s="82"/>
+      <c r="BE8" s="83"/>
     </row>
     <row r="9" spans="1:57" ht="15" customHeight="1">
-      <c r="A9" s="100"/>
-      <c r="B9" s="101"/>
-      <c r="C9" s="101"/>
-      <c r="D9" s="101"/>
-      <c r="E9" s="101"/>
-      <c r="F9" s="101"/>
-      <c r="G9" s="102"/>
-      <c r="H9" s="83"/>
-      <c r="I9" s="84"/>
-      <c r="J9" s="84"/>
-      <c r="K9" s="84"/>
-      <c r="L9" s="84"/>
-      <c r="M9" s="84"/>
-      <c r="N9" s="85"/>
-      <c r="O9" s="83"/>
-      <c r="P9" s="81"/>
-      <c r="Q9" s="81"/>
-      <c r="R9" s="81"/>
-      <c r="S9" s="81"/>
-      <c r="T9" s="81"/>
-      <c r="U9" s="81"/>
-      <c r="V9" s="81"/>
-      <c r="W9" s="81"/>
-      <c r="X9" s="81"/>
-      <c r="Y9" s="81"/>
-      <c r="Z9" s="81"/>
-      <c r="AA9" s="81"/>
-      <c r="AB9" s="81"/>
-      <c r="AC9" s="81"/>
-      <c r="AD9" s="81"/>
-      <c r="AE9" s="81"/>
-      <c r="AF9" s="81"/>
-      <c r="AG9" s="81"/>
-      <c r="AH9" s="81"/>
-      <c r="AI9" s="81"/>
-      <c r="AJ9" s="81"/>
-      <c r="AK9" s="81"/>
-      <c r="AL9" s="81"/>
-      <c r="AM9" s="81"/>
-      <c r="AN9" s="81"/>
-      <c r="AO9" s="81"/>
-      <c r="AP9" s="89"/>
-      <c r="AQ9" s="80"/>
-      <c r="AR9" s="81"/>
-      <c r="AS9" s="81"/>
-      <c r="AT9" s="81"/>
-      <c r="AU9" s="81"/>
-      <c r="AV9" s="81"/>
-      <c r="AW9" s="81"/>
-      <c r="AX9" s="81"/>
-      <c r="AY9" s="81"/>
-      <c r="AZ9" s="81"/>
-      <c r="BA9" s="81"/>
-      <c r="BB9" s="81"/>
-      <c r="BC9" s="81"/>
-      <c r="BD9" s="81"/>
-      <c r="BE9" s="82"/>
+      <c r="A9" s="101"/>
+      <c r="B9" s="102"/>
+      <c r="C9" s="102"/>
+      <c r="D9" s="102"/>
+      <c r="E9" s="102"/>
+      <c r="F9" s="102"/>
+      <c r="G9" s="103"/>
+      <c r="H9" s="84"/>
+      <c r="I9" s="85"/>
+      <c r="J9" s="85"/>
+      <c r="K9" s="85"/>
+      <c r="L9" s="85"/>
+      <c r="M9" s="85"/>
+      <c r="N9" s="86"/>
+      <c r="O9" s="84"/>
+      <c r="P9" s="82"/>
+      <c r="Q9" s="82"/>
+      <c r="R9" s="82"/>
+      <c r="S9" s="82"/>
+      <c r="T9" s="82"/>
+      <c r="U9" s="82"/>
+      <c r="V9" s="82"/>
+      <c r="W9" s="82"/>
+      <c r="X9" s="82"/>
+      <c r="Y9" s="82"/>
+      <c r="Z9" s="82"/>
+      <c r="AA9" s="82"/>
+      <c r="AB9" s="82"/>
+      <c r="AC9" s="82"/>
+      <c r="AD9" s="82"/>
+      <c r="AE9" s="82"/>
+      <c r="AF9" s="82"/>
+      <c r="AG9" s="82"/>
+      <c r="AH9" s="82"/>
+      <c r="AI9" s="82"/>
+      <c r="AJ9" s="82"/>
+      <c r="AK9" s="82"/>
+      <c r="AL9" s="82"/>
+      <c r="AM9" s="82"/>
+      <c r="AN9" s="82"/>
+      <c r="AO9" s="82"/>
+      <c r="AP9" s="90"/>
+      <c r="AQ9" s="81"/>
+      <c r="AR9" s="82"/>
+      <c r="AS9" s="82"/>
+      <c r="AT9" s="82"/>
+      <c r="AU9" s="82"/>
+      <c r="AV9" s="82"/>
+      <c r="AW9" s="82"/>
+      <c r="AX9" s="82"/>
+      <c r="AY9" s="82"/>
+      <c r="AZ9" s="82"/>
+      <c r="BA9" s="82"/>
+      <c r="BB9" s="82"/>
+      <c r="BC9" s="82"/>
+      <c r="BD9" s="82"/>
+      <c r="BE9" s="83"/>
     </row>
     <row r="10" spans="1:57" ht="15" customHeight="1">
-      <c r="A10" s="100"/>
-      <c r="B10" s="101"/>
-      <c r="C10" s="101"/>
-      <c r="D10" s="101"/>
-      <c r="E10" s="101"/>
-      <c r="F10" s="101"/>
-      <c r="G10" s="102"/>
-      <c r="H10" s="83"/>
-      <c r="I10" s="84"/>
-      <c r="J10" s="84"/>
-      <c r="K10" s="84"/>
-      <c r="L10" s="84"/>
-      <c r="M10" s="84"/>
-      <c r="N10" s="85"/>
-      <c r="O10" s="83"/>
-      <c r="P10" s="81"/>
-      <c r="Q10" s="81"/>
-      <c r="R10" s="81"/>
-      <c r="S10" s="81"/>
-      <c r="T10" s="81"/>
-      <c r="U10" s="81"/>
-      <c r="V10" s="81"/>
-      <c r="W10" s="81"/>
-      <c r="X10" s="81"/>
-      <c r="Y10" s="81"/>
-      <c r="Z10" s="81"/>
-      <c r="AA10" s="81"/>
-      <c r="AB10" s="81"/>
-      <c r="AC10" s="81"/>
-      <c r="AD10" s="81"/>
-      <c r="AE10" s="81"/>
-      <c r="AF10" s="81"/>
-      <c r="AG10" s="81"/>
-      <c r="AH10" s="81"/>
-      <c r="AI10" s="81"/>
-      <c r="AJ10" s="81"/>
-      <c r="AK10" s="81"/>
-      <c r="AL10" s="81"/>
-      <c r="AM10" s="81"/>
-      <c r="AN10" s="81"/>
-      <c r="AO10" s="81"/>
-      <c r="AP10" s="89"/>
-      <c r="AQ10" s="80"/>
-      <c r="AR10" s="81"/>
-      <c r="AS10" s="81"/>
-      <c r="AT10" s="81"/>
-      <c r="AU10" s="81"/>
-      <c r="AV10" s="81"/>
-      <c r="AW10" s="81"/>
-      <c r="AX10" s="81"/>
-      <c r="AY10" s="81"/>
-      <c r="AZ10" s="81"/>
-      <c r="BA10" s="81"/>
-      <c r="BB10" s="81"/>
-      <c r="BC10" s="81"/>
-      <c r="BD10" s="81"/>
-      <c r="BE10" s="82"/>
+      <c r="A10" s="101"/>
+      <c r="B10" s="102"/>
+      <c r="C10" s="102"/>
+      <c r="D10" s="102"/>
+      <c r="E10" s="102"/>
+      <c r="F10" s="102"/>
+      <c r="G10" s="103"/>
+      <c r="H10" s="84"/>
+      <c r="I10" s="85"/>
+      <c r="J10" s="85"/>
+      <c r="K10" s="85"/>
+      <c r="L10" s="85"/>
+      <c r="M10" s="85"/>
+      <c r="N10" s="86"/>
+      <c r="O10" s="84"/>
+      <c r="P10" s="82"/>
+      <c r="Q10" s="82"/>
+      <c r="R10" s="82"/>
+      <c r="S10" s="82"/>
+      <c r="T10" s="82"/>
+      <c r="U10" s="82"/>
+      <c r="V10" s="82"/>
+      <c r="W10" s="82"/>
+      <c r="X10" s="82"/>
+      <c r="Y10" s="82"/>
+      <c r="Z10" s="82"/>
+      <c r="AA10" s="82"/>
+      <c r="AB10" s="82"/>
+      <c r="AC10" s="82"/>
+      <c r="AD10" s="82"/>
+      <c r="AE10" s="82"/>
+      <c r="AF10" s="82"/>
+      <c r="AG10" s="82"/>
+      <c r="AH10" s="82"/>
+      <c r="AI10" s="82"/>
+      <c r="AJ10" s="82"/>
+      <c r="AK10" s="82"/>
+      <c r="AL10" s="82"/>
+      <c r="AM10" s="82"/>
+      <c r="AN10" s="82"/>
+      <c r="AO10" s="82"/>
+      <c r="AP10" s="90"/>
+      <c r="AQ10" s="81"/>
+      <c r="AR10" s="82"/>
+      <c r="AS10" s="82"/>
+      <c r="AT10" s="82"/>
+      <c r="AU10" s="82"/>
+      <c r="AV10" s="82"/>
+      <c r="AW10" s="82"/>
+      <c r="AX10" s="82"/>
+      <c r="AY10" s="82"/>
+      <c r="AZ10" s="82"/>
+      <c r="BA10" s="82"/>
+      <c r="BB10" s="82"/>
+      <c r="BC10" s="82"/>
+      <c r="BD10" s="82"/>
+      <c r="BE10" s="83"/>
     </row>
     <row r="11" spans="1:57" ht="15" customHeight="1">
-      <c r="A11" s="100"/>
-      <c r="B11" s="101"/>
-      <c r="C11" s="101"/>
-      <c r="D11" s="101"/>
-      <c r="E11" s="101"/>
-      <c r="F11" s="101"/>
-      <c r="G11" s="102"/>
-      <c r="H11" s="83"/>
-      <c r="I11" s="84"/>
-      <c r="J11" s="84"/>
-      <c r="K11" s="84"/>
-      <c r="L11" s="84"/>
-      <c r="M11" s="84"/>
-      <c r="N11" s="85"/>
-      <c r="O11" s="83"/>
-      <c r="P11" s="81"/>
-      <c r="Q11" s="81"/>
-      <c r="R11" s="81"/>
-      <c r="S11" s="81"/>
-      <c r="T11" s="81"/>
-      <c r="U11" s="81"/>
-      <c r="V11" s="81"/>
-      <c r="W11" s="81"/>
-      <c r="X11" s="81"/>
-      <c r="Y11" s="81"/>
-      <c r="Z11" s="81"/>
-      <c r="AA11" s="81"/>
-      <c r="AB11" s="81"/>
-      <c r="AC11" s="81"/>
-      <c r="AD11" s="81"/>
-      <c r="AE11" s="81"/>
-      <c r="AF11" s="81"/>
-      <c r="AG11" s="81"/>
-      <c r="AH11" s="81"/>
-      <c r="AI11" s="81"/>
-      <c r="AJ11" s="81"/>
-      <c r="AK11" s="81"/>
-      <c r="AL11" s="81"/>
-      <c r="AM11" s="81"/>
-      <c r="AN11" s="81"/>
-      <c r="AO11" s="81"/>
-      <c r="AP11" s="89"/>
-      <c r="AQ11" s="80"/>
-      <c r="AR11" s="81"/>
-      <c r="AS11" s="81"/>
-      <c r="AT11" s="81"/>
-      <c r="AU11" s="81"/>
-      <c r="AV11" s="81"/>
-      <c r="AW11" s="81"/>
-      <c r="AX11" s="81"/>
-      <c r="AY11" s="81"/>
-      <c r="AZ11" s="81"/>
-      <c r="BA11" s="81"/>
-      <c r="BB11" s="81"/>
-      <c r="BC11" s="81"/>
-      <c r="BD11" s="81"/>
-      <c r="BE11" s="82"/>
+      <c r="A11" s="101"/>
+      <c r="B11" s="102"/>
+      <c r="C11" s="102"/>
+      <c r="D11" s="102"/>
+      <c r="E11" s="102"/>
+      <c r="F11" s="102"/>
+      <c r="G11" s="103"/>
+      <c r="H11" s="84"/>
+      <c r="I11" s="85"/>
+      <c r="J11" s="85"/>
+      <c r="K11" s="85"/>
+      <c r="L11" s="85"/>
+      <c r="M11" s="85"/>
+      <c r="N11" s="86"/>
+      <c r="O11" s="84"/>
+      <c r="P11" s="82"/>
+      <c r="Q11" s="82"/>
+      <c r="R11" s="82"/>
+      <c r="S11" s="82"/>
+      <c r="T11" s="82"/>
+      <c r="U11" s="82"/>
+      <c r="V11" s="82"/>
+      <c r="W11" s="82"/>
+      <c r="X11" s="82"/>
+      <c r="Y11" s="82"/>
+      <c r="Z11" s="82"/>
+      <c r="AA11" s="82"/>
+      <c r="AB11" s="82"/>
+      <c r="AC11" s="82"/>
+      <c r="AD11" s="82"/>
+      <c r="AE11" s="82"/>
+      <c r="AF11" s="82"/>
+      <c r="AG11" s="82"/>
+      <c r="AH11" s="82"/>
+      <c r="AI11" s="82"/>
+      <c r="AJ11" s="82"/>
+      <c r="AK11" s="82"/>
+      <c r="AL11" s="82"/>
+      <c r="AM11" s="82"/>
+      <c r="AN11" s="82"/>
+      <c r="AO11" s="82"/>
+      <c r="AP11" s="90"/>
+      <c r="AQ11" s="81"/>
+      <c r="AR11" s="82"/>
+      <c r="AS11" s="82"/>
+      <c r="AT11" s="82"/>
+      <c r="AU11" s="82"/>
+      <c r="AV11" s="82"/>
+      <c r="AW11" s="82"/>
+      <c r="AX11" s="82"/>
+      <c r="AY11" s="82"/>
+      <c r="AZ11" s="82"/>
+      <c r="BA11" s="82"/>
+      <c r="BB11" s="82"/>
+      <c r="BC11" s="82"/>
+      <c r="BD11" s="82"/>
+      <c r="BE11" s="83"/>
     </row>
     <row r="12" spans="1:57" ht="15" customHeight="1">
-      <c r="A12" s="100"/>
-      <c r="B12" s="101"/>
-      <c r="C12" s="101"/>
-      <c r="D12" s="101"/>
-      <c r="E12" s="101"/>
-      <c r="F12" s="101"/>
-      <c r="G12" s="102"/>
-      <c r="H12" s="83"/>
-      <c r="I12" s="84"/>
-      <c r="J12" s="84"/>
-      <c r="K12" s="84"/>
-      <c r="L12" s="84"/>
-      <c r="M12" s="84"/>
-      <c r="N12" s="85"/>
-      <c r="O12" s="83"/>
-      <c r="P12" s="81"/>
-      <c r="Q12" s="81"/>
-      <c r="R12" s="81"/>
-      <c r="S12" s="81"/>
-      <c r="T12" s="81"/>
-      <c r="U12" s="81"/>
-      <c r="V12" s="81"/>
-      <c r="W12" s="81"/>
-      <c r="X12" s="81"/>
-      <c r="Y12" s="81"/>
-      <c r="Z12" s="81"/>
-      <c r="AA12" s="81"/>
-      <c r="AB12" s="81"/>
-      <c r="AC12" s="81"/>
-      <c r="AD12" s="81"/>
-      <c r="AE12" s="81"/>
-      <c r="AF12" s="81"/>
-      <c r="AG12" s="81"/>
-      <c r="AH12" s="81"/>
-      <c r="AI12" s="81"/>
-      <c r="AJ12" s="81"/>
-      <c r="AK12" s="81"/>
-      <c r="AL12" s="81"/>
-      <c r="AM12" s="81"/>
-      <c r="AN12" s="81"/>
-      <c r="AO12" s="81"/>
-      <c r="AP12" s="89"/>
-      <c r="AQ12" s="80"/>
-      <c r="AR12" s="81"/>
-      <c r="AS12" s="81"/>
-      <c r="AT12" s="81"/>
-      <c r="AU12" s="81"/>
-      <c r="AV12" s="81"/>
-      <c r="AW12" s="81"/>
-      <c r="AX12" s="81"/>
-      <c r="AY12" s="81"/>
-      <c r="AZ12" s="81"/>
-      <c r="BA12" s="81"/>
-      <c r="BB12" s="81"/>
-      <c r="BC12" s="81"/>
-      <c r="BD12" s="81"/>
-      <c r="BE12" s="82"/>
+      <c r="A12" s="101"/>
+      <c r="B12" s="102"/>
+      <c r="C12" s="102"/>
+      <c r="D12" s="102"/>
+      <c r="E12" s="102"/>
+      <c r="F12" s="102"/>
+      <c r="G12" s="103"/>
+      <c r="H12" s="84"/>
+      <c r="I12" s="85"/>
+      <c r="J12" s="85"/>
+      <c r="K12" s="85"/>
+      <c r="L12" s="85"/>
+      <c r="M12" s="85"/>
+      <c r="N12" s="86"/>
+      <c r="O12" s="84"/>
+      <c r="P12" s="82"/>
+      <c r="Q12" s="82"/>
+      <c r="R12" s="82"/>
+      <c r="S12" s="82"/>
+      <c r="T12" s="82"/>
+      <c r="U12" s="82"/>
+      <c r="V12" s="82"/>
+      <c r="W12" s="82"/>
+      <c r="X12" s="82"/>
+      <c r="Y12" s="82"/>
+      <c r="Z12" s="82"/>
+      <c r="AA12" s="82"/>
+      <c r="AB12" s="82"/>
+      <c r="AC12" s="82"/>
+      <c r="AD12" s="82"/>
+      <c r="AE12" s="82"/>
+      <c r="AF12" s="82"/>
+      <c r="AG12" s="82"/>
+      <c r="AH12" s="82"/>
+      <c r="AI12" s="82"/>
+      <c r="AJ12" s="82"/>
+      <c r="AK12" s="82"/>
+      <c r="AL12" s="82"/>
+      <c r="AM12" s="82"/>
+      <c r="AN12" s="82"/>
+      <c r="AO12" s="82"/>
+      <c r="AP12" s="90"/>
+      <c r="AQ12" s="81"/>
+      <c r="AR12" s="82"/>
+      <c r="AS12" s="82"/>
+      <c r="AT12" s="82"/>
+      <c r="AU12" s="82"/>
+      <c r="AV12" s="82"/>
+      <c r="AW12" s="82"/>
+      <c r="AX12" s="82"/>
+      <c r="AY12" s="82"/>
+      <c r="AZ12" s="82"/>
+      <c r="BA12" s="82"/>
+      <c r="BB12" s="82"/>
+      <c r="BC12" s="82"/>
+      <c r="BD12" s="82"/>
+      <c r="BE12" s="83"/>
     </row>
     <row r="13" spans="1:57" ht="15" customHeight="1">
-      <c r="A13" s="100"/>
-      <c r="B13" s="101"/>
-      <c r="C13" s="101"/>
-      <c r="D13" s="101"/>
-      <c r="E13" s="101"/>
-      <c r="F13" s="101"/>
-      <c r="G13" s="102"/>
-      <c r="H13" s="83"/>
-      <c r="I13" s="84"/>
-      <c r="J13" s="84"/>
-      <c r="K13" s="84"/>
-      <c r="L13" s="84"/>
-      <c r="M13" s="84"/>
-      <c r="N13" s="85"/>
-      <c r="O13" s="83"/>
-      <c r="P13" s="81"/>
-      <c r="Q13" s="81"/>
-      <c r="R13" s="81"/>
-      <c r="S13" s="81"/>
-      <c r="T13" s="81"/>
-      <c r="U13" s="81"/>
-      <c r="V13" s="81"/>
-      <c r="W13" s="81"/>
-      <c r="X13" s="81"/>
-      <c r="Y13" s="81"/>
-      <c r="Z13" s="81"/>
-      <c r="AA13" s="81"/>
-      <c r="AB13" s="81"/>
-      <c r="AC13" s="81"/>
-      <c r="AD13" s="81"/>
-      <c r="AE13" s="81"/>
-      <c r="AF13" s="81"/>
-      <c r="AG13" s="81"/>
-      <c r="AH13" s="81"/>
-      <c r="AI13" s="81"/>
-      <c r="AJ13" s="81"/>
-      <c r="AK13" s="81"/>
-      <c r="AL13" s="81"/>
-      <c r="AM13" s="81"/>
-      <c r="AN13" s="81"/>
-      <c r="AO13" s="81"/>
-      <c r="AP13" s="89"/>
-      <c r="AQ13" s="80"/>
-      <c r="AR13" s="81"/>
-      <c r="AS13" s="81"/>
-      <c r="AT13" s="81"/>
-      <c r="AU13" s="81"/>
-      <c r="AV13" s="81"/>
-      <c r="AW13" s="81"/>
-      <c r="AX13" s="81"/>
-      <c r="AY13" s="81"/>
-      <c r="AZ13" s="81"/>
-      <c r="BA13" s="81"/>
-      <c r="BB13" s="81"/>
-      <c r="BC13" s="81"/>
-      <c r="BD13" s="81"/>
-      <c r="BE13" s="82"/>
+      <c r="A13" s="101"/>
+      <c r="B13" s="102"/>
+      <c r="C13" s="102"/>
+      <c r="D13" s="102"/>
+      <c r="E13" s="102"/>
+      <c r="F13" s="102"/>
+      <c r="G13" s="103"/>
+      <c r="H13" s="84"/>
+      <c r="I13" s="85"/>
+      <c r="J13" s="85"/>
+      <c r="K13" s="85"/>
+      <c r="L13" s="85"/>
+      <c r="M13" s="85"/>
+      <c r="N13" s="86"/>
+      <c r="O13" s="84"/>
+      <c r="P13" s="82"/>
+      <c r="Q13" s="82"/>
+      <c r="R13" s="82"/>
+      <c r="S13" s="82"/>
+      <c r="T13" s="82"/>
+      <c r="U13" s="82"/>
+      <c r="V13" s="82"/>
+      <c r="W13" s="82"/>
+      <c r="X13" s="82"/>
+      <c r="Y13" s="82"/>
+      <c r="Z13" s="82"/>
+      <c r="AA13" s="82"/>
+      <c r="AB13" s="82"/>
+      <c r="AC13" s="82"/>
+      <c r="AD13" s="82"/>
+      <c r="AE13" s="82"/>
+      <c r="AF13" s="82"/>
+      <c r="AG13" s="82"/>
+      <c r="AH13" s="82"/>
+      <c r="AI13" s="82"/>
+      <c r="AJ13" s="82"/>
+      <c r="AK13" s="82"/>
+      <c r="AL13" s="82"/>
+      <c r="AM13" s="82"/>
+      <c r="AN13" s="82"/>
+      <c r="AO13" s="82"/>
+      <c r="AP13" s="90"/>
+      <c r="AQ13" s="81"/>
+      <c r="AR13" s="82"/>
+      <c r="AS13" s="82"/>
+      <c r="AT13" s="82"/>
+      <c r="AU13" s="82"/>
+      <c r="AV13" s="82"/>
+      <c r="AW13" s="82"/>
+      <c r="AX13" s="82"/>
+      <c r="AY13" s="82"/>
+      <c r="AZ13" s="82"/>
+      <c r="BA13" s="82"/>
+      <c r="BB13" s="82"/>
+      <c r="BC13" s="82"/>
+      <c r="BD13" s="82"/>
+      <c r="BE13" s="83"/>
     </row>
     <row r="14" spans="1:57" ht="15" customHeight="1">
-      <c r="A14" s="100"/>
-      <c r="B14" s="101"/>
-      <c r="C14" s="101"/>
-      <c r="D14" s="101"/>
-      <c r="E14" s="101"/>
-      <c r="F14" s="101"/>
-      <c r="G14" s="102"/>
-      <c r="H14" s="83"/>
-      <c r="I14" s="84"/>
-      <c r="J14" s="84"/>
-      <c r="K14" s="84"/>
-      <c r="L14" s="84"/>
-      <c r="M14" s="84"/>
-      <c r="N14" s="85"/>
-      <c r="O14" s="83"/>
-      <c r="P14" s="81"/>
-      <c r="Q14" s="81"/>
-      <c r="R14" s="81"/>
-      <c r="S14" s="81"/>
-      <c r="T14" s="81"/>
-      <c r="U14" s="81"/>
-      <c r="V14" s="81"/>
-      <c r="W14" s="81"/>
-      <c r="X14" s="81"/>
-      <c r="Y14" s="81"/>
-      <c r="Z14" s="81"/>
-      <c r="AA14" s="81"/>
-      <c r="AB14" s="81"/>
-      <c r="AC14" s="81"/>
-      <c r="AD14" s="81"/>
-      <c r="AE14" s="81"/>
-      <c r="AF14" s="81"/>
-      <c r="AG14" s="81"/>
-      <c r="AH14" s="81"/>
-      <c r="AI14" s="81"/>
-      <c r="AJ14" s="81"/>
-      <c r="AK14" s="81"/>
-      <c r="AL14" s="81"/>
-      <c r="AM14" s="81"/>
-      <c r="AN14" s="81"/>
-      <c r="AO14" s="81"/>
-      <c r="AP14" s="89"/>
-      <c r="AQ14" s="80"/>
-      <c r="AR14" s="81"/>
-      <c r="AS14" s="81"/>
-      <c r="AT14" s="81"/>
-      <c r="AU14" s="81"/>
-      <c r="AV14" s="81"/>
-      <c r="AW14" s="81"/>
-      <c r="AX14" s="81"/>
-      <c r="AY14" s="81"/>
-      <c r="AZ14" s="81"/>
-      <c r="BA14" s="81"/>
-      <c r="BB14" s="81"/>
-      <c r="BC14" s="81"/>
-      <c r="BD14" s="81"/>
-      <c r="BE14" s="82"/>
+      <c r="A14" s="101"/>
+      <c r="B14" s="102"/>
+      <c r="C14" s="102"/>
+      <c r="D14" s="102"/>
+      <c r="E14" s="102"/>
+      <c r="F14" s="102"/>
+      <c r="G14" s="103"/>
+      <c r="H14" s="84"/>
+      <c r="I14" s="85"/>
+      <c r="J14" s="85"/>
+      <c r="K14" s="85"/>
+      <c r="L14" s="85"/>
+      <c r="M14" s="85"/>
+      <c r="N14" s="86"/>
+      <c r="O14" s="84"/>
+      <c r="P14" s="82"/>
+      <c r="Q14" s="82"/>
+      <c r="R14" s="82"/>
+      <c r="S14" s="82"/>
+      <c r="T14" s="82"/>
+      <c r="U14" s="82"/>
+      <c r="V14" s="82"/>
+      <c r="W14" s="82"/>
+      <c r="X14" s="82"/>
+      <c r="Y14" s="82"/>
+      <c r="Z14" s="82"/>
+      <c r="AA14" s="82"/>
+      <c r="AB14" s="82"/>
+      <c r="AC14" s="82"/>
+      <c r="AD14" s="82"/>
+      <c r="AE14" s="82"/>
+      <c r="AF14" s="82"/>
+      <c r="AG14" s="82"/>
+      <c r="AH14" s="82"/>
+      <c r="AI14" s="82"/>
+      <c r="AJ14" s="82"/>
+      <c r="AK14" s="82"/>
+      <c r="AL14" s="82"/>
+      <c r="AM14" s="82"/>
+      <c r="AN14" s="82"/>
+      <c r="AO14" s="82"/>
+      <c r="AP14" s="90"/>
+      <c r="AQ14" s="81"/>
+      <c r="AR14" s="82"/>
+      <c r="AS14" s="82"/>
+      <c r="AT14" s="82"/>
+      <c r="AU14" s="82"/>
+      <c r="AV14" s="82"/>
+      <c r="AW14" s="82"/>
+      <c r="AX14" s="82"/>
+      <c r="AY14" s="82"/>
+      <c r="AZ14" s="82"/>
+      <c r="BA14" s="82"/>
+      <c r="BB14" s="82"/>
+      <c r="BC14" s="82"/>
+      <c r="BD14" s="82"/>
+      <c r="BE14" s="83"/>
     </row>
     <row r="15" spans="1:57" ht="15" customHeight="1">
-      <c r="A15" s="100"/>
-      <c r="B15" s="101"/>
-      <c r="C15" s="101"/>
-      <c r="D15" s="101"/>
-      <c r="E15" s="101"/>
-      <c r="F15" s="101"/>
-      <c r="G15" s="102"/>
-      <c r="H15" s="83"/>
-      <c r="I15" s="84"/>
-      <c r="J15" s="84"/>
-      <c r="K15" s="84"/>
-      <c r="L15" s="84"/>
-      <c r="M15" s="84"/>
-      <c r="N15" s="85"/>
-      <c r="O15" s="83"/>
-      <c r="P15" s="81"/>
-      <c r="Q15" s="81"/>
-      <c r="R15" s="81"/>
-      <c r="S15" s="81"/>
-      <c r="T15" s="81"/>
-      <c r="U15" s="81"/>
-      <c r="V15" s="81"/>
-      <c r="W15" s="81"/>
-      <c r="X15" s="81"/>
-      <c r="Y15" s="81"/>
-      <c r="Z15" s="81"/>
-      <c r="AA15" s="81"/>
-      <c r="AB15" s="81"/>
-      <c r="AC15" s="81"/>
-      <c r="AD15" s="81"/>
-      <c r="AE15" s="81"/>
-      <c r="AF15" s="81"/>
-      <c r="AG15" s="81"/>
-      <c r="AH15" s="81"/>
-      <c r="AI15" s="81"/>
-      <c r="AJ15" s="81"/>
-      <c r="AK15" s="81"/>
-      <c r="AL15" s="81"/>
-      <c r="AM15" s="81"/>
-      <c r="AN15" s="81"/>
-      <c r="AO15" s="81"/>
-      <c r="AP15" s="89"/>
-      <c r="AQ15" s="80"/>
-      <c r="AR15" s="81"/>
-      <c r="AS15" s="81"/>
-      <c r="AT15" s="81"/>
-      <c r="AU15" s="81"/>
-      <c r="AV15" s="81"/>
-      <c r="AW15" s="81"/>
-      <c r="AX15" s="81"/>
-      <c r="AY15" s="81"/>
-      <c r="AZ15" s="81"/>
-      <c r="BA15" s="81"/>
-      <c r="BB15" s="81"/>
-      <c r="BC15" s="81"/>
-      <c r="BD15" s="81"/>
-      <c r="BE15" s="82"/>
+      <c r="A15" s="101"/>
+      <c r="B15" s="102"/>
+      <c r="C15" s="102"/>
+      <c r="D15" s="102"/>
+      <c r="E15" s="102"/>
+      <c r="F15" s="102"/>
+      <c r="G15" s="103"/>
+      <c r="H15" s="84"/>
+      <c r="I15" s="85"/>
+      <c r="J15" s="85"/>
+      <c r="K15" s="85"/>
+      <c r="L15" s="85"/>
+      <c r="M15" s="85"/>
+      <c r="N15" s="86"/>
+      <c r="O15" s="84"/>
+      <c r="P15" s="82"/>
+      <c r="Q15" s="82"/>
+      <c r="R15" s="82"/>
+      <c r="S15" s="82"/>
+      <c r="T15" s="82"/>
+      <c r="U15" s="82"/>
+      <c r="V15" s="82"/>
+      <c r="W15" s="82"/>
+      <c r="X15" s="82"/>
+      <c r="Y15" s="82"/>
+      <c r="Z15" s="82"/>
+      <c r="AA15" s="82"/>
+      <c r="AB15" s="82"/>
+      <c r="AC15" s="82"/>
+      <c r="AD15" s="82"/>
+      <c r="AE15" s="82"/>
+      <c r="AF15" s="82"/>
+      <c r="AG15" s="82"/>
+      <c r="AH15" s="82"/>
+      <c r="AI15" s="82"/>
+      <c r="AJ15" s="82"/>
+      <c r="AK15" s="82"/>
+      <c r="AL15" s="82"/>
+      <c r="AM15" s="82"/>
+      <c r="AN15" s="82"/>
+      <c r="AO15" s="82"/>
+      <c r="AP15" s="90"/>
+      <c r="AQ15" s="81"/>
+      <c r="AR15" s="82"/>
+      <c r="AS15" s="82"/>
+      <c r="AT15" s="82"/>
+      <c r="AU15" s="82"/>
+      <c r="AV15" s="82"/>
+      <c r="AW15" s="82"/>
+      <c r="AX15" s="82"/>
+      <c r="AY15" s="82"/>
+      <c r="AZ15" s="82"/>
+      <c r="BA15" s="82"/>
+      <c r="BB15" s="82"/>
+      <c r="BC15" s="82"/>
+      <c r="BD15" s="82"/>
+      <c r="BE15" s="83"/>
     </row>
     <row r="16" spans="1:57" ht="15" customHeight="1">
-      <c r="A16" s="100"/>
-      <c r="B16" s="101"/>
-      <c r="C16" s="101"/>
-      <c r="D16" s="101"/>
-      <c r="E16" s="101"/>
-      <c r="F16" s="101"/>
-      <c r="G16" s="102"/>
-      <c r="H16" s="83"/>
-      <c r="I16" s="84"/>
-      <c r="J16" s="84"/>
-      <c r="K16" s="84"/>
-      <c r="L16" s="84"/>
-      <c r="M16" s="84"/>
-      <c r="N16" s="85"/>
-      <c r="O16" s="83"/>
-      <c r="P16" s="81"/>
-      <c r="Q16" s="81"/>
-      <c r="R16" s="81"/>
-      <c r="S16" s="81"/>
-      <c r="T16" s="81"/>
-      <c r="U16" s="81"/>
-      <c r="V16" s="81"/>
-      <c r="W16" s="81"/>
-      <c r="X16" s="81"/>
-      <c r="Y16" s="81"/>
-      <c r="Z16" s="81"/>
-      <c r="AA16" s="81"/>
-      <c r="AB16" s="81"/>
-      <c r="AC16" s="81"/>
-      <c r="AD16" s="81"/>
-      <c r="AE16" s="81"/>
-      <c r="AF16" s="81"/>
-      <c r="AG16" s="81"/>
-      <c r="AH16" s="81"/>
-      <c r="AI16" s="81"/>
-      <c r="AJ16" s="81"/>
-      <c r="AK16" s="81"/>
-      <c r="AL16" s="81"/>
-      <c r="AM16" s="81"/>
-      <c r="AN16" s="81"/>
-      <c r="AO16" s="81"/>
-      <c r="AP16" s="89"/>
-      <c r="AQ16" s="80"/>
-      <c r="AR16" s="81"/>
-      <c r="AS16" s="81"/>
-      <c r="AT16" s="81"/>
-      <c r="AU16" s="81"/>
-      <c r="AV16" s="81"/>
-      <c r="AW16" s="81"/>
-      <c r="AX16" s="81"/>
-      <c r="AY16" s="81"/>
-      <c r="AZ16" s="81"/>
-      <c r="BA16" s="81"/>
-      <c r="BB16" s="81"/>
-      <c r="BC16" s="81"/>
-      <c r="BD16" s="81"/>
-      <c r="BE16" s="82"/>
+      <c r="A16" s="101"/>
+      <c r="B16" s="102"/>
+      <c r="C16" s="102"/>
+      <c r="D16" s="102"/>
+      <c r="E16" s="102"/>
+      <c r="F16" s="102"/>
+      <c r="G16" s="103"/>
+      <c r="H16" s="84"/>
+      <c r="I16" s="85"/>
+      <c r="J16" s="85"/>
+      <c r="K16" s="85"/>
+      <c r="L16" s="85"/>
+      <c r="M16" s="85"/>
+      <c r="N16" s="86"/>
+      <c r="O16" s="84"/>
+      <c r="P16" s="82"/>
+      <c r="Q16" s="82"/>
+      <c r="R16" s="82"/>
+      <c r="S16" s="82"/>
+      <c r="T16" s="82"/>
+      <c r="U16" s="82"/>
+      <c r="V16" s="82"/>
+      <c r="W16" s="82"/>
+      <c r="X16" s="82"/>
+      <c r="Y16" s="82"/>
+      <c r="Z16" s="82"/>
+      <c r="AA16" s="82"/>
+      <c r="AB16" s="82"/>
+      <c r="AC16" s="82"/>
+      <c r="AD16" s="82"/>
+      <c r="AE16" s="82"/>
+      <c r="AF16" s="82"/>
+      <c r="AG16" s="82"/>
+      <c r="AH16" s="82"/>
+      <c r="AI16" s="82"/>
+      <c r="AJ16" s="82"/>
+      <c r="AK16" s="82"/>
+      <c r="AL16" s="82"/>
+      <c r="AM16" s="82"/>
+      <c r="AN16" s="82"/>
+      <c r="AO16" s="82"/>
+      <c r="AP16" s="90"/>
+      <c r="AQ16" s="81"/>
+      <c r="AR16" s="82"/>
+      <c r="AS16" s="82"/>
+      <c r="AT16" s="82"/>
+      <c r="AU16" s="82"/>
+      <c r="AV16" s="82"/>
+      <c r="AW16" s="82"/>
+      <c r="AX16" s="82"/>
+      <c r="AY16" s="82"/>
+      <c r="AZ16" s="82"/>
+      <c r="BA16" s="82"/>
+      <c r="BB16" s="82"/>
+      <c r="BC16" s="82"/>
+      <c r="BD16" s="82"/>
+      <c r="BE16" s="83"/>
     </row>
     <row r="17" spans="1:57" ht="15" customHeight="1">
-      <c r="A17" s="100"/>
-      <c r="B17" s="101"/>
-      <c r="C17" s="101"/>
-      <c r="D17" s="101"/>
-      <c r="E17" s="101"/>
-      <c r="F17" s="101"/>
-      <c r="G17" s="102"/>
-      <c r="H17" s="83"/>
-      <c r="I17" s="84"/>
-      <c r="J17" s="84"/>
-      <c r="K17" s="84"/>
-      <c r="L17" s="84"/>
-      <c r="M17" s="84"/>
-      <c r="N17" s="85"/>
-      <c r="O17" s="83"/>
-      <c r="P17" s="81"/>
-      <c r="Q17" s="81"/>
-      <c r="R17" s="81"/>
-      <c r="S17" s="81"/>
-      <c r="T17" s="81"/>
-      <c r="U17" s="81"/>
-      <c r="V17" s="81"/>
-      <c r="W17" s="81"/>
-      <c r="X17" s="81"/>
-      <c r="Y17" s="81"/>
-      <c r="Z17" s="81"/>
-      <c r="AA17" s="81"/>
-      <c r="AB17" s="81"/>
-      <c r="AC17" s="81"/>
-      <c r="AD17" s="81"/>
-      <c r="AE17" s="81"/>
-      <c r="AF17" s="81"/>
-      <c r="AG17" s="81"/>
-      <c r="AH17" s="81"/>
-      <c r="AI17" s="81"/>
-      <c r="AJ17" s="81"/>
-      <c r="AK17" s="81"/>
-      <c r="AL17" s="81"/>
-      <c r="AM17" s="81"/>
-      <c r="AN17" s="81"/>
-      <c r="AO17" s="81"/>
-      <c r="AP17" s="89"/>
-      <c r="AQ17" s="80"/>
-      <c r="AR17" s="81"/>
-      <c r="AS17" s="81"/>
-      <c r="AT17" s="81"/>
-      <c r="AU17" s="81"/>
-      <c r="AV17" s="81"/>
-      <c r="AW17" s="81"/>
-      <c r="AX17" s="81"/>
-      <c r="AY17" s="81"/>
-      <c r="AZ17" s="81"/>
-      <c r="BA17" s="81"/>
-      <c r="BB17" s="81"/>
-      <c r="BC17" s="81"/>
-      <c r="BD17" s="81"/>
-      <c r="BE17" s="82"/>
+      <c r="A17" s="101"/>
+      <c r="B17" s="102"/>
+      <c r="C17" s="102"/>
+      <c r="D17" s="102"/>
+      <c r="E17" s="102"/>
+      <c r="F17" s="102"/>
+      <c r="G17" s="103"/>
+      <c r="H17" s="84"/>
+      <c r="I17" s="85"/>
+      <c r="J17" s="85"/>
+      <c r="K17" s="85"/>
+      <c r="L17" s="85"/>
+      <c r="M17" s="85"/>
+      <c r="N17" s="86"/>
+      <c r="O17" s="84"/>
+      <c r="P17" s="82"/>
+      <c r="Q17" s="82"/>
+      <c r="R17" s="82"/>
+      <c r="S17" s="82"/>
+      <c r="T17" s="82"/>
+      <c r="U17" s="82"/>
+      <c r="V17" s="82"/>
+      <c r="W17" s="82"/>
+      <c r="X17" s="82"/>
+      <c r="Y17" s="82"/>
+      <c r="Z17" s="82"/>
+      <c r="AA17" s="82"/>
+      <c r="AB17" s="82"/>
+      <c r="AC17" s="82"/>
+      <c r="AD17" s="82"/>
+      <c r="AE17" s="82"/>
+      <c r="AF17" s="82"/>
+      <c r="AG17" s="82"/>
+      <c r="AH17" s="82"/>
+      <c r="AI17" s="82"/>
+      <c r="AJ17" s="82"/>
+      <c r="AK17" s="82"/>
+      <c r="AL17" s="82"/>
+      <c r="AM17" s="82"/>
+      <c r="AN17" s="82"/>
+      <c r="AO17" s="82"/>
+      <c r="AP17" s="90"/>
+      <c r="AQ17" s="81"/>
+      <c r="AR17" s="82"/>
+      <c r="AS17" s="82"/>
+      <c r="AT17" s="82"/>
+      <c r="AU17" s="82"/>
+      <c r="AV17" s="82"/>
+      <c r="AW17" s="82"/>
+      <c r="AX17" s="82"/>
+      <c r="AY17" s="82"/>
+      <c r="AZ17" s="82"/>
+      <c r="BA17" s="82"/>
+      <c r="BB17" s="82"/>
+      <c r="BC17" s="82"/>
+      <c r="BD17" s="82"/>
+      <c r="BE17" s="83"/>
     </row>
     <row r="18" spans="1:57" ht="15" customHeight="1">
-      <c r="A18" s="100"/>
-      <c r="B18" s="101"/>
-      <c r="C18" s="101"/>
-      <c r="D18" s="101"/>
-      <c r="E18" s="101"/>
-      <c r="F18" s="101"/>
-      <c r="G18" s="102"/>
-      <c r="H18" s="83"/>
-      <c r="I18" s="84"/>
-      <c r="J18" s="84"/>
-      <c r="K18" s="84"/>
-      <c r="L18" s="84"/>
-      <c r="M18" s="84"/>
-      <c r="N18" s="85"/>
-      <c r="O18" s="83"/>
-      <c r="P18" s="81"/>
-      <c r="Q18" s="81"/>
-      <c r="R18" s="81"/>
-      <c r="S18" s="81"/>
-      <c r="T18" s="81"/>
-      <c r="U18" s="81"/>
-      <c r="V18" s="81"/>
-      <c r="W18" s="81"/>
-      <c r="X18" s="81"/>
-      <c r="Y18" s="81"/>
-      <c r="Z18" s="81"/>
-      <c r="AA18" s="81"/>
-      <c r="AB18" s="81"/>
-      <c r="AC18" s="81"/>
-      <c r="AD18" s="81"/>
-      <c r="AE18" s="81"/>
-      <c r="AF18" s="81"/>
-      <c r="AG18" s="81"/>
-      <c r="AH18" s="81"/>
-      <c r="AI18" s="81"/>
-      <c r="AJ18" s="81"/>
-      <c r="AK18" s="81"/>
-      <c r="AL18" s="81"/>
-      <c r="AM18" s="81"/>
-      <c r="AN18" s="81"/>
-      <c r="AO18" s="81"/>
-      <c r="AP18" s="89"/>
-      <c r="AQ18" s="80"/>
-      <c r="AR18" s="81"/>
-      <c r="AS18" s="81"/>
-      <c r="AT18" s="81"/>
-      <c r="AU18" s="81"/>
-      <c r="AV18" s="81"/>
-      <c r="AW18" s="81"/>
-      <c r="AX18" s="81"/>
-      <c r="AY18" s="81"/>
-      <c r="AZ18" s="81"/>
-      <c r="BA18" s="81"/>
-      <c r="BB18" s="81"/>
-      <c r="BC18" s="81"/>
-      <c r="BD18" s="81"/>
-      <c r="BE18" s="82"/>
+      <c r="A18" s="101"/>
+      <c r="B18" s="102"/>
+      <c r="C18" s="102"/>
+      <c r="D18" s="102"/>
+      <c r="E18" s="102"/>
+      <c r="F18" s="102"/>
+      <c r="G18" s="103"/>
+      <c r="H18" s="84"/>
+      <c r="I18" s="85"/>
+      <c r="J18" s="85"/>
+      <c r="K18" s="85"/>
+      <c r="L18" s="85"/>
+      <c r="M18" s="85"/>
+      <c r="N18" s="86"/>
+      <c r="O18" s="84"/>
+      <c r="P18" s="82"/>
+      <c r="Q18" s="82"/>
+      <c r="R18" s="82"/>
+      <c r="S18" s="82"/>
+      <c r="T18" s="82"/>
+      <c r="U18" s="82"/>
+      <c r="V18" s="82"/>
+      <c r="W18" s="82"/>
+      <c r="X18" s="82"/>
+      <c r="Y18" s="82"/>
+      <c r="Z18" s="82"/>
+      <c r="AA18" s="82"/>
+      <c r="AB18" s="82"/>
+      <c r="AC18" s="82"/>
+      <c r="AD18" s="82"/>
+      <c r="AE18" s="82"/>
+      <c r="AF18" s="82"/>
+      <c r="AG18" s="82"/>
+      <c r="AH18" s="82"/>
+      <c r="AI18" s="82"/>
+      <c r="AJ18" s="82"/>
+      <c r="AK18" s="82"/>
+      <c r="AL18" s="82"/>
+      <c r="AM18" s="82"/>
+      <c r="AN18" s="82"/>
+      <c r="AO18" s="82"/>
+      <c r="AP18" s="90"/>
+      <c r="AQ18" s="81"/>
+      <c r="AR18" s="82"/>
+      <c r="AS18" s="82"/>
+      <c r="AT18" s="82"/>
+      <c r="AU18" s="82"/>
+      <c r="AV18" s="82"/>
+      <c r="AW18" s="82"/>
+      <c r="AX18" s="82"/>
+      <c r="AY18" s="82"/>
+      <c r="AZ18" s="82"/>
+      <c r="BA18" s="82"/>
+      <c r="BB18" s="82"/>
+      <c r="BC18" s="82"/>
+      <c r="BD18" s="82"/>
+      <c r="BE18" s="83"/>
     </row>
     <row r="19" spans="1:57" ht="15" customHeight="1">
-      <c r="A19" s="100"/>
-      <c r="B19" s="101"/>
-      <c r="C19" s="101"/>
-      <c r="D19" s="101"/>
-      <c r="E19" s="101"/>
-      <c r="F19" s="101"/>
-      <c r="G19" s="102"/>
-      <c r="H19" s="83"/>
-      <c r="I19" s="84"/>
-      <c r="J19" s="84"/>
-      <c r="K19" s="84"/>
-      <c r="L19" s="84"/>
-      <c r="M19" s="84"/>
-      <c r="N19" s="85"/>
-      <c r="O19" s="83"/>
-      <c r="P19" s="81"/>
-      <c r="Q19" s="81"/>
-      <c r="R19" s="81"/>
-      <c r="S19" s="81"/>
-      <c r="T19" s="81"/>
-      <c r="U19" s="81"/>
-      <c r="V19" s="81"/>
-      <c r="W19" s="81"/>
-      <c r="X19" s="81"/>
-      <c r="Y19" s="81"/>
-      <c r="Z19" s="81"/>
-      <c r="AA19" s="81"/>
-      <c r="AB19" s="81"/>
-      <c r="AC19" s="81"/>
-      <c r="AD19" s="81"/>
-      <c r="AE19" s="81"/>
-      <c r="AF19" s="81"/>
-      <c r="AG19" s="81"/>
-      <c r="AH19" s="81"/>
-      <c r="AI19" s="81"/>
-      <c r="AJ19" s="81"/>
-      <c r="AK19" s="81"/>
-      <c r="AL19" s="81"/>
-      <c r="AM19" s="81"/>
-      <c r="AN19" s="81"/>
-      <c r="AO19" s="81"/>
-      <c r="AP19" s="89"/>
-      <c r="AQ19" s="80"/>
-      <c r="AR19" s="81"/>
-      <c r="AS19" s="81"/>
-      <c r="AT19" s="81"/>
-      <c r="AU19" s="81"/>
-      <c r="AV19" s="81"/>
-      <c r="AW19" s="81"/>
-      <c r="AX19" s="81"/>
-      <c r="AY19" s="81"/>
-      <c r="AZ19" s="81"/>
-      <c r="BA19" s="81"/>
-      <c r="BB19" s="81"/>
-      <c r="BC19" s="81"/>
-      <c r="BD19" s="81"/>
-      <c r="BE19" s="82"/>
+      <c r="A19" s="101"/>
+      <c r="B19" s="102"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="103"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="85"/>
+      <c r="J19" s="85"/>
+      <c r="K19" s="85"/>
+      <c r="L19" s="85"/>
+      <c r="M19" s="85"/>
+      <c r="N19" s="86"/>
+      <c r="O19" s="84"/>
+      <c r="P19" s="82"/>
+      <c r="Q19" s="82"/>
+      <c r="R19" s="82"/>
+      <c r="S19" s="82"/>
+      <c r="T19" s="82"/>
+      <c r="U19" s="82"/>
+      <c r="V19" s="82"/>
+      <c r="W19" s="82"/>
+      <c r="X19" s="82"/>
+      <c r="Y19" s="82"/>
+      <c r="Z19" s="82"/>
+      <c r="AA19" s="82"/>
+      <c r="AB19" s="82"/>
+      <c r="AC19" s="82"/>
+      <c r="AD19" s="82"/>
+      <c r="AE19" s="82"/>
+      <c r="AF19" s="82"/>
+      <c r="AG19" s="82"/>
+      <c r="AH19" s="82"/>
+      <c r="AI19" s="82"/>
+      <c r="AJ19" s="82"/>
+      <c r="AK19" s="82"/>
+      <c r="AL19" s="82"/>
+      <c r="AM19" s="82"/>
+      <c r="AN19" s="82"/>
+      <c r="AO19" s="82"/>
+      <c r="AP19" s="90"/>
+      <c r="AQ19" s="81"/>
+      <c r="AR19" s="82"/>
+      <c r="AS19" s="82"/>
+      <c r="AT19" s="82"/>
+      <c r="AU19" s="82"/>
+      <c r="AV19" s="82"/>
+      <c r="AW19" s="82"/>
+      <c r="AX19" s="82"/>
+      <c r="AY19" s="82"/>
+      <c r="AZ19" s="82"/>
+      <c r="BA19" s="82"/>
+      <c r="BB19" s="82"/>
+      <c r="BC19" s="82"/>
+      <c r="BD19" s="82"/>
+      <c r="BE19" s="83"/>
     </row>
     <row r="20" spans="1:57" ht="15" customHeight="1">
-      <c r="A20" s="100"/>
-      <c r="B20" s="101"/>
-      <c r="C20" s="101"/>
-      <c r="D20" s="101"/>
-      <c r="E20" s="101"/>
-      <c r="F20" s="101"/>
-      <c r="G20" s="102"/>
-      <c r="H20" s="83"/>
-      <c r="I20" s="84"/>
-      <c r="J20" s="84"/>
-      <c r="K20" s="84"/>
-      <c r="L20" s="84"/>
-      <c r="M20" s="84"/>
-      <c r="N20" s="85"/>
-      <c r="O20" s="83"/>
-      <c r="P20" s="81"/>
-      <c r="Q20" s="81"/>
-      <c r="R20" s="81"/>
-      <c r="S20" s="81"/>
-      <c r="T20" s="81"/>
-      <c r="U20" s="81"/>
-      <c r="V20" s="81"/>
-      <c r="W20" s="81"/>
-      <c r="X20" s="81"/>
-      <c r="Y20" s="81"/>
-      <c r="Z20" s="81"/>
-      <c r="AA20" s="81"/>
-      <c r="AB20" s="81"/>
-      <c r="AC20" s="81"/>
-      <c r="AD20" s="81"/>
-      <c r="AE20" s="81"/>
-      <c r="AF20" s="81"/>
-      <c r="AG20" s="81"/>
-      <c r="AH20" s="81"/>
-      <c r="AI20" s="81"/>
-      <c r="AJ20" s="81"/>
-      <c r="AK20" s="81"/>
-      <c r="AL20" s="81"/>
-      <c r="AM20" s="81"/>
-      <c r="AN20" s="81"/>
-      <c r="AO20" s="81"/>
-      <c r="AP20" s="89"/>
-      <c r="AQ20" s="80"/>
-      <c r="AR20" s="81"/>
-      <c r="AS20" s="81"/>
-      <c r="AT20" s="81"/>
-      <c r="AU20" s="81"/>
-      <c r="AV20" s="81"/>
-      <c r="AW20" s="81"/>
-      <c r="AX20" s="81"/>
-      <c r="AY20" s="81"/>
-      <c r="AZ20" s="81"/>
-      <c r="BA20" s="81"/>
-      <c r="BB20" s="81"/>
-      <c r="BC20" s="81"/>
-      <c r="BD20" s="81"/>
-      <c r="BE20" s="82"/>
+      <c r="A20" s="101"/>
+      <c r="B20" s="102"/>
+      <c r="C20" s="102"/>
+      <c r="D20" s="102"/>
+      <c r="E20" s="102"/>
+      <c r="F20" s="102"/>
+      <c r="G20" s="103"/>
+      <c r="H20" s="84"/>
+      <c r="I20" s="85"/>
+      <c r="J20" s="85"/>
+      <c r="K20" s="85"/>
+      <c r="L20" s="85"/>
+      <c r="M20" s="85"/>
+      <c r="N20" s="86"/>
+      <c r="O20" s="84"/>
+      <c r="P20" s="82"/>
+      <c r="Q20" s="82"/>
+      <c r="R20" s="82"/>
+      <c r="S20" s="82"/>
+      <c r="T20" s="82"/>
+      <c r="U20" s="82"/>
+      <c r="V20" s="82"/>
+      <c r="W20" s="82"/>
+      <c r="X20" s="82"/>
+      <c r="Y20" s="82"/>
+      <c r="Z20" s="82"/>
+      <c r="AA20" s="82"/>
+      <c r="AB20" s="82"/>
+      <c r="AC20" s="82"/>
+      <c r="AD20" s="82"/>
+      <c r="AE20" s="82"/>
+      <c r="AF20" s="82"/>
+      <c r="AG20" s="82"/>
+      <c r="AH20" s="82"/>
+      <c r="AI20" s="82"/>
+      <c r="AJ20" s="82"/>
+      <c r="AK20" s="82"/>
+      <c r="AL20" s="82"/>
+      <c r="AM20" s="82"/>
+      <c r="AN20" s="82"/>
+      <c r="AO20" s="82"/>
+      <c r="AP20" s="90"/>
+      <c r="AQ20" s="81"/>
+      <c r="AR20" s="82"/>
+      <c r="AS20" s="82"/>
+      <c r="AT20" s="82"/>
+      <c r="AU20" s="82"/>
+      <c r="AV20" s="82"/>
+      <c r="AW20" s="82"/>
+      <c r="AX20" s="82"/>
+      <c r="AY20" s="82"/>
+      <c r="AZ20" s="82"/>
+      <c r="BA20" s="82"/>
+      <c r="BB20" s="82"/>
+      <c r="BC20" s="82"/>
+      <c r="BD20" s="82"/>
+      <c r="BE20" s="83"/>
     </row>
     <row r="21" spans="1:57" ht="15" customHeight="1">
-      <c r="A21" s="100"/>
-      <c r="B21" s="101"/>
-      <c r="C21" s="101"/>
-      <c r="D21" s="101"/>
-      <c r="E21" s="101"/>
-      <c r="F21" s="101"/>
-      <c r="G21" s="102"/>
-      <c r="H21" s="83"/>
-      <c r="I21" s="84"/>
-      <c r="J21" s="84"/>
-      <c r="K21" s="84"/>
-      <c r="L21" s="84"/>
-      <c r="M21" s="84"/>
-      <c r="N21" s="85"/>
-      <c r="O21" s="83"/>
-      <c r="P21" s="81"/>
-      <c r="Q21" s="81"/>
-      <c r="R21" s="81"/>
-      <c r="S21" s="81"/>
-      <c r="T21" s="81"/>
-      <c r="U21" s="81"/>
-      <c r="V21" s="81"/>
-      <c r="W21" s="81"/>
-      <c r="X21" s="81"/>
-      <c r="Y21" s="81"/>
-      <c r="Z21" s="81"/>
-      <c r="AA21" s="81"/>
-      <c r="AB21" s="81"/>
-      <c r="AC21" s="81"/>
-      <c r="AD21" s="81"/>
-      <c r="AE21" s="81"/>
-      <c r="AF21" s="81"/>
-      <c r="AG21" s="81"/>
-      <c r="AH21" s="81"/>
-      <c r="AI21" s="81"/>
-      <c r="AJ21" s="81"/>
-      <c r="AK21" s="81"/>
-      <c r="AL21" s="81"/>
-      <c r="AM21" s="81"/>
-      <c r="AN21" s="81"/>
-      <c r="AO21" s="81"/>
-      <c r="AP21" s="89"/>
-      <c r="AQ21" s="80"/>
-      <c r="AR21" s="81"/>
-      <c r="AS21" s="81"/>
-      <c r="AT21" s="81"/>
-      <c r="AU21" s="81"/>
-      <c r="AV21" s="81"/>
-      <c r="AW21" s="81"/>
-      <c r="AX21" s="81"/>
-      <c r="AY21" s="81"/>
-      <c r="AZ21" s="81"/>
-      <c r="BA21" s="81"/>
-      <c r="BB21" s="81"/>
-      <c r="BC21" s="81"/>
-      <c r="BD21" s="81"/>
-      <c r="BE21" s="82"/>
+      <c r="A21" s="101"/>
+      <c r="B21" s="102"/>
+      <c r="C21" s="102"/>
+      <c r="D21" s="102"/>
+      <c r="E21" s="102"/>
+      <c r="F21" s="102"/>
+      <c r="G21" s="103"/>
+      <c r="H21" s="84"/>
+      <c r="I21" s="85"/>
+      <c r="J21" s="85"/>
+      <c r="K21" s="85"/>
+      <c r="L21" s="85"/>
+      <c r="M21" s="85"/>
+      <c r="N21" s="86"/>
+      <c r="O21" s="84"/>
+      <c r="P21" s="82"/>
+      <c r="Q21" s="82"/>
+      <c r="R21" s="82"/>
+      <c r="S21" s="82"/>
+      <c r="T21" s="82"/>
+      <c r="U21" s="82"/>
+      <c r="V21" s="82"/>
+      <c r="W21" s="82"/>
+      <c r="X21" s="82"/>
+      <c r="Y21" s="82"/>
+      <c r="Z21" s="82"/>
+      <c r="AA21" s="82"/>
+      <c r="AB21" s="82"/>
+      <c r="AC21" s="82"/>
+      <c r="AD21" s="82"/>
+      <c r="AE21" s="82"/>
+      <c r="AF21" s="82"/>
+      <c r="AG21" s="82"/>
+      <c r="AH21" s="82"/>
+      <c r="AI21" s="82"/>
+      <c r="AJ21" s="82"/>
+      <c r="AK21" s="82"/>
+      <c r="AL21" s="82"/>
+      <c r="AM21" s="82"/>
+      <c r="AN21" s="82"/>
+      <c r="AO21" s="82"/>
+      <c r="AP21" s="90"/>
+      <c r="AQ21" s="81"/>
+      <c r="AR21" s="82"/>
+      <c r="AS21" s="82"/>
+      <c r="AT21" s="82"/>
+      <c r="AU21" s="82"/>
+      <c r="AV21" s="82"/>
+      <c r="AW21" s="82"/>
+      <c r="AX21" s="82"/>
+      <c r="AY21" s="82"/>
+      <c r="AZ21" s="82"/>
+      <c r="BA21" s="82"/>
+      <c r="BB21" s="82"/>
+      <c r="BC21" s="82"/>
+      <c r="BD21" s="82"/>
+      <c r="BE21" s="83"/>
     </row>
     <row r="22" spans="1:57" ht="15" customHeight="1">
-      <c r="A22" s="100"/>
-      <c r="B22" s="101"/>
-      <c r="C22" s="101"/>
-      <c r="D22" s="101"/>
-      <c r="E22" s="101"/>
-      <c r="F22" s="101"/>
-      <c r="G22" s="102"/>
-      <c r="H22" s="83"/>
-      <c r="I22" s="84"/>
-      <c r="J22" s="84"/>
-      <c r="K22" s="84"/>
-      <c r="L22" s="84"/>
-      <c r="M22" s="84"/>
-      <c r="N22" s="85"/>
-      <c r="O22" s="83"/>
-      <c r="P22" s="81"/>
-      <c r="Q22" s="81"/>
-      <c r="R22" s="81"/>
-      <c r="S22" s="81"/>
-      <c r="T22" s="81"/>
-      <c r="U22" s="81"/>
-      <c r="V22" s="81"/>
-      <c r="W22" s="81"/>
-      <c r="X22" s="81"/>
-      <c r="Y22" s="81"/>
-      <c r="Z22" s="81"/>
-      <c r="AA22" s="81"/>
-      <c r="AB22" s="81"/>
-      <c r="AC22" s="81"/>
-      <c r="AD22" s="81"/>
-      <c r="AE22" s="81"/>
-      <c r="AF22" s="81"/>
-      <c r="AG22" s="81"/>
-      <c r="AH22" s="81"/>
-      <c r="AI22" s="81"/>
-      <c r="AJ22" s="81"/>
-      <c r="AK22" s="81"/>
-      <c r="AL22" s="81"/>
-      <c r="AM22" s="81"/>
-      <c r="AN22" s="81"/>
-      <c r="AO22" s="81"/>
-      <c r="AP22" s="89"/>
-      <c r="AQ22" s="80"/>
-      <c r="AR22" s="81"/>
-      <c r="AS22" s="81"/>
-      <c r="AT22" s="81"/>
-      <c r="AU22" s="81"/>
-      <c r="AV22" s="81"/>
-      <c r="AW22" s="81"/>
-      <c r="AX22" s="81"/>
-      <c r="AY22" s="81"/>
-      <c r="AZ22" s="81"/>
-      <c r="BA22" s="81"/>
-      <c r="BB22" s="81"/>
-      <c r="BC22" s="81"/>
-      <c r="BD22" s="81"/>
-      <c r="BE22" s="82"/>
+      <c r="A22" s="101"/>
+      <c r="B22" s="102"/>
+      <c r="C22" s="102"/>
+      <c r="D22" s="102"/>
+      <c r="E22" s="102"/>
+      <c r="F22" s="102"/>
+      <c r="G22" s="103"/>
+      <c r="H22" s="84"/>
+      <c r="I22" s="85"/>
+      <c r="J22" s="85"/>
+      <c r="K22" s="85"/>
+      <c r="L22" s="85"/>
+      <c r="M22" s="85"/>
+      <c r="N22" s="86"/>
+      <c r="O22" s="84"/>
+      <c r="P22" s="82"/>
+      <c r="Q22" s="82"/>
+      <c r="R22" s="82"/>
+      <c r="S22" s="82"/>
+      <c r="T22" s="82"/>
+      <c r="U22" s="82"/>
+      <c r="V22" s="82"/>
+      <c r="W22" s="82"/>
+      <c r="X22" s="82"/>
+      <c r="Y22" s="82"/>
+      <c r="Z22" s="82"/>
+      <c r="AA22" s="82"/>
+      <c r="AB22" s="82"/>
+      <c r="AC22" s="82"/>
+      <c r="AD22" s="82"/>
+      <c r="AE22" s="82"/>
+      <c r="AF22" s="82"/>
+      <c r="AG22" s="82"/>
+      <c r="AH22" s="82"/>
+      <c r="AI22" s="82"/>
+      <c r="AJ22" s="82"/>
+      <c r="AK22" s="82"/>
+      <c r="AL22" s="82"/>
+      <c r="AM22" s="82"/>
+      <c r="AN22" s="82"/>
+      <c r="AO22" s="82"/>
+      <c r="AP22" s="90"/>
+      <c r="AQ22" s="81"/>
+      <c r="AR22" s="82"/>
+      <c r="AS22" s="82"/>
+      <c r="AT22" s="82"/>
+      <c r="AU22" s="82"/>
+      <c r="AV22" s="82"/>
+      <c r="AW22" s="82"/>
+      <c r="AX22" s="82"/>
+      <c r="AY22" s="82"/>
+      <c r="AZ22" s="82"/>
+      <c r="BA22" s="82"/>
+      <c r="BB22" s="82"/>
+      <c r="BC22" s="82"/>
+      <c r="BD22" s="82"/>
+      <c r="BE22" s="83"/>
     </row>
     <row r="23" spans="1:57" ht="15" customHeight="1">
-      <c r="A23" s="100"/>
-      <c r="B23" s="101"/>
-      <c r="C23" s="101"/>
-      <c r="D23" s="101"/>
-      <c r="E23" s="101"/>
-      <c r="F23" s="101"/>
-      <c r="G23" s="102"/>
-      <c r="H23" s="83"/>
-      <c r="I23" s="84"/>
-      <c r="J23" s="84"/>
-      <c r="K23" s="84"/>
-      <c r="L23" s="84"/>
-      <c r="M23" s="84"/>
-      <c r="N23" s="85"/>
-      <c r="O23" s="83"/>
-      <c r="P23" s="81"/>
-      <c r="Q23" s="81"/>
-      <c r="R23" s="81"/>
-      <c r="S23" s="81"/>
-      <c r="T23" s="81"/>
-      <c r="U23" s="81"/>
-      <c r="V23" s="81"/>
-      <c r="W23" s="81"/>
-      <c r="X23" s="81"/>
-      <c r="Y23" s="81"/>
-      <c r="Z23" s="81"/>
-      <c r="AA23" s="81"/>
-      <c r="AB23" s="81"/>
-      <c r="AC23" s="81"/>
-      <c r="AD23" s="81"/>
-      <c r="AE23" s="81"/>
-      <c r="AF23" s="81"/>
-      <c r="AG23" s="81"/>
-      <c r="AH23" s="81"/>
-      <c r="AI23" s="81"/>
-      <c r="AJ23" s="81"/>
-      <c r="AK23" s="81"/>
-      <c r="AL23" s="81"/>
-      <c r="AM23" s="81"/>
-      <c r="AN23" s="81"/>
-      <c r="AO23" s="81"/>
-      <c r="AP23" s="89"/>
-      <c r="AQ23" s="80"/>
-      <c r="AR23" s="81"/>
-      <c r="AS23" s="81"/>
-      <c r="AT23" s="81"/>
-      <c r="AU23" s="81"/>
-      <c r="AV23" s="81"/>
-      <c r="AW23" s="81"/>
-      <c r="AX23" s="81"/>
-      <c r="AY23" s="81"/>
-      <c r="AZ23" s="81"/>
-      <c r="BA23" s="81"/>
-      <c r="BB23" s="81"/>
-      <c r="BC23" s="81"/>
-      <c r="BD23" s="81"/>
-      <c r="BE23" s="82"/>
+      <c r="A23" s="101"/>
+      <c r="B23" s="102"/>
+      <c r="C23" s="102"/>
+      <c r="D23" s="102"/>
+      <c r="E23" s="102"/>
+      <c r="F23" s="102"/>
+      <c r="G23" s="103"/>
+      <c r="H23" s="84"/>
+      <c r="I23" s="85"/>
+      <c r="J23" s="85"/>
+      <c r="K23" s="85"/>
+      <c r="L23" s="85"/>
+      <c r="M23" s="85"/>
+      <c r="N23" s="86"/>
+      <c r="O23" s="84"/>
+      <c r="P23" s="82"/>
+      <c r="Q23" s="82"/>
+      <c r="R23" s="82"/>
+      <c r="S23" s="82"/>
+      <c r="T23" s="82"/>
+      <c r="U23" s="82"/>
+      <c r="V23" s="82"/>
+      <c r="W23" s="82"/>
+      <c r="X23" s="82"/>
+      <c r="Y23" s="82"/>
+      <c r="Z23" s="82"/>
+      <c r="AA23" s="82"/>
+      <c r="AB23" s="82"/>
+      <c r="AC23" s="82"/>
+      <c r="AD23" s="82"/>
+      <c r="AE23" s="82"/>
+      <c r="AF23" s="82"/>
+      <c r="AG23" s="82"/>
+      <c r="AH23" s="82"/>
+      <c r="AI23" s="82"/>
+      <c r="AJ23" s="82"/>
+      <c r="AK23" s="82"/>
+      <c r="AL23" s="82"/>
+      <c r="AM23" s="82"/>
+      <c r="AN23" s="82"/>
+      <c r="AO23" s="82"/>
+      <c r="AP23" s="90"/>
+      <c r="AQ23" s="81"/>
+      <c r="AR23" s="82"/>
+      <c r="AS23" s="82"/>
+      <c r="AT23" s="82"/>
+      <c r="AU23" s="82"/>
+      <c r="AV23" s="82"/>
+      <c r="AW23" s="82"/>
+      <c r="AX23" s="82"/>
+      <c r="AY23" s="82"/>
+      <c r="AZ23" s="82"/>
+      <c r="BA23" s="82"/>
+      <c r="BB23" s="82"/>
+      <c r="BC23" s="82"/>
+      <c r="BD23" s="82"/>
+      <c r="BE23" s="83"/>
     </row>
     <row r="24" spans="1:57" ht="15" customHeight="1">
-      <c r="A24" s="100"/>
-      <c r="B24" s="101"/>
-      <c r="C24" s="101"/>
-      <c r="D24" s="101"/>
-      <c r="E24" s="101"/>
-      <c r="F24" s="101"/>
-      <c r="G24" s="102"/>
-      <c r="H24" s="83"/>
-      <c r="I24" s="84"/>
-      <c r="J24" s="84"/>
-      <c r="K24" s="84"/>
-      <c r="L24" s="84"/>
-      <c r="M24" s="84"/>
-      <c r="N24" s="85"/>
-      <c r="O24" s="83"/>
-      <c r="P24" s="81"/>
-      <c r="Q24" s="81"/>
-      <c r="R24" s="81"/>
-      <c r="S24" s="81"/>
-      <c r="T24" s="81"/>
-      <c r="U24" s="81"/>
-      <c r="V24" s="81"/>
-      <c r="W24" s="81"/>
-      <c r="X24" s="81"/>
-      <c r="Y24" s="81"/>
-      <c r="Z24" s="81"/>
-      <c r="AA24" s="81"/>
-      <c r="AB24" s="81"/>
-      <c r="AC24" s="81"/>
-      <c r="AD24" s="81"/>
-      <c r="AE24" s="81"/>
-      <c r="AF24" s="81"/>
-      <c r="AG24" s="81"/>
-      <c r="AH24" s="81"/>
-      <c r="AI24" s="81"/>
-      <c r="AJ24" s="81"/>
-      <c r="AK24" s="81"/>
-      <c r="AL24" s="81"/>
-      <c r="AM24" s="81"/>
-      <c r="AN24" s="81"/>
-      <c r="AO24" s="81"/>
-      <c r="AP24" s="89"/>
-      <c r="AQ24" s="80"/>
-      <c r="AR24" s="81"/>
-      <c r="AS24" s="81"/>
-      <c r="AT24" s="81"/>
-      <c r="AU24" s="81"/>
-      <c r="AV24" s="81"/>
-      <c r="AW24" s="81"/>
-      <c r="AX24" s="81"/>
-      <c r="AY24" s="81"/>
-      <c r="AZ24" s="81"/>
-      <c r="BA24" s="81"/>
-      <c r="BB24" s="81"/>
-      <c r="BC24" s="81"/>
-      <c r="BD24" s="81"/>
-      <c r="BE24" s="82"/>
+      <c r="A24" s="101"/>
+      <c r="B24" s="102"/>
+      <c r="C24" s="102"/>
+      <c r="D24" s="102"/>
+      <c r="E24" s="102"/>
+      <c r="F24" s="102"/>
+      <c r="G24" s="103"/>
+      <c r="H24" s="84"/>
+      <c r="I24" s="85"/>
+      <c r="J24" s="85"/>
+      <c r="K24" s="85"/>
+      <c r="L24" s="85"/>
+      <c r="M24" s="85"/>
+      <c r="N24" s="86"/>
+      <c r="O24" s="84"/>
+      <c r="P24" s="82"/>
+      <c r="Q24" s="82"/>
+      <c r="R24" s="82"/>
+      <c r="S24" s="82"/>
+      <c r="T24" s="82"/>
+      <c r="U24" s="82"/>
+      <c r="V24" s="82"/>
+      <c r="W24" s="82"/>
+      <c r="X24" s="82"/>
+      <c r="Y24" s="82"/>
+      <c r="Z24" s="82"/>
+      <c r="AA24" s="82"/>
+      <c r="AB24" s="82"/>
+      <c r="AC24" s="82"/>
+      <c r="AD24" s="82"/>
+      <c r="AE24" s="82"/>
+      <c r="AF24" s="82"/>
+      <c r="AG24" s="82"/>
+      <c r="AH24" s="82"/>
+      <c r="AI24" s="82"/>
+      <c r="AJ24" s="82"/>
+      <c r="AK24" s="82"/>
+      <c r="AL24" s="82"/>
+      <c r="AM24" s="82"/>
+      <c r="AN24" s="82"/>
+      <c r="AO24" s="82"/>
+      <c r="AP24" s="90"/>
+      <c r="AQ24" s="81"/>
+      <c r="AR24" s="82"/>
+      <c r="AS24" s="82"/>
+      <c r="AT24" s="82"/>
+      <c r="AU24" s="82"/>
+      <c r="AV24" s="82"/>
+      <c r="AW24" s="82"/>
+      <c r="AX24" s="82"/>
+      <c r="AY24" s="82"/>
+      <c r="AZ24" s="82"/>
+      <c r="BA24" s="82"/>
+      <c r="BB24" s="82"/>
+      <c r="BC24" s="82"/>
+      <c r="BD24" s="82"/>
+      <c r="BE24" s="83"/>
     </row>
     <row r="25" spans="1:57" ht="15" customHeight="1">
-      <c r="A25" s="100"/>
-      <c r="B25" s="101"/>
-      <c r="C25" s="101"/>
-      <c r="D25" s="101"/>
-      <c r="E25" s="101"/>
-      <c r="F25" s="101"/>
-      <c r="G25" s="102"/>
-      <c r="H25" s="83"/>
-      <c r="I25" s="84"/>
-      <c r="J25" s="84"/>
-      <c r="K25" s="84"/>
-      <c r="L25" s="84"/>
-      <c r="M25" s="84"/>
-      <c r="N25" s="85"/>
-      <c r="O25" s="83"/>
-      <c r="P25" s="81"/>
-      <c r="Q25" s="81"/>
-      <c r="R25" s="81"/>
-      <c r="S25" s="81"/>
-      <c r="T25" s="81"/>
-      <c r="U25" s="81"/>
-      <c r="V25" s="81"/>
-      <c r="W25" s="81"/>
-      <c r="X25" s="81"/>
-      <c r="Y25" s="81"/>
-      <c r="Z25" s="81"/>
-      <c r="AA25" s="81"/>
-      <c r="AB25" s="81"/>
-      <c r="AC25" s="81"/>
-      <c r="AD25" s="81"/>
-      <c r="AE25" s="81"/>
-      <c r="AF25" s="81"/>
-      <c r="AG25" s="81"/>
-      <c r="AH25" s="81"/>
-      <c r="AI25" s="81"/>
-      <c r="AJ25" s="81"/>
-      <c r="AK25" s="81"/>
-      <c r="AL25" s="81"/>
-      <c r="AM25" s="81"/>
-      <c r="AN25" s="81"/>
-      <c r="AO25" s="81"/>
-      <c r="AP25" s="89"/>
-      <c r="AQ25" s="80"/>
-      <c r="AR25" s="81"/>
-      <c r="AS25" s="81"/>
-      <c r="AT25" s="81"/>
-      <c r="AU25" s="81"/>
-      <c r="AV25" s="81"/>
-      <c r="AW25" s="81"/>
-      <c r="AX25" s="81"/>
-      <c r="AY25" s="81"/>
-      <c r="AZ25" s="81"/>
-      <c r="BA25" s="81"/>
-      <c r="BB25" s="81"/>
-      <c r="BC25" s="81"/>
-      <c r="BD25" s="81"/>
-      <c r="BE25" s="82"/>
+      <c r="A25" s="101"/>
+      <c r="B25" s="102"/>
+      <c r="C25" s="102"/>
+      <c r="D25" s="102"/>
+      <c r="E25" s="102"/>
+      <c r="F25" s="102"/>
+      <c r="G25" s="103"/>
+      <c r="H25" s="84"/>
+      <c r="I25" s="85"/>
+      <c r="J25" s="85"/>
+      <c r="K25" s="85"/>
+      <c r="L25" s="85"/>
+      <c r="M25" s="85"/>
+      <c r="N25" s="86"/>
+      <c r="O25" s="84"/>
+      <c r="P25" s="82"/>
+      <c r="Q25" s="82"/>
+      <c r="R25" s="82"/>
+      <c r="S25" s="82"/>
+      <c r="T25" s="82"/>
+      <c r="U25" s="82"/>
+      <c r="V25" s="82"/>
+      <c r="W25" s="82"/>
+      <c r="X25" s="82"/>
+      <c r="Y25" s="82"/>
+      <c r="Z25" s="82"/>
+      <c r="AA25" s="82"/>
+      <c r="AB25" s="82"/>
+      <c r="AC25" s="82"/>
+      <c r="AD25" s="82"/>
+      <c r="AE25" s="82"/>
+      <c r="AF25" s="82"/>
+      <c r="AG25" s="82"/>
+      <c r="AH25" s="82"/>
+      <c r="AI25" s="82"/>
+      <c r="AJ25" s="82"/>
+      <c r="AK25" s="82"/>
+      <c r="AL25" s="82"/>
+      <c r="AM25" s="82"/>
+      <c r="AN25" s="82"/>
+      <c r="AO25" s="82"/>
+      <c r="AP25" s="90"/>
+      <c r="AQ25" s="81"/>
+      <c r="AR25" s="82"/>
+      <c r="AS25" s="82"/>
+      <c r="AT25" s="82"/>
+      <c r="AU25" s="82"/>
+      <c r="AV25" s="82"/>
+      <c r="AW25" s="82"/>
+      <c r="AX25" s="82"/>
+      <c r="AY25" s="82"/>
+      <c r="AZ25" s="82"/>
+      <c r="BA25" s="82"/>
+      <c r="BB25" s="82"/>
+      <c r="BC25" s="82"/>
+      <c r="BD25" s="82"/>
+      <c r="BE25" s="83"/>
     </row>
     <row r="26" spans="1:57" ht="15" customHeight="1">
-      <c r="A26" s="100"/>
-      <c r="B26" s="101"/>
-      <c r="C26" s="101"/>
-      <c r="D26" s="101"/>
-      <c r="E26" s="101"/>
-      <c r="F26" s="101"/>
-      <c r="G26" s="102"/>
-      <c r="H26" s="83"/>
-      <c r="I26" s="84"/>
-      <c r="J26" s="84"/>
-      <c r="K26" s="84"/>
-      <c r="L26" s="84"/>
-      <c r="M26" s="84"/>
-      <c r="N26" s="85"/>
-      <c r="O26" s="83"/>
-      <c r="P26" s="81"/>
-      <c r="Q26" s="81"/>
-      <c r="R26" s="81"/>
-      <c r="S26" s="81"/>
-      <c r="T26" s="81"/>
-      <c r="U26" s="81"/>
-      <c r="V26" s="81"/>
-      <c r="W26" s="81"/>
-      <c r="X26" s="81"/>
-      <c r="Y26" s="81"/>
-      <c r="Z26" s="81"/>
-      <c r="AA26" s="81"/>
-      <c r="AB26" s="81"/>
-      <c r="AC26" s="81"/>
-      <c r="AD26" s="81"/>
-      <c r="AE26" s="81"/>
-      <c r="AF26" s="81"/>
-      <c r="AG26" s="81"/>
-      <c r="AH26" s="81"/>
-      <c r="AI26" s="81"/>
-      <c r="AJ26" s="81"/>
-      <c r="AK26" s="81"/>
-      <c r="AL26" s="81"/>
-      <c r="AM26" s="81"/>
-      <c r="AN26" s="81"/>
-      <c r="AO26" s="81"/>
-      <c r="AP26" s="89"/>
-      <c r="AQ26" s="80"/>
-      <c r="AR26" s="81"/>
-      <c r="AS26" s="81"/>
-      <c r="AT26" s="81"/>
-      <c r="AU26" s="81"/>
-      <c r="AV26" s="81"/>
-      <c r="AW26" s="81"/>
-      <c r="AX26" s="81"/>
-      <c r="AY26" s="81"/>
-      <c r="AZ26" s="81"/>
-      <c r="BA26" s="81"/>
-      <c r="BB26" s="81"/>
-      <c r="BC26" s="81"/>
-      <c r="BD26" s="81"/>
-      <c r="BE26" s="82"/>
+      <c r="A26" s="101"/>
+      <c r="B26" s="102"/>
+      <c r="C26" s="102"/>
+      <c r="D26" s="102"/>
+      <c r="E26" s="102"/>
+      <c r="F26" s="102"/>
+      <c r="G26" s="103"/>
+      <c r="H26" s="84"/>
+      <c r="I26" s="85"/>
+      <c r="J26" s="85"/>
+      <c r="K26" s="85"/>
+      <c r="L26" s="85"/>
+      <c r="M26" s="85"/>
+      <c r="N26" s="86"/>
+      <c r="O26" s="84"/>
+      <c r="P26" s="82"/>
+      <c r="Q26" s="82"/>
+      <c r="R26" s="82"/>
+      <c r="S26" s="82"/>
+      <c r="T26" s="82"/>
+      <c r="U26" s="82"/>
+      <c r="V26" s="82"/>
+      <c r="W26" s="82"/>
+      <c r="X26" s="82"/>
+      <c r="Y26" s="82"/>
+      <c r="Z26" s="82"/>
+      <c r="AA26" s="82"/>
+      <c r="AB26" s="82"/>
+      <c r="AC26" s="82"/>
+      <c r="AD26" s="82"/>
+      <c r="AE26" s="82"/>
+      <c r="AF26" s="82"/>
+      <c r="AG26" s="82"/>
+      <c r="AH26" s="82"/>
+      <c r="AI26" s="82"/>
+      <c r="AJ26" s="82"/>
+      <c r="AK26" s="82"/>
+      <c r="AL26" s="82"/>
+      <c r="AM26" s="82"/>
+      <c r="AN26" s="82"/>
+      <c r="AO26" s="82"/>
+      <c r="AP26" s="90"/>
+      <c r="AQ26" s="81"/>
+      <c r="AR26" s="82"/>
+      <c r="AS26" s="82"/>
+      <c r="AT26" s="82"/>
+      <c r="AU26" s="82"/>
+      <c r="AV26" s="82"/>
+      <c r="AW26" s="82"/>
+      <c r="AX26" s="82"/>
+      <c r="AY26" s="82"/>
+      <c r="AZ26" s="82"/>
+      <c r="BA26" s="82"/>
+      <c r="BB26" s="82"/>
+      <c r="BC26" s="82"/>
+      <c r="BD26" s="82"/>
+      <c r="BE26" s="83"/>
     </row>
     <row r="27" spans="1:57" ht="15" customHeight="1">
-      <c r="A27" s="100"/>
-      <c r="B27" s="101"/>
-      <c r="C27" s="101"/>
-      <c r="D27" s="101"/>
-      <c r="E27" s="101"/>
-      <c r="F27" s="101"/>
-      <c r="G27" s="102"/>
-      <c r="H27" s="83"/>
-      <c r="I27" s="84"/>
-      <c r="J27" s="84"/>
-      <c r="K27" s="84"/>
-      <c r="L27" s="84"/>
-      <c r="M27" s="84"/>
-      <c r="N27" s="85"/>
-      <c r="O27" s="83"/>
-      <c r="P27" s="81"/>
-      <c r="Q27" s="81"/>
-      <c r="R27" s="81"/>
-      <c r="S27" s="81"/>
-      <c r="T27" s="81"/>
-      <c r="U27" s="81"/>
-      <c r="V27" s="81"/>
-      <c r="W27" s="81"/>
-      <c r="X27" s="81"/>
-      <c r="Y27" s="81"/>
-      <c r="Z27" s="81"/>
-      <c r="AA27" s="81"/>
-      <c r="AB27" s="81"/>
-      <c r="AC27" s="81"/>
-      <c r="AD27" s="81"/>
-      <c r="AE27" s="81"/>
-      <c r="AF27" s="81"/>
-      <c r="AG27" s="81"/>
-      <c r="AH27" s="81"/>
-      <c r="AI27" s="81"/>
-      <c r="AJ27" s="81"/>
-      <c r="AK27" s="81"/>
-      <c r="AL27" s="81"/>
-      <c r="AM27" s="81"/>
-      <c r="AN27" s="81"/>
-      <c r="AO27" s="81"/>
-      <c r="AP27" s="89"/>
-      <c r="AQ27" s="80"/>
-      <c r="AR27" s="81"/>
-      <c r="AS27" s="81"/>
-      <c r="AT27" s="81"/>
-      <c r="AU27" s="81"/>
-      <c r="AV27" s="81"/>
-      <c r="AW27" s="81"/>
-      <c r="AX27" s="81"/>
-      <c r="AY27" s="81"/>
-      <c r="AZ27" s="81"/>
-      <c r="BA27" s="81"/>
-      <c r="BB27" s="81"/>
-      <c r="BC27" s="81"/>
-      <c r="BD27" s="81"/>
-      <c r="BE27" s="82"/>
+      <c r="A27" s="101"/>
+      <c r="B27" s="102"/>
+      <c r="C27" s="102"/>
+      <c r="D27" s="102"/>
+      <c r="E27" s="102"/>
+      <c r="F27" s="102"/>
+      <c r="G27" s="103"/>
+      <c r="H27" s="84"/>
+      <c r="I27" s="85"/>
+      <c r="J27" s="85"/>
+      <c r="K27" s="85"/>
+      <c r="L27" s="85"/>
+      <c r="M27" s="85"/>
+      <c r="N27" s="86"/>
+      <c r="O27" s="84"/>
+      <c r="P27" s="82"/>
+      <c r="Q27" s="82"/>
+      <c r="R27" s="82"/>
+      <c r="S27" s="82"/>
+      <c r="T27" s="82"/>
+      <c r="U27" s="82"/>
+      <c r="V27" s="82"/>
+      <c r="W27" s="82"/>
+      <c r="X27" s="82"/>
+      <c r="Y27" s="82"/>
+      <c r="Z27" s="82"/>
+      <c r="AA27" s="82"/>
+      <c r="AB27" s="82"/>
+      <c r="AC27" s="82"/>
+      <c r="AD27" s="82"/>
+      <c r="AE27" s="82"/>
+      <c r="AF27" s="82"/>
+      <c r="AG27" s="82"/>
+      <c r="AH27" s="82"/>
+      <c r="AI27" s="82"/>
+      <c r="AJ27" s="82"/>
+      <c r="AK27" s="82"/>
+      <c r="AL27" s="82"/>
+      <c r="AM27" s="82"/>
+      <c r="AN27" s="82"/>
+      <c r="AO27" s="82"/>
+      <c r="AP27" s="90"/>
+      <c r="AQ27" s="81"/>
+      <c r="AR27" s="82"/>
+      <c r="AS27" s="82"/>
+      <c r="AT27" s="82"/>
+      <c r="AU27" s="82"/>
+      <c r="AV27" s="82"/>
+      <c r="AW27" s="82"/>
+      <c r="AX27" s="82"/>
+      <c r="AY27" s="82"/>
+      <c r="AZ27" s="82"/>
+      <c r="BA27" s="82"/>
+      <c r="BB27" s="82"/>
+      <c r="BC27" s="82"/>
+      <c r="BD27" s="82"/>
+      <c r="BE27" s="83"/>
     </row>
     <row r="28" spans="1:57" ht="15" customHeight="1">
-      <c r="A28" s="100"/>
-      <c r="B28" s="101"/>
-      <c r="C28" s="101"/>
-      <c r="D28" s="101"/>
-      <c r="E28" s="101"/>
-      <c r="F28" s="101"/>
-      <c r="G28" s="102"/>
-      <c r="H28" s="83"/>
-      <c r="I28" s="84"/>
-      <c r="J28" s="84"/>
-      <c r="K28" s="84"/>
-      <c r="L28" s="84"/>
-      <c r="M28" s="84"/>
-      <c r="N28" s="85"/>
-      <c r="O28" s="83"/>
-      <c r="P28" s="81"/>
-      <c r="Q28" s="81"/>
-      <c r="R28" s="81"/>
-      <c r="S28" s="81"/>
-      <c r="T28" s="81"/>
-      <c r="U28" s="81"/>
-      <c r="V28" s="81"/>
-      <c r="W28" s="81"/>
-      <c r="X28" s="81"/>
-      <c r="Y28" s="81"/>
-      <c r="Z28" s="81"/>
-      <c r="AA28" s="81"/>
-      <c r="AB28" s="81"/>
-      <c r="AC28" s="81"/>
-      <c r="AD28" s="81"/>
-      <c r="AE28" s="81"/>
-      <c r="AF28" s="81"/>
-      <c r="AG28" s="81"/>
-      <c r="AH28" s="81"/>
-      <c r="AI28" s="81"/>
-      <c r="AJ28" s="81"/>
-      <c r="AK28" s="81"/>
-      <c r="AL28" s="81"/>
-      <c r="AM28" s="81"/>
-      <c r="AN28" s="81"/>
-      <c r="AO28" s="81"/>
-      <c r="AP28" s="89"/>
-      <c r="AQ28" s="80"/>
-      <c r="AR28" s="81"/>
-      <c r="AS28" s="81"/>
-      <c r="AT28" s="81"/>
-      <c r="AU28" s="81"/>
-      <c r="AV28" s="81"/>
-      <c r="AW28" s="81"/>
-      <c r="AX28" s="81"/>
-      <c r="AY28" s="81"/>
-      <c r="AZ28" s="81"/>
-      <c r="BA28" s="81"/>
-      <c r="BB28" s="81"/>
-      <c r="BC28" s="81"/>
-      <c r="BD28" s="81"/>
-      <c r="BE28" s="82"/>
+      <c r="A28" s="101"/>
+      <c r="B28" s="102"/>
+      <c r="C28" s="102"/>
+      <c r="D28" s="102"/>
+      <c r="E28" s="102"/>
+      <c r="F28" s="102"/>
+      <c r="G28" s="103"/>
+      <c r="H28" s="84"/>
+      <c r="I28" s="85"/>
+      <c r="J28" s="85"/>
+      <c r="K28" s="85"/>
+      <c r="L28" s="85"/>
+      <c r="M28" s="85"/>
+      <c r="N28" s="86"/>
+      <c r="O28" s="84"/>
+      <c r="P28" s="82"/>
+      <c r="Q28" s="82"/>
+      <c r="R28" s="82"/>
+      <c r="S28" s="82"/>
+      <c r="T28" s="82"/>
+      <c r="U28" s="82"/>
+      <c r="V28" s="82"/>
+      <c r="W28" s="82"/>
+      <c r="X28" s="82"/>
+      <c r="Y28" s="82"/>
+      <c r="Z28" s="82"/>
+      <c r="AA28" s="82"/>
+      <c r="AB28" s="82"/>
+      <c r="AC28" s="82"/>
+      <c r="AD28" s="82"/>
+      <c r="AE28" s="82"/>
+      <c r="AF28" s="82"/>
+      <c r="AG28" s="82"/>
+      <c r="AH28" s="82"/>
+      <c r="AI28" s="82"/>
+      <c r="AJ28" s="82"/>
+      <c r="AK28" s="82"/>
+      <c r="AL28" s="82"/>
+      <c r="AM28" s="82"/>
+      <c r="AN28" s="82"/>
+      <c r="AO28" s="82"/>
+      <c r="AP28" s="90"/>
+      <c r="AQ28" s="81"/>
+      <c r="AR28" s="82"/>
+      <c r="AS28" s="82"/>
+      <c r="AT28" s="82"/>
+      <c r="AU28" s="82"/>
+      <c r="AV28" s="82"/>
+      <c r="AW28" s="82"/>
+      <c r="AX28" s="82"/>
+      <c r="AY28" s="82"/>
+      <c r="AZ28" s="82"/>
+      <c r="BA28" s="82"/>
+      <c r="BB28" s="82"/>
+      <c r="BC28" s="82"/>
+      <c r="BD28" s="82"/>
+      <c r="BE28" s="83"/>
     </row>
     <row r="29" spans="1:57" ht="15" customHeight="1">
-      <c r="A29" s="100"/>
-      <c r="B29" s="101"/>
-      <c r="C29" s="101"/>
-      <c r="D29" s="101"/>
-      <c r="E29" s="101"/>
-      <c r="F29" s="101"/>
-      <c r="G29" s="102"/>
-      <c r="H29" s="83"/>
-      <c r="I29" s="84"/>
-      <c r="J29" s="84"/>
-      <c r="K29" s="84"/>
-      <c r="L29" s="84"/>
-      <c r="M29" s="84"/>
-      <c r="N29" s="85"/>
-      <c r="O29" s="83"/>
-      <c r="P29" s="81"/>
-      <c r="Q29" s="81"/>
-      <c r="R29" s="81"/>
-      <c r="S29" s="81"/>
-      <c r="T29" s="81"/>
-      <c r="U29" s="81"/>
-      <c r="V29" s="81"/>
-      <c r="W29" s="81"/>
-      <c r="X29" s="81"/>
-      <c r="Y29" s="81"/>
-      <c r="Z29" s="81"/>
-      <c r="AA29" s="81"/>
-      <c r="AB29" s="81"/>
-      <c r="AC29" s="81"/>
-      <c r="AD29" s="81"/>
-      <c r="AE29" s="81"/>
-      <c r="AF29" s="81"/>
-      <c r="AG29" s="81"/>
-      <c r="AH29" s="81"/>
-      <c r="AI29" s="81"/>
-      <c r="AJ29" s="81"/>
-      <c r="AK29" s="81"/>
-      <c r="AL29" s="81"/>
-      <c r="AM29" s="81"/>
-      <c r="AN29" s="81"/>
-      <c r="AO29" s="81"/>
-      <c r="AP29" s="89"/>
-      <c r="AQ29" s="80"/>
-      <c r="AR29" s="81"/>
-      <c r="AS29" s="81"/>
-      <c r="AT29" s="81"/>
-      <c r="AU29" s="81"/>
-      <c r="AV29" s="81"/>
-      <c r="AW29" s="81"/>
-      <c r="AX29" s="81"/>
-      <c r="AY29" s="81"/>
-      <c r="AZ29" s="81"/>
-      <c r="BA29" s="81"/>
-      <c r="BB29" s="81"/>
-      <c r="BC29" s="81"/>
-      <c r="BD29" s="81"/>
-      <c r="BE29" s="82"/>
+      <c r="A29" s="101"/>
+      <c r="B29" s="102"/>
+      <c r="C29" s="102"/>
+      <c r="D29" s="102"/>
+      <c r="E29" s="102"/>
+      <c r="F29" s="102"/>
+      <c r="G29" s="103"/>
+      <c r="H29" s="84"/>
+      <c r="I29" s="85"/>
+      <c r="J29" s="85"/>
+      <c r="K29" s="85"/>
+      <c r="L29" s="85"/>
+      <c r="M29" s="85"/>
+      <c r="N29" s="86"/>
+      <c r="O29" s="84"/>
+      <c r="P29" s="82"/>
+      <c r="Q29" s="82"/>
+      <c r="R29" s="82"/>
+      <c r="S29" s="82"/>
+      <c r="T29" s="82"/>
+      <c r="U29" s="82"/>
+      <c r="V29" s="82"/>
+      <c r="W29" s="82"/>
+      <c r="X29" s="82"/>
+      <c r="Y29" s="82"/>
+      <c r="Z29" s="82"/>
+      <c r="AA29" s="82"/>
+      <c r="AB29" s="82"/>
+      <c r="AC29" s="82"/>
+      <c r="AD29" s="82"/>
+      <c r="AE29" s="82"/>
+      <c r="AF29" s="82"/>
+      <c r="AG29" s="82"/>
+      <c r="AH29" s="82"/>
+      <c r="AI29" s="82"/>
+      <c r="AJ29" s="82"/>
+      <c r="AK29" s="82"/>
+      <c r="AL29" s="82"/>
+      <c r="AM29" s="82"/>
+      <c r="AN29" s="82"/>
+      <c r="AO29" s="82"/>
+      <c r="AP29" s="90"/>
+      <c r="AQ29" s="81"/>
+      <c r="AR29" s="82"/>
+      <c r="AS29" s="82"/>
+      <c r="AT29" s="82"/>
+      <c r="AU29" s="82"/>
+      <c r="AV29" s="82"/>
+      <c r="AW29" s="82"/>
+      <c r="AX29" s="82"/>
+      <c r="AY29" s="82"/>
+      <c r="AZ29" s="82"/>
+      <c r="BA29" s="82"/>
+      <c r="BB29" s="82"/>
+      <c r="BC29" s="82"/>
+      <c r="BD29" s="82"/>
+      <c r="BE29" s="83"/>
     </row>
     <row r="30" spans="1:57" ht="15" customHeight="1">
-      <c r="A30" s="100"/>
-      <c r="B30" s="101"/>
-      <c r="C30" s="101"/>
-      <c r="D30" s="101"/>
-      <c r="E30" s="101"/>
-      <c r="F30" s="101"/>
-      <c r="G30" s="102"/>
-      <c r="H30" s="83"/>
-      <c r="I30" s="84"/>
-      <c r="J30" s="84"/>
-      <c r="K30" s="84"/>
-      <c r="L30" s="84"/>
-      <c r="M30" s="84"/>
-      <c r="N30" s="85"/>
-      <c r="O30" s="83"/>
-      <c r="P30" s="81"/>
-      <c r="Q30" s="81"/>
-      <c r="R30" s="81"/>
-      <c r="S30" s="81"/>
-      <c r="T30" s="81"/>
-      <c r="U30" s="81"/>
-      <c r="V30" s="81"/>
-      <c r="W30" s="81"/>
-      <c r="X30" s="81"/>
-      <c r="Y30" s="81"/>
-      <c r="Z30" s="81"/>
-      <c r="AA30" s="81"/>
-      <c r="AB30" s="81"/>
-      <c r="AC30" s="81"/>
-      <c r="AD30" s="81"/>
-      <c r="AE30" s="81"/>
-      <c r="AF30" s="81"/>
-      <c r="AG30" s="81"/>
-      <c r="AH30" s="81"/>
-      <c r="AI30" s="81"/>
-      <c r="AJ30" s="81"/>
-      <c r="AK30" s="81"/>
-      <c r="AL30" s="81"/>
-      <c r="AM30" s="81"/>
-      <c r="AN30" s="81"/>
-      <c r="AO30" s="81"/>
-      <c r="AP30" s="89"/>
-      <c r="AQ30" s="80"/>
-      <c r="AR30" s="81"/>
-      <c r="AS30" s="81"/>
-      <c r="AT30" s="81"/>
-      <c r="AU30" s="81"/>
-      <c r="AV30" s="81"/>
-      <c r="AW30" s="81"/>
-      <c r="AX30" s="81"/>
-      <c r="AY30" s="81"/>
-      <c r="AZ30" s="81"/>
-      <c r="BA30" s="81"/>
-      <c r="BB30" s="81"/>
-      <c r="BC30" s="81"/>
-      <c r="BD30" s="81"/>
-      <c r="BE30" s="82"/>
+      <c r="A30" s="101"/>
+      <c r="B30" s="102"/>
+      <c r="C30" s="102"/>
+      <c r="D30" s="102"/>
+      <c r="E30" s="102"/>
+      <c r="F30" s="102"/>
+      <c r="G30" s="103"/>
+      <c r="H30" s="84"/>
+      <c r="I30" s="85"/>
+      <c r="J30" s="85"/>
+      <c r="K30" s="85"/>
+      <c r="L30" s="85"/>
+      <c r="M30" s="85"/>
+      <c r="N30" s="86"/>
+      <c r="O30" s="84"/>
+      <c r="P30" s="82"/>
+      <c r="Q30" s="82"/>
+      <c r="R30" s="82"/>
+      <c r="S30" s="82"/>
+      <c r="T30" s="82"/>
+      <c r="U30" s="82"/>
+      <c r="V30" s="82"/>
+      <c r="W30" s="82"/>
+      <c r="X30" s="82"/>
+      <c r="Y30" s="82"/>
+      <c r="Z30" s="82"/>
+      <c r="AA30" s="82"/>
+      <c r="AB30" s="82"/>
+      <c r="AC30" s="82"/>
+      <c r="AD30" s="82"/>
+      <c r="AE30" s="82"/>
+      <c r="AF30" s="82"/>
+      <c r="AG30" s="82"/>
+      <c r="AH30" s="82"/>
+      <c r="AI30" s="82"/>
+      <c r="AJ30" s="82"/>
+      <c r="AK30" s="82"/>
+      <c r="AL30" s="82"/>
+      <c r="AM30" s="82"/>
+      <c r="AN30" s="82"/>
+      <c r="AO30" s="82"/>
+      <c r="AP30" s="90"/>
+      <c r="AQ30" s="81"/>
+      <c r="AR30" s="82"/>
+      <c r="AS30" s="82"/>
+      <c r="AT30" s="82"/>
+      <c r="AU30" s="82"/>
+      <c r="AV30" s="82"/>
+      <c r="AW30" s="82"/>
+      <c r="AX30" s="82"/>
+      <c r="AY30" s="82"/>
+      <c r="AZ30" s="82"/>
+      <c r="BA30" s="82"/>
+      <c r="BB30" s="82"/>
+      <c r="BC30" s="82"/>
+      <c r="BD30" s="82"/>
+      <c r="BE30" s="83"/>
     </row>
     <row r="31" spans="1:57" ht="15" customHeight="1">
-      <c r="A31" s="100"/>
-      <c r="B31" s="101"/>
-      <c r="C31" s="101"/>
-      <c r="D31" s="101"/>
-      <c r="E31" s="101"/>
-      <c r="F31" s="101"/>
-      <c r="G31" s="102"/>
-      <c r="H31" s="83"/>
-      <c r="I31" s="84"/>
-      <c r="J31" s="84"/>
-      <c r="K31" s="84"/>
-      <c r="L31" s="84"/>
-      <c r="M31" s="84"/>
-      <c r="N31" s="85"/>
-      <c r="O31" s="83"/>
-      <c r="P31" s="81"/>
-      <c r="Q31" s="81"/>
-      <c r="R31" s="81"/>
-      <c r="S31" s="81"/>
-      <c r="T31" s="81"/>
-      <c r="U31" s="81"/>
-      <c r="V31" s="81"/>
-      <c r="W31" s="81"/>
-      <c r="X31" s="81"/>
-      <c r="Y31" s="81"/>
-      <c r="Z31" s="81"/>
-      <c r="AA31" s="81"/>
-      <c r="AB31" s="81"/>
-      <c r="AC31" s="81"/>
-      <c r="AD31" s="81"/>
-      <c r="AE31" s="81"/>
-      <c r="AF31" s="81"/>
-      <c r="AG31" s="81"/>
-      <c r="AH31" s="81"/>
-      <c r="AI31" s="81"/>
-      <c r="AJ31" s="81"/>
-      <c r="AK31" s="81"/>
-      <c r="AL31" s="81"/>
-      <c r="AM31" s="81"/>
-      <c r="AN31" s="81"/>
-      <c r="AO31" s="81"/>
-      <c r="AP31" s="89"/>
-      <c r="AQ31" s="80"/>
-      <c r="AR31" s="81"/>
-      <c r="AS31" s="81"/>
-      <c r="AT31" s="81"/>
-      <c r="AU31" s="81"/>
-      <c r="AV31" s="81"/>
-      <c r="AW31" s="81"/>
-      <c r="AX31" s="81"/>
-      <c r="AY31" s="81"/>
-      <c r="AZ31" s="81"/>
-      <c r="BA31" s="81"/>
-      <c r="BB31" s="81"/>
-      <c r="BC31" s="81"/>
-      <c r="BD31" s="81"/>
-      <c r="BE31" s="82"/>
+      <c r="A31" s="101"/>
+      <c r="B31" s="102"/>
+      <c r="C31" s="102"/>
+      <c r="D31" s="102"/>
+      <c r="E31" s="102"/>
+      <c r="F31" s="102"/>
+      <c r="G31" s="103"/>
+      <c r="H31" s="84"/>
+      <c r="I31" s="85"/>
+      <c r="J31" s="85"/>
+      <c r="K31" s="85"/>
+      <c r="L31" s="85"/>
+      <c r="M31" s="85"/>
+      <c r="N31" s="86"/>
+      <c r="O31" s="84"/>
+      <c r="P31" s="82"/>
+      <c r="Q31" s="82"/>
+      <c r="R31" s="82"/>
+      <c r="S31" s="82"/>
+      <c r="T31" s="82"/>
+      <c r="U31" s="82"/>
+      <c r="V31" s="82"/>
+      <c r="W31" s="82"/>
+      <c r="X31" s="82"/>
+      <c r="Y31" s="82"/>
+      <c r="Z31" s="82"/>
+      <c r="AA31" s="82"/>
+      <c r="AB31" s="82"/>
+      <c r="AC31" s="82"/>
+      <c r="AD31" s="82"/>
+      <c r="AE31" s="82"/>
+      <c r="AF31" s="82"/>
+      <c r="AG31" s="82"/>
+      <c r="AH31" s="82"/>
+      <c r="AI31" s="82"/>
+      <c r="AJ31" s="82"/>
+      <c r="AK31" s="82"/>
+      <c r="AL31" s="82"/>
+      <c r="AM31" s="82"/>
+      <c r="AN31" s="82"/>
+      <c r="AO31" s="82"/>
+      <c r="AP31" s="90"/>
+      <c r="AQ31" s="81"/>
+      <c r="AR31" s="82"/>
+      <c r="AS31" s="82"/>
+      <c r="AT31" s="82"/>
+      <c r="AU31" s="82"/>
+      <c r="AV31" s="82"/>
+      <c r="AW31" s="82"/>
+      <c r="AX31" s="82"/>
+      <c r="AY31" s="82"/>
+      <c r="AZ31" s="82"/>
+      <c r="BA31" s="82"/>
+      <c r="BB31" s="82"/>
+      <c r="BC31" s="82"/>
+      <c r="BD31" s="82"/>
+      <c r="BE31" s="83"/>
     </row>
     <row r="32" spans="1:57" ht="15" customHeight="1">
-      <c r="A32" s="100"/>
-      <c r="B32" s="101"/>
-      <c r="C32" s="101"/>
-      <c r="D32" s="101"/>
-      <c r="E32" s="101"/>
-      <c r="F32" s="101"/>
-      <c r="G32" s="102"/>
-      <c r="H32" s="83"/>
-      <c r="I32" s="84"/>
-      <c r="J32" s="84"/>
-      <c r="K32" s="84"/>
-      <c r="L32" s="84"/>
-      <c r="M32" s="84"/>
-      <c r="N32" s="85"/>
-      <c r="O32" s="83"/>
-      <c r="P32" s="81"/>
-      <c r="Q32" s="81"/>
-      <c r="R32" s="81"/>
-      <c r="S32" s="81"/>
-      <c r="T32" s="81"/>
-      <c r="U32" s="81"/>
-      <c r="V32" s="81"/>
-      <c r="W32" s="81"/>
-      <c r="X32" s="81"/>
-      <c r="Y32" s="81"/>
-      <c r="Z32" s="81"/>
-      <c r="AA32" s="81"/>
-      <c r="AB32" s="81"/>
-      <c r="AC32" s="81"/>
-      <c r="AD32" s="81"/>
-      <c r="AE32" s="81"/>
-      <c r="AF32" s="81"/>
-      <c r="AG32" s="81"/>
-      <c r="AH32" s="81"/>
-      <c r="AI32" s="81"/>
-      <c r="AJ32" s="81"/>
-      <c r="AK32" s="81"/>
-      <c r="AL32" s="81"/>
-      <c r="AM32" s="81"/>
-      <c r="AN32" s="81"/>
-      <c r="AO32" s="81"/>
-      <c r="AP32" s="89"/>
-      <c r="AQ32" s="80"/>
-      <c r="AR32" s="81"/>
-      <c r="AS32" s="81"/>
-      <c r="AT32" s="81"/>
-      <c r="AU32" s="81"/>
-      <c r="AV32" s="81"/>
-      <c r="AW32" s="81"/>
-      <c r="AX32" s="81"/>
-      <c r="AY32" s="81"/>
-      <c r="AZ32" s="81"/>
-      <c r="BA32" s="81"/>
-      <c r="BB32" s="81"/>
-      <c r="BC32" s="81"/>
-      <c r="BD32" s="81"/>
-      <c r="BE32" s="82"/>
+      <c r="A32" s="101"/>
+      <c r="B32" s="102"/>
+      <c r="C32" s="102"/>
+      <c r="D32" s="102"/>
+      <c r="E32" s="102"/>
+      <c r="F32" s="102"/>
+      <c r="G32" s="103"/>
+      <c r="H32" s="84"/>
+      <c r="I32" s="85"/>
+      <c r="J32" s="85"/>
+      <c r="K32" s="85"/>
+      <c r="L32" s="85"/>
+      <c r="M32" s="85"/>
+      <c r="N32" s="86"/>
+      <c r="O32" s="84"/>
+      <c r="P32" s="82"/>
+      <c r="Q32" s="82"/>
+      <c r="R32" s="82"/>
+      <c r="S32" s="82"/>
+      <c r="T32" s="82"/>
+      <c r="U32" s="82"/>
+      <c r="V32" s="82"/>
+      <c r="W32" s="82"/>
+      <c r="X32" s="82"/>
+      <c r="Y32" s="82"/>
+      <c r="Z32" s="82"/>
+      <c r="AA32" s="82"/>
+      <c r="AB32" s="82"/>
+      <c r="AC32" s="82"/>
+      <c r="AD32" s="82"/>
+      <c r="AE32" s="82"/>
+      <c r="AF32" s="82"/>
+      <c r="AG32" s="82"/>
+      <c r="AH32" s="82"/>
+      <c r="AI32" s="82"/>
+      <c r="AJ32" s="82"/>
+      <c r="AK32" s="82"/>
+      <c r="AL32" s="82"/>
+      <c r="AM32" s="82"/>
+      <c r="AN32" s="82"/>
+      <c r="AO32" s="82"/>
+      <c r="AP32" s="90"/>
+      <c r="AQ32" s="81"/>
+      <c r="AR32" s="82"/>
+      <c r="AS32" s="82"/>
+      <c r="AT32" s="82"/>
+      <c r="AU32" s="82"/>
+      <c r="AV32" s="82"/>
+      <c r="AW32" s="82"/>
+      <c r="AX32" s="82"/>
+      <c r="AY32" s="82"/>
+      <c r="AZ32" s="82"/>
+      <c r="BA32" s="82"/>
+      <c r="BB32" s="82"/>
+      <c r="BC32" s="82"/>
+      <c r="BD32" s="82"/>
+      <c r="BE32" s="83"/>
     </row>
     <row r="33" spans="1:57" ht="15" customHeight="1">
-      <c r="A33" s="100"/>
-      <c r="B33" s="101"/>
-      <c r="C33" s="101"/>
-      <c r="D33" s="101"/>
-      <c r="E33" s="101"/>
-      <c r="F33" s="101"/>
-      <c r="G33" s="102"/>
-      <c r="H33" s="83"/>
-      <c r="I33" s="84"/>
-      <c r="J33" s="84"/>
-      <c r="K33" s="84"/>
-      <c r="L33" s="84"/>
-      <c r="M33" s="84"/>
-      <c r="N33" s="85"/>
-      <c r="O33" s="83"/>
-      <c r="P33" s="81"/>
-      <c r="Q33" s="81"/>
-      <c r="R33" s="81"/>
-      <c r="S33" s="81"/>
-      <c r="T33" s="81"/>
-      <c r="U33" s="81"/>
-      <c r="V33" s="81"/>
-      <c r="W33" s="81"/>
-      <c r="X33" s="81"/>
-      <c r="Y33" s="81"/>
-      <c r="Z33" s="81"/>
-      <c r="AA33" s="81"/>
-      <c r="AB33" s="81"/>
-      <c r="AC33" s="81"/>
-      <c r="AD33" s="81"/>
-      <c r="AE33" s="81"/>
-      <c r="AF33" s="81"/>
-      <c r="AG33" s="81"/>
-      <c r="AH33" s="81"/>
-      <c r="AI33" s="81"/>
-      <c r="AJ33" s="81"/>
-      <c r="AK33" s="81"/>
-      <c r="AL33" s="81"/>
-      <c r="AM33" s="81"/>
-      <c r="AN33" s="81"/>
-      <c r="AO33" s="81"/>
-      <c r="AP33" s="89"/>
-      <c r="AQ33" s="80"/>
-      <c r="AR33" s="81"/>
-      <c r="AS33" s="81"/>
-      <c r="AT33" s="81"/>
-      <c r="AU33" s="81"/>
-      <c r="AV33" s="81"/>
-      <c r="AW33" s="81"/>
-      <c r="AX33" s="81"/>
-      <c r="AY33" s="81"/>
-      <c r="AZ33" s="81"/>
-      <c r="BA33" s="81"/>
-      <c r="BB33" s="81"/>
-      <c r="BC33" s="81"/>
-      <c r="BD33" s="81"/>
-      <c r="BE33" s="82"/>
+      <c r="A33" s="101"/>
+      <c r="B33" s="102"/>
+      <c r="C33" s="102"/>
+      <c r="D33" s="102"/>
+      <c r="E33" s="102"/>
+      <c r="F33" s="102"/>
+      <c r="G33" s="103"/>
+      <c r="H33" s="84"/>
+      <c r="I33" s="85"/>
+      <c r="J33" s="85"/>
+      <c r="K33" s="85"/>
+      <c r="L33" s="85"/>
+      <c r="M33" s="85"/>
+      <c r="N33" s="86"/>
+      <c r="O33" s="84"/>
+      <c r="P33" s="82"/>
+      <c r="Q33" s="82"/>
+      <c r="R33" s="82"/>
+      <c r="S33" s="82"/>
+      <c r="T33" s="82"/>
+      <c r="U33" s="82"/>
+      <c r="V33" s="82"/>
+      <c r="W33" s="82"/>
+      <c r="X33" s="82"/>
+      <c r="Y33" s="82"/>
+      <c r="Z33" s="82"/>
+      <c r="AA33" s="82"/>
+      <c r="AB33" s="82"/>
+      <c r="AC33" s="82"/>
+      <c r="AD33" s="82"/>
+      <c r="AE33" s="82"/>
+      <c r="AF33" s="82"/>
+      <c r="AG33" s="82"/>
+      <c r="AH33" s="82"/>
+      <c r="AI33" s="82"/>
+      <c r="AJ33" s="82"/>
+      <c r="AK33" s="82"/>
+      <c r="AL33" s="82"/>
+      <c r="AM33" s="82"/>
+      <c r="AN33" s="82"/>
+      <c r="AO33" s="82"/>
+      <c r="AP33" s="90"/>
+      <c r="AQ33" s="81"/>
+      <c r="AR33" s="82"/>
+      <c r="AS33" s="82"/>
+      <c r="AT33" s="82"/>
+      <c r="AU33" s="82"/>
+      <c r="AV33" s="82"/>
+      <c r="AW33" s="82"/>
+      <c r="AX33" s="82"/>
+      <c r="AY33" s="82"/>
+      <c r="AZ33" s="82"/>
+      <c r="BA33" s="82"/>
+      <c r="BB33" s="82"/>
+      <c r="BC33" s="82"/>
+      <c r="BD33" s="82"/>
+      <c r="BE33" s="83"/>
     </row>
     <row r="34" spans="1:57" ht="15" customHeight="1">
-      <c r="A34" s="100"/>
-      <c r="B34" s="101"/>
-      <c r="C34" s="101"/>
-      <c r="D34" s="101"/>
-      <c r="E34" s="101"/>
-      <c r="F34" s="101"/>
-      <c r="G34" s="102"/>
-      <c r="H34" s="83"/>
-      <c r="I34" s="84"/>
-      <c r="J34" s="84"/>
-      <c r="K34" s="84"/>
-      <c r="L34" s="84"/>
-      <c r="M34" s="84"/>
-      <c r="N34" s="85"/>
-      <c r="O34" s="83"/>
-      <c r="P34" s="81"/>
-      <c r="Q34" s="81"/>
-      <c r="R34" s="81"/>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="81"/>
-      <c r="V34" s="81"/>
-      <c r="W34" s="81"/>
-      <c r="X34" s="81"/>
-      <c r="Y34" s="81"/>
-      <c r="Z34" s="81"/>
-      <c r="AA34" s="81"/>
-      <c r="AB34" s="81"/>
-      <c r="AC34" s="81"/>
-      <c r="AD34" s="81"/>
-      <c r="AE34" s="81"/>
-      <c r="AF34" s="81"/>
-      <c r="AG34" s="81"/>
-      <c r="AH34" s="81"/>
-      <c r="AI34" s="81"/>
-      <c r="AJ34" s="81"/>
-      <c r="AK34" s="81"/>
-      <c r="AL34" s="81"/>
-      <c r="AM34" s="81"/>
-      <c r="AN34" s="81"/>
-      <c r="AO34" s="81"/>
-      <c r="AP34" s="89"/>
-      <c r="AQ34" s="80"/>
-      <c r="AR34" s="81"/>
-      <c r="AS34" s="81"/>
-      <c r="AT34" s="81"/>
-      <c r="AU34" s="81"/>
-      <c r="AV34" s="81"/>
-      <c r="AW34" s="81"/>
-      <c r="AX34" s="81"/>
-      <c r="AY34" s="81"/>
-      <c r="AZ34" s="81"/>
-      <c r="BA34" s="81"/>
-      <c r="BB34" s="81"/>
-      <c r="BC34" s="81"/>
-      <c r="BD34" s="81"/>
-      <c r="BE34" s="82"/>
+      <c r="A34" s="101"/>
+      <c r="B34" s="102"/>
+      <c r="C34" s="102"/>
+      <c r="D34" s="102"/>
+      <c r="E34" s="102"/>
+      <c r="F34" s="102"/>
+      <c r="G34" s="103"/>
+      <c r="H34" s="84"/>
+      <c r="I34" s="85"/>
+      <c r="J34" s="85"/>
+      <c r="K34" s="85"/>
+      <c r="L34" s="85"/>
+      <c r="M34" s="85"/>
+      <c r="N34" s="86"/>
+      <c r="O34" s="84"/>
+      <c r="P34" s="82"/>
+      <c r="Q34" s="82"/>
+      <c r="R34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="82"/>
+      <c r="V34" s="82"/>
+      <c r="W34" s="82"/>
+      <c r="X34" s="82"/>
+      <c r="Y34" s="82"/>
+      <c r="Z34" s="82"/>
+      <c r="AA34" s="82"/>
+      <c r="AB34" s="82"/>
+      <c r="AC34" s="82"/>
+      <c r="AD34" s="82"/>
+      <c r="AE34" s="82"/>
+      <c r="AF34" s="82"/>
+      <c r="AG34" s="82"/>
+      <c r="AH34" s="82"/>
+      <c r="AI34" s="82"/>
+      <c r="AJ34" s="82"/>
+      <c r="AK34" s="82"/>
+      <c r="AL34" s="82"/>
+      <c r="AM34" s="82"/>
+      <c r="AN34" s="82"/>
+      <c r="AO34" s="82"/>
+      <c r="AP34" s="90"/>
+      <c r="AQ34" s="81"/>
+      <c r="AR34" s="82"/>
+      <c r="AS34" s="82"/>
+      <c r="AT34" s="82"/>
+      <c r="AU34" s="82"/>
+      <c r="AV34" s="82"/>
+      <c r="AW34" s="82"/>
+      <c r="AX34" s="82"/>
+      <c r="AY34" s="82"/>
+      <c r="AZ34" s="82"/>
+      <c r="BA34" s="82"/>
+      <c r="BB34" s="82"/>
+      <c r="BC34" s="82"/>
+      <c r="BD34" s="82"/>
+      <c r="BE34" s="83"/>
     </row>
     <row r="35" spans="1:57" ht="15" customHeight="1" thickBot="1">
-      <c r="A35" s="121"/>
-      <c r="B35" s="122"/>
-      <c r="C35" s="122"/>
-      <c r="D35" s="122"/>
-      <c r="E35" s="122"/>
-      <c r="F35" s="122"/>
-      <c r="G35" s="123"/>
-      <c r="H35" s="127"/>
-      <c r="I35" s="128"/>
-      <c r="J35" s="128"/>
-      <c r="K35" s="128"/>
-      <c r="L35" s="128"/>
-      <c r="M35" s="128"/>
-      <c r="N35" s="129"/>
-      <c r="O35" s="127"/>
-      <c r="P35" s="125"/>
-      <c r="Q35" s="125"/>
-      <c r="R35" s="125"/>
-      <c r="S35" s="125"/>
-      <c r="T35" s="125"/>
-      <c r="U35" s="125"/>
-      <c r="V35" s="125"/>
-      <c r="W35" s="125"/>
-      <c r="X35" s="125"/>
-      <c r="Y35" s="125"/>
-      <c r="Z35" s="125"/>
-      <c r="AA35" s="125"/>
-      <c r="AB35" s="125"/>
-      <c r="AC35" s="125"/>
-      <c r="AD35" s="125"/>
-      <c r="AE35" s="125"/>
-      <c r="AF35" s="125"/>
-      <c r="AG35" s="125"/>
-      <c r="AH35" s="125"/>
-      <c r="AI35" s="125"/>
-      <c r="AJ35" s="125"/>
-      <c r="AK35" s="125"/>
-      <c r="AL35" s="125"/>
-      <c r="AM35" s="125"/>
-      <c r="AN35" s="125"/>
-      <c r="AO35" s="125"/>
-      <c r="AP35" s="130"/>
-      <c r="AQ35" s="124"/>
-      <c r="AR35" s="125"/>
-      <c r="AS35" s="125"/>
-      <c r="AT35" s="125"/>
-      <c r="AU35" s="125"/>
-      <c r="AV35" s="125"/>
-      <c r="AW35" s="125"/>
-      <c r="AX35" s="125"/>
-      <c r="AY35" s="125"/>
-      <c r="AZ35" s="125"/>
-      <c r="BA35" s="125"/>
-      <c r="BB35" s="125"/>
-      <c r="BC35" s="125"/>
-      <c r="BD35" s="125"/>
-      <c r="BE35" s="126"/>
+      <c r="A35" s="122"/>
+      <c r="B35" s="123"/>
+      <c r="C35" s="123"/>
+      <c r="D35" s="123"/>
+      <c r="E35" s="123"/>
+      <c r="F35" s="123"/>
+      <c r="G35" s="124"/>
+      <c r="H35" s="128"/>
+      <c r="I35" s="129"/>
+      <c r="J35" s="129"/>
+      <c r="K35" s="129"/>
+      <c r="L35" s="129"/>
+      <c r="M35" s="129"/>
+      <c r="N35" s="130"/>
+      <c r="O35" s="128"/>
+      <c r="P35" s="126"/>
+      <c r="Q35" s="126"/>
+      <c r="R35" s="126"/>
+      <c r="S35" s="126"/>
+      <c r="T35" s="126"/>
+      <c r="U35" s="126"/>
+      <c r="V35" s="126"/>
+      <c r="W35" s="126"/>
+      <c r="X35" s="126"/>
+      <c r="Y35" s="126"/>
+      <c r="Z35" s="126"/>
+      <c r="AA35" s="126"/>
+      <c r="AB35" s="126"/>
+      <c r="AC35" s="126"/>
+      <c r="AD35" s="126"/>
+      <c r="AE35" s="126"/>
+      <c r="AF35" s="126"/>
+      <c r="AG35" s="126"/>
+      <c r="AH35" s="126"/>
+      <c r="AI35" s="126"/>
+      <c r="AJ35" s="126"/>
+      <c r="AK35" s="126"/>
+      <c r="AL35" s="126"/>
+      <c r="AM35" s="126"/>
+      <c r="AN35" s="126"/>
+      <c r="AO35" s="126"/>
+      <c r="AP35" s="131"/>
+      <c r="AQ35" s="125"/>
+      <c r="AR35" s="126"/>
+      <c r="AS35" s="126"/>
+      <c r="AT35" s="126"/>
+      <c r="AU35" s="126"/>
+      <c r="AV35" s="126"/>
+      <c r="AW35" s="126"/>
+      <c r="AX35" s="126"/>
+      <c r="AY35" s="126"/>
+      <c r="AZ35" s="126"/>
+      <c r="BA35" s="126"/>
+      <c r="BB35" s="126"/>
+      <c r="BC35" s="126"/>
+      <c r="BD35" s="126"/>
+      <c r="BE35" s="127"/>
     </row>
   </sheetData>
   <mergeCells count="133">

--- a/development/MS/spec/MSBB/Panel/MSBBP1210_SloReg.xlsx
+++ b/development/MS/spec/MSBB/Panel/MSBBP1210_SloReg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\mcframeDEV\development\MS\spec\MSBB\Panel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675FD08B-2CA2-4FCD-B240-F357C773A556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD1919B-6703-476B-BCB1-C1CA0AA99650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-3330" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9145" uniqueCount="2369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9147" uniqueCount="2371">
   <si>
     <t>検索</t>
     <rPh sb="0" eb="2">
@@ -10047,6 +10047,12 @@
   </si>
   <si>
     <t>sls_dpt_cd</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>MS.MSUAP0010.SlsCondTyp</t>
   </si>
 </sst>
 </file>
@@ -11462,14 +11468,14 @@
     <xf numFmtId="0" fontId="27" fillId="24" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -11480,79 +11486,7 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11561,29 +11495,8 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -11614,6 +11527,99 @@
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -31034,7 +31040,7 @@
       </c>
       <c r="J224" s="25"/>
       <c r="K224" s="25" t="s">
-        <v>26</v>
+        <v>2369</v>
       </c>
       <c r="L224" s="25"/>
       <c r="M224" s="25"/>
@@ -32648,16 +32654,20 @@
       </c>
       <c r="J244" s="61"/>
       <c r="K244" s="61" t="s">
-        <v>2246</v>
+        <v>2369</v>
       </c>
       <c r="L244" s="61"/>
       <c r="M244" s="61"/>
       <c r="N244" s="61"/>
       <c r="O244" s="61"/>
       <c r="P244" s="61"/>
-      <c r="Q244" s="61"/>
+      <c r="Q244" s="61" t="s">
+        <v>2370</v>
+      </c>
       <c r="R244" s="61"/>
-      <c r="S244" s="61"/>
+      <c r="S244" s="61" t="s">
+        <v>2248</v>
+      </c>
       <c r="T244" s="61"/>
       <c r="U244" s="61"/>
       <c r="V244" s="61"/>
@@ -64848,65 +64858,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:57" ht="38.25" customHeight="1" thickBot="1">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="104" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
-      <c r="V1" s="109"/>
-      <c r="W1" s="109"/>
-      <c r="X1" s="109"/>
-      <c r="Y1" s="109"/>
-      <c r="Z1" s="109"/>
-      <c r="AA1" s="109"/>
-      <c r="AB1" s="109"/>
-      <c r="AC1" s="109"/>
-      <c r="AD1" s="109"/>
-      <c r="AE1" s="109"/>
-      <c r="AF1" s="109"/>
-      <c r="AG1" s="109"/>
-      <c r="AH1" s="109"/>
-      <c r="AI1" s="109"/>
-      <c r="AJ1" s="109"/>
-      <c r="AK1" s="109"/>
-      <c r="AL1" s="109"/>
-      <c r="AM1" s="109"/>
-      <c r="AN1" s="109"/>
-      <c r="AO1" s="109"/>
-      <c r="AP1" s="109"/>
-      <c r="AQ1" s="109"/>
-      <c r="AR1" s="109"/>
-      <c r="AS1" s="109"/>
-      <c r="AT1" s="109"/>
-      <c r="AU1" s="109"/>
-      <c r="AV1" s="109"/>
-      <c r="AW1" s="109"/>
-      <c r="AX1" s="109"/>
-      <c r="AY1" s="109"/>
-      <c r="AZ1" s="109"/>
-      <c r="BA1" s="109"/>
-      <c r="BB1" s="109"/>
-      <c r="BC1" s="109"/>
-      <c r="BD1" s="109"/>
-      <c r="BE1" s="110"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="105"/>
+      <c r="H1" s="105"/>
+      <c r="I1" s="105"/>
+      <c r="J1" s="105"/>
+      <c r="K1" s="105"/>
+      <c r="L1" s="105"/>
+      <c r="M1" s="105"/>
+      <c r="N1" s="105"/>
+      <c r="O1" s="105"/>
+      <c r="P1" s="105"/>
+      <c r="Q1" s="105"/>
+      <c r="R1" s="105"/>
+      <c r="S1" s="105"/>
+      <c r="T1" s="105"/>
+      <c r="U1" s="105"/>
+      <c r="V1" s="105"/>
+      <c r="W1" s="105"/>
+      <c r="X1" s="105"/>
+      <c r="Y1" s="105"/>
+      <c r="Z1" s="105"/>
+      <c r="AA1" s="105"/>
+      <c r="AB1" s="105"/>
+      <c r="AC1" s="105"/>
+      <c r="AD1" s="105"/>
+      <c r="AE1" s="105"/>
+      <c r="AF1" s="105"/>
+      <c r="AG1" s="105"/>
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="106"/>
     </row>
     <row r="2" spans="1:57" ht="12" customHeight="1" thickBot="1">
       <c r="A2" s="14"/>
@@ -64953,145 +64963,145 @@
       <c r="AP2" s="14"/>
     </row>
     <row r="3" spans="1:57" ht="15" customHeight="1" thickBot="1">
-      <c r="A3" s="121" t="s">
+      <c r="A3" s="87" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="112"/>
-      <c r="C3" s="112"/>
-      <c r="D3" s="112"/>
-      <c r="E3" s="112"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="113"/>
-      <c r="H3" s="111" t="s">
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="107" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="112"/>
-      <c r="J3" s="112"/>
-      <c r="K3" s="112"/>
-      <c r="L3" s="112"/>
-      <c r="M3" s="112"/>
-      <c r="N3" s="113"/>
-      <c r="O3" s="111" t="s">
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
+      <c r="K3" s="88"/>
+      <c r="L3" s="88"/>
+      <c r="M3" s="88"/>
+      <c r="N3" s="89"/>
+      <c r="O3" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="P3" s="114"/>
-      <c r="Q3" s="114"/>
-      <c r="R3" s="114"/>
-      <c r="S3" s="114"/>
-      <c r="T3" s="114"/>
-      <c r="U3" s="114"/>
-      <c r="V3" s="114"/>
-      <c r="W3" s="114"/>
-      <c r="X3" s="114"/>
-      <c r="Y3" s="114"/>
-      <c r="Z3" s="114"/>
-      <c r="AA3" s="114"/>
-      <c r="AB3" s="114"/>
-      <c r="AC3" s="114"/>
-      <c r="AD3" s="114"/>
-      <c r="AE3" s="114"/>
-      <c r="AF3" s="114"/>
-      <c r="AG3" s="114"/>
-      <c r="AH3" s="114"/>
-      <c r="AI3" s="114"/>
-      <c r="AJ3" s="114"/>
-      <c r="AK3" s="114"/>
-      <c r="AL3" s="114"/>
-      <c r="AM3" s="114"/>
-      <c r="AN3" s="114"/>
-      <c r="AO3" s="114"/>
-      <c r="AP3" s="115"/>
-      <c r="AQ3" s="111" t="s">
+      <c r="P3" s="108"/>
+      <c r="Q3" s="108"/>
+      <c r="R3" s="108"/>
+      <c r="S3" s="108"/>
+      <c r="T3" s="108"/>
+      <c r="U3" s="108"/>
+      <c r="V3" s="108"/>
+      <c r="W3" s="108"/>
+      <c r="X3" s="108"/>
+      <c r="Y3" s="108"/>
+      <c r="Z3" s="108"/>
+      <c r="AA3" s="108"/>
+      <c r="AB3" s="108"/>
+      <c r="AC3" s="108"/>
+      <c r="AD3" s="108"/>
+      <c r="AE3" s="108"/>
+      <c r="AF3" s="108"/>
+      <c r="AG3" s="108"/>
+      <c r="AH3" s="108"/>
+      <c r="AI3" s="108"/>
+      <c r="AJ3" s="108"/>
+      <c r="AK3" s="108"/>
+      <c r="AL3" s="108"/>
+      <c r="AM3" s="108"/>
+      <c r="AN3" s="108"/>
+      <c r="AO3" s="108"/>
+      <c r="AP3" s="109"/>
+      <c r="AQ3" s="107" t="s">
         <v>10</v>
       </c>
-      <c r="AR3" s="116"/>
-      <c r="AS3" s="116"/>
-      <c r="AT3" s="116"/>
-      <c r="AU3" s="116"/>
-      <c r="AV3" s="116"/>
-      <c r="AW3" s="116"/>
-      <c r="AX3" s="116"/>
-      <c r="AY3" s="116"/>
-      <c r="AZ3" s="116"/>
-      <c r="BA3" s="116"/>
-      <c r="BB3" s="116"/>
-      <c r="BC3" s="116"/>
-      <c r="BD3" s="116"/>
-      <c r="BE3" s="117"/>
+      <c r="AR3" s="110"/>
+      <c r="AS3" s="110"/>
+      <c r="AT3" s="110"/>
+      <c r="AU3" s="110"/>
+      <c r="AV3" s="110"/>
+      <c r="AW3" s="110"/>
+      <c r="AX3" s="110"/>
+      <c r="AY3" s="110"/>
+      <c r="AZ3" s="110"/>
+      <c r="BA3" s="110"/>
+      <c r="BB3" s="110"/>
+      <c r="BC3" s="110"/>
+      <c r="BD3" s="110"/>
+      <c r="BE3" s="111"/>
     </row>
     <row r="4" spans="1:57" ht="15" customHeight="1">
-      <c r="A4" s="118">
+      <c r="A4" s="112">
         <v>1</v>
       </c>
-      <c r="B4" s="119"/>
-      <c r="C4" s="119"/>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="101"/>
-      <c r="I4" s="102"/>
-      <c r="J4" s="102"/>
-      <c r="K4" s="102"/>
-      <c r="L4" s="102"/>
-      <c r="M4" s="102"/>
-      <c r="N4" s="103"/>
-      <c r="O4" s="101" t="s">
+      <c r="B4" s="113"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="116"/>
+      <c r="L4" s="116"/>
+      <c r="M4" s="116"/>
+      <c r="N4" s="117"/>
+      <c r="O4" s="115" t="s">
         <v>11</v>
       </c>
-      <c r="P4" s="104"/>
-      <c r="Q4" s="104"/>
-      <c r="R4" s="104"/>
-      <c r="S4" s="104"/>
-      <c r="T4" s="104"/>
-      <c r="U4" s="104"/>
-      <c r="V4" s="104"/>
-      <c r="W4" s="104"/>
-      <c r="X4" s="104"/>
-      <c r="Y4" s="104"/>
-      <c r="Z4" s="104"/>
-      <c r="AA4" s="104"/>
-      <c r="AB4" s="104"/>
-      <c r="AC4" s="104"/>
-      <c r="AD4" s="104"/>
-      <c r="AE4" s="104"/>
-      <c r="AF4" s="104"/>
-      <c r="AG4" s="104"/>
-      <c r="AH4" s="104"/>
-      <c r="AI4" s="104"/>
-      <c r="AJ4" s="104"/>
-      <c r="AK4" s="104"/>
-      <c r="AL4" s="104"/>
-      <c r="AM4" s="104"/>
-      <c r="AN4" s="104"/>
-      <c r="AO4" s="104"/>
-      <c r="AP4" s="105"/>
-      <c r="AQ4" s="106"/>
-      <c r="AR4" s="104"/>
-      <c r="AS4" s="104"/>
-      <c r="AT4" s="104"/>
-      <c r="AU4" s="104"/>
-      <c r="AV4" s="104"/>
-      <c r="AW4" s="104"/>
-      <c r="AX4" s="104"/>
-      <c r="AY4" s="104"/>
-      <c r="AZ4" s="104"/>
-      <c r="BA4" s="104"/>
-      <c r="BB4" s="104"/>
-      <c r="BC4" s="104"/>
-      <c r="BD4" s="104"/>
-      <c r="BE4" s="107"/>
+      <c r="P4" s="118"/>
+      <c r="Q4" s="118"/>
+      <c r="R4" s="118"/>
+      <c r="S4" s="118"/>
+      <c r="T4" s="118"/>
+      <c r="U4" s="118"/>
+      <c r="V4" s="118"/>
+      <c r="W4" s="118"/>
+      <c r="X4" s="118"/>
+      <c r="Y4" s="118"/>
+      <c r="Z4" s="118"/>
+      <c r="AA4" s="118"/>
+      <c r="AB4" s="118"/>
+      <c r="AC4" s="118"/>
+      <c r="AD4" s="118"/>
+      <c r="AE4" s="118"/>
+      <c r="AF4" s="118"/>
+      <c r="AG4" s="118"/>
+      <c r="AH4" s="118"/>
+      <c r="AI4" s="118"/>
+      <c r="AJ4" s="118"/>
+      <c r="AK4" s="118"/>
+      <c r="AL4" s="118"/>
+      <c r="AM4" s="118"/>
+      <c r="AN4" s="118"/>
+      <c r="AO4" s="118"/>
+      <c r="AP4" s="119"/>
+      <c r="AQ4" s="120"/>
+      <c r="AR4" s="118"/>
+      <c r="AS4" s="118"/>
+      <c r="AT4" s="118"/>
+      <c r="AU4" s="118"/>
+      <c r="AV4" s="118"/>
+      <c r="AW4" s="118"/>
+      <c r="AX4" s="118"/>
+      <c r="AY4" s="118"/>
+      <c r="AZ4" s="118"/>
+      <c r="BA4" s="118"/>
+      <c r="BB4" s="118"/>
+      <c r="BC4" s="118"/>
+      <c r="BD4" s="118"/>
+      <c r="BE4" s="121"/>
     </row>
     <row r="5" spans="1:57" ht="105.75" customHeight="1">
-      <c r="A5" s="81">
+      <c r="A5" s="101">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B5" s="82"/>
-      <c r="C5" s="82"/>
-      <c r="D5" s="82"/>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
-      <c r="G5" s="83"/>
+      <c r="B5" s="102"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="102"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="102"/>
+      <c r="G5" s="103"/>
       <c r="H5" s="84" t="s">
         <v>1796</v>
       </c>
@@ -65104,61 +65114,61 @@
       <c r="O5" s="84" t="s">
         <v>1798</v>
       </c>
-      <c r="P5" s="87"/>
-      <c r="Q5" s="87"/>
-      <c r="R5" s="87"/>
-      <c r="S5" s="87"/>
-      <c r="T5" s="87"/>
-      <c r="U5" s="87"/>
-      <c r="V5" s="87"/>
-      <c r="W5" s="87"/>
-      <c r="X5" s="87"/>
-      <c r="Y5" s="87"/>
-      <c r="Z5" s="87"/>
-      <c r="AA5" s="87"/>
-      <c r="AB5" s="87"/>
-      <c r="AC5" s="87"/>
-      <c r="AD5" s="87"/>
-      <c r="AE5" s="87"/>
-      <c r="AF5" s="87"/>
-      <c r="AG5" s="87"/>
-      <c r="AH5" s="87"/>
-      <c r="AI5" s="87"/>
-      <c r="AJ5" s="87"/>
-      <c r="AK5" s="87"/>
-      <c r="AL5" s="87"/>
-      <c r="AM5" s="87"/>
-      <c r="AN5" s="87"/>
-      <c r="AO5" s="87"/>
-      <c r="AP5" s="88"/>
-      <c r="AQ5" s="92" t="s">
+      <c r="P5" s="82"/>
+      <c r="Q5" s="82"/>
+      <c r="R5" s="82"/>
+      <c r="S5" s="82"/>
+      <c r="T5" s="82"/>
+      <c r="U5" s="82"/>
+      <c r="V5" s="82"/>
+      <c r="W5" s="82"/>
+      <c r="X5" s="82"/>
+      <c r="Y5" s="82"/>
+      <c r="Z5" s="82"/>
+      <c r="AA5" s="82"/>
+      <c r="AB5" s="82"/>
+      <c r="AC5" s="82"/>
+      <c r="AD5" s="82"/>
+      <c r="AE5" s="82"/>
+      <c r="AF5" s="82"/>
+      <c r="AG5" s="82"/>
+      <c r="AH5" s="82"/>
+      <c r="AI5" s="82"/>
+      <c r="AJ5" s="82"/>
+      <c r="AK5" s="82"/>
+      <c r="AL5" s="82"/>
+      <c r="AM5" s="82"/>
+      <c r="AN5" s="82"/>
+      <c r="AO5" s="82"/>
+      <c r="AP5" s="90"/>
+      <c r="AQ5" s="81" t="s">
         <v>1797</v>
       </c>
-      <c r="AR5" s="87"/>
-      <c r="AS5" s="87"/>
-      <c r="AT5" s="87"/>
-      <c r="AU5" s="87"/>
-      <c r="AV5" s="87"/>
-      <c r="AW5" s="87"/>
-      <c r="AX5" s="87"/>
-      <c r="AY5" s="87"/>
-      <c r="AZ5" s="87"/>
-      <c r="BA5" s="87"/>
-      <c r="BB5" s="87"/>
-      <c r="BC5" s="87"/>
-      <c r="BD5" s="87"/>
-      <c r="BE5" s="93"/>
+      <c r="AR5" s="82"/>
+      <c r="AS5" s="82"/>
+      <c r="AT5" s="82"/>
+      <c r="AU5" s="82"/>
+      <c r="AV5" s="82"/>
+      <c r="AW5" s="82"/>
+      <c r="AX5" s="82"/>
+      <c r="AY5" s="82"/>
+      <c r="AZ5" s="82"/>
+      <c r="BA5" s="82"/>
+      <c r="BB5" s="82"/>
+      <c r="BC5" s="82"/>
+      <c r="BD5" s="82"/>
+      <c r="BE5" s="83"/>
     </row>
     <row r="6" spans="1:57" ht="36.6" customHeight="1">
-      <c r="A6" s="81">
+      <c r="A6" s="101">
         <v>1.2</v>
       </c>
-      <c r="B6" s="82"/>
-      <c r="C6" s="82"/>
-      <c r="D6" s="82"/>
-      <c r="E6" s="82"/>
-      <c r="F6" s="82"/>
-      <c r="G6" s="83"/>
+      <c r="B6" s="102"/>
+      <c r="C6" s="102"/>
+      <c r="D6" s="102"/>
+      <c r="E6" s="102"/>
+      <c r="F6" s="102"/>
+      <c r="G6" s="103"/>
       <c r="H6" s="84" t="s">
         <v>1824</v>
       </c>
@@ -65171,124 +65181,124 @@
       <c r="O6" s="84" t="s">
         <v>1823</v>
       </c>
-      <c r="P6" s="122"/>
-      <c r="Q6" s="122"/>
-      <c r="R6" s="122"/>
-      <c r="S6" s="122"/>
-      <c r="T6" s="122"/>
-      <c r="U6" s="122"/>
-      <c r="V6" s="122"/>
-      <c r="W6" s="122"/>
-      <c r="X6" s="122"/>
-      <c r="Y6" s="122"/>
-      <c r="Z6" s="122"/>
-      <c r="AA6" s="122"/>
-      <c r="AB6" s="122"/>
-      <c r="AC6" s="122"/>
-      <c r="AD6" s="122"/>
-      <c r="AE6" s="122"/>
-      <c r="AF6" s="122"/>
-      <c r="AG6" s="122"/>
-      <c r="AH6" s="122"/>
-      <c r="AI6" s="122"/>
-      <c r="AJ6" s="122"/>
-      <c r="AK6" s="122"/>
-      <c r="AL6" s="122"/>
-      <c r="AM6" s="122"/>
-      <c r="AN6" s="122"/>
-      <c r="AO6" s="122"/>
-      <c r="AP6" s="123"/>
-      <c r="AQ6" s="92" t="s">
+      <c r="P6" s="91"/>
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
+      <c r="V6" s="91"/>
+      <c r="W6" s="91"/>
+      <c r="X6" s="91"/>
+      <c r="Y6" s="91"/>
+      <c r="Z6" s="91"/>
+      <c r="AA6" s="91"/>
+      <c r="AB6" s="91"/>
+      <c r="AC6" s="91"/>
+      <c r="AD6" s="91"/>
+      <c r="AE6" s="91"/>
+      <c r="AF6" s="91"/>
+      <c r="AG6" s="91"/>
+      <c r="AH6" s="91"/>
+      <c r="AI6" s="91"/>
+      <c r="AJ6" s="91"/>
+      <c r="AK6" s="91"/>
+      <c r="AL6" s="91"/>
+      <c r="AM6" s="91"/>
+      <c r="AN6" s="91"/>
+      <c r="AO6" s="91"/>
+      <c r="AP6" s="92"/>
+      <c r="AQ6" s="81" t="s">
         <v>1797</v>
       </c>
-      <c r="AR6" s="87"/>
-      <c r="AS6" s="87"/>
-      <c r="AT6" s="87"/>
-      <c r="AU6" s="87"/>
-      <c r="AV6" s="87"/>
-      <c r="AW6" s="87"/>
-      <c r="AX6" s="87"/>
-      <c r="AY6" s="87"/>
-      <c r="AZ6" s="87"/>
-      <c r="BA6" s="87"/>
-      <c r="BB6" s="87"/>
-      <c r="BC6" s="87"/>
-      <c r="BD6" s="87"/>
-      <c r="BE6" s="93"/>
+      <c r="AR6" s="82"/>
+      <c r="AS6" s="82"/>
+      <c r="AT6" s="82"/>
+      <c r="AU6" s="82"/>
+      <c r="AV6" s="82"/>
+      <c r="AW6" s="82"/>
+      <c r="AX6" s="82"/>
+      <c r="AY6" s="82"/>
+      <c r="AZ6" s="82"/>
+      <c r="BA6" s="82"/>
+      <c r="BB6" s="82"/>
+      <c r="BC6" s="82"/>
+      <c r="BD6" s="82"/>
+      <c r="BE6" s="83"/>
     </row>
     <row r="7" spans="1:57" ht="15" customHeight="1">
-      <c r="A7" s="81">
+      <c r="A7" s="101">
         <v>1.3</v>
       </c>
-      <c r="B7" s="82"/>
-      <c r="C7" s="82"/>
-      <c r="D7" s="82"/>
-      <c r="E7" s="82"/>
-      <c r="F7" s="82"/>
-      <c r="G7" s="83"/>
+      <c r="B7" s="102"/>
+      <c r="C7" s="102"/>
+      <c r="D7" s="102"/>
+      <c r="E7" s="102"/>
+      <c r="F7" s="102"/>
+      <c r="G7" s="103"/>
       <c r="H7" s="84"/>
-      <c r="I7" s="124"/>
-      <c r="J7" s="124"/>
-      <c r="K7" s="124"/>
-      <c r="L7" s="124"/>
-      <c r="M7" s="124"/>
-      <c r="N7" s="125"/>
-      <c r="O7" s="126" t="s">
+      <c r="I7" s="93"/>
+      <c r="J7" s="93"/>
+      <c r="K7" s="93"/>
+      <c r="L7" s="93"/>
+      <c r="M7" s="93"/>
+      <c r="N7" s="94"/>
+      <c r="O7" s="95" t="s">
         <v>2237</v>
       </c>
-      <c r="P7" s="127"/>
-      <c r="Q7" s="127"/>
-      <c r="R7" s="127"/>
-      <c r="S7" s="127"/>
-      <c r="T7" s="127"/>
-      <c r="U7" s="127"/>
-      <c r="V7" s="127"/>
-      <c r="W7" s="127"/>
-      <c r="X7" s="127"/>
-      <c r="Y7" s="127"/>
-      <c r="Z7" s="127"/>
-      <c r="AA7" s="127"/>
-      <c r="AB7" s="127"/>
-      <c r="AC7" s="127"/>
-      <c r="AD7" s="127"/>
-      <c r="AE7" s="127"/>
-      <c r="AF7" s="127"/>
-      <c r="AG7" s="127"/>
-      <c r="AH7" s="127"/>
-      <c r="AI7" s="127"/>
-      <c r="AJ7" s="127"/>
-      <c r="AK7" s="127"/>
-      <c r="AL7" s="127"/>
-      <c r="AM7" s="127"/>
-      <c r="AN7" s="127"/>
-      <c r="AO7" s="127"/>
-      <c r="AP7" s="128"/>
-      <c r="AQ7" s="129" t="s">
+      <c r="P7" s="96"/>
+      <c r="Q7" s="96"/>
+      <c r="R7" s="96"/>
+      <c r="S7" s="96"/>
+      <c r="T7" s="96"/>
+      <c r="U7" s="96"/>
+      <c r="V7" s="96"/>
+      <c r="W7" s="96"/>
+      <c r="X7" s="96"/>
+      <c r="Y7" s="96"/>
+      <c r="Z7" s="96"/>
+      <c r="AA7" s="96"/>
+      <c r="AB7" s="96"/>
+      <c r="AC7" s="96"/>
+      <c r="AD7" s="96"/>
+      <c r="AE7" s="96"/>
+      <c r="AF7" s="96"/>
+      <c r="AG7" s="96"/>
+      <c r="AH7" s="96"/>
+      <c r="AI7" s="96"/>
+      <c r="AJ7" s="96"/>
+      <c r="AK7" s="96"/>
+      <c r="AL7" s="96"/>
+      <c r="AM7" s="96"/>
+      <c r="AN7" s="96"/>
+      <c r="AO7" s="96"/>
+      <c r="AP7" s="97"/>
+      <c r="AQ7" s="98" t="s">
         <v>2238</v>
       </c>
-      <c r="AR7" s="130"/>
-      <c r="AS7" s="130"/>
-      <c r="AT7" s="130"/>
-      <c r="AU7" s="130"/>
-      <c r="AV7" s="130"/>
-      <c r="AW7" s="130"/>
-      <c r="AX7" s="130"/>
-      <c r="AY7" s="130"/>
-      <c r="AZ7" s="130"/>
-      <c r="BA7" s="130"/>
-      <c r="BB7" s="130"/>
-      <c r="BC7" s="130"/>
-      <c r="BD7" s="130"/>
-      <c r="BE7" s="131"/>
+      <c r="AR7" s="99"/>
+      <c r="AS7" s="99"/>
+      <c r="AT7" s="99"/>
+      <c r="AU7" s="99"/>
+      <c r="AV7" s="99"/>
+      <c r="AW7" s="99"/>
+      <c r="AX7" s="99"/>
+      <c r="AY7" s="99"/>
+      <c r="AZ7" s="99"/>
+      <c r="BA7" s="99"/>
+      <c r="BB7" s="99"/>
+      <c r="BC7" s="99"/>
+      <c r="BD7" s="99"/>
+      <c r="BE7" s="100"/>
     </row>
     <row r="8" spans="1:57" ht="15" customHeight="1">
-      <c r="A8" s="81"/>
-      <c r="B8" s="82"/>
-      <c r="C8" s="82"/>
-      <c r="D8" s="82"/>
-      <c r="E8" s="82"/>
-      <c r="F8" s="82"/>
-      <c r="G8" s="83"/>
+      <c r="A8" s="101"/>
+      <c r="B8" s="102"/>
+      <c r="C8" s="102"/>
+      <c r="D8" s="102"/>
+      <c r="E8" s="102"/>
+      <c r="F8" s="102"/>
+      <c r="G8" s="103"/>
       <c r="H8" s="84"/>
       <c r="I8" s="85"/>
       <c r="J8" s="85"/>
@@ -65297,57 +65307,57 @@
       <c r="M8" s="85"/>
       <c r="N8" s="86"/>
       <c r="O8" s="84"/>
-      <c r="P8" s="87"/>
-      <c r="Q8" s="87"/>
-      <c r="R8" s="87"/>
-      <c r="S8" s="87"/>
-      <c r="T8" s="87"/>
-      <c r="U8" s="87"/>
-      <c r="V8" s="87"/>
-      <c r="W8" s="87"/>
-      <c r="X8" s="87"/>
-      <c r="Y8" s="87"/>
-      <c r="Z8" s="87"/>
-      <c r="AA8" s="87"/>
-      <c r="AB8" s="87"/>
-      <c r="AC8" s="87"/>
-      <c r="AD8" s="87"/>
-      <c r="AE8" s="87"/>
-      <c r="AF8" s="87"/>
-      <c r="AG8" s="87"/>
-      <c r="AH8" s="87"/>
-      <c r="AI8" s="87"/>
-      <c r="AJ8" s="87"/>
-      <c r="AK8" s="87"/>
-      <c r="AL8" s="87"/>
-      <c r="AM8" s="87"/>
-      <c r="AN8" s="87"/>
-      <c r="AO8" s="87"/>
-      <c r="AP8" s="88"/>
-      <c r="AQ8" s="92"/>
-      <c r="AR8" s="87"/>
-      <c r="AS8" s="87"/>
-      <c r="AT8" s="87"/>
-      <c r="AU8" s="87"/>
-      <c r="AV8" s="87"/>
-      <c r="AW8" s="87"/>
-      <c r="AX8" s="87"/>
-      <c r="AY8" s="87"/>
-      <c r="AZ8" s="87"/>
-      <c r="BA8" s="87"/>
-      <c r="BB8" s="87"/>
-      <c r="BC8" s="87"/>
-      <c r="BD8" s="87"/>
-      <c r="BE8" s="93"/>
+      <c r="P8" s="82"/>
+      <c r="Q8" s="82"/>
+      <c r="R8" s="82"/>
+      <c r="S8" s="82"/>
+      <c r="T8" s="82"/>
+      <c r="U8" s="82"/>
+      <c r="V8" s="82"/>
+      <c r="W8" s="82"/>
+      <c r="X8" s="82"/>
+      <c r="Y8" s="82"/>
+      <c r="Z8" s="82"/>
+      <c r="AA8" s="82"/>
+      <c r="AB8" s="82"/>
+      <c r="AC8" s="82"/>
+      <c r="AD8" s="82"/>
+      <c r="AE8" s="82"/>
+      <c r="AF8" s="82"/>
+      <c r="AG8" s="82"/>
+      <c r="AH8" s="82"/>
+      <c r="AI8" s="82"/>
+      <c r="AJ8" s="82"/>
+      <c r="AK8" s="82"/>
+      <c r="AL8" s="82"/>
+      <c r="AM8" s="82"/>
+      <c r="AN8" s="82"/>
+      <c r="AO8" s="82"/>
+      <c r="AP8" s="90"/>
+      <c r="AQ8" s="81"/>
+      <c r="AR8" s="82"/>
+      <c r="AS8" s="82"/>
+      <c r="AT8" s="82"/>
+      <c r="AU8" s="82"/>
+      <c r="AV8" s="82"/>
+      <c r="AW8" s="82"/>
+      <c r="AX8" s="82"/>
+      <c r="AY8" s="82"/>
+      <c r="AZ8" s="82"/>
+      <c r="BA8" s="82"/>
+      <c r="BB8" s="82"/>
+      <c r="BC8" s="82"/>
+      <c r="BD8" s="82"/>
+      <c r="BE8" s="83"/>
     </row>
     <row r="9" spans="1:57" ht="15" customHeight="1">
-      <c r="A9" s="81"/>
-      <c r="B9" s="82"/>
-      <c r="C9" s="82"/>
-      <c r="D9" s="82"/>
-      <c r="E9" s="82"/>
-      <c r="F9" s="82"/>
-      <c r="G9" s="83"/>
+      <c r="A9" s="101"/>
+      <c r="B9" s="102"/>
+      <c r="C9" s="102"/>
+      <c r="D9" s="102"/>
+      <c r="E9" s="102"/>
+      <c r="F9" s="102"/>
+      <c r="G9" s="103"/>
       <c r="H9" s="84"/>
       <c r="I9" s="85"/>
       <c r="J9" s="85"/>
@@ -65356,57 +65366,57 @@
       <c r="M9" s="85"/>
       <c r="N9" s="86"/>
       <c r="O9" s="84"/>
-      <c r="P9" s="87"/>
-      <c r="Q9" s="87"/>
-      <c r="R9" s="87"/>
-      <c r="S9" s="87"/>
-      <c r="T9" s="87"/>
-      <c r="U9" s="87"/>
-      <c r="V9" s="87"/>
-      <c r="W9" s="87"/>
-      <c r="X9" s="87"/>
-      <c r="Y9" s="87"/>
-      <c r="Z9" s="87"/>
-      <c r="AA9" s="87"/>
-      <c r="AB9" s="87"/>
-      <c r="AC9" s="87"/>
-      <c r="AD9" s="87"/>
-      <c r="AE9" s="87"/>
-      <c r="AF9" s="87"/>
-      <c r="AG9" s="87"/>
-      <c r="AH9" s="87"/>
-      <c r="AI9" s="87"/>
-      <c r="AJ9" s="87"/>
-      <c r="AK9" s="87"/>
-      <c r="AL9" s="87"/>
-      <c r="AM9" s="87"/>
-      <c r="AN9" s="87"/>
-      <c r="AO9" s="87"/>
-      <c r="AP9" s="88"/>
-      <c r="AQ9" s="92"/>
-      <c r="AR9" s="87"/>
-      <c r="AS9" s="87"/>
-      <c r="AT9" s="87"/>
-      <c r="AU9" s="87"/>
-      <c r="AV9" s="87"/>
-      <c r="AW9" s="87"/>
-      <c r="AX9" s="87"/>
-      <c r="AY9" s="87"/>
-      <c r="AZ9" s="87"/>
-      <c r="BA9" s="87"/>
-      <c r="BB9" s="87"/>
-      <c r="BC9" s="87"/>
-      <c r="BD9" s="87"/>
-      <c r="BE9" s="93"/>
+      <c r="P9" s="82"/>
+      <c r="Q9" s="82"/>
+      <c r="R9" s="82"/>
+      <c r="S9" s="82"/>
+      <c r="T9" s="82"/>
+      <c r="U9" s="82"/>
+      <c r="V9" s="82"/>
+      <c r="W9" s="82"/>
+      <c r="X9" s="82"/>
+      <c r="Y9" s="82"/>
+      <c r="Z9" s="82"/>
+      <c r="AA9" s="82"/>
+      <c r="AB9" s="82"/>
+      <c r="AC9" s="82"/>
+      <c r="AD9" s="82"/>
+      <c r="AE9" s="82"/>
+      <c r="AF9" s="82"/>
+      <c r="AG9" s="82"/>
+      <c r="AH9" s="82"/>
+      <c r="AI9" s="82"/>
+      <c r="AJ9" s="82"/>
+      <c r="AK9" s="82"/>
+      <c r="AL9" s="82"/>
+      <c r="AM9" s="82"/>
+      <c r="AN9" s="82"/>
+      <c r="AO9" s="82"/>
+      <c r="AP9" s="90"/>
+      <c r="AQ9" s="81"/>
+      <c r="AR9" s="82"/>
+      <c r="AS9" s="82"/>
+      <c r="AT9" s="82"/>
+      <c r="AU9" s="82"/>
+      <c r="AV9" s="82"/>
+      <c r="AW9" s="82"/>
+      <c r="AX9" s="82"/>
+      <c r="AY9" s="82"/>
+      <c r="AZ9" s="82"/>
+      <c r="BA9" s="82"/>
+      <c r="BB9" s="82"/>
+      <c r="BC9" s="82"/>
+      <c r="BD9" s="82"/>
+      <c r="BE9" s="83"/>
     </row>
     <row r="10" spans="1:57" ht="15" customHeight="1">
-      <c r="A10" s="81"/>
-      <c r="B10" s="82"/>
-      <c r="C10" s="82"/>
-      <c r="D10" s="82"/>
-      <c r="E10" s="82"/>
-      <c r="F10" s="82"/>
-      <c r="G10" s="83"/>
+      <c r="A10" s="101"/>
+      <c r="B10" s="102"/>
+      <c r="C10" s="102"/>
+      <c r="D10" s="102"/>
+      <c r="E10" s="102"/>
+      <c r="F10" s="102"/>
+      <c r="G10" s="103"/>
       <c r="H10" s="84"/>
       <c r="I10" s="85"/>
       <c r="J10" s="85"/>
@@ -65415,57 +65425,57 @@
       <c r="M10" s="85"/>
       <c r="N10" s="86"/>
       <c r="O10" s="84"/>
-      <c r="P10" s="87"/>
-      <c r="Q10" s="87"/>
-      <c r="R10" s="87"/>
-      <c r="S10" s="87"/>
-      <c r="T10" s="87"/>
-      <c r="U10" s="87"/>
-      <c r="V10" s="87"/>
-      <c r="W10" s="87"/>
-      <c r="X10" s="87"/>
-      <c r="Y10" s="87"/>
-      <c r="Z10" s="87"/>
-      <c r="AA10" s="87"/>
-      <c r="AB10" s="87"/>
-      <c r="AC10" s="87"/>
-      <c r="AD10" s="87"/>
-      <c r="AE10" s="87"/>
-      <c r="AF10" s="87"/>
-      <c r="AG10" s="87"/>
-      <c r="AH10" s="87"/>
-      <c r="AI10" s="87"/>
-      <c r="AJ10" s="87"/>
-      <c r="AK10" s="87"/>
-      <c r="AL10" s="87"/>
-      <c r="AM10" s="87"/>
-      <c r="AN10" s="87"/>
-      <c r="AO10" s="87"/>
-      <c r="AP10" s="88"/>
-      <c r="AQ10" s="92"/>
-      <c r="AR10" s="87"/>
-      <c r="AS10" s="87"/>
-      <c r="AT10" s="87"/>
-      <c r="AU10" s="87"/>
-      <c r="AV10" s="87"/>
-      <c r="AW10" s="87"/>
-      <c r="AX10" s="87"/>
-      <c r="AY10" s="87"/>
-      <c r="AZ10" s="87"/>
-      <c r="BA10" s="87"/>
-      <c r="BB10" s="87"/>
-      <c r="BC10" s="87"/>
-      <c r="BD10" s="87"/>
-      <c r="BE10" s="93"/>
+      <c r="P10" s="82"/>
+      <c r="Q10" s="82"/>
+      <c r="R10" s="82"/>
+      <c r="S10" s="82"/>
+      <c r="T10" s="82"/>
+      <c r="U10" s="82"/>
+      <c r="V10" s="82"/>
+      <c r="W10" s="82"/>
+      <c r="X10" s="82"/>
+      <c r="Y10" s="82"/>
+      <c r="Z10" s="82"/>
+      <c r="AA10" s="82"/>
+      <c r="AB10" s="82"/>
+      <c r="AC10" s="82"/>
+      <c r="AD10" s="82"/>
+      <c r="AE10" s="82"/>
+      <c r="AF10" s="82"/>
+      <c r="AG10" s="82"/>
+      <c r="AH10" s="82"/>
+      <c r="AI10" s="82"/>
+      <c r="AJ10" s="82"/>
+      <c r="AK10" s="82"/>
+      <c r="AL10" s="82"/>
+      <c r="AM10" s="82"/>
+      <c r="AN10" s="82"/>
+      <c r="AO10" s="82"/>
+      <c r="AP10" s="90"/>
+      <c r="AQ10" s="81"/>
+      <c r="AR10" s="82"/>
+      <c r="AS10" s="82"/>
+      <c r="AT10" s="82"/>
+      <c r="AU10" s="82"/>
+      <c r="AV10" s="82"/>
+      <c r="AW10" s="82"/>
+      <c r="AX10" s="82"/>
+      <c r="AY10" s="82"/>
+      <c r="AZ10" s="82"/>
+      <c r="BA10" s="82"/>
+      <c r="BB10" s="82"/>
+      <c r="BC10" s="82"/>
+      <c r="BD10" s="82"/>
+      <c r="BE10" s="83"/>
     </row>
     <row r="11" spans="1:57" ht="15" customHeight="1">
-      <c r="A11" s="81"/>
-      <c r="B11" s="82"/>
-      <c r="C11" s="82"/>
-      <c r="D11" s="82"/>
-      <c r="E11" s="82"/>
-      <c r="F11" s="82"/>
-      <c r="G11" s="83"/>
+      <c r="A11" s="101"/>
+      <c r="B11" s="102"/>
+      <c r="C11" s="102"/>
+      <c r="D11" s="102"/>
+      <c r="E11" s="102"/>
+      <c r="F11" s="102"/>
+      <c r="G11" s="103"/>
       <c r="H11" s="84"/>
       <c r="I11" s="85"/>
       <c r="J11" s="85"/>
@@ -65474,57 +65484,57 @@
       <c r="M11" s="85"/>
       <c r="N11" s="86"/>
       <c r="O11" s="84"/>
-      <c r="P11" s="87"/>
-      <c r="Q11" s="87"/>
-      <c r="R11" s="87"/>
-      <c r="S11" s="87"/>
-      <c r="T11" s="87"/>
-      <c r="U11" s="87"/>
-      <c r="V11" s="87"/>
-      <c r="W11" s="87"/>
-      <c r="X11" s="87"/>
-      <c r="Y11" s="87"/>
-      <c r="Z11" s="87"/>
-      <c r="AA11" s="87"/>
-      <c r="AB11" s="87"/>
-      <c r="AC11" s="87"/>
-      <c r="AD11" s="87"/>
-      <c r="AE11" s="87"/>
-      <c r="AF11" s="87"/>
-      <c r="AG11" s="87"/>
-      <c r="AH11" s="87"/>
-      <c r="AI11" s="87"/>
-      <c r="AJ11" s="87"/>
-      <c r="AK11" s="87"/>
-      <c r="AL11" s="87"/>
-      <c r="AM11" s="87"/>
-      <c r="AN11" s="87"/>
-      <c r="AO11" s="87"/>
-      <c r="AP11" s="88"/>
-      <c r="AQ11" s="92"/>
-      <c r="AR11" s="87"/>
-      <c r="AS11" s="87"/>
-      <c r="AT11" s="87"/>
-      <c r="AU11" s="87"/>
-      <c r="AV11" s="87"/>
-      <c r="AW11" s="87"/>
-      <c r="AX11" s="87"/>
-      <c r="AY11" s="87"/>
-      <c r="AZ11" s="87"/>
-      <c r="BA11" s="87"/>
-      <c r="BB11" s="87"/>
-      <c r="BC11" s="87"/>
-      <c r="BD11" s="87"/>
-      <c r="BE11" s="93"/>
+      <c r="P11" s="82"/>
+      <c r="Q11" s="82"/>
+      <c r="R11" s="82"/>
+      <c r="S11" s="82"/>
+      <c r="T11" s="82"/>
+      <c r="U11" s="82"/>
+      <c r="V11" s="82"/>
+      <c r="W11" s="82"/>
+      <c r="X11" s="82"/>
+      <c r="Y11" s="82"/>
+      <c r="Z11" s="82"/>
+      <c r="AA11" s="82"/>
+      <c r="AB11" s="82"/>
+      <c r="AC11" s="82"/>
+      <c r="AD11" s="82"/>
+      <c r="AE11" s="82"/>
+      <c r="AF11" s="82"/>
+      <c r="AG11" s="82"/>
+      <c r="AH11" s="82"/>
+      <c r="AI11" s="82"/>
+      <c r="AJ11" s="82"/>
+      <c r="AK11" s="82"/>
+      <c r="AL11" s="82"/>
+      <c r="AM11" s="82"/>
+      <c r="AN11" s="82"/>
+      <c r="AO11" s="82"/>
+      <c r="AP11" s="90"/>
+      <c r="AQ11" s="81"/>
+      <c r="AR11" s="82"/>
+      <c r="AS11" s="82"/>
+      <c r="AT11" s="82"/>
+      <c r="AU11" s="82"/>
+      <c r="AV11" s="82"/>
+      <c r="AW11" s="82"/>
+      <c r="AX11" s="82"/>
+      <c r="AY11" s="82"/>
+      <c r="AZ11" s="82"/>
+      <c r="BA11" s="82"/>
+      <c r="BB11" s="82"/>
+      <c r="BC11" s="82"/>
+      <c r="BD11" s="82"/>
+      <c r="BE11" s="83"/>
     </row>
     <row r="12" spans="1:57" ht="15" customHeight="1">
-      <c r="A12" s="81"/>
-      <c r="B12" s="82"/>
-      <c r="C12" s="82"/>
-      <c r="D12" s="82"/>
-      <c r="E12" s="82"/>
-      <c r="F12" s="82"/>
-      <c r="G12" s="83"/>
+      <c r="A12" s="101"/>
+      <c r="B12" s="102"/>
+      <c r="C12" s="102"/>
+      <c r="D12" s="102"/>
+      <c r="E12" s="102"/>
+      <c r="F12" s="102"/>
+      <c r="G12" s="103"/>
       <c r="H12" s="84"/>
       <c r="I12" s="85"/>
       <c r="J12" s="85"/>
@@ -65533,57 +65543,57 @@
       <c r="M12" s="85"/>
       <c r="N12" s="86"/>
       <c r="O12" s="84"/>
-      <c r="P12" s="87"/>
-      <c r="Q12" s="87"/>
-      <c r="R12" s="87"/>
-      <c r="S12" s="87"/>
-      <c r="T12" s="87"/>
-      <c r="U12" s="87"/>
-      <c r="V12" s="87"/>
-      <c r="W12" s="87"/>
-      <c r="X12" s="87"/>
-      <c r="Y12" s="87"/>
-      <c r="Z12" s="87"/>
-      <c r="AA12" s="87"/>
-      <c r="AB12" s="87"/>
-      <c r="AC12" s="87"/>
-      <c r="AD12" s="87"/>
-      <c r="AE12" s="87"/>
-      <c r="AF12" s="87"/>
-      <c r="AG12" s="87"/>
-      <c r="AH12" s="87"/>
-      <c r="AI12" s="87"/>
-      <c r="AJ12" s="87"/>
-      <c r="AK12" s="87"/>
-      <c r="AL12" s="87"/>
-      <c r="AM12" s="87"/>
-      <c r="AN12" s="87"/>
-      <c r="AO12" s="87"/>
-      <c r="AP12" s="88"/>
-      <c r="AQ12" s="92"/>
-      <c r="AR12" s="87"/>
-      <c r="AS12" s="87"/>
-      <c r="AT12" s="87"/>
-      <c r="AU12" s="87"/>
-      <c r="AV12" s="87"/>
-      <c r="AW12" s="87"/>
-      <c r="AX12" s="87"/>
-      <c r="AY12" s="87"/>
-      <c r="AZ12" s="87"/>
-      <c r="BA12" s="87"/>
-      <c r="BB12" s="87"/>
-      <c r="BC12" s="87"/>
-      <c r="BD12" s="87"/>
-      <c r="BE12" s="93"/>
+      <c r="P12" s="82"/>
+      <c r="Q12" s="82"/>
+      <c r="R12" s="82"/>
+      <c r="S12" s="82"/>
+      <c r="T12" s="82"/>
+      <c r="U12" s="82"/>
+      <c r="V12" s="82"/>
+      <c r="W12" s="82"/>
+      <c r="X12" s="82"/>
+      <c r="Y12" s="82"/>
+      <c r="Z12" s="82"/>
+      <c r="AA12" s="82"/>
+      <c r="AB12" s="82"/>
+      <c r="AC12" s="82"/>
+      <c r="AD12" s="82"/>
+      <c r="AE12" s="82"/>
+      <c r="AF12" s="82"/>
+      <c r="AG12" s="82"/>
+      <c r="AH12" s="82"/>
+      <c r="AI12" s="82"/>
+      <c r="AJ12" s="82"/>
+      <c r="AK12" s="82"/>
+      <c r="AL12" s="82"/>
+      <c r="AM12" s="82"/>
+      <c r="AN12" s="82"/>
+      <c r="AO12" s="82"/>
+      <c r="AP12" s="90"/>
+      <c r="AQ12" s="81"/>
+      <c r="AR12" s="82"/>
+      <c r="AS12" s="82"/>
+      <c r="AT12" s="82"/>
+      <c r="AU12" s="82"/>
+      <c r="AV12" s="82"/>
+      <c r="AW12" s="82"/>
+      <c r="AX12" s="82"/>
+      <c r="AY12" s="82"/>
+      <c r="AZ12" s="82"/>
+      <c r="BA12" s="82"/>
+      <c r="BB12" s="82"/>
+      <c r="BC12" s="82"/>
+      <c r="BD12" s="82"/>
+      <c r="BE12" s="83"/>
     </row>
     <row r="13" spans="1:57" ht="15" customHeight="1">
-      <c r="A13" s="81"/>
-      <c r="B13" s="82"/>
-      <c r="C13" s="82"/>
-      <c r="D13" s="82"/>
-      <c r="E13" s="82"/>
-      <c r="F13" s="82"/>
-      <c r="G13" s="83"/>
+      <c r="A13" s="101"/>
+      <c r="B13" s="102"/>
+      <c r="C13" s="102"/>
+      <c r="D13" s="102"/>
+      <c r="E13" s="102"/>
+      <c r="F13" s="102"/>
+      <c r="G13" s="103"/>
       <c r="H13" s="84"/>
       <c r="I13" s="85"/>
       <c r="J13" s="85"/>
@@ -65592,57 +65602,57 @@
       <c r="M13" s="85"/>
       <c r="N13" s="86"/>
       <c r="O13" s="84"/>
-      <c r="P13" s="87"/>
-      <c r="Q13" s="87"/>
-      <c r="R13" s="87"/>
-      <c r="S13" s="87"/>
-      <c r="T13" s="87"/>
-      <c r="U13" s="87"/>
-      <c r="V13" s="87"/>
-      <c r="W13" s="87"/>
-      <c r="X13" s="87"/>
-      <c r="Y13" s="87"/>
-      <c r="Z13" s="87"/>
-      <c r="AA13" s="87"/>
-      <c r="AB13" s="87"/>
-      <c r="AC13" s="87"/>
-      <c r="AD13" s="87"/>
-      <c r="AE13" s="87"/>
-      <c r="AF13" s="87"/>
-      <c r="AG13" s="87"/>
-      <c r="AH13" s="87"/>
-      <c r="AI13" s="87"/>
-      <c r="AJ13" s="87"/>
-      <c r="AK13" s="87"/>
-      <c r="AL13" s="87"/>
-      <c r="AM13" s="87"/>
-      <c r="AN13" s="87"/>
-      <c r="AO13" s="87"/>
-      <c r="AP13" s="88"/>
-      <c r="AQ13" s="92"/>
-      <c r="AR13" s="87"/>
-      <c r="AS13" s="87"/>
-      <c r="AT13" s="87"/>
-      <c r="AU13" s="87"/>
-      <c r="AV13" s="87"/>
-      <c r="AW13" s="87"/>
-      <c r="AX13" s="87"/>
-      <c r="AY13" s="87"/>
-      <c r="AZ13" s="87"/>
-      <c r="BA13" s="87"/>
-      <c r="BB13" s="87"/>
-      <c r="BC13" s="87"/>
-      <c r="BD13" s="87"/>
-      <c r="BE13" s="93"/>
+      <c r="P13" s="82"/>
+      <c r="Q13" s="82"/>
+      <c r="R13" s="82"/>
+      <c r="S13" s="82"/>
+      <c r="T13" s="82"/>
+      <c r="U13" s="82"/>
+      <c r="V13" s="82"/>
+      <c r="W13" s="82"/>
+      <c r="X13" s="82"/>
+      <c r="Y13" s="82"/>
+      <c r="Z13" s="82"/>
+      <c r="AA13" s="82"/>
+      <c r="AB13" s="82"/>
+      <c r="AC13" s="82"/>
+      <c r="AD13" s="82"/>
+      <c r="AE13" s="82"/>
+      <c r="AF13" s="82"/>
+      <c r="AG13" s="82"/>
+      <c r="AH13" s="82"/>
+      <c r="AI13" s="82"/>
+      <c r="AJ13" s="82"/>
+      <c r="AK13" s="82"/>
+      <c r="AL13" s="82"/>
+      <c r="AM13" s="82"/>
+      <c r="AN13" s="82"/>
+      <c r="AO13" s="82"/>
+      <c r="AP13" s="90"/>
+      <c r="AQ13" s="81"/>
+      <c r="AR13" s="82"/>
+      <c r="AS13" s="82"/>
+      <c r="AT13" s="82"/>
+      <c r="AU13" s="82"/>
+      <c r="AV13" s="82"/>
+      <c r="AW13" s="82"/>
+      <c r="AX13" s="82"/>
+      <c r="AY13" s="82"/>
+      <c r="AZ13" s="82"/>
+      <c r="BA13" s="82"/>
+      <c r="BB13" s="82"/>
+      <c r="BC13" s="82"/>
+      <c r="BD13" s="82"/>
+      <c r="BE13" s="83"/>
     </row>
     <row r="14" spans="1:57" ht="15" customHeight="1">
-      <c r="A14" s="81"/>
-      <c r="B14" s="82"/>
-      <c r="C14" s="82"/>
-      <c r="D14" s="82"/>
-      <c r="E14" s="82"/>
-      <c r="F14" s="82"/>
-      <c r="G14" s="83"/>
+      <c r="A14" s="101"/>
+      <c r="B14" s="102"/>
+      <c r="C14" s="102"/>
+      <c r="D14" s="102"/>
+      <c r="E14" s="102"/>
+      <c r="F14" s="102"/>
+      <c r="G14" s="103"/>
       <c r="H14" s="84"/>
       <c r="I14" s="85"/>
       <c r="J14" s="85"/>
@@ -65651,57 +65661,57 @@
       <c r="M14" s="85"/>
       <c r="N14" s="86"/>
       <c r="O14" s="84"/>
-      <c r="P14" s="87"/>
-      <c r="Q14" s="87"/>
-      <c r="R14" s="87"/>
-      <c r="S14" s="87"/>
-      <c r="T14" s="87"/>
-      <c r="U14" s="87"/>
-      <c r="V14" s="87"/>
-      <c r="W14" s="87"/>
-      <c r="X14" s="87"/>
-      <c r="Y14" s="87"/>
-      <c r="Z14" s="87"/>
-      <c r="AA14" s="87"/>
-      <c r="AB14" s="87"/>
-      <c r="AC14" s="87"/>
-      <c r="AD14" s="87"/>
-      <c r="AE14" s="87"/>
-      <c r="AF14" s="87"/>
-      <c r="AG14" s="87"/>
-      <c r="AH14" s="87"/>
-      <c r="AI14" s="87"/>
-      <c r="AJ14" s="87"/>
-      <c r="AK14" s="87"/>
-      <c r="AL14" s="87"/>
-      <c r="AM14" s="87"/>
-      <c r="AN14" s="87"/>
-      <c r="AO14" s="87"/>
-      <c r="AP14" s="88"/>
-      <c r="AQ14" s="92"/>
-      <c r="AR14" s="87"/>
-      <c r="AS14" s="87"/>
-      <c r="AT14" s="87"/>
-      <c r="AU14" s="87"/>
-      <c r="AV14" s="87"/>
-      <c r="AW14" s="87"/>
-      <c r="AX14" s="87"/>
-      <c r="AY14" s="87"/>
-      <c r="AZ14" s="87"/>
-      <c r="BA14" s="87"/>
-      <c r="BB14" s="87"/>
-      <c r="BC14" s="87"/>
-      <c r="BD14" s="87"/>
-      <c r="BE14" s="93"/>
+      <c r="P14" s="82"/>
+      <c r="Q14" s="82"/>
+      <c r="R14" s="82"/>
+      <c r="S14" s="82"/>
+      <c r="T14" s="82"/>
+      <c r="U14" s="82"/>
+      <c r="V14" s="82"/>
+      <c r="W14" s="82"/>
+      <c r="X14" s="82"/>
+      <c r="Y14" s="82"/>
+      <c r="Z14" s="82"/>
+      <c r="AA14" s="82"/>
+      <c r="AB14" s="82"/>
+      <c r="AC14" s="82"/>
+      <c r="AD14" s="82"/>
+      <c r="AE14" s="82"/>
+      <c r="AF14" s="82"/>
+      <c r="AG14" s="82"/>
+      <c r="AH14" s="82"/>
+      <c r="AI14" s="82"/>
+      <c r="AJ14" s="82"/>
+      <c r="AK14" s="82"/>
+      <c r="AL14" s="82"/>
+      <c r="AM14" s="82"/>
+      <c r="AN14" s="82"/>
+      <c r="AO14" s="82"/>
+      <c r="AP14" s="90"/>
+      <c r="AQ14" s="81"/>
+      <c r="AR14" s="82"/>
+      <c r="AS14" s="82"/>
+      <c r="AT14" s="82"/>
+      <c r="AU14" s="82"/>
+      <c r="AV14" s="82"/>
+      <c r="AW14" s="82"/>
+      <c r="AX14" s="82"/>
+      <c r="AY14" s="82"/>
+      <c r="AZ14" s="82"/>
+      <c r="BA14" s="82"/>
+      <c r="BB14" s="82"/>
+      <c r="BC14" s="82"/>
+      <c r="BD14" s="82"/>
+      <c r="BE14" s="83"/>
     </row>
     <row r="15" spans="1:57" ht="15" customHeight="1">
-      <c r="A15" s="81"/>
-      <c r="B15" s="82"/>
-      <c r="C15" s="82"/>
-      <c r="D15" s="82"/>
-      <c r="E15" s="82"/>
-      <c r="F15" s="82"/>
-      <c r="G15" s="83"/>
+      <c r="A15" s="101"/>
+      <c r="B15" s="102"/>
+      <c r="C15" s="102"/>
+      <c r="D15" s="102"/>
+      <c r="E15" s="102"/>
+      <c r="F15" s="102"/>
+      <c r="G15" s="103"/>
       <c r="H15" s="84"/>
       <c r="I15" s="85"/>
       <c r="J15" s="85"/>
@@ -65710,57 +65720,57 @@
       <c r="M15" s="85"/>
       <c r="N15" s="86"/>
       <c r="O15" s="84"/>
-      <c r="P15" s="87"/>
-      <c r="Q15" s="87"/>
-      <c r="R15" s="87"/>
-      <c r="S15" s="87"/>
-      <c r="T15" s="87"/>
-      <c r="U15" s="87"/>
-      <c r="V15" s="87"/>
-      <c r="W15" s="87"/>
-      <c r="X15" s="87"/>
-      <c r="Y15" s="87"/>
-      <c r="Z15" s="87"/>
-      <c r="AA15" s="87"/>
-      <c r="AB15" s="87"/>
-      <c r="AC15" s="87"/>
-      <c r="AD15" s="87"/>
-      <c r="AE15" s="87"/>
-      <c r="AF15" s="87"/>
-      <c r="AG15" s="87"/>
-      <c r="AH15" s="87"/>
-      <c r="AI15" s="87"/>
-      <c r="AJ15" s="87"/>
-      <c r="AK15" s="87"/>
-      <c r="AL15" s="87"/>
-      <c r="AM15" s="87"/>
-      <c r="AN15" s="87"/>
-      <c r="AO15" s="87"/>
-      <c r="AP15" s="88"/>
-      <c r="AQ15" s="92"/>
-      <c r="AR15" s="87"/>
-      <c r="AS15" s="87"/>
-      <c r="AT15" s="87"/>
-      <c r="AU15" s="87"/>
-      <c r="AV15" s="87"/>
-      <c r="AW15" s="87"/>
-      <c r="AX15" s="87"/>
-      <c r="AY15" s="87"/>
-      <c r="AZ15" s="87"/>
-      <c r="BA15" s="87"/>
-      <c r="BB15" s="87"/>
-      <c r="BC15" s="87"/>
-      <c r="BD15" s="87"/>
-      <c r="BE15" s="93"/>
+      <c r="P15" s="82"/>
+      <c r="Q15" s="82"/>
+      <c r="R15" s="82"/>
+      <c r="S15" s="82"/>
+      <c r="T15" s="82"/>
+      <c r="U15" s="82"/>
+      <c r="V15" s="82"/>
+      <c r="W15" s="82"/>
+      <c r="X15" s="82"/>
+      <c r="Y15" s="82"/>
+      <c r="Z15" s="82"/>
+      <c r="AA15" s="82"/>
+      <c r="AB15" s="82"/>
+      <c r="AC15" s="82"/>
+      <c r="AD15" s="82"/>
+      <c r="AE15" s="82"/>
+      <c r="AF15" s="82"/>
+      <c r="AG15" s="82"/>
+      <c r="AH15" s="82"/>
+      <c r="AI15" s="82"/>
+      <c r="AJ15" s="82"/>
+      <c r="AK15" s="82"/>
+      <c r="AL15" s="82"/>
+      <c r="AM15" s="82"/>
+      <c r="AN15" s="82"/>
+      <c r="AO15" s="82"/>
+      <c r="AP15" s="90"/>
+      <c r="AQ15" s="81"/>
+      <c r="AR15" s="82"/>
+      <c r="AS15" s="82"/>
+      <c r="AT15" s="82"/>
+      <c r="AU15" s="82"/>
+      <c r="AV15" s="82"/>
+      <c r="AW15" s="82"/>
+      <c r="AX15" s="82"/>
+      <c r="AY15" s="82"/>
+      <c r="AZ15" s="82"/>
+      <c r="BA15" s="82"/>
+      <c r="BB15" s="82"/>
+      <c r="BC15" s="82"/>
+      <c r="BD15" s="82"/>
+      <c r="BE15" s="83"/>
     </row>
     <row r="16" spans="1:57" ht="15" customHeight="1">
-      <c r="A16" s="81"/>
-      <c r="B16" s="82"/>
-      <c r="C16" s="82"/>
-      <c r="D16" s="82"/>
-      <c r="E16" s="82"/>
-      <c r="F16" s="82"/>
-      <c r="G16" s="83"/>
+      <c r="A16" s="101"/>
+      <c r="B16" s="102"/>
+      <c r="C16" s="102"/>
+      <c r="D16" s="102"/>
+      <c r="E16" s="102"/>
+      <c r="F16" s="102"/>
+      <c r="G16" s="103"/>
       <c r="H16" s="84"/>
       <c r="I16" s="85"/>
       <c r="J16" s="85"/>
@@ -65769,57 +65779,57 @@
       <c r="M16" s="85"/>
       <c r="N16" s="86"/>
       <c r="O16" s="84"/>
-      <c r="P16" s="87"/>
-      <c r="Q16" s="87"/>
-      <c r="R16" s="87"/>
-      <c r="S16" s="87"/>
-      <c r="T16" s="87"/>
-      <c r="U16" s="87"/>
-      <c r="V16" s="87"/>
-      <c r="W16" s="87"/>
-      <c r="X16" s="87"/>
-      <c r="Y16" s="87"/>
-      <c r="Z16" s="87"/>
-      <c r="AA16" s="87"/>
-      <c r="AB16" s="87"/>
-      <c r="AC16" s="87"/>
-      <c r="AD16" s="87"/>
-      <c r="AE16" s="87"/>
-      <c r="AF16" s="87"/>
-      <c r="AG16" s="87"/>
-      <c r="AH16" s="87"/>
-      <c r="AI16" s="87"/>
-      <c r="AJ16" s="87"/>
-      <c r="AK16" s="87"/>
-      <c r="AL16" s="87"/>
-      <c r="AM16" s="87"/>
-      <c r="AN16" s="87"/>
-      <c r="AO16" s="87"/>
-      <c r="AP16" s="88"/>
-      <c r="AQ16" s="92"/>
-      <c r="AR16" s="87"/>
-      <c r="AS16" s="87"/>
-      <c r="AT16" s="87"/>
-      <c r="AU16" s="87"/>
-      <c r="AV16" s="87"/>
-      <c r="AW16" s="87"/>
-      <c r="AX16" s="87"/>
-      <c r="AY16" s="87"/>
-      <c r="AZ16" s="87"/>
-      <c r="BA16" s="87"/>
-      <c r="BB16" s="87"/>
-      <c r="BC16" s="87"/>
-      <c r="BD16" s="87"/>
-      <c r="BE16" s="93"/>
+      <c r="P16" s="82"/>
+      <c r="Q16" s="82"/>
+      <c r="R16" s="82"/>
+      <c r="S16" s="82"/>
+      <c r="T16" s="82"/>
+      <c r="U16" s="82"/>
+      <c r="V16" s="82"/>
+      <c r="W16" s="82"/>
+      <c r="X16" s="82"/>
+      <c r="Y16" s="82"/>
+      <c r="Z16" s="82"/>
+      <c r="AA16" s="82"/>
+      <c r="AB16" s="82"/>
+      <c r="AC16" s="82"/>
+      <c r="AD16" s="82"/>
+      <c r="AE16" s="82"/>
+      <c r="AF16" s="82"/>
+      <c r="AG16" s="82"/>
+      <c r="AH16" s="82"/>
+      <c r="AI16" s="82"/>
+      <c r="AJ16" s="82"/>
+      <c r="AK16" s="82"/>
+      <c r="AL16" s="82"/>
+      <c r="AM16" s="82"/>
+      <c r="AN16" s="82"/>
+      <c r="AO16" s="82"/>
+      <c r="AP16" s="90"/>
+      <c r="AQ16" s="81"/>
+      <c r="AR16" s="82"/>
+      <c r="AS16" s="82"/>
+      <c r="AT16" s="82"/>
+      <c r="AU16" s="82"/>
+      <c r="AV16" s="82"/>
+      <c r="AW16" s="82"/>
+      <c r="AX16" s="82"/>
+      <c r="AY16" s="82"/>
+      <c r="AZ16" s="82"/>
+      <c r="BA16" s="82"/>
+      <c r="BB16" s="82"/>
+      <c r="BC16" s="82"/>
+      <c r="BD16" s="82"/>
+      <c r="BE16" s="83"/>
     </row>
     <row r="17" spans="1:57" ht="15" customHeight="1">
-      <c r="A17" s="81"/>
-      <c r="B17" s="82"/>
-      <c r="C17" s="82"/>
-      <c r="D17" s="82"/>
-      <c r="E17" s="82"/>
-      <c r="F17" s="82"/>
-      <c r="G17" s="83"/>
+      <c r="A17" s="101"/>
+      <c r="B17" s="102"/>
+      <c r="C17" s="102"/>
+      <c r="D17" s="102"/>
+      <c r="E17" s="102"/>
+      <c r="F17" s="102"/>
+      <c r="G17" s="103"/>
       <c r="H17" s="84"/>
       <c r="I17" s="85"/>
       <c r="J17" s="85"/>
@@ -65828,57 +65838,57 @@
       <c r="M17" s="85"/>
       <c r="N17" s="86"/>
       <c r="O17" s="84"/>
-      <c r="P17" s="87"/>
-      <c r="Q17" s="87"/>
-      <c r="R17" s="87"/>
-      <c r="S17" s="87"/>
-      <c r="T17" s="87"/>
-      <c r="U17" s="87"/>
-      <c r="V17" s="87"/>
-      <c r="W17" s="87"/>
-      <c r="X17" s="87"/>
-      <c r="Y17" s="87"/>
-      <c r="Z17" s="87"/>
-      <c r="AA17" s="87"/>
-      <c r="AB17" s="87"/>
-      <c r="AC17" s="87"/>
-      <c r="AD17" s="87"/>
-      <c r="AE17" s="87"/>
-      <c r="AF17" s="87"/>
-      <c r="AG17" s="87"/>
-      <c r="AH17" s="87"/>
-      <c r="AI17" s="87"/>
-      <c r="AJ17" s="87"/>
-      <c r="AK17" s="87"/>
-      <c r="AL17" s="87"/>
-      <c r="AM17" s="87"/>
-      <c r="AN17" s="87"/>
-      <c r="AO17" s="87"/>
-      <c r="AP17" s="88"/>
-      <c r="AQ17" s="92"/>
-      <c r="AR17" s="87"/>
-      <c r="AS17" s="87"/>
-      <c r="AT17" s="87"/>
-      <c r="AU17" s="87"/>
-      <c r="AV17" s="87"/>
-      <c r="AW17" s="87"/>
-      <c r="AX17" s="87"/>
-      <c r="AY17" s="87"/>
-      <c r="AZ17" s="87"/>
-      <c r="BA17" s="87"/>
-      <c r="BB17" s="87"/>
-      <c r="BC17" s="87"/>
-      <c r="BD17" s="87"/>
-      <c r="BE17" s="93"/>
+      <c r="P17" s="82"/>
+      <c r="Q17" s="82"/>
+      <c r="R17" s="82"/>
+      <c r="S17" s="82"/>
+      <c r="T17" s="82"/>
+      <c r="U17" s="82"/>
+      <c r="V17" s="82"/>
+      <c r="W17" s="82"/>
+      <c r="X17" s="82"/>
+      <c r="Y17" s="82"/>
+      <c r="Z17" s="82"/>
+      <c r="AA17" s="82"/>
+      <c r="AB17" s="82"/>
+      <c r="AC17" s="82"/>
+      <c r="AD17" s="82"/>
+      <c r="AE17" s="82"/>
+      <c r="AF17" s="82"/>
+      <c r="AG17" s="82"/>
+      <c r="AH17" s="82"/>
+      <c r="AI17" s="82"/>
+      <c r="AJ17" s="82"/>
+      <c r="AK17" s="82"/>
+      <c r="AL17" s="82"/>
+      <c r="AM17" s="82"/>
+      <c r="AN17" s="82"/>
+      <c r="AO17" s="82"/>
+      <c r="AP17" s="90"/>
+      <c r="AQ17" s="81"/>
+      <c r="AR17" s="82"/>
+      <c r="AS17" s="82"/>
+      <c r="AT17" s="82"/>
+      <c r="AU17" s="82"/>
+      <c r="AV17" s="82"/>
+      <c r="AW17" s="82"/>
+      <c r="AX17" s="82"/>
+      <c r="AY17" s="82"/>
+      <c r="AZ17" s="82"/>
+      <c r="BA17" s="82"/>
+      <c r="BB17" s="82"/>
+      <c r="BC17" s="82"/>
+      <c r="BD17" s="82"/>
+      <c r="BE17" s="83"/>
     </row>
     <row r="18" spans="1:57" ht="15" customHeight="1">
-      <c r="A18" s="81"/>
-      <c r="B18" s="82"/>
-      <c r="C18" s="82"/>
-      <c r="D18" s="82"/>
-      <c r="E18" s="82"/>
-      <c r="F18" s="82"/>
-      <c r="G18" s="83"/>
+      <c r="A18" s="101"/>
+      <c r="B18" s="102"/>
+      <c r="C18" s="102"/>
+      <c r="D18" s="102"/>
+      <c r="E18" s="102"/>
+      <c r="F18" s="102"/>
+      <c r="G18" s="103"/>
       <c r="H18" s="84"/>
       <c r="I18" s="85"/>
       <c r="J18" s="85"/>
@@ -65887,57 +65897,57 @@
       <c r="M18" s="85"/>
       <c r="N18" s="86"/>
       <c r="O18" s="84"/>
-      <c r="P18" s="87"/>
-      <c r="Q18" s="87"/>
-      <c r="R18" s="87"/>
-      <c r="S18" s="87"/>
-      <c r="T18" s="87"/>
-      <c r="U18" s="87"/>
-      <c r="V18" s="87"/>
-      <c r="W18" s="87"/>
-      <c r="X18" s="87"/>
-      <c r="Y18" s="87"/>
-      <c r="Z18" s="87"/>
-      <c r="AA18" s="87"/>
-      <c r="AB18" s="87"/>
-      <c r="AC18" s="87"/>
-      <c r="AD18" s="87"/>
-      <c r="AE18" s="87"/>
-      <c r="AF18" s="87"/>
-      <c r="AG18" s="87"/>
-      <c r="AH18" s="87"/>
-      <c r="AI18" s="87"/>
-      <c r="AJ18" s="87"/>
-      <c r="AK18" s="87"/>
-      <c r="AL18" s="87"/>
-      <c r="AM18" s="87"/>
-      <c r="AN18" s="87"/>
-      <c r="AO18" s="87"/>
-      <c r="AP18" s="88"/>
-      <c r="AQ18" s="92"/>
-      <c r="AR18" s="87"/>
-      <c r="AS18" s="87"/>
-      <c r="AT18" s="87"/>
-      <c r="AU18" s="87"/>
-      <c r="AV18" s="87"/>
-      <c r="AW18" s="87"/>
-      <c r="AX18" s="87"/>
-      <c r="AY18" s="87"/>
-      <c r="AZ18" s="87"/>
-      <c r="BA18" s="87"/>
-      <c r="BB18" s="87"/>
-      <c r="BC18" s="87"/>
-      <c r="BD18" s="87"/>
-      <c r="BE18" s="93"/>
+      <c r="P18" s="82"/>
+      <c r="Q18" s="82"/>
+      <c r="R18" s="82"/>
+      <c r="S18" s="82"/>
+      <c r="T18" s="82"/>
+      <c r="U18" s="82"/>
+      <c r="V18" s="82"/>
+      <c r="W18" s="82"/>
+      <c r="X18" s="82"/>
+      <c r="Y18" s="82"/>
+      <c r="Z18" s="82"/>
+      <c r="AA18" s="82"/>
+      <c r="AB18" s="82"/>
+      <c r="AC18" s="82"/>
+      <c r="AD18" s="82"/>
+      <c r="AE18" s="82"/>
+      <c r="AF18" s="82"/>
+      <c r="AG18" s="82"/>
+      <c r="AH18" s="82"/>
+      <c r="AI18" s="82"/>
+      <c r="AJ18" s="82"/>
+      <c r="AK18" s="82"/>
+      <c r="AL18" s="82"/>
+      <c r="AM18" s="82"/>
+      <c r="AN18" s="82"/>
+      <c r="AO18" s="82"/>
+      <c r="AP18" s="90"/>
+      <c r="AQ18" s="81"/>
+      <c r="AR18" s="82"/>
+      <c r="AS18" s="82"/>
+      <c r="AT18" s="82"/>
+      <c r="AU18" s="82"/>
+      <c r="AV18" s="82"/>
+      <c r="AW18" s="82"/>
+      <c r="AX18" s="82"/>
+      <c r="AY18" s="82"/>
+      <c r="AZ18" s="82"/>
+      <c r="BA18" s="82"/>
+      <c r="BB18" s="82"/>
+      <c r="BC18" s="82"/>
+      <c r="BD18" s="82"/>
+      <c r="BE18" s="83"/>
     </row>
     <row r="19" spans="1:57" ht="15" customHeight="1">
-      <c r="A19" s="81"/>
-      <c r="B19" s="82"/>
-      <c r="C19" s="82"/>
-      <c r="D19" s="82"/>
-      <c r="E19" s="82"/>
-      <c r="F19" s="82"/>
-      <c r="G19" s="83"/>
+      <c r="A19" s="101"/>
+      <c r="B19" s="102"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="103"/>
       <c r="H19" s="84"/>
       <c r="I19" s="85"/>
       <c r="J19" s="85"/>
@@ -65946,57 +65956,57 @@
       <c r="M19" s="85"/>
       <c r="N19" s="86"/>
       <c r="O19" s="84"/>
-      <c r="P19" s="87"/>
-      <c r="Q19" s="87"/>
-      <c r="R19" s="87"/>
-      <c r="S19" s="87"/>
-      <c r="T19" s="87"/>
-      <c r="U19" s="87"/>
-      <c r="V19" s="87"/>
-      <c r="W19" s="87"/>
-      <c r="X19" s="87"/>
-      <c r="Y19" s="87"/>
-      <c r="Z19" s="87"/>
-      <c r="AA19" s="87"/>
-      <c r="AB19" s="87"/>
-      <c r="AC19" s="87"/>
-      <c r="AD19" s="87"/>
-      <c r="AE19" s="87"/>
-      <c r="AF19" s="87"/>
-      <c r="AG19" s="87"/>
-      <c r="AH19" s="87"/>
-      <c r="AI19" s="87"/>
-      <c r="AJ19" s="87"/>
-      <c r="AK19" s="87"/>
-      <c r="AL19" s="87"/>
-      <c r="AM19" s="87"/>
-      <c r="AN19" s="87"/>
-      <c r="AO19" s="87"/>
-      <c r="AP19" s="88"/>
-      <c r="AQ19" s="92"/>
-      <c r="AR19" s="87"/>
-      <c r="AS19" s="87"/>
-      <c r="AT19" s="87"/>
-      <c r="AU19" s="87"/>
-      <c r="AV19" s="87"/>
-      <c r="AW19" s="87"/>
-      <c r="AX19" s="87"/>
-      <c r="AY19" s="87"/>
-      <c r="AZ19" s="87"/>
-      <c r="BA19" s="87"/>
-      <c r="BB19" s="87"/>
-      <c r="BC19" s="87"/>
-      <c r="BD19" s="87"/>
-      <c r="BE19" s="93"/>
+      <c r="P19" s="82"/>
+      <c r="Q19" s="82"/>
+      <c r="R19" s="82"/>
+      <c r="S19" s="82"/>
+      <c r="T19" s="82"/>
+      <c r="U19" s="82"/>
+      <c r="V19" s="82"/>
+      <c r="W19" s="82"/>
+      <c r="X19" s="82"/>
+      <c r="Y19" s="82"/>
+      <c r="Z19" s="82"/>
+      <c r="AA19" s="82"/>
+      <c r="AB19" s="82"/>
+      <c r="AC19" s="82"/>
+      <c r="AD19" s="82"/>
+      <c r="AE19" s="82"/>
+      <c r="AF19" s="82"/>
+      <c r="AG19" s="82"/>
+      <c r="AH19" s="82"/>
+      <c r="AI19" s="82"/>
+      <c r="AJ19" s="82"/>
+      <c r="AK19" s="82"/>
+      <c r="AL19" s="82"/>
+      <c r="AM19" s="82"/>
+      <c r="AN19" s="82"/>
+      <c r="AO19" s="82"/>
+      <c r="AP19" s="90"/>
+      <c r="AQ19" s="81"/>
+      <c r="AR19" s="82"/>
+      <c r="AS19" s="82"/>
+      <c r="AT19" s="82"/>
+      <c r="AU19" s="82"/>
+      <c r="AV19" s="82"/>
+      <c r="AW19" s="82"/>
+      <c r="AX19" s="82"/>
+      <c r="AY19" s="82"/>
+      <c r="AZ19" s="82"/>
+      <c r="BA19" s="82"/>
+      <c r="BB19" s="82"/>
+      <c r="BC19" s="82"/>
+      <c r="BD19" s="82"/>
+      <c r="BE19" s="83"/>
     </row>
     <row r="20" spans="1:57" ht="15" customHeight="1">
-      <c r="A20" s="81"/>
-      <c r="B20" s="82"/>
-      <c r="C20" s="82"/>
-      <c r="D20" s="82"/>
-      <c r="E20" s="82"/>
-      <c r="F20" s="82"/>
-      <c r="G20" s="83"/>
+      <c r="A20" s="101"/>
+      <c r="B20" s="102"/>
+      <c r="C20" s="102"/>
+      <c r="D20" s="102"/>
+      <c r="E20" s="102"/>
+      <c r="F20" s="102"/>
+      <c r="G20" s="103"/>
       <c r="H20" s="84"/>
       <c r="I20" s="85"/>
       <c r="J20" s="85"/>
@@ -66005,57 +66015,57 @@
       <c r="M20" s="85"/>
       <c r="N20" s="86"/>
       <c r="O20" s="84"/>
-      <c r="P20" s="87"/>
-      <c r="Q20" s="87"/>
-      <c r="R20" s="87"/>
-      <c r="S20" s="87"/>
-      <c r="T20" s="87"/>
-      <c r="U20" s="87"/>
-      <c r="V20" s="87"/>
-      <c r="W20" s="87"/>
-      <c r="X20" s="87"/>
-      <c r="Y20" s="87"/>
-      <c r="Z20" s="87"/>
-      <c r="AA20" s="87"/>
-      <c r="AB20" s="87"/>
-      <c r="AC20" s="87"/>
-      <c r="AD20" s="87"/>
-      <c r="AE20" s="87"/>
-      <c r="AF20" s="87"/>
-      <c r="AG20" s="87"/>
-      <c r="AH20" s="87"/>
-      <c r="AI20" s="87"/>
-      <c r="AJ20" s="87"/>
-      <c r="AK20" s="87"/>
-      <c r="AL20" s="87"/>
-      <c r="AM20" s="87"/>
-      <c r="AN20" s="87"/>
-      <c r="AO20" s="87"/>
-      <c r="AP20" s="88"/>
-      <c r="AQ20" s="92"/>
-      <c r="AR20" s="87"/>
-      <c r="AS20" s="87"/>
-      <c r="AT20" s="87"/>
-      <c r="AU20" s="87"/>
-      <c r="AV20" s="87"/>
-      <c r="AW20" s="87"/>
-      <c r="AX20" s="87"/>
-      <c r="AY20" s="87"/>
-      <c r="AZ20" s="87"/>
-      <c r="BA20" s="87"/>
-      <c r="BB20" s="87"/>
-      <c r="BC20" s="87"/>
-      <c r="BD20" s="87"/>
-      <c r="BE20" s="93"/>
+      <c r="P20" s="82"/>
+      <c r="Q20" s="82"/>
+      <c r="R20" s="82"/>
+      <c r="S20" s="82"/>
+      <c r="T20" s="82"/>
+      <c r="U20" s="82"/>
+      <c r="V20" s="82"/>
+      <c r="W20" s="82"/>
+      <c r="X20" s="82"/>
+      <c r="Y20" s="82"/>
+      <c r="Z20" s="82"/>
+      <c r="AA20" s="82"/>
+      <c r="AB20" s="82"/>
+      <c r="AC20" s="82"/>
+      <c r="AD20" s="82"/>
+      <c r="AE20" s="82"/>
+      <c r="AF20" s="82"/>
+      <c r="AG20" s="82"/>
+      <c r="AH20" s="82"/>
+      <c r="AI20" s="82"/>
+      <c r="AJ20" s="82"/>
+      <c r="AK20" s="82"/>
+      <c r="AL20" s="82"/>
+      <c r="AM20" s="82"/>
+      <c r="AN20" s="82"/>
+      <c r="AO20" s="82"/>
+      <c r="AP20" s="90"/>
+      <c r="AQ20" s="81"/>
+      <c r="AR20" s="82"/>
+      <c r="AS20" s="82"/>
+      <c r="AT20" s="82"/>
+      <c r="AU20" s="82"/>
+      <c r="AV20" s="82"/>
+      <c r="AW20" s="82"/>
+      <c r="AX20" s="82"/>
+      <c r="AY20" s="82"/>
+      <c r="AZ20" s="82"/>
+      <c r="BA20" s="82"/>
+      <c r="BB20" s="82"/>
+      <c r="BC20" s="82"/>
+      <c r="BD20" s="82"/>
+      <c r="BE20" s="83"/>
     </row>
     <row r="21" spans="1:57" ht="15" customHeight="1">
-      <c r="A21" s="81"/>
-      <c r="B21" s="82"/>
-      <c r="C21" s="82"/>
-      <c r="D21" s="82"/>
-      <c r="E21" s="82"/>
-      <c r="F21" s="82"/>
-      <c r="G21" s="83"/>
+      <c r="A21" s="101"/>
+      <c r="B21" s="102"/>
+      <c r="C21" s="102"/>
+      <c r="D21" s="102"/>
+      <c r="E21" s="102"/>
+      <c r="F21" s="102"/>
+      <c r="G21" s="103"/>
       <c r="H21" s="84"/>
       <c r="I21" s="85"/>
       <c r="J21" s="85"/>
@@ -66064,57 +66074,57 @@
       <c r="M21" s="85"/>
       <c r="N21" s="86"/>
       <c r="O21" s="84"/>
-      <c r="P21" s="87"/>
-      <c r="Q21" s="87"/>
-      <c r="R21" s="87"/>
-      <c r="S21" s="87"/>
-      <c r="T21" s="87"/>
-      <c r="U21" s="87"/>
-      <c r="V21" s="87"/>
-      <c r="W21" s="87"/>
-      <c r="X21" s="87"/>
-      <c r="Y21" s="87"/>
-      <c r="Z21" s="87"/>
-      <c r="AA21" s="87"/>
-      <c r="AB21" s="87"/>
-      <c r="AC21" s="87"/>
-      <c r="AD21" s="87"/>
-      <c r="AE21" s="87"/>
-      <c r="AF21" s="87"/>
-      <c r="AG21" s="87"/>
-      <c r="AH21" s="87"/>
-      <c r="AI21" s="87"/>
-      <c r="AJ21" s="87"/>
-      <c r="AK21" s="87"/>
-      <c r="AL21" s="87"/>
-      <c r="AM21" s="87"/>
-      <c r="AN21" s="87"/>
-      <c r="AO21" s="87"/>
-      <c r="AP21" s="88"/>
-      <c r="AQ21" s="92"/>
-      <c r="AR21" s="87"/>
-      <c r="AS21" s="87"/>
-      <c r="AT21" s="87"/>
-      <c r="AU21" s="87"/>
-      <c r="AV21" s="87"/>
-      <c r="AW21" s="87"/>
-      <c r="AX21" s="87"/>
-      <c r="AY21" s="87"/>
-      <c r="AZ21" s="87"/>
-      <c r="BA21" s="87"/>
-      <c r="BB21" s="87"/>
-      <c r="BC21" s="87"/>
-      <c r="BD21" s="87"/>
-      <c r="BE21" s="93"/>
+      <c r="P21" s="82"/>
+      <c r="Q21" s="82"/>
+      <c r="R21" s="82"/>
+      <c r="S21" s="82"/>
+      <c r="T21" s="82"/>
+      <c r="U21" s="82"/>
+      <c r="V21" s="82"/>
+      <c r="W21" s="82"/>
+      <c r="X21" s="82"/>
+      <c r="Y21" s="82"/>
+      <c r="Z21" s="82"/>
+      <c r="AA21" s="82"/>
+      <c r="AB21" s="82"/>
+      <c r="AC21" s="82"/>
+      <c r="AD21" s="82"/>
+      <c r="AE21" s="82"/>
+      <c r="AF21" s="82"/>
+      <c r="AG21" s="82"/>
+      <c r="AH21" s="82"/>
+      <c r="AI21" s="82"/>
+      <c r="AJ21" s="82"/>
+      <c r="AK21" s="82"/>
+      <c r="AL21" s="82"/>
+      <c r="AM21" s="82"/>
+      <c r="AN21" s="82"/>
+      <c r="AO21" s="82"/>
+      <c r="AP21" s="90"/>
+      <c r="AQ21" s="81"/>
+      <c r="AR21" s="82"/>
+      <c r="AS21" s="82"/>
+      <c r="AT21" s="82"/>
+      <c r="AU21" s="82"/>
+      <c r="AV21" s="82"/>
+      <c r="AW21" s="82"/>
+      <c r="AX21" s="82"/>
+      <c r="AY21" s="82"/>
+      <c r="AZ21" s="82"/>
+      <c r="BA21" s="82"/>
+      <c r="BB21" s="82"/>
+      <c r="BC21" s="82"/>
+      <c r="BD21" s="82"/>
+      <c r="BE21" s="83"/>
     </row>
     <row r="22" spans="1:57" ht="15" customHeight="1">
-      <c r="A22" s="81"/>
-      <c r="B22" s="82"/>
-      <c r="C22" s="82"/>
-      <c r="D22" s="82"/>
-      <c r="E22" s="82"/>
-      <c r="F22" s="82"/>
-      <c r="G22" s="83"/>
+      <c r="A22" s="101"/>
+      <c r="B22" s="102"/>
+      <c r="C22" s="102"/>
+      <c r="D22" s="102"/>
+      <c r="E22" s="102"/>
+      <c r="F22" s="102"/>
+      <c r="G22" s="103"/>
       <c r="H22" s="84"/>
       <c r="I22" s="85"/>
       <c r="J22" s="85"/>
@@ -66123,57 +66133,57 @@
       <c r="M22" s="85"/>
       <c r="N22" s="86"/>
       <c r="O22" s="84"/>
-      <c r="P22" s="87"/>
-      <c r="Q22" s="87"/>
-      <c r="R22" s="87"/>
-      <c r="S22" s="87"/>
-      <c r="T22" s="87"/>
-      <c r="U22" s="87"/>
-      <c r="V22" s="87"/>
-      <c r="W22" s="87"/>
-      <c r="X22" s="87"/>
-      <c r="Y22" s="87"/>
-      <c r="Z22" s="87"/>
-      <c r="AA22" s="87"/>
-      <c r="AB22" s="87"/>
-      <c r="AC22" s="87"/>
-      <c r="AD22" s="87"/>
-      <c r="AE22" s="87"/>
-      <c r="AF22" s="87"/>
-      <c r="AG22" s="87"/>
-      <c r="AH22" s="87"/>
-      <c r="AI22" s="87"/>
-      <c r="AJ22" s="87"/>
-      <c r="AK22" s="87"/>
-      <c r="AL22" s="87"/>
-      <c r="AM22" s="87"/>
-      <c r="AN22" s="87"/>
-      <c r="AO22" s="87"/>
-      <c r="AP22" s="88"/>
-      <c r="AQ22" s="92"/>
-      <c r="AR22" s="87"/>
-      <c r="AS22" s="87"/>
-      <c r="AT22" s="87"/>
-      <c r="AU22" s="87"/>
-      <c r="AV22" s="87"/>
-      <c r="AW22" s="87"/>
-      <c r="AX22" s="87"/>
-      <c r="AY22" s="87"/>
-      <c r="AZ22" s="87"/>
-      <c r="BA22" s="87"/>
-      <c r="BB22" s="87"/>
-      <c r="BC22" s="87"/>
-      <c r="BD22" s="87"/>
-      <c r="BE22" s="93"/>
+      <c r="P22" s="82"/>
+      <c r="Q22" s="82"/>
+      <c r="R22" s="82"/>
+      <c r="S22" s="82"/>
+      <c r="T22" s="82"/>
+      <c r="U22" s="82"/>
+      <c r="V22" s="82"/>
+      <c r="W22" s="82"/>
+      <c r="X22" s="82"/>
+      <c r="Y22" s="82"/>
+      <c r="Z22" s="82"/>
+      <c r="AA22" s="82"/>
+      <c r="AB22" s="82"/>
+      <c r="AC22" s="82"/>
+      <c r="AD22" s="82"/>
+      <c r="AE22" s="82"/>
+      <c r="AF22" s="82"/>
+      <c r="AG22" s="82"/>
+      <c r="AH22" s="82"/>
+      <c r="AI22" s="82"/>
+      <c r="AJ22" s="82"/>
+      <c r="AK22" s="82"/>
+      <c r="AL22" s="82"/>
+      <c r="AM22" s="82"/>
+      <c r="AN22" s="82"/>
+      <c r="AO22" s="82"/>
+      <c r="AP22" s="90"/>
+      <c r="AQ22" s="81"/>
+      <c r="AR22" s="82"/>
+      <c r="AS22" s="82"/>
+      <c r="AT22" s="82"/>
+      <c r="AU22" s="82"/>
+      <c r="AV22" s="82"/>
+      <c r="AW22" s="82"/>
+      <c r="AX22" s="82"/>
+      <c r="AY22" s="82"/>
+      <c r="AZ22" s="82"/>
+      <c r="BA22" s="82"/>
+      <c r="BB22" s="82"/>
+      <c r="BC22" s="82"/>
+      <c r="BD22" s="82"/>
+      <c r="BE22" s="83"/>
     </row>
     <row r="23" spans="1:57" ht="15" customHeight="1">
-      <c r="A23" s="81"/>
-      <c r="B23" s="82"/>
-      <c r="C23" s="82"/>
-      <c r="D23" s="82"/>
-      <c r="E23" s="82"/>
-      <c r="F23" s="82"/>
-      <c r="G23" s="83"/>
+      <c r="A23" s="101"/>
+      <c r="B23" s="102"/>
+      <c r="C23" s="102"/>
+      <c r="D23" s="102"/>
+      <c r="E23" s="102"/>
+      <c r="F23" s="102"/>
+      <c r="G23" s="103"/>
       <c r="H23" s="84"/>
       <c r="I23" s="85"/>
       <c r="J23" s="85"/>
@@ -66182,57 +66192,57 @@
       <c r="M23" s="85"/>
       <c r="N23" s="86"/>
       <c r="O23" s="84"/>
-      <c r="P23" s="87"/>
-      <c r="Q23" s="87"/>
-      <c r="R23" s="87"/>
-      <c r="S23" s="87"/>
-      <c r="T23" s="87"/>
-      <c r="U23" s="87"/>
-      <c r="V23" s="87"/>
-      <c r="W23" s="87"/>
-      <c r="X23" s="87"/>
-      <c r="Y23" s="87"/>
-      <c r="Z23" s="87"/>
-      <c r="AA23" s="87"/>
-      <c r="AB23" s="87"/>
-      <c r="AC23" s="87"/>
-      <c r="AD23" s="87"/>
-      <c r="AE23" s="87"/>
-      <c r="AF23" s="87"/>
-      <c r="AG23" s="87"/>
-      <c r="AH23" s="87"/>
-      <c r="AI23" s="87"/>
-      <c r="AJ23" s="87"/>
-      <c r="AK23" s="87"/>
-      <c r="AL23" s="87"/>
-      <c r="AM23" s="87"/>
-      <c r="AN23" s="87"/>
-      <c r="AO23" s="87"/>
-      <c r="AP23" s="88"/>
-      <c r="AQ23" s="92"/>
-      <c r="AR23" s="87"/>
-      <c r="AS23" s="87"/>
-      <c r="AT23" s="87"/>
-      <c r="AU23" s="87"/>
-      <c r="AV23" s="87"/>
-      <c r="AW23" s="87"/>
-      <c r="AX23" s="87"/>
-      <c r="AY23" s="87"/>
-      <c r="AZ23" s="87"/>
-      <c r="BA23" s="87"/>
-      <c r="BB23" s="87"/>
-      <c r="BC23" s="87"/>
-      <c r="BD23" s="87"/>
-      <c r="BE23" s="93"/>
+      <c r="P23" s="82"/>
+      <c r="Q23" s="82"/>
+      <c r="R23" s="82"/>
+      <c r="S23" s="82"/>
+      <c r="T23" s="82"/>
+      <c r="U23" s="82"/>
+      <c r="V23" s="82"/>
+      <c r="W23" s="82"/>
+      <c r="X23" s="82"/>
+      <c r="Y23" s="82"/>
+      <c r="Z23" s="82"/>
+      <c r="AA23" s="82"/>
+      <c r="AB23" s="82"/>
+      <c r="AC23" s="82"/>
+      <c r="AD23" s="82"/>
+      <c r="AE23" s="82"/>
+      <c r="AF23" s="82"/>
+      <c r="AG23" s="82"/>
+      <c r="AH23" s="82"/>
+      <c r="AI23" s="82"/>
+      <c r="AJ23" s="82"/>
+      <c r="AK23" s="82"/>
+      <c r="AL23" s="82"/>
+      <c r="AM23" s="82"/>
+      <c r="AN23" s="82"/>
+      <c r="AO23" s="82"/>
+      <c r="AP23" s="90"/>
+      <c r="AQ23" s="81"/>
+      <c r="AR23" s="82"/>
+      <c r="AS23" s="82"/>
+      <c r="AT23" s="82"/>
+      <c r="AU23" s="82"/>
+      <c r="AV23" s="82"/>
+      <c r="AW23" s="82"/>
+      <c r="AX23" s="82"/>
+      <c r="AY23" s="82"/>
+      <c r="AZ23" s="82"/>
+      <c r="BA23" s="82"/>
+      <c r="BB23" s="82"/>
+      <c r="BC23" s="82"/>
+      <c r="BD23" s="82"/>
+      <c r="BE23" s="83"/>
     </row>
     <row r="24" spans="1:57" ht="15" customHeight="1">
-      <c r="A24" s="81"/>
-      <c r="B24" s="82"/>
-      <c r="C24" s="82"/>
-      <c r="D24" s="82"/>
-      <c r="E24" s="82"/>
-      <c r="F24" s="82"/>
-      <c r="G24" s="83"/>
+      <c r="A24" s="101"/>
+      <c r="B24" s="102"/>
+      <c r="C24" s="102"/>
+      <c r="D24" s="102"/>
+      <c r="E24" s="102"/>
+      <c r="F24" s="102"/>
+      <c r="G24" s="103"/>
       <c r="H24" s="84"/>
       <c r="I24" s="85"/>
       <c r="J24" s="85"/>
@@ -66241,57 +66251,57 @@
       <c r="M24" s="85"/>
       <c r="N24" s="86"/>
       <c r="O24" s="84"/>
-      <c r="P24" s="87"/>
-      <c r="Q24" s="87"/>
-      <c r="R24" s="87"/>
-      <c r="S24" s="87"/>
-      <c r="T24" s="87"/>
-      <c r="U24" s="87"/>
-      <c r="V24" s="87"/>
-      <c r="W24" s="87"/>
-      <c r="X24" s="87"/>
-      <c r="Y24" s="87"/>
-      <c r="Z24" s="87"/>
-      <c r="AA24" s="87"/>
-      <c r="AB24" s="87"/>
-      <c r="AC24" s="87"/>
-      <c r="AD24" s="87"/>
-      <c r="AE24" s="87"/>
-      <c r="AF24" s="87"/>
-      <c r="AG24" s="87"/>
-      <c r="AH24" s="87"/>
-      <c r="AI24" s="87"/>
-      <c r="AJ24" s="87"/>
-      <c r="AK24" s="87"/>
-      <c r="AL24" s="87"/>
-      <c r="AM24" s="87"/>
-      <c r="AN24" s="87"/>
-      <c r="AO24" s="87"/>
-      <c r="AP24" s="88"/>
-      <c r="AQ24" s="92"/>
-      <c r="AR24" s="87"/>
-      <c r="AS24" s="87"/>
-      <c r="AT24" s="87"/>
-      <c r="AU24" s="87"/>
-      <c r="AV24" s="87"/>
-      <c r="AW24" s="87"/>
-      <c r="AX24" s="87"/>
-      <c r="AY24" s="87"/>
-      <c r="AZ24" s="87"/>
-      <c r="BA24" s="87"/>
-      <c r="BB24" s="87"/>
-      <c r="BC24" s="87"/>
-      <c r="BD24" s="87"/>
-      <c r="BE24" s="93"/>
+      <c r="P24" s="82"/>
+      <c r="Q24" s="82"/>
+      <c r="R24" s="82"/>
+      <c r="S24" s="82"/>
+      <c r="T24" s="82"/>
+      <c r="U24" s="82"/>
+      <c r="V24" s="82"/>
+      <c r="W24" s="82"/>
+      <c r="X24" s="82"/>
+      <c r="Y24" s="82"/>
+      <c r="Z24" s="82"/>
+      <c r="AA24" s="82"/>
+      <c r="AB24" s="82"/>
+      <c r="AC24" s="82"/>
+      <c r="AD24" s="82"/>
+      <c r="AE24" s="82"/>
+      <c r="AF24" s="82"/>
+      <c r="AG24" s="82"/>
+      <c r="AH24" s="82"/>
+      <c r="AI24" s="82"/>
+      <c r="AJ24" s="82"/>
+      <c r="AK24" s="82"/>
+      <c r="AL24" s="82"/>
+      <c r="AM24" s="82"/>
+      <c r="AN24" s="82"/>
+      <c r="AO24" s="82"/>
+      <c r="AP24" s="90"/>
+      <c r="AQ24" s="81"/>
+      <c r="AR24" s="82"/>
+      <c r="AS24" s="82"/>
+      <c r="AT24" s="82"/>
+      <c r="AU24" s="82"/>
+      <c r="AV24" s="82"/>
+      <c r="AW24" s="82"/>
+      <c r="AX24" s="82"/>
+      <c r="AY24" s="82"/>
+      <c r="AZ24" s="82"/>
+      <c r="BA24" s="82"/>
+      <c r="BB24" s="82"/>
+      <c r="BC24" s="82"/>
+      <c r="BD24" s="82"/>
+      <c r="BE24" s="83"/>
     </row>
     <row r="25" spans="1:57" ht="15" customHeight="1">
-      <c r="A25" s="81"/>
-      <c r="B25" s="82"/>
-      <c r="C25" s="82"/>
-      <c r="D25" s="82"/>
-      <c r="E25" s="82"/>
-      <c r="F25" s="82"/>
-      <c r="G25" s="83"/>
+      <c r="A25" s="101"/>
+      <c r="B25" s="102"/>
+      <c r="C25" s="102"/>
+      <c r="D25" s="102"/>
+      <c r="E25" s="102"/>
+      <c r="F25" s="102"/>
+      <c r="G25" s="103"/>
       <c r="H25" s="84"/>
       <c r="I25" s="85"/>
       <c r="J25" s="85"/>
@@ -66300,57 +66310,57 @@
       <c r="M25" s="85"/>
       <c r="N25" s="86"/>
       <c r="O25" s="84"/>
-      <c r="P25" s="87"/>
-      <c r="Q25" s="87"/>
-      <c r="R25" s="87"/>
-      <c r="S25" s="87"/>
-      <c r="T25" s="87"/>
-      <c r="U25" s="87"/>
-      <c r="V25" s="87"/>
-      <c r="W25" s="87"/>
-      <c r="X25" s="87"/>
-      <c r="Y25" s="87"/>
-      <c r="Z25" s="87"/>
-      <c r="AA25" s="87"/>
-      <c r="AB25" s="87"/>
-      <c r="AC25" s="87"/>
-      <c r="AD25" s="87"/>
-      <c r="AE25" s="87"/>
-      <c r="AF25" s="87"/>
-      <c r="AG25" s="87"/>
-      <c r="AH25" s="87"/>
-      <c r="AI25" s="87"/>
-      <c r="AJ25" s="87"/>
-      <c r="AK25" s="87"/>
-      <c r="AL25" s="87"/>
-      <c r="AM25" s="87"/>
-      <c r="AN25" s="87"/>
-      <c r="AO25" s="87"/>
-      <c r="AP25" s="88"/>
-      <c r="AQ25" s="92"/>
-      <c r="AR25" s="87"/>
-      <c r="AS25" s="87"/>
-      <c r="AT25" s="87"/>
-      <c r="AU25" s="87"/>
-      <c r="AV25" s="87"/>
-      <c r="AW25" s="87"/>
-      <c r="AX25" s="87"/>
-      <c r="AY25" s="87"/>
-      <c r="AZ25" s="87"/>
-      <c r="BA25" s="87"/>
-      <c r="BB25" s="87"/>
-      <c r="BC25" s="87"/>
-      <c r="BD25" s="87"/>
-      <c r="BE25" s="93"/>
+      <c r="P25" s="82"/>
+      <c r="Q25" s="82"/>
+      <c r="R25" s="82"/>
+      <c r="S25" s="82"/>
+      <c r="T25" s="82"/>
+      <c r="U25" s="82"/>
+      <c r="V25" s="82"/>
+      <c r="W25" s="82"/>
+      <c r="X25" s="82"/>
+      <c r="Y25" s="82"/>
+      <c r="Z25" s="82"/>
+      <c r="AA25" s="82"/>
+      <c r="AB25" s="82"/>
+      <c r="AC25" s="82"/>
+      <c r="AD25" s="82"/>
+      <c r="AE25" s="82"/>
+      <c r="AF25" s="82"/>
+      <c r="AG25" s="82"/>
+      <c r="AH25" s="82"/>
+      <c r="AI25" s="82"/>
+      <c r="AJ25" s="82"/>
+      <c r="AK25" s="82"/>
+      <c r="AL25" s="82"/>
+      <c r="AM25" s="82"/>
+      <c r="AN25" s="82"/>
+      <c r="AO25" s="82"/>
+      <c r="AP25" s="90"/>
+      <c r="AQ25" s="81"/>
+      <c r="AR25" s="82"/>
+      <c r="AS25" s="82"/>
+      <c r="AT25" s="82"/>
+      <c r="AU25" s="82"/>
+      <c r="AV25" s="82"/>
+      <c r="AW25" s="82"/>
+      <c r="AX25" s="82"/>
+      <c r="AY25" s="82"/>
+      <c r="AZ25" s="82"/>
+      <c r="BA25" s="82"/>
+      <c r="BB25" s="82"/>
+      <c r="BC25" s="82"/>
+      <c r="BD25" s="82"/>
+      <c r="BE25" s="83"/>
     </row>
     <row r="26" spans="1:57" ht="15" customHeight="1">
-      <c r="A26" s="81"/>
-      <c r="B26" s="82"/>
-      <c r="C26" s="82"/>
-      <c r="D26" s="82"/>
-      <c r="E26" s="82"/>
-      <c r="F26" s="82"/>
-      <c r="G26" s="83"/>
+      <c r="A26" s="101"/>
+      <c r="B26" s="102"/>
+      <c r="C26" s="102"/>
+      <c r="D26" s="102"/>
+      <c r="E26" s="102"/>
+      <c r="F26" s="102"/>
+      <c r="G26" s="103"/>
       <c r="H26" s="84"/>
       <c r="I26" s="85"/>
       <c r="J26" s="85"/>
@@ -66359,57 +66369,57 @@
       <c r="M26" s="85"/>
       <c r="N26" s="86"/>
       <c r="O26" s="84"/>
-      <c r="P26" s="87"/>
-      <c r="Q26" s="87"/>
-      <c r="R26" s="87"/>
-      <c r="S26" s="87"/>
-      <c r="T26" s="87"/>
-      <c r="U26" s="87"/>
-      <c r="V26" s="87"/>
-      <c r="W26" s="87"/>
-      <c r="X26" s="87"/>
-      <c r="Y26" s="87"/>
-      <c r="Z26" s="87"/>
-      <c r="AA26" s="87"/>
-      <c r="AB26" s="87"/>
-      <c r="AC26" s="87"/>
-      <c r="AD26" s="87"/>
-      <c r="AE26" s="87"/>
-      <c r="AF26" s="87"/>
-      <c r="AG26" s="87"/>
-      <c r="AH26" s="87"/>
-      <c r="AI26" s="87"/>
-      <c r="AJ26" s="87"/>
-      <c r="AK26" s="87"/>
-      <c r="AL26" s="87"/>
-      <c r="AM26" s="87"/>
-      <c r="AN26" s="87"/>
-      <c r="AO26" s="87"/>
-      <c r="AP26" s="88"/>
-      <c r="AQ26" s="92"/>
-      <c r="AR26" s="87"/>
-      <c r="AS26" s="87"/>
-      <c r="AT26" s="87"/>
-      <c r="AU26" s="87"/>
-      <c r="AV26" s="87"/>
-      <c r="AW26" s="87"/>
-      <c r="AX26" s="87"/>
-      <c r="AY26" s="87"/>
-      <c r="AZ26" s="87"/>
-      <c r="BA26" s="87"/>
-      <c r="BB26" s="87"/>
-      <c r="BC26" s="87"/>
-      <c r="BD26" s="87"/>
-      <c r="BE26" s="93"/>
+      <c r="P26" s="82"/>
+      <c r="Q26" s="82"/>
+      <c r="R26" s="82"/>
+      <c r="S26" s="82"/>
+      <c r="T26" s="82"/>
+      <c r="U26" s="82"/>
+      <c r="V26" s="82"/>
+      <c r="W26" s="82"/>
+      <c r="X26" s="82"/>
+      <c r="Y26" s="82"/>
+      <c r="Z26" s="82"/>
+      <c r="AA26" s="82"/>
+      <c r="AB26" s="82"/>
+      <c r="AC26" s="82"/>
+      <c r="AD26" s="82"/>
+      <c r="AE26" s="82"/>
+      <c r="AF26" s="82"/>
+      <c r="AG26" s="82"/>
+      <c r="AH26" s="82"/>
+      <c r="AI26" s="82"/>
+      <c r="AJ26" s="82"/>
+      <c r="AK26" s="82"/>
+      <c r="AL26" s="82"/>
+      <c r="AM26" s="82"/>
+      <c r="AN26" s="82"/>
+      <c r="AO26" s="82"/>
+      <c r="AP26" s="90"/>
+      <c r="AQ26" s="81"/>
+      <c r="AR26" s="82"/>
+      <c r="AS26" s="82"/>
+      <c r="AT26" s="82"/>
+      <c r="AU26" s="82"/>
+      <c r="AV26" s="82"/>
+      <c r="AW26" s="82"/>
+      <c r="AX26" s="82"/>
+      <c r="AY26" s="82"/>
+      <c r="AZ26" s="82"/>
+      <c r="BA26" s="82"/>
+      <c r="BB26" s="82"/>
+      <c r="BC26" s="82"/>
+      <c r="BD26" s="82"/>
+      <c r="BE26" s="83"/>
     </row>
     <row r="27" spans="1:57" ht="15" customHeight="1">
-      <c r="A27" s="81"/>
-      <c r="B27" s="82"/>
-      <c r="C27" s="82"/>
-      <c r="D27" s="82"/>
-      <c r="E27" s="82"/>
-      <c r="F27" s="82"/>
-      <c r="G27" s="83"/>
+      <c r="A27" s="101"/>
+      <c r="B27" s="102"/>
+      <c r="C27" s="102"/>
+      <c r="D27" s="102"/>
+      <c r="E27" s="102"/>
+      <c r="F27" s="102"/>
+      <c r="G27" s="103"/>
       <c r="H27" s="84"/>
       <c r="I27" s="85"/>
       <c r="J27" s="85"/>
@@ -66418,57 +66428,57 @@
       <c r="M27" s="85"/>
       <c r="N27" s="86"/>
       <c r="O27" s="84"/>
-      <c r="P27" s="87"/>
-      <c r="Q27" s="87"/>
-      <c r="R27" s="87"/>
-      <c r="S27" s="87"/>
-      <c r="T27" s="87"/>
-      <c r="U27" s="87"/>
-      <c r="V27" s="87"/>
-      <c r="W27" s="87"/>
-      <c r="X27" s="87"/>
-      <c r="Y27" s="87"/>
-      <c r="Z27" s="87"/>
-      <c r="AA27" s="87"/>
-      <c r="AB27" s="87"/>
-      <c r="AC27" s="87"/>
-      <c r="AD27" s="87"/>
-      <c r="AE27" s="87"/>
-      <c r="AF27" s="87"/>
-      <c r="AG27" s="87"/>
-      <c r="AH27" s="87"/>
-      <c r="AI27" s="87"/>
-      <c r="AJ27" s="87"/>
-      <c r="AK27" s="87"/>
-      <c r="AL27" s="87"/>
-      <c r="AM27" s="87"/>
-      <c r="AN27" s="87"/>
-      <c r="AO27" s="87"/>
-      <c r="AP27" s="88"/>
-      <c r="AQ27" s="92"/>
-      <c r="AR27" s="87"/>
-      <c r="AS27" s="87"/>
-      <c r="AT27" s="87"/>
-      <c r="AU27" s="87"/>
-      <c r="AV27" s="87"/>
-      <c r="AW27" s="87"/>
-      <c r="AX27" s="87"/>
-      <c r="AY27" s="87"/>
-      <c r="AZ27" s="87"/>
-      <c r="BA27" s="87"/>
-      <c r="BB27" s="87"/>
-      <c r="BC27" s="87"/>
-      <c r="BD27" s="87"/>
-      <c r="BE27" s="93"/>
+      <c r="P27" s="82"/>
+      <c r="Q27" s="82"/>
+      <c r="R27" s="82"/>
+      <c r="S27" s="82"/>
+      <c r="T27" s="82"/>
+      <c r="U27" s="82"/>
+      <c r="V27" s="82"/>
+      <c r="W27" s="82"/>
+      <c r="X27" s="82"/>
+      <c r="Y27" s="82"/>
+      <c r="Z27" s="82"/>
+      <c r="AA27" s="82"/>
+      <c r="AB27" s="82"/>
+      <c r="AC27" s="82"/>
+      <c r="AD27" s="82"/>
+      <c r="AE27" s="82"/>
+      <c r="AF27" s="82"/>
+      <c r="AG27" s="82"/>
+      <c r="AH27" s="82"/>
+      <c r="AI27" s="82"/>
+      <c r="AJ27" s="82"/>
+      <c r="AK27" s="82"/>
+      <c r="AL27" s="82"/>
+      <c r="AM27" s="82"/>
+      <c r="AN27" s="82"/>
+      <c r="AO27" s="82"/>
+      <c r="AP27" s="90"/>
+      <c r="AQ27" s="81"/>
+      <c r="AR27" s="82"/>
+      <c r="AS27" s="82"/>
+      <c r="AT27" s="82"/>
+      <c r="AU27" s="82"/>
+      <c r="AV27" s="82"/>
+      <c r="AW27" s="82"/>
+      <c r="AX27" s="82"/>
+      <c r="AY27" s="82"/>
+      <c r="AZ27" s="82"/>
+      <c r="BA27" s="82"/>
+      <c r="BB27" s="82"/>
+      <c r="BC27" s="82"/>
+      <c r="BD27" s="82"/>
+      <c r="BE27" s="83"/>
     </row>
     <row r="28" spans="1:57" ht="15" customHeight="1">
-      <c r="A28" s="81"/>
-      <c r="B28" s="82"/>
-      <c r="C28" s="82"/>
-      <c r="D28" s="82"/>
-      <c r="E28" s="82"/>
-      <c r="F28" s="82"/>
-      <c r="G28" s="83"/>
+      <c r="A28" s="101"/>
+      <c r="B28" s="102"/>
+      <c r="C28" s="102"/>
+      <c r="D28" s="102"/>
+      <c r="E28" s="102"/>
+      <c r="F28" s="102"/>
+      <c r="G28" s="103"/>
       <c r="H28" s="84"/>
       <c r="I28" s="85"/>
       <c r="J28" s="85"/>
@@ -66477,57 +66487,57 @@
       <c r="M28" s="85"/>
       <c r="N28" s="86"/>
       <c r="O28" s="84"/>
-      <c r="P28" s="87"/>
-      <c r="Q28" s="87"/>
-      <c r="R28" s="87"/>
-      <c r="S28" s="87"/>
-      <c r="T28" s="87"/>
-      <c r="U28" s="87"/>
-      <c r="V28" s="87"/>
-      <c r="W28" s="87"/>
-      <c r="X28" s="87"/>
-      <c r="Y28" s="87"/>
-      <c r="Z28" s="87"/>
-      <c r="AA28" s="87"/>
-      <c r="AB28" s="87"/>
-      <c r="AC28" s="87"/>
-      <c r="AD28" s="87"/>
-      <c r="AE28" s="87"/>
-      <c r="AF28" s="87"/>
-      <c r="AG28" s="87"/>
-      <c r="AH28" s="87"/>
-      <c r="AI28" s="87"/>
-      <c r="AJ28" s="87"/>
-      <c r="AK28" s="87"/>
-      <c r="AL28" s="87"/>
-      <c r="AM28" s="87"/>
-      <c r="AN28" s="87"/>
-      <c r="AO28" s="87"/>
-      <c r="AP28" s="88"/>
-      <c r="AQ28" s="92"/>
-      <c r="AR28" s="87"/>
-      <c r="AS28" s="87"/>
-      <c r="AT28" s="87"/>
-      <c r="AU28" s="87"/>
-      <c r="AV28" s="87"/>
-      <c r="AW28" s="87"/>
-      <c r="AX28" s="87"/>
-      <c r="AY28" s="87"/>
-      <c r="AZ28" s="87"/>
-      <c r="BA28" s="87"/>
-      <c r="BB28" s="87"/>
-      <c r="BC28" s="87"/>
-      <c r="BD28" s="87"/>
-      <c r="BE28" s="93"/>
+      <c r="P28" s="82"/>
+      <c r="Q28" s="82"/>
+      <c r="R28" s="82"/>
+      <c r="S28" s="82"/>
+      <c r="T28" s="82"/>
+      <c r="U28" s="82"/>
+      <c r="V28" s="82"/>
+      <c r="W28" s="82"/>
+      <c r="X28" s="82"/>
+      <c r="Y28" s="82"/>
+      <c r="Z28" s="82"/>
+      <c r="AA28" s="82"/>
+      <c r="AB28" s="82"/>
+      <c r="AC28" s="82"/>
+      <c r="AD28" s="82"/>
+      <c r="AE28" s="82"/>
+      <c r="AF28" s="82"/>
+      <c r="AG28" s="82"/>
+      <c r="AH28" s="82"/>
+      <c r="AI28" s="82"/>
+      <c r="AJ28" s="82"/>
+      <c r="AK28" s="82"/>
+      <c r="AL28" s="82"/>
+      <c r="AM28" s="82"/>
+      <c r="AN28" s="82"/>
+      <c r="AO28" s="82"/>
+      <c r="AP28" s="90"/>
+      <c r="AQ28" s="81"/>
+      <c r="AR28" s="82"/>
+      <c r="AS28" s="82"/>
+      <c r="AT28" s="82"/>
+      <c r="AU28" s="82"/>
+      <c r="AV28" s="82"/>
+      <c r="AW28" s="82"/>
+      <c r="AX28" s="82"/>
+      <c r="AY28" s="82"/>
+      <c r="AZ28" s="82"/>
+      <c r="BA28" s="82"/>
+      <c r="BB28" s="82"/>
+      <c r="BC28" s="82"/>
+      <c r="BD28" s="82"/>
+      <c r="BE28" s="83"/>
     </row>
     <row r="29" spans="1:57" ht="15" customHeight="1">
-      <c r="A29" s="81"/>
-      <c r="B29" s="82"/>
-      <c r="C29" s="82"/>
-      <c r="D29" s="82"/>
-      <c r="E29" s="82"/>
-      <c r="F29" s="82"/>
-      <c r="G29" s="83"/>
+      <c r="A29" s="101"/>
+      <c r="B29" s="102"/>
+      <c r="C29" s="102"/>
+      <c r="D29" s="102"/>
+      <c r="E29" s="102"/>
+      <c r="F29" s="102"/>
+      <c r="G29" s="103"/>
       <c r="H29" s="84"/>
       <c r="I29" s="85"/>
       <c r="J29" s="85"/>
@@ -66536,57 +66546,57 @@
       <c r="M29" s="85"/>
       <c r="N29" s="86"/>
       <c r="O29" s="84"/>
-      <c r="P29" s="87"/>
-      <c r="Q29" s="87"/>
-      <c r="R29" s="87"/>
-      <c r="S29" s="87"/>
-      <c r="T29" s="87"/>
-      <c r="U29" s="87"/>
-      <c r="V29" s="87"/>
-      <c r="W29" s="87"/>
-      <c r="X29" s="87"/>
-      <c r="Y29" s="87"/>
-      <c r="Z29" s="87"/>
-      <c r="AA29" s="87"/>
-      <c r="AB29" s="87"/>
-      <c r="AC29" s="87"/>
-      <c r="AD29" s="87"/>
-      <c r="AE29" s="87"/>
-      <c r="AF29" s="87"/>
-      <c r="AG29" s="87"/>
-      <c r="AH29" s="87"/>
-      <c r="AI29" s="87"/>
-      <c r="AJ29" s="87"/>
-      <c r="AK29" s="87"/>
-      <c r="AL29" s="87"/>
-      <c r="AM29" s="87"/>
-      <c r="AN29" s="87"/>
-      <c r="AO29" s="87"/>
-      <c r="AP29" s="88"/>
-      <c r="AQ29" s="92"/>
-      <c r="AR29" s="87"/>
-      <c r="AS29" s="87"/>
-      <c r="AT29" s="87"/>
-      <c r="AU29" s="87"/>
-      <c r="AV29" s="87"/>
-      <c r="AW29" s="87"/>
-      <c r="AX29" s="87"/>
-      <c r="AY29" s="87"/>
-      <c r="AZ29" s="87"/>
-      <c r="BA29" s="87"/>
-      <c r="BB29" s="87"/>
-      <c r="BC29" s="87"/>
-      <c r="BD29" s="87"/>
-      <c r="BE29" s="93"/>
+      <c r="P29" s="82"/>
+      <c r="Q29" s="82"/>
+      <c r="R29" s="82"/>
+      <c r="S29" s="82"/>
+      <c r="T29" s="82"/>
+      <c r="U29" s="82"/>
+      <c r="V29" s="82"/>
+      <c r="W29" s="82"/>
+      <c r="X29" s="82"/>
+      <c r="Y29" s="82"/>
+      <c r="Z29" s="82"/>
+      <c r="AA29" s="82"/>
+      <c r="AB29" s="82"/>
+      <c r="AC29" s="82"/>
+      <c r="AD29" s="82"/>
+      <c r="AE29" s="82"/>
+      <c r="AF29" s="82"/>
+      <c r="AG29" s="82"/>
+      <c r="AH29" s="82"/>
+      <c r="AI29" s="82"/>
+      <c r="AJ29" s="82"/>
+      <c r="AK29" s="82"/>
+      <c r="AL29" s="82"/>
+      <c r="AM29" s="82"/>
+      <c r="AN29" s="82"/>
+      <c r="AO29" s="82"/>
+      <c r="AP29" s="90"/>
+      <c r="AQ29" s="81"/>
+      <c r="AR29" s="82"/>
+      <c r="AS29" s="82"/>
+      <c r="AT29" s="82"/>
+      <c r="AU29" s="82"/>
+      <c r="AV29" s="82"/>
+      <c r="AW29" s="82"/>
+      <c r="AX29" s="82"/>
+      <c r="AY29" s="82"/>
+      <c r="AZ29" s="82"/>
+      <c r="BA29" s="82"/>
+      <c r="BB29" s="82"/>
+      <c r="BC29" s="82"/>
+      <c r="BD29" s="82"/>
+      <c r="BE29" s="83"/>
     </row>
     <row r="30" spans="1:57" ht="15" customHeight="1">
-      <c r="A30" s="81"/>
-      <c r="B30" s="82"/>
-      <c r="C30" s="82"/>
-      <c r="D30" s="82"/>
-      <c r="E30" s="82"/>
-      <c r="F30" s="82"/>
-      <c r="G30" s="83"/>
+      <c r="A30" s="101"/>
+      <c r="B30" s="102"/>
+      <c r="C30" s="102"/>
+      <c r="D30" s="102"/>
+      <c r="E30" s="102"/>
+      <c r="F30" s="102"/>
+      <c r="G30" s="103"/>
       <c r="H30" s="84"/>
       <c r="I30" s="85"/>
       <c r="J30" s="85"/>
@@ -66595,57 +66605,57 @@
       <c r="M30" s="85"/>
       <c r="N30" s="86"/>
       <c r="O30" s="84"/>
-      <c r="P30" s="87"/>
-      <c r="Q30" s="87"/>
-      <c r="R30" s="87"/>
-      <c r="S30" s="87"/>
-      <c r="T30" s="87"/>
-      <c r="U30" s="87"/>
-      <c r="V30" s="87"/>
-      <c r="W30" s="87"/>
-      <c r="X30" s="87"/>
-      <c r="Y30" s="87"/>
-      <c r="Z30" s="87"/>
-      <c r="AA30" s="87"/>
-      <c r="AB30" s="87"/>
-      <c r="AC30" s="87"/>
-      <c r="AD30" s="87"/>
-      <c r="AE30" s="87"/>
-      <c r="AF30" s="87"/>
-      <c r="AG30" s="87"/>
-      <c r="AH30" s="87"/>
-      <c r="AI30" s="87"/>
-      <c r="AJ30" s="87"/>
-      <c r="AK30" s="87"/>
-      <c r="AL30" s="87"/>
-      <c r="AM30" s="87"/>
-      <c r="AN30" s="87"/>
-      <c r="AO30" s="87"/>
-      <c r="AP30" s="88"/>
-      <c r="AQ30" s="92"/>
-      <c r="AR30" s="87"/>
-      <c r="AS30" s="87"/>
-      <c r="AT30" s="87"/>
-      <c r="AU30" s="87"/>
-      <c r="AV30" s="87"/>
-      <c r="AW30" s="87"/>
-      <c r="AX30" s="87"/>
-      <c r="AY30" s="87"/>
-      <c r="AZ30" s="87"/>
-      <c r="BA30" s="87"/>
-      <c r="BB30" s="87"/>
-      <c r="BC30" s="87"/>
-      <c r="BD30" s="87"/>
-      <c r="BE30" s="93"/>
+      <c r="P30" s="82"/>
+      <c r="Q30" s="82"/>
+      <c r="R30" s="82"/>
+      <c r="S30" s="82"/>
+      <c r="T30" s="82"/>
+      <c r="U30" s="82"/>
+      <c r="V30" s="82"/>
+      <c r="W30" s="82"/>
+      <c r="X30" s="82"/>
+      <c r="Y30" s="82"/>
+      <c r="Z30" s="82"/>
+      <c r="AA30" s="82"/>
+      <c r="AB30" s="82"/>
+      <c r="AC30" s="82"/>
+      <c r="AD30" s="82"/>
+      <c r="AE30" s="82"/>
+      <c r="AF30" s="82"/>
+      <c r="AG30" s="82"/>
+      <c r="AH30" s="82"/>
+      <c r="AI30" s="82"/>
+      <c r="AJ30" s="82"/>
+      <c r="AK30" s="82"/>
+      <c r="AL30" s="82"/>
+      <c r="AM30" s="82"/>
+      <c r="AN30" s="82"/>
+      <c r="AO30" s="82"/>
+      <c r="AP30" s="90"/>
+      <c r="AQ30" s="81"/>
+      <c r="AR30" s="82"/>
+      <c r="AS30" s="82"/>
+      <c r="AT30" s="82"/>
+      <c r="AU30" s="82"/>
+      <c r="AV30" s="82"/>
+      <c r="AW30" s="82"/>
+      <c r="AX30" s="82"/>
+      <c r="AY30" s="82"/>
+      <c r="AZ30" s="82"/>
+      <c r="BA30" s="82"/>
+      <c r="BB30" s="82"/>
+      <c r="BC30" s="82"/>
+      <c r="BD30" s="82"/>
+      <c r="BE30" s="83"/>
     </row>
     <row r="31" spans="1:57" ht="15" customHeight="1">
-      <c r="A31" s="81"/>
-      <c r="B31" s="82"/>
-      <c r="C31" s="82"/>
-      <c r="D31" s="82"/>
-      <c r="E31" s="82"/>
-      <c r="F31" s="82"/>
-      <c r="G31" s="83"/>
+      <c r="A31" s="101"/>
+      <c r="B31" s="102"/>
+      <c r="C31" s="102"/>
+      <c r="D31" s="102"/>
+      <c r="E31" s="102"/>
+      <c r="F31" s="102"/>
+      <c r="G31" s="103"/>
       <c r="H31" s="84"/>
       <c r="I31" s="85"/>
       <c r="J31" s="85"/>
@@ -66654,57 +66664,57 @@
       <c r="M31" s="85"/>
       <c r="N31" s="86"/>
       <c r="O31" s="84"/>
-      <c r="P31" s="87"/>
-      <c r="Q31" s="87"/>
-      <c r="R31" s="87"/>
-      <c r="S31" s="87"/>
-      <c r="T31" s="87"/>
-      <c r="U31" s="87"/>
-      <c r="V31" s="87"/>
-      <c r="W31" s="87"/>
-      <c r="X31" s="87"/>
-      <c r="Y31" s="87"/>
-      <c r="Z31" s="87"/>
-      <c r="AA31" s="87"/>
-      <c r="AB31" s="87"/>
-      <c r="AC31" s="87"/>
-      <c r="AD31" s="87"/>
-      <c r="AE31" s="87"/>
-      <c r="AF31" s="87"/>
-      <c r="AG31" s="87"/>
-      <c r="AH31" s="87"/>
-      <c r="AI31" s="87"/>
-      <c r="AJ31" s="87"/>
-      <c r="AK31" s="87"/>
-      <c r="AL31" s="87"/>
-      <c r="AM31" s="87"/>
-      <c r="AN31" s="87"/>
-      <c r="AO31" s="87"/>
-      <c r="AP31" s="88"/>
-      <c r="AQ31" s="92"/>
-      <c r="AR31" s="87"/>
-      <c r="AS31" s="87"/>
-      <c r="AT31" s="87"/>
-      <c r="AU31" s="87"/>
-      <c r="AV31" s="87"/>
-      <c r="AW31" s="87"/>
-      <c r="AX31" s="87"/>
-      <c r="AY31" s="87"/>
-      <c r="AZ31" s="87"/>
-      <c r="BA31" s="87"/>
-      <c r="BB31" s="87"/>
-      <c r="BC31" s="87"/>
-      <c r="BD31" s="87"/>
-      <c r="BE31" s="93"/>
+      <c r="P31" s="82"/>
+      <c r="Q31" s="82"/>
+      <c r="R31" s="82"/>
+      <c r="S31" s="82"/>
+      <c r="T31" s="82"/>
+      <c r="U31" s="82"/>
+      <c r="V31" s="82"/>
+      <c r="W31" s="82"/>
+      <c r="X31" s="82"/>
+      <c r="Y31" s="82"/>
+      <c r="Z31" s="82"/>
+      <c r="AA31" s="82"/>
+      <c r="AB31" s="82"/>
+      <c r="AC31" s="82"/>
+      <c r="AD31" s="82"/>
+      <c r="AE31" s="82"/>
+      <c r="AF31" s="82"/>
+      <c r="AG31" s="82"/>
+      <c r="AH31" s="82"/>
+      <c r="AI31" s="82"/>
+      <c r="AJ31" s="82"/>
+      <c r="AK31" s="82"/>
+      <c r="AL31" s="82"/>
+      <c r="AM31" s="82"/>
+      <c r="AN31" s="82"/>
+      <c r="AO31" s="82"/>
+      <c r="AP31" s="90"/>
+      <c r="AQ31" s="81"/>
+      <c r="AR31" s="82"/>
+      <c r="AS31" s="82"/>
+      <c r="AT31" s="82"/>
+      <c r="AU31" s="82"/>
+      <c r="AV31" s="82"/>
+      <c r="AW31" s="82"/>
+      <c r="AX31" s="82"/>
+      <c r="AY31" s="82"/>
+      <c r="AZ31" s="82"/>
+      <c r="BA31" s="82"/>
+      <c r="BB31" s="82"/>
+      <c r="BC31" s="82"/>
+      <c r="BD31" s="82"/>
+      <c r="BE31" s="83"/>
     </row>
     <row r="32" spans="1:57" ht="15" customHeight="1">
-      <c r="A32" s="81"/>
-      <c r="B32" s="82"/>
-      <c r="C32" s="82"/>
-      <c r="D32" s="82"/>
-      <c r="E32" s="82"/>
-      <c r="F32" s="82"/>
-      <c r="G32" s="83"/>
+      <c r="A32" s="101"/>
+      <c r="B32" s="102"/>
+      <c r="C32" s="102"/>
+      <c r="D32" s="102"/>
+      <c r="E32" s="102"/>
+      <c r="F32" s="102"/>
+      <c r="G32" s="103"/>
       <c r="H32" s="84"/>
       <c r="I32" s="85"/>
       <c r="J32" s="85"/>
@@ -66713,57 +66723,57 @@
       <c r="M32" s="85"/>
       <c r="N32" s="86"/>
       <c r="O32" s="84"/>
-      <c r="P32" s="87"/>
-      <c r="Q32" s="87"/>
-      <c r="R32" s="87"/>
-      <c r="S32" s="87"/>
-      <c r="T32" s="87"/>
-      <c r="U32" s="87"/>
-      <c r="V32" s="87"/>
-      <c r="W32" s="87"/>
-      <c r="X32" s="87"/>
-      <c r="Y32" s="87"/>
-      <c r="Z32" s="87"/>
-      <c r="AA32" s="87"/>
-      <c r="AB32" s="87"/>
-      <c r="AC32" s="87"/>
-      <c r="AD32" s="87"/>
-      <c r="AE32" s="87"/>
-      <c r="AF32" s="87"/>
-      <c r="AG32" s="87"/>
-      <c r="AH32" s="87"/>
-      <c r="AI32" s="87"/>
-      <c r="AJ32" s="87"/>
-      <c r="AK32" s="87"/>
-      <c r="AL32" s="87"/>
-      <c r="AM32" s="87"/>
-      <c r="AN32" s="87"/>
-      <c r="AO32" s="87"/>
-      <c r="AP32" s="88"/>
-      <c r="AQ32" s="92"/>
-      <c r="AR32" s="87"/>
-      <c r="AS32" s="87"/>
-      <c r="AT32" s="87"/>
-      <c r="AU32" s="87"/>
-      <c r="AV32" s="87"/>
-      <c r="AW32" s="87"/>
-      <c r="AX32" s="87"/>
-      <c r="AY32" s="87"/>
-      <c r="AZ32" s="87"/>
-      <c r="BA32" s="87"/>
-      <c r="BB32" s="87"/>
-      <c r="BC32" s="87"/>
-      <c r="BD32" s="87"/>
-      <c r="BE32" s="93"/>
+      <c r="P32" s="82"/>
+      <c r="Q32" s="82"/>
+      <c r="R32" s="82"/>
+      <c r="S32" s="82"/>
+      <c r="T32" s="82"/>
+      <c r="U32" s="82"/>
+      <c r="V32" s="82"/>
+      <c r="W32" s="82"/>
+      <c r="X32" s="82"/>
+      <c r="Y32" s="82"/>
+      <c r="Z32" s="82"/>
+      <c r="AA32" s="82"/>
+      <c r="AB32" s="82"/>
+      <c r="AC32" s="82"/>
+      <c r="AD32" s="82"/>
+      <c r="AE32" s="82"/>
+      <c r="AF32" s="82"/>
+      <c r="AG32" s="82"/>
+      <c r="AH32" s="82"/>
+      <c r="AI32" s="82"/>
+      <c r="AJ32" s="82"/>
+      <c r="AK32" s="82"/>
+      <c r="AL32" s="82"/>
+      <c r="AM32" s="82"/>
+      <c r="AN32" s="82"/>
+      <c r="AO32" s="82"/>
+      <c r="AP32" s="90"/>
+      <c r="AQ32" s="81"/>
+      <c r="AR32" s="82"/>
+      <c r="AS32" s="82"/>
+      <c r="AT32" s="82"/>
+      <c r="AU32" s="82"/>
+      <c r="AV32" s="82"/>
+      <c r="AW32" s="82"/>
+      <c r="AX32" s="82"/>
+      <c r="AY32" s="82"/>
+      <c r="AZ32" s="82"/>
+      <c r="BA32" s="82"/>
+      <c r="BB32" s="82"/>
+      <c r="BC32" s="82"/>
+      <c r="BD32" s="82"/>
+      <c r="BE32" s="83"/>
     </row>
     <row r="33" spans="1:57" ht="15" customHeight="1">
-      <c r="A33" s="81"/>
-      <c r="B33" s="82"/>
-      <c r="C33" s="82"/>
-      <c r="D33" s="82"/>
-      <c r="E33" s="82"/>
-      <c r="F33" s="82"/>
-      <c r="G33" s="83"/>
+      <c r="A33" s="101"/>
+      <c r="B33" s="102"/>
+      <c r="C33" s="102"/>
+      <c r="D33" s="102"/>
+      <c r="E33" s="102"/>
+      <c r="F33" s="102"/>
+      <c r="G33" s="103"/>
       <c r="H33" s="84"/>
       <c r="I33" s="85"/>
       <c r="J33" s="85"/>
@@ -66772,57 +66782,57 @@
       <c r="M33" s="85"/>
       <c r="N33" s="86"/>
       <c r="O33" s="84"/>
-      <c r="P33" s="87"/>
-      <c r="Q33" s="87"/>
-      <c r="R33" s="87"/>
-      <c r="S33" s="87"/>
-      <c r="T33" s="87"/>
-      <c r="U33" s="87"/>
-      <c r="V33" s="87"/>
-      <c r="W33" s="87"/>
-      <c r="X33" s="87"/>
-      <c r="Y33" s="87"/>
-      <c r="Z33" s="87"/>
-      <c r="AA33" s="87"/>
-      <c r="AB33" s="87"/>
-      <c r="AC33" s="87"/>
-      <c r="AD33" s="87"/>
-      <c r="AE33" s="87"/>
-      <c r="AF33" s="87"/>
-      <c r="AG33" s="87"/>
-      <c r="AH33" s="87"/>
-      <c r="AI33" s="87"/>
-      <c r="AJ33" s="87"/>
-      <c r="AK33" s="87"/>
-      <c r="AL33" s="87"/>
-      <c r="AM33" s="87"/>
-      <c r="AN33" s="87"/>
-      <c r="AO33" s="87"/>
-      <c r="AP33" s="88"/>
-      <c r="AQ33" s="92"/>
-      <c r="AR33" s="87"/>
-      <c r="AS33" s="87"/>
-      <c r="AT33" s="87"/>
-      <c r="AU33" s="87"/>
-      <c r="AV33" s="87"/>
-      <c r="AW33" s="87"/>
-      <c r="AX33" s="87"/>
-      <c r="AY33" s="87"/>
-      <c r="AZ33" s="87"/>
-      <c r="BA33" s="87"/>
-      <c r="BB33" s="87"/>
-      <c r="BC33" s="87"/>
-      <c r="BD33" s="87"/>
-      <c r="BE33" s="93"/>
+      <c r="P33" s="82"/>
+      <c r="Q33" s="82"/>
+      <c r="R33" s="82"/>
+      <c r="S33" s="82"/>
+      <c r="T33" s="82"/>
+      <c r="U33" s="82"/>
+      <c r="V33" s="82"/>
+      <c r="W33" s="82"/>
+      <c r="X33" s="82"/>
+      <c r="Y33" s="82"/>
+      <c r="Z33" s="82"/>
+      <c r="AA33" s="82"/>
+      <c r="AB33" s="82"/>
+      <c r="AC33" s="82"/>
+      <c r="AD33" s="82"/>
+      <c r="AE33" s="82"/>
+      <c r="AF33" s="82"/>
+      <c r="AG33" s="82"/>
+      <c r="AH33" s="82"/>
+      <c r="AI33" s="82"/>
+      <c r="AJ33" s="82"/>
+      <c r="AK33" s="82"/>
+      <c r="AL33" s="82"/>
+      <c r="AM33" s="82"/>
+      <c r="AN33" s="82"/>
+      <c r="AO33" s="82"/>
+      <c r="AP33" s="90"/>
+      <c r="AQ33" s="81"/>
+      <c r="AR33" s="82"/>
+      <c r="AS33" s="82"/>
+      <c r="AT33" s="82"/>
+      <c r="AU33" s="82"/>
+      <c r="AV33" s="82"/>
+      <c r="AW33" s="82"/>
+      <c r="AX33" s="82"/>
+      <c r="AY33" s="82"/>
+      <c r="AZ33" s="82"/>
+      <c r="BA33" s="82"/>
+      <c r="BB33" s="82"/>
+      <c r="BC33" s="82"/>
+      <c r="BD33" s="82"/>
+      <c r="BE33" s="83"/>
     </row>
     <row r="34" spans="1:57" ht="15" customHeight="1">
-      <c r="A34" s="81"/>
-      <c r="B34" s="82"/>
-      <c r="C34" s="82"/>
-      <c r="D34" s="82"/>
-      <c r="E34" s="82"/>
-      <c r="F34" s="82"/>
-      <c r="G34" s="83"/>
+      <c r="A34" s="101"/>
+      <c r="B34" s="102"/>
+      <c r="C34" s="102"/>
+      <c r="D34" s="102"/>
+      <c r="E34" s="102"/>
+      <c r="F34" s="102"/>
+      <c r="G34" s="103"/>
       <c r="H34" s="84"/>
       <c r="I34" s="85"/>
       <c r="J34" s="85"/>
@@ -66831,110 +66841,219 @@
       <c r="M34" s="85"/>
       <c r="N34" s="86"/>
       <c r="O34" s="84"/>
-      <c r="P34" s="87"/>
-      <c r="Q34" s="87"/>
-      <c r="R34" s="87"/>
-      <c r="S34" s="87"/>
-      <c r="T34" s="87"/>
-      <c r="U34" s="87"/>
-      <c r="V34" s="87"/>
-      <c r="W34" s="87"/>
-      <c r="X34" s="87"/>
-      <c r="Y34" s="87"/>
-      <c r="Z34" s="87"/>
-      <c r="AA34" s="87"/>
-      <c r="AB34" s="87"/>
-      <c r="AC34" s="87"/>
-      <c r="AD34" s="87"/>
-      <c r="AE34" s="87"/>
-      <c r="AF34" s="87"/>
-      <c r="AG34" s="87"/>
-      <c r="AH34" s="87"/>
-      <c r="AI34" s="87"/>
-      <c r="AJ34" s="87"/>
-      <c r="AK34" s="87"/>
-      <c r="AL34" s="87"/>
-      <c r="AM34" s="87"/>
-      <c r="AN34" s="87"/>
-      <c r="AO34" s="87"/>
-      <c r="AP34" s="88"/>
-      <c r="AQ34" s="92"/>
-      <c r="AR34" s="87"/>
-      <c r="AS34" s="87"/>
-      <c r="AT34" s="87"/>
-      <c r="AU34" s="87"/>
-      <c r="AV34" s="87"/>
-      <c r="AW34" s="87"/>
-      <c r="AX34" s="87"/>
-      <c r="AY34" s="87"/>
-      <c r="AZ34" s="87"/>
-      <c r="BA34" s="87"/>
-      <c r="BB34" s="87"/>
-      <c r="BC34" s="87"/>
-      <c r="BD34" s="87"/>
-      <c r="BE34" s="93"/>
+      <c r="P34" s="82"/>
+      <c r="Q34" s="82"/>
+      <c r="R34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="82"/>
+      <c r="V34" s="82"/>
+      <c r="W34" s="82"/>
+      <c r="X34" s="82"/>
+      <c r="Y34" s="82"/>
+      <c r="Z34" s="82"/>
+      <c r="AA34" s="82"/>
+      <c r="AB34" s="82"/>
+      <c r="AC34" s="82"/>
+      <c r="AD34" s="82"/>
+      <c r="AE34" s="82"/>
+      <c r="AF34" s="82"/>
+      <c r="AG34" s="82"/>
+      <c r="AH34" s="82"/>
+      <c r="AI34" s="82"/>
+      <c r="AJ34" s="82"/>
+      <c r="AK34" s="82"/>
+      <c r="AL34" s="82"/>
+      <c r="AM34" s="82"/>
+      <c r="AN34" s="82"/>
+      <c r="AO34" s="82"/>
+      <c r="AP34" s="90"/>
+      <c r="AQ34" s="81"/>
+      <c r="AR34" s="82"/>
+      <c r="AS34" s="82"/>
+      <c r="AT34" s="82"/>
+      <c r="AU34" s="82"/>
+      <c r="AV34" s="82"/>
+      <c r="AW34" s="82"/>
+      <c r="AX34" s="82"/>
+      <c r="AY34" s="82"/>
+      <c r="AZ34" s="82"/>
+      <c r="BA34" s="82"/>
+      <c r="BB34" s="82"/>
+      <c r="BC34" s="82"/>
+      <c r="BD34" s="82"/>
+      <c r="BE34" s="83"/>
     </row>
     <row r="35" spans="1:57" ht="15" customHeight="1" thickBot="1">
-      <c r="A35" s="98"/>
-      <c r="B35" s="99"/>
-      <c r="C35" s="99"/>
-      <c r="D35" s="99"/>
-      <c r="E35" s="99"/>
-      <c r="F35" s="99"/>
-      <c r="G35" s="100"/>
-      <c r="H35" s="94"/>
-      <c r="I35" s="95"/>
-      <c r="J35" s="95"/>
-      <c r="K35" s="95"/>
-      <c r="L35" s="95"/>
-      <c r="M35" s="95"/>
-      <c r="N35" s="96"/>
-      <c r="O35" s="94"/>
-      <c r="P35" s="90"/>
-      <c r="Q35" s="90"/>
-      <c r="R35" s="90"/>
-      <c r="S35" s="90"/>
-      <c r="T35" s="90"/>
-      <c r="U35" s="90"/>
-      <c r="V35" s="90"/>
-      <c r="W35" s="90"/>
-      <c r="X35" s="90"/>
-      <c r="Y35" s="90"/>
-      <c r="Z35" s="90"/>
-      <c r="AA35" s="90"/>
-      <c r="AB35" s="90"/>
-      <c r="AC35" s="90"/>
-      <c r="AD35" s="90"/>
-      <c r="AE35" s="90"/>
-      <c r="AF35" s="90"/>
-      <c r="AG35" s="90"/>
-      <c r="AH35" s="90"/>
-      <c r="AI35" s="90"/>
-      <c r="AJ35" s="90"/>
-      <c r="AK35" s="90"/>
-      <c r="AL35" s="90"/>
-      <c r="AM35" s="90"/>
-      <c r="AN35" s="90"/>
-      <c r="AO35" s="90"/>
-      <c r="AP35" s="97"/>
-      <c r="AQ35" s="89"/>
-      <c r="AR35" s="90"/>
-      <c r="AS35" s="90"/>
-      <c r="AT35" s="90"/>
-      <c r="AU35" s="90"/>
-      <c r="AV35" s="90"/>
-      <c r="AW35" s="90"/>
-      <c r="AX35" s="90"/>
-      <c r="AY35" s="90"/>
-      <c r="AZ35" s="90"/>
-      <c r="BA35" s="90"/>
-      <c r="BB35" s="90"/>
-      <c r="BC35" s="90"/>
-      <c r="BD35" s="90"/>
-      <c r="BE35" s="91"/>
+      <c r="A35" s="122"/>
+      <c r="B35" s="123"/>
+      <c r="C35" s="123"/>
+      <c r="D35" s="123"/>
+      <c r="E35" s="123"/>
+      <c r="F35" s="123"/>
+      <c r="G35" s="124"/>
+      <c r="H35" s="128"/>
+      <c r="I35" s="129"/>
+      <c r="J35" s="129"/>
+      <c r="K35" s="129"/>
+      <c r="L35" s="129"/>
+      <c r="M35" s="129"/>
+      <c r="N35" s="130"/>
+      <c r="O35" s="128"/>
+      <c r="P35" s="126"/>
+      <c r="Q35" s="126"/>
+      <c r="R35" s="126"/>
+      <c r="S35" s="126"/>
+      <c r="T35" s="126"/>
+      <c r="U35" s="126"/>
+      <c r="V35" s="126"/>
+      <c r="W35" s="126"/>
+      <c r="X35" s="126"/>
+      <c r="Y35" s="126"/>
+      <c r="Z35" s="126"/>
+      <c r="AA35" s="126"/>
+      <c r="AB35" s="126"/>
+      <c r="AC35" s="126"/>
+      <c r="AD35" s="126"/>
+      <c r="AE35" s="126"/>
+      <c r="AF35" s="126"/>
+      <c r="AG35" s="126"/>
+      <c r="AH35" s="126"/>
+      <c r="AI35" s="126"/>
+      <c r="AJ35" s="126"/>
+      <c r="AK35" s="126"/>
+      <c r="AL35" s="126"/>
+      <c r="AM35" s="126"/>
+      <c r="AN35" s="126"/>
+      <c r="AO35" s="126"/>
+      <c r="AP35" s="131"/>
+      <c r="AQ35" s="125"/>
+      <c r="AR35" s="126"/>
+      <c r="AS35" s="126"/>
+      <c r="AT35" s="126"/>
+      <c r="AU35" s="126"/>
+      <c r="AV35" s="126"/>
+      <c r="AW35" s="126"/>
+      <c r="AX35" s="126"/>
+      <c r="AY35" s="126"/>
+      <c r="AZ35" s="126"/>
+      <c r="BA35" s="126"/>
+      <c r="BB35" s="126"/>
+      <c r="BC35" s="126"/>
+      <c r="BD35" s="126"/>
+      <c r="BE35" s="127"/>
     </row>
   </sheetData>
   <mergeCells count="133">
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="O19:AP19"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AQ35:BE35"/>
+    <mergeCell ref="AQ33:BE33"/>
+    <mergeCell ref="AQ34:BE34"/>
+    <mergeCell ref="AQ32:BE32"/>
+    <mergeCell ref="AQ31:BE31"/>
+    <mergeCell ref="O27:AP27"/>
+    <mergeCell ref="AQ27:BE27"/>
+    <mergeCell ref="H30:N30"/>
+    <mergeCell ref="O30:AP30"/>
+    <mergeCell ref="AQ30:BE30"/>
+    <mergeCell ref="AQ28:BE28"/>
+    <mergeCell ref="H28:N28"/>
+    <mergeCell ref="O28:AP28"/>
+    <mergeCell ref="H35:N35"/>
+    <mergeCell ref="O35:AP35"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="H33:N33"/>
+    <mergeCell ref="H34:N34"/>
+    <mergeCell ref="O34:AP34"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="O33:AP33"/>
+    <mergeCell ref="O32:AP32"/>
+    <mergeCell ref="H31:N31"/>
+    <mergeCell ref="O31:AP31"/>
+    <mergeCell ref="H27:N27"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="H32:N32"/>
+    <mergeCell ref="H29:N29"/>
+    <mergeCell ref="O29:AP29"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:AP20"/>
+    <mergeCell ref="AQ17:BE17"/>
+    <mergeCell ref="H26:N26"/>
+    <mergeCell ref="O26:AP26"/>
+    <mergeCell ref="AQ26:BE26"/>
+    <mergeCell ref="AQ19:BE19"/>
+    <mergeCell ref="H25:N25"/>
+    <mergeCell ref="H24:N24"/>
+    <mergeCell ref="O24:AP24"/>
+    <mergeCell ref="O25:AP25"/>
+    <mergeCell ref="AQ25:BE25"/>
+    <mergeCell ref="H22:N22"/>
+    <mergeCell ref="AQ24:BE24"/>
+    <mergeCell ref="H23:N23"/>
+    <mergeCell ref="O23:AP23"/>
+    <mergeCell ref="AQ23:BE23"/>
+    <mergeCell ref="AQ20:BE20"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:AP21"/>
+    <mergeCell ref="AQ18:BE18"/>
+    <mergeCell ref="AQ21:BE21"/>
+    <mergeCell ref="O22:AP22"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="H4:N4"/>
+    <mergeCell ref="O4:AP4"/>
+    <mergeCell ref="AQ4:BE4"/>
+    <mergeCell ref="H13:N13"/>
+    <mergeCell ref="O13:AP13"/>
+    <mergeCell ref="AQ13:BE13"/>
+    <mergeCell ref="H14:N14"/>
+    <mergeCell ref="O14:AP14"/>
+    <mergeCell ref="AQ14:BE14"/>
+    <mergeCell ref="AQ16:BE16"/>
+    <mergeCell ref="H15:N15"/>
+    <mergeCell ref="O18:AP18"/>
+    <mergeCell ref="H9:N9"/>
+    <mergeCell ref="O9:AP9"/>
+    <mergeCell ref="AQ9:BE9"/>
+    <mergeCell ref="H10:N10"/>
+    <mergeCell ref="O10:AP10"/>
+    <mergeCell ref="AQ10:BE10"/>
+    <mergeCell ref="H11:N11"/>
+    <mergeCell ref="O11:AP11"/>
+    <mergeCell ref="AQ11:BE11"/>
+    <mergeCell ref="H16:N16"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="O15:AP15"/>
+    <mergeCell ref="A1:BE1"/>
+    <mergeCell ref="H3:N3"/>
+    <mergeCell ref="O3:AP3"/>
+    <mergeCell ref="AQ3:BE3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
     <mergeCell ref="AQ22:BE22"/>
     <mergeCell ref="AQ29:BE29"/>
     <mergeCell ref="H17:N17"/>
@@ -66959,115 +67078,6 @@
     <mergeCell ref="A9:G9"/>
     <mergeCell ref="O16:AP16"/>
     <mergeCell ref="O17:AP17"/>
-    <mergeCell ref="A1:BE1"/>
-    <mergeCell ref="H3:N3"/>
-    <mergeCell ref="O3:AP3"/>
-    <mergeCell ref="AQ3:BE3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="O15:AP15"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="H4:N4"/>
-    <mergeCell ref="O4:AP4"/>
-    <mergeCell ref="AQ4:BE4"/>
-    <mergeCell ref="H13:N13"/>
-    <mergeCell ref="O13:AP13"/>
-    <mergeCell ref="AQ13:BE13"/>
-    <mergeCell ref="H14:N14"/>
-    <mergeCell ref="O14:AP14"/>
-    <mergeCell ref="AQ14:BE14"/>
-    <mergeCell ref="AQ16:BE16"/>
-    <mergeCell ref="H15:N15"/>
-    <mergeCell ref="O18:AP18"/>
-    <mergeCell ref="H9:N9"/>
-    <mergeCell ref="O9:AP9"/>
-    <mergeCell ref="AQ9:BE9"/>
-    <mergeCell ref="H10:N10"/>
-    <mergeCell ref="O10:AP10"/>
-    <mergeCell ref="AQ10:BE10"/>
-    <mergeCell ref="H11:N11"/>
-    <mergeCell ref="O11:AP11"/>
-    <mergeCell ref="AQ11:BE11"/>
-    <mergeCell ref="H16:N16"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:AP20"/>
-    <mergeCell ref="AQ17:BE17"/>
-    <mergeCell ref="H26:N26"/>
-    <mergeCell ref="O26:AP26"/>
-    <mergeCell ref="AQ26:BE26"/>
-    <mergeCell ref="AQ19:BE19"/>
-    <mergeCell ref="H25:N25"/>
-    <mergeCell ref="H24:N24"/>
-    <mergeCell ref="O24:AP24"/>
-    <mergeCell ref="O25:AP25"/>
-    <mergeCell ref="AQ25:BE25"/>
-    <mergeCell ref="H22:N22"/>
-    <mergeCell ref="AQ24:BE24"/>
-    <mergeCell ref="H23:N23"/>
-    <mergeCell ref="O23:AP23"/>
-    <mergeCell ref="AQ23:BE23"/>
-    <mergeCell ref="AQ20:BE20"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:AP21"/>
-    <mergeCell ref="AQ18:BE18"/>
-    <mergeCell ref="AQ21:BE21"/>
-    <mergeCell ref="O22:AP22"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="H33:N33"/>
-    <mergeCell ref="H34:N34"/>
-    <mergeCell ref="O34:AP34"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="O33:AP33"/>
-    <mergeCell ref="O32:AP32"/>
-    <mergeCell ref="H31:N31"/>
-    <mergeCell ref="O31:AP31"/>
-    <mergeCell ref="H27:N27"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="H32:N32"/>
-    <mergeCell ref="H29:N29"/>
-    <mergeCell ref="O29:AP29"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="O19:AP19"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="AQ35:BE35"/>
-    <mergeCell ref="AQ33:BE33"/>
-    <mergeCell ref="AQ34:BE34"/>
-    <mergeCell ref="AQ32:BE32"/>
-    <mergeCell ref="AQ31:BE31"/>
-    <mergeCell ref="O27:AP27"/>
-    <mergeCell ref="AQ27:BE27"/>
-    <mergeCell ref="H30:N30"/>
-    <mergeCell ref="O30:AP30"/>
-    <mergeCell ref="AQ30:BE30"/>
-    <mergeCell ref="AQ28:BE28"/>
-    <mergeCell ref="H28:N28"/>
-    <mergeCell ref="O28:AP28"/>
-    <mergeCell ref="H35:N35"/>
-    <mergeCell ref="O35:AP35"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A20:G20"/>
   </mergeCells>
   <phoneticPr fontId="5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>

--- a/development/MS/spec/MSBB/Panel/MSBBP1210_SloReg.xlsx
+++ b/development/MS/spec/MSBB/Panel/MSBBP1210_SloReg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\mcframeDEV\development\MS\spec\MSBB\Panel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD1919B-6703-476B-BCB1-C1CA0AA99650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0280817E-DAD2-42EA-8203-BA5B56634C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-3330" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9147" uniqueCount="2371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9148" uniqueCount="2373">
   <si>
     <t>検索</t>
     <rPh sb="0" eb="2">
@@ -9683,9 +9683,6 @@
     <t>F</t>
   </si>
   <si>
-    <t>sales_cond</t>
-  </si>
-  <si>
     <t>sales_cond_nm</t>
   </si>
   <si>
@@ -10053,6 +10050,15 @@
   </si>
   <si>
     <t>MS.MSUAP0010.SlsCondTyp</t>
+  </si>
+  <si>
+    <t>dlv_day_week_typ</t>
+  </si>
+  <si>
+    <t>sls_cond_typ</t>
+  </si>
+  <si>
+    <t>sls_cond_typ_nm</t>
   </si>
 </sst>
 </file>
@@ -13436,7 +13442,7 @@
       <c r="O16" s="25"/>
       <c r="P16" s="25"/>
       <c r="Q16" s="25" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
       <c r="R16" s="25"/>
       <c r="S16" s="25" t="s">
@@ -14273,7 +14279,7 @@
       <c r="B28" s="27"/>
       <c r="C28" s="27"/>
       <c r="D28" s="27" t="s">
-        <v>2363</v>
+        <v>2362</v>
       </c>
       <c r="E28" s="28" t="s">
         <v>1858</v>
@@ -14298,16 +14304,16 @@
       <c r="O28" s="27"/>
       <c r="P28" s="27"/>
       <c r="Q28" s="27" t="s">
-        <v>2367</v>
+        <v>2366</v>
       </c>
       <c r="R28" s="27"/>
       <c r="S28" s="27" t="s">
-        <v>2362</v>
+        <v>2361</v>
       </c>
       <c r="T28" s="27"/>
       <c r="U28" s="27"/>
       <c r="V28" s="27" t="s">
-        <v>2368</v>
+        <v>2367</v>
       </c>
       <c r="W28" s="27"/>
       <c r="X28" s="27"/>
@@ -20261,7 +20267,7 @@
       <c r="B104" s="25"/>
       <c r="C104" s="25"/>
       <c r="D104" s="25" t="s">
-        <v>2364</v>
+        <v>2363</v>
       </c>
       <c r="E104" s="37" t="s">
         <v>1908</v>
@@ -20270,7 +20276,7 @@
         <v>179</v>
       </c>
       <c r="G104" s="25" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
       <c r="H104" s="25"/>
       <c r="I104" s="25" t="s">
@@ -24923,7 +24929,7 @@
       <c r="B157" s="25"/>
       <c r="C157" s="25"/>
       <c r="D157" s="25" t="s">
-        <v>2347</v>
+        <v>2346</v>
       </c>
       <c r="E157" s="37" t="s">
         <v>1951</v>
@@ -24932,7 +24938,7 @@
         <v>881</v>
       </c>
       <c r="G157" s="25" t="s">
-        <v>2307</v>
+        <v>2306</v>
       </c>
       <c r="H157" s="25"/>
       <c r="I157" s="25" t="s">
@@ -31040,7 +31046,7 @@
       </c>
       <c r="J224" s="25"/>
       <c r="K224" s="25" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="L224" s="25"/>
       <c r="M224" s="25"/>
@@ -31889,7 +31895,7 @@
       <c r="B234" s="50"/>
       <c r="C234" s="50"/>
       <c r="D234" s="25" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
       <c r="E234" s="50"/>
       <c r="F234" s="50"/>
@@ -32443,7 +32449,7 @@
       </c>
       <c r="R241" s="25"/>
       <c r="S241" s="25" t="s">
-        <v>381</v>
+        <v>2370</v>
       </c>
       <c r="T241" s="25"/>
       <c r="U241" s="25" t="s">
@@ -32585,7 +32591,7 @@
       <c r="G243" s="61"/>
       <c r="H243" s="61"/>
       <c r="I243" s="61" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
       <c r="J243" s="61"/>
       <c r="K243" s="61" t="s">
@@ -32637,24 +32643,24 @@
       <c r="B244" s="61"/>
       <c r="C244" s="61"/>
       <c r="D244" s="61" t="s">
-        <v>2247</v>
+        <v>2371</v>
       </c>
       <c r="E244" s="62" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
       <c r="F244" s="61" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="G244" s="61" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="H244" s="61"/>
       <c r="I244" s="61" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="J244" s="61"/>
       <c r="K244" s="61" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="L244" s="61"/>
       <c r="M244" s="61"/>
@@ -32662,14 +32668,16 @@
       <c r="O244" s="61"/>
       <c r="P244" s="61"/>
       <c r="Q244" s="61" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="R244" s="61"/>
       <c r="S244" s="61" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="T244" s="61"/>
-      <c r="U244" s="61"/>
+      <c r="U244" s="61" t="s">
+        <v>2372</v>
+      </c>
       <c r="V244" s="61"/>
       <c r="W244" s="61"/>
       <c r="X244" s="61"/>
@@ -32706,18 +32714,18 @@
       <c r="B245" s="61"/>
       <c r="C245" s="61"/>
       <c r="D245" s="61" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="E245" s="62" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="F245" s="61" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="G245" s="61"/>
       <c r="H245" s="61"/>
       <c r="I245" s="61" t="s">
-        <v>2255</v>
+        <v>2254</v>
       </c>
       <c r="J245" s="61"/>
       <c r="K245" s="61" t="s">
@@ -32769,20 +32777,20 @@
       <c r="B246" s="61"/>
       <c r="C246" s="61"/>
       <c r="D246" s="61" t="s">
+        <v>2256</v>
+      </c>
+      <c r="E246" s="62" t="s">
+        <v>2258</v>
+      </c>
+      <c r="F246" s="61" t="s">
         <v>2257</v>
-      </c>
-      <c r="E246" s="62" t="s">
-        <v>2259</v>
-      </c>
-      <c r="F246" s="61" t="s">
-        <v>2258</v>
       </c>
       <c r="G246" s="61" t="s">
         <v>2</v>
       </c>
       <c r="H246" s="61"/>
       <c r="I246" s="61" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="J246" s="61"/>
       <c r="K246" s="61" t="s">
@@ -32834,11 +32842,11 @@
       <c r="B247" s="61"/>
       <c r="C247" s="61"/>
       <c r="D247" s="61" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="E247" s="62"/>
       <c r="F247" s="61" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="G247" s="61" t="s">
         <v>2</v>
@@ -32897,18 +32905,18 @@
       <c r="B248" s="61"/>
       <c r="C248" s="61"/>
       <c r="D248" s="61" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="E248" s="62"/>
       <c r="F248" s="61" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="G248" s="61" t="s">
         <v>2</v>
       </c>
       <c r="H248" s="61"/>
       <c r="I248" s="61" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="J248" s="61"/>
       <c r="K248" s="61" t="s">
@@ -32960,18 +32968,18 @@
       <c r="B249" s="61"/>
       <c r="C249" s="61"/>
       <c r="D249" s="61" t="s">
-        <v>2276</v>
+        <v>2275</v>
       </c>
       <c r="E249" s="62"/>
       <c r="F249" s="61" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="G249" s="61" t="s">
         <v>2</v>
       </c>
       <c r="H249" s="61"/>
       <c r="I249" s="61" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="J249" s="61"/>
       <c r="K249" s="61" t="s">
@@ -33023,11 +33031,11 @@
       <c r="B250" s="61"/>
       <c r="C250" s="61"/>
       <c r="D250" s="61" t="s">
-        <v>2277</v>
+        <v>2276</v>
       </c>
       <c r="E250" s="62"/>
       <c r="F250" s="61" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="G250" s="61" t="s">
         <v>2</v>
@@ -33086,21 +33094,21 @@
       <c r="B251" s="63"/>
       <c r="C251" s="63"/>
       <c r="D251" s="63" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
       <c r="E251" s="50"/>
       <c r="F251" s="50"/>
       <c r="G251" s="50"/>
       <c r="H251" s="50"/>
       <c r="I251" s="50" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="J251" s="50"/>
       <c r="K251" s="50" t="s">
+        <v>2288</v>
+      </c>
+      <c r="L251" s="50" t="s">
         <v>2289</v>
-      </c>
-      <c r="L251" s="50" t="s">
-        <v>2290</v>
       </c>
       <c r="M251" s="50"/>
       <c r="N251" s="50"/>
@@ -33150,22 +33158,22 @@
       <c r="B252" s="61"/>
       <c r="C252" s="61"/>
       <c r="D252" s="61" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="E252" s="62"/>
       <c r="F252" s="61" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="G252" s="61" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="H252" s="61"/>
       <c r="I252" s="61" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
       <c r="J252" s="61"/>
       <c r="K252" s="61" t="s">
-        <v>2292</v>
+        <v>2291</v>
       </c>
       <c r="L252" s="61"/>
       <c r="M252" s="61"/>
@@ -33173,7 +33181,7 @@
       <c r="O252" s="61"/>
       <c r="P252" s="61"/>
       <c r="Q252" s="61" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
       <c r="R252" s="61"/>
       <c r="S252" s="61"/>
@@ -33218,7 +33226,7 @@
       </c>
       <c r="AM252" s="33"/>
       <c r="AN252" s="33" t="s">
-        <v>2278</v>
+        <v>2277</v>
       </c>
       <c r="AO252" s="33"/>
       <c r="AP252" s="33"/>
@@ -33239,20 +33247,20 @@
       <c r="B253" s="61"/>
       <c r="C253" s="61"/>
       <c r="D253" s="61" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
       <c r="E253" s="62"/>
       <c r="F253" s="61" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="G253" s="61"/>
       <c r="H253" s="61"/>
       <c r="I253" s="61" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
       <c r="J253" s="61"/>
       <c r="K253" s="61" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="L253" s="61"/>
       <c r="M253" s="61"/>
@@ -33260,7 +33268,7 @@
       <c r="O253" s="61"/>
       <c r="P253" s="61"/>
       <c r="Q253" s="61" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="R253" s="61"/>
       <c r="S253" s="61"/>
@@ -33305,7 +33313,7 @@
       </c>
       <c r="AM253" s="33"/>
       <c r="AN253" s="33" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="AO253" s="33"/>
       <c r="AP253" s="33"/>
@@ -33326,20 +33334,20 @@
       <c r="B254" s="61"/>
       <c r="C254" s="61"/>
       <c r="D254" s="61" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="E254" s="62"/>
       <c r="F254" s="61" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="G254" s="61"/>
       <c r="H254" s="61"/>
       <c r="I254" s="61" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
       <c r="J254" s="61"/>
       <c r="K254" s="61" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="L254" s="61"/>
       <c r="M254" s="61"/>
@@ -33347,7 +33355,7 @@
       <c r="O254" s="61"/>
       <c r="P254" s="61"/>
       <c r="Q254" s="61" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="R254" s="61"/>
       <c r="S254" s="61"/>
@@ -33392,7 +33400,7 @@
       </c>
       <c r="AM254" s="33"/>
       <c r="AN254" s="33" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="AO254" s="33"/>
       <c r="AP254" s="33"/>
@@ -33413,20 +33421,20 @@
       <c r="B255" s="61"/>
       <c r="C255" s="61"/>
       <c r="D255" s="61" t="s">
-        <v>2283</v>
+        <v>2282</v>
       </c>
       <c r="E255" s="62"/>
       <c r="F255" s="61" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="G255" s="61"/>
       <c r="H255" s="61"/>
       <c r="I255" s="61" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
       <c r="J255" s="61"/>
       <c r="K255" s="61" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="L255" s="61"/>
       <c r="M255" s="61"/>
@@ -33434,7 +33442,7 @@
       <c r="O255" s="61"/>
       <c r="P255" s="61"/>
       <c r="Q255" s="61" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="R255" s="61"/>
       <c r="S255" s="61"/>
@@ -33479,7 +33487,7 @@
       </c>
       <c r="AM255" s="33"/>
       <c r="AN255" s="33" t="s">
-        <v>2301</v>
+        <v>2300</v>
       </c>
       <c r="AO255" s="33"/>
       <c r="AP255" s="33"/>
@@ -33500,22 +33508,22 @@
       <c r="B256" s="61"/>
       <c r="C256" s="61"/>
       <c r="D256" s="61" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="E256" s="62"/>
       <c r="F256" s="61" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="G256" s="61" t="s">
         <v>2</v>
       </c>
       <c r="H256" s="61"/>
       <c r="I256" s="61" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
       <c r="J256" s="61"/>
       <c r="K256" s="61" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
       <c r="L256" s="61"/>
       <c r="M256" s="61"/>
@@ -33566,7 +33574,7 @@
       </c>
       <c r="AM256" s="33"/>
       <c r="AN256" s="33" t="s">
-        <v>2302</v>
+        <v>2301</v>
       </c>
       <c r="AO256" s="33"/>
       <c r="AP256" s="33"/>
@@ -33587,18 +33595,18 @@
       <c r="B257" s="61"/>
       <c r="C257" s="61"/>
       <c r="D257" s="61" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
       <c r="E257" s="62"/>
       <c r="F257" s="61" t="s">
+        <v>2315</v>
+      </c>
+      <c r="G257" s="61" t="s">
         <v>2316</v>
-      </c>
-      <c r="G257" s="61" t="s">
-        <v>2317</v>
       </c>
       <c r="H257" s="61"/>
       <c r="I257" s="61" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="J257" s="61"/>
       <c r="K257" s="61" t="s">
@@ -33650,18 +33658,18 @@
       <c r="B258" s="61"/>
       <c r="C258" s="61"/>
       <c r="D258" s="61" t="s">
-        <v>2285</v>
+        <v>2284</v>
       </c>
       <c r="E258" s="62"/>
       <c r="F258" s="61" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="G258" s="61" t="s">
         <v>2</v>
       </c>
       <c r="H258" s="61"/>
       <c r="I258" s="61" t="s">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="J258" s="61"/>
       <c r="K258" s="61" t="s">
@@ -33713,18 +33721,18 @@
       <c r="B259" s="61"/>
       <c r="C259" s="61"/>
       <c r="D259" s="61" t="s">
-        <v>2286</v>
+        <v>2285</v>
       </c>
       <c r="E259" s="62"/>
       <c r="F259" s="61" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="G259" s="61" t="s">
         <v>2</v>
       </c>
       <c r="H259" s="61"/>
       <c r="I259" s="61" t="s">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="J259" s="61"/>
       <c r="K259" s="61" t="s">
@@ -33776,28 +33784,28 @@
       <c r="B260" s="25"/>
       <c r="C260" s="25"/>
       <c r="D260" s="61" t="s">
-        <v>2319</v>
+        <v>2318</v>
       </c>
       <c r="E260" s="64" t="s">
+        <v>2308</v>
+      </c>
+      <c r="F260" s="65" t="s">
         <v>2309</v>
-      </c>
-      <c r="F260" s="65" t="s">
-        <v>2310</v>
       </c>
       <c r="G260" s="65" t="s">
         <v>2</v>
       </c>
       <c r="H260" s="65"/>
       <c r="I260" s="65" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="J260" s="65"/>
       <c r="K260" s="65" t="s">
-        <v>2311</v>
+        <v>2310</v>
       </c>
       <c r="L260" s="65"/>
       <c r="M260" s="65" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
       <c r="N260" s="25"/>
       <c r="O260" s="25"/>
@@ -33836,7 +33844,7 @@
         <v>1814</v>
       </c>
       <c r="AI260" s="25" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
       <c r="AJ260" s="25" t="s">
         <v>1805</v>
@@ -33865,18 +33873,18 @@
       <c r="B261" s="61"/>
       <c r="C261" s="61"/>
       <c r="D261" s="61" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
       <c r="E261" s="62"/>
       <c r="F261" s="61" t="s">
-        <v>2275</v>
+        <v>2274</v>
       </c>
       <c r="G261" s="61" t="s">
         <v>2</v>
       </c>
       <c r="H261" s="61"/>
       <c r="I261" s="61" t="s">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="J261" s="61"/>
       <c r="K261" s="61" t="s">
@@ -33928,28 +33936,28 @@
       <c r="B262" s="25"/>
       <c r="C262" s="25"/>
       <c r="D262" s="61" t="s">
+        <v>2319</v>
+      </c>
+      <c r="E262" s="64" t="s">
+        <v>2321</v>
+      </c>
+      <c r="F262" s="65" t="s">
         <v>2320</v>
-      </c>
-      <c r="E262" s="64" t="s">
-        <v>2322</v>
-      </c>
-      <c r="F262" s="65" t="s">
-        <v>2321</v>
       </c>
       <c r="G262" s="65" t="s">
         <v>2</v>
       </c>
       <c r="H262" s="65"/>
       <c r="I262" s="65" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="J262" s="65"/>
       <c r="K262" s="65" t="s">
-        <v>2311</v>
+        <v>2310</v>
       </c>
       <c r="L262" s="65"/>
       <c r="M262" s="65" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
       <c r="N262" s="25"/>
       <c r="O262" s="25"/>
@@ -33988,7 +33996,7 @@
         <v>1814</v>
       </c>
       <c r="AI262" s="25" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
       <c r="AJ262" s="25" t="s">
         <v>1805</v>
@@ -35225,18 +35233,18 @@
       <c r="O279" s="25"/>
       <c r="P279" s="25"/>
       <c r="Q279" s="25" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="R279" s="25"/>
       <c r="S279" s="25" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="T279" s="25"/>
       <c r="U279" s="25" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="V279" s="25" t="s">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="W279" s="25" t="s">
         <v>1597</v>
@@ -35306,11 +35314,11 @@
       </c>
       <c r="R280" s="25"/>
       <c r="S280" s="25" t="s">
-        <v>2350</v>
+        <v>2349</v>
       </c>
       <c r="T280" s="25"/>
       <c r="U280" s="25" t="s">
-        <v>2354</v>
+        <v>2353</v>
       </c>
       <c r="V280" s="25" t="s">
         <v>1598</v>
@@ -35383,11 +35391,11 @@
       </c>
       <c r="R281" s="25"/>
       <c r="S281" s="25" t="s">
-        <v>2351</v>
+        <v>2350</v>
       </c>
       <c r="T281" s="25"/>
       <c r="U281" s="25" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
       <c r="V281" s="25" t="s">
         <v>1600</v>
@@ -35460,11 +35468,11 @@
       </c>
       <c r="R282" s="25"/>
       <c r="S282" s="25" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="T282" s="25"/>
       <c r="U282" s="25" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="V282" s="25" t="s">
         <v>1602</v>
@@ -35767,7 +35775,7 @@
       <c r="B286" s="25"/>
       <c r="C286" s="25"/>
       <c r="D286" s="25" t="s">
-        <v>2323</v>
+        <v>2322</v>
       </c>
       <c r="E286" s="37" t="s">
         <v>2041</v>
@@ -38052,20 +38060,20 @@
       <c r="B311" s="61"/>
       <c r="C311" s="61"/>
       <c r="D311" s="61" t="s">
+        <v>2333</v>
+      </c>
+      <c r="E311" s="62" t="s">
         <v>2334</v>
       </c>
-      <c r="E311" s="62" t="s">
-        <v>2335</v>
-      </c>
       <c r="F311" s="61" t="s">
-        <v>2324</v>
+        <v>2323</v>
       </c>
       <c r="G311" s="61" t="s">
-        <v>2324</v>
+        <v>2323</v>
       </c>
       <c r="H311" s="61"/>
       <c r="I311" s="61" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="J311" s="61"/>
       <c r="K311" s="61" t="s">
@@ -38139,20 +38147,20 @@
       <c r="B312" s="61"/>
       <c r="C312" s="61"/>
       <c r="D312" s="61" t="s">
-        <v>2331</v>
+        <v>2330</v>
       </c>
       <c r="E312" s="62" t="s">
+        <v>2335</v>
+      </c>
+      <c r="F312" s="61" t="s">
         <v>2336</v>
       </c>
-      <c r="F312" s="61" t="s">
-        <v>2337</v>
-      </c>
       <c r="G312" s="61" t="s">
-        <v>2325</v>
+        <v>2324</v>
       </c>
       <c r="H312" s="61"/>
       <c r="I312" s="61" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="J312" s="61"/>
       <c r="K312" s="61" t="s">
@@ -38226,20 +38234,20 @@
       <c r="B313" s="61"/>
       <c r="C313" s="61"/>
       <c r="D313" s="61" t="s">
-        <v>2330</v>
+        <v>2329</v>
       </c>
       <c r="E313" s="62" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="F313" s="61" t="s">
-        <v>2326</v>
+        <v>2325</v>
       </c>
       <c r="G313" s="61" t="s">
-        <v>2326</v>
+        <v>2325</v>
       </c>
       <c r="H313" s="61"/>
       <c r="I313" s="61" t="s">
-        <v>2329</v>
+        <v>2328</v>
       </c>
       <c r="J313" s="61"/>
       <c r="K313" s="61" t="s">
@@ -38313,20 +38321,20 @@
       <c r="B314" s="61"/>
       <c r="C314" s="61"/>
       <c r="D314" s="61" t="s">
+        <v>2342</v>
+      </c>
+      <c r="E314" s="62" t="s">
         <v>2343</v>
       </c>
-      <c r="E314" s="62" t="s">
+      <c r="F314" s="61" t="s">
         <v>2344</v>
       </c>
-      <c r="F314" s="61" t="s">
-        <v>2345</v>
-      </c>
       <c r="G314" s="61" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
       <c r="H314" s="61"/>
       <c r="I314" s="61" t="s">
-        <v>2346</v>
+        <v>2345</v>
       </c>
       <c r="J314" s="61"/>
       <c r="K314" s="61" t="s">
@@ -38400,20 +38408,20 @@
       <c r="B315" s="61"/>
       <c r="C315" s="61"/>
       <c r="D315" s="61" t="s">
-        <v>2333</v>
+        <v>2332</v>
       </c>
       <c r="E315" s="62" t="s">
+        <v>2337</v>
+      </c>
+      <c r="F315" s="61" t="s">
         <v>2338</v>
       </c>
-      <c r="F315" s="61" t="s">
-        <v>2339</v>
-      </c>
       <c r="G315" s="61" t="s">
-        <v>2327</v>
+        <v>2326</v>
       </c>
       <c r="H315" s="61"/>
       <c r="I315" s="61" t="s">
-        <v>2332</v>
+        <v>2331</v>
       </c>
       <c r="J315" s="61"/>
       <c r="K315" s="61" t="s">
@@ -39311,7 +39319,7 @@
       <c r="B325" s="25"/>
       <c r="C325" s="25"/>
       <c r="D325" s="25" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
       <c r="E325" s="37" t="s">
         <v>2072</v>
@@ -39389,11 +39397,11 @@
       <c r="E326" s="64"/>
       <c r="F326" s="65"/>
       <c r="G326" s="65" t="s">
-        <v>2361</v>
+        <v>2360</v>
       </c>
       <c r="H326" s="65"/>
       <c r="I326" s="65" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="J326" s="65"/>
       <c r="K326" s="65" t="s">
@@ -39453,16 +39461,16 @@
       <c r="B327" s="65"/>
       <c r="C327" s="65"/>
       <c r="D327" s="65" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="E327" s="64"/>
       <c r="F327" s="65"/>
       <c r="G327" s="65" t="s">
-        <v>2358</v>
+        <v>2357</v>
       </c>
       <c r="H327" s="65"/>
       <c r="I327" s="65" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="J327" s="65"/>
       <c r="K327" s="65" t="s">
@@ -39540,16 +39548,16 @@
       <c r="B328" s="65"/>
       <c r="C328" s="65"/>
       <c r="D328" s="65" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="E328" s="64"/>
       <c r="F328" s="65"/>
       <c r="G328" s="65" t="s">
-        <v>2360</v>
+        <v>2359</v>
       </c>
       <c r="H328" s="65"/>
       <c r="I328" s="65" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="J328" s="65"/>
       <c r="K328" s="65" t="s">

--- a/development/MS/spec/MSBB/Panel/MSBBP1210_SloReg.xlsx
+++ b/development/MS/spec/MSBB/Panel/MSBBP1210_SloReg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\mcframeDEV\development\MS\spec\MSBB\Panel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0280817E-DAD2-42EA-8203-BA5B56634C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B66E7E-7363-4693-AA4D-49B3EB50A3CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-3330" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,7 @@
     <sheet name="来歴" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32532,7 +32533,7 @@
       </c>
       <c r="J242" s="61"/>
       <c r="K242" s="61" t="s">
-        <v>2246</v>
+        <v>2368</v>
       </c>
       <c r="L242" s="61"/>
       <c r="M242" s="61"/>

--- a/development/MS/spec/MSBB/Panel/MSBBP1210_SloReg.xlsx
+++ b/development/MS/spec/MSBB/Panel/MSBBP1210_SloReg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\mcframeDEV\development\MS\spec\MSBB\Panel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B66E7E-7363-4693-AA4D-49B3EB50A3CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1F4ECD3-545D-4153-980A-79BDC39F73F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-3330" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,6 @@
     <sheet name="来歴" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9148" uniqueCount="2373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9151" uniqueCount="2375">
   <si>
     <t>検索</t>
     <rPh sb="0" eb="2">
@@ -10060,6 +10059,12 @@
   </si>
   <si>
     <t>sls_cond_typ_nm</t>
+  </si>
+  <si>
+    <t>MS.MSUAP0010.FreeRsnTyp</t>
+  </si>
+  <si>
+    <t>free_rsn_typ_nm</t>
   </si>
 </sst>
 </file>
@@ -11475,14 +11480,14 @@
     <xf numFmtId="0" fontId="27" fillId="24" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -11493,7 +11498,79 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11502,8 +11579,29 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -11534,99 +11632,6 @@
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -32540,11 +32545,17 @@
       <c r="N242" s="61"/>
       <c r="O242" s="61"/>
       <c r="P242" s="61"/>
-      <c r="Q242" s="61"/>
+      <c r="Q242" s="61" t="s">
+        <v>2373</v>
+      </c>
       <c r="R242" s="61"/>
-      <c r="S242" s="61"/>
+      <c r="S242" s="61" t="s">
+        <v>2244</v>
+      </c>
       <c r="T242" s="61"/>
-      <c r="U242" s="61"/>
+      <c r="U242" s="61" t="s">
+        <v>2374</v>
+      </c>
       <c r="V242" s="61"/>
       <c r="W242" s="61"/>
       <c r="X242" s="61"/>
@@ -64867,65 +64878,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:57" ht="38.25" customHeight="1" thickBot="1">
-      <c r="A1" s="104" t="s">
+      <c r="A1" s="108" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
-      <c r="G1" s="105"/>
-      <c r="H1" s="105"/>
-      <c r="I1" s="105"/>
-      <c r="J1" s="105"/>
-      <c r="K1" s="105"/>
-      <c r="L1" s="105"/>
-      <c r="M1" s="105"/>
-      <c r="N1" s="105"/>
-      <c r="O1" s="105"/>
-      <c r="P1" s="105"/>
-      <c r="Q1" s="105"/>
-      <c r="R1" s="105"/>
-      <c r="S1" s="105"/>
-      <c r="T1" s="105"/>
-      <c r="U1" s="105"/>
-      <c r="V1" s="105"/>
-      <c r="W1" s="105"/>
-      <c r="X1" s="105"/>
-      <c r="Y1" s="105"/>
-      <c r="Z1" s="105"/>
-      <c r="AA1" s="105"/>
-      <c r="AB1" s="105"/>
-      <c r="AC1" s="105"/>
-      <c r="AD1" s="105"/>
-      <c r="AE1" s="105"/>
-      <c r="AF1" s="105"/>
-      <c r="AG1" s="105"/>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="106"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
+      <c r="V1" s="109"/>
+      <c r="W1" s="109"/>
+      <c r="X1" s="109"/>
+      <c r="Y1" s="109"/>
+      <c r="Z1" s="109"/>
+      <c r="AA1" s="109"/>
+      <c r="AB1" s="109"/>
+      <c r="AC1" s="109"/>
+      <c r="AD1" s="109"/>
+      <c r="AE1" s="109"/>
+      <c r="AF1" s="109"/>
+      <c r="AG1" s="109"/>
+      <c r="AH1" s="109"/>
+      <c r="AI1" s="109"/>
+      <c r="AJ1" s="109"/>
+      <c r="AK1" s="109"/>
+      <c r="AL1" s="109"/>
+      <c r="AM1" s="109"/>
+      <c r="AN1" s="109"/>
+      <c r="AO1" s="109"/>
+      <c r="AP1" s="109"/>
+      <c r="AQ1" s="109"/>
+      <c r="AR1" s="109"/>
+      <c r="AS1" s="109"/>
+      <c r="AT1" s="109"/>
+      <c r="AU1" s="109"/>
+      <c r="AV1" s="109"/>
+      <c r="AW1" s="109"/>
+      <c r="AX1" s="109"/>
+      <c r="AY1" s="109"/>
+      <c r="AZ1" s="109"/>
+      <c r="BA1" s="109"/>
+      <c r="BB1" s="109"/>
+      <c r="BC1" s="109"/>
+      <c r="BD1" s="109"/>
+      <c r="BE1" s="110"/>
     </row>
     <row r="2" spans="1:57" ht="12" customHeight="1" thickBot="1">
       <c r="A2" s="14"/>
@@ -64972,145 +64983,145 @@
       <c r="AP2" s="14"/>
     </row>
     <row r="3" spans="1:57" ht="15" customHeight="1" thickBot="1">
-      <c r="A3" s="87" t="s">
+      <c r="A3" s="121" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="107" t="s">
+      <c r="B3" s="112"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="112"/>
+      <c r="F3" s="112"/>
+      <c r="G3" s="113"/>
+      <c r="H3" s="111" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88"/>
-      <c r="M3" s="88"/>
-      <c r="N3" s="89"/>
-      <c r="O3" s="107" t="s">
+      <c r="I3" s="112"/>
+      <c r="J3" s="112"/>
+      <c r="K3" s="112"/>
+      <c r="L3" s="112"/>
+      <c r="M3" s="112"/>
+      <c r="N3" s="113"/>
+      <c r="O3" s="111" t="s">
         <v>9</v>
       </c>
-      <c r="P3" s="108"/>
-      <c r="Q3" s="108"/>
-      <c r="R3" s="108"/>
-      <c r="S3" s="108"/>
-      <c r="T3" s="108"/>
-      <c r="U3" s="108"/>
-      <c r="V3" s="108"/>
-      <c r="W3" s="108"/>
-      <c r="X3" s="108"/>
-      <c r="Y3" s="108"/>
-      <c r="Z3" s="108"/>
-      <c r="AA3" s="108"/>
-      <c r="AB3" s="108"/>
-      <c r="AC3" s="108"/>
-      <c r="AD3" s="108"/>
-      <c r="AE3" s="108"/>
-      <c r="AF3" s="108"/>
-      <c r="AG3" s="108"/>
-      <c r="AH3" s="108"/>
-      <c r="AI3" s="108"/>
-      <c r="AJ3" s="108"/>
-      <c r="AK3" s="108"/>
-      <c r="AL3" s="108"/>
-      <c r="AM3" s="108"/>
-      <c r="AN3" s="108"/>
-      <c r="AO3" s="108"/>
-      <c r="AP3" s="109"/>
-      <c r="AQ3" s="107" t="s">
+      <c r="P3" s="114"/>
+      <c r="Q3" s="114"/>
+      <c r="R3" s="114"/>
+      <c r="S3" s="114"/>
+      <c r="T3" s="114"/>
+      <c r="U3" s="114"/>
+      <c r="V3" s="114"/>
+      <c r="W3" s="114"/>
+      <c r="X3" s="114"/>
+      <c r="Y3" s="114"/>
+      <c r="Z3" s="114"/>
+      <c r="AA3" s="114"/>
+      <c r="AB3" s="114"/>
+      <c r="AC3" s="114"/>
+      <c r="AD3" s="114"/>
+      <c r="AE3" s="114"/>
+      <c r="AF3" s="114"/>
+      <c r="AG3" s="114"/>
+      <c r="AH3" s="114"/>
+      <c r="AI3" s="114"/>
+      <c r="AJ3" s="114"/>
+      <c r="AK3" s="114"/>
+      <c r="AL3" s="114"/>
+      <c r="AM3" s="114"/>
+      <c r="AN3" s="114"/>
+      <c r="AO3" s="114"/>
+      <c r="AP3" s="115"/>
+      <c r="AQ3" s="111" t="s">
         <v>10</v>
       </c>
-      <c r="AR3" s="110"/>
-      <c r="AS3" s="110"/>
-      <c r="AT3" s="110"/>
-      <c r="AU3" s="110"/>
-      <c r="AV3" s="110"/>
-      <c r="AW3" s="110"/>
-      <c r="AX3" s="110"/>
-      <c r="AY3" s="110"/>
-      <c r="AZ3" s="110"/>
-      <c r="BA3" s="110"/>
-      <c r="BB3" s="110"/>
-      <c r="BC3" s="110"/>
-      <c r="BD3" s="110"/>
-      <c r="BE3" s="111"/>
+      <c r="AR3" s="116"/>
+      <c r="AS3" s="116"/>
+      <c r="AT3" s="116"/>
+      <c r="AU3" s="116"/>
+      <c r="AV3" s="116"/>
+      <c r="AW3" s="116"/>
+      <c r="AX3" s="116"/>
+      <c r="AY3" s="116"/>
+      <c r="AZ3" s="116"/>
+      <c r="BA3" s="116"/>
+      <c r="BB3" s="116"/>
+      <c r="BC3" s="116"/>
+      <c r="BD3" s="116"/>
+      <c r="BE3" s="117"/>
     </row>
     <row r="4" spans="1:57" ht="15" customHeight="1">
-      <c r="A4" s="112">
+      <c r="A4" s="118">
         <v>1</v>
       </c>
-      <c r="B4" s="113"/>
-      <c r="C4" s="113"/>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="116"/>
-      <c r="L4" s="116"/>
-      <c r="M4" s="116"/>
-      <c r="N4" s="117"/>
-      <c r="O4" s="115" t="s">
+      <c r="B4" s="119"/>
+      <c r="C4" s="119"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="102"/>
+      <c r="J4" s="102"/>
+      <c r="K4" s="102"/>
+      <c r="L4" s="102"/>
+      <c r="M4" s="102"/>
+      <c r="N4" s="103"/>
+      <c r="O4" s="101" t="s">
         <v>11</v>
       </c>
-      <c r="P4" s="118"/>
-      <c r="Q4" s="118"/>
-      <c r="R4" s="118"/>
-      <c r="S4" s="118"/>
-      <c r="T4" s="118"/>
-      <c r="U4" s="118"/>
-      <c r="V4" s="118"/>
-      <c r="W4" s="118"/>
-      <c r="X4" s="118"/>
-      <c r="Y4" s="118"/>
-      <c r="Z4" s="118"/>
-      <c r="AA4" s="118"/>
-      <c r="AB4" s="118"/>
-      <c r="AC4" s="118"/>
-      <c r="AD4" s="118"/>
-      <c r="AE4" s="118"/>
-      <c r="AF4" s="118"/>
-      <c r="AG4" s="118"/>
-      <c r="AH4" s="118"/>
-      <c r="AI4" s="118"/>
-      <c r="AJ4" s="118"/>
-      <c r="AK4" s="118"/>
-      <c r="AL4" s="118"/>
-      <c r="AM4" s="118"/>
-      <c r="AN4" s="118"/>
-      <c r="AO4" s="118"/>
-      <c r="AP4" s="119"/>
-      <c r="AQ4" s="120"/>
-      <c r="AR4" s="118"/>
-      <c r="AS4" s="118"/>
-      <c r="AT4" s="118"/>
-      <c r="AU4" s="118"/>
-      <c r="AV4" s="118"/>
-      <c r="AW4" s="118"/>
-      <c r="AX4" s="118"/>
-      <c r="AY4" s="118"/>
-      <c r="AZ4" s="118"/>
-      <c r="BA4" s="118"/>
-      <c r="BB4" s="118"/>
-      <c r="BC4" s="118"/>
-      <c r="BD4" s="118"/>
-      <c r="BE4" s="121"/>
+      <c r="P4" s="104"/>
+      <c r="Q4" s="104"/>
+      <c r="R4" s="104"/>
+      <c r="S4" s="104"/>
+      <c r="T4" s="104"/>
+      <c r="U4" s="104"/>
+      <c r="V4" s="104"/>
+      <c r="W4" s="104"/>
+      <c r="X4" s="104"/>
+      <c r="Y4" s="104"/>
+      <c r="Z4" s="104"/>
+      <c r="AA4" s="104"/>
+      <c r="AB4" s="104"/>
+      <c r="AC4" s="104"/>
+      <c r="AD4" s="104"/>
+      <c r="AE4" s="104"/>
+      <c r="AF4" s="104"/>
+      <c r="AG4" s="104"/>
+      <c r="AH4" s="104"/>
+      <c r="AI4" s="104"/>
+      <c r="AJ4" s="104"/>
+      <c r="AK4" s="104"/>
+      <c r="AL4" s="104"/>
+      <c r="AM4" s="104"/>
+      <c r="AN4" s="104"/>
+      <c r="AO4" s="104"/>
+      <c r="AP4" s="105"/>
+      <c r="AQ4" s="106"/>
+      <c r="AR4" s="104"/>
+      <c r="AS4" s="104"/>
+      <c r="AT4" s="104"/>
+      <c r="AU4" s="104"/>
+      <c r="AV4" s="104"/>
+      <c r="AW4" s="104"/>
+      <c r="AX4" s="104"/>
+      <c r="AY4" s="104"/>
+      <c r="AZ4" s="104"/>
+      <c r="BA4" s="104"/>
+      <c r="BB4" s="104"/>
+      <c r="BC4" s="104"/>
+      <c r="BD4" s="104"/>
+      <c r="BE4" s="107"/>
     </row>
     <row r="5" spans="1:57" ht="105.75" customHeight="1">
-      <c r="A5" s="101">
+      <c r="A5" s="81">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="102"/>
-      <c r="G5" s="103"/>
+      <c r="B5" s="82"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="83"/>
       <c r="H5" s="84" t="s">
         <v>1796</v>
       </c>
@@ -65123,61 +65134,61 @@
       <c r="O5" s="84" t="s">
         <v>1798</v>
       </c>
-      <c r="P5" s="82"/>
-      <c r="Q5" s="82"/>
-      <c r="R5" s="82"/>
-      <c r="S5" s="82"/>
-      <c r="T5" s="82"/>
-      <c r="U5" s="82"/>
-      <c r="V5" s="82"/>
-      <c r="W5" s="82"/>
-      <c r="X5" s="82"/>
-      <c r="Y5" s="82"/>
-      <c r="Z5" s="82"/>
-      <c r="AA5" s="82"/>
-      <c r="AB5" s="82"/>
-      <c r="AC5" s="82"/>
-      <c r="AD5" s="82"/>
-      <c r="AE5" s="82"/>
-      <c r="AF5" s="82"/>
-      <c r="AG5" s="82"/>
-      <c r="AH5" s="82"/>
-      <c r="AI5" s="82"/>
-      <c r="AJ5" s="82"/>
-      <c r="AK5" s="82"/>
-      <c r="AL5" s="82"/>
-      <c r="AM5" s="82"/>
-      <c r="AN5" s="82"/>
-      <c r="AO5" s="82"/>
-      <c r="AP5" s="90"/>
-      <c r="AQ5" s="81" t="s">
+      <c r="P5" s="87"/>
+      <c r="Q5" s="87"/>
+      <c r="R5" s="87"/>
+      <c r="S5" s="87"/>
+      <c r="T5" s="87"/>
+      <c r="U5" s="87"/>
+      <c r="V5" s="87"/>
+      <c r="W5" s="87"/>
+      <c r="X5" s="87"/>
+      <c r="Y5" s="87"/>
+      <c r="Z5" s="87"/>
+      <c r="AA5" s="87"/>
+      <c r="AB5" s="87"/>
+      <c r="AC5" s="87"/>
+      <c r="AD5" s="87"/>
+      <c r="AE5" s="87"/>
+      <c r="AF5" s="87"/>
+      <c r="AG5" s="87"/>
+      <c r="AH5" s="87"/>
+      <c r="AI5" s="87"/>
+      <c r="AJ5" s="87"/>
+      <c r="AK5" s="87"/>
+      <c r="AL5" s="87"/>
+      <c r="AM5" s="87"/>
+      <c r="AN5" s="87"/>
+      <c r="AO5" s="87"/>
+      <c r="AP5" s="88"/>
+      <c r="AQ5" s="92" t="s">
         <v>1797</v>
       </c>
-      <c r="AR5" s="82"/>
-      <c r="AS5" s="82"/>
-      <c r="AT5" s="82"/>
-      <c r="AU5" s="82"/>
-      <c r="AV5" s="82"/>
-      <c r="AW5" s="82"/>
-      <c r="AX5" s="82"/>
-      <c r="AY5" s="82"/>
-      <c r="AZ5" s="82"/>
-      <c r="BA5" s="82"/>
-      <c r="BB5" s="82"/>
-      <c r="BC5" s="82"/>
-      <c r="BD5" s="82"/>
-      <c r="BE5" s="83"/>
+      <c r="AR5" s="87"/>
+      <c r="AS5" s="87"/>
+      <c r="AT5" s="87"/>
+      <c r="AU5" s="87"/>
+      <c r="AV5" s="87"/>
+      <c r="AW5" s="87"/>
+      <c r="AX5" s="87"/>
+      <c r="AY5" s="87"/>
+      <c r="AZ5" s="87"/>
+      <c r="BA5" s="87"/>
+      <c r="BB5" s="87"/>
+      <c r="BC5" s="87"/>
+      <c r="BD5" s="87"/>
+      <c r="BE5" s="93"/>
     </row>
     <row r="6" spans="1:57" ht="36.6" customHeight="1">
-      <c r="A6" s="101">
+      <c r="A6" s="81">
         <v>1.2</v>
       </c>
-      <c r="B6" s="102"/>
-      <c r="C6" s="102"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="102"/>
-      <c r="F6" s="102"/>
-      <c r="G6" s="103"/>
+      <c r="B6" s="82"/>
+      <c r="C6" s="82"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="82"/>
+      <c r="G6" s="83"/>
       <c r="H6" s="84" t="s">
         <v>1824</v>
       </c>
@@ -65190,124 +65201,124 @@
       <c r="O6" s="84" t="s">
         <v>1823</v>
       </c>
-      <c r="P6" s="91"/>
-      <c r="Q6" s="91"/>
-      <c r="R6" s="91"/>
-      <c r="S6" s="91"/>
-      <c r="T6" s="91"/>
-      <c r="U6" s="91"/>
-      <c r="V6" s="91"/>
-      <c r="W6" s="91"/>
-      <c r="X6" s="91"/>
-      <c r="Y6" s="91"/>
-      <c r="Z6" s="91"/>
-      <c r="AA6" s="91"/>
-      <c r="AB6" s="91"/>
-      <c r="AC6" s="91"/>
-      <c r="AD6" s="91"/>
-      <c r="AE6" s="91"/>
-      <c r="AF6" s="91"/>
-      <c r="AG6" s="91"/>
-      <c r="AH6" s="91"/>
-      <c r="AI6" s="91"/>
-      <c r="AJ6" s="91"/>
-      <c r="AK6" s="91"/>
-      <c r="AL6" s="91"/>
-      <c r="AM6" s="91"/>
-      <c r="AN6" s="91"/>
-      <c r="AO6" s="91"/>
-      <c r="AP6" s="92"/>
-      <c r="AQ6" s="81" t="s">
+      <c r="P6" s="122"/>
+      <c r="Q6" s="122"/>
+      <c r="R6" s="122"/>
+      <c r="S6" s="122"/>
+      <c r="T6" s="122"/>
+      <c r="U6" s="122"/>
+      <c r="V6" s="122"/>
+      <c r="W6" s="122"/>
+      <c r="X6" s="122"/>
+      <c r="Y6" s="122"/>
+      <c r="Z6" s="122"/>
+      <c r="AA6" s="122"/>
+      <c r="AB6" s="122"/>
+      <c r="AC6" s="122"/>
+      <c r="AD6" s="122"/>
+      <c r="AE6" s="122"/>
+      <c r="AF6" s="122"/>
+      <c r="AG6" s="122"/>
+      <c r="AH6" s="122"/>
+      <c r="AI6" s="122"/>
+      <c r="AJ6" s="122"/>
+      <c r="AK6" s="122"/>
+      <c r="AL6" s="122"/>
+      <c r="AM6" s="122"/>
+      <c r="AN6" s="122"/>
+      <c r="AO6" s="122"/>
+      <c r="AP6" s="123"/>
+      <c r="AQ6" s="92" t="s">
         <v>1797</v>
       </c>
-      <c r="AR6" s="82"/>
-      <c r="AS6" s="82"/>
-      <c r="AT6" s="82"/>
-      <c r="AU6" s="82"/>
-      <c r="AV6" s="82"/>
-      <c r="AW6" s="82"/>
-      <c r="AX6" s="82"/>
-      <c r="AY6" s="82"/>
-      <c r="AZ6" s="82"/>
-      <c r="BA6" s="82"/>
-      <c r="BB6" s="82"/>
-      <c r="BC6" s="82"/>
-      <c r="BD6" s="82"/>
-      <c r="BE6" s="83"/>
+      <c r="AR6" s="87"/>
+      <c r="AS6" s="87"/>
+      <c r="AT6" s="87"/>
+      <c r="AU6" s="87"/>
+      <c r="AV6" s="87"/>
+      <c r="AW6" s="87"/>
+      <c r="AX6" s="87"/>
+      <c r="AY6" s="87"/>
+      <c r="AZ6" s="87"/>
+      <c r="BA6" s="87"/>
+      <c r="BB6" s="87"/>
+      <c r="BC6" s="87"/>
+      <c r="BD6" s="87"/>
+      <c r="BE6" s="93"/>
     </row>
     <row r="7" spans="1:57" ht="15" customHeight="1">
-      <c r="A7" s="101">
+      <c r="A7" s="81">
         <v>1.3</v>
       </c>
-      <c r="B7" s="102"/>
-      <c r="C7" s="102"/>
-      <c r="D7" s="102"/>
-      <c r="E7" s="102"/>
-      <c r="F7" s="102"/>
-      <c r="G7" s="103"/>
+      <c r="B7" s="82"/>
+      <c r="C7" s="82"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="83"/>
       <c r="H7" s="84"/>
-      <c r="I7" s="93"/>
-      <c r="J7" s="93"/>
-      <c r="K7" s="93"/>
-      <c r="L7" s="93"/>
-      <c r="M7" s="93"/>
-      <c r="N7" s="94"/>
-      <c r="O7" s="95" t="s">
+      <c r="I7" s="124"/>
+      <c r="J7" s="124"/>
+      <c r="K7" s="124"/>
+      <c r="L7" s="124"/>
+      <c r="M7" s="124"/>
+      <c r="N7" s="125"/>
+      <c r="O7" s="126" t="s">
         <v>2237</v>
       </c>
-      <c r="P7" s="96"/>
-      <c r="Q7" s="96"/>
-      <c r="R7" s="96"/>
-      <c r="S7" s="96"/>
-      <c r="T7" s="96"/>
-      <c r="U7" s="96"/>
-      <c r="V7" s="96"/>
-      <c r="W7" s="96"/>
-      <c r="X7" s="96"/>
-      <c r="Y7" s="96"/>
-      <c r="Z7" s="96"/>
-      <c r="AA7" s="96"/>
-      <c r="AB7" s="96"/>
-      <c r="AC7" s="96"/>
-      <c r="AD7" s="96"/>
-      <c r="AE7" s="96"/>
-      <c r="AF7" s="96"/>
-      <c r="AG7" s="96"/>
-      <c r="AH7" s="96"/>
-      <c r="AI7" s="96"/>
-      <c r="AJ7" s="96"/>
-      <c r="AK7" s="96"/>
-      <c r="AL7" s="96"/>
-      <c r="AM7" s="96"/>
-      <c r="AN7" s="96"/>
-      <c r="AO7" s="96"/>
-      <c r="AP7" s="97"/>
-      <c r="AQ7" s="98" t="s">
+      <c r="P7" s="127"/>
+      <c r="Q7" s="127"/>
+      <c r="R7" s="127"/>
+      <c r="S7" s="127"/>
+      <c r="T7" s="127"/>
+      <c r="U7" s="127"/>
+      <c r="V7" s="127"/>
+      <c r="W7" s="127"/>
+      <c r="X7" s="127"/>
+      <c r="Y7" s="127"/>
+      <c r="Z7" s="127"/>
+      <c r="AA7" s="127"/>
+      <c r="AB7" s="127"/>
+      <c r="AC7" s="127"/>
+      <c r="AD7" s="127"/>
+      <c r="AE7" s="127"/>
+      <c r="AF7" s="127"/>
+      <c r="AG7" s="127"/>
+      <c r="AH7" s="127"/>
+      <c r="AI7" s="127"/>
+      <c r="AJ7" s="127"/>
+      <c r="AK7" s="127"/>
+      <c r="AL7" s="127"/>
+      <c r="AM7" s="127"/>
+      <c r="AN7" s="127"/>
+      <c r="AO7" s="127"/>
+      <c r="AP7" s="128"/>
+      <c r="AQ7" s="129" t="s">
         <v>2238</v>
       </c>
-      <c r="AR7" s="99"/>
-      <c r="AS7" s="99"/>
-      <c r="AT7" s="99"/>
-      <c r="AU7" s="99"/>
-      <c r="AV7" s="99"/>
-      <c r="AW7" s="99"/>
-      <c r="AX7" s="99"/>
-      <c r="AY7" s="99"/>
-      <c r="AZ7" s="99"/>
-      <c r="BA7" s="99"/>
-      <c r="BB7" s="99"/>
-      <c r="BC7" s="99"/>
-      <c r="BD7" s="99"/>
-      <c r="BE7" s="100"/>
+      <c r="AR7" s="130"/>
+      <c r="AS7" s="130"/>
+      <c r="AT7" s="130"/>
+      <c r="AU7" s="130"/>
+      <c r="AV7" s="130"/>
+      <c r="AW7" s="130"/>
+      <c r="AX7" s="130"/>
+      <c r="AY7" s="130"/>
+      <c r="AZ7" s="130"/>
+      <c r="BA7" s="130"/>
+      <c r="BB7" s="130"/>
+      <c r="BC7" s="130"/>
+      <c r="BD7" s="130"/>
+      <c r="BE7" s="131"/>
     </row>
     <row r="8" spans="1:57" ht="15" customHeight="1">
-      <c r="A8" s="101"/>
-      <c r="B8" s="102"/>
-      <c r="C8" s="102"/>
-      <c r="D8" s="102"/>
-      <c r="E8" s="102"/>
-      <c r="F8" s="102"/>
-      <c r="G8" s="103"/>
+      <c r="A8" s="81"/>
+      <c r="B8" s="82"/>
+      <c r="C8" s="82"/>
+      <c r="D8" s="82"/>
+      <c r="E8" s="82"/>
+      <c r="F8" s="82"/>
+      <c r="G8" s="83"/>
       <c r="H8" s="84"/>
       <c r="I8" s="85"/>
       <c r="J8" s="85"/>
@@ -65316,57 +65327,57 @@
       <c r="M8" s="85"/>
       <c r="N8" s="86"/>
       <c r="O8" s="84"/>
-      <c r="P8" s="82"/>
-      <c r="Q8" s="82"/>
-      <c r="R8" s="82"/>
-      <c r="S8" s="82"/>
-      <c r="T8" s="82"/>
-      <c r="U8" s="82"/>
-      <c r="V8" s="82"/>
-      <c r="W8" s="82"/>
-      <c r="X8" s="82"/>
-      <c r="Y8" s="82"/>
-      <c r="Z8" s="82"/>
-      <c r="AA8" s="82"/>
-      <c r="AB8" s="82"/>
-      <c r="AC8" s="82"/>
-      <c r="AD8" s="82"/>
-      <c r="AE8" s="82"/>
-      <c r="AF8" s="82"/>
-      <c r="AG8" s="82"/>
-      <c r="AH8" s="82"/>
-      <c r="AI8" s="82"/>
-      <c r="AJ8" s="82"/>
-      <c r="AK8" s="82"/>
-      <c r="AL8" s="82"/>
-      <c r="AM8" s="82"/>
-      <c r="AN8" s="82"/>
-      <c r="AO8" s="82"/>
-      <c r="AP8" s="90"/>
-      <c r="AQ8" s="81"/>
-      <c r="AR8" s="82"/>
-      <c r="AS8" s="82"/>
-      <c r="AT8" s="82"/>
-      <c r="AU8" s="82"/>
-      <c r="AV8" s="82"/>
-      <c r="AW8" s="82"/>
-      <c r="AX8" s="82"/>
-      <c r="AY8" s="82"/>
-      <c r="AZ8" s="82"/>
-      <c r="BA8" s="82"/>
-      <c r="BB8" s="82"/>
-      <c r="BC8" s="82"/>
-      <c r="BD8" s="82"/>
-      <c r="BE8" s="83"/>
+      <c r="P8" s="87"/>
+      <c r="Q8" s="87"/>
+      <c r="R8" s="87"/>
+      <c r="S8" s="87"/>
+      <c r="T8" s="87"/>
+      <c r="U8" s="87"/>
+      <c r="V8" s="87"/>
+      <c r="W8" s="87"/>
+      <c r="X8" s="87"/>
+      <c r="Y8" s="87"/>
+      <c r="Z8" s="87"/>
+      <c r="AA8" s="87"/>
+      <c r="AB8" s="87"/>
+      <c r="AC8" s="87"/>
+      <c r="AD8" s="87"/>
+      <c r="AE8" s="87"/>
+      <c r="AF8" s="87"/>
+      <c r="AG8" s="87"/>
+      <c r="AH8" s="87"/>
+      <c r="AI8" s="87"/>
+      <c r="AJ8" s="87"/>
+      <c r="AK8" s="87"/>
+      <c r="AL8" s="87"/>
+      <c r="AM8" s="87"/>
+      <c r="AN8" s="87"/>
+      <c r="AO8" s="87"/>
+      <c r="AP8" s="88"/>
+      <c r="AQ8" s="92"/>
+      <c r="AR8" s="87"/>
+      <c r="AS8" s="87"/>
+      <c r="AT8" s="87"/>
+      <c r="AU8" s="87"/>
+      <c r="AV8" s="87"/>
+      <c r="AW8" s="87"/>
+      <c r="AX8" s="87"/>
+      <c r="AY8" s="87"/>
+      <c r="AZ8" s="87"/>
+      <c r="BA8" s="87"/>
+      <c r="BB8" s="87"/>
+      <c r="BC8" s="87"/>
+      <c r="BD8" s="87"/>
+      <c r="BE8" s="93"/>
     </row>
     <row r="9" spans="1:57" ht="15" customHeight="1">
-      <c r="A9" s="101"/>
-      <c r="B9" s="102"/>
-      <c r="C9" s="102"/>
-      <c r="D9" s="102"/>
-      <c r="E9" s="102"/>
-      <c r="F9" s="102"/>
-      <c r="G9" s="103"/>
+      <c r="A9" s="81"/>
+      <c r="B9" s="82"/>
+      <c r="C9" s="82"/>
+      <c r="D9" s="82"/>
+      <c r="E9" s="82"/>
+      <c r="F9" s="82"/>
+      <c r="G9" s="83"/>
       <c r="H9" s="84"/>
       <c r="I9" s="85"/>
       <c r="J9" s="85"/>
@@ -65375,57 +65386,57 @@
       <c r="M9" s="85"/>
       <c r="N9" s="86"/>
       <c r="O9" s="84"/>
-      <c r="P9" s="82"/>
-      <c r="Q9" s="82"/>
-      <c r="R9" s="82"/>
-      <c r="S9" s="82"/>
-      <c r="T9" s="82"/>
-      <c r="U9" s="82"/>
-      <c r="V9" s="82"/>
-      <c r="W9" s="82"/>
-      <c r="X9" s="82"/>
-      <c r="Y9" s="82"/>
-      <c r="Z9" s="82"/>
-      <c r="AA9" s="82"/>
-      <c r="AB9" s="82"/>
-      <c r="AC9" s="82"/>
-      <c r="AD9" s="82"/>
-      <c r="AE9" s="82"/>
-      <c r="AF9" s="82"/>
-      <c r="AG9" s="82"/>
-      <c r="AH9" s="82"/>
-      <c r="AI9" s="82"/>
-      <c r="AJ9" s="82"/>
-      <c r="AK9" s="82"/>
-      <c r="AL9" s="82"/>
-      <c r="AM9" s="82"/>
-      <c r="AN9" s="82"/>
-      <c r="AO9" s="82"/>
-      <c r="AP9" s="90"/>
-      <c r="AQ9" s="81"/>
-      <c r="AR9" s="82"/>
-      <c r="AS9" s="82"/>
-      <c r="AT9" s="82"/>
-      <c r="AU9" s="82"/>
-      <c r="AV9" s="82"/>
-      <c r="AW9" s="82"/>
-      <c r="AX9" s="82"/>
-      <c r="AY9" s="82"/>
-      <c r="AZ9" s="82"/>
-      <c r="BA9" s="82"/>
-      <c r="BB9" s="82"/>
-      <c r="BC9" s="82"/>
-      <c r="BD9" s="82"/>
-      <c r="BE9" s="83"/>
+      <c r="P9" s="87"/>
+      <c r="Q9" s="87"/>
+      <c r="R9" s="87"/>
+      <c r="S9" s="87"/>
+      <c r="T9" s="87"/>
+      <c r="U9" s="87"/>
+      <c r="V9" s="87"/>
+      <c r="W9" s="87"/>
+      <c r="X9" s="87"/>
+      <c r="Y9" s="87"/>
+      <c r="Z9" s="87"/>
+      <c r="AA9" s="87"/>
+      <c r="AB9" s="87"/>
+      <c r="AC9" s="87"/>
+      <c r="AD9" s="87"/>
+      <c r="AE9" s="87"/>
+      <c r="AF9" s="87"/>
+      <c r="AG9" s="87"/>
+      <c r="AH9" s="87"/>
+      <c r="AI9" s="87"/>
+      <c r="AJ9" s="87"/>
+      <c r="AK9" s="87"/>
+      <c r="AL9" s="87"/>
+      <c r="AM9" s="87"/>
+      <c r="AN9" s="87"/>
+      <c r="AO9" s="87"/>
+      <c r="AP9" s="88"/>
+      <c r="AQ9" s="92"/>
+      <c r="AR9" s="87"/>
+      <c r="AS9" s="87"/>
+      <c r="AT9" s="87"/>
+      <c r="AU9" s="87"/>
+      <c r="AV9" s="87"/>
+      <c r="AW9" s="87"/>
+      <c r="AX9" s="87"/>
+      <c r="AY9" s="87"/>
+      <c r="AZ9" s="87"/>
+      <c r="BA9" s="87"/>
+      <c r="BB9" s="87"/>
+      <c r="BC9" s="87"/>
+      <c r="BD9" s="87"/>
+      <c r="BE9" s="93"/>
     </row>
     <row r="10" spans="1:57" ht="15" customHeight="1">
-      <c r="A10" s="101"/>
-      <c r="B10" s="102"/>
-      <c r="C10" s="102"/>
-      <c r="D10" s="102"/>
-      <c r="E10" s="102"/>
-      <c r="F10" s="102"/>
-      <c r="G10" s="103"/>
+      <c r="A10" s="81"/>
+      <c r="B10" s="82"/>
+      <c r="C10" s="82"/>
+      <c r="D10" s="82"/>
+      <c r="E10" s="82"/>
+      <c r="F10" s="82"/>
+      <c r="G10" s="83"/>
       <c r="H10" s="84"/>
       <c r="I10" s="85"/>
       <c r="J10" s="85"/>
@@ -65434,57 +65445,57 @@
       <c r="M10" s="85"/>
       <c r="N10" s="86"/>
       <c r="O10" s="84"/>
-      <c r="P10" s="82"/>
-      <c r="Q10" s="82"/>
-      <c r="R10" s="82"/>
-      <c r="S10" s="82"/>
-      <c r="T10" s="82"/>
-      <c r="U10" s="82"/>
-      <c r="V10" s="82"/>
-      <c r="W10" s="82"/>
-      <c r="X10" s="82"/>
-      <c r="Y10" s="82"/>
-      <c r="Z10" s="82"/>
-      <c r="AA10" s="82"/>
-      <c r="AB10" s="82"/>
-      <c r="AC10" s="82"/>
-      <c r="AD10" s="82"/>
-      <c r="AE10" s="82"/>
-      <c r="AF10" s="82"/>
-      <c r="AG10" s="82"/>
-      <c r="AH10" s="82"/>
-      <c r="AI10" s="82"/>
-      <c r="AJ10" s="82"/>
-      <c r="AK10" s="82"/>
-      <c r="AL10" s="82"/>
-      <c r="AM10" s="82"/>
-      <c r="AN10" s="82"/>
-      <c r="AO10" s="82"/>
-      <c r="AP10" s="90"/>
-      <c r="AQ10" s="81"/>
-      <c r="AR10" s="82"/>
-      <c r="AS10" s="82"/>
-      <c r="AT10" s="82"/>
-      <c r="AU10" s="82"/>
-      <c r="AV10" s="82"/>
-      <c r="AW10" s="82"/>
-      <c r="AX10" s="82"/>
-      <c r="AY10" s="82"/>
-      <c r="AZ10" s="82"/>
-      <c r="BA10" s="82"/>
-      <c r="BB10" s="82"/>
-      <c r="BC10" s="82"/>
-      <c r="BD10" s="82"/>
-      <c r="BE10" s="83"/>
+      <c r="P10" s="87"/>
+      <c r="Q10" s="87"/>
+      <c r="R10" s="87"/>
+      <c r="S10" s="87"/>
+      <c r="T10" s="87"/>
+      <c r="U10" s="87"/>
+      <c r="V10" s="87"/>
+      <c r="W10" s="87"/>
+      <c r="X10" s="87"/>
+      <c r="Y10" s="87"/>
+      <c r="Z10" s="87"/>
+      <c r="AA10" s="87"/>
+      <c r="AB10" s="87"/>
+      <c r="AC10" s="87"/>
+      <c r="AD10" s="87"/>
+      <c r="AE10" s="87"/>
+      <c r="AF10" s="87"/>
+      <c r="AG10" s="87"/>
+      <c r="AH10" s="87"/>
+      <c r="AI10" s="87"/>
+      <c r="AJ10" s="87"/>
+      <c r="AK10" s="87"/>
+      <c r="AL10" s="87"/>
+      <c r="AM10" s="87"/>
+      <c r="AN10" s="87"/>
+      <c r="AO10" s="87"/>
+      <c r="AP10" s="88"/>
+      <c r="AQ10" s="92"/>
+      <c r="AR10" s="87"/>
+      <c r="AS10" s="87"/>
+      <c r="AT10" s="87"/>
+      <c r="AU10" s="87"/>
+      <c r="AV10" s="87"/>
+      <c r="AW10" s="87"/>
+      <c r="AX10" s="87"/>
+      <c r="AY10" s="87"/>
+      <c r="AZ10" s="87"/>
+      <c r="BA10" s="87"/>
+      <c r="BB10" s="87"/>
+      <c r="BC10" s="87"/>
+      <c r="BD10" s="87"/>
+      <c r="BE10" s="93"/>
     </row>
     <row r="11" spans="1:57" ht="15" customHeight="1">
-      <c r="A11" s="101"/>
-      <c r="B11" s="102"/>
-      <c r="C11" s="102"/>
-      <c r="D11" s="102"/>
-      <c r="E11" s="102"/>
-      <c r="F11" s="102"/>
-      <c r="G11" s="103"/>
+      <c r="A11" s="81"/>
+      <c r="B11" s="82"/>
+      <c r="C11" s="82"/>
+      <c r="D11" s="82"/>
+      <c r="E11" s="82"/>
+      <c r="F11" s="82"/>
+      <c r="G11" s="83"/>
       <c r="H11" s="84"/>
       <c r="I11" s="85"/>
       <c r="J11" s="85"/>
@@ -65493,57 +65504,57 @@
       <c r="M11" s="85"/>
       <c r="N11" s="86"/>
       <c r="O11" s="84"/>
-      <c r="P11" s="82"/>
-      <c r="Q11" s="82"/>
-      <c r="R11" s="82"/>
-      <c r="S11" s="82"/>
-      <c r="T11" s="82"/>
-      <c r="U11" s="82"/>
-      <c r="V11" s="82"/>
-      <c r="W11" s="82"/>
-      <c r="X11" s="82"/>
-      <c r="Y11" s="82"/>
-      <c r="Z11" s="82"/>
-      <c r="AA11" s="82"/>
-      <c r="AB11" s="82"/>
-      <c r="AC11" s="82"/>
-      <c r="AD11" s="82"/>
-      <c r="AE11" s="82"/>
-      <c r="AF11" s="82"/>
-      <c r="AG11" s="82"/>
-      <c r="AH11" s="82"/>
-      <c r="AI11" s="82"/>
-      <c r="AJ11" s="82"/>
-      <c r="AK11" s="82"/>
-      <c r="AL11" s="82"/>
-      <c r="AM11" s="82"/>
-      <c r="AN11" s="82"/>
-      <c r="AO11" s="82"/>
-      <c r="AP11" s="90"/>
-      <c r="AQ11" s="81"/>
-      <c r="AR11" s="82"/>
-      <c r="AS11" s="82"/>
-      <c r="AT11" s="82"/>
-      <c r="AU11" s="82"/>
-      <c r="AV11" s="82"/>
-      <c r="AW11" s="82"/>
-      <c r="AX11" s="82"/>
-      <c r="AY11" s="82"/>
-      <c r="AZ11" s="82"/>
-      <c r="BA11" s="82"/>
-      <c r="BB11" s="82"/>
-      <c r="BC11" s="82"/>
-      <c r="BD11" s="82"/>
-      <c r="BE11" s="83"/>
+      <c r="P11" s="87"/>
+      <c r="Q11" s="87"/>
+      <c r="R11" s="87"/>
+      <c r="S11" s="87"/>
+      <c r="T11" s="87"/>
+      <c r="U11" s="87"/>
+      <c r="V11" s="87"/>
+      <c r="W11" s="87"/>
+      <c r="X11" s="87"/>
+      <c r="Y11" s="87"/>
+      <c r="Z11" s="87"/>
+      <c r="AA11" s="87"/>
+      <c r="AB11" s="87"/>
+      <c r="AC11" s="87"/>
+      <c r="AD11" s="87"/>
+      <c r="AE11" s="87"/>
+      <c r="AF11" s="87"/>
+      <c r="AG11" s="87"/>
+      <c r="AH11" s="87"/>
+      <c r="AI11" s="87"/>
+      <c r="AJ11" s="87"/>
+      <c r="AK11" s="87"/>
+      <c r="AL11" s="87"/>
+      <c r="AM11" s="87"/>
+      <c r="AN11" s="87"/>
+      <c r="AO11" s="87"/>
+      <c r="AP11" s="88"/>
+      <c r="AQ11" s="92"/>
+      <c r="AR11" s="87"/>
+      <c r="AS11" s="87"/>
+      <c r="AT11" s="87"/>
+      <c r="AU11" s="87"/>
+      <c r="AV11" s="87"/>
+      <c r="AW11" s="87"/>
+      <c r="AX11" s="87"/>
+      <c r="AY11" s="87"/>
+      <c r="AZ11" s="87"/>
+      <c r="BA11" s="87"/>
+      <c r="BB11" s="87"/>
+      <c r="BC11" s="87"/>
+      <c r="BD11" s="87"/>
+      <c r="BE11" s="93"/>
     </row>
     <row r="12" spans="1:57" ht="15" customHeight="1">
-      <c r="A12" s="101"/>
-      <c r="B12" s="102"/>
-      <c r="C12" s="102"/>
-      <c r="D12" s="102"/>
-      <c r="E12" s="102"/>
-      <c r="F12" s="102"/>
-      <c r="G12" s="103"/>
+      <c r="A12" s="81"/>
+      <c r="B12" s="82"/>
+      <c r="C12" s="82"/>
+      <c r="D12" s="82"/>
+      <c r="E12" s="82"/>
+      <c r="F12" s="82"/>
+      <c r="G12" s="83"/>
       <c r="H12" s="84"/>
       <c r="I12" s="85"/>
       <c r="J12" s="85"/>
@@ -65552,57 +65563,57 @@
       <c r="M12" s="85"/>
       <c r="N12" s="86"/>
       <c r="O12" s="84"/>
-      <c r="P12" s="82"/>
-      <c r="Q12" s="82"/>
-      <c r="R12" s="82"/>
-      <c r="S12" s="82"/>
-      <c r="T12" s="82"/>
-      <c r="U12" s="82"/>
-      <c r="V12" s="82"/>
-      <c r="W12" s="82"/>
-      <c r="X12" s="82"/>
-      <c r="Y12" s="82"/>
-      <c r="Z12" s="82"/>
-      <c r="AA12" s="82"/>
-      <c r="AB12" s="82"/>
-      <c r="AC12" s="82"/>
-      <c r="AD12" s="82"/>
-      <c r="AE12" s="82"/>
-      <c r="AF12" s="82"/>
-      <c r="AG12" s="82"/>
-      <c r="AH12" s="82"/>
-      <c r="AI12" s="82"/>
-      <c r="AJ12" s="82"/>
-      <c r="AK12" s="82"/>
-      <c r="AL12" s="82"/>
-      <c r="AM12" s="82"/>
-      <c r="AN12" s="82"/>
-      <c r="AO12" s="82"/>
-      <c r="AP12" s="90"/>
-      <c r="AQ12" s="81"/>
-      <c r="AR12" s="82"/>
-      <c r="AS12" s="82"/>
-      <c r="AT12" s="82"/>
-      <c r="AU12" s="82"/>
-      <c r="AV12" s="82"/>
-      <c r="AW12" s="82"/>
-      <c r="AX12" s="82"/>
-      <c r="AY12" s="82"/>
-      <c r="AZ12" s="82"/>
-      <c r="BA12" s="82"/>
-      <c r="BB12" s="82"/>
-      <c r="BC12" s="82"/>
-      <c r="BD12" s="82"/>
-      <c r="BE12" s="83"/>
+      <c r="P12" s="87"/>
+      <c r="Q12" s="87"/>
+      <c r="R12" s="87"/>
+      <c r="S12" s="87"/>
+      <c r="T12" s="87"/>
+      <c r="U12" s="87"/>
+      <c r="V12" s="87"/>
+      <c r="W12" s="87"/>
+      <c r="X12" s="87"/>
+      <c r="Y12" s="87"/>
+      <c r="Z12" s="87"/>
+      <c r="AA12" s="87"/>
+      <c r="AB12" s="87"/>
+      <c r="AC12" s="87"/>
+      <c r="AD12" s="87"/>
+      <c r="AE12" s="87"/>
+      <c r="AF12" s="87"/>
+      <c r="AG12" s="87"/>
+      <c r="AH12" s="87"/>
+      <c r="AI12" s="87"/>
+      <c r="AJ12" s="87"/>
+      <c r="AK12" s="87"/>
+      <c r="AL12" s="87"/>
+      <c r="AM12" s="87"/>
+      <c r="AN12" s="87"/>
+      <c r="AO12" s="87"/>
+      <c r="AP12" s="88"/>
+      <c r="AQ12" s="92"/>
+      <c r="AR12" s="87"/>
+      <c r="AS12" s="87"/>
+      <c r="AT12" s="87"/>
+      <c r="AU12" s="87"/>
+      <c r="AV12" s="87"/>
+      <c r="AW12" s="87"/>
+      <c r="AX12" s="87"/>
+      <c r="AY12" s="87"/>
+      <c r="AZ12" s="87"/>
+      <c r="BA12" s="87"/>
+      <c r="BB12" s="87"/>
+      <c r="BC12" s="87"/>
+      <c r="BD12" s="87"/>
+      <c r="BE12" s="93"/>
     </row>
     <row r="13" spans="1:57" ht="15" customHeight="1">
-      <c r="A13" s="101"/>
-      <c r="B13" s="102"/>
-      <c r="C13" s="102"/>
-      <c r="D13" s="102"/>
-      <c r="E13" s="102"/>
-      <c r="F13" s="102"/>
-      <c r="G13" s="103"/>
+      <c r="A13" s="81"/>
+      <c r="B13" s="82"/>
+      <c r="C13" s="82"/>
+      <c r="D13" s="82"/>
+      <c r="E13" s="82"/>
+      <c r="F13" s="82"/>
+      <c r="G13" s="83"/>
       <c r="H13" s="84"/>
       <c r="I13" s="85"/>
       <c r="J13" s="85"/>
@@ -65611,57 +65622,57 @@
       <c r="M13" s="85"/>
       <c r="N13" s="86"/>
       <c r="O13" s="84"/>
-      <c r="P13" s="82"/>
-      <c r="Q13" s="82"/>
-      <c r="R13" s="82"/>
-      <c r="S13" s="82"/>
-      <c r="T13" s="82"/>
-      <c r="U13" s="82"/>
-      <c r="V13" s="82"/>
-      <c r="W13" s="82"/>
-      <c r="X13" s="82"/>
-      <c r="Y13" s="82"/>
-      <c r="Z13" s="82"/>
-      <c r="AA13" s="82"/>
-      <c r="AB13" s="82"/>
-      <c r="AC13" s="82"/>
-      <c r="AD13" s="82"/>
-      <c r="AE13" s="82"/>
-      <c r="AF13" s="82"/>
-      <c r="AG13" s="82"/>
-      <c r="AH13" s="82"/>
-      <c r="AI13" s="82"/>
-      <c r="AJ13" s="82"/>
-      <c r="AK13" s="82"/>
-      <c r="AL13" s="82"/>
-      <c r="AM13" s="82"/>
-      <c r="AN13" s="82"/>
-      <c r="AO13" s="82"/>
-      <c r="AP13" s="90"/>
-      <c r="AQ13" s="81"/>
-      <c r="AR13" s="82"/>
-      <c r="AS13" s="82"/>
-      <c r="AT13" s="82"/>
-      <c r="AU13" s="82"/>
-      <c r="AV13" s="82"/>
-      <c r="AW13" s="82"/>
-      <c r="AX13" s="82"/>
-      <c r="AY13" s="82"/>
-      <c r="AZ13" s="82"/>
-      <c r="BA13" s="82"/>
-      <c r="BB13" s="82"/>
-      <c r="BC13" s="82"/>
-      <c r="BD13" s="82"/>
-      <c r="BE13" s="83"/>
+      <c r="P13" s="87"/>
+      <c r="Q13" s="87"/>
+      <c r="R13" s="87"/>
+      <c r="S13" s="87"/>
+      <c r="T13" s="87"/>
+      <c r="U13" s="87"/>
+      <c r="V13" s="87"/>
+      <c r="W13" s="87"/>
+      <c r="X13" s="87"/>
+      <c r="Y13" s="87"/>
+      <c r="Z13" s="87"/>
+      <c r="AA13" s="87"/>
+      <c r="AB13" s="87"/>
+      <c r="AC13" s="87"/>
+      <c r="AD13" s="87"/>
+      <c r="AE13" s="87"/>
+      <c r="AF13" s="87"/>
+      <c r="AG13" s="87"/>
+      <c r="AH13" s="87"/>
+      <c r="AI13" s="87"/>
+      <c r="AJ13" s="87"/>
+      <c r="AK13" s="87"/>
+      <c r="AL13" s="87"/>
+      <c r="AM13" s="87"/>
+      <c r="AN13" s="87"/>
+      <c r="AO13" s="87"/>
+      <c r="AP13" s="88"/>
+      <c r="AQ13" s="92"/>
+      <c r="AR13" s="87"/>
+      <c r="AS13" s="87"/>
+      <c r="AT13" s="87"/>
+      <c r="AU13" s="87"/>
+      <c r="AV13" s="87"/>
+      <c r="AW13" s="87"/>
+      <c r="AX13" s="87"/>
+      <c r="AY13" s="87"/>
+      <c r="AZ13" s="87"/>
+      <c r="BA13" s="87"/>
+      <c r="BB13" s="87"/>
+      <c r="BC13" s="87"/>
+      <c r="BD13" s="87"/>
+      <c r="BE13" s="93"/>
     </row>
     <row r="14" spans="1:57" ht="15" customHeight="1">
-      <c r="A14" s="101"/>
-      <c r="B14" s="102"/>
-      <c r="C14" s="102"/>
-      <c r="D14" s="102"/>
-      <c r="E14" s="102"/>
-      <c r="F14" s="102"/>
-      <c r="G14" s="103"/>
+      <c r="A14" s="81"/>
+      <c r="B14" s="82"/>
+      <c r="C14" s="82"/>
+      <c r="D14" s="82"/>
+      <c r="E14" s="82"/>
+      <c r="F14" s="82"/>
+      <c r="G14" s="83"/>
       <c r="H14" s="84"/>
       <c r="I14" s="85"/>
       <c r="J14" s="85"/>
@@ -65670,57 +65681,57 @@
       <c r="M14" s="85"/>
       <c r="N14" s="86"/>
       <c r="O14" s="84"/>
-      <c r="P14" s="82"/>
-      <c r="Q14" s="82"/>
-      <c r="R14" s="82"/>
-      <c r="S14" s="82"/>
-      <c r="T14" s="82"/>
-      <c r="U14" s="82"/>
-      <c r="V14" s="82"/>
-      <c r="W14" s="82"/>
-      <c r="X14" s="82"/>
-      <c r="Y14" s="82"/>
-      <c r="Z14" s="82"/>
-      <c r="AA14" s="82"/>
-      <c r="AB14" s="82"/>
-      <c r="AC14" s="82"/>
-      <c r="AD14" s="82"/>
-      <c r="AE14" s="82"/>
-      <c r="AF14" s="82"/>
-      <c r="AG14" s="82"/>
-      <c r="AH14" s="82"/>
-      <c r="AI14" s="82"/>
-      <c r="AJ14" s="82"/>
-      <c r="AK14" s="82"/>
-      <c r="AL14" s="82"/>
-      <c r="AM14" s="82"/>
-      <c r="AN14" s="82"/>
-      <c r="AO14" s="82"/>
-      <c r="AP14" s="90"/>
-      <c r="AQ14" s="81"/>
-      <c r="AR14" s="82"/>
-      <c r="AS14" s="82"/>
-      <c r="AT14" s="82"/>
-      <c r="AU14" s="82"/>
-      <c r="AV14" s="82"/>
-      <c r="AW14" s="82"/>
-      <c r="AX14" s="82"/>
-      <c r="AY14" s="82"/>
-      <c r="AZ14" s="82"/>
-      <c r="BA14" s="82"/>
-      <c r="BB14" s="82"/>
-      <c r="BC14" s="82"/>
-      <c r="BD14" s="82"/>
-      <c r="BE14" s="83"/>
+      <c r="P14" s="87"/>
+      <c r="Q14" s="87"/>
+      <c r="R14" s="87"/>
+      <c r="S14" s="87"/>
+      <c r="T14" s="87"/>
+      <c r="U14" s="87"/>
+      <c r="V14" s="87"/>
+      <c r="W14" s="87"/>
+      <c r="X14" s="87"/>
+      <c r="Y14" s="87"/>
+      <c r="Z14" s="87"/>
+      <c r="AA14" s="87"/>
+      <c r="AB14" s="87"/>
+      <c r="AC14" s="87"/>
+      <c r="AD14" s="87"/>
+      <c r="AE14" s="87"/>
+      <c r="AF14" s="87"/>
+      <c r="AG14" s="87"/>
+      <c r="AH14" s="87"/>
+      <c r="AI14" s="87"/>
+      <c r="AJ14" s="87"/>
+      <c r="AK14" s="87"/>
+      <c r="AL14" s="87"/>
+      <c r="AM14" s="87"/>
+      <c r="AN14" s="87"/>
+      <c r="AO14" s="87"/>
+      <c r="AP14" s="88"/>
+      <c r="AQ14" s="92"/>
+      <c r="AR14" s="87"/>
+      <c r="AS14" s="87"/>
+      <c r="AT14" s="87"/>
+      <c r="AU14" s="87"/>
+      <c r="AV14" s="87"/>
+      <c r="AW14" s="87"/>
+      <c r="AX14" s="87"/>
+      <c r="AY14" s="87"/>
+      <c r="AZ14" s="87"/>
+      <c r="BA14" s="87"/>
+      <c r="BB14" s="87"/>
+      <c r="BC14" s="87"/>
+      <c r="BD14" s="87"/>
+      <c r="BE14" s="93"/>
     </row>
     <row r="15" spans="1:57" ht="15" customHeight="1">
-      <c r="A15" s="101"/>
-      <c r="B15" s="102"/>
-      <c r="C15" s="102"/>
-      <c r="D15" s="102"/>
-      <c r="E15" s="102"/>
-      <c r="F15" s="102"/>
-      <c r="G15" s="103"/>
+      <c r="A15" s="81"/>
+      <c r="B15" s="82"/>
+      <c r="C15" s="82"/>
+      <c r="D15" s="82"/>
+      <c r="E15" s="82"/>
+      <c r="F15" s="82"/>
+      <c r="G15" s="83"/>
       <c r="H15" s="84"/>
       <c r="I15" s="85"/>
       <c r="J15" s="85"/>
@@ -65729,57 +65740,57 @@
       <c r="M15" s="85"/>
       <c r="N15" s="86"/>
       <c r="O15" s="84"/>
-      <c r="P15" s="82"/>
-      <c r="Q15" s="82"/>
-      <c r="R15" s="82"/>
-      <c r="S15" s="82"/>
-      <c r="T15" s="82"/>
-      <c r="U15" s="82"/>
-      <c r="V15" s="82"/>
-      <c r="W15" s="82"/>
-      <c r="X15" s="82"/>
-      <c r="Y15" s="82"/>
-      <c r="Z15" s="82"/>
-      <c r="AA15" s="82"/>
-      <c r="AB15" s="82"/>
-      <c r="AC15" s="82"/>
-      <c r="AD15" s="82"/>
-      <c r="AE15" s="82"/>
-      <c r="AF15" s="82"/>
-      <c r="AG15" s="82"/>
-      <c r="AH15" s="82"/>
-      <c r="AI15" s="82"/>
-      <c r="AJ15" s="82"/>
-      <c r="AK15" s="82"/>
-      <c r="AL15" s="82"/>
-      <c r="AM15" s="82"/>
-      <c r="AN15" s="82"/>
-      <c r="AO15" s="82"/>
-      <c r="AP15" s="90"/>
-      <c r="AQ15" s="81"/>
-      <c r="AR15" s="82"/>
-      <c r="AS15" s="82"/>
-      <c r="AT15" s="82"/>
-      <c r="AU15" s="82"/>
-      <c r="AV15" s="82"/>
-      <c r="AW15" s="82"/>
-      <c r="AX15" s="82"/>
-      <c r="AY15" s="82"/>
-      <c r="AZ15" s="82"/>
-      <c r="BA15" s="82"/>
-      <c r="BB15" s="82"/>
-      <c r="BC15" s="82"/>
-      <c r="BD15" s="82"/>
-      <c r="BE15" s="83"/>
+      <c r="P15" s="87"/>
+      <c r="Q15" s="87"/>
+      <c r="R15" s="87"/>
+      <c r="S15" s="87"/>
+      <c r="T15" s="87"/>
+      <c r="U15" s="87"/>
+      <c r="V15" s="87"/>
+      <c r="W15" s="87"/>
+      <c r="X15" s="87"/>
+      <c r="Y15" s="87"/>
+      <c r="Z15" s="87"/>
+      <c r="AA15" s="87"/>
+      <c r="AB15" s="87"/>
+      <c r="AC15" s="87"/>
+      <c r="AD15" s="87"/>
+      <c r="AE15" s="87"/>
+      <c r="AF15" s="87"/>
+      <c r="AG15" s="87"/>
+      <c r="AH15" s="87"/>
+      <c r="AI15" s="87"/>
+      <c r="AJ15" s="87"/>
+      <c r="AK15" s="87"/>
+      <c r="AL15" s="87"/>
+      <c r="AM15" s="87"/>
+      <c r="AN15" s="87"/>
+      <c r="AO15" s="87"/>
+      <c r="AP15" s="88"/>
+      <c r="AQ15" s="92"/>
+      <c r="AR15" s="87"/>
+      <c r="AS15" s="87"/>
+      <c r="AT15" s="87"/>
+      <c r="AU15" s="87"/>
+      <c r="AV15" s="87"/>
+      <c r="AW15" s="87"/>
+      <c r="AX15" s="87"/>
+      <c r="AY15" s="87"/>
+      <c r="AZ15" s="87"/>
+      <c r="BA15" s="87"/>
+      <c r="BB15" s="87"/>
+      <c r="BC15" s="87"/>
+      <c r="BD15" s="87"/>
+      <c r="BE15" s="93"/>
     </row>
     <row r="16" spans="1:57" ht="15" customHeight="1">
-      <c r="A16" s="101"/>
-      <c r="B16" s="102"/>
-      <c r="C16" s="102"/>
-      <c r="D16" s="102"/>
-      <c r="E16" s="102"/>
-      <c r="F16" s="102"/>
-      <c r="G16" s="103"/>
+      <c r="A16" s="81"/>
+      <c r="B16" s="82"/>
+      <c r="C16" s="82"/>
+      <c r="D16" s="82"/>
+      <c r="E16" s="82"/>
+      <c r="F16" s="82"/>
+      <c r="G16" s="83"/>
       <c r="H16" s="84"/>
       <c r="I16" s="85"/>
       <c r="J16" s="85"/>
@@ -65788,57 +65799,57 @@
       <c r="M16" s="85"/>
       <c r="N16" s="86"/>
       <c r="O16" s="84"/>
-      <c r="P16" s="82"/>
-      <c r="Q16" s="82"/>
-      <c r="R16" s="82"/>
-      <c r="S16" s="82"/>
-      <c r="T16" s="82"/>
-      <c r="U16" s="82"/>
-      <c r="V16" s="82"/>
-      <c r="W16" s="82"/>
-      <c r="X16" s="82"/>
-      <c r="Y16" s="82"/>
-      <c r="Z16" s="82"/>
-      <c r="AA16" s="82"/>
-      <c r="AB16" s="82"/>
-      <c r="AC16" s="82"/>
-      <c r="AD16" s="82"/>
-      <c r="AE16" s="82"/>
-      <c r="AF16" s="82"/>
-      <c r="AG16" s="82"/>
-      <c r="AH16" s="82"/>
-      <c r="AI16" s="82"/>
-      <c r="AJ16" s="82"/>
-      <c r="AK16" s="82"/>
-      <c r="AL16" s="82"/>
-      <c r="AM16" s="82"/>
-      <c r="AN16" s="82"/>
-      <c r="AO16" s="82"/>
-      <c r="AP16" s="90"/>
-      <c r="AQ16" s="81"/>
-      <c r="AR16" s="82"/>
-      <c r="AS16" s="82"/>
-      <c r="AT16" s="82"/>
-      <c r="AU16" s="82"/>
-      <c r="AV16" s="82"/>
-      <c r="AW16" s="82"/>
-      <c r="AX16" s="82"/>
-      <c r="AY16" s="82"/>
-      <c r="AZ16" s="82"/>
-      <c r="BA16" s="82"/>
-      <c r="BB16" s="82"/>
-      <c r="BC16" s="82"/>
-      <c r="BD16" s="82"/>
-      <c r="BE16" s="83"/>
+      <c r="P16" s="87"/>
+      <c r="Q16" s="87"/>
+      <c r="R16" s="87"/>
+      <c r="S16" s="87"/>
+      <c r="T16" s="87"/>
+      <c r="U16" s="87"/>
+      <c r="V16" s="87"/>
+      <c r="W16" s="87"/>
+      <c r="X16" s="87"/>
+      <c r="Y16" s="87"/>
+      <c r="Z16" s="87"/>
+      <c r="AA16" s="87"/>
+      <c r="AB16" s="87"/>
+      <c r="AC16" s="87"/>
+      <c r="AD16" s="87"/>
+      <c r="AE16" s="87"/>
+      <c r="AF16" s="87"/>
+      <c r="AG16" s="87"/>
+      <c r="AH16" s="87"/>
+      <c r="AI16" s="87"/>
+      <c r="AJ16" s="87"/>
+      <c r="AK16" s="87"/>
+      <c r="AL16" s="87"/>
+      <c r="AM16" s="87"/>
+      <c r="AN16" s="87"/>
+      <c r="AO16" s="87"/>
+      <c r="AP16" s="88"/>
+      <c r="AQ16" s="92"/>
+      <c r="AR16" s="87"/>
+      <c r="AS16" s="87"/>
+      <c r="AT16" s="87"/>
+      <c r="AU16" s="87"/>
+      <c r="AV16" s="87"/>
+      <c r="AW16" s="87"/>
+      <c r="AX16" s="87"/>
+      <c r="AY16" s="87"/>
+      <c r="AZ16" s="87"/>
+      <c r="BA16" s="87"/>
+      <c r="BB16" s="87"/>
+      <c r="BC16" s="87"/>
+      <c r="BD16" s="87"/>
+      <c r="BE16" s="93"/>
     </row>
     <row r="17" spans="1:57" ht="15" customHeight="1">
-      <c r="A17" s="101"/>
-      <c r="B17" s="102"/>
-      <c r="C17" s="102"/>
-      <c r="D17" s="102"/>
-      <c r="E17" s="102"/>
-      <c r="F17" s="102"/>
-      <c r="G17" s="103"/>
+      <c r="A17" s="81"/>
+      <c r="B17" s="82"/>
+      <c r="C17" s="82"/>
+      <c r="D17" s="82"/>
+      <c r="E17" s="82"/>
+      <c r="F17" s="82"/>
+      <c r="G17" s="83"/>
       <c r="H17" s="84"/>
       <c r="I17" s="85"/>
       <c r="J17" s="85"/>
@@ -65847,57 +65858,57 @@
       <c r="M17" s="85"/>
       <c r="N17" s="86"/>
       <c r="O17" s="84"/>
-      <c r="P17" s="82"/>
-      <c r="Q17" s="82"/>
-      <c r="R17" s="82"/>
-      <c r="S17" s="82"/>
-      <c r="T17" s="82"/>
-      <c r="U17" s="82"/>
-      <c r="V17" s="82"/>
-      <c r="W17" s="82"/>
-      <c r="X17" s="82"/>
-      <c r="Y17" s="82"/>
-      <c r="Z17" s="82"/>
-      <c r="AA17" s="82"/>
-      <c r="AB17" s="82"/>
-      <c r="AC17" s="82"/>
-      <c r="AD17" s="82"/>
-      <c r="AE17" s="82"/>
-      <c r="AF17" s="82"/>
-      <c r="AG17" s="82"/>
-      <c r="AH17" s="82"/>
-      <c r="AI17" s="82"/>
-      <c r="AJ17" s="82"/>
-      <c r="AK17" s="82"/>
-      <c r="AL17" s="82"/>
-      <c r="AM17" s="82"/>
-      <c r="AN17" s="82"/>
-      <c r="AO17" s="82"/>
-      <c r="AP17" s="90"/>
-      <c r="AQ17" s="81"/>
-      <c r="AR17" s="82"/>
-      <c r="AS17" s="82"/>
-      <c r="AT17" s="82"/>
-      <c r="AU17" s="82"/>
-      <c r="AV17" s="82"/>
-      <c r="AW17" s="82"/>
-      <c r="AX17" s="82"/>
-      <c r="AY17" s="82"/>
-      <c r="AZ17" s="82"/>
-      <c r="BA17" s="82"/>
-      <c r="BB17" s="82"/>
-      <c r="BC17" s="82"/>
-      <c r="BD17" s="82"/>
-      <c r="BE17" s="83"/>
+      <c r="P17" s="87"/>
+      <c r="Q17" s="87"/>
+      <c r="R17" s="87"/>
+      <c r="S17" s="87"/>
+      <c r="T17" s="87"/>
+      <c r="U17" s="87"/>
+      <c r="V17" s="87"/>
+      <c r="W17" s="87"/>
+      <c r="X17" s="87"/>
+      <c r="Y17" s="87"/>
+      <c r="Z17" s="87"/>
+      <c r="AA17" s="87"/>
+      <c r="AB17" s="87"/>
+      <c r="AC17" s="87"/>
+      <c r="AD17" s="87"/>
+      <c r="AE17" s="87"/>
+      <c r="AF17" s="87"/>
+      <c r="AG17" s="87"/>
+      <c r="AH17" s="87"/>
+      <c r="AI17" s="87"/>
+      <c r="AJ17" s="87"/>
+      <c r="AK17" s="87"/>
+      <c r="AL17" s="87"/>
+      <c r="AM17" s="87"/>
+      <c r="AN17" s="87"/>
+      <c r="AO17" s="87"/>
+      <c r="AP17" s="88"/>
+      <c r="AQ17" s="92"/>
+      <c r="AR17" s="87"/>
+      <c r="AS17" s="87"/>
+      <c r="AT17" s="87"/>
+      <c r="AU17" s="87"/>
+      <c r="AV17" s="87"/>
+      <c r="AW17" s="87"/>
+      <c r="AX17" s="87"/>
+      <c r="AY17" s="87"/>
+      <c r="AZ17" s="87"/>
+      <c r="BA17" s="87"/>
+      <c r="BB17" s="87"/>
+      <c r="BC17" s="87"/>
+      <c r="BD17" s="87"/>
+      <c r="BE17" s="93"/>
     </row>
     <row r="18" spans="1:57" ht="15" customHeight="1">
-      <c r="A18" s="101"/>
-      <c r="B18" s="102"/>
-      <c r="C18" s="102"/>
-      <c r="D18" s="102"/>
-      <c r="E18" s="102"/>
-      <c r="F18" s="102"/>
-      <c r="G18" s="103"/>
+      <c r="A18" s="81"/>
+      <c r="B18" s="82"/>
+      <c r="C18" s="82"/>
+      <c r="D18" s="82"/>
+      <c r="E18" s="82"/>
+      <c r="F18" s="82"/>
+      <c r="G18" s="83"/>
       <c r="H18" s="84"/>
       <c r="I18" s="85"/>
       <c r="J18" s="85"/>
@@ -65906,57 +65917,57 @@
       <c r="M18" s="85"/>
       <c r="N18" s="86"/>
       <c r="O18" s="84"/>
-      <c r="P18" s="82"/>
-      <c r="Q18" s="82"/>
-      <c r="R18" s="82"/>
-      <c r="S18" s="82"/>
-      <c r="T18" s="82"/>
-      <c r="U18" s="82"/>
-      <c r="V18" s="82"/>
-      <c r="W18" s="82"/>
-      <c r="X18" s="82"/>
-      <c r="Y18" s="82"/>
-      <c r="Z18" s="82"/>
-      <c r="AA18" s="82"/>
-      <c r="AB18" s="82"/>
-      <c r="AC18" s="82"/>
-      <c r="AD18" s="82"/>
-      <c r="AE18" s="82"/>
-      <c r="AF18" s="82"/>
-      <c r="AG18" s="82"/>
-      <c r="AH18" s="82"/>
-      <c r="AI18" s="82"/>
-      <c r="AJ18" s="82"/>
-      <c r="AK18" s="82"/>
-      <c r="AL18" s="82"/>
-      <c r="AM18" s="82"/>
-      <c r="AN18" s="82"/>
-      <c r="AO18" s="82"/>
-      <c r="AP18" s="90"/>
-      <c r="AQ18" s="81"/>
-      <c r="AR18" s="82"/>
-      <c r="AS18" s="82"/>
-      <c r="AT18" s="82"/>
-      <c r="AU18" s="82"/>
-      <c r="AV18" s="82"/>
-      <c r="AW18" s="82"/>
-      <c r="AX18" s="82"/>
-      <c r="AY18" s="82"/>
-      <c r="AZ18" s="82"/>
-      <c r="BA18" s="82"/>
-      <c r="BB18" s="82"/>
-      <c r="BC18" s="82"/>
-      <c r="BD18" s="82"/>
-      <c r="BE18" s="83"/>
+      <c r="P18" s="87"/>
+      <c r="Q18" s="87"/>
+      <c r="R18" s="87"/>
+      <c r="S18" s="87"/>
+      <c r="T18" s="87"/>
+      <c r="U18" s="87"/>
+      <c r="V18" s="87"/>
+      <c r="W18" s="87"/>
+      <c r="X18" s="87"/>
+      <c r="Y18" s="87"/>
+      <c r="Z18" s="87"/>
+      <c r="AA18" s="87"/>
+      <c r="AB18" s="87"/>
+      <c r="AC18" s="87"/>
+      <c r="AD18" s="87"/>
+      <c r="AE18" s="87"/>
+      <c r="AF18" s="87"/>
+      <c r="AG18" s="87"/>
+      <c r="AH18" s="87"/>
+      <c r="AI18" s="87"/>
+      <c r="AJ18" s="87"/>
+      <c r="AK18" s="87"/>
+      <c r="AL18" s="87"/>
+      <c r="AM18" s="87"/>
+      <c r="AN18" s="87"/>
+      <c r="AO18" s="87"/>
+      <c r="AP18" s="88"/>
+      <c r="AQ18" s="92"/>
+      <c r="AR18" s="87"/>
+      <c r="AS18" s="87"/>
+      <c r="AT18" s="87"/>
+      <c r="AU18" s="87"/>
+      <c r="AV18" s="87"/>
+      <c r="AW18" s="87"/>
+      <c r="AX18" s="87"/>
+      <c r="AY18" s="87"/>
+      <c r="AZ18" s="87"/>
+      <c r="BA18" s="87"/>
+      <c r="BB18" s="87"/>
+      <c r="BC18" s="87"/>
+      <c r="BD18" s="87"/>
+      <c r="BE18" s="93"/>
     </row>
     <row r="19" spans="1:57" ht="15" customHeight="1">
-      <c r="A19" s="101"/>
-      <c r="B19" s="102"/>
-      <c r="C19" s="102"/>
-      <c r="D19" s="102"/>
-      <c r="E19" s="102"/>
-      <c r="F19" s="102"/>
-      <c r="G19" s="103"/>
+      <c r="A19" s="81"/>
+      <c r="B19" s="82"/>
+      <c r="C19" s="82"/>
+      <c r="D19" s="82"/>
+      <c r="E19" s="82"/>
+      <c r="F19" s="82"/>
+      <c r="G19" s="83"/>
       <c r="H19" s="84"/>
       <c r="I19" s="85"/>
       <c r="J19" s="85"/>
@@ -65965,57 +65976,57 @@
       <c r="M19" s="85"/>
       <c r="N19" s="86"/>
       <c r="O19" s="84"/>
-      <c r="P19" s="82"/>
-      <c r="Q19" s="82"/>
-      <c r="R19" s="82"/>
-      <c r="S19" s="82"/>
-      <c r="T19" s="82"/>
-      <c r="U19" s="82"/>
-      <c r="V19" s="82"/>
-      <c r="W19" s="82"/>
-      <c r="X19" s="82"/>
-      <c r="Y19" s="82"/>
-      <c r="Z19" s="82"/>
-      <c r="AA19" s="82"/>
-      <c r="AB19" s="82"/>
-      <c r="AC19" s="82"/>
-      <c r="AD19" s="82"/>
-      <c r="AE19" s="82"/>
-      <c r="AF19" s="82"/>
-      <c r="AG19" s="82"/>
-      <c r="AH19" s="82"/>
-      <c r="AI19" s="82"/>
-      <c r="AJ19" s="82"/>
-      <c r="AK19" s="82"/>
-      <c r="AL19" s="82"/>
-      <c r="AM19" s="82"/>
-      <c r="AN19" s="82"/>
-      <c r="AO19" s="82"/>
-      <c r="AP19" s="90"/>
-      <c r="AQ19" s="81"/>
-      <c r="AR19" s="82"/>
-      <c r="AS19" s="82"/>
-      <c r="AT19" s="82"/>
-      <c r="AU19" s="82"/>
-      <c r="AV19" s="82"/>
-      <c r="AW19" s="82"/>
-      <c r="AX19" s="82"/>
-      <c r="AY19" s="82"/>
-      <c r="AZ19" s="82"/>
-      <c r="BA19" s="82"/>
-      <c r="BB19" s="82"/>
-      <c r="BC19" s="82"/>
-      <c r="BD19" s="82"/>
-      <c r="BE19" s="83"/>
+      <c r="P19" s="87"/>
+      <c r="Q19" s="87"/>
+      <c r="R19" s="87"/>
+      <c r="S19" s="87"/>
+      <c r="T19" s="87"/>
+      <c r="U19" s="87"/>
+      <c r="V19" s="87"/>
+      <c r="W19" s="87"/>
+      <c r="X19" s="87"/>
+      <c r="Y19" s="87"/>
+      <c r="Z19" s="87"/>
+      <c r="AA19" s="87"/>
+      <c r="AB19" s="87"/>
+      <c r="AC19" s="87"/>
+      <c r="AD19" s="87"/>
+      <c r="AE19" s="87"/>
+      <c r="AF19" s="87"/>
+      <c r="AG19" s="87"/>
+      <c r="AH19" s="87"/>
+      <c r="AI19" s="87"/>
+      <c r="AJ19" s="87"/>
+      <c r="AK19" s="87"/>
+      <c r="AL19" s="87"/>
+      <c r="AM19" s="87"/>
+      <c r="AN19" s="87"/>
+      <c r="AO19" s="87"/>
+      <c r="AP19" s="88"/>
+      <c r="AQ19" s="92"/>
+      <c r="AR19" s="87"/>
+      <c r="AS19" s="87"/>
+      <c r="AT19" s="87"/>
+      <c r="AU19" s="87"/>
+      <c r="AV19" s="87"/>
+      <c r="AW19" s="87"/>
+      <c r="AX19" s="87"/>
+      <c r="AY19" s="87"/>
+      <c r="AZ19" s="87"/>
+      <c r="BA19" s="87"/>
+      <c r="BB19" s="87"/>
+      <c r="BC19" s="87"/>
+      <c r="BD19" s="87"/>
+      <c r="BE19" s="93"/>
     </row>
     <row r="20" spans="1:57" ht="15" customHeight="1">
-      <c r="A20" s="101"/>
-      <c r="B20" s="102"/>
-      <c r="C20" s="102"/>
-      <c r="D20" s="102"/>
-      <c r="E20" s="102"/>
-      <c r="F20" s="102"/>
-      <c r="G20" s="103"/>
+      <c r="A20" s="81"/>
+      <c r="B20" s="82"/>
+      <c r="C20" s="82"/>
+      <c r="D20" s="82"/>
+      <c r="E20" s="82"/>
+      <c r="F20" s="82"/>
+      <c r="G20" s="83"/>
       <c r="H20" s="84"/>
       <c r="I20" s="85"/>
       <c r="J20" s="85"/>
@@ -66024,57 +66035,57 @@
       <c r="M20" s="85"/>
       <c r="N20" s="86"/>
       <c r="O20" s="84"/>
-      <c r="P20" s="82"/>
-      <c r="Q20" s="82"/>
-      <c r="R20" s="82"/>
-      <c r="S20" s="82"/>
-      <c r="T20" s="82"/>
-      <c r="U20" s="82"/>
-      <c r="V20" s="82"/>
-      <c r="W20" s="82"/>
-      <c r="X20" s="82"/>
-      <c r="Y20" s="82"/>
-      <c r="Z20" s="82"/>
-      <c r="AA20" s="82"/>
-      <c r="AB20" s="82"/>
-      <c r="AC20" s="82"/>
-      <c r="AD20" s="82"/>
-      <c r="AE20" s="82"/>
-      <c r="AF20" s="82"/>
-      <c r="AG20" s="82"/>
-      <c r="AH20" s="82"/>
-      <c r="AI20" s="82"/>
-      <c r="AJ20" s="82"/>
-      <c r="AK20" s="82"/>
-      <c r="AL20" s="82"/>
-      <c r="AM20" s="82"/>
-      <c r="AN20" s="82"/>
-      <c r="AO20" s="82"/>
-      <c r="AP20" s="90"/>
-      <c r="AQ20" s="81"/>
-      <c r="AR20" s="82"/>
-      <c r="AS20" s="82"/>
-      <c r="AT20" s="82"/>
-      <c r="AU20" s="82"/>
-      <c r="AV20" s="82"/>
-      <c r="AW20" s="82"/>
-      <c r="AX20" s="82"/>
-      <c r="AY20" s="82"/>
-      <c r="AZ20" s="82"/>
-      <c r="BA20" s="82"/>
-      <c r="BB20" s="82"/>
-      <c r="BC20" s="82"/>
-      <c r="BD20" s="82"/>
-      <c r="BE20" s="83"/>
+      <c r="P20" s="87"/>
+      <c r="Q20" s="87"/>
+      <c r="R20" s="87"/>
+      <c r="S20" s="87"/>
+      <c r="T20" s="87"/>
+      <c r="U20" s="87"/>
+      <c r="V20" s="87"/>
+      <c r="W20" s="87"/>
+      <c r="X20" s="87"/>
+      <c r="Y20" s="87"/>
+      <c r="Z20" s="87"/>
+      <c r="AA20" s="87"/>
+      <c r="AB20" s="87"/>
+      <c r="AC20" s="87"/>
+      <c r="AD20" s="87"/>
+      <c r="AE20" s="87"/>
+      <c r="AF20" s="87"/>
+      <c r="AG20" s="87"/>
+      <c r="AH20" s="87"/>
+      <c r="AI20" s="87"/>
+      <c r="AJ20" s="87"/>
+      <c r="AK20" s="87"/>
+      <c r="AL20" s="87"/>
+      <c r="AM20" s="87"/>
+      <c r="AN20" s="87"/>
+      <c r="AO20" s="87"/>
+      <c r="AP20" s="88"/>
+      <c r="AQ20" s="92"/>
+      <c r="AR20" s="87"/>
+      <c r="AS20" s="87"/>
+      <c r="AT20" s="87"/>
+      <c r="AU20" s="87"/>
+      <c r="AV20" s="87"/>
+      <c r="AW20" s="87"/>
+      <c r="AX20" s="87"/>
+      <c r="AY20" s="87"/>
+      <c r="AZ20" s="87"/>
+      <c r="BA20" s="87"/>
+      <c r="BB20" s="87"/>
+      <c r="BC20" s="87"/>
+      <c r="BD20" s="87"/>
+      <c r="BE20" s="93"/>
     </row>
     <row r="21" spans="1:57" ht="15" customHeight="1">
-      <c r="A21" s="101"/>
-      <c r="B21" s="102"/>
-      <c r="C21" s="102"/>
-      <c r="D21" s="102"/>
-      <c r="E21" s="102"/>
-      <c r="F21" s="102"/>
-      <c r="G21" s="103"/>
+      <c r="A21" s="81"/>
+      <c r="B21" s="82"/>
+      <c r="C21" s="82"/>
+      <c r="D21" s="82"/>
+      <c r="E21" s="82"/>
+      <c r="F21" s="82"/>
+      <c r="G21" s="83"/>
       <c r="H21" s="84"/>
       <c r="I21" s="85"/>
       <c r="J21" s="85"/>
@@ -66083,57 +66094,57 @@
       <c r="M21" s="85"/>
       <c r="N21" s="86"/>
       <c r="O21" s="84"/>
-      <c r="P21" s="82"/>
-      <c r="Q21" s="82"/>
-      <c r="R21" s="82"/>
-      <c r="S21" s="82"/>
-      <c r="T21" s="82"/>
-      <c r="U21" s="82"/>
-      <c r="V21" s="82"/>
-      <c r="W21" s="82"/>
-      <c r="X21" s="82"/>
-      <c r="Y21" s="82"/>
-      <c r="Z21" s="82"/>
-      <c r="AA21" s="82"/>
-      <c r="AB21" s="82"/>
-      <c r="AC21" s="82"/>
-      <c r="AD21" s="82"/>
-      <c r="AE21" s="82"/>
-      <c r="AF21" s="82"/>
-      <c r="AG21" s="82"/>
-      <c r="AH21" s="82"/>
-      <c r="AI21" s="82"/>
-      <c r="AJ21" s="82"/>
-      <c r="AK21" s="82"/>
-      <c r="AL21" s="82"/>
-      <c r="AM21" s="82"/>
-      <c r="AN21" s="82"/>
-      <c r="AO21" s="82"/>
-      <c r="AP21" s="90"/>
-      <c r="AQ21" s="81"/>
-      <c r="AR21" s="82"/>
-      <c r="AS21" s="82"/>
-      <c r="AT21" s="82"/>
-      <c r="AU21" s="82"/>
-      <c r="AV21" s="82"/>
-      <c r="AW21" s="82"/>
-      <c r="AX21" s="82"/>
-      <c r="AY21" s="82"/>
-      <c r="AZ21" s="82"/>
-      <c r="BA21" s="82"/>
-      <c r="BB21" s="82"/>
-      <c r="BC21" s="82"/>
-      <c r="BD21" s="82"/>
-      <c r="BE21" s="83"/>
+      <c r="P21" s="87"/>
+      <c r="Q21" s="87"/>
+      <c r="R21" s="87"/>
+      <c r="S21" s="87"/>
+      <c r="T21" s="87"/>
+      <c r="U21" s="87"/>
+      <c r="V21" s="87"/>
+      <c r="W21" s="87"/>
+      <c r="X21" s="87"/>
+      <c r="Y21" s="87"/>
+      <c r="Z21" s="87"/>
+      <c r="AA21" s="87"/>
+      <c r="AB21" s="87"/>
+      <c r="AC21" s="87"/>
+      <c r="AD21" s="87"/>
+      <c r="AE21" s="87"/>
+      <c r="AF21" s="87"/>
+      <c r="AG21" s="87"/>
+      <c r="AH21" s="87"/>
+      <c r="AI21" s="87"/>
+      <c r="AJ21" s="87"/>
+      <c r="AK21" s="87"/>
+      <c r="AL21" s="87"/>
+      <c r="AM21" s="87"/>
+      <c r="AN21" s="87"/>
+      <c r="AO21" s="87"/>
+      <c r="AP21" s="88"/>
+      <c r="AQ21" s="92"/>
+      <c r="AR21" s="87"/>
+      <c r="AS21" s="87"/>
+      <c r="AT21" s="87"/>
+      <c r="AU21" s="87"/>
+      <c r="AV21" s="87"/>
+      <c r="AW21" s="87"/>
+      <c r="AX21" s="87"/>
+      <c r="AY21" s="87"/>
+      <c r="AZ21" s="87"/>
+      <c r="BA21" s="87"/>
+      <c r="BB21" s="87"/>
+      <c r="BC21" s="87"/>
+      <c r="BD21" s="87"/>
+      <c r="BE21" s="93"/>
     </row>
     <row r="22" spans="1:57" ht="15" customHeight="1">
-      <c r="A22" s="101"/>
-      <c r="B22" s="102"/>
-      <c r="C22" s="102"/>
-      <c r="D22" s="102"/>
-      <c r="E22" s="102"/>
-      <c r="F22" s="102"/>
-      <c r="G22" s="103"/>
+      <c r="A22" s="81"/>
+      <c r="B22" s="82"/>
+      <c r="C22" s="82"/>
+      <c r="D22" s="82"/>
+      <c r="E22" s="82"/>
+      <c r="F22" s="82"/>
+      <c r="G22" s="83"/>
       <c r="H22" s="84"/>
       <c r="I22" s="85"/>
       <c r="J22" s="85"/>
@@ -66142,57 +66153,57 @@
       <c r="M22" s="85"/>
       <c r="N22" s="86"/>
       <c r="O22" s="84"/>
-      <c r="P22" s="82"/>
-      <c r="Q22" s="82"/>
-      <c r="R22" s="82"/>
-      <c r="S22" s="82"/>
-      <c r="T22" s="82"/>
-      <c r="U22" s="82"/>
-      <c r="V22" s="82"/>
-      <c r="W22" s="82"/>
-      <c r="X22" s="82"/>
-      <c r="Y22" s="82"/>
-      <c r="Z22" s="82"/>
-      <c r="AA22" s="82"/>
-      <c r="AB22" s="82"/>
-      <c r="AC22" s="82"/>
-      <c r="AD22" s="82"/>
-      <c r="AE22" s="82"/>
-      <c r="AF22" s="82"/>
-      <c r="AG22" s="82"/>
-      <c r="AH22" s="82"/>
-      <c r="AI22" s="82"/>
-      <c r="AJ22" s="82"/>
-      <c r="AK22" s="82"/>
-      <c r="AL22" s="82"/>
-      <c r="AM22" s="82"/>
-      <c r="AN22" s="82"/>
-      <c r="AO22" s="82"/>
-      <c r="AP22" s="90"/>
-      <c r="AQ22" s="81"/>
-      <c r="AR22" s="82"/>
-      <c r="AS22" s="82"/>
-      <c r="AT22" s="82"/>
-      <c r="AU22" s="82"/>
-      <c r="AV22" s="82"/>
-      <c r="AW22" s="82"/>
-      <c r="AX22" s="82"/>
-      <c r="AY22" s="82"/>
-      <c r="AZ22" s="82"/>
-      <c r="BA22" s="82"/>
-      <c r="BB22" s="82"/>
-      <c r="BC22" s="82"/>
-      <c r="BD22" s="82"/>
-      <c r="BE22" s="83"/>
+      <c r="P22" s="87"/>
+      <c r="Q22" s="87"/>
+      <c r="R22" s="87"/>
+      <c r="S22" s="87"/>
+      <c r="T22" s="87"/>
+      <c r="U22" s="87"/>
+      <c r="V22" s="87"/>
+      <c r="W22" s="87"/>
+      <c r="X22" s="87"/>
+      <c r="Y22" s="87"/>
+      <c r="Z22" s="87"/>
+      <c r="AA22" s="87"/>
+      <c r="AB22" s="87"/>
+      <c r="AC22" s="87"/>
+      <c r="AD22" s="87"/>
+      <c r="AE22" s="87"/>
+      <c r="AF22" s="87"/>
+      <c r="AG22" s="87"/>
+      <c r="AH22" s="87"/>
+      <c r="AI22" s="87"/>
+      <c r="AJ22" s="87"/>
+      <c r="AK22" s="87"/>
+      <c r="AL22" s="87"/>
+      <c r="AM22" s="87"/>
+      <c r="AN22" s="87"/>
+      <c r="AO22" s="87"/>
+      <c r="AP22" s="88"/>
+      <c r="AQ22" s="92"/>
+      <c r="AR22" s="87"/>
+      <c r="AS22" s="87"/>
+      <c r="AT22" s="87"/>
+      <c r="AU22" s="87"/>
+      <c r="AV22" s="87"/>
+      <c r="AW22" s="87"/>
+      <c r="AX22" s="87"/>
+      <c r="AY22" s="87"/>
+      <c r="AZ22" s="87"/>
+      <c r="BA22" s="87"/>
+      <c r="BB22" s="87"/>
+      <c r="BC22" s="87"/>
+      <c r="BD22" s="87"/>
+      <c r="BE22" s="93"/>
     </row>
     <row r="23" spans="1:57" ht="15" customHeight="1">
-      <c r="A23" s="101"/>
-      <c r="B23" s="102"/>
-      <c r="C23" s="102"/>
-      <c r="D23" s="102"/>
-      <c r="E23" s="102"/>
-      <c r="F23" s="102"/>
-      <c r="G23" s="103"/>
+      <c r="A23" s="81"/>
+      <c r="B23" s="82"/>
+      <c r="C23" s="82"/>
+      <c r="D23" s="82"/>
+      <c r="E23" s="82"/>
+      <c r="F23" s="82"/>
+      <c r="G23" s="83"/>
       <c r="H23" s="84"/>
       <c r="I23" s="85"/>
       <c r="J23" s="85"/>
@@ -66201,57 +66212,57 @@
       <c r="M23" s="85"/>
       <c r="N23" s="86"/>
       <c r="O23" s="84"/>
-      <c r="P23" s="82"/>
-      <c r="Q23" s="82"/>
-      <c r="R23" s="82"/>
-      <c r="S23" s="82"/>
-      <c r="T23" s="82"/>
-      <c r="U23" s="82"/>
-      <c r="V23" s="82"/>
-      <c r="W23" s="82"/>
-      <c r="X23" s="82"/>
-      <c r="Y23" s="82"/>
-      <c r="Z23" s="82"/>
-      <c r="AA23" s="82"/>
-      <c r="AB23" s="82"/>
-      <c r="AC23" s="82"/>
-      <c r="AD23" s="82"/>
-      <c r="AE23" s="82"/>
-      <c r="AF23" s="82"/>
-      <c r="AG23" s="82"/>
-      <c r="AH23" s="82"/>
-      <c r="AI23" s="82"/>
-      <c r="AJ23" s="82"/>
-      <c r="AK23" s="82"/>
-      <c r="AL23" s="82"/>
-      <c r="AM23" s="82"/>
-      <c r="AN23" s="82"/>
-      <c r="AO23" s="82"/>
-      <c r="AP23" s="90"/>
-      <c r="AQ23" s="81"/>
-      <c r="AR23" s="82"/>
-      <c r="AS23" s="82"/>
-      <c r="AT23" s="82"/>
-      <c r="AU23" s="82"/>
-      <c r="AV23" s="82"/>
-      <c r="AW23" s="82"/>
-      <c r="AX23" s="82"/>
-      <c r="AY23" s="82"/>
-      <c r="AZ23" s="82"/>
-      <c r="BA23" s="82"/>
-      <c r="BB23" s="82"/>
-      <c r="BC23" s="82"/>
-      <c r="BD23" s="82"/>
-      <c r="BE23" s="83"/>
+      <c r="P23" s="87"/>
+      <c r="Q23" s="87"/>
+      <c r="R23" s="87"/>
+      <c r="S23" s="87"/>
+      <c r="T23" s="87"/>
+      <c r="U23" s="87"/>
+      <c r="V23" s="87"/>
+      <c r="W23" s="87"/>
+      <c r="X23" s="87"/>
+      <c r="Y23" s="87"/>
+      <c r="Z23" s="87"/>
+      <c r="AA23" s="87"/>
+      <c r="AB23" s="87"/>
+      <c r="AC23" s="87"/>
+      <c r="AD23" s="87"/>
+      <c r="AE23" s="87"/>
+      <c r="AF23" s="87"/>
+      <c r="AG23" s="87"/>
+      <c r="AH23" s="87"/>
+      <c r="AI23" s="87"/>
+      <c r="AJ23" s="87"/>
+      <c r="AK23" s="87"/>
+      <c r="AL23" s="87"/>
+      <c r="AM23" s="87"/>
+      <c r="AN23" s="87"/>
+      <c r="AO23" s="87"/>
+      <c r="AP23" s="88"/>
+      <c r="AQ23" s="92"/>
+      <c r="AR23" s="87"/>
+      <c r="AS23" s="87"/>
+      <c r="AT23" s="87"/>
+      <c r="AU23" s="87"/>
+      <c r="AV23" s="87"/>
+      <c r="AW23" s="87"/>
+      <c r="AX23" s="87"/>
+      <c r="AY23" s="87"/>
+      <c r="AZ23" s="87"/>
+      <c r="BA23" s="87"/>
+      <c r="BB23" s="87"/>
+      <c r="BC23" s="87"/>
+      <c r="BD23" s="87"/>
+      <c r="BE23" s="93"/>
     </row>
     <row r="24" spans="1:57" ht="15" customHeight="1">
-      <c r="A24" s="101"/>
-      <c r="B24" s="102"/>
-      <c r="C24" s="102"/>
-      <c r="D24" s="102"/>
-      <c r="E24" s="102"/>
-      <c r="F24" s="102"/>
-      <c r="G24" s="103"/>
+      <c r="A24" s="81"/>
+      <c r="B24" s="82"/>
+      <c r="C24" s="82"/>
+      <c r="D24" s="82"/>
+      <c r="E24" s="82"/>
+      <c r="F24" s="82"/>
+      <c r="G24" s="83"/>
       <c r="H24" s="84"/>
       <c r="I24" s="85"/>
       <c r="J24" s="85"/>
@@ -66260,57 +66271,57 @@
       <c r="M24" s="85"/>
       <c r="N24" s="86"/>
       <c r="O24" s="84"/>
-      <c r="P24" s="82"/>
-      <c r="Q24" s="82"/>
-      <c r="R24" s="82"/>
-      <c r="S24" s="82"/>
-      <c r="T24" s="82"/>
-      <c r="U24" s="82"/>
-      <c r="V24" s="82"/>
-      <c r="W24" s="82"/>
-      <c r="X24" s="82"/>
-      <c r="Y24" s="82"/>
-      <c r="Z24" s="82"/>
-      <c r="AA24" s="82"/>
-      <c r="AB24" s="82"/>
-      <c r="AC24" s="82"/>
-      <c r="AD24" s="82"/>
-      <c r="AE24" s="82"/>
-      <c r="AF24" s="82"/>
-      <c r="AG24" s="82"/>
-      <c r="AH24" s="82"/>
-      <c r="AI24" s="82"/>
-      <c r="AJ24" s="82"/>
-      <c r="AK24" s="82"/>
-      <c r="AL24" s="82"/>
-      <c r="AM24" s="82"/>
-      <c r="AN24" s="82"/>
-      <c r="AO24" s="82"/>
-      <c r="AP24" s="90"/>
-      <c r="AQ24" s="81"/>
-      <c r="AR24" s="82"/>
-      <c r="AS24" s="82"/>
-      <c r="AT24" s="82"/>
-      <c r="AU24" s="82"/>
-      <c r="AV24" s="82"/>
-      <c r="AW24" s="82"/>
-      <c r="AX24" s="82"/>
-      <c r="AY24" s="82"/>
-      <c r="AZ24" s="82"/>
-      <c r="BA24" s="82"/>
-      <c r="BB24" s="82"/>
-      <c r="BC24" s="82"/>
-      <c r="BD24" s="82"/>
-      <c r="BE24" s="83"/>
+      <c r="P24" s="87"/>
+      <c r="Q24" s="87"/>
+      <c r="R24" s="87"/>
+      <c r="S24" s="87"/>
+      <c r="T24" s="87"/>
+      <c r="U24" s="87"/>
+      <c r="V24" s="87"/>
+      <c r="W24" s="87"/>
+      <c r="X24" s="87"/>
+      <c r="Y24" s="87"/>
+      <c r="Z24" s="87"/>
+      <c r="AA24" s="87"/>
+      <c r="AB24" s="87"/>
+      <c r="AC24" s="87"/>
+      <c r="AD24" s="87"/>
+      <c r="AE24" s="87"/>
+      <c r="AF24" s="87"/>
+      <c r="AG24" s="87"/>
+      <c r="AH24" s="87"/>
+      <c r="AI24" s="87"/>
+      <c r="AJ24" s="87"/>
+      <c r="AK24" s="87"/>
+      <c r="AL24" s="87"/>
+      <c r="AM24" s="87"/>
+      <c r="AN24" s="87"/>
+      <c r="AO24" s="87"/>
+      <c r="AP24" s="88"/>
+      <c r="AQ24" s="92"/>
+      <c r="AR24" s="87"/>
+      <c r="AS24" s="87"/>
+      <c r="AT24" s="87"/>
+      <c r="AU24" s="87"/>
+      <c r="AV24" s="87"/>
+      <c r="AW24" s="87"/>
+      <c r="AX24" s="87"/>
+      <c r="AY24" s="87"/>
+      <c r="AZ24" s="87"/>
+      <c r="BA24" s="87"/>
+      <c r="BB24" s="87"/>
+      <c r="BC24" s="87"/>
+      <c r="BD24" s="87"/>
+      <c r="BE24" s="93"/>
     </row>
     <row r="25" spans="1:57" ht="15" customHeight="1">
-      <c r="A25" s="101"/>
-      <c r="B25" s="102"/>
-      <c r="C25" s="102"/>
-      <c r="D25" s="102"/>
-      <c r="E25" s="102"/>
-      <c r="F25" s="102"/>
-      <c r="G25" s="103"/>
+      <c r="A25" s="81"/>
+      <c r="B25" s="82"/>
+      <c r="C25" s="82"/>
+      <c r="D25" s="82"/>
+      <c r="E25" s="82"/>
+      <c r="F25" s="82"/>
+      <c r="G25" s="83"/>
       <c r="H25" s="84"/>
       <c r="I25" s="85"/>
       <c r="J25" s="85"/>
@@ -66319,57 +66330,57 @@
       <c r="M25" s="85"/>
       <c r="N25" s="86"/>
       <c r="O25" s="84"/>
-      <c r="P25" s="82"/>
-      <c r="Q25" s="82"/>
-      <c r="R25" s="82"/>
-      <c r="S25" s="82"/>
-      <c r="T25" s="82"/>
-      <c r="U25" s="82"/>
-      <c r="V25" s="82"/>
-      <c r="W25" s="82"/>
-      <c r="X25" s="82"/>
-      <c r="Y25" s="82"/>
-      <c r="Z25" s="82"/>
-      <c r="AA25" s="82"/>
-      <c r="AB25" s="82"/>
-      <c r="AC25" s="82"/>
-      <c r="AD25" s="82"/>
-      <c r="AE25" s="82"/>
-      <c r="AF25" s="82"/>
-      <c r="AG25" s="82"/>
-      <c r="AH25" s="82"/>
-      <c r="AI25" s="82"/>
-      <c r="AJ25" s="82"/>
-      <c r="AK25" s="82"/>
-      <c r="AL25" s="82"/>
-      <c r="AM25" s="82"/>
-      <c r="AN25" s="82"/>
-      <c r="AO25" s="82"/>
-      <c r="AP25" s="90"/>
-      <c r="AQ25" s="81"/>
-      <c r="AR25" s="82"/>
-      <c r="AS25" s="82"/>
-      <c r="AT25" s="82"/>
-      <c r="AU25" s="82"/>
-      <c r="AV25" s="82"/>
-      <c r="AW25" s="82"/>
-      <c r="AX25" s="82"/>
-      <c r="AY25" s="82"/>
-      <c r="AZ25" s="82"/>
-      <c r="BA25" s="82"/>
-      <c r="BB25" s="82"/>
-      <c r="BC25" s="82"/>
-      <c r="BD25" s="82"/>
-      <c r="BE25" s="83"/>
+      <c r="P25" s="87"/>
+      <c r="Q25" s="87"/>
+      <c r="R25" s="87"/>
+      <c r="S25" s="87"/>
+      <c r="T25" s="87"/>
+      <c r="U25" s="87"/>
+      <c r="V25" s="87"/>
+      <c r="W25" s="87"/>
+      <c r="X25" s="87"/>
+      <c r="Y25" s="87"/>
+      <c r="Z25" s="87"/>
+      <c r="AA25" s="87"/>
+      <c r="AB25" s="87"/>
+      <c r="AC25" s="87"/>
+      <c r="AD25" s="87"/>
+      <c r="AE25" s="87"/>
+      <c r="AF25" s="87"/>
+      <c r="AG25" s="87"/>
+      <c r="AH25" s="87"/>
+      <c r="AI25" s="87"/>
+      <c r="AJ25" s="87"/>
+      <c r="AK25" s="87"/>
+      <c r="AL25" s="87"/>
+      <c r="AM25" s="87"/>
+      <c r="AN25" s="87"/>
+      <c r="AO25" s="87"/>
+      <c r="AP25" s="88"/>
+      <c r="AQ25" s="92"/>
+      <c r="AR25" s="87"/>
+      <c r="AS25" s="87"/>
+      <c r="AT25" s="87"/>
+      <c r="AU25" s="87"/>
+      <c r="AV25" s="87"/>
+      <c r="AW25" s="87"/>
+      <c r="AX25" s="87"/>
+      <c r="AY25" s="87"/>
+      <c r="AZ25" s="87"/>
+      <c r="BA25" s="87"/>
+      <c r="BB25" s="87"/>
+      <c r="BC25" s="87"/>
+      <c r="BD25" s="87"/>
+      <c r="BE25" s="93"/>
     </row>
     <row r="26" spans="1:57" ht="15" customHeight="1">
-      <c r="A26" s="101"/>
-      <c r="B26" s="102"/>
-      <c r="C26" s="102"/>
-      <c r="D26" s="102"/>
-      <c r="E26" s="102"/>
-      <c r="F26" s="102"/>
-      <c r="G26" s="103"/>
+      <c r="A26" s="81"/>
+      <c r="B26" s="82"/>
+      <c r="C26" s="82"/>
+      <c r="D26" s="82"/>
+      <c r="E26" s="82"/>
+      <c r="F26" s="82"/>
+      <c r="G26" s="83"/>
       <c r="H26" s="84"/>
       <c r="I26" s="85"/>
       <c r="J26" s="85"/>
@@ -66378,57 +66389,57 @@
       <c r="M26" s="85"/>
       <c r="N26" s="86"/>
       <c r="O26" s="84"/>
-      <c r="P26" s="82"/>
-      <c r="Q26" s="82"/>
-      <c r="R26" s="82"/>
-      <c r="S26" s="82"/>
-      <c r="T26" s="82"/>
-      <c r="U26" s="82"/>
-      <c r="V26" s="82"/>
-      <c r="W26" s="82"/>
-      <c r="X26" s="82"/>
-      <c r="Y26" s="82"/>
-      <c r="Z26" s="82"/>
-      <c r="AA26" s="82"/>
-      <c r="AB26" s="82"/>
-      <c r="AC26" s="82"/>
-      <c r="AD26" s="82"/>
-      <c r="AE26" s="82"/>
-      <c r="AF26" s="82"/>
-      <c r="AG26" s="82"/>
-      <c r="AH26" s="82"/>
-      <c r="AI26" s="82"/>
-      <c r="AJ26" s="82"/>
-      <c r="AK26" s="82"/>
-      <c r="AL26" s="82"/>
-      <c r="AM26" s="82"/>
-      <c r="AN26" s="82"/>
-      <c r="AO26" s="82"/>
-      <c r="AP26" s="90"/>
-      <c r="AQ26" s="81"/>
-      <c r="AR26" s="82"/>
-      <c r="AS26" s="82"/>
-      <c r="AT26" s="82"/>
-      <c r="AU26" s="82"/>
-      <c r="AV26" s="82"/>
-      <c r="AW26" s="82"/>
-      <c r="AX26" s="82"/>
-      <c r="AY26" s="82"/>
-      <c r="AZ26" s="82"/>
-      <c r="BA26" s="82"/>
-      <c r="BB26" s="82"/>
-      <c r="BC26" s="82"/>
-      <c r="BD26" s="82"/>
-      <c r="BE26" s="83"/>
+      <c r="P26" s="87"/>
+      <c r="Q26" s="87"/>
+      <c r="R26" s="87"/>
+      <c r="S26" s="87"/>
+      <c r="T26" s="87"/>
+      <c r="U26" s="87"/>
+      <c r="V26" s="87"/>
+      <c r="W26" s="87"/>
+      <c r="X26" s="87"/>
+      <c r="Y26" s="87"/>
+      <c r="Z26" s="87"/>
+      <c r="AA26" s="87"/>
+      <c r="AB26" s="87"/>
+      <c r="AC26" s="87"/>
+      <c r="AD26" s="87"/>
+      <c r="AE26" s="87"/>
+      <c r="AF26" s="87"/>
+      <c r="AG26" s="87"/>
+      <c r="AH26" s="87"/>
+      <c r="AI26" s="87"/>
+      <c r="AJ26" s="87"/>
+      <c r="AK26" s="87"/>
+      <c r="AL26" s="87"/>
+      <c r="AM26" s="87"/>
+      <c r="AN26" s="87"/>
+      <c r="AO26" s="87"/>
+      <c r="AP26" s="88"/>
+      <c r="AQ26" s="92"/>
+      <c r="AR26" s="87"/>
+      <c r="AS26" s="87"/>
+      <c r="AT26" s="87"/>
+      <c r="AU26" s="87"/>
+      <c r="AV26" s="87"/>
+      <c r="AW26" s="87"/>
+      <c r="AX26" s="87"/>
+      <c r="AY26" s="87"/>
+      <c r="AZ26" s="87"/>
+      <c r="BA26" s="87"/>
+      <c r="BB26" s="87"/>
+      <c r="BC26" s="87"/>
+      <c r="BD26" s="87"/>
+      <c r="BE26" s="93"/>
     </row>
     <row r="27" spans="1:57" ht="15" customHeight="1">
-      <c r="A27" s="101"/>
-      <c r="B27" s="102"/>
-      <c r="C27" s="102"/>
-      <c r="D27" s="102"/>
-      <c r="E27" s="102"/>
-      <c r="F27" s="102"/>
-      <c r="G27" s="103"/>
+      <c r="A27" s="81"/>
+      <c r="B27" s="82"/>
+      <c r="C27" s="82"/>
+      <c r="D27" s="82"/>
+      <c r="E27" s="82"/>
+      <c r="F27" s="82"/>
+      <c r="G27" s="83"/>
       <c r="H27" s="84"/>
       <c r="I27" s="85"/>
       <c r="J27" s="85"/>
@@ -66437,57 +66448,57 @@
       <c r="M27" s="85"/>
       <c r="N27" s="86"/>
       <c r="O27" s="84"/>
-      <c r="P27" s="82"/>
-      <c r="Q27" s="82"/>
-      <c r="R27" s="82"/>
-      <c r="S27" s="82"/>
-      <c r="T27" s="82"/>
-      <c r="U27" s="82"/>
-      <c r="V27" s="82"/>
-      <c r="W27" s="82"/>
-      <c r="X27" s="82"/>
-      <c r="Y27" s="82"/>
-      <c r="Z27" s="82"/>
-      <c r="AA27" s="82"/>
-      <c r="AB27" s="82"/>
-      <c r="AC27" s="82"/>
-      <c r="AD27" s="82"/>
-      <c r="AE27" s="82"/>
-      <c r="AF27" s="82"/>
-      <c r="AG27" s="82"/>
-      <c r="AH27" s="82"/>
-      <c r="AI27" s="82"/>
-      <c r="AJ27" s="82"/>
-      <c r="AK27" s="82"/>
-      <c r="AL27" s="82"/>
-      <c r="AM27" s="82"/>
-      <c r="AN27" s="82"/>
-      <c r="AO27" s="82"/>
-      <c r="AP27" s="90"/>
-      <c r="AQ27" s="81"/>
-      <c r="AR27" s="82"/>
-      <c r="AS27" s="82"/>
-      <c r="AT27" s="82"/>
-      <c r="AU27" s="82"/>
-      <c r="AV27" s="82"/>
-      <c r="AW27" s="82"/>
-      <c r="AX27" s="82"/>
-      <c r="AY27" s="82"/>
-      <c r="AZ27" s="82"/>
-      <c r="BA27" s="82"/>
-      <c r="BB27" s="82"/>
-      <c r="BC27" s="82"/>
-      <c r="BD27" s="82"/>
-      <c r="BE27" s="83"/>
+      <c r="P27" s="87"/>
+      <c r="Q27" s="87"/>
+      <c r="R27" s="87"/>
+      <c r="S27" s="87"/>
+      <c r="T27" s="87"/>
+      <c r="U27" s="87"/>
+      <c r="V27" s="87"/>
+      <c r="W27" s="87"/>
+      <c r="X27" s="87"/>
+      <c r="Y27" s="87"/>
+      <c r="Z27" s="87"/>
+      <c r="AA27" s="87"/>
+      <c r="AB27" s="87"/>
+      <c r="AC27" s="87"/>
+      <c r="AD27" s="87"/>
+      <c r="AE27" s="87"/>
+      <c r="AF27" s="87"/>
+      <c r="AG27" s="87"/>
+      <c r="AH27" s="87"/>
+      <c r="AI27" s="87"/>
+      <c r="AJ27" s="87"/>
+      <c r="AK27" s="87"/>
+      <c r="AL27" s="87"/>
+      <c r="AM27" s="87"/>
+      <c r="AN27" s="87"/>
+      <c r="AO27" s="87"/>
+      <c r="AP27" s="88"/>
+      <c r="AQ27" s="92"/>
+      <c r="AR27" s="87"/>
+      <c r="AS27" s="87"/>
+      <c r="AT27" s="87"/>
+      <c r="AU27" s="87"/>
+      <c r="AV27" s="87"/>
+      <c r="AW27" s="87"/>
+      <c r="AX27" s="87"/>
+      <c r="AY27" s="87"/>
+      <c r="AZ27" s="87"/>
+      <c r="BA27" s="87"/>
+      <c r="BB27" s="87"/>
+      <c r="BC27" s="87"/>
+      <c r="BD27" s="87"/>
+      <c r="BE27" s="93"/>
     </row>
     <row r="28" spans="1:57" ht="15" customHeight="1">
-      <c r="A28" s="101"/>
-      <c r="B28" s="102"/>
-      <c r="C28" s="102"/>
-      <c r="D28" s="102"/>
-      <c r="E28" s="102"/>
-      <c r="F28" s="102"/>
-      <c r="G28" s="103"/>
+      <c r="A28" s="81"/>
+      <c r="B28" s="82"/>
+      <c r="C28" s="82"/>
+      <c r="D28" s="82"/>
+      <c r="E28" s="82"/>
+      <c r="F28" s="82"/>
+      <c r="G28" s="83"/>
       <c r="H28" s="84"/>
       <c r="I28" s="85"/>
       <c r="J28" s="85"/>
@@ -66496,57 +66507,57 @@
       <c r="M28" s="85"/>
       <c r="N28" s="86"/>
       <c r="O28" s="84"/>
-      <c r="P28" s="82"/>
-      <c r="Q28" s="82"/>
-      <c r="R28" s="82"/>
-      <c r="S28" s="82"/>
-      <c r="T28" s="82"/>
-      <c r="U28" s="82"/>
-      <c r="V28" s="82"/>
-      <c r="W28" s="82"/>
-      <c r="X28" s="82"/>
-      <c r="Y28" s="82"/>
-      <c r="Z28" s="82"/>
-      <c r="AA28" s="82"/>
-      <c r="AB28" s="82"/>
-      <c r="AC28" s="82"/>
-      <c r="AD28" s="82"/>
-      <c r="AE28" s="82"/>
-      <c r="AF28" s="82"/>
-      <c r="AG28" s="82"/>
-      <c r="AH28" s="82"/>
-      <c r="AI28" s="82"/>
-      <c r="AJ28" s="82"/>
-      <c r="AK28" s="82"/>
-      <c r="AL28" s="82"/>
-      <c r="AM28" s="82"/>
-      <c r="AN28" s="82"/>
-      <c r="AO28" s="82"/>
-      <c r="AP28" s="90"/>
-      <c r="AQ28" s="81"/>
-      <c r="AR28" s="82"/>
-      <c r="AS28" s="82"/>
-      <c r="AT28" s="82"/>
-      <c r="AU28" s="82"/>
-      <c r="AV28" s="82"/>
-      <c r="AW28" s="82"/>
-      <c r="AX28" s="82"/>
-      <c r="AY28" s="82"/>
-      <c r="AZ28" s="82"/>
-      <c r="BA28" s="82"/>
-      <c r="BB28" s="82"/>
-      <c r="BC28" s="82"/>
-      <c r="BD28" s="82"/>
-      <c r="BE28" s="83"/>
+      <c r="P28" s="87"/>
+      <c r="Q28" s="87"/>
+      <c r="R28" s="87"/>
+      <c r="S28" s="87"/>
+      <c r="T28" s="87"/>
+      <c r="U28" s="87"/>
+      <c r="V28" s="87"/>
+      <c r="W28" s="87"/>
+      <c r="X28" s="87"/>
+      <c r="Y28" s="87"/>
+      <c r="Z28" s="87"/>
+      <c r="AA28" s="87"/>
+      <c r="AB28" s="87"/>
+      <c r="AC28" s="87"/>
+      <c r="AD28" s="87"/>
+      <c r="AE28" s="87"/>
+      <c r="AF28" s="87"/>
+      <c r="AG28" s="87"/>
+      <c r="AH28" s="87"/>
+      <c r="AI28" s="87"/>
+      <c r="AJ28" s="87"/>
+      <c r="AK28" s="87"/>
+      <c r="AL28" s="87"/>
+      <c r="AM28" s="87"/>
+      <c r="AN28" s="87"/>
+      <c r="AO28" s="87"/>
+      <c r="AP28" s="88"/>
+      <c r="AQ28" s="92"/>
+      <c r="AR28" s="87"/>
+      <c r="AS28" s="87"/>
+      <c r="AT28" s="87"/>
+      <c r="AU28" s="87"/>
+      <c r="AV28" s="87"/>
+      <c r="AW28" s="87"/>
+      <c r="AX28" s="87"/>
+      <c r="AY28" s="87"/>
+      <c r="AZ28" s="87"/>
+      <c r="BA28" s="87"/>
+      <c r="BB28" s="87"/>
+      <c r="BC28" s="87"/>
+      <c r="BD28" s="87"/>
+      <c r="BE28" s="93"/>
     </row>
     <row r="29" spans="1:57" ht="15" customHeight="1">
-      <c r="A29" s="101"/>
-      <c r="B29" s="102"/>
-      <c r="C29" s="102"/>
-      <c r="D29" s="102"/>
-      <c r="E29" s="102"/>
-      <c r="F29" s="102"/>
-      <c r="G29" s="103"/>
+      <c r="A29" s="81"/>
+      <c r="B29" s="82"/>
+      <c r="C29" s="82"/>
+      <c r="D29" s="82"/>
+      <c r="E29" s="82"/>
+      <c r="F29" s="82"/>
+      <c r="G29" s="83"/>
       <c r="H29" s="84"/>
       <c r="I29" s="85"/>
       <c r="J29" s="85"/>
@@ -66555,57 +66566,57 @@
       <c r="M29" s="85"/>
       <c r="N29" s="86"/>
       <c r="O29" s="84"/>
-      <c r="P29" s="82"/>
-      <c r="Q29" s="82"/>
-      <c r="R29" s="82"/>
-      <c r="S29" s="82"/>
-      <c r="T29" s="82"/>
-      <c r="U29" s="82"/>
-      <c r="V29" s="82"/>
-      <c r="W29" s="82"/>
-      <c r="X29" s="82"/>
-      <c r="Y29" s="82"/>
-      <c r="Z29" s="82"/>
-      <c r="AA29" s="82"/>
-      <c r="AB29" s="82"/>
-      <c r="AC29" s="82"/>
-      <c r="AD29" s="82"/>
-      <c r="AE29" s="82"/>
-      <c r="AF29" s="82"/>
-      <c r="AG29" s="82"/>
-      <c r="AH29" s="82"/>
-      <c r="AI29" s="82"/>
-      <c r="AJ29" s="82"/>
-      <c r="AK29" s="82"/>
-      <c r="AL29" s="82"/>
-      <c r="AM29" s="82"/>
-      <c r="AN29" s="82"/>
-      <c r="AO29" s="82"/>
-      <c r="AP29" s="90"/>
-      <c r="AQ29" s="81"/>
-      <c r="AR29" s="82"/>
-      <c r="AS29" s="82"/>
-      <c r="AT29" s="82"/>
-      <c r="AU29" s="82"/>
-      <c r="AV29" s="82"/>
-      <c r="AW29" s="82"/>
-      <c r="AX29" s="82"/>
-      <c r="AY29" s="82"/>
-      <c r="AZ29" s="82"/>
-      <c r="BA29" s="82"/>
-      <c r="BB29" s="82"/>
-      <c r="BC29" s="82"/>
-      <c r="BD29" s="82"/>
-      <c r="BE29" s="83"/>
+      <c r="P29" s="87"/>
+      <c r="Q29" s="87"/>
+      <c r="R29" s="87"/>
+      <c r="S29" s="87"/>
+      <c r="T29" s="87"/>
+      <c r="U29" s="87"/>
+      <c r="V29" s="87"/>
+      <c r="W29" s="87"/>
+      <c r="X29" s="87"/>
+      <c r="Y29" s="87"/>
+      <c r="Z29" s="87"/>
+      <c r="AA29" s="87"/>
+      <c r="AB29" s="87"/>
+      <c r="AC29" s="87"/>
+      <c r="AD29" s="87"/>
+      <c r="AE29" s="87"/>
+      <c r="AF29" s="87"/>
+      <c r="AG29" s="87"/>
+      <c r="AH29" s="87"/>
+      <c r="AI29" s="87"/>
+      <c r="AJ29" s="87"/>
+      <c r="AK29" s="87"/>
+      <c r="AL29" s="87"/>
+      <c r="AM29" s="87"/>
+      <c r="AN29" s="87"/>
+      <c r="AO29" s="87"/>
+      <c r="AP29" s="88"/>
+      <c r="AQ29" s="92"/>
+      <c r="AR29" s="87"/>
+      <c r="AS29" s="87"/>
+      <c r="AT29" s="87"/>
+      <c r="AU29" s="87"/>
+      <c r="AV29" s="87"/>
+      <c r="AW29" s="87"/>
+      <c r="AX29" s="87"/>
+      <c r="AY29" s="87"/>
+      <c r="AZ29" s="87"/>
+      <c r="BA29" s="87"/>
+      <c r="BB29" s="87"/>
+      <c r="BC29" s="87"/>
+      <c r="BD29" s="87"/>
+      <c r="BE29" s="93"/>
     </row>
     <row r="30" spans="1:57" ht="15" customHeight="1">
-      <c r="A30" s="101"/>
-      <c r="B30" s="102"/>
-      <c r="C30" s="102"/>
-      <c r="D30" s="102"/>
-      <c r="E30" s="102"/>
-      <c r="F30" s="102"/>
-      <c r="G30" s="103"/>
+      <c r="A30" s="81"/>
+      <c r="B30" s="82"/>
+      <c r="C30" s="82"/>
+      <c r="D30" s="82"/>
+      <c r="E30" s="82"/>
+      <c r="F30" s="82"/>
+      <c r="G30" s="83"/>
       <c r="H30" s="84"/>
       <c r="I30" s="85"/>
       <c r="J30" s="85"/>
@@ -66614,57 +66625,57 @@
       <c r="M30" s="85"/>
       <c r="N30" s="86"/>
       <c r="O30" s="84"/>
-      <c r="P30" s="82"/>
-      <c r="Q30" s="82"/>
-      <c r="R30" s="82"/>
-      <c r="S30" s="82"/>
-      <c r="T30" s="82"/>
-      <c r="U30" s="82"/>
-      <c r="V30" s="82"/>
-      <c r="W30" s="82"/>
-      <c r="X30" s="82"/>
-      <c r="Y30" s="82"/>
-      <c r="Z30" s="82"/>
-      <c r="AA30" s="82"/>
-      <c r="AB30" s="82"/>
-      <c r="AC30" s="82"/>
-      <c r="AD30" s="82"/>
-      <c r="AE30" s="82"/>
-      <c r="AF30" s="82"/>
-      <c r="AG30" s="82"/>
-      <c r="AH30" s="82"/>
-      <c r="AI30" s="82"/>
-      <c r="AJ30" s="82"/>
-      <c r="AK30" s="82"/>
-      <c r="AL30" s="82"/>
-      <c r="AM30" s="82"/>
-      <c r="AN30" s="82"/>
-      <c r="AO30" s="82"/>
-      <c r="AP30" s="90"/>
-      <c r="AQ30" s="81"/>
-      <c r="AR30" s="82"/>
-      <c r="AS30" s="82"/>
-      <c r="AT30" s="82"/>
-      <c r="AU30" s="82"/>
-      <c r="AV30" s="82"/>
-      <c r="AW30" s="82"/>
-      <c r="AX30" s="82"/>
-      <c r="AY30" s="82"/>
-      <c r="AZ30" s="82"/>
-      <c r="BA30" s="82"/>
-      <c r="BB30" s="82"/>
-      <c r="BC30" s="82"/>
-      <c r="BD30" s="82"/>
-      <c r="BE30" s="83"/>
+      <c r="P30" s="87"/>
+      <c r="Q30" s="87"/>
+      <c r="R30" s="87"/>
+      <c r="S30" s="87"/>
+      <c r="T30" s="87"/>
+      <c r="U30" s="87"/>
+      <c r="V30" s="87"/>
+      <c r="W30" s="87"/>
+      <c r="X30" s="87"/>
+      <c r="Y30" s="87"/>
+      <c r="Z30" s="87"/>
+      <c r="AA30" s="87"/>
+      <c r="AB30" s="87"/>
+      <c r="AC30" s="87"/>
+      <c r="AD30" s="87"/>
+      <c r="AE30" s="87"/>
+      <c r="AF30" s="87"/>
+      <c r="AG30" s="87"/>
+      <c r="AH30" s="87"/>
+      <c r="AI30" s="87"/>
+      <c r="AJ30" s="87"/>
+      <c r="AK30" s="87"/>
+      <c r="AL30" s="87"/>
+      <c r="AM30" s="87"/>
+      <c r="AN30" s="87"/>
+      <c r="AO30" s="87"/>
+      <c r="AP30" s="88"/>
+      <c r="AQ30" s="92"/>
+      <c r="AR30" s="87"/>
+      <c r="AS30" s="87"/>
+      <c r="AT30" s="87"/>
+      <c r="AU30" s="87"/>
+      <c r="AV30" s="87"/>
+      <c r="AW30" s="87"/>
+      <c r="AX30" s="87"/>
+      <c r="AY30" s="87"/>
+      <c r="AZ30" s="87"/>
+      <c r="BA30" s="87"/>
+      <c r="BB30" s="87"/>
+      <c r="BC30" s="87"/>
+      <c r="BD30" s="87"/>
+      <c r="BE30" s="93"/>
     </row>
     <row r="31" spans="1:57" ht="15" customHeight="1">
-      <c r="A31" s="101"/>
-      <c r="B31" s="102"/>
-      <c r="C31" s="102"/>
-      <c r="D31" s="102"/>
-      <c r="E31" s="102"/>
-      <c r="F31" s="102"/>
-      <c r="G31" s="103"/>
+      <c r="A31" s="81"/>
+      <c r="B31" s="82"/>
+      <c r="C31" s="82"/>
+      <c r="D31" s="82"/>
+      <c r="E31" s="82"/>
+      <c r="F31" s="82"/>
+      <c r="G31" s="83"/>
       <c r="H31" s="84"/>
       <c r="I31" s="85"/>
       <c r="J31" s="85"/>
@@ -66673,57 +66684,57 @@
       <c r="M31" s="85"/>
       <c r="N31" s="86"/>
       <c r="O31" s="84"/>
-      <c r="P31" s="82"/>
-      <c r="Q31" s="82"/>
-      <c r="R31" s="82"/>
-      <c r="S31" s="82"/>
-      <c r="T31" s="82"/>
-      <c r="U31" s="82"/>
-      <c r="V31" s="82"/>
-      <c r="W31" s="82"/>
-      <c r="X31" s="82"/>
-      <c r="Y31" s="82"/>
-      <c r="Z31" s="82"/>
-      <c r="AA31" s="82"/>
-      <c r="AB31" s="82"/>
-      <c r="AC31" s="82"/>
-      <c r="AD31" s="82"/>
-      <c r="AE31" s="82"/>
-      <c r="AF31" s="82"/>
-      <c r="AG31" s="82"/>
-      <c r="AH31" s="82"/>
-      <c r="AI31" s="82"/>
-      <c r="AJ31" s="82"/>
-      <c r="AK31" s="82"/>
-      <c r="AL31" s="82"/>
-      <c r="AM31" s="82"/>
-      <c r="AN31" s="82"/>
-      <c r="AO31" s="82"/>
-      <c r="AP31" s="90"/>
-      <c r="AQ31" s="81"/>
-      <c r="AR31" s="82"/>
-      <c r="AS31" s="82"/>
-      <c r="AT31" s="82"/>
-      <c r="AU31" s="82"/>
-      <c r="AV31" s="82"/>
-      <c r="AW31" s="82"/>
-      <c r="AX31" s="82"/>
-      <c r="AY31" s="82"/>
-      <c r="AZ31" s="82"/>
-      <c r="BA31" s="82"/>
-      <c r="BB31" s="82"/>
-      <c r="BC31" s="82"/>
-      <c r="BD31" s="82"/>
-      <c r="BE31" s="83"/>
+      <c r="P31" s="87"/>
+      <c r="Q31" s="87"/>
+      <c r="R31" s="87"/>
+      <c r="S31" s="87"/>
+      <c r="T31" s="87"/>
+      <c r="U31" s="87"/>
+      <c r="V31" s="87"/>
+      <c r="W31" s="87"/>
+      <c r="X31" s="87"/>
+      <c r="Y31" s="87"/>
+      <c r="Z31" s="87"/>
+      <c r="AA31" s="87"/>
+      <c r="AB31" s="87"/>
+      <c r="AC31" s="87"/>
+      <c r="AD31" s="87"/>
+      <c r="AE31" s="87"/>
+      <c r="AF31" s="87"/>
+      <c r="AG31" s="87"/>
+      <c r="AH31" s="87"/>
+      <c r="AI31" s="87"/>
+      <c r="AJ31" s="87"/>
+      <c r="AK31" s="87"/>
+      <c r="AL31" s="87"/>
+      <c r="AM31" s="87"/>
+      <c r="AN31" s="87"/>
+      <c r="AO31" s="87"/>
+      <c r="AP31" s="88"/>
+      <c r="AQ31" s="92"/>
+      <c r="AR31" s="87"/>
+      <c r="AS31" s="87"/>
+      <c r="AT31" s="87"/>
+      <c r="AU31" s="87"/>
+      <c r="AV31" s="87"/>
+      <c r="AW31" s="87"/>
+      <c r="AX31" s="87"/>
+      <c r="AY31" s="87"/>
+      <c r="AZ31" s="87"/>
+      <c r="BA31" s="87"/>
+      <c r="BB31" s="87"/>
+      <c r="BC31" s="87"/>
+      <c r="BD31" s="87"/>
+      <c r="BE31" s="93"/>
     </row>
     <row r="32" spans="1:57" ht="15" customHeight="1">
-      <c r="A32" s="101"/>
-      <c r="B32" s="102"/>
-      <c r="C32" s="102"/>
-      <c r="D32" s="102"/>
-      <c r="E32" s="102"/>
-      <c r="F32" s="102"/>
-      <c r="G32" s="103"/>
+      <c r="A32" s="81"/>
+      <c r="B32" s="82"/>
+      <c r="C32" s="82"/>
+      <c r="D32" s="82"/>
+      <c r="E32" s="82"/>
+      <c r="F32" s="82"/>
+      <c r="G32" s="83"/>
       <c r="H32" s="84"/>
       <c r="I32" s="85"/>
       <c r="J32" s="85"/>
@@ -66732,57 +66743,57 @@
       <c r="M32" s="85"/>
       <c r="N32" s="86"/>
       <c r="O32" s="84"/>
-      <c r="P32" s="82"/>
-      <c r="Q32" s="82"/>
-      <c r="R32" s="82"/>
-      <c r="S32" s="82"/>
-      <c r="T32" s="82"/>
-      <c r="U32" s="82"/>
-      <c r="V32" s="82"/>
-      <c r="W32" s="82"/>
-      <c r="X32" s="82"/>
-      <c r="Y32" s="82"/>
-      <c r="Z32" s="82"/>
-      <c r="AA32" s="82"/>
-      <c r="AB32" s="82"/>
-      <c r="AC32" s="82"/>
-      <c r="AD32" s="82"/>
-      <c r="AE32" s="82"/>
-      <c r="AF32" s="82"/>
-      <c r="AG32" s="82"/>
-      <c r="AH32" s="82"/>
-      <c r="AI32" s="82"/>
-      <c r="AJ32" s="82"/>
-      <c r="AK32" s="82"/>
-      <c r="AL32" s="82"/>
-      <c r="AM32" s="82"/>
-      <c r="AN32" s="82"/>
-      <c r="AO32" s="82"/>
-      <c r="AP32" s="90"/>
-      <c r="AQ32" s="81"/>
-      <c r="AR32" s="82"/>
-      <c r="AS32" s="82"/>
-      <c r="AT32" s="82"/>
-      <c r="AU32" s="82"/>
-      <c r="AV32" s="82"/>
-      <c r="AW32" s="82"/>
-      <c r="AX32" s="82"/>
-      <c r="AY32" s="82"/>
-      <c r="AZ32" s="82"/>
-      <c r="BA32" s="82"/>
-      <c r="BB32" s="82"/>
-      <c r="BC32" s="82"/>
-      <c r="BD32" s="82"/>
-      <c r="BE32" s="83"/>
+      <c r="P32" s="87"/>
+      <c r="Q32" s="87"/>
+      <c r="R32" s="87"/>
+      <c r="S32" s="87"/>
+      <c r="T32" s="87"/>
+      <c r="U32" s="87"/>
+      <c r="V32" s="87"/>
+      <c r="W32" s="87"/>
+      <c r="X32" s="87"/>
+      <c r="Y32" s="87"/>
+      <c r="Z32" s="87"/>
+      <c r="AA32" s="87"/>
+      <c r="AB32" s="87"/>
+      <c r="AC32" s="87"/>
+      <c r="AD32" s="87"/>
+      <c r="AE32" s="87"/>
+      <c r="AF32" s="87"/>
+      <c r="AG32" s="87"/>
+      <c r="AH32" s="87"/>
+      <c r="AI32" s="87"/>
+      <c r="AJ32" s="87"/>
+      <c r="AK32" s="87"/>
+      <c r="AL32" s="87"/>
+      <c r="AM32" s="87"/>
+      <c r="AN32" s="87"/>
+      <c r="AO32" s="87"/>
+      <c r="AP32" s="88"/>
+      <c r="AQ32" s="92"/>
+      <c r="AR32" s="87"/>
+      <c r="AS32" s="87"/>
+      <c r="AT32" s="87"/>
+      <c r="AU32" s="87"/>
+      <c r="AV32" s="87"/>
+      <c r="AW32" s="87"/>
+      <c r="AX32" s="87"/>
+      <c r="AY32" s="87"/>
+      <c r="AZ32" s="87"/>
+      <c r="BA32" s="87"/>
+      <c r="BB32" s="87"/>
+      <c r="BC32" s="87"/>
+      <c r="BD32" s="87"/>
+      <c r="BE32" s="93"/>
     </row>
     <row r="33" spans="1:57" ht="15" customHeight="1">
-      <c r="A33" s="101"/>
-      <c r="B33" s="102"/>
-      <c r="C33" s="102"/>
-      <c r="D33" s="102"/>
-      <c r="E33" s="102"/>
-      <c r="F33" s="102"/>
-      <c r="G33" s="103"/>
+      <c r="A33" s="81"/>
+      <c r="B33" s="82"/>
+      <c r="C33" s="82"/>
+      <c r="D33" s="82"/>
+      <c r="E33" s="82"/>
+      <c r="F33" s="82"/>
+      <c r="G33" s="83"/>
       <c r="H33" s="84"/>
       <c r="I33" s="85"/>
       <c r="J33" s="85"/>
@@ -66791,57 +66802,57 @@
       <c r="M33" s="85"/>
       <c r="N33" s="86"/>
       <c r="O33" s="84"/>
-      <c r="P33" s="82"/>
-      <c r="Q33" s="82"/>
-      <c r="R33" s="82"/>
-      <c r="S33" s="82"/>
-      <c r="T33" s="82"/>
-      <c r="U33" s="82"/>
-      <c r="V33" s="82"/>
-      <c r="W33" s="82"/>
-      <c r="X33" s="82"/>
-      <c r="Y33" s="82"/>
-      <c r="Z33" s="82"/>
-      <c r="AA33" s="82"/>
-      <c r="AB33" s="82"/>
-      <c r="AC33" s="82"/>
-      <c r="AD33" s="82"/>
-      <c r="AE33" s="82"/>
-      <c r="AF33" s="82"/>
-      <c r="AG33" s="82"/>
-      <c r="AH33" s="82"/>
-      <c r="AI33" s="82"/>
-      <c r="AJ33" s="82"/>
-      <c r="AK33" s="82"/>
-      <c r="AL33" s="82"/>
-      <c r="AM33" s="82"/>
-      <c r="AN33" s="82"/>
-      <c r="AO33" s="82"/>
-      <c r="AP33" s="90"/>
-      <c r="AQ33" s="81"/>
-      <c r="AR33" s="82"/>
-      <c r="AS33" s="82"/>
-      <c r="AT33" s="82"/>
-      <c r="AU33" s="82"/>
-      <c r="AV33" s="82"/>
-      <c r="AW33" s="82"/>
-      <c r="AX33" s="82"/>
-      <c r="AY33" s="82"/>
-      <c r="AZ33" s="82"/>
-      <c r="BA33" s="82"/>
-      <c r="BB33" s="82"/>
-      <c r="BC33" s="82"/>
-      <c r="BD33" s="82"/>
-      <c r="BE33" s="83"/>
+      <c r="P33" s="87"/>
+      <c r="Q33" s="87"/>
+      <c r="R33" s="87"/>
+      <c r="S33" s="87"/>
+      <c r="T33" s="87"/>
+      <c r="U33" s="87"/>
+      <c r="V33" s="87"/>
+      <c r="W33" s="87"/>
+      <c r="X33" s="87"/>
+      <c r="Y33" s="87"/>
+      <c r="Z33" s="87"/>
+      <c r="AA33" s="87"/>
+      <c r="AB33" s="87"/>
+      <c r="AC33" s="87"/>
+      <c r="AD33" s="87"/>
+      <c r="AE33" s="87"/>
+      <c r="AF33" s="87"/>
+      <c r="AG33" s="87"/>
+      <c r="AH33" s="87"/>
+      <c r="AI33" s="87"/>
+      <c r="AJ33" s="87"/>
+      <c r="AK33" s="87"/>
+      <c r="AL33" s="87"/>
+      <c r="AM33" s="87"/>
+      <c r="AN33" s="87"/>
+      <c r="AO33" s="87"/>
+      <c r="AP33" s="88"/>
+      <c r="AQ33" s="92"/>
+      <c r="AR33" s="87"/>
+      <c r="AS33" s="87"/>
+      <c r="AT33" s="87"/>
+      <c r="AU33" s="87"/>
+      <c r="AV33" s="87"/>
+      <c r="AW33" s="87"/>
+      <c r="AX33" s="87"/>
+      <c r="AY33" s="87"/>
+      <c r="AZ33" s="87"/>
+      <c r="BA33" s="87"/>
+      <c r="BB33" s="87"/>
+      <c r="BC33" s="87"/>
+      <c r="BD33" s="87"/>
+      <c r="BE33" s="93"/>
     </row>
     <row r="34" spans="1:57" ht="15" customHeight="1">
-      <c r="A34" s="101"/>
-      <c r="B34" s="102"/>
-      <c r="C34" s="102"/>
-      <c r="D34" s="102"/>
-      <c r="E34" s="102"/>
-      <c r="F34" s="102"/>
-      <c r="G34" s="103"/>
+      <c r="A34" s="81"/>
+      <c r="B34" s="82"/>
+      <c r="C34" s="82"/>
+      <c r="D34" s="82"/>
+      <c r="E34" s="82"/>
+      <c r="F34" s="82"/>
+      <c r="G34" s="83"/>
       <c r="H34" s="84"/>
       <c r="I34" s="85"/>
       <c r="J34" s="85"/>
@@ -66850,110 +66861,219 @@
       <c r="M34" s="85"/>
       <c r="N34" s="86"/>
       <c r="O34" s="84"/>
-      <c r="P34" s="82"/>
-      <c r="Q34" s="82"/>
-      <c r="R34" s="82"/>
-      <c r="S34" s="82"/>
-      <c r="T34" s="82"/>
-      <c r="U34" s="82"/>
-      <c r="V34" s="82"/>
-      <c r="W34" s="82"/>
-      <c r="X34" s="82"/>
-      <c r="Y34" s="82"/>
-      <c r="Z34" s="82"/>
-      <c r="AA34" s="82"/>
-      <c r="AB34" s="82"/>
-      <c r="AC34" s="82"/>
-      <c r="AD34" s="82"/>
-      <c r="AE34" s="82"/>
-      <c r="AF34" s="82"/>
-      <c r="AG34" s="82"/>
-      <c r="AH34" s="82"/>
-      <c r="AI34" s="82"/>
-      <c r="AJ34" s="82"/>
-      <c r="AK34" s="82"/>
-      <c r="AL34" s="82"/>
-      <c r="AM34" s="82"/>
-      <c r="AN34" s="82"/>
-      <c r="AO34" s="82"/>
-      <c r="AP34" s="90"/>
-      <c r="AQ34" s="81"/>
-      <c r="AR34" s="82"/>
-      <c r="AS34" s="82"/>
-      <c r="AT34" s="82"/>
-      <c r="AU34" s="82"/>
-      <c r="AV34" s="82"/>
-      <c r="AW34" s="82"/>
-      <c r="AX34" s="82"/>
-      <c r="AY34" s="82"/>
-      <c r="AZ34" s="82"/>
-      <c r="BA34" s="82"/>
-      <c r="BB34" s="82"/>
-      <c r="BC34" s="82"/>
-      <c r="BD34" s="82"/>
-      <c r="BE34" s="83"/>
+      <c r="P34" s="87"/>
+      <c r="Q34" s="87"/>
+      <c r="R34" s="87"/>
+      <c r="S34" s="87"/>
+      <c r="T34" s="87"/>
+      <c r="U34" s="87"/>
+      <c r="V34" s="87"/>
+      <c r="W34" s="87"/>
+      <c r="X34" s="87"/>
+      <c r="Y34" s="87"/>
+      <c r="Z34" s="87"/>
+      <c r="AA34" s="87"/>
+      <c r="AB34" s="87"/>
+      <c r="AC34" s="87"/>
+      <c r="AD34" s="87"/>
+      <c r="AE34" s="87"/>
+      <c r="AF34" s="87"/>
+      <c r="AG34" s="87"/>
+      <c r="AH34" s="87"/>
+      <c r="AI34" s="87"/>
+      <c r="AJ34" s="87"/>
+      <c r="AK34" s="87"/>
+      <c r="AL34" s="87"/>
+      <c r="AM34" s="87"/>
+      <c r="AN34" s="87"/>
+      <c r="AO34" s="87"/>
+      <c r="AP34" s="88"/>
+      <c r="AQ34" s="92"/>
+      <c r="AR34" s="87"/>
+      <c r="AS34" s="87"/>
+      <c r="AT34" s="87"/>
+      <c r="AU34" s="87"/>
+      <c r="AV34" s="87"/>
+      <c r="AW34" s="87"/>
+      <c r="AX34" s="87"/>
+      <c r="AY34" s="87"/>
+      <c r="AZ34" s="87"/>
+      <c r="BA34" s="87"/>
+      <c r="BB34" s="87"/>
+      <c r="BC34" s="87"/>
+      <c r="BD34" s="87"/>
+      <c r="BE34" s="93"/>
     </row>
     <row r="35" spans="1:57" ht="15" customHeight="1" thickBot="1">
-      <c r="A35" s="122"/>
-      <c r="B35" s="123"/>
-      <c r="C35" s="123"/>
-      <c r="D35" s="123"/>
-      <c r="E35" s="123"/>
-      <c r="F35" s="123"/>
-      <c r="G35" s="124"/>
-      <c r="H35" s="128"/>
-      <c r="I35" s="129"/>
-      <c r="J35" s="129"/>
-      <c r="K35" s="129"/>
-      <c r="L35" s="129"/>
-      <c r="M35" s="129"/>
-      <c r="N35" s="130"/>
-      <c r="O35" s="128"/>
-      <c r="P35" s="126"/>
-      <c r="Q35" s="126"/>
-      <c r="R35" s="126"/>
-      <c r="S35" s="126"/>
-      <c r="T35" s="126"/>
-      <c r="U35" s="126"/>
-      <c r="V35" s="126"/>
-      <c r="W35" s="126"/>
-      <c r="X35" s="126"/>
-      <c r="Y35" s="126"/>
-      <c r="Z35" s="126"/>
-      <c r="AA35" s="126"/>
-      <c r="AB35" s="126"/>
-      <c r="AC35" s="126"/>
-      <c r="AD35" s="126"/>
-      <c r="AE35" s="126"/>
-      <c r="AF35" s="126"/>
-      <c r="AG35" s="126"/>
-      <c r="AH35" s="126"/>
-      <c r="AI35" s="126"/>
-      <c r="AJ35" s="126"/>
-      <c r="AK35" s="126"/>
-      <c r="AL35" s="126"/>
-      <c r="AM35" s="126"/>
-      <c r="AN35" s="126"/>
-      <c r="AO35" s="126"/>
-      <c r="AP35" s="131"/>
-      <c r="AQ35" s="125"/>
-      <c r="AR35" s="126"/>
-      <c r="AS35" s="126"/>
-      <c r="AT35" s="126"/>
-      <c r="AU35" s="126"/>
-      <c r="AV35" s="126"/>
-      <c r="AW35" s="126"/>
-      <c r="AX35" s="126"/>
-      <c r="AY35" s="126"/>
-      <c r="AZ35" s="126"/>
-      <c r="BA35" s="126"/>
-      <c r="BB35" s="126"/>
-      <c r="BC35" s="126"/>
-      <c r="BD35" s="126"/>
-      <c r="BE35" s="127"/>
+      <c r="A35" s="98"/>
+      <c r="B35" s="99"/>
+      <c r="C35" s="99"/>
+      <c r="D35" s="99"/>
+      <c r="E35" s="99"/>
+      <c r="F35" s="99"/>
+      <c r="G35" s="100"/>
+      <c r="H35" s="94"/>
+      <c r="I35" s="95"/>
+      <c r="J35" s="95"/>
+      <c r="K35" s="95"/>
+      <c r="L35" s="95"/>
+      <c r="M35" s="95"/>
+      <c r="N35" s="96"/>
+      <c r="O35" s="94"/>
+      <c r="P35" s="90"/>
+      <c r="Q35" s="90"/>
+      <c r="R35" s="90"/>
+      <c r="S35" s="90"/>
+      <c r="T35" s="90"/>
+      <c r="U35" s="90"/>
+      <c r="V35" s="90"/>
+      <c r="W35" s="90"/>
+      <c r="X35" s="90"/>
+      <c r="Y35" s="90"/>
+      <c r="Z35" s="90"/>
+      <c r="AA35" s="90"/>
+      <c r="AB35" s="90"/>
+      <c r="AC35" s="90"/>
+      <c r="AD35" s="90"/>
+      <c r="AE35" s="90"/>
+      <c r="AF35" s="90"/>
+      <c r="AG35" s="90"/>
+      <c r="AH35" s="90"/>
+      <c r="AI35" s="90"/>
+      <c r="AJ35" s="90"/>
+      <c r="AK35" s="90"/>
+      <c r="AL35" s="90"/>
+      <c r="AM35" s="90"/>
+      <c r="AN35" s="90"/>
+      <c r="AO35" s="90"/>
+      <c r="AP35" s="97"/>
+      <c r="AQ35" s="89"/>
+      <c r="AR35" s="90"/>
+      <c r="AS35" s="90"/>
+      <c r="AT35" s="90"/>
+      <c r="AU35" s="90"/>
+      <c r="AV35" s="90"/>
+      <c r="AW35" s="90"/>
+      <c r="AX35" s="90"/>
+      <c r="AY35" s="90"/>
+      <c r="AZ35" s="90"/>
+      <c r="BA35" s="90"/>
+      <c r="BB35" s="90"/>
+      <c r="BC35" s="90"/>
+      <c r="BD35" s="90"/>
+      <c r="BE35" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="133">
+    <mergeCell ref="AQ22:BE22"/>
+    <mergeCell ref="AQ29:BE29"/>
+    <mergeCell ref="H17:N17"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="H12:N12"/>
+    <mergeCell ref="O12:AP12"/>
+    <mergeCell ref="AQ12:BE12"/>
+    <mergeCell ref="H8:N8"/>
+    <mergeCell ref="AQ6:BE6"/>
+    <mergeCell ref="H5:N5"/>
+    <mergeCell ref="O8:AP8"/>
+    <mergeCell ref="AQ8:BE8"/>
+    <mergeCell ref="O5:AP5"/>
+    <mergeCell ref="AQ5:BE5"/>
+    <mergeCell ref="H6:N6"/>
+    <mergeCell ref="O6:AP6"/>
+    <mergeCell ref="H7:N7"/>
+    <mergeCell ref="O7:AP7"/>
+    <mergeCell ref="AQ7:BE7"/>
+    <mergeCell ref="AQ15:BE15"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="O16:AP16"/>
+    <mergeCell ref="O17:AP17"/>
+    <mergeCell ref="A1:BE1"/>
+    <mergeCell ref="H3:N3"/>
+    <mergeCell ref="O3:AP3"/>
+    <mergeCell ref="AQ3:BE3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="O15:AP15"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="H4:N4"/>
+    <mergeCell ref="O4:AP4"/>
+    <mergeCell ref="AQ4:BE4"/>
+    <mergeCell ref="H13:N13"/>
+    <mergeCell ref="O13:AP13"/>
+    <mergeCell ref="AQ13:BE13"/>
+    <mergeCell ref="H14:N14"/>
+    <mergeCell ref="O14:AP14"/>
+    <mergeCell ref="AQ14:BE14"/>
+    <mergeCell ref="AQ16:BE16"/>
+    <mergeCell ref="H15:N15"/>
+    <mergeCell ref="O18:AP18"/>
+    <mergeCell ref="H9:N9"/>
+    <mergeCell ref="O9:AP9"/>
+    <mergeCell ref="AQ9:BE9"/>
+    <mergeCell ref="H10:N10"/>
+    <mergeCell ref="O10:AP10"/>
+    <mergeCell ref="AQ10:BE10"/>
+    <mergeCell ref="H11:N11"/>
+    <mergeCell ref="O11:AP11"/>
+    <mergeCell ref="AQ11:BE11"/>
+    <mergeCell ref="H16:N16"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:AP20"/>
+    <mergeCell ref="AQ17:BE17"/>
+    <mergeCell ref="H26:N26"/>
+    <mergeCell ref="O26:AP26"/>
+    <mergeCell ref="AQ26:BE26"/>
+    <mergeCell ref="AQ19:BE19"/>
+    <mergeCell ref="H25:N25"/>
+    <mergeCell ref="H24:N24"/>
+    <mergeCell ref="O24:AP24"/>
+    <mergeCell ref="O25:AP25"/>
+    <mergeCell ref="AQ25:BE25"/>
+    <mergeCell ref="H22:N22"/>
+    <mergeCell ref="AQ24:BE24"/>
+    <mergeCell ref="H23:N23"/>
+    <mergeCell ref="O23:AP23"/>
+    <mergeCell ref="AQ23:BE23"/>
+    <mergeCell ref="AQ20:BE20"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:AP21"/>
+    <mergeCell ref="AQ18:BE18"/>
+    <mergeCell ref="AQ21:BE21"/>
+    <mergeCell ref="O22:AP22"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="H33:N33"/>
+    <mergeCell ref="H34:N34"/>
+    <mergeCell ref="O34:AP34"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="O33:AP33"/>
+    <mergeCell ref="O32:AP32"/>
+    <mergeCell ref="H31:N31"/>
+    <mergeCell ref="O31:AP31"/>
+    <mergeCell ref="H27:N27"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="H32:N32"/>
+    <mergeCell ref="H29:N29"/>
+    <mergeCell ref="O29:AP29"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A24:G24"/>
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="H19:N19"/>
     <mergeCell ref="O19:AP19"/>
@@ -66978,115 +67098,6 @@
     <mergeCell ref="A31:G31"/>
     <mergeCell ref="A25:G25"/>
     <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="H33:N33"/>
-    <mergeCell ref="H34:N34"/>
-    <mergeCell ref="O34:AP34"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="O33:AP33"/>
-    <mergeCell ref="O32:AP32"/>
-    <mergeCell ref="H31:N31"/>
-    <mergeCell ref="O31:AP31"/>
-    <mergeCell ref="H27:N27"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="H32:N32"/>
-    <mergeCell ref="H29:N29"/>
-    <mergeCell ref="O29:AP29"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:AP20"/>
-    <mergeCell ref="AQ17:BE17"/>
-    <mergeCell ref="H26:N26"/>
-    <mergeCell ref="O26:AP26"/>
-    <mergeCell ref="AQ26:BE26"/>
-    <mergeCell ref="AQ19:BE19"/>
-    <mergeCell ref="H25:N25"/>
-    <mergeCell ref="H24:N24"/>
-    <mergeCell ref="O24:AP24"/>
-    <mergeCell ref="O25:AP25"/>
-    <mergeCell ref="AQ25:BE25"/>
-    <mergeCell ref="H22:N22"/>
-    <mergeCell ref="AQ24:BE24"/>
-    <mergeCell ref="H23:N23"/>
-    <mergeCell ref="O23:AP23"/>
-    <mergeCell ref="AQ23:BE23"/>
-    <mergeCell ref="AQ20:BE20"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:AP21"/>
-    <mergeCell ref="AQ18:BE18"/>
-    <mergeCell ref="AQ21:BE21"/>
-    <mergeCell ref="O22:AP22"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="H4:N4"/>
-    <mergeCell ref="O4:AP4"/>
-    <mergeCell ref="AQ4:BE4"/>
-    <mergeCell ref="H13:N13"/>
-    <mergeCell ref="O13:AP13"/>
-    <mergeCell ref="AQ13:BE13"/>
-    <mergeCell ref="H14:N14"/>
-    <mergeCell ref="O14:AP14"/>
-    <mergeCell ref="AQ14:BE14"/>
-    <mergeCell ref="AQ16:BE16"/>
-    <mergeCell ref="H15:N15"/>
-    <mergeCell ref="O18:AP18"/>
-    <mergeCell ref="H9:N9"/>
-    <mergeCell ref="O9:AP9"/>
-    <mergeCell ref="AQ9:BE9"/>
-    <mergeCell ref="H10:N10"/>
-    <mergeCell ref="O10:AP10"/>
-    <mergeCell ref="AQ10:BE10"/>
-    <mergeCell ref="H11:N11"/>
-    <mergeCell ref="O11:AP11"/>
-    <mergeCell ref="AQ11:BE11"/>
-    <mergeCell ref="H16:N16"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="O15:AP15"/>
-    <mergeCell ref="A1:BE1"/>
-    <mergeCell ref="H3:N3"/>
-    <mergeCell ref="O3:AP3"/>
-    <mergeCell ref="AQ3:BE3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="AQ22:BE22"/>
-    <mergeCell ref="AQ29:BE29"/>
-    <mergeCell ref="H17:N17"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="H12:N12"/>
-    <mergeCell ref="O12:AP12"/>
-    <mergeCell ref="AQ12:BE12"/>
-    <mergeCell ref="H8:N8"/>
-    <mergeCell ref="AQ6:BE6"/>
-    <mergeCell ref="H5:N5"/>
-    <mergeCell ref="O8:AP8"/>
-    <mergeCell ref="AQ8:BE8"/>
-    <mergeCell ref="O5:AP5"/>
-    <mergeCell ref="AQ5:BE5"/>
-    <mergeCell ref="H6:N6"/>
-    <mergeCell ref="O6:AP6"/>
-    <mergeCell ref="H7:N7"/>
-    <mergeCell ref="O7:AP7"/>
-    <mergeCell ref="AQ7:BE7"/>
-    <mergeCell ref="AQ15:BE15"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="O16:AP16"/>
-    <mergeCell ref="O17:AP17"/>
   </mergeCells>
   <phoneticPr fontId="5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>

--- a/development/MS/spec/MSBB/Panel/MSBBP1210_SloReg.xlsx
+++ b/development/MS/spec/MSBB/Panel/MSBBP1210_SloReg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\mcframeDEV\development\MS\spec\MSBB\Panel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1F4ECD3-545D-4153-980A-79BDC39F73F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1A4C8A-8B3D-4628-985A-35EF6697A60A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-3330" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9151" uniqueCount="2375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9175" uniqueCount="2375">
   <si>
     <t>検索</t>
     <rPh sb="0" eb="2">
@@ -11480,14 +11480,14 @@
     <xf numFmtId="0" fontId="27" fillId="24" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -11498,79 +11498,7 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11579,29 +11507,8 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -11632,6 +11539,99 @@
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -32622,18 +32622,42 @@
       <c r="V243" s="61"/>
       <c r="W243" s="61"/>
       <c r="X243" s="61"/>
-      <c r="Z243" s="33"/>
-      <c r="AA243" s="33"/>
-      <c r="AB243" s="33"/>
-      <c r="AC243" s="33"/>
-      <c r="AD243" s="33"/>
-      <c r="AE243" s="33"/>
-      <c r="AF243" s="33"/>
-      <c r="AG243" s="33"/>
-      <c r="AH243" s="33"/>
-      <c r="AI243" s="33"/>
-      <c r="AJ243" s="33"/>
-      <c r="AK243" s="33"/>
+      <c r="Z243" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA243" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB243" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC243" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD243" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE243" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF243" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG243" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH243" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI243" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ243" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK243" s="25" t="s">
+        <v>25</v>
+      </c>
       <c r="AM243" s="33"/>
       <c r="AN243" s="33"/>
       <c r="AO243" s="33"/>
@@ -32756,18 +32780,42 @@
       <c r="V245" s="61"/>
       <c r="W245" s="61"/>
       <c r="X245" s="61"/>
-      <c r="Z245" s="33"/>
-      <c r="AA245" s="33"/>
-      <c r="AB245" s="33"/>
-      <c r="AC245" s="33"/>
-      <c r="AD245" s="33"/>
-      <c r="AE245" s="33"/>
-      <c r="AF245" s="33"/>
-      <c r="AG245" s="33"/>
-      <c r="AH245" s="33"/>
-      <c r="AI245" s="33"/>
-      <c r="AJ245" s="33"/>
-      <c r="AK245" s="33"/>
+      <c r="Z245" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA245" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB245" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC245" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD245" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE245" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF245" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG245" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH245" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI245" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ245" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK245" s="25" t="s">
+        <v>25</v>
+      </c>
       <c r="AM245" s="33"/>
       <c r="AN245" s="33"/>
       <c r="AO245" s="33"/>
@@ -64878,65 +64926,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:57" ht="38.25" customHeight="1" thickBot="1">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="104" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
-      <c r="V1" s="109"/>
-      <c r="W1" s="109"/>
-      <c r="X1" s="109"/>
-      <c r="Y1" s="109"/>
-      <c r="Z1" s="109"/>
-      <c r="AA1" s="109"/>
-      <c r="AB1" s="109"/>
-      <c r="AC1" s="109"/>
-      <c r="AD1" s="109"/>
-      <c r="AE1" s="109"/>
-      <c r="AF1" s="109"/>
-      <c r="AG1" s="109"/>
-      <c r="AH1" s="109"/>
-      <c r="AI1" s="109"/>
-      <c r="AJ1" s="109"/>
-      <c r="AK1" s="109"/>
-      <c r="AL1" s="109"/>
-      <c r="AM1" s="109"/>
-      <c r="AN1" s="109"/>
-      <c r="AO1" s="109"/>
-      <c r="AP1" s="109"/>
-      <c r="AQ1" s="109"/>
-      <c r="AR1" s="109"/>
-      <c r="AS1" s="109"/>
-      <c r="AT1" s="109"/>
-      <c r="AU1" s="109"/>
-      <c r="AV1" s="109"/>
-      <c r="AW1" s="109"/>
-      <c r="AX1" s="109"/>
-      <c r="AY1" s="109"/>
-      <c r="AZ1" s="109"/>
-      <c r="BA1" s="109"/>
-      <c r="BB1" s="109"/>
-      <c r="BC1" s="109"/>
-      <c r="BD1" s="109"/>
-      <c r="BE1" s="110"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="105"/>
+      <c r="H1" s="105"/>
+      <c r="I1" s="105"/>
+      <c r="J1" s="105"/>
+      <c r="K1" s="105"/>
+      <c r="L1" s="105"/>
+      <c r="M1" s="105"/>
+      <c r="N1" s="105"/>
+      <c r="O1" s="105"/>
+      <c r="P1" s="105"/>
+      <c r="Q1" s="105"/>
+      <c r="R1" s="105"/>
+      <c r="S1" s="105"/>
+      <c r="T1" s="105"/>
+      <c r="U1" s="105"/>
+      <c r="V1" s="105"/>
+      <c r="W1" s="105"/>
+      <c r="X1" s="105"/>
+      <c r="Y1" s="105"/>
+      <c r="Z1" s="105"/>
+      <c r="AA1" s="105"/>
+      <c r="AB1" s="105"/>
+      <c r="AC1" s="105"/>
+      <c r="AD1" s="105"/>
+      <c r="AE1" s="105"/>
+      <c r="AF1" s="105"/>
+      <c r="AG1" s="105"/>
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="106"/>
     </row>
     <row r="2" spans="1:57" ht="12" customHeight="1" thickBot="1">
       <c r="A2" s="14"/>
@@ -64983,145 +65031,145 @@
       <c r="AP2" s="14"/>
     </row>
     <row r="3" spans="1:57" ht="15" customHeight="1" thickBot="1">
-      <c r="A3" s="121" t="s">
+      <c r="A3" s="87" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="112"/>
-      <c r="C3" s="112"/>
-      <c r="D3" s="112"/>
-      <c r="E3" s="112"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="113"/>
-      <c r="H3" s="111" t="s">
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="107" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="112"/>
-      <c r="J3" s="112"/>
-      <c r="K3" s="112"/>
-      <c r="L3" s="112"/>
-      <c r="M3" s="112"/>
-      <c r="N3" s="113"/>
-      <c r="O3" s="111" t="s">
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
+      <c r="K3" s="88"/>
+      <c r="L3" s="88"/>
+      <c r="M3" s="88"/>
+      <c r="N3" s="89"/>
+      <c r="O3" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="P3" s="114"/>
-      <c r="Q3" s="114"/>
-      <c r="R3" s="114"/>
-      <c r="S3" s="114"/>
-      <c r="T3" s="114"/>
-      <c r="U3" s="114"/>
-      <c r="V3" s="114"/>
-      <c r="W3" s="114"/>
-      <c r="X3" s="114"/>
-      <c r="Y3" s="114"/>
-      <c r="Z3" s="114"/>
-      <c r="AA3" s="114"/>
-      <c r="AB3" s="114"/>
-      <c r="AC3" s="114"/>
-      <c r="AD3" s="114"/>
-      <c r="AE3" s="114"/>
-      <c r="AF3" s="114"/>
-      <c r="AG3" s="114"/>
-      <c r="AH3" s="114"/>
-      <c r="AI3" s="114"/>
-      <c r="AJ3" s="114"/>
-      <c r="AK3" s="114"/>
-      <c r="AL3" s="114"/>
-      <c r="AM3" s="114"/>
-      <c r="AN3" s="114"/>
-      <c r="AO3" s="114"/>
-      <c r="AP3" s="115"/>
-      <c r="AQ3" s="111" t="s">
+      <c r="P3" s="108"/>
+      <c r="Q3" s="108"/>
+      <c r="R3" s="108"/>
+      <c r="S3" s="108"/>
+      <c r="T3" s="108"/>
+      <c r="U3" s="108"/>
+      <c r="V3" s="108"/>
+      <c r="W3" s="108"/>
+      <c r="X3" s="108"/>
+      <c r="Y3" s="108"/>
+      <c r="Z3" s="108"/>
+      <c r="AA3" s="108"/>
+      <c r="AB3" s="108"/>
+      <c r="AC3" s="108"/>
+      <c r="AD3" s="108"/>
+      <c r="AE3" s="108"/>
+      <c r="AF3" s="108"/>
+      <c r="AG3" s="108"/>
+      <c r="AH3" s="108"/>
+      <c r="AI3" s="108"/>
+      <c r="AJ3" s="108"/>
+      <c r="AK3" s="108"/>
+      <c r="AL3" s="108"/>
+      <c r="AM3" s="108"/>
+      <c r="AN3" s="108"/>
+      <c r="AO3" s="108"/>
+      <c r="AP3" s="109"/>
+      <c r="AQ3" s="107" t="s">
         <v>10</v>
       </c>
-      <c r="AR3" s="116"/>
-      <c r="AS3" s="116"/>
-      <c r="AT3" s="116"/>
-      <c r="AU3" s="116"/>
-      <c r="AV3" s="116"/>
-      <c r="AW3" s="116"/>
-      <c r="AX3" s="116"/>
-      <c r="AY3" s="116"/>
-      <c r="AZ3" s="116"/>
-      <c r="BA3" s="116"/>
-      <c r="BB3" s="116"/>
-      <c r="BC3" s="116"/>
-      <c r="BD3" s="116"/>
-      <c r="BE3" s="117"/>
+      <c r="AR3" s="110"/>
+      <c r="AS3" s="110"/>
+      <c r="AT3" s="110"/>
+      <c r="AU3" s="110"/>
+      <c r="AV3" s="110"/>
+      <c r="AW3" s="110"/>
+      <c r="AX3" s="110"/>
+      <c r="AY3" s="110"/>
+      <c r="AZ3" s="110"/>
+      <c r="BA3" s="110"/>
+      <c r="BB3" s="110"/>
+      <c r="BC3" s="110"/>
+      <c r="BD3" s="110"/>
+      <c r="BE3" s="111"/>
     </row>
     <row r="4" spans="1:57" ht="15" customHeight="1">
-      <c r="A4" s="118">
+      <c r="A4" s="112">
         <v>1</v>
       </c>
-      <c r="B4" s="119"/>
-      <c r="C4" s="119"/>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="101"/>
-      <c r="I4" s="102"/>
-      <c r="J4" s="102"/>
-      <c r="K4" s="102"/>
-      <c r="L4" s="102"/>
-      <c r="M4" s="102"/>
-      <c r="N4" s="103"/>
-      <c r="O4" s="101" t="s">
+      <c r="B4" s="113"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="116"/>
+      <c r="L4" s="116"/>
+      <c r="M4" s="116"/>
+      <c r="N4" s="117"/>
+      <c r="O4" s="115" t="s">
         <v>11</v>
       </c>
-      <c r="P4" s="104"/>
-      <c r="Q4" s="104"/>
-      <c r="R4" s="104"/>
-      <c r="S4" s="104"/>
-      <c r="T4" s="104"/>
-      <c r="U4" s="104"/>
-      <c r="V4" s="104"/>
-      <c r="W4" s="104"/>
-      <c r="X4" s="104"/>
-      <c r="Y4" s="104"/>
-      <c r="Z4" s="104"/>
-      <c r="AA4" s="104"/>
-      <c r="AB4" s="104"/>
-      <c r="AC4" s="104"/>
-      <c r="AD4" s="104"/>
-      <c r="AE4" s="104"/>
-      <c r="AF4" s="104"/>
-      <c r="AG4" s="104"/>
-      <c r="AH4" s="104"/>
-      <c r="AI4" s="104"/>
-      <c r="AJ4" s="104"/>
-      <c r="AK4" s="104"/>
-      <c r="AL4" s="104"/>
-      <c r="AM4" s="104"/>
-      <c r="AN4" s="104"/>
-      <c r="AO4" s="104"/>
-      <c r="AP4" s="105"/>
-      <c r="AQ4" s="106"/>
-      <c r="AR4" s="104"/>
-      <c r="AS4" s="104"/>
-      <c r="AT4" s="104"/>
-      <c r="AU4" s="104"/>
-      <c r="AV4" s="104"/>
-      <c r="AW4" s="104"/>
-      <c r="AX4" s="104"/>
-      <c r="AY4" s="104"/>
-      <c r="AZ4" s="104"/>
-      <c r="BA4" s="104"/>
-      <c r="BB4" s="104"/>
-      <c r="BC4" s="104"/>
-      <c r="BD4" s="104"/>
-      <c r="BE4" s="107"/>
+      <c r="P4" s="118"/>
+      <c r="Q4" s="118"/>
+      <c r="R4" s="118"/>
+      <c r="S4" s="118"/>
+      <c r="T4" s="118"/>
+      <c r="U4" s="118"/>
+      <c r="V4" s="118"/>
+      <c r="W4" s="118"/>
+      <c r="X4" s="118"/>
+      <c r="Y4" s="118"/>
+      <c r="Z4" s="118"/>
+      <c r="AA4" s="118"/>
+      <c r="AB4" s="118"/>
+      <c r="AC4" s="118"/>
+      <c r="AD4" s="118"/>
+      <c r="AE4" s="118"/>
+      <c r="AF4" s="118"/>
+      <c r="AG4" s="118"/>
+      <c r="AH4" s="118"/>
+      <c r="AI4" s="118"/>
+      <c r="AJ4" s="118"/>
+      <c r="AK4" s="118"/>
+      <c r="AL4" s="118"/>
+      <c r="AM4" s="118"/>
+      <c r="AN4" s="118"/>
+      <c r="AO4" s="118"/>
+      <c r="AP4" s="119"/>
+      <c r="AQ4" s="120"/>
+      <c r="AR4" s="118"/>
+      <c r="AS4" s="118"/>
+      <c r="AT4" s="118"/>
+      <c r="AU4" s="118"/>
+      <c r="AV4" s="118"/>
+      <c r="AW4" s="118"/>
+      <c r="AX4" s="118"/>
+      <c r="AY4" s="118"/>
+      <c r="AZ4" s="118"/>
+      <c r="BA4" s="118"/>
+      <c r="BB4" s="118"/>
+      <c r="BC4" s="118"/>
+      <c r="BD4" s="118"/>
+      <c r="BE4" s="121"/>
     </row>
     <row r="5" spans="1:57" ht="105.75" customHeight="1">
-      <c r="A5" s="81">
+      <c r="A5" s="101">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B5" s="82"/>
-      <c r="C5" s="82"/>
-      <c r="D5" s="82"/>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
-      <c r="G5" s="83"/>
+      <c r="B5" s="102"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="102"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="102"/>
+      <c r="G5" s="103"/>
       <c r="H5" s="84" t="s">
         <v>1796</v>
       </c>
@@ -65134,61 +65182,61 @@
       <c r="O5" s="84" t="s">
         <v>1798</v>
       </c>
-      <c r="P5" s="87"/>
-      <c r="Q5" s="87"/>
-      <c r="R5" s="87"/>
-      <c r="S5" s="87"/>
-      <c r="T5" s="87"/>
-      <c r="U5" s="87"/>
-      <c r="V5" s="87"/>
-      <c r="W5" s="87"/>
-      <c r="X5" s="87"/>
-      <c r="Y5" s="87"/>
-      <c r="Z5" s="87"/>
-      <c r="AA5" s="87"/>
-      <c r="AB5" s="87"/>
-      <c r="AC5" s="87"/>
-      <c r="AD5" s="87"/>
-      <c r="AE5" s="87"/>
-      <c r="AF5" s="87"/>
-      <c r="AG5" s="87"/>
-      <c r="AH5" s="87"/>
-      <c r="AI5" s="87"/>
-      <c r="AJ5" s="87"/>
-      <c r="AK5" s="87"/>
-      <c r="AL5" s="87"/>
-      <c r="AM5" s="87"/>
-      <c r="AN5" s="87"/>
-      <c r="AO5" s="87"/>
-      <c r="AP5" s="88"/>
-      <c r="AQ5" s="92" t="s">
+      <c r="P5" s="82"/>
+      <c r="Q5" s="82"/>
+      <c r="R5" s="82"/>
+      <c r="S5" s="82"/>
+      <c r="T5" s="82"/>
+      <c r="U5" s="82"/>
+      <c r="V5" s="82"/>
+      <c r="W5" s="82"/>
+      <c r="X5" s="82"/>
+      <c r="Y5" s="82"/>
+      <c r="Z5" s="82"/>
+      <c r="AA5" s="82"/>
+      <c r="AB5" s="82"/>
+      <c r="AC5" s="82"/>
+      <c r="AD5" s="82"/>
+      <c r="AE5" s="82"/>
+      <c r="AF5" s="82"/>
+      <c r="AG5" s="82"/>
+      <c r="AH5" s="82"/>
+      <c r="AI5" s="82"/>
+      <c r="AJ5" s="82"/>
+      <c r="AK5" s="82"/>
+      <c r="AL5" s="82"/>
+      <c r="AM5" s="82"/>
+      <c r="AN5" s="82"/>
+      <c r="AO5" s="82"/>
+      <c r="AP5" s="90"/>
+      <c r="AQ5" s="81" t="s">
         <v>1797</v>
       </c>
-      <c r="AR5" s="87"/>
-      <c r="AS5" s="87"/>
-      <c r="AT5" s="87"/>
-      <c r="AU5" s="87"/>
-      <c r="AV5" s="87"/>
-      <c r="AW5" s="87"/>
-      <c r="AX5" s="87"/>
-      <c r="AY5" s="87"/>
-      <c r="AZ5" s="87"/>
-      <c r="BA5" s="87"/>
-      <c r="BB5" s="87"/>
-      <c r="BC5" s="87"/>
-      <c r="BD5" s="87"/>
-      <c r="BE5" s="93"/>
+      <c r="AR5" s="82"/>
+      <c r="AS5" s="82"/>
+      <c r="AT5" s="82"/>
+      <c r="AU5" s="82"/>
+      <c r="AV5" s="82"/>
+      <c r="AW5" s="82"/>
+      <c r="AX5" s="82"/>
+      <c r="AY5" s="82"/>
+      <c r="AZ5" s="82"/>
+      <c r="BA5" s="82"/>
+      <c r="BB5" s="82"/>
+      <c r="BC5" s="82"/>
+      <c r="BD5" s="82"/>
+      <c r="BE5" s="83"/>
     </row>
     <row r="6" spans="1:57" ht="36.6" customHeight="1">
-      <c r="A6" s="81">
+      <c r="A6" s="101">
         <v>1.2</v>
       </c>
-      <c r="B6" s="82"/>
-      <c r="C6" s="82"/>
-      <c r="D6" s="82"/>
-      <c r="E6" s="82"/>
-      <c r="F6" s="82"/>
-      <c r="G6" s="83"/>
+      <c r="B6" s="102"/>
+      <c r="C6" s="102"/>
+      <c r="D6" s="102"/>
+      <c r="E6" s="102"/>
+      <c r="F6" s="102"/>
+      <c r="G6" s="103"/>
       <c r="H6" s="84" t="s">
         <v>1824</v>
       </c>
@@ -65201,124 +65249,124 @@
       <c r="O6" s="84" t="s">
         <v>1823</v>
       </c>
-      <c r="P6" s="122"/>
-      <c r="Q6" s="122"/>
-      <c r="R6" s="122"/>
-      <c r="S6" s="122"/>
-      <c r="T6" s="122"/>
-      <c r="U6" s="122"/>
-      <c r="V6" s="122"/>
-      <c r="W6" s="122"/>
-      <c r="X6" s="122"/>
-      <c r="Y6" s="122"/>
-      <c r="Z6" s="122"/>
-      <c r="AA6" s="122"/>
-      <c r="AB6" s="122"/>
-      <c r="AC6" s="122"/>
-      <c r="AD6" s="122"/>
-      <c r="AE6" s="122"/>
-      <c r="AF6" s="122"/>
-      <c r="AG6" s="122"/>
-      <c r="AH6" s="122"/>
-      <c r="AI6" s="122"/>
-      <c r="AJ6" s="122"/>
-      <c r="AK6" s="122"/>
-      <c r="AL6" s="122"/>
-      <c r="AM6" s="122"/>
-      <c r="AN6" s="122"/>
-      <c r="AO6" s="122"/>
-      <c r="AP6" s="123"/>
-      <c r="AQ6" s="92" t="s">
+      <c r="P6" s="91"/>
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
+      <c r="V6" s="91"/>
+      <c r="W6" s="91"/>
+      <c r="X6" s="91"/>
+      <c r="Y6" s="91"/>
+      <c r="Z6" s="91"/>
+      <c r="AA6" s="91"/>
+      <c r="AB6" s="91"/>
+      <c r="AC6" s="91"/>
+      <c r="AD6" s="91"/>
+      <c r="AE6" s="91"/>
+      <c r="AF6" s="91"/>
+      <c r="AG6" s="91"/>
+      <c r="AH6" s="91"/>
+      <c r="AI6" s="91"/>
+      <c r="AJ6" s="91"/>
+      <c r="AK6" s="91"/>
+      <c r="AL6" s="91"/>
+      <c r="AM6" s="91"/>
+      <c r="AN6" s="91"/>
+      <c r="AO6" s="91"/>
+      <c r="AP6" s="92"/>
+      <c r="AQ6" s="81" t="s">
         <v>1797</v>
       </c>
-      <c r="AR6" s="87"/>
-      <c r="AS6" s="87"/>
-      <c r="AT6" s="87"/>
-      <c r="AU6" s="87"/>
-      <c r="AV6" s="87"/>
-      <c r="AW6" s="87"/>
-      <c r="AX6" s="87"/>
-      <c r="AY6" s="87"/>
-      <c r="AZ6" s="87"/>
-      <c r="BA6" s="87"/>
-      <c r="BB6" s="87"/>
-      <c r="BC6" s="87"/>
-      <c r="BD6" s="87"/>
-      <c r="BE6" s="93"/>
+      <c r="AR6" s="82"/>
+      <c r="AS6" s="82"/>
+      <c r="AT6" s="82"/>
+      <c r="AU6" s="82"/>
+      <c r="AV6" s="82"/>
+      <c r="AW6" s="82"/>
+      <c r="AX6" s="82"/>
+      <c r="AY6" s="82"/>
+      <c r="AZ6" s="82"/>
+      <c r="BA6" s="82"/>
+      <c r="BB6" s="82"/>
+      <c r="BC6" s="82"/>
+      <c r="BD6" s="82"/>
+      <c r="BE6" s="83"/>
     </row>
     <row r="7" spans="1:57" ht="15" customHeight="1">
-      <c r="A7" s="81">
+      <c r="A7" s="101">
         <v>1.3</v>
       </c>
-      <c r="B7" s="82"/>
-      <c r="C7" s="82"/>
-      <c r="D7" s="82"/>
-      <c r="E7" s="82"/>
-      <c r="F7" s="82"/>
-      <c r="G7" s="83"/>
+      <c r="B7" s="102"/>
+      <c r="C7" s="102"/>
+      <c r="D7" s="102"/>
+      <c r="E7" s="102"/>
+      <c r="F7" s="102"/>
+      <c r="G7" s="103"/>
       <c r="H7" s="84"/>
-      <c r="I7" s="124"/>
-      <c r="J7" s="124"/>
-      <c r="K7" s="124"/>
-      <c r="L7" s="124"/>
-      <c r="M7" s="124"/>
-      <c r="N7" s="125"/>
-      <c r="O7" s="126" t="s">
+      <c r="I7" s="93"/>
+      <c r="J7" s="93"/>
+      <c r="K7" s="93"/>
+      <c r="L7" s="93"/>
+      <c r="M7" s="93"/>
+      <c r="N7" s="94"/>
+      <c r="O7" s="95" t="s">
         <v>2237</v>
       </c>
-      <c r="P7" s="127"/>
-      <c r="Q7" s="127"/>
-      <c r="R7" s="127"/>
-      <c r="S7" s="127"/>
-      <c r="T7" s="127"/>
-      <c r="U7" s="127"/>
-      <c r="V7" s="127"/>
-      <c r="W7" s="127"/>
-      <c r="X7" s="127"/>
-      <c r="Y7" s="127"/>
-      <c r="Z7" s="127"/>
-      <c r="AA7" s="127"/>
-      <c r="AB7" s="127"/>
-      <c r="AC7" s="127"/>
-      <c r="AD7" s="127"/>
-      <c r="AE7" s="127"/>
-      <c r="AF7" s="127"/>
-      <c r="AG7" s="127"/>
-      <c r="AH7" s="127"/>
-      <c r="AI7" s="127"/>
-      <c r="AJ7" s="127"/>
-      <c r="AK7" s="127"/>
-      <c r="AL7" s="127"/>
-      <c r="AM7" s="127"/>
-      <c r="AN7" s="127"/>
-      <c r="AO7" s="127"/>
-      <c r="AP7" s="128"/>
-      <c r="AQ7" s="129" t="s">
+      <c r="P7" s="96"/>
+      <c r="Q7" s="96"/>
+      <c r="R7" s="96"/>
+      <c r="S7" s="96"/>
+      <c r="T7" s="96"/>
+      <c r="U7" s="96"/>
+      <c r="V7" s="96"/>
+      <c r="W7" s="96"/>
+      <c r="X7" s="96"/>
+      <c r="Y7" s="96"/>
+      <c r="Z7" s="96"/>
+      <c r="AA7" s="96"/>
+      <c r="AB7" s="96"/>
+      <c r="AC7" s="96"/>
+      <c r="AD7" s="96"/>
+      <c r="AE7" s="96"/>
+      <c r="AF7" s="96"/>
+      <c r="AG7" s="96"/>
+      <c r="AH7" s="96"/>
+      <c r="AI7" s="96"/>
+      <c r="AJ7" s="96"/>
+      <c r="AK7" s="96"/>
+      <c r="AL7" s="96"/>
+      <c r="AM7" s="96"/>
+      <c r="AN7" s="96"/>
+      <c r="AO7" s="96"/>
+      <c r="AP7" s="97"/>
+      <c r="AQ7" s="98" t="s">
         <v>2238</v>
       </c>
-      <c r="AR7" s="130"/>
-      <c r="AS7" s="130"/>
-      <c r="AT7" s="130"/>
-      <c r="AU7" s="130"/>
-      <c r="AV7" s="130"/>
-      <c r="AW7" s="130"/>
-      <c r="AX7" s="130"/>
-      <c r="AY7" s="130"/>
-      <c r="AZ7" s="130"/>
-      <c r="BA7" s="130"/>
-      <c r="BB7" s="130"/>
-      <c r="BC7" s="130"/>
-      <c r="BD7" s="130"/>
-      <c r="BE7" s="131"/>
+      <c r="AR7" s="99"/>
+      <c r="AS7" s="99"/>
+      <c r="AT7" s="99"/>
+      <c r="AU7" s="99"/>
+      <c r="AV7" s="99"/>
+      <c r="AW7" s="99"/>
+      <c r="AX7" s="99"/>
+      <c r="AY7" s="99"/>
+      <c r="AZ7" s="99"/>
+      <c r="BA7" s="99"/>
+      <c r="BB7" s="99"/>
+      <c r="BC7" s="99"/>
+      <c r="BD7" s="99"/>
+      <c r="BE7" s="100"/>
     </row>
     <row r="8" spans="1:57" ht="15" customHeight="1">
-      <c r="A8" s="81"/>
-      <c r="B8" s="82"/>
-      <c r="C8" s="82"/>
-      <c r="D8" s="82"/>
-      <c r="E8" s="82"/>
-      <c r="F8" s="82"/>
-      <c r="G8" s="83"/>
+      <c r="A8" s="101"/>
+      <c r="B8" s="102"/>
+      <c r="C8" s="102"/>
+      <c r="D8" s="102"/>
+      <c r="E8" s="102"/>
+      <c r="F8" s="102"/>
+      <c r="G8" s="103"/>
       <c r="H8" s="84"/>
       <c r="I8" s="85"/>
       <c r="J8" s="85"/>
@@ -65327,57 +65375,57 @@
       <c r="M8" s="85"/>
       <c r="N8" s="86"/>
       <c r="O8" s="84"/>
-      <c r="P8" s="87"/>
-      <c r="Q8" s="87"/>
-      <c r="R8" s="87"/>
-      <c r="S8" s="87"/>
-      <c r="T8" s="87"/>
-      <c r="U8" s="87"/>
-      <c r="V8" s="87"/>
-      <c r="W8" s="87"/>
-      <c r="X8" s="87"/>
-      <c r="Y8" s="87"/>
-      <c r="Z8" s="87"/>
-      <c r="AA8" s="87"/>
-      <c r="AB8" s="87"/>
-      <c r="AC8" s="87"/>
-      <c r="AD8" s="87"/>
-      <c r="AE8" s="87"/>
-      <c r="AF8" s="87"/>
-      <c r="AG8" s="87"/>
-      <c r="AH8" s="87"/>
-      <c r="AI8" s="87"/>
-      <c r="AJ8" s="87"/>
-      <c r="AK8" s="87"/>
-      <c r="AL8" s="87"/>
-      <c r="AM8" s="87"/>
-      <c r="AN8" s="87"/>
-      <c r="AO8" s="87"/>
-      <c r="AP8" s="88"/>
-      <c r="AQ8" s="92"/>
-      <c r="AR8" s="87"/>
-      <c r="AS8" s="87"/>
-      <c r="AT8" s="87"/>
-      <c r="AU8" s="87"/>
-      <c r="AV8" s="87"/>
-      <c r="AW8" s="87"/>
-      <c r="AX8" s="87"/>
-      <c r="AY8" s="87"/>
-      <c r="AZ8" s="87"/>
-      <c r="BA8" s="87"/>
-      <c r="BB8" s="87"/>
-      <c r="BC8" s="87"/>
-      <c r="BD8" s="87"/>
-      <c r="BE8" s="93"/>
+      <c r="P8" s="82"/>
+      <c r="Q8" s="82"/>
+      <c r="R8" s="82"/>
+      <c r="S8" s="82"/>
+      <c r="T8" s="82"/>
+      <c r="U8" s="82"/>
+      <c r="V8" s="82"/>
+      <c r="W8" s="82"/>
+      <c r="X8" s="82"/>
+      <c r="Y8" s="82"/>
+      <c r="Z8" s="82"/>
+      <c r="AA8" s="82"/>
+      <c r="AB8" s="82"/>
+      <c r="AC8" s="82"/>
+      <c r="AD8" s="82"/>
+      <c r="AE8" s="82"/>
+      <c r="AF8" s="82"/>
+      <c r="AG8" s="82"/>
+      <c r="AH8" s="82"/>
+      <c r="AI8" s="82"/>
+      <c r="AJ8" s="82"/>
+      <c r="AK8" s="82"/>
+      <c r="AL8" s="82"/>
+      <c r="AM8" s="82"/>
+      <c r="AN8" s="82"/>
+      <c r="AO8" s="82"/>
+      <c r="AP8" s="90"/>
+      <c r="AQ8" s="81"/>
+      <c r="AR8" s="82"/>
+      <c r="AS8" s="82"/>
+      <c r="AT8" s="82"/>
+      <c r="AU8" s="82"/>
+      <c r="AV8" s="82"/>
+      <c r="AW8" s="82"/>
+      <c r="AX8" s="82"/>
+      <c r="AY8" s="82"/>
+      <c r="AZ8" s="82"/>
+      <c r="BA8" s="82"/>
+      <c r="BB8" s="82"/>
+      <c r="BC8" s="82"/>
+      <c r="BD8" s="82"/>
+      <c r="BE8" s="83"/>
     </row>
     <row r="9" spans="1:57" ht="15" customHeight="1">
-      <c r="A9" s="81"/>
-      <c r="B9" s="82"/>
-      <c r="C9" s="82"/>
-      <c r="D9" s="82"/>
-      <c r="E9" s="82"/>
-      <c r="F9" s="82"/>
-      <c r="G9" s="83"/>
+      <c r="A9" s="101"/>
+      <c r="B9" s="102"/>
+      <c r="C9" s="102"/>
+      <c r="D9" s="102"/>
+      <c r="E9" s="102"/>
+      <c r="F9" s="102"/>
+      <c r="G9" s="103"/>
       <c r="H9" s="84"/>
       <c r="I9" s="85"/>
       <c r="J9" s="85"/>
@@ -65386,57 +65434,57 @@
       <c r="M9" s="85"/>
       <c r="N9" s="86"/>
       <c r="O9" s="84"/>
-      <c r="P9" s="87"/>
-      <c r="Q9" s="87"/>
-      <c r="R9" s="87"/>
-      <c r="S9" s="87"/>
-      <c r="T9" s="87"/>
-      <c r="U9" s="87"/>
-      <c r="V9" s="87"/>
-      <c r="W9" s="87"/>
-      <c r="X9" s="87"/>
-      <c r="Y9" s="87"/>
-      <c r="Z9" s="87"/>
-      <c r="AA9" s="87"/>
-      <c r="AB9" s="87"/>
-      <c r="AC9" s="87"/>
-      <c r="AD9" s="87"/>
-      <c r="AE9" s="87"/>
-      <c r="AF9" s="87"/>
-      <c r="AG9" s="87"/>
-      <c r="AH9" s="87"/>
-      <c r="AI9" s="87"/>
-      <c r="AJ9" s="87"/>
-      <c r="AK9" s="87"/>
-      <c r="AL9" s="87"/>
-      <c r="AM9" s="87"/>
-      <c r="AN9" s="87"/>
-      <c r="AO9" s="87"/>
-      <c r="AP9" s="88"/>
-      <c r="AQ9" s="92"/>
-      <c r="AR9" s="87"/>
-      <c r="AS9" s="87"/>
-      <c r="AT9" s="87"/>
-      <c r="AU9" s="87"/>
-      <c r="AV9" s="87"/>
-      <c r="AW9" s="87"/>
-      <c r="AX9" s="87"/>
-      <c r="AY9" s="87"/>
-      <c r="AZ9" s="87"/>
-      <c r="BA9" s="87"/>
-      <c r="BB9" s="87"/>
-      <c r="BC9" s="87"/>
-      <c r="BD9" s="87"/>
-      <c r="BE9" s="93"/>
+      <c r="P9" s="82"/>
+      <c r="Q9" s="82"/>
+      <c r="R9" s="82"/>
+      <c r="S9" s="82"/>
+      <c r="T9" s="82"/>
+      <c r="U9" s="82"/>
+      <c r="V9" s="82"/>
+      <c r="W9" s="82"/>
+      <c r="X9" s="82"/>
+      <c r="Y9" s="82"/>
+      <c r="Z9" s="82"/>
+      <c r="AA9" s="82"/>
+      <c r="AB9" s="82"/>
+      <c r="AC9" s="82"/>
+      <c r="AD9" s="82"/>
+      <c r="AE9" s="82"/>
+      <c r="AF9" s="82"/>
+      <c r="AG9" s="82"/>
+      <c r="AH9" s="82"/>
+      <c r="AI9" s="82"/>
+      <c r="AJ9" s="82"/>
+      <c r="AK9" s="82"/>
+      <c r="AL9" s="82"/>
+      <c r="AM9" s="82"/>
+      <c r="AN9" s="82"/>
+      <c r="AO9" s="82"/>
+      <c r="AP9" s="90"/>
+      <c r="AQ9" s="81"/>
+      <c r="AR9" s="82"/>
+      <c r="AS9" s="82"/>
+      <c r="AT9" s="82"/>
+      <c r="AU9" s="82"/>
+      <c r="AV9" s="82"/>
+      <c r="AW9" s="82"/>
+      <c r="AX9" s="82"/>
+      <c r="AY9" s="82"/>
+      <c r="AZ9" s="82"/>
+      <c r="BA9" s="82"/>
+      <c r="BB9" s="82"/>
+      <c r="BC9" s="82"/>
+      <c r="BD9" s="82"/>
+      <c r="BE9" s="83"/>
     </row>
     <row r="10" spans="1:57" ht="15" customHeight="1">
-      <c r="A10" s="81"/>
-      <c r="B10" s="82"/>
-      <c r="C10" s="82"/>
-      <c r="D10" s="82"/>
-      <c r="E10" s="82"/>
-      <c r="F10" s="82"/>
-      <c r="G10" s="83"/>
+      <c r="A10" s="101"/>
+      <c r="B10" s="102"/>
+      <c r="C10" s="102"/>
+      <c r="D10" s="102"/>
+      <c r="E10" s="102"/>
+      <c r="F10" s="102"/>
+      <c r="G10" s="103"/>
       <c r="H10" s="84"/>
       <c r="I10" s="85"/>
       <c r="J10" s="85"/>
@@ -65445,57 +65493,57 @@
       <c r="M10" s="85"/>
       <c r="N10" s="86"/>
       <c r="O10" s="84"/>
-      <c r="P10" s="87"/>
-      <c r="Q10" s="87"/>
-      <c r="R10" s="87"/>
-      <c r="S10" s="87"/>
-      <c r="T10" s="87"/>
-      <c r="U10" s="87"/>
-      <c r="V10" s="87"/>
-      <c r="W10" s="87"/>
-      <c r="X10" s="87"/>
-      <c r="Y10" s="87"/>
-      <c r="Z10" s="87"/>
-      <c r="AA10" s="87"/>
-      <c r="AB10" s="87"/>
-      <c r="AC10" s="87"/>
-      <c r="AD10" s="87"/>
-      <c r="AE10" s="87"/>
-      <c r="AF10" s="87"/>
-      <c r="AG10" s="87"/>
-      <c r="AH10" s="87"/>
-      <c r="AI10" s="87"/>
-      <c r="AJ10" s="87"/>
-      <c r="AK10" s="87"/>
-      <c r="AL10" s="87"/>
-      <c r="AM10" s="87"/>
-      <c r="AN10" s="87"/>
-      <c r="AO10" s="87"/>
-      <c r="AP10" s="88"/>
-      <c r="AQ10" s="92"/>
-      <c r="AR10" s="87"/>
-      <c r="AS10" s="87"/>
-      <c r="AT10" s="87"/>
-      <c r="AU10" s="87"/>
-      <c r="AV10" s="87"/>
-      <c r="AW10" s="87"/>
-      <c r="AX10" s="87"/>
-      <c r="AY10" s="87"/>
-      <c r="AZ10" s="87"/>
-      <c r="BA10" s="87"/>
-      <c r="BB10" s="87"/>
-      <c r="BC10" s="87"/>
-      <c r="BD10" s="87"/>
-      <c r="BE10" s="93"/>
+      <c r="P10" s="82"/>
+      <c r="Q10" s="82"/>
+      <c r="R10" s="82"/>
+      <c r="S10" s="82"/>
+      <c r="T10" s="82"/>
+      <c r="U10" s="82"/>
+      <c r="V10" s="82"/>
+      <c r="W10" s="82"/>
+      <c r="X10" s="82"/>
+      <c r="Y10" s="82"/>
+      <c r="Z10" s="82"/>
+      <c r="AA10" s="82"/>
+      <c r="AB10" s="82"/>
+      <c r="AC10" s="82"/>
+      <c r="AD10" s="82"/>
+      <c r="AE10" s="82"/>
+      <c r="AF10" s="82"/>
+      <c r="AG10" s="82"/>
+      <c r="AH10" s="82"/>
+      <c r="AI10" s="82"/>
+      <c r="AJ10" s="82"/>
+      <c r="AK10" s="82"/>
+      <c r="AL10" s="82"/>
+      <c r="AM10" s="82"/>
+      <c r="AN10" s="82"/>
+      <c r="AO10" s="82"/>
+      <c r="AP10" s="90"/>
+      <c r="AQ10" s="81"/>
+      <c r="AR10" s="82"/>
+      <c r="AS10" s="82"/>
+      <c r="AT10" s="82"/>
+      <c r="AU10" s="82"/>
+      <c r="AV10" s="82"/>
+      <c r="AW10" s="82"/>
+      <c r="AX10" s="82"/>
+      <c r="AY10" s="82"/>
+      <c r="AZ10" s="82"/>
+      <c r="BA10" s="82"/>
+      <c r="BB10" s="82"/>
+      <c r="BC10" s="82"/>
+      <c r="BD10" s="82"/>
+      <c r="BE10" s="83"/>
     </row>
     <row r="11" spans="1:57" ht="15" customHeight="1">
-      <c r="A11" s="81"/>
-      <c r="B11" s="82"/>
-      <c r="C11" s="82"/>
-      <c r="D11" s="82"/>
-      <c r="E11" s="82"/>
-      <c r="F11" s="82"/>
-      <c r="G11" s="83"/>
+      <c r="A11" s="101"/>
+      <c r="B11" s="102"/>
+      <c r="C11" s="102"/>
+      <c r="D11" s="102"/>
+      <c r="E11" s="102"/>
+      <c r="F11" s="102"/>
+      <c r="G11" s="103"/>
       <c r="H11" s="84"/>
       <c r="I11" s="85"/>
       <c r="J11" s="85"/>
@@ -65504,57 +65552,57 @@
       <c r="M11" s="85"/>
       <c r="N11" s="86"/>
       <c r="O11" s="84"/>
-      <c r="P11" s="87"/>
-      <c r="Q11" s="87"/>
-      <c r="R11" s="87"/>
-      <c r="S11" s="87"/>
-      <c r="T11" s="87"/>
-      <c r="U11" s="87"/>
-      <c r="V11" s="87"/>
-      <c r="W11" s="87"/>
-      <c r="X11" s="87"/>
-      <c r="Y11" s="87"/>
-      <c r="Z11" s="87"/>
-      <c r="AA11" s="87"/>
-      <c r="AB11" s="87"/>
-      <c r="AC11" s="87"/>
-      <c r="AD11" s="87"/>
-      <c r="AE11" s="87"/>
-      <c r="AF11" s="87"/>
-      <c r="AG11" s="87"/>
-      <c r="AH11" s="87"/>
-      <c r="AI11" s="87"/>
-      <c r="AJ11" s="87"/>
-      <c r="AK11" s="87"/>
-      <c r="AL11" s="87"/>
-      <c r="AM11" s="87"/>
-      <c r="AN11" s="87"/>
-      <c r="AO11" s="87"/>
-      <c r="AP11" s="88"/>
-      <c r="AQ11" s="92"/>
-      <c r="AR11" s="87"/>
-      <c r="AS11" s="87"/>
-      <c r="AT11" s="87"/>
-      <c r="AU11" s="87"/>
-      <c r="AV11" s="87"/>
-      <c r="AW11" s="87"/>
-      <c r="AX11" s="87"/>
-      <c r="AY11" s="87"/>
-      <c r="AZ11" s="87"/>
-      <c r="BA11" s="87"/>
-      <c r="BB11" s="87"/>
-      <c r="BC11" s="87"/>
-      <c r="BD11" s="87"/>
-      <c r="BE11" s="93"/>
+      <c r="P11" s="82"/>
+      <c r="Q11" s="82"/>
+      <c r="R11" s="82"/>
+      <c r="S11" s="82"/>
+      <c r="T11" s="82"/>
+      <c r="U11" s="82"/>
+      <c r="V11" s="82"/>
+      <c r="W11" s="82"/>
+      <c r="X11" s="82"/>
+      <c r="Y11" s="82"/>
+      <c r="Z11" s="82"/>
+      <c r="AA11" s="82"/>
+      <c r="AB11" s="82"/>
+      <c r="AC11" s="82"/>
+      <c r="AD11" s="82"/>
+      <c r="AE11" s="82"/>
+      <c r="AF11" s="82"/>
+      <c r="AG11" s="82"/>
+      <c r="AH11" s="82"/>
+      <c r="AI11" s="82"/>
+      <c r="AJ11" s="82"/>
+      <c r="AK11" s="82"/>
+      <c r="AL11" s="82"/>
+      <c r="AM11" s="82"/>
+      <c r="AN11" s="82"/>
+      <c r="AO11" s="82"/>
+      <c r="AP11" s="90"/>
+      <c r="AQ11" s="81"/>
+      <c r="AR11" s="82"/>
+      <c r="AS11" s="82"/>
+      <c r="AT11" s="82"/>
+      <c r="AU11" s="82"/>
+      <c r="AV11" s="82"/>
+      <c r="AW11" s="82"/>
+      <c r="AX11" s="82"/>
+      <c r="AY11" s="82"/>
+      <c r="AZ11" s="82"/>
+      <c r="BA11" s="82"/>
+      <c r="BB11" s="82"/>
+      <c r="BC11" s="82"/>
+      <c r="BD11" s="82"/>
+      <c r="BE11" s="83"/>
     </row>
     <row r="12" spans="1:57" ht="15" customHeight="1">
-      <c r="A12" s="81"/>
-      <c r="B12" s="82"/>
-      <c r="C12" s="82"/>
-      <c r="D12" s="82"/>
-      <c r="E12" s="82"/>
-      <c r="F12" s="82"/>
-      <c r="G12" s="83"/>
+      <c r="A12" s="101"/>
+      <c r="B12" s="102"/>
+      <c r="C12" s="102"/>
+      <c r="D12" s="102"/>
+      <c r="E12" s="102"/>
+      <c r="F12" s="102"/>
+      <c r="G12" s="103"/>
       <c r="H12" s="84"/>
       <c r="I12" s="85"/>
       <c r="J12" s="85"/>
@@ -65563,57 +65611,57 @@
       <c r="M12" s="85"/>
       <c r="N12" s="86"/>
       <c r="O12" s="84"/>
-      <c r="P12" s="87"/>
-      <c r="Q12" s="87"/>
-      <c r="R12" s="87"/>
-      <c r="S12" s="87"/>
-      <c r="T12" s="87"/>
-      <c r="U12" s="87"/>
-      <c r="V12" s="87"/>
-      <c r="W12" s="87"/>
-      <c r="X12" s="87"/>
-      <c r="Y12" s="87"/>
-      <c r="Z12" s="87"/>
-      <c r="AA12" s="87"/>
-      <c r="AB12" s="87"/>
-      <c r="AC12" s="87"/>
-      <c r="AD12" s="87"/>
-      <c r="AE12" s="87"/>
-      <c r="AF12" s="87"/>
-      <c r="AG12" s="87"/>
-      <c r="AH12" s="87"/>
-      <c r="AI12" s="87"/>
-      <c r="AJ12" s="87"/>
-      <c r="AK12" s="87"/>
-      <c r="AL12" s="87"/>
-      <c r="AM12" s="87"/>
-      <c r="AN12" s="87"/>
-      <c r="AO12" s="87"/>
-      <c r="AP12" s="88"/>
-      <c r="AQ12" s="92"/>
-      <c r="AR12" s="87"/>
-      <c r="AS12" s="87"/>
-      <c r="AT12" s="87"/>
-      <c r="AU12" s="87"/>
-      <c r="AV12" s="87"/>
-      <c r="AW12" s="87"/>
-      <c r="AX12" s="87"/>
-      <c r="AY12" s="87"/>
-      <c r="AZ12" s="87"/>
-      <c r="BA12" s="87"/>
-      <c r="BB12" s="87"/>
-      <c r="BC12" s="87"/>
-      <c r="BD12" s="87"/>
-      <c r="BE12" s="93"/>
+      <c r="P12" s="82"/>
+      <c r="Q12" s="82"/>
+      <c r="R12" s="82"/>
+      <c r="S12" s="82"/>
+      <c r="T12" s="82"/>
+      <c r="U12" s="82"/>
+      <c r="V12" s="82"/>
+      <c r="W12" s="82"/>
+      <c r="X12" s="82"/>
+      <c r="Y12" s="82"/>
+      <c r="Z12" s="82"/>
+      <c r="AA12" s="82"/>
+      <c r="AB12" s="82"/>
+      <c r="AC12" s="82"/>
+      <c r="AD12" s="82"/>
+      <c r="AE12" s="82"/>
+      <c r="AF12" s="82"/>
+      <c r="AG12" s="82"/>
+      <c r="AH12" s="82"/>
+      <c r="AI12" s="82"/>
+      <c r="AJ12" s="82"/>
+      <c r="AK12" s="82"/>
+      <c r="AL12" s="82"/>
+      <c r="AM12" s="82"/>
+      <c r="AN12" s="82"/>
+      <c r="AO12" s="82"/>
+      <c r="AP12" s="90"/>
+      <c r="AQ12" s="81"/>
+      <c r="AR12" s="82"/>
+      <c r="AS12" s="82"/>
+      <c r="AT12" s="82"/>
+      <c r="AU12" s="82"/>
+      <c r="AV12" s="82"/>
+      <c r="AW12" s="82"/>
+      <c r="AX12" s="82"/>
+      <c r="AY12" s="82"/>
+      <c r="AZ12" s="82"/>
+      <c r="BA12" s="82"/>
+      <c r="BB12" s="82"/>
+      <c r="BC12" s="82"/>
+      <c r="BD12" s="82"/>
+      <c r="BE12" s="83"/>
     </row>
     <row r="13" spans="1:57" ht="15" customHeight="1">
-      <c r="A13" s="81"/>
-      <c r="B13" s="82"/>
-      <c r="C13" s="82"/>
-      <c r="D13" s="82"/>
-      <c r="E13" s="82"/>
-      <c r="F13" s="82"/>
-      <c r="G13" s="83"/>
+      <c r="A13" s="101"/>
+      <c r="B13" s="102"/>
+      <c r="C13" s="102"/>
+      <c r="D13" s="102"/>
+      <c r="E13" s="102"/>
+      <c r="F13" s="102"/>
+      <c r="G13" s="103"/>
       <c r="H13" s="84"/>
       <c r="I13" s="85"/>
       <c r="J13" s="85"/>
@@ -65622,57 +65670,57 @@
       <c r="M13" s="85"/>
       <c r="N13" s="86"/>
       <c r="O13" s="84"/>
-      <c r="P13" s="87"/>
-      <c r="Q13" s="87"/>
-      <c r="R13" s="87"/>
-      <c r="S13" s="87"/>
-      <c r="T13" s="87"/>
-      <c r="U13" s="87"/>
-      <c r="V13" s="87"/>
-      <c r="W13" s="87"/>
-      <c r="X13" s="87"/>
-      <c r="Y13" s="87"/>
-      <c r="Z13" s="87"/>
-      <c r="AA13" s="87"/>
-      <c r="AB13" s="87"/>
-      <c r="AC13" s="87"/>
-      <c r="AD13" s="87"/>
-      <c r="AE13" s="87"/>
-      <c r="AF13" s="87"/>
-      <c r="AG13" s="87"/>
-      <c r="AH13" s="87"/>
-      <c r="AI13" s="87"/>
-      <c r="AJ13" s="87"/>
-      <c r="AK13" s="87"/>
-      <c r="AL13" s="87"/>
-      <c r="AM13" s="87"/>
-      <c r="AN13" s="87"/>
-      <c r="AO13" s="87"/>
-      <c r="AP13" s="88"/>
-      <c r="AQ13" s="92"/>
-      <c r="AR13" s="87"/>
-      <c r="AS13" s="87"/>
-      <c r="AT13" s="87"/>
-      <c r="AU13" s="87"/>
-      <c r="AV13" s="87"/>
-      <c r="AW13" s="87"/>
-      <c r="AX13" s="87"/>
-      <c r="AY13" s="87"/>
-      <c r="AZ13" s="87"/>
-      <c r="BA13" s="87"/>
-      <c r="BB13" s="87"/>
-      <c r="BC13" s="87"/>
-      <c r="BD13" s="87"/>
-      <c r="BE13" s="93"/>
+      <c r="P13" s="82"/>
+      <c r="Q13" s="82"/>
+      <c r="R13" s="82"/>
+      <c r="S13" s="82"/>
+      <c r="T13" s="82"/>
+      <c r="U13" s="82"/>
+      <c r="V13" s="82"/>
+      <c r="W13" s="82"/>
+      <c r="X13" s="82"/>
+      <c r="Y13" s="82"/>
+      <c r="Z13" s="82"/>
+      <c r="AA13" s="82"/>
+      <c r="AB13" s="82"/>
+      <c r="AC13" s="82"/>
+      <c r="AD13" s="82"/>
+      <c r="AE13" s="82"/>
+      <c r="AF13" s="82"/>
+      <c r="AG13" s="82"/>
+      <c r="AH13" s="82"/>
+      <c r="AI13" s="82"/>
+      <c r="AJ13" s="82"/>
+      <c r="AK13" s="82"/>
+      <c r="AL13" s="82"/>
+      <c r="AM13" s="82"/>
+      <c r="AN13" s="82"/>
+      <c r="AO13" s="82"/>
+      <c r="AP13" s="90"/>
+      <c r="AQ13" s="81"/>
+      <c r="AR13" s="82"/>
+      <c r="AS13" s="82"/>
+      <c r="AT13" s="82"/>
+      <c r="AU13" s="82"/>
+      <c r="AV13" s="82"/>
+      <c r="AW13" s="82"/>
+      <c r="AX13" s="82"/>
+      <c r="AY13" s="82"/>
+      <c r="AZ13" s="82"/>
+      <c r="BA13" s="82"/>
+      <c r="BB13" s="82"/>
+      <c r="BC13" s="82"/>
+      <c r="BD13" s="82"/>
+      <c r="BE13" s="83"/>
     </row>
     <row r="14" spans="1:57" ht="15" customHeight="1">
-      <c r="A14" s="81"/>
-      <c r="B14" s="82"/>
-      <c r="C14" s="82"/>
-      <c r="D14" s="82"/>
-      <c r="E14" s="82"/>
-      <c r="F14" s="82"/>
-      <c r="G14" s="83"/>
+      <c r="A14" s="101"/>
+      <c r="B14" s="102"/>
+      <c r="C14" s="102"/>
+      <c r="D14" s="102"/>
+      <c r="E14" s="102"/>
+      <c r="F14" s="102"/>
+      <c r="G14" s="103"/>
       <c r="H14" s="84"/>
       <c r="I14" s="85"/>
       <c r="J14" s="85"/>
@@ -65681,57 +65729,57 @@
       <c r="M14" s="85"/>
       <c r="N14" s="86"/>
       <c r="O14" s="84"/>
-      <c r="P14" s="87"/>
-      <c r="Q14" s="87"/>
-      <c r="R14" s="87"/>
-      <c r="S14" s="87"/>
-      <c r="T14" s="87"/>
-      <c r="U14" s="87"/>
-      <c r="V14" s="87"/>
-      <c r="W14" s="87"/>
-      <c r="X14" s="87"/>
-      <c r="Y14" s="87"/>
-      <c r="Z14" s="87"/>
-      <c r="AA14" s="87"/>
-      <c r="AB14" s="87"/>
-      <c r="AC14" s="87"/>
-      <c r="AD14" s="87"/>
-      <c r="AE14" s="87"/>
-      <c r="AF14" s="87"/>
-      <c r="AG14" s="87"/>
-      <c r="AH14" s="87"/>
-      <c r="AI14" s="87"/>
-      <c r="AJ14" s="87"/>
-      <c r="AK14" s="87"/>
-      <c r="AL14" s="87"/>
-      <c r="AM14" s="87"/>
-      <c r="AN14" s="87"/>
-      <c r="AO14" s="87"/>
-      <c r="AP14" s="88"/>
-      <c r="AQ14" s="92"/>
-      <c r="AR14" s="87"/>
-      <c r="AS14" s="87"/>
-      <c r="AT14" s="87"/>
-      <c r="AU14" s="87"/>
-      <c r="AV14" s="87"/>
-      <c r="AW14" s="87"/>
-      <c r="AX14" s="87"/>
-      <c r="AY14" s="87"/>
-      <c r="AZ14" s="87"/>
-      <c r="BA14" s="87"/>
-      <c r="BB14" s="87"/>
-      <c r="BC14" s="87"/>
-      <c r="BD14" s="87"/>
-      <c r="BE14" s="93"/>
+      <c r="P14" s="82"/>
+      <c r="Q14" s="82"/>
+      <c r="R14" s="82"/>
+      <c r="S14" s="82"/>
+      <c r="T14" s="82"/>
+      <c r="U14" s="82"/>
+      <c r="V14" s="82"/>
+      <c r="W14" s="82"/>
+      <c r="X14" s="82"/>
+      <c r="Y14" s="82"/>
+      <c r="Z14" s="82"/>
+      <c r="AA14" s="82"/>
+      <c r="AB14" s="82"/>
+      <c r="AC14" s="82"/>
+      <c r="AD14" s="82"/>
+      <c r="AE14" s="82"/>
+      <c r="AF14" s="82"/>
+      <c r="AG14" s="82"/>
+      <c r="AH14" s="82"/>
+      <c r="AI14" s="82"/>
+      <c r="AJ14" s="82"/>
+      <c r="AK14" s="82"/>
+      <c r="AL14" s="82"/>
+      <c r="AM14" s="82"/>
+      <c r="AN14" s="82"/>
+      <c r="AO14" s="82"/>
+      <c r="AP14" s="90"/>
+      <c r="AQ14" s="81"/>
+      <c r="AR14" s="82"/>
+      <c r="AS14" s="82"/>
+      <c r="AT14" s="82"/>
+      <c r="AU14" s="82"/>
+      <c r="AV14" s="82"/>
+      <c r="AW14" s="82"/>
+      <c r="AX14" s="82"/>
+      <c r="AY14" s="82"/>
+      <c r="AZ14" s="82"/>
+      <c r="BA14" s="82"/>
+      <c r="BB14" s="82"/>
+      <c r="BC14" s="82"/>
+      <c r="BD14" s="82"/>
+      <c r="BE14" s="83"/>
     </row>
     <row r="15" spans="1:57" ht="15" customHeight="1">
-      <c r="A15" s="81"/>
-      <c r="B15" s="82"/>
-      <c r="C15" s="82"/>
-      <c r="D15" s="82"/>
-      <c r="E15" s="82"/>
-      <c r="F15" s="82"/>
-      <c r="G15" s="83"/>
+      <c r="A15" s="101"/>
+      <c r="B15" s="102"/>
+      <c r="C15" s="102"/>
+      <c r="D15" s="102"/>
+      <c r="E15" s="102"/>
+      <c r="F15" s="102"/>
+      <c r="G15" s="103"/>
       <c r="H15" s="84"/>
       <c r="I15" s="85"/>
       <c r="J15" s="85"/>
@@ -65740,57 +65788,57 @@
       <c r="M15" s="85"/>
       <c r="N15" s="86"/>
       <c r="O15" s="84"/>
-      <c r="P15" s="87"/>
-      <c r="Q15" s="87"/>
-      <c r="R15" s="87"/>
-      <c r="S15" s="87"/>
-      <c r="T15" s="87"/>
-      <c r="U15" s="87"/>
-      <c r="V15" s="87"/>
-      <c r="W15" s="87"/>
-      <c r="X15" s="87"/>
-      <c r="Y15" s="87"/>
-      <c r="Z15" s="87"/>
-      <c r="AA15" s="87"/>
-      <c r="AB15" s="87"/>
-      <c r="AC15" s="87"/>
-      <c r="AD15" s="87"/>
-      <c r="AE15" s="87"/>
-      <c r="AF15" s="87"/>
-      <c r="AG15" s="87"/>
-      <c r="AH15" s="87"/>
-      <c r="AI15" s="87"/>
-      <c r="AJ15" s="87"/>
-      <c r="AK15" s="87"/>
-      <c r="AL15" s="87"/>
-      <c r="AM15" s="87"/>
-      <c r="AN15" s="87"/>
-      <c r="AO15" s="87"/>
-      <c r="AP15" s="88"/>
-      <c r="AQ15" s="92"/>
-      <c r="AR15" s="87"/>
-      <c r="AS15" s="87"/>
-      <c r="AT15" s="87"/>
-      <c r="AU15" s="87"/>
-      <c r="AV15" s="87"/>
-      <c r="AW15" s="87"/>
-      <c r="AX15" s="87"/>
-      <c r="AY15" s="87"/>
-      <c r="AZ15" s="87"/>
-      <c r="BA15" s="87"/>
-      <c r="BB15" s="87"/>
-      <c r="BC15" s="87"/>
-      <c r="BD15" s="87"/>
-      <c r="BE15" s="93"/>
+      <c r="P15" s="82"/>
+      <c r="Q15" s="82"/>
+      <c r="R15" s="82"/>
+      <c r="S15" s="82"/>
+      <c r="T15" s="82"/>
+      <c r="U15" s="82"/>
+      <c r="V15" s="82"/>
+      <c r="W15" s="82"/>
+      <c r="X15" s="82"/>
+      <c r="Y15" s="82"/>
+      <c r="Z15" s="82"/>
+      <c r="AA15" s="82"/>
+      <c r="AB15" s="82"/>
+      <c r="AC15" s="82"/>
+      <c r="AD15" s="82"/>
+      <c r="AE15" s="82"/>
+      <c r="AF15" s="82"/>
+      <c r="AG15" s="82"/>
+      <c r="AH15" s="82"/>
+      <c r="AI15" s="82"/>
+      <c r="AJ15" s="82"/>
+      <c r="AK15" s="82"/>
+      <c r="AL15" s="82"/>
+      <c r="AM15" s="82"/>
+      <c r="AN15" s="82"/>
+      <c r="AO15" s="82"/>
+      <c r="AP15" s="90"/>
+      <c r="AQ15" s="81"/>
+      <c r="AR15" s="82"/>
+      <c r="AS15" s="82"/>
+      <c r="AT15" s="82"/>
+      <c r="AU15" s="82"/>
+      <c r="AV15" s="82"/>
+      <c r="AW15" s="82"/>
+      <c r="AX15" s="82"/>
+      <c r="AY15" s="82"/>
+      <c r="AZ15" s="82"/>
+      <c r="BA15" s="82"/>
+      <c r="BB15" s="82"/>
+      <c r="BC15" s="82"/>
+      <c r="BD15" s="82"/>
+      <c r="BE15" s="83"/>
     </row>
     <row r="16" spans="1:57" ht="15" customHeight="1">
-      <c r="A16" s="81"/>
-      <c r="B16" s="82"/>
-      <c r="C16" s="82"/>
-      <c r="D16" s="82"/>
-      <c r="E16" s="82"/>
-      <c r="F16" s="82"/>
-      <c r="G16" s="83"/>
+      <c r="A16" s="101"/>
+      <c r="B16" s="102"/>
+      <c r="C16" s="102"/>
+      <c r="D16" s="102"/>
+      <c r="E16" s="102"/>
+      <c r="F16" s="102"/>
+      <c r="G16" s="103"/>
       <c r="H16" s="84"/>
       <c r="I16" s="85"/>
       <c r="J16" s="85"/>
@@ -65799,57 +65847,57 @@
       <c r="M16" s="85"/>
       <c r="N16" s="86"/>
       <c r="O16" s="84"/>
-      <c r="P16" s="87"/>
-      <c r="Q16" s="87"/>
-      <c r="R16" s="87"/>
-      <c r="S16" s="87"/>
-      <c r="T16" s="87"/>
-      <c r="U16" s="87"/>
-      <c r="V16" s="87"/>
-      <c r="W16" s="87"/>
-      <c r="X16" s="87"/>
-      <c r="Y16" s="87"/>
-      <c r="Z16" s="87"/>
-      <c r="AA16" s="87"/>
-      <c r="AB16" s="87"/>
-      <c r="AC16" s="87"/>
-      <c r="AD16" s="87"/>
-      <c r="AE16" s="87"/>
-      <c r="AF16" s="87"/>
-      <c r="AG16" s="87"/>
-      <c r="AH16" s="87"/>
-      <c r="AI16" s="87"/>
-      <c r="AJ16" s="87"/>
-      <c r="AK16" s="87"/>
-      <c r="AL16" s="87"/>
-      <c r="AM16" s="87"/>
-      <c r="AN16" s="87"/>
-      <c r="AO16" s="87"/>
-      <c r="AP16" s="88"/>
-      <c r="AQ16" s="92"/>
-      <c r="AR16" s="87"/>
-      <c r="AS16" s="87"/>
-      <c r="AT16" s="87"/>
-      <c r="AU16" s="87"/>
-      <c r="AV16" s="87"/>
-      <c r="AW16" s="87"/>
-      <c r="AX16" s="87"/>
-      <c r="AY16" s="87"/>
-      <c r="AZ16" s="87"/>
-      <c r="BA16" s="87"/>
-      <c r="BB16" s="87"/>
-      <c r="BC16" s="87"/>
-      <c r="BD16" s="87"/>
-      <c r="BE16" s="93"/>
+      <c r="P16" s="82"/>
+      <c r="Q16" s="82"/>
+      <c r="R16" s="82"/>
+      <c r="S16" s="82"/>
+      <c r="T16" s="82"/>
+      <c r="U16" s="82"/>
+      <c r="V16" s="82"/>
+      <c r="W16" s="82"/>
+      <c r="X16" s="82"/>
+      <c r="Y16" s="82"/>
+      <c r="Z16" s="82"/>
+      <c r="AA16" s="82"/>
+      <c r="AB16" s="82"/>
+      <c r="AC16" s="82"/>
+      <c r="AD16" s="82"/>
+      <c r="AE16" s="82"/>
+      <c r="AF16" s="82"/>
+      <c r="AG16" s="82"/>
+      <c r="AH16" s="82"/>
+      <c r="AI16" s="82"/>
+      <c r="AJ16" s="82"/>
+      <c r="AK16" s="82"/>
+      <c r="AL16" s="82"/>
+      <c r="AM16" s="82"/>
+      <c r="AN16" s="82"/>
+      <c r="AO16" s="82"/>
+      <c r="AP16" s="90"/>
+      <c r="AQ16" s="81"/>
+      <c r="AR16" s="82"/>
+      <c r="AS16" s="82"/>
+      <c r="AT16" s="82"/>
+      <c r="AU16" s="82"/>
+      <c r="AV16" s="82"/>
+      <c r="AW16" s="82"/>
+      <c r="AX16" s="82"/>
+      <c r="AY16" s="82"/>
+      <c r="AZ16" s="82"/>
+      <c r="BA16" s="82"/>
+      <c r="BB16" s="82"/>
+      <c r="BC16" s="82"/>
+      <c r="BD16" s="82"/>
+      <c r="BE16" s="83"/>
     </row>
     <row r="17" spans="1:57" ht="15" customHeight="1">
-      <c r="A17" s="81"/>
-      <c r="B17" s="82"/>
-      <c r="C17" s="82"/>
-      <c r="D17" s="82"/>
-      <c r="E17" s="82"/>
-      <c r="F17" s="82"/>
-      <c r="G17" s="83"/>
+      <c r="A17" s="101"/>
+      <c r="B17" s="102"/>
+      <c r="C17" s="102"/>
+      <c r="D17" s="102"/>
+      <c r="E17" s="102"/>
+      <c r="F17" s="102"/>
+      <c r="G17" s="103"/>
       <c r="H17" s="84"/>
       <c r="I17" s="85"/>
       <c r="J17" s="85"/>
@@ -65858,57 +65906,57 @@
       <c r="M17" s="85"/>
       <c r="N17" s="86"/>
       <c r="O17" s="84"/>
-      <c r="P17" s="87"/>
-      <c r="Q17" s="87"/>
-      <c r="R17" s="87"/>
-      <c r="S17" s="87"/>
-      <c r="T17" s="87"/>
-      <c r="U17" s="87"/>
-      <c r="V17" s="87"/>
-      <c r="W17" s="87"/>
-      <c r="X17" s="87"/>
-      <c r="Y17" s="87"/>
-      <c r="Z17" s="87"/>
-      <c r="AA17" s="87"/>
-      <c r="AB17" s="87"/>
-      <c r="AC17" s="87"/>
-      <c r="AD17" s="87"/>
-      <c r="AE17" s="87"/>
-      <c r="AF17" s="87"/>
-      <c r="AG17" s="87"/>
-      <c r="AH17" s="87"/>
-      <c r="AI17" s="87"/>
-      <c r="AJ17" s="87"/>
-      <c r="AK17" s="87"/>
-      <c r="AL17" s="87"/>
-      <c r="AM17" s="87"/>
-      <c r="AN17" s="87"/>
-      <c r="AO17" s="87"/>
-      <c r="AP17" s="88"/>
-      <c r="AQ17" s="92"/>
-      <c r="AR17" s="87"/>
-      <c r="AS17" s="87"/>
-      <c r="AT17" s="87"/>
-      <c r="AU17" s="87"/>
-      <c r="AV17" s="87"/>
-      <c r="AW17" s="87"/>
-      <c r="AX17" s="87"/>
-      <c r="AY17" s="87"/>
-      <c r="AZ17" s="87"/>
-      <c r="BA17" s="87"/>
-      <c r="BB17" s="87"/>
-      <c r="BC17" s="87"/>
-      <c r="BD17" s="87"/>
-      <c r="BE17" s="93"/>
+      <c r="P17" s="82"/>
+      <c r="Q17" s="82"/>
+      <c r="R17" s="82"/>
+      <c r="S17" s="82"/>
+      <c r="T17" s="82"/>
+      <c r="U17" s="82"/>
+      <c r="V17" s="82"/>
+      <c r="W17" s="82"/>
+      <c r="X17" s="82"/>
+      <c r="Y17" s="82"/>
+      <c r="Z17" s="82"/>
+      <c r="AA17" s="82"/>
+      <c r="AB17" s="82"/>
+      <c r="AC17" s="82"/>
+      <c r="AD17" s="82"/>
+      <c r="AE17" s="82"/>
+      <c r="AF17" s="82"/>
+      <c r="AG17" s="82"/>
+      <c r="AH17" s="82"/>
+      <c r="AI17" s="82"/>
+      <c r="AJ17" s="82"/>
+      <c r="AK17" s="82"/>
+      <c r="AL17" s="82"/>
+      <c r="AM17" s="82"/>
+      <c r="AN17" s="82"/>
+      <c r="AO17" s="82"/>
+      <c r="AP17" s="90"/>
+      <c r="AQ17" s="81"/>
+      <c r="AR17" s="82"/>
+      <c r="AS17" s="82"/>
+      <c r="AT17" s="82"/>
+      <c r="AU17" s="82"/>
+      <c r="AV17" s="82"/>
+      <c r="AW17" s="82"/>
+      <c r="AX17" s="82"/>
+      <c r="AY17" s="82"/>
+      <c r="AZ17" s="82"/>
+      <c r="BA17" s="82"/>
+      <c r="BB17" s="82"/>
+      <c r="BC17" s="82"/>
+      <c r="BD17" s="82"/>
+      <c r="BE17" s="83"/>
     </row>
     <row r="18" spans="1:57" ht="15" customHeight="1">
-      <c r="A18" s="81"/>
-      <c r="B18" s="82"/>
-      <c r="C18" s="82"/>
-      <c r="D18" s="82"/>
-      <c r="E18" s="82"/>
-      <c r="F18" s="82"/>
-      <c r="G18" s="83"/>
+      <c r="A18" s="101"/>
+      <c r="B18" s="102"/>
+      <c r="C18" s="102"/>
+      <c r="D18" s="102"/>
+      <c r="E18" s="102"/>
+      <c r="F18" s="102"/>
+      <c r="G18" s="103"/>
       <c r="H18" s="84"/>
       <c r="I18" s="85"/>
       <c r="J18" s="85"/>
@@ -65917,57 +65965,57 @@
       <c r="M18" s="85"/>
       <c r="N18" s="86"/>
       <c r="O18" s="84"/>
-      <c r="P18" s="87"/>
-      <c r="Q18" s="87"/>
-      <c r="R18" s="87"/>
-      <c r="S18" s="87"/>
-      <c r="T18" s="87"/>
-      <c r="U18" s="87"/>
-      <c r="V18" s="87"/>
-      <c r="W18" s="87"/>
-      <c r="X18" s="87"/>
-      <c r="Y18" s="87"/>
-      <c r="Z18" s="87"/>
-      <c r="AA18" s="87"/>
-      <c r="AB18" s="87"/>
-      <c r="AC18" s="87"/>
-      <c r="AD18" s="87"/>
-      <c r="AE18" s="87"/>
-      <c r="AF18" s="87"/>
-      <c r="AG18" s="87"/>
-      <c r="AH18" s="87"/>
-      <c r="AI18" s="87"/>
-      <c r="AJ18" s="87"/>
-      <c r="AK18" s="87"/>
-      <c r="AL18" s="87"/>
-      <c r="AM18" s="87"/>
-      <c r="AN18" s="87"/>
-      <c r="AO18" s="87"/>
-      <c r="AP18" s="88"/>
-      <c r="AQ18" s="92"/>
-      <c r="AR18" s="87"/>
-      <c r="AS18" s="87"/>
-      <c r="AT18" s="87"/>
-      <c r="AU18" s="87"/>
-      <c r="AV18" s="87"/>
-      <c r="AW18" s="87"/>
-      <c r="AX18" s="87"/>
-      <c r="AY18" s="87"/>
-      <c r="AZ18" s="87"/>
-      <c r="BA18" s="87"/>
-      <c r="BB18" s="87"/>
-      <c r="BC18" s="87"/>
-      <c r="BD18" s="87"/>
-      <c r="BE18" s="93"/>
+      <c r="P18" s="82"/>
+      <c r="Q18" s="82"/>
+      <c r="R18" s="82"/>
+      <c r="S18" s="82"/>
+      <c r="T18" s="82"/>
+      <c r="U18" s="82"/>
+      <c r="V18" s="82"/>
+      <c r="W18" s="82"/>
+      <c r="X18" s="82"/>
+      <c r="Y18" s="82"/>
+      <c r="Z18" s="82"/>
+      <c r="AA18" s="82"/>
+      <c r="AB18" s="82"/>
+      <c r="AC18" s="82"/>
+      <c r="AD18" s="82"/>
+      <c r="AE18" s="82"/>
+      <c r="AF18" s="82"/>
+      <c r="AG18" s="82"/>
+      <c r="AH18" s="82"/>
+      <c r="AI18" s="82"/>
+      <c r="AJ18" s="82"/>
+      <c r="AK18" s="82"/>
+      <c r="AL18" s="82"/>
+      <c r="AM18" s="82"/>
+      <c r="AN18" s="82"/>
+      <c r="AO18" s="82"/>
+      <c r="AP18" s="90"/>
+      <c r="AQ18" s="81"/>
+      <c r="AR18" s="82"/>
+      <c r="AS18" s="82"/>
+      <c r="AT18" s="82"/>
+      <c r="AU18" s="82"/>
+      <c r="AV18" s="82"/>
+      <c r="AW18" s="82"/>
+      <c r="AX18" s="82"/>
+      <c r="AY18" s="82"/>
+      <c r="AZ18" s="82"/>
+      <c r="BA18" s="82"/>
+      <c r="BB18" s="82"/>
+      <c r="BC18" s="82"/>
+      <c r="BD18" s="82"/>
+      <c r="BE18" s="83"/>
     </row>
     <row r="19" spans="1:57" ht="15" customHeight="1">
-      <c r="A19" s="81"/>
-      <c r="B19" s="82"/>
-      <c r="C19" s="82"/>
-      <c r="D19" s="82"/>
-      <c r="E19" s="82"/>
-      <c r="F19" s="82"/>
-      <c r="G19" s="83"/>
+      <c r="A19" s="101"/>
+      <c r="B19" s="102"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="103"/>
       <c r="H19" s="84"/>
       <c r="I19" s="85"/>
       <c r="J19" s="85"/>
@@ -65976,57 +66024,57 @@
       <c r="M19" s="85"/>
       <c r="N19" s="86"/>
       <c r="O19" s="84"/>
-      <c r="P19" s="87"/>
-      <c r="Q19" s="87"/>
-      <c r="R19" s="87"/>
-      <c r="S19" s="87"/>
-      <c r="T19" s="87"/>
-      <c r="U19" s="87"/>
-      <c r="V19" s="87"/>
-      <c r="W19" s="87"/>
-      <c r="X19" s="87"/>
-      <c r="Y19" s="87"/>
-      <c r="Z19" s="87"/>
-      <c r="AA19" s="87"/>
-      <c r="AB19" s="87"/>
-      <c r="AC19" s="87"/>
-      <c r="AD19" s="87"/>
-      <c r="AE19" s="87"/>
-      <c r="AF19" s="87"/>
-      <c r="AG19" s="87"/>
-      <c r="AH19" s="87"/>
-      <c r="AI19" s="87"/>
-      <c r="AJ19" s="87"/>
-      <c r="AK19" s="87"/>
-      <c r="AL19" s="87"/>
-      <c r="AM19" s="87"/>
-      <c r="AN19" s="87"/>
-      <c r="AO19" s="87"/>
-      <c r="AP19" s="88"/>
-      <c r="AQ19" s="92"/>
-      <c r="AR19" s="87"/>
-      <c r="AS19" s="87"/>
-      <c r="AT19" s="87"/>
-      <c r="AU19" s="87"/>
-      <c r="AV19" s="87"/>
-      <c r="AW19" s="87"/>
-      <c r="AX19" s="87"/>
-      <c r="AY19" s="87"/>
-      <c r="AZ19" s="87"/>
-      <c r="BA19" s="87"/>
-      <c r="BB19" s="87"/>
-      <c r="BC19" s="87"/>
-      <c r="BD19" s="87"/>
-      <c r="BE19" s="93"/>
+      <c r="P19" s="82"/>
+      <c r="Q19" s="82"/>
+      <c r="R19" s="82"/>
+      <c r="S19" s="82"/>
+      <c r="T19" s="82"/>
+      <c r="U19" s="82"/>
+      <c r="V19" s="82"/>
+      <c r="W19" s="82"/>
+      <c r="X19" s="82"/>
+      <c r="Y19" s="82"/>
+      <c r="Z19" s="82"/>
+      <c r="AA19" s="82"/>
+      <c r="AB19" s="82"/>
+      <c r="AC19" s="82"/>
+      <c r="AD19" s="82"/>
+      <c r="AE19" s="82"/>
+      <c r="AF19" s="82"/>
+      <c r="AG19" s="82"/>
+      <c r="AH19" s="82"/>
+      <c r="AI19" s="82"/>
+      <c r="AJ19" s="82"/>
+      <c r="AK19" s="82"/>
+      <c r="AL19" s="82"/>
+      <c r="AM19" s="82"/>
+      <c r="AN19" s="82"/>
+      <c r="AO19" s="82"/>
+      <c r="AP19" s="90"/>
+      <c r="AQ19" s="81"/>
+      <c r="AR19" s="82"/>
+      <c r="AS19" s="82"/>
+      <c r="AT19" s="82"/>
+      <c r="AU19" s="82"/>
+      <c r="AV19" s="82"/>
+      <c r="AW19" s="82"/>
+      <c r="AX19" s="82"/>
+      <c r="AY19" s="82"/>
+      <c r="AZ19" s="82"/>
+      <c r="BA19" s="82"/>
+      <c r="BB19" s="82"/>
+      <c r="BC19" s="82"/>
+      <c r="BD19" s="82"/>
+      <c r="BE19" s="83"/>
     </row>
     <row r="20" spans="1:57" ht="15" customHeight="1">
-      <c r="A20" s="81"/>
-      <c r="B20" s="82"/>
-      <c r="C20" s="82"/>
-      <c r="D20" s="82"/>
-      <c r="E20" s="82"/>
-      <c r="F20" s="82"/>
-      <c r="G20" s="83"/>
+      <c r="A20" s="101"/>
+      <c r="B20" s="102"/>
+      <c r="C20" s="102"/>
+      <c r="D20" s="102"/>
+      <c r="E20" s="102"/>
+      <c r="F20" s="102"/>
+      <c r="G20" s="103"/>
       <c r="H20" s="84"/>
       <c r="I20" s="85"/>
       <c r="J20" s="85"/>
@@ -66035,57 +66083,57 @@
       <c r="M20" s="85"/>
       <c r="N20" s="86"/>
       <c r="O20" s="84"/>
-      <c r="P20" s="87"/>
-      <c r="Q20" s="87"/>
-      <c r="R20" s="87"/>
-      <c r="S20" s="87"/>
-      <c r="T20" s="87"/>
-      <c r="U20" s="87"/>
-      <c r="V20" s="87"/>
-      <c r="W20" s="87"/>
-      <c r="X20" s="87"/>
-      <c r="Y20" s="87"/>
-      <c r="Z20" s="87"/>
-      <c r="AA20" s="87"/>
-      <c r="AB20" s="87"/>
-      <c r="AC20" s="87"/>
-      <c r="AD20" s="87"/>
-      <c r="AE20" s="87"/>
-      <c r="AF20" s="87"/>
-      <c r="AG20" s="87"/>
-      <c r="AH20" s="87"/>
-      <c r="AI20" s="87"/>
-      <c r="AJ20" s="87"/>
-      <c r="AK20" s="87"/>
-      <c r="AL20" s="87"/>
-      <c r="AM20" s="87"/>
-      <c r="AN20" s="87"/>
-      <c r="AO20" s="87"/>
-      <c r="AP20" s="88"/>
-      <c r="AQ20" s="92"/>
-      <c r="AR20" s="87"/>
-      <c r="AS20" s="87"/>
-      <c r="AT20" s="87"/>
-      <c r="AU20" s="87"/>
-      <c r="AV20" s="87"/>
-      <c r="AW20" s="87"/>
-      <c r="AX20" s="87"/>
-      <c r="AY20" s="87"/>
-      <c r="AZ20" s="87"/>
-      <c r="BA20" s="87"/>
-      <c r="BB20" s="87"/>
-      <c r="BC20" s="87"/>
-      <c r="BD20" s="87"/>
-      <c r="BE20" s="93"/>
+      <c r="P20" s="82"/>
+      <c r="Q20" s="82"/>
+      <c r="R20" s="82"/>
+      <c r="S20" s="82"/>
+      <c r="T20" s="82"/>
+      <c r="U20" s="82"/>
+      <c r="V20" s="82"/>
+      <c r="W20" s="82"/>
+      <c r="X20" s="82"/>
+      <c r="Y20" s="82"/>
+      <c r="Z20" s="82"/>
+      <c r="AA20" s="82"/>
+      <c r="AB20" s="82"/>
+      <c r="AC20" s="82"/>
+      <c r="AD20" s="82"/>
+      <c r="AE20" s="82"/>
+      <c r="AF20" s="82"/>
+      <c r="AG20" s="82"/>
+      <c r="AH20" s="82"/>
+      <c r="AI20" s="82"/>
+      <c r="AJ20" s="82"/>
+      <c r="AK20" s="82"/>
+      <c r="AL20" s="82"/>
+      <c r="AM20" s="82"/>
+      <c r="AN20" s="82"/>
+      <c r="AO20" s="82"/>
+      <c r="AP20" s="90"/>
+      <c r="AQ20" s="81"/>
+      <c r="AR20" s="82"/>
+      <c r="AS20" s="82"/>
+      <c r="AT20" s="82"/>
+      <c r="AU20" s="82"/>
+      <c r="AV20" s="82"/>
+      <c r="AW20" s="82"/>
+      <c r="AX20" s="82"/>
+      <c r="AY20" s="82"/>
+      <c r="AZ20" s="82"/>
+      <c r="BA20" s="82"/>
+      <c r="BB20" s="82"/>
+      <c r="BC20" s="82"/>
+      <c r="BD20" s="82"/>
+      <c r="BE20" s="83"/>
     </row>
     <row r="21" spans="1:57" ht="15" customHeight="1">
-      <c r="A21" s="81"/>
-      <c r="B21" s="82"/>
-      <c r="C21" s="82"/>
-      <c r="D21" s="82"/>
-      <c r="E21" s="82"/>
-      <c r="F21" s="82"/>
-      <c r="G21" s="83"/>
+      <c r="A21" s="101"/>
+      <c r="B21" s="102"/>
+      <c r="C21" s="102"/>
+      <c r="D21" s="102"/>
+      <c r="E21" s="102"/>
+      <c r="F21" s="102"/>
+      <c r="G21" s="103"/>
       <c r="H21" s="84"/>
       <c r="I21" s="85"/>
       <c r="J21" s="85"/>
@@ -66094,57 +66142,57 @@
       <c r="M21" s="85"/>
       <c r="N21" s="86"/>
       <c r="O21" s="84"/>
-      <c r="P21" s="87"/>
-      <c r="Q21" s="87"/>
-      <c r="R21" s="87"/>
-      <c r="S21" s="87"/>
-      <c r="T21" s="87"/>
-      <c r="U21" s="87"/>
-      <c r="V21" s="87"/>
-      <c r="W21" s="87"/>
-      <c r="X21" s="87"/>
-      <c r="Y21" s="87"/>
-      <c r="Z21" s="87"/>
-      <c r="AA21" s="87"/>
-      <c r="AB21" s="87"/>
-      <c r="AC21" s="87"/>
-      <c r="AD21" s="87"/>
-      <c r="AE21" s="87"/>
-      <c r="AF21" s="87"/>
-      <c r="AG21" s="87"/>
-      <c r="AH21" s="87"/>
-      <c r="AI21" s="87"/>
-      <c r="AJ21" s="87"/>
-      <c r="AK21" s="87"/>
-      <c r="AL21" s="87"/>
-      <c r="AM21" s="87"/>
-      <c r="AN21" s="87"/>
-      <c r="AO21" s="87"/>
-      <c r="AP21" s="88"/>
-      <c r="AQ21" s="92"/>
-      <c r="AR21" s="87"/>
-      <c r="AS21" s="87"/>
-      <c r="AT21" s="87"/>
-      <c r="AU21" s="87"/>
-      <c r="AV21" s="87"/>
-      <c r="AW21" s="87"/>
-      <c r="AX21" s="87"/>
-      <c r="AY21" s="87"/>
-      <c r="AZ21" s="87"/>
-      <c r="BA21" s="87"/>
-      <c r="BB21" s="87"/>
-      <c r="BC21" s="87"/>
-      <c r="BD21" s="87"/>
-      <c r="BE21" s="93"/>
+      <c r="P21" s="82"/>
+      <c r="Q21" s="82"/>
+      <c r="R21" s="82"/>
+      <c r="S21" s="82"/>
+      <c r="T21" s="82"/>
+      <c r="U21" s="82"/>
+      <c r="V21" s="82"/>
+      <c r="W21" s="82"/>
+      <c r="X21" s="82"/>
+      <c r="Y21" s="82"/>
+      <c r="Z21" s="82"/>
+      <c r="AA21" s="82"/>
+      <c r="AB21" s="82"/>
+      <c r="AC21" s="82"/>
+      <c r="AD21" s="82"/>
+      <c r="AE21" s="82"/>
+      <c r="AF21" s="82"/>
+      <c r="AG21" s="82"/>
+      <c r="AH21" s="82"/>
+      <c r="AI21" s="82"/>
+      <c r="AJ21" s="82"/>
+      <c r="AK21" s="82"/>
+      <c r="AL21" s="82"/>
+      <c r="AM21" s="82"/>
+      <c r="AN21" s="82"/>
+      <c r="AO21" s="82"/>
+      <c r="AP21" s="90"/>
+      <c r="AQ21" s="81"/>
+      <c r="AR21" s="82"/>
+      <c r="AS21" s="82"/>
+      <c r="AT21" s="82"/>
+      <c r="AU21" s="82"/>
+      <c r="AV21" s="82"/>
+      <c r="AW21" s="82"/>
+      <c r="AX21" s="82"/>
+      <c r="AY21" s="82"/>
+      <c r="AZ21" s="82"/>
+      <c r="BA21" s="82"/>
+      <c r="BB21" s="82"/>
+      <c r="BC21" s="82"/>
+      <c r="BD21" s="82"/>
+      <c r="BE21" s="83"/>
     </row>
     <row r="22" spans="1:57" ht="15" customHeight="1">
-      <c r="A22" s="81"/>
-      <c r="B22" s="82"/>
-      <c r="C22" s="82"/>
-      <c r="D22" s="82"/>
-      <c r="E22" s="82"/>
-      <c r="F22" s="82"/>
-      <c r="G22" s="83"/>
+      <c r="A22" s="101"/>
+      <c r="B22" s="102"/>
+      <c r="C22" s="102"/>
+      <c r="D22" s="102"/>
+      <c r="E22" s="102"/>
+      <c r="F22" s="102"/>
+      <c r="G22" s="103"/>
       <c r="H22" s="84"/>
       <c r="I22" s="85"/>
       <c r="J22" s="85"/>
@@ -66153,57 +66201,57 @@
       <c r="M22" s="85"/>
       <c r="N22" s="86"/>
       <c r="O22" s="84"/>
-      <c r="P22" s="87"/>
-      <c r="Q22" s="87"/>
-      <c r="R22" s="87"/>
-      <c r="S22" s="87"/>
-      <c r="T22" s="87"/>
-      <c r="U22" s="87"/>
-      <c r="V22" s="87"/>
-      <c r="W22" s="87"/>
-      <c r="X22" s="87"/>
-      <c r="Y22" s="87"/>
-      <c r="Z22" s="87"/>
-      <c r="AA22" s="87"/>
-      <c r="AB22" s="87"/>
-      <c r="AC22" s="87"/>
-      <c r="AD22" s="87"/>
-      <c r="AE22" s="87"/>
-      <c r="AF22" s="87"/>
-      <c r="AG22" s="87"/>
-      <c r="AH22" s="87"/>
-      <c r="AI22" s="87"/>
-      <c r="AJ22" s="87"/>
-      <c r="AK22" s="87"/>
-      <c r="AL22" s="87"/>
-      <c r="AM22" s="87"/>
-      <c r="AN22" s="87"/>
-      <c r="AO22" s="87"/>
-      <c r="AP22" s="88"/>
-      <c r="AQ22" s="92"/>
-      <c r="AR22" s="87"/>
-      <c r="AS22" s="87"/>
-      <c r="AT22" s="87"/>
-      <c r="AU22" s="87"/>
-      <c r="AV22" s="87"/>
-      <c r="AW22" s="87"/>
-      <c r="AX22" s="87"/>
-      <c r="AY22" s="87"/>
-      <c r="AZ22" s="87"/>
-      <c r="BA22" s="87"/>
-      <c r="BB22" s="87"/>
-      <c r="BC22" s="87"/>
-      <c r="BD22" s="87"/>
-      <c r="BE22" s="93"/>
+      <c r="P22" s="82"/>
+      <c r="Q22" s="82"/>
+      <c r="R22" s="82"/>
+      <c r="S22" s="82"/>
+      <c r="T22" s="82"/>
+      <c r="U22" s="82"/>
+      <c r="V22" s="82"/>
+      <c r="W22" s="82"/>
+      <c r="X22" s="82"/>
+      <c r="Y22" s="82"/>
+      <c r="Z22" s="82"/>
+      <c r="AA22" s="82"/>
+      <c r="AB22" s="82"/>
+      <c r="AC22" s="82"/>
+      <c r="AD22" s="82"/>
+      <c r="AE22" s="82"/>
+      <c r="AF22" s="82"/>
+      <c r="AG22" s="82"/>
+      <c r="AH22" s="82"/>
+      <c r="AI22" s="82"/>
+      <c r="AJ22" s="82"/>
+      <c r="AK22" s="82"/>
+      <c r="AL22" s="82"/>
+      <c r="AM22" s="82"/>
+      <c r="AN22" s="82"/>
+      <c r="AO22" s="82"/>
+      <c r="AP22" s="90"/>
+      <c r="AQ22" s="81"/>
+      <c r="AR22" s="82"/>
+      <c r="AS22" s="82"/>
+      <c r="AT22" s="82"/>
+      <c r="AU22" s="82"/>
+      <c r="AV22" s="82"/>
+      <c r="AW22" s="82"/>
+      <c r="AX22" s="82"/>
+      <c r="AY22" s="82"/>
+      <c r="AZ22" s="82"/>
+      <c r="BA22" s="82"/>
+      <c r="BB22" s="82"/>
+      <c r="BC22" s="82"/>
+      <c r="BD22" s="82"/>
+      <c r="BE22" s="83"/>
     </row>
     <row r="23" spans="1:57" ht="15" customHeight="1">
-      <c r="A23" s="81"/>
-      <c r="B23" s="82"/>
-      <c r="C23" s="82"/>
-      <c r="D23" s="82"/>
-      <c r="E23" s="82"/>
-      <c r="F23" s="82"/>
-      <c r="G23" s="83"/>
+      <c r="A23" s="101"/>
+      <c r="B23" s="102"/>
+      <c r="C23" s="102"/>
+      <c r="D23" s="102"/>
+      <c r="E23" s="102"/>
+      <c r="F23" s="102"/>
+      <c r="G23" s="103"/>
       <c r="H23" s="84"/>
       <c r="I23" s="85"/>
       <c r="J23" s="85"/>
@@ -66212,57 +66260,57 @@
       <c r="M23" s="85"/>
       <c r="N23" s="86"/>
       <c r="O23" s="84"/>
-      <c r="P23" s="87"/>
-      <c r="Q23" s="87"/>
-      <c r="R23" s="87"/>
-      <c r="S23" s="87"/>
-      <c r="T23" s="87"/>
-      <c r="U23" s="87"/>
-      <c r="V23" s="87"/>
-      <c r="W23" s="87"/>
-      <c r="X23" s="87"/>
-      <c r="Y23" s="87"/>
-      <c r="Z23" s="87"/>
-      <c r="AA23" s="87"/>
-      <c r="AB23" s="87"/>
-      <c r="AC23" s="87"/>
-      <c r="AD23" s="87"/>
-      <c r="AE23" s="87"/>
-      <c r="AF23" s="87"/>
-      <c r="AG23" s="87"/>
-      <c r="AH23" s="87"/>
-      <c r="AI23" s="87"/>
-      <c r="AJ23" s="87"/>
-      <c r="AK23" s="87"/>
-      <c r="AL23" s="87"/>
-      <c r="AM23" s="87"/>
-      <c r="AN23" s="87"/>
-      <c r="AO23" s="87"/>
-      <c r="AP23" s="88"/>
-      <c r="AQ23" s="92"/>
-      <c r="AR23" s="87"/>
-      <c r="AS23" s="87"/>
-      <c r="AT23" s="87"/>
-      <c r="AU23" s="87"/>
-      <c r="AV23" s="87"/>
-      <c r="AW23" s="87"/>
-      <c r="AX23" s="87"/>
-      <c r="AY23" s="87"/>
-      <c r="AZ23" s="87"/>
-      <c r="BA23" s="87"/>
-      <c r="BB23" s="87"/>
-      <c r="BC23" s="87"/>
-      <c r="BD23" s="87"/>
-      <c r="BE23" s="93"/>
+      <c r="P23" s="82"/>
+      <c r="Q23" s="82"/>
+      <c r="R23" s="82"/>
+      <c r="S23" s="82"/>
+      <c r="T23" s="82"/>
+      <c r="U23" s="82"/>
+      <c r="V23" s="82"/>
+      <c r="W23" s="82"/>
+      <c r="X23" s="82"/>
+      <c r="Y23" s="82"/>
+      <c r="Z23" s="82"/>
+      <c r="AA23" s="82"/>
+      <c r="AB23" s="82"/>
+      <c r="AC23" s="82"/>
+      <c r="AD23" s="82"/>
+      <c r="AE23" s="82"/>
+      <c r="AF23" s="82"/>
+      <c r="AG23" s="82"/>
+      <c r="AH23" s="82"/>
+      <c r="AI23" s="82"/>
+      <c r="AJ23" s="82"/>
+      <c r="AK23" s="82"/>
+      <c r="AL23" s="82"/>
+      <c r="AM23" s="82"/>
+      <c r="AN23" s="82"/>
+      <c r="AO23" s="82"/>
+      <c r="AP23" s="90"/>
+      <c r="AQ23" s="81"/>
+      <c r="AR23" s="82"/>
+      <c r="AS23" s="82"/>
+      <c r="AT23" s="82"/>
+      <c r="AU23" s="82"/>
+      <c r="AV23" s="82"/>
+      <c r="AW23" s="82"/>
+      <c r="AX23" s="82"/>
+      <c r="AY23" s="82"/>
+      <c r="AZ23" s="82"/>
+      <c r="BA23" s="82"/>
+      <c r="BB23" s="82"/>
+      <c r="BC23" s="82"/>
+      <c r="BD23" s="82"/>
+      <c r="BE23" s="83"/>
     </row>
     <row r="24" spans="1:57" ht="15" customHeight="1">
-      <c r="A24" s="81"/>
-      <c r="B24" s="82"/>
-      <c r="C24" s="82"/>
-      <c r="D24" s="82"/>
-      <c r="E24" s="82"/>
-      <c r="F24" s="82"/>
-      <c r="G24" s="83"/>
+      <c r="A24" s="101"/>
+      <c r="B24" s="102"/>
+      <c r="C24" s="102"/>
+      <c r="D24" s="102"/>
+      <c r="E24" s="102"/>
+      <c r="F24" s="102"/>
+      <c r="G24" s="103"/>
       <c r="H24" s="84"/>
       <c r="I24" s="85"/>
       <c r="J24" s="85"/>
@@ -66271,57 +66319,57 @@
       <c r="M24" s="85"/>
       <c r="N24" s="86"/>
       <c r="O24" s="84"/>
-      <c r="P24" s="87"/>
-      <c r="Q24" s="87"/>
-      <c r="R24" s="87"/>
-      <c r="S24" s="87"/>
-      <c r="T24" s="87"/>
-      <c r="U24" s="87"/>
-      <c r="V24" s="87"/>
-      <c r="W24" s="87"/>
-      <c r="X24" s="87"/>
-      <c r="Y24" s="87"/>
-      <c r="Z24" s="87"/>
-      <c r="AA24" s="87"/>
-      <c r="AB24" s="87"/>
-      <c r="AC24" s="87"/>
-      <c r="AD24" s="87"/>
-      <c r="AE24" s="87"/>
-      <c r="AF24" s="87"/>
-      <c r="AG24" s="87"/>
-      <c r="AH24" s="87"/>
-      <c r="AI24" s="87"/>
-      <c r="AJ24" s="87"/>
-      <c r="AK24" s="87"/>
-      <c r="AL24" s="87"/>
-      <c r="AM24" s="87"/>
-      <c r="AN24" s="87"/>
-      <c r="AO24" s="87"/>
-      <c r="AP24" s="88"/>
-      <c r="AQ24" s="92"/>
-      <c r="AR24" s="87"/>
-      <c r="AS24" s="87"/>
-      <c r="AT24" s="87"/>
-      <c r="AU24" s="87"/>
-      <c r="AV24" s="87"/>
-      <c r="AW24" s="87"/>
-      <c r="AX24" s="87"/>
-      <c r="AY24" s="87"/>
-      <c r="AZ24" s="87"/>
-      <c r="BA24" s="87"/>
-      <c r="BB24" s="87"/>
-      <c r="BC24" s="87"/>
-      <c r="BD24" s="87"/>
-      <c r="BE24" s="93"/>
+      <c r="P24" s="82"/>
+      <c r="Q24" s="82"/>
+      <c r="R24" s="82"/>
+      <c r="S24" s="82"/>
+      <c r="T24" s="82"/>
+      <c r="U24" s="82"/>
+      <c r="V24" s="82"/>
+      <c r="W24" s="82"/>
+      <c r="X24" s="82"/>
+      <c r="Y24" s="82"/>
+      <c r="Z24" s="82"/>
+      <c r="AA24" s="82"/>
+      <c r="AB24" s="82"/>
+      <c r="AC24" s="82"/>
+      <c r="AD24" s="82"/>
+      <c r="AE24" s="82"/>
+      <c r="AF24" s="82"/>
+      <c r="AG24" s="82"/>
+      <c r="AH24" s="82"/>
+      <c r="AI24" s="82"/>
+      <c r="AJ24" s="82"/>
+      <c r="AK24" s="82"/>
+      <c r="AL24" s="82"/>
+      <c r="AM24" s="82"/>
+      <c r="AN24" s="82"/>
+      <c r="AO24" s="82"/>
+      <c r="AP24" s="90"/>
+      <c r="AQ24" s="81"/>
+      <c r="AR24" s="82"/>
+      <c r="AS24" s="82"/>
+      <c r="AT24" s="82"/>
+      <c r="AU24" s="82"/>
+      <c r="AV24" s="82"/>
+      <c r="AW24" s="82"/>
+      <c r="AX24" s="82"/>
+      <c r="AY24" s="82"/>
+      <c r="AZ24" s="82"/>
+      <c r="BA24" s="82"/>
+      <c r="BB24" s="82"/>
+      <c r="BC24" s="82"/>
+      <c r="BD24" s="82"/>
+      <c r="BE24" s="83"/>
     </row>
     <row r="25" spans="1:57" ht="15" customHeight="1">
-      <c r="A25" s="81"/>
-      <c r="B25" s="82"/>
-      <c r="C25" s="82"/>
-      <c r="D25" s="82"/>
-      <c r="E25" s="82"/>
-      <c r="F25" s="82"/>
-      <c r="G25" s="83"/>
+      <c r="A25" s="101"/>
+      <c r="B25" s="102"/>
+      <c r="C25" s="102"/>
+      <c r="D25" s="102"/>
+      <c r="E25" s="102"/>
+      <c r="F25" s="102"/>
+      <c r="G25" s="103"/>
       <c r="H25" s="84"/>
       <c r="I25" s="85"/>
       <c r="J25" s="85"/>
@@ -66330,57 +66378,57 @@
       <c r="M25" s="85"/>
       <c r="N25" s="86"/>
       <c r="O25" s="84"/>
-      <c r="P25" s="87"/>
-      <c r="Q25" s="87"/>
-      <c r="R25" s="87"/>
-      <c r="S25" s="87"/>
-      <c r="T25" s="87"/>
-      <c r="U25" s="87"/>
-      <c r="V25" s="87"/>
-      <c r="W25" s="87"/>
-      <c r="X25" s="87"/>
-      <c r="Y25" s="87"/>
-      <c r="Z25" s="87"/>
-      <c r="AA25" s="87"/>
-      <c r="AB25" s="87"/>
-      <c r="AC25" s="87"/>
-      <c r="AD25" s="87"/>
-      <c r="AE25" s="87"/>
-      <c r="AF25" s="87"/>
-      <c r="AG25" s="87"/>
-      <c r="AH25" s="87"/>
-      <c r="AI25" s="87"/>
-      <c r="AJ25" s="87"/>
-      <c r="AK25" s="87"/>
-      <c r="AL25" s="87"/>
-      <c r="AM25" s="87"/>
-      <c r="AN25" s="87"/>
-      <c r="AO25" s="87"/>
-      <c r="AP25" s="88"/>
-      <c r="AQ25" s="92"/>
-      <c r="AR25" s="87"/>
-      <c r="AS25" s="87"/>
-      <c r="AT25" s="87"/>
-      <c r="AU25" s="87"/>
-      <c r="AV25" s="87"/>
-      <c r="AW25" s="87"/>
-      <c r="AX25" s="87"/>
-      <c r="AY25" s="87"/>
-      <c r="AZ25" s="87"/>
-      <c r="BA25" s="87"/>
-      <c r="BB25" s="87"/>
-      <c r="BC25" s="87"/>
-      <c r="BD25" s="87"/>
-      <c r="BE25" s="93"/>
+      <c r="P25" s="82"/>
+      <c r="Q25" s="82"/>
+      <c r="R25" s="82"/>
+      <c r="S25" s="82"/>
+      <c r="T25" s="82"/>
+      <c r="U25" s="82"/>
+      <c r="V25" s="82"/>
+      <c r="W25" s="82"/>
+      <c r="X25" s="82"/>
+      <c r="Y25" s="82"/>
+      <c r="Z25" s="82"/>
+      <c r="AA25" s="82"/>
+      <c r="AB25" s="82"/>
+      <c r="AC25" s="82"/>
+      <c r="AD25" s="82"/>
+      <c r="AE25" s="82"/>
+      <c r="AF25" s="82"/>
+      <c r="AG25" s="82"/>
+      <c r="AH25" s="82"/>
+      <c r="AI25" s="82"/>
+      <c r="AJ25" s="82"/>
+      <c r="AK25" s="82"/>
+      <c r="AL25" s="82"/>
+      <c r="AM25" s="82"/>
+      <c r="AN25" s="82"/>
+      <c r="AO25" s="82"/>
+      <c r="AP25" s="90"/>
+      <c r="AQ25" s="81"/>
+      <c r="AR25" s="82"/>
+      <c r="AS25" s="82"/>
+      <c r="AT25" s="82"/>
+      <c r="AU25" s="82"/>
+      <c r="AV25" s="82"/>
+      <c r="AW25" s="82"/>
+      <c r="AX25" s="82"/>
+      <c r="AY25" s="82"/>
+      <c r="AZ25" s="82"/>
+      <c r="BA25" s="82"/>
+      <c r="BB25" s="82"/>
+      <c r="BC25" s="82"/>
+      <c r="BD25" s="82"/>
+      <c r="BE25" s="83"/>
     </row>
     <row r="26" spans="1:57" ht="15" customHeight="1">
-      <c r="A26" s="81"/>
-      <c r="B26" s="82"/>
-      <c r="C26" s="82"/>
-      <c r="D26" s="82"/>
-      <c r="E26" s="82"/>
-      <c r="F26" s="82"/>
-      <c r="G26" s="83"/>
+      <c r="A26" s="101"/>
+      <c r="B26" s="102"/>
+      <c r="C26" s="102"/>
+      <c r="D26" s="102"/>
+      <c r="E26" s="102"/>
+      <c r="F26" s="102"/>
+      <c r="G26" s="103"/>
       <c r="H26" s="84"/>
       <c r="I26" s="85"/>
       <c r="J26" s="85"/>
@@ -66389,57 +66437,57 @@
       <c r="M26" s="85"/>
       <c r="N26" s="86"/>
       <c r="O26" s="84"/>
-      <c r="P26" s="87"/>
-      <c r="Q26" s="87"/>
-      <c r="R26" s="87"/>
-      <c r="S26" s="87"/>
-      <c r="T26" s="87"/>
-      <c r="U26" s="87"/>
-      <c r="V26" s="87"/>
-      <c r="W26" s="87"/>
-      <c r="X26" s="87"/>
-      <c r="Y26" s="87"/>
-      <c r="Z26" s="87"/>
-      <c r="AA26" s="87"/>
-      <c r="AB26" s="87"/>
-      <c r="AC26" s="87"/>
-      <c r="AD26" s="87"/>
-      <c r="AE26" s="87"/>
-      <c r="AF26" s="87"/>
-      <c r="AG26" s="87"/>
-      <c r="AH26" s="87"/>
-      <c r="AI26" s="87"/>
-      <c r="AJ26" s="87"/>
-      <c r="AK26" s="87"/>
-      <c r="AL26" s="87"/>
-      <c r="AM26" s="87"/>
-      <c r="AN26" s="87"/>
-      <c r="AO26" s="87"/>
-      <c r="AP26" s="88"/>
-      <c r="AQ26" s="92"/>
-      <c r="AR26" s="87"/>
-      <c r="AS26" s="87"/>
-      <c r="AT26" s="87"/>
-      <c r="AU26" s="87"/>
-      <c r="AV26" s="87"/>
-      <c r="AW26" s="87"/>
-      <c r="AX26" s="87"/>
-      <c r="AY26" s="87"/>
-      <c r="AZ26" s="87"/>
-      <c r="BA26" s="87"/>
-      <c r="BB26" s="87"/>
-      <c r="BC26" s="87"/>
-      <c r="BD26" s="87"/>
-      <c r="BE26" s="93"/>
+      <c r="P26" s="82"/>
+      <c r="Q26" s="82"/>
+      <c r="R26" s="82"/>
+      <c r="S26" s="82"/>
+      <c r="T26" s="82"/>
+      <c r="U26" s="82"/>
+      <c r="V26" s="82"/>
+      <c r="W26" s="82"/>
+      <c r="X26" s="82"/>
+      <c r="Y26" s="82"/>
+      <c r="Z26" s="82"/>
+      <c r="AA26" s="82"/>
+      <c r="AB26" s="82"/>
+      <c r="AC26" s="82"/>
+      <c r="AD26" s="82"/>
+      <c r="AE26" s="82"/>
+      <c r="AF26" s="82"/>
+      <c r="AG26" s="82"/>
+      <c r="AH26" s="82"/>
+      <c r="AI26" s="82"/>
+      <c r="AJ26" s="82"/>
+      <c r="AK26" s="82"/>
+      <c r="AL26" s="82"/>
+      <c r="AM26" s="82"/>
+      <c r="AN26" s="82"/>
+      <c r="AO26" s="82"/>
+      <c r="AP26" s="90"/>
+      <c r="AQ26" s="81"/>
+      <c r="AR26" s="82"/>
+      <c r="AS26" s="82"/>
+      <c r="AT26" s="82"/>
+      <c r="AU26" s="82"/>
+      <c r="AV26" s="82"/>
+      <c r="AW26" s="82"/>
+      <c r="AX26" s="82"/>
+      <c r="AY26" s="82"/>
+      <c r="AZ26" s="82"/>
+      <c r="BA26" s="82"/>
+      <c r="BB26" s="82"/>
+      <c r="BC26" s="82"/>
+      <c r="BD26" s="82"/>
+      <c r="BE26" s="83"/>
     </row>
     <row r="27" spans="1:57" ht="15" customHeight="1">
-      <c r="A27" s="81"/>
-      <c r="B27" s="82"/>
-      <c r="C27" s="82"/>
-      <c r="D27" s="82"/>
-      <c r="E27" s="82"/>
-      <c r="F27" s="82"/>
-      <c r="G27" s="83"/>
+      <c r="A27" s="101"/>
+      <c r="B27" s="102"/>
+      <c r="C27" s="102"/>
+      <c r="D27" s="102"/>
+      <c r="E27" s="102"/>
+      <c r="F27" s="102"/>
+      <c r="G27" s="103"/>
       <c r="H27" s="84"/>
       <c r="I27" s="85"/>
       <c r="J27" s="85"/>
@@ -66448,57 +66496,57 @@
       <c r="M27" s="85"/>
       <c r="N27" s="86"/>
       <c r="O27" s="84"/>
-      <c r="P27" s="87"/>
-      <c r="Q27" s="87"/>
-      <c r="R27" s="87"/>
-      <c r="S27" s="87"/>
-      <c r="T27" s="87"/>
-      <c r="U27" s="87"/>
-      <c r="V27" s="87"/>
-      <c r="W27" s="87"/>
-      <c r="X27" s="87"/>
-      <c r="Y27" s="87"/>
-      <c r="Z27" s="87"/>
-      <c r="AA27" s="87"/>
-      <c r="AB27" s="87"/>
-      <c r="AC27" s="87"/>
-      <c r="AD27" s="87"/>
-      <c r="AE27" s="87"/>
-      <c r="AF27" s="87"/>
-      <c r="AG27" s="87"/>
-      <c r="AH27" s="87"/>
-      <c r="AI27" s="87"/>
-      <c r="AJ27" s="87"/>
-      <c r="AK27" s="87"/>
-      <c r="AL27" s="87"/>
-      <c r="AM27" s="87"/>
-      <c r="AN27" s="87"/>
-      <c r="AO27" s="87"/>
-      <c r="AP27" s="88"/>
-      <c r="AQ27" s="92"/>
-      <c r="AR27" s="87"/>
-      <c r="AS27" s="87"/>
-      <c r="AT27" s="87"/>
-      <c r="AU27" s="87"/>
-      <c r="AV27" s="87"/>
-      <c r="AW27" s="87"/>
-      <c r="AX27" s="87"/>
-      <c r="AY27" s="87"/>
-      <c r="AZ27" s="87"/>
-      <c r="BA27" s="87"/>
-      <c r="BB27" s="87"/>
-      <c r="BC27" s="87"/>
-      <c r="BD27" s="87"/>
-      <c r="BE27" s="93"/>
+      <c r="P27" s="82"/>
+      <c r="Q27" s="82"/>
+      <c r="R27" s="82"/>
+      <c r="S27" s="82"/>
+      <c r="T27" s="82"/>
+      <c r="U27" s="82"/>
+      <c r="V27" s="82"/>
+      <c r="W27" s="82"/>
+      <c r="X27" s="82"/>
+      <c r="Y27" s="82"/>
+      <c r="Z27" s="82"/>
+      <c r="AA27" s="82"/>
+      <c r="AB27" s="82"/>
+      <c r="AC27" s="82"/>
+      <c r="AD27" s="82"/>
+      <c r="AE27" s="82"/>
+      <c r="AF27" s="82"/>
+      <c r="AG27" s="82"/>
+      <c r="AH27" s="82"/>
+      <c r="AI27" s="82"/>
+      <c r="AJ27" s="82"/>
+      <c r="AK27" s="82"/>
+      <c r="AL27" s="82"/>
+      <c r="AM27" s="82"/>
+      <c r="AN27" s="82"/>
+      <c r="AO27" s="82"/>
+      <c r="AP27" s="90"/>
+      <c r="AQ27" s="81"/>
+      <c r="AR27" s="82"/>
+      <c r="AS27" s="82"/>
+      <c r="AT27" s="82"/>
+      <c r="AU27" s="82"/>
+      <c r="AV27" s="82"/>
+      <c r="AW27" s="82"/>
+      <c r="AX27" s="82"/>
+      <c r="AY27" s="82"/>
+      <c r="AZ27" s="82"/>
+      <c r="BA27" s="82"/>
+      <c r="BB27" s="82"/>
+      <c r="BC27" s="82"/>
+      <c r="BD27" s="82"/>
+      <c r="BE27" s="83"/>
     </row>
     <row r="28" spans="1:57" ht="15" customHeight="1">
-      <c r="A28" s="81"/>
-      <c r="B28" s="82"/>
-      <c r="C28" s="82"/>
-      <c r="D28" s="82"/>
-      <c r="E28" s="82"/>
-      <c r="F28" s="82"/>
-      <c r="G28" s="83"/>
+      <c r="A28" s="101"/>
+      <c r="B28" s="102"/>
+      <c r="C28" s="102"/>
+      <c r="D28" s="102"/>
+      <c r="E28" s="102"/>
+      <c r="F28" s="102"/>
+      <c r="G28" s="103"/>
       <c r="H28" s="84"/>
       <c r="I28" s="85"/>
       <c r="J28" s="85"/>
@@ -66507,57 +66555,57 @@
       <c r="M28" s="85"/>
       <c r="N28" s="86"/>
       <c r="O28" s="84"/>
-      <c r="P28" s="87"/>
-      <c r="Q28" s="87"/>
-      <c r="R28" s="87"/>
-      <c r="S28" s="87"/>
-      <c r="T28" s="87"/>
-      <c r="U28" s="87"/>
-      <c r="V28" s="87"/>
-      <c r="W28" s="87"/>
-      <c r="X28" s="87"/>
-      <c r="Y28" s="87"/>
-      <c r="Z28" s="87"/>
-      <c r="AA28" s="87"/>
-      <c r="AB28" s="87"/>
-      <c r="AC28" s="87"/>
-      <c r="AD28" s="87"/>
-      <c r="AE28" s="87"/>
-      <c r="AF28" s="87"/>
-      <c r="AG28" s="87"/>
-      <c r="AH28" s="87"/>
-      <c r="AI28" s="87"/>
-      <c r="AJ28" s="87"/>
-      <c r="AK28" s="87"/>
-      <c r="AL28" s="87"/>
-      <c r="AM28" s="87"/>
-      <c r="AN28" s="87"/>
-      <c r="AO28" s="87"/>
-      <c r="AP28" s="88"/>
-      <c r="AQ28" s="92"/>
-      <c r="AR28" s="87"/>
-      <c r="AS28" s="87"/>
-      <c r="AT28" s="87"/>
-      <c r="AU28" s="87"/>
-      <c r="AV28" s="87"/>
-      <c r="AW28" s="87"/>
-      <c r="AX28" s="87"/>
-      <c r="AY28" s="87"/>
-      <c r="AZ28" s="87"/>
-      <c r="BA28" s="87"/>
-      <c r="BB28" s="87"/>
-      <c r="BC28" s="87"/>
-      <c r="BD28" s="87"/>
-      <c r="BE28" s="93"/>
+      <c r="P28" s="82"/>
+      <c r="Q28" s="82"/>
+      <c r="R28" s="82"/>
+      <c r="S28" s="82"/>
+      <c r="T28" s="82"/>
+      <c r="U28" s="82"/>
+      <c r="V28" s="82"/>
+      <c r="W28" s="82"/>
+      <c r="X28" s="82"/>
+      <c r="Y28" s="82"/>
+      <c r="Z28" s="82"/>
+      <c r="AA28" s="82"/>
+      <c r="AB28" s="82"/>
+      <c r="AC28" s="82"/>
+      <c r="AD28" s="82"/>
+      <c r="AE28" s="82"/>
+      <c r="AF28" s="82"/>
+      <c r="AG28" s="82"/>
+      <c r="AH28" s="82"/>
+      <c r="AI28" s="82"/>
+      <c r="AJ28" s="82"/>
+      <c r="AK28" s="82"/>
+      <c r="AL28" s="82"/>
+      <c r="AM28" s="82"/>
+      <c r="AN28" s="82"/>
+      <c r="AO28" s="82"/>
+      <c r="AP28" s="90"/>
+      <c r="AQ28" s="81"/>
+      <c r="AR28" s="82"/>
+      <c r="AS28" s="82"/>
+      <c r="AT28" s="82"/>
+      <c r="AU28" s="82"/>
+      <c r="AV28" s="82"/>
+      <c r="AW28" s="82"/>
+      <c r="AX28" s="82"/>
+      <c r="AY28" s="82"/>
+      <c r="AZ28" s="82"/>
+      <c r="BA28" s="82"/>
+      <c r="BB28" s="82"/>
+      <c r="BC28" s="82"/>
+      <c r="BD28" s="82"/>
+      <c r="BE28" s="83"/>
     </row>
     <row r="29" spans="1:57" ht="15" customHeight="1">
-      <c r="A29" s="81"/>
-      <c r="B29" s="82"/>
-      <c r="C29" s="82"/>
-      <c r="D29" s="82"/>
-      <c r="E29" s="82"/>
-      <c r="F29" s="82"/>
-      <c r="G29" s="83"/>
+      <c r="A29" s="101"/>
+      <c r="B29" s="102"/>
+      <c r="C29" s="102"/>
+      <c r="D29" s="102"/>
+      <c r="E29" s="102"/>
+      <c r="F29" s="102"/>
+      <c r="G29" s="103"/>
       <c r="H29" s="84"/>
       <c r="I29" s="85"/>
       <c r="J29" s="85"/>
@@ -66566,57 +66614,57 @@
       <c r="M29" s="85"/>
       <c r="N29" s="86"/>
       <c r="O29" s="84"/>
-      <c r="P29" s="87"/>
-      <c r="Q29" s="87"/>
-      <c r="R29" s="87"/>
-      <c r="S29" s="87"/>
-      <c r="T29" s="87"/>
-      <c r="U29" s="87"/>
-      <c r="V29" s="87"/>
-      <c r="W29" s="87"/>
-      <c r="X29" s="87"/>
-      <c r="Y29" s="87"/>
-      <c r="Z29" s="87"/>
-      <c r="AA29" s="87"/>
-      <c r="AB29" s="87"/>
-      <c r="AC29" s="87"/>
-      <c r="AD29" s="87"/>
-      <c r="AE29" s="87"/>
-      <c r="AF29" s="87"/>
-      <c r="AG29" s="87"/>
-      <c r="AH29" s="87"/>
-      <c r="AI29" s="87"/>
-      <c r="AJ29" s="87"/>
-      <c r="AK29" s="87"/>
-      <c r="AL29" s="87"/>
-      <c r="AM29" s="87"/>
-      <c r="AN29" s="87"/>
-      <c r="AO29" s="87"/>
-      <c r="AP29" s="88"/>
-      <c r="AQ29" s="92"/>
-      <c r="AR29" s="87"/>
-      <c r="AS29" s="87"/>
-      <c r="AT29" s="87"/>
-      <c r="AU29" s="87"/>
-      <c r="AV29" s="87"/>
-      <c r="AW29" s="87"/>
-      <c r="AX29" s="87"/>
-      <c r="AY29" s="87"/>
-      <c r="AZ29" s="87"/>
-      <c r="BA29" s="87"/>
-      <c r="BB29" s="87"/>
-      <c r="BC29" s="87"/>
-      <c r="BD29" s="87"/>
-      <c r="BE29" s="93"/>
+      <c r="P29" s="82"/>
+      <c r="Q29" s="82"/>
+      <c r="R29" s="82"/>
+      <c r="S29" s="82"/>
+      <c r="T29" s="82"/>
+      <c r="U29" s="82"/>
+      <c r="V29" s="82"/>
+      <c r="W29" s="82"/>
+      <c r="X29" s="82"/>
+      <c r="Y29" s="82"/>
+      <c r="Z29" s="82"/>
+      <c r="AA29" s="82"/>
+      <c r="AB29" s="82"/>
+      <c r="AC29" s="82"/>
+      <c r="AD29" s="82"/>
+      <c r="AE29" s="82"/>
+      <c r="AF29" s="82"/>
+      <c r="AG29" s="82"/>
+      <c r="AH29" s="82"/>
+      <c r="AI29" s="82"/>
+      <c r="AJ29" s="82"/>
+      <c r="AK29" s="82"/>
+      <c r="AL29" s="82"/>
+      <c r="AM29" s="82"/>
+      <c r="AN29" s="82"/>
+      <c r="AO29" s="82"/>
+      <c r="AP29" s="90"/>
+      <c r="AQ29" s="81"/>
+      <c r="AR29" s="82"/>
+      <c r="AS29" s="82"/>
+      <c r="AT29" s="82"/>
+      <c r="AU29" s="82"/>
+      <c r="AV29" s="82"/>
+      <c r="AW29" s="82"/>
+      <c r="AX29" s="82"/>
+      <c r="AY29" s="82"/>
+      <c r="AZ29" s="82"/>
+      <c r="BA29" s="82"/>
+      <c r="BB29" s="82"/>
+      <c r="BC29" s="82"/>
+      <c r="BD29" s="82"/>
+      <c r="BE29" s="83"/>
     </row>
     <row r="30" spans="1:57" ht="15" customHeight="1">
-      <c r="A30" s="81"/>
-      <c r="B30" s="82"/>
-      <c r="C30" s="82"/>
-      <c r="D30" s="82"/>
-      <c r="E30" s="82"/>
-      <c r="F30" s="82"/>
-      <c r="G30" s="83"/>
+      <c r="A30" s="101"/>
+      <c r="B30" s="102"/>
+      <c r="C30" s="102"/>
+      <c r="D30" s="102"/>
+      <c r="E30" s="102"/>
+      <c r="F30" s="102"/>
+      <c r="G30" s="103"/>
       <c r="H30" s="84"/>
       <c r="I30" s="85"/>
       <c r="J30" s="85"/>
@@ -66625,57 +66673,57 @@
       <c r="M30" s="85"/>
       <c r="N30" s="86"/>
       <c r="O30" s="84"/>
-      <c r="P30" s="87"/>
-      <c r="Q30" s="87"/>
-      <c r="R30" s="87"/>
-      <c r="S30" s="87"/>
-      <c r="T30" s="87"/>
-      <c r="U30" s="87"/>
-      <c r="V30" s="87"/>
-      <c r="W30" s="87"/>
-      <c r="X30" s="87"/>
-      <c r="Y30" s="87"/>
-      <c r="Z30" s="87"/>
-      <c r="AA30" s="87"/>
-      <c r="AB30" s="87"/>
-      <c r="AC30" s="87"/>
-      <c r="AD30" s="87"/>
-      <c r="AE30" s="87"/>
-      <c r="AF30" s="87"/>
-      <c r="AG30" s="87"/>
-      <c r="AH30" s="87"/>
-      <c r="AI30" s="87"/>
-      <c r="AJ30" s="87"/>
-      <c r="AK30" s="87"/>
-      <c r="AL30" s="87"/>
-      <c r="AM30" s="87"/>
-      <c r="AN30" s="87"/>
-      <c r="AO30" s="87"/>
-      <c r="AP30" s="88"/>
-      <c r="AQ30" s="92"/>
-      <c r="AR30" s="87"/>
-      <c r="AS30" s="87"/>
-      <c r="AT30" s="87"/>
-      <c r="AU30" s="87"/>
-      <c r="AV30" s="87"/>
-      <c r="AW30" s="87"/>
-      <c r="AX30" s="87"/>
-      <c r="AY30" s="87"/>
-      <c r="AZ30" s="87"/>
-      <c r="BA30" s="87"/>
-      <c r="BB30" s="87"/>
-      <c r="BC30" s="87"/>
-      <c r="BD30" s="87"/>
-      <c r="BE30" s="93"/>
+      <c r="P30" s="82"/>
+      <c r="Q30" s="82"/>
+      <c r="R30" s="82"/>
+      <c r="S30" s="82"/>
+      <c r="T30" s="82"/>
+      <c r="U30" s="82"/>
+      <c r="V30" s="82"/>
+      <c r="W30" s="82"/>
+      <c r="X30" s="82"/>
+      <c r="Y30" s="82"/>
+      <c r="Z30" s="82"/>
+      <c r="AA30" s="82"/>
+      <c r="AB30" s="82"/>
+      <c r="AC30" s="82"/>
+      <c r="AD30" s="82"/>
+      <c r="AE30" s="82"/>
+      <c r="AF30" s="82"/>
+      <c r="AG30" s="82"/>
+      <c r="AH30" s="82"/>
+      <c r="AI30" s="82"/>
+      <c r="AJ30" s="82"/>
+      <c r="AK30" s="82"/>
+      <c r="AL30" s="82"/>
+      <c r="AM30" s="82"/>
+      <c r="AN30" s="82"/>
+      <c r="AO30" s="82"/>
+      <c r="AP30" s="90"/>
+      <c r="AQ30" s="81"/>
+      <c r="AR30" s="82"/>
+      <c r="AS30" s="82"/>
+      <c r="AT30" s="82"/>
+      <c r="AU30" s="82"/>
+      <c r="AV30" s="82"/>
+      <c r="AW30" s="82"/>
+      <c r="AX30" s="82"/>
+      <c r="AY30" s="82"/>
+      <c r="AZ30" s="82"/>
+      <c r="BA30" s="82"/>
+      <c r="BB30" s="82"/>
+      <c r="BC30" s="82"/>
+      <c r="BD30" s="82"/>
+      <c r="BE30" s="83"/>
     </row>
     <row r="31" spans="1:57" ht="15" customHeight="1">
-      <c r="A31" s="81"/>
-      <c r="B31" s="82"/>
-      <c r="C31" s="82"/>
-      <c r="D31" s="82"/>
-      <c r="E31" s="82"/>
-      <c r="F31" s="82"/>
-      <c r="G31" s="83"/>
+      <c r="A31" s="101"/>
+      <c r="B31" s="102"/>
+      <c r="C31" s="102"/>
+      <c r="D31" s="102"/>
+      <c r="E31" s="102"/>
+      <c r="F31" s="102"/>
+      <c r="G31" s="103"/>
       <c r="H31" s="84"/>
       <c r="I31" s="85"/>
       <c r="J31" s="85"/>
@@ -66684,57 +66732,57 @@
       <c r="M31" s="85"/>
       <c r="N31" s="86"/>
       <c r="O31" s="84"/>
-      <c r="P31" s="87"/>
-      <c r="Q31" s="87"/>
-      <c r="R31" s="87"/>
-      <c r="S31" s="87"/>
-      <c r="T31" s="87"/>
-      <c r="U31" s="87"/>
-      <c r="V31" s="87"/>
-      <c r="W31" s="87"/>
-      <c r="X31" s="87"/>
-      <c r="Y31" s="87"/>
-      <c r="Z31" s="87"/>
-      <c r="AA31" s="87"/>
-      <c r="AB31" s="87"/>
-      <c r="AC31" s="87"/>
-      <c r="AD31" s="87"/>
-      <c r="AE31" s="87"/>
-      <c r="AF31" s="87"/>
-      <c r="AG31" s="87"/>
-      <c r="AH31" s="87"/>
-      <c r="AI31" s="87"/>
-      <c r="AJ31" s="87"/>
-      <c r="AK31" s="87"/>
-      <c r="AL31" s="87"/>
-      <c r="AM31" s="87"/>
-      <c r="AN31" s="87"/>
-      <c r="AO31" s="87"/>
-      <c r="AP31" s="88"/>
-      <c r="AQ31" s="92"/>
-      <c r="AR31" s="87"/>
-      <c r="AS31" s="87"/>
-      <c r="AT31" s="87"/>
-      <c r="AU31" s="87"/>
-      <c r="AV31" s="87"/>
-      <c r="AW31" s="87"/>
-      <c r="AX31" s="87"/>
-      <c r="AY31" s="87"/>
-      <c r="AZ31" s="87"/>
-      <c r="BA31" s="87"/>
-      <c r="BB31" s="87"/>
-      <c r="BC31" s="87"/>
-      <c r="BD31" s="87"/>
-      <c r="BE31" s="93"/>
+      <c r="P31" s="82"/>
+      <c r="Q31" s="82"/>
+      <c r="R31" s="82"/>
+      <c r="S31" s="82"/>
+      <c r="T31" s="82"/>
+      <c r="U31" s="82"/>
+      <c r="V31" s="82"/>
+      <c r="W31" s="82"/>
+      <c r="X31" s="82"/>
+      <c r="Y31" s="82"/>
+      <c r="Z31" s="82"/>
+      <c r="AA31" s="82"/>
+      <c r="AB31" s="82"/>
+      <c r="AC31" s="82"/>
+      <c r="AD31" s="82"/>
+      <c r="AE31" s="82"/>
+      <c r="AF31" s="82"/>
+      <c r="AG31" s="82"/>
+      <c r="AH31" s="82"/>
+      <c r="AI31" s="82"/>
+      <c r="AJ31" s="82"/>
+      <c r="AK31" s="82"/>
+      <c r="AL31" s="82"/>
+      <c r="AM31" s="82"/>
+      <c r="AN31" s="82"/>
+      <c r="AO31" s="82"/>
+      <c r="AP31" s="90"/>
+      <c r="AQ31" s="81"/>
+      <c r="AR31" s="82"/>
+      <c r="AS31" s="82"/>
+      <c r="AT31" s="82"/>
+      <c r="AU31" s="82"/>
+      <c r="AV31" s="82"/>
+      <c r="AW31" s="82"/>
+      <c r="AX31" s="82"/>
+      <c r="AY31" s="82"/>
+      <c r="AZ31" s="82"/>
+      <c r="BA31" s="82"/>
+      <c r="BB31" s="82"/>
+      <c r="BC31" s="82"/>
+      <c r="BD31" s="82"/>
+      <c r="BE31" s="83"/>
     </row>
     <row r="32" spans="1:57" ht="15" customHeight="1">
-      <c r="A32" s="81"/>
-      <c r="B32" s="82"/>
-      <c r="C32" s="82"/>
-      <c r="D32" s="82"/>
-      <c r="E32" s="82"/>
-      <c r="F32" s="82"/>
-      <c r="G32" s="83"/>
+      <c r="A32" s="101"/>
+      <c r="B32" s="102"/>
+      <c r="C32" s="102"/>
+      <c r="D32" s="102"/>
+      <c r="E32" s="102"/>
+      <c r="F32" s="102"/>
+      <c r="G32" s="103"/>
       <c r="H32" s="84"/>
       <c r="I32" s="85"/>
       <c r="J32" s="85"/>
@@ -66743,57 +66791,57 @@
       <c r="M32" s="85"/>
       <c r="N32" s="86"/>
       <c r="O32" s="84"/>
-      <c r="P32" s="87"/>
-      <c r="Q32" s="87"/>
-      <c r="R32" s="87"/>
-      <c r="S32" s="87"/>
-      <c r="T32" s="87"/>
-      <c r="U32" s="87"/>
-      <c r="V32" s="87"/>
-      <c r="W32" s="87"/>
-      <c r="X32" s="87"/>
-      <c r="Y32" s="87"/>
-      <c r="Z32" s="87"/>
-      <c r="AA32" s="87"/>
-      <c r="AB32" s="87"/>
-      <c r="AC32" s="87"/>
-      <c r="AD32" s="87"/>
-      <c r="AE32" s="87"/>
-      <c r="AF32" s="87"/>
-      <c r="AG32" s="87"/>
-      <c r="AH32" s="87"/>
-      <c r="AI32" s="87"/>
-      <c r="AJ32" s="87"/>
-      <c r="AK32" s="87"/>
-      <c r="AL32" s="87"/>
-      <c r="AM32" s="87"/>
-      <c r="AN32" s="87"/>
-      <c r="AO32" s="87"/>
-      <c r="AP32" s="88"/>
-      <c r="AQ32" s="92"/>
-      <c r="AR32" s="87"/>
-      <c r="AS32" s="87"/>
-      <c r="AT32" s="87"/>
-      <c r="AU32" s="87"/>
-      <c r="AV32" s="87"/>
-      <c r="AW32" s="87"/>
-      <c r="AX32" s="87"/>
-      <c r="AY32" s="87"/>
-      <c r="AZ32" s="87"/>
-      <c r="BA32" s="87"/>
-      <c r="BB32" s="87"/>
-      <c r="BC32" s="87"/>
-      <c r="BD32" s="87"/>
-      <c r="BE32" s="93"/>
+      <c r="P32" s="82"/>
+      <c r="Q32" s="82"/>
+      <c r="R32" s="82"/>
+      <c r="S32" s="82"/>
+      <c r="T32" s="82"/>
+      <c r="U32" s="82"/>
+      <c r="V32" s="82"/>
+      <c r="W32" s="82"/>
+      <c r="X32" s="82"/>
+      <c r="Y32" s="82"/>
+      <c r="Z32" s="82"/>
+      <c r="AA32" s="82"/>
+      <c r="AB32" s="82"/>
+      <c r="AC32" s="82"/>
+      <c r="AD32" s="82"/>
+      <c r="AE32" s="82"/>
+      <c r="AF32" s="82"/>
+      <c r="AG32" s="82"/>
+      <c r="AH32" s="82"/>
+      <c r="AI32" s="82"/>
+      <c r="AJ32" s="82"/>
+      <c r="AK32" s="82"/>
+      <c r="AL32" s="82"/>
+      <c r="AM32" s="82"/>
+      <c r="AN32" s="82"/>
+      <c r="AO32" s="82"/>
+      <c r="AP32" s="90"/>
+      <c r="AQ32" s="81"/>
+      <c r="AR32" s="82"/>
+      <c r="AS32" s="82"/>
+      <c r="AT32" s="82"/>
+      <c r="AU32" s="82"/>
+      <c r="AV32" s="82"/>
+      <c r="AW32" s="82"/>
+      <c r="AX32" s="82"/>
+      <c r="AY32" s="82"/>
+      <c r="AZ32" s="82"/>
+      <c r="BA32" s="82"/>
+      <c r="BB32" s="82"/>
+      <c r="BC32" s="82"/>
+      <c r="BD32" s="82"/>
+      <c r="BE32" s="83"/>
     </row>
     <row r="33" spans="1:57" ht="15" customHeight="1">
-      <c r="A33" s="81"/>
-      <c r="B33" s="82"/>
-      <c r="C33" s="82"/>
-      <c r="D33" s="82"/>
-      <c r="E33" s="82"/>
-      <c r="F33" s="82"/>
-      <c r="G33" s="83"/>
+      <c r="A33" s="101"/>
+      <c r="B33" s="102"/>
+      <c r="C33" s="102"/>
+      <c r="D33" s="102"/>
+      <c r="E33" s="102"/>
+      <c r="F33" s="102"/>
+      <c r="G33" s="103"/>
       <c r="H33" s="84"/>
       <c r="I33" s="85"/>
       <c r="J33" s="85"/>
@@ -66802,57 +66850,57 @@
       <c r="M33" s="85"/>
       <c r="N33" s="86"/>
       <c r="O33" s="84"/>
-      <c r="P33" s="87"/>
-      <c r="Q33" s="87"/>
-      <c r="R33" s="87"/>
-      <c r="S33" s="87"/>
-      <c r="T33" s="87"/>
-      <c r="U33" s="87"/>
-      <c r="V33" s="87"/>
-      <c r="W33" s="87"/>
-      <c r="X33" s="87"/>
-      <c r="Y33" s="87"/>
-      <c r="Z33" s="87"/>
-      <c r="AA33" s="87"/>
-      <c r="AB33" s="87"/>
-      <c r="AC33" s="87"/>
-      <c r="AD33" s="87"/>
-      <c r="AE33" s="87"/>
-      <c r="AF33" s="87"/>
-      <c r="AG33" s="87"/>
-      <c r="AH33" s="87"/>
-      <c r="AI33" s="87"/>
-      <c r="AJ33" s="87"/>
-      <c r="AK33" s="87"/>
-      <c r="AL33" s="87"/>
-      <c r="AM33" s="87"/>
-      <c r="AN33" s="87"/>
-      <c r="AO33" s="87"/>
-      <c r="AP33" s="88"/>
-      <c r="AQ33" s="92"/>
-      <c r="AR33" s="87"/>
-      <c r="AS33" s="87"/>
-      <c r="AT33" s="87"/>
-      <c r="AU33" s="87"/>
-      <c r="AV33" s="87"/>
-      <c r="AW33" s="87"/>
-      <c r="AX33" s="87"/>
-      <c r="AY33" s="87"/>
-      <c r="AZ33" s="87"/>
-      <c r="BA33" s="87"/>
-      <c r="BB33" s="87"/>
-      <c r="BC33" s="87"/>
-      <c r="BD33" s="87"/>
-      <c r="BE33" s="93"/>
+      <c r="P33" s="82"/>
+      <c r="Q33" s="82"/>
+      <c r="R33" s="82"/>
+      <c r="S33" s="82"/>
+      <c r="T33" s="82"/>
+      <c r="U33" s="82"/>
+      <c r="V33" s="82"/>
+      <c r="W33" s="82"/>
+      <c r="X33" s="82"/>
+      <c r="Y33" s="82"/>
+      <c r="Z33" s="82"/>
+      <c r="AA33" s="82"/>
+      <c r="AB33" s="82"/>
+      <c r="AC33" s="82"/>
+      <c r="AD33" s="82"/>
+      <c r="AE33" s="82"/>
+      <c r="AF33" s="82"/>
+      <c r="AG33" s="82"/>
+      <c r="AH33" s="82"/>
+      <c r="AI33" s="82"/>
+      <c r="AJ33" s="82"/>
+      <c r="AK33" s="82"/>
+      <c r="AL33" s="82"/>
+      <c r="AM33" s="82"/>
+      <c r="AN33" s="82"/>
+      <c r="AO33" s="82"/>
+      <c r="AP33" s="90"/>
+      <c r="AQ33" s="81"/>
+      <c r="AR33" s="82"/>
+      <c r="AS33" s="82"/>
+      <c r="AT33" s="82"/>
+      <c r="AU33" s="82"/>
+      <c r="AV33" s="82"/>
+      <c r="AW33" s="82"/>
+      <c r="AX33" s="82"/>
+      <c r="AY33" s="82"/>
+      <c r="AZ33" s="82"/>
+      <c r="BA33" s="82"/>
+      <c r="BB33" s="82"/>
+      <c r="BC33" s="82"/>
+      <c r="BD33" s="82"/>
+      <c r="BE33" s="83"/>
     </row>
     <row r="34" spans="1:57" ht="15" customHeight="1">
-      <c r="A34" s="81"/>
-      <c r="B34" s="82"/>
-      <c r="C34" s="82"/>
-      <c r="D34" s="82"/>
-      <c r="E34" s="82"/>
-      <c r="F34" s="82"/>
-      <c r="G34" s="83"/>
+      <c r="A34" s="101"/>
+      <c r="B34" s="102"/>
+      <c r="C34" s="102"/>
+      <c r="D34" s="102"/>
+      <c r="E34" s="102"/>
+      <c r="F34" s="102"/>
+      <c r="G34" s="103"/>
       <c r="H34" s="84"/>
       <c r="I34" s="85"/>
       <c r="J34" s="85"/>
@@ -66861,110 +66909,219 @@
       <c r="M34" s="85"/>
       <c r="N34" s="86"/>
       <c r="O34" s="84"/>
-      <c r="P34" s="87"/>
-      <c r="Q34" s="87"/>
-      <c r="R34" s="87"/>
-      <c r="S34" s="87"/>
-      <c r="T34" s="87"/>
-      <c r="U34" s="87"/>
-      <c r="V34" s="87"/>
-      <c r="W34" s="87"/>
-      <c r="X34" s="87"/>
-      <c r="Y34" s="87"/>
-      <c r="Z34" s="87"/>
-      <c r="AA34" s="87"/>
-      <c r="AB34" s="87"/>
-      <c r="AC34" s="87"/>
-      <c r="AD34" s="87"/>
-      <c r="AE34" s="87"/>
-      <c r="AF34" s="87"/>
-      <c r="AG34" s="87"/>
-      <c r="AH34" s="87"/>
-      <c r="AI34" s="87"/>
-      <c r="AJ34" s="87"/>
-      <c r="AK34" s="87"/>
-      <c r="AL34" s="87"/>
-      <c r="AM34" s="87"/>
-      <c r="AN34" s="87"/>
-      <c r="AO34" s="87"/>
-      <c r="AP34" s="88"/>
-      <c r="AQ34" s="92"/>
-      <c r="AR34" s="87"/>
-      <c r="AS34" s="87"/>
-      <c r="AT34" s="87"/>
-      <c r="AU34" s="87"/>
-      <c r="AV34" s="87"/>
-      <c r="AW34" s="87"/>
-      <c r="AX34" s="87"/>
-      <c r="AY34" s="87"/>
-      <c r="AZ34" s="87"/>
-      <c r="BA34" s="87"/>
-      <c r="BB34" s="87"/>
-      <c r="BC34" s="87"/>
-      <c r="BD34" s="87"/>
-      <c r="BE34" s="93"/>
+      <c r="P34" s="82"/>
+      <c r="Q34" s="82"/>
+      <c r="R34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="82"/>
+      <c r="V34" s="82"/>
+      <c r="W34" s="82"/>
+      <c r="X34" s="82"/>
+      <c r="Y34" s="82"/>
+      <c r="Z34" s="82"/>
+      <c r="AA34" s="82"/>
+      <c r="AB34" s="82"/>
+      <c r="AC34" s="82"/>
+      <c r="AD34" s="82"/>
+      <c r="AE34" s="82"/>
+      <c r="AF34" s="82"/>
+      <c r="AG34" s="82"/>
+      <c r="AH34" s="82"/>
+      <c r="AI34" s="82"/>
+      <c r="AJ34" s="82"/>
+      <c r="AK34" s="82"/>
+      <c r="AL34" s="82"/>
+      <c r="AM34" s="82"/>
+      <c r="AN34" s="82"/>
+      <c r="AO34" s="82"/>
+      <c r="AP34" s="90"/>
+      <c r="AQ34" s="81"/>
+      <c r="AR34" s="82"/>
+      <c r="AS34" s="82"/>
+      <c r="AT34" s="82"/>
+      <c r="AU34" s="82"/>
+      <c r="AV34" s="82"/>
+      <c r="AW34" s="82"/>
+      <c r="AX34" s="82"/>
+      <c r="AY34" s="82"/>
+      <c r="AZ34" s="82"/>
+      <c r="BA34" s="82"/>
+      <c r="BB34" s="82"/>
+      <c r="BC34" s="82"/>
+      <c r="BD34" s="82"/>
+      <c r="BE34" s="83"/>
     </row>
     <row r="35" spans="1:57" ht="15" customHeight="1" thickBot="1">
-      <c r="A35" s="98"/>
-      <c r="B35" s="99"/>
-      <c r="C35" s="99"/>
-      <c r="D35" s="99"/>
-      <c r="E35" s="99"/>
-      <c r="F35" s="99"/>
-      <c r="G35" s="100"/>
-      <c r="H35" s="94"/>
-      <c r="I35" s="95"/>
-      <c r="J35" s="95"/>
-      <c r="K35" s="95"/>
-      <c r="L35" s="95"/>
-      <c r="M35" s="95"/>
-      <c r="N35" s="96"/>
-      <c r="O35" s="94"/>
-      <c r="P35" s="90"/>
-      <c r="Q35" s="90"/>
-      <c r="R35" s="90"/>
-      <c r="S35" s="90"/>
-      <c r="T35" s="90"/>
-      <c r="U35" s="90"/>
-      <c r="V35" s="90"/>
-      <c r="W35" s="90"/>
-      <c r="X35" s="90"/>
-      <c r="Y35" s="90"/>
-      <c r="Z35" s="90"/>
-      <c r="AA35" s="90"/>
-      <c r="AB35" s="90"/>
-      <c r="AC35" s="90"/>
-      <c r="AD35" s="90"/>
-      <c r="AE35" s="90"/>
-      <c r="AF35" s="90"/>
-      <c r="AG35" s="90"/>
-      <c r="AH35" s="90"/>
-      <c r="AI35" s="90"/>
-      <c r="AJ35" s="90"/>
-      <c r="AK35" s="90"/>
-      <c r="AL35" s="90"/>
-      <c r="AM35" s="90"/>
-      <c r="AN35" s="90"/>
-      <c r="AO35" s="90"/>
-      <c r="AP35" s="97"/>
-      <c r="AQ35" s="89"/>
-      <c r="AR35" s="90"/>
-      <c r="AS35" s="90"/>
-      <c r="AT35" s="90"/>
-      <c r="AU35" s="90"/>
-      <c r="AV35" s="90"/>
-      <c r="AW35" s="90"/>
-      <c r="AX35" s="90"/>
-      <c r="AY35" s="90"/>
-      <c r="AZ35" s="90"/>
-      <c r="BA35" s="90"/>
-      <c r="BB35" s="90"/>
-      <c r="BC35" s="90"/>
-      <c r="BD35" s="90"/>
-      <c r="BE35" s="91"/>
+      <c r="A35" s="122"/>
+      <c r="B35" s="123"/>
+      <c r="C35" s="123"/>
+      <c r="D35" s="123"/>
+      <c r="E35" s="123"/>
+      <c r="F35" s="123"/>
+      <c r="G35" s="124"/>
+      <c r="H35" s="128"/>
+      <c r="I35" s="129"/>
+      <c r="J35" s="129"/>
+      <c r="K35" s="129"/>
+      <c r="L35" s="129"/>
+      <c r="M35" s="129"/>
+      <c r="N35" s="130"/>
+      <c r="O35" s="128"/>
+      <c r="P35" s="126"/>
+      <c r="Q35" s="126"/>
+      <c r="R35" s="126"/>
+      <c r="S35" s="126"/>
+      <c r="T35" s="126"/>
+      <c r="U35" s="126"/>
+      <c r="V35" s="126"/>
+      <c r="W35" s="126"/>
+      <c r="X35" s="126"/>
+      <c r="Y35" s="126"/>
+      <c r="Z35" s="126"/>
+      <c r="AA35" s="126"/>
+      <c r="AB35" s="126"/>
+      <c r="AC35" s="126"/>
+      <c r="AD35" s="126"/>
+      <c r="AE35" s="126"/>
+      <c r="AF35" s="126"/>
+      <c r="AG35" s="126"/>
+      <c r="AH35" s="126"/>
+      <c r="AI35" s="126"/>
+      <c r="AJ35" s="126"/>
+      <c r="AK35" s="126"/>
+      <c r="AL35" s="126"/>
+      <c r="AM35" s="126"/>
+      <c r="AN35" s="126"/>
+      <c r="AO35" s="126"/>
+      <c r="AP35" s="131"/>
+      <c r="AQ35" s="125"/>
+      <c r="AR35" s="126"/>
+      <c r="AS35" s="126"/>
+      <c r="AT35" s="126"/>
+      <c r="AU35" s="126"/>
+      <c r="AV35" s="126"/>
+      <c r="AW35" s="126"/>
+      <c r="AX35" s="126"/>
+      <c r="AY35" s="126"/>
+      <c r="AZ35" s="126"/>
+      <c r="BA35" s="126"/>
+      <c r="BB35" s="126"/>
+      <c r="BC35" s="126"/>
+      <c r="BD35" s="126"/>
+      <c r="BE35" s="127"/>
     </row>
   </sheetData>
   <mergeCells count="133">
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="O19:AP19"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AQ35:BE35"/>
+    <mergeCell ref="AQ33:BE33"/>
+    <mergeCell ref="AQ34:BE34"/>
+    <mergeCell ref="AQ32:BE32"/>
+    <mergeCell ref="AQ31:BE31"/>
+    <mergeCell ref="O27:AP27"/>
+    <mergeCell ref="AQ27:BE27"/>
+    <mergeCell ref="H30:N30"/>
+    <mergeCell ref="O30:AP30"/>
+    <mergeCell ref="AQ30:BE30"/>
+    <mergeCell ref="AQ28:BE28"/>
+    <mergeCell ref="H28:N28"/>
+    <mergeCell ref="O28:AP28"/>
+    <mergeCell ref="H35:N35"/>
+    <mergeCell ref="O35:AP35"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="H33:N33"/>
+    <mergeCell ref="H34:N34"/>
+    <mergeCell ref="O34:AP34"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="O33:AP33"/>
+    <mergeCell ref="O32:AP32"/>
+    <mergeCell ref="H31:N31"/>
+    <mergeCell ref="O31:AP31"/>
+    <mergeCell ref="H27:N27"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="H32:N32"/>
+    <mergeCell ref="H29:N29"/>
+    <mergeCell ref="O29:AP29"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:AP20"/>
+    <mergeCell ref="AQ17:BE17"/>
+    <mergeCell ref="H26:N26"/>
+    <mergeCell ref="O26:AP26"/>
+    <mergeCell ref="AQ26:BE26"/>
+    <mergeCell ref="AQ19:BE19"/>
+    <mergeCell ref="H25:N25"/>
+    <mergeCell ref="H24:N24"/>
+    <mergeCell ref="O24:AP24"/>
+    <mergeCell ref="O25:AP25"/>
+    <mergeCell ref="AQ25:BE25"/>
+    <mergeCell ref="H22:N22"/>
+    <mergeCell ref="AQ24:BE24"/>
+    <mergeCell ref="H23:N23"/>
+    <mergeCell ref="O23:AP23"/>
+    <mergeCell ref="AQ23:BE23"/>
+    <mergeCell ref="AQ20:BE20"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:AP21"/>
+    <mergeCell ref="AQ18:BE18"/>
+    <mergeCell ref="AQ21:BE21"/>
+    <mergeCell ref="O22:AP22"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="H4:N4"/>
+    <mergeCell ref="O4:AP4"/>
+    <mergeCell ref="AQ4:BE4"/>
+    <mergeCell ref="H13:N13"/>
+    <mergeCell ref="O13:AP13"/>
+    <mergeCell ref="AQ13:BE13"/>
+    <mergeCell ref="H14:N14"/>
+    <mergeCell ref="O14:AP14"/>
+    <mergeCell ref="AQ14:BE14"/>
+    <mergeCell ref="AQ16:BE16"/>
+    <mergeCell ref="H15:N15"/>
+    <mergeCell ref="O18:AP18"/>
+    <mergeCell ref="H9:N9"/>
+    <mergeCell ref="O9:AP9"/>
+    <mergeCell ref="AQ9:BE9"/>
+    <mergeCell ref="H10:N10"/>
+    <mergeCell ref="O10:AP10"/>
+    <mergeCell ref="AQ10:BE10"/>
+    <mergeCell ref="H11:N11"/>
+    <mergeCell ref="O11:AP11"/>
+    <mergeCell ref="AQ11:BE11"/>
+    <mergeCell ref="H16:N16"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="O15:AP15"/>
+    <mergeCell ref="A1:BE1"/>
+    <mergeCell ref="H3:N3"/>
+    <mergeCell ref="O3:AP3"/>
+    <mergeCell ref="AQ3:BE3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
     <mergeCell ref="AQ22:BE22"/>
     <mergeCell ref="AQ29:BE29"/>
     <mergeCell ref="H17:N17"/>
@@ -66989,115 +67146,6 @@
     <mergeCell ref="A9:G9"/>
     <mergeCell ref="O16:AP16"/>
     <mergeCell ref="O17:AP17"/>
-    <mergeCell ref="A1:BE1"/>
-    <mergeCell ref="H3:N3"/>
-    <mergeCell ref="O3:AP3"/>
-    <mergeCell ref="AQ3:BE3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="O15:AP15"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="H4:N4"/>
-    <mergeCell ref="O4:AP4"/>
-    <mergeCell ref="AQ4:BE4"/>
-    <mergeCell ref="H13:N13"/>
-    <mergeCell ref="O13:AP13"/>
-    <mergeCell ref="AQ13:BE13"/>
-    <mergeCell ref="H14:N14"/>
-    <mergeCell ref="O14:AP14"/>
-    <mergeCell ref="AQ14:BE14"/>
-    <mergeCell ref="AQ16:BE16"/>
-    <mergeCell ref="H15:N15"/>
-    <mergeCell ref="O18:AP18"/>
-    <mergeCell ref="H9:N9"/>
-    <mergeCell ref="O9:AP9"/>
-    <mergeCell ref="AQ9:BE9"/>
-    <mergeCell ref="H10:N10"/>
-    <mergeCell ref="O10:AP10"/>
-    <mergeCell ref="AQ10:BE10"/>
-    <mergeCell ref="H11:N11"/>
-    <mergeCell ref="O11:AP11"/>
-    <mergeCell ref="AQ11:BE11"/>
-    <mergeCell ref="H16:N16"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:AP20"/>
-    <mergeCell ref="AQ17:BE17"/>
-    <mergeCell ref="H26:N26"/>
-    <mergeCell ref="O26:AP26"/>
-    <mergeCell ref="AQ26:BE26"/>
-    <mergeCell ref="AQ19:BE19"/>
-    <mergeCell ref="H25:N25"/>
-    <mergeCell ref="H24:N24"/>
-    <mergeCell ref="O24:AP24"/>
-    <mergeCell ref="O25:AP25"/>
-    <mergeCell ref="AQ25:BE25"/>
-    <mergeCell ref="H22:N22"/>
-    <mergeCell ref="AQ24:BE24"/>
-    <mergeCell ref="H23:N23"/>
-    <mergeCell ref="O23:AP23"/>
-    <mergeCell ref="AQ23:BE23"/>
-    <mergeCell ref="AQ20:BE20"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:AP21"/>
-    <mergeCell ref="AQ18:BE18"/>
-    <mergeCell ref="AQ21:BE21"/>
-    <mergeCell ref="O22:AP22"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="H33:N33"/>
-    <mergeCell ref="H34:N34"/>
-    <mergeCell ref="O34:AP34"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="O33:AP33"/>
-    <mergeCell ref="O32:AP32"/>
-    <mergeCell ref="H31:N31"/>
-    <mergeCell ref="O31:AP31"/>
-    <mergeCell ref="H27:N27"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="H32:N32"/>
-    <mergeCell ref="H29:N29"/>
-    <mergeCell ref="O29:AP29"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="O19:AP19"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="AQ35:BE35"/>
-    <mergeCell ref="AQ33:BE33"/>
-    <mergeCell ref="AQ34:BE34"/>
-    <mergeCell ref="AQ32:BE32"/>
-    <mergeCell ref="AQ31:BE31"/>
-    <mergeCell ref="O27:AP27"/>
-    <mergeCell ref="AQ27:BE27"/>
-    <mergeCell ref="H30:N30"/>
-    <mergeCell ref="O30:AP30"/>
-    <mergeCell ref="AQ30:BE30"/>
-    <mergeCell ref="AQ28:BE28"/>
-    <mergeCell ref="H28:N28"/>
-    <mergeCell ref="O28:AP28"/>
-    <mergeCell ref="H35:N35"/>
-    <mergeCell ref="O35:AP35"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A20:G20"/>
   </mergeCells>
   <phoneticPr fontId="5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>

--- a/development/MS/spec/MSBB/Panel/MSBBP1210_SloReg.xlsx
+++ b/development/MS/spec/MSBB/Panel/MSBBP1210_SloReg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\mcframeDEV\development\MS\spec\MSBB\Panel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A93CCB-963C-4C1E-ADCD-BC34BDC59AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{980672A7-32EC-46C4-AF6A-A347D00F1CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-3330" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9174" uniqueCount="2374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9175" uniqueCount="2375">
   <si>
     <t>検索</t>
     <rPh sb="0" eb="2">
@@ -10055,10 +10055,13 @@
     <t>free_rsn_typ_nm</t>
   </si>
   <si>
-    <t>bp_nm</t>
-  </si>
-  <si>
     <t>MS.MSUAP0030.SloBp</t>
+  </si>
+  <si>
+    <t>cst_nm;sls_usr_cd</t>
+  </si>
+  <si>
+    <t>bp_nm;sls_usr_cd</t>
   </si>
 </sst>
 </file>
@@ -13910,7 +13913,7 @@
       </c>
       <c r="L21" s="25"/>
       <c r="M21" s="25" t="s">
-        <v>85</v>
+        <v>2308</v>
       </c>
       <c r="N21" s="25"/>
       <c r="O21" s="25"/>
@@ -19303,20 +19306,22 @@
         <v>49</v>
       </c>
       <c r="L93" s="65"/>
-      <c r="M93" s="65"/>
+      <c r="M93" s="65" t="s">
+        <v>2308</v>
+      </c>
       <c r="N93" s="65"/>
       <c r="O93" s="65"/>
       <c r="P93" s="65"/>
       <c r="Q93" s="61" t="s">
-        <v>2373</v>
+        <v>2372</v>
       </c>
       <c r="R93" s="61"/>
       <c r="S93" s="61" t="s">
-        <v>152</v>
+        <v>2373</v>
       </c>
       <c r="T93" s="61"/>
       <c r="U93" s="61" t="s">
-        <v>2372</v>
+        <v>2374</v>
       </c>
       <c r="V93" s="65" t="s">
         <v>2364</v>
@@ -20119,86 +20124,86 @@
       <c r="AY101" s="50"/>
       <c r="AZ101" s="50"/>
     </row>
-    <row r="102" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A102" s="50">
+    <row r="102" spans="1:52" s="66" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A102" s="63">
         <v>40</v>
       </c>
-      <c r="B102" s="25"/>
-      <c r="C102" s="25"/>
-      <c r="D102" s="25" t="s">
+      <c r="B102" s="65"/>
+      <c r="C102" s="65"/>
+      <c r="D102" s="65" t="s">
         <v>1170</v>
       </c>
-      <c r="E102" s="37" t="s">
+      <c r="E102" s="64" t="s">
         <v>1903</v>
       </c>
-      <c r="F102" s="25" t="s">
+      <c r="F102" s="65" t="s">
         <v>178</v>
       </c>
-      <c r="G102" s="25" t="s">
+      <c r="G102" s="65" t="s">
         <v>209</v>
       </c>
-      <c r="H102" s="25"/>
-      <c r="I102" s="25" t="s">
+      <c r="H102" s="65"/>
+      <c r="I102" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="J102" s="25"/>
-      <c r="K102" s="25" t="s">
+      <c r="J102" s="65"/>
+      <c r="K102" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="L102" s="25"/>
-      <c r="M102" s="25"/>
-      <c r="N102" s="25"/>
-      <c r="O102" s="25"/>
-      <c r="P102" s="25"/>
-      <c r="Q102" s="25"/>
-      <c r="R102" s="25"/>
-      <c r="S102" s="25"/>
-      <c r="T102" s="25"/>
-      <c r="U102" s="25"/>
-      <c r="V102" s="25"/>
-      <c r="W102" s="25"/>
-      <c r="X102" s="25"/>
-      <c r="Z102" s="25"/>
-      <c r="AA102" s="25"/>
-      <c r="AB102" s="25" t="s">
+      <c r="L102" s="65"/>
+      <c r="M102" s="65"/>
+      <c r="N102" s="65"/>
+      <c r="O102" s="65"/>
+      <c r="P102" s="65"/>
+      <c r="Q102" s="65"/>
+      <c r="R102" s="65"/>
+      <c r="S102" s="65"/>
+      <c r="T102" s="65"/>
+      <c r="U102" s="65"/>
+      <c r="V102" s="65"/>
+      <c r="W102" s="65"/>
+      <c r="X102" s="65"/>
+      <c r="Z102" s="65"/>
+      <c r="AA102" s="65"/>
+      <c r="AB102" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="AC102" s="25" t="s">
+      <c r="AC102" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="AD102" s="25"/>
-      <c r="AE102" s="25"/>
-      <c r="AF102" s="25"/>
-      <c r="AG102" s="25" t="s">
+      <c r="AD102" s="65"/>
+      <c r="AE102" s="65"/>
+      <c r="AF102" s="65"/>
+      <c r="AG102" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="AH102" s="25" t="s">
+      <c r="AH102" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="AI102" s="25"/>
-      <c r="AJ102" s="25"/>
-      <c r="AK102" s="25"/>
-      <c r="AM102" s="25"/>
-      <c r="AN102" s="25" t="s">
+      <c r="AI102" s="65"/>
+      <c r="AJ102" s="65"/>
+      <c r="AK102" s="65"/>
+      <c r="AM102" s="65"/>
+      <c r="AN102" s="65" t="s">
         <v>332</v>
       </c>
-      <c r="AO102" s="25"/>
-      <c r="AP102" s="25" t="s">
+      <c r="AO102" s="65"/>
+      <c r="AP102" s="65" t="s">
         <v>332</v>
       </c>
-      <c r="AQ102" s="25" t="s">
+      <c r="AQ102" s="65" t="s">
         <v>332</v>
       </c>
-      <c r="AR102" s="25"/>
-      <c r="AS102" s="25" t="s">
+      <c r="AR102" s="65"/>
+      <c r="AS102" s="65" t="s">
         <v>332</v>
       </c>
-      <c r="AT102" s="25"/>
-      <c r="AU102" s="25"/>
-      <c r="AV102" s="25"/>
-      <c r="AW102" s="25"/>
-      <c r="AX102" s="25"/>
-      <c r="AZ102" s="26"/>
+      <c r="AT102" s="65"/>
+      <c r="AU102" s="65"/>
+      <c r="AV102" s="65"/>
+      <c r="AW102" s="65"/>
+      <c r="AX102" s="65"/>
+      <c r="AZ102" s="68"/>
     </row>
     <row r="103" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A103" s="50">

--- a/development/MS/spec/MSBB/Panel/MSBBP1210_SloReg.xlsx
+++ b/development/MS/spec/MSBB/Panel/MSBBP1210_SloReg.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\mcframeDEV\development\MS\spec\MSBB\Panel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03CCA0DE-6BD8-4F35-98C7-7120DF01119A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DFE13DD-CDA5-48B9-830E-7641FA3330A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-3330" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MSBBP1210" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9175" uniqueCount="2379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9193" uniqueCount="2382">
   <si>
     <t>検索</t>
     <rPh sb="0" eb="2">
@@ -10067,6 +10067,15 @@
   </si>
   <si>
     <t>MS.MSUAP0030.SloDlv</t>
+  </si>
+  <si>
+    <t>Partial Shipment</t>
+  </si>
+  <si>
+    <t>分納</t>
+  </si>
+  <si>
+    <t>par_ship</t>
   </si>
 </sst>
 </file>
@@ -11691,14 +11700,7 @@
     <cellStyle name="Total" xfId="37" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="32" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="27">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="26">
     <dxf>
       <fill>
         <patternFill>
@@ -12189,7 +12191,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AZ654"/>
+  <dimension ref="A1:AZ655"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4.875" style="12" customWidth="1"/>
@@ -39710,7 +39712,7 @@
       <c r="B329" s="50"/>
       <c r="C329" s="50"/>
       <c r="D329" s="50" t="s">
-        <v>809</v>
+        <v>1030</v>
       </c>
       <c r="E329" s="50"/>
       <c r="F329" s="50"/>
@@ -39724,7 +39726,7 @@
         <v>248</v>
       </c>
       <c r="L329" s="50" t="s">
-        <v>1149</v>
+        <v>776</v>
       </c>
       <c r="M329" s="50"/>
       <c r="N329" s="50"/>
@@ -39746,23 +39748,23 @@
         <v>80</v>
       </c>
       <c r="AB329" s="50" t="s">
-        <v>30</v>
+        <v>282</v>
       </c>
       <c r="AC329" s="50" t="s">
-        <v>30</v>
+        <v>282</v>
       </c>
       <c r="AD329" s="50" t="s">
-        <v>80</v>
+        <v>282</v>
       </c>
       <c r="AE329" s="50"/>
       <c r="AF329" s="50" t="s">
         <v>80</v>
       </c>
       <c r="AG329" s="50" t="s">
-        <v>30</v>
+        <v>282</v>
       </c>
       <c r="AH329" s="50" t="s">
-        <v>30</v>
+        <v>282</v>
       </c>
       <c r="AI329" s="50" t="s">
         <v>80</v>
@@ -39796,11 +39798,17 @@
       <c r="B330" s="25"/>
       <c r="C330" s="25"/>
       <c r="D330" s="25" t="s">
-        <v>946</v>
-      </c>
-      <c r="E330" s="37"/>
-      <c r="F330" s="25"/>
-      <c r="G330" s="25"/>
+        <v>1031</v>
+      </c>
+      <c r="E330" s="37" t="s">
+        <v>2016</v>
+      </c>
+      <c r="F330" s="25" t="s">
+        <v>1032</v>
+      </c>
+      <c r="G330" s="25" t="s">
+        <v>997</v>
+      </c>
       <c r="H330" s="25"/>
       <c r="I330" s="25" t="s">
         <v>23</v>
@@ -39822,54 +39830,30 @@
       <c r="V330" s="25"/>
       <c r="W330" s="25"/>
       <c r="X330" s="25"/>
-      <c r="Z330" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA330" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB330" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="AC330" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="AD330" s="25" t="s">
-        <v>25</v>
-      </c>
+      <c r="Z330" s="25"/>
+      <c r="AA330" s="25"/>
+      <c r="AB330" s="25"/>
+      <c r="AC330" s="25"/>
+      <c r="AD330" s="25"/>
       <c r="AE330" s="25"/>
-      <c r="AF330" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG330" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="AH330" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="AI330" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ330" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AK330" s="25" t="s">
-        <v>25</v>
-      </c>
+      <c r="AF330" s="25"/>
+      <c r="AG330" s="25"/>
+      <c r="AH330" s="25"/>
+      <c r="AI330" s="25"/>
+      <c r="AJ330" s="25"/>
+      <c r="AK330" s="25"/>
       <c r="AM330" s="25"/>
       <c r="AN330" s="25" t="s">
-        <v>679</v>
+        <v>1033</v>
       </c>
       <c r="AO330" s="25"/>
-      <c r="AP330" s="25" t="s">
-        <v>679</v>
-      </c>
+      <c r="AP330" s="25"/>
       <c r="AQ330" s="25" t="s">
-        <v>679</v>
+        <v>1034</v>
       </c>
       <c r="AR330" s="25"/>
       <c r="AS330" s="25" t="s">
-        <v>679</v>
+        <v>1034</v>
       </c>
       <c r="AT330" s="25"/>
       <c r="AU330" s="25"/>
@@ -39885,11 +39869,17 @@
       <c r="B331" s="25"/>
       <c r="C331" s="25"/>
       <c r="D331" s="25" t="s">
-        <v>966</v>
-      </c>
-      <c r="E331" s="37"/>
-      <c r="F331" s="25"/>
-      <c r="G331" s="25"/>
+        <v>1035</v>
+      </c>
+      <c r="E331" s="37" t="s">
+        <v>2017</v>
+      </c>
+      <c r="F331" s="25" t="s">
+        <v>1036</v>
+      </c>
+      <c r="G331" s="25" t="s">
+        <v>997</v>
+      </c>
       <c r="H331" s="25"/>
       <c r="I331" s="25" t="s">
         <v>23</v>
@@ -39925,19 +39915,13 @@
       <c r="AK331" s="25"/>
       <c r="AM331" s="25"/>
       <c r="AN331" s="25" t="s">
-        <v>854</v>
+        <v>1037</v>
       </c>
       <c r="AO331" s="25"/>
-      <c r="AP331" s="25" t="s">
-        <v>854</v>
-      </c>
-      <c r="AQ331" s="25" t="s">
-        <v>854</v>
-      </c>
+      <c r="AP331" s="25"/>
+      <c r="AQ331" s="25"/>
       <c r="AR331" s="25"/>
-      <c r="AS331" s="25" t="s">
-        <v>854</v>
-      </c>
+      <c r="AS331" s="25"/>
       <c r="AT331" s="25"/>
       <c r="AU331" s="25"/>
       <c r="AV331" s="25"/>
@@ -39946,27 +39930,33 @@
       <c r="AZ331" s="26"/>
     </row>
     <row r="332" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A332" s="50">
+      <c r="A332" s="25">
         <v>70</v>
       </c>
       <c r="B332" s="25"/>
       <c r="C332" s="25"/>
       <c r="D332" s="25" t="s">
-        <v>967</v>
-      </c>
-      <c r="E332" s="37"/>
-      <c r="F332" s="25"/>
+        <v>657</v>
+      </c>
+      <c r="E332" s="37" t="s">
+        <v>2018</v>
+      </c>
+      <c r="F332" s="25" t="s">
+        <v>380</v>
+      </c>
       <c r="G332" s="25"/>
       <c r="H332" s="25"/>
       <c r="I332" s="25" t="s">
-        <v>23</v>
+        <v>1371</v>
       </c>
       <c r="J332" s="25"/>
       <c r="K332" s="25" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L332" s="25"/>
-      <c r="M332" s="25"/>
+      <c r="M332" s="25" t="s">
+        <v>682</v>
+      </c>
       <c r="N332" s="25"/>
       <c r="O332" s="25"/>
       <c r="P332" s="25"/>
@@ -39978,29 +39968,53 @@
       <c r="V332" s="25"/>
       <c r="W332" s="25"/>
       <c r="X332" s="25"/>
-      <c r="Z332" s="25"/>
-      <c r="AA332" s="25"/>
-      <c r="AB332" s="25"/>
-      <c r="AC332" s="25"/>
-      <c r="AD332" s="25"/>
+      <c r="Z332" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA332" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB332" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC332" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD332" s="25" t="s">
+        <v>70</v>
+      </c>
       <c r="AE332" s="25"/>
-      <c r="AF332" s="25"/>
-      <c r="AG332" s="25"/>
-      <c r="AH332" s="25"/>
-      <c r="AI332" s="25"/>
-      <c r="AJ332" s="25"/>
-      <c r="AK332" s="25"/>
+      <c r="AF332" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG332" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="AH332" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="AI332" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ332" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK332" s="25" t="s">
+        <v>70</v>
+      </c>
       <c r="AM332" s="25"/>
       <c r="AN332" s="25" t="s">
-        <v>968</v>
+        <v>381</v>
       </c>
       <c r="AO332" s="25"/>
-      <c r="AP332" s="25" t="s">
-        <v>968</v>
-      </c>
-      <c r="AQ332" s="25"/>
+      <c r="AP332" s="25"/>
+      <c r="AQ332" s="25" t="s">
+        <v>381</v>
+      </c>
       <c r="AR332" s="25"/>
-      <c r="AS332" s="25"/>
+      <c r="AS332" s="25" t="s">
+        <v>381</v>
+      </c>
       <c r="AT332" s="25"/>
       <c r="AU332" s="25"/>
       <c r="AV332" s="25"/>
@@ -40009,65 +40023,93 @@
       <c r="AZ332" s="26"/>
     </row>
     <row r="333" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A333" s="50">
+      <c r="A333" s="25">
         <v>70</v>
       </c>
       <c r="B333" s="25"/>
       <c r="C333" s="25"/>
       <c r="D333" s="25" t="s">
-        <v>969</v>
-      </c>
-      <c r="E333" s="37"/>
-      <c r="F333" s="25"/>
-      <c r="G333" s="25"/>
+        <v>1530</v>
+      </c>
+      <c r="E333" s="37" t="s">
+        <v>2019</v>
+      </c>
+      <c r="F333" s="25" t="s">
+        <v>375</v>
+      </c>
+      <c r="G333" s="25" t="s">
+        <v>375</v>
+      </c>
       <c r="H333" s="25"/>
       <c r="I333" s="25" t="s">
-        <v>23</v>
+        <v>631</v>
       </c>
       <c r="J333" s="25"/>
       <c r="K333" s="25" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="L333" s="25"/>
       <c r="M333" s="25"/>
       <c r="N333" s="25"/>
       <c r="O333" s="25"/>
       <c r="P333" s="25"/>
-      <c r="Q333" s="25"/>
+      <c r="Q333" s="25" t="s">
+        <v>601</v>
+      </c>
       <c r="R333" s="25"/>
-      <c r="S333" s="25"/>
+      <c r="S333" s="25" t="s">
+        <v>381</v>
+      </c>
       <c r="T333" s="25"/>
-      <c r="U333" s="25"/>
+      <c r="U333" s="25" t="s">
+        <v>623</v>
+      </c>
       <c r="V333" s="25"/>
       <c r="W333" s="25"/>
       <c r="X333" s="25"/>
-      <c r="Z333" s="25"/>
-      <c r="AA333" s="25"/>
-      <c r="AB333" s="25"/>
-      <c r="AC333" s="25"/>
-      <c r="AD333" s="25"/>
+      <c r="Z333" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA333" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB333" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC333" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD333" s="25" t="s">
+        <v>19</v>
+      </c>
       <c r="AE333" s="25"/>
-      <c r="AF333" s="25"/>
-      <c r="AG333" s="25"/>
-      <c r="AH333" s="25"/>
-      <c r="AI333" s="25"/>
-      <c r="AJ333" s="25"/>
-      <c r="AK333" s="25"/>
+      <c r="AF333" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG333" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AH333" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI333" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ333" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK333" s="25" t="s">
+        <v>25</v>
+      </c>
       <c r="AM333" s="25"/>
       <c r="AN333" s="25" t="s">
-        <v>970</v>
+        <v>1530</v>
       </c>
       <c r="AO333" s="25"/>
-      <c r="AP333" s="25" t="s">
-        <v>970</v>
-      </c>
-      <c r="AQ333" s="25" t="s">
-        <v>970</v>
-      </c>
+      <c r="AP333" s="25"/>
+      <c r="AQ333" s="25"/>
       <c r="AR333" s="25"/>
-      <c r="AS333" s="25" t="s">
-        <v>970</v>
-      </c>
+      <c r="AS333" s="25"/>
       <c r="AT333" s="25"/>
       <c r="AU333" s="25"/>
       <c r="AV333" s="25"/>
@@ -40079,72 +40121,87 @@
       <c r="A334" s="50">
         <v>70</v>
       </c>
-      <c r="B334" s="25"/>
-      <c r="C334" s="25"/>
-      <c r="D334" s="25" t="s">
-        <v>971</v>
-      </c>
-      <c r="E334" s="37"/>
-      <c r="F334" s="25"/>
-      <c r="G334" s="25"/>
-      <c r="H334" s="25"/>
-      <c r="I334" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="J334" s="25"/>
-      <c r="K334" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="L334" s="25"/>
-      <c r="M334" s="25"/>
-      <c r="N334" s="25"/>
-      <c r="O334" s="25"/>
-      <c r="P334" s="25"/>
-      <c r="Q334" s="25" t="s">
-        <v>608</v>
-      </c>
-      <c r="R334" s="25"/>
-      <c r="S334" s="25" t="s">
-        <v>810</v>
-      </c>
-      <c r="T334" s="25"/>
-      <c r="U334" s="25"/>
-      <c r="V334" s="25"/>
-      <c r="W334" s="25"/>
-      <c r="X334" s="25"/>
-      <c r="Z334" s="25"/>
-      <c r="AA334" s="25"/>
-      <c r="AB334" s="25"/>
-      <c r="AC334" s="25"/>
-      <c r="AD334" s="25"/>
-      <c r="AE334" s="25"/>
-      <c r="AF334" s="25"/>
-      <c r="AG334" s="25"/>
-      <c r="AH334" s="25"/>
-      <c r="AI334" s="25"/>
-      <c r="AJ334" s="25"/>
-      <c r="AK334" s="25"/>
-      <c r="AM334" s="25"/>
-      <c r="AN334" s="25" t="s">
-        <v>972</v>
-      </c>
-      <c r="AO334" s="25"/>
-      <c r="AP334" s="25" t="s">
-        <v>972</v>
-      </c>
-      <c r="AQ334" s="25" t="s">
-        <v>972</v>
-      </c>
-      <c r="AR334" s="25"/>
-      <c r="AS334" s="25" t="s">
-        <v>972</v>
-      </c>
-      <c r="AT334" s="25"/>
-      <c r="AU334" s="25"/>
-      <c r="AV334" s="25"/>
-      <c r="AW334" s="25"/>
-      <c r="AX334" s="25"/>
-      <c r="AZ334" s="26"/>
+      <c r="B334" s="50"/>
+      <c r="C334" s="50"/>
+      <c r="D334" s="50" t="s">
+        <v>809</v>
+      </c>
+      <c r="E334" s="50"/>
+      <c r="F334" s="50"/>
+      <c r="G334" s="50"/>
+      <c r="H334" s="50"/>
+      <c r="I334" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="J334" s="50"/>
+      <c r="K334" s="50" t="s">
+        <v>248</v>
+      </c>
+      <c r="L334" s="50" t="s">
+        <v>1149</v>
+      </c>
+      <c r="M334" s="50"/>
+      <c r="N334" s="50"/>
+      <c r="O334" s="50"/>
+      <c r="P334" s="50"/>
+      <c r="Q334" s="50"/>
+      <c r="R334" s="50"/>
+      <c r="S334" s="50"/>
+      <c r="T334" s="50"/>
+      <c r="U334" s="50"/>
+      <c r="V334" s="50"/>
+      <c r="W334" s="50"/>
+      <c r="X334" s="50"/>
+      <c r="Y334" s="50"/>
+      <c r="Z334" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA334" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB334" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC334" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD334" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE334" s="50"/>
+      <c r="AF334" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG334" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="AH334" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="AI334" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ334" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK334" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL334" s="50"/>
+      <c r="AM334" s="50"/>
+      <c r="AN334" s="50"/>
+      <c r="AO334" s="50"/>
+      <c r="AP334" s="50"/>
+      <c r="AQ334" s="50"/>
+      <c r="AR334" s="50"/>
+      <c r="AS334" s="50"/>
+      <c r="AT334" s="50"/>
+      <c r="AU334" s="50"/>
+      <c r="AV334" s="50"/>
+      <c r="AW334" s="50"/>
+      <c r="AX334" s="50"/>
+      <c r="AY334" s="50"/>
+      <c r="AZ334" s="50"/>
     </row>
     <row r="335" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A335" s="50">
@@ -40153,7 +40210,7 @@
       <c r="B335" s="25"/>
       <c r="C335" s="25"/>
       <c r="D335" s="25" t="s">
-        <v>973</v>
+        <v>946</v>
       </c>
       <c r="E335" s="37"/>
       <c r="F335" s="25"/>
@@ -40179,29 +40236,55 @@
       <c r="V335" s="25"/>
       <c r="W335" s="25"/>
       <c r="X335" s="25"/>
-      <c r="Z335" s="25"/>
-      <c r="AA335" s="25"/>
-      <c r="AB335" s="25"/>
-      <c r="AC335" s="25"/>
-      <c r="AD335" s="25"/>
+      <c r="Z335" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA335" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB335" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC335" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD335" s="25" t="s">
+        <v>25</v>
+      </c>
       <c r="AE335" s="25"/>
-      <c r="AF335" s="25"/>
-      <c r="AG335" s="25"/>
-      <c r="AH335" s="25"/>
-      <c r="AI335" s="25"/>
-      <c r="AJ335" s="25"/>
-      <c r="AK335" s="25"/>
+      <c r="AF335" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG335" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH335" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI335" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ335" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK335" s="25" t="s">
+        <v>25</v>
+      </c>
       <c r="AM335" s="25"/>
       <c r="AN335" s="25" t="s">
-        <v>974</v>
+        <v>679</v>
       </c>
       <c r="AO335" s="25"/>
       <c r="AP335" s="25" t="s">
-        <v>974</v>
-      </c>
-      <c r="AQ335" s="25"/>
+        <v>679</v>
+      </c>
+      <c r="AQ335" s="25" t="s">
+        <v>679</v>
+      </c>
       <c r="AR335" s="25"/>
-      <c r="AS335" s="25"/>
+      <c r="AS335" s="25" t="s">
+        <v>679</v>
+      </c>
       <c r="AT335" s="25"/>
       <c r="AU335" s="25"/>
       <c r="AV335" s="25"/>
@@ -40216,7 +40299,7 @@
       <c r="B336" s="25"/>
       <c r="C336" s="25"/>
       <c r="D336" s="25" t="s">
-        <v>975</v>
+        <v>966</v>
       </c>
       <c r="E336" s="37"/>
       <c r="F336" s="25"/>
@@ -40256,15 +40339,19 @@
       <c r="AK336" s="25"/>
       <c r="AM336" s="25"/>
       <c r="AN336" s="25" t="s">
-        <v>976</v>
+        <v>854</v>
       </c>
       <c r="AO336" s="25"/>
       <c r="AP336" s="25" t="s">
-        <v>976</v>
-      </c>
-      <c r="AQ336" s="25"/>
+        <v>854</v>
+      </c>
+      <c r="AQ336" s="25" t="s">
+        <v>854</v>
+      </c>
       <c r="AR336" s="25"/>
-      <c r="AS336" s="25"/>
+      <c r="AS336" s="25" t="s">
+        <v>854</v>
+      </c>
       <c r="AT336" s="25"/>
       <c r="AU336" s="25"/>
       <c r="AV336" s="25"/>
@@ -40279,7 +40366,7 @@
       <c r="B337" s="25"/>
       <c r="C337" s="25"/>
       <c r="D337" s="25" t="s">
-        <v>977</v>
+        <v>967</v>
       </c>
       <c r="E337" s="37"/>
       <c r="F337" s="25"/>
@@ -40318,9 +40405,13 @@
       <c r="AJ337" s="25"/>
       <c r="AK337" s="25"/>
       <c r="AM337" s="25"/>
-      <c r="AN337" s="25"/>
+      <c r="AN337" s="25" t="s">
+        <v>968</v>
+      </c>
       <c r="AO337" s="25"/>
-      <c r="AP337" s="25"/>
+      <c r="AP337" s="25" t="s">
+        <v>968</v>
+      </c>
       <c r="AQ337" s="25"/>
       <c r="AR337" s="25"/>
       <c r="AS337" s="25"/>
@@ -40338,7 +40429,7 @@
       <c r="B338" s="25"/>
       <c r="C338" s="25"/>
       <c r="D338" s="25" t="s">
-        <v>978</v>
+        <v>969</v>
       </c>
       <c r="E338" s="37"/>
       <c r="F338" s="25"/>
@@ -40378,15 +40469,19 @@
       <c r="AK338" s="25"/>
       <c r="AM338" s="25"/>
       <c r="AN338" s="25" t="s">
-        <v>979</v>
+        <v>970</v>
       </c>
       <c r="AO338" s="25"/>
       <c r="AP338" s="25" t="s">
-        <v>979</v>
-      </c>
-      <c r="AQ338" s="25"/>
+        <v>970</v>
+      </c>
+      <c r="AQ338" s="25" t="s">
+        <v>970</v>
+      </c>
       <c r="AR338" s="25"/>
-      <c r="AS338" s="25"/>
+      <c r="AS338" s="25" t="s">
+        <v>970</v>
+      </c>
       <c r="AT338" s="25"/>
       <c r="AU338" s="25"/>
       <c r="AV338" s="25"/>
@@ -40401,7 +40496,7 @@
       <c r="B339" s="25"/>
       <c r="C339" s="25"/>
       <c r="D339" s="25" t="s">
-        <v>980</v>
+        <v>971</v>
       </c>
       <c r="E339" s="37"/>
       <c r="F339" s="25"/>
@@ -40419,9 +40514,13 @@
       <c r="N339" s="25"/>
       <c r="O339" s="25"/>
       <c r="P339" s="25"/>
-      <c r="Q339" s="25"/>
+      <c r="Q339" s="25" t="s">
+        <v>608</v>
+      </c>
       <c r="R339" s="25"/>
-      <c r="S339" s="25"/>
+      <c r="S339" s="25" t="s">
+        <v>810</v>
+      </c>
       <c r="T339" s="25"/>
       <c r="U339" s="25"/>
       <c r="V339" s="25"/>
@@ -40441,15 +40540,19 @@
       <c r="AK339" s="25"/>
       <c r="AM339" s="25"/>
       <c r="AN339" s="25" t="s">
-        <v>981</v>
+        <v>972</v>
       </c>
       <c r="AO339" s="25"/>
       <c r="AP339" s="25" t="s">
-        <v>981</v>
-      </c>
-      <c r="AQ339" s="25"/>
+        <v>972</v>
+      </c>
+      <c r="AQ339" s="25" t="s">
+        <v>972</v>
+      </c>
       <c r="AR339" s="25"/>
-      <c r="AS339" s="25"/>
+      <c r="AS339" s="25" t="s">
+        <v>972</v>
+      </c>
       <c r="AT339" s="25"/>
       <c r="AU339" s="25"/>
       <c r="AV339" s="25"/>
@@ -40464,7 +40567,7 @@
       <c r="B340" s="25"/>
       <c r="C340" s="25"/>
       <c r="D340" s="25" t="s">
-        <v>983</v>
+        <v>973</v>
       </c>
       <c r="E340" s="37"/>
       <c r="F340" s="25"/>
@@ -40482,17 +40585,11 @@
       <c r="N340" s="25"/>
       <c r="O340" s="25"/>
       <c r="P340" s="25"/>
-      <c r="Q340" s="25" t="s">
-        <v>1399</v>
-      </c>
+      <c r="Q340" s="25"/>
       <c r="R340" s="25"/>
-      <c r="S340" s="25" t="s">
-        <v>811</v>
-      </c>
+      <c r="S340" s="25"/>
       <c r="T340" s="25"/>
-      <c r="U340" s="25" t="s">
-        <v>269</v>
-      </c>
+      <c r="U340" s="25"/>
       <c r="V340" s="25"/>
       <c r="W340" s="25"/>
       <c r="X340" s="25"/>
@@ -40510,19 +40607,15 @@
       <c r="AK340" s="25"/>
       <c r="AM340" s="25"/>
       <c r="AN340" s="25" t="s">
-        <v>984</v>
+        <v>974</v>
       </c>
       <c r="AO340" s="25"/>
       <c r="AP340" s="25" t="s">
-        <v>984</v>
-      </c>
-      <c r="AQ340" s="25" t="s">
-        <v>984</v>
-      </c>
+        <v>974</v>
+      </c>
+      <c r="AQ340" s="25"/>
       <c r="AR340" s="25"/>
-      <c r="AS340" s="25" t="s">
-        <v>984</v>
-      </c>
+      <c r="AS340" s="25"/>
       <c r="AT340" s="25"/>
       <c r="AU340" s="25"/>
       <c r="AV340" s="25"/>
@@ -40537,7 +40630,7 @@
       <c r="B341" s="25"/>
       <c r="C341" s="25"/>
       <c r="D341" s="25" t="s">
-        <v>985</v>
+        <v>975</v>
       </c>
       <c r="E341" s="37"/>
       <c r="F341" s="25"/>
@@ -40577,11 +40670,11 @@
       <c r="AK341" s="25"/>
       <c r="AM341" s="25"/>
       <c r="AN341" s="25" t="s">
-        <v>811</v>
+        <v>976</v>
       </c>
       <c r="AO341" s="25"/>
       <c r="AP341" s="25" t="s">
-        <v>811</v>
+        <v>976</v>
       </c>
       <c r="AQ341" s="25"/>
       <c r="AR341" s="25"/>
@@ -40597,87 +40690,60 @@
       <c r="A342" s="50">
         <v>70</v>
       </c>
-      <c r="B342" s="50"/>
-      <c r="C342" s="50"/>
-      <c r="D342" s="50" t="s">
-        <v>941</v>
-      </c>
-      <c r="E342" s="50"/>
-      <c r="F342" s="50"/>
-      <c r="G342" s="50"/>
-      <c r="H342" s="50"/>
-      <c r="I342" s="50" t="s">
-        <v>31</v>
-      </c>
-      <c r="J342" s="50"/>
-      <c r="K342" s="50" t="s">
-        <v>248</v>
-      </c>
-      <c r="L342" s="50" t="s">
-        <v>290</v>
-      </c>
-      <c r="M342" s="50"/>
-      <c r="N342" s="50"/>
-      <c r="O342" s="50"/>
-      <c r="P342" s="50"/>
-      <c r="Q342" s="50"/>
-      <c r="R342" s="50"/>
-      <c r="S342" s="50"/>
-      <c r="T342" s="50"/>
-      <c r="U342" s="50"/>
-      <c r="V342" s="50"/>
-      <c r="W342" s="50"/>
-      <c r="X342" s="50"/>
-      <c r="Y342" s="50"/>
-      <c r="Z342" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA342" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB342" s="50" t="s">
-        <v>282</v>
-      </c>
-      <c r="AC342" s="50" t="s">
-        <v>282</v>
-      </c>
-      <c r="AD342" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AE342" s="50"/>
-      <c r="AF342" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG342" s="50" t="s">
-        <v>282</v>
-      </c>
-      <c r="AH342" s="50" t="s">
-        <v>282</v>
-      </c>
-      <c r="AI342" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AJ342" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AK342" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL342" s="50"/>
-      <c r="AM342" s="50"/>
-      <c r="AN342" s="50"/>
-      <c r="AO342" s="50"/>
-      <c r="AP342" s="50"/>
-      <c r="AQ342" s="50"/>
-      <c r="AR342" s="50"/>
-      <c r="AS342" s="50"/>
-      <c r="AT342" s="50"/>
-      <c r="AU342" s="50"/>
-      <c r="AV342" s="50"/>
-      <c r="AW342" s="50"/>
-      <c r="AX342" s="50"/>
-      <c r="AY342" s="50"/>
-      <c r="AZ342" s="50"/>
+      <c r="B342" s="25"/>
+      <c r="C342" s="25"/>
+      <c r="D342" s="25" t="s">
+        <v>977</v>
+      </c>
+      <c r="E342" s="37"/>
+      <c r="F342" s="25"/>
+      <c r="G342" s="25"/>
+      <c r="H342" s="25"/>
+      <c r="I342" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="J342" s="25"/>
+      <c r="K342" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L342" s="25"/>
+      <c r="M342" s="25"/>
+      <c r="N342" s="25"/>
+      <c r="O342" s="25"/>
+      <c r="P342" s="25"/>
+      <c r="Q342" s="25"/>
+      <c r="R342" s="25"/>
+      <c r="S342" s="25"/>
+      <c r="T342" s="25"/>
+      <c r="U342" s="25"/>
+      <c r="V342" s="25"/>
+      <c r="W342" s="25"/>
+      <c r="X342" s="25"/>
+      <c r="Z342" s="25"/>
+      <c r="AA342" s="25"/>
+      <c r="AB342" s="25"/>
+      <c r="AC342" s="25"/>
+      <c r="AD342" s="25"/>
+      <c r="AE342" s="25"/>
+      <c r="AF342" s="25"/>
+      <c r="AG342" s="25"/>
+      <c r="AH342" s="25"/>
+      <c r="AI342" s="25"/>
+      <c r="AJ342" s="25"/>
+      <c r="AK342" s="25"/>
+      <c r="AM342" s="25"/>
+      <c r="AN342" s="25"/>
+      <c r="AO342" s="25"/>
+      <c r="AP342" s="25"/>
+      <c r="AQ342" s="25"/>
+      <c r="AR342" s="25"/>
+      <c r="AS342" s="25"/>
+      <c r="AT342" s="25"/>
+      <c r="AU342" s="25"/>
+      <c r="AV342" s="25"/>
+      <c r="AW342" s="25"/>
+      <c r="AX342" s="25"/>
+      <c r="AZ342" s="26"/>
     </row>
     <row r="343" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A343" s="50">
@@ -40686,17 +40752,11 @@
       <c r="B343" s="25"/>
       <c r="C343" s="25"/>
       <c r="D343" s="25" t="s">
-        <v>951</v>
-      </c>
-      <c r="E343" s="37" t="s">
-        <v>2063</v>
-      </c>
-      <c r="F343" s="25" t="s">
-        <v>856</v>
-      </c>
-      <c r="G343" s="25" t="s">
-        <v>47</v>
-      </c>
+        <v>978</v>
+      </c>
+      <c r="E343" s="37"/>
+      <c r="F343" s="25"/>
+      <c r="G343" s="25"/>
       <c r="H343" s="25"/>
       <c r="I343" s="25" t="s">
         <v>23</v>
@@ -40732,19 +40792,15 @@
       <c r="AK343" s="25"/>
       <c r="AM343" s="25"/>
       <c r="AN343" s="25" t="s">
-        <v>666</v>
+        <v>979</v>
       </c>
       <c r="AO343" s="25"/>
       <c r="AP343" s="25" t="s">
-        <v>666</v>
-      </c>
-      <c r="AQ343" s="25" t="s">
-        <v>666</v>
-      </c>
+        <v>979</v>
+      </c>
+      <c r="AQ343" s="25"/>
       <c r="AR343" s="25"/>
-      <c r="AS343" s="25" t="s">
-        <v>666</v>
-      </c>
+      <c r="AS343" s="25"/>
       <c r="AT343" s="25"/>
       <c r="AU343" s="25"/>
       <c r="AV343" s="25"/>
@@ -40756,87 +40812,64 @@
       <c r="A344" s="50">
         <v>70</v>
       </c>
-      <c r="B344" s="50"/>
-      <c r="C344" s="50"/>
-      <c r="D344" s="50" t="s">
-        <v>942</v>
-      </c>
-      <c r="E344" s="50"/>
-      <c r="F344" s="50"/>
-      <c r="G344" s="50"/>
-      <c r="H344" s="50"/>
-      <c r="I344" s="50" t="s">
-        <v>31</v>
-      </c>
-      <c r="J344" s="50"/>
-      <c r="K344" s="50" t="s">
-        <v>248</v>
-      </c>
-      <c r="L344" s="50" t="s">
-        <v>291</v>
-      </c>
-      <c r="M344" s="50"/>
-      <c r="N344" s="50"/>
-      <c r="O344" s="50"/>
-      <c r="P344" s="50"/>
-      <c r="Q344" s="50"/>
-      <c r="R344" s="50"/>
-      <c r="S344" s="50"/>
-      <c r="T344" s="50"/>
-      <c r="U344" s="50"/>
-      <c r="V344" s="50"/>
-      <c r="W344" s="50"/>
-      <c r="X344" s="50"/>
-      <c r="Y344" s="50"/>
-      <c r="Z344" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA344" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB344" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC344" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AD344" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AE344" s="50"/>
-      <c r="AF344" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG344" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AH344" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI344" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AJ344" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AK344" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL344" s="50"/>
-      <c r="AM344" s="50"/>
-      <c r="AN344" s="50"/>
-      <c r="AO344" s="50"/>
-      <c r="AP344" s="50"/>
-      <c r="AQ344" s="50"/>
-      <c r="AR344" s="50"/>
-      <c r="AS344" s="50"/>
-      <c r="AT344" s="50"/>
-      <c r="AU344" s="50"/>
-      <c r="AV344" s="50"/>
-      <c r="AW344" s="50"/>
-      <c r="AX344" s="50"/>
-      <c r="AY344" s="50"/>
-      <c r="AZ344" s="50"/>
+      <c r="B344" s="25"/>
+      <c r="C344" s="25"/>
+      <c r="D344" s="25" t="s">
+        <v>980</v>
+      </c>
+      <c r="E344" s="37"/>
+      <c r="F344" s="25"/>
+      <c r="G344" s="25"/>
+      <c r="H344" s="25"/>
+      <c r="I344" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="J344" s="25"/>
+      <c r="K344" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L344" s="25"/>
+      <c r="M344" s="25"/>
+      <c r="N344" s="25"/>
+      <c r="O344" s="25"/>
+      <c r="P344" s="25"/>
+      <c r="Q344" s="25"/>
+      <c r="R344" s="25"/>
+      <c r="S344" s="25"/>
+      <c r="T344" s="25"/>
+      <c r="U344" s="25"/>
+      <c r="V344" s="25"/>
+      <c r="W344" s="25"/>
+      <c r="X344" s="25"/>
+      <c r="Z344" s="25"/>
+      <c r="AA344" s="25"/>
+      <c r="AB344" s="25"/>
+      <c r="AC344" s="25"/>
+      <c r="AD344" s="25"/>
+      <c r="AE344" s="25"/>
+      <c r="AF344" s="25"/>
+      <c r="AG344" s="25"/>
+      <c r="AH344" s="25"/>
+      <c r="AI344" s="25"/>
+      <c r="AJ344" s="25"/>
+      <c r="AK344" s="25"/>
+      <c r="AM344" s="25"/>
+      <c r="AN344" s="25" t="s">
+        <v>981</v>
+      </c>
+      <c r="AO344" s="25"/>
+      <c r="AP344" s="25" t="s">
+        <v>981</v>
+      </c>
+      <c r="AQ344" s="25"/>
+      <c r="AR344" s="25"/>
+      <c r="AS344" s="25"/>
+      <c r="AT344" s="25"/>
+      <c r="AU344" s="25"/>
+      <c r="AV344" s="25"/>
+      <c r="AW344" s="25"/>
+      <c r="AX344" s="25"/>
+      <c r="AZ344" s="26"/>
     </row>
     <row r="345" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A345" s="50">
@@ -40845,17 +40878,11 @@
       <c r="B345" s="25"/>
       <c r="C345" s="25"/>
       <c r="D345" s="25" t="s">
-        <v>986</v>
-      </c>
-      <c r="E345" s="37" t="s">
-        <v>2064</v>
-      </c>
-      <c r="F345" s="25" t="s">
-        <v>869</v>
-      </c>
-      <c r="G345" s="25" t="s">
-        <v>47</v>
-      </c>
+        <v>983</v>
+      </c>
+      <c r="E345" s="37"/>
+      <c r="F345" s="25"/>
+      <c r="G345" s="25"/>
       <c r="H345" s="25"/>
       <c r="I345" s="25" t="s">
         <v>23</v>
@@ -40869,11 +40896,17 @@
       <c r="N345" s="25"/>
       <c r="O345" s="25"/>
       <c r="P345" s="25"/>
-      <c r="Q345" s="25"/>
+      <c r="Q345" s="25" t="s">
+        <v>1399</v>
+      </c>
       <c r="R345" s="25"/>
-      <c r="S345" s="25"/>
+      <c r="S345" s="25" t="s">
+        <v>811</v>
+      </c>
       <c r="T345" s="25"/>
-      <c r="U345" s="25"/>
+      <c r="U345" s="25" t="s">
+        <v>269</v>
+      </c>
       <c r="V345" s="25"/>
       <c r="W345" s="25"/>
       <c r="X345" s="25"/>
@@ -40891,15 +40924,19 @@
       <c r="AK345" s="25"/>
       <c r="AM345" s="25"/>
       <c r="AN345" s="25" t="s">
-        <v>1150</v>
+        <v>984</v>
       </c>
       <c r="AO345" s="25"/>
       <c r="AP345" s="25" t="s">
-        <v>1150</v>
-      </c>
-      <c r="AQ345" s="25"/>
+        <v>984</v>
+      </c>
+      <c r="AQ345" s="25" t="s">
+        <v>984</v>
+      </c>
       <c r="AR345" s="25"/>
-      <c r="AS345" s="25"/>
+      <c r="AS345" s="25" t="s">
+        <v>984</v>
+      </c>
       <c r="AT345" s="25"/>
       <c r="AU345" s="25"/>
       <c r="AV345" s="25"/>
@@ -40911,341 +40948,335 @@
       <c r="A346" s="50">
         <v>70</v>
       </c>
-      <c r="B346" s="50"/>
-      <c r="C346" s="50"/>
-      <c r="D346" s="50" t="s">
-        <v>987</v>
-      </c>
-      <c r="E346" s="50"/>
-      <c r="F346" s="50"/>
-      <c r="G346" s="50"/>
-      <c r="H346" s="50"/>
-      <c r="I346" s="50" t="s">
-        <v>31</v>
-      </c>
-      <c r="J346" s="50"/>
-      <c r="K346" s="50" t="s">
-        <v>248</v>
-      </c>
-      <c r="L346" s="50" t="s">
-        <v>290</v>
-      </c>
-      <c r="M346" s="50"/>
-      <c r="N346" s="50"/>
-      <c r="O346" s="50"/>
-      <c r="P346" s="50"/>
-      <c r="Q346" s="50"/>
-      <c r="R346" s="50"/>
-      <c r="S346" s="50"/>
-      <c r="T346" s="50"/>
-      <c r="U346" s="50"/>
-      <c r="V346" s="50"/>
-      <c r="W346" s="50"/>
-      <c r="X346" s="50"/>
-      <c r="Y346" s="50"/>
-      <c r="Z346" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA346" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB346" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC346" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AD346" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AE346" s="50"/>
-      <c r="AF346" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG346" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AH346" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI346" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AJ346" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AK346" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL346" s="50"/>
-      <c r="AM346" s="50"/>
-      <c r="AN346" s="50"/>
-      <c r="AO346" s="50"/>
-      <c r="AP346" s="50"/>
-      <c r="AQ346" s="50"/>
-      <c r="AR346" s="50"/>
-      <c r="AS346" s="50"/>
-      <c r="AT346" s="50"/>
-      <c r="AU346" s="50"/>
-      <c r="AV346" s="50"/>
-      <c r="AW346" s="50"/>
-      <c r="AX346" s="50"/>
-      <c r="AY346" s="50"/>
-      <c r="AZ346" s="50"/>
+      <c r="B346" s="25"/>
+      <c r="C346" s="25"/>
+      <c r="D346" s="25" t="s">
+        <v>985</v>
+      </c>
+      <c r="E346" s="37"/>
+      <c r="F346" s="25"/>
+      <c r="G346" s="25"/>
+      <c r="H346" s="25"/>
+      <c r="I346" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="J346" s="25"/>
+      <c r="K346" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L346" s="25"/>
+      <c r="M346" s="25"/>
+      <c r="N346" s="25"/>
+      <c r="O346" s="25"/>
+      <c r="P346" s="25"/>
+      <c r="Q346" s="25"/>
+      <c r="R346" s="25"/>
+      <c r="S346" s="25"/>
+      <c r="T346" s="25"/>
+      <c r="U346" s="25"/>
+      <c r="V346" s="25"/>
+      <c r="W346" s="25"/>
+      <c r="X346" s="25"/>
+      <c r="Z346" s="25"/>
+      <c r="AA346" s="25"/>
+      <c r="AB346" s="25"/>
+      <c r="AC346" s="25"/>
+      <c r="AD346" s="25"/>
+      <c r="AE346" s="25"/>
+      <c r="AF346" s="25"/>
+      <c r="AG346" s="25"/>
+      <c r="AH346" s="25"/>
+      <c r="AI346" s="25"/>
+      <c r="AJ346" s="25"/>
+      <c r="AK346" s="25"/>
+      <c r="AM346" s="25"/>
+      <c r="AN346" s="25" t="s">
+        <v>811</v>
+      </c>
+      <c r="AO346" s="25"/>
+      <c r="AP346" s="25" t="s">
+        <v>811</v>
+      </c>
+      <c r="AQ346" s="25"/>
+      <c r="AR346" s="25"/>
+      <c r="AS346" s="25"/>
+      <c r="AT346" s="25"/>
+      <c r="AU346" s="25"/>
+      <c r="AV346" s="25"/>
+      <c r="AW346" s="25"/>
+      <c r="AX346" s="25"/>
+      <c r="AZ346" s="26"/>
     </row>
     <row r="347" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A347" s="50">
         <v>70</v>
       </c>
-      <c r="B347" s="25"/>
-      <c r="C347" s="25"/>
-      <c r="D347" s="25" t="s">
-        <v>988</v>
-      </c>
-      <c r="E347" s="37" t="s">
-        <v>2065</v>
-      </c>
-      <c r="F347" s="25" t="s">
-        <v>884</v>
-      </c>
-      <c r="G347" s="25" t="s">
-        <v>989</v>
-      </c>
-      <c r="H347" s="25"/>
-      <c r="I347" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="J347" s="25"/>
-      <c r="K347" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="L347" s="25"/>
-      <c r="M347" s="25"/>
-      <c r="N347" s="25"/>
-      <c r="O347" s="25"/>
-      <c r="P347" s="25"/>
-      <c r="Q347" s="25"/>
-      <c r="R347" s="25"/>
-      <c r="S347" s="25"/>
-      <c r="T347" s="25"/>
-      <c r="U347" s="25"/>
-      <c r="V347" s="25"/>
-      <c r="W347" s="25"/>
-      <c r="X347" s="25"/>
-      <c r="Z347" s="25"/>
-      <c r="AA347" s="25"/>
-      <c r="AB347" s="25"/>
-      <c r="AC347" s="25"/>
-      <c r="AD347" s="25"/>
-      <c r="AE347" s="25"/>
-      <c r="AF347" s="25"/>
-      <c r="AG347" s="25"/>
-      <c r="AH347" s="25"/>
-      <c r="AI347" s="25"/>
-      <c r="AJ347" s="25"/>
-      <c r="AK347" s="25"/>
-      <c r="AM347" s="25"/>
-      <c r="AN347" s="25" t="s">
-        <v>1400</v>
-      </c>
-      <c r="AO347" s="25"/>
-      <c r="AP347" s="25" t="s">
-        <v>1400</v>
-      </c>
-      <c r="AQ347" s="25" t="s">
-        <v>1400</v>
-      </c>
-      <c r="AR347" s="25"/>
-      <c r="AS347" s="25" t="s">
-        <v>1400</v>
-      </c>
-      <c r="AT347" s="25"/>
-      <c r="AU347" s="25"/>
-      <c r="AV347" s="25"/>
-      <c r="AW347" s="25"/>
-      <c r="AX347" s="25"/>
-      <c r="AZ347" s="26"/>
+      <c r="B347" s="50"/>
+      <c r="C347" s="50"/>
+      <c r="D347" s="50" t="s">
+        <v>941</v>
+      </c>
+      <c r="E347" s="50"/>
+      <c r="F347" s="50"/>
+      <c r="G347" s="50"/>
+      <c r="H347" s="50"/>
+      <c r="I347" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="J347" s="50"/>
+      <c r="K347" s="50" t="s">
+        <v>248</v>
+      </c>
+      <c r="L347" s="50" t="s">
+        <v>290</v>
+      </c>
+      <c r="M347" s="50"/>
+      <c r="N347" s="50"/>
+      <c r="O347" s="50"/>
+      <c r="P347" s="50"/>
+      <c r="Q347" s="50"/>
+      <c r="R347" s="50"/>
+      <c r="S347" s="50"/>
+      <c r="T347" s="50"/>
+      <c r="U347" s="50"/>
+      <c r="V347" s="50"/>
+      <c r="W347" s="50"/>
+      <c r="X347" s="50"/>
+      <c r="Y347" s="50"/>
+      <c r="Z347" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA347" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB347" s="50" t="s">
+        <v>282</v>
+      </c>
+      <c r="AC347" s="50" t="s">
+        <v>282</v>
+      </c>
+      <c r="AD347" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE347" s="50"/>
+      <c r="AF347" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG347" s="50" t="s">
+        <v>282</v>
+      </c>
+      <c r="AH347" s="50" t="s">
+        <v>282</v>
+      </c>
+      <c r="AI347" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ347" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK347" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL347" s="50"/>
+      <c r="AM347" s="50"/>
+      <c r="AN347" s="50"/>
+      <c r="AO347" s="50"/>
+      <c r="AP347" s="50"/>
+      <c r="AQ347" s="50"/>
+      <c r="AR347" s="50"/>
+      <c r="AS347" s="50"/>
+      <c r="AT347" s="50"/>
+      <c r="AU347" s="50"/>
+      <c r="AV347" s="50"/>
+      <c r="AW347" s="50"/>
+      <c r="AX347" s="50"/>
+      <c r="AY347" s="50"/>
+      <c r="AZ347" s="50"/>
     </row>
     <row r="348" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A348" s="50">
         <v>70</v>
       </c>
-      <c r="B348" s="50"/>
-      <c r="C348" s="50"/>
-      <c r="D348" s="50" t="s">
-        <v>990</v>
-      </c>
-      <c r="E348" s="50"/>
-      <c r="F348" s="50"/>
-      <c r="G348" s="50"/>
-      <c r="H348" s="50"/>
-      <c r="I348" s="50" t="s">
-        <v>31</v>
-      </c>
-      <c r="J348" s="50"/>
-      <c r="K348" s="50" t="s">
-        <v>248</v>
-      </c>
-      <c r="L348" s="50" t="s">
-        <v>291</v>
-      </c>
-      <c r="M348" s="50"/>
-      <c r="N348" s="50"/>
-      <c r="O348" s="50"/>
-      <c r="P348" s="50"/>
-      <c r="Q348" s="50"/>
-      <c r="R348" s="50"/>
-      <c r="S348" s="50"/>
-      <c r="T348" s="50"/>
-      <c r="U348" s="50"/>
-      <c r="V348" s="50"/>
-      <c r="W348" s="50"/>
-      <c r="X348" s="50"/>
-      <c r="Y348" s="50"/>
-      <c r="Z348" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA348" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB348" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC348" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AD348" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AE348" s="50"/>
-      <c r="AF348" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG348" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AH348" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI348" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AJ348" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AK348" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL348" s="50"/>
-      <c r="AM348" s="50"/>
-      <c r="AN348" s="50"/>
-      <c r="AO348" s="50"/>
-      <c r="AP348" s="50"/>
-      <c r="AQ348" s="50"/>
-      <c r="AR348" s="50"/>
-      <c r="AS348" s="50"/>
-      <c r="AT348" s="50"/>
-      <c r="AU348" s="50"/>
-      <c r="AV348" s="50"/>
-      <c r="AW348" s="50"/>
-      <c r="AX348" s="50"/>
-      <c r="AY348" s="50"/>
-      <c r="AZ348" s="50"/>
+      <c r="B348" s="25"/>
+      <c r="C348" s="25"/>
+      <c r="D348" s="25" t="s">
+        <v>951</v>
+      </c>
+      <c r="E348" s="37" t="s">
+        <v>2063</v>
+      </c>
+      <c r="F348" s="25" t="s">
+        <v>856</v>
+      </c>
+      <c r="G348" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="H348" s="25"/>
+      <c r="I348" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="J348" s="25"/>
+      <c r="K348" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L348" s="25"/>
+      <c r="M348" s="25"/>
+      <c r="N348" s="25"/>
+      <c r="O348" s="25"/>
+      <c r="P348" s="25"/>
+      <c r="Q348" s="25"/>
+      <c r="R348" s="25"/>
+      <c r="S348" s="25"/>
+      <c r="T348" s="25"/>
+      <c r="U348" s="25"/>
+      <c r="V348" s="25"/>
+      <c r="W348" s="25"/>
+      <c r="X348" s="25"/>
+      <c r="Z348" s="25"/>
+      <c r="AA348" s="25"/>
+      <c r="AB348" s="25"/>
+      <c r="AC348" s="25"/>
+      <c r="AD348" s="25"/>
+      <c r="AE348" s="25"/>
+      <c r="AF348" s="25"/>
+      <c r="AG348" s="25"/>
+      <c r="AH348" s="25"/>
+      <c r="AI348" s="25"/>
+      <c r="AJ348" s="25"/>
+      <c r="AK348" s="25"/>
+      <c r="AM348" s="25"/>
+      <c r="AN348" s="25" t="s">
+        <v>666</v>
+      </c>
+      <c r="AO348" s="25"/>
+      <c r="AP348" s="25" t="s">
+        <v>666</v>
+      </c>
+      <c r="AQ348" s="25" t="s">
+        <v>666</v>
+      </c>
+      <c r="AR348" s="25"/>
+      <c r="AS348" s="25" t="s">
+        <v>666</v>
+      </c>
+      <c r="AT348" s="25"/>
+      <c r="AU348" s="25"/>
+      <c r="AV348" s="25"/>
+      <c r="AW348" s="25"/>
+      <c r="AX348" s="25"/>
+      <c r="AZ348" s="26"/>
     </row>
     <row r="349" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A349" s="50">
         <v>70</v>
       </c>
-      <c r="B349" s="25"/>
-      <c r="C349" s="25"/>
-      <c r="D349" s="25" t="s">
-        <v>991</v>
-      </c>
-      <c r="E349" s="37" t="s">
-        <v>2066</v>
-      </c>
-      <c r="F349" s="25" t="s">
-        <v>992</v>
-      </c>
-      <c r="G349" s="25" t="s">
-        <v>993</v>
-      </c>
-      <c r="H349" s="25"/>
-      <c r="I349" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="J349" s="25"/>
-      <c r="K349" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="L349" s="25"/>
-      <c r="M349" s="25"/>
-      <c r="N349" s="25"/>
-      <c r="O349" s="25"/>
-      <c r="P349" s="25"/>
-      <c r="Q349" s="25"/>
-      <c r="R349" s="25"/>
-      <c r="S349" s="25"/>
-      <c r="T349" s="25"/>
-      <c r="U349" s="25"/>
-      <c r="V349" s="25"/>
-      <c r="W349" s="25"/>
-      <c r="X349" s="25"/>
-      <c r="Z349" s="25"/>
-      <c r="AA349" s="25"/>
-      <c r="AB349" s="25"/>
-      <c r="AC349" s="25"/>
-      <c r="AD349" s="25"/>
-      <c r="AE349" s="25"/>
-      <c r="AF349" s="25"/>
-      <c r="AG349" s="25"/>
-      <c r="AH349" s="25"/>
-      <c r="AI349" s="25"/>
-      <c r="AJ349" s="25"/>
-      <c r="AK349" s="25"/>
-      <c r="AM349" s="25"/>
-      <c r="AN349" s="25" t="s">
-        <v>1164</v>
-      </c>
-      <c r="AO349" s="25"/>
-      <c r="AP349" s="25" t="s">
-        <v>1164</v>
-      </c>
-      <c r="AQ349" s="25"/>
-      <c r="AR349" s="25"/>
-      <c r="AS349" s="25"/>
-      <c r="AT349" s="25"/>
-      <c r="AU349" s="25"/>
-      <c r="AV349" s="25"/>
-      <c r="AW349" s="25"/>
-      <c r="AX349" s="25"/>
-      <c r="AZ349" s="26"/>
+      <c r="B349" s="50"/>
+      <c r="C349" s="50"/>
+      <c r="D349" s="50" t="s">
+        <v>942</v>
+      </c>
+      <c r="E349" s="50"/>
+      <c r="F349" s="50"/>
+      <c r="G349" s="50"/>
+      <c r="H349" s="50"/>
+      <c r="I349" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="J349" s="50"/>
+      <c r="K349" s="50" t="s">
+        <v>248</v>
+      </c>
+      <c r="L349" s="50" t="s">
+        <v>291</v>
+      </c>
+      <c r="M349" s="50"/>
+      <c r="N349" s="50"/>
+      <c r="O349" s="50"/>
+      <c r="P349" s="50"/>
+      <c r="Q349" s="50"/>
+      <c r="R349" s="50"/>
+      <c r="S349" s="50"/>
+      <c r="T349" s="50"/>
+      <c r="U349" s="50"/>
+      <c r="V349" s="50"/>
+      <c r="W349" s="50"/>
+      <c r="X349" s="50"/>
+      <c r="Y349" s="50"/>
+      <c r="Z349" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA349" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB349" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC349" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD349" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE349" s="50"/>
+      <c r="AF349" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG349" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH349" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI349" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ349" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK349" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL349" s="50"/>
+      <c r="AM349" s="50"/>
+      <c r="AN349" s="50"/>
+      <c r="AO349" s="50"/>
+      <c r="AP349" s="50"/>
+      <c r="AQ349" s="50"/>
+      <c r="AR349" s="50"/>
+      <c r="AS349" s="50"/>
+      <c r="AT349" s="50"/>
+      <c r="AU349" s="50"/>
+      <c r="AV349" s="50"/>
+      <c r="AW349" s="50"/>
+      <c r="AX349" s="50"/>
+      <c r="AY349" s="50"/>
+      <c r="AZ349" s="50"/>
     </row>
     <row r="350" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A350" s="25">
+      <c r="A350" s="50">
         <v>70</v>
       </c>
       <c r="B350" s="25"/>
       <c r="C350" s="25"/>
       <c r="D350" s="25" t="s">
-        <v>447</v>
+        <v>986</v>
       </c>
       <c r="E350" s="37" t="s">
-        <v>1936</v>
+        <v>2064</v>
       </c>
       <c r="F350" s="25" t="s">
-        <v>392</v>
+        <v>869</v>
       </c>
       <c r="G350" s="25" t="s">
         <v>47</v>
       </c>
       <c r="H350" s="25"/>
       <c r="I350" s="25" t="s">
-        <v>1325</v>
+        <v>23</v>
       </c>
       <c r="J350" s="25"/>
       <c r="K350" s="25" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L350" s="25"/>
       <c r="M350" s="25"/>
@@ -41260,47 +41291,25 @@
       <c r="V350" s="25"/>
       <c r="W350" s="25"/>
       <c r="X350" s="25"/>
-      <c r="Z350" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA350" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB350" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC350" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD350" s="25" t="s">
-        <v>25</v>
-      </c>
+      <c r="Z350" s="25"/>
+      <c r="AA350" s="25"/>
+      <c r="AB350" s="25"/>
+      <c r="AC350" s="25"/>
+      <c r="AD350" s="25"/>
       <c r="AE350" s="25"/>
-      <c r="AF350" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG350" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AH350" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AI350" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ350" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AK350" s="25" t="s">
-        <v>25</v>
-      </c>
+      <c r="AF350" s="25"/>
+      <c r="AG350" s="25"/>
+      <c r="AH350" s="25"/>
+      <c r="AI350" s="25"/>
+      <c r="AJ350" s="25"/>
+      <c r="AK350" s="25"/>
       <c r="AM350" s="25"/>
       <c r="AN350" s="25" t="s">
-        <v>447</v>
+        <v>1150</v>
       </c>
       <c r="AO350" s="25"/>
       <c r="AP350" s="25" t="s">
-        <v>447</v>
+        <v>1150</v>
       </c>
       <c r="AQ350" s="25"/>
       <c r="AR350" s="25"/>
@@ -41313,370 +41322,344 @@
       <c r="AZ350" s="26"/>
     </row>
     <row r="351" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A351" s="25">
-        <v>70</v>
-      </c>
-      <c r="B351" s="25"/>
-      <c r="C351" s="25"/>
-      <c r="D351" s="25" t="s">
-        <v>947</v>
-      </c>
-      <c r="E351" s="37" t="s">
-        <v>2067</v>
-      </c>
-      <c r="F351" s="25" t="s">
-        <v>283</v>
-      </c>
-      <c r="G351" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="H351" s="25"/>
-      <c r="I351" s="25" t="s">
-        <v>1401</v>
-      </c>
-      <c r="J351" s="25"/>
-      <c r="K351" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="L351" s="25"/>
-      <c r="M351" s="25"/>
-      <c r="N351" s="25"/>
-      <c r="O351" s="25"/>
-      <c r="P351" s="25"/>
-      <c r="Q351" s="25"/>
-      <c r="R351" s="25"/>
-      <c r="S351" s="25"/>
-      <c r="T351" s="25"/>
-      <c r="U351" s="25"/>
-      <c r="V351" s="25"/>
-      <c r="W351" s="25"/>
-      <c r="X351" s="25" t="s">
-        <v>1648</v>
-      </c>
-      <c r="Z351" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA351" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB351" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC351" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD351" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE351" s="25"/>
-      <c r="AF351" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG351" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH351" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AI351" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ351" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AK351" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM351" s="25"/>
-      <c r="AN351" s="25" t="s">
-        <v>947</v>
-      </c>
-      <c r="AO351" s="25"/>
-      <c r="AP351" s="25" t="s">
-        <v>947</v>
-      </c>
-      <c r="AQ351" s="25" t="s">
-        <v>947</v>
-      </c>
-      <c r="AR351" s="25"/>
-      <c r="AS351" s="25" t="s">
-        <v>947</v>
-      </c>
-      <c r="AT351" s="25"/>
-      <c r="AU351" s="25"/>
-      <c r="AV351" s="25"/>
-      <c r="AW351" s="25"/>
-      <c r="AX351" s="25"/>
-      <c r="AZ351" s="26"/>
+      <c r="A351" s="50">
+        <v>70</v>
+      </c>
+      <c r="B351" s="50"/>
+      <c r="C351" s="50"/>
+      <c r="D351" s="50" t="s">
+        <v>987</v>
+      </c>
+      <c r="E351" s="50"/>
+      <c r="F351" s="50"/>
+      <c r="G351" s="50"/>
+      <c r="H351" s="50"/>
+      <c r="I351" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="J351" s="50"/>
+      <c r="K351" s="50" t="s">
+        <v>248</v>
+      </c>
+      <c r="L351" s="50" t="s">
+        <v>290</v>
+      </c>
+      <c r="M351" s="50"/>
+      <c r="N351" s="50"/>
+      <c r="O351" s="50"/>
+      <c r="P351" s="50"/>
+      <c r="Q351" s="50"/>
+      <c r="R351" s="50"/>
+      <c r="S351" s="50"/>
+      <c r="T351" s="50"/>
+      <c r="U351" s="50"/>
+      <c r="V351" s="50"/>
+      <c r="W351" s="50"/>
+      <c r="X351" s="50"/>
+      <c r="Y351" s="50"/>
+      <c r="Z351" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA351" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB351" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC351" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD351" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE351" s="50"/>
+      <c r="AF351" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG351" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH351" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI351" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ351" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK351" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL351" s="50"/>
+      <c r="AM351" s="50"/>
+      <c r="AN351" s="50"/>
+      <c r="AO351" s="50"/>
+      <c r="AP351" s="50"/>
+      <c r="AQ351" s="50"/>
+      <c r="AR351" s="50"/>
+      <c r="AS351" s="50"/>
+      <c r="AT351" s="50"/>
+      <c r="AU351" s="50"/>
+      <c r="AV351" s="50"/>
+      <c r="AW351" s="50"/>
+      <c r="AX351" s="50"/>
+      <c r="AY351" s="50"/>
+      <c r="AZ351" s="50"/>
     </row>
     <row r="352" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A352" s="50">
         <v>70</v>
       </c>
-      <c r="B352" s="50"/>
-      <c r="C352" s="50"/>
-      <c r="D352" s="50" t="s">
-        <v>597</v>
-      </c>
-      <c r="E352" s="50"/>
-      <c r="F352" s="50"/>
-      <c r="G352" s="50"/>
-      <c r="H352" s="50"/>
-      <c r="I352" s="50" t="s">
-        <v>31</v>
-      </c>
-      <c r="J352" s="50"/>
-      <c r="K352" s="50" t="s">
-        <v>248</v>
-      </c>
-      <c r="L352" s="50" t="s">
-        <v>291</v>
-      </c>
-      <c r="M352" s="50"/>
-      <c r="N352" s="50"/>
-      <c r="O352" s="50"/>
-      <c r="P352" s="50"/>
-      <c r="Q352" s="50"/>
-      <c r="R352" s="50"/>
-      <c r="S352" s="50"/>
-      <c r="T352" s="50"/>
-      <c r="U352" s="50"/>
-      <c r="V352" s="50"/>
-      <c r="W352" s="50"/>
-      <c r="X352" s="50"/>
-      <c r="Y352" s="50"/>
-      <c r="Z352" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA352" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB352" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC352" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AD352" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AE352" s="50"/>
-      <c r="AF352" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG352" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AH352" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI352" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AJ352" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AK352" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL352" s="50"/>
-      <c r="AM352" s="50"/>
-      <c r="AN352" s="50"/>
-      <c r="AO352" s="50"/>
-      <c r="AP352" s="50"/>
-      <c r="AQ352" s="50"/>
-      <c r="AR352" s="50"/>
-      <c r="AS352" s="50"/>
-      <c r="AT352" s="50"/>
-      <c r="AU352" s="50"/>
-      <c r="AV352" s="50"/>
-      <c r="AW352" s="50"/>
-      <c r="AX352" s="50"/>
-      <c r="AY352" s="50"/>
-      <c r="AZ352" s="50"/>
+      <c r="B352" s="25"/>
+      <c r="C352" s="25"/>
+      <c r="D352" s="25" t="s">
+        <v>988</v>
+      </c>
+      <c r="E352" s="37" t="s">
+        <v>2065</v>
+      </c>
+      <c r="F352" s="25" t="s">
+        <v>884</v>
+      </c>
+      <c r="G352" s="25" t="s">
+        <v>989</v>
+      </c>
+      <c r="H352" s="25"/>
+      <c r="I352" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="J352" s="25"/>
+      <c r="K352" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L352" s="25"/>
+      <c r="M352" s="25"/>
+      <c r="N352" s="25"/>
+      <c r="O352" s="25"/>
+      <c r="P352" s="25"/>
+      <c r="Q352" s="25"/>
+      <c r="R352" s="25"/>
+      <c r="S352" s="25"/>
+      <c r="T352" s="25"/>
+      <c r="U352" s="25"/>
+      <c r="V352" s="25"/>
+      <c r="W352" s="25"/>
+      <c r="X352" s="25"/>
+      <c r="Z352" s="25"/>
+      <c r="AA352" s="25"/>
+      <c r="AB352" s="25"/>
+      <c r="AC352" s="25"/>
+      <c r="AD352" s="25"/>
+      <c r="AE352" s="25"/>
+      <c r="AF352" s="25"/>
+      <c r="AG352" s="25"/>
+      <c r="AH352" s="25"/>
+      <c r="AI352" s="25"/>
+      <c r="AJ352" s="25"/>
+      <c r="AK352" s="25"/>
+      <c r="AM352" s="25"/>
+      <c r="AN352" s="25" t="s">
+        <v>1400</v>
+      </c>
+      <c r="AO352" s="25"/>
+      <c r="AP352" s="25" t="s">
+        <v>1400</v>
+      </c>
+      <c r="AQ352" s="25" t="s">
+        <v>1400</v>
+      </c>
+      <c r="AR352" s="25"/>
+      <c r="AS352" s="25" t="s">
+        <v>1400</v>
+      </c>
+      <c r="AT352" s="25"/>
+      <c r="AU352" s="25"/>
+      <c r="AV352" s="25"/>
+      <c r="AW352" s="25"/>
+      <c r="AX352" s="25"/>
+      <c r="AZ352" s="26"/>
     </row>
     <row r="353" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A353" s="50">
         <v>70</v>
       </c>
-      <c r="B353" s="25"/>
-      <c r="C353" s="25"/>
-      <c r="D353" s="25" t="s">
-        <v>345</v>
-      </c>
-      <c r="E353" s="37" t="s">
-        <v>2068</v>
-      </c>
-      <c r="F353" s="25" t="s">
-        <v>994</v>
-      </c>
-      <c r="G353" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="H353" s="25"/>
-      <c r="I353" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="J353" s="25"/>
-      <c r="K353" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="L353" s="25"/>
-      <c r="M353" s="25"/>
-      <c r="N353" s="25"/>
-      <c r="O353" s="25"/>
-      <c r="P353" s="25"/>
-      <c r="Q353" s="25"/>
-      <c r="R353" s="25"/>
-      <c r="S353" s="25"/>
-      <c r="T353" s="25"/>
-      <c r="U353" s="25"/>
-      <c r="V353" s="25"/>
-      <c r="W353" s="25"/>
-      <c r="X353" s="25" t="s">
-        <v>1648</v>
-      </c>
-      <c r="Z353" s="25"/>
-      <c r="AA353" s="25"/>
-      <c r="AB353" s="25"/>
-      <c r="AC353" s="25"/>
-      <c r="AD353" s="25"/>
-      <c r="AE353" s="25"/>
-      <c r="AF353" s="25"/>
-      <c r="AG353" s="25"/>
-      <c r="AH353" s="25"/>
-      <c r="AI353" s="25"/>
-      <c r="AJ353" s="25"/>
-      <c r="AK353" s="25"/>
-      <c r="AM353" s="25"/>
-      <c r="AN353" s="25" t="s">
-        <v>344</v>
-      </c>
-      <c r="AO353" s="25"/>
-      <c r="AP353" s="25" t="s">
-        <v>344</v>
-      </c>
-      <c r="AQ353" s="25"/>
-      <c r="AR353" s="25"/>
-      <c r="AS353" s="25"/>
-      <c r="AT353" s="25"/>
-      <c r="AU353" s="25"/>
-      <c r="AV353" s="25"/>
-      <c r="AW353" s="25"/>
-      <c r="AX353" s="25"/>
-      <c r="AZ353" s="26"/>
+      <c r="B353" s="50"/>
+      <c r="C353" s="50"/>
+      <c r="D353" s="50" t="s">
+        <v>990</v>
+      </c>
+      <c r="E353" s="50"/>
+      <c r="F353" s="50"/>
+      <c r="G353" s="50"/>
+      <c r="H353" s="50"/>
+      <c r="I353" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="J353" s="50"/>
+      <c r="K353" s="50" t="s">
+        <v>248</v>
+      </c>
+      <c r="L353" s="50" t="s">
+        <v>291</v>
+      </c>
+      <c r="M353" s="50"/>
+      <c r="N353" s="50"/>
+      <c r="O353" s="50"/>
+      <c r="P353" s="50"/>
+      <c r="Q353" s="50"/>
+      <c r="R353" s="50"/>
+      <c r="S353" s="50"/>
+      <c r="T353" s="50"/>
+      <c r="U353" s="50"/>
+      <c r="V353" s="50"/>
+      <c r="W353" s="50"/>
+      <c r="X353" s="50"/>
+      <c r="Y353" s="50"/>
+      <c r="Z353" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA353" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB353" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC353" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD353" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE353" s="50"/>
+      <c r="AF353" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG353" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH353" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI353" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ353" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK353" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL353" s="50"/>
+      <c r="AM353" s="50"/>
+      <c r="AN353" s="50"/>
+      <c r="AO353" s="50"/>
+      <c r="AP353" s="50"/>
+      <c r="AQ353" s="50"/>
+      <c r="AR353" s="50"/>
+      <c r="AS353" s="50"/>
+      <c r="AT353" s="50"/>
+      <c r="AU353" s="50"/>
+      <c r="AV353" s="50"/>
+      <c r="AW353" s="50"/>
+      <c r="AX353" s="50"/>
+      <c r="AY353" s="50"/>
+      <c r="AZ353" s="50"/>
     </row>
     <row r="354" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A354" s="50">
         <v>70</v>
       </c>
-      <c r="B354" s="50"/>
-      <c r="C354" s="50"/>
-      <c r="D354" s="50" t="s">
-        <v>261</v>
-      </c>
-      <c r="E354" s="50"/>
-      <c r="F354" s="50"/>
-      <c r="G354" s="50"/>
-      <c r="H354" s="50"/>
-      <c r="I354" s="50" t="s">
-        <v>31</v>
-      </c>
-      <c r="J354" s="50"/>
-      <c r="K354" s="50" t="s">
-        <v>248</v>
-      </c>
-      <c r="L354" s="50" t="s">
-        <v>290</v>
-      </c>
-      <c r="M354" s="50"/>
-      <c r="N354" s="50"/>
-      <c r="O354" s="50"/>
-      <c r="P354" s="50"/>
-      <c r="Q354" s="50"/>
-      <c r="R354" s="50"/>
-      <c r="S354" s="50"/>
-      <c r="T354" s="50"/>
-      <c r="U354" s="50"/>
-      <c r="V354" s="50"/>
-      <c r="W354" s="50"/>
-      <c r="X354" s="50"/>
-      <c r="Y354" s="50"/>
-      <c r="Z354" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA354" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB354" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC354" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AD354" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AE354" s="50"/>
-      <c r="AF354" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG354" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AH354" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI354" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AJ354" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AK354" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL354" s="50"/>
-      <c r="AM354" s="50"/>
-      <c r="AN354" s="50"/>
-      <c r="AO354" s="50"/>
-      <c r="AP354" s="50"/>
-      <c r="AQ354" s="50"/>
-      <c r="AR354" s="50"/>
-      <c r="AS354" s="50"/>
-      <c r="AT354" s="50"/>
-      <c r="AU354" s="50"/>
-      <c r="AV354" s="50"/>
-      <c r="AW354" s="50"/>
-      <c r="AX354" s="50"/>
-      <c r="AY354" s="50"/>
-      <c r="AZ354" s="50"/>
+      <c r="B354" s="25"/>
+      <c r="C354" s="25"/>
+      <c r="D354" s="25" t="s">
+        <v>991</v>
+      </c>
+      <c r="E354" s="37" t="s">
+        <v>2066</v>
+      </c>
+      <c r="F354" s="25" t="s">
+        <v>992</v>
+      </c>
+      <c r="G354" s="25" t="s">
+        <v>993</v>
+      </c>
+      <c r="H354" s="25"/>
+      <c r="I354" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="J354" s="25"/>
+      <c r="K354" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L354" s="25"/>
+      <c r="M354" s="25"/>
+      <c r="N354" s="25"/>
+      <c r="O354" s="25"/>
+      <c r="P354" s="25"/>
+      <c r="Q354" s="25"/>
+      <c r="R354" s="25"/>
+      <c r="S354" s="25"/>
+      <c r="T354" s="25"/>
+      <c r="U354" s="25"/>
+      <c r="V354" s="25"/>
+      <c r="W354" s="25"/>
+      <c r="X354" s="25"/>
+      <c r="Z354" s="25"/>
+      <c r="AA354" s="25"/>
+      <c r="AB354" s="25"/>
+      <c r="AC354" s="25"/>
+      <c r="AD354" s="25"/>
+      <c r="AE354" s="25"/>
+      <c r="AF354" s="25"/>
+      <c r="AG354" s="25"/>
+      <c r="AH354" s="25"/>
+      <c r="AI354" s="25"/>
+      <c r="AJ354" s="25"/>
+      <c r="AK354" s="25"/>
+      <c r="AM354" s="25"/>
+      <c r="AN354" s="25" t="s">
+        <v>1164</v>
+      </c>
+      <c r="AO354" s="25"/>
+      <c r="AP354" s="25" t="s">
+        <v>1164</v>
+      </c>
+      <c r="AQ354" s="25"/>
+      <c r="AR354" s="25"/>
+      <c r="AS354" s="25"/>
+      <c r="AT354" s="25"/>
+      <c r="AU354" s="25"/>
+      <c r="AV354" s="25"/>
+      <c r="AW354" s="25"/>
+      <c r="AX354" s="25"/>
+      <c r="AZ354" s="26"/>
     </row>
     <row r="355" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A355" s="50">
+      <c r="A355" s="25">
         <v>70</v>
       </c>
       <c r="B355" s="25"/>
       <c r="C355" s="25"/>
       <c r="D355" s="25" t="s">
-        <v>262</v>
+        <v>447</v>
       </c>
       <c r="E355" s="37" t="s">
-        <v>2069</v>
+        <v>1936</v>
       </c>
       <c r="F355" s="25" t="s">
-        <v>259</v>
+        <v>392</v>
       </c>
       <c r="G355" s="25" t="s">
         <v>47</v>
       </c>
       <c r="H355" s="25"/>
       <c r="I355" s="25" t="s">
-        <v>23</v>
+        <v>1325</v>
       </c>
       <c r="J355" s="25"/>
       <c r="K355" s="25" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L355" s="25"/>
       <c r="M355" s="25"/>
@@ -41690,28 +41673,48 @@
       <c r="U355" s="25"/>
       <c r="V355" s="25"/>
       <c r="W355" s="25"/>
-      <c r="X355" s="25" t="s">
-        <v>1653</v>
-      </c>
-      <c r="Z355" s="25"/>
-      <c r="AA355" s="25"/>
-      <c r="AB355" s="25"/>
-      <c r="AC355" s="25"/>
-      <c r="AD355" s="25"/>
+      <c r="X355" s="25"/>
+      <c r="Z355" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA355" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB355" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC355" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD355" s="25" t="s">
+        <v>25</v>
+      </c>
       <c r="AE355" s="25"/>
-      <c r="AF355" s="25"/>
-      <c r="AG355" s="25"/>
-      <c r="AH355" s="25"/>
-      <c r="AI355" s="25"/>
-      <c r="AJ355" s="25"/>
-      <c r="AK355" s="25"/>
+      <c r="AF355" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG355" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH355" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI355" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ355" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK355" s="25" t="s">
+        <v>25</v>
+      </c>
       <c r="AM355" s="25"/>
       <c r="AN355" s="25" t="s">
-        <v>263</v>
+        <v>447</v>
       </c>
       <c r="AO355" s="25"/>
       <c r="AP355" s="25" t="s">
-        <v>263</v>
+        <v>447</v>
       </c>
       <c r="AQ355" s="25"/>
       <c r="AR355" s="25"/>
@@ -41724,1129 +41727,1155 @@
       <c r="AZ355" s="26"/>
     </row>
     <row r="356" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A356" s="50">
-        <v>70</v>
-      </c>
-      <c r="B356" s="50"/>
-      <c r="C356" s="50"/>
-      <c r="D356" s="50" t="s">
-        <v>995</v>
-      </c>
-      <c r="E356" s="50"/>
-      <c r="F356" s="50"/>
-      <c r="G356" s="50"/>
-      <c r="H356" s="50"/>
-      <c r="I356" s="50" t="s">
-        <v>31</v>
-      </c>
-      <c r="J356" s="50"/>
-      <c r="K356" s="50" t="s">
-        <v>248</v>
-      </c>
-      <c r="L356" s="50" t="s">
-        <v>291</v>
-      </c>
-      <c r="M356" s="50"/>
-      <c r="N356" s="50"/>
-      <c r="O356" s="50"/>
-      <c r="P356" s="50"/>
-      <c r="Q356" s="50"/>
-      <c r="R356" s="50"/>
-      <c r="S356" s="50"/>
-      <c r="T356" s="50"/>
-      <c r="U356" s="50"/>
-      <c r="V356" s="50"/>
-      <c r="W356" s="50"/>
-      <c r="X356" s="50"/>
-      <c r="Y356" s="50"/>
-      <c r="Z356" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA356" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB356" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC356" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AD356" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AE356" s="50"/>
-      <c r="AF356" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG356" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AH356" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI356" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AJ356" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AK356" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL356" s="50"/>
-      <c r="AM356" s="50"/>
-      <c r="AN356" s="50"/>
-      <c r="AO356" s="50"/>
-      <c r="AP356" s="50"/>
-      <c r="AQ356" s="50"/>
-      <c r="AR356" s="50"/>
-      <c r="AS356" s="50"/>
-      <c r="AT356" s="50"/>
-      <c r="AU356" s="50"/>
-      <c r="AV356" s="50"/>
-      <c r="AW356" s="50"/>
-      <c r="AX356" s="50"/>
-      <c r="AY356" s="50"/>
-      <c r="AZ356" s="50"/>
+      <c r="A356" s="25">
+        <v>70</v>
+      </c>
+      <c r="B356" s="25"/>
+      <c r="C356" s="25"/>
+      <c r="D356" s="25" t="s">
+        <v>947</v>
+      </c>
+      <c r="E356" s="37" t="s">
+        <v>2067</v>
+      </c>
+      <c r="F356" s="25" t="s">
+        <v>283</v>
+      </c>
+      <c r="G356" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="H356" s="25"/>
+      <c r="I356" s="25" t="s">
+        <v>1401</v>
+      </c>
+      <c r="J356" s="25"/>
+      <c r="K356" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="L356" s="25"/>
+      <c r="M356" s="25"/>
+      <c r="N356" s="25"/>
+      <c r="O356" s="25"/>
+      <c r="P356" s="25"/>
+      <c r="Q356" s="25"/>
+      <c r="R356" s="25"/>
+      <c r="S356" s="25"/>
+      <c r="T356" s="25"/>
+      <c r="U356" s="25"/>
+      <c r="V356" s="25"/>
+      <c r="W356" s="25"/>
+      <c r="X356" s="25" t="s">
+        <v>1648</v>
+      </c>
+      <c r="Z356" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA356" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB356" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC356" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD356" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE356" s="25"/>
+      <c r="AF356" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG356" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AH356" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI356" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ356" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK356" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM356" s="25"/>
+      <c r="AN356" s="25" t="s">
+        <v>947</v>
+      </c>
+      <c r="AO356" s="25"/>
+      <c r="AP356" s="25" t="s">
+        <v>947</v>
+      </c>
+      <c r="AQ356" s="25" t="s">
+        <v>947</v>
+      </c>
+      <c r="AR356" s="25"/>
+      <c r="AS356" s="25" t="s">
+        <v>947</v>
+      </c>
+      <c r="AT356" s="25"/>
+      <c r="AU356" s="25"/>
+      <c r="AV356" s="25"/>
+      <c r="AW356" s="25"/>
+      <c r="AX356" s="25"/>
+      <c r="AZ356" s="26"/>
     </row>
     <row r="357" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A357" s="50">
         <v>70</v>
       </c>
-      <c r="B357" s="25"/>
-      <c r="C357" s="25"/>
-      <c r="D357" s="25" t="s">
-        <v>996</v>
-      </c>
-      <c r="E357" s="37" t="s">
-        <v>2070</v>
-      </c>
-      <c r="F357" s="25" t="s">
-        <v>260</v>
-      </c>
-      <c r="G357" s="25" t="s">
-        <v>997</v>
-      </c>
-      <c r="H357" s="25"/>
-      <c r="I357" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="J357" s="25"/>
-      <c r="K357" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="L357" s="25"/>
-      <c r="M357" s="25"/>
-      <c r="N357" s="25"/>
-      <c r="O357" s="25"/>
-      <c r="P357" s="25"/>
-      <c r="Q357" s="25"/>
-      <c r="R357" s="25"/>
-      <c r="S357" s="25"/>
-      <c r="T357" s="25"/>
-      <c r="U357" s="25"/>
-      <c r="V357" s="25"/>
-      <c r="W357" s="25"/>
-      <c r="X357" s="25" t="s">
-        <v>1653</v>
-      </c>
-      <c r="Z357" s="25"/>
-      <c r="AA357" s="25"/>
-      <c r="AB357" s="25"/>
-      <c r="AC357" s="25"/>
-      <c r="AD357" s="25"/>
-      <c r="AE357" s="25"/>
-      <c r="AF357" s="25"/>
-      <c r="AG357" s="25"/>
-      <c r="AH357" s="25"/>
-      <c r="AI357" s="25"/>
-      <c r="AJ357" s="25"/>
-      <c r="AK357" s="25"/>
-      <c r="AM357" s="25"/>
-      <c r="AN357" s="25" t="s">
-        <v>998</v>
-      </c>
-      <c r="AO357" s="25"/>
-      <c r="AP357" s="25" t="s">
-        <v>998</v>
-      </c>
-      <c r="AQ357" s="25"/>
-      <c r="AR357" s="25"/>
-      <c r="AS357" s="25"/>
-      <c r="AT357" s="25"/>
-      <c r="AU357" s="25"/>
-      <c r="AV357" s="25"/>
-      <c r="AW357" s="25"/>
-      <c r="AX357" s="25"/>
-      <c r="AZ357" s="26"/>
+      <c r="B357" s="50"/>
+      <c r="C357" s="50"/>
+      <c r="D357" s="50" t="s">
+        <v>597</v>
+      </c>
+      <c r="E357" s="50"/>
+      <c r="F357" s="50"/>
+      <c r="G357" s="50"/>
+      <c r="H357" s="50"/>
+      <c r="I357" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="J357" s="50"/>
+      <c r="K357" s="50" t="s">
+        <v>248</v>
+      </c>
+      <c r="L357" s="50" t="s">
+        <v>291</v>
+      </c>
+      <c r="M357" s="50"/>
+      <c r="N357" s="50"/>
+      <c r="O357" s="50"/>
+      <c r="P357" s="50"/>
+      <c r="Q357" s="50"/>
+      <c r="R357" s="50"/>
+      <c r="S357" s="50"/>
+      <c r="T357" s="50"/>
+      <c r="U357" s="50"/>
+      <c r="V357" s="50"/>
+      <c r="W357" s="50"/>
+      <c r="X357" s="50"/>
+      <c r="Y357" s="50"/>
+      <c r="Z357" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA357" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB357" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC357" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD357" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE357" s="50"/>
+      <c r="AF357" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG357" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH357" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI357" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ357" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK357" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL357" s="50"/>
+      <c r="AM357" s="50"/>
+      <c r="AN357" s="50"/>
+      <c r="AO357" s="50"/>
+      <c r="AP357" s="50"/>
+      <c r="AQ357" s="50"/>
+      <c r="AR357" s="50"/>
+      <c r="AS357" s="50"/>
+      <c r="AT357" s="50"/>
+      <c r="AU357" s="50"/>
+      <c r="AV357" s="50"/>
+      <c r="AW357" s="50"/>
+      <c r="AX357" s="50"/>
+      <c r="AY357" s="50"/>
+      <c r="AZ357" s="50"/>
     </row>
     <row r="358" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A358" s="50">
         <v>70</v>
       </c>
-      <c r="B358" s="50"/>
-      <c r="C358" s="50"/>
-      <c r="D358" s="50" t="s">
-        <v>999</v>
-      </c>
-      <c r="E358" s="50"/>
-      <c r="F358" s="50"/>
-      <c r="G358" s="50"/>
-      <c r="H358" s="50"/>
-      <c r="I358" s="50" t="s">
-        <v>31</v>
-      </c>
-      <c r="J358" s="50"/>
-      <c r="K358" s="50" t="s">
-        <v>248</v>
-      </c>
-      <c r="L358" s="50" t="s">
-        <v>291</v>
-      </c>
-      <c r="M358" s="50"/>
-      <c r="N358" s="50"/>
-      <c r="O358" s="50"/>
-      <c r="P358" s="50"/>
-      <c r="Q358" s="50"/>
-      <c r="R358" s="50"/>
-      <c r="S358" s="50"/>
-      <c r="T358" s="50"/>
-      <c r="U358" s="50"/>
-      <c r="V358" s="50"/>
-      <c r="W358" s="50"/>
-      <c r="X358" s="50"/>
-      <c r="Y358" s="50"/>
-      <c r="Z358" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA358" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB358" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC358" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AD358" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AE358" s="50"/>
-      <c r="AF358" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG358" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AH358" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI358" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AJ358" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AK358" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL358" s="50"/>
-      <c r="AM358" s="50"/>
-      <c r="AN358" s="50"/>
-      <c r="AO358" s="50"/>
-      <c r="AP358" s="50"/>
-      <c r="AQ358" s="50"/>
-      <c r="AR358" s="50"/>
-      <c r="AS358" s="50"/>
-      <c r="AT358" s="50"/>
-      <c r="AU358" s="50"/>
-      <c r="AV358" s="50"/>
-      <c r="AW358" s="50"/>
-      <c r="AX358" s="50"/>
-      <c r="AY358" s="50"/>
-      <c r="AZ358" s="50"/>
+      <c r="B358" s="25"/>
+      <c r="C358" s="25"/>
+      <c r="D358" s="25" t="s">
+        <v>345</v>
+      </c>
+      <c r="E358" s="37" t="s">
+        <v>2068</v>
+      </c>
+      <c r="F358" s="25" t="s">
+        <v>994</v>
+      </c>
+      <c r="G358" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="H358" s="25"/>
+      <c r="I358" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="J358" s="25"/>
+      <c r="K358" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L358" s="25"/>
+      <c r="M358" s="25"/>
+      <c r="N358" s="25"/>
+      <c r="O358" s="25"/>
+      <c r="P358" s="25"/>
+      <c r="Q358" s="25"/>
+      <c r="R358" s="25"/>
+      <c r="S358" s="25"/>
+      <c r="T358" s="25"/>
+      <c r="U358" s="25"/>
+      <c r="V358" s="25"/>
+      <c r="W358" s="25"/>
+      <c r="X358" s="25" t="s">
+        <v>1648</v>
+      </c>
+      <c r="Z358" s="25"/>
+      <c r="AA358" s="25"/>
+      <c r="AB358" s="25"/>
+      <c r="AC358" s="25"/>
+      <c r="AD358" s="25"/>
+      <c r="AE358" s="25"/>
+      <c r="AF358" s="25"/>
+      <c r="AG358" s="25"/>
+      <c r="AH358" s="25"/>
+      <c r="AI358" s="25"/>
+      <c r="AJ358" s="25"/>
+      <c r="AK358" s="25"/>
+      <c r="AM358" s="25"/>
+      <c r="AN358" s="25" t="s">
+        <v>344</v>
+      </c>
+      <c r="AO358" s="25"/>
+      <c r="AP358" s="25" t="s">
+        <v>344</v>
+      </c>
+      <c r="AQ358" s="25"/>
+      <c r="AR358" s="25"/>
+      <c r="AS358" s="25"/>
+      <c r="AT358" s="25"/>
+      <c r="AU358" s="25"/>
+      <c r="AV358" s="25"/>
+      <c r="AW358" s="25"/>
+      <c r="AX358" s="25"/>
+      <c r="AZ358" s="26"/>
     </row>
     <row r="359" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A359" s="50">
         <v>70</v>
       </c>
-      <c r="B359" s="25"/>
-      <c r="C359" s="25"/>
-      <c r="D359" s="25" t="s">
-        <v>1000</v>
-      </c>
-      <c r="E359" s="37" t="s">
-        <v>2071</v>
-      </c>
-      <c r="F359" s="25" t="s">
-        <v>1001</v>
-      </c>
-      <c r="G359" s="25" t="s">
-        <v>997</v>
-      </c>
-      <c r="H359" s="25"/>
-      <c r="I359" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="J359" s="25"/>
-      <c r="K359" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="L359" s="25"/>
-      <c r="M359" s="25"/>
-      <c r="N359" s="25"/>
-      <c r="O359" s="25"/>
-      <c r="P359" s="25"/>
-      <c r="Q359" s="25"/>
-      <c r="R359" s="25"/>
-      <c r="S359" s="25"/>
-      <c r="T359" s="25"/>
-      <c r="U359" s="25"/>
-      <c r="V359" s="25"/>
-      <c r="W359" s="25"/>
-      <c r="X359" s="25" t="s">
-        <v>1653</v>
-      </c>
-      <c r="Z359" s="25"/>
-      <c r="AA359" s="25"/>
-      <c r="AB359" s="25"/>
-      <c r="AC359" s="25"/>
-      <c r="AD359" s="25"/>
-      <c r="AE359" s="25"/>
-      <c r="AF359" s="25"/>
-      <c r="AG359" s="25"/>
-      <c r="AH359" s="25"/>
-      <c r="AI359" s="25"/>
-      <c r="AJ359" s="25"/>
-      <c r="AK359" s="25"/>
-      <c r="AM359" s="25"/>
-      <c r="AN359" s="25" t="s">
-        <v>1002</v>
-      </c>
-      <c r="AO359" s="25"/>
-      <c r="AP359" s="25" t="s">
-        <v>1002</v>
-      </c>
-      <c r="AQ359" s="25"/>
-      <c r="AR359" s="25"/>
-      <c r="AS359" s="25"/>
-      <c r="AT359" s="25"/>
-      <c r="AU359" s="25"/>
-      <c r="AV359" s="25"/>
-      <c r="AW359" s="25"/>
-      <c r="AX359" s="25"/>
-      <c r="AZ359" s="26"/>
+      <c r="B359" s="50"/>
+      <c r="C359" s="50"/>
+      <c r="D359" s="50" t="s">
+        <v>261</v>
+      </c>
+      <c r="E359" s="50"/>
+      <c r="F359" s="50"/>
+      <c r="G359" s="50"/>
+      <c r="H359" s="50"/>
+      <c r="I359" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="J359" s="50"/>
+      <c r="K359" s="50" t="s">
+        <v>248</v>
+      </c>
+      <c r="L359" s="50" t="s">
+        <v>290</v>
+      </c>
+      <c r="M359" s="50"/>
+      <c r="N359" s="50"/>
+      <c r="O359" s="50"/>
+      <c r="P359" s="50"/>
+      <c r="Q359" s="50"/>
+      <c r="R359" s="50"/>
+      <c r="S359" s="50"/>
+      <c r="T359" s="50"/>
+      <c r="U359" s="50"/>
+      <c r="V359" s="50"/>
+      <c r="W359" s="50"/>
+      <c r="X359" s="50"/>
+      <c r="Y359" s="50"/>
+      <c r="Z359" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA359" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB359" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC359" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD359" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE359" s="50"/>
+      <c r="AF359" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG359" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH359" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI359" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ359" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK359" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL359" s="50"/>
+      <c r="AM359" s="50"/>
+      <c r="AN359" s="50"/>
+      <c r="AO359" s="50"/>
+      <c r="AP359" s="50"/>
+      <c r="AQ359" s="50"/>
+      <c r="AR359" s="50"/>
+      <c r="AS359" s="50"/>
+      <c r="AT359" s="50"/>
+      <c r="AU359" s="50"/>
+      <c r="AV359" s="50"/>
+      <c r="AW359" s="50"/>
+      <c r="AX359" s="50"/>
+      <c r="AY359" s="50"/>
+      <c r="AZ359" s="50"/>
     </row>
     <row r="360" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A360" s="50">
         <v>70</v>
       </c>
-      <c r="B360" s="50"/>
-      <c r="C360" s="50"/>
-      <c r="D360" s="50" t="s">
-        <v>1003</v>
-      </c>
-      <c r="E360" s="50"/>
-      <c r="F360" s="50"/>
-      <c r="G360" s="50"/>
-      <c r="H360" s="50"/>
-      <c r="I360" s="50" t="s">
-        <v>31</v>
-      </c>
-      <c r="J360" s="50"/>
-      <c r="K360" s="50" t="s">
-        <v>248</v>
-      </c>
-      <c r="L360" s="50" t="s">
-        <v>291</v>
-      </c>
-      <c r="M360" s="50"/>
-      <c r="N360" s="50"/>
-      <c r="O360" s="50"/>
-      <c r="P360" s="50"/>
-      <c r="Q360" s="50"/>
-      <c r="R360" s="50"/>
-      <c r="S360" s="50"/>
-      <c r="T360" s="50"/>
-      <c r="U360" s="50"/>
-      <c r="V360" s="50"/>
-      <c r="W360" s="50"/>
-      <c r="X360" s="50"/>
-      <c r="Y360" s="50"/>
-      <c r="Z360" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA360" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB360" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC360" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AD360" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AE360" s="50"/>
-      <c r="AF360" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG360" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AH360" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI360" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AJ360" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AK360" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL360" s="50"/>
-      <c r="AM360" s="50"/>
-      <c r="AN360" s="50"/>
-      <c r="AO360" s="50"/>
-      <c r="AP360" s="50"/>
-      <c r="AQ360" s="50"/>
-      <c r="AR360" s="50"/>
-      <c r="AS360" s="50"/>
-      <c r="AT360" s="50"/>
-      <c r="AU360" s="50"/>
-      <c r="AV360" s="50"/>
-      <c r="AW360" s="50"/>
-      <c r="AX360" s="50"/>
-      <c r="AY360" s="50"/>
-      <c r="AZ360" s="50"/>
+      <c r="B360" s="25"/>
+      <c r="C360" s="25"/>
+      <c r="D360" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="E360" s="37" t="s">
+        <v>2069</v>
+      </c>
+      <c r="F360" s="25" t="s">
+        <v>259</v>
+      </c>
+      <c r="G360" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="H360" s="25"/>
+      <c r="I360" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="J360" s="25"/>
+      <c r="K360" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L360" s="25"/>
+      <c r="M360" s="25"/>
+      <c r="N360" s="25"/>
+      <c r="O360" s="25"/>
+      <c r="P360" s="25"/>
+      <c r="Q360" s="25"/>
+      <c r="R360" s="25"/>
+      <c r="S360" s="25"/>
+      <c r="T360" s="25"/>
+      <c r="U360" s="25"/>
+      <c r="V360" s="25"/>
+      <c r="W360" s="25"/>
+      <c r="X360" s="25" t="s">
+        <v>1653</v>
+      </c>
+      <c r="Z360" s="25"/>
+      <c r="AA360" s="25"/>
+      <c r="AB360" s="25"/>
+      <c r="AC360" s="25"/>
+      <c r="AD360" s="25"/>
+      <c r="AE360" s="25"/>
+      <c r="AF360" s="25"/>
+      <c r="AG360" s="25"/>
+      <c r="AH360" s="25"/>
+      <c r="AI360" s="25"/>
+      <c r="AJ360" s="25"/>
+      <c r="AK360" s="25"/>
+      <c r="AM360" s="25"/>
+      <c r="AN360" s="25" t="s">
+        <v>263</v>
+      </c>
+      <c r="AO360" s="25"/>
+      <c r="AP360" s="25" t="s">
+        <v>263</v>
+      </c>
+      <c r="AQ360" s="25"/>
+      <c r="AR360" s="25"/>
+      <c r="AS360" s="25"/>
+      <c r="AT360" s="25"/>
+      <c r="AU360" s="25"/>
+      <c r="AV360" s="25"/>
+      <c r="AW360" s="25"/>
+      <c r="AX360" s="25"/>
+      <c r="AZ360" s="26"/>
     </row>
     <row r="361" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A361" s="50">
         <v>70</v>
       </c>
-      <c r="B361" s="25"/>
-      <c r="C361" s="25"/>
-      <c r="D361" s="25" t="s">
-        <v>1004</v>
-      </c>
-      <c r="E361" s="37" t="s">
-        <v>2072</v>
-      </c>
-      <c r="F361" s="25" t="s">
-        <v>264</v>
-      </c>
-      <c r="G361" s="25" t="s">
-        <v>997</v>
-      </c>
-      <c r="H361" s="25"/>
-      <c r="I361" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="J361" s="25"/>
-      <c r="K361" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="L361" s="25"/>
-      <c r="M361" s="25"/>
-      <c r="N361" s="25"/>
-      <c r="O361" s="25"/>
-      <c r="P361" s="25"/>
-      <c r="Q361" s="25"/>
-      <c r="R361" s="25"/>
-      <c r="S361" s="25"/>
-      <c r="T361" s="25"/>
-      <c r="U361" s="25"/>
-      <c r="V361" s="25"/>
-      <c r="W361" s="25"/>
-      <c r="X361" s="25" t="s">
-        <v>1653</v>
-      </c>
-      <c r="Z361" s="25"/>
-      <c r="AA361" s="25"/>
-      <c r="AB361" s="25"/>
-      <c r="AC361" s="25"/>
-      <c r="AD361" s="25"/>
-      <c r="AE361" s="25"/>
-      <c r="AF361" s="25"/>
-      <c r="AG361" s="25"/>
-      <c r="AH361" s="25"/>
-      <c r="AI361" s="25"/>
-      <c r="AJ361" s="25"/>
-      <c r="AK361" s="25"/>
-      <c r="AM361" s="25"/>
-      <c r="AN361" s="25" t="s">
-        <v>1005</v>
-      </c>
-      <c r="AO361" s="25"/>
-      <c r="AP361" s="25" t="s">
-        <v>1005</v>
-      </c>
-      <c r="AQ361" s="25"/>
-      <c r="AR361" s="25"/>
-      <c r="AS361" s="25"/>
-      <c r="AT361" s="25"/>
-      <c r="AU361" s="25"/>
-      <c r="AV361" s="25"/>
-      <c r="AW361" s="25"/>
-      <c r="AX361" s="25"/>
-      <c r="AZ361" s="26"/>
+      <c r="B361" s="50"/>
+      <c r="C361" s="50"/>
+      <c r="D361" s="50" t="s">
+        <v>995</v>
+      </c>
+      <c r="E361" s="50"/>
+      <c r="F361" s="50"/>
+      <c r="G361" s="50"/>
+      <c r="H361" s="50"/>
+      <c r="I361" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="J361" s="50"/>
+      <c r="K361" s="50" t="s">
+        <v>248</v>
+      </c>
+      <c r="L361" s="50" t="s">
+        <v>291</v>
+      </c>
+      <c r="M361" s="50"/>
+      <c r="N361" s="50"/>
+      <c r="O361" s="50"/>
+      <c r="P361" s="50"/>
+      <c r="Q361" s="50"/>
+      <c r="R361" s="50"/>
+      <c r="S361" s="50"/>
+      <c r="T361" s="50"/>
+      <c r="U361" s="50"/>
+      <c r="V361" s="50"/>
+      <c r="W361" s="50"/>
+      <c r="X361" s="50"/>
+      <c r="Y361" s="50"/>
+      <c r="Z361" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA361" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB361" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC361" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD361" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE361" s="50"/>
+      <c r="AF361" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG361" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH361" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI361" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ361" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK361" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL361" s="50"/>
+      <c r="AM361" s="50"/>
+      <c r="AN361" s="50"/>
+      <c r="AO361" s="50"/>
+      <c r="AP361" s="50"/>
+      <c r="AQ361" s="50"/>
+      <c r="AR361" s="50"/>
+      <c r="AS361" s="50"/>
+      <c r="AT361" s="50"/>
+      <c r="AU361" s="50"/>
+      <c r="AV361" s="50"/>
+      <c r="AW361" s="50"/>
+      <c r="AX361" s="50"/>
+      <c r="AY361" s="50"/>
+      <c r="AZ361" s="50"/>
     </row>
     <row r="362" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A362" s="50">
         <v>70</v>
       </c>
-      <c r="B362" s="50"/>
-      <c r="C362" s="50"/>
-      <c r="D362" s="50" t="s">
-        <v>1006</v>
-      </c>
-      <c r="E362" s="50"/>
-      <c r="F362" s="50"/>
-      <c r="G362" s="50"/>
-      <c r="H362" s="50"/>
-      <c r="I362" s="50" t="s">
-        <v>31</v>
-      </c>
-      <c r="J362" s="50"/>
-      <c r="K362" s="50" t="s">
-        <v>248</v>
-      </c>
-      <c r="L362" s="50" t="s">
-        <v>290</v>
-      </c>
-      <c r="M362" s="50"/>
-      <c r="N362" s="50"/>
-      <c r="O362" s="50"/>
-      <c r="P362" s="50"/>
-      <c r="Q362" s="50"/>
-      <c r="R362" s="50"/>
-      <c r="S362" s="50"/>
-      <c r="T362" s="50"/>
-      <c r="U362" s="50"/>
-      <c r="V362" s="50"/>
-      <c r="W362" s="50"/>
-      <c r="X362" s="50"/>
-      <c r="Y362" s="50"/>
-      <c r="Z362" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA362" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB362" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC362" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AD362" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AE362" s="50"/>
-      <c r="AF362" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG362" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AH362" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI362" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AJ362" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AK362" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL362" s="50"/>
-      <c r="AM362" s="50"/>
-      <c r="AN362" s="50"/>
-      <c r="AO362" s="50"/>
-      <c r="AP362" s="50"/>
-      <c r="AQ362" s="50"/>
-      <c r="AR362" s="50"/>
-      <c r="AS362" s="50"/>
-      <c r="AT362" s="50"/>
-      <c r="AU362" s="50"/>
-      <c r="AV362" s="50"/>
-      <c r="AW362" s="50"/>
-      <c r="AX362" s="50"/>
-      <c r="AY362" s="50"/>
-      <c r="AZ362" s="50"/>
+      <c r="B362" s="25"/>
+      <c r="C362" s="25"/>
+      <c r="D362" s="25" t="s">
+        <v>996</v>
+      </c>
+      <c r="E362" s="37" t="s">
+        <v>2070</v>
+      </c>
+      <c r="F362" s="25" t="s">
+        <v>260</v>
+      </c>
+      <c r="G362" s="25" t="s">
+        <v>997</v>
+      </c>
+      <c r="H362" s="25"/>
+      <c r="I362" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="J362" s="25"/>
+      <c r="K362" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L362" s="25"/>
+      <c r="M362" s="25"/>
+      <c r="N362" s="25"/>
+      <c r="O362" s="25"/>
+      <c r="P362" s="25"/>
+      <c r="Q362" s="25"/>
+      <c r="R362" s="25"/>
+      <c r="S362" s="25"/>
+      <c r="T362" s="25"/>
+      <c r="U362" s="25"/>
+      <c r="V362" s="25"/>
+      <c r="W362" s="25"/>
+      <c r="X362" s="25" t="s">
+        <v>1653</v>
+      </c>
+      <c r="Z362" s="25"/>
+      <c r="AA362" s="25"/>
+      <c r="AB362" s="25"/>
+      <c r="AC362" s="25"/>
+      <c r="AD362" s="25"/>
+      <c r="AE362" s="25"/>
+      <c r="AF362" s="25"/>
+      <c r="AG362" s="25"/>
+      <c r="AH362" s="25"/>
+      <c r="AI362" s="25"/>
+      <c r="AJ362" s="25"/>
+      <c r="AK362" s="25"/>
+      <c r="AM362" s="25"/>
+      <c r="AN362" s="25" t="s">
+        <v>998</v>
+      </c>
+      <c r="AO362" s="25"/>
+      <c r="AP362" s="25" t="s">
+        <v>998</v>
+      </c>
+      <c r="AQ362" s="25"/>
+      <c r="AR362" s="25"/>
+      <c r="AS362" s="25"/>
+      <c r="AT362" s="25"/>
+      <c r="AU362" s="25"/>
+      <c r="AV362" s="25"/>
+      <c r="AW362" s="25"/>
+      <c r="AX362" s="25"/>
+      <c r="AZ362" s="26"/>
     </row>
     <row r="363" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A363" s="50">
         <v>70</v>
       </c>
-      <c r="B363" s="25"/>
-      <c r="C363" s="25"/>
-      <c r="D363" s="25" t="s">
-        <v>1007</v>
-      </c>
-      <c r="E363" s="37" t="s">
-        <v>2073</v>
-      </c>
-      <c r="F363" s="25" t="s">
-        <v>265</v>
-      </c>
-      <c r="G363" s="25" t="s">
-        <v>997</v>
-      </c>
-      <c r="H363" s="25"/>
-      <c r="I363" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="J363" s="25"/>
-      <c r="K363" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="L363" s="25"/>
-      <c r="M363" s="25"/>
-      <c r="N363" s="25"/>
-      <c r="O363" s="25"/>
-      <c r="P363" s="25"/>
-      <c r="Q363" s="25"/>
-      <c r="R363" s="25"/>
-      <c r="S363" s="25"/>
-      <c r="T363" s="25"/>
-      <c r="U363" s="25"/>
-      <c r="V363" s="25"/>
-      <c r="W363" s="25"/>
-      <c r="X363" s="25" t="s">
-        <v>1649</v>
-      </c>
-      <c r="Z363" s="25"/>
-      <c r="AA363" s="25"/>
-      <c r="AB363" s="25"/>
-      <c r="AC363" s="25"/>
-      <c r="AD363" s="25"/>
-      <c r="AE363" s="25"/>
-      <c r="AF363" s="25"/>
-      <c r="AG363" s="25"/>
-      <c r="AH363" s="25"/>
-      <c r="AI363" s="25"/>
-      <c r="AJ363" s="25"/>
-      <c r="AK363" s="25"/>
-      <c r="AM363" s="25"/>
-      <c r="AN363" s="25" t="s">
-        <v>1008</v>
-      </c>
-      <c r="AO363" s="25"/>
-      <c r="AP363" s="25" t="s">
-        <v>1008</v>
-      </c>
-      <c r="AQ363" s="25"/>
-      <c r="AR363" s="25"/>
-      <c r="AS363" s="25"/>
-      <c r="AT363" s="25"/>
-      <c r="AU363" s="25"/>
-      <c r="AV363" s="25"/>
-      <c r="AW363" s="25"/>
-      <c r="AX363" s="25"/>
-      <c r="AZ363" s="26"/>
+      <c r="B363" s="50"/>
+      <c r="C363" s="50"/>
+      <c r="D363" s="50" t="s">
+        <v>999</v>
+      </c>
+      <c r="E363" s="50"/>
+      <c r="F363" s="50"/>
+      <c r="G363" s="50"/>
+      <c r="H363" s="50"/>
+      <c r="I363" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="J363" s="50"/>
+      <c r="K363" s="50" t="s">
+        <v>248</v>
+      </c>
+      <c r="L363" s="50" t="s">
+        <v>291</v>
+      </c>
+      <c r="M363" s="50"/>
+      <c r="N363" s="50"/>
+      <c r="O363" s="50"/>
+      <c r="P363" s="50"/>
+      <c r="Q363" s="50"/>
+      <c r="R363" s="50"/>
+      <c r="S363" s="50"/>
+      <c r="T363" s="50"/>
+      <c r="U363" s="50"/>
+      <c r="V363" s="50"/>
+      <c r="W363" s="50"/>
+      <c r="X363" s="50"/>
+      <c r="Y363" s="50"/>
+      <c r="Z363" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA363" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB363" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC363" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD363" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE363" s="50"/>
+      <c r="AF363" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG363" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH363" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI363" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ363" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK363" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL363" s="50"/>
+      <c r="AM363" s="50"/>
+      <c r="AN363" s="50"/>
+      <c r="AO363" s="50"/>
+      <c r="AP363" s="50"/>
+      <c r="AQ363" s="50"/>
+      <c r="AR363" s="50"/>
+      <c r="AS363" s="50"/>
+      <c r="AT363" s="50"/>
+      <c r="AU363" s="50"/>
+      <c r="AV363" s="50"/>
+      <c r="AW363" s="50"/>
+      <c r="AX363" s="50"/>
+      <c r="AY363" s="50"/>
+      <c r="AZ363" s="50"/>
     </row>
     <row r="364" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A364" s="50">
         <v>70</v>
       </c>
-      <c r="B364" s="50"/>
-      <c r="C364" s="50"/>
-      <c r="D364" s="50" t="s">
-        <v>1009</v>
-      </c>
-      <c r="E364" s="50"/>
-      <c r="F364" s="50"/>
-      <c r="G364" s="50"/>
-      <c r="H364" s="50"/>
-      <c r="I364" s="50" t="s">
-        <v>31</v>
-      </c>
-      <c r="J364" s="50"/>
-      <c r="K364" s="50" t="s">
-        <v>248</v>
-      </c>
-      <c r="L364" s="50" t="s">
-        <v>291</v>
-      </c>
-      <c r="M364" s="50"/>
-      <c r="N364" s="50"/>
-      <c r="O364" s="50"/>
-      <c r="P364" s="50"/>
-      <c r="Q364" s="50"/>
-      <c r="R364" s="50"/>
-      <c r="S364" s="50"/>
-      <c r="T364" s="50"/>
-      <c r="U364" s="50"/>
-      <c r="V364" s="50"/>
-      <c r="W364" s="50"/>
-      <c r="X364" s="50"/>
-      <c r="Y364" s="50"/>
-      <c r="Z364" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA364" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB364" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC364" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AD364" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AE364" s="50"/>
-      <c r="AF364" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG364" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AH364" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI364" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AJ364" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AK364" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL364" s="50"/>
-      <c r="AM364" s="50"/>
-      <c r="AN364" s="50"/>
-      <c r="AO364" s="50"/>
-      <c r="AP364" s="50"/>
-      <c r="AQ364" s="50"/>
-      <c r="AR364" s="50"/>
-      <c r="AS364" s="50"/>
-      <c r="AT364" s="50"/>
-      <c r="AU364" s="50"/>
-      <c r="AV364" s="50"/>
-      <c r="AW364" s="50"/>
-      <c r="AX364" s="50"/>
-      <c r="AY364" s="50"/>
-      <c r="AZ364" s="50"/>
+      <c r="B364" s="25"/>
+      <c r="C364" s="25"/>
+      <c r="D364" s="25" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E364" s="37" t="s">
+        <v>2071</v>
+      </c>
+      <c r="F364" s="25" t="s">
+        <v>1001</v>
+      </c>
+      <c r="G364" s="25" t="s">
+        <v>997</v>
+      </c>
+      <c r="H364" s="25"/>
+      <c r="I364" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="J364" s="25"/>
+      <c r="K364" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L364" s="25"/>
+      <c r="M364" s="25"/>
+      <c r="N364" s="25"/>
+      <c r="O364" s="25"/>
+      <c r="P364" s="25"/>
+      <c r="Q364" s="25"/>
+      <c r="R364" s="25"/>
+      <c r="S364" s="25"/>
+      <c r="T364" s="25"/>
+      <c r="U364" s="25"/>
+      <c r="V364" s="25"/>
+      <c r="W364" s="25"/>
+      <c r="X364" s="25" t="s">
+        <v>1653</v>
+      </c>
+      <c r="Z364" s="25"/>
+      <c r="AA364" s="25"/>
+      <c r="AB364" s="25"/>
+      <c r="AC364" s="25"/>
+      <c r="AD364" s="25"/>
+      <c r="AE364" s="25"/>
+      <c r="AF364" s="25"/>
+      <c r="AG364" s="25"/>
+      <c r="AH364" s="25"/>
+      <c r="AI364" s="25"/>
+      <c r="AJ364" s="25"/>
+      <c r="AK364" s="25"/>
+      <c r="AM364" s="25"/>
+      <c r="AN364" s="25" t="s">
+        <v>1002</v>
+      </c>
+      <c r="AO364" s="25"/>
+      <c r="AP364" s="25" t="s">
+        <v>1002</v>
+      </c>
+      <c r="AQ364" s="25"/>
+      <c r="AR364" s="25"/>
+      <c r="AS364" s="25"/>
+      <c r="AT364" s="25"/>
+      <c r="AU364" s="25"/>
+      <c r="AV364" s="25"/>
+      <c r="AW364" s="25"/>
+      <c r="AX364" s="25"/>
+      <c r="AZ364" s="26"/>
     </row>
     <row r="365" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A365" s="50">
         <v>70</v>
       </c>
-      <c r="B365" s="25"/>
-      <c r="C365" s="25"/>
-      <c r="D365" s="25" t="s">
-        <v>1010</v>
-      </c>
-      <c r="E365" s="37" t="s">
-        <v>2074</v>
-      </c>
-      <c r="F365" s="25" t="s">
-        <v>266</v>
-      </c>
-      <c r="G365" s="25" t="s">
-        <v>997</v>
-      </c>
-      <c r="H365" s="25"/>
-      <c r="I365" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="J365" s="25"/>
-      <c r="K365" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="L365" s="25"/>
-      <c r="M365" s="25"/>
-      <c r="N365" s="25"/>
-      <c r="O365" s="25"/>
-      <c r="P365" s="25"/>
-      <c r="Q365" s="25"/>
-      <c r="R365" s="25"/>
-      <c r="S365" s="25"/>
-      <c r="T365" s="25"/>
-      <c r="U365" s="25"/>
-      <c r="V365" s="25"/>
-      <c r="W365" s="25"/>
-      <c r="X365" s="25" t="s">
-        <v>1649</v>
-      </c>
-      <c r="Z365" s="25"/>
-      <c r="AA365" s="25"/>
-      <c r="AB365" s="25"/>
-      <c r="AC365" s="25"/>
-      <c r="AD365" s="25"/>
-      <c r="AE365" s="25"/>
-      <c r="AF365" s="25"/>
-      <c r="AG365" s="25"/>
-      <c r="AH365" s="25"/>
-      <c r="AI365" s="25"/>
-      <c r="AJ365" s="25"/>
-      <c r="AK365" s="25"/>
-      <c r="AM365" s="25"/>
-      <c r="AN365" s="25" t="s">
-        <v>1011</v>
-      </c>
-      <c r="AO365" s="25"/>
-      <c r="AP365" s="25" t="s">
-        <v>1011</v>
-      </c>
-      <c r="AQ365" s="25"/>
-      <c r="AR365" s="25"/>
-      <c r="AS365" s="25"/>
-      <c r="AT365" s="25"/>
-      <c r="AU365" s="25"/>
-      <c r="AV365" s="25"/>
-      <c r="AW365" s="25"/>
-      <c r="AX365" s="25"/>
-      <c r="AZ365" s="26"/>
+      <c r="B365" s="50"/>
+      <c r="C365" s="50"/>
+      <c r="D365" s="50" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E365" s="50"/>
+      <c r="F365" s="50"/>
+      <c r="G365" s="50"/>
+      <c r="H365" s="50"/>
+      <c r="I365" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="J365" s="50"/>
+      <c r="K365" s="50" t="s">
+        <v>248</v>
+      </c>
+      <c r="L365" s="50" t="s">
+        <v>291</v>
+      </c>
+      <c r="M365" s="50"/>
+      <c r="N365" s="50"/>
+      <c r="O365" s="50"/>
+      <c r="P365" s="50"/>
+      <c r="Q365" s="50"/>
+      <c r="R365" s="50"/>
+      <c r="S365" s="50"/>
+      <c r="T365" s="50"/>
+      <c r="U365" s="50"/>
+      <c r="V365" s="50"/>
+      <c r="W365" s="50"/>
+      <c r="X365" s="50"/>
+      <c r="Y365" s="50"/>
+      <c r="Z365" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA365" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB365" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC365" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD365" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE365" s="50"/>
+      <c r="AF365" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG365" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH365" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI365" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ365" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK365" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL365" s="50"/>
+      <c r="AM365" s="50"/>
+      <c r="AN365" s="50"/>
+      <c r="AO365" s="50"/>
+      <c r="AP365" s="50"/>
+      <c r="AQ365" s="50"/>
+      <c r="AR365" s="50"/>
+      <c r="AS365" s="50"/>
+      <c r="AT365" s="50"/>
+      <c r="AU365" s="50"/>
+      <c r="AV365" s="50"/>
+      <c r="AW365" s="50"/>
+      <c r="AX365" s="50"/>
+      <c r="AY365" s="50"/>
+      <c r="AZ365" s="50"/>
     </row>
     <row r="366" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A366" s="50">
         <v>70</v>
       </c>
-      <c r="B366" s="50"/>
-      <c r="C366" s="50"/>
-      <c r="D366" s="50" t="s">
-        <v>1012</v>
-      </c>
-      <c r="E366" s="50"/>
-      <c r="F366" s="50"/>
-      <c r="G366" s="50"/>
-      <c r="H366" s="50"/>
-      <c r="I366" s="50" t="s">
-        <v>31</v>
-      </c>
-      <c r="J366" s="50"/>
-      <c r="K366" s="50" t="s">
-        <v>248</v>
-      </c>
-      <c r="L366" s="50" t="s">
-        <v>291</v>
-      </c>
-      <c r="M366" s="50"/>
-      <c r="N366" s="50"/>
-      <c r="O366" s="50"/>
-      <c r="P366" s="50"/>
-      <c r="Q366" s="50"/>
-      <c r="R366" s="50"/>
-      <c r="S366" s="50"/>
-      <c r="T366" s="50"/>
-      <c r="U366" s="50"/>
-      <c r="V366" s="50"/>
-      <c r="W366" s="50"/>
-      <c r="X366" s="50"/>
-      <c r="Y366" s="50"/>
-      <c r="Z366" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA366" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB366" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC366" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AD366" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AE366" s="50"/>
-      <c r="AF366" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG366" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AH366" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI366" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AJ366" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AK366" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL366" s="50"/>
-      <c r="AM366" s="50"/>
-      <c r="AN366" s="50"/>
-      <c r="AO366" s="50"/>
-      <c r="AP366" s="50"/>
-      <c r="AQ366" s="50"/>
-      <c r="AR366" s="50"/>
-      <c r="AS366" s="50"/>
-      <c r="AT366" s="50"/>
-      <c r="AU366" s="50"/>
-      <c r="AV366" s="50"/>
-      <c r="AW366" s="50"/>
-      <c r="AX366" s="50"/>
-      <c r="AY366" s="50"/>
-      <c r="AZ366" s="50"/>
+      <c r="B366" s="25"/>
+      <c r="C366" s="25"/>
+      <c r="D366" s="25" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E366" s="37" t="s">
+        <v>2072</v>
+      </c>
+      <c r="F366" s="25" t="s">
+        <v>264</v>
+      </c>
+      <c r="G366" s="25" t="s">
+        <v>997</v>
+      </c>
+      <c r="H366" s="25"/>
+      <c r="I366" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="J366" s="25"/>
+      <c r="K366" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L366" s="25"/>
+      <c r="M366" s="25"/>
+      <c r="N366" s="25"/>
+      <c r="O366" s="25"/>
+      <c r="P366" s="25"/>
+      <c r="Q366" s="25"/>
+      <c r="R366" s="25"/>
+      <c r="S366" s="25"/>
+      <c r="T366" s="25"/>
+      <c r="U366" s="25"/>
+      <c r="V366" s="25"/>
+      <c r="W366" s="25"/>
+      <c r="X366" s="25" t="s">
+        <v>1653</v>
+      </c>
+      <c r="Z366" s="25"/>
+      <c r="AA366" s="25"/>
+      <c r="AB366" s="25"/>
+      <c r="AC366" s="25"/>
+      <c r="AD366" s="25"/>
+      <c r="AE366" s="25"/>
+      <c r="AF366" s="25"/>
+      <c r="AG366" s="25"/>
+      <c r="AH366" s="25"/>
+      <c r="AI366" s="25"/>
+      <c r="AJ366" s="25"/>
+      <c r="AK366" s="25"/>
+      <c r="AM366" s="25"/>
+      <c r="AN366" s="25" t="s">
+        <v>1005</v>
+      </c>
+      <c r="AO366" s="25"/>
+      <c r="AP366" s="25" t="s">
+        <v>1005</v>
+      </c>
+      <c r="AQ366" s="25"/>
+      <c r="AR366" s="25"/>
+      <c r="AS366" s="25"/>
+      <c r="AT366" s="25"/>
+      <c r="AU366" s="25"/>
+      <c r="AV366" s="25"/>
+      <c r="AW366" s="25"/>
+      <c r="AX366" s="25"/>
+      <c r="AZ366" s="26"/>
     </row>
     <row r="367" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A367" s="50">
         <v>70</v>
       </c>
-      <c r="B367" s="25"/>
-      <c r="C367" s="25"/>
-      <c r="D367" s="25" t="s">
-        <v>1013</v>
-      </c>
-      <c r="E367" s="37" t="s">
-        <v>2075</v>
-      </c>
-      <c r="F367" s="25" t="s">
-        <v>268</v>
-      </c>
-      <c r="G367" s="25" t="s">
-        <v>997</v>
-      </c>
-      <c r="H367" s="25"/>
-      <c r="I367" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="J367" s="25"/>
-      <c r="K367" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="L367" s="25"/>
-      <c r="M367" s="25"/>
-      <c r="N367" s="25"/>
-      <c r="O367" s="25"/>
-      <c r="P367" s="25"/>
-      <c r="Q367" s="25"/>
-      <c r="R367" s="25"/>
-      <c r="S367" s="25"/>
-      <c r="T367" s="25"/>
-      <c r="U367" s="25"/>
-      <c r="V367" s="25"/>
-      <c r="W367" s="25"/>
-      <c r="X367" s="25" t="s">
-        <v>1649</v>
-      </c>
-      <c r="Z367" s="25"/>
-      <c r="AA367" s="25"/>
-      <c r="AB367" s="25"/>
-      <c r="AC367" s="25"/>
-      <c r="AD367" s="25"/>
-      <c r="AE367" s="25"/>
-      <c r="AF367" s="25"/>
-      <c r="AG367" s="25"/>
-      <c r="AH367" s="25"/>
-      <c r="AI367" s="25"/>
-      <c r="AJ367" s="25"/>
-      <c r="AK367" s="25"/>
-      <c r="AM367" s="25"/>
-      <c r="AN367" s="25" t="s">
-        <v>1014</v>
-      </c>
-      <c r="AO367" s="25"/>
-      <c r="AP367" s="25" t="s">
-        <v>1014</v>
-      </c>
-      <c r="AQ367" s="25"/>
-      <c r="AR367" s="25"/>
-      <c r="AS367" s="25"/>
-      <c r="AT367" s="25"/>
-      <c r="AU367" s="25"/>
-      <c r="AV367" s="25"/>
-      <c r="AW367" s="25"/>
-      <c r="AX367" s="25"/>
-      <c r="AZ367" s="26"/>
+      <c r="B367" s="50"/>
+      <c r="C367" s="50"/>
+      <c r="D367" s="50" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E367" s="50"/>
+      <c r="F367" s="50"/>
+      <c r="G367" s="50"/>
+      <c r="H367" s="50"/>
+      <c r="I367" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="J367" s="50"/>
+      <c r="K367" s="50" t="s">
+        <v>248</v>
+      </c>
+      <c r="L367" s="50" t="s">
+        <v>290</v>
+      </c>
+      <c r="M367" s="50"/>
+      <c r="N367" s="50"/>
+      <c r="O367" s="50"/>
+      <c r="P367" s="50"/>
+      <c r="Q367" s="50"/>
+      <c r="R367" s="50"/>
+      <c r="S367" s="50"/>
+      <c r="T367" s="50"/>
+      <c r="U367" s="50"/>
+      <c r="V367" s="50"/>
+      <c r="W367" s="50"/>
+      <c r="X367" s="50"/>
+      <c r="Y367" s="50"/>
+      <c r="Z367" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA367" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB367" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC367" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD367" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE367" s="50"/>
+      <c r="AF367" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG367" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH367" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI367" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ367" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK367" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL367" s="50"/>
+      <c r="AM367" s="50"/>
+      <c r="AN367" s="50"/>
+      <c r="AO367" s="50"/>
+      <c r="AP367" s="50"/>
+      <c r="AQ367" s="50"/>
+      <c r="AR367" s="50"/>
+      <c r="AS367" s="50"/>
+      <c r="AT367" s="50"/>
+      <c r="AU367" s="50"/>
+      <c r="AV367" s="50"/>
+      <c r="AW367" s="50"/>
+      <c r="AX367" s="50"/>
+      <c r="AY367" s="50"/>
+      <c r="AZ367" s="50"/>
     </row>
     <row r="368" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A368" s="50">
         <v>70</v>
       </c>
-      <c r="B368" s="50"/>
-      <c r="C368" s="50"/>
-      <c r="D368" s="50" t="s">
-        <v>1015</v>
-      </c>
-      <c r="E368" s="50"/>
-      <c r="F368" s="50"/>
-      <c r="G368" s="50"/>
-      <c r="H368" s="50"/>
-      <c r="I368" s="50" t="s">
-        <v>31</v>
-      </c>
-      <c r="J368" s="50"/>
-      <c r="K368" s="50" t="s">
-        <v>248</v>
-      </c>
-      <c r="L368" s="50" t="s">
-        <v>291</v>
-      </c>
-      <c r="M368" s="50"/>
-      <c r="N368" s="50"/>
-      <c r="O368" s="50"/>
-      <c r="P368" s="50"/>
-      <c r="Q368" s="50"/>
-      <c r="R368" s="50"/>
-      <c r="S368" s="50"/>
-      <c r="T368" s="50"/>
-      <c r="U368" s="50"/>
-      <c r="V368" s="50"/>
-      <c r="W368" s="50"/>
-      <c r="X368" s="50"/>
-      <c r="Y368" s="50"/>
-      <c r="Z368" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA368" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB368" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC368" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AD368" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AE368" s="50"/>
-      <c r="AF368" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG368" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AH368" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI368" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AJ368" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AK368" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL368" s="50"/>
-      <c r="AM368" s="50"/>
-      <c r="AN368" s="50"/>
-      <c r="AO368" s="50"/>
-      <c r="AP368" s="50"/>
-      <c r="AQ368" s="50"/>
-      <c r="AR368" s="50"/>
-      <c r="AS368" s="50"/>
-      <c r="AT368" s="50"/>
-      <c r="AU368" s="50"/>
-      <c r="AV368" s="50"/>
-      <c r="AW368" s="50"/>
-      <c r="AX368" s="50"/>
-      <c r="AY368" s="50"/>
-      <c r="AZ368" s="50"/>
+      <c r="B368" s="25"/>
+      <c r="C368" s="25"/>
+      <c r="D368" s="25" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E368" s="37" t="s">
+        <v>2073</v>
+      </c>
+      <c r="F368" s="25" t="s">
+        <v>265</v>
+      </c>
+      <c r="G368" s="25" t="s">
+        <v>997</v>
+      </c>
+      <c r="H368" s="25"/>
+      <c r="I368" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="J368" s="25"/>
+      <c r="K368" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L368" s="25"/>
+      <c r="M368" s="25"/>
+      <c r="N368" s="25"/>
+      <c r="O368" s="25"/>
+      <c r="P368" s="25"/>
+      <c r="Q368" s="25"/>
+      <c r="R368" s="25"/>
+      <c r="S368" s="25"/>
+      <c r="T368" s="25"/>
+      <c r="U368" s="25"/>
+      <c r="V368" s="25"/>
+      <c r="W368" s="25"/>
+      <c r="X368" s="25" t="s">
+        <v>1649</v>
+      </c>
+      <c r="Z368" s="25"/>
+      <c r="AA368" s="25"/>
+      <c r="AB368" s="25"/>
+      <c r="AC368" s="25"/>
+      <c r="AD368" s="25"/>
+      <c r="AE368" s="25"/>
+      <c r="AF368" s="25"/>
+      <c r="AG368" s="25"/>
+      <c r="AH368" s="25"/>
+      <c r="AI368" s="25"/>
+      <c r="AJ368" s="25"/>
+      <c r="AK368" s="25"/>
+      <c r="AM368" s="25"/>
+      <c r="AN368" s="25" t="s">
+        <v>1008</v>
+      </c>
+      <c r="AO368" s="25"/>
+      <c r="AP368" s="25" t="s">
+        <v>1008</v>
+      </c>
+      <c r="AQ368" s="25"/>
+      <c r="AR368" s="25"/>
+      <c r="AS368" s="25"/>
+      <c r="AT368" s="25"/>
+      <c r="AU368" s="25"/>
+      <c r="AV368" s="25"/>
+      <c r="AW368" s="25"/>
+      <c r="AX368" s="25"/>
+      <c r="AZ368" s="26"/>
     </row>
     <row r="369" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A369" s="50">
         <v>70</v>
       </c>
-      <c r="B369" s="25"/>
-      <c r="C369" s="25"/>
-      <c r="D369" s="25" t="s">
-        <v>1016</v>
-      </c>
-      <c r="E369" s="37" t="s">
-        <v>2076</v>
-      </c>
-      <c r="F369" s="25" t="s">
-        <v>267</v>
-      </c>
-      <c r="G369" s="25" t="s">
-        <v>997</v>
-      </c>
-      <c r="H369" s="25"/>
-      <c r="I369" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="J369" s="25"/>
-      <c r="K369" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="L369" s="25"/>
-      <c r="M369" s="25"/>
-      <c r="N369" s="25"/>
-      <c r="O369" s="25"/>
-      <c r="P369" s="25"/>
-      <c r="Q369" s="25"/>
-      <c r="R369" s="25"/>
-      <c r="S369" s="25"/>
-      <c r="T369" s="25"/>
-      <c r="U369" s="25"/>
-      <c r="V369" s="25"/>
-      <c r="W369" s="25"/>
-      <c r="X369" s="25" t="s">
-        <v>1649</v>
-      </c>
-      <c r="Z369" s="25"/>
-      <c r="AA369" s="25"/>
-      <c r="AB369" s="25"/>
-      <c r="AC369" s="25"/>
-      <c r="AD369" s="25"/>
-      <c r="AE369" s="25"/>
-      <c r="AF369" s="25"/>
-      <c r="AG369" s="25"/>
-      <c r="AH369" s="25"/>
-      <c r="AI369" s="25"/>
-      <c r="AJ369" s="25"/>
-      <c r="AK369" s="25"/>
-      <c r="AM369" s="25"/>
-      <c r="AN369" s="25" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AO369" s="25"/>
-      <c r="AP369" s="25" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AQ369" s="25"/>
-      <c r="AR369" s="25"/>
-      <c r="AS369" s="25"/>
-      <c r="AT369" s="25"/>
-      <c r="AU369" s="25"/>
-      <c r="AV369" s="25"/>
-      <c r="AW369" s="25"/>
-      <c r="AX369" s="25"/>
-      <c r="AZ369" s="26"/>
+      <c r="B369" s="50"/>
+      <c r="C369" s="50"/>
+      <c r="D369" s="50" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E369" s="50"/>
+      <c r="F369" s="50"/>
+      <c r="G369" s="50"/>
+      <c r="H369" s="50"/>
+      <c r="I369" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="J369" s="50"/>
+      <c r="K369" s="50" t="s">
+        <v>248</v>
+      </c>
+      <c r="L369" s="50" t="s">
+        <v>291</v>
+      </c>
+      <c r="M369" s="50"/>
+      <c r="N369" s="50"/>
+      <c r="O369" s="50"/>
+      <c r="P369" s="50"/>
+      <c r="Q369" s="50"/>
+      <c r="R369" s="50"/>
+      <c r="S369" s="50"/>
+      <c r="T369" s="50"/>
+      <c r="U369" s="50"/>
+      <c r="V369" s="50"/>
+      <c r="W369" s="50"/>
+      <c r="X369" s="50"/>
+      <c r="Y369" s="50"/>
+      <c r="Z369" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA369" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB369" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC369" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD369" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE369" s="50"/>
+      <c r="AF369" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG369" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH369" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI369" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ369" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK369" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL369" s="50"/>
+      <c r="AM369" s="50"/>
+      <c r="AN369" s="50"/>
+      <c r="AO369" s="50"/>
+      <c r="AP369" s="50"/>
+      <c r="AQ369" s="50"/>
+      <c r="AR369" s="50"/>
+      <c r="AS369" s="50"/>
+      <c r="AT369" s="50"/>
+      <c r="AU369" s="50"/>
+      <c r="AV369" s="50"/>
+      <c r="AW369" s="50"/>
+      <c r="AX369" s="50"/>
+      <c r="AY369" s="50"/>
+      <c r="AZ369" s="50"/>
     </row>
     <row r="370" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A370" s="25">
+      <c r="A370" s="50">
         <v>70</v>
       </c>
       <c r="B370" s="25"/>
       <c r="C370" s="25"/>
       <c r="D370" s="25" t="s">
-        <v>943</v>
+        <v>1010</v>
       </c>
       <c r="E370" s="37" t="s">
-        <v>1926</v>
+        <v>2074</v>
       </c>
       <c r="F370" s="25" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="G370" s="25" t="s">
-        <v>137</v>
+        <v>997</v>
       </c>
       <c r="H370" s="25"/>
       <c r="I370" s="25" t="s">
-        <v>1320</v>
+        <v>23</v>
       </c>
       <c r="J370" s="25"/>
       <c r="K370" s="25" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L370" s="25"/>
       <c r="M370" s="25"/>
@@ -42860,56 +42889,32 @@
       <c r="U370" s="25"/>
       <c r="V370" s="25"/>
       <c r="W370" s="25"/>
-      <c r="X370" s="25"/>
-      <c r="Z370" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA370" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB370" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="AC370" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="AD370" s="25" t="s">
-        <v>31</v>
-      </c>
+      <c r="X370" s="25" t="s">
+        <v>1649</v>
+      </c>
+      <c r="Z370" s="25"/>
+      <c r="AA370" s="25"/>
+      <c r="AB370" s="25"/>
+      <c r="AC370" s="25"/>
+      <c r="AD370" s="25"/>
       <c r="AE370" s="25"/>
-      <c r="AF370" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG370" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="AH370" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="AI370" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ370" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AK370" s="25" t="s">
-        <v>25</v>
-      </c>
+      <c r="AF370" s="25"/>
+      <c r="AG370" s="25"/>
+      <c r="AH370" s="25"/>
+      <c r="AI370" s="25"/>
+      <c r="AJ370" s="25"/>
+      <c r="AK370" s="25"/>
       <c r="AM370" s="25"/>
       <c r="AN370" s="25" t="s">
-        <v>943</v>
+        <v>1011</v>
       </c>
       <c r="AO370" s="25"/>
       <c r="AP370" s="25" t="s">
-        <v>943</v>
-      </c>
-      <c r="AQ370" s="25" t="s">
-        <v>943</v>
-      </c>
+        <v>1011</v>
+      </c>
+      <c r="AQ370" s="25"/>
       <c r="AR370" s="25"/>
-      <c r="AS370" s="25" t="s">
-        <v>943</v>
-      </c>
+      <c r="AS370" s="25"/>
       <c r="AT370" s="25"/>
       <c r="AU370" s="25"/>
       <c r="AV370" s="25"/>
@@ -42918,135 +42923,116 @@
       <c r="AZ370" s="26"/>
     </row>
     <row r="371" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A371" s="25">
-        <v>70</v>
-      </c>
-      <c r="B371" s="25"/>
-      <c r="C371" s="25"/>
-      <c r="D371" s="25" t="s">
-        <v>466</v>
-      </c>
-      <c r="E371" s="37" t="s">
-        <v>2077</v>
-      </c>
-      <c r="F371" s="25" t="s">
-        <v>1193</v>
-      </c>
-      <c r="G371" s="25" t="s">
-        <v>1194</v>
-      </c>
-      <c r="H371" s="25"/>
-      <c r="I371" s="25" t="s">
-        <v>1402</v>
-      </c>
-      <c r="J371" s="25"/>
-      <c r="K371" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="L371" s="25"/>
-      <c r="M371" s="25"/>
-      <c r="N371" s="25"/>
-      <c r="O371" s="25"/>
-      <c r="P371" s="25"/>
-      <c r="Q371" s="25" t="s">
-        <v>1403</v>
-      </c>
-      <c r="R371" s="25"/>
-      <c r="S371" s="25" t="s">
-        <v>467</v>
-      </c>
-      <c r="T371" s="25"/>
-      <c r="U371" s="25"/>
-      <c r="V371" s="25" t="s">
-        <v>1217</v>
-      </c>
-      <c r="W371" s="25" t="s">
-        <v>1217</v>
-      </c>
-      <c r="X371" s="25" t="s">
-        <v>1656</v>
-      </c>
-      <c r="Z371" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA371" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB371" s="25" t="s">
+      <c r="A371" s="50">
+        <v>70</v>
+      </c>
+      <c r="B371" s="50"/>
+      <c r="C371" s="50"/>
+      <c r="D371" s="50" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E371" s="50"/>
+      <c r="F371" s="50"/>
+      <c r="G371" s="50"/>
+      <c r="H371" s="50"/>
+      <c r="I371" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="AC371" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="AD371" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="AE371" s="25"/>
-      <c r="AF371" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG371" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="AH371" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="AI371" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ371" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AK371" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM371" s="25"/>
-      <c r="AN371" s="25" t="s">
-        <v>466</v>
-      </c>
-      <c r="AO371" s="25"/>
-      <c r="AP371" s="25" t="s">
-        <v>466</v>
-      </c>
-      <c r="AQ371" s="25" t="s">
-        <v>466</v>
-      </c>
-      <c r="AR371" s="25"/>
-      <c r="AS371" s="25" t="s">
-        <v>466</v>
-      </c>
-      <c r="AT371" s="25"/>
-      <c r="AU371" s="25"/>
-      <c r="AV371" s="25"/>
-      <c r="AW371" s="25"/>
-      <c r="AX371" s="25"/>
-      <c r="AZ371" s="26"/>
+      <c r="J371" s="50"/>
+      <c r="K371" s="50" t="s">
+        <v>248</v>
+      </c>
+      <c r="L371" s="50" t="s">
+        <v>291</v>
+      </c>
+      <c r="M371" s="50"/>
+      <c r="N371" s="50"/>
+      <c r="O371" s="50"/>
+      <c r="P371" s="50"/>
+      <c r="Q371" s="50"/>
+      <c r="R371" s="50"/>
+      <c r="S371" s="50"/>
+      <c r="T371" s="50"/>
+      <c r="U371" s="50"/>
+      <c r="V371" s="50"/>
+      <c r="W371" s="50"/>
+      <c r="X371" s="50"/>
+      <c r="Y371" s="50"/>
+      <c r="Z371" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA371" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB371" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC371" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD371" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE371" s="50"/>
+      <c r="AF371" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG371" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH371" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI371" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ371" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK371" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL371" s="50"/>
+      <c r="AM371" s="50"/>
+      <c r="AN371" s="50"/>
+      <c r="AO371" s="50"/>
+      <c r="AP371" s="50"/>
+      <c r="AQ371" s="50"/>
+      <c r="AR371" s="50"/>
+      <c r="AS371" s="50"/>
+      <c r="AT371" s="50"/>
+      <c r="AU371" s="50"/>
+      <c r="AV371" s="50"/>
+      <c r="AW371" s="50"/>
+      <c r="AX371" s="50"/>
+      <c r="AY371" s="50"/>
+      <c r="AZ371" s="50"/>
     </row>
     <row r="372" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A372" s="25">
+      <c r="A372" s="50">
         <v>70</v>
       </c>
       <c r="B372" s="25"/>
       <c r="C372" s="25"/>
       <c r="D372" s="25" t="s">
-        <v>467</v>
+        <v>1013</v>
       </c>
       <c r="E372" s="37" t="s">
-        <v>2078</v>
+        <v>2075</v>
       </c>
       <c r="F372" s="25" t="s">
-        <v>465</v>
+        <v>268</v>
       </c>
       <c r="G372" s="25" t="s">
-        <v>47</v>
+        <v>997</v>
       </c>
       <c r="H372" s="25"/>
       <c r="I372" s="25" t="s">
-        <v>1404</v>
+        <v>23</v>
       </c>
       <c r="J372" s="25"/>
       <c r="K372" s="25" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L372" s="25"/>
       <c r="M372" s="25"/>
@@ -43061,49 +43047,27 @@
       <c r="V372" s="25"/>
       <c r="W372" s="25"/>
       <c r="X372" s="25" t="s">
-        <v>1656</v>
-      </c>
-      <c r="Z372" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA372" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB372" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC372" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD372" s="25" t="s">
-        <v>25</v>
-      </c>
+        <v>1649</v>
+      </c>
+      <c r="Z372" s="25"/>
+      <c r="AA372" s="25"/>
+      <c r="AB372" s="25"/>
+      <c r="AC372" s="25"/>
+      <c r="AD372" s="25"/>
       <c r="AE372" s="25"/>
-      <c r="AF372" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG372" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AH372" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AI372" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ372" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AK372" s="25" t="s">
-        <v>25</v>
-      </c>
+      <c r="AF372" s="25"/>
+      <c r="AG372" s="25"/>
+      <c r="AH372" s="25"/>
+      <c r="AI372" s="25"/>
+      <c r="AJ372" s="25"/>
+      <c r="AK372" s="25"/>
       <c r="AM372" s="25"/>
       <c r="AN372" s="25" t="s">
-        <v>467</v>
+        <v>1014</v>
       </c>
       <c r="AO372" s="25"/>
       <c r="AP372" s="25" t="s">
-        <v>467</v>
+        <v>1014</v>
       </c>
       <c r="AQ372" s="25"/>
       <c r="AR372" s="25"/>
@@ -43116,203 +43080,187 @@
       <c r="AZ372" s="26"/>
     </row>
     <row r="373" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A373" s="25">
-        <v>70</v>
-      </c>
-      <c r="B373" s="25"/>
-      <c r="C373" s="25"/>
-      <c r="D373" s="25" t="s">
-        <v>1174</v>
-      </c>
-      <c r="E373" s="37" t="s">
-        <v>2079</v>
-      </c>
-      <c r="F373" s="25" t="s">
-        <v>584</v>
-      </c>
-      <c r="G373" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="H373" s="25"/>
-      <c r="I373" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="J373" s="25"/>
-      <c r="K373" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="L373" s="25"/>
-      <c r="M373" s="25"/>
-      <c r="N373" s="25"/>
-      <c r="O373" s="25"/>
-      <c r="P373" s="25"/>
-      <c r="Q373" s="25"/>
-      <c r="R373" s="25"/>
-      <c r="S373" s="25"/>
-      <c r="T373" s="25"/>
-      <c r="U373" s="25"/>
-      <c r="V373" s="25"/>
-      <c r="W373" s="25"/>
-      <c r="X373" s="25" t="s">
-        <v>1535</v>
-      </c>
-      <c r="Z373" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA373" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB373" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC373" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD373" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE373" s="25"/>
-      <c r="AF373" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG373" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH373" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AI373" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ373" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AK373" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM373" s="25"/>
-      <c r="AN373" s="25"/>
-      <c r="AO373" s="25"/>
-      <c r="AP373" s="25"/>
-      <c r="AQ373" s="25" t="s">
-        <v>1174</v>
-      </c>
-      <c r="AR373" s="25"/>
-      <c r="AS373" s="25" t="s">
-        <v>1174</v>
-      </c>
-      <c r="AT373" s="25"/>
-      <c r="AU373" s="25"/>
-      <c r="AV373" s="25"/>
-      <c r="AW373" s="25"/>
-      <c r="AX373" s="25"/>
-      <c r="AZ373" s="26"/>
+      <c r="A373" s="50">
+        <v>70</v>
+      </c>
+      <c r="B373" s="50"/>
+      <c r="C373" s="50"/>
+      <c r="D373" s="50" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E373" s="50"/>
+      <c r="F373" s="50"/>
+      <c r="G373" s="50"/>
+      <c r="H373" s="50"/>
+      <c r="I373" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="J373" s="50"/>
+      <c r="K373" s="50" t="s">
+        <v>248</v>
+      </c>
+      <c r="L373" s="50" t="s">
+        <v>291</v>
+      </c>
+      <c r="M373" s="50"/>
+      <c r="N373" s="50"/>
+      <c r="O373" s="50"/>
+      <c r="P373" s="50"/>
+      <c r="Q373" s="50"/>
+      <c r="R373" s="50"/>
+      <c r="S373" s="50"/>
+      <c r="T373" s="50"/>
+      <c r="U373" s="50"/>
+      <c r="V373" s="50"/>
+      <c r="W373" s="50"/>
+      <c r="X373" s="50"/>
+      <c r="Y373" s="50"/>
+      <c r="Z373" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA373" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB373" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC373" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD373" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE373" s="50"/>
+      <c r="AF373" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG373" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH373" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI373" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ373" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK373" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL373" s="50"/>
+      <c r="AM373" s="50"/>
+      <c r="AN373" s="50"/>
+      <c r="AO373" s="50"/>
+      <c r="AP373" s="50"/>
+      <c r="AQ373" s="50"/>
+      <c r="AR373" s="50"/>
+      <c r="AS373" s="50"/>
+      <c r="AT373" s="50"/>
+      <c r="AU373" s="50"/>
+      <c r="AV373" s="50"/>
+      <c r="AW373" s="50"/>
+      <c r="AX373" s="50"/>
+      <c r="AY373" s="50"/>
+      <c r="AZ373" s="50"/>
     </row>
     <row r="374" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A374" s="50">
         <v>70</v>
       </c>
-      <c r="B374" s="50"/>
-      <c r="C374" s="50"/>
-      <c r="D374" s="50" t="s">
-        <v>1018</v>
-      </c>
-      <c r="E374" s="50"/>
-      <c r="F374" s="50"/>
-      <c r="G374" s="50"/>
-      <c r="H374" s="50"/>
-      <c r="I374" s="50" t="s">
-        <v>31</v>
-      </c>
-      <c r="J374" s="50"/>
-      <c r="K374" s="50" t="s">
-        <v>248</v>
-      </c>
-      <c r="L374" s="50" t="s">
-        <v>1405</v>
-      </c>
-      <c r="M374" s="50"/>
-      <c r="N374" s="50"/>
-      <c r="O374" s="50"/>
-      <c r="P374" s="50"/>
-      <c r="Q374" s="50"/>
-      <c r="R374" s="50"/>
-      <c r="S374" s="50"/>
-      <c r="T374" s="50"/>
-      <c r="U374" s="50"/>
-      <c r="V374" s="50"/>
-      <c r="W374" s="50"/>
-      <c r="X374" s="50"/>
-      <c r="Y374" s="50"/>
-      <c r="Z374" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA374" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB374" s="50" t="s">
-        <v>282</v>
-      </c>
-      <c r="AC374" s="50" t="s">
-        <v>282</v>
-      </c>
-      <c r="AD374" s="50" t="s">
-        <v>282</v>
-      </c>
-      <c r="AE374" s="50"/>
-      <c r="AF374" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG374" s="50" t="s">
-        <v>282</v>
-      </c>
-      <c r="AH374" s="50" t="s">
-        <v>282</v>
-      </c>
-      <c r="AI374" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AJ374" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AK374" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL374" s="50"/>
-      <c r="AM374" s="50"/>
-      <c r="AN374" s="50"/>
-      <c r="AO374" s="50"/>
-      <c r="AP374" s="50"/>
-      <c r="AQ374" s="50"/>
-      <c r="AR374" s="50"/>
-      <c r="AS374" s="50"/>
-      <c r="AT374" s="50"/>
-      <c r="AU374" s="50"/>
-      <c r="AV374" s="50"/>
-      <c r="AW374" s="50"/>
-      <c r="AX374" s="50"/>
-      <c r="AY374" s="50"/>
-      <c r="AZ374" s="50"/>
+      <c r="B374" s="25"/>
+      <c r="C374" s="25"/>
+      <c r="D374" s="25" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E374" s="37" t="s">
+        <v>2076</v>
+      </c>
+      <c r="F374" s="25" t="s">
+        <v>267</v>
+      </c>
+      <c r="G374" s="25" t="s">
+        <v>997</v>
+      </c>
+      <c r="H374" s="25"/>
+      <c r="I374" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="J374" s="25"/>
+      <c r="K374" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L374" s="25"/>
+      <c r="M374" s="25"/>
+      <c r="N374" s="25"/>
+      <c r="O374" s="25"/>
+      <c r="P374" s="25"/>
+      <c r="Q374" s="25"/>
+      <c r="R374" s="25"/>
+      <c r="S374" s="25"/>
+      <c r="T374" s="25"/>
+      <c r="U374" s="25"/>
+      <c r="V374" s="25"/>
+      <c r="W374" s="25"/>
+      <c r="X374" s="25" t="s">
+        <v>1649</v>
+      </c>
+      <c r="Z374" s="25"/>
+      <c r="AA374" s="25"/>
+      <c r="AB374" s="25"/>
+      <c r="AC374" s="25"/>
+      <c r="AD374" s="25"/>
+      <c r="AE374" s="25"/>
+      <c r="AF374" s="25"/>
+      <c r="AG374" s="25"/>
+      <c r="AH374" s="25"/>
+      <c r="AI374" s="25"/>
+      <c r="AJ374" s="25"/>
+      <c r="AK374" s="25"/>
+      <c r="AM374" s="25"/>
+      <c r="AN374" s="25" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AO374" s="25"/>
+      <c r="AP374" s="25" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AQ374" s="25"/>
+      <c r="AR374" s="25"/>
+      <c r="AS374" s="25"/>
+      <c r="AT374" s="25"/>
+      <c r="AU374" s="25"/>
+      <c r="AV374" s="25"/>
+      <c r="AW374" s="25"/>
+      <c r="AX374" s="25"/>
+      <c r="AZ374" s="26"/>
     </row>
     <row r="375" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A375" s="50">
+      <c r="A375" s="25">
         <v>70</v>
       </c>
       <c r="B375" s="25"/>
       <c r="C375" s="25"/>
       <c r="D375" s="25" t="s">
-        <v>1019</v>
-      </c>
-      <c r="E375" s="37"/>
-      <c r="F375" s="25"/>
-      <c r="G375" s="25"/>
+        <v>943</v>
+      </c>
+      <c r="E375" s="37" t="s">
+        <v>1926</v>
+      </c>
+      <c r="F375" s="25" t="s">
+        <v>271</v>
+      </c>
+      <c r="G375" s="25" t="s">
+        <v>137</v>
+      </c>
       <c r="H375" s="25"/>
       <c r="I375" s="25" t="s">
-        <v>23</v>
+        <v>1320</v>
       </c>
       <c r="J375" s="25"/>
       <c r="K375" s="25" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L375" s="25"/>
       <c r="M375" s="25"/>
@@ -43334,23 +43282,23 @@
         <v>25</v>
       </c>
       <c r="AB375" s="25" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="AC375" s="25" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="AD375" s="25" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="AE375" s="25"/>
       <c r="AF375" s="25" t="s">
         <v>25</v>
       </c>
       <c r="AG375" s="25" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="AH375" s="25" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="AI375" s="25" t="s">
         <v>25</v>
@@ -43363,18 +43311,18 @@
       </c>
       <c r="AM375" s="25"/>
       <c r="AN375" s="25" t="s">
-        <v>688</v>
+        <v>943</v>
       </c>
       <c r="AO375" s="25"/>
       <c r="AP375" s="25" t="s">
-        <v>688</v>
+        <v>943</v>
       </c>
       <c r="AQ375" s="25" t="s">
-        <v>688</v>
+        <v>943</v>
       </c>
       <c r="AR375" s="25"/>
       <c r="AS375" s="25" t="s">
-        <v>688</v>
+        <v>943</v>
       </c>
       <c r="AT375" s="25"/>
       <c r="AU375" s="25"/>
@@ -43384,70 +43332,104 @@
       <c r="AZ375" s="26"/>
     </row>
     <row r="376" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A376" s="50">
+      <c r="A376" s="25">
         <v>70</v>
       </c>
       <c r="B376" s="25"/>
       <c r="C376" s="25"/>
       <c r="D376" s="25" t="s">
-        <v>1020</v>
-      </c>
-      <c r="E376" s="37"/>
-      <c r="F376" s="25"/>
-      <c r="G376" s="25"/>
+        <v>466</v>
+      </c>
+      <c r="E376" s="37" t="s">
+        <v>2077</v>
+      </c>
+      <c r="F376" s="25" t="s">
+        <v>1193</v>
+      </c>
+      <c r="G376" s="25" t="s">
+        <v>1194</v>
+      </c>
       <c r="H376" s="25"/>
       <c r="I376" s="25" t="s">
-        <v>23</v>
+        <v>1402</v>
       </c>
       <c r="J376" s="25"/>
       <c r="K376" s="25" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="L376" s="25"/>
       <c r="M376" s="25"/>
       <c r="N376" s="25"/>
       <c r="O376" s="25"/>
       <c r="P376" s="25"/>
-      <c r="Q376" s="25"/>
+      <c r="Q376" s="25" t="s">
+        <v>1403</v>
+      </c>
       <c r="R376" s="25"/>
-      <c r="S376" s="25"/>
+      <c r="S376" s="25" t="s">
+        <v>467</v>
+      </c>
       <c r="T376" s="25"/>
       <c r="U376" s="25"/>
-      <c r="V376" s="25"/>
-      <c r="W376" s="25"/>
-      <c r="X376" s="25"/>
-      <c r="Z376" s="25"/>
-      <c r="AA376" s="25"/>
-      <c r="AB376" s="25"/>
-      <c r="AC376" s="25"/>
-      <c r="AD376" s="25"/>
+      <c r="V376" s="25" t="s">
+        <v>1217</v>
+      </c>
+      <c r="W376" s="25" t="s">
+        <v>1217</v>
+      </c>
+      <c r="X376" s="25" t="s">
+        <v>1656</v>
+      </c>
+      <c r="Z376" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA376" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB376" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC376" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD376" s="25" t="s">
+        <v>31</v>
+      </c>
       <c r="AE376" s="25"/>
-      <c r="AF376" s="25"/>
-      <c r="AG376" s="25"/>
-      <c r="AH376" s="25"/>
-      <c r="AI376" s="25"/>
-      <c r="AJ376" s="25"/>
-      <c r="AK376" s="25"/>
+      <c r="AF376" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG376" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH376" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI376" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ376" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK376" s="25" t="s">
+        <v>25</v>
+      </c>
       <c r="AM376" s="25"/>
       <c r="AN376" s="25" t="s">
-        <v>272</v>
+        <v>466</v>
       </c>
       <c r="AO376" s="25"/>
       <c r="AP376" s="25" t="s">
-        <v>272</v>
+        <v>466</v>
       </c>
       <c r="AQ376" s="25" t="s">
-        <v>272</v>
-      </c>
-      <c r="AR376" s="25" t="s">
-        <v>272</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="AR376" s="25"/>
       <c r="AS376" s="25" t="s">
-        <v>272</v>
-      </c>
-      <c r="AT376" s="25" t="s">
-        <v>272</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="AT376" s="25"/>
       <c r="AU376" s="25"/>
       <c r="AV376" s="25"/>
       <c r="AW376" s="25"/>
@@ -43455,24 +43437,30 @@
       <c r="AZ376" s="26"/>
     </row>
     <row r="377" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A377" s="50">
+      <c r="A377" s="25">
         <v>70</v>
       </c>
       <c r="B377" s="25"/>
       <c r="C377" s="25"/>
       <c r="D377" s="25" t="s">
-        <v>1021</v>
-      </c>
-      <c r="E377" s="37"/>
-      <c r="F377" s="25"/>
-      <c r="G377" s="25"/>
+        <v>467</v>
+      </c>
+      <c r="E377" s="37" t="s">
+        <v>2078</v>
+      </c>
+      <c r="F377" s="25" t="s">
+        <v>465</v>
+      </c>
+      <c r="G377" s="25" t="s">
+        <v>47</v>
+      </c>
       <c r="H377" s="25"/>
       <c r="I377" s="25" t="s">
-        <v>23</v>
+        <v>1404</v>
       </c>
       <c r="J377" s="25"/>
       <c r="K377" s="25" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L377" s="25"/>
       <c r="M377" s="25"/>
@@ -43486,7 +43474,9 @@
       <c r="U377" s="25"/>
       <c r="V377" s="25"/>
       <c r="W377" s="25"/>
-      <c r="X377" s="25"/>
+      <c r="X377" s="25" t="s">
+        <v>1656</v>
+      </c>
       <c r="Z377" s="25" t="s">
         <v>25</v>
       </c>
@@ -43494,23 +43484,23 @@
         <v>25</v>
       </c>
       <c r="AB377" s="25" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AC377" s="25" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AD377" s="25" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AE377" s="25"/>
       <c r="AF377" s="25" t="s">
         <v>25</v>
       </c>
       <c r="AG377" s="25" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AH377" s="25" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AI377" s="25" t="s">
         <v>25</v>
@@ -43523,19 +43513,15 @@
       </c>
       <c r="AM377" s="25"/>
       <c r="AN377" s="25" t="s">
-        <v>689</v>
+        <v>467</v>
       </c>
       <c r="AO377" s="25"/>
       <c r="AP377" s="25" t="s">
-        <v>689</v>
-      </c>
-      <c r="AQ377" s="25" t="s">
-        <v>689</v>
-      </c>
+        <v>467</v>
+      </c>
+      <c r="AQ377" s="25"/>
       <c r="AR377" s="25"/>
-      <c r="AS377" s="25" t="s">
-        <v>689</v>
-      </c>
+      <c r="AS377" s="25"/>
       <c r="AT377" s="25"/>
       <c r="AU377" s="25"/>
       <c r="AV377" s="25"/>
@@ -43544,24 +43530,30 @@
       <c r="AZ377" s="26"/>
     </row>
     <row r="378" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A378" s="50">
+      <c r="A378" s="25">
         <v>70</v>
       </c>
       <c r="B378" s="25"/>
       <c r="C378" s="25"/>
       <c r="D378" s="25" t="s">
-        <v>1022</v>
-      </c>
-      <c r="E378" s="37"/>
-      <c r="F378" s="25"/>
-      <c r="G378" s="25"/>
+        <v>1174</v>
+      </c>
+      <c r="E378" s="37" t="s">
+        <v>2079</v>
+      </c>
+      <c r="F378" s="25" t="s">
+        <v>584</v>
+      </c>
+      <c r="G378" s="25" t="s">
+        <v>47</v>
+      </c>
       <c r="H378" s="25"/>
       <c r="I378" s="25" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="J378" s="25"/>
       <c r="K378" s="25" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L378" s="25"/>
       <c r="M378" s="25"/>
@@ -43575,39 +43567,55 @@
       <c r="U378" s="25"/>
       <c r="V378" s="25"/>
       <c r="W378" s="25"/>
-      <c r="X378" s="25"/>
-      <c r="Z378" s="25"/>
-      <c r="AA378" s="25"/>
-      <c r="AB378" s="25"/>
-      <c r="AC378" s="25"/>
-      <c r="AD378" s="25"/>
+      <c r="X378" s="25" t="s">
+        <v>1535</v>
+      </c>
+      <c r="Z378" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA378" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB378" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC378" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD378" s="25" t="s">
+        <v>19</v>
+      </c>
       <c r="AE378" s="25"/>
-      <c r="AF378" s="25"/>
-      <c r="AG378" s="25"/>
-      <c r="AH378" s="25"/>
-      <c r="AI378" s="25"/>
-      <c r="AJ378" s="25"/>
-      <c r="AK378" s="25"/>
+      <c r="AF378" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG378" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AH378" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI378" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ378" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK378" s="25" t="s">
+        <v>25</v>
+      </c>
       <c r="AM378" s="25"/>
-      <c r="AN378" s="25" t="s">
-        <v>1023</v>
-      </c>
+      <c r="AN378" s="25"/>
       <c r="AO378" s="25"/>
-      <c r="AP378" s="25" t="s">
-        <v>1023</v>
-      </c>
+      <c r="AP378" s="25"/>
       <c r="AQ378" s="25" t="s">
-        <v>1023</v>
-      </c>
-      <c r="AR378" s="25" t="s">
-        <v>1023</v>
-      </c>
+        <v>1174</v>
+      </c>
+      <c r="AR378" s="25"/>
       <c r="AS378" s="25" t="s">
-        <v>1023</v>
-      </c>
-      <c r="AT378" s="25" t="s">
-        <v>1023</v>
-      </c>
+        <v>1174</v>
+      </c>
+      <c r="AT378" s="25"/>
       <c r="AU378" s="25"/>
       <c r="AV378" s="25"/>
       <c r="AW378" s="25"/>
@@ -43618,90 +43626,87 @@
       <c r="A379" s="50">
         <v>70</v>
       </c>
-      <c r="B379" s="25"/>
-      <c r="C379" s="25"/>
-      <c r="D379" s="25" t="s">
-        <v>1024</v>
-      </c>
-      <c r="E379" s="37"/>
-      <c r="F379" s="25"/>
-      <c r="G379" s="25"/>
-      <c r="H379" s="25"/>
-      <c r="I379" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="J379" s="25"/>
-      <c r="K379" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="L379" s="25"/>
-      <c r="M379" s="25"/>
-      <c r="N379" s="25"/>
-      <c r="O379" s="25"/>
-      <c r="P379" s="25"/>
-      <c r="Q379" s="25"/>
-      <c r="R379" s="25"/>
-      <c r="S379" s="25"/>
-      <c r="T379" s="25"/>
-      <c r="U379" s="25"/>
-      <c r="V379" s="25"/>
-      <c r="W379" s="25"/>
-      <c r="X379" s="25"/>
-      <c r="Z379" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA379" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB379" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC379" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD379" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE379" s="25"/>
-      <c r="AF379" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG379" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH379" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AI379" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ379" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AK379" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM379" s="25"/>
-      <c r="AN379" s="25" t="s">
-        <v>690</v>
-      </c>
-      <c r="AO379" s="25"/>
-      <c r="AP379" s="25" t="s">
-        <v>690</v>
-      </c>
-      <c r="AQ379" s="25" t="s">
-        <v>690</v>
-      </c>
-      <c r="AR379" s="25"/>
-      <c r="AS379" s="25" t="s">
-        <v>690</v>
-      </c>
-      <c r="AT379" s="25"/>
-      <c r="AU379" s="25"/>
-      <c r="AV379" s="25"/>
-      <c r="AW379" s="25"/>
-      <c r="AX379" s="25"/>
-      <c r="AZ379" s="26"/>
+      <c r="B379" s="50"/>
+      <c r="C379" s="50"/>
+      <c r="D379" s="50" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E379" s="50"/>
+      <c r="F379" s="50"/>
+      <c r="G379" s="50"/>
+      <c r="H379" s="50"/>
+      <c r="I379" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="J379" s="50"/>
+      <c r="K379" s="50" t="s">
+        <v>248</v>
+      </c>
+      <c r="L379" s="50" t="s">
+        <v>1405</v>
+      </c>
+      <c r="M379" s="50"/>
+      <c r="N379" s="50"/>
+      <c r="O379" s="50"/>
+      <c r="P379" s="50"/>
+      <c r="Q379" s="50"/>
+      <c r="R379" s="50"/>
+      <c r="S379" s="50"/>
+      <c r="T379" s="50"/>
+      <c r="U379" s="50"/>
+      <c r="V379" s="50"/>
+      <c r="W379" s="50"/>
+      <c r="X379" s="50"/>
+      <c r="Y379" s="50"/>
+      <c r="Z379" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA379" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB379" s="50" t="s">
+        <v>282</v>
+      </c>
+      <c r="AC379" s="50" t="s">
+        <v>282</v>
+      </c>
+      <c r="AD379" s="50" t="s">
+        <v>282</v>
+      </c>
+      <c r="AE379" s="50"/>
+      <c r="AF379" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG379" s="50" t="s">
+        <v>282</v>
+      </c>
+      <c r="AH379" s="50" t="s">
+        <v>282</v>
+      </c>
+      <c r="AI379" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ379" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK379" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL379" s="50"/>
+      <c r="AM379" s="50"/>
+      <c r="AN379" s="50"/>
+      <c r="AO379" s="50"/>
+      <c r="AP379" s="50"/>
+      <c r="AQ379" s="50"/>
+      <c r="AR379" s="50"/>
+      <c r="AS379" s="50"/>
+      <c r="AT379" s="50"/>
+      <c r="AU379" s="50"/>
+      <c r="AV379" s="50"/>
+      <c r="AW379" s="50"/>
+      <c r="AX379" s="50"/>
+      <c r="AY379" s="50"/>
+      <c r="AZ379" s="50"/>
     </row>
     <row r="380" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A380" s="50">
@@ -43710,7 +43715,7 @@
       <c r="B380" s="25"/>
       <c r="C380" s="25"/>
       <c r="D380" s="25" t="s">
-        <v>1025</v>
+        <v>1019</v>
       </c>
       <c r="E380" s="37"/>
       <c r="F380" s="25"/>
@@ -43736,38 +43741,56 @@
       <c r="V380" s="25"/>
       <c r="W380" s="25"/>
       <c r="X380" s="25"/>
-      <c r="Z380" s="25"/>
-      <c r="AA380" s="25"/>
-      <c r="AB380" s="25"/>
-      <c r="AC380" s="25"/>
-      <c r="AD380" s="25"/>
+      <c r="Z380" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA380" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB380" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC380" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD380" s="25" t="s">
+        <v>19</v>
+      </c>
       <c r="AE380" s="25"/>
-      <c r="AF380" s="25"/>
-      <c r="AG380" s="25"/>
-      <c r="AH380" s="25"/>
-      <c r="AI380" s="25"/>
-      <c r="AJ380" s="25"/>
-      <c r="AK380" s="25"/>
+      <c r="AF380" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG380" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AH380" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI380" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ380" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK380" s="25" t="s">
+        <v>25</v>
+      </c>
       <c r="AM380" s="25"/>
       <c r="AN380" s="25" t="s">
-        <v>1026</v>
+        <v>688</v>
       </c>
       <c r="AO380" s="25"/>
       <c r="AP380" s="25" t="s">
-        <v>1026</v>
+        <v>688</v>
       </c>
       <c r="AQ380" s="25" t="s">
-        <v>1026</v>
-      </c>
-      <c r="AR380" s="25" t="s">
-        <v>1026</v>
-      </c>
+        <v>688</v>
+      </c>
+      <c r="AR380" s="25"/>
       <c r="AS380" s="25" t="s">
-        <v>1026</v>
-      </c>
-      <c r="AT380" s="25" t="s">
-        <v>1026</v>
-      </c>
+        <v>688</v>
+      </c>
+      <c r="AT380" s="25"/>
       <c r="AU380" s="25"/>
       <c r="AV380" s="25"/>
       <c r="AW380" s="25"/>
@@ -43781,7 +43804,7 @@
       <c r="B381" s="25"/>
       <c r="C381" s="25"/>
       <c r="D381" s="25" t="s">
-        <v>1027</v>
+        <v>1020</v>
       </c>
       <c r="E381" s="37"/>
       <c r="F381" s="25"/>
@@ -43807,56 +43830,38 @@
       <c r="V381" s="25"/>
       <c r="W381" s="25"/>
       <c r="X381" s="25"/>
-      <c r="Z381" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA381" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB381" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC381" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD381" s="25" t="s">
-        <v>19</v>
-      </c>
+      <c r="Z381" s="25"/>
+      <c r="AA381" s="25"/>
+      <c r="AB381" s="25"/>
+      <c r="AC381" s="25"/>
+      <c r="AD381" s="25"/>
       <c r="AE381" s="25"/>
-      <c r="AF381" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG381" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH381" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AI381" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ381" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AK381" s="25" t="s">
-        <v>25</v>
-      </c>
+      <c r="AF381" s="25"/>
+      <c r="AG381" s="25"/>
+      <c r="AH381" s="25"/>
+      <c r="AI381" s="25"/>
+      <c r="AJ381" s="25"/>
+      <c r="AK381" s="25"/>
       <c r="AM381" s="25"/>
       <c r="AN381" s="25" t="s">
-        <v>691</v>
+        <v>272</v>
       </c>
       <c r="AO381" s="25"/>
       <c r="AP381" s="25" t="s">
-        <v>691</v>
+        <v>272</v>
       </c>
       <c r="AQ381" s="25" t="s">
-        <v>691</v>
-      </c>
-      <c r="AR381" s="25"/>
+        <v>272</v>
+      </c>
+      <c r="AR381" s="25" t="s">
+        <v>272</v>
+      </c>
       <c r="AS381" s="25" t="s">
-        <v>691</v>
-      </c>
-      <c r="AT381" s="25"/>
+        <v>272</v>
+      </c>
+      <c r="AT381" s="25" t="s">
+        <v>272</v>
+      </c>
       <c r="AU381" s="25"/>
       <c r="AV381" s="25"/>
       <c r="AW381" s="25"/>
@@ -43870,7 +43875,7 @@
       <c r="B382" s="25"/>
       <c r="C382" s="25"/>
       <c r="D382" s="25" t="s">
-        <v>1028</v>
+        <v>1021</v>
       </c>
       <c r="E382" s="37"/>
       <c r="F382" s="25"/>
@@ -43896,38 +43901,56 @@
       <c r="V382" s="25"/>
       <c r="W382" s="25"/>
       <c r="X382" s="25"/>
-      <c r="Z382" s="25"/>
-      <c r="AA382" s="25"/>
-      <c r="AB382" s="25"/>
-      <c r="AC382" s="25"/>
-      <c r="AD382" s="25"/>
+      <c r="Z382" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA382" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB382" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC382" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD382" s="25" t="s">
+        <v>19</v>
+      </c>
       <c r="AE382" s="25"/>
-      <c r="AF382" s="25"/>
-      <c r="AG382" s="25"/>
-      <c r="AH382" s="25"/>
-      <c r="AI382" s="25"/>
-      <c r="AJ382" s="25"/>
-      <c r="AK382" s="25"/>
+      <c r="AF382" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG382" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AH382" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI382" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ382" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK382" s="25" t="s">
+        <v>25</v>
+      </c>
       <c r="AM382" s="25"/>
       <c r="AN382" s="25" t="s">
-        <v>273</v>
+        <v>689</v>
       </c>
       <c r="AO382" s="25"/>
       <c r="AP382" s="25" t="s">
-        <v>273</v>
+        <v>689</v>
       </c>
       <c r="AQ382" s="25" t="s">
-        <v>273</v>
-      </c>
-      <c r="AR382" s="25" t="s">
-        <v>273</v>
-      </c>
+        <v>689</v>
+      </c>
+      <c r="AR382" s="25"/>
       <c r="AS382" s="25" t="s">
-        <v>273</v>
-      </c>
-      <c r="AT382" s="25" t="s">
-        <v>273</v>
-      </c>
+        <v>689</v>
+      </c>
+      <c r="AT382" s="25"/>
       <c r="AU382" s="25"/>
       <c r="AV382" s="25"/>
       <c r="AW382" s="25"/>
@@ -43935,30 +43958,24 @@
       <c r="AZ382" s="26"/>
     </row>
     <row r="383" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A383" s="25">
+      <c r="A383" s="50">
         <v>70</v>
       </c>
       <c r="B383" s="25"/>
       <c r="C383" s="25"/>
       <c r="D383" s="25" t="s">
-        <v>933</v>
-      </c>
-      <c r="E383" s="37" t="s">
-        <v>2080</v>
-      </c>
-      <c r="F383" s="25" t="s">
-        <v>711</v>
-      </c>
-      <c r="G383" s="25" t="s">
-        <v>712</v>
-      </c>
+        <v>1022</v>
+      </c>
+      <c r="E383" s="37"/>
+      <c r="F383" s="25"/>
+      <c r="G383" s="25"/>
       <c r="H383" s="25"/>
       <c r="I383" s="25" t="s">
-        <v>1406</v>
+        <v>23</v>
       </c>
       <c r="J383" s="25"/>
       <c r="K383" s="25" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L383" s="25"/>
       <c r="M383" s="25"/>
@@ -43973,56 +43990,38 @@
       <c r="V383" s="25"/>
       <c r="W383" s="25"/>
       <c r="X383" s="25"/>
-      <c r="Z383" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA383" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB383" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC383" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD383" s="25" t="s">
-        <v>19</v>
-      </c>
+      <c r="Z383" s="25"/>
+      <c r="AA383" s="25"/>
+      <c r="AB383" s="25"/>
+      <c r="AC383" s="25"/>
+      <c r="AD383" s="25"/>
       <c r="AE383" s="25"/>
-      <c r="AF383" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG383" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH383" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AI383" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ383" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AK383" s="25" t="s">
-        <v>25</v>
-      </c>
+      <c r="AF383" s="25"/>
+      <c r="AG383" s="25"/>
+      <c r="AH383" s="25"/>
+      <c r="AI383" s="25"/>
+      <c r="AJ383" s="25"/>
+      <c r="AK383" s="25"/>
       <c r="AM383" s="25"/>
       <c r="AN383" s="25" t="s">
-        <v>933</v>
+        <v>1023</v>
       </c>
       <c r="AO383" s="25"/>
       <c r="AP383" s="25" t="s">
-        <v>933</v>
+        <v>1023</v>
       </c>
       <c r="AQ383" s="25" t="s">
-        <v>933</v>
-      </c>
-      <c r="AR383" s="25"/>
+        <v>1023</v>
+      </c>
+      <c r="AR383" s="25" t="s">
+        <v>1023</v>
+      </c>
       <c r="AS383" s="25" t="s">
-        <v>933</v>
-      </c>
-      <c r="AT383" s="25"/>
+        <v>1023</v>
+      </c>
+      <c r="AT383" s="25" t="s">
+        <v>1023</v>
+      </c>
       <c r="AU383" s="25"/>
       <c r="AV383" s="25"/>
       <c r="AW383" s="25"/>
@@ -44033,87 +44032,90 @@
       <c r="A384" s="50">
         <v>70</v>
       </c>
-      <c r="B384" s="50"/>
-      <c r="C384" s="50"/>
-      <c r="D384" s="50" t="s">
-        <v>775</v>
-      </c>
-      <c r="E384" s="50"/>
-      <c r="F384" s="50"/>
-      <c r="G384" s="50"/>
-      <c r="H384" s="50"/>
-      <c r="I384" s="50" t="s">
-        <v>31</v>
-      </c>
-      <c r="J384" s="50"/>
-      <c r="K384" s="50" t="s">
-        <v>248</v>
-      </c>
-      <c r="L384" s="50" t="s">
-        <v>776</v>
-      </c>
-      <c r="M384" s="50"/>
-      <c r="N384" s="50"/>
-      <c r="O384" s="50"/>
-      <c r="P384" s="50"/>
-      <c r="Q384" s="50"/>
-      <c r="R384" s="50"/>
-      <c r="S384" s="50"/>
-      <c r="T384" s="50"/>
-      <c r="U384" s="50"/>
-      <c r="V384" s="50"/>
-      <c r="W384" s="50"/>
-      <c r="X384" s="50"/>
-      <c r="Y384" s="50"/>
-      <c r="Z384" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA384" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB384" s="50" t="s">
-        <v>282</v>
-      </c>
-      <c r="AC384" s="50" t="s">
-        <v>282</v>
-      </c>
-      <c r="AD384" s="50" t="s">
-        <v>282</v>
-      </c>
-      <c r="AE384" s="50"/>
-      <c r="AF384" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG384" s="50" t="s">
-        <v>282</v>
-      </c>
-      <c r="AH384" s="50" t="s">
-        <v>282</v>
-      </c>
-      <c r="AI384" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AJ384" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AK384" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL384" s="50"/>
-      <c r="AM384" s="50"/>
-      <c r="AN384" s="50"/>
-      <c r="AO384" s="50"/>
-      <c r="AP384" s="50"/>
-      <c r="AQ384" s="50"/>
-      <c r="AR384" s="50"/>
-      <c r="AS384" s="50"/>
-      <c r="AT384" s="50"/>
-      <c r="AU384" s="50"/>
-      <c r="AV384" s="50"/>
-      <c r="AW384" s="50"/>
-      <c r="AX384" s="50"/>
-      <c r="AY384" s="50"/>
-      <c r="AZ384" s="50"/>
+      <c r="B384" s="25"/>
+      <c r="C384" s="25"/>
+      <c r="D384" s="25" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E384" s="37"/>
+      <c r="F384" s="25"/>
+      <c r="G384" s="25"/>
+      <c r="H384" s="25"/>
+      <c r="I384" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="J384" s="25"/>
+      <c r="K384" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L384" s="25"/>
+      <c r="M384" s="25"/>
+      <c r="N384" s="25"/>
+      <c r="O384" s="25"/>
+      <c r="P384" s="25"/>
+      <c r="Q384" s="25"/>
+      <c r="R384" s="25"/>
+      <c r="S384" s="25"/>
+      <c r="T384" s="25"/>
+      <c r="U384" s="25"/>
+      <c r="V384" s="25"/>
+      <c r="W384" s="25"/>
+      <c r="X384" s="25"/>
+      <c r="Z384" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA384" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB384" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC384" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD384" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE384" s="25"/>
+      <c r="AF384" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG384" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AH384" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI384" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ384" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK384" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM384" s="25"/>
+      <c r="AN384" s="25" t="s">
+        <v>690</v>
+      </c>
+      <c r="AO384" s="25"/>
+      <c r="AP384" s="25" t="s">
+        <v>690</v>
+      </c>
+      <c r="AQ384" s="25" t="s">
+        <v>690</v>
+      </c>
+      <c r="AR384" s="25"/>
+      <c r="AS384" s="25" t="s">
+        <v>690</v>
+      </c>
+      <c r="AT384" s="25"/>
+      <c r="AU384" s="25"/>
+      <c r="AV384" s="25"/>
+      <c r="AW384" s="25"/>
+      <c r="AX384" s="25"/>
+      <c r="AZ384" s="26"/>
     </row>
     <row r="385" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A385" s="50">
@@ -44122,17 +44124,11 @@
       <c r="B385" s="25"/>
       <c r="C385" s="25"/>
       <c r="D385" s="25" t="s">
-        <v>777</v>
-      </c>
-      <c r="E385" s="37" t="s">
-        <v>2014</v>
-      </c>
-      <c r="F385" s="25" t="s">
-        <v>664</v>
-      </c>
-      <c r="G385" s="25" t="s">
-        <v>47</v>
-      </c>
+        <v>1025</v>
+      </c>
+      <c r="E385" s="37"/>
+      <c r="F385" s="25"/>
+      <c r="G385" s="25"/>
       <c r="H385" s="25"/>
       <c r="I385" s="25" t="s">
         <v>23</v>
@@ -44168,18 +44164,24 @@
       <c r="AK385" s="25"/>
       <c r="AM385" s="25"/>
       <c r="AN385" s="25" t="s">
-        <v>779</v>
+        <v>1026</v>
       </c>
       <c r="AO385" s="25"/>
-      <c r="AP385" s="25"/>
+      <c r="AP385" s="25" t="s">
+        <v>1026</v>
+      </c>
       <c r="AQ385" s="25" t="s">
-        <v>580</v>
-      </c>
-      <c r="AR385" s="25"/>
+        <v>1026</v>
+      </c>
+      <c r="AR385" s="25" t="s">
+        <v>1026</v>
+      </c>
       <c r="AS385" s="25" t="s">
-        <v>580</v>
-      </c>
-      <c r="AT385" s="25"/>
+        <v>1026</v>
+      </c>
+      <c r="AT385" s="25" t="s">
+        <v>1026</v>
+      </c>
       <c r="AU385" s="25"/>
       <c r="AV385" s="25"/>
       <c r="AW385" s="25"/>
@@ -44193,17 +44195,11 @@
       <c r="B386" s="25"/>
       <c r="C386" s="25"/>
       <c r="D386" s="25" t="s">
-        <v>778</v>
-      </c>
-      <c r="E386" s="37" t="s">
-        <v>2015</v>
-      </c>
-      <c r="F386" s="25" t="s">
-        <v>1029</v>
-      </c>
-      <c r="G386" s="25" t="s">
-        <v>47</v>
-      </c>
+        <v>1027</v>
+      </c>
+      <c r="E386" s="37"/>
+      <c r="F386" s="25"/>
+      <c r="G386" s="25"/>
       <c r="H386" s="25"/>
       <c r="I386" s="25" t="s">
         <v>23</v>
@@ -44225,27 +44221,55 @@
       <c r="V386" s="25"/>
       <c r="W386" s="25"/>
       <c r="X386" s="25"/>
-      <c r="Z386" s="25"/>
-      <c r="AA386" s="25"/>
-      <c r="AB386" s="25"/>
-      <c r="AC386" s="25"/>
-      <c r="AD386" s="25"/>
+      <c r="Z386" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA386" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB386" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC386" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD386" s="25" t="s">
+        <v>19</v>
+      </c>
       <c r="AE386" s="25"/>
-      <c r="AF386" s="25"/>
-      <c r="AG386" s="25"/>
-      <c r="AH386" s="25"/>
-      <c r="AI386" s="25"/>
-      <c r="AJ386" s="25"/>
-      <c r="AK386" s="25"/>
+      <c r="AF386" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG386" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AH386" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI386" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ386" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK386" s="25" t="s">
+        <v>25</v>
+      </c>
       <c r="AM386" s="25"/>
       <c r="AN386" s="25" t="s">
-        <v>780</v>
+        <v>691</v>
       </c>
       <c r="AO386" s="25"/>
-      <c r="AP386" s="25"/>
-      <c r="AQ386" s="25"/>
+      <c r="AP386" s="25" t="s">
+        <v>691</v>
+      </c>
+      <c r="AQ386" s="25" t="s">
+        <v>691</v>
+      </c>
       <c r="AR386" s="25"/>
-      <c r="AS386" s="25"/>
+      <c r="AS386" s="25" t="s">
+        <v>691</v>
+      </c>
       <c r="AT386" s="25"/>
       <c r="AU386" s="25"/>
       <c r="AV386" s="25"/>
@@ -44257,113 +44281,98 @@
       <c r="A387" s="50">
         <v>70</v>
       </c>
-      <c r="B387" s="50"/>
-      <c r="C387" s="50"/>
-      <c r="D387" s="50" t="s">
-        <v>1030</v>
-      </c>
-      <c r="E387" s="50"/>
-      <c r="F387" s="50"/>
-      <c r="G387" s="50"/>
-      <c r="H387" s="50"/>
-      <c r="I387" s="50" t="s">
-        <v>31</v>
-      </c>
-      <c r="J387" s="50"/>
-      <c r="K387" s="50" t="s">
-        <v>248</v>
-      </c>
-      <c r="L387" s="50" t="s">
-        <v>776</v>
-      </c>
-      <c r="M387" s="50"/>
-      <c r="N387" s="50"/>
-      <c r="O387" s="50"/>
-      <c r="P387" s="50"/>
-      <c r="Q387" s="50"/>
-      <c r="R387" s="50"/>
-      <c r="S387" s="50"/>
-      <c r="T387" s="50"/>
-      <c r="U387" s="50"/>
-      <c r="V387" s="50"/>
-      <c r="W387" s="50"/>
-      <c r="X387" s="50"/>
-      <c r="Y387" s="50"/>
-      <c r="Z387" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA387" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB387" s="50" t="s">
-        <v>282</v>
-      </c>
-      <c r="AC387" s="50" t="s">
-        <v>282</v>
-      </c>
-      <c r="AD387" s="50" t="s">
-        <v>282</v>
-      </c>
-      <c r="AE387" s="50"/>
-      <c r="AF387" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG387" s="50" t="s">
-        <v>282</v>
-      </c>
-      <c r="AH387" s="50" t="s">
-        <v>282</v>
-      </c>
-      <c r="AI387" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AJ387" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AK387" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL387" s="50"/>
-      <c r="AM387" s="50"/>
-      <c r="AN387" s="50"/>
-      <c r="AO387" s="50"/>
-      <c r="AP387" s="50"/>
-      <c r="AQ387" s="50"/>
-      <c r="AR387" s="50"/>
-      <c r="AS387" s="50"/>
-      <c r="AT387" s="50"/>
-      <c r="AU387" s="50"/>
-      <c r="AV387" s="50"/>
-      <c r="AW387" s="50"/>
-      <c r="AX387" s="50"/>
-      <c r="AY387" s="50"/>
-      <c r="AZ387" s="50"/>
+      <c r="B387" s="25"/>
+      <c r="C387" s="25"/>
+      <c r="D387" s="25" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E387" s="37"/>
+      <c r="F387" s="25"/>
+      <c r="G387" s="25"/>
+      <c r="H387" s="25"/>
+      <c r="I387" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="J387" s="25"/>
+      <c r="K387" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L387" s="25"/>
+      <c r="M387" s="25"/>
+      <c r="N387" s="25"/>
+      <c r="O387" s="25"/>
+      <c r="P387" s="25"/>
+      <c r="Q387" s="25"/>
+      <c r="R387" s="25"/>
+      <c r="S387" s="25"/>
+      <c r="T387" s="25"/>
+      <c r="U387" s="25"/>
+      <c r="V387" s="25"/>
+      <c r="W387" s="25"/>
+      <c r="X387" s="25"/>
+      <c r="Z387" s="25"/>
+      <c r="AA387" s="25"/>
+      <c r="AB387" s="25"/>
+      <c r="AC387" s="25"/>
+      <c r="AD387" s="25"/>
+      <c r="AE387" s="25"/>
+      <c r="AF387" s="25"/>
+      <c r="AG387" s="25"/>
+      <c r="AH387" s="25"/>
+      <c r="AI387" s="25"/>
+      <c r="AJ387" s="25"/>
+      <c r="AK387" s="25"/>
+      <c r="AM387" s="25"/>
+      <c r="AN387" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="AO387" s="25"/>
+      <c r="AP387" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="AQ387" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="AR387" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="AS387" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="AT387" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="AU387" s="25"/>
+      <c r="AV387" s="25"/>
+      <c r="AW387" s="25"/>
+      <c r="AX387" s="25"/>
+      <c r="AZ387" s="26"/>
     </row>
     <row r="388" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A388" s="50">
+      <c r="A388" s="25">
         <v>70</v>
       </c>
       <c r="B388" s="25"/>
       <c r="C388" s="25"/>
       <c r="D388" s="25" t="s">
-        <v>1031</v>
+        <v>933</v>
       </c>
       <c r="E388" s="37" t="s">
-        <v>2016</v>
+        <v>2080</v>
       </c>
       <c r="F388" s="25" t="s">
-        <v>1032</v>
+        <v>711</v>
       </c>
       <c r="G388" s="25" t="s">
-        <v>997</v>
+        <v>712</v>
       </c>
       <c r="H388" s="25"/>
       <c r="I388" s="25" t="s">
-        <v>23</v>
+        <v>1406</v>
       </c>
       <c r="J388" s="25"/>
       <c r="K388" s="25" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L388" s="25"/>
       <c r="M388" s="25"/>
@@ -44378,30 +44387,54 @@
       <c r="V388" s="25"/>
       <c r="W388" s="25"/>
       <c r="X388" s="25"/>
-      <c r="Z388" s="25"/>
-      <c r="AA388" s="25"/>
-      <c r="AB388" s="25"/>
-      <c r="AC388" s="25"/>
-      <c r="AD388" s="25"/>
+      <c r="Z388" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA388" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB388" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC388" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD388" s="25" t="s">
+        <v>19</v>
+      </c>
       <c r="AE388" s="25"/>
-      <c r="AF388" s="25"/>
-      <c r="AG388" s="25"/>
-      <c r="AH388" s="25"/>
-      <c r="AI388" s="25"/>
-      <c r="AJ388" s="25"/>
-      <c r="AK388" s="25"/>
+      <c r="AF388" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG388" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AH388" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI388" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ388" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK388" s="25" t="s">
+        <v>25</v>
+      </c>
       <c r="AM388" s="25"/>
       <c r="AN388" s="25" t="s">
-        <v>1033</v>
+        <v>933</v>
       </c>
       <c r="AO388" s="25"/>
-      <c r="AP388" s="25"/>
+      <c r="AP388" s="25" t="s">
+        <v>933</v>
+      </c>
       <c r="AQ388" s="25" t="s">
-        <v>1034</v>
+        <v>933</v>
       </c>
       <c r="AR388" s="25"/>
       <c r="AS388" s="25" t="s">
-        <v>1034</v>
+        <v>933</v>
       </c>
       <c r="AT388" s="25"/>
       <c r="AU388" s="25"/>
@@ -44414,97 +44447,116 @@
       <c r="A389" s="50">
         <v>70</v>
       </c>
-      <c r="B389" s="25"/>
-      <c r="C389" s="25"/>
-      <c r="D389" s="25" t="s">
-        <v>1035</v>
-      </c>
-      <c r="E389" s="37" t="s">
-        <v>2017</v>
-      </c>
-      <c r="F389" s="25" t="s">
-        <v>1036</v>
-      </c>
-      <c r="G389" s="25" t="s">
-        <v>997</v>
-      </c>
-      <c r="H389" s="25"/>
-      <c r="I389" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="J389" s="25"/>
-      <c r="K389" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="L389" s="25"/>
-      <c r="M389" s="25"/>
-      <c r="N389" s="25"/>
-      <c r="O389" s="25"/>
-      <c r="P389" s="25"/>
-      <c r="Q389" s="25"/>
-      <c r="R389" s="25"/>
-      <c r="S389" s="25"/>
-      <c r="T389" s="25"/>
-      <c r="U389" s="25"/>
-      <c r="V389" s="25"/>
-      <c r="W389" s="25"/>
-      <c r="X389" s="25"/>
-      <c r="Z389" s="25"/>
-      <c r="AA389" s="25"/>
-      <c r="AB389" s="25"/>
-      <c r="AC389" s="25"/>
-      <c r="AD389" s="25"/>
-      <c r="AE389" s="25"/>
-      <c r="AF389" s="25"/>
-      <c r="AG389" s="25"/>
-      <c r="AH389" s="25"/>
-      <c r="AI389" s="25"/>
-      <c r="AJ389" s="25"/>
-      <c r="AK389" s="25"/>
-      <c r="AM389" s="25"/>
-      <c r="AN389" s="25" t="s">
-        <v>1037</v>
-      </c>
-      <c r="AO389" s="25"/>
-      <c r="AP389" s="25"/>
-      <c r="AQ389" s="25"/>
-      <c r="AR389" s="25"/>
-      <c r="AS389" s="25"/>
-      <c r="AT389" s="25"/>
-      <c r="AU389" s="25"/>
-      <c r="AV389" s="25"/>
-      <c r="AW389" s="25"/>
-      <c r="AX389" s="25"/>
-      <c r="AZ389" s="26"/>
+      <c r="B389" s="50"/>
+      <c r="C389" s="50"/>
+      <c r="D389" s="50" t="s">
+        <v>775</v>
+      </c>
+      <c r="E389" s="50"/>
+      <c r="F389" s="50"/>
+      <c r="G389" s="50"/>
+      <c r="H389" s="50"/>
+      <c r="I389" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="J389" s="50"/>
+      <c r="K389" s="50" t="s">
+        <v>248</v>
+      </c>
+      <c r="L389" s="50" t="s">
+        <v>776</v>
+      </c>
+      <c r="M389" s="50"/>
+      <c r="N389" s="50"/>
+      <c r="O389" s="50"/>
+      <c r="P389" s="50"/>
+      <c r="Q389" s="50"/>
+      <c r="R389" s="50"/>
+      <c r="S389" s="50"/>
+      <c r="T389" s="50"/>
+      <c r="U389" s="50"/>
+      <c r="V389" s="50"/>
+      <c r="W389" s="50"/>
+      <c r="X389" s="50"/>
+      <c r="Y389" s="50"/>
+      <c r="Z389" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA389" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB389" s="50" t="s">
+        <v>282</v>
+      </c>
+      <c r="AC389" s="50" t="s">
+        <v>282</v>
+      </c>
+      <c r="AD389" s="50" t="s">
+        <v>282</v>
+      </c>
+      <c r="AE389" s="50"/>
+      <c r="AF389" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG389" s="50" t="s">
+        <v>282</v>
+      </c>
+      <c r="AH389" s="50" t="s">
+        <v>282</v>
+      </c>
+      <c r="AI389" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ389" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK389" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL389" s="50"/>
+      <c r="AM389" s="50"/>
+      <c r="AN389" s="50"/>
+      <c r="AO389" s="50"/>
+      <c r="AP389" s="50"/>
+      <c r="AQ389" s="50"/>
+      <c r="AR389" s="50"/>
+      <c r="AS389" s="50"/>
+      <c r="AT389" s="50"/>
+      <c r="AU389" s="50"/>
+      <c r="AV389" s="50"/>
+      <c r="AW389" s="50"/>
+      <c r="AX389" s="50"/>
+      <c r="AY389" s="50"/>
+      <c r="AZ389" s="50"/>
     </row>
     <row r="390" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A390" s="25">
+      <c r="A390" s="50">
         <v>70</v>
       </c>
       <c r="B390" s="25"/>
       <c r="C390" s="25"/>
       <c r="D390" s="25" t="s">
-        <v>657</v>
+        <v>777</v>
       </c>
       <c r="E390" s="37" t="s">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="F390" s="25" t="s">
-        <v>380</v>
-      </c>
-      <c r="G390" s="25"/>
+        <v>664</v>
+      </c>
+      <c r="G390" s="25" t="s">
+        <v>47</v>
+      </c>
       <c r="H390" s="25"/>
       <c r="I390" s="25" t="s">
-        <v>1371</v>
+        <v>23</v>
       </c>
       <c r="J390" s="25"/>
       <c r="K390" s="25" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L390" s="25"/>
-      <c r="M390" s="25" t="s">
-        <v>682</v>
-      </c>
+      <c r="M390" s="25"/>
       <c r="N390" s="25"/>
       <c r="O390" s="25"/>
       <c r="P390" s="25"/>
@@ -44516,52 +44568,30 @@
       <c r="V390" s="25"/>
       <c r="W390" s="25"/>
       <c r="X390" s="25"/>
-      <c r="Z390" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA390" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB390" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC390" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD390" s="25" t="s">
-        <v>70</v>
-      </c>
+      <c r="Z390" s="25"/>
+      <c r="AA390" s="25"/>
+      <c r="AB390" s="25"/>
+      <c r="AC390" s="25"/>
+      <c r="AD390" s="25"/>
       <c r="AE390" s="25"/>
-      <c r="AF390" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG390" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="AH390" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI390" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="AJ390" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK390" s="25" t="s">
-        <v>70</v>
-      </c>
+      <c r="AF390" s="25"/>
+      <c r="AG390" s="25"/>
+      <c r="AH390" s="25"/>
+      <c r="AI390" s="25"/>
+      <c r="AJ390" s="25"/>
+      <c r="AK390" s="25"/>
       <c r="AM390" s="25"/>
       <c r="AN390" s="25" t="s">
-        <v>381</v>
+        <v>779</v>
       </c>
       <c r="AO390" s="25"/>
       <c r="AP390" s="25"/>
       <c r="AQ390" s="25" t="s">
-        <v>381</v>
+        <v>580</v>
       </c>
       <c r="AR390" s="25"/>
       <c r="AS390" s="25" t="s">
-        <v>381</v>
+        <v>580</v>
       </c>
       <c r="AT390" s="25"/>
       <c r="AU390" s="25"/>
@@ -44571,87 +44601,59 @@
       <c r="AZ390" s="26"/>
     </row>
     <row r="391" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A391" s="25">
+      <c r="A391" s="50">
         <v>70</v>
       </c>
       <c r="B391" s="25"/>
       <c r="C391" s="25"/>
       <c r="D391" s="25" t="s">
-        <v>1530</v>
+        <v>778</v>
       </c>
       <c r="E391" s="37" t="s">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="F391" s="25" t="s">
-        <v>375</v>
+        <v>1029</v>
       </c>
       <c r="G391" s="25" t="s">
-        <v>375</v>
+        <v>47</v>
       </c>
       <c r="H391" s="25"/>
       <c r="I391" s="25" t="s">
-        <v>631</v>
+        <v>23</v>
       </c>
       <c r="J391" s="25"/>
       <c r="K391" s="25" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="L391" s="25"/>
       <c r="M391" s="25"/>
       <c r="N391" s="25"/>
       <c r="O391" s="25"/>
       <c r="P391" s="25"/>
-      <c r="Q391" s="25" t="s">
-        <v>601</v>
-      </c>
+      <c r="Q391" s="25"/>
       <c r="R391" s="25"/>
-      <c r="S391" s="25" t="s">
-        <v>381</v>
-      </c>
+      <c r="S391" s="25"/>
       <c r="T391" s="25"/>
-      <c r="U391" s="25" t="s">
-        <v>623</v>
-      </c>
+      <c r="U391" s="25"/>
       <c r="V391" s="25"/>
       <c r="W391" s="25"/>
       <c r="X391" s="25"/>
-      <c r="Z391" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA391" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB391" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC391" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD391" s="25" t="s">
-        <v>19</v>
-      </c>
+      <c r="Z391" s="25"/>
+      <c r="AA391" s="25"/>
+      <c r="AB391" s="25"/>
+      <c r="AC391" s="25"/>
+      <c r="AD391" s="25"/>
       <c r="AE391" s="25"/>
-      <c r="AF391" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG391" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH391" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AI391" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ391" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AK391" s="25" t="s">
-        <v>25</v>
-      </c>
+      <c r="AF391" s="25"/>
+      <c r="AG391" s="25"/>
+      <c r="AH391" s="25"/>
+      <c r="AI391" s="25"/>
+      <c r="AJ391" s="25"/>
+      <c r="AK391" s="25"/>
       <c r="AM391" s="25"/>
       <c r="AN391" s="25" t="s">
-        <v>1530</v>
+        <v>780</v>
       </c>
       <c r="AO391" s="25"/>
       <c r="AP391" s="25"/>
@@ -63078,20 +63080,20 @@
       <c r="B623" s="25"/>
       <c r="C623" s="25"/>
       <c r="D623" s="25" t="s">
-        <v>638</v>
+        <v>2381</v>
       </c>
       <c r="E623" s="37" t="s">
-        <v>2214</v>
+        <v>2379</v>
       </c>
       <c r="F623" s="25" t="s">
-        <v>83</v>
+        <v>2380</v>
       </c>
       <c r="G623" s="25" t="s">
-        <v>89</v>
+        <v>2</v>
       </c>
       <c r="H623" s="25"/>
       <c r="I623" s="25" t="s">
-        <v>639</v>
+        <v>2381</v>
       </c>
       <c r="J623" s="25"/>
       <c r="K623" s="25" t="s">
@@ -63104,36 +63106,32 @@
       <c r="N623" s="25"/>
       <c r="O623" s="25"/>
       <c r="P623" s="25"/>
-      <c r="Q623" s="25" t="s">
-        <v>1640</v>
-      </c>
+      <c r="Q623" s="25"/>
       <c r="R623" s="25"/>
       <c r="S623" s="25"/>
-      <c r="T623" s="25" t="s">
-        <v>1474</v>
-      </c>
+      <c r="T623" s="25"/>
       <c r="U623" s="25"/>
       <c r="V623" s="25"/>
       <c r="W623" s="25"/>
       <c r="X623" s="25"/>
       <c r="Z623" s="25" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="AA623" s="25" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="AB623" s="25" t="s">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="AC623" s="25" t="s">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="AD623" s="25" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="AE623" s="25"/>
       <c r="AF623" s="25" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="AG623" s="25" t="s">
         <v>19</v>
@@ -63145,10 +63143,10 @@
         <v>76</v>
       </c>
       <c r="AJ623" s="25" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="AK623" s="25" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="AM623" s="25"/>
       <c r="AN623" s="25"/>
@@ -63171,7 +63169,7 @@
       <c r="B624" s="25"/>
       <c r="C624" s="25"/>
       <c r="D624" s="25" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E624" s="37" t="s">
         <v>2214</v>
@@ -63198,7 +63196,7 @@
       <c r="O624" s="25"/>
       <c r="P624" s="25"/>
       <c r="Q624" s="25" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="R624" s="25"/>
       <c r="S624" s="25"/>
@@ -63210,38 +63208,38 @@
       <c r="W624" s="25"/>
       <c r="X624" s="25"/>
       <c r="Z624" s="25" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="AA624" s="25" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="AB624" s="25" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="AC624" s="25" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="AD624" s="25" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="AE624" s="25"/>
       <c r="AF624" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG624" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AH624" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI624" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="AG624" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="AH624" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI624" s="25" t="s">
-        <v>70</v>
-      </c>
       <c r="AJ624" s="25" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="AK624" s="25" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="AM624" s="25"/>
       <c r="AN624" s="25"/>
@@ -63264,20 +63262,20 @@
       <c r="B625" s="25"/>
       <c r="C625" s="25"/>
       <c r="D625" s="25" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="E625" s="37" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="F625" s="25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G625" s="25" t="s">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="H625" s="25"/>
       <c r="I625" s="25" t="s">
-        <v>1475</v>
+        <v>639</v>
       </c>
       <c r="J625" s="25"/>
       <c r="K625" s="25" t="s">
@@ -63291,12 +63289,12 @@
       <c r="O625" s="25"/>
       <c r="P625" s="25"/>
       <c r="Q625" s="25" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="R625" s="25"/>
       <c r="S625" s="25"/>
       <c r="T625" s="25" t="s">
-        <v>42</v>
+        <v>1474</v>
       </c>
       <c r="U625" s="25"/>
       <c r="V625" s="25"/>
@@ -63309,29 +63307,29 @@
         <v>76</v>
       </c>
       <c r="AB625" s="25" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="AC625" s="25" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="AD625" s="25" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="AE625" s="25"/>
       <c r="AF625" s="25" t="s">
         <v>76</v>
       </c>
       <c r="AG625" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="AH625" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="AI625" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ625" s="25" t="s">
         <v>76</v>
-      </c>
-      <c r="AH625" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="AI625" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="AJ625" s="25" t="s">
-        <v>19</v>
       </c>
       <c r="AK625" s="25" t="s">
         <v>76</v>
@@ -63351,287 +63349,315 @@
       <c r="AZ625" s="26"/>
     </row>
     <row r="626" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A626" s="9"/>
-      <c r="AM626" s="40"/>
-      <c r="AN626" s="40"/>
-      <c r="AO626" s="40"/>
-      <c r="AP626" s="40"/>
-      <c r="AQ626" s="40"/>
-      <c r="AR626" s="40"/>
-      <c r="AS626" s="40"/>
-      <c r="AT626" s="40"/>
-      <c r="AU626" s="40"/>
-      <c r="AV626" s="40"/>
-      <c r="AW626" s="40"/>
-      <c r="AX626" s="40"/>
-      <c r="AZ626" s="13"/>
+      <c r="A626" s="33">
+        <v>100</v>
+      </c>
+      <c r="B626" s="25"/>
+      <c r="C626" s="25"/>
+      <c r="D626" s="25" t="s">
+        <v>640</v>
+      </c>
+      <c r="E626" s="37" t="s">
+        <v>2215</v>
+      </c>
+      <c r="F626" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="G626" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="H626" s="25"/>
+      <c r="I626" s="25" t="s">
+        <v>1475</v>
+      </c>
+      <c r="J626" s="25"/>
+      <c r="K626" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="L626" s="25"/>
+      <c r="M626" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="N626" s="25"/>
+      <c r="O626" s="25"/>
+      <c r="P626" s="25"/>
+      <c r="Q626" s="25" t="s">
+        <v>1642</v>
+      </c>
+      <c r="R626" s="25"/>
+      <c r="S626" s="25"/>
+      <c r="T626" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="U626" s="25"/>
+      <c r="V626" s="25"/>
+      <c r="W626" s="25"/>
+      <c r="X626" s="25"/>
+      <c r="Z626" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA626" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB626" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC626" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD626" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE626" s="25"/>
+      <c r="AF626" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG626" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="AH626" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="AI626" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ626" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AK626" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="AM626" s="25"/>
+      <c r="AN626" s="25"/>
+      <c r="AO626" s="25"/>
+      <c r="AP626" s="25"/>
+      <c r="AQ626" s="25"/>
+      <c r="AR626" s="25"/>
+      <c r="AS626" s="25"/>
+      <c r="AT626" s="25"/>
+      <c r="AU626" s="25"/>
+      <c r="AV626" s="25"/>
+      <c r="AW626" s="25"/>
+      <c r="AX626" s="25"/>
+      <c r="AZ626" s="26"/>
     </row>
     <row r="627" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A627" s="33">
+      <c r="A627" s="9"/>
+      <c r="AM627" s="40"/>
+      <c r="AN627" s="40"/>
+      <c r="AO627" s="40"/>
+      <c r="AP627" s="40"/>
+      <c r="AQ627" s="40"/>
+      <c r="AR627" s="40"/>
+      <c r="AS627" s="40"/>
+      <c r="AT627" s="40"/>
+      <c r="AU627" s="40"/>
+      <c r="AV627" s="40"/>
+      <c r="AW627" s="40"/>
+      <c r="AX627" s="40"/>
+      <c r="AZ627" s="13"/>
+    </row>
+    <row r="628" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A628" s="33">
         <v>110</v>
       </c>
-      <c r="B627" s="33" t="s">
+      <c r="B628" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C627" s="33"/>
-      <c r="D627" s="33" t="s">
+      <c r="C628" s="33"/>
+      <c r="D628" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="E627" s="34"/>
-      <c r="F627" s="33"/>
-      <c r="G627" s="33"/>
-      <c r="H627" s="33"/>
-      <c r="I627" s="33" t="s">
+      <c r="E628" s="34"/>
+      <c r="F628" s="33"/>
+      <c r="G628" s="33"/>
+      <c r="H628" s="33"/>
+      <c r="I628" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="J627" s="33"/>
-      <c r="K627" s="33" t="s">
+      <c r="J628" s="33"/>
+      <c r="K628" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="L627" s="33"/>
-      <c r="M627" s="33" t="s">
+      <c r="L628" s="33"/>
+      <c r="M628" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="N627" s="33" t="s">
+      <c r="N628" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="O627" s="33"/>
-      <c r="P627" s="33"/>
-      <c r="Q627" s="36"/>
-      <c r="R627" s="36"/>
-      <c r="S627" s="36"/>
-      <c r="T627" s="36"/>
-      <c r="U627" s="36"/>
-      <c r="V627" s="36"/>
-      <c r="W627" s="36"/>
-      <c r="X627" s="36"/>
-      <c r="Y627" s="49"/>
-      <c r="Z627" s="36"/>
-      <c r="AA627" s="36"/>
-      <c r="AB627" s="36"/>
-      <c r="AC627" s="36"/>
-      <c r="AD627" s="36"/>
-      <c r="AE627" s="36"/>
-      <c r="AF627" s="36"/>
-      <c r="AG627" s="36"/>
-      <c r="AH627" s="36"/>
-      <c r="AI627" s="36"/>
-      <c r="AJ627" s="36"/>
-      <c r="AK627" s="36"/>
-      <c r="AL627" s="49"/>
-      <c r="AM627" s="33"/>
-      <c r="AN627" s="33"/>
-      <c r="AO627" s="33"/>
-      <c r="AP627" s="33"/>
-      <c r="AQ627" s="33"/>
-      <c r="AR627" s="33"/>
-      <c r="AS627" s="33"/>
-      <c r="AT627" s="33"/>
-      <c r="AU627" s="33"/>
-      <c r="AV627" s="33"/>
-      <c r="AW627" s="33"/>
-      <c r="AX627" s="33"/>
-      <c r="AY627" s="49"/>
-      <c r="AZ627" s="35"/>
-    </row>
-    <row r="628" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A628" s="9"/>
-      <c r="AM628" s="40"/>
-      <c r="AN628" s="40"/>
-      <c r="AO628" s="40"/>
-      <c r="AP628" s="40"/>
-      <c r="AQ628" s="40"/>
-      <c r="AR628" s="40"/>
-      <c r="AS628" s="40"/>
-      <c r="AT628" s="40"/>
-      <c r="AU628" s="40"/>
-      <c r="AV628" s="40"/>
-      <c r="AW628" s="40"/>
-      <c r="AX628" s="40"/>
-      <c r="AZ628" s="13"/>
+      <c r="O628" s="33"/>
+      <c r="P628" s="33"/>
+      <c r="Q628" s="36"/>
+      <c r="R628" s="36"/>
+      <c r="S628" s="36"/>
+      <c r="T628" s="36"/>
+      <c r="U628" s="36"/>
+      <c r="V628" s="36"/>
+      <c r="W628" s="36"/>
+      <c r="X628" s="36"/>
+      <c r="Y628" s="49"/>
+      <c r="Z628" s="36"/>
+      <c r="AA628" s="36"/>
+      <c r="AB628" s="36"/>
+      <c r="AC628" s="36"/>
+      <c r="AD628" s="36"/>
+      <c r="AE628" s="36"/>
+      <c r="AF628" s="36"/>
+      <c r="AG628" s="36"/>
+      <c r="AH628" s="36"/>
+      <c r="AI628" s="36"/>
+      <c r="AJ628" s="36"/>
+      <c r="AK628" s="36"/>
+      <c r="AL628" s="49"/>
+      <c r="AM628" s="33"/>
+      <c r="AN628" s="33"/>
+      <c r="AO628" s="33"/>
+      <c r="AP628" s="33"/>
+      <c r="AQ628" s="33"/>
+      <c r="AR628" s="33"/>
+      <c r="AS628" s="33"/>
+      <c r="AT628" s="33"/>
+      <c r="AU628" s="33"/>
+      <c r="AV628" s="33"/>
+      <c r="AW628" s="33"/>
+      <c r="AX628" s="33"/>
+      <c r="AY628" s="49"/>
+      <c r="AZ628" s="35"/>
     </row>
     <row r="629" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A629" s="33">
-        <v>120</v>
-      </c>
-      <c r="B629" s="33" t="s">
-        <v>829</v>
-      </c>
-      <c r="C629" s="33"/>
-      <c r="D629" s="33" t="s">
-        <v>830</v>
-      </c>
-      <c r="E629" s="34"/>
-      <c r="F629" s="33"/>
-      <c r="G629" s="33"/>
-      <c r="H629" s="33"/>
-      <c r="I629" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="J629" s="33"/>
-      <c r="K629" s="33" t="s">
-        <v>131</v>
-      </c>
-      <c r="L629" s="33"/>
-      <c r="M629" s="33"/>
-      <c r="N629" s="33"/>
-      <c r="O629" s="33"/>
-      <c r="P629" s="33"/>
-      <c r="Q629" s="36"/>
-      <c r="R629" s="36"/>
-      <c r="S629" s="36"/>
-      <c r="T629" s="36"/>
-      <c r="U629" s="36"/>
-      <c r="V629" s="36"/>
-      <c r="W629" s="36"/>
-      <c r="X629" s="36"/>
-      <c r="Y629" s="49"/>
-      <c r="Z629" s="36"/>
-      <c r="AA629" s="36"/>
-      <c r="AB629" s="36"/>
-      <c r="AC629" s="36"/>
-      <c r="AD629" s="36"/>
-      <c r="AE629" s="36"/>
-      <c r="AF629" s="36"/>
-      <c r="AG629" s="36"/>
-      <c r="AH629" s="36"/>
-      <c r="AI629" s="36"/>
-      <c r="AJ629" s="36"/>
-      <c r="AK629" s="36"/>
-      <c r="AL629" s="49"/>
-      <c r="AM629" s="33"/>
-      <c r="AN629" s="33"/>
-      <c r="AO629" s="33"/>
-      <c r="AP629" s="33"/>
-      <c r="AQ629" s="33"/>
-      <c r="AR629" s="33"/>
-      <c r="AS629" s="33"/>
-      <c r="AT629" s="33"/>
-      <c r="AU629" s="33"/>
-      <c r="AV629" s="33"/>
-      <c r="AW629" s="33" t="s">
-        <v>1476</v>
-      </c>
-      <c r="AX629" s="33" t="s">
-        <v>1476</v>
-      </c>
-      <c r="AY629" s="49"/>
-      <c r="AZ629" s="35"/>
+      <c r="A629" s="9"/>
+      <c r="AM629" s="40"/>
+      <c r="AN629" s="40"/>
+      <c r="AO629" s="40"/>
+      <c r="AP629" s="40"/>
+      <c r="AQ629" s="40"/>
+      <c r="AR629" s="40"/>
+      <c r="AS629" s="40"/>
+      <c r="AT629" s="40"/>
+      <c r="AU629" s="40"/>
+      <c r="AV629" s="40"/>
+      <c r="AW629" s="40"/>
+      <c r="AX629" s="40"/>
+      <c r="AZ629" s="13"/>
     </row>
     <row r="630" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A630" s="33">
         <v>120</v>
       </c>
-      <c r="B630" s="27"/>
-      <c r="C630" s="27"/>
-      <c r="D630" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="E630" s="28" t="s">
-        <v>2180</v>
-      </c>
-      <c r="F630" s="27" t="s">
-        <v>569</v>
-      </c>
-      <c r="G630" s="27"/>
-      <c r="H630" s="27"/>
-      <c r="I630" s="27" t="s">
-        <v>1457</v>
-      </c>
-      <c r="J630" s="27"/>
-      <c r="K630" s="27" t="s">
+      <c r="B630" s="33" t="s">
+        <v>829</v>
+      </c>
+      <c r="C630" s="33"/>
+      <c r="D630" s="33" t="s">
+        <v>830</v>
+      </c>
+      <c r="E630" s="34"/>
+      <c r="F630" s="33"/>
+      <c r="G630" s="33"/>
+      <c r="H630" s="33"/>
+      <c r="I630" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="J630" s="33"/>
+      <c r="K630" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="L630" s="27"/>
-      <c r="M630" s="27"/>
-      <c r="N630" s="27"/>
-      <c r="O630" s="27"/>
-      <c r="P630" s="27"/>
-      <c r="Q630" s="27"/>
-      <c r="R630" s="27"/>
-      <c r="S630" s="27"/>
-      <c r="T630" s="27"/>
-      <c r="U630" s="27"/>
-      <c r="V630" s="27"/>
-      <c r="W630" s="27"/>
-      <c r="X630" s="27"/>
-      <c r="Z630" s="27"/>
-      <c r="AA630" s="27"/>
-      <c r="AB630" s="27"/>
-      <c r="AC630" s="27"/>
-      <c r="AD630" s="27"/>
-      <c r="AE630" s="27"/>
-      <c r="AF630" s="27"/>
-      <c r="AG630" s="27"/>
-      <c r="AH630" s="27"/>
-      <c r="AI630" s="27"/>
-      <c r="AJ630" s="27"/>
-      <c r="AK630" s="27"/>
-      <c r="AM630" s="25"/>
-      <c r="AN630" s="25"/>
-      <c r="AO630" s="25"/>
-      <c r="AP630" s="25"/>
-      <c r="AQ630" s="25"/>
-      <c r="AR630" s="25"/>
-      <c r="AS630" s="25"/>
-      <c r="AT630" s="25"/>
-      <c r="AU630" s="25"/>
-      <c r="AV630" s="25"/>
-      <c r="AW630" s="25" t="s">
-        <v>1376</v>
-      </c>
-      <c r="AX630" s="25"/>
-      <c r="AZ630" s="29"/>
+      <c r="L630" s="33"/>
+      <c r="M630" s="33"/>
+      <c r="N630" s="33"/>
+      <c r="O630" s="33"/>
+      <c r="P630" s="33"/>
+      <c r="Q630" s="36"/>
+      <c r="R630" s="36"/>
+      <c r="S630" s="36"/>
+      <c r="T630" s="36"/>
+      <c r="U630" s="36"/>
+      <c r="V630" s="36"/>
+      <c r="W630" s="36"/>
+      <c r="X630" s="36"/>
+      <c r="Y630" s="49"/>
+      <c r="Z630" s="36"/>
+      <c r="AA630" s="36"/>
+      <c r="AB630" s="36"/>
+      <c r="AC630" s="36"/>
+      <c r="AD630" s="36"/>
+      <c r="AE630" s="36"/>
+      <c r="AF630" s="36"/>
+      <c r="AG630" s="36"/>
+      <c r="AH630" s="36"/>
+      <c r="AI630" s="36"/>
+      <c r="AJ630" s="36"/>
+      <c r="AK630" s="36"/>
+      <c r="AL630" s="49"/>
+      <c r="AM630" s="33"/>
+      <c r="AN630" s="33"/>
+      <c r="AO630" s="33"/>
+      <c r="AP630" s="33"/>
+      <c r="AQ630" s="33"/>
+      <c r="AR630" s="33"/>
+      <c r="AS630" s="33"/>
+      <c r="AT630" s="33"/>
+      <c r="AU630" s="33"/>
+      <c r="AV630" s="33"/>
+      <c r="AW630" s="33" t="s">
+        <v>1476</v>
+      </c>
+      <c r="AX630" s="33" t="s">
+        <v>1476</v>
+      </c>
+      <c r="AY630" s="49"/>
+      <c r="AZ630" s="35"/>
     </row>
     <row r="631" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A631" s="33">
         <v>120</v>
       </c>
-      <c r="B631" s="25"/>
-      <c r="C631" s="25"/>
-      <c r="D631" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="E631" s="37" t="s">
-        <v>2181</v>
-      </c>
-      <c r="F631" s="25" t="s">
-        <v>570</v>
-      </c>
-      <c r="G631" s="25"/>
-      <c r="H631" s="25"/>
-      <c r="I631" s="25" t="s">
-        <v>1458</v>
-      </c>
-      <c r="J631" s="25"/>
-      <c r="K631" s="25" t="s">
+      <c r="B631" s="27"/>
+      <c r="C631" s="27"/>
+      <c r="D631" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="E631" s="28" t="s">
+        <v>2180</v>
+      </c>
+      <c r="F631" s="27" t="s">
+        <v>569</v>
+      </c>
+      <c r="G631" s="27"/>
+      <c r="H631" s="27"/>
+      <c r="I631" s="27" t="s">
+        <v>1457</v>
+      </c>
+      <c r="J631" s="27"/>
+      <c r="K631" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="L631" s="25"/>
-      <c r="M631" s="25"/>
-      <c r="N631" s="25"/>
-      <c r="O631" s="25"/>
-      <c r="P631" s="25"/>
-      <c r="Q631" s="25"/>
-      <c r="R631" s="25"/>
-      <c r="S631" s="25"/>
-      <c r="T631" s="25"/>
-      <c r="U631" s="25"/>
-      <c r="V631" s="25"/>
-      <c r="W631" s="25"/>
-      <c r="X631" s="25"/>
-      <c r="Z631" s="25"/>
-      <c r="AA631" s="25"/>
-      <c r="AB631" s="25"/>
-      <c r="AC631" s="25"/>
-      <c r="AD631" s="25"/>
-      <c r="AE631" s="25"/>
-      <c r="AF631" s="25"/>
-      <c r="AG631" s="25"/>
-      <c r="AH631" s="25"/>
-      <c r="AI631" s="25"/>
-      <c r="AJ631" s="25"/>
-      <c r="AK631" s="25"/>
+      <c r="L631" s="27"/>
+      <c r="M631" s="27"/>
+      <c r="N631" s="27"/>
+      <c r="O631" s="27"/>
+      <c r="P631" s="27"/>
+      <c r="Q631" s="27"/>
+      <c r="R631" s="27"/>
+      <c r="S631" s="27"/>
+      <c r="T631" s="27"/>
+      <c r="U631" s="27"/>
+      <c r="V631" s="27"/>
+      <c r="W631" s="27"/>
+      <c r="X631" s="27"/>
+      <c r="Z631" s="27"/>
+      <c r="AA631" s="27"/>
+      <c r="AB631" s="27"/>
+      <c r="AC631" s="27"/>
+      <c r="AD631" s="27"/>
+      <c r="AE631" s="27"/>
+      <c r="AF631" s="27"/>
+      <c r="AG631" s="27"/>
+      <c r="AH631" s="27"/>
+      <c r="AI631" s="27"/>
+      <c r="AJ631" s="27"/>
+      <c r="AK631" s="27"/>
       <c r="AM631" s="25"/>
       <c r="AN631" s="25"/>
       <c r="AO631" s="25"/>
@@ -63643,10 +63669,10 @@
       <c r="AU631" s="25"/>
       <c r="AV631" s="25"/>
       <c r="AW631" s="25" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="AX631" s="25"/>
-      <c r="AZ631" s="26"/>
+      <c r="AZ631" s="29"/>
     </row>
     <row r="632" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A632" s="33">
@@ -63655,18 +63681,18 @@
       <c r="B632" s="25"/>
       <c r="C632" s="25"/>
       <c r="D632" s="25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E632" s="37" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="F632" s="25" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G632" s="25"/>
       <c r="H632" s="25"/>
       <c r="I632" s="25" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="J632" s="25"/>
       <c r="K632" s="25" t="s">
@@ -63708,7 +63734,7 @@
       <c r="AU632" s="25"/>
       <c r="AV632" s="25"/>
       <c r="AW632" s="25" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="AX632" s="25"/>
       <c r="AZ632" s="26"/>
@@ -63720,18 +63746,18 @@
       <c r="B633" s="25"/>
       <c r="C633" s="25"/>
       <c r="D633" s="25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E633" s="37" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
       <c r="F633" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G633" s="25"/>
       <c r="H633" s="25"/>
       <c r="I633" s="25" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="J633" s="25"/>
       <c r="K633" s="25" t="s">
@@ -63773,7 +63799,7 @@
       <c r="AU633" s="25"/>
       <c r="AV633" s="25"/>
       <c r="AW633" s="25" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="AX633" s="25"/>
       <c r="AZ633" s="26"/>
@@ -63785,18 +63811,18 @@
       <c r="B634" s="25"/>
       <c r="C634" s="25"/>
       <c r="D634" s="25" t="s">
-        <v>151</v>
+        <v>79</v>
       </c>
       <c r="E634" s="37" t="s">
-        <v>1891</v>
+        <v>2183</v>
       </c>
       <c r="F634" s="25" t="s">
-        <v>831</v>
+        <v>572</v>
       </c>
       <c r="G634" s="25"/>
       <c r="H634" s="25"/>
       <c r="I634" s="25" t="s">
-        <v>158</v>
+        <v>1460</v>
       </c>
       <c r="J634" s="25"/>
       <c r="K634" s="25" t="s">
@@ -63838,7 +63864,7 @@
       <c r="AU634" s="25"/>
       <c r="AV634" s="25"/>
       <c r="AW634" s="25" t="s">
-        <v>1477</v>
+        <v>1379</v>
       </c>
       <c r="AX634" s="25"/>
       <c r="AZ634" s="26"/>
@@ -63850,13 +63876,13 @@
       <c r="B635" s="25"/>
       <c r="C635" s="25"/>
       <c r="D635" s="25" t="s">
-        <v>469</v>
+        <v>151</v>
       </c>
       <c r="E635" s="37" t="s">
-        <v>2216</v>
+        <v>1891</v>
       </c>
       <c r="F635" s="25" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="G635" s="25"/>
       <c r="H635" s="25"/>
@@ -63903,7 +63929,7 @@
       <c r="AU635" s="25"/>
       <c r="AV635" s="25"/>
       <c r="AW635" s="25" t="s">
-        <v>650</v>
+        <v>1477</v>
       </c>
       <c r="AX635" s="25"/>
       <c r="AZ635" s="26"/>
@@ -63915,13 +63941,13 @@
       <c r="B636" s="25"/>
       <c r="C636" s="25"/>
       <c r="D636" s="25" t="s">
-        <v>191</v>
+        <v>469</v>
       </c>
       <c r="E636" s="37" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="F636" s="25" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="G636" s="25"/>
       <c r="H636" s="25"/>
@@ -63968,7 +63994,7 @@
       <c r="AU636" s="25"/>
       <c r="AV636" s="25"/>
       <c r="AW636" s="25" t="s">
-        <v>1226</v>
+        <v>650</v>
       </c>
       <c r="AX636" s="25"/>
       <c r="AZ636" s="26"/>
@@ -63980,13 +64006,13 @@
       <c r="B637" s="25"/>
       <c r="C637" s="25"/>
       <c r="D637" s="25" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E637" s="37" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
       <c r="F637" s="25" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="G637" s="25"/>
       <c r="H637" s="25"/>
@@ -64033,7 +64059,7 @@
       <c r="AU637" s="25"/>
       <c r="AV637" s="25"/>
       <c r="AW637" s="25" t="s">
-        <v>652</v>
+        <v>1226</v>
       </c>
       <c r="AX637" s="25"/>
       <c r="AZ637" s="26"/>
@@ -64045,13 +64071,13 @@
       <c r="B638" s="25"/>
       <c r="C638" s="25"/>
       <c r="D638" s="25" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E638" s="37" t="s">
-        <v>2219</v>
+        <v>2218</v>
       </c>
       <c r="F638" s="25" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="G638" s="25"/>
       <c r="H638" s="25"/>
@@ -64098,7 +64124,7 @@
       <c r="AU638" s="25"/>
       <c r="AV638" s="25"/>
       <c r="AW638" s="25" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="AX638" s="25"/>
       <c r="AZ638" s="26"/>
@@ -64110,18 +64136,18 @@
       <c r="B639" s="25"/>
       <c r="C639" s="25"/>
       <c r="D639" s="25" t="s">
-        <v>246</v>
+        <v>195</v>
       </c>
       <c r="E639" s="37" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="F639" s="25" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="G639" s="25"/>
       <c r="H639" s="25"/>
       <c r="I639" s="25" t="s">
-        <v>1392</v>
+        <v>158</v>
       </c>
       <c r="J639" s="25"/>
       <c r="K639" s="25" t="s">
@@ -64163,7 +64189,7 @@
       <c r="AU639" s="25"/>
       <c r="AV639" s="25"/>
       <c r="AW639" s="25" t="s">
-        <v>1478</v>
+        <v>654</v>
       </c>
       <c r="AX639" s="25"/>
       <c r="AZ639" s="26"/>
@@ -64175,18 +64201,18 @@
       <c r="B640" s="25"/>
       <c r="C640" s="25"/>
       <c r="D640" s="25" t="s">
-        <v>573</v>
+        <v>246</v>
       </c>
       <c r="E640" s="37" t="s">
-        <v>2221</v>
+        <v>2220</v>
       </c>
       <c r="F640" s="25" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="G640" s="25"/>
       <c r="H640" s="25"/>
       <c r="I640" s="25" t="s">
-        <v>1398</v>
+        <v>1392</v>
       </c>
       <c r="J640" s="25"/>
       <c r="K640" s="25" t="s">
@@ -64228,7 +64254,7 @@
       <c r="AU640" s="25"/>
       <c r="AV640" s="25"/>
       <c r="AW640" s="25" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="AX640" s="25"/>
       <c r="AZ640" s="26"/>
@@ -64240,18 +64266,18 @@
       <c r="B641" s="25"/>
       <c r="C641" s="25"/>
       <c r="D641" s="25" t="s">
-        <v>838</v>
+        <v>573</v>
       </c>
       <c r="E641" s="37" t="s">
-        <v>1906</v>
+        <v>2221</v>
       </c>
       <c r="F641" s="25" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="G641" s="25"/>
       <c r="H641" s="25"/>
       <c r="I641" s="25" t="s">
-        <v>1312</v>
+        <v>1398</v>
       </c>
       <c r="J641" s="25"/>
       <c r="K641" s="25" t="s">
@@ -64293,7 +64319,7 @@
       <c r="AU641" s="25"/>
       <c r="AV641" s="25"/>
       <c r="AW641" s="25" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="AX641" s="25"/>
       <c r="AZ641" s="26"/>
@@ -64305,18 +64331,18 @@
       <c r="B642" s="25"/>
       <c r="C642" s="25"/>
       <c r="D642" s="25" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="E642" s="37" t="s">
-        <v>2222</v>
+        <v>1906</v>
       </c>
       <c r="F642" s="25" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="G642" s="25"/>
       <c r="H642" s="25"/>
       <c r="I642" s="25" t="s">
-        <v>138</v>
+        <v>1312</v>
       </c>
       <c r="J642" s="25"/>
       <c r="K642" s="25" t="s">
@@ -64358,7 +64384,7 @@
       <c r="AU642" s="25"/>
       <c r="AV642" s="25"/>
       <c r="AW642" s="25" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="AX642" s="25"/>
       <c r="AZ642" s="26"/>
@@ -64370,18 +64396,18 @@
       <c r="B643" s="25"/>
       <c r="C643" s="25"/>
       <c r="D643" s="25" t="s">
-        <v>197</v>
+        <v>840</v>
       </c>
       <c r="E643" s="37" t="s">
-        <v>1904</v>
+        <v>2222</v>
       </c>
       <c r="F643" s="25" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="G643" s="25"/>
       <c r="H643" s="25"/>
       <c r="I643" s="25" t="s">
-        <v>1310</v>
+        <v>138</v>
       </c>
       <c r="J643" s="25"/>
       <c r="K643" s="25" t="s">
@@ -64423,7 +64449,7 @@
       <c r="AU643" s="25"/>
       <c r="AV643" s="25"/>
       <c r="AW643" s="25" t="s">
-        <v>908</v>
+        <v>1481</v>
       </c>
       <c r="AX643" s="25"/>
       <c r="AZ643" s="26"/>
@@ -64435,18 +64461,18 @@
       <c r="B644" s="25"/>
       <c r="C644" s="25"/>
       <c r="D644" s="25" t="s">
-        <v>843</v>
+        <v>197</v>
       </c>
       <c r="E644" s="37" t="s">
-        <v>2223</v>
+        <v>1904</v>
       </c>
       <c r="F644" s="25" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="G644" s="25"/>
       <c r="H644" s="25"/>
       <c r="I644" s="25" t="s">
-        <v>875</v>
+        <v>1310</v>
       </c>
       <c r="J644" s="25"/>
       <c r="K644" s="25" t="s">
@@ -64487,10 +64513,10 @@
       <c r="AT644" s="25"/>
       <c r="AU644" s="25"/>
       <c r="AV644" s="25"/>
-      <c r="AW644" s="25"/>
-      <c r="AX644" s="25" t="s">
-        <v>1482</v>
-      </c>
+      <c r="AW644" s="25" t="s">
+        <v>908</v>
+      </c>
+      <c r="AX644" s="25"/>
       <c r="AZ644" s="26"/>
     </row>
     <row r="645" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
@@ -64500,18 +64526,18 @@
       <c r="B645" s="25"/>
       <c r="C645" s="25"/>
       <c r="D645" s="25" t="s">
-        <v>854</v>
+        <v>843</v>
       </c>
       <c r="E645" s="37" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
       <c r="F645" s="25" t="s">
-        <v>855</v>
+        <v>844</v>
       </c>
       <c r="G645" s="25"/>
       <c r="H645" s="25"/>
       <c r="I645" s="25" t="s">
-        <v>51</v>
+        <v>875</v>
       </c>
       <c r="J645" s="25"/>
       <c r="K645" s="25" t="s">
@@ -64554,7 +64580,7 @@
       <c r="AV645" s="25"/>
       <c r="AW645" s="25"/>
       <c r="AX645" s="25" t="s">
-        <v>854</v>
+        <v>1482</v>
       </c>
       <c r="AZ645" s="26"/>
     </row>
@@ -64565,18 +64591,18 @@
       <c r="B646" s="25"/>
       <c r="C646" s="25"/>
       <c r="D646" s="25" t="s">
-        <v>666</v>
+        <v>854</v>
       </c>
       <c r="E646" s="37" t="s">
-        <v>2063</v>
+        <v>2224</v>
       </c>
       <c r="F646" s="25" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="G646" s="25"/>
       <c r="H646" s="25"/>
       <c r="I646" s="25" t="s">
-        <v>875</v>
+        <v>51</v>
       </c>
       <c r="J646" s="25"/>
       <c r="K646" s="25" t="s">
@@ -64619,69 +64645,130 @@
       <c r="AV646" s="25"/>
       <c r="AW646" s="25"/>
       <c r="AX646" s="25" t="s">
+        <v>854</v>
+      </c>
+      <c r="AZ646" s="26"/>
+    </row>
+    <row r="647" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A647" s="33">
+        <v>120</v>
+      </c>
+      <c r="B647" s="25"/>
+      <c r="C647" s="25"/>
+      <c r="D647" s="25" t="s">
         <v>666</v>
       </c>
-      <c r="AZ646" s="26"/>
-    </row>
-    <row r="647" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A647" s="5"/>
-      <c r="B647" s="6"/>
-      <c r="C647" s="6"/>
-      <c r="D647" s="8" t="s">
+      <c r="E647" s="37" t="s">
+        <v>2063</v>
+      </c>
+      <c r="F647" s="25" t="s">
+        <v>856</v>
+      </c>
+      <c r="G647" s="25"/>
+      <c r="H647" s="25"/>
+      <c r="I647" s="25" t="s">
+        <v>875</v>
+      </c>
+      <c r="J647" s="25"/>
+      <c r="K647" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="L647" s="25"/>
+      <c r="M647" s="25"/>
+      <c r="N647" s="25"/>
+      <c r="O647" s="25"/>
+      <c r="P647" s="25"/>
+      <c r="Q647" s="25"/>
+      <c r="R647" s="25"/>
+      <c r="S647" s="25"/>
+      <c r="T647" s="25"/>
+      <c r="U647" s="25"/>
+      <c r="V647" s="25"/>
+      <c r="W647" s="25"/>
+      <c r="X647" s="25"/>
+      <c r="Z647" s="25"/>
+      <c r="AA647" s="25"/>
+      <c r="AB647" s="25"/>
+      <c r="AC647" s="25"/>
+      <c r="AD647" s="25"/>
+      <c r="AE647" s="25"/>
+      <c r="AF647" s="25"/>
+      <c r="AG647" s="25"/>
+      <c r="AH647" s="25"/>
+      <c r="AI647" s="25"/>
+      <c r="AJ647" s="25"/>
+      <c r="AK647" s="25"/>
+      <c r="AM647" s="25"/>
+      <c r="AN647" s="25"/>
+      <c r="AO647" s="25"/>
+      <c r="AP647" s="25"/>
+      <c r="AQ647" s="25"/>
+      <c r="AR647" s="25"/>
+      <c r="AS647" s="25"/>
+      <c r="AT647" s="25"/>
+      <c r="AU647" s="25"/>
+      <c r="AV647" s="25"/>
+      <c r="AW647" s="25"/>
+      <c r="AX647" s="25" t="s">
+        <v>666</v>
+      </c>
+      <c r="AZ647" s="26"/>
+    </row>
+    <row r="648" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A648" s="5"/>
+      <c r="B648" s="6"/>
+      <c r="C648" s="6"/>
+      <c r="D648" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E647" s="8"/>
-      <c r="F647" s="8"/>
-      <c r="G647" s="8"/>
-      <c r="H647" s="8"/>
-      <c r="I647" s="8"/>
-      <c r="J647" s="8"/>
-      <c r="K647" s="8"/>
-      <c r="L647" s="8"/>
-      <c r="M647" s="8"/>
-      <c r="N647" s="8"/>
-      <c r="O647" s="8"/>
-      <c r="P647" s="8"/>
-      <c r="Q647" s="8"/>
-      <c r="R647" s="8"/>
-      <c r="S647" s="8"/>
-      <c r="T647" s="8"/>
-      <c r="U647" s="8"/>
-      <c r="V647" s="8"/>
-      <c r="W647" s="8"/>
-      <c r="X647" s="8"/>
-      <c r="Y647" s="8"/>
-      <c r="Z647" s="8"/>
-      <c r="AA647" s="8"/>
-      <c r="AB647" s="8"/>
-      <c r="AC647" s="8"/>
-      <c r="AD647" s="8"/>
-      <c r="AE647" s="8"/>
-      <c r="AF647" s="8"/>
-      <c r="AG647" s="8"/>
-      <c r="AH647" s="8"/>
-      <c r="AI647" s="8"/>
-      <c r="AJ647" s="8"/>
-      <c r="AK647" s="8"/>
-      <c r="AL647" s="8"/>
-      <c r="AM647" s="8"/>
-      <c r="AN647" s="8"/>
-      <c r="AO647" s="8"/>
-      <c r="AP647" s="8"/>
-      <c r="AQ647" s="8"/>
-      <c r="AR647" s="8"/>
-      <c r="AS647" s="8"/>
-      <c r="AT647" s="8"/>
-      <c r="AU647" s="8"/>
-      <c r="AV647" s="8"/>
-      <c r="AW647" s="8"/>
-      <c r="AX647" s="8"/>
-      <c r="AY647" s="8"/>
-      <c r="AZ647" s="30"/>
-    </row>
-    <row r="648" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A648" s="9"/>
-      <c r="AZ648" s="13"/>
+      <c r="E648" s="8"/>
+      <c r="F648" s="8"/>
+      <c r="G648" s="8"/>
+      <c r="H648" s="8"/>
+      <c r="I648" s="8"/>
+      <c r="J648" s="8"/>
+      <c r="K648" s="8"/>
+      <c r="L648" s="8"/>
+      <c r="M648" s="8"/>
+      <c r="N648" s="8"/>
+      <c r="O648" s="8"/>
+      <c r="P648" s="8"/>
+      <c r="Q648" s="8"/>
+      <c r="R648" s="8"/>
+      <c r="S648" s="8"/>
+      <c r="T648" s="8"/>
+      <c r="U648" s="8"/>
+      <c r="V648" s="8"/>
+      <c r="W648" s="8"/>
+      <c r="X648" s="8"/>
+      <c r="Y648" s="8"/>
+      <c r="Z648" s="8"/>
+      <c r="AA648" s="8"/>
+      <c r="AB648" s="8"/>
+      <c r="AC648" s="8"/>
+      <c r="AD648" s="8"/>
+      <c r="AE648" s="8"/>
+      <c r="AF648" s="8"/>
+      <c r="AG648" s="8"/>
+      <c r="AH648" s="8"/>
+      <c r="AI648" s="8"/>
+      <c r="AJ648" s="8"/>
+      <c r="AK648" s="8"/>
+      <c r="AL648" s="8"/>
+      <c r="AM648" s="8"/>
+      <c r="AN648" s="8"/>
+      <c r="AO648" s="8"/>
+      <c r="AP648" s="8"/>
+      <c r="AQ648" s="8"/>
+      <c r="AR648" s="8"/>
+      <c r="AS648" s="8"/>
+      <c r="AT648" s="8"/>
+      <c r="AU648" s="8"/>
+      <c r="AV648" s="8"/>
+      <c r="AW648" s="8"/>
+      <c r="AX648" s="8"/>
+      <c r="AY648" s="8"/>
+      <c r="AZ648" s="30"/>
     </row>
     <row r="649" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A649" s="9"/>
@@ -64704,58 +64791,62 @@
       <c r="AZ653" s="13"/>
     </row>
     <row r="654" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A654" s="11"/>
-      <c r="B654" s="31"/>
-      <c r="C654" s="31"/>
-      <c r="D654" s="31"/>
-      <c r="E654" s="31"/>
-      <c r="F654" s="31"/>
-      <c r="G654" s="31"/>
-      <c r="H654" s="31"/>
-      <c r="I654" s="31"/>
-      <c r="J654" s="31"/>
-      <c r="K654" s="31"/>
-      <c r="L654" s="31"/>
-      <c r="M654" s="31"/>
-      <c r="N654" s="31"/>
-      <c r="O654" s="31"/>
-      <c r="P654" s="31"/>
-      <c r="Q654" s="31"/>
-      <c r="R654" s="31"/>
-      <c r="S654" s="31"/>
-      <c r="T654" s="31"/>
-      <c r="U654" s="31"/>
-      <c r="V654" s="31"/>
-      <c r="W654" s="31"/>
-      <c r="X654" s="31"/>
-      <c r="Y654" s="31"/>
-      <c r="Z654" s="31"/>
-      <c r="AA654" s="31"/>
-      <c r="AB654" s="31"/>
-      <c r="AC654" s="31"/>
-      <c r="AD654" s="31"/>
-      <c r="AE654" s="31"/>
-      <c r="AF654" s="31"/>
-      <c r="AG654" s="31"/>
-      <c r="AH654" s="31"/>
-      <c r="AI654" s="31"/>
-      <c r="AJ654" s="31"/>
-      <c r="AK654" s="31"/>
-      <c r="AL654" s="31"/>
-      <c r="AM654" s="31"/>
-      <c r="AN654" s="31"/>
-      <c r="AO654" s="31"/>
-      <c r="AP654" s="31"/>
-      <c r="AQ654" s="31"/>
-      <c r="AR654" s="31"/>
-      <c r="AS654" s="31"/>
-      <c r="AT654" s="31"/>
-      <c r="AU654" s="31"/>
-      <c r="AV654" s="31"/>
-      <c r="AW654" s="31"/>
-      <c r="AX654" s="31"/>
-      <c r="AY654" s="31"/>
-      <c r="AZ654" s="51"/>
+      <c r="A654" s="9"/>
+      <c r="AZ654" s="13"/>
+    </row>
+    <row r="655" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A655" s="11"/>
+      <c r="B655" s="31"/>
+      <c r="C655" s="31"/>
+      <c r="D655" s="31"/>
+      <c r="E655" s="31"/>
+      <c r="F655" s="31"/>
+      <c r="G655" s="31"/>
+      <c r="H655" s="31"/>
+      <c r="I655" s="31"/>
+      <c r="J655" s="31"/>
+      <c r="K655" s="31"/>
+      <c r="L655" s="31"/>
+      <c r="M655" s="31"/>
+      <c r="N655" s="31"/>
+      <c r="O655" s="31"/>
+      <c r="P655" s="31"/>
+      <c r="Q655" s="31"/>
+      <c r="R655" s="31"/>
+      <c r="S655" s="31"/>
+      <c r="T655" s="31"/>
+      <c r="U655" s="31"/>
+      <c r="V655" s="31"/>
+      <c r="W655" s="31"/>
+      <c r="X655" s="31"/>
+      <c r="Y655" s="31"/>
+      <c r="Z655" s="31"/>
+      <c r="AA655" s="31"/>
+      <c r="AB655" s="31"/>
+      <c r="AC655" s="31"/>
+      <c r="AD655" s="31"/>
+      <c r="AE655" s="31"/>
+      <c r="AF655" s="31"/>
+      <c r="AG655" s="31"/>
+      <c r="AH655" s="31"/>
+      <c r="AI655" s="31"/>
+      <c r="AJ655" s="31"/>
+      <c r="AK655" s="31"/>
+      <c r="AL655" s="31"/>
+      <c r="AM655" s="31"/>
+      <c r="AN655" s="31"/>
+      <c r="AO655" s="31"/>
+      <c r="AP655" s="31"/>
+      <c r="AQ655" s="31"/>
+      <c r="AR655" s="31"/>
+      <c r="AS655" s="31"/>
+      <c r="AT655" s="31"/>
+      <c r="AU655" s="31"/>
+      <c r="AV655" s="31"/>
+      <c r="AW655" s="31"/>
+      <c r="AX655" s="31"/>
+      <c r="AY655" s="31"/>
+      <c r="AZ655" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -64774,74 +64865,69 @@
     <mergeCell ref="I5:J5"/>
   </mergeCells>
   <phoneticPr fontId="5"/>
-  <conditionalFormatting sqref="V279:X282 V325:X328 V330:X341">
-    <cfRule type="expression" dxfId="26" priority="44">
+  <conditionalFormatting sqref="V279:X282 V335:X346 V325:X328 V330:X331">
+    <cfRule type="expression" dxfId="25" priority="44">
       <formula>$A279=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V343:X343">
-    <cfRule type="expression" dxfId="25" priority="40">
-      <formula>$A343=""</formula>
+  <conditionalFormatting sqref="V348:X348">
+    <cfRule type="expression" dxfId="24" priority="40">
+      <formula>$A348=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V345:X345">
-    <cfRule type="expression" dxfId="24" priority="39">
-      <formula>$A345=""</formula>
+  <conditionalFormatting sqref="V350:X350">
+    <cfRule type="expression" dxfId="23" priority="39">
+      <formula>$A350=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V347:X347">
-    <cfRule type="expression" dxfId="23" priority="38">
-      <formula>$A347=""</formula>
+  <conditionalFormatting sqref="V352:X352">
+    <cfRule type="expression" dxfId="22" priority="38">
+      <formula>$A352=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V349:X349">
-    <cfRule type="expression" dxfId="22" priority="37">
-      <formula>$A349=""</formula>
+  <conditionalFormatting sqref="V354:X354">
+    <cfRule type="expression" dxfId="21" priority="37">
+      <formula>$A354=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V353:X353">
-    <cfRule type="expression" dxfId="21" priority="36">
-      <formula>$A353=""</formula>
+  <conditionalFormatting sqref="V358:X358">
+    <cfRule type="expression" dxfId="20" priority="36">
+      <formula>$A358=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V355:X355">
-    <cfRule type="expression" dxfId="20" priority="35">
-      <formula>$A355=""</formula>
+  <conditionalFormatting sqref="V360:X360">
+    <cfRule type="expression" dxfId="19" priority="35">
+      <formula>$A360=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V357:X357">
-    <cfRule type="expression" dxfId="19" priority="8">
-      <formula>$A357=""</formula>
+  <conditionalFormatting sqref="V362:X362">
+    <cfRule type="expression" dxfId="18" priority="8">
+      <formula>$A362=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V359:X359">
-    <cfRule type="expression" dxfId="18" priority="7">
-      <formula>$A359=""</formula>
+  <conditionalFormatting sqref="V364:X364">
+    <cfRule type="expression" dxfId="17" priority="7">
+      <formula>$A364=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V361:X361">
-    <cfRule type="expression" dxfId="17" priority="6">
-      <formula>$A361=""</formula>
+  <conditionalFormatting sqref="V366:X366">
+    <cfRule type="expression" dxfId="16" priority="6">
+      <formula>$A366=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V363:X363 V365:X365 V367:X367 V369:X369">
-    <cfRule type="expression" dxfId="16" priority="34">
-      <formula>$A363=""</formula>
+  <conditionalFormatting sqref="V368:X368 V370:X370 V372:X372 V374:X374">
+    <cfRule type="expression" dxfId="15" priority="34">
+      <formula>$A368=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V375:X382">
-    <cfRule type="expression" dxfId="15" priority="32">
-      <formula>$A375=""</formula>
+  <conditionalFormatting sqref="V380:X387">
+    <cfRule type="expression" dxfId="14" priority="32">
+      <formula>$A380=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V385:X386">
-    <cfRule type="expression" dxfId="14" priority="30">
-      <formula>$A385=""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V388:X389">
-    <cfRule type="expression" dxfId="13" priority="28">
-      <formula>$A388=""</formula>
+  <conditionalFormatting sqref="V390:X391">
+    <cfRule type="expression" dxfId="13" priority="30">
+      <formula>$A390=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V397:X398">
@@ -64914,7 +65000,7 @@
     <hyperlink ref="D233" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="D555" r:id="rId3" display="qtn_upd_cntr@Hdr2" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="AS555" r:id="rId4" display="qtn_upd_cntr@Hdr2" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D625" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="D626" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId6"/>

--- a/development/MS/spec/MSBB/Panel/MSBBP1210_SloReg.xlsx
+++ b/development/MS/spec/MSBB/Panel/MSBBP1210_SloReg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\mcframeDEV\development\MS\spec\MSBB\Panel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DFE13DD-CDA5-48B9-830E-7641FA3330A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{339B0663-8F18-4D1C-8C87-B8C32FF1E74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11500,14 +11500,14 @@
     <xf numFmtId="0" fontId="27" fillId="24" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -11518,7 +11518,79 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11527,8 +11599,29 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -11559,99 +11652,6 @@
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -39705,417 +39705,417 @@
       <c r="AX328" s="65"/>
       <c r="AZ328" s="68"/>
     </row>
-    <row r="329" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A329" s="50">
-        <v>70</v>
-      </c>
-      <c r="B329" s="50"/>
-      <c r="C329" s="50"/>
-      <c r="D329" s="50" t="s">
+    <row r="329" spans="1:52" s="66" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A329" s="63">
+        <v>70</v>
+      </c>
+      <c r="B329" s="63"/>
+      <c r="C329" s="63"/>
+      <c r="D329" s="63" t="s">
         <v>1030</v>
       </c>
-      <c r="E329" s="50"/>
-      <c r="F329" s="50"/>
-      <c r="G329" s="50"/>
-      <c r="H329" s="50"/>
-      <c r="I329" s="50" t="s">
+      <c r="E329" s="63"/>
+      <c r="F329" s="63"/>
+      <c r="G329" s="63"/>
+      <c r="H329" s="63"/>
+      <c r="I329" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="J329" s="50"/>
-      <c r="K329" s="50" t="s">
+      <c r="J329" s="63"/>
+      <c r="K329" s="63" t="s">
         <v>248</v>
       </c>
-      <c r="L329" s="50" t="s">
+      <c r="L329" s="63" t="s">
         <v>776</v>
       </c>
-      <c r="M329" s="50"/>
-      <c r="N329" s="50"/>
-      <c r="O329" s="50"/>
-      <c r="P329" s="50"/>
-      <c r="Q329" s="50"/>
-      <c r="R329" s="50"/>
-      <c r="S329" s="50"/>
-      <c r="T329" s="50"/>
-      <c r="U329" s="50"/>
-      <c r="V329" s="50"/>
-      <c r="W329" s="50"/>
-      <c r="X329" s="50"/>
-      <c r="Y329" s="50"/>
-      <c r="Z329" s="50" t="s">
+      <c r="M329" s="63"/>
+      <c r="N329" s="63"/>
+      <c r="O329" s="63"/>
+      <c r="P329" s="63"/>
+      <c r="Q329" s="63"/>
+      <c r="R329" s="63"/>
+      <c r="S329" s="63"/>
+      <c r="T329" s="63"/>
+      <c r="U329" s="63"/>
+      <c r="V329" s="63"/>
+      <c r="W329" s="63"/>
+      <c r="X329" s="63"/>
+      <c r="Y329" s="63"/>
+      <c r="Z329" s="63" t="s">
         <v>80</v>
       </c>
-      <c r="AA329" s="50" t="s">
+      <c r="AA329" s="63" t="s">
         <v>80</v>
       </c>
-      <c r="AB329" s="50" t="s">
+      <c r="AB329" s="63" t="s">
         <v>282</v>
       </c>
-      <c r="AC329" s="50" t="s">
+      <c r="AC329" s="63" t="s">
         <v>282</v>
       </c>
-      <c r="AD329" s="50" t="s">
+      <c r="AD329" s="63" t="s">
         <v>282</v>
       </c>
-      <c r="AE329" s="50"/>
-      <c r="AF329" s="50" t="s">
+      <c r="AE329" s="63"/>
+      <c r="AF329" s="63" t="s">
         <v>80</v>
       </c>
-      <c r="AG329" s="50" t="s">
+      <c r="AG329" s="63" t="s">
         <v>282</v>
       </c>
-      <c r="AH329" s="50" t="s">
+      <c r="AH329" s="63" t="s">
         <v>282</v>
       </c>
-      <c r="AI329" s="50" t="s">
+      <c r="AI329" s="63" t="s">
         <v>80</v>
       </c>
-      <c r="AJ329" s="50" t="s">
+      <c r="AJ329" s="63" t="s">
         <v>80</v>
       </c>
-      <c r="AK329" s="50" t="s">
+      <c r="AK329" s="63" t="s">
         <v>80</v>
       </c>
-      <c r="AL329" s="50"/>
-      <c r="AM329" s="50"/>
-      <c r="AN329" s="50"/>
-      <c r="AO329" s="50"/>
-      <c r="AP329" s="50"/>
-      <c r="AQ329" s="50"/>
-      <c r="AR329" s="50"/>
-      <c r="AS329" s="50"/>
-      <c r="AT329" s="50"/>
-      <c r="AU329" s="50"/>
-      <c r="AV329" s="50"/>
-      <c r="AW329" s="50"/>
-      <c r="AX329" s="50"/>
-      <c r="AY329" s="50"/>
-      <c r="AZ329" s="50"/>
-    </row>
-    <row r="330" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A330" s="50">
-        <v>70</v>
-      </c>
-      <c r="B330" s="25"/>
-      <c r="C330" s="25"/>
-      <c r="D330" s="25" t="s">
+      <c r="AL329" s="63"/>
+      <c r="AM329" s="63"/>
+      <c r="AN329" s="63"/>
+      <c r="AO329" s="63"/>
+      <c r="AP329" s="63"/>
+      <c r="AQ329" s="63"/>
+      <c r="AR329" s="63"/>
+      <c r="AS329" s="63"/>
+      <c r="AT329" s="63"/>
+      <c r="AU329" s="63"/>
+      <c r="AV329" s="63"/>
+      <c r="AW329" s="63"/>
+      <c r="AX329" s="63"/>
+      <c r="AY329" s="63"/>
+      <c r="AZ329" s="63"/>
+    </row>
+    <row r="330" spans="1:52" s="66" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A330" s="63">
+        <v>70</v>
+      </c>
+      <c r="B330" s="65"/>
+      <c r="C330" s="65"/>
+      <c r="D330" s="65" t="s">
         <v>1031</v>
       </c>
-      <c r="E330" s="37" t="s">
+      <c r="E330" s="64" t="s">
         <v>2016</v>
       </c>
-      <c r="F330" s="25" t="s">
+      <c r="F330" s="65" t="s">
         <v>1032</v>
       </c>
-      <c r="G330" s="25" t="s">
+      <c r="G330" s="65" t="s">
         <v>997</v>
       </c>
-      <c r="H330" s="25"/>
-      <c r="I330" s="25" t="s">
+      <c r="H330" s="65"/>
+      <c r="I330" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="J330" s="25"/>
-      <c r="K330" s="25" t="s">
+      <c r="J330" s="65"/>
+      <c r="K330" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="L330" s="25"/>
-      <c r="M330" s="25"/>
-      <c r="N330" s="25"/>
-      <c r="O330" s="25"/>
-      <c r="P330" s="25"/>
-      <c r="Q330" s="25"/>
-      <c r="R330" s="25"/>
-      <c r="S330" s="25"/>
-      <c r="T330" s="25"/>
-      <c r="U330" s="25"/>
-      <c r="V330" s="25"/>
-      <c r="W330" s="25"/>
-      <c r="X330" s="25"/>
-      <c r="Z330" s="25"/>
-      <c r="AA330" s="25"/>
-      <c r="AB330" s="25"/>
-      <c r="AC330" s="25"/>
-      <c r="AD330" s="25"/>
-      <c r="AE330" s="25"/>
-      <c r="AF330" s="25"/>
-      <c r="AG330" s="25"/>
-      <c r="AH330" s="25"/>
-      <c r="AI330" s="25"/>
-      <c r="AJ330" s="25"/>
-      <c r="AK330" s="25"/>
-      <c r="AM330" s="25"/>
-      <c r="AN330" s="25" t="s">
+      <c r="L330" s="65"/>
+      <c r="M330" s="65"/>
+      <c r="N330" s="65"/>
+      <c r="O330" s="65"/>
+      <c r="P330" s="65"/>
+      <c r="Q330" s="65"/>
+      <c r="R330" s="65"/>
+      <c r="S330" s="65"/>
+      <c r="T330" s="65"/>
+      <c r="U330" s="65"/>
+      <c r="V330" s="65"/>
+      <c r="W330" s="65"/>
+      <c r="X330" s="65"/>
+      <c r="Z330" s="65"/>
+      <c r="AA330" s="65"/>
+      <c r="AB330" s="65"/>
+      <c r="AC330" s="65"/>
+      <c r="AD330" s="65"/>
+      <c r="AE330" s="65"/>
+      <c r="AF330" s="65"/>
+      <c r="AG330" s="65"/>
+      <c r="AH330" s="65"/>
+      <c r="AI330" s="65"/>
+      <c r="AJ330" s="65"/>
+      <c r="AK330" s="65"/>
+      <c r="AM330" s="65"/>
+      <c r="AN330" s="65" t="s">
         <v>1033</v>
       </c>
-      <c r="AO330" s="25"/>
-      <c r="AP330" s="25"/>
-      <c r="AQ330" s="25" t="s">
+      <c r="AO330" s="65"/>
+      <c r="AP330" s="65"/>
+      <c r="AQ330" s="65" t="s">
         <v>1034</v>
       </c>
-      <c r="AR330" s="25"/>
-      <c r="AS330" s="25" t="s">
+      <c r="AR330" s="65"/>
+      <c r="AS330" s="65" t="s">
         <v>1034</v>
       </c>
-      <c r="AT330" s="25"/>
-      <c r="AU330" s="25"/>
-      <c r="AV330" s="25"/>
-      <c r="AW330" s="25"/>
-      <c r="AX330" s="25"/>
-      <c r="AZ330" s="26"/>
-    </row>
-    <row r="331" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A331" s="50">
-        <v>70</v>
-      </c>
-      <c r="B331" s="25"/>
-      <c r="C331" s="25"/>
-      <c r="D331" s="25" t="s">
+      <c r="AT330" s="65"/>
+      <c r="AU330" s="65"/>
+      <c r="AV330" s="65"/>
+      <c r="AW330" s="65"/>
+      <c r="AX330" s="65"/>
+      <c r="AZ330" s="68"/>
+    </row>
+    <row r="331" spans="1:52" s="66" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A331" s="63">
+        <v>70</v>
+      </c>
+      <c r="B331" s="65"/>
+      <c r="C331" s="65"/>
+      <c r="D331" s="65" t="s">
         <v>1035</v>
       </c>
-      <c r="E331" s="37" t="s">
+      <c r="E331" s="64" t="s">
         <v>2017</v>
       </c>
-      <c r="F331" s="25" t="s">
+      <c r="F331" s="65" t="s">
         <v>1036</v>
       </c>
-      <c r="G331" s="25" t="s">
+      <c r="G331" s="65" t="s">
         <v>997</v>
       </c>
-      <c r="H331" s="25"/>
-      <c r="I331" s="25" t="s">
+      <c r="H331" s="65"/>
+      <c r="I331" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="J331" s="25"/>
-      <c r="K331" s="25" t="s">
+      <c r="J331" s="65"/>
+      <c r="K331" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="L331" s="25"/>
-      <c r="M331" s="25"/>
-      <c r="N331" s="25"/>
-      <c r="O331" s="25"/>
-      <c r="P331" s="25"/>
-      <c r="Q331" s="25"/>
-      <c r="R331" s="25"/>
-      <c r="S331" s="25"/>
-      <c r="T331" s="25"/>
-      <c r="U331" s="25"/>
-      <c r="V331" s="25"/>
-      <c r="W331" s="25"/>
-      <c r="X331" s="25"/>
-      <c r="Z331" s="25"/>
-      <c r="AA331" s="25"/>
-      <c r="AB331" s="25"/>
-      <c r="AC331" s="25"/>
-      <c r="AD331" s="25"/>
-      <c r="AE331" s="25"/>
-      <c r="AF331" s="25"/>
-      <c r="AG331" s="25"/>
-      <c r="AH331" s="25"/>
-      <c r="AI331" s="25"/>
-      <c r="AJ331" s="25"/>
-      <c r="AK331" s="25"/>
-      <c r="AM331" s="25"/>
-      <c r="AN331" s="25" t="s">
+      <c r="L331" s="65"/>
+      <c r="M331" s="65"/>
+      <c r="N331" s="65"/>
+      <c r="O331" s="65"/>
+      <c r="P331" s="65"/>
+      <c r="Q331" s="65"/>
+      <c r="R331" s="65"/>
+      <c r="S331" s="65"/>
+      <c r="T331" s="65"/>
+      <c r="U331" s="65"/>
+      <c r="V331" s="65"/>
+      <c r="W331" s="65"/>
+      <c r="X331" s="65"/>
+      <c r="Z331" s="65"/>
+      <c r="AA331" s="65"/>
+      <c r="AB331" s="65"/>
+      <c r="AC331" s="65"/>
+      <c r="AD331" s="65"/>
+      <c r="AE331" s="65"/>
+      <c r="AF331" s="65"/>
+      <c r="AG331" s="65"/>
+      <c r="AH331" s="65"/>
+      <c r="AI331" s="65"/>
+      <c r="AJ331" s="65"/>
+      <c r="AK331" s="65"/>
+      <c r="AM331" s="65"/>
+      <c r="AN331" s="65" t="s">
         <v>1037</v>
       </c>
-      <c r="AO331" s="25"/>
-      <c r="AP331" s="25"/>
-      <c r="AQ331" s="25"/>
-      <c r="AR331" s="25"/>
-      <c r="AS331" s="25"/>
-      <c r="AT331" s="25"/>
-      <c r="AU331" s="25"/>
-      <c r="AV331" s="25"/>
-      <c r="AW331" s="25"/>
-      <c r="AX331" s="25"/>
-      <c r="AZ331" s="26"/>
-    </row>
-    <row r="332" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A332" s="25">
-        <v>70</v>
-      </c>
-      <c r="B332" s="25"/>
-      <c r="C332" s="25"/>
-      <c r="D332" s="25" t="s">
+      <c r="AO331" s="65"/>
+      <c r="AP331" s="65"/>
+      <c r="AQ331" s="65"/>
+      <c r="AR331" s="65"/>
+      <c r="AS331" s="65"/>
+      <c r="AT331" s="65"/>
+      <c r="AU331" s="65"/>
+      <c r="AV331" s="65"/>
+      <c r="AW331" s="65"/>
+      <c r="AX331" s="65"/>
+      <c r="AZ331" s="68"/>
+    </row>
+    <row r="332" spans="1:52" s="66" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A332" s="65">
+        <v>70</v>
+      </c>
+      <c r="B332" s="65"/>
+      <c r="C332" s="65"/>
+      <c r="D332" s="65" t="s">
         <v>657</v>
       </c>
-      <c r="E332" s="37" t="s">
+      <c r="E332" s="64" t="s">
         <v>2018</v>
       </c>
-      <c r="F332" s="25" t="s">
+      <c r="F332" s="65" t="s">
         <v>380</v>
       </c>
-      <c r="G332" s="25"/>
-      <c r="H332" s="25"/>
-      <c r="I332" s="25" t="s">
+      <c r="G332" s="65"/>
+      <c r="H332" s="65"/>
+      <c r="I332" s="65" t="s">
         <v>1371</v>
       </c>
-      <c r="J332" s="25"/>
-      <c r="K332" s="25" t="s">
+      <c r="J332" s="65"/>
+      <c r="K332" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="L332" s="25"/>
-      <c r="M332" s="25" t="s">
+      <c r="L332" s="65"/>
+      <c r="M332" s="65" t="s">
         <v>682</v>
       </c>
-      <c r="N332" s="25"/>
-      <c r="O332" s="25"/>
-      <c r="P332" s="25"/>
-      <c r="Q332" s="25"/>
-      <c r="R332" s="25"/>
-      <c r="S332" s="25"/>
-      <c r="T332" s="25"/>
-      <c r="U332" s="25"/>
-      <c r="V332" s="25"/>
-      <c r="W332" s="25"/>
-      <c r="X332" s="25"/>
-      <c r="Z332" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA332" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB332" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC332" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD332" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE332" s="25"/>
-      <c r="AF332" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG332" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="AH332" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI332" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="AJ332" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK332" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="AM332" s="25"/>
-      <c r="AN332" s="25" t="s">
+      <c r="N332" s="65"/>
+      <c r="O332" s="65"/>
+      <c r="P332" s="65"/>
+      <c r="Q332" s="65"/>
+      <c r="R332" s="65"/>
+      <c r="S332" s="65"/>
+      <c r="T332" s="65"/>
+      <c r="U332" s="65"/>
+      <c r="V332" s="65"/>
+      <c r="W332" s="65"/>
+      <c r="X332" s="65"/>
+      <c r="Z332" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA332" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB332" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC332" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD332" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="AE332" s="65"/>
+      <c r="AF332" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG332" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="AH332" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="AI332" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ332" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK332" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM332" s="65"/>
+      <c r="AN332" s="65" t="s">
         <v>381</v>
       </c>
-      <c r="AO332" s="25"/>
-      <c r="AP332" s="25"/>
-      <c r="AQ332" s="25" t="s">
+      <c r="AO332" s="65"/>
+      <c r="AP332" s="65"/>
+      <c r="AQ332" s="65" t="s">
         <v>381</v>
       </c>
-      <c r="AR332" s="25"/>
-      <c r="AS332" s="25" t="s">
+      <c r="AR332" s="65"/>
+      <c r="AS332" s="65" t="s">
         <v>381</v>
       </c>
-      <c r="AT332" s="25"/>
-      <c r="AU332" s="25"/>
-      <c r="AV332" s="25"/>
-      <c r="AW332" s="25"/>
-      <c r="AX332" s="25"/>
-      <c r="AZ332" s="26"/>
-    </row>
-    <row r="333" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A333" s="25">
-        <v>70</v>
-      </c>
-      <c r="B333" s="25"/>
-      <c r="C333" s="25"/>
-      <c r="D333" s="25" t="s">
+      <c r="AT332" s="65"/>
+      <c r="AU332" s="65"/>
+      <c r="AV332" s="65"/>
+      <c r="AW332" s="65"/>
+      <c r="AX332" s="65"/>
+      <c r="AZ332" s="68"/>
+    </row>
+    <row r="333" spans="1:52" s="66" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A333" s="65">
+        <v>70</v>
+      </c>
+      <c r="B333" s="65"/>
+      <c r="C333" s="65"/>
+      <c r="D333" s="65" t="s">
         <v>1530</v>
       </c>
-      <c r="E333" s="37" t="s">
+      <c r="E333" s="64" t="s">
         <v>2019</v>
       </c>
-      <c r="F333" s="25" t="s">
+      <c r="F333" s="65" t="s">
         <v>375</v>
       </c>
-      <c r="G333" s="25" t="s">
+      <c r="G333" s="65" t="s">
         <v>375</v>
       </c>
-      <c r="H333" s="25"/>
-      <c r="I333" s="25" t="s">
+      <c r="H333" s="65"/>
+      <c r="I333" s="65" t="s">
         <v>631</v>
       </c>
-      <c r="J333" s="25"/>
-      <c r="K333" s="25" t="s">
+      <c r="J333" s="65"/>
+      <c r="K333" s="65" t="s">
         <v>49</v>
       </c>
-      <c r="L333" s="25"/>
-      <c r="M333" s="25"/>
-      <c r="N333" s="25"/>
-      <c r="O333" s="25"/>
-      <c r="P333" s="25"/>
-      <c r="Q333" s="25" t="s">
+      <c r="L333" s="65"/>
+      <c r="M333" s="65"/>
+      <c r="N333" s="65"/>
+      <c r="O333" s="65"/>
+      <c r="P333" s="65"/>
+      <c r="Q333" s="65" t="s">
         <v>601</v>
       </c>
-      <c r="R333" s="25"/>
-      <c r="S333" s="25" t="s">
+      <c r="R333" s="65"/>
+      <c r="S333" s="65" t="s">
         <v>381</v>
       </c>
-      <c r="T333" s="25"/>
-      <c r="U333" s="25" t="s">
+      <c r="T333" s="65"/>
+      <c r="U333" s="65" t="s">
         <v>623</v>
       </c>
-      <c r="V333" s="25"/>
-      <c r="W333" s="25"/>
-      <c r="X333" s="25"/>
-      <c r="Z333" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA333" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB333" s="25" t="s">
+      <c r="V333" s="65"/>
+      <c r="W333" s="65"/>
+      <c r="X333" s="65"/>
+      <c r="Z333" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA333" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB333" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="AC333" s="25" t="s">
+      <c r="AC333" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="AD333" s="25" t="s">
+      <c r="AD333" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="AE333" s="25"/>
-      <c r="AF333" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG333" s="25" t="s">
+      <c r="AE333" s="65"/>
+      <c r="AF333" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG333" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="AH333" s="25" t="s">
+      <c r="AH333" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="AI333" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ333" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AK333" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM333" s="25"/>
-      <c r="AN333" s="25" t="s">
+      <c r="AI333" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ333" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK333" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM333" s="65"/>
+      <c r="AN333" s="65" t="s">
         <v>1530</v>
       </c>
-      <c r="AO333" s="25"/>
-      <c r="AP333" s="25"/>
-      <c r="AQ333" s="25"/>
-      <c r="AR333" s="25"/>
-      <c r="AS333" s="25"/>
-      <c r="AT333" s="25"/>
-      <c r="AU333" s="25"/>
-      <c r="AV333" s="25"/>
-      <c r="AW333" s="25"/>
-      <c r="AX333" s="25"/>
-      <c r="AZ333" s="26"/>
+      <c r="AO333" s="65"/>
+      <c r="AP333" s="65"/>
+      <c r="AQ333" s="65"/>
+      <c r="AR333" s="65"/>
+      <c r="AS333" s="65"/>
+      <c r="AT333" s="65"/>
+      <c r="AU333" s="65"/>
+      <c r="AV333" s="65"/>
+      <c r="AW333" s="65"/>
+      <c r="AX333" s="65"/>
+      <c r="AZ333" s="68"/>
     </row>
     <row r="334" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A334" s="50">
@@ -64865,7 +64865,7 @@
     <mergeCell ref="I5:J5"/>
   </mergeCells>
   <phoneticPr fontId="5"/>
-  <conditionalFormatting sqref="V279:X282 V335:X346 V325:X328 V330:X331">
+  <conditionalFormatting sqref="V279:X282 V325:X328 V330:X331 V335:X346">
     <cfRule type="expression" dxfId="25" priority="44">
       <formula>$A279=""</formula>
     </cfRule>
@@ -65023,65 +65023,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:57" ht="38.25" customHeight="1" thickBot="1">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="108"/>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
-      <c r="V1" s="108"/>
-      <c r="W1" s="108"/>
-      <c r="X1" s="108"/>
-      <c r="Y1" s="108"/>
-      <c r="Z1" s="108"/>
-      <c r="AA1" s="108"/>
-      <c r="AB1" s="108"/>
-      <c r="AC1" s="108"/>
-      <c r="AD1" s="108"/>
-      <c r="AE1" s="108"/>
-      <c r="AF1" s="108"/>
-      <c r="AG1" s="108"/>
-      <c r="AH1" s="108"/>
-      <c r="AI1" s="108"/>
-      <c r="AJ1" s="108"/>
-      <c r="AK1" s="108"/>
-      <c r="AL1" s="108"/>
-      <c r="AM1" s="108"/>
-      <c r="AN1" s="108"/>
-      <c r="AO1" s="108"/>
-      <c r="AP1" s="108"/>
-      <c r="AQ1" s="108"/>
-      <c r="AR1" s="108"/>
-      <c r="AS1" s="108"/>
-      <c r="AT1" s="108"/>
-      <c r="AU1" s="108"/>
-      <c r="AV1" s="108"/>
-      <c r="AW1" s="108"/>
-      <c r="AX1" s="108"/>
-      <c r="AY1" s="108"/>
-      <c r="AZ1" s="108"/>
-      <c r="BA1" s="108"/>
-      <c r="BB1" s="108"/>
-      <c r="BC1" s="108"/>
-      <c r="BD1" s="108"/>
-      <c r="BE1" s="109"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="112"/>
+      <c r="H1" s="112"/>
+      <c r="I1" s="112"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
+      <c r="V1" s="112"/>
+      <c r="W1" s="112"/>
+      <c r="X1" s="112"/>
+      <c r="Y1" s="112"/>
+      <c r="Z1" s="112"/>
+      <c r="AA1" s="112"/>
+      <c r="AB1" s="112"/>
+      <c r="AC1" s="112"/>
+      <c r="AD1" s="112"/>
+      <c r="AE1" s="112"/>
+      <c r="AF1" s="112"/>
+      <c r="AG1" s="112"/>
+      <c r="AH1" s="112"/>
+      <c r="AI1" s="112"/>
+      <c r="AJ1" s="112"/>
+      <c r="AK1" s="112"/>
+      <c r="AL1" s="112"/>
+      <c r="AM1" s="112"/>
+      <c r="AN1" s="112"/>
+      <c r="AO1" s="112"/>
+      <c r="AP1" s="112"/>
+      <c r="AQ1" s="112"/>
+      <c r="AR1" s="112"/>
+      <c r="AS1" s="112"/>
+      <c r="AT1" s="112"/>
+      <c r="AU1" s="112"/>
+      <c r="AV1" s="112"/>
+      <c r="AW1" s="112"/>
+      <c r="AX1" s="112"/>
+      <c r="AY1" s="112"/>
+      <c r="AZ1" s="112"/>
+      <c r="BA1" s="112"/>
+      <c r="BB1" s="112"/>
+      <c r="BC1" s="112"/>
+      <c r="BD1" s="112"/>
+      <c r="BE1" s="113"/>
     </row>
     <row r="2" spans="1:57" ht="12" customHeight="1" thickBot="1">
       <c r="A2" s="14"/>
@@ -65128,145 +65128,145 @@
       <c r="AP2" s="14"/>
     </row>
     <row r="3" spans="1:57" ht="15" customHeight="1" thickBot="1">
-      <c r="A3" s="90" t="s">
+      <c r="A3" s="124" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="91"/>
-      <c r="C3" s="91"/>
-      <c r="D3" s="91"/>
-      <c r="E3" s="91"/>
-      <c r="F3" s="91"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="110" t="s">
+      <c r="B3" s="115"/>
+      <c r="C3" s="115"/>
+      <c r="D3" s="115"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="116"/>
+      <c r="H3" s="114" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="91"/>
-      <c r="J3" s="91"/>
-      <c r="K3" s="91"/>
-      <c r="L3" s="91"/>
-      <c r="M3" s="91"/>
-      <c r="N3" s="92"/>
-      <c r="O3" s="110" t="s">
+      <c r="I3" s="115"/>
+      <c r="J3" s="115"/>
+      <c r="K3" s="115"/>
+      <c r="L3" s="115"/>
+      <c r="M3" s="115"/>
+      <c r="N3" s="116"/>
+      <c r="O3" s="114" t="s">
         <v>9</v>
       </c>
-      <c r="P3" s="111"/>
-      <c r="Q3" s="111"/>
-      <c r="R3" s="111"/>
-      <c r="S3" s="111"/>
-      <c r="T3" s="111"/>
-      <c r="U3" s="111"/>
-      <c r="V3" s="111"/>
-      <c r="W3" s="111"/>
-      <c r="X3" s="111"/>
-      <c r="Y3" s="111"/>
-      <c r="Z3" s="111"/>
-      <c r="AA3" s="111"/>
-      <c r="AB3" s="111"/>
-      <c r="AC3" s="111"/>
-      <c r="AD3" s="111"/>
-      <c r="AE3" s="111"/>
-      <c r="AF3" s="111"/>
-      <c r="AG3" s="111"/>
-      <c r="AH3" s="111"/>
-      <c r="AI3" s="111"/>
-      <c r="AJ3" s="111"/>
-      <c r="AK3" s="111"/>
-      <c r="AL3" s="111"/>
-      <c r="AM3" s="111"/>
-      <c r="AN3" s="111"/>
-      <c r="AO3" s="111"/>
-      <c r="AP3" s="112"/>
-      <c r="AQ3" s="110" t="s">
+      <c r="P3" s="117"/>
+      <c r="Q3" s="117"/>
+      <c r="R3" s="117"/>
+      <c r="S3" s="117"/>
+      <c r="T3" s="117"/>
+      <c r="U3" s="117"/>
+      <c r="V3" s="117"/>
+      <c r="W3" s="117"/>
+      <c r="X3" s="117"/>
+      <c r="Y3" s="117"/>
+      <c r="Z3" s="117"/>
+      <c r="AA3" s="117"/>
+      <c r="AB3" s="117"/>
+      <c r="AC3" s="117"/>
+      <c r="AD3" s="117"/>
+      <c r="AE3" s="117"/>
+      <c r="AF3" s="117"/>
+      <c r="AG3" s="117"/>
+      <c r="AH3" s="117"/>
+      <c r="AI3" s="117"/>
+      <c r="AJ3" s="117"/>
+      <c r="AK3" s="117"/>
+      <c r="AL3" s="117"/>
+      <c r="AM3" s="117"/>
+      <c r="AN3" s="117"/>
+      <c r="AO3" s="117"/>
+      <c r="AP3" s="118"/>
+      <c r="AQ3" s="114" t="s">
         <v>10</v>
       </c>
-      <c r="AR3" s="113"/>
-      <c r="AS3" s="113"/>
-      <c r="AT3" s="113"/>
-      <c r="AU3" s="113"/>
-      <c r="AV3" s="113"/>
-      <c r="AW3" s="113"/>
-      <c r="AX3" s="113"/>
-      <c r="AY3" s="113"/>
-      <c r="AZ3" s="113"/>
-      <c r="BA3" s="113"/>
-      <c r="BB3" s="113"/>
-      <c r="BC3" s="113"/>
-      <c r="BD3" s="113"/>
-      <c r="BE3" s="114"/>
+      <c r="AR3" s="119"/>
+      <c r="AS3" s="119"/>
+      <c r="AT3" s="119"/>
+      <c r="AU3" s="119"/>
+      <c r="AV3" s="119"/>
+      <c r="AW3" s="119"/>
+      <c r="AX3" s="119"/>
+      <c r="AY3" s="119"/>
+      <c r="AZ3" s="119"/>
+      <c r="BA3" s="119"/>
+      <c r="BB3" s="119"/>
+      <c r="BC3" s="119"/>
+      <c r="BD3" s="119"/>
+      <c r="BE3" s="120"/>
     </row>
     <row r="4" spans="1:57" ht="15" customHeight="1">
-      <c r="A4" s="115">
+      <c r="A4" s="121">
         <v>1</v>
       </c>
-      <c r="B4" s="116"/>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="119"/>
-      <c r="L4" s="119"/>
-      <c r="M4" s="119"/>
-      <c r="N4" s="120"/>
-      <c r="O4" s="118" t="s">
+      <c r="B4" s="122"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="122"/>
+      <c r="G4" s="123"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="105"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="105"/>
+      <c r="L4" s="105"/>
+      <c r="M4" s="105"/>
+      <c r="N4" s="106"/>
+      <c r="O4" s="104" t="s">
         <v>11</v>
       </c>
-      <c r="P4" s="121"/>
-      <c r="Q4" s="121"/>
-      <c r="R4" s="121"/>
-      <c r="S4" s="121"/>
-      <c r="T4" s="121"/>
-      <c r="U4" s="121"/>
-      <c r="V4" s="121"/>
-      <c r="W4" s="121"/>
-      <c r="X4" s="121"/>
-      <c r="Y4" s="121"/>
-      <c r="Z4" s="121"/>
-      <c r="AA4" s="121"/>
-      <c r="AB4" s="121"/>
-      <c r="AC4" s="121"/>
-      <c r="AD4" s="121"/>
-      <c r="AE4" s="121"/>
-      <c r="AF4" s="121"/>
-      <c r="AG4" s="121"/>
-      <c r="AH4" s="121"/>
-      <c r="AI4" s="121"/>
-      <c r="AJ4" s="121"/>
-      <c r="AK4" s="121"/>
-      <c r="AL4" s="121"/>
-      <c r="AM4" s="121"/>
-      <c r="AN4" s="121"/>
-      <c r="AO4" s="121"/>
-      <c r="AP4" s="122"/>
-      <c r="AQ4" s="123"/>
-      <c r="AR4" s="121"/>
-      <c r="AS4" s="121"/>
-      <c r="AT4" s="121"/>
-      <c r="AU4" s="121"/>
-      <c r="AV4" s="121"/>
-      <c r="AW4" s="121"/>
-      <c r="AX4" s="121"/>
-      <c r="AY4" s="121"/>
-      <c r="AZ4" s="121"/>
-      <c r="BA4" s="121"/>
-      <c r="BB4" s="121"/>
-      <c r="BC4" s="121"/>
-      <c r="BD4" s="121"/>
-      <c r="BE4" s="124"/>
+      <c r="P4" s="107"/>
+      <c r="Q4" s="107"/>
+      <c r="R4" s="107"/>
+      <c r="S4" s="107"/>
+      <c r="T4" s="107"/>
+      <c r="U4" s="107"/>
+      <c r="V4" s="107"/>
+      <c r="W4" s="107"/>
+      <c r="X4" s="107"/>
+      <c r="Y4" s="107"/>
+      <c r="Z4" s="107"/>
+      <c r="AA4" s="107"/>
+      <c r="AB4" s="107"/>
+      <c r="AC4" s="107"/>
+      <c r="AD4" s="107"/>
+      <c r="AE4" s="107"/>
+      <c r="AF4" s="107"/>
+      <c r="AG4" s="107"/>
+      <c r="AH4" s="107"/>
+      <c r="AI4" s="107"/>
+      <c r="AJ4" s="107"/>
+      <c r="AK4" s="107"/>
+      <c r="AL4" s="107"/>
+      <c r="AM4" s="107"/>
+      <c r="AN4" s="107"/>
+      <c r="AO4" s="107"/>
+      <c r="AP4" s="108"/>
+      <c r="AQ4" s="109"/>
+      <c r="AR4" s="107"/>
+      <c r="AS4" s="107"/>
+      <c r="AT4" s="107"/>
+      <c r="AU4" s="107"/>
+      <c r="AV4" s="107"/>
+      <c r="AW4" s="107"/>
+      <c r="AX4" s="107"/>
+      <c r="AY4" s="107"/>
+      <c r="AZ4" s="107"/>
+      <c r="BA4" s="107"/>
+      <c r="BB4" s="107"/>
+      <c r="BC4" s="107"/>
+      <c r="BD4" s="107"/>
+      <c r="BE4" s="110"/>
     </row>
     <row r="5" spans="1:57" ht="105.75" customHeight="1">
-      <c r="A5" s="104">
+      <c r="A5" s="84">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B5" s="105"/>
-      <c r="C5" s="105"/>
-      <c r="D5" s="105"/>
-      <c r="E5" s="105"/>
-      <c r="F5" s="105"/>
-      <c r="G5" s="106"/>
+      <c r="B5" s="85"/>
+      <c r="C5" s="85"/>
+      <c r="D5" s="85"/>
+      <c r="E5" s="85"/>
+      <c r="F5" s="85"/>
+      <c r="G5" s="86"/>
       <c r="H5" s="87" t="s">
         <v>1788</v>
       </c>
@@ -65279,61 +65279,61 @@
       <c r="O5" s="87" t="s">
         <v>1790</v>
       </c>
-      <c r="P5" s="85"/>
-      <c r="Q5" s="85"/>
-      <c r="R5" s="85"/>
-      <c r="S5" s="85"/>
-      <c r="T5" s="85"/>
-      <c r="U5" s="85"/>
-      <c r="V5" s="85"/>
-      <c r="W5" s="85"/>
-      <c r="X5" s="85"/>
-      <c r="Y5" s="85"/>
-      <c r="Z5" s="85"/>
-      <c r="AA5" s="85"/>
-      <c r="AB5" s="85"/>
-      <c r="AC5" s="85"/>
-      <c r="AD5" s="85"/>
-      <c r="AE5" s="85"/>
-      <c r="AF5" s="85"/>
-      <c r="AG5" s="85"/>
-      <c r="AH5" s="85"/>
-      <c r="AI5" s="85"/>
-      <c r="AJ5" s="85"/>
-      <c r="AK5" s="85"/>
-      <c r="AL5" s="85"/>
-      <c r="AM5" s="85"/>
-      <c r="AN5" s="85"/>
-      <c r="AO5" s="85"/>
-      <c r="AP5" s="93"/>
-      <c r="AQ5" s="84" t="s">
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
+      <c r="W5" s="90"/>
+      <c r="X5" s="90"/>
+      <c r="Y5" s="90"/>
+      <c r="Z5" s="90"/>
+      <c r="AA5" s="90"/>
+      <c r="AB5" s="90"/>
+      <c r="AC5" s="90"/>
+      <c r="AD5" s="90"/>
+      <c r="AE5" s="90"/>
+      <c r="AF5" s="90"/>
+      <c r="AG5" s="90"/>
+      <c r="AH5" s="90"/>
+      <c r="AI5" s="90"/>
+      <c r="AJ5" s="90"/>
+      <c r="AK5" s="90"/>
+      <c r="AL5" s="90"/>
+      <c r="AM5" s="90"/>
+      <c r="AN5" s="90"/>
+      <c r="AO5" s="90"/>
+      <c r="AP5" s="91"/>
+      <c r="AQ5" s="95" t="s">
         <v>1789</v>
       </c>
-      <c r="AR5" s="85"/>
-      <c r="AS5" s="85"/>
-      <c r="AT5" s="85"/>
-      <c r="AU5" s="85"/>
-      <c r="AV5" s="85"/>
-      <c r="AW5" s="85"/>
-      <c r="AX5" s="85"/>
-      <c r="AY5" s="85"/>
-      <c r="AZ5" s="85"/>
-      <c r="BA5" s="85"/>
-      <c r="BB5" s="85"/>
-      <c r="BC5" s="85"/>
-      <c r="BD5" s="85"/>
-      <c r="BE5" s="86"/>
+      <c r="AR5" s="90"/>
+      <c r="AS5" s="90"/>
+      <c r="AT5" s="90"/>
+      <c r="AU5" s="90"/>
+      <c r="AV5" s="90"/>
+      <c r="AW5" s="90"/>
+      <c r="AX5" s="90"/>
+      <c r="AY5" s="90"/>
+      <c r="AZ5" s="90"/>
+      <c r="BA5" s="90"/>
+      <c r="BB5" s="90"/>
+      <c r="BC5" s="90"/>
+      <c r="BD5" s="90"/>
+      <c r="BE5" s="96"/>
     </row>
     <row r="6" spans="1:57" ht="36.6" customHeight="1">
-      <c r="A6" s="104">
+      <c r="A6" s="84">
         <v>1.2</v>
       </c>
-      <c r="B6" s="105"/>
-      <c r="C6" s="105"/>
-      <c r="D6" s="105"/>
-      <c r="E6" s="105"/>
-      <c r="F6" s="105"/>
-      <c r="G6" s="106"/>
+      <c r="B6" s="85"/>
+      <c r="C6" s="85"/>
+      <c r="D6" s="85"/>
+      <c r="E6" s="85"/>
+      <c r="F6" s="85"/>
+      <c r="G6" s="86"/>
       <c r="H6" s="87" t="s">
         <v>1814</v>
       </c>
@@ -65346,124 +65346,124 @@
       <c r="O6" s="87" t="s">
         <v>1813</v>
       </c>
-      <c r="P6" s="94"/>
-      <c r="Q6" s="94"/>
-      <c r="R6" s="94"/>
-      <c r="S6" s="94"/>
-      <c r="T6" s="94"/>
-      <c r="U6" s="94"/>
-      <c r="V6" s="94"/>
-      <c r="W6" s="94"/>
-      <c r="X6" s="94"/>
-      <c r="Y6" s="94"/>
-      <c r="Z6" s="94"/>
-      <c r="AA6" s="94"/>
-      <c r="AB6" s="94"/>
-      <c r="AC6" s="94"/>
-      <c r="AD6" s="94"/>
-      <c r="AE6" s="94"/>
-      <c r="AF6" s="94"/>
-      <c r="AG6" s="94"/>
-      <c r="AH6" s="94"/>
-      <c r="AI6" s="94"/>
-      <c r="AJ6" s="94"/>
-      <c r="AK6" s="94"/>
-      <c r="AL6" s="94"/>
-      <c r="AM6" s="94"/>
-      <c r="AN6" s="94"/>
-      <c r="AO6" s="94"/>
-      <c r="AP6" s="95"/>
-      <c r="AQ6" s="84" t="s">
+      <c r="P6" s="125"/>
+      <c r="Q6" s="125"/>
+      <c r="R6" s="125"/>
+      <c r="S6" s="125"/>
+      <c r="T6" s="125"/>
+      <c r="U6" s="125"/>
+      <c r="V6" s="125"/>
+      <c r="W6" s="125"/>
+      <c r="X6" s="125"/>
+      <c r="Y6" s="125"/>
+      <c r="Z6" s="125"/>
+      <c r="AA6" s="125"/>
+      <c r="AB6" s="125"/>
+      <c r="AC6" s="125"/>
+      <c r="AD6" s="125"/>
+      <c r="AE6" s="125"/>
+      <c r="AF6" s="125"/>
+      <c r="AG6" s="125"/>
+      <c r="AH6" s="125"/>
+      <c r="AI6" s="125"/>
+      <c r="AJ6" s="125"/>
+      <c r="AK6" s="125"/>
+      <c r="AL6" s="125"/>
+      <c r="AM6" s="125"/>
+      <c r="AN6" s="125"/>
+      <c r="AO6" s="125"/>
+      <c r="AP6" s="126"/>
+      <c r="AQ6" s="95" t="s">
         <v>1789</v>
       </c>
-      <c r="AR6" s="85"/>
-      <c r="AS6" s="85"/>
-      <c r="AT6" s="85"/>
-      <c r="AU6" s="85"/>
-      <c r="AV6" s="85"/>
-      <c r="AW6" s="85"/>
-      <c r="AX6" s="85"/>
-      <c r="AY6" s="85"/>
-      <c r="AZ6" s="85"/>
-      <c r="BA6" s="85"/>
-      <c r="BB6" s="85"/>
-      <c r="BC6" s="85"/>
-      <c r="BD6" s="85"/>
-      <c r="BE6" s="86"/>
+      <c r="AR6" s="90"/>
+      <c r="AS6" s="90"/>
+      <c r="AT6" s="90"/>
+      <c r="AU6" s="90"/>
+      <c r="AV6" s="90"/>
+      <c r="AW6" s="90"/>
+      <c r="AX6" s="90"/>
+      <c r="AY6" s="90"/>
+      <c r="AZ6" s="90"/>
+      <c r="BA6" s="90"/>
+      <c r="BB6" s="90"/>
+      <c r="BC6" s="90"/>
+      <c r="BD6" s="90"/>
+      <c r="BE6" s="96"/>
     </row>
     <row r="7" spans="1:57" ht="15" customHeight="1">
-      <c r="A7" s="104">
+      <c r="A7" s="84">
         <v>1.3</v>
       </c>
-      <c r="B7" s="105"/>
-      <c r="C7" s="105"/>
-      <c r="D7" s="105"/>
-      <c r="E7" s="105"/>
-      <c r="F7" s="105"/>
-      <c r="G7" s="106"/>
+      <c r="B7" s="85"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="85"/>
+      <c r="G7" s="86"/>
       <c r="H7" s="87"/>
-      <c r="I7" s="96"/>
-      <c r="J7" s="96"/>
-      <c r="K7" s="96"/>
-      <c r="L7" s="96"/>
-      <c r="M7" s="96"/>
-      <c r="N7" s="97"/>
-      <c r="O7" s="98" t="s">
+      <c r="I7" s="127"/>
+      <c r="J7" s="127"/>
+      <c r="K7" s="127"/>
+      <c r="L7" s="127"/>
+      <c r="M7" s="127"/>
+      <c r="N7" s="128"/>
+      <c r="O7" s="129" t="s">
         <v>2227</v>
       </c>
-      <c r="P7" s="99"/>
-      <c r="Q7" s="99"/>
-      <c r="R7" s="99"/>
-      <c r="S7" s="99"/>
-      <c r="T7" s="99"/>
-      <c r="U7" s="99"/>
-      <c r="V7" s="99"/>
-      <c r="W7" s="99"/>
-      <c r="X7" s="99"/>
-      <c r="Y7" s="99"/>
-      <c r="Z7" s="99"/>
-      <c r="AA7" s="99"/>
-      <c r="AB7" s="99"/>
-      <c r="AC7" s="99"/>
-      <c r="AD7" s="99"/>
-      <c r="AE7" s="99"/>
-      <c r="AF7" s="99"/>
-      <c r="AG7" s="99"/>
-      <c r="AH7" s="99"/>
-      <c r="AI7" s="99"/>
-      <c r="AJ7" s="99"/>
-      <c r="AK7" s="99"/>
-      <c r="AL7" s="99"/>
-      <c r="AM7" s="99"/>
-      <c r="AN7" s="99"/>
-      <c r="AO7" s="99"/>
-      <c r="AP7" s="100"/>
-      <c r="AQ7" s="101" t="s">
+      <c r="P7" s="130"/>
+      <c r="Q7" s="130"/>
+      <c r="R7" s="130"/>
+      <c r="S7" s="130"/>
+      <c r="T7" s="130"/>
+      <c r="U7" s="130"/>
+      <c r="V7" s="130"/>
+      <c r="W7" s="130"/>
+      <c r="X7" s="130"/>
+      <c r="Y7" s="130"/>
+      <c r="Z7" s="130"/>
+      <c r="AA7" s="130"/>
+      <c r="AB7" s="130"/>
+      <c r="AC7" s="130"/>
+      <c r="AD7" s="130"/>
+      <c r="AE7" s="130"/>
+      <c r="AF7" s="130"/>
+      <c r="AG7" s="130"/>
+      <c r="AH7" s="130"/>
+      <c r="AI7" s="130"/>
+      <c r="AJ7" s="130"/>
+      <c r="AK7" s="130"/>
+      <c r="AL7" s="130"/>
+      <c r="AM7" s="130"/>
+      <c r="AN7" s="130"/>
+      <c r="AO7" s="130"/>
+      <c r="AP7" s="131"/>
+      <c r="AQ7" s="132" t="s">
         <v>2228</v>
       </c>
-      <c r="AR7" s="102"/>
-      <c r="AS7" s="102"/>
-      <c r="AT7" s="102"/>
-      <c r="AU7" s="102"/>
-      <c r="AV7" s="102"/>
-      <c r="AW7" s="102"/>
-      <c r="AX7" s="102"/>
-      <c r="AY7" s="102"/>
-      <c r="AZ7" s="102"/>
-      <c r="BA7" s="102"/>
-      <c r="BB7" s="102"/>
-      <c r="BC7" s="102"/>
-      <c r="BD7" s="102"/>
-      <c r="BE7" s="103"/>
+      <c r="AR7" s="133"/>
+      <c r="AS7" s="133"/>
+      <c r="AT7" s="133"/>
+      <c r="AU7" s="133"/>
+      <c r="AV7" s="133"/>
+      <c r="AW7" s="133"/>
+      <c r="AX7" s="133"/>
+      <c r="AY7" s="133"/>
+      <c r="AZ7" s="133"/>
+      <c r="BA7" s="133"/>
+      <c r="BB7" s="133"/>
+      <c r="BC7" s="133"/>
+      <c r="BD7" s="133"/>
+      <c r="BE7" s="134"/>
     </row>
     <row r="8" spans="1:57" ht="15" customHeight="1">
-      <c r="A8" s="104"/>
-      <c r="B8" s="105"/>
-      <c r="C8" s="105"/>
-      <c r="D8" s="105"/>
-      <c r="E8" s="105"/>
-      <c r="F8" s="105"/>
-      <c r="G8" s="106"/>
+      <c r="A8" s="84"/>
+      <c r="B8" s="85"/>
+      <c r="C8" s="85"/>
+      <c r="D8" s="85"/>
+      <c r="E8" s="85"/>
+      <c r="F8" s="85"/>
+      <c r="G8" s="86"/>
       <c r="H8" s="87"/>
       <c r="I8" s="88"/>
       <c r="J8" s="88"/>
@@ -65472,57 +65472,57 @@
       <c r="M8" s="88"/>
       <c r="N8" s="89"/>
       <c r="O8" s="87"/>
-      <c r="P8" s="85"/>
-      <c r="Q8" s="85"/>
-      <c r="R8" s="85"/>
-      <c r="S8" s="85"/>
-      <c r="T8" s="85"/>
-      <c r="U8" s="85"/>
-      <c r="V8" s="85"/>
-      <c r="W8" s="85"/>
-      <c r="X8" s="85"/>
-      <c r="Y8" s="85"/>
-      <c r="Z8" s="85"/>
-      <c r="AA8" s="85"/>
-      <c r="AB8" s="85"/>
-      <c r="AC8" s="85"/>
-      <c r="AD8" s="85"/>
-      <c r="AE8" s="85"/>
-      <c r="AF8" s="85"/>
-      <c r="AG8" s="85"/>
-      <c r="AH8" s="85"/>
-      <c r="AI8" s="85"/>
-      <c r="AJ8" s="85"/>
-      <c r="AK8" s="85"/>
-      <c r="AL8" s="85"/>
-      <c r="AM8" s="85"/>
-      <c r="AN8" s="85"/>
-      <c r="AO8" s="85"/>
-      <c r="AP8" s="93"/>
-      <c r="AQ8" s="84"/>
-      <c r="AR8" s="85"/>
-      <c r="AS8" s="85"/>
-      <c r="AT8" s="85"/>
-      <c r="AU8" s="85"/>
-      <c r="AV8" s="85"/>
-      <c r="AW8" s="85"/>
-      <c r="AX8" s="85"/>
-      <c r="AY8" s="85"/>
-      <c r="AZ8" s="85"/>
-      <c r="BA8" s="85"/>
-      <c r="BB8" s="85"/>
-      <c r="BC8" s="85"/>
-      <c r="BD8" s="85"/>
-      <c r="BE8" s="86"/>
+      <c r="P8" s="90"/>
+      <c r="Q8" s="90"/>
+      <c r="R8" s="90"/>
+      <c r="S8" s="90"/>
+      <c r="T8" s="90"/>
+      <c r="U8" s="90"/>
+      <c r="V8" s="90"/>
+      <c r="W8" s="90"/>
+      <c r="X8" s="90"/>
+      <c r="Y8" s="90"/>
+      <c r="Z8" s="90"/>
+      <c r="AA8" s="90"/>
+      <c r="AB8" s="90"/>
+      <c r="AC8" s="90"/>
+      <c r="AD8" s="90"/>
+      <c r="AE8" s="90"/>
+      <c r="AF8" s="90"/>
+      <c r="AG8" s="90"/>
+      <c r="AH8" s="90"/>
+      <c r="AI8" s="90"/>
+      <c r="AJ8" s="90"/>
+      <c r="AK8" s="90"/>
+      <c r="AL8" s="90"/>
+      <c r="AM8" s="90"/>
+      <c r="AN8" s="90"/>
+      <c r="AO8" s="90"/>
+      <c r="AP8" s="91"/>
+      <c r="AQ8" s="95"/>
+      <c r="AR8" s="90"/>
+      <c r="AS8" s="90"/>
+      <c r="AT8" s="90"/>
+      <c r="AU8" s="90"/>
+      <c r="AV8" s="90"/>
+      <c r="AW8" s="90"/>
+      <c r="AX8" s="90"/>
+      <c r="AY8" s="90"/>
+      <c r="AZ8" s="90"/>
+      <c r="BA8" s="90"/>
+      <c r="BB8" s="90"/>
+      <c r="BC8" s="90"/>
+      <c r="BD8" s="90"/>
+      <c r="BE8" s="96"/>
     </row>
     <row r="9" spans="1:57" ht="15" customHeight="1">
-      <c r="A9" s="104"/>
-      <c r="B9" s="105"/>
-      <c r="C9" s="105"/>
-      <c r="D9" s="105"/>
-      <c r="E9" s="105"/>
-      <c r="F9" s="105"/>
-      <c r="G9" s="106"/>
+      <c r="A9" s="84"/>
+      <c r="B9" s="85"/>
+      <c r="C9" s="85"/>
+      <c r="D9" s="85"/>
+      <c r="E9" s="85"/>
+      <c r="F9" s="85"/>
+      <c r="G9" s="86"/>
       <c r="H9" s="87"/>
       <c r="I9" s="88"/>
       <c r="J9" s="88"/>
@@ -65531,57 +65531,57 @@
       <c r="M9" s="88"/>
       <c r="N9" s="89"/>
       <c r="O9" s="87"/>
-      <c r="P9" s="85"/>
-      <c r="Q9" s="85"/>
-      <c r="R9" s="85"/>
-      <c r="S9" s="85"/>
-      <c r="T9" s="85"/>
-      <c r="U9" s="85"/>
-      <c r="V9" s="85"/>
-      <c r="W9" s="85"/>
-      <c r="X9" s="85"/>
-      <c r="Y9" s="85"/>
-      <c r="Z9" s="85"/>
-      <c r="AA9" s="85"/>
-      <c r="AB9" s="85"/>
-      <c r="AC9" s="85"/>
-      <c r="AD9" s="85"/>
-      <c r="AE9" s="85"/>
-      <c r="AF9" s="85"/>
-      <c r="AG9" s="85"/>
-      <c r="AH9" s="85"/>
-      <c r="AI9" s="85"/>
-      <c r="AJ9" s="85"/>
-      <c r="AK9" s="85"/>
-      <c r="AL9" s="85"/>
-      <c r="AM9" s="85"/>
-      <c r="AN9" s="85"/>
-      <c r="AO9" s="85"/>
-      <c r="AP9" s="93"/>
-      <c r="AQ9" s="84"/>
-      <c r="AR9" s="85"/>
-      <c r="AS9" s="85"/>
-      <c r="AT9" s="85"/>
-      <c r="AU9" s="85"/>
-      <c r="AV9" s="85"/>
-      <c r="AW9" s="85"/>
-      <c r="AX9" s="85"/>
-      <c r="AY9" s="85"/>
-      <c r="AZ9" s="85"/>
-      <c r="BA9" s="85"/>
-      <c r="BB9" s="85"/>
-      <c r="BC9" s="85"/>
-      <c r="BD9" s="85"/>
-      <c r="BE9" s="86"/>
+      <c r="P9" s="90"/>
+      <c r="Q9" s="90"/>
+      <c r="R9" s="90"/>
+      <c r="S9" s="90"/>
+      <c r="T9" s="90"/>
+      <c r="U9" s="90"/>
+      <c r="V9" s="90"/>
+      <c r="W9" s="90"/>
+      <c r="X9" s="90"/>
+      <c r="Y9" s="90"/>
+      <c r="Z9" s="90"/>
+      <c r="AA9" s="90"/>
+      <c r="AB9" s="90"/>
+      <c r="AC9" s="90"/>
+      <c r="AD9" s="90"/>
+      <c r="AE9" s="90"/>
+      <c r="AF9" s="90"/>
+      <c r="AG9" s="90"/>
+      <c r="AH9" s="90"/>
+      <c r="AI9" s="90"/>
+      <c r="AJ9" s="90"/>
+      <c r="AK9" s="90"/>
+      <c r="AL9" s="90"/>
+      <c r="AM9" s="90"/>
+      <c r="AN9" s="90"/>
+      <c r="AO9" s="90"/>
+      <c r="AP9" s="91"/>
+      <c r="AQ9" s="95"/>
+      <c r="AR9" s="90"/>
+      <c r="AS9" s="90"/>
+      <c r="AT9" s="90"/>
+      <c r="AU9" s="90"/>
+      <c r="AV9" s="90"/>
+      <c r="AW9" s="90"/>
+      <c r="AX9" s="90"/>
+      <c r="AY9" s="90"/>
+      <c r="AZ9" s="90"/>
+      <c r="BA9" s="90"/>
+      <c r="BB9" s="90"/>
+      <c r="BC9" s="90"/>
+      <c r="BD9" s="90"/>
+      <c r="BE9" s="96"/>
     </row>
     <row r="10" spans="1:57" ht="15" customHeight="1">
-      <c r="A10" s="104"/>
-      <c r="B10" s="105"/>
-      <c r="C10" s="105"/>
-      <c r="D10" s="105"/>
-      <c r="E10" s="105"/>
-      <c r="F10" s="105"/>
-      <c r="G10" s="106"/>
+      <c r="A10" s="84"/>
+      <c r="B10" s="85"/>
+      <c r="C10" s="85"/>
+      <c r="D10" s="85"/>
+      <c r="E10" s="85"/>
+      <c r="F10" s="85"/>
+      <c r="G10" s="86"/>
       <c r="H10" s="87"/>
       <c r="I10" s="88"/>
       <c r="J10" s="88"/>
@@ -65590,57 +65590,57 @@
       <c r="M10" s="88"/>
       <c r="N10" s="89"/>
       <c r="O10" s="87"/>
-      <c r="P10" s="85"/>
-      <c r="Q10" s="85"/>
-      <c r="R10" s="85"/>
-      <c r="S10" s="85"/>
-      <c r="T10" s="85"/>
-      <c r="U10" s="85"/>
-      <c r="V10" s="85"/>
-      <c r="W10" s="85"/>
-      <c r="X10" s="85"/>
-      <c r="Y10" s="85"/>
-      <c r="Z10" s="85"/>
-      <c r="AA10" s="85"/>
-      <c r="AB10" s="85"/>
-      <c r="AC10" s="85"/>
-      <c r="AD10" s="85"/>
-      <c r="AE10" s="85"/>
-      <c r="AF10" s="85"/>
-      <c r="AG10" s="85"/>
-      <c r="AH10" s="85"/>
-      <c r="AI10" s="85"/>
-      <c r="AJ10" s="85"/>
-      <c r="AK10" s="85"/>
-      <c r="AL10" s="85"/>
-      <c r="AM10" s="85"/>
-      <c r="AN10" s="85"/>
-      <c r="AO10" s="85"/>
-      <c r="AP10" s="93"/>
-      <c r="AQ10" s="84"/>
-      <c r="AR10" s="85"/>
-      <c r="AS10" s="85"/>
-      <c r="AT10" s="85"/>
-      <c r="AU10" s="85"/>
-      <c r="AV10" s="85"/>
-      <c r="AW10" s="85"/>
-      <c r="AX10" s="85"/>
-      <c r="AY10" s="85"/>
-      <c r="AZ10" s="85"/>
-      <c r="BA10" s="85"/>
-      <c r="BB10" s="85"/>
-      <c r="BC10" s="85"/>
-      <c r="BD10" s="85"/>
-      <c r="BE10" s="86"/>
+      <c r="P10" s="90"/>
+      <c r="Q10" s="90"/>
+      <c r="R10" s="90"/>
+      <c r="S10" s="90"/>
+      <c r="T10" s="90"/>
+      <c r="U10" s="90"/>
+      <c r="V10" s="90"/>
+      <c r="W10" s="90"/>
+      <c r="X10" s="90"/>
+      <c r="Y10" s="90"/>
+      <c r="Z10" s="90"/>
+      <c r="AA10" s="90"/>
+      <c r="AB10" s="90"/>
+      <c r="AC10" s="90"/>
+      <c r="AD10" s="90"/>
+      <c r="AE10" s="90"/>
+      <c r="AF10" s="90"/>
+      <c r="AG10" s="90"/>
+      <c r="AH10" s="90"/>
+      <c r="AI10" s="90"/>
+      <c r="AJ10" s="90"/>
+      <c r="AK10" s="90"/>
+      <c r="AL10" s="90"/>
+      <c r="AM10" s="90"/>
+      <c r="AN10" s="90"/>
+      <c r="AO10" s="90"/>
+      <c r="AP10" s="91"/>
+      <c r="AQ10" s="95"/>
+      <c r="AR10" s="90"/>
+      <c r="AS10" s="90"/>
+      <c r="AT10" s="90"/>
+      <c r="AU10" s="90"/>
+      <c r="AV10" s="90"/>
+      <c r="AW10" s="90"/>
+      <c r="AX10" s="90"/>
+      <c r="AY10" s="90"/>
+      <c r="AZ10" s="90"/>
+      <c r="BA10" s="90"/>
+      <c r="BB10" s="90"/>
+      <c r="BC10" s="90"/>
+      <c r="BD10" s="90"/>
+      <c r="BE10" s="96"/>
     </row>
     <row r="11" spans="1:57" ht="15" customHeight="1">
-      <c r="A11" s="104"/>
-      <c r="B11" s="105"/>
-      <c r="C11" s="105"/>
-      <c r="D11" s="105"/>
-      <c r="E11" s="105"/>
-      <c r="F11" s="105"/>
-      <c r="G11" s="106"/>
+      <c r="A11" s="84"/>
+      <c r="B11" s="85"/>
+      <c r="C11" s="85"/>
+      <c r="D11" s="85"/>
+      <c r="E11" s="85"/>
+      <c r="F11" s="85"/>
+      <c r="G11" s="86"/>
       <c r="H11" s="87"/>
       <c r="I11" s="88"/>
       <c r="J11" s="88"/>
@@ -65649,57 +65649,57 @@
       <c r="M11" s="88"/>
       <c r="N11" s="89"/>
       <c r="O11" s="87"/>
-      <c r="P11" s="85"/>
-      <c r="Q11" s="85"/>
-      <c r="R11" s="85"/>
-      <c r="S11" s="85"/>
-      <c r="T11" s="85"/>
-      <c r="U11" s="85"/>
-      <c r="V11" s="85"/>
-      <c r="W11" s="85"/>
-      <c r="X11" s="85"/>
-      <c r="Y11" s="85"/>
-      <c r="Z11" s="85"/>
-      <c r="AA11" s="85"/>
-      <c r="AB11" s="85"/>
-      <c r="AC11" s="85"/>
-      <c r="AD11" s="85"/>
-      <c r="AE11" s="85"/>
-      <c r="AF11" s="85"/>
-      <c r="AG11" s="85"/>
-      <c r="AH11" s="85"/>
-      <c r="AI11" s="85"/>
-      <c r="AJ11" s="85"/>
-      <c r="AK11" s="85"/>
-      <c r="AL11" s="85"/>
-      <c r="AM11" s="85"/>
-      <c r="AN11" s="85"/>
-      <c r="AO11" s="85"/>
-      <c r="AP11" s="93"/>
-      <c r="AQ11" s="84"/>
-      <c r="AR11" s="85"/>
-      <c r="AS11" s="85"/>
-      <c r="AT11" s="85"/>
-      <c r="AU11" s="85"/>
-      <c r="AV11" s="85"/>
-      <c r="AW11" s="85"/>
-      <c r="AX11" s="85"/>
-      <c r="AY11" s="85"/>
-      <c r="AZ11" s="85"/>
-      <c r="BA11" s="85"/>
-      <c r="BB11" s="85"/>
-      <c r="BC11" s="85"/>
-      <c r="BD11" s="85"/>
-      <c r="BE11" s="86"/>
+      <c r="P11" s="90"/>
+      <c r="Q11" s="90"/>
+      <c r="R11" s="90"/>
+      <c r="S11" s="90"/>
+      <c r="T11" s="90"/>
+      <c r="U11" s="90"/>
+      <c r="V11" s="90"/>
+      <c r="W11" s="90"/>
+      <c r="X11" s="90"/>
+      <c r="Y11" s="90"/>
+      <c r="Z11" s="90"/>
+      <c r="AA11" s="90"/>
+      <c r="AB11" s="90"/>
+      <c r="AC11" s="90"/>
+      <c r="AD11" s="90"/>
+      <c r="AE11" s="90"/>
+      <c r="AF11" s="90"/>
+      <c r="AG11" s="90"/>
+      <c r="AH11" s="90"/>
+      <c r="AI11" s="90"/>
+      <c r="AJ11" s="90"/>
+      <c r="AK11" s="90"/>
+      <c r="AL11" s="90"/>
+      <c r="AM11" s="90"/>
+      <c r="AN11" s="90"/>
+      <c r="AO11" s="90"/>
+      <c r="AP11" s="91"/>
+      <c r="AQ11" s="95"/>
+      <c r="AR11" s="90"/>
+      <c r="AS11" s="90"/>
+      <c r="AT11" s="90"/>
+      <c r="AU11" s="90"/>
+      <c r="AV11" s="90"/>
+      <c r="AW11" s="90"/>
+      <c r="AX11" s="90"/>
+      <c r="AY11" s="90"/>
+      <c r="AZ11" s="90"/>
+      <c r="BA11" s="90"/>
+      <c r="BB11" s="90"/>
+      <c r="BC11" s="90"/>
+      <c r="BD11" s="90"/>
+      <c r="BE11" s="96"/>
     </row>
     <row r="12" spans="1:57" ht="15" customHeight="1">
-      <c r="A12" s="104"/>
-      <c r="B12" s="105"/>
-      <c r="C12" s="105"/>
-      <c r="D12" s="105"/>
-      <c r="E12" s="105"/>
-      <c r="F12" s="105"/>
-      <c r="G12" s="106"/>
+      <c r="A12" s="84"/>
+      <c r="B12" s="85"/>
+      <c r="C12" s="85"/>
+      <c r="D12" s="85"/>
+      <c r="E12" s="85"/>
+      <c r="F12" s="85"/>
+      <c r="G12" s="86"/>
       <c r="H12" s="87"/>
       <c r="I12" s="88"/>
       <c r="J12" s="88"/>
@@ -65708,57 +65708,57 @@
       <c r="M12" s="88"/>
       <c r="N12" s="89"/>
       <c r="O12" s="87"/>
-      <c r="P12" s="85"/>
-      <c r="Q12" s="85"/>
-      <c r="R12" s="85"/>
-      <c r="S12" s="85"/>
-      <c r="T12" s="85"/>
-      <c r="U12" s="85"/>
-      <c r="V12" s="85"/>
-      <c r="W12" s="85"/>
-      <c r="X12" s="85"/>
-      <c r="Y12" s="85"/>
-      <c r="Z12" s="85"/>
-      <c r="AA12" s="85"/>
-      <c r="AB12" s="85"/>
-      <c r="AC12" s="85"/>
-      <c r="AD12" s="85"/>
-      <c r="AE12" s="85"/>
-      <c r="AF12" s="85"/>
-      <c r="AG12" s="85"/>
-      <c r="AH12" s="85"/>
-      <c r="AI12" s="85"/>
-      <c r="AJ12" s="85"/>
-      <c r="AK12" s="85"/>
-      <c r="AL12" s="85"/>
-      <c r="AM12" s="85"/>
-      <c r="AN12" s="85"/>
-      <c r="AO12" s="85"/>
-      <c r="AP12" s="93"/>
-      <c r="AQ12" s="84"/>
-      <c r="AR12" s="85"/>
-      <c r="AS12" s="85"/>
-      <c r="AT12" s="85"/>
-      <c r="AU12" s="85"/>
-      <c r="AV12" s="85"/>
-      <c r="AW12" s="85"/>
-      <c r="AX12" s="85"/>
-      <c r="AY12" s="85"/>
-      <c r="AZ12" s="85"/>
-      <c r="BA12" s="85"/>
-      <c r="BB12" s="85"/>
-      <c r="BC12" s="85"/>
-      <c r="BD12" s="85"/>
-      <c r="BE12" s="86"/>
+      <c r="P12" s="90"/>
+      <c r="Q12" s="90"/>
+      <c r="R12" s="90"/>
+      <c r="S12" s="90"/>
+      <c r="T12" s="90"/>
+      <c r="U12" s="90"/>
+      <c r="V12" s="90"/>
+      <c r="W12" s="90"/>
+      <c r="X12" s="90"/>
+      <c r="Y12" s="90"/>
+      <c r="Z12" s="90"/>
+      <c r="AA12" s="90"/>
+      <c r="AB12" s="90"/>
+      <c r="AC12" s="90"/>
+      <c r="AD12" s="90"/>
+      <c r="AE12" s="90"/>
+      <c r="AF12" s="90"/>
+      <c r="AG12" s="90"/>
+      <c r="AH12" s="90"/>
+      <c r="AI12" s="90"/>
+      <c r="AJ12" s="90"/>
+      <c r="AK12" s="90"/>
+      <c r="AL12" s="90"/>
+      <c r="AM12" s="90"/>
+      <c r="AN12" s="90"/>
+      <c r="AO12" s="90"/>
+      <c r="AP12" s="91"/>
+      <c r="AQ12" s="95"/>
+      <c r="AR12" s="90"/>
+      <c r="AS12" s="90"/>
+      <c r="AT12" s="90"/>
+      <c r="AU12" s="90"/>
+      <c r="AV12" s="90"/>
+      <c r="AW12" s="90"/>
+      <c r="AX12" s="90"/>
+      <c r="AY12" s="90"/>
+      <c r="AZ12" s="90"/>
+      <c r="BA12" s="90"/>
+      <c r="BB12" s="90"/>
+      <c r="BC12" s="90"/>
+      <c r="BD12" s="90"/>
+      <c r="BE12" s="96"/>
     </row>
     <row r="13" spans="1:57" ht="15" customHeight="1">
-      <c r="A13" s="104"/>
-      <c r="B13" s="105"/>
-      <c r="C13" s="105"/>
-      <c r="D13" s="105"/>
-      <c r="E13" s="105"/>
-      <c r="F13" s="105"/>
-      <c r="G13" s="106"/>
+      <c r="A13" s="84"/>
+      <c r="B13" s="85"/>
+      <c r="C13" s="85"/>
+      <c r="D13" s="85"/>
+      <c r="E13" s="85"/>
+      <c r="F13" s="85"/>
+      <c r="G13" s="86"/>
       <c r="H13" s="87"/>
       <c r="I13" s="88"/>
       <c r="J13" s="88"/>
@@ -65767,57 +65767,57 @@
       <c r="M13" s="88"/>
       <c r="N13" s="89"/>
       <c r="O13" s="87"/>
-      <c r="P13" s="85"/>
-      <c r="Q13" s="85"/>
-      <c r="R13" s="85"/>
-      <c r="S13" s="85"/>
-      <c r="T13" s="85"/>
-      <c r="U13" s="85"/>
-      <c r="V13" s="85"/>
-      <c r="W13" s="85"/>
-      <c r="X13" s="85"/>
-      <c r="Y13" s="85"/>
-      <c r="Z13" s="85"/>
-      <c r="AA13" s="85"/>
-      <c r="AB13" s="85"/>
-      <c r="AC13" s="85"/>
-      <c r="AD13" s="85"/>
-      <c r="AE13" s="85"/>
-      <c r="AF13" s="85"/>
-      <c r="AG13" s="85"/>
-      <c r="AH13" s="85"/>
-      <c r="AI13" s="85"/>
-      <c r="AJ13" s="85"/>
-      <c r="AK13" s="85"/>
-      <c r="AL13" s="85"/>
-      <c r="AM13" s="85"/>
-      <c r="AN13" s="85"/>
-      <c r="AO13" s="85"/>
-      <c r="AP13" s="93"/>
-      <c r="AQ13" s="84"/>
-      <c r="AR13" s="85"/>
-      <c r="AS13" s="85"/>
-      <c r="AT13" s="85"/>
-      <c r="AU13" s="85"/>
-      <c r="AV13" s="85"/>
-      <c r="AW13" s="85"/>
-      <c r="AX13" s="85"/>
-      <c r="AY13" s="85"/>
-      <c r="AZ13" s="85"/>
-      <c r="BA13" s="85"/>
-      <c r="BB13" s="85"/>
-      <c r="BC13" s="85"/>
-      <c r="BD13" s="85"/>
-      <c r="BE13" s="86"/>
+      <c r="P13" s="90"/>
+      <c r="Q13" s="90"/>
+      <c r="R13" s="90"/>
+      <c r="S13" s="90"/>
+      <c r="T13" s="90"/>
+      <c r="U13" s="90"/>
+      <c r="V13" s="90"/>
+      <c r="W13" s="90"/>
+      <c r="X13" s="90"/>
+      <c r="Y13" s="90"/>
+      <c r="Z13" s="90"/>
+      <c r="AA13" s="90"/>
+      <c r="AB13" s="90"/>
+      <c r="AC13" s="90"/>
+      <c r="AD13" s="90"/>
+      <c r="AE13" s="90"/>
+      <c r="AF13" s="90"/>
+      <c r="AG13" s="90"/>
+      <c r="AH13" s="90"/>
+      <c r="AI13" s="90"/>
+      <c r="AJ13" s="90"/>
+      <c r="AK13" s="90"/>
+      <c r="AL13" s="90"/>
+      <c r="AM13" s="90"/>
+      <c r="AN13" s="90"/>
+      <c r="AO13" s="90"/>
+      <c r="AP13" s="91"/>
+      <c r="AQ13" s="95"/>
+      <c r="AR13" s="90"/>
+      <c r="AS13" s="90"/>
+      <c r="AT13" s="90"/>
+      <c r="AU13" s="90"/>
+      <c r="AV13" s="90"/>
+      <c r="AW13" s="90"/>
+      <c r="AX13" s="90"/>
+      <c r="AY13" s="90"/>
+      <c r="AZ13" s="90"/>
+      <c r="BA13" s="90"/>
+      <c r="BB13" s="90"/>
+      <c r="BC13" s="90"/>
+      <c r="BD13" s="90"/>
+      <c r="BE13" s="96"/>
     </row>
     <row r="14" spans="1:57" ht="15" customHeight="1">
-      <c r="A14" s="104"/>
-      <c r="B14" s="105"/>
-      <c r="C14" s="105"/>
-      <c r="D14" s="105"/>
-      <c r="E14" s="105"/>
-      <c r="F14" s="105"/>
-      <c r="G14" s="106"/>
+      <c r="A14" s="84"/>
+      <c r="B14" s="85"/>
+      <c r="C14" s="85"/>
+      <c r="D14" s="85"/>
+      <c r="E14" s="85"/>
+      <c r="F14" s="85"/>
+      <c r="G14" s="86"/>
       <c r="H14" s="87"/>
       <c r="I14" s="88"/>
       <c r="J14" s="88"/>
@@ -65826,57 +65826,57 @@
       <c r="M14" s="88"/>
       <c r="N14" s="89"/>
       <c r="O14" s="87"/>
-      <c r="P14" s="85"/>
-      <c r="Q14" s="85"/>
-      <c r="R14" s="85"/>
-      <c r="S14" s="85"/>
-      <c r="T14" s="85"/>
-      <c r="U14" s="85"/>
-      <c r="V14" s="85"/>
-      <c r="W14" s="85"/>
-      <c r="X14" s="85"/>
-      <c r="Y14" s="85"/>
-      <c r="Z14" s="85"/>
-      <c r="AA14" s="85"/>
-      <c r="AB14" s="85"/>
-      <c r="AC14" s="85"/>
-      <c r="AD14" s="85"/>
-      <c r="AE14" s="85"/>
-      <c r="AF14" s="85"/>
-      <c r="AG14" s="85"/>
-      <c r="AH14" s="85"/>
-      <c r="AI14" s="85"/>
-      <c r="AJ14" s="85"/>
-      <c r="AK14" s="85"/>
-      <c r="AL14" s="85"/>
-      <c r="AM14" s="85"/>
-      <c r="AN14" s="85"/>
-      <c r="AO14" s="85"/>
-      <c r="AP14" s="93"/>
-      <c r="AQ14" s="84"/>
-      <c r="AR14" s="85"/>
-      <c r="AS14" s="85"/>
-      <c r="AT14" s="85"/>
-      <c r="AU14" s="85"/>
-      <c r="AV14" s="85"/>
-      <c r="AW14" s="85"/>
-      <c r="AX14" s="85"/>
-      <c r="AY14" s="85"/>
-      <c r="AZ14" s="85"/>
-      <c r="BA14" s="85"/>
-      <c r="BB14" s="85"/>
-      <c r="BC14" s="85"/>
-      <c r="BD14" s="85"/>
-      <c r="BE14" s="86"/>
+      <c r="P14" s="90"/>
+      <c r="Q14" s="90"/>
+      <c r="R14" s="90"/>
+      <c r="S14" s="90"/>
+      <c r="T14" s="90"/>
+      <c r="U14" s="90"/>
+      <c r="V14" s="90"/>
+      <c r="W14" s="90"/>
+      <c r="X14" s="90"/>
+      <c r="Y14" s="90"/>
+      <c r="Z14" s="90"/>
+      <c r="AA14" s="90"/>
+      <c r="AB14" s="90"/>
+      <c r="AC14" s="90"/>
+      <c r="AD14" s="90"/>
+      <c r="AE14" s="90"/>
+      <c r="AF14" s="90"/>
+      <c r="AG14" s="90"/>
+      <c r="AH14" s="90"/>
+      <c r="AI14" s="90"/>
+      <c r="AJ14" s="90"/>
+      <c r="AK14" s="90"/>
+      <c r="AL14" s="90"/>
+      <c r="AM14" s="90"/>
+      <c r="AN14" s="90"/>
+      <c r="AO14" s="90"/>
+      <c r="AP14" s="91"/>
+      <c r="AQ14" s="95"/>
+      <c r="AR14" s="90"/>
+      <c r="AS14" s="90"/>
+      <c r="AT14" s="90"/>
+      <c r="AU14" s="90"/>
+      <c r="AV14" s="90"/>
+      <c r="AW14" s="90"/>
+      <c r="AX14" s="90"/>
+      <c r="AY14" s="90"/>
+      <c r="AZ14" s="90"/>
+      <c r="BA14" s="90"/>
+      <c r="BB14" s="90"/>
+      <c r="BC14" s="90"/>
+      <c r="BD14" s="90"/>
+      <c r="BE14" s="96"/>
     </row>
     <row r="15" spans="1:57" ht="15" customHeight="1">
-      <c r="A15" s="104"/>
-      <c r="B15" s="105"/>
-      <c r="C15" s="105"/>
-      <c r="D15" s="105"/>
-      <c r="E15" s="105"/>
-      <c r="F15" s="105"/>
-      <c r="G15" s="106"/>
+      <c r="A15" s="84"/>
+      <c r="B15" s="85"/>
+      <c r="C15" s="85"/>
+      <c r="D15" s="85"/>
+      <c r="E15" s="85"/>
+      <c r="F15" s="85"/>
+      <c r="G15" s="86"/>
       <c r="H15" s="87"/>
       <c r="I15" s="88"/>
       <c r="J15" s="88"/>
@@ -65885,57 +65885,57 @@
       <c r="M15" s="88"/>
       <c r="N15" s="89"/>
       <c r="O15" s="87"/>
-      <c r="P15" s="85"/>
-      <c r="Q15" s="85"/>
-      <c r="R15" s="85"/>
-      <c r="S15" s="85"/>
-      <c r="T15" s="85"/>
-      <c r="U15" s="85"/>
-      <c r="V15" s="85"/>
-      <c r="W15" s="85"/>
-      <c r="X15" s="85"/>
-      <c r="Y15" s="85"/>
-      <c r="Z15" s="85"/>
-      <c r="AA15" s="85"/>
-      <c r="AB15" s="85"/>
-      <c r="AC15" s="85"/>
-      <c r="AD15" s="85"/>
-      <c r="AE15" s="85"/>
-      <c r="AF15" s="85"/>
-      <c r="AG15" s="85"/>
-      <c r="AH15" s="85"/>
-      <c r="AI15" s="85"/>
-      <c r="AJ15" s="85"/>
-      <c r="AK15" s="85"/>
-      <c r="AL15" s="85"/>
-      <c r="AM15" s="85"/>
-      <c r="AN15" s="85"/>
-      <c r="AO15" s="85"/>
-      <c r="AP15" s="93"/>
-      <c r="AQ15" s="84"/>
-      <c r="AR15" s="85"/>
-      <c r="AS15" s="85"/>
-      <c r="AT15" s="85"/>
-      <c r="AU15" s="85"/>
-      <c r="AV15" s="85"/>
-      <c r="AW15" s="85"/>
-      <c r="AX15" s="85"/>
-      <c r="AY15" s="85"/>
-      <c r="AZ15" s="85"/>
-      <c r="BA15" s="85"/>
-      <c r="BB15" s="85"/>
-      <c r="BC15" s="85"/>
-      <c r="BD15" s="85"/>
-      <c r="BE15" s="86"/>
+      <c r="P15" s="90"/>
+      <c r="Q15" s="90"/>
+      <c r="R15" s="90"/>
+      <c r="S15" s="90"/>
+      <c r="T15" s="90"/>
+      <c r="U15" s="90"/>
+      <c r="V15" s="90"/>
+      <c r="W15" s="90"/>
+      <c r="X15" s="90"/>
+      <c r="Y15" s="90"/>
+      <c r="Z15" s="90"/>
+      <c r="AA15" s="90"/>
+      <c r="AB15" s="90"/>
+      <c r="AC15" s="90"/>
+      <c r="AD15" s="90"/>
+      <c r="AE15" s="90"/>
+      <c r="AF15" s="90"/>
+      <c r="AG15" s="90"/>
+      <c r="AH15" s="90"/>
+      <c r="AI15" s="90"/>
+      <c r="AJ15" s="90"/>
+      <c r="AK15" s="90"/>
+      <c r="AL15" s="90"/>
+      <c r="AM15" s="90"/>
+      <c r="AN15" s="90"/>
+      <c r="AO15" s="90"/>
+      <c r="AP15" s="91"/>
+      <c r="AQ15" s="95"/>
+      <c r="AR15" s="90"/>
+      <c r="AS15" s="90"/>
+      <c r="AT15" s="90"/>
+      <c r="AU15" s="90"/>
+      <c r="AV15" s="90"/>
+      <c r="AW15" s="90"/>
+      <c r="AX15" s="90"/>
+      <c r="AY15" s="90"/>
+      <c r="AZ15" s="90"/>
+      <c r="BA15" s="90"/>
+      <c r="BB15" s="90"/>
+      <c r="BC15" s="90"/>
+      <c r="BD15" s="90"/>
+      <c r="BE15" s="96"/>
     </row>
     <row r="16" spans="1:57" ht="15" customHeight="1">
-      <c r="A16" s="104"/>
-      <c r="B16" s="105"/>
-      <c r="C16" s="105"/>
-      <c r="D16" s="105"/>
-      <c r="E16" s="105"/>
-      <c r="F16" s="105"/>
-      <c r="G16" s="106"/>
+      <c r="A16" s="84"/>
+      <c r="B16" s="85"/>
+      <c r="C16" s="85"/>
+      <c r="D16" s="85"/>
+      <c r="E16" s="85"/>
+      <c r="F16" s="85"/>
+      <c r="G16" s="86"/>
       <c r="H16" s="87"/>
       <c r="I16" s="88"/>
       <c r="J16" s="88"/>
@@ -65944,57 +65944,57 @@
       <c r="M16" s="88"/>
       <c r="N16" s="89"/>
       <c r="O16" s="87"/>
-      <c r="P16" s="85"/>
-      <c r="Q16" s="85"/>
-      <c r="R16" s="85"/>
-      <c r="S16" s="85"/>
-      <c r="T16" s="85"/>
-      <c r="U16" s="85"/>
-      <c r="V16" s="85"/>
-      <c r="W16" s="85"/>
-      <c r="X16" s="85"/>
-      <c r="Y16" s="85"/>
-      <c r="Z16" s="85"/>
-      <c r="AA16" s="85"/>
-      <c r="AB16" s="85"/>
-      <c r="AC16" s="85"/>
-      <c r="AD16" s="85"/>
-      <c r="AE16" s="85"/>
-      <c r="AF16" s="85"/>
-      <c r="AG16" s="85"/>
-      <c r="AH16" s="85"/>
-      <c r="AI16" s="85"/>
-      <c r="AJ16" s="85"/>
-      <c r="AK16" s="85"/>
-      <c r="AL16" s="85"/>
-      <c r="AM16" s="85"/>
-      <c r="AN16" s="85"/>
-      <c r="AO16" s="85"/>
-      <c r="AP16" s="93"/>
-      <c r="AQ16" s="84"/>
-      <c r="AR16" s="85"/>
-      <c r="AS16" s="85"/>
-      <c r="AT16" s="85"/>
-      <c r="AU16" s="85"/>
-      <c r="AV16" s="85"/>
-      <c r="AW16" s="85"/>
-      <c r="AX16" s="85"/>
-      <c r="AY16" s="85"/>
-      <c r="AZ16" s="85"/>
-      <c r="BA16" s="85"/>
-      <c r="BB16" s="85"/>
-      <c r="BC16" s="85"/>
-      <c r="BD16" s="85"/>
-      <c r="BE16" s="86"/>
+      <c r="P16" s="90"/>
+      <c r="Q16" s="90"/>
+      <c r="R16" s="90"/>
+      <c r="S16" s="90"/>
+      <c r="T16" s="90"/>
+      <c r="U16" s="90"/>
+      <c r="V16" s="90"/>
+      <c r="W16" s="90"/>
+      <c r="X16" s="90"/>
+      <c r="Y16" s="90"/>
+      <c r="Z16" s="90"/>
+      <c r="AA16" s="90"/>
+      <c r="AB16" s="90"/>
+      <c r="AC16" s="90"/>
+      <c r="AD16" s="90"/>
+      <c r="AE16" s="90"/>
+      <c r="AF16" s="90"/>
+      <c r="AG16" s="90"/>
+      <c r="AH16" s="90"/>
+      <c r="AI16" s="90"/>
+      <c r="AJ16" s="90"/>
+      <c r="AK16" s="90"/>
+      <c r="AL16" s="90"/>
+      <c r="AM16" s="90"/>
+      <c r="AN16" s="90"/>
+      <c r="AO16" s="90"/>
+      <c r="AP16" s="91"/>
+      <c r="AQ16" s="95"/>
+      <c r="AR16" s="90"/>
+      <c r="AS16" s="90"/>
+      <c r="AT16" s="90"/>
+      <c r="AU16" s="90"/>
+      <c r="AV16" s="90"/>
+      <c r="AW16" s="90"/>
+      <c r="AX16" s="90"/>
+      <c r="AY16" s="90"/>
+      <c r="AZ16" s="90"/>
+      <c r="BA16" s="90"/>
+      <c r="BB16" s="90"/>
+      <c r="BC16" s="90"/>
+      <c r="BD16" s="90"/>
+      <c r="BE16" s="96"/>
     </row>
     <row r="17" spans="1:57" ht="15" customHeight="1">
-      <c r="A17" s="104"/>
-      <c r="B17" s="105"/>
-      <c r="C17" s="105"/>
-      <c r="D17" s="105"/>
-      <c r="E17" s="105"/>
-      <c r="F17" s="105"/>
-      <c r="G17" s="106"/>
+      <c r="A17" s="84"/>
+      <c r="B17" s="85"/>
+      <c r="C17" s="85"/>
+      <c r="D17" s="85"/>
+      <c r="E17" s="85"/>
+      <c r="F17" s="85"/>
+      <c r="G17" s="86"/>
       <c r="H17" s="87"/>
       <c r="I17" s="88"/>
       <c r="J17" s="88"/>
@@ -66003,57 +66003,57 @@
       <c r="M17" s="88"/>
       <c r="N17" s="89"/>
       <c r="O17" s="87"/>
-      <c r="P17" s="85"/>
-      <c r="Q17" s="85"/>
-      <c r="R17" s="85"/>
-      <c r="S17" s="85"/>
-      <c r="T17" s="85"/>
-      <c r="U17" s="85"/>
-      <c r="V17" s="85"/>
-      <c r="W17" s="85"/>
-      <c r="X17" s="85"/>
-      <c r="Y17" s="85"/>
-      <c r="Z17" s="85"/>
-      <c r="AA17" s="85"/>
-      <c r="AB17" s="85"/>
-      <c r="AC17" s="85"/>
-      <c r="AD17" s="85"/>
-      <c r="AE17" s="85"/>
-      <c r="AF17" s="85"/>
-      <c r="AG17" s="85"/>
-      <c r="AH17" s="85"/>
-      <c r="AI17" s="85"/>
-      <c r="AJ17" s="85"/>
-      <c r="AK17" s="85"/>
-      <c r="AL17" s="85"/>
-      <c r="AM17" s="85"/>
-      <c r="AN17" s="85"/>
-      <c r="AO17" s="85"/>
-      <c r="AP17" s="93"/>
-      <c r="AQ17" s="84"/>
-      <c r="AR17" s="85"/>
-      <c r="AS17" s="85"/>
-      <c r="AT17" s="85"/>
-      <c r="AU17" s="85"/>
-      <c r="AV17" s="85"/>
-      <c r="AW17" s="85"/>
-      <c r="AX17" s="85"/>
-      <c r="AY17" s="85"/>
-      <c r="AZ17" s="85"/>
-      <c r="BA17" s="85"/>
-      <c r="BB17" s="85"/>
-      <c r="BC17" s="85"/>
-      <c r="BD17" s="85"/>
-      <c r="BE17" s="86"/>
+      <c r="P17" s="90"/>
+      <c r="Q17" s="90"/>
+      <c r="R17" s="90"/>
+      <c r="S17" s="90"/>
+      <c r="T17" s="90"/>
+      <c r="U17" s="90"/>
+      <c r="V17" s="90"/>
+      <c r="W17" s="90"/>
+      <c r="X17" s="90"/>
+      <c r="Y17" s="90"/>
+      <c r="Z17" s="90"/>
+      <c r="AA17" s="90"/>
+      <c r="AB17" s="90"/>
+      <c r="AC17" s="90"/>
+      <c r="AD17" s="90"/>
+      <c r="AE17" s="90"/>
+      <c r="AF17" s="90"/>
+      <c r="AG17" s="90"/>
+      <c r="AH17" s="90"/>
+      <c r="AI17" s="90"/>
+      <c r="AJ17" s="90"/>
+      <c r="AK17" s="90"/>
+      <c r="AL17" s="90"/>
+      <c r="AM17" s="90"/>
+      <c r="AN17" s="90"/>
+      <c r="AO17" s="90"/>
+      <c r="AP17" s="91"/>
+      <c r="AQ17" s="95"/>
+      <c r="AR17" s="90"/>
+      <c r="AS17" s="90"/>
+      <c r="AT17" s="90"/>
+      <c r="AU17" s="90"/>
+      <c r="AV17" s="90"/>
+      <c r="AW17" s="90"/>
+      <c r="AX17" s="90"/>
+      <c r="AY17" s="90"/>
+      <c r="AZ17" s="90"/>
+      <c r="BA17" s="90"/>
+      <c r="BB17" s="90"/>
+      <c r="BC17" s="90"/>
+      <c r="BD17" s="90"/>
+      <c r="BE17" s="96"/>
     </row>
     <row r="18" spans="1:57" ht="15" customHeight="1">
-      <c r="A18" s="104"/>
-      <c r="B18" s="105"/>
-      <c r="C18" s="105"/>
-      <c r="D18" s="105"/>
-      <c r="E18" s="105"/>
-      <c r="F18" s="105"/>
-      <c r="G18" s="106"/>
+      <c r="A18" s="84"/>
+      <c r="B18" s="85"/>
+      <c r="C18" s="85"/>
+      <c r="D18" s="85"/>
+      <c r="E18" s="85"/>
+      <c r="F18" s="85"/>
+      <c r="G18" s="86"/>
       <c r="H18" s="87"/>
       <c r="I18" s="88"/>
       <c r="J18" s="88"/>
@@ -66062,57 +66062,57 @@
       <c r="M18" s="88"/>
       <c r="N18" s="89"/>
       <c r="O18" s="87"/>
-      <c r="P18" s="85"/>
-      <c r="Q18" s="85"/>
-      <c r="R18" s="85"/>
-      <c r="S18" s="85"/>
-      <c r="T18" s="85"/>
-      <c r="U18" s="85"/>
-      <c r="V18" s="85"/>
-      <c r="W18" s="85"/>
-      <c r="X18" s="85"/>
-      <c r="Y18" s="85"/>
-      <c r="Z18" s="85"/>
-      <c r="AA18" s="85"/>
-      <c r="AB18" s="85"/>
-      <c r="AC18" s="85"/>
-      <c r="AD18" s="85"/>
-      <c r="AE18" s="85"/>
-      <c r="AF18" s="85"/>
-      <c r="AG18" s="85"/>
-      <c r="AH18" s="85"/>
-      <c r="AI18" s="85"/>
-      <c r="AJ18" s="85"/>
-      <c r="AK18" s="85"/>
-      <c r="AL18" s="85"/>
-      <c r="AM18" s="85"/>
-      <c r="AN18" s="85"/>
-      <c r="AO18" s="85"/>
-      <c r="AP18" s="93"/>
-      <c r="AQ18" s="84"/>
-      <c r="AR18" s="85"/>
-      <c r="AS18" s="85"/>
-      <c r="AT18" s="85"/>
-      <c r="AU18" s="85"/>
-      <c r="AV18" s="85"/>
-      <c r="AW18" s="85"/>
-      <c r="AX18" s="85"/>
-      <c r="AY18" s="85"/>
-      <c r="AZ18" s="85"/>
-      <c r="BA18" s="85"/>
-      <c r="BB18" s="85"/>
-      <c r="BC18" s="85"/>
-      <c r="BD18" s="85"/>
-      <c r="BE18" s="86"/>
+      <c r="P18" s="90"/>
+      <c r="Q18" s="90"/>
+      <c r="R18" s="90"/>
+      <c r="S18" s="90"/>
+      <c r="T18" s="90"/>
+      <c r="U18" s="90"/>
+      <c r="V18" s="90"/>
+      <c r="W18" s="90"/>
+      <c r="X18" s="90"/>
+      <c r="Y18" s="90"/>
+      <c r="Z18" s="90"/>
+      <c r="AA18" s="90"/>
+      <c r="AB18" s="90"/>
+      <c r="AC18" s="90"/>
+      <c r="AD18" s="90"/>
+      <c r="AE18" s="90"/>
+      <c r="AF18" s="90"/>
+      <c r="AG18" s="90"/>
+      <c r="AH18" s="90"/>
+      <c r="AI18" s="90"/>
+      <c r="AJ18" s="90"/>
+      <c r="AK18" s="90"/>
+      <c r="AL18" s="90"/>
+      <c r="AM18" s="90"/>
+      <c r="AN18" s="90"/>
+      <c r="AO18" s="90"/>
+      <c r="AP18" s="91"/>
+      <c r="AQ18" s="95"/>
+      <c r="AR18" s="90"/>
+      <c r="AS18" s="90"/>
+      <c r="AT18" s="90"/>
+      <c r="AU18" s="90"/>
+      <c r="AV18" s="90"/>
+      <c r="AW18" s="90"/>
+      <c r="AX18" s="90"/>
+      <c r="AY18" s="90"/>
+      <c r="AZ18" s="90"/>
+      <c r="BA18" s="90"/>
+      <c r="BB18" s="90"/>
+      <c r="BC18" s="90"/>
+      <c r="BD18" s="90"/>
+      <c r="BE18" s="96"/>
     </row>
     <row r="19" spans="1:57" ht="15" customHeight="1">
-      <c r="A19" s="104"/>
-      <c r="B19" s="105"/>
-      <c r="C19" s="105"/>
-      <c r="D19" s="105"/>
-      <c r="E19" s="105"/>
-      <c r="F19" s="105"/>
-      <c r="G19" s="106"/>
+      <c r="A19" s="84"/>
+      <c r="B19" s="85"/>
+      <c r="C19" s="85"/>
+      <c r="D19" s="85"/>
+      <c r="E19" s="85"/>
+      <c r="F19" s="85"/>
+      <c r="G19" s="86"/>
       <c r="H19" s="87"/>
       <c r="I19" s="88"/>
       <c r="J19" s="88"/>
@@ -66121,57 +66121,57 @@
       <c r="M19" s="88"/>
       <c r="N19" s="89"/>
       <c r="O19" s="87"/>
-      <c r="P19" s="85"/>
-      <c r="Q19" s="85"/>
-      <c r="R19" s="85"/>
-      <c r="S19" s="85"/>
-      <c r="T19" s="85"/>
-      <c r="U19" s="85"/>
-      <c r="V19" s="85"/>
-      <c r="W19" s="85"/>
-      <c r="X19" s="85"/>
-      <c r="Y19" s="85"/>
-      <c r="Z19" s="85"/>
-      <c r="AA19" s="85"/>
-      <c r="AB19" s="85"/>
-      <c r="AC19" s="85"/>
-      <c r="AD19" s="85"/>
-      <c r="AE19" s="85"/>
-      <c r="AF19" s="85"/>
-      <c r="AG19" s="85"/>
-      <c r="AH19" s="85"/>
-      <c r="AI19" s="85"/>
-      <c r="AJ19" s="85"/>
-      <c r="AK19" s="85"/>
-      <c r="AL19" s="85"/>
-      <c r="AM19" s="85"/>
-      <c r="AN19" s="85"/>
-      <c r="AO19" s="85"/>
-      <c r="AP19" s="93"/>
-      <c r="AQ19" s="84"/>
-      <c r="AR19" s="85"/>
-      <c r="AS19" s="85"/>
-      <c r="AT19" s="85"/>
-      <c r="AU19" s="85"/>
-      <c r="AV19" s="85"/>
-      <c r="AW19" s="85"/>
-      <c r="AX19" s="85"/>
-      <c r="AY19" s="85"/>
-      <c r="AZ19" s="85"/>
-      <c r="BA19" s="85"/>
-      <c r="BB19" s="85"/>
-      <c r="BC19" s="85"/>
-      <c r="BD19" s="85"/>
-      <c r="BE19" s="86"/>
+      <c r="P19" s="90"/>
+      <c r="Q19" s="90"/>
+      <c r="R19" s="90"/>
+      <c r="S19" s="90"/>
+      <c r="T19" s="90"/>
+      <c r="U19" s="90"/>
+      <c r="V19" s="90"/>
+      <c r="W19" s="90"/>
+      <c r="X19" s="90"/>
+      <c r="Y19" s="90"/>
+      <c r="Z19" s="90"/>
+      <c r="AA19" s="90"/>
+      <c r="AB19" s="90"/>
+      <c r="AC19" s="90"/>
+      <c r="AD19" s="90"/>
+      <c r="AE19" s="90"/>
+      <c r="AF19" s="90"/>
+      <c r="AG19" s="90"/>
+      <c r="AH19" s="90"/>
+      <c r="AI19" s="90"/>
+      <c r="AJ19" s="90"/>
+      <c r="AK19" s="90"/>
+      <c r="AL19" s="90"/>
+      <c r="AM19" s="90"/>
+      <c r="AN19" s="90"/>
+      <c r="AO19" s="90"/>
+      <c r="AP19" s="91"/>
+      <c r="AQ19" s="95"/>
+      <c r="AR19" s="90"/>
+      <c r="AS19" s="90"/>
+      <c r="AT19" s="90"/>
+      <c r="AU19" s="90"/>
+      <c r="AV19" s="90"/>
+      <c r="AW19" s="90"/>
+      <c r="AX19" s="90"/>
+      <c r="AY19" s="90"/>
+      <c r="AZ19" s="90"/>
+      <c r="BA19" s="90"/>
+      <c r="BB19" s="90"/>
+      <c r="BC19" s="90"/>
+      <c r="BD19" s="90"/>
+      <c r="BE19" s="96"/>
     </row>
     <row r="20" spans="1:57" ht="15" customHeight="1">
-      <c r="A20" s="104"/>
-      <c r="B20" s="105"/>
-      <c r="C20" s="105"/>
-      <c r="D20" s="105"/>
-      <c r="E20" s="105"/>
-      <c r="F20" s="105"/>
-      <c r="G20" s="106"/>
+      <c r="A20" s="84"/>
+      <c r="B20" s="85"/>
+      <c r="C20" s="85"/>
+      <c r="D20" s="85"/>
+      <c r="E20" s="85"/>
+      <c r="F20" s="85"/>
+      <c r="G20" s="86"/>
       <c r="H20" s="87"/>
       <c r="I20" s="88"/>
       <c r="J20" s="88"/>
@@ -66180,57 +66180,57 @@
       <c r="M20" s="88"/>
       <c r="N20" s="89"/>
       <c r="O20" s="87"/>
-      <c r="P20" s="85"/>
-      <c r="Q20" s="85"/>
-      <c r="R20" s="85"/>
-      <c r="S20" s="85"/>
-      <c r="T20" s="85"/>
-      <c r="U20" s="85"/>
-      <c r="V20" s="85"/>
-      <c r="W20" s="85"/>
-      <c r="X20" s="85"/>
-      <c r="Y20" s="85"/>
-      <c r="Z20" s="85"/>
-      <c r="AA20" s="85"/>
-      <c r="AB20" s="85"/>
-      <c r="AC20" s="85"/>
-      <c r="AD20" s="85"/>
-      <c r="AE20" s="85"/>
-      <c r="AF20" s="85"/>
-      <c r="AG20" s="85"/>
-      <c r="AH20" s="85"/>
-      <c r="AI20" s="85"/>
-      <c r="AJ20" s="85"/>
-      <c r="AK20" s="85"/>
-      <c r="AL20" s="85"/>
-      <c r="AM20" s="85"/>
-      <c r="AN20" s="85"/>
-      <c r="AO20" s="85"/>
-      <c r="AP20" s="93"/>
-      <c r="AQ20" s="84"/>
-      <c r="AR20" s="85"/>
-      <c r="AS20" s="85"/>
-      <c r="AT20" s="85"/>
-      <c r="AU20" s="85"/>
-      <c r="AV20" s="85"/>
-      <c r="AW20" s="85"/>
-      <c r="AX20" s="85"/>
-      <c r="AY20" s="85"/>
-      <c r="AZ20" s="85"/>
-      <c r="BA20" s="85"/>
-      <c r="BB20" s="85"/>
-      <c r="BC20" s="85"/>
-      <c r="BD20" s="85"/>
-      <c r="BE20" s="86"/>
+      <c r="P20" s="90"/>
+      <c r="Q20" s="90"/>
+      <c r="R20" s="90"/>
+      <c r="S20" s="90"/>
+      <c r="T20" s="90"/>
+      <c r="U20" s="90"/>
+      <c r="V20" s="90"/>
+      <c r="W20" s="90"/>
+      <c r="X20" s="90"/>
+      <c r="Y20" s="90"/>
+      <c r="Z20" s="90"/>
+      <c r="AA20" s="90"/>
+      <c r="AB20" s="90"/>
+      <c r="AC20" s="90"/>
+      <c r="AD20" s="90"/>
+      <c r="AE20" s="90"/>
+      <c r="AF20" s="90"/>
+      <c r="AG20" s="90"/>
+      <c r="AH20" s="90"/>
+      <c r="AI20" s="90"/>
+      <c r="AJ20" s="90"/>
+      <c r="AK20" s="90"/>
+      <c r="AL20" s="90"/>
+      <c r="AM20" s="90"/>
+      <c r="AN20" s="90"/>
+      <c r="AO20" s="90"/>
+      <c r="AP20" s="91"/>
+      <c r="AQ20" s="95"/>
+      <c r="AR20" s="90"/>
+      <c r="AS20" s="90"/>
+      <c r="AT20" s="90"/>
+      <c r="AU20" s="90"/>
+      <c r="AV20" s="90"/>
+      <c r="AW20" s="90"/>
+      <c r="AX20" s="90"/>
+      <c r="AY20" s="90"/>
+      <c r="AZ20" s="90"/>
+      <c r="BA20" s="90"/>
+      <c r="BB20" s="90"/>
+      <c r="BC20" s="90"/>
+      <c r="BD20" s="90"/>
+      <c r="BE20" s="96"/>
     </row>
     <row r="21" spans="1:57" ht="15" customHeight="1">
-      <c r="A21" s="104"/>
-      <c r="B21" s="105"/>
-      <c r="C21" s="105"/>
-      <c r="D21" s="105"/>
-      <c r="E21" s="105"/>
-      <c r="F21" s="105"/>
-      <c r="G21" s="106"/>
+      <c r="A21" s="84"/>
+      <c r="B21" s="85"/>
+      <c r="C21" s="85"/>
+      <c r="D21" s="85"/>
+      <c r="E21" s="85"/>
+      <c r="F21" s="85"/>
+      <c r="G21" s="86"/>
       <c r="H21" s="87"/>
       <c r="I21" s="88"/>
       <c r="J21" s="88"/>
@@ -66239,57 +66239,57 @@
       <c r="M21" s="88"/>
       <c r="N21" s="89"/>
       <c r="O21" s="87"/>
-      <c r="P21" s="85"/>
-      <c r="Q21" s="85"/>
-      <c r="R21" s="85"/>
-      <c r="S21" s="85"/>
-      <c r="T21" s="85"/>
-      <c r="U21" s="85"/>
-      <c r="V21" s="85"/>
-      <c r="W21" s="85"/>
-      <c r="X21" s="85"/>
-      <c r="Y21" s="85"/>
-      <c r="Z21" s="85"/>
-      <c r="AA21" s="85"/>
-      <c r="AB21" s="85"/>
-      <c r="AC21" s="85"/>
-      <c r="AD21" s="85"/>
-      <c r="AE21" s="85"/>
-      <c r="AF21" s="85"/>
-      <c r="AG21" s="85"/>
-      <c r="AH21" s="85"/>
-      <c r="AI21" s="85"/>
-      <c r="AJ21" s="85"/>
-      <c r="AK21" s="85"/>
-      <c r="AL21" s="85"/>
-      <c r="AM21" s="85"/>
-      <c r="AN21" s="85"/>
-      <c r="AO21" s="85"/>
-      <c r="AP21" s="93"/>
-      <c r="AQ21" s="84"/>
-      <c r="AR21" s="85"/>
-      <c r="AS21" s="85"/>
-      <c r="AT21" s="85"/>
-      <c r="AU21" s="85"/>
-      <c r="AV21" s="85"/>
-      <c r="AW21" s="85"/>
-      <c r="AX21" s="85"/>
-      <c r="AY21" s="85"/>
-      <c r="AZ21" s="85"/>
-      <c r="BA21" s="85"/>
-      <c r="BB21" s="85"/>
-      <c r="BC21" s="85"/>
-      <c r="BD21" s="85"/>
-      <c r="BE21" s="86"/>
+      <c r="P21" s="90"/>
+      <c r="Q21" s="90"/>
+      <c r="R21" s="90"/>
+      <c r="S21" s="90"/>
+      <c r="T21" s="90"/>
+      <c r="U21" s="90"/>
+      <c r="V21" s="90"/>
+      <c r="W21" s="90"/>
+      <c r="X21" s="90"/>
+      <c r="Y21" s="90"/>
+      <c r="Z21" s="90"/>
+      <c r="AA21" s="90"/>
+      <c r="AB21" s="90"/>
+      <c r="AC21" s="90"/>
+      <c r="AD21" s="90"/>
+      <c r="AE21" s="90"/>
+      <c r="AF21" s="90"/>
+      <c r="AG21" s="90"/>
+      <c r="AH21" s="90"/>
+      <c r="AI21" s="90"/>
+      <c r="AJ21" s="90"/>
+      <c r="AK21" s="90"/>
+      <c r="AL21" s="90"/>
+      <c r="AM21" s="90"/>
+      <c r="AN21" s="90"/>
+      <c r="AO21" s="90"/>
+      <c r="AP21" s="91"/>
+      <c r="AQ21" s="95"/>
+      <c r="AR21" s="90"/>
+      <c r="AS21" s="90"/>
+      <c r="AT21" s="90"/>
+      <c r="AU21" s="90"/>
+      <c r="AV21" s="90"/>
+      <c r="AW21" s="90"/>
+      <c r="AX21" s="90"/>
+      <c r="AY21" s="90"/>
+      <c r="AZ21" s="90"/>
+      <c r="BA21" s="90"/>
+      <c r="BB21" s="90"/>
+      <c r="BC21" s="90"/>
+      <c r="BD21" s="90"/>
+      <c r="BE21" s="96"/>
     </row>
     <row r="22" spans="1:57" ht="15" customHeight="1">
-      <c r="A22" s="104"/>
-      <c r="B22" s="105"/>
-      <c r="C22" s="105"/>
-      <c r="D22" s="105"/>
-      <c r="E22" s="105"/>
-      <c r="F22" s="105"/>
-      <c r="G22" s="106"/>
+      <c r="A22" s="84"/>
+      <c r="B22" s="85"/>
+      <c r="C22" s="85"/>
+      <c r="D22" s="85"/>
+      <c r="E22" s="85"/>
+      <c r="F22" s="85"/>
+      <c r="G22" s="86"/>
       <c r="H22" s="87"/>
       <c r="I22" s="88"/>
       <c r="J22" s="88"/>
@@ -66298,57 +66298,57 @@
       <c r="M22" s="88"/>
       <c r="N22" s="89"/>
       <c r="O22" s="87"/>
-      <c r="P22" s="85"/>
-      <c r="Q22" s="85"/>
-      <c r="R22" s="85"/>
-      <c r="S22" s="85"/>
-      <c r="T22" s="85"/>
-      <c r="U22" s="85"/>
-      <c r="V22" s="85"/>
-      <c r="W22" s="85"/>
-      <c r="X22" s="85"/>
-      <c r="Y22" s="85"/>
-      <c r="Z22" s="85"/>
-      <c r="AA22" s="85"/>
-      <c r="AB22" s="85"/>
-      <c r="AC22" s="85"/>
-      <c r="AD22" s="85"/>
-      <c r="AE22" s="85"/>
-      <c r="AF22" s="85"/>
-      <c r="AG22" s="85"/>
-      <c r="AH22" s="85"/>
-      <c r="AI22" s="85"/>
-      <c r="AJ22" s="85"/>
-      <c r="AK22" s="85"/>
-      <c r="AL22" s="85"/>
-      <c r="AM22" s="85"/>
-      <c r="AN22" s="85"/>
-      <c r="AO22" s="85"/>
-      <c r="AP22" s="93"/>
-      <c r="AQ22" s="84"/>
-      <c r="AR22" s="85"/>
-      <c r="AS22" s="85"/>
-      <c r="AT22" s="85"/>
-      <c r="AU22" s="85"/>
-      <c r="AV22" s="85"/>
-      <c r="AW22" s="85"/>
-      <c r="AX22" s="85"/>
-      <c r="AY22" s="85"/>
-      <c r="AZ22" s="85"/>
-      <c r="BA22" s="85"/>
-      <c r="BB22" s="85"/>
-      <c r="BC22" s="85"/>
-      <c r="BD22" s="85"/>
-      <c r="BE22" s="86"/>
+      <c r="P22" s="90"/>
+      <c r="Q22" s="90"/>
+      <c r="R22" s="90"/>
+      <c r="S22" s="90"/>
+      <c r="T22" s="90"/>
+      <c r="U22" s="90"/>
+      <c r="V22" s="90"/>
+      <c r="W22" s="90"/>
+      <c r="X22" s="90"/>
+      <c r="Y22" s="90"/>
+      <c r="Z22" s="90"/>
+      <c r="AA22" s="90"/>
+      <c r="AB22" s="90"/>
+      <c r="AC22" s="90"/>
+      <c r="AD22" s="90"/>
+      <c r="AE22" s="90"/>
+      <c r="AF22" s="90"/>
+      <c r="AG22" s="90"/>
+      <c r="AH22" s="90"/>
+      <c r="AI22" s="90"/>
+      <c r="AJ22" s="90"/>
+      <c r="AK22" s="90"/>
+      <c r="AL22" s="90"/>
+      <c r="AM22" s="90"/>
+      <c r="AN22" s="90"/>
+      <c r="AO22" s="90"/>
+      <c r="AP22" s="91"/>
+      <c r="AQ22" s="95"/>
+      <c r="AR22" s="90"/>
+      <c r="AS22" s="90"/>
+      <c r="AT22" s="90"/>
+      <c r="AU22" s="90"/>
+      <c r="AV22" s="90"/>
+      <c r="AW22" s="90"/>
+      <c r="AX22" s="90"/>
+      <c r="AY22" s="90"/>
+      <c r="AZ22" s="90"/>
+      <c r="BA22" s="90"/>
+      <c r="BB22" s="90"/>
+      <c r="BC22" s="90"/>
+      <c r="BD22" s="90"/>
+      <c r="BE22" s="96"/>
     </row>
     <row r="23" spans="1:57" ht="15" customHeight="1">
-      <c r="A23" s="104"/>
-      <c r="B23" s="105"/>
-      <c r="C23" s="105"/>
-      <c r="D23" s="105"/>
-      <c r="E23" s="105"/>
-      <c r="F23" s="105"/>
-      <c r="G23" s="106"/>
+      <c r="A23" s="84"/>
+      <c r="B23" s="85"/>
+      <c r="C23" s="85"/>
+      <c r="D23" s="85"/>
+      <c r="E23" s="85"/>
+      <c r="F23" s="85"/>
+      <c r="G23" s="86"/>
       <c r="H23" s="87"/>
       <c r="I23" s="88"/>
       <c r="J23" s="88"/>
@@ -66357,57 +66357,57 @@
       <c r="M23" s="88"/>
       <c r="N23" s="89"/>
       <c r="O23" s="87"/>
-      <c r="P23" s="85"/>
-      <c r="Q23" s="85"/>
-      <c r="R23" s="85"/>
-      <c r="S23" s="85"/>
-      <c r="T23" s="85"/>
-      <c r="U23" s="85"/>
-      <c r="V23" s="85"/>
-      <c r="W23" s="85"/>
-      <c r="X23" s="85"/>
-      <c r="Y23" s="85"/>
-      <c r="Z23" s="85"/>
-      <c r="AA23" s="85"/>
-      <c r="AB23" s="85"/>
-      <c r="AC23" s="85"/>
-      <c r="AD23" s="85"/>
-      <c r="AE23" s="85"/>
-      <c r="AF23" s="85"/>
-      <c r="AG23" s="85"/>
-      <c r="AH23" s="85"/>
-      <c r="AI23" s="85"/>
-      <c r="AJ23" s="85"/>
-      <c r="AK23" s="85"/>
-      <c r="AL23" s="85"/>
-      <c r="AM23" s="85"/>
-      <c r="AN23" s="85"/>
-      <c r="AO23" s="85"/>
-      <c r="AP23" s="93"/>
-      <c r="AQ23" s="84"/>
-      <c r="AR23" s="85"/>
-      <c r="AS23" s="85"/>
-      <c r="AT23" s="85"/>
-      <c r="AU23" s="85"/>
-      <c r="AV23" s="85"/>
-      <c r="AW23" s="85"/>
-      <c r="AX23" s="85"/>
-      <c r="AY23" s="85"/>
-      <c r="AZ23" s="85"/>
-      <c r="BA23" s="85"/>
-      <c r="BB23" s="85"/>
-      <c r="BC23" s="85"/>
-      <c r="BD23" s="85"/>
-      <c r="BE23" s="86"/>
+      <c r="P23" s="90"/>
+      <c r="Q23" s="90"/>
+      <c r="R23" s="90"/>
+      <c r="S23" s="90"/>
+      <c r="T23" s="90"/>
+      <c r="U23" s="90"/>
+      <c r="V23" s="90"/>
+      <c r="W23" s="90"/>
+      <c r="X23" s="90"/>
+      <c r="Y23" s="90"/>
+      <c r="Z23" s="90"/>
+      <c r="AA23" s="90"/>
+      <c r="AB23" s="90"/>
+      <c r="AC23" s="90"/>
+      <c r="AD23" s="90"/>
+      <c r="AE23" s="90"/>
+      <c r="AF23" s="90"/>
+      <c r="AG23" s="90"/>
+      <c r="AH23" s="90"/>
+      <c r="AI23" s="90"/>
+      <c r="AJ23" s="90"/>
+      <c r="AK23" s="90"/>
+      <c r="AL23" s="90"/>
+      <c r="AM23" s="90"/>
+      <c r="AN23" s="90"/>
+      <c r="AO23" s="90"/>
+      <c r="AP23" s="91"/>
+      <c r="AQ23" s="95"/>
+      <c r="AR23" s="90"/>
+      <c r="AS23" s="90"/>
+      <c r="AT23" s="90"/>
+      <c r="AU23" s="90"/>
+      <c r="AV23" s="90"/>
+      <c r="AW23" s="90"/>
+      <c r="AX23" s="90"/>
+      <c r="AY23" s="90"/>
+      <c r="AZ23" s="90"/>
+      <c r="BA23" s="90"/>
+      <c r="BB23" s="90"/>
+      <c r="BC23" s="90"/>
+      <c r="BD23" s="90"/>
+      <c r="BE23" s="96"/>
     </row>
     <row r="24" spans="1:57" ht="15" customHeight="1">
-      <c r="A24" s="104"/>
-      <c r="B24" s="105"/>
-      <c r="C24" s="105"/>
-      <c r="D24" s="105"/>
-      <c r="E24" s="105"/>
-      <c r="F24" s="105"/>
-      <c r="G24" s="106"/>
+      <c r="A24" s="84"/>
+      <c r="B24" s="85"/>
+      <c r="C24" s="85"/>
+      <c r="D24" s="85"/>
+      <c r="E24" s="85"/>
+      <c r="F24" s="85"/>
+      <c r="G24" s="86"/>
       <c r="H24" s="87"/>
       <c r="I24" s="88"/>
       <c r="J24" s="88"/>
@@ -66416,57 +66416,57 @@
       <c r="M24" s="88"/>
       <c r="N24" s="89"/>
       <c r="O24" s="87"/>
-      <c r="P24" s="85"/>
-      <c r="Q24" s="85"/>
-      <c r="R24" s="85"/>
-      <c r="S24" s="85"/>
-      <c r="T24" s="85"/>
-      <c r="U24" s="85"/>
-      <c r="V24" s="85"/>
-      <c r="W24" s="85"/>
-      <c r="X24" s="85"/>
-      <c r="Y24" s="85"/>
-      <c r="Z24" s="85"/>
-      <c r="AA24" s="85"/>
-      <c r="AB24" s="85"/>
-      <c r="AC24" s="85"/>
-      <c r="AD24" s="85"/>
-      <c r="AE24" s="85"/>
-      <c r="AF24" s="85"/>
-      <c r="AG24" s="85"/>
-      <c r="AH24" s="85"/>
-      <c r="AI24" s="85"/>
-      <c r="AJ24" s="85"/>
-      <c r="AK24" s="85"/>
-      <c r="AL24" s="85"/>
-      <c r="AM24" s="85"/>
-      <c r="AN24" s="85"/>
-      <c r="AO24" s="85"/>
-      <c r="AP24" s="93"/>
-      <c r="AQ24" s="84"/>
-      <c r="AR24" s="85"/>
-      <c r="AS24" s="85"/>
-      <c r="AT24" s="85"/>
-      <c r="AU24" s="85"/>
-      <c r="AV24" s="85"/>
-      <c r="AW24" s="85"/>
-      <c r="AX24" s="85"/>
-      <c r="AY24" s="85"/>
-      <c r="AZ24" s="85"/>
-      <c r="BA24" s="85"/>
-      <c r="BB24" s="85"/>
-      <c r="BC24" s="85"/>
-      <c r="BD24" s="85"/>
-      <c r="BE24" s="86"/>
+      <c r="P24" s="90"/>
+      <c r="Q24" s="90"/>
+      <c r="R24" s="90"/>
+      <c r="S24" s="90"/>
+      <c r="T24" s="90"/>
+      <c r="U24" s="90"/>
+      <c r="V24" s="90"/>
+      <c r="W24" s="90"/>
+      <c r="X24" s="90"/>
+      <c r="Y24" s="90"/>
+      <c r="Z24" s="90"/>
+      <c r="AA24" s="90"/>
+      <c r="AB24" s="90"/>
+      <c r="AC24" s="90"/>
+      <c r="AD24" s="90"/>
+      <c r="AE24" s="90"/>
+      <c r="AF24" s="90"/>
+      <c r="AG24" s="90"/>
+      <c r="AH24" s="90"/>
+      <c r="AI24" s="90"/>
+      <c r="AJ24" s="90"/>
+      <c r="AK24" s="90"/>
+      <c r="AL24" s="90"/>
+      <c r="AM24" s="90"/>
+      <c r="AN24" s="90"/>
+      <c r="AO24" s="90"/>
+      <c r="AP24" s="91"/>
+      <c r="AQ24" s="95"/>
+      <c r="AR24" s="90"/>
+      <c r="AS24" s="90"/>
+      <c r="AT24" s="90"/>
+      <c r="AU24" s="90"/>
+      <c r="AV24" s="90"/>
+      <c r="AW24" s="90"/>
+      <c r="AX24" s="90"/>
+      <c r="AY24" s="90"/>
+      <c r="AZ24" s="90"/>
+      <c r="BA24" s="90"/>
+      <c r="BB24" s="90"/>
+      <c r="BC24" s="90"/>
+      <c r="BD24" s="90"/>
+      <c r="BE24" s="96"/>
     </row>
     <row r="25" spans="1:57" ht="15" customHeight="1">
-      <c r="A25" s="104"/>
-      <c r="B25" s="105"/>
-      <c r="C25" s="105"/>
-      <c r="D25" s="105"/>
-      <c r="E25" s="105"/>
-      <c r="F25" s="105"/>
-      <c r="G25" s="106"/>
+      <c r="A25" s="84"/>
+      <c r="B25" s="85"/>
+      <c r="C25" s="85"/>
+      <c r="D25" s="85"/>
+      <c r="E25" s="85"/>
+      <c r="F25" s="85"/>
+      <c r="G25" s="86"/>
       <c r="H25" s="87"/>
       <c r="I25" s="88"/>
       <c r="J25" s="88"/>
@@ -66475,57 +66475,57 @@
       <c r="M25" s="88"/>
       <c r="N25" s="89"/>
       <c r="O25" s="87"/>
-      <c r="P25" s="85"/>
-      <c r="Q25" s="85"/>
-      <c r="R25" s="85"/>
-      <c r="S25" s="85"/>
-      <c r="T25" s="85"/>
-      <c r="U25" s="85"/>
-      <c r="V25" s="85"/>
-      <c r="W25" s="85"/>
-      <c r="X25" s="85"/>
-      <c r="Y25" s="85"/>
-      <c r="Z25" s="85"/>
-      <c r="AA25" s="85"/>
-      <c r="AB25" s="85"/>
-      <c r="AC25" s="85"/>
-      <c r="AD25" s="85"/>
-      <c r="AE25" s="85"/>
-      <c r="AF25" s="85"/>
-      <c r="AG25" s="85"/>
-      <c r="AH25" s="85"/>
-      <c r="AI25" s="85"/>
-      <c r="AJ25" s="85"/>
-      <c r="AK25" s="85"/>
-      <c r="AL25" s="85"/>
-      <c r="AM25" s="85"/>
-      <c r="AN25" s="85"/>
-      <c r="AO25" s="85"/>
-      <c r="AP25" s="93"/>
-      <c r="AQ25" s="84"/>
-      <c r="AR25" s="85"/>
-      <c r="AS25" s="85"/>
-      <c r="AT25" s="85"/>
-      <c r="AU25" s="85"/>
-      <c r="AV25" s="85"/>
-      <c r="AW25" s="85"/>
-      <c r="AX25" s="85"/>
-      <c r="AY25" s="85"/>
-      <c r="AZ25" s="85"/>
-      <c r="BA25" s="85"/>
-      <c r="BB25" s="85"/>
-      <c r="BC25" s="85"/>
-      <c r="BD25" s="85"/>
-      <c r="BE25" s="86"/>
+      <c r="P25" s="90"/>
+      <c r="Q25" s="90"/>
+      <c r="R25" s="90"/>
+      <c r="S25" s="90"/>
+      <c r="T25" s="90"/>
+      <c r="U25" s="90"/>
+      <c r="V25" s="90"/>
+      <c r="W25" s="90"/>
+      <c r="X25" s="90"/>
+      <c r="Y25" s="90"/>
+      <c r="Z25" s="90"/>
+      <c r="AA25" s="90"/>
+      <c r="AB25" s="90"/>
+      <c r="AC25" s="90"/>
+      <c r="AD25" s="90"/>
+      <c r="AE25" s="90"/>
+      <c r="AF25" s="90"/>
+      <c r="AG25" s="90"/>
+      <c r="AH25" s="90"/>
+      <c r="AI25" s="90"/>
+      <c r="AJ25" s="90"/>
+      <c r="AK25" s="90"/>
+      <c r="AL25" s="90"/>
+      <c r="AM25" s="90"/>
+      <c r="AN25" s="90"/>
+      <c r="AO25" s="90"/>
+      <c r="AP25" s="91"/>
+      <c r="AQ25" s="95"/>
+      <c r="AR25" s="90"/>
+      <c r="AS25" s="90"/>
+      <c r="AT25" s="90"/>
+      <c r="AU25" s="90"/>
+      <c r="AV25" s="90"/>
+      <c r="AW25" s="90"/>
+      <c r="AX25" s="90"/>
+      <c r="AY25" s="90"/>
+      <c r="AZ25" s="90"/>
+      <c r="BA25" s="90"/>
+      <c r="BB25" s="90"/>
+      <c r="BC25" s="90"/>
+      <c r="BD25" s="90"/>
+      <c r="BE25" s="96"/>
     </row>
     <row r="26" spans="1:57" ht="15" customHeight="1">
-      <c r="A26" s="104"/>
-      <c r="B26" s="105"/>
-      <c r="C26" s="105"/>
-      <c r="D26" s="105"/>
-      <c r="E26" s="105"/>
-      <c r="F26" s="105"/>
-      <c r="G26" s="106"/>
+      <c r="A26" s="84"/>
+      <c r="B26" s="85"/>
+      <c r="C26" s="85"/>
+      <c r="D26" s="85"/>
+      <c r="E26" s="85"/>
+      <c r="F26" s="85"/>
+      <c r="G26" s="86"/>
       <c r="H26" s="87"/>
       <c r="I26" s="88"/>
       <c r="J26" s="88"/>
@@ -66534,57 +66534,57 @@
       <c r="M26" s="88"/>
       <c r="N26" s="89"/>
       <c r="O26" s="87"/>
-      <c r="P26" s="85"/>
-      <c r="Q26" s="85"/>
-      <c r="R26" s="85"/>
-      <c r="S26" s="85"/>
-      <c r="T26" s="85"/>
-      <c r="U26" s="85"/>
-      <c r="V26" s="85"/>
-      <c r="W26" s="85"/>
-      <c r="X26" s="85"/>
-      <c r="Y26" s="85"/>
-      <c r="Z26" s="85"/>
-      <c r="AA26" s="85"/>
-      <c r="AB26" s="85"/>
-      <c r="AC26" s="85"/>
-      <c r="AD26" s="85"/>
-      <c r="AE26" s="85"/>
-      <c r="AF26" s="85"/>
-      <c r="AG26" s="85"/>
-      <c r="AH26" s="85"/>
-      <c r="AI26" s="85"/>
-      <c r="AJ26" s="85"/>
-      <c r="AK26" s="85"/>
-      <c r="AL26" s="85"/>
-      <c r="AM26" s="85"/>
-      <c r="AN26" s="85"/>
-      <c r="AO26" s="85"/>
-      <c r="AP26" s="93"/>
-      <c r="AQ26" s="84"/>
-      <c r="AR26" s="85"/>
-      <c r="AS26" s="85"/>
-      <c r="AT26" s="85"/>
-      <c r="AU26" s="85"/>
-      <c r="AV26" s="85"/>
-      <c r="AW26" s="85"/>
-      <c r="AX26" s="85"/>
-      <c r="AY26" s="85"/>
-      <c r="AZ26" s="85"/>
-      <c r="BA26" s="85"/>
-      <c r="BB26" s="85"/>
-      <c r="BC26" s="85"/>
-      <c r="BD26" s="85"/>
-      <c r="BE26" s="86"/>
+      <c r="P26" s="90"/>
+      <c r="Q26" s="90"/>
+      <c r="R26" s="90"/>
+      <c r="S26" s="90"/>
+      <c r="T26" s="90"/>
+      <c r="U26" s="90"/>
+      <c r="V26" s="90"/>
+      <c r="W26" s="90"/>
+      <c r="X26" s="90"/>
+      <c r="Y26" s="90"/>
+      <c r="Z26" s="90"/>
+      <c r="AA26" s="90"/>
+      <c r="AB26" s="90"/>
+      <c r="AC26" s="90"/>
+      <c r="AD26" s="90"/>
+      <c r="AE26" s="90"/>
+      <c r="AF26" s="90"/>
+      <c r="AG26" s="90"/>
+      <c r="AH26" s="90"/>
+      <c r="AI26" s="90"/>
+      <c r="AJ26" s="90"/>
+      <c r="AK26" s="90"/>
+      <c r="AL26" s="90"/>
+      <c r="AM26" s="90"/>
+      <c r="AN26" s="90"/>
+      <c r="AO26" s="90"/>
+      <c r="AP26" s="91"/>
+      <c r="AQ26" s="95"/>
+      <c r="AR26" s="90"/>
+      <c r="AS26" s="90"/>
+      <c r="AT26" s="90"/>
+      <c r="AU26" s="90"/>
+      <c r="AV26" s="90"/>
+      <c r="AW26" s="90"/>
+      <c r="AX26" s="90"/>
+      <c r="AY26" s="90"/>
+      <c r="AZ26" s="90"/>
+      <c r="BA26" s="90"/>
+      <c r="BB26" s="90"/>
+      <c r="BC26" s="90"/>
+      <c r="BD26" s="90"/>
+      <c r="BE26" s="96"/>
     </row>
     <row r="27" spans="1:57" ht="15" customHeight="1">
-      <c r="A27" s="104"/>
-      <c r="B27" s="105"/>
-      <c r="C27" s="105"/>
-      <c r="D27" s="105"/>
-      <c r="E27" s="105"/>
-      <c r="F27" s="105"/>
-      <c r="G27" s="106"/>
+      <c r="A27" s="84"/>
+      <c r="B27" s="85"/>
+      <c r="C27" s="85"/>
+      <c r="D27" s="85"/>
+      <c r="E27" s="85"/>
+      <c r="F27" s="85"/>
+      <c r="G27" s="86"/>
       <c r="H27" s="87"/>
       <c r="I27" s="88"/>
       <c r="J27" s="88"/>
@@ -66593,57 +66593,57 @@
       <c r="M27" s="88"/>
       <c r="N27" s="89"/>
       <c r="O27" s="87"/>
-      <c r="P27" s="85"/>
-      <c r="Q27" s="85"/>
-      <c r="R27" s="85"/>
-      <c r="S27" s="85"/>
-      <c r="T27" s="85"/>
-      <c r="U27" s="85"/>
-      <c r="V27" s="85"/>
-      <c r="W27" s="85"/>
-      <c r="X27" s="85"/>
-      <c r="Y27" s="85"/>
-      <c r="Z27" s="85"/>
-      <c r="AA27" s="85"/>
-      <c r="AB27" s="85"/>
-      <c r="AC27" s="85"/>
-      <c r="AD27" s="85"/>
-      <c r="AE27" s="85"/>
-      <c r="AF27" s="85"/>
-      <c r="AG27" s="85"/>
-      <c r="AH27" s="85"/>
-      <c r="AI27" s="85"/>
-      <c r="AJ27" s="85"/>
-      <c r="AK27" s="85"/>
-      <c r="AL27" s="85"/>
-      <c r="AM27" s="85"/>
-      <c r="AN27" s="85"/>
-      <c r="AO27" s="85"/>
-      <c r="AP27" s="93"/>
-      <c r="AQ27" s="84"/>
-      <c r="AR27" s="85"/>
-      <c r="AS27" s="85"/>
-      <c r="AT27" s="85"/>
-      <c r="AU27" s="85"/>
-      <c r="AV27" s="85"/>
-      <c r="AW27" s="85"/>
-      <c r="AX27" s="85"/>
-      <c r="AY27" s="85"/>
-      <c r="AZ27" s="85"/>
-      <c r="BA27" s="85"/>
-      <c r="BB27" s="85"/>
-      <c r="BC27" s="85"/>
-      <c r="BD27" s="85"/>
-      <c r="BE27" s="86"/>
+      <c r="P27" s="90"/>
+      <c r="Q27" s="90"/>
+      <c r="R27" s="90"/>
+      <c r="S27" s="90"/>
+      <c r="T27" s="90"/>
+      <c r="U27" s="90"/>
+      <c r="V27" s="90"/>
+      <c r="W27" s="90"/>
+      <c r="X27" s="90"/>
+      <c r="Y27" s="90"/>
+      <c r="Z27" s="90"/>
+      <c r="AA27" s="90"/>
+      <c r="AB27" s="90"/>
+      <c r="AC27" s="90"/>
+      <c r="AD27" s="90"/>
+      <c r="AE27" s="90"/>
+      <c r="AF27" s="90"/>
+      <c r="AG27" s="90"/>
+      <c r="AH27" s="90"/>
+      <c r="AI27" s="90"/>
+      <c r="AJ27" s="90"/>
+      <c r="AK27" s="90"/>
+      <c r="AL27" s="90"/>
+      <c r="AM27" s="90"/>
+      <c r="AN27" s="90"/>
+      <c r="AO27" s="90"/>
+      <c r="AP27" s="91"/>
+      <c r="AQ27" s="95"/>
+      <c r="AR27" s="90"/>
+      <c r="AS27" s="90"/>
+      <c r="AT27" s="90"/>
+      <c r="AU27" s="90"/>
+      <c r="AV27" s="90"/>
+      <c r="AW27" s="90"/>
+      <c r="AX27" s="90"/>
+      <c r="AY27" s="90"/>
+      <c r="AZ27" s="90"/>
+      <c r="BA27" s="90"/>
+      <c r="BB27" s="90"/>
+      <c r="BC27" s="90"/>
+      <c r="BD27" s="90"/>
+      <c r="BE27" s="96"/>
     </row>
     <row r="28" spans="1:57" ht="15" customHeight="1">
-      <c r="A28" s="104"/>
-      <c r="B28" s="105"/>
-      <c r="C28" s="105"/>
-      <c r="D28" s="105"/>
-      <c r="E28" s="105"/>
-      <c r="F28" s="105"/>
-      <c r="G28" s="106"/>
+      <c r="A28" s="84"/>
+      <c r="B28" s="85"/>
+      <c r="C28" s="85"/>
+      <c r="D28" s="85"/>
+      <c r="E28" s="85"/>
+      <c r="F28" s="85"/>
+      <c r="G28" s="86"/>
       <c r="H28" s="87"/>
       <c r="I28" s="88"/>
       <c r="J28" s="88"/>
@@ -66652,57 +66652,57 @@
       <c r="M28" s="88"/>
       <c r="N28" s="89"/>
       <c r="O28" s="87"/>
-      <c r="P28" s="85"/>
-      <c r="Q28" s="85"/>
-      <c r="R28" s="85"/>
-      <c r="S28" s="85"/>
-      <c r="T28" s="85"/>
-      <c r="U28" s="85"/>
-      <c r="V28" s="85"/>
-      <c r="W28" s="85"/>
-      <c r="X28" s="85"/>
-      <c r="Y28" s="85"/>
-      <c r="Z28" s="85"/>
-      <c r="AA28" s="85"/>
-      <c r="AB28" s="85"/>
-      <c r="AC28" s="85"/>
-      <c r="AD28" s="85"/>
-      <c r="AE28" s="85"/>
-      <c r="AF28" s="85"/>
-      <c r="AG28" s="85"/>
-      <c r="AH28" s="85"/>
-      <c r="AI28" s="85"/>
-      <c r="AJ28" s="85"/>
-      <c r="AK28" s="85"/>
-      <c r="AL28" s="85"/>
-      <c r="AM28" s="85"/>
-      <c r="AN28" s="85"/>
-      <c r="AO28" s="85"/>
-      <c r="AP28" s="93"/>
-      <c r="AQ28" s="84"/>
-      <c r="AR28" s="85"/>
-      <c r="AS28" s="85"/>
-      <c r="AT28" s="85"/>
-      <c r="AU28" s="85"/>
-      <c r="AV28" s="85"/>
-      <c r="AW28" s="85"/>
-      <c r="AX28" s="85"/>
-      <c r="AY28" s="85"/>
-      <c r="AZ28" s="85"/>
-      <c r="BA28" s="85"/>
-      <c r="BB28" s="85"/>
-      <c r="BC28" s="85"/>
-      <c r="BD28" s="85"/>
-      <c r="BE28" s="86"/>
+      <c r="P28" s="90"/>
+      <c r="Q28" s="90"/>
+      <c r="R28" s="90"/>
+      <c r="S28" s="90"/>
+      <c r="T28" s="90"/>
+      <c r="U28" s="90"/>
+      <c r="V28" s="90"/>
+      <c r="W28" s="90"/>
+      <c r="X28" s="90"/>
+      <c r="Y28" s="90"/>
+      <c r="Z28" s="90"/>
+      <c r="AA28" s="90"/>
+      <c r="AB28" s="90"/>
+      <c r="AC28" s="90"/>
+      <c r="AD28" s="90"/>
+      <c r="AE28" s="90"/>
+      <c r="AF28" s="90"/>
+      <c r="AG28" s="90"/>
+      <c r="AH28" s="90"/>
+      <c r="AI28" s="90"/>
+      <c r="AJ28" s="90"/>
+      <c r="AK28" s="90"/>
+      <c r="AL28" s="90"/>
+      <c r="AM28" s="90"/>
+      <c r="AN28" s="90"/>
+      <c r="AO28" s="90"/>
+      <c r="AP28" s="91"/>
+      <c r="AQ28" s="95"/>
+      <c r="AR28" s="90"/>
+      <c r="AS28" s="90"/>
+      <c r="AT28" s="90"/>
+      <c r="AU28" s="90"/>
+      <c r="AV28" s="90"/>
+      <c r="AW28" s="90"/>
+      <c r="AX28" s="90"/>
+      <c r="AY28" s="90"/>
+      <c r="AZ28" s="90"/>
+      <c r="BA28" s="90"/>
+      <c r="BB28" s="90"/>
+      <c r="BC28" s="90"/>
+      <c r="BD28" s="90"/>
+      <c r="BE28" s="96"/>
     </row>
     <row r="29" spans="1:57" ht="15" customHeight="1">
-      <c r="A29" s="104"/>
-      <c r="B29" s="105"/>
-      <c r="C29" s="105"/>
-      <c r="D29" s="105"/>
-      <c r="E29" s="105"/>
-      <c r="F29" s="105"/>
-      <c r="G29" s="106"/>
+      <c r="A29" s="84"/>
+      <c r="B29" s="85"/>
+      <c r="C29" s="85"/>
+      <c r="D29" s="85"/>
+      <c r="E29" s="85"/>
+      <c r="F29" s="85"/>
+      <c r="G29" s="86"/>
       <c r="H29" s="87"/>
       <c r="I29" s="88"/>
       <c r="J29" s="88"/>
@@ -66711,57 +66711,57 @@
       <c r="M29" s="88"/>
       <c r="N29" s="89"/>
       <c r="O29" s="87"/>
-      <c r="P29" s="85"/>
-      <c r="Q29" s="85"/>
-      <c r="R29" s="85"/>
-      <c r="S29" s="85"/>
-      <c r="T29" s="85"/>
-      <c r="U29" s="85"/>
-      <c r="V29" s="85"/>
-      <c r="W29" s="85"/>
-      <c r="X29" s="85"/>
-      <c r="Y29" s="85"/>
-      <c r="Z29" s="85"/>
-      <c r="AA29" s="85"/>
-      <c r="AB29" s="85"/>
-      <c r="AC29" s="85"/>
-      <c r="AD29" s="85"/>
-      <c r="AE29" s="85"/>
-      <c r="AF29" s="85"/>
-      <c r="AG29" s="85"/>
-      <c r="AH29" s="85"/>
-      <c r="AI29" s="85"/>
-      <c r="AJ29" s="85"/>
-      <c r="AK29" s="85"/>
-      <c r="AL29" s="85"/>
-      <c r="AM29" s="85"/>
-      <c r="AN29" s="85"/>
-      <c r="AO29" s="85"/>
-      <c r="AP29" s="93"/>
-      <c r="AQ29" s="84"/>
-      <c r="AR29" s="85"/>
-      <c r="AS29" s="85"/>
-      <c r="AT29" s="85"/>
-      <c r="AU29" s="85"/>
-      <c r="AV29" s="85"/>
-      <c r="AW29" s="85"/>
-      <c r="AX29" s="85"/>
-      <c r="AY29" s="85"/>
-      <c r="AZ29" s="85"/>
-      <c r="BA29" s="85"/>
-      <c r="BB29" s="85"/>
-      <c r="BC29" s="85"/>
-      <c r="BD29" s="85"/>
-      <c r="BE29" s="86"/>
+      <c r="P29" s="90"/>
+      <c r="Q29" s="90"/>
+      <c r="R29" s="90"/>
+      <c r="S29" s="90"/>
+      <c r="T29" s="90"/>
+      <c r="U29" s="90"/>
+      <c r="V29" s="90"/>
+      <c r="W29" s="90"/>
+      <c r="X29" s="90"/>
+      <c r="Y29" s="90"/>
+      <c r="Z29" s="90"/>
+      <c r="AA29" s="90"/>
+      <c r="AB29" s="90"/>
+      <c r="AC29" s="90"/>
+      <c r="AD29" s="90"/>
+      <c r="AE29" s="90"/>
+      <c r="AF29" s="90"/>
+      <c r="AG29" s="90"/>
+      <c r="AH29" s="90"/>
+      <c r="AI29" s="90"/>
+      <c r="AJ29" s="90"/>
+      <c r="AK29" s="90"/>
+      <c r="AL29" s="90"/>
+      <c r="AM29" s="90"/>
+      <c r="AN29" s="90"/>
+      <c r="AO29" s="90"/>
+      <c r="AP29" s="91"/>
+      <c r="AQ29" s="95"/>
+      <c r="AR29" s="90"/>
+      <c r="AS29" s="90"/>
+      <c r="AT29" s="90"/>
+      <c r="AU29" s="90"/>
+      <c r="AV29" s="90"/>
+      <c r="AW29" s="90"/>
+      <c r="AX29" s="90"/>
+      <c r="AY29" s="90"/>
+      <c r="AZ29" s="90"/>
+      <c r="BA29" s="90"/>
+      <c r="BB29" s="90"/>
+      <c r="BC29" s="90"/>
+      <c r="BD29" s="90"/>
+      <c r="BE29" s="96"/>
     </row>
     <row r="30" spans="1:57" ht="15" customHeight="1">
-      <c r="A30" s="104"/>
-      <c r="B30" s="105"/>
-      <c r="C30" s="105"/>
-      <c r="D30" s="105"/>
-      <c r="E30" s="105"/>
-      <c r="F30" s="105"/>
-      <c r="G30" s="106"/>
+      <c r="A30" s="84"/>
+      <c r="B30" s="85"/>
+      <c r="C30" s="85"/>
+      <c r="D30" s="85"/>
+      <c r="E30" s="85"/>
+      <c r="F30" s="85"/>
+      <c r="G30" s="86"/>
       <c r="H30" s="87"/>
       <c r="I30" s="88"/>
       <c r="J30" s="88"/>
@@ -66770,57 +66770,57 @@
       <c r="M30" s="88"/>
       <c r="N30" s="89"/>
       <c r="O30" s="87"/>
-      <c r="P30" s="85"/>
-      <c r="Q30" s="85"/>
-      <c r="R30" s="85"/>
-      <c r="S30" s="85"/>
-      <c r="T30" s="85"/>
-      <c r="U30" s="85"/>
-      <c r="V30" s="85"/>
-      <c r="W30" s="85"/>
-      <c r="X30" s="85"/>
-      <c r="Y30" s="85"/>
-      <c r="Z30" s="85"/>
-      <c r="AA30" s="85"/>
-      <c r="AB30" s="85"/>
-      <c r="AC30" s="85"/>
-      <c r="AD30" s="85"/>
-      <c r="AE30" s="85"/>
-      <c r="AF30" s="85"/>
-      <c r="AG30" s="85"/>
-      <c r="AH30" s="85"/>
-      <c r="AI30" s="85"/>
-      <c r="AJ30" s="85"/>
-      <c r="AK30" s="85"/>
-      <c r="AL30" s="85"/>
-      <c r="AM30" s="85"/>
-      <c r="AN30" s="85"/>
-      <c r="AO30" s="85"/>
-      <c r="AP30" s="93"/>
-      <c r="AQ30" s="84"/>
-      <c r="AR30" s="85"/>
-      <c r="AS30" s="85"/>
-      <c r="AT30" s="85"/>
-      <c r="AU30" s="85"/>
-      <c r="AV30" s="85"/>
-      <c r="AW30" s="85"/>
-      <c r="AX30" s="85"/>
-      <c r="AY30" s="85"/>
-      <c r="AZ30" s="85"/>
-      <c r="BA30" s="85"/>
-      <c r="BB30" s="85"/>
-      <c r="BC30" s="85"/>
-      <c r="BD30" s="85"/>
-      <c r="BE30" s="86"/>
+      <c r="P30" s="90"/>
+      <c r="Q30" s="90"/>
+      <c r="R30" s="90"/>
+      <c r="S30" s="90"/>
+      <c r="T30" s="90"/>
+      <c r="U30" s="90"/>
+      <c r="V30" s="90"/>
+      <c r="W30" s="90"/>
+      <c r="X30" s="90"/>
+      <c r="Y30" s="90"/>
+      <c r="Z30" s="90"/>
+      <c r="AA30" s="90"/>
+      <c r="AB30" s="90"/>
+      <c r="AC30" s="90"/>
+      <c r="AD30" s="90"/>
+      <c r="AE30" s="90"/>
+      <c r="AF30" s="90"/>
+      <c r="AG30" s="90"/>
+      <c r="AH30" s="90"/>
+      <c r="AI30" s="90"/>
+      <c r="AJ30" s="90"/>
+      <c r="AK30" s="90"/>
+      <c r="AL30" s="90"/>
+      <c r="AM30" s="90"/>
+      <c r="AN30" s="90"/>
+      <c r="AO30" s="90"/>
+      <c r="AP30" s="91"/>
+      <c r="AQ30" s="95"/>
+      <c r="AR30" s="90"/>
+      <c r="AS30" s="90"/>
+      <c r="AT30" s="90"/>
+      <c r="AU30" s="90"/>
+      <c r="AV30" s="90"/>
+      <c r="AW30" s="90"/>
+      <c r="AX30" s="90"/>
+      <c r="AY30" s="90"/>
+      <c r="AZ30" s="90"/>
+      <c r="BA30" s="90"/>
+      <c r="BB30" s="90"/>
+      <c r="BC30" s="90"/>
+      <c r="BD30" s="90"/>
+      <c r="BE30" s="96"/>
     </row>
     <row r="31" spans="1:57" ht="15" customHeight="1">
-      <c r="A31" s="104"/>
-      <c r="B31" s="105"/>
-      <c r="C31" s="105"/>
-      <c r="D31" s="105"/>
-      <c r="E31" s="105"/>
-      <c r="F31" s="105"/>
-      <c r="G31" s="106"/>
+      <c r="A31" s="84"/>
+      <c r="B31" s="85"/>
+      <c r="C31" s="85"/>
+      <c r="D31" s="85"/>
+      <c r="E31" s="85"/>
+      <c r="F31" s="85"/>
+      <c r="G31" s="86"/>
       <c r="H31" s="87"/>
       <c r="I31" s="88"/>
       <c r="J31" s="88"/>
@@ -66829,57 +66829,57 @@
       <c r="M31" s="88"/>
       <c r="N31" s="89"/>
       <c r="O31" s="87"/>
-      <c r="P31" s="85"/>
-      <c r="Q31" s="85"/>
-      <c r="R31" s="85"/>
-      <c r="S31" s="85"/>
-      <c r="T31" s="85"/>
-      <c r="U31" s="85"/>
-      <c r="V31" s="85"/>
-      <c r="W31" s="85"/>
-      <c r="X31" s="85"/>
-      <c r="Y31" s="85"/>
-      <c r="Z31" s="85"/>
-      <c r="AA31" s="85"/>
-      <c r="AB31" s="85"/>
-      <c r="AC31" s="85"/>
-      <c r="AD31" s="85"/>
-      <c r="AE31" s="85"/>
-      <c r="AF31" s="85"/>
-      <c r="AG31" s="85"/>
-      <c r="AH31" s="85"/>
-      <c r="AI31" s="85"/>
-      <c r="AJ31" s="85"/>
-      <c r="AK31" s="85"/>
-      <c r="AL31" s="85"/>
-      <c r="AM31" s="85"/>
-      <c r="AN31" s="85"/>
-      <c r="AO31" s="85"/>
-      <c r="AP31" s="93"/>
-      <c r="AQ31" s="84"/>
-      <c r="AR31" s="85"/>
-      <c r="AS31" s="85"/>
-      <c r="AT31" s="85"/>
-      <c r="AU31" s="85"/>
-      <c r="AV31" s="85"/>
-      <c r="AW31" s="85"/>
-      <c r="AX31" s="85"/>
-      <c r="AY31" s="85"/>
-      <c r="AZ31" s="85"/>
-      <c r="BA31" s="85"/>
-      <c r="BB31" s="85"/>
-      <c r="BC31" s="85"/>
-      <c r="BD31" s="85"/>
-      <c r="BE31" s="86"/>
+      <c r="P31" s="90"/>
+      <c r="Q31" s="90"/>
+      <c r="R31" s="90"/>
+      <c r="S31" s="90"/>
+      <c r="T31" s="90"/>
+      <c r="U31" s="90"/>
+      <c r="V31" s="90"/>
+      <c r="W31" s="90"/>
+      <c r="X31" s="90"/>
+      <c r="Y31" s="90"/>
+      <c r="Z31" s="90"/>
+      <c r="AA31" s="90"/>
+      <c r="AB31" s="90"/>
+      <c r="AC31" s="90"/>
+      <c r="AD31" s="90"/>
+      <c r="AE31" s="90"/>
+      <c r="AF31" s="90"/>
+      <c r="AG31" s="90"/>
+      <c r="AH31" s="90"/>
+      <c r="AI31" s="90"/>
+      <c r="AJ31" s="90"/>
+      <c r="AK31" s="90"/>
+      <c r="AL31" s="90"/>
+      <c r="AM31" s="90"/>
+      <c r="AN31" s="90"/>
+      <c r="AO31" s="90"/>
+      <c r="AP31" s="91"/>
+      <c r="AQ31" s="95"/>
+      <c r="AR31" s="90"/>
+      <c r="AS31" s="90"/>
+      <c r="AT31" s="90"/>
+      <c r="AU31" s="90"/>
+      <c r="AV31" s="90"/>
+      <c r="AW31" s="90"/>
+      <c r="AX31" s="90"/>
+      <c r="AY31" s="90"/>
+      <c r="AZ31" s="90"/>
+      <c r="BA31" s="90"/>
+      <c r="BB31" s="90"/>
+      <c r="BC31" s="90"/>
+      <c r="BD31" s="90"/>
+      <c r="BE31" s="96"/>
     </row>
     <row r="32" spans="1:57" ht="15" customHeight="1">
-      <c r="A32" s="104"/>
-      <c r="B32" s="105"/>
-      <c r="C32" s="105"/>
-      <c r="D32" s="105"/>
-      <c r="E32" s="105"/>
-      <c r="F32" s="105"/>
-      <c r="G32" s="106"/>
+      <c r="A32" s="84"/>
+      <c r="B32" s="85"/>
+      <c r="C32" s="85"/>
+      <c r="D32" s="85"/>
+      <c r="E32" s="85"/>
+      <c r="F32" s="85"/>
+      <c r="G32" s="86"/>
       <c r="H32" s="87"/>
       <c r="I32" s="88"/>
       <c r="J32" s="88"/>
@@ -66888,57 +66888,57 @@
       <c r="M32" s="88"/>
       <c r="N32" s="89"/>
       <c r="O32" s="87"/>
-      <c r="P32" s="85"/>
-      <c r="Q32" s="85"/>
-      <c r="R32" s="85"/>
-      <c r="S32" s="85"/>
-      <c r="T32" s="85"/>
-      <c r="U32" s="85"/>
-      <c r="V32" s="85"/>
-      <c r="W32" s="85"/>
-      <c r="X32" s="85"/>
-      <c r="Y32" s="85"/>
-      <c r="Z32" s="85"/>
-      <c r="AA32" s="85"/>
-      <c r="AB32" s="85"/>
-      <c r="AC32" s="85"/>
-      <c r="AD32" s="85"/>
-      <c r="AE32" s="85"/>
-      <c r="AF32" s="85"/>
-      <c r="AG32" s="85"/>
-      <c r="AH32" s="85"/>
-      <c r="AI32" s="85"/>
-      <c r="AJ32" s="85"/>
-      <c r="AK32" s="85"/>
-      <c r="AL32" s="85"/>
-      <c r="AM32" s="85"/>
-      <c r="AN32" s="85"/>
-      <c r="AO32" s="85"/>
-      <c r="AP32" s="93"/>
-      <c r="AQ32" s="84"/>
-      <c r="AR32" s="85"/>
-      <c r="AS32" s="85"/>
-      <c r="AT32" s="85"/>
-      <c r="AU32" s="85"/>
-      <c r="AV32" s="85"/>
-      <c r="AW32" s="85"/>
-      <c r="AX32" s="85"/>
-      <c r="AY32" s="85"/>
-      <c r="AZ32" s="85"/>
-      <c r="BA32" s="85"/>
-      <c r="BB32" s="85"/>
-      <c r="BC32" s="85"/>
-      <c r="BD32" s="85"/>
-      <c r="BE32" s="86"/>
+      <c r="P32" s="90"/>
+      <c r="Q32" s="90"/>
+      <c r="R32" s="90"/>
+      <c r="S32" s="90"/>
+      <c r="T32" s="90"/>
+      <c r="U32" s="90"/>
+      <c r="V32" s="90"/>
+      <c r="W32" s="90"/>
+      <c r="X32" s="90"/>
+      <c r="Y32" s="90"/>
+      <c r="Z32" s="90"/>
+      <c r="AA32" s="90"/>
+      <c r="AB32" s="90"/>
+      <c r="AC32" s="90"/>
+      <c r="AD32" s="90"/>
+      <c r="AE32" s="90"/>
+      <c r="AF32" s="90"/>
+      <c r="AG32" s="90"/>
+      <c r="AH32" s="90"/>
+      <c r="AI32" s="90"/>
+      <c r="AJ32" s="90"/>
+      <c r="AK32" s="90"/>
+      <c r="AL32" s="90"/>
+      <c r="AM32" s="90"/>
+      <c r="AN32" s="90"/>
+      <c r="AO32" s="90"/>
+      <c r="AP32" s="91"/>
+      <c r="AQ32" s="95"/>
+      <c r="AR32" s="90"/>
+      <c r="AS32" s="90"/>
+      <c r="AT32" s="90"/>
+      <c r="AU32" s="90"/>
+      <c r="AV32" s="90"/>
+      <c r="AW32" s="90"/>
+      <c r="AX32" s="90"/>
+      <c r="AY32" s="90"/>
+      <c r="AZ32" s="90"/>
+      <c r="BA32" s="90"/>
+      <c r="BB32" s="90"/>
+      <c r="BC32" s="90"/>
+      <c r="BD32" s="90"/>
+      <c r="BE32" s="96"/>
     </row>
     <row r="33" spans="1:57" ht="15" customHeight="1">
-      <c r="A33" s="104"/>
-      <c r="B33" s="105"/>
-      <c r="C33" s="105"/>
-      <c r="D33" s="105"/>
-      <c r="E33" s="105"/>
-      <c r="F33" s="105"/>
-      <c r="G33" s="106"/>
+      <c r="A33" s="84"/>
+      <c r="B33" s="85"/>
+      <c r="C33" s="85"/>
+      <c r="D33" s="85"/>
+      <c r="E33" s="85"/>
+      <c r="F33" s="85"/>
+      <c r="G33" s="86"/>
       <c r="H33" s="87"/>
       <c r="I33" s="88"/>
       <c r="J33" s="88"/>
@@ -66947,57 +66947,57 @@
       <c r="M33" s="88"/>
       <c r="N33" s="89"/>
       <c r="O33" s="87"/>
-      <c r="P33" s="85"/>
-      <c r="Q33" s="85"/>
-      <c r="R33" s="85"/>
-      <c r="S33" s="85"/>
-      <c r="T33" s="85"/>
-      <c r="U33" s="85"/>
-      <c r="V33" s="85"/>
-      <c r="W33" s="85"/>
-      <c r="X33" s="85"/>
-      <c r="Y33" s="85"/>
-      <c r="Z33" s="85"/>
-      <c r="AA33" s="85"/>
-      <c r="AB33" s="85"/>
-      <c r="AC33" s="85"/>
-      <c r="AD33" s="85"/>
-      <c r="AE33" s="85"/>
-      <c r="AF33" s="85"/>
-      <c r="AG33" s="85"/>
-      <c r="AH33" s="85"/>
-      <c r="AI33" s="85"/>
-      <c r="AJ33" s="85"/>
-      <c r="AK33" s="85"/>
-      <c r="AL33" s="85"/>
-      <c r="AM33" s="85"/>
-      <c r="AN33" s="85"/>
-      <c r="AO33" s="85"/>
-      <c r="AP33" s="93"/>
-      <c r="AQ33" s="84"/>
-      <c r="AR33" s="85"/>
-      <c r="AS33" s="85"/>
-      <c r="AT33" s="85"/>
-      <c r="AU33" s="85"/>
-      <c r="AV33" s="85"/>
-      <c r="AW33" s="85"/>
-      <c r="AX33" s="85"/>
-      <c r="AY33" s="85"/>
-      <c r="AZ33" s="85"/>
-      <c r="BA33" s="85"/>
-      <c r="BB33" s="85"/>
-      <c r="BC33" s="85"/>
-      <c r="BD33" s="85"/>
-      <c r="BE33" s="86"/>
+      <c r="P33" s="90"/>
+      <c r="Q33" s="90"/>
+      <c r="R33" s="90"/>
+      <c r="S33" s="90"/>
+      <c r="T33" s="90"/>
+      <c r="U33" s="90"/>
+      <c r="V33" s="90"/>
+      <c r="W33" s="90"/>
+      <c r="X33" s="90"/>
+      <c r="Y33" s="90"/>
+      <c r="Z33" s="90"/>
+      <c r="AA33" s="90"/>
+      <c r="AB33" s="90"/>
+      <c r="AC33" s="90"/>
+      <c r="AD33" s="90"/>
+      <c r="AE33" s="90"/>
+      <c r="AF33" s="90"/>
+      <c r="AG33" s="90"/>
+      <c r="AH33" s="90"/>
+      <c r="AI33" s="90"/>
+      <c r="AJ33" s="90"/>
+      <c r="AK33" s="90"/>
+      <c r="AL33" s="90"/>
+      <c r="AM33" s="90"/>
+      <c r="AN33" s="90"/>
+      <c r="AO33" s="90"/>
+      <c r="AP33" s="91"/>
+      <c r="AQ33" s="95"/>
+      <c r="AR33" s="90"/>
+      <c r="AS33" s="90"/>
+      <c r="AT33" s="90"/>
+      <c r="AU33" s="90"/>
+      <c r="AV33" s="90"/>
+      <c r="AW33" s="90"/>
+      <c r="AX33" s="90"/>
+      <c r="AY33" s="90"/>
+      <c r="AZ33" s="90"/>
+      <c r="BA33" s="90"/>
+      <c r="BB33" s="90"/>
+      <c r="BC33" s="90"/>
+      <c r="BD33" s="90"/>
+      <c r="BE33" s="96"/>
     </row>
     <row r="34" spans="1:57" ht="15" customHeight="1">
-      <c r="A34" s="104"/>
-      <c r="B34" s="105"/>
-      <c r="C34" s="105"/>
-      <c r="D34" s="105"/>
-      <c r="E34" s="105"/>
-      <c r="F34" s="105"/>
-      <c r="G34" s="106"/>
+      <c r="A34" s="84"/>
+      <c r="B34" s="85"/>
+      <c r="C34" s="85"/>
+      <c r="D34" s="85"/>
+      <c r="E34" s="85"/>
+      <c r="F34" s="85"/>
+      <c r="G34" s="86"/>
       <c r="H34" s="87"/>
       <c r="I34" s="88"/>
       <c r="J34" s="88"/>
@@ -67006,110 +67006,219 @@
       <c r="M34" s="88"/>
       <c r="N34" s="89"/>
       <c r="O34" s="87"/>
-      <c r="P34" s="85"/>
-      <c r="Q34" s="85"/>
-      <c r="R34" s="85"/>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="85"/>
-      <c r="V34" s="85"/>
-      <c r="W34" s="85"/>
-      <c r="X34" s="85"/>
-      <c r="Y34" s="85"/>
-      <c r="Z34" s="85"/>
-      <c r="AA34" s="85"/>
-      <c r="AB34" s="85"/>
-      <c r="AC34" s="85"/>
-      <c r="AD34" s="85"/>
-      <c r="AE34" s="85"/>
-      <c r="AF34" s="85"/>
-      <c r="AG34" s="85"/>
-      <c r="AH34" s="85"/>
-      <c r="AI34" s="85"/>
-      <c r="AJ34" s="85"/>
-      <c r="AK34" s="85"/>
-      <c r="AL34" s="85"/>
-      <c r="AM34" s="85"/>
-      <c r="AN34" s="85"/>
-      <c r="AO34" s="85"/>
-      <c r="AP34" s="93"/>
-      <c r="AQ34" s="84"/>
-      <c r="AR34" s="85"/>
-      <c r="AS34" s="85"/>
-      <c r="AT34" s="85"/>
-      <c r="AU34" s="85"/>
-      <c r="AV34" s="85"/>
-      <c r="AW34" s="85"/>
-      <c r="AX34" s="85"/>
-      <c r="AY34" s="85"/>
-      <c r="AZ34" s="85"/>
-      <c r="BA34" s="85"/>
-      <c r="BB34" s="85"/>
-      <c r="BC34" s="85"/>
-      <c r="BD34" s="85"/>
-      <c r="BE34" s="86"/>
+      <c r="P34" s="90"/>
+      <c r="Q34" s="90"/>
+      <c r="R34" s="90"/>
+      <c r="S34" s="90"/>
+      <c r="T34" s="90"/>
+      <c r="U34" s="90"/>
+      <c r="V34" s="90"/>
+      <c r="W34" s="90"/>
+      <c r="X34" s="90"/>
+      <c r="Y34" s="90"/>
+      <c r="Z34" s="90"/>
+      <c r="AA34" s="90"/>
+      <c r="AB34" s="90"/>
+      <c r="AC34" s="90"/>
+      <c r="AD34" s="90"/>
+      <c r="AE34" s="90"/>
+      <c r="AF34" s="90"/>
+      <c r="AG34" s="90"/>
+      <c r="AH34" s="90"/>
+      <c r="AI34" s="90"/>
+      <c r="AJ34" s="90"/>
+      <c r="AK34" s="90"/>
+      <c r="AL34" s="90"/>
+      <c r="AM34" s="90"/>
+      <c r="AN34" s="90"/>
+      <c r="AO34" s="90"/>
+      <c r="AP34" s="91"/>
+      <c r="AQ34" s="95"/>
+      <c r="AR34" s="90"/>
+      <c r="AS34" s="90"/>
+      <c r="AT34" s="90"/>
+      <c r="AU34" s="90"/>
+      <c r="AV34" s="90"/>
+      <c r="AW34" s="90"/>
+      <c r="AX34" s="90"/>
+      <c r="AY34" s="90"/>
+      <c r="AZ34" s="90"/>
+      <c r="BA34" s="90"/>
+      <c r="BB34" s="90"/>
+      <c r="BC34" s="90"/>
+      <c r="BD34" s="90"/>
+      <c r="BE34" s="96"/>
     </row>
     <row r="35" spans="1:57" ht="15" customHeight="1" thickBot="1">
-      <c r="A35" s="125"/>
-      <c r="B35" s="126"/>
-      <c r="C35" s="126"/>
-      <c r="D35" s="126"/>
-      <c r="E35" s="126"/>
-      <c r="F35" s="126"/>
-      <c r="G35" s="127"/>
-      <c r="H35" s="131"/>
-      <c r="I35" s="132"/>
-      <c r="J35" s="132"/>
-      <c r="K35" s="132"/>
-      <c r="L35" s="132"/>
-      <c r="M35" s="132"/>
-      <c r="N35" s="133"/>
-      <c r="O35" s="131"/>
-      <c r="P35" s="129"/>
-      <c r="Q35" s="129"/>
-      <c r="R35" s="129"/>
-      <c r="S35" s="129"/>
-      <c r="T35" s="129"/>
-      <c r="U35" s="129"/>
-      <c r="V35" s="129"/>
-      <c r="W35" s="129"/>
-      <c r="X35" s="129"/>
-      <c r="Y35" s="129"/>
-      <c r="Z35" s="129"/>
-      <c r="AA35" s="129"/>
-      <c r="AB35" s="129"/>
-      <c r="AC35" s="129"/>
-      <c r="AD35" s="129"/>
-      <c r="AE35" s="129"/>
-      <c r="AF35" s="129"/>
-      <c r="AG35" s="129"/>
-      <c r="AH35" s="129"/>
-      <c r="AI35" s="129"/>
-      <c r="AJ35" s="129"/>
-      <c r="AK35" s="129"/>
-      <c r="AL35" s="129"/>
-      <c r="AM35" s="129"/>
-      <c r="AN35" s="129"/>
-      <c r="AO35" s="129"/>
-      <c r="AP35" s="134"/>
-      <c r="AQ35" s="128"/>
-      <c r="AR35" s="129"/>
-      <c r="AS35" s="129"/>
-      <c r="AT35" s="129"/>
-      <c r="AU35" s="129"/>
-      <c r="AV35" s="129"/>
-      <c r="AW35" s="129"/>
-      <c r="AX35" s="129"/>
-      <c r="AY35" s="129"/>
-      <c r="AZ35" s="129"/>
-      <c r="BA35" s="129"/>
-      <c r="BB35" s="129"/>
-      <c r="BC35" s="129"/>
-      <c r="BD35" s="129"/>
-      <c r="BE35" s="130"/>
+      <c r="A35" s="101"/>
+      <c r="B35" s="102"/>
+      <c r="C35" s="102"/>
+      <c r="D35" s="102"/>
+      <c r="E35" s="102"/>
+      <c r="F35" s="102"/>
+      <c r="G35" s="103"/>
+      <c r="H35" s="97"/>
+      <c r="I35" s="98"/>
+      <c r="J35" s="98"/>
+      <c r="K35" s="98"/>
+      <c r="L35" s="98"/>
+      <c r="M35" s="98"/>
+      <c r="N35" s="99"/>
+      <c r="O35" s="97"/>
+      <c r="P35" s="93"/>
+      <c r="Q35" s="93"/>
+      <c r="R35" s="93"/>
+      <c r="S35" s="93"/>
+      <c r="T35" s="93"/>
+      <c r="U35" s="93"/>
+      <c r="V35" s="93"/>
+      <c r="W35" s="93"/>
+      <c r="X35" s="93"/>
+      <c r="Y35" s="93"/>
+      <c r="Z35" s="93"/>
+      <c r="AA35" s="93"/>
+      <c r="AB35" s="93"/>
+      <c r="AC35" s="93"/>
+      <c r="AD35" s="93"/>
+      <c r="AE35" s="93"/>
+      <c r="AF35" s="93"/>
+      <c r="AG35" s="93"/>
+      <c r="AH35" s="93"/>
+      <c r="AI35" s="93"/>
+      <c r="AJ35" s="93"/>
+      <c r="AK35" s="93"/>
+      <c r="AL35" s="93"/>
+      <c r="AM35" s="93"/>
+      <c r="AN35" s="93"/>
+      <c r="AO35" s="93"/>
+      <c r="AP35" s="100"/>
+      <c r="AQ35" s="92"/>
+      <c r="AR35" s="93"/>
+      <c r="AS35" s="93"/>
+      <c r="AT35" s="93"/>
+      <c r="AU35" s="93"/>
+      <c r="AV35" s="93"/>
+      <c r="AW35" s="93"/>
+      <c r="AX35" s="93"/>
+      <c r="AY35" s="93"/>
+      <c r="AZ35" s="93"/>
+      <c r="BA35" s="93"/>
+      <c r="BB35" s="93"/>
+      <c r="BC35" s="93"/>
+      <c r="BD35" s="93"/>
+      <c r="BE35" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="133">
+    <mergeCell ref="AQ22:BE22"/>
+    <mergeCell ref="AQ29:BE29"/>
+    <mergeCell ref="H17:N17"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="H12:N12"/>
+    <mergeCell ref="O12:AP12"/>
+    <mergeCell ref="AQ12:BE12"/>
+    <mergeCell ref="H8:N8"/>
+    <mergeCell ref="AQ6:BE6"/>
+    <mergeCell ref="H5:N5"/>
+    <mergeCell ref="O8:AP8"/>
+    <mergeCell ref="AQ8:BE8"/>
+    <mergeCell ref="O5:AP5"/>
+    <mergeCell ref="AQ5:BE5"/>
+    <mergeCell ref="H6:N6"/>
+    <mergeCell ref="O6:AP6"/>
+    <mergeCell ref="H7:N7"/>
+    <mergeCell ref="O7:AP7"/>
+    <mergeCell ref="AQ7:BE7"/>
+    <mergeCell ref="AQ15:BE15"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="O16:AP16"/>
+    <mergeCell ref="O17:AP17"/>
+    <mergeCell ref="A1:BE1"/>
+    <mergeCell ref="H3:N3"/>
+    <mergeCell ref="O3:AP3"/>
+    <mergeCell ref="AQ3:BE3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="O15:AP15"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="H4:N4"/>
+    <mergeCell ref="O4:AP4"/>
+    <mergeCell ref="AQ4:BE4"/>
+    <mergeCell ref="H13:N13"/>
+    <mergeCell ref="O13:AP13"/>
+    <mergeCell ref="AQ13:BE13"/>
+    <mergeCell ref="H14:N14"/>
+    <mergeCell ref="O14:AP14"/>
+    <mergeCell ref="AQ14:BE14"/>
+    <mergeCell ref="AQ16:BE16"/>
+    <mergeCell ref="H15:N15"/>
+    <mergeCell ref="O18:AP18"/>
+    <mergeCell ref="H9:N9"/>
+    <mergeCell ref="O9:AP9"/>
+    <mergeCell ref="AQ9:BE9"/>
+    <mergeCell ref="H10:N10"/>
+    <mergeCell ref="O10:AP10"/>
+    <mergeCell ref="AQ10:BE10"/>
+    <mergeCell ref="H11:N11"/>
+    <mergeCell ref="O11:AP11"/>
+    <mergeCell ref="AQ11:BE11"/>
+    <mergeCell ref="H16:N16"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:AP20"/>
+    <mergeCell ref="AQ17:BE17"/>
+    <mergeCell ref="H26:N26"/>
+    <mergeCell ref="O26:AP26"/>
+    <mergeCell ref="AQ26:BE26"/>
+    <mergeCell ref="AQ19:BE19"/>
+    <mergeCell ref="H25:N25"/>
+    <mergeCell ref="H24:N24"/>
+    <mergeCell ref="O24:AP24"/>
+    <mergeCell ref="O25:AP25"/>
+    <mergeCell ref="AQ25:BE25"/>
+    <mergeCell ref="H22:N22"/>
+    <mergeCell ref="AQ24:BE24"/>
+    <mergeCell ref="H23:N23"/>
+    <mergeCell ref="O23:AP23"/>
+    <mergeCell ref="AQ23:BE23"/>
+    <mergeCell ref="AQ20:BE20"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:AP21"/>
+    <mergeCell ref="AQ18:BE18"/>
+    <mergeCell ref="AQ21:BE21"/>
+    <mergeCell ref="O22:AP22"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="H33:N33"/>
+    <mergeCell ref="H34:N34"/>
+    <mergeCell ref="O34:AP34"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="O33:AP33"/>
+    <mergeCell ref="O32:AP32"/>
+    <mergeCell ref="H31:N31"/>
+    <mergeCell ref="O31:AP31"/>
+    <mergeCell ref="H27:N27"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="H32:N32"/>
+    <mergeCell ref="H29:N29"/>
+    <mergeCell ref="O29:AP29"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A24:G24"/>
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="H19:N19"/>
     <mergeCell ref="O19:AP19"/>
@@ -67134,115 +67243,6 @@
     <mergeCell ref="A31:G31"/>
     <mergeCell ref="A25:G25"/>
     <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="H33:N33"/>
-    <mergeCell ref="H34:N34"/>
-    <mergeCell ref="O34:AP34"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="O33:AP33"/>
-    <mergeCell ref="O32:AP32"/>
-    <mergeCell ref="H31:N31"/>
-    <mergeCell ref="O31:AP31"/>
-    <mergeCell ref="H27:N27"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="H32:N32"/>
-    <mergeCell ref="H29:N29"/>
-    <mergeCell ref="O29:AP29"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:AP20"/>
-    <mergeCell ref="AQ17:BE17"/>
-    <mergeCell ref="H26:N26"/>
-    <mergeCell ref="O26:AP26"/>
-    <mergeCell ref="AQ26:BE26"/>
-    <mergeCell ref="AQ19:BE19"/>
-    <mergeCell ref="H25:N25"/>
-    <mergeCell ref="H24:N24"/>
-    <mergeCell ref="O24:AP24"/>
-    <mergeCell ref="O25:AP25"/>
-    <mergeCell ref="AQ25:BE25"/>
-    <mergeCell ref="H22:N22"/>
-    <mergeCell ref="AQ24:BE24"/>
-    <mergeCell ref="H23:N23"/>
-    <mergeCell ref="O23:AP23"/>
-    <mergeCell ref="AQ23:BE23"/>
-    <mergeCell ref="AQ20:BE20"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:AP21"/>
-    <mergeCell ref="AQ18:BE18"/>
-    <mergeCell ref="AQ21:BE21"/>
-    <mergeCell ref="O22:AP22"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="H4:N4"/>
-    <mergeCell ref="O4:AP4"/>
-    <mergeCell ref="AQ4:BE4"/>
-    <mergeCell ref="H13:N13"/>
-    <mergeCell ref="O13:AP13"/>
-    <mergeCell ref="AQ13:BE13"/>
-    <mergeCell ref="H14:N14"/>
-    <mergeCell ref="O14:AP14"/>
-    <mergeCell ref="AQ14:BE14"/>
-    <mergeCell ref="AQ16:BE16"/>
-    <mergeCell ref="H15:N15"/>
-    <mergeCell ref="O18:AP18"/>
-    <mergeCell ref="H9:N9"/>
-    <mergeCell ref="O9:AP9"/>
-    <mergeCell ref="AQ9:BE9"/>
-    <mergeCell ref="H10:N10"/>
-    <mergeCell ref="O10:AP10"/>
-    <mergeCell ref="AQ10:BE10"/>
-    <mergeCell ref="H11:N11"/>
-    <mergeCell ref="O11:AP11"/>
-    <mergeCell ref="AQ11:BE11"/>
-    <mergeCell ref="H16:N16"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="O15:AP15"/>
-    <mergeCell ref="A1:BE1"/>
-    <mergeCell ref="H3:N3"/>
-    <mergeCell ref="O3:AP3"/>
-    <mergeCell ref="AQ3:BE3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="AQ22:BE22"/>
-    <mergeCell ref="AQ29:BE29"/>
-    <mergeCell ref="H17:N17"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="H12:N12"/>
-    <mergeCell ref="O12:AP12"/>
-    <mergeCell ref="AQ12:BE12"/>
-    <mergeCell ref="H8:N8"/>
-    <mergeCell ref="AQ6:BE6"/>
-    <mergeCell ref="H5:N5"/>
-    <mergeCell ref="O8:AP8"/>
-    <mergeCell ref="AQ8:BE8"/>
-    <mergeCell ref="O5:AP5"/>
-    <mergeCell ref="AQ5:BE5"/>
-    <mergeCell ref="H6:N6"/>
-    <mergeCell ref="O6:AP6"/>
-    <mergeCell ref="H7:N7"/>
-    <mergeCell ref="O7:AP7"/>
-    <mergeCell ref="AQ7:BE7"/>
-    <mergeCell ref="AQ15:BE15"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="O16:AP16"/>
-    <mergeCell ref="O17:AP17"/>
   </mergeCells>
   <phoneticPr fontId="5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>

--- a/development/MS/spec/MSBB/Panel/MSBBP1210_SloReg.xlsx
+++ b/development/MS/spec/MSBB/Panel/MSBBP1210_SloReg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\mcframeDEV\development\MS\spec\MSBB\Panel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{339B0663-8F18-4D1C-8C87-B8C32FF1E74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4253BF70-5A2F-403E-8B18-8D007AE4B317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9193" uniqueCount="2382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9171" uniqueCount="2383">
   <si>
     <t>検索</t>
     <rPh sb="0" eb="2">
@@ -9970,15 +9970,9 @@
     <t>itm_nm;stk_mng_typ;asset_mng_typ_nm;asset_mng_typ;sundry_itm_flg;dscnt_itm_flg;unit_cd;unit_nm;dec_place;rnd_typ;ship_unit_nm;ship_unit_cd;ship_unit_dec_place;lot_mng_typ;lot_no_typ;sublot_mng_typ;sublot_no_typ;sno1_mng_typ;slo_sno1_flg;sno1_num_typ;sno2_mng_typ;slo_sno2_flg;sno2_num_typ;sno3_mng_typ;slo_sno3_flg;sno3_num_typ;sno4_mng_typ;slo_sno4_flg;sno4_num_typ;cntry_org_cd;cntry_org_nm;itm_bill_crryovr_times;slo_proc_flg;ver_flg;sls_upri_cng_flg;bp_itm_cd;bp_itm_nm;vmi_flg;iv_itm_nm;trd_cur_upri;wtax_rate;tax_cd;tax_nm;tax_rate;tax_typ;inc_tax_flg;ship_unit_conv_base_qty;ship_unit_conv_qty;ship_unit_qty;dscnt_rsn_cd;dscnt_rsn_nm;cost_upri;bill_crryovr_times;dest_cd1;dest_nm1;dest_cd2;dest_nm2;dest_cd3;dest_nm3;dlv_rqst_dt;dlv_rqst_hm;ship_rqst_dt;ship_rqst_hm;dlv_day_week_typ_nm;dlv_day_week_typ;via_dlv_typ_nm;via_dlv_typ;sls_cststk_flg;gd_nm;gd_cd;ship_schd_split_typ;alloc_scope_typ;alloc_typ;sls_upri_req_typ;def_ship_inst_typ;ship_inst_typ;ship_term_cd;ship_term_nm;slo_proc_typ;proc_typ;dlv_cd;dlv_nm;dlv_sundry_flg;pri_prnt_flg;dlv_lg_grp_cd;dlv_lg_grp_nm;dlv_cntry_cd;dlv_cntry_nm;dlv_zip_cd;dlv_addr1;dlv_addr2;dlv_addr3;dlv_addr4;dlv_tel;dlv_fax;dlv_cntct_dpt;dlv_cntct_psn;prnt_lcl_cd;tdlv_req_flg;tdlv_cd;tdlv_nm;tdlv_sundry_flg;tdlv_lg_grp_cd;tdlv_lg_grp_nm;tdlv_cntry_cd;tdlv_cntry_nm;tdlv_zip_cd;tdlv_addr1;tdlv_addr2;tdlv_addr3;tdlv_addr4;tdlv_tel;tdlv_fax;tdlv_cntct_dpt;tdlv_cntct_psn;list_pri;wl_sale_upri;upri_typ;upri_typ_nm;upri_rate;trd_cur_dscnt_amt;trd_cur_amt</t>
   </si>
   <si>
-    <t>trd_cur_amt</t>
-  </si>
-  <si>
     <t>金額</t>
   </si>
   <si>
-    <t>trd_cur_dscnt_amt</t>
-  </si>
-  <si>
     <t>値引額</t>
   </si>
   <si>
@@ -10076,6 +10070,18 @@
   </si>
   <si>
     <t>par_ship</t>
+  </si>
+  <si>
+    <t>trd_cur_upri_amt_p.trd_cur_upri#</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>trd_cur_upri_amt_p.trd_cur_amt#</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>trd_cur_upri_amt_p.trd_cur_dscnt_amt#</t>
+    <phoneticPr fontId="5"/>
   </si>
 </sst>
 </file>
@@ -11265,7 +11271,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -11500,14 +11506,14 @@
     <xf numFmtId="0" fontId="27" fillId="24" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -11518,79 +11524,7 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11599,29 +11533,8 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -11652,6 +11565,105 @@
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="26" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -13461,7 +13473,7 @@
       <c r="O16" s="25"/>
       <c r="P16" s="25"/>
       <c r="Q16" s="25" t="s">
-        <v>2355</v>
+        <v>2353</v>
       </c>
       <c r="R16" s="25"/>
       <c r="S16" s="25" t="s">
@@ -14298,7 +14310,7 @@
       <c r="B28" s="69"/>
       <c r="C28" s="69"/>
       <c r="D28" s="69" t="s">
-        <v>2352</v>
+        <v>2350</v>
       </c>
       <c r="E28" s="70" t="s">
         <v>1848</v>
@@ -14323,16 +14335,16 @@
       <c r="O28" s="69"/>
       <c r="P28" s="69"/>
       <c r="Q28" s="69" t="s">
-        <v>2356</v>
+        <v>2354</v>
       </c>
       <c r="R28" s="69"/>
       <c r="S28" s="69" t="s">
-        <v>2351</v>
+        <v>2349</v>
       </c>
       <c r="T28" s="69"/>
       <c r="U28" s="69"/>
       <c r="V28" s="69" t="s">
-        <v>2357</v>
+        <v>2355</v>
       </c>
       <c r="W28" s="69"/>
       <c r="X28" s="69"/>
@@ -16004,7 +16016,7 @@
         <v>130</v>
       </c>
       <c r="L46" s="63" t="s">
-        <v>2368</v>
+        <v>2366</v>
       </c>
       <c r="M46" s="63"/>
       <c r="N46" s="63"/>
@@ -16097,21 +16109,21 @@
       <c r="O47" s="25"/>
       <c r="P47" s="25"/>
       <c r="Q47" s="25" t="s">
-        <v>2378</v>
+        <v>2376</v>
       </c>
       <c r="R47" s="25"/>
       <c r="S47" s="25" t="s">
-        <v>2367</v>
+        <v>2365</v>
       </c>
       <c r="T47" s="25"/>
       <c r="U47" s="25" t="s">
-        <v>2371</v>
+        <v>2369</v>
       </c>
       <c r="V47" s="25" t="s">
-        <v>2376</v>
+        <v>2374</v>
       </c>
       <c r="W47" s="25" t="s">
-        <v>2377</v>
+        <v>2375</v>
       </c>
       <c r="X47" s="25"/>
       <c r="Z47" s="25"/>
@@ -17952,17 +17964,17 @@
       </c>
       <c r="R73" s="25"/>
       <c r="S73" s="25" t="s">
-        <v>2374</v>
+        <v>2372</v>
       </c>
       <c r="T73" s="25"/>
       <c r="U73" s="25" t="s">
-        <v>2375</v>
+        <v>2373</v>
       </c>
       <c r="V73" s="25" t="s">
-        <v>2373</v>
+        <v>2371</v>
       </c>
       <c r="W73" s="25" t="s">
-        <v>2372</v>
+        <v>2370</v>
       </c>
       <c r="X73" s="25"/>
       <c r="Z73" s="25"/>
@@ -19320,18 +19332,18 @@
       <c r="O93" s="65"/>
       <c r="P93" s="65"/>
       <c r="Q93" s="61" t="s">
-        <v>2365</v>
+        <v>2363</v>
       </c>
       <c r="R93" s="61"/>
       <c r="S93" s="61" t="s">
-        <v>2370</v>
+        <v>2368</v>
       </c>
       <c r="T93" s="61"/>
       <c r="U93" s="61" t="s">
-        <v>2369</v>
+        <v>2367</v>
       </c>
       <c r="V93" s="65" t="s">
-        <v>2357</v>
+        <v>2355</v>
       </c>
       <c r="W93" s="65"/>
       <c r="X93" s="65"/>
@@ -20286,7 +20298,7 @@
       <c r="B104" s="25"/>
       <c r="C104" s="25"/>
       <c r="D104" s="25" t="s">
-        <v>2353</v>
+        <v>2351</v>
       </c>
       <c r="E104" s="37" t="s">
         <v>1898</v>
@@ -20295,7 +20307,7 @@
         <v>179</v>
       </c>
       <c r="G104" s="25" t="s">
-        <v>2354</v>
+        <v>2352</v>
       </c>
       <c r="H104" s="25"/>
       <c r="I104" s="25" t="s">
@@ -31065,7 +31077,7 @@
       </c>
       <c r="J224" s="25"/>
       <c r="K224" s="25" t="s">
-        <v>2358</v>
+        <v>2356</v>
       </c>
       <c r="L224" s="25"/>
       <c r="M224" s="25"/>
@@ -32468,7 +32480,7 @@
       </c>
       <c r="R241" s="25"/>
       <c r="S241" s="25" t="s">
-        <v>2360</v>
+        <v>2358</v>
       </c>
       <c r="T241" s="25"/>
       <c r="U241" s="25" t="s">
@@ -32551,7 +32563,7 @@
       </c>
       <c r="J242" s="61"/>
       <c r="K242" s="61" t="s">
-        <v>2358</v>
+        <v>2356</v>
       </c>
       <c r="L242" s="61"/>
       <c r="M242" s="61"/>
@@ -32559,7 +32571,7 @@
       <c r="O242" s="61"/>
       <c r="P242" s="61"/>
       <c r="Q242" s="61" t="s">
-        <v>2363</v>
+        <v>2361</v>
       </c>
       <c r="R242" s="61"/>
       <c r="S242" s="61" t="s">
@@ -32567,7 +32579,7 @@
       </c>
       <c r="T242" s="61"/>
       <c r="U242" s="61" t="s">
-        <v>2364</v>
+        <v>2362</v>
       </c>
       <c r="V242" s="61"/>
       <c r="W242" s="61"/>
@@ -32692,7 +32704,7 @@
       <c r="B244" s="61"/>
       <c r="C244" s="61"/>
       <c r="D244" s="61" t="s">
-        <v>2361</v>
+        <v>2359</v>
       </c>
       <c r="E244" s="62" t="s">
         <v>2240</v>
@@ -32709,7 +32721,7 @@
       </c>
       <c r="J244" s="61"/>
       <c r="K244" s="61" t="s">
-        <v>2358</v>
+        <v>2356</v>
       </c>
       <c r="L244" s="61"/>
       <c r="M244" s="61"/>
@@ -32717,7 +32729,7 @@
       <c r="O244" s="61"/>
       <c r="P244" s="61"/>
       <c r="Q244" s="61" t="s">
-        <v>2359</v>
+        <v>2357</v>
       </c>
       <c r="R244" s="61"/>
       <c r="S244" s="61" t="s">
@@ -32725,7 +32737,7 @@
       </c>
       <c r="T244" s="61"/>
       <c r="U244" s="61" t="s">
-        <v>2362</v>
+        <v>2360</v>
       </c>
       <c r="V244" s="61"/>
       <c r="W244" s="61"/>
@@ -39458,1554 +39470,1510 @@
       <c r="AX325" s="25"/>
       <c r="AZ325" s="26"/>
     </row>
-    <row r="326" spans="1:52" s="66" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A326" s="63">
-        <v>70</v>
-      </c>
-      <c r="B326" s="65"/>
-      <c r="C326" s="65"/>
-      <c r="D326" s="65" t="s">
-        <v>1705</v>
-      </c>
-      <c r="E326" s="64"/>
-      <c r="F326" s="65"/>
-      <c r="G326" s="65" t="s">
-        <v>2350</v>
-      </c>
-      <c r="H326" s="65"/>
-      <c r="I326" s="65" t="s">
-        <v>2317</v>
-      </c>
-      <c r="J326" s="65"/>
-      <c r="K326" s="65" t="s">
-        <v>2236</v>
-      </c>
-      <c r="L326" s="65"/>
-      <c r="M326" s="65"/>
-      <c r="N326" s="65"/>
-      <c r="O326" s="65"/>
-      <c r="P326" s="65"/>
-      <c r="Q326" s="65"/>
-      <c r="R326" s="65"/>
-      <c r="S326" s="65"/>
-      <c r="T326" s="65"/>
-      <c r="U326" s="65"/>
-      <c r="V326" s="65"/>
-      <c r="W326" s="65"/>
-      <c r="X326" s="65"/>
-      <c r="Z326" s="65"/>
-      <c r="AA326" s="65"/>
-      <c r="AB326" s="65"/>
-      <c r="AC326" s="65"/>
-      <c r="AD326" s="65"/>
-      <c r="AE326" s="65"/>
-      <c r="AF326" s="65"/>
-      <c r="AG326" s="65"/>
-      <c r="AH326" s="65"/>
-      <c r="AI326" s="65"/>
-      <c r="AJ326" s="65"/>
-      <c r="AK326" s="65"/>
-      <c r="AM326" s="65"/>
-      <c r="AN326" s="65" t="s">
+    <row r="326" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A326" s="50">
+        <v>70</v>
+      </c>
+      <c r="B326" s="50"/>
+      <c r="C326" s="50"/>
+      <c r="D326" s="50" t="s">
+        <v>809</v>
+      </c>
+      <c r="E326" s="50"/>
+      <c r="F326" s="50"/>
+      <c r="G326" s="50"/>
+      <c r="H326" s="50"/>
+      <c r="I326" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="J326" s="50"/>
+      <c r="K326" s="50" t="s">
+        <v>248</v>
+      </c>
+      <c r="L326" s="50" t="s">
+        <v>1149</v>
+      </c>
+      <c r="M326" s="50"/>
+      <c r="N326" s="50"/>
+      <c r="O326" s="50"/>
+      <c r="P326" s="50"/>
+      <c r="Q326" s="50"/>
+      <c r="R326" s="50"/>
+      <c r="S326" s="50"/>
+      <c r="T326" s="50"/>
+      <c r="U326" s="50"/>
+      <c r="V326" s="50"/>
+      <c r="W326" s="50"/>
+      <c r="X326" s="50"/>
+      <c r="Y326" s="50"/>
+      <c r="Z326" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA326" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB326" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC326" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD326" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE326" s="50"/>
+      <c r="AF326" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG326" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="AH326" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="AI326" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ326" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK326" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL326" s="50"/>
+      <c r="AM326" s="50"/>
+      <c r="AN326" s="50"/>
+      <c r="AO326" s="50"/>
+      <c r="AP326" s="50"/>
+      <c r="AQ326" s="50"/>
+      <c r="AR326" s="50"/>
+      <c r="AS326" s="50"/>
+      <c r="AT326" s="50"/>
+      <c r="AU326" s="50"/>
+      <c r="AV326" s="50"/>
+      <c r="AW326" s="50"/>
+      <c r="AX326" s="50"/>
+      <c r="AY326" s="50"/>
+      <c r="AZ326" s="50"/>
+    </row>
+    <row r="327" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A327" s="135">
+        <v>70</v>
+      </c>
+      <c r="B327" s="33"/>
+      <c r="C327" s="33"/>
+      <c r="D327" s="33" t="s">
+        <v>946</v>
+      </c>
+      <c r="E327" s="54"/>
+      <c r="F327" s="33"/>
+      <c r="G327" s="33"/>
+      <c r="H327" s="33"/>
+      <c r="I327" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="J327" s="33"/>
+      <c r="K327" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="L327" s="33"/>
+      <c r="M327" s="33"/>
+      <c r="N327" s="33"/>
+      <c r="O327" s="33"/>
+      <c r="P327" s="33"/>
+      <c r="Q327" s="33"/>
+      <c r="R327" s="33"/>
+      <c r="S327" s="33"/>
+      <c r="T327" s="33"/>
+      <c r="U327" s="33"/>
+      <c r="V327" s="33"/>
+      <c r="W327" s="33"/>
+      <c r="X327" s="33"/>
+      <c r="Z327" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA327" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB327" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC327" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD327" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE327" s="33"/>
+      <c r="AF327" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG327" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH327" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI327" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ327" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK327" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM327" s="33"/>
+      <c r="AN327" s="33" t="s">
+        <v>679</v>
+      </c>
+      <c r="AO327" s="33"/>
+      <c r="AP327" s="33" t="s">
+        <v>679</v>
+      </c>
+      <c r="AQ327" s="33" t="s">
+        <v>679</v>
+      </c>
+      <c r="AR327" s="33"/>
+      <c r="AS327" s="33" t="s">
+        <v>679</v>
+      </c>
+      <c r="AT327" s="33"/>
+      <c r="AU327" s="33"/>
+      <c r="AV327" s="33"/>
+      <c r="AW327" s="33"/>
+      <c r="AX327" s="33"/>
+      <c r="AZ327" s="35"/>
+    </row>
+    <row r="328" spans="1:52" s="66" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A328" s="136">
+        <v>70</v>
+      </c>
+      <c r="B328" s="61"/>
+      <c r="C328" s="61"/>
+      <c r="D328" s="61" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E328" s="62"/>
+      <c r="F328" s="61"/>
+      <c r="G328" s="61" t="s">
+        <v>2348</v>
+      </c>
+      <c r="H328" s="61"/>
+      <c r="I328" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="J328" s="61"/>
+      <c r="K328" s="61" t="s">
+        <v>24</v>
+      </c>
+      <c r="L328" s="61"/>
+      <c r="M328" s="61"/>
+      <c r="N328" s="61"/>
+      <c r="O328" s="61"/>
+      <c r="P328" s="61"/>
+      <c r="Q328" s="61"/>
+      <c r="R328" s="61"/>
+      <c r="S328" s="61"/>
+      <c r="T328" s="61"/>
+      <c r="U328" s="61"/>
+      <c r="V328" s="61"/>
+      <c r="W328" s="61"/>
+      <c r="X328" s="61"/>
+      <c r="Z328" s="61"/>
+      <c r="AA328" s="61"/>
+      <c r="AB328" s="61"/>
+      <c r="AC328" s="61"/>
+      <c r="AD328" s="61"/>
+      <c r="AE328" s="61"/>
+      <c r="AF328" s="61"/>
+      <c r="AG328" s="61"/>
+      <c r="AH328" s="61"/>
+      <c r="AI328" s="61"/>
+      <c r="AJ328" s="61"/>
+      <c r="AK328" s="61"/>
+      <c r="AM328" s="61"/>
+      <c r="AN328" s="61" t="s">
         <v>965</v>
       </c>
-      <c r="AO326" s="65"/>
-      <c r="AP326" s="65" t="s">
+      <c r="AO328" s="61"/>
+      <c r="AP328" s="61" t="s">
         <v>965</v>
       </c>
-      <c r="AQ326" s="65" t="s">
+      <c r="AQ328" s="61" t="s">
         <v>965</v>
       </c>
-      <c r="AR326" s="65"/>
-      <c r="AS326" s="65" t="s">
+      <c r="AR328" s="61"/>
+      <c r="AS328" s="61" t="s">
         <v>965</v>
       </c>
-      <c r="AT326" s="65"/>
-      <c r="AU326" s="65"/>
-      <c r="AV326" s="65"/>
-      <c r="AW326" s="65"/>
-      <c r="AX326" s="65"/>
-      <c r="AZ326" s="68"/>
-    </row>
-    <row r="327" spans="1:52" s="66" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A327" s="63">
-        <v>70</v>
-      </c>
-      <c r="B327" s="65"/>
-      <c r="C327" s="65"/>
-      <c r="D327" s="65" t="s">
+      <c r="AT328" s="61"/>
+      <c r="AU328" s="61"/>
+      <c r="AV328" s="61"/>
+      <c r="AW328" s="61"/>
+      <c r="AX328" s="61"/>
+      <c r="AZ328" s="67"/>
+    </row>
+    <row r="329" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A329" s="135">
+        <v>70</v>
+      </c>
+      <c r="B329" s="33"/>
+      <c r="C329" s="33"/>
+      <c r="D329" s="33" t="s">
+        <v>966</v>
+      </c>
+      <c r="E329" s="54"/>
+      <c r="F329" s="33"/>
+      <c r="G329" s="33"/>
+      <c r="H329" s="33"/>
+      <c r="I329" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="J329" s="33"/>
+      <c r="K329" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="L329" s="33"/>
+      <c r="M329" s="33"/>
+      <c r="N329" s="33"/>
+      <c r="O329" s="33"/>
+      <c r="P329" s="33"/>
+      <c r="Q329" s="33"/>
+      <c r="R329" s="33"/>
+      <c r="S329" s="33"/>
+      <c r="T329" s="33"/>
+      <c r="U329" s="33"/>
+      <c r="V329" s="33"/>
+      <c r="W329" s="33"/>
+      <c r="X329" s="33"/>
+      <c r="Z329" s="33"/>
+      <c r="AA329" s="33"/>
+      <c r="AB329" s="33"/>
+      <c r="AC329" s="33"/>
+      <c r="AD329" s="33"/>
+      <c r="AE329" s="33"/>
+      <c r="AF329" s="33"/>
+      <c r="AG329" s="33"/>
+      <c r="AH329" s="33"/>
+      <c r="AI329" s="33"/>
+      <c r="AJ329" s="33"/>
+      <c r="AK329" s="33"/>
+      <c r="AM329" s="33"/>
+      <c r="AN329" s="33" t="s">
+        <v>854</v>
+      </c>
+      <c r="AO329" s="33"/>
+      <c r="AP329" s="33" t="s">
+        <v>854</v>
+      </c>
+      <c r="AQ329" s="33" t="s">
+        <v>854</v>
+      </c>
+      <c r="AR329" s="33"/>
+      <c r="AS329" s="33" t="s">
+        <v>854</v>
+      </c>
+      <c r="AT329" s="33"/>
+      <c r="AU329" s="33"/>
+      <c r="AV329" s="33"/>
+      <c r="AW329" s="33"/>
+      <c r="AX329" s="33"/>
+      <c r="AZ329" s="35"/>
+    </row>
+    <row r="330" spans="1:52" s="66" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A330" s="136">
+        <v>70</v>
+      </c>
+      <c r="B330" s="61"/>
+      <c r="C330" s="61"/>
+      <c r="D330" s="61" t="s">
+        <v>2381</v>
+      </c>
+      <c r="E330" s="62"/>
+      <c r="F330" s="61"/>
+      <c r="G330" s="61" t="s">
         <v>2346</v>
       </c>
-      <c r="E327" s="64"/>
-      <c r="F327" s="65"/>
-      <c r="G327" s="65" t="s">
+      <c r="H330" s="61"/>
+      <c r="I330" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="J330" s="61"/>
+      <c r="K330" s="61" t="s">
+        <v>24</v>
+      </c>
+      <c r="L330" s="61"/>
+      <c r="M330" s="61"/>
+      <c r="N330" s="61"/>
+      <c r="O330" s="61"/>
+      <c r="P330" s="61"/>
+      <c r="Q330" s="61"/>
+      <c r="R330" s="61"/>
+      <c r="S330" s="61"/>
+      <c r="T330" s="61"/>
+      <c r="U330" s="61"/>
+      <c r="V330" s="61"/>
+      <c r="W330" s="61"/>
+      <c r="X330" s="61"/>
+      <c r="Z330" s="61"/>
+      <c r="AA330" s="61"/>
+      <c r="AB330" s="61"/>
+      <c r="AC330" s="61"/>
+      <c r="AD330" s="61"/>
+      <c r="AE330" s="61"/>
+      <c r="AF330" s="61"/>
+      <c r="AG330" s="61"/>
+      <c r="AH330" s="61"/>
+      <c r="AI330" s="61"/>
+      <c r="AJ330" s="61"/>
+      <c r="AK330" s="61"/>
+      <c r="AM330" s="61"/>
+      <c r="AN330" s="61" t="s">
+        <v>883</v>
+      </c>
+      <c r="AO330" s="61"/>
+      <c r="AP330" s="61" t="s">
+        <v>883</v>
+      </c>
+      <c r="AQ330" s="61"/>
+      <c r="AR330" s="61"/>
+      <c r="AS330" s="61"/>
+      <c r="AT330" s="61"/>
+      <c r="AU330" s="61"/>
+      <c r="AV330" s="61"/>
+      <c r="AW330" s="61"/>
+      <c r="AX330" s="61"/>
+      <c r="AZ330" s="67"/>
+    </row>
+    <row r="331" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A331" s="135">
+        <v>70</v>
+      </c>
+      <c r="B331" s="33"/>
+      <c r="C331" s="33"/>
+      <c r="D331" s="33" t="s">
+        <v>967</v>
+      </c>
+      <c r="E331" s="54"/>
+      <c r="F331" s="33"/>
+      <c r="G331" s="33"/>
+      <c r="H331" s="33"/>
+      <c r="I331" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="J331" s="33"/>
+      <c r="K331" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="L331" s="33"/>
+      <c r="M331" s="33"/>
+      <c r="N331" s="33"/>
+      <c r="O331" s="33"/>
+      <c r="P331" s="33"/>
+      <c r="Q331" s="33"/>
+      <c r="R331" s="33"/>
+      <c r="S331" s="33"/>
+      <c r="T331" s="33"/>
+      <c r="U331" s="33"/>
+      <c r="V331" s="33"/>
+      <c r="W331" s="33"/>
+      <c r="X331" s="33"/>
+      <c r="Z331" s="33"/>
+      <c r="AA331" s="33"/>
+      <c r="AB331" s="33"/>
+      <c r="AC331" s="33"/>
+      <c r="AD331" s="33"/>
+      <c r="AE331" s="33"/>
+      <c r="AF331" s="33"/>
+      <c r="AG331" s="33"/>
+      <c r="AH331" s="33"/>
+      <c r="AI331" s="33"/>
+      <c r="AJ331" s="33"/>
+      <c r="AK331" s="33"/>
+      <c r="AM331" s="33"/>
+      <c r="AN331" s="33" t="s">
+        <v>968</v>
+      </c>
+      <c r="AO331" s="33"/>
+      <c r="AP331" s="33" t="s">
+        <v>968</v>
+      </c>
+      <c r="AQ331" s="33"/>
+      <c r="AR331" s="33"/>
+      <c r="AS331" s="33"/>
+      <c r="AT331" s="33"/>
+      <c r="AU331" s="33"/>
+      <c r="AV331" s="33"/>
+      <c r="AW331" s="33"/>
+      <c r="AX331" s="33"/>
+      <c r="AZ331" s="35"/>
+    </row>
+    <row r="332" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A332" s="135">
+        <v>70</v>
+      </c>
+      <c r="B332" s="33"/>
+      <c r="C332" s="33"/>
+      <c r="D332" s="33" t="s">
+        <v>969</v>
+      </c>
+      <c r="E332" s="54"/>
+      <c r="F332" s="33"/>
+      <c r="G332" s="33"/>
+      <c r="H332" s="33"/>
+      <c r="I332" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="J332" s="33"/>
+      <c r="K332" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="L332" s="33"/>
+      <c r="M332" s="33"/>
+      <c r="N332" s="33"/>
+      <c r="O332" s="33"/>
+      <c r="P332" s="33"/>
+      <c r="Q332" s="33"/>
+      <c r="R332" s="33"/>
+      <c r="S332" s="33"/>
+      <c r="T332" s="33"/>
+      <c r="U332" s="33"/>
+      <c r="V332" s="33"/>
+      <c r="W332" s="33"/>
+      <c r="X332" s="33"/>
+      <c r="Z332" s="33"/>
+      <c r="AA332" s="33"/>
+      <c r="AB332" s="33"/>
+      <c r="AC332" s="33"/>
+      <c r="AD332" s="33"/>
+      <c r="AE332" s="33"/>
+      <c r="AF332" s="33"/>
+      <c r="AG332" s="33"/>
+      <c r="AH332" s="33"/>
+      <c r="AI332" s="33"/>
+      <c r="AJ332" s="33"/>
+      <c r="AK332" s="33"/>
+      <c r="AM332" s="33"/>
+      <c r="AN332" s="33" t="s">
+        <v>970</v>
+      </c>
+      <c r="AO332" s="33"/>
+      <c r="AP332" s="33" t="s">
+        <v>970</v>
+      </c>
+      <c r="AQ332" s="33" t="s">
+        <v>970</v>
+      </c>
+      <c r="AR332" s="33"/>
+      <c r="AS332" s="33" t="s">
+        <v>970</v>
+      </c>
+      <c r="AT332" s="33"/>
+      <c r="AU332" s="33"/>
+      <c r="AV332" s="33"/>
+      <c r="AW332" s="33"/>
+      <c r="AX332" s="33"/>
+      <c r="AZ332" s="35"/>
+    </row>
+    <row r="333" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A333" s="135">
+        <v>70</v>
+      </c>
+      <c r="B333" s="33"/>
+      <c r="C333" s="33"/>
+      <c r="D333" s="33" t="s">
+        <v>971</v>
+      </c>
+      <c r="E333" s="54"/>
+      <c r="F333" s="33"/>
+      <c r="G333" s="33"/>
+      <c r="H333" s="33"/>
+      <c r="I333" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="J333" s="33"/>
+      <c r="K333" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="L333" s="33"/>
+      <c r="M333" s="33"/>
+      <c r="N333" s="33"/>
+      <c r="O333" s="33"/>
+      <c r="P333" s="33"/>
+      <c r="Q333" s="33" t="s">
+        <v>608</v>
+      </c>
+      <c r="R333" s="33"/>
+      <c r="S333" s="33" t="s">
+        <v>810</v>
+      </c>
+      <c r="T333" s="33"/>
+      <c r="U333" s="33"/>
+      <c r="V333" s="33"/>
+      <c r="W333" s="33"/>
+      <c r="X333" s="33"/>
+      <c r="Z333" s="33"/>
+      <c r="AA333" s="33"/>
+      <c r="AB333" s="33"/>
+      <c r="AC333" s="33"/>
+      <c r="AD333" s="33"/>
+      <c r="AE333" s="33"/>
+      <c r="AF333" s="33"/>
+      <c r="AG333" s="33"/>
+      <c r="AH333" s="33"/>
+      <c r="AI333" s="33"/>
+      <c r="AJ333" s="33"/>
+      <c r="AK333" s="33"/>
+      <c r="AM333" s="33"/>
+      <c r="AN333" s="33" t="s">
+        <v>972</v>
+      </c>
+      <c r="AO333" s="33"/>
+      <c r="AP333" s="33" t="s">
+        <v>972</v>
+      </c>
+      <c r="AQ333" s="33" t="s">
+        <v>972</v>
+      </c>
+      <c r="AR333" s="33"/>
+      <c r="AS333" s="33" t="s">
+        <v>972</v>
+      </c>
+      <c r="AT333" s="33"/>
+      <c r="AU333" s="33"/>
+      <c r="AV333" s="33"/>
+      <c r="AW333" s="33"/>
+      <c r="AX333" s="33"/>
+      <c r="AZ333" s="35"/>
+    </row>
+    <row r="334" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A334" s="135">
+        <v>70</v>
+      </c>
+      <c r="B334" s="33"/>
+      <c r="C334" s="33"/>
+      <c r="D334" s="33" t="s">
+        <v>973</v>
+      </c>
+      <c r="E334" s="54"/>
+      <c r="F334" s="33"/>
+      <c r="G334" s="33"/>
+      <c r="H334" s="33"/>
+      <c r="I334" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="J334" s="33"/>
+      <c r="K334" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="L334" s="33"/>
+      <c r="M334" s="33"/>
+      <c r="N334" s="33"/>
+      <c r="O334" s="33"/>
+      <c r="P334" s="33"/>
+      <c r="Q334" s="33"/>
+      <c r="R334" s="33"/>
+      <c r="S334" s="33"/>
+      <c r="T334" s="33"/>
+      <c r="U334" s="33"/>
+      <c r="V334" s="33"/>
+      <c r="W334" s="33"/>
+      <c r="X334" s="33"/>
+      <c r="Z334" s="33"/>
+      <c r="AA334" s="33"/>
+      <c r="AB334" s="33"/>
+      <c r="AC334" s="33"/>
+      <c r="AD334" s="33"/>
+      <c r="AE334" s="33"/>
+      <c r="AF334" s="33"/>
+      <c r="AG334" s="33"/>
+      <c r="AH334" s="33"/>
+      <c r="AI334" s="33"/>
+      <c r="AJ334" s="33"/>
+      <c r="AK334" s="33"/>
+      <c r="AM334" s="33"/>
+      <c r="AN334" s="33" t="s">
+        <v>974</v>
+      </c>
+      <c r="AO334" s="33"/>
+      <c r="AP334" s="33" t="s">
+        <v>974</v>
+      </c>
+      <c r="AQ334" s="33"/>
+      <c r="AR334" s="33"/>
+      <c r="AS334" s="33"/>
+      <c r="AT334" s="33"/>
+      <c r="AU334" s="33"/>
+      <c r="AV334" s="33"/>
+      <c r="AW334" s="33"/>
+      <c r="AX334" s="33"/>
+      <c r="AZ334" s="35"/>
+    </row>
+    <row r="335" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A335" s="135">
+        <v>70</v>
+      </c>
+      <c r="B335" s="33"/>
+      <c r="C335" s="33"/>
+      <c r="D335" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="E335" s="54"/>
+      <c r="F335" s="33"/>
+      <c r="G335" s="33"/>
+      <c r="H335" s="33"/>
+      <c r="I335" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="J335" s="33"/>
+      <c r="K335" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="L335" s="33"/>
+      <c r="M335" s="33"/>
+      <c r="N335" s="33"/>
+      <c r="O335" s="33"/>
+      <c r="P335" s="33"/>
+      <c r="Q335" s="33"/>
+      <c r="R335" s="33"/>
+      <c r="S335" s="33"/>
+      <c r="T335" s="33"/>
+      <c r="U335" s="33"/>
+      <c r="V335" s="33"/>
+      <c r="W335" s="33"/>
+      <c r="X335" s="33"/>
+      <c r="Z335" s="33"/>
+      <c r="AA335" s="33"/>
+      <c r="AB335" s="33"/>
+      <c r="AC335" s="33"/>
+      <c r="AD335" s="33"/>
+      <c r="AE335" s="33"/>
+      <c r="AF335" s="33"/>
+      <c r="AG335" s="33"/>
+      <c r="AH335" s="33"/>
+      <c r="AI335" s="33"/>
+      <c r="AJ335" s="33"/>
+      <c r="AK335" s="33"/>
+      <c r="AM335" s="33"/>
+      <c r="AN335" s="33" t="s">
+        <v>976</v>
+      </c>
+      <c r="AO335" s="33"/>
+      <c r="AP335" s="33" t="s">
+        <v>976</v>
+      </c>
+      <c r="AQ335" s="33"/>
+      <c r="AR335" s="33"/>
+      <c r="AS335" s="33"/>
+      <c r="AT335" s="33"/>
+      <c r="AU335" s="33"/>
+      <c r="AV335" s="33"/>
+      <c r="AW335" s="33"/>
+      <c r="AX335" s="33"/>
+      <c r="AZ335" s="35"/>
+    </row>
+    <row r="336" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A336" s="135">
+        <v>70</v>
+      </c>
+      <c r="B336" s="33"/>
+      <c r="C336" s="33"/>
+      <c r="D336" s="33" t="s">
+        <v>977</v>
+      </c>
+      <c r="E336" s="54"/>
+      <c r="F336" s="33"/>
+      <c r="G336" s="33"/>
+      <c r="H336" s="33"/>
+      <c r="I336" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="J336" s="33"/>
+      <c r="K336" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="L336" s="33"/>
+      <c r="M336" s="33"/>
+      <c r="N336" s="33"/>
+      <c r="O336" s="33"/>
+      <c r="P336" s="33"/>
+      <c r="Q336" s="33"/>
+      <c r="R336" s="33"/>
+      <c r="S336" s="33"/>
+      <c r="T336" s="33"/>
+      <c r="U336" s="33"/>
+      <c r="V336" s="33"/>
+      <c r="W336" s="33"/>
+      <c r="X336" s="33"/>
+      <c r="Z336" s="33"/>
+      <c r="AA336" s="33"/>
+      <c r="AB336" s="33"/>
+      <c r="AC336" s="33"/>
+      <c r="AD336" s="33"/>
+      <c r="AE336" s="33"/>
+      <c r="AF336" s="33"/>
+      <c r="AG336" s="33"/>
+      <c r="AH336" s="33"/>
+      <c r="AI336" s="33"/>
+      <c r="AJ336" s="33"/>
+      <c r="AK336" s="33"/>
+      <c r="AM336" s="33"/>
+      <c r="AN336" s="33"/>
+      <c r="AO336" s="33"/>
+      <c r="AP336" s="33"/>
+      <c r="AQ336" s="33"/>
+      <c r="AR336" s="33"/>
+      <c r="AS336" s="33"/>
+      <c r="AT336" s="33"/>
+      <c r="AU336" s="33"/>
+      <c r="AV336" s="33"/>
+      <c r="AW336" s="33"/>
+      <c r="AX336" s="33"/>
+      <c r="AZ336" s="35"/>
+    </row>
+    <row r="337" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A337" s="135">
+        <v>70</v>
+      </c>
+      <c r="B337" s="33"/>
+      <c r="C337" s="33"/>
+      <c r="D337" s="33" t="s">
+        <v>978</v>
+      </c>
+      <c r="E337" s="54"/>
+      <c r="F337" s="33"/>
+      <c r="G337" s="33"/>
+      <c r="H337" s="33"/>
+      <c r="I337" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="J337" s="33"/>
+      <c r="K337" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="L337" s="33"/>
+      <c r="M337" s="33"/>
+      <c r="N337" s="33"/>
+      <c r="O337" s="33"/>
+      <c r="P337" s="33"/>
+      <c r="Q337" s="33"/>
+      <c r="R337" s="33"/>
+      <c r="S337" s="33"/>
+      <c r="T337" s="33"/>
+      <c r="U337" s="33"/>
+      <c r="V337" s="33"/>
+      <c r="W337" s="33"/>
+      <c r="X337" s="33"/>
+      <c r="Z337" s="33"/>
+      <c r="AA337" s="33"/>
+      <c r="AB337" s="33"/>
+      <c r="AC337" s="33"/>
+      <c r="AD337" s="33"/>
+      <c r="AE337" s="33"/>
+      <c r="AF337" s="33"/>
+      <c r="AG337" s="33"/>
+      <c r="AH337" s="33"/>
+      <c r="AI337" s="33"/>
+      <c r="AJ337" s="33"/>
+      <c r="AK337" s="33"/>
+      <c r="AM337" s="33"/>
+      <c r="AN337" s="33" t="s">
+        <v>979</v>
+      </c>
+      <c r="AO337" s="33"/>
+      <c r="AP337" s="33" t="s">
+        <v>979</v>
+      </c>
+      <c r="AQ337" s="33"/>
+      <c r="AR337" s="33"/>
+      <c r="AS337" s="33"/>
+      <c r="AT337" s="33"/>
+      <c r="AU337" s="33"/>
+      <c r="AV337" s="33"/>
+      <c r="AW337" s="33"/>
+      <c r="AX337" s="33"/>
+      <c r="AZ337" s="35"/>
+    </row>
+    <row r="338" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A338" s="135">
+        <v>70</v>
+      </c>
+      <c r="B338" s="33"/>
+      <c r="C338" s="33"/>
+      <c r="D338" s="33" t="s">
+        <v>980</v>
+      </c>
+      <c r="E338" s="54"/>
+      <c r="F338" s="33"/>
+      <c r="G338" s="33"/>
+      <c r="H338" s="33"/>
+      <c r="I338" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="J338" s="33"/>
+      <c r="K338" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="L338" s="33"/>
+      <c r="M338" s="33"/>
+      <c r="N338" s="33"/>
+      <c r="O338" s="33"/>
+      <c r="P338" s="33"/>
+      <c r="Q338" s="33"/>
+      <c r="R338" s="33"/>
+      <c r="S338" s="33"/>
+      <c r="T338" s="33"/>
+      <c r="U338" s="33"/>
+      <c r="V338" s="33"/>
+      <c r="W338" s="33"/>
+      <c r="X338" s="33"/>
+      <c r="Z338" s="33"/>
+      <c r="AA338" s="33"/>
+      <c r="AB338" s="33"/>
+      <c r="AC338" s="33"/>
+      <c r="AD338" s="33"/>
+      <c r="AE338" s="33"/>
+      <c r="AF338" s="33"/>
+      <c r="AG338" s="33"/>
+      <c r="AH338" s="33"/>
+      <c r="AI338" s="33"/>
+      <c r="AJ338" s="33"/>
+      <c r="AK338" s="33"/>
+      <c r="AM338" s="33"/>
+      <c r="AN338" s="33" t="s">
+        <v>981</v>
+      </c>
+      <c r="AO338" s="33"/>
+      <c r="AP338" s="33" t="s">
+        <v>981</v>
+      </c>
+      <c r="AQ338" s="33"/>
+      <c r="AR338" s="33"/>
+      <c r="AS338" s="33"/>
+      <c r="AT338" s="33"/>
+      <c r="AU338" s="33"/>
+      <c r="AV338" s="33"/>
+      <c r="AW338" s="33"/>
+      <c r="AX338" s="33"/>
+      <c r="AZ338" s="35"/>
+    </row>
+    <row r="339" spans="1:52" s="66" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A339" s="136">
+        <v>70</v>
+      </c>
+      <c r="B339" s="61"/>
+      <c r="C339" s="61"/>
+      <c r="D339" s="61" t="s">
+        <v>2382</v>
+      </c>
+      <c r="E339" s="62"/>
+      <c r="F339" s="61"/>
+      <c r="G339" s="61" t="s">
         <v>2347</v>
       </c>
-      <c r="H327" s="65"/>
-      <c r="I327" s="65" t="s">
-        <v>2317</v>
-      </c>
-      <c r="J327" s="65"/>
-      <c r="K327" s="65" t="s">
-        <v>2236</v>
-      </c>
-      <c r="L327" s="65"/>
-      <c r="M327" s="65"/>
-      <c r="N327" s="65"/>
-      <c r="O327" s="65"/>
-      <c r="P327" s="65"/>
-      <c r="Q327" s="65"/>
-      <c r="R327" s="65"/>
-      <c r="S327" s="65"/>
-      <c r="T327" s="65"/>
-      <c r="U327" s="65"/>
-      <c r="V327" s="65"/>
-      <c r="W327" s="65"/>
-      <c r="X327" s="65"/>
-      <c r="Z327" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA327" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB327" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC327" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD327" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE327" s="65"/>
-      <c r="AF327" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG327" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AH327" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AI327" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ327" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AK327" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM327" s="65"/>
-      <c r="AN327" s="65" t="s">
-        <v>883</v>
-      </c>
-      <c r="AO327" s="65"/>
-      <c r="AP327" s="65" t="s">
-        <v>883</v>
-      </c>
-      <c r="AQ327" s="65"/>
-      <c r="AR327" s="65"/>
-      <c r="AS327" s="65"/>
-      <c r="AT327" s="65"/>
-      <c r="AU327" s="65"/>
-      <c r="AV327" s="65"/>
-      <c r="AW327" s="65"/>
-      <c r="AX327" s="65"/>
-      <c r="AZ327" s="68"/>
-    </row>
-    <row r="328" spans="1:52" s="66" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A328" s="63">
-        <v>70</v>
-      </c>
-      <c r="B328" s="65"/>
-      <c r="C328" s="65"/>
-      <c r="D328" s="65" t="s">
-        <v>2348</v>
-      </c>
-      <c r="E328" s="64"/>
-      <c r="F328" s="65"/>
-      <c r="G328" s="65" t="s">
-        <v>2349</v>
-      </c>
-      <c r="H328" s="65"/>
-      <c r="I328" s="65" t="s">
-        <v>2317</v>
-      </c>
-      <c r="J328" s="65"/>
-      <c r="K328" s="65" t="s">
-        <v>2236</v>
-      </c>
-      <c r="L328" s="65"/>
-      <c r="M328" s="65"/>
-      <c r="N328" s="65"/>
-      <c r="O328" s="65"/>
-      <c r="P328" s="65"/>
-      <c r="Q328" s="65"/>
-      <c r="R328" s="65"/>
-      <c r="S328" s="65"/>
-      <c r="T328" s="65"/>
-      <c r="U328" s="65"/>
-      <c r="V328" s="65"/>
-      <c r="W328" s="65"/>
-      <c r="X328" s="65"/>
-      <c r="Z328" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA328" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB328" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC328" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD328" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE328" s="65"/>
-      <c r="AF328" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG328" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AH328" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AI328" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ328" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AK328" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM328" s="65"/>
-      <c r="AN328" s="65" t="s">
+      <c r="H339" s="61"/>
+      <c r="I339" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="J339" s="61"/>
+      <c r="K339" s="61" t="s">
+        <v>24</v>
+      </c>
+      <c r="L339" s="61"/>
+      <c r="M339" s="61"/>
+      <c r="N339" s="61"/>
+      <c r="O339" s="61"/>
+      <c r="P339" s="61"/>
+      <c r="Q339" s="61"/>
+      <c r="R339" s="61"/>
+      <c r="S339" s="61"/>
+      <c r="T339" s="61"/>
+      <c r="U339" s="61"/>
+      <c r="V339" s="61"/>
+      <c r="W339" s="61"/>
+      <c r="X339" s="61"/>
+      <c r="Z339" s="61"/>
+      <c r="AA339" s="61"/>
+      <c r="AB339" s="61"/>
+      <c r="AC339" s="61"/>
+      <c r="AD339" s="61"/>
+      <c r="AE339" s="61"/>
+      <c r="AF339" s="61"/>
+      <c r="AG339" s="61"/>
+      <c r="AH339" s="61"/>
+      <c r="AI339" s="61"/>
+      <c r="AJ339" s="61"/>
+      <c r="AK339" s="61"/>
+      <c r="AM339" s="61"/>
+      <c r="AN339" s="61" t="s">
         <v>982</v>
       </c>
-      <c r="AO328" s="65"/>
-      <c r="AP328" s="65" t="s">
+      <c r="AO339" s="61"/>
+      <c r="AP339" s="61" t="s">
         <v>982</v>
       </c>
-      <c r="AQ328" s="65" t="s">
+      <c r="AQ339" s="61" t="s">
         <v>982</v>
       </c>
-      <c r="AR328" s="65"/>
-      <c r="AS328" s="65" t="s">
+      <c r="AR339" s="61"/>
+      <c r="AS339" s="61" t="s">
         <v>982</v>
       </c>
-      <c r="AT328" s="65"/>
-      <c r="AU328" s="65"/>
-      <c r="AV328" s="65"/>
-      <c r="AW328" s="65"/>
-      <c r="AX328" s="65"/>
-      <c r="AZ328" s="68"/>
-    </row>
-    <row r="329" spans="1:52" s="66" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A329" s="63">
-        <v>70</v>
-      </c>
-      <c r="B329" s="63"/>
-      <c r="C329" s="63"/>
-      <c r="D329" s="63" t="s">
+      <c r="AT339" s="61"/>
+      <c r="AU339" s="61"/>
+      <c r="AV339" s="61"/>
+      <c r="AW339" s="61"/>
+      <c r="AX339" s="61"/>
+      <c r="AZ339" s="67"/>
+    </row>
+    <row r="340" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A340" s="135">
+        <v>70</v>
+      </c>
+      <c r="B340" s="33"/>
+      <c r="C340" s="33"/>
+      <c r="D340" s="33" t="s">
+        <v>983</v>
+      </c>
+      <c r="E340" s="54"/>
+      <c r="F340" s="33"/>
+      <c r="G340" s="33"/>
+      <c r="H340" s="33"/>
+      <c r="I340" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="J340" s="33"/>
+      <c r="K340" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="L340" s="33"/>
+      <c r="M340" s="33"/>
+      <c r="N340" s="33"/>
+      <c r="O340" s="33"/>
+      <c r="P340" s="33"/>
+      <c r="Q340" s="33" t="s">
+        <v>1399</v>
+      </c>
+      <c r="R340" s="33"/>
+      <c r="S340" s="33" t="s">
+        <v>811</v>
+      </c>
+      <c r="T340" s="33"/>
+      <c r="U340" s="33" t="s">
+        <v>269</v>
+      </c>
+      <c r="V340" s="33"/>
+      <c r="W340" s="33"/>
+      <c r="X340" s="33"/>
+      <c r="Z340" s="33"/>
+      <c r="AA340" s="33"/>
+      <c r="AB340" s="33"/>
+      <c r="AC340" s="33"/>
+      <c r="AD340" s="33"/>
+      <c r="AE340" s="33"/>
+      <c r="AF340" s="33"/>
+      <c r="AG340" s="33"/>
+      <c r="AH340" s="33"/>
+      <c r="AI340" s="33"/>
+      <c r="AJ340" s="33"/>
+      <c r="AK340" s="33"/>
+      <c r="AM340" s="33"/>
+      <c r="AN340" s="33" t="s">
+        <v>984</v>
+      </c>
+      <c r="AO340" s="33"/>
+      <c r="AP340" s="33" t="s">
+        <v>984</v>
+      </c>
+      <c r="AQ340" s="33" t="s">
+        <v>984</v>
+      </c>
+      <c r="AR340" s="33"/>
+      <c r="AS340" s="33" t="s">
+        <v>984</v>
+      </c>
+      <c r="AT340" s="33"/>
+      <c r="AU340" s="33"/>
+      <c r="AV340" s="33"/>
+      <c r="AW340" s="33"/>
+      <c r="AX340" s="33"/>
+      <c r="AZ340" s="35"/>
+    </row>
+    <row r="341" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A341" s="135">
+        <v>70</v>
+      </c>
+      <c r="B341" s="33"/>
+      <c r="C341" s="33"/>
+      <c r="D341" s="33" t="s">
+        <v>985</v>
+      </c>
+      <c r="E341" s="54"/>
+      <c r="F341" s="33"/>
+      <c r="G341" s="33"/>
+      <c r="H341" s="33"/>
+      <c r="I341" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="J341" s="33"/>
+      <c r="K341" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="L341" s="33"/>
+      <c r="M341" s="33"/>
+      <c r="N341" s="33"/>
+      <c r="O341" s="33"/>
+      <c r="P341" s="33"/>
+      <c r="Q341" s="33"/>
+      <c r="R341" s="33"/>
+      <c r="S341" s="33"/>
+      <c r="T341" s="33"/>
+      <c r="U341" s="33"/>
+      <c r="V341" s="33"/>
+      <c r="W341" s="33"/>
+      <c r="X341" s="33"/>
+      <c r="Z341" s="33"/>
+      <c r="AA341" s="33"/>
+      <c r="AB341" s="33"/>
+      <c r="AC341" s="33"/>
+      <c r="AD341" s="33"/>
+      <c r="AE341" s="33"/>
+      <c r="AF341" s="33"/>
+      <c r="AG341" s="33"/>
+      <c r="AH341" s="33"/>
+      <c r="AI341" s="33"/>
+      <c r="AJ341" s="33"/>
+      <c r="AK341" s="33"/>
+      <c r="AM341" s="33"/>
+      <c r="AN341" s="33" t="s">
+        <v>811</v>
+      </c>
+      <c r="AO341" s="33"/>
+      <c r="AP341" s="33" t="s">
+        <v>811</v>
+      </c>
+      <c r="AQ341" s="33"/>
+      <c r="AR341" s="33"/>
+      <c r="AS341" s="33"/>
+      <c r="AT341" s="33"/>
+      <c r="AU341" s="33"/>
+      <c r="AV341" s="33"/>
+      <c r="AW341" s="33"/>
+      <c r="AX341" s="33"/>
+      <c r="AZ341" s="35"/>
+    </row>
+    <row r="342" spans="1:52" s="66" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A342" s="63">
+        <v>70</v>
+      </c>
+      <c r="B342" s="63"/>
+      <c r="C342" s="63"/>
+      <c r="D342" s="63" t="s">
         <v>1030</v>
       </c>
-      <c r="E329" s="63"/>
-      <c r="F329" s="63"/>
-      <c r="G329" s="63"/>
-      <c r="H329" s="63"/>
-      <c r="I329" s="63" t="s">
+      <c r="E342" s="63"/>
+      <c r="F342" s="63"/>
+      <c r="G342" s="63"/>
+      <c r="H342" s="63"/>
+      <c r="I342" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="J329" s="63"/>
-      <c r="K329" s="63" t="s">
+      <c r="J342" s="63"/>
+      <c r="K342" s="63" t="s">
         <v>248</v>
       </c>
-      <c r="L329" s="63" t="s">
+      <c r="L342" s="63" t="s">
         <v>776</v>
       </c>
-      <c r="M329" s="63"/>
-      <c r="N329" s="63"/>
-      <c r="O329" s="63"/>
-      <c r="P329" s="63"/>
-      <c r="Q329" s="63"/>
-      <c r="R329" s="63"/>
-      <c r="S329" s="63"/>
-      <c r="T329" s="63"/>
-      <c r="U329" s="63"/>
-      <c r="V329" s="63"/>
-      <c r="W329" s="63"/>
-      <c r="X329" s="63"/>
-      <c r="Y329" s="63"/>
-      <c r="Z329" s="63" t="s">
+      <c r="M342" s="63"/>
+      <c r="N342" s="63"/>
+      <c r="O342" s="63"/>
+      <c r="P342" s="63"/>
+      <c r="Q342" s="63"/>
+      <c r="R342" s="63"/>
+      <c r="S342" s="63"/>
+      <c r="T342" s="63"/>
+      <c r="U342" s="63"/>
+      <c r="V342" s="63"/>
+      <c r="W342" s="63"/>
+      <c r="X342" s="63"/>
+      <c r="Y342" s="63"/>
+      <c r="Z342" s="63" t="s">
         <v>80</v>
       </c>
-      <c r="AA329" s="63" t="s">
+      <c r="AA342" s="63" t="s">
         <v>80</v>
       </c>
-      <c r="AB329" s="63" t="s">
+      <c r="AB342" s="63" t="s">
         <v>282</v>
       </c>
-      <c r="AC329" s="63" t="s">
+      <c r="AC342" s="63" t="s">
         <v>282</v>
       </c>
-      <c r="AD329" s="63" t="s">
+      <c r="AD342" s="63" t="s">
         <v>282</v>
       </c>
-      <c r="AE329" s="63"/>
-      <c r="AF329" s="63" t="s">
+      <c r="AE342" s="63"/>
+      <c r="AF342" s="63" t="s">
         <v>80</v>
       </c>
-      <c r="AG329" s="63" t="s">
+      <c r="AG342" s="63" t="s">
         <v>282</v>
       </c>
-      <c r="AH329" s="63" t="s">
+      <c r="AH342" s="63" t="s">
         <v>282</v>
       </c>
-      <c r="AI329" s="63" t="s">
+      <c r="AI342" s="63" t="s">
         <v>80</v>
       </c>
-      <c r="AJ329" s="63" t="s">
+      <c r="AJ342" s="63" t="s">
         <v>80</v>
       </c>
-      <c r="AK329" s="63" t="s">
+      <c r="AK342" s="63" t="s">
         <v>80</v>
       </c>
-      <c r="AL329" s="63"/>
-      <c r="AM329" s="63"/>
-      <c r="AN329" s="63"/>
-      <c r="AO329" s="63"/>
-      <c r="AP329" s="63"/>
-      <c r="AQ329" s="63"/>
-      <c r="AR329" s="63"/>
-      <c r="AS329" s="63"/>
-      <c r="AT329" s="63"/>
-      <c r="AU329" s="63"/>
-      <c r="AV329" s="63"/>
-      <c r="AW329" s="63"/>
-      <c r="AX329" s="63"/>
-      <c r="AY329" s="63"/>
-      <c r="AZ329" s="63"/>
-    </row>
-    <row r="330" spans="1:52" s="66" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A330" s="63">
-        <v>70</v>
-      </c>
-      <c r="B330" s="65"/>
-      <c r="C330" s="65"/>
-      <c r="D330" s="65" t="s">
+      <c r="AL342" s="63"/>
+      <c r="AM342" s="63"/>
+      <c r="AN342" s="63"/>
+      <c r="AO342" s="63"/>
+      <c r="AP342" s="63"/>
+      <c r="AQ342" s="63"/>
+      <c r="AR342" s="63"/>
+      <c r="AS342" s="63"/>
+      <c r="AT342" s="63"/>
+      <c r="AU342" s="63"/>
+      <c r="AV342" s="63"/>
+      <c r="AW342" s="63"/>
+      <c r="AX342" s="63"/>
+      <c r="AY342" s="63"/>
+      <c r="AZ342" s="63"/>
+    </row>
+    <row r="343" spans="1:52" s="66" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A343" s="63">
+        <v>70</v>
+      </c>
+      <c r="B343" s="65"/>
+      <c r="C343" s="65"/>
+      <c r="D343" s="65" t="s">
         <v>1031</v>
       </c>
-      <c r="E330" s="64" t="s">
+      <c r="E343" s="64" t="s">
         <v>2016</v>
       </c>
-      <c r="F330" s="65" t="s">
+      <c r="F343" s="65" t="s">
         <v>1032</v>
       </c>
-      <c r="G330" s="65" t="s">
+      <c r="G343" s="65" t="s">
         <v>997</v>
       </c>
-      <c r="H330" s="65"/>
-      <c r="I330" s="65" t="s">
+      <c r="H343" s="65"/>
+      <c r="I343" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="J330" s="65"/>
-      <c r="K330" s="65" t="s">
+      <c r="J343" s="65"/>
+      <c r="K343" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="L330" s="65"/>
-      <c r="M330" s="65"/>
-      <c r="N330" s="65"/>
-      <c r="O330" s="65"/>
-      <c r="P330" s="65"/>
-      <c r="Q330" s="65"/>
-      <c r="R330" s="65"/>
-      <c r="S330" s="65"/>
-      <c r="T330" s="65"/>
-      <c r="U330" s="65"/>
-      <c r="V330" s="65"/>
-      <c r="W330" s="65"/>
-      <c r="X330" s="65"/>
-      <c r="Z330" s="65"/>
-      <c r="AA330" s="65"/>
-      <c r="AB330" s="65"/>
-      <c r="AC330" s="65"/>
-      <c r="AD330" s="65"/>
-      <c r="AE330" s="65"/>
-      <c r="AF330" s="65"/>
-      <c r="AG330" s="65"/>
-      <c r="AH330" s="65"/>
-      <c r="AI330" s="65"/>
-      <c r="AJ330" s="65"/>
-      <c r="AK330" s="65"/>
-      <c r="AM330" s="65"/>
-      <c r="AN330" s="65" t="s">
+      <c r="L343" s="65"/>
+      <c r="M343" s="65"/>
+      <c r="N343" s="65"/>
+      <c r="O343" s="65"/>
+      <c r="P343" s="65"/>
+      <c r="Q343" s="65"/>
+      <c r="R343" s="65"/>
+      <c r="S343" s="65"/>
+      <c r="T343" s="65"/>
+      <c r="U343" s="65"/>
+      <c r="V343" s="65"/>
+      <c r="W343" s="65"/>
+      <c r="X343" s="65"/>
+      <c r="Z343" s="65"/>
+      <c r="AA343" s="65"/>
+      <c r="AB343" s="65"/>
+      <c r="AC343" s="65"/>
+      <c r="AD343" s="65"/>
+      <c r="AE343" s="65"/>
+      <c r="AF343" s="65"/>
+      <c r="AG343" s="65"/>
+      <c r="AH343" s="65"/>
+      <c r="AI343" s="65"/>
+      <c r="AJ343" s="65"/>
+      <c r="AK343" s="65"/>
+      <c r="AM343" s="65"/>
+      <c r="AN343" s="65" t="s">
         <v>1033</v>
       </c>
-      <c r="AO330" s="65"/>
-      <c r="AP330" s="65"/>
-      <c r="AQ330" s="65" t="s">
+      <c r="AO343" s="65"/>
+      <c r="AP343" s="65"/>
+      <c r="AQ343" s="65" t="s">
         <v>1034</v>
       </c>
-      <c r="AR330" s="65"/>
-      <c r="AS330" s="65" t="s">
+      <c r="AR343" s="65"/>
+      <c r="AS343" s="65" t="s">
         <v>1034</v>
       </c>
-      <c r="AT330" s="65"/>
-      <c r="AU330" s="65"/>
-      <c r="AV330" s="65"/>
-      <c r="AW330" s="65"/>
-      <c r="AX330" s="65"/>
-      <c r="AZ330" s="68"/>
-    </row>
-    <row r="331" spans="1:52" s="66" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A331" s="63">
-        <v>70</v>
-      </c>
-      <c r="B331" s="65"/>
-      <c r="C331" s="65"/>
-      <c r="D331" s="65" t="s">
+      <c r="AT343" s="65"/>
+      <c r="AU343" s="65"/>
+      <c r="AV343" s="65"/>
+      <c r="AW343" s="65"/>
+      <c r="AX343" s="65"/>
+      <c r="AZ343" s="68"/>
+    </row>
+    <row r="344" spans="1:52" s="66" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A344" s="63">
+        <v>70</v>
+      </c>
+      <c r="B344" s="65"/>
+      <c r="C344" s="65"/>
+      <c r="D344" s="65" t="s">
         <v>1035</v>
       </c>
-      <c r="E331" s="64" t="s">
+      <c r="E344" s="64" t="s">
         <v>2017</v>
       </c>
-      <c r="F331" s="65" t="s">
+      <c r="F344" s="65" t="s">
         <v>1036</v>
       </c>
-      <c r="G331" s="65" t="s">
+      <c r="G344" s="65" t="s">
         <v>997</v>
       </c>
-      <c r="H331" s="65"/>
-      <c r="I331" s="65" t="s">
+      <c r="H344" s="65"/>
+      <c r="I344" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="J331" s="65"/>
-      <c r="K331" s="65" t="s">
+      <c r="J344" s="65"/>
+      <c r="K344" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="L331" s="65"/>
-      <c r="M331" s="65"/>
-      <c r="N331" s="65"/>
-      <c r="O331" s="65"/>
-      <c r="P331" s="65"/>
-      <c r="Q331" s="65"/>
-      <c r="R331" s="65"/>
-      <c r="S331" s="65"/>
-      <c r="T331" s="65"/>
-      <c r="U331" s="65"/>
-      <c r="V331" s="65"/>
-      <c r="W331" s="65"/>
-      <c r="X331" s="65"/>
-      <c r="Z331" s="65"/>
-      <c r="AA331" s="65"/>
-      <c r="AB331" s="65"/>
-      <c r="AC331" s="65"/>
-      <c r="AD331" s="65"/>
-      <c r="AE331" s="65"/>
-      <c r="AF331" s="65"/>
-      <c r="AG331" s="65"/>
-      <c r="AH331" s="65"/>
-      <c r="AI331" s="65"/>
-      <c r="AJ331" s="65"/>
-      <c r="AK331" s="65"/>
-      <c r="AM331" s="65"/>
-      <c r="AN331" s="65" t="s">
+      <c r="L344" s="65"/>
+      <c r="M344" s="65"/>
+      <c r="N344" s="65"/>
+      <c r="O344" s="65"/>
+      <c r="P344" s="65"/>
+      <c r="Q344" s="65"/>
+      <c r="R344" s="65"/>
+      <c r="S344" s="65"/>
+      <c r="T344" s="65"/>
+      <c r="U344" s="65"/>
+      <c r="V344" s="65"/>
+      <c r="W344" s="65"/>
+      <c r="X344" s="65"/>
+      <c r="Z344" s="65"/>
+      <c r="AA344" s="65"/>
+      <c r="AB344" s="65"/>
+      <c r="AC344" s="65"/>
+      <c r="AD344" s="65"/>
+      <c r="AE344" s="65"/>
+      <c r="AF344" s="65"/>
+      <c r="AG344" s="65"/>
+      <c r="AH344" s="65"/>
+      <c r="AI344" s="65"/>
+      <c r="AJ344" s="65"/>
+      <c r="AK344" s="65"/>
+      <c r="AM344" s="65"/>
+      <c r="AN344" s="65" t="s">
         <v>1037</v>
       </c>
-      <c r="AO331" s="65"/>
-      <c r="AP331" s="65"/>
-      <c r="AQ331" s="65"/>
-      <c r="AR331" s="65"/>
-      <c r="AS331" s="65"/>
-      <c r="AT331" s="65"/>
-      <c r="AU331" s="65"/>
-      <c r="AV331" s="65"/>
-      <c r="AW331" s="65"/>
-      <c r="AX331" s="65"/>
-      <c r="AZ331" s="68"/>
-    </row>
-    <row r="332" spans="1:52" s="66" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A332" s="65">
-        <v>70</v>
-      </c>
-      <c r="B332" s="65"/>
-      <c r="C332" s="65"/>
-      <c r="D332" s="65" t="s">
+      <c r="AO344" s="65"/>
+      <c r="AP344" s="65"/>
+      <c r="AQ344" s="65"/>
+      <c r="AR344" s="65"/>
+      <c r="AS344" s="65"/>
+      <c r="AT344" s="65"/>
+      <c r="AU344" s="65"/>
+      <c r="AV344" s="65"/>
+      <c r="AW344" s="65"/>
+      <c r="AX344" s="65"/>
+      <c r="AZ344" s="68"/>
+    </row>
+    <row r="345" spans="1:52" s="66" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A345" s="65">
+        <v>70</v>
+      </c>
+      <c r="B345" s="65"/>
+      <c r="C345" s="65"/>
+      <c r="D345" s="65" t="s">
         <v>657</v>
       </c>
-      <c r="E332" s="64" t="s">
+      <c r="E345" s="64" t="s">
         <v>2018</v>
       </c>
-      <c r="F332" s="65" t="s">
+      <c r="F345" s="65" t="s">
         <v>380</v>
       </c>
-      <c r="G332" s="65"/>
-      <c r="H332" s="65"/>
-      <c r="I332" s="65" t="s">
+      <c r="G345" s="65"/>
+      <c r="H345" s="65"/>
+      <c r="I345" s="65" t="s">
         <v>1371</v>
       </c>
-      <c r="J332" s="65"/>
-      <c r="K332" s="65" t="s">
+      <c r="J345" s="65"/>
+      <c r="K345" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="L332" s="65"/>
-      <c r="M332" s="65" t="s">
+      <c r="L345" s="65"/>
+      <c r="M345" s="65" t="s">
         <v>682</v>
       </c>
-      <c r="N332" s="65"/>
-      <c r="O332" s="65"/>
-      <c r="P332" s="65"/>
-      <c r="Q332" s="65"/>
-      <c r="R332" s="65"/>
-      <c r="S332" s="65"/>
-      <c r="T332" s="65"/>
-      <c r="U332" s="65"/>
-      <c r="V332" s="65"/>
-      <c r="W332" s="65"/>
-      <c r="X332" s="65"/>
-      <c r="Z332" s="65" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA332" s="65" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB332" s="65" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC332" s="65" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD332" s="65" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE332" s="65"/>
-      <c r="AF332" s="65" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG332" s="65" t="s">
-        <v>70</v>
-      </c>
-      <c r="AH332" s="65" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI332" s="65" t="s">
-        <v>70</v>
-      </c>
-      <c r="AJ332" s="65" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK332" s="65" t="s">
-        <v>70</v>
-      </c>
-      <c r="AM332" s="65"/>
-      <c r="AN332" s="65" t="s">
+      <c r="N345" s="65"/>
+      <c r="O345" s="65"/>
+      <c r="P345" s="65"/>
+      <c r="Q345" s="65"/>
+      <c r="R345" s="65"/>
+      <c r="S345" s="65"/>
+      <c r="T345" s="65"/>
+      <c r="U345" s="65"/>
+      <c r="V345" s="65"/>
+      <c r="W345" s="65"/>
+      <c r="X345" s="65"/>
+      <c r="Z345" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA345" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB345" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC345" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD345" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="AE345" s="65"/>
+      <c r="AF345" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG345" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="AH345" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="AI345" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ345" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK345" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM345" s="65"/>
+      <c r="AN345" s="65" t="s">
         <v>381</v>
       </c>
-      <c r="AO332" s="65"/>
-      <c r="AP332" s="65"/>
-      <c r="AQ332" s="65" t="s">
+      <c r="AO345" s="65"/>
+      <c r="AP345" s="65"/>
+      <c r="AQ345" s="65" t="s">
         <v>381</v>
       </c>
-      <c r="AR332" s="65"/>
-      <c r="AS332" s="65" t="s">
+      <c r="AR345" s="65"/>
+      <c r="AS345" s="65" t="s">
         <v>381</v>
       </c>
-      <c r="AT332" s="65"/>
-      <c r="AU332" s="65"/>
-      <c r="AV332" s="65"/>
-      <c r="AW332" s="65"/>
-      <c r="AX332" s="65"/>
-      <c r="AZ332" s="68"/>
-    </row>
-    <row r="333" spans="1:52" s="66" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A333" s="65">
-        <v>70</v>
-      </c>
-      <c r="B333" s="65"/>
-      <c r="C333" s="65"/>
-      <c r="D333" s="65" t="s">
+      <c r="AT345" s="65"/>
+      <c r="AU345" s="65"/>
+      <c r="AV345" s="65"/>
+      <c r="AW345" s="65"/>
+      <c r="AX345" s="65"/>
+      <c r="AZ345" s="68"/>
+    </row>
+    <row r="346" spans="1:52" s="66" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A346" s="65">
+        <v>70</v>
+      </c>
+      <c r="B346" s="65"/>
+      <c r="C346" s="65"/>
+      <c r="D346" s="65" t="s">
         <v>1530</v>
       </c>
-      <c r="E333" s="64" t="s">
+      <c r="E346" s="64" t="s">
         <v>2019</v>
       </c>
-      <c r="F333" s="65" t="s">
+      <c r="F346" s="65" t="s">
         <v>375</v>
       </c>
-      <c r="G333" s="65" t="s">
+      <c r="G346" s="65" t="s">
         <v>375</v>
       </c>
-      <c r="H333" s="65"/>
-      <c r="I333" s="65" t="s">
+      <c r="H346" s="65"/>
+      <c r="I346" s="65" t="s">
         <v>631</v>
       </c>
-      <c r="J333" s="65"/>
-      <c r="K333" s="65" t="s">
+      <c r="J346" s="65"/>
+      <c r="K346" s="65" t="s">
         <v>49</v>
       </c>
-      <c r="L333" s="65"/>
-      <c r="M333" s="65"/>
-      <c r="N333" s="65"/>
-      <c r="O333" s="65"/>
-      <c r="P333" s="65"/>
-      <c r="Q333" s="65" t="s">
+      <c r="L346" s="65"/>
+      <c r="M346" s="65"/>
+      <c r="N346" s="65"/>
+      <c r="O346" s="65"/>
+      <c r="P346" s="65"/>
+      <c r="Q346" s="65" t="s">
         <v>601</v>
       </c>
-      <c r="R333" s="65"/>
-      <c r="S333" s="65" t="s">
+      <c r="R346" s="65"/>
+      <c r="S346" s="65" t="s">
         <v>381</v>
       </c>
-      <c r="T333" s="65"/>
-      <c r="U333" s="65" t="s">
+      <c r="T346" s="65"/>
+      <c r="U346" s="65" t="s">
         <v>623</v>
       </c>
-      <c r="V333" s="65"/>
-      <c r="W333" s="65"/>
-      <c r="X333" s="65"/>
-      <c r="Z333" s="65" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA333" s="65" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB333" s="65" t="s">
+      <c r="V346" s="65"/>
+      <c r="W346" s="65"/>
+      <c r="X346" s="65"/>
+      <c r="Z346" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA346" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB346" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="AC333" s="65" t="s">
+      <c r="AC346" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="AD333" s="65" t="s">
+      <c r="AD346" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="AE333" s="65"/>
-      <c r="AF333" s="65" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG333" s="65" t="s">
+      <c r="AE346" s="65"/>
+      <c r="AF346" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG346" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="AH333" s="65" t="s">
+      <c r="AH346" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="AI333" s="65" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ333" s="65" t="s">
-        <v>25</v>
-      </c>
-      <c r="AK333" s="65" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM333" s="65"/>
-      <c r="AN333" s="65" t="s">
+      <c r="AI346" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ346" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK346" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM346" s="65"/>
+      <c r="AN346" s="65" t="s">
         <v>1530</v>
       </c>
-      <c r="AO333" s="65"/>
-      <c r="AP333" s="65"/>
-      <c r="AQ333" s="65"/>
-      <c r="AR333" s="65"/>
-      <c r="AS333" s="65"/>
-      <c r="AT333" s="65"/>
-      <c r="AU333" s="65"/>
-      <c r="AV333" s="65"/>
-      <c r="AW333" s="65"/>
-      <c r="AX333" s="65"/>
-      <c r="AZ333" s="68"/>
-    </row>
-    <row r="334" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A334" s="50">
-        <v>70</v>
-      </c>
-      <c r="B334" s="50"/>
-      <c r="C334" s="50"/>
-      <c r="D334" s="50" t="s">
-        <v>809</v>
-      </c>
-      <c r="E334" s="50"/>
-      <c r="F334" s="50"/>
-      <c r="G334" s="50"/>
-      <c r="H334" s="50"/>
-      <c r="I334" s="50" t="s">
-        <v>31</v>
-      </c>
-      <c r="J334" s="50"/>
-      <c r="K334" s="50" t="s">
-        <v>248</v>
-      </c>
-      <c r="L334" s="50" t="s">
-        <v>1149</v>
-      </c>
-      <c r="M334" s="50"/>
-      <c r="N334" s="50"/>
-      <c r="O334" s="50"/>
-      <c r="P334" s="50"/>
-      <c r="Q334" s="50"/>
-      <c r="R334" s="50"/>
-      <c r="S334" s="50"/>
-      <c r="T334" s="50"/>
-      <c r="U334" s="50"/>
-      <c r="V334" s="50"/>
-      <c r="W334" s="50"/>
-      <c r="X334" s="50"/>
-      <c r="Y334" s="50"/>
-      <c r="Z334" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA334" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB334" s="50" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC334" s="50" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD334" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AE334" s="50"/>
-      <c r="AF334" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG334" s="50" t="s">
-        <v>30</v>
-      </c>
-      <c r="AH334" s="50" t="s">
-        <v>30</v>
-      </c>
-      <c r="AI334" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AJ334" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AK334" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL334" s="50"/>
-      <c r="AM334" s="50"/>
-      <c r="AN334" s="50"/>
-      <c r="AO334" s="50"/>
-      <c r="AP334" s="50"/>
-      <c r="AQ334" s="50"/>
-      <c r="AR334" s="50"/>
-      <c r="AS334" s="50"/>
-      <c r="AT334" s="50"/>
-      <c r="AU334" s="50"/>
-      <c r="AV334" s="50"/>
-      <c r="AW334" s="50"/>
-      <c r="AX334" s="50"/>
-      <c r="AY334" s="50"/>
-      <c r="AZ334" s="50"/>
-    </row>
-    <row r="335" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A335" s="50">
-        <v>70</v>
-      </c>
-      <c r="B335" s="25"/>
-      <c r="C335" s="25"/>
-      <c r="D335" s="25" t="s">
-        <v>946</v>
-      </c>
-      <c r="E335" s="37"/>
-      <c r="F335" s="25"/>
-      <c r="G335" s="25"/>
-      <c r="H335" s="25"/>
-      <c r="I335" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="J335" s="25"/>
-      <c r="K335" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="L335" s="25"/>
-      <c r="M335" s="25"/>
-      <c r="N335" s="25"/>
-      <c r="O335" s="25"/>
-      <c r="P335" s="25"/>
-      <c r="Q335" s="25"/>
-      <c r="R335" s="25"/>
-      <c r="S335" s="25"/>
-      <c r="T335" s="25"/>
-      <c r="U335" s="25"/>
-      <c r="V335" s="25"/>
-      <c r="W335" s="25"/>
-      <c r="X335" s="25"/>
-      <c r="Z335" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA335" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB335" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="AC335" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="AD335" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE335" s="25"/>
-      <c r="AF335" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG335" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="AH335" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="AI335" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ335" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AK335" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM335" s="25"/>
-      <c r="AN335" s="25" t="s">
-        <v>679</v>
-      </c>
-      <c r="AO335" s="25"/>
-      <c r="AP335" s="25" t="s">
-        <v>679</v>
-      </c>
-      <c r="AQ335" s="25" t="s">
-        <v>679</v>
-      </c>
-      <c r="AR335" s="25"/>
-      <c r="AS335" s="25" t="s">
-        <v>679</v>
-      </c>
-      <c r="AT335" s="25"/>
-      <c r="AU335" s="25"/>
-      <c r="AV335" s="25"/>
-      <c r="AW335" s="25"/>
-      <c r="AX335" s="25"/>
-      <c r="AZ335" s="26"/>
-    </row>
-    <row r="336" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A336" s="50">
-        <v>70</v>
-      </c>
-      <c r="B336" s="25"/>
-      <c r="C336" s="25"/>
-      <c r="D336" s="25" t="s">
-        <v>966</v>
-      </c>
-      <c r="E336" s="37"/>
-      <c r="F336" s="25"/>
-      <c r="G336" s="25"/>
-      <c r="H336" s="25"/>
-      <c r="I336" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="J336" s="25"/>
-      <c r="K336" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="L336" s="25"/>
-      <c r="M336" s="25"/>
-      <c r="N336" s="25"/>
-      <c r="O336" s="25"/>
-      <c r="P336" s="25"/>
-      <c r="Q336" s="25"/>
-      <c r="R336" s="25"/>
-      <c r="S336" s="25"/>
-      <c r="T336" s="25"/>
-      <c r="U336" s="25"/>
-      <c r="V336" s="25"/>
-      <c r="W336" s="25"/>
-      <c r="X336" s="25"/>
-      <c r="Z336" s="25"/>
-      <c r="AA336" s="25"/>
-      <c r="AB336" s="25"/>
-      <c r="AC336" s="25"/>
-      <c r="AD336" s="25"/>
-      <c r="AE336" s="25"/>
-      <c r="AF336" s="25"/>
-      <c r="AG336" s="25"/>
-      <c r="AH336" s="25"/>
-      <c r="AI336" s="25"/>
-      <c r="AJ336" s="25"/>
-      <c r="AK336" s="25"/>
-      <c r="AM336" s="25"/>
-      <c r="AN336" s="25" t="s">
-        <v>854</v>
-      </c>
-      <c r="AO336" s="25"/>
-      <c r="AP336" s="25" t="s">
-        <v>854</v>
-      </c>
-      <c r="AQ336" s="25" t="s">
-        <v>854</v>
-      </c>
-      <c r="AR336" s="25"/>
-      <c r="AS336" s="25" t="s">
-        <v>854</v>
-      </c>
-      <c r="AT336" s="25"/>
-      <c r="AU336" s="25"/>
-      <c r="AV336" s="25"/>
-      <c r="AW336" s="25"/>
-      <c r="AX336" s="25"/>
-      <c r="AZ336" s="26"/>
-    </row>
-    <row r="337" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A337" s="50">
-        <v>70</v>
-      </c>
-      <c r="B337" s="25"/>
-      <c r="C337" s="25"/>
-      <c r="D337" s="25" t="s">
-        <v>967</v>
-      </c>
-      <c r="E337" s="37"/>
-      <c r="F337" s="25"/>
-      <c r="G337" s="25"/>
-      <c r="H337" s="25"/>
-      <c r="I337" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="J337" s="25"/>
-      <c r="K337" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="L337" s="25"/>
-      <c r="M337" s="25"/>
-      <c r="N337" s="25"/>
-      <c r="O337" s="25"/>
-      <c r="P337" s="25"/>
-      <c r="Q337" s="25"/>
-      <c r="R337" s="25"/>
-      <c r="S337" s="25"/>
-      <c r="T337" s="25"/>
-      <c r="U337" s="25"/>
-      <c r="V337" s="25"/>
-      <c r="W337" s="25"/>
-      <c r="X337" s="25"/>
-      <c r="Z337" s="25"/>
-      <c r="AA337" s="25"/>
-      <c r="AB337" s="25"/>
-      <c r="AC337" s="25"/>
-      <c r="AD337" s="25"/>
-      <c r="AE337" s="25"/>
-      <c r="AF337" s="25"/>
-      <c r="AG337" s="25"/>
-      <c r="AH337" s="25"/>
-      <c r="AI337" s="25"/>
-      <c r="AJ337" s="25"/>
-      <c r="AK337" s="25"/>
-      <c r="AM337" s="25"/>
-      <c r="AN337" s="25" t="s">
-        <v>968</v>
-      </c>
-      <c r="AO337" s="25"/>
-      <c r="AP337" s="25" t="s">
-        <v>968</v>
-      </c>
-      <c r="AQ337" s="25"/>
-      <c r="AR337" s="25"/>
-      <c r="AS337" s="25"/>
-      <c r="AT337" s="25"/>
-      <c r="AU337" s="25"/>
-      <c r="AV337" s="25"/>
-      <c r="AW337" s="25"/>
-      <c r="AX337" s="25"/>
-      <c r="AZ337" s="26"/>
-    </row>
-    <row r="338" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A338" s="50">
-        <v>70</v>
-      </c>
-      <c r="B338" s="25"/>
-      <c r="C338" s="25"/>
-      <c r="D338" s="25" t="s">
-        <v>969</v>
-      </c>
-      <c r="E338" s="37"/>
-      <c r="F338" s="25"/>
-      <c r="G338" s="25"/>
-      <c r="H338" s="25"/>
-      <c r="I338" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="J338" s="25"/>
-      <c r="K338" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="L338" s="25"/>
-      <c r="M338" s="25"/>
-      <c r="N338" s="25"/>
-      <c r="O338" s="25"/>
-      <c r="P338" s="25"/>
-      <c r="Q338" s="25"/>
-      <c r="R338" s="25"/>
-      <c r="S338" s="25"/>
-      <c r="T338" s="25"/>
-      <c r="U338" s="25"/>
-      <c r="V338" s="25"/>
-      <c r="W338" s="25"/>
-      <c r="X338" s="25"/>
-      <c r="Z338" s="25"/>
-      <c r="AA338" s="25"/>
-      <c r="AB338" s="25"/>
-      <c r="AC338" s="25"/>
-      <c r="AD338" s="25"/>
-      <c r="AE338" s="25"/>
-      <c r="AF338" s="25"/>
-      <c r="AG338" s="25"/>
-      <c r="AH338" s="25"/>
-      <c r="AI338" s="25"/>
-      <c r="AJ338" s="25"/>
-      <c r="AK338" s="25"/>
-      <c r="AM338" s="25"/>
-      <c r="AN338" s="25" t="s">
-        <v>970</v>
-      </c>
-      <c r="AO338" s="25"/>
-      <c r="AP338" s="25" t="s">
-        <v>970</v>
-      </c>
-      <c r="AQ338" s="25" t="s">
-        <v>970</v>
-      </c>
-      <c r="AR338" s="25"/>
-      <c r="AS338" s="25" t="s">
-        <v>970</v>
-      </c>
-      <c r="AT338" s="25"/>
-      <c r="AU338" s="25"/>
-      <c r="AV338" s="25"/>
-      <c r="AW338" s="25"/>
-      <c r="AX338" s="25"/>
-      <c r="AZ338" s="26"/>
-    </row>
-    <row r="339" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A339" s="50">
-        <v>70</v>
-      </c>
-      <c r="B339" s="25"/>
-      <c r="C339" s="25"/>
-      <c r="D339" s="25" t="s">
-        <v>971</v>
-      </c>
-      <c r="E339" s="37"/>
-      <c r="F339" s="25"/>
-      <c r="G339" s="25"/>
-      <c r="H339" s="25"/>
-      <c r="I339" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="J339" s="25"/>
-      <c r="K339" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="L339" s="25"/>
-      <c r="M339" s="25"/>
-      <c r="N339" s="25"/>
-      <c r="O339" s="25"/>
-      <c r="P339" s="25"/>
-      <c r="Q339" s="25" t="s">
-        <v>608</v>
-      </c>
-      <c r="R339" s="25"/>
-      <c r="S339" s="25" t="s">
-        <v>810</v>
-      </c>
-      <c r="T339" s="25"/>
-      <c r="U339" s="25"/>
-      <c r="V339" s="25"/>
-      <c r="W339" s="25"/>
-      <c r="X339" s="25"/>
-      <c r="Z339" s="25"/>
-      <c r="AA339" s="25"/>
-      <c r="AB339" s="25"/>
-      <c r="AC339" s="25"/>
-      <c r="AD339" s="25"/>
-      <c r="AE339" s="25"/>
-      <c r="AF339" s="25"/>
-      <c r="AG339" s="25"/>
-      <c r="AH339" s="25"/>
-      <c r="AI339" s="25"/>
-      <c r="AJ339" s="25"/>
-      <c r="AK339" s="25"/>
-      <c r="AM339" s="25"/>
-      <c r="AN339" s="25" t="s">
-        <v>972</v>
-      </c>
-      <c r="AO339" s="25"/>
-      <c r="AP339" s="25" t="s">
-        <v>972</v>
-      </c>
-      <c r="AQ339" s="25" t="s">
-        <v>972</v>
-      </c>
-      <c r="AR339" s="25"/>
-      <c r="AS339" s="25" t="s">
-        <v>972</v>
-      </c>
-      <c r="AT339" s="25"/>
-      <c r="AU339" s="25"/>
-      <c r="AV339" s="25"/>
-      <c r="AW339" s="25"/>
-      <c r="AX339" s="25"/>
-      <c r="AZ339" s="26"/>
-    </row>
-    <row r="340" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A340" s="50">
-        <v>70</v>
-      </c>
-      <c r="B340" s="25"/>
-      <c r="C340" s="25"/>
-      <c r="D340" s="25" t="s">
-        <v>973</v>
-      </c>
-      <c r="E340" s="37"/>
-      <c r="F340" s="25"/>
-      <c r="G340" s="25"/>
-      <c r="H340" s="25"/>
-      <c r="I340" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="J340" s="25"/>
-      <c r="K340" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="L340" s="25"/>
-      <c r="M340" s="25"/>
-      <c r="N340" s="25"/>
-      <c r="O340" s="25"/>
-      <c r="P340" s="25"/>
-      <c r="Q340" s="25"/>
-      <c r="R340" s="25"/>
-      <c r="S340" s="25"/>
-      <c r="T340" s="25"/>
-      <c r="U340" s="25"/>
-      <c r="V340" s="25"/>
-      <c r="W340" s="25"/>
-      <c r="X340" s="25"/>
-      <c r="Z340" s="25"/>
-      <c r="AA340" s="25"/>
-      <c r="AB340" s="25"/>
-      <c r="AC340" s="25"/>
-      <c r="AD340" s="25"/>
-      <c r="AE340" s="25"/>
-      <c r="AF340" s="25"/>
-      <c r="AG340" s="25"/>
-      <c r="AH340" s="25"/>
-      <c r="AI340" s="25"/>
-      <c r="AJ340" s="25"/>
-      <c r="AK340" s="25"/>
-      <c r="AM340" s="25"/>
-      <c r="AN340" s="25" t="s">
-        <v>974</v>
-      </c>
-      <c r="AO340" s="25"/>
-      <c r="AP340" s="25" t="s">
-        <v>974</v>
-      </c>
-      <c r="AQ340" s="25"/>
-      <c r="AR340" s="25"/>
-      <c r="AS340" s="25"/>
-      <c r="AT340" s="25"/>
-      <c r="AU340" s="25"/>
-      <c r="AV340" s="25"/>
-      <c r="AW340" s="25"/>
-      <c r="AX340" s="25"/>
-      <c r="AZ340" s="26"/>
-    </row>
-    <row r="341" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A341" s="50">
-        <v>70</v>
-      </c>
-      <c r="B341" s="25"/>
-      <c r="C341" s="25"/>
-      <c r="D341" s="25" t="s">
-        <v>975</v>
-      </c>
-      <c r="E341" s="37"/>
-      <c r="F341" s="25"/>
-      <c r="G341" s="25"/>
-      <c r="H341" s="25"/>
-      <c r="I341" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="J341" s="25"/>
-      <c r="K341" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="L341" s="25"/>
-      <c r="M341" s="25"/>
-      <c r="N341" s="25"/>
-      <c r="O341" s="25"/>
-      <c r="P341" s="25"/>
-      <c r="Q341" s="25"/>
-      <c r="R341" s="25"/>
-      <c r="S341" s="25"/>
-      <c r="T341" s="25"/>
-      <c r="U341" s="25"/>
-      <c r="V341" s="25"/>
-      <c r="W341" s="25"/>
-      <c r="X341" s="25"/>
-      <c r="Z341" s="25"/>
-      <c r="AA341" s="25"/>
-      <c r="AB341" s="25"/>
-      <c r="AC341" s="25"/>
-      <c r="AD341" s="25"/>
-      <c r="AE341" s="25"/>
-      <c r="AF341" s="25"/>
-      <c r="AG341" s="25"/>
-      <c r="AH341" s="25"/>
-      <c r="AI341" s="25"/>
-      <c r="AJ341" s="25"/>
-      <c r="AK341" s="25"/>
-      <c r="AM341" s="25"/>
-      <c r="AN341" s="25" t="s">
-        <v>976</v>
-      </c>
-      <c r="AO341" s="25"/>
-      <c r="AP341" s="25" t="s">
-        <v>976</v>
-      </c>
-      <c r="AQ341" s="25"/>
-      <c r="AR341" s="25"/>
-      <c r="AS341" s="25"/>
-      <c r="AT341" s="25"/>
-      <c r="AU341" s="25"/>
-      <c r="AV341" s="25"/>
-      <c r="AW341" s="25"/>
-      <c r="AX341" s="25"/>
-      <c r="AZ341" s="26"/>
-    </row>
-    <row r="342" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A342" s="50">
-        <v>70</v>
-      </c>
-      <c r="B342" s="25"/>
-      <c r="C342" s="25"/>
-      <c r="D342" s="25" t="s">
-        <v>977</v>
-      </c>
-      <c r="E342" s="37"/>
-      <c r="F342" s="25"/>
-      <c r="G342" s="25"/>
-      <c r="H342" s="25"/>
-      <c r="I342" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="J342" s="25"/>
-      <c r="K342" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="L342" s="25"/>
-      <c r="M342" s="25"/>
-      <c r="N342" s="25"/>
-      <c r="O342" s="25"/>
-      <c r="P342" s="25"/>
-      <c r="Q342" s="25"/>
-      <c r="R342" s="25"/>
-      <c r="S342" s="25"/>
-      <c r="T342" s="25"/>
-      <c r="U342" s="25"/>
-      <c r="V342" s="25"/>
-      <c r="W342" s="25"/>
-      <c r="X342" s="25"/>
-      <c r="Z342" s="25"/>
-      <c r="AA342" s="25"/>
-      <c r="AB342" s="25"/>
-      <c r="AC342" s="25"/>
-      <c r="AD342" s="25"/>
-      <c r="AE342" s="25"/>
-      <c r="AF342" s="25"/>
-      <c r="AG342" s="25"/>
-      <c r="AH342" s="25"/>
-      <c r="AI342" s="25"/>
-      <c r="AJ342" s="25"/>
-      <c r="AK342" s="25"/>
-      <c r="AM342" s="25"/>
-      <c r="AN342" s="25"/>
-      <c r="AO342" s="25"/>
-      <c r="AP342" s="25"/>
-      <c r="AQ342" s="25"/>
-      <c r="AR342" s="25"/>
-      <c r="AS342" s="25"/>
-      <c r="AT342" s="25"/>
-      <c r="AU342" s="25"/>
-      <c r="AV342" s="25"/>
-      <c r="AW342" s="25"/>
-      <c r="AX342" s="25"/>
-      <c r="AZ342" s="26"/>
-    </row>
-    <row r="343" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A343" s="50">
-        <v>70</v>
-      </c>
-      <c r="B343" s="25"/>
-      <c r="C343" s="25"/>
-      <c r="D343" s="25" t="s">
-        <v>978</v>
-      </c>
-      <c r="E343" s="37"/>
-      <c r="F343" s="25"/>
-      <c r="G343" s="25"/>
-      <c r="H343" s="25"/>
-      <c r="I343" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="J343" s="25"/>
-      <c r="K343" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="L343" s="25"/>
-      <c r="M343" s="25"/>
-      <c r="N343" s="25"/>
-      <c r="O343" s="25"/>
-      <c r="P343" s="25"/>
-      <c r="Q343" s="25"/>
-      <c r="R343" s="25"/>
-      <c r="S343" s="25"/>
-      <c r="T343" s="25"/>
-      <c r="U343" s="25"/>
-      <c r="V343" s="25"/>
-      <c r="W343" s="25"/>
-      <c r="X343" s="25"/>
-      <c r="Z343" s="25"/>
-      <c r="AA343" s="25"/>
-      <c r="AB343" s="25"/>
-      <c r="AC343" s="25"/>
-      <c r="AD343" s="25"/>
-      <c r="AE343" s="25"/>
-      <c r="AF343" s="25"/>
-      <c r="AG343" s="25"/>
-      <c r="AH343" s="25"/>
-      <c r="AI343" s="25"/>
-      <c r="AJ343" s="25"/>
-      <c r="AK343" s="25"/>
-      <c r="AM343" s="25"/>
-      <c r="AN343" s="25" t="s">
-        <v>979</v>
-      </c>
-      <c r="AO343" s="25"/>
-      <c r="AP343" s="25" t="s">
-        <v>979</v>
-      </c>
-      <c r="AQ343" s="25"/>
-      <c r="AR343" s="25"/>
-      <c r="AS343" s="25"/>
-      <c r="AT343" s="25"/>
-      <c r="AU343" s="25"/>
-      <c r="AV343" s="25"/>
-      <c r="AW343" s="25"/>
-      <c r="AX343" s="25"/>
-      <c r="AZ343" s="26"/>
-    </row>
-    <row r="344" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A344" s="50">
-        <v>70</v>
-      </c>
-      <c r="B344" s="25"/>
-      <c r="C344" s="25"/>
-      <c r="D344" s="25" t="s">
-        <v>980</v>
-      </c>
-      <c r="E344" s="37"/>
-      <c r="F344" s="25"/>
-      <c r="G344" s="25"/>
-      <c r="H344" s="25"/>
-      <c r="I344" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="J344" s="25"/>
-      <c r="K344" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="L344" s="25"/>
-      <c r="M344" s="25"/>
-      <c r="N344" s="25"/>
-      <c r="O344" s="25"/>
-      <c r="P344" s="25"/>
-      <c r="Q344" s="25"/>
-      <c r="R344" s="25"/>
-      <c r="S344" s="25"/>
-      <c r="T344" s="25"/>
-      <c r="U344" s="25"/>
-      <c r="V344" s="25"/>
-      <c r="W344" s="25"/>
-      <c r="X344" s="25"/>
-      <c r="Z344" s="25"/>
-      <c r="AA344" s="25"/>
-      <c r="AB344" s="25"/>
-      <c r="AC344" s="25"/>
-      <c r="AD344" s="25"/>
-      <c r="AE344" s="25"/>
-      <c r="AF344" s="25"/>
-      <c r="AG344" s="25"/>
-      <c r="AH344" s="25"/>
-      <c r="AI344" s="25"/>
-      <c r="AJ344" s="25"/>
-      <c r="AK344" s="25"/>
-      <c r="AM344" s="25"/>
-      <c r="AN344" s="25" t="s">
-        <v>981</v>
-      </c>
-      <c r="AO344" s="25"/>
-      <c r="AP344" s="25" t="s">
-        <v>981</v>
-      </c>
-      <c r="AQ344" s="25"/>
-      <c r="AR344" s="25"/>
-      <c r="AS344" s="25"/>
-      <c r="AT344" s="25"/>
-      <c r="AU344" s="25"/>
-      <c r="AV344" s="25"/>
-      <c r="AW344" s="25"/>
-      <c r="AX344" s="25"/>
-      <c r="AZ344" s="26"/>
-    </row>
-    <row r="345" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A345" s="50">
-        <v>70</v>
-      </c>
-      <c r="B345" s="25"/>
-      <c r="C345" s="25"/>
-      <c r="D345" s="25" t="s">
-        <v>983</v>
-      </c>
-      <c r="E345" s="37"/>
-      <c r="F345" s="25"/>
-      <c r="G345" s="25"/>
-      <c r="H345" s="25"/>
-      <c r="I345" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="J345" s="25"/>
-      <c r="K345" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="L345" s="25"/>
-      <c r="M345" s="25"/>
-      <c r="N345" s="25"/>
-      <c r="O345" s="25"/>
-      <c r="P345" s="25"/>
-      <c r="Q345" s="25" t="s">
-        <v>1399</v>
-      </c>
-      <c r="R345" s="25"/>
-      <c r="S345" s="25" t="s">
-        <v>811</v>
-      </c>
-      <c r="T345" s="25"/>
-      <c r="U345" s="25" t="s">
-        <v>269</v>
-      </c>
-      <c r="V345" s="25"/>
-      <c r="W345" s="25"/>
-      <c r="X345" s="25"/>
-      <c r="Z345" s="25"/>
-      <c r="AA345" s="25"/>
-      <c r="AB345" s="25"/>
-      <c r="AC345" s="25"/>
-      <c r="AD345" s="25"/>
-      <c r="AE345" s="25"/>
-      <c r="AF345" s="25"/>
-      <c r="AG345" s="25"/>
-      <c r="AH345" s="25"/>
-      <c r="AI345" s="25"/>
-      <c r="AJ345" s="25"/>
-      <c r="AK345" s="25"/>
-      <c r="AM345" s="25"/>
-      <c r="AN345" s="25" t="s">
-        <v>984</v>
-      </c>
-      <c r="AO345" s="25"/>
-      <c r="AP345" s="25" t="s">
-        <v>984</v>
-      </c>
-      <c r="AQ345" s="25" t="s">
-        <v>984</v>
-      </c>
-      <c r="AR345" s="25"/>
-      <c r="AS345" s="25" t="s">
-        <v>984</v>
-      </c>
-      <c r="AT345" s="25"/>
-      <c r="AU345" s="25"/>
-      <c r="AV345" s="25"/>
-      <c r="AW345" s="25"/>
-      <c r="AX345" s="25"/>
-      <c r="AZ345" s="26"/>
-    </row>
-    <row r="346" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A346" s="50">
-        <v>70</v>
-      </c>
-      <c r="B346" s="25"/>
-      <c r="C346" s="25"/>
-      <c r="D346" s="25" t="s">
-        <v>985</v>
-      </c>
-      <c r="E346" s="37"/>
-      <c r="F346" s="25"/>
-      <c r="G346" s="25"/>
-      <c r="H346" s="25"/>
-      <c r="I346" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="J346" s="25"/>
-      <c r="K346" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="L346" s="25"/>
-      <c r="M346" s="25"/>
-      <c r="N346" s="25"/>
-      <c r="O346" s="25"/>
-      <c r="P346" s="25"/>
-      <c r="Q346" s="25"/>
-      <c r="R346" s="25"/>
-      <c r="S346" s="25"/>
-      <c r="T346" s="25"/>
-      <c r="U346" s="25"/>
-      <c r="V346" s="25"/>
-      <c r="W346" s="25"/>
-      <c r="X346" s="25"/>
-      <c r="Z346" s="25"/>
-      <c r="AA346" s="25"/>
-      <c r="AB346" s="25"/>
-      <c r="AC346" s="25"/>
-      <c r="AD346" s="25"/>
-      <c r="AE346" s="25"/>
-      <c r="AF346" s="25"/>
-      <c r="AG346" s="25"/>
-      <c r="AH346" s="25"/>
-      <c r="AI346" s="25"/>
-      <c r="AJ346" s="25"/>
-      <c r="AK346" s="25"/>
-      <c r="AM346" s="25"/>
-      <c r="AN346" s="25" t="s">
-        <v>811</v>
-      </c>
-      <c r="AO346" s="25"/>
-      <c r="AP346" s="25" t="s">
-        <v>811</v>
-      </c>
-      <c r="AQ346" s="25"/>
-      <c r="AR346" s="25"/>
-      <c r="AS346" s="25"/>
-      <c r="AT346" s="25"/>
-      <c r="AU346" s="25"/>
-      <c r="AV346" s="25"/>
-      <c r="AW346" s="25"/>
-      <c r="AX346" s="25"/>
-      <c r="AZ346" s="26"/>
+      <c r="AO346" s="65"/>
+      <c r="AP346" s="65"/>
+      <c r="AQ346" s="65"/>
+      <c r="AR346" s="65"/>
+      <c r="AS346" s="65"/>
+      <c r="AT346" s="65"/>
+      <c r="AU346" s="65"/>
+      <c r="AV346" s="65"/>
+      <c r="AW346" s="65"/>
+      <c r="AX346" s="65"/>
+      <c r="AZ346" s="68"/>
     </row>
     <row r="347" spans="1:52" s="4" customFormat="1" ht="15.75" customHeight="1">
       <c r="A347" s="50">
@@ -45532,7 +45500,7 @@
         <v>248</v>
       </c>
       <c r="L402" s="50" t="s">
-        <v>2366</v>
+        <v>2364</v>
       </c>
       <c r="M402" s="50"/>
       <c r="N402" s="50"/>
@@ -63080,20 +63048,20 @@
       <c r="B623" s="25"/>
       <c r="C623" s="25"/>
       <c r="D623" s="25" t="s">
-        <v>2381</v>
+        <v>2379</v>
       </c>
       <c r="E623" s="37" t="s">
-        <v>2379</v>
+        <v>2377</v>
       </c>
       <c r="F623" s="25" t="s">
-        <v>2380</v>
+        <v>2378</v>
       </c>
       <c r="G623" s="25" t="s">
         <v>2</v>
       </c>
       <c r="H623" s="25"/>
       <c r="I623" s="25" t="s">
-        <v>2381</v>
+        <v>2379</v>
       </c>
       <c r="J623" s="25"/>
       <c r="K623" s="25" t="s">
@@ -64865,133 +64833,133 @@
     <mergeCell ref="I5:J5"/>
   </mergeCells>
   <phoneticPr fontId="5"/>
-  <conditionalFormatting sqref="V279:X282 V325:X328 V330:X331 V335:X346">
-    <cfRule type="expression" dxfId="25" priority="44">
+  <conditionalFormatting sqref="V279:X282 V325:X325 V343:X344 V327:X341">
+    <cfRule type="expression" dxfId="25" priority="45">
       <formula>$A279=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V348:X348">
-    <cfRule type="expression" dxfId="24" priority="40">
+    <cfRule type="expression" dxfId="24" priority="41">
       <formula>$A348=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V350:X350">
-    <cfRule type="expression" dxfId="23" priority="39">
+    <cfRule type="expression" dxfId="23" priority="40">
       <formula>$A350=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V352:X352">
-    <cfRule type="expression" dxfId="22" priority="38">
+    <cfRule type="expression" dxfId="22" priority="39">
       <formula>$A352=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V354:X354">
-    <cfRule type="expression" dxfId="21" priority="37">
+    <cfRule type="expression" dxfId="21" priority="38">
       <formula>$A354=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V358:X358">
-    <cfRule type="expression" dxfId="20" priority="36">
+    <cfRule type="expression" dxfId="20" priority="37">
       <formula>$A358=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V360:X360">
-    <cfRule type="expression" dxfId="19" priority="35">
+    <cfRule type="expression" dxfId="19" priority="36">
       <formula>$A360=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V362:X362">
-    <cfRule type="expression" dxfId="18" priority="8">
+    <cfRule type="expression" dxfId="18" priority="9">
       <formula>$A362=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V364:X364">
-    <cfRule type="expression" dxfId="17" priority="7">
+    <cfRule type="expression" dxfId="17" priority="8">
       <formula>$A364=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V366:X366">
-    <cfRule type="expression" dxfId="16" priority="6">
+    <cfRule type="expression" dxfId="16" priority="7">
       <formula>$A366=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V368:X368 V370:X370 V372:X372 V374:X374">
-    <cfRule type="expression" dxfId="15" priority="34">
+    <cfRule type="expression" dxfId="15" priority="35">
       <formula>$A368=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V380:X387">
-    <cfRule type="expression" dxfId="14" priority="32">
+    <cfRule type="expression" dxfId="14" priority="33">
       <formula>$A380=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V390:X391">
-    <cfRule type="expression" dxfId="13" priority="30">
+    <cfRule type="expression" dxfId="13" priority="31">
       <formula>$A390=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V397:X398">
-    <cfRule type="expression" dxfId="12" priority="26">
+    <cfRule type="expression" dxfId="12" priority="27">
       <formula>$A397=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V400:X401">
-    <cfRule type="expression" dxfId="11" priority="24">
+    <cfRule type="expression" dxfId="11" priority="25">
       <formula>$A400=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V403:X420">
-    <cfRule type="expression" dxfId="10" priority="12">
+    <cfRule type="expression" dxfId="10" priority="13">
       <formula>$A403=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V430:X447">
-    <cfRule type="expression" dxfId="9" priority="20">
+    <cfRule type="expression" dxfId="9" priority="21">
       <formula>$A430=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V475:X477">
-    <cfRule type="expression" dxfId="8" priority="18">
+    <cfRule type="expression" dxfId="8" priority="19">
       <formula>$A475=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V479:X481">
-    <cfRule type="expression" dxfId="7" priority="16">
+    <cfRule type="expression" dxfId="7" priority="17">
       <formula>$A479=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V483:X483">
-    <cfRule type="expression" dxfId="6" priority="11">
+    <cfRule type="expression" dxfId="6" priority="12">
       <formula>$A483=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V526:X526">
-    <cfRule type="expression" dxfId="5" priority="15">
+    <cfRule type="expression" dxfId="5" priority="16">
       <formula>$A526=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V532:X532 V534:X534 V536:X536 V538:X538 V540:X540 V542:X542 V544:X544 V550:X550 V552:X552">
-    <cfRule type="expression" dxfId="4" priority="14">
+    <cfRule type="expression" dxfId="4" priority="15">
       <formula>$A532=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V546:X546">
-    <cfRule type="expression" dxfId="3" priority="10">
+    <cfRule type="expression" dxfId="3" priority="11">
       <formula>$A546=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V548:X548">
-    <cfRule type="expression" dxfId="2" priority="9">
+    <cfRule type="expression" dxfId="2" priority="10">
       <formula>$A548=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V561:X561">
-    <cfRule type="expression" dxfId="1" priority="13">
+    <cfRule type="expression" dxfId="1" priority="14">
       <formula>$A561=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X527:X530">
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>$A527=""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -65023,65 +64991,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:57" ht="38.25" customHeight="1" thickBot="1">
-      <c r="A1" s="111" t="s">
+      <c r="A1" s="107" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
-      <c r="V1" s="112"/>
-      <c r="W1" s="112"/>
-      <c r="X1" s="112"/>
-      <c r="Y1" s="112"/>
-      <c r="Z1" s="112"/>
-      <c r="AA1" s="112"/>
-      <c r="AB1" s="112"/>
-      <c r="AC1" s="112"/>
-      <c r="AD1" s="112"/>
-      <c r="AE1" s="112"/>
-      <c r="AF1" s="112"/>
-      <c r="AG1" s="112"/>
-      <c r="AH1" s="112"/>
-      <c r="AI1" s="112"/>
-      <c r="AJ1" s="112"/>
-      <c r="AK1" s="112"/>
-      <c r="AL1" s="112"/>
-      <c r="AM1" s="112"/>
-      <c r="AN1" s="112"/>
-      <c r="AO1" s="112"/>
-      <c r="AP1" s="112"/>
-      <c r="AQ1" s="112"/>
-      <c r="AR1" s="112"/>
-      <c r="AS1" s="112"/>
-      <c r="AT1" s="112"/>
-      <c r="AU1" s="112"/>
-      <c r="AV1" s="112"/>
-      <c r="AW1" s="112"/>
-      <c r="AX1" s="112"/>
-      <c r="AY1" s="112"/>
-      <c r="AZ1" s="112"/>
-      <c r="BA1" s="112"/>
-      <c r="BB1" s="112"/>
-      <c r="BC1" s="112"/>
-      <c r="BD1" s="112"/>
-      <c r="BE1" s="113"/>
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="108"/>
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
+      <c r="V1" s="108"/>
+      <c r="W1" s="108"/>
+      <c r="X1" s="108"/>
+      <c r="Y1" s="108"/>
+      <c r="Z1" s="108"/>
+      <c r="AA1" s="108"/>
+      <c r="AB1" s="108"/>
+      <c r="AC1" s="108"/>
+      <c r="AD1" s="108"/>
+      <c r="AE1" s="108"/>
+      <c r="AF1" s="108"/>
+      <c r="AG1" s="108"/>
+      <c r="AH1" s="108"/>
+      <c r="AI1" s="108"/>
+      <c r="AJ1" s="108"/>
+      <c r="AK1" s="108"/>
+      <c r="AL1" s="108"/>
+      <c r="AM1" s="108"/>
+      <c r="AN1" s="108"/>
+      <c r="AO1" s="108"/>
+      <c r="AP1" s="108"/>
+      <c r="AQ1" s="108"/>
+      <c r="AR1" s="108"/>
+      <c r="AS1" s="108"/>
+      <c r="AT1" s="108"/>
+      <c r="AU1" s="108"/>
+      <c r="AV1" s="108"/>
+      <c r="AW1" s="108"/>
+      <c r="AX1" s="108"/>
+      <c r="AY1" s="108"/>
+      <c r="AZ1" s="108"/>
+      <c r="BA1" s="108"/>
+      <c r="BB1" s="108"/>
+      <c r="BC1" s="108"/>
+      <c r="BD1" s="108"/>
+      <c r="BE1" s="109"/>
     </row>
     <row r="2" spans="1:57" ht="12" customHeight="1" thickBot="1">
       <c r="A2" s="14"/>
@@ -65128,145 +65096,145 @@
       <c r="AP2" s="14"/>
     </row>
     <row r="3" spans="1:57" ht="15" customHeight="1" thickBot="1">
-      <c r="A3" s="124" t="s">
+      <c r="A3" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="115"/>
-      <c r="C3" s="115"/>
-      <c r="D3" s="115"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="115"/>
-      <c r="G3" s="116"/>
-      <c r="H3" s="114" t="s">
+      <c r="B3" s="91"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="91"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="110" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="115"/>
-      <c r="J3" s="115"/>
-      <c r="K3" s="115"/>
-      <c r="L3" s="115"/>
-      <c r="M3" s="115"/>
-      <c r="N3" s="116"/>
-      <c r="O3" s="114" t="s">
+      <c r="I3" s="91"/>
+      <c r="J3" s="91"/>
+      <c r="K3" s="91"/>
+      <c r="L3" s="91"/>
+      <c r="M3" s="91"/>
+      <c r="N3" s="92"/>
+      <c r="O3" s="110" t="s">
         <v>9</v>
       </c>
-      <c r="P3" s="117"/>
-      <c r="Q3" s="117"/>
-      <c r="R3" s="117"/>
-      <c r="S3" s="117"/>
-      <c r="T3" s="117"/>
-      <c r="U3" s="117"/>
-      <c r="V3" s="117"/>
-      <c r="W3" s="117"/>
-      <c r="X3" s="117"/>
-      <c r="Y3" s="117"/>
-      <c r="Z3" s="117"/>
-      <c r="AA3" s="117"/>
-      <c r="AB3" s="117"/>
-      <c r="AC3" s="117"/>
-      <c r="AD3" s="117"/>
-      <c r="AE3" s="117"/>
-      <c r="AF3" s="117"/>
-      <c r="AG3" s="117"/>
-      <c r="AH3" s="117"/>
-      <c r="AI3" s="117"/>
-      <c r="AJ3" s="117"/>
-      <c r="AK3" s="117"/>
-      <c r="AL3" s="117"/>
-      <c r="AM3" s="117"/>
-      <c r="AN3" s="117"/>
-      <c r="AO3" s="117"/>
-      <c r="AP3" s="118"/>
-      <c r="AQ3" s="114" t="s">
+      <c r="P3" s="111"/>
+      <c r="Q3" s="111"/>
+      <c r="R3" s="111"/>
+      <c r="S3" s="111"/>
+      <c r="T3" s="111"/>
+      <c r="U3" s="111"/>
+      <c r="V3" s="111"/>
+      <c r="W3" s="111"/>
+      <c r="X3" s="111"/>
+      <c r="Y3" s="111"/>
+      <c r="Z3" s="111"/>
+      <c r="AA3" s="111"/>
+      <c r="AB3" s="111"/>
+      <c r="AC3" s="111"/>
+      <c r="AD3" s="111"/>
+      <c r="AE3" s="111"/>
+      <c r="AF3" s="111"/>
+      <c r="AG3" s="111"/>
+      <c r="AH3" s="111"/>
+      <c r="AI3" s="111"/>
+      <c r="AJ3" s="111"/>
+      <c r="AK3" s="111"/>
+      <c r="AL3" s="111"/>
+      <c r="AM3" s="111"/>
+      <c r="AN3" s="111"/>
+      <c r="AO3" s="111"/>
+      <c r="AP3" s="112"/>
+      <c r="AQ3" s="110" t="s">
         <v>10</v>
       </c>
-      <c r="AR3" s="119"/>
-      <c r="AS3" s="119"/>
-      <c r="AT3" s="119"/>
-      <c r="AU3" s="119"/>
-      <c r="AV3" s="119"/>
-      <c r="AW3" s="119"/>
-      <c r="AX3" s="119"/>
-      <c r="AY3" s="119"/>
-      <c r="AZ3" s="119"/>
-      <c r="BA3" s="119"/>
-      <c r="BB3" s="119"/>
-      <c r="BC3" s="119"/>
-      <c r="BD3" s="119"/>
-      <c r="BE3" s="120"/>
+      <c r="AR3" s="113"/>
+      <c r="AS3" s="113"/>
+      <c r="AT3" s="113"/>
+      <c r="AU3" s="113"/>
+      <c r="AV3" s="113"/>
+      <c r="AW3" s="113"/>
+      <c r="AX3" s="113"/>
+      <c r="AY3" s="113"/>
+      <c r="AZ3" s="113"/>
+      <c r="BA3" s="113"/>
+      <c r="BB3" s="113"/>
+      <c r="BC3" s="113"/>
+      <c r="BD3" s="113"/>
+      <c r="BE3" s="114"/>
     </row>
     <row r="4" spans="1:57" ht="15" customHeight="1">
-      <c r="A4" s="121">
+      <c r="A4" s="115">
         <v>1</v>
       </c>
-      <c r="B4" s="122"/>
-      <c r="C4" s="122"/>
-      <c r="D4" s="122"/>
-      <c r="E4" s="122"/>
-      <c r="F4" s="122"/>
-      <c r="G4" s="123"/>
-      <c r="H4" s="104"/>
-      <c r="I4" s="105"/>
-      <c r="J4" s="105"/>
-      <c r="K4" s="105"/>
-      <c r="L4" s="105"/>
-      <c r="M4" s="105"/>
-      <c r="N4" s="106"/>
-      <c r="O4" s="104" t="s">
+      <c r="B4" s="116"/>
+      <c r="C4" s="116"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="119"/>
+      <c r="L4" s="119"/>
+      <c r="M4" s="119"/>
+      <c r="N4" s="120"/>
+      <c r="O4" s="118" t="s">
         <v>11</v>
       </c>
-      <c r="P4" s="107"/>
-      <c r="Q4" s="107"/>
-      <c r="R4" s="107"/>
-      <c r="S4" s="107"/>
-      <c r="T4" s="107"/>
-      <c r="U4" s="107"/>
-      <c r="V4" s="107"/>
-      <c r="W4" s="107"/>
-      <c r="X4" s="107"/>
-      <c r="Y4" s="107"/>
-      <c r="Z4" s="107"/>
-      <c r="AA4" s="107"/>
-      <c r="AB4" s="107"/>
-      <c r="AC4" s="107"/>
-      <c r="AD4" s="107"/>
-      <c r="AE4" s="107"/>
-      <c r="AF4" s="107"/>
-      <c r="AG4" s="107"/>
-      <c r="AH4" s="107"/>
-      <c r="AI4" s="107"/>
-      <c r="AJ4" s="107"/>
-      <c r="AK4" s="107"/>
-      <c r="AL4" s="107"/>
-      <c r="AM4" s="107"/>
-      <c r="AN4" s="107"/>
-      <c r="AO4" s="107"/>
-      <c r="AP4" s="108"/>
-      <c r="AQ4" s="109"/>
-      <c r="AR4" s="107"/>
-      <c r="AS4" s="107"/>
-      <c r="AT4" s="107"/>
-      <c r="AU4" s="107"/>
-      <c r="AV4" s="107"/>
-      <c r="AW4" s="107"/>
-      <c r="AX4" s="107"/>
-      <c r="AY4" s="107"/>
-      <c r="AZ4" s="107"/>
-      <c r="BA4" s="107"/>
-      <c r="BB4" s="107"/>
-      <c r="BC4" s="107"/>
-      <c r="BD4" s="107"/>
-      <c r="BE4" s="110"/>
+      <c r="P4" s="121"/>
+      <c r="Q4" s="121"/>
+      <c r="R4" s="121"/>
+      <c r="S4" s="121"/>
+      <c r="T4" s="121"/>
+      <c r="U4" s="121"/>
+      <c r="V4" s="121"/>
+      <c r="W4" s="121"/>
+      <c r="X4" s="121"/>
+      <c r="Y4" s="121"/>
+      <c r="Z4" s="121"/>
+      <c r="AA4" s="121"/>
+      <c r="AB4" s="121"/>
+      <c r="AC4" s="121"/>
+      <c r="AD4" s="121"/>
+      <c r="AE4" s="121"/>
+      <c r="AF4" s="121"/>
+      <c r="AG4" s="121"/>
+      <c r="AH4" s="121"/>
+      <c r="AI4" s="121"/>
+      <c r="AJ4" s="121"/>
+      <c r="AK4" s="121"/>
+      <c r="AL4" s="121"/>
+      <c r="AM4" s="121"/>
+      <c r="AN4" s="121"/>
+      <c r="AO4" s="121"/>
+      <c r="AP4" s="122"/>
+      <c r="AQ4" s="123"/>
+      <c r="AR4" s="121"/>
+      <c r="AS4" s="121"/>
+      <c r="AT4" s="121"/>
+      <c r="AU4" s="121"/>
+      <c r="AV4" s="121"/>
+      <c r="AW4" s="121"/>
+      <c r="AX4" s="121"/>
+      <c r="AY4" s="121"/>
+      <c r="AZ4" s="121"/>
+      <c r="BA4" s="121"/>
+      <c r="BB4" s="121"/>
+      <c r="BC4" s="121"/>
+      <c r="BD4" s="121"/>
+      <c r="BE4" s="124"/>
     </row>
     <row r="5" spans="1:57" ht="105.75" customHeight="1">
-      <c r="A5" s="84">
+      <c r="A5" s="104">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B5" s="85"/>
-      <c r="C5" s="85"/>
-      <c r="D5" s="85"/>
-      <c r="E5" s="85"/>
-      <c r="F5" s="85"/>
-      <c r="G5" s="86"/>
+      <c r="B5" s="105"/>
+      <c r="C5" s="105"/>
+      <c r="D5" s="105"/>
+      <c r="E5" s="105"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="106"/>
       <c r="H5" s="87" t="s">
         <v>1788</v>
       </c>
@@ -65279,61 +65247,61 @@
       <c r="O5" s="87" t="s">
         <v>1790</v>
       </c>
-      <c r="P5" s="90"/>
-      <c r="Q5" s="90"/>
-      <c r="R5" s="90"/>
-      <c r="S5" s="90"/>
-      <c r="T5" s="90"/>
-      <c r="U5" s="90"/>
-      <c r="V5" s="90"/>
-      <c r="W5" s="90"/>
-      <c r="X5" s="90"/>
-      <c r="Y5" s="90"/>
-      <c r="Z5" s="90"/>
-      <c r="AA5" s="90"/>
-      <c r="AB5" s="90"/>
-      <c r="AC5" s="90"/>
-      <c r="AD5" s="90"/>
-      <c r="AE5" s="90"/>
-      <c r="AF5" s="90"/>
-      <c r="AG5" s="90"/>
-      <c r="AH5" s="90"/>
-      <c r="AI5" s="90"/>
-      <c r="AJ5" s="90"/>
-      <c r="AK5" s="90"/>
-      <c r="AL5" s="90"/>
-      <c r="AM5" s="90"/>
-      <c r="AN5" s="90"/>
-      <c r="AO5" s="90"/>
-      <c r="AP5" s="91"/>
-      <c r="AQ5" s="95" t="s">
+      <c r="P5" s="85"/>
+      <c r="Q5" s="85"/>
+      <c r="R5" s="85"/>
+      <c r="S5" s="85"/>
+      <c r="T5" s="85"/>
+      <c r="U5" s="85"/>
+      <c r="V5" s="85"/>
+      <c r="W5" s="85"/>
+      <c r="X5" s="85"/>
+      <c r="Y5" s="85"/>
+      <c r="Z5" s="85"/>
+      <c r="AA5" s="85"/>
+      <c r="AB5" s="85"/>
+      <c r="AC5" s="85"/>
+      <c r="AD5" s="85"/>
+      <c r="AE5" s="85"/>
+      <c r="AF5" s="85"/>
+      <c r="AG5" s="85"/>
+      <c r="AH5" s="85"/>
+      <c r="AI5" s="85"/>
+      <c r="AJ5" s="85"/>
+      <c r="AK5" s="85"/>
+      <c r="AL5" s="85"/>
+      <c r="AM5" s="85"/>
+      <c r="AN5" s="85"/>
+      <c r="AO5" s="85"/>
+      <c r="AP5" s="93"/>
+      <c r="AQ5" s="84" t="s">
         <v>1789</v>
       </c>
-      <c r="AR5" s="90"/>
-      <c r="AS5" s="90"/>
-      <c r="AT5" s="90"/>
-      <c r="AU5" s="90"/>
-      <c r="AV5" s="90"/>
-      <c r="AW5" s="90"/>
-      <c r="AX5" s="90"/>
-      <c r="AY5" s="90"/>
-      <c r="AZ5" s="90"/>
-      <c r="BA5" s="90"/>
-      <c r="BB5" s="90"/>
-      <c r="BC5" s="90"/>
-      <c r="BD5" s="90"/>
-      <c r="BE5" s="96"/>
+      <c r="AR5" s="85"/>
+      <c r="AS5" s="85"/>
+      <c r="AT5" s="85"/>
+      <c r="AU5" s="85"/>
+      <c r="AV5" s="85"/>
+      <c r="AW5" s="85"/>
+      <c r="AX5" s="85"/>
+      <c r="AY5" s="85"/>
+      <c r="AZ5" s="85"/>
+      <c r="BA5" s="85"/>
+      <c r="BB5" s="85"/>
+      <c r="BC5" s="85"/>
+      <c r="BD5" s="85"/>
+      <c r="BE5" s="86"/>
     </row>
     <row r="6" spans="1:57" ht="36.6" customHeight="1">
-      <c r="A6" s="84">
+      <c r="A6" s="104">
         <v>1.2</v>
       </c>
-      <c r="B6" s="85"/>
-      <c r="C6" s="85"/>
-      <c r="D6" s="85"/>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="86"/>
+      <c r="B6" s="105"/>
+      <c r="C6" s="105"/>
+      <c r="D6" s="105"/>
+      <c r="E6" s="105"/>
+      <c r="F6" s="105"/>
+      <c r="G6" s="106"/>
       <c r="H6" s="87" t="s">
         <v>1814</v>
       </c>
@@ -65346,124 +65314,124 @@
       <c r="O6" s="87" t="s">
         <v>1813</v>
       </c>
-      <c r="P6" s="125"/>
-      <c r="Q6" s="125"/>
-      <c r="R6" s="125"/>
-      <c r="S6" s="125"/>
-      <c r="T6" s="125"/>
-      <c r="U6" s="125"/>
-      <c r="V6" s="125"/>
-      <c r="W6" s="125"/>
-      <c r="X6" s="125"/>
-      <c r="Y6" s="125"/>
-      <c r="Z6" s="125"/>
-      <c r="AA6" s="125"/>
-      <c r="AB6" s="125"/>
-      <c r="AC6" s="125"/>
-      <c r="AD6" s="125"/>
-      <c r="AE6" s="125"/>
-      <c r="AF6" s="125"/>
-      <c r="AG6" s="125"/>
-      <c r="AH6" s="125"/>
-      <c r="AI6" s="125"/>
-      <c r="AJ6" s="125"/>
-      <c r="AK6" s="125"/>
-      <c r="AL6" s="125"/>
-      <c r="AM6" s="125"/>
-      <c r="AN6" s="125"/>
-      <c r="AO6" s="125"/>
-      <c r="AP6" s="126"/>
-      <c r="AQ6" s="95" t="s">
+      <c r="P6" s="94"/>
+      <c r="Q6" s="94"/>
+      <c r="R6" s="94"/>
+      <c r="S6" s="94"/>
+      <c r="T6" s="94"/>
+      <c r="U6" s="94"/>
+      <c r="V6" s="94"/>
+      <c r="W6" s="94"/>
+      <c r="X6" s="94"/>
+      <c r="Y6" s="94"/>
+      <c r="Z6" s="94"/>
+      <c r="AA6" s="94"/>
+      <c r="AB6" s="94"/>
+      <c r="AC6" s="94"/>
+      <c r="AD6" s="94"/>
+      <c r="AE6" s="94"/>
+      <c r="AF6" s="94"/>
+      <c r="AG6" s="94"/>
+      <c r="AH6" s="94"/>
+      <c r="AI6" s="94"/>
+      <c r="AJ6" s="94"/>
+      <c r="AK6" s="94"/>
+      <c r="AL6" s="94"/>
+      <c r="AM6" s="94"/>
+      <c r="AN6" s="94"/>
+      <c r="AO6" s="94"/>
+      <c r="AP6" s="95"/>
+      <c r="AQ6" s="84" t="s">
         <v>1789</v>
       </c>
-      <c r="AR6" s="90"/>
-      <c r="AS6" s="90"/>
-      <c r="AT6" s="90"/>
-      <c r="AU6" s="90"/>
-      <c r="AV6" s="90"/>
-      <c r="AW6" s="90"/>
-      <c r="AX6" s="90"/>
-      <c r="AY6" s="90"/>
-      <c r="AZ6" s="90"/>
-      <c r="BA6" s="90"/>
-      <c r="BB6" s="90"/>
-      <c r="BC6" s="90"/>
-      <c r="BD6" s="90"/>
-      <c r="BE6" s="96"/>
+      <c r="AR6" s="85"/>
+      <c r="AS6" s="85"/>
+      <c r="AT6" s="85"/>
+      <c r="AU6" s="85"/>
+      <c r="AV6" s="85"/>
+      <c r="AW6" s="85"/>
+      <c r="AX6" s="85"/>
+      <c r="AY6" s="85"/>
+      <c r="AZ6" s="85"/>
+      <c r="BA6" s="85"/>
+      <c r="BB6" s="85"/>
+      <c r="BC6" s="85"/>
+      <c r="BD6" s="85"/>
+      <c r="BE6" s="86"/>
     </row>
     <row r="7" spans="1:57" ht="15" customHeight="1">
-      <c r="A7" s="84">
+      <c r="A7" s="104">
         <v>1.3</v>
       </c>
-      <c r="B7" s="85"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="85"/>
-      <c r="G7" s="86"/>
+      <c r="B7" s="105"/>
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="105"/>
+      <c r="F7" s="105"/>
+      <c r="G7" s="106"/>
       <c r="H7" s="87"/>
-      <c r="I7" s="127"/>
-      <c r="J7" s="127"/>
-      <c r="K7" s="127"/>
-      <c r="L7" s="127"/>
-      <c r="M7" s="127"/>
-      <c r="N7" s="128"/>
-      <c r="O7" s="129" t="s">
+      <c r="I7" s="96"/>
+      <c r="J7" s="96"/>
+      <c r="K7" s="96"/>
+      <c r="L7" s="96"/>
+      <c r="M7" s="96"/>
+      <c r="N7" s="97"/>
+      <c r="O7" s="98" t="s">
         <v>2227</v>
       </c>
-      <c r="P7" s="130"/>
-      <c r="Q7" s="130"/>
-      <c r="R7" s="130"/>
-      <c r="S7" s="130"/>
-      <c r="T7" s="130"/>
-      <c r="U7" s="130"/>
-      <c r="V7" s="130"/>
-      <c r="W7" s="130"/>
-      <c r="X7" s="130"/>
-      <c r="Y7" s="130"/>
-      <c r="Z7" s="130"/>
-      <c r="AA7" s="130"/>
-      <c r="AB7" s="130"/>
-      <c r="AC7" s="130"/>
-      <c r="AD7" s="130"/>
-      <c r="AE7" s="130"/>
-      <c r="AF7" s="130"/>
-      <c r="AG7" s="130"/>
-      <c r="AH7" s="130"/>
-      <c r="AI7" s="130"/>
-      <c r="AJ7" s="130"/>
-      <c r="AK7" s="130"/>
-      <c r="AL7" s="130"/>
-      <c r="AM7" s="130"/>
-      <c r="AN7" s="130"/>
-      <c r="AO7" s="130"/>
-      <c r="AP7" s="131"/>
-      <c r="AQ7" s="132" t="s">
+      <c r="P7" s="99"/>
+      <c r="Q7" s="99"/>
+      <c r="R7" s="99"/>
+      <c r="S7" s="99"/>
+      <c r="T7" s="99"/>
+      <c r="U7" s="99"/>
+      <c r="V7" s="99"/>
+      <c r="W7" s="99"/>
+      <c r="X7" s="99"/>
+      <c r="Y7" s="99"/>
+      <c r="Z7" s="99"/>
+      <c r="AA7" s="99"/>
+      <c r="AB7" s="99"/>
+      <c r="AC7" s="99"/>
+      <c r="AD7" s="99"/>
+      <c r="AE7" s="99"/>
+      <c r="AF7" s="99"/>
+      <c r="AG7" s="99"/>
+      <c r="AH7" s="99"/>
+      <c r="AI7" s="99"/>
+      <c r="AJ7" s="99"/>
+      <c r="AK7" s="99"/>
+      <c r="AL7" s="99"/>
+      <c r="AM7" s="99"/>
+      <c r="AN7" s="99"/>
+      <c r="AO7" s="99"/>
+      <c r="AP7" s="100"/>
+      <c r="AQ7" s="101" t="s">
         <v>2228</v>
       </c>
-      <c r="AR7" s="133"/>
-      <c r="AS7" s="133"/>
-      <c r="AT7" s="133"/>
-      <c r="AU7" s="133"/>
-      <c r="AV7" s="133"/>
-      <c r="AW7" s="133"/>
-      <c r="AX7" s="133"/>
-      <c r="AY7" s="133"/>
-      <c r="AZ7" s="133"/>
-      <c r="BA7" s="133"/>
-      <c r="BB7" s="133"/>
-      <c r="BC7" s="133"/>
-      <c r="BD7" s="133"/>
-      <c r="BE7" s="134"/>
+      <c r="AR7" s="102"/>
+      <c r="AS7" s="102"/>
+      <c r="AT7" s="102"/>
+      <c r="AU7" s="102"/>
+      <c r="AV7" s="102"/>
+      <c r="AW7" s="102"/>
+      <c r="AX7" s="102"/>
+      <c r="AY7" s="102"/>
+      <c r="AZ7" s="102"/>
+      <c r="BA7" s="102"/>
+      <c r="BB7" s="102"/>
+      <c r="BC7" s="102"/>
+      <c r="BD7" s="102"/>
+      <c r="BE7" s="103"/>
     </row>
     <row r="8" spans="1:57" ht="15" customHeight="1">
-      <c r="A8" s="84"/>
-      <c r="B8" s="85"/>
-      <c r="C8" s="85"/>
-      <c r="D8" s="85"/>
-      <c r="E8" s="85"/>
-      <c r="F8" s="85"/>
-      <c r="G8" s="86"/>
+      <c r="A8" s="104"/>
+      <c r="B8" s="105"/>
+      <c r="C8" s="105"/>
+      <c r="D8" s="105"/>
+      <c r="E8" s="105"/>
+      <c r="F8" s="105"/>
+      <c r="G8" s="106"/>
       <c r="H8" s="87"/>
       <c r="I8" s="88"/>
       <c r="J8" s="88"/>
@@ -65472,57 +65440,57 @@
       <c r="M8" s="88"/>
       <c r="N8" s="89"/>
       <c r="O8" s="87"/>
-      <c r="P8" s="90"/>
-      <c r="Q8" s="90"/>
-      <c r="R8" s="90"/>
-      <c r="S8" s="90"/>
-      <c r="T8" s="90"/>
-      <c r="U8" s="90"/>
-      <c r="V8" s="90"/>
-      <c r="W8" s="90"/>
-      <c r="X8" s="90"/>
-      <c r="Y8" s="90"/>
-      <c r="Z8" s="90"/>
-      <c r="AA8" s="90"/>
-      <c r="AB8" s="90"/>
-      <c r="AC8" s="90"/>
-      <c r="AD8" s="90"/>
-      <c r="AE8" s="90"/>
-      <c r="AF8" s="90"/>
-      <c r="AG8" s="90"/>
-      <c r="AH8" s="90"/>
-      <c r="AI8" s="90"/>
-      <c r="AJ8" s="90"/>
-      <c r="AK8" s="90"/>
-      <c r="AL8" s="90"/>
-      <c r="AM8" s="90"/>
-      <c r="AN8" s="90"/>
-      <c r="AO8" s="90"/>
-      <c r="AP8" s="91"/>
-      <c r="AQ8" s="95"/>
-      <c r="AR8" s="90"/>
-      <c r="AS8" s="90"/>
-      <c r="AT8" s="90"/>
-      <c r="AU8" s="90"/>
-      <c r="AV8" s="90"/>
-      <c r="AW8" s="90"/>
-      <c r="AX8" s="90"/>
-      <c r="AY8" s="90"/>
-      <c r="AZ8" s="90"/>
-      <c r="BA8" s="90"/>
-      <c r="BB8" s="90"/>
-      <c r="BC8" s="90"/>
-      <c r="BD8" s="90"/>
-      <c r="BE8" s="96"/>
+      <c r="P8" s="85"/>
+      <c r="Q8" s="85"/>
+      <c r="R8" s="85"/>
+      <c r="S8" s="85"/>
+      <c r="T8" s="85"/>
+      <c r="U8" s="85"/>
+      <c r="V8" s="85"/>
+      <c r="W8" s="85"/>
+      <c r="X8" s="85"/>
+      <c r="Y8" s="85"/>
+      <c r="Z8" s="85"/>
+      <c r="AA8" s="85"/>
+      <c r="AB8" s="85"/>
+      <c r="AC8" s="85"/>
+      <c r="AD8" s="85"/>
+      <c r="AE8" s="85"/>
+      <c r="AF8" s="85"/>
+      <c r="AG8" s="85"/>
+      <c r="AH8" s="85"/>
+      <c r="AI8" s="85"/>
+      <c r="AJ8" s="85"/>
+      <c r="AK8" s="85"/>
+      <c r="AL8" s="85"/>
+      <c r="AM8" s="85"/>
+      <c r="AN8" s="85"/>
+      <c r="AO8" s="85"/>
+      <c r="AP8" s="93"/>
+      <c r="AQ8" s="84"/>
+      <c r="AR8" s="85"/>
+      <c r="AS8" s="85"/>
+      <c r="AT8" s="85"/>
+      <c r="AU8" s="85"/>
+      <c r="AV8" s="85"/>
+      <c r="AW8" s="85"/>
+      <c r="AX8" s="85"/>
+      <c r="AY8" s="85"/>
+      <c r="AZ8" s="85"/>
+      <c r="BA8" s="85"/>
+      <c r="BB8" s="85"/>
+      <c r="BC8" s="85"/>
+      <c r="BD8" s="85"/>
+      <c r="BE8" s="86"/>
     </row>
     <row r="9" spans="1:57" ht="15" customHeight="1">
-      <c r="A9" s="84"/>
-      <c r="B9" s="85"/>
-      <c r="C9" s="85"/>
-      <c r="D9" s="85"/>
-      <c r="E9" s="85"/>
-      <c r="F9" s="85"/>
-      <c r="G9" s="86"/>
+      <c r="A9" s="104"/>
+      <c r="B9" s="105"/>
+      <c r="C9" s="105"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="105"/>
+      <c r="F9" s="105"/>
+      <c r="G9" s="106"/>
       <c r="H9" s="87"/>
       <c r="I9" s="88"/>
       <c r="J9" s="88"/>
@@ -65531,57 +65499,57 @@
       <c r="M9" s="88"/>
       <c r="N9" s="89"/>
       <c r="O9" s="87"/>
-      <c r="P9" s="90"/>
-      <c r="Q9" s="90"/>
-      <c r="R9" s="90"/>
-      <c r="S9" s="90"/>
-      <c r="T9" s="90"/>
-      <c r="U9" s="90"/>
-      <c r="V9" s="90"/>
-      <c r="W9" s="90"/>
-      <c r="X9" s="90"/>
-      <c r="Y9" s="90"/>
-      <c r="Z9" s="90"/>
-      <c r="AA9" s="90"/>
-      <c r="AB9" s="90"/>
-      <c r="AC9" s="90"/>
-      <c r="AD9" s="90"/>
-      <c r="AE9" s="90"/>
-      <c r="AF9" s="90"/>
-      <c r="AG9" s="90"/>
-      <c r="AH9" s="90"/>
-      <c r="AI9" s="90"/>
-      <c r="AJ9" s="90"/>
-      <c r="AK9" s="90"/>
-      <c r="AL9" s="90"/>
-      <c r="AM9" s="90"/>
-      <c r="AN9" s="90"/>
-      <c r="AO9" s="90"/>
-      <c r="AP9" s="91"/>
-      <c r="AQ9" s="95"/>
-      <c r="AR9" s="90"/>
-      <c r="AS9" s="90"/>
-      <c r="AT9" s="90"/>
-      <c r="AU9" s="90"/>
-      <c r="AV9" s="90"/>
-      <c r="AW9" s="90"/>
-      <c r="AX9" s="90"/>
-      <c r="AY9" s="90"/>
-      <c r="AZ9" s="90"/>
-      <c r="BA9" s="90"/>
-      <c r="BB9" s="90"/>
-      <c r="BC9" s="90"/>
-      <c r="BD9" s="90"/>
-      <c r="BE9" s="96"/>
+      <c r="P9" s="85"/>
+      <c r="Q9" s="85"/>
+      <c r="R9" s="85"/>
+      <c r="S9" s="85"/>
+      <c r="T9" s="85"/>
+      <c r="U9" s="85"/>
+      <c r="V9" s="85"/>
+      <c r="W9" s="85"/>
+      <c r="X9" s="85"/>
+      <c r="Y9" s="85"/>
+      <c r="Z9" s="85"/>
+      <c r="AA9" s="85"/>
+      <c r="AB9" s="85"/>
+      <c r="AC9" s="85"/>
+      <c r="AD9" s="85"/>
+      <c r="AE9" s="85"/>
+      <c r="AF9" s="85"/>
+      <c r="AG9" s="85"/>
+      <c r="AH9" s="85"/>
+      <c r="AI9" s="85"/>
+      <c r="AJ9" s="85"/>
+      <c r="AK9" s="85"/>
+      <c r="AL9" s="85"/>
+      <c r="AM9" s="85"/>
+      <c r="AN9" s="85"/>
+      <c r="AO9" s="85"/>
+      <c r="AP9" s="93"/>
+      <c r="AQ9" s="84"/>
+      <c r="AR9" s="85"/>
+      <c r="AS9" s="85"/>
+      <c r="AT9" s="85"/>
+      <c r="AU9" s="85"/>
+      <c r="AV9" s="85"/>
+      <c r="AW9" s="85"/>
+      <c r="AX9" s="85"/>
+      <c r="AY9" s="85"/>
+      <c r="AZ9" s="85"/>
+      <c r="BA9" s="85"/>
+      <c r="BB9" s="85"/>
+      <c r="BC9" s="85"/>
+      <c r="BD9" s="85"/>
+      <c r="BE9" s="86"/>
     </row>
     <row r="10" spans="1:57" ht="15" customHeight="1">
-      <c r="A10" s="84"/>
-      <c r="B10" s="85"/>
-      <c r="C10" s="85"/>
-      <c r="D10" s="85"/>
-      <c r="E10" s="85"/>
-      <c r="F10" s="85"/>
-      <c r="G10" s="86"/>
+      <c r="A10" s="104"/>
+      <c r="B10" s="105"/>
+      <c r="C10" s="105"/>
+      <c r="D10" s="105"/>
+      <c r="E10" s="105"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="106"/>
       <c r="H10" s="87"/>
       <c r="I10" s="88"/>
       <c r="J10" s="88"/>
@@ -65590,57 +65558,57 @@
       <c r="M10" s="88"/>
       <c r="N10" s="89"/>
       <c r="O10" s="87"/>
-      <c r="P10" s="90"/>
-      <c r="Q10" s="90"/>
-      <c r="R10" s="90"/>
-      <c r="S10" s="90"/>
-      <c r="T10" s="90"/>
-      <c r="U10" s="90"/>
-      <c r="V10" s="90"/>
-      <c r="W10" s="90"/>
-      <c r="X10" s="90"/>
-      <c r="Y10" s="90"/>
-      <c r="Z10" s="90"/>
-      <c r="AA10" s="90"/>
-      <c r="AB10" s="90"/>
-      <c r="AC10" s="90"/>
-      <c r="AD10" s="90"/>
-      <c r="AE10" s="90"/>
-      <c r="AF10" s="90"/>
-      <c r="AG10" s="90"/>
-      <c r="AH10" s="90"/>
-      <c r="AI10" s="90"/>
-      <c r="AJ10" s="90"/>
-      <c r="AK10" s="90"/>
-      <c r="AL10" s="90"/>
-      <c r="AM10" s="90"/>
-      <c r="AN10" s="90"/>
-      <c r="AO10" s="90"/>
-      <c r="AP10" s="91"/>
-      <c r="AQ10" s="95"/>
-      <c r="AR10" s="90"/>
-      <c r="AS10" s="90"/>
-      <c r="AT10" s="90"/>
-      <c r="AU10" s="90"/>
-      <c r="AV10" s="90"/>
-      <c r="AW10" s="90"/>
-      <c r="AX10" s="90"/>
-      <c r="AY10" s="90"/>
-      <c r="AZ10" s="90"/>
-      <c r="BA10" s="90"/>
-      <c r="BB10" s="90"/>
-      <c r="BC10" s="90"/>
-      <c r="BD10" s="90"/>
-      <c r="BE10" s="96"/>
+      <c r="P10" s="85"/>
+      <c r="Q10" s="85"/>
+      <c r="R10" s="85"/>
+      <c r="S10" s="85"/>
+      <c r="T10" s="85"/>
+      <c r="U10" s="85"/>
+      <c r="V10" s="85"/>
+      <c r="W10" s="85"/>
+      <c r="X10" s="85"/>
+      <c r="Y10" s="85"/>
+      <c r="Z10" s="85"/>
+      <c r="AA10" s="85"/>
+      <c r="AB10" s="85"/>
+      <c r="AC10" s="85"/>
+      <c r="AD10" s="85"/>
+      <c r="AE10" s="85"/>
+      <c r="AF10" s="85"/>
+      <c r="AG10" s="85"/>
+      <c r="AH10" s="85"/>
+      <c r="AI10" s="85"/>
+      <c r="AJ10" s="85"/>
+      <c r="AK10" s="85"/>
+      <c r="AL10" s="85"/>
+      <c r="AM10" s="85"/>
+      <c r="AN10" s="85"/>
+      <c r="AO10" s="85"/>
+      <c r="AP10" s="93"/>
+      <c r="AQ10" s="84"/>
+      <c r="AR10" s="85"/>
+      <c r="AS10" s="85"/>
+      <c r="AT10" s="85"/>
+      <c r="AU10" s="85"/>
+      <c r="AV10" s="85"/>
+      <c r="AW10" s="85"/>
+      <c r="AX10" s="85"/>
+      <c r="AY10" s="85"/>
+      <c r="AZ10" s="85"/>
+      <c r="BA10" s="85"/>
+      <c r="BB10" s="85"/>
+      <c r="BC10" s="85"/>
+      <c r="BD10" s="85"/>
+      <c r="BE10" s="86"/>
     </row>
     <row r="11" spans="1:57" ht="15" customHeight="1">
-      <c r="A11" s="84"/>
-      <c r="B11" s="85"/>
-      <c r="C11" s="85"/>
-      <c r="D11" s="85"/>
-      <c r="E11" s="85"/>
-      <c r="F11" s="85"/>
-      <c r="G11" s="86"/>
+      <c r="A11" s="104"/>
+      <c r="B11" s="105"/>
+      <c r="C11" s="105"/>
+      <c r="D11" s="105"/>
+      <c r="E11" s="105"/>
+      <c r="F11" s="105"/>
+      <c r="G11" s="106"/>
       <c r="H11" s="87"/>
       <c r="I11" s="88"/>
       <c r="J11" s="88"/>
@@ -65649,57 +65617,57 @@
       <c r="M11" s="88"/>
       <c r="N11" s="89"/>
       <c r="O11" s="87"/>
-      <c r="P11" s="90"/>
-      <c r="Q11" s="90"/>
-      <c r="R11" s="90"/>
-      <c r="S11" s="90"/>
-      <c r="T11" s="90"/>
-      <c r="U11" s="90"/>
-      <c r="V11" s="90"/>
-      <c r="W11" s="90"/>
-      <c r="X11" s="90"/>
-      <c r="Y11" s="90"/>
-      <c r="Z11" s="90"/>
-      <c r="AA11" s="90"/>
-      <c r="AB11" s="90"/>
-      <c r="AC11" s="90"/>
-      <c r="AD11" s="90"/>
-      <c r="AE11" s="90"/>
-      <c r="AF11" s="90"/>
-      <c r="AG11" s="90"/>
-      <c r="AH11" s="90"/>
-      <c r="AI11" s="90"/>
-      <c r="AJ11" s="90"/>
-      <c r="AK11" s="90"/>
-      <c r="AL11" s="90"/>
-      <c r="AM11" s="90"/>
-      <c r="AN11" s="90"/>
-      <c r="AO11" s="90"/>
-      <c r="AP11" s="91"/>
-      <c r="AQ11" s="95"/>
-      <c r="AR11" s="90"/>
-      <c r="AS11" s="90"/>
-      <c r="AT11" s="90"/>
-      <c r="AU11" s="90"/>
-      <c r="AV11" s="90"/>
-      <c r="AW11" s="90"/>
-      <c r="AX11" s="90"/>
-      <c r="AY11" s="90"/>
-      <c r="AZ11" s="90"/>
-      <c r="BA11" s="90"/>
-      <c r="BB11" s="90"/>
-      <c r="BC11" s="90"/>
-      <c r="BD11" s="90"/>
-      <c r="BE11" s="96"/>
+      <c r="P11" s="85"/>
+      <c r="Q11" s="85"/>
+      <c r="R11" s="85"/>
+      <c r="S11" s="85"/>
+      <c r="T11" s="85"/>
+      <c r="U11" s="85"/>
+      <c r="V11" s="85"/>
+      <c r="W11" s="85"/>
+      <c r="X11" s="85"/>
+      <c r="Y11" s="85"/>
+      <c r="Z11" s="85"/>
+      <c r="AA11" s="85"/>
+      <c r="AB11" s="85"/>
+      <c r="AC11" s="85"/>
+      <c r="AD11" s="85"/>
+      <c r="AE11" s="85"/>
+      <c r="AF11" s="85"/>
+      <c r="AG11" s="85"/>
+      <c r="AH11" s="85"/>
+      <c r="AI11" s="85"/>
+      <c r="AJ11" s="85"/>
+      <c r="AK11" s="85"/>
+      <c r="AL11" s="85"/>
+      <c r="AM11" s="85"/>
+      <c r="AN11" s="85"/>
+      <c r="AO11" s="85"/>
+      <c r="AP11" s="93"/>
+      <c r="AQ11" s="84"/>
+      <c r="AR11" s="85"/>
+      <c r="AS11" s="85"/>
+      <c r="AT11" s="85"/>
+      <c r="AU11" s="85"/>
+      <c r="AV11" s="85"/>
+      <c r="AW11" s="85"/>
+      <c r="AX11" s="85"/>
+      <c r="AY11" s="85"/>
+      <c r="AZ11" s="85"/>
+      <c r="BA11" s="85"/>
+      <c r="BB11" s="85"/>
+      <c r="BC11" s="85"/>
+      <c r="BD11" s="85"/>
+      <c r="BE11" s="86"/>
     </row>
     <row r="12" spans="1:57" ht="15" customHeight="1">
-      <c r="A12" s="84"/>
-      <c r="B12" s="85"/>
-      <c r="C12" s="85"/>
-      <c r="D12" s="85"/>
-      <c r="E12" s="85"/>
-      <c r="F12" s="85"/>
-      <c r="G12" s="86"/>
+      <c r="A12" s="104"/>
+      <c r="B12" s="105"/>
+      <c r="C12" s="105"/>
+      <c r="D12" s="105"/>
+      <c r="E12" s="105"/>
+      <c r="F12" s="105"/>
+      <c r="G12" s="106"/>
       <c r="H12" s="87"/>
       <c r="I12" s="88"/>
       <c r="J12" s="88"/>
@@ -65708,57 +65676,57 @@
       <c r="M12" s="88"/>
       <c r="N12" s="89"/>
       <c r="O12" s="87"/>
-      <c r="P12" s="90"/>
-      <c r="Q12" s="90"/>
-      <c r="R12" s="90"/>
-      <c r="S12" s="90"/>
-      <c r="T12" s="90"/>
-      <c r="U12" s="90"/>
-      <c r="V12" s="90"/>
-      <c r="W12" s="90"/>
-      <c r="X12" s="90"/>
-      <c r="Y12" s="90"/>
-      <c r="Z12" s="90"/>
-      <c r="AA12" s="90"/>
-      <c r="AB12" s="90"/>
-      <c r="AC12" s="90"/>
-      <c r="AD12" s="90"/>
-      <c r="AE12" s="90"/>
-      <c r="AF12" s="90"/>
-      <c r="AG12" s="90"/>
-      <c r="AH12" s="90"/>
-      <c r="AI12" s="90"/>
-      <c r="AJ12" s="90"/>
-      <c r="AK12" s="90"/>
-      <c r="AL12" s="90"/>
-      <c r="AM12" s="90"/>
-      <c r="AN12" s="90"/>
-      <c r="AO12" s="90"/>
-      <c r="AP12" s="91"/>
-      <c r="AQ12" s="95"/>
-      <c r="AR12" s="90"/>
-      <c r="AS12" s="90"/>
-      <c r="AT12" s="90"/>
-      <c r="AU12" s="90"/>
-      <c r="AV12" s="90"/>
-      <c r="AW12" s="90"/>
-      <c r="AX12" s="90"/>
-      <c r="AY12" s="90"/>
-      <c r="AZ12" s="90"/>
-      <c r="BA12" s="90"/>
-      <c r="BB12" s="90"/>
-      <c r="BC12" s="90"/>
-      <c r="BD12" s="90"/>
-      <c r="BE12" s="96"/>
+      <c r="P12" s="85"/>
+      <c r="Q12" s="85"/>
+      <c r="R12" s="85"/>
+      <c r="S12" s="85"/>
+      <c r="T12" s="85"/>
+      <c r="U12" s="85"/>
+      <c r="V12" s="85"/>
+      <c r="W12" s="85"/>
+      <c r="X12" s="85"/>
+      <c r="Y12" s="85"/>
+      <c r="Z12" s="85"/>
+      <c r="AA12" s="85"/>
+      <c r="AB12" s="85"/>
+      <c r="AC12" s="85"/>
+      <c r="AD12" s="85"/>
+      <c r="AE12" s="85"/>
+      <c r="AF12" s="85"/>
+      <c r="AG12" s="85"/>
+      <c r="AH12" s="85"/>
+      <c r="AI12" s="85"/>
+      <c r="AJ12" s="85"/>
+      <c r="AK12" s="85"/>
+      <c r="AL12" s="85"/>
+      <c r="AM12" s="85"/>
+      <c r="AN12" s="85"/>
+      <c r="AO12" s="85"/>
+      <c r="AP12" s="93"/>
+      <c r="AQ12" s="84"/>
+      <c r="AR12" s="85"/>
+      <c r="AS12" s="85"/>
+      <c r="AT12" s="85"/>
+      <c r="AU12" s="85"/>
+      <c r="AV12" s="85"/>
+      <c r="AW12" s="85"/>
+      <c r="AX12" s="85"/>
+      <c r="AY12" s="85"/>
+      <c r="AZ12" s="85"/>
+      <c r="BA12" s="85"/>
+      <c r="BB12" s="85"/>
+      <c r="BC12" s="85"/>
+      <c r="BD12" s="85"/>
+      <c r="BE12" s="86"/>
     </row>
     <row r="13" spans="1:57" ht="15" customHeight="1">
-      <c r="A13" s="84"/>
-      <c r="B13" s="85"/>
-      <c r="C13" s="85"/>
-      <c r="D13" s="85"/>
-      <c r="E13" s="85"/>
-      <c r="F13" s="85"/>
-      <c r="G13" s="86"/>
+      <c r="A13" s="104"/>
+      <c r="B13" s="105"/>
+      <c r="C13" s="105"/>
+      <c r="D13" s="105"/>
+      <c r="E13" s="105"/>
+      <c r="F13" s="105"/>
+      <c r="G13" s="106"/>
       <c r="H13" s="87"/>
       <c r="I13" s="88"/>
       <c r="J13" s="88"/>
@@ -65767,57 +65735,57 @@
       <c r="M13" s="88"/>
       <c r="N13" s="89"/>
       <c r="O13" s="87"/>
-      <c r="P13" s="90"/>
-      <c r="Q13" s="90"/>
-      <c r="R13" s="90"/>
-      <c r="S13" s="90"/>
-      <c r="T13" s="90"/>
-      <c r="U13" s="90"/>
-      <c r="V13" s="90"/>
-      <c r="W13" s="90"/>
-      <c r="X13" s="90"/>
-      <c r="Y13" s="90"/>
-      <c r="Z13" s="90"/>
-      <c r="AA13" s="90"/>
-      <c r="AB13" s="90"/>
-      <c r="AC13" s="90"/>
-      <c r="AD13" s="90"/>
-      <c r="AE13" s="90"/>
-      <c r="AF13" s="90"/>
-      <c r="AG13" s="90"/>
-      <c r="AH13" s="90"/>
-      <c r="AI13" s="90"/>
-      <c r="AJ13" s="90"/>
-      <c r="AK13" s="90"/>
-      <c r="AL13" s="90"/>
-      <c r="AM13" s="90"/>
-      <c r="AN13" s="90"/>
-      <c r="AO13" s="90"/>
-      <c r="AP13" s="91"/>
-      <c r="AQ13" s="95"/>
-      <c r="AR13" s="90"/>
-      <c r="AS13" s="90"/>
-      <c r="AT13" s="90"/>
-      <c r="AU13" s="90"/>
-      <c r="AV13" s="90"/>
-      <c r="AW13" s="90"/>
-      <c r="AX13" s="90"/>
-      <c r="AY13" s="90"/>
-      <c r="AZ13" s="90"/>
-      <c r="BA13" s="90"/>
-      <c r="BB13" s="90"/>
-      <c r="BC13" s="90"/>
-      <c r="BD13" s="90"/>
-      <c r="BE13" s="96"/>
+      <c r="P13" s="85"/>
+      <c r="Q13" s="85"/>
+      <c r="R13" s="85"/>
+      <c r="S13" s="85"/>
+      <c r="T13" s="85"/>
+      <c r="U13" s="85"/>
+      <c r="V13" s="85"/>
+      <c r="W13" s="85"/>
+      <c r="X13" s="85"/>
+      <c r="Y13" s="85"/>
+      <c r="Z13" s="85"/>
+      <c r="AA13" s="85"/>
+      <c r="AB13" s="85"/>
+      <c r="AC13" s="85"/>
+      <c r="AD13" s="85"/>
+      <c r="AE13" s="85"/>
+      <c r="AF13" s="85"/>
+      <c r="AG13" s="85"/>
+      <c r="AH13" s="85"/>
+      <c r="AI13" s="85"/>
+      <c r="AJ13" s="85"/>
+      <c r="AK13" s="85"/>
+      <c r="AL13" s="85"/>
+      <c r="AM13" s="85"/>
+      <c r="AN13" s="85"/>
+      <c r="AO13" s="85"/>
+      <c r="AP13" s="93"/>
+      <c r="AQ13" s="84"/>
+      <c r="AR13" s="85"/>
+      <c r="AS13" s="85"/>
+      <c r="AT13" s="85"/>
+      <c r="AU13" s="85"/>
+      <c r="AV13" s="85"/>
+      <c r="AW13" s="85"/>
+      <c r="AX13" s="85"/>
+      <c r="AY13" s="85"/>
+      <c r="AZ13" s="85"/>
+      <c r="BA13" s="85"/>
+      <c r="BB13" s="85"/>
+      <c r="BC13" s="85"/>
+      <c r="BD13" s="85"/>
+      <c r="BE13" s="86"/>
     </row>
     <row r="14" spans="1:57" ht="15" customHeight="1">
-      <c r="A14" s="84"/>
-      <c r="B14" s="85"/>
-      <c r="C14" s="85"/>
-      <c r="D14" s="85"/>
-      <c r="E14" s="85"/>
-      <c r="F14" s="85"/>
-      <c r="G14" s="86"/>
+      <c r="A14" s="104"/>
+      <c r="B14" s="105"/>
+      <c r="C14" s="105"/>
+      <c r="D14" s="105"/>
+      <c r="E14" s="105"/>
+      <c r="F14" s="105"/>
+      <c r="G14" s="106"/>
       <c r="H14" s="87"/>
       <c r="I14" s="88"/>
       <c r="J14" s="88"/>
@@ -65826,57 +65794,57 @@
       <c r="M14" s="88"/>
       <c r="N14" s="89"/>
       <c r="O14" s="87"/>
-      <c r="P14" s="90"/>
-      <c r="Q14" s="90"/>
-      <c r="R14" s="90"/>
-      <c r="S14" s="90"/>
-      <c r="T14" s="90"/>
-      <c r="U14" s="90"/>
-      <c r="V14" s="90"/>
-      <c r="W14" s="90"/>
-      <c r="X14" s="90"/>
-      <c r="Y14" s="90"/>
-      <c r="Z14" s="90"/>
-      <c r="AA14" s="90"/>
-      <c r="AB14" s="90"/>
-      <c r="AC14" s="90"/>
-      <c r="AD14" s="90"/>
-      <c r="AE14" s="90"/>
-      <c r="AF14" s="90"/>
-      <c r="AG14" s="90"/>
-      <c r="AH14" s="90"/>
-      <c r="AI14" s="90"/>
-      <c r="AJ14" s="90"/>
-      <c r="AK14" s="90"/>
-      <c r="AL14" s="90"/>
-      <c r="AM14" s="90"/>
-      <c r="AN14" s="90"/>
-      <c r="AO14" s="90"/>
-      <c r="AP14" s="91"/>
-      <c r="AQ14" s="95"/>
-      <c r="AR14" s="90"/>
-      <c r="AS14" s="90"/>
-      <c r="AT14" s="90"/>
-      <c r="AU14" s="90"/>
-      <c r="AV14" s="90"/>
-      <c r="AW14" s="90"/>
-      <c r="AX14" s="90"/>
-      <c r="AY14" s="90"/>
-      <c r="AZ14" s="90"/>
-      <c r="BA14" s="90"/>
-      <c r="BB14" s="90"/>
-      <c r="BC14" s="90"/>
-      <c r="BD14" s="90"/>
-      <c r="BE14" s="96"/>
+      <c r="P14" s="85"/>
+      <c r="Q14" s="85"/>
+      <c r="R14" s="85"/>
+      <c r="S14" s="85"/>
+      <c r="T14" s="85"/>
+      <c r="U14" s="85"/>
+      <c r="V14" s="85"/>
+      <c r="W14" s="85"/>
+      <c r="X14" s="85"/>
+      <c r="Y14" s="85"/>
+      <c r="Z14" s="85"/>
+      <c r="AA14" s="85"/>
+      <c r="AB14" s="85"/>
+      <c r="AC14" s="85"/>
+      <c r="AD14" s="85"/>
+      <c r="AE14" s="85"/>
+      <c r="AF14" s="85"/>
+      <c r="AG14" s="85"/>
+      <c r="AH14" s="85"/>
+      <c r="AI14" s="85"/>
+      <c r="AJ14" s="85"/>
+      <c r="AK14" s="85"/>
+      <c r="AL14" s="85"/>
+      <c r="AM14" s="85"/>
+      <c r="AN14" s="85"/>
+      <c r="AO14" s="85"/>
+      <c r="AP14" s="93"/>
+      <c r="AQ14" s="84"/>
+      <c r="AR14" s="85"/>
+      <c r="AS14" s="85"/>
+      <c r="AT14" s="85"/>
+      <c r="AU14" s="85"/>
+      <c r="AV14" s="85"/>
+      <c r="AW14" s="85"/>
+      <c r="AX14" s="85"/>
+      <c r="AY14" s="85"/>
+      <c r="AZ14" s="85"/>
+      <c r="BA14" s="85"/>
+      <c r="BB14" s="85"/>
+      <c r="BC14" s="85"/>
+      <c r="BD14" s="85"/>
+      <c r="BE14" s="86"/>
     </row>
     <row r="15" spans="1:57" ht="15" customHeight="1">
-      <c r="A15" s="84"/>
-      <c r="B15" s="85"/>
-      <c r="C15" s="85"/>
-      <c r="D15" s="85"/>
-      <c r="E15" s="85"/>
-      <c r="F15" s="85"/>
-      <c r="G15" s="86"/>
+      <c r="A15" s="104"/>
+      <c r="B15" s="105"/>
+      <c r="C15" s="105"/>
+      <c r="D15" s="105"/>
+      <c r="E15" s="105"/>
+      <c r="F15" s="105"/>
+      <c r="G15" s="106"/>
       <c r="H15" s="87"/>
       <c r="I15" s="88"/>
       <c r="J15" s="88"/>
@@ -65885,57 +65853,57 @@
       <c r="M15" s="88"/>
       <c r="N15" s="89"/>
       <c r="O15" s="87"/>
-      <c r="P15" s="90"/>
-      <c r="Q15" s="90"/>
-      <c r="R15" s="90"/>
-      <c r="S15" s="90"/>
-      <c r="T15" s="90"/>
-      <c r="U15" s="90"/>
-      <c r="V15" s="90"/>
-      <c r="W15" s="90"/>
-      <c r="X15" s="90"/>
-      <c r="Y15" s="90"/>
-      <c r="Z15" s="90"/>
-      <c r="AA15" s="90"/>
-      <c r="AB15" s="90"/>
-      <c r="AC15" s="90"/>
-      <c r="AD15" s="90"/>
-      <c r="AE15" s="90"/>
-      <c r="AF15" s="90"/>
-      <c r="AG15" s="90"/>
-      <c r="AH15" s="90"/>
-      <c r="AI15" s="90"/>
-      <c r="AJ15" s="90"/>
-      <c r="AK15" s="90"/>
-      <c r="AL15" s="90"/>
-      <c r="AM15" s="90"/>
-      <c r="AN15" s="90"/>
-      <c r="AO15" s="90"/>
-      <c r="AP15" s="91"/>
-      <c r="AQ15" s="95"/>
-      <c r="AR15" s="90"/>
-      <c r="AS15" s="90"/>
-      <c r="AT15" s="90"/>
-      <c r="AU15" s="90"/>
-      <c r="AV15" s="90"/>
-      <c r="AW15" s="90"/>
-      <c r="AX15" s="90"/>
-      <c r="AY15" s="90"/>
-      <c r="AZ15" s="90"/>
-      <c r="BA15" s="90"/>
-      <c r="BB15" s="90"/>
-      <c r="BC15" s="90"/>
-      <c r="BD15" s="90"/>
-      <c r="BE15" s="96"/>
+      <c r="P15" s="85"/>
+      <c r="Q15" s="85"/>
+      <c r="R15" s="85"/>
+      <c r="S15" s="85"/>
+      <c r="T15" s="85"/>
+      <c r="U15" s="85"/>
+      <c r="V15" s="85"/>
+      <c r="W15" s="85"/>
+      <c r="X15" s="85"/>
+      <c r="Y15" s="85"/>
+      <c r="Z15" s="85"/>
+      <c r="AA15" s="85"/>
+      <c r="AB15" s="85"/>
+      <c r="AC15" s="85"/>
+      <c r="AD15" s="85"/>
+      <c r="AE15" s="85"/>
+      <c r="AF15" s="85"/>
+      <c r="AG15" s="85"/>
+      <c r="AH15" s="85"/>
+      <c r="AI15" s="85"/>
+      <c r="AJ15" s="85"/>
+      <c r="AK15" s="85"/>
+      <c r="AL15" s="85"/>
+      <c r="AM15" s="85"/>
+      <c r="AN15" s="85"/>
+      <c r="AO15" s="85"/>
+      <c r="AP15" s="93"/>
+      <c r="AQ15" s="84"/>
+      <c r="AR15" s="85"/>
+      <c r="AS15" s="85"/>
+      <c r="AT15" s="85"/>
+      <c r="AU15" s="85"/>
+      <c r="AV15" s="85"/>
+      <c r="AW15" s="85"/>
+      <c r="AX15" s="85"/>
+      <c r="AY15" s="85"/>
+      <c r="AZ15" s="85"/>
+      <c r="BA15" s="85"/>
+      <c r="BB15" s="85"/>
+      <c r="BC15" s="85"/>
+      <c r="BD15" s="85"/>
+      <c r="BE15" s="86"/>
     </row>
     <row r="16" spans="1:57" ht="15" customHeight="1">
-      <c r="A16" s="84"/>
-      <c r="B16" s="85"/>
-      <c r="C16" s="85"/>
-      <c r="D16" s="85"/>
-      <c r="E16" s="85"/>
-      <c r="F16" s="85"/>
-      <c r="G16" s="86"/>
+      <c r="A16" s="104"/>
+      <c r="B16" s="105"/>
+      <c r="C16" s="105"/>
+      <c r="D16" s="105"/>
+      <c r="E16" s="105"/>
+      <c r="F16" s="105"/>
+      <c r="G16" s="106"/>
       <c r="H16" s="87"/>
       <c r="I16" s="88"/>
       <c r="J16" s="88"/>
@@ -65944,57 +65912,57 @@
       <c r="M16" s="88"/>
       <c r="N16" s="89"/>
       <c r="O16" s="87"/>
-      <c r="P16" s="90"/>
-      <c r="Q16" s="90"/>
-      <c r="R16" s="90"/>
-      <c r="S16" s="90"/>
-      <c r="T16" s="90"/>
-      <c r="U16" s="90"/>
-      <c r="V16" s="90"/>
-      <c r="W16" s="90"/>
-      <c r="X16" s="90"/>
-      <c r="Y16" s="90"/>
-      <c r="Z16" s="90"/>
-      <c r="AA16" s="90"/>
-      <c r="AB16" s="90"/>
-      <c r="AC16" s="90"/>
-      <c r="AD16" s="90"/>
-      <c r="AE16" s="90"/>
-      <c r="AF16" s="90"/>
-      <c r="AG16" s="90"/>
-      <c r="AH16" s="90"/>
-      <c r="AI16" s="90"/>
-      <c r="AJ16" s="90"/>
-      <c r="AK16" s="90"/>
-      <c r="AL16" s="90"/>
-      <c r="AM16" s="90"/>
-      <c r="AN16" s="90"/>
-      <c r="AO16" s="90"/>
-      <c r="AP16" s="91"/>
-      <c r="AQ16" s="95"/>
-      <c r="AR16" s="90"/>
-      <c r="AS16" s="90"/>
-      <c r="AT16" s="90"/>
-      <c r="AU16" s="90"/>
-      <c r="AV16" s="90"/>
-      <c r="AW16" s="90"/>
-      <c r="AX16" s="90"/>
-      <c r="AY16" s="90"/>
-      <c r="AZ16" s="90"/>
-      <c r="BA16" s="90"/>
-      <c r="BB16" s="90"/>
-      <c r="BC16" s="90"/>
-      <c r="BD16" s="90"/>
-      <c r="BE16" s="96"/>
+      <c r="P16" s="85"/>
+      <c r="Q16" s="85"/>
+      <c r="R16" s="85"/>
+      <c r="S16" s="85"/>
+      <c r="T16" s="85"/>
+      <c r="U16" s="85"/>
+      <c r="V16" s="85"/>
+      <c r="W16" s="85"/>
+      <c r="X16" s="85"/>
+      <c r="Y16" s="85"/>
+      <c r="Z16" s="85"/>
+      <c r="AA16" s="85"/>
+      <c r="AB16" s="85"/>
+      <c r="AC16" s="85"/>
+      <c r="AD16" s="85"/>
+      <c r="AE16" s="85"/>
+      <c r="AF16" s="85"/>
+      <c r="AG16" s="85"/>
+      <c r="AH16" s="85"/>
+      <c r="AI16" s="85"/>
+      <c r="AJ16" s="85"/>
+      <c r="AK16" s="85"/>
+      <c r="AL16" s="85"/>
+      <c r="AM16" s="85"/>
+      <c r="AN16" s="85"/>
+      <c r="AO16" s="85"/>
+      <c r="AP16" s="93"/>
+      <c r="AQ16" s="84"/>
+      <c r="AR16" s="85"/>
+      <c r="AS16" s="85"/>
+      <c r="AT16" s="85"/>
+      <c r="AU16" s="85"/>
+      <c r="AV16" s="85"/>
+      <c r="AW16" s="85"/>
+      <c r="AX16" s="85"/>
+      <c r="AY16" s="85"/>
+      <c r="AZ16" s="85"/>
+      <c r="BA16" s="85"/>
+      <c r="BB16" s="85"/>
+      <c r="BC16" s="85"/>
+      <c r="BD16" s="85"/>
+      <c r="BE16" s="86"/>
     </row>
     <row r="17" spans="1:57" ht="15" customHeight="1">
-      <c r="A17" s="84"/>
-      <c r="B17" s="85"/>
-      <c r="C17" s="85"/>
-      <c r="D17" s="85"/>
-      <c r="E17" s="85"/>
-      <c r="F17" s="85"/>
-      <c r="G17" s="86"/>
+      <c r="A17" s="104"/>
+      <c r="B17" s="105"/>
+      <c r="C17" s="105"/>
+      <c r="D17" s="105"/>
+      <c r="E17" s="105"/>
+      <c r="F17" s="105"/>
+      <c r="G17" s="106"/>
       <c r="H17" s="87"/>
       <c r="I17" s="88"/>
       <c r="J17" s="88"/>
@@ -66003,57 +65971,57 @@
       <c r="M17" s="88"/>
       <c r="N17" s="89"/>
       <c r="O17" s="87"/>
-      <c r="P17" s="90"/>
-      <c r="Q17" s="90"/>
-      <c r="R17" s="90"/>
-      <c r="S17" s="90"/>
-      <c r="T17" s="90"/>
-      <c r="U17" s="90"/>
-      <c r="V17" s="90"/>
-      <c r="W17" s="90"/>
-      <c r="X17" s="90"/>
-      <c r="Y17" s="90"/>
-      <c r="Z17" s="90"/>
-      <c r="AA17" s="90"/>
-      <c r="AB17" s="90"/>
-      <c r="AC17" s="90"/>
-      <c r="AD17" s="90"/>
-      <c r="AE17" s="90"/>
-      <c r="AF17" s="90"/>
-      <c r="AG17" s="90"/>
-      <c r="AH17" s="90"/>
-      <c r="AI17" s="90"/>
-      <c r="AJ17" s="90"/>
-      <c r="AK17" s="90"/>
-      <c r="AL17" s="90"/>
-      <c r="AM17" s="90"/>
-      <c r="AN17" s="90"/>
-      <c r="AO17" s="90"/>
-      <c r="AP17" s="91"/>
-      <c r="AQ17" s="95"/>
-      <c r="AR17" s="90"/>
-      <c r="AS17" s="90"/>
-      <c r="AT17" s="90"/>
-      <c r="AU17" s="90"/>
-      <c r="AV17" s="90"/>
-      <c r="AW17" s="90"/>
-      <c r="AX17" s="90"/>
-      <c r="AY17" s="90"/>
-      <c r="AZ17" s="90"/>
-      <c r="BA17" s="90"/>
-      <c r="BB17" s="90"/>
-      <c r="BC17" s="90"/>
-      <c r="BD17" s="90"/>
-      <c r="BE17" s="96"/>
+      <c r="P17" s="85"/>
+      <c r="Q17" s="85"/>
+      <c r="R17" s="85"/>
+      <c r="S17" s="85"/>
+      <c r="T17" s="85"/>
+      <c r="U17" s="85"/>
+      <c r="V17" s="85"/>
+      <c r="W17" s="85"/>
+      <c r="X17" s="85"/>
+      <c r="Y17" s="85"/>
+      <c r="Z17" s="85"/>
+      <c r="AA17" s="85"/>
+      <c r="AB17" s="85"/>
+      <c r="AC17" s="85"/>
+      <c r="AD17" s="85"/>
+      <c r="AE17" s="85"/>
+      <c r="AF17" s="85"/>
+      <c r="AG17" s="85"/>
+      <c r="AH17" s="85"/>
+      <c r="AI17" s="85"/>
+      <c r="AJ17" s="85"/>
+      <c r="AK17" s="85"/>
+      <c r="AL17" s="85"/>
+      <c r="AM17" s="85"/>
+      <c r="AN17" s="85"/>
+      <c r="AO17" s="85"/>
+      <c r="AP17" s="93"/>
+      <c r="AQ17" s="84"/>
+      <c r="AR17" s="85"/>
+      <c r="AS17" s="85"/>
+      <c r="AT17" s="85"/>
+      <c r="AU17" s="85"/>
+      <c r="AV17" s="85"/>
+      <c r="AW17" s="85"/>
+      <c r="AX17" s="85"/>
+      <c r="AY17" s="85"/>
+      <c r="AZ17" s="85"/>
+      <c r="BA17" s="85"/>
+      <c r="BB17" s="85"/>
+      <c r="BC17" s="85"/>
+      <c r="BD17" s="85"/>
+      <c r="BE17" s="86"/>
     </row>
     <row r="18" spans="1:57" ht="15" customHeight="1">
-      <c r="A18" s="84"/>
-      <c r="B18" s="85"/>
-      <c r="C18" s="85"/>
-      <c r="D18" s="85"/>
-      <c r="E18" s="85"/>
-      <c r="F18" s="85"/>
-      <c r="G18" s="86"/>
+      <c r="A18" s="104"/>
+      <c r="B18" s="105"/>
+      <c r="C18" s="105"/>
+      <c r="D18" s="105"/>
+      <c r="E18" s="105"/>
+      <c r="F18" s="105"/>
+      <c r="G18" s="106"/>
       <c r="H18" s="87"/>
       <c r="I18" s="88"/>
       <c r="J18" s="88"/>
@@ -66062,57 +66030,57 @@
       <c r="M18" s="88"/>
       <c r="N18" s="89"/>
       <c r="O18" s="87"/>
-      <c r="P18" s="90"/>
-      <c r="Q18" s="90"/>
-      <c r="R18" s="90"/>
-      <c r="S18" s="90"/>
-      <c r="T18" s="90"/>
-      <c r="U18" s="90"/>
-      <c r="V18" s="90"/>
-      <c r="W18" s="90"/>
-      <c r="X18" s="90"/>
-      <c r="Y18" s="90"/>
-      <c r="Z18" s="90"/>
-      <c r="AA18" s="90"/>
-      <c r="AB18" s="90"/>
-      <c r="AC18" s="90"/>
-      <c r="AD18" s="90"/>
-      <c r="AE18" s="90"/>
-      <c r="AF18" s="90"/>
-      <c r="AG18" s="90"/>
-      <c r="AH18" s="90"/>
-      <c r="AI18" s="90"/>
-      <c r="AJ18" s="90"/>
-      <c r="AK18" s="90"/>
-      <c r="AL18" s="90"/>
-      <c r="AM18" s="90"/>
-      <c r="AN18" s="90"/>
-      <c r="AO18" s="90"/>
-      <c r="AP18" s="91"/>
-      <c r="AQ18" s="95"/>
-      <c r="AR18" s="90"/>
-      <c r="AS18" s="90"/>
-      <c r="AT18" s="90"/>
-      <c r="AU18" s="90"/>
-      <c r="AV18" s="90"/>
-      <c r="AW18" s="90"/>
-      <c r="AX18" s="90"/>
-      <c r="AY18" s="90"/>
-      <c r="AZ18" s="90"/>
-      <c r="BA18" s="90"/>
-      <c r="BB18" s="90"/>
-      <c r="BC18" s="90"/>
-      <c r="BD18" s="90"/>
-      <c r="BE18" s="96"/>
+      <c r="P18" s="85"/>
+      <c r="Q18" s="85"/>
+      <c r="R18" s="85"/>
+      <c r="S18" s="85"/>
+      <c r="T18" s="85"/>
+      <c r="U18" s="85"/>
+      <c r="V18" s="85"/>
+      <c r="W18" s="85"/>
+      <c r="X18" s="85"/>
+      <c r="Y18" s="85"/>
+      <c r="Z18" s="85"/>
+      <c r="AA18" s="85"/>
+      <c r="AB18" s="85"/>
+      <c r="AC18" s="85"/>
+      <c r="AD18" s="85"/>
+      <c r="AE18" s="85"/>
+      <c r="AF18" s="85"/>
+      <c r="AG18" s="85"/>
+      <c r="AH18" s="85"/>
+      <c r="AI18" s="85"/>
+      <c r="AJ18" s="85"/>
+      <c r="AK18" s="85"/>
+      <c r="AL18" s="85"/>
+      <c r="AM18" s="85"/>
+      <c r="AN18" s="85"/>
+      <c r="AO18" s="85"/>
+      <c r="AP18" s="93"/>
+      <c r="AQ18" s="84"/>
+      <c r="AR18" s="85"/>
+      <c r="AS18" s="85"/>
+      <c r="AT18" s="85"/>
+      <c r="AU18" s="85"/>
+      <c r="AV18" s="85"/>
+      <c r="AW18" s="85"/>
+      <c r="AX18" s="85"/>
+      <c r="AY18" s="85"/>
+      <c r="AZ18" s="85"/>
+      <c r="BA18" s="85"/>
+      <c r="BB18" s="85"/>
+      <c r="BC18" s="85"/>
+      <c r="BD18" s="85"/>
+      <c r="BE18" s="86"/>
     </row>
     <row r="19" spans="1:57" ht="15" customHeight="1">
-      <c r="A19" s="84"/>
-      <c r="B19" s="85"/>
-      <c r="C19" s="85"/>
-      <c r="D19" s="85"/>
-      <c r="E19" s="85"/>
-      <c r="F19" s="85"/>
-      <c r="G19" s="86"/>
+      <c r="A19" s="104"/>
+      <c r="B19" s="105"/>
+      <c r="C19" s="105"/>
+      <c r="D19" s="105"/>
+      <c r="E19" s="105"/>
+      <c r="F19" s="105"/>
+      <c r="G19" s="106"/>
       <c r="H19" s="87"/>
       <c r="I19" s="88"/>
       <c r="J19" s="88"/>
@@ -66121,57 +66089,57 @@
       <c r="M19" s="88"/>
       <c r="N19" s="89"/>
       <c r="O19" s="87"/>
-      <c r="P19" s="90"/>
-      <c r="Q19" s="90"/>
-      <c r="R19" s="90"/>
-      <c r="S19" s="90"/>
-      <c r="T19" s="90"/>
-      <c r="U19" s="90"/>
-      <c r="V19" s="90"/>
-      <c r="W19" s="90"/>
-      <c r="X19" s="90"/>
-      <c r="Y19" s="90"/>
-      <c r="Z19" s="90"/>
-      <c r="AA19" s="90"/>
-      <c r="AB19" s="90"/>
-      <c r="AC19" s="90"/>
-      <c r="AD19" s="90"/>
-      <c r="AE19" s="90"/>
-      <c r="AF19" s="90"/>
-      <c r="AG19" s="90"/>
-      <c r="AH19" s="90"/>
-      <c r="AI19" s="90"/>
-      <c r="AJ19" s="90"/>
-      <c r="AK19" s="90"/>
-      <c r="AL19" s="90"/>
-      <c r="AM19" s="90"/>
-      <c r="AN19" s="90"/>
-      <c r="AO19" s="90"/>
-      <c r="AP19" s="91"/>
-      <c r="AQ19" s="95"/>
-      <c r="AR19" s="90"/>
-      <c r="AS19" s="90"/>
-      <c r="AT19" s="90"/>
-      <c r="AU19" s="90"/>
-      <c r="AV19" s="90"/>
-      <c r="AW19" s="90"/>
-      <c r="AX19" s="90"/>
-      <c r="AY19" s="90"/>
-      <c r="AZ19" s="90"/>
-      <c r="BA19" s="90"/>
-      <c r="BB19" s="90"/>
-      <c r="BC19" s="90"/>
-      <c r="BD19" s="90"/>
-      <c r="BE19" s="96"/>
+      <c r="P19" s="85"/>
+      <c r="Q19" s="85"/>
+      <c r="R19" s="85"/>
+      <c r="S19" s="85"/>
+      <c r="T19" s="85"/>
+      <c r="U19" s="85"/>
+      <c r="V19" s="85"/>
+      <c r="W19" s="85"/>
+      <c r="X19" s="85"/>
+      <c r="Y19" s="85"/>
+      <c r="Z19" s="85"/>
+      <c r="AA19" s="85"/>
+      <c r="AB19" s="85"/>
+      <c r="AC19" s="85"/>
+      <c r="AD19" s="85"/>
+      <c r="AE19" s="85"/>
+      <c r="AF19" s="85"/>
+      <c r="AG19" s="85"/>
+      <c r="AH19" s="85"/>
+      <c r="AI19" s="85"/>
+      <c r="AJ19" s="85"/>
+      <c r="AK19" s="85"/>
+      <c r="AL19" s="85"/>
+      <c r="AM19" s="85"/>
+      <c r="AN19" s="85"/>
+      <c r="AO19" s="85"/>
+      <c r="AP19" s="93"/>
+      <c r="AQ19" s="84"/>
+      <c r="AR19" s="85"/>
+      <c r="AS19" s="85"/>
+      <c r="AT19" s="85"/>
+      <c r="AU19" s="85"/>
+      <c r="AV19" s="85"/>
+      <c r="AW19" s="85"/>
+      <c r="AX19" s="85"/>
+      <c r="AY19" s="85"/>
+      <c r="AZ19" s="85"/>
+      <c r="BA19" s="85"/>
+      <c r="BB19" s="85"/>
+      <c r="BC19" s="85"/>
+      <c r="BD19" s="85"/>
+      <c r="BE19" s="86"/>
     </row>
     <row r="20" spans="1:57" ht="15" customHeight="1">
-      <c r="A20" s="84"/>
-      <c r="B20" s="85"/>
-      <c r="C20" s="85"/>
-      <c r="D20" s="85"/>
-      <c r="E20" s="85"/>
-      <c r="F20" s="85"/>
-      <c r="G20" s="86"/>
+      <c r="A20" s="104"/>
+      <c r="B20" s="105"/>
+      <c r="C20" s="105"/>
+      <c r="D20" s="105"/>
+      <c r="E20" s="105"/>
+      <c r="F20" s="105"/>
+      <c r="G20" s="106"/>
       <c r="H20" s="87"/>
       <c r="I20" s="88"/>
       <c r="J20" s="88"/>
@@ -66180,57 +66148,57 @@
       <c r="M20" s="88"/>
       <c r="N20" s="89"/>
       <c r="O20" s="87"/>
-      <c r="P20" s="90"/>
-      <c r="Q20" s="90"/>
-      <c r="R20" s="90"/>
-      <c r="S20" s="90"/>
-      <c r="T20" s="90"/>
-      <c r="U20" s="90"/>
-      <c r="V20" s="90"/>
-      <c r="W20" s="90"/>
-      <c r="X20" s="90"/>
-      <c r="Y20" s="90"/>
-      <c r="Z20" s="90"/>
-      <c r="AA20" s="90"/>
-      <c r="AB20" s="90"/>
-      <c r="AC20" s="90"/>
-      <c r="AD20" s="90"/>
-      <c r="AE20" s="90"/>
-      <c r="AF20" s="90"/>
-      <c r="AG20" s="90"/>
-      <c r="AH20" s="90"/>
-      <c r="AI20" s="90"/>
-      <c r="AJ20" s="90"/>
-      <c r="AK20" s="90"/>
-      <c r="AL20" s="90"/>
-      <c r="AM20" s="90"/>
-      <c r="AN20" s="90"/>
-      <c r="AO20" s="90"/>
-      <c r="AP20" s="91"/>
-      <c r="AQ20" s="95"/>
-      <c r="AR20" s="90"/>
-      <c r="AS20" s="90"/>
-      <c r="AT20" s="90"/>
-      <c r="AU20" s="90"/>
-      <c r="AV20" s="90"/>
-      <c r="AW20" s="90"/>
-      <c r="AX20" s="90"/>
-      <c r="AY20" s="90"/>
-      <c r="AZ20" s="90"/>
-      <c r="BA20" s="90"/>
-      <c r="BB20" s="90"/>
-      <c r="BC20" s="90"/>
-      <c r="BD20" s="90"/>
-      <c r="BE20" s="96"/>
+      <c r="P20" s="85"/>
+      <c r="Q20" s="85"/>
+      <c r="R20" s="85"/>
+      <c r="S20" s="85"/>
+      <c r="T20" s="85"/>
+      <c r="U20" s="85"/>
+      <c r="V20" s="85"/>
+      <c r="W20" s="85"/>
+      <c r="X20" s="85"/>
+      <c r="Y20" s="85"/>
+      <c r="Z20" s="85"/>
+      <c r="AA20" s="85"/>
+      <c r="AB20" s="85"/>
+      <c r="AC20" s="85"/>
+      <c r="AD20" s="85"/>
+      <c r="AE20" s="85"/>
+      <c r="AF20" s="85"/>
+      <c r="AG20" s="85"/>
+      <c r="AH20" s="85"/>
+      <c r="AI20" s="85"/>
+      <c r="AJ20" s="85"/>
+      <c r="AK20" s="85"/>
+      <c r="AL20" s="85"/>
+      <c r="AM20" s="85"/>
+      <c r="AN20" s="85"/>
+      <c r="AO20" s="85"/>
+      <c r="AP20" s="93"/>
+      <c r="AQ20" s="84"/>
+      <c r="AR20" s="85"/>
+      <c r="AS20" s="85"/>
+      <c r="AT20" s="85"/>
+      <c r="AU20" s="85"/>
+      <c r="AV20" s="85"/>
+      <c r="AW20" s="85"/>
+      <c r="AX20" s="85"/>
+      <c r="AY20" s="85"/>
+      <c r="AZ20" s="85"/>
+      <c r="BA20" s="85"/>
+      <c r="BB20" s="85"/>
+      <c r="BC20" s="85"/>
+      <c r="BD20" s="85"/>
+      <c r="BE20" s="86"/>
     </row>
     <row r="21" spans="1:57" ht="15" customHeight="1">
-      <c r="A21" s="84"/>
-      <c r="B21" s="85"/>
-      <c r="C21" s="85"/>
-      <c r="D21" s="85"/>
-      <c r="E21" s="85"/>
-      <c r="F21" s="85"/>
-      <c r="G21" s="86"/>
+      <c r="A21" s="104"/>
+      <c r="B21" s="105"/>
+      <c r="C21" s="105"/>
+      <c r="D21" s="105"/>
+      <c r="E21" s="105"/>
+      <c r="F21" s="105"/>
+      <c r="G21" s="106"/>
       <c r="H21" s="87"/>
       <c r="I21" s="88"/>
       <c r="J21" s="88"/>
@@ -66239,57 +66207,57 @@
       <c r="M21" s="88"/>
       <c r="N21" s="89"/>
       <c r="O21" s="87"/>
-      <c r="P21" s="90"/>
-      <c r="Q21" s="90"/>
-      <c r="R21" s="90"/>
-      <c r="S21" s="90"/>
-      <c r="T21" s="90"/>
-      <c r="U21" s="90"/>
-      <c r="V21" s="90"/>
-      <c r="W21" s="90"/>
-      <c r="X21" s="90"/>
-      <c r="Y21" s="90"/>
-      <c r="Z21" s="90"/>
-      <c r="AA21" s="90"/>
-      <c r="AB21" s="90"/>
-      <c r="AC21" s="90"/>
-      <c r="AD21" s="90"/>
-      <c r="AE21" s="90"/>
-      <c r="AF21" s="90"/>
-      <c r="AG21" s="90"/>
-      <c r="AH21" s="90"/>
-      <c r="AI21" s="90"/>
-      <c r="AJ21" s="90"/>
-      <c r="AK21" s="90"/>
-      <c r="AL21" s="90"/>
-      <c r="AM21" s="90"/>
-      <c r="AN21" s="90"/>
-      <c r="AO21" s="90"/>
-      <c r="AP21" s="91"/>
-      <c r="AQ21" s="95"/>
-      <c r="AR21" s="90"/>
-      <c r="AS21" s="90"/>
-      <c r="AT21" s="90"/>
-      <c r="AU21" s="90"/>
-      <c r="AV21" s="90"/>
-      <c r="AW21" s="90"/>
-      <c r="AX21" s="90"/>
-      <c r="AY21" s="90"/>
-      <c r="AZ21" s="90"/>
-      <c r="BA21" s="90"/>
-      <c r="BB21" s="90"/>
-      <c r="BC21" s="90"/>
-      <c r="BD21" s="90"/>
-      <c r="BE21" s="96"/>
+      <c r="P21" s="85"/>
+      <c r="Q21" s="85"/>
+      <c r="R21" s="85"/>
+      <c r="S21" s="85"/>
+      <c r="T21" s="85"/>
+      <c r="U21" s="85"/>
+      <c r="V21" s="85"/>
+      <c r="W21" s="85"/>
+      <c r="X21" s="85"/>
+      <c r="Y21" s="85"/>
+      <c r="Z21" s="85"/>
+      <c r="AA21" s="85"/>
+      <c r="AB21" s="85"/>
+      <c r="AC21" s="85"/>
+      <c r="AD21" s="85"/>
+      <c r="AE21" s="85"/>
+      <c r="AF21" s="85"/>
+      <c r="AG21" s="85"/>
+      <c r="AH21" s="85"/>
+      <c r="AI21" s="85"/>
+      <c r="AJ21" s="85"/>
+      <c r="AK21" s="85"/>
+      <c r="AL21" s="85"/>
+      <c r="AM21" s="85"/>
+      <c r="AN21" s="85"/>
+      <c r="AO21" s="85"/>
+      <c r="AP21" s="93"/>
+      <c r="AQ21" s="84"/>
+      <c r="AR21" s="85"/>
+      <c r="AS21" s="85"/>
+      <c r="AT21" s="85"/>
+      <c r="AU21" s="85"/>
+      <c r="AV21" s="85"/>
+      <c r="AW21" s="85"/>
+      <c r="AX21" s="85"/>
+      <c r="AY21" s="85"/>
+      <c r="AZ21" s="85"/>
+      <c r="BA21" s="85"/>
+      <c r="BB21" s="85"/>
+      <c r="BC21" s="85"/>
+      <c r="BD21" s="85"/>
+      <c r="BE21" s="86"/>
     </row>
     <row r="22" spans="1:57" ht="15" customHeight="1">
-      <c r="A22" s="84"/>
-      <c r="B22" s="85"/>
-      <c r="C22" s="85"/>
-      <c r="D22" s="85"/>
-      <c r="E22" s="85"/>
-      <c r="F22" s="85"/>
-      <c r="G22" s="86"/>
+      <c r="A22" s="104"/>
+      <c r="B22" s="105"/>
+      <c r="C22" s="105"/>
+      <c r="D22" s="105"/>
+      <c r="E22" s="105"/>
+      <c r="F22" s="105"/>
+      <c r="G22" s="106"/>
       <c r="H22" s="87"/>
       <c r="I22" s="88"/>
       <c r="J22" s="88"/>
@@ -66298,57 +66266,57 @@
       <c r="M22" s="88"/>
       <c r="N22" s="89"/>
       <c r="O22" s="87"/>
-      <c r="P22" s="90"/>
-      <c r="Q22" s="90"/>
-      <c r="R22" s="90"/>
-      <c r="S22" s="90"/>
-      <c r="T22" s="90"/>
-      <c r="U22" s="90"/>
-      <c r="V22" s="90"/>
-      <c r="W22" s="90"/>
-      <c r="X22" s="90"/>
-      <c r="Y22" s="90"/>
-      <c r="Z22" s="90"/>
-      <c r="AA22" s="90"/>
-      <c r="AB22" s="90"/>
-      <c r="AC22" s="90"/>
-      <c r="AD22" s="90"/>
-      <c r="AE22" s="90"/>
-      <c r="AF22" s="90"/>
-      <c r="AG22" s="90"/>
-      <c r="AH22" s="90"/>
-      <c r="AI22" s="90"/>
-      <c r="AJ22" s="90"/>
-      <c r="AK22" s="90"/>
-      <c r="AL22" s="90"/>
-      <c r="AM22" s="90"/>
-      <c r="AN22" s="90"/>
-      <c r="AO22" s="90"/>
-      <c r="AP22" s="91"/>
-      <c r="AQ22" s="95"/>
-      <c r="AR22" s="90"/>
-      <c r="AS22" s="90"/>
-      <c r="AT22" s="90"/>
-      <c r="AU22" s="90"/>
-      <c r="AV22" s="90"/>
-      <c r="AW22" s="90"/>
-      <c r="AX22" s="90"/>
-      <c r="AY22" s="90"/>
-      <c r="AZ22" s="90"/>
-      <c r="BA22" s="90"/>
-      <c r="BB22" s="90"/>
-      <c r="BC22" s="90"/>
-      <c r="BD22" s="90"/>
-      <c r="BE22" s="96"/>
+      <c r="P22" s="85"/>
+      <c r="Q22" s="85"/>
+      <c r="R22" s="85"/>
+      <c r="S22" s="85"/>
+      <c r="T22" s="85"/>
+      <c r="U22" s="85"/>
+      <c r="V22" s="85"/>
+      <c r="W22" s="85"/>
+      <c r="X22" s="85"/>
+      <c r="Y22" s="85"/>
+      <c r="Z22" s="85"/>
+      <c r="AA22" s="85"/>
+      <c r="AB22" s="85"/>
+      <c r="AC22" s="85"/>
+      <c r="AD22" s="85"/>
+      <c r="AE22" s="85"/>
+      <c r="AF22" s="85"/>
+      <c r="AG22" s="85"/>
+      <c r="AH22" s="85"/>
+      <c r="AI22" s="85"/>
+      <c r="AJ22" s="85"/>
+      <c r="AK22" s="85"/>
+      <c r="AL22" s="85"/>
+      <c r="AM22" s="85"/>
+      <c r="AN22" s="85"/>
+      <c r="AO22" s="85"/>
+      <c r="AP22" s="93"/>
+      <c r="AQ22" s="84"/>
+      <c r="AR22" s="85"/>
+      <c r="AS22" s="85"/>
+      <c r="AT22" s="85"/>
+      <c r="AU22" s="85"/>
+      <c r="AV22" s="85"/>
+      <c r="AW22" s="85"/>
+      <c r="AX22" s="85"/>
+      <c r="AY22" s="85"/>
+      <c r="AZ22" s="85"/>
+      <c r="BA22" s="85"/>
+      <c r="BB22" s="85"/>
+      <c r="BC22" s="85"/>
+      <c r="BD22" s="85"/>
+      <c r="BE22" s="86"/>
     </row>
     <row r="23" spans="1:57" ht="15" customHeight="1">
-      <c r="A23" s="84"/>
-      <c r="B23" s="85"/>
-      <c r="C23" s="85"/>
-      <c r="D23" s="85"/>
-      <c r="E23" s="85"/>
-      <c r="F23" s="85"/>
-      <c r="G23" s="86"/>
+      <c r="A23" s="104"/>
+      <c r="B23" s="105"/>
+      <c r="C23" s="105"/>
+      <c r="D23" s="105"/>
+      <c r="E23" s="105"/>
+      <c r="F23" s="105"/>
+      <c r="G23" s="106"/>
       <c r="H23" s="87"/>
       <c r="I23" s="88"/>
       <c r="J23" s="88"/>
@@ -66357,57 +66325,57 @@
       <c r="M23" s="88"/>
       <c r="N23" s="89"/>
       <c r="O23" s="87"/>
-      <c r="P23" s="90"/>
-      <c r="Q23" s="90"/>
-      <c r="R23" s="90"/>
-      <c r="S23" s="90"/>
-      <c r="T23" s="90"/>
-      <c r="U23" s="90"/>
-      <c r="V23" s="90"/>
-      <c r="W23" s="90"/>
-      <c r="X23" s="90"/>
-      <c r="Y23" s="90"/>
-      <c r="Z23" s="90"/>
-      <c r="AA23" s="90"/>
-      <c r="AB23" s="90"/>
-      <c r="AC23" s="90"/>
-      <c r="AD23" s="90"/>
-      <c r="AE23" s="90"/>
-      <c r="AF23" s="90"/>
-      <c r="AG23" s="90"/>
-      <c r="AH23" s="90"/>
-      <c r="AI23" s="90"/>
-      <c r="AJ23" s="90"/>
-      <c r="AK23" s="90"/>
-      <c r="AL23" s="90"/>
-      <c r="AM23" s="90"/>
-      <c r="AN23" s="90"/>
-      <c r="AO23" s="90"/>
-      <c r="AP23" s="91"/>
-      <c r="AQ23" s="95"/>
-      <c r="AR23" s="90"/>
-      <c r="AS23" s="90"/>
-      <c r="AT23" s="90"/>
-      <c r="AU23" s="90"/>
-      <c r="AV23" s="90"/>
-      <c r="AW23" s="90"/>
-      <c r="AX23" s="90"/>
-      <c r="AY23" s="90"/>
-      <c r="AZ23" s="90"/>
-      <c r="BA23" s="90"/>
-      <c r="BB23" s="90"/>
-      <c r="BC23" s="90"/>
-      <c r="BD23" s="90"/>
-      <c r="BE23" s="96"/>
+      <c r="P23" s="85"/>
+      <c r="Q23" s="85"/>
+      <c r="R23" s="85"/>
+      <c r="S23" s="85"/>
+      <c r="T23" s="85"/>
+      <c r="U23" s="85"/>
+      <c r="V23" s="85"/>
+      <c r="W23" s="85"/>
+      <c r="X23" s="85"/>
+      <c r="Y23" s="85"/>
+      <c r="Z23" s="85"/>
+      <c r="AA23" s="85"/>
+      <c r="AB23" s="85"/>
+      <c r="AC23" s="85"/>
+      <c r="AD23" s="85"/>
+      <c r="AE23" s="85"/>
+      <c r="AF23" s="85"/>
+      <c r="AG23" s="85"/>
+      <c r="AH23" s="85"/>
+      <c r="AI23" s="85"/>
+      <c r="AJ23" s="85"/>
+      <c r="AK23" s="85"/>
+      <c r="AL23" s="85"/>
+      <c r="AM23" s="85"/>
+      <c r="AN23" s="85"/>
+      <c r="AO23" s="85"/>
+      <c r="AP23" s="93"/>
+      <c r="AQ23" s="84"/>
+      <c r="AR23" s="85"/>
+      <c r="AS23" s="85"/>
+      <c r="AT23" s="85"/>
+      <c r="AU23" s="85"/>
+      <c r="AV23" s="85"/>
+      <c r="AW23" s="85"/>
+      <c r="AX23" s="85"/>
+      <c r="AY23" s="85"/>
+      <c r="AZ23" s="85"/>
+      <c r="BA23" s="85"/>
+      <c r="BB23" s="85"/>
+      <c r="BC23" s="85"/>
+      <c r="BD23" s="85"/>
+      <c r="BE23" s="86"/>
     </row>
     <row r="24" spans="1:57" ht="15" customHeight="1">
-      <c r="A24" s="84"/>
-      <c r="B24" s="85"/>
-      <c r="C24" s="85"/>
-      <c r="D24" s="85"/>
-      <c r="E24" s="85"/>
-      <c r="F24" s="85"/>
-      <c r="G24" s="86"/>
+      <c r="A24" s="104"/>
+      <c r="B24" s="105"/>
+      <c r="C24" s="105"/>
+      <c r="D24" s="105"/>
+      <c r="E24" s="105"/>
+      <c r="F24" s="105"/>
+      <c r="G24" s="106"/>
       <c r="H24" s="87"/>
       <c r="I24" s="88"/>
       <c r="J24" s="88"/>
@@ -66416,57 +66384,57 @@
       <c r="M24" s="88"/>
       <c r="N24" s="89"/>
       <c r="O24" s="87"/>
-      <c r="P24" s="90"/>
-      <c r="Q24" s="90"/>
-      <c r="R24" s="90"/>
-      <c r="S24" s="90"/>
-      <c r="T24" s="90"/>
-      <c r="U24" s="90"/>
-      <c r="V24" s="90"/>
-      <c r="W24" s="90"/>
-      <c r="X24" s="90"/>
-      <c r="Y24" s="90"/>
-      <c r="Z24" s="90"/>
-      <c r="AA24" s="90"/>
-      <c r="AB24" s="90"/>
-      <c r="AC24" s="90"/>
-      <c r="AD24" s="90"/>
-      <c r="AE24" s="90"/>
-      <c r="AF24" s="90"/>
-      <c r="AG24" s="90"/>
-      <c r="AH24" s="90"/>
-      <c r="AI24" s="90"/>
-      <c r="AJ24" s="90"/>
-      <c r="AK24" s="90"/>
-      <c r="AL24" s="90"/>
-      <c r="AM24" s="90"/>
-      <c r="AN24" s="90"/>
-      <c r="AO24" s="90"/>
-      <c r="AP24" s="91"/>
-      <c r="AQ24" s="95"/>
-      <c r="AR24" s="90"/>
-      <c r="AS24" s="90"/>
-      <c r="AT24" s="90"/>
-      <c r="AU24" s="90"/>
-      <c r="AV24" s="90"/>
-      <c r="AW24" s="90"/>
-      <c r="AX24" s="90"/>
-      <c r="AY24" s="90"/>
-      <c r="AZ24" s="90"/>
-      <c r="BA24" s="90"/>
-      <c r="BB24" s="90"/>
-      <c r="BC24" s="90"/>
-      <c r="BD24" s="90"/>
-      <c r="BE24" s="96"/>
+      <c r="P24" s="85"/>
+      <c r="Q24" s="85"/>
+      <c r="R24" s="85"/>
+      <c r="S24" s="85"/>
+      <c r="T24" s="85"/>
+      <c r="U24" s="85"/>
+      <c r="V24" s="85"/>
+      <c r="W24" s="85"/>
+      <c r="X24" s="85"/>
+      <c r="Y24" s="85"/>
+      <c r="Z24" s="85"/>
+      <c r="AA24" s="85"/>
+      <c r="AB24" s="85"/>
+      <c r="AC24" s="85"/>
+      <c r="AD24" s="85"/>
+      <c r="AE24" s="85"/>
+      <c r="AF24" s="85"/>
+      <c r="AG24" s="85"/>
+      <c r="AH24" s="85"/>
+      <c r="AI24" s="85"/>
+      <c r="AJ24" s="85"/>
+      <c r="AK24" s="85"/>
+      <c r="AL24" s="85"/>
+      <c r="AM24" s="85"/>
+      <c r="AN24" s="85"/>
+      <c r="AO24" s="85"/>
+      <c r="AP24" s="93"/>
+      <c r="AQ24" s="84"/>
+      <c r="AR24" s="85"/>
+      <c r="AS24" s="85"/>
+      <c r="AT24" s="85"/>
+      <c r="AU24" s="85"/>
+      <c r="AV24" s="85"/>
+      <c r="AW24" s="85"/>
+      <c r="AX24" s="85"/>
+      <c r="AY24" s="85"/>
+      <c r="AZ24" s="85"/>
+      <c r="BA24" s="85"/>
+      <c r="BB24" s="85"/>
+      <c r="BC24" s="85"/>
+      <c r="BD24" s="85"/>
+      <c r="BE24" s="86"/>
     </row>
     <row r="25" spans="1:57" ht="15" customHeight="1">
-      <c r="A25" s="84"/>
-      <c r="B25" s="85"/>
-      <c r="C25" s="85"/>
-      <c r="D25" s="85"/>
-      <c r="E25" s="85"/>
-      <c r="F25" s="85"/>
-      <c r="G25" s="86"/>
+      <c r="A25" s="104"/>
+      <c r="B25" s="105"/>
+      <c r="C25" s="105"/>
+      <c r="D25" s="105"/>
+      <c r="E25" s="105"/>
+      <c r="F25" s="105"/>
+      <c r="G25" s="106"/>
       <c r="H25" s="87"/>
       <c r="I25" s="88"/>
       <c r="J25" s="88"/>
@@ -66475,57 +66443,57 @@
       <c r="M25" s="88"/>
       <c r="N25" s="89"/>
       <c r="O25" s="87"/>
-      <c r="P25" s="90"/>
-      <c r="Q25" s="90"/>
-      <c r="R25" s="90"/>
-      <c r="S25" s="90"/>
-      <c r="T25" s="90"/>
-      <c r="U25" s="90"/>
-      <c r="V25" s="90"/>
-      <c r="W25" s="90"/>
-      <c r="X25" s="90"/>
-      <c r="Y25" s="90"/>
-      <c r="Z25" s="90"/>
-      <c r="AA25" s="90"/>
-      <c r="AB25" s="90"/>
-      <c r="AC25" s="90"/>
-      <c r="AD25" s="90"/>
-      <c r="AE25" s="90"/>
-      <c r="AF25" s="90"/>
-      <c r="AG25" s="90"/>
-      <c r="AH25" s="90"/>
-      <c r="AI25" s="90"/>
-      <c r="AJ25" s="90"/>
-      <c r="AK25" s="90"/>
-      <c r="AL25" s="90"/>
-      <c r="AM25" s="90"/>
-      <c r="AN25" s="90"/>
-      <c r="AO25" s="90"/>
-      <c r="AP25" s="91"/>
-      <c r="AQ25" s="95"/>
-      <c r="AR25" s="90"/>
-      <c r="AS25" s="90"/>
-      <c r="AT25" s="90"/>
-      <c r="AU25" s="90"/>
-      <c r="AV25" s="90"/>
-      <c r="AW25" s="90"/>
-      <c r="AX25" s="90"/>
-      <c r="AY25" s="90"/>
-      <c r="AZ25" s="90"/>
-      <c r="BA25" s="90"/>
-      <c r="BB25" s="90"/>
-      <c r="BC25" s="90"/>
-      <c r="BD25" s="90"/>
-      <c r="BE25" s="96"/>
+      <c r="P25" s="85"/>
+      <c r="Q25" s="85"/>
+      <c r="R25" s="85"/>
+      <c r="S25" s="85"/>
+      <c r="T25" s="85"/>
+      <c r="U25" s="85"/>
+      <c r="V25" s="85"/>
+      <c r="W25" s="85"/>
+      <c r="X25" s="85"/>
+      <c r="Y25" s="85"/>
+      <c r="Z25" s="85"/>
+      <c r="AA25" s="85"/>
+      <c r="AB25" s="85"/>
+      <c r="AC25" s="85"/>
+      <c r="AD25" s="85"/>
+      <c r="AE25" s="85"/>
+      <c r="AF25" s="85"/>
+      <c r="AG25" s="85"/>
+      <c r="AH25" s="85"/>
+      <c r="AI25" s="85"/>
+      <c r="AJ25" s="85"/>
+      <c r="AK25" s="85"/>
+      <c r="AL25" s="85"/>
+      <c r="AM25" s="85"/>
+      <c r="AN25" s="85"/>
+      <c r="AO25" s="85"/>
+      <c r="AP25" s="93"/>
+      <c r="AQ25" s="84"/>
+      <c r="AR25" s="85"/>
+      <c r="AS25" s="85"/>
+      <c r="AT25" s="85"/>
+      <c r="AU25" s="85"/>
+      <c r="AV25" s="85"/>
+      <c r="AW25" s="85"/>
+      <c r="AX25" s="85"/>
+      <c r="AY25" s="85"/>
+      <c r="AZ25" s="85"/>
+      <c r="BA25" s="85"/>
+      <c r="BB25" s="85"/>
+      <c r="BC25" s="85"/>
+      <c r="BD25" s="85"/>
+      <c r="BE25" s="86"/>
     </row>
     <row r="26" spans="1:57" ht="15" customHeight="1">
-      <c r="A26" s="84"/>
-      <c r="B26" s="85"/>
-      <c r="C26" s="85"/>
-      <c r="D26" s="85"/>
-      <c r="E26" s="85"/>
-      <c r="F26" s="85"/>
-      <c r="G26" s="86"/>
+      <c r="A26" s="104"/>
+      <c r="B26" s="105"/>
+      <c r="C26" s="105"/>
+      <c r="D26" s="105"/>
+      <c r="E26" s="105"/>
+      <c r="F26" s="105"/>
+      <c r="G26" s="106"/>
       <c r="H26" s="87"/>
       <c r="I26" s="88"/>
       <c r="J26" s="88"/>
@@ -66534,57 +66502,57 @@
       <c r="M26" s="88"/>
       <c r="N26" s="89"/>
       <c r="O26" s="87"/>
-      <c r="P26" s="90"/>
-      <c r="Q26" s="90"/>
-      <c r="R26" s="90"/>
-      <c r="S26" s="90"/>
-      <c r="T26" s="90"/>
-      <c r="U26" s="90"/>
-      <c r="V26" s="90"/>
-      <c r="W26" s="90"/>
-      <c r="X26" s="90"/>
-      <c r="Y26" s="90"/>
-      <c r="Z26" s="90"/>
-      <c r="AA26" s="90"/>
-      <c r="AB26" s="90"/>
-      <c r="AC26" s="90"/>
-      <c r="AD26" s="90"/>
-      <c r="AE26" s="90"/>
-      <c r="AF26" s="90"/>
-      <c r="AG26" s="90"/>
-      <c r="AH26" s="90"/>
-      <c r="AI26" s="90"/>
-      <c r="AJ26" s="90"/>
-      <c r="AK26" s="90"/>
-      <c r="AL26" s="90"/>
-      <c r="AM26" s="90"/>
-      <c r="AN26" s="90"/>
-      <c r="AO26" s="90"/>
-      <c r="AP26" s="91"/>
-      <c r="AQ26" s="95"/>
-      <c r="AR26" s="90"/>
-      <c r="AS26" s="90"/>
-      <c r="AT26" s="90"/>
-      <c r="AU26" s="90"/>
-      <c r="AV26" s="90"/>
-      <c r="AW26" s="90"/>
-      <c r="AX26" s="90"/>
-      <c r="AY26" s="90"/>
-      <c r="AZ26" s="90"/>
-      <c r="BA26" s="90"/>
-      <c r="BB26" s="90"/>
-      <c r="BC26" s="90"/>
-      <c r="BD26" s="90"/>
-      <c r="BE26" s="96"/>
+      <c r="P26" s="85"/>
+      <c r="Q26" s="85"/>
+      <c r="R26" s="85"/>
+      <c r="S26" s="85"/>
+      <c r="T26" s="85"/>
+      <c r="U26" s="85"/>
+      <c r="V26" s="85"/>
+      <c r="W26" s="85"/>
+      <c r="X26" s="85"/>
+      <c r="Y26" s="85"/>
+      <c r="Z26" s="85"/>
+      <c r="AA26" s="85"/>
+      <c r="AB26" s="85"/>
+      <c r="AC26" s="85"/>
+      <c r="AD26" s="85"/>
+      <c r="AE26" s="85"/>
+      <c r="AF26" s="85"/>
+      <c r="AG26" s="85"/>
+      <c r="AH26" s="85"/>
+      <c r="AI26" s="85"/>
+      <c r="AJ26" s="85"/>
+      <c r="AK26" s="85"/>
+      <c r="AL26" s="85"/>
+      <c r="AM26" s="85"/>
+      <c r="AN26" s="85"/>
+      <c r="AO26" s="85"/>
+      <c r="AP26" s="93"/>
+      <c r="AQ26" s="84"/>
+      <c r="AR26" s="85"/>
+      <c r="AS26" s="85"/>
+      <c r="AT26" s="85"/>
+      <c r="AU26" s="85"/>
+      <c r="AV26" s="85"/>
+      <c r="AW26" s="85"/>
+      <c r="AX26" s="85"/>
+      <c r="AY26" s="85"/>
+      <c r="AZ26" s="85"/>
+      <c r="BA26" s="85"/>
+      <c r="BB26" s="85"/>
+      <c r="BC26" s="85"/>
+      <c r="BD26" s="85"/>
+      <c r="BE26" s="86"/>
     </row>
     <row r="27" spans="1:57" ht="15" customHeight="1">
-      <c r="A27" s="84"/>
-      <c r="B27" s="85"/>
-      <c r="C27" s="85"/>
-      <c r="D27" s="85"/>
-      <c r="E27" s="85"/>
-      <c r="F27" s="85"/>
-      <c r="G27" s="86"/>
+      <c r="A27" s="104"/>
+      <c r="B27" s="105"/>
+      <c r="C27" s="105"/>
+      <c r="D27" s="105"/>
+      <c r="E27" s="105"/>
+      <c r="F27" s="105"/>
+      <c r="G27" s="106"/>
       <c r="H27" s="87"/>
       <c r="I27" s="88"/>
       <c r="J27" s="88"/>
@@ -66593,57 +66561,57 @@
       <c r="M27" s="88"/>
       <c r="N27" s="89"/>
       <c r="O27" s="87"/>
-      <c r="P27" s="90"/>
-      <c r="Q27" s="90"/>
-      <c r="R27" s="90"/>
-      <c r="S27" s="90"/>
-      <c r="T27" s="90"/>
-      <c r="U27" s="90"/>
-      <c r="V27" s="90"/>
-      <c r="W27" s="90"/>
-      <c r="X27" s="90"/>
-      <c r="Y27" s="90"/>
-      <c r="Z27" s="90"/>
-      <c r="AA27" s="90"/>
-      <c r="AB27" s="90"/>
-      <c r="AC27" s="90"/>
-      <c r="AD27" s="90"/>
-      <c r="AE27" s="90"/>
-      <c r="AF27" s="90"/>
-      <c r="AG27" s="90"/>
-      <c r="AH27" s="90"/>
-      <c r="AI27" s="90"/>
-      <c r="AJ27" s="90"/>
-      <c r="AK27" s="90"/>
-      <c r="AL27" s="90"/>
-      <c r="AM27" s="90"/>
-      <c r="AN27" s="90"/>
-      <c r="AO27" s="90"/>
-      <c r="AP27" s="91"/>
-      <c r="AQ27" s="95"/>
-      <c r="AR27" s="90"/>
-      <c r="AS27" s="90"/>
-      <c r="AT27" s="90"/>
-      <c r="AU27" s="90"/>
-      <c r="AV27" s="90"/>
-      <c r="AW27" s="90"/>
-      <c r="AX27" s="90"/>
-      <c r="AY27" s="90"/>
-      <c r="AZ27" s="90"/>
-      <c r="BA27" s="90"/>
-      <c r="BB27" s="90"/>
-      <c r="BC27" s="90"/>
-      <c r="BD27" s="90"/>
-      <c r="BE27" s="96"/>
+      <c r="P27" s="85"/>
+      <c r="Q27" s="85"/>
+      <c r="R27" s="85"/>
+      <c r="S27" s="85"/>
+      <c r="T27" s="85"/>
+      <c r="U27" s="85"/>
+      <c r="V27" s="85"/>
+      <c r="W27" s="85"/>
+      <c r="X27" s="85"/>
+      <c r="Y27" s="85"/>
+      <c r="Z27" s="85"/>
+      <c r="AA27" s="85"/>
+      <c r="AB27" s="85"/>
+      <c r="AC27" s="85"/>
+      <c r="AD27" s="85"/>
+      <c r="AE27" s="85"/>
+      <c r="AF27" s="85"/>
+      <c r="AG27" s="85"/>
+      <c r="AH27" s="85"/>
+      <c r="AI27" s="85"/>
+      <c r="AJ27" s="85"/>
+      <c r="AK27" s="85"/>
+      <c r="AL27" s="85"/>
+      <c r="AM27" s="85"/>
+      <c r="AN27" s="85"/>
+      <c r="AO27" s="85"/>
+      <c r="AP27" s="93"/>
+      <c r="AQ27" s="84"/>
+      <c r="AR27" s="85"/>
+      <c r="AS27" s="85"/>
+      <c r="AT27" s="85"/>
+      <c r="AU27" s="85"/>
+      <c r="AV27" s="85"/>
+      <c r="AW27" s="85"/>
+      <c r="AX27" s="85"/>
+      <c r="AY27" s="85"/>
+      <c r="AZ27" s="85"/>
+      <c r="BA27" s="85"/>
+      <c r="BB27" s="85"/>
+      <c r="BC27" s="85"/>
+      <c r="BD27" s="85"/>
+      <c r="BE27" s="86"/>
     </row>
     <row r="28" spans="1:57" ht="15" customHeight="1">
-      <c r="A28" s="84"/>
-      <c r="B28" s="85"/>
-      <c r="C28" s="85"/>
-      <c r="D28" s="85"/>
-      <c r="E28" s="85"/>
-      <c r="F28" s="85"/>
-      <c r="G28" s="86"/>
+      <c r="A28" s="104"/>
+      <c r="B28" s="105"/>
+      <c r="C28" s="105"/>
+      <c r="D28" s="105"/>
+      <c r="E28" s="105"/>
+      <c r="F28" s="105"/>
+      <c r="G28" s="106"/>
       <c r="H28" s="87"/>
       <c r="I28" s="88"/>
       <c r="J28" s="88"/>
@@ -66652,57 +66620,57 @@
       <c r="M28" s="88"/>
       <c r="N28" s="89"/>
       <c r="O28" s="87"/>
-      <c r="P28" s="90"/>
-      <c r="Q28" s="90"/>
-      <c r="R28" s="90"/>
-      <c r="S28" s="90"/>
-      <c r="T28" s="90"/>
-      <c r="U28" s="90"/>
-      <c r="V28" s="90"/>
-      <c r="W28" s="90"/>
-      <c r="X28" s="90"/>
-      <c r="Y28" s="90"/>
-      <c r="Z28" s="90"/>
-      <c r="AA28" s="90"/>
-      <c r="AB28" s="90"/>
-      <c r="AC28" s="90"/>
-      <c r="AD28" s="90"/>
-      <c r="AE28" s="90"/>
-      <c r="AF28" s="90"/>
-      <c r="AG28" s="90"/>
-      <c r="AH28" s="90"/>
-      <c r="AI28" s="90"/>
-      <c r="AJ28" s="90"/>
-      <c r="AK28" s="90"/>
-      <c r="AL28" s="90"/>
-      <c r="AM28" s="90"/>
-      <c r="AN28" s="90"/>
-      <c r="AO28" s="90"/>
-      <c r="AP28" s="91"/>
-      <c r="AQ28" s="95"/>
-      <c r="AR28" s="90"/>
-      <c r="AS28" s="90"/>
-      <c r="AT28" s="90"/>
-      <c r="AU28" s="90"/>
-      <c r="AV28" s="90"/>
-      <c r="AW28" s="90"/>
-      <c r="AX28" s="90"/>
-      <c r="AY28" s="90"/>
-      <c r="AZ28" s="90"/>
-      <c r="BA28" s="90"/>
-      <c r="BB28" s="90"/>
-      <c r="BC28" s="90"/>
-      <c r="BD28" s="90"/>
-      <c r="BE28" s="96"/>
+      <c r="P28" s="85"/>
+      <c r="Q28" s="85"/>
+      <c r="R28" s="85"/>
+      <c r="S28" s="85"/>
+      <c r="T28" s="85"/>
+      <c r="U28" s="85"/>
+      <c r="V28" s="85"/>
+      <c r="W28" s="85"/>
+      <c r="X28" s="85"/>
+      <c r="Y28" s="85"/>
+      <c r="Z28" s="85"/>
+      <c r="AA28" s="85"/>
+      <c r="AB28" s="85"/>
+      <c r="AC28" s="85"/>
+      <c r="AD28" s="85"/>
+      <c r="AE28" s="85"/>
+      <c r="AF28" s="85"/>
+      <c r="AG28" s="85"/>
+      <c r="AH28" s="85"/>
+      <c r="AI28" s="85"/>
+      <c r="AJ28" s="85"/>
+      <c r="AK28" s="85"/>
+      <c r="AL28" s="85"/>
+      <c r="AM28" s="85"/>
+      <c r="AN28" s="85"/>
+      <c r="AO28" s="85"/>
+      <c r="AP28" s="93"/>
+      <c r="AQ28" s="84"/>
+      <c r="AR28" s="85"/>
+      <c r="AS28" s="85"/>
+      <c r="AT28" s="85"/>
+      <c r="AU28" s="85"/>
+      <c r="AV28" s="85"/>
+      <c r="AW28" s="85"/>
+      <c r="AX28" s="85"/>
+      <c r="AY28" s="85"/>
+      <c r="AZ28" s="85"/>
+      <c r="BA28" s="85"/>
+      <c r="BB28" s="85"/>
+      <c r="BC28" s="85"/>
+      <c r="BD28" s="85"/>
+      <c r="BE28" s="86"/>
     </row>
     <row r="29" spans="1:57" ht="15" customHeight="1">
-      <c r="A29" s="84"/>
-      <c r="B29" s="85"/>
-      <c r="C29" s="85"/>
-      <c r="D29" s="85"/>
-      <c r="E29" s="85"/>
-      <c r="F29" s="85"/>
-      <c r="G29" s="86"/>
+      <c r="A29" s="104"/>
+      <c r="B29" s="105"/>
+      <c r="C29" s="105"/>
+      <c r="D29" s="105"/>
+      <c r="E29" s="105"/>
+      <c r="F29" s="105"/>
+      <c r="G29" s="106"/>
       <c r="H29" s="87"/>
       <c r="I29" s="88"/>
       <c r="J29" s="88"/>
@@ -66711,57 +66679,57 @@
       <c r="M29" s="88"/>
       <c r="N29" s="89"/>
       <c r="O29" s="87"/>
-      <c r="P29" s="90"/>
-      <c r="Q29" s="90"/>
-      <c r="R29" s="90"/>
-      <c r="S29" s="90"/>
-      <c r="T29" s="90"/>
-      <c r="U29" s="90"/>
-      <c r="V29" s="90"/>
-      <c r="W29" s="90"/>
-      <c r="X29" s="90"/>
-      <c r="Y29" s="90"/>
-      <c r="Z29" s="90"/>
-      <c r="AA29" s="90"/>
-      <c r="AB29" s="90"/>
-      <c r="AC29" s="90"/>
-      <c r="AD29" s="90"/>
-      <c r="AE29" s="90"/>
-      <c r="AF29" s="90"/>
-      <c r="AG29" s="90"/>
-      <c r="AH29" s="90"/>
-      <c r="AI29" s="90"/>
-      <c r="AJ29" s="90"/>
-      <c r="AK29" s="90"/>
-      <c r="AL29" s="90"/>
-      <c r="AM29" s="90"/>
-      <c r="AN29" s="90"/>
-      <c r="AO29" s="90"/>
-      <c r="AP29" s="91"/>
-      <c r="AQ29" s="95"/>
-      <c r="AR29" s="90"/>
-      <c r="AS29" s="90"/>
-      <c r="AT29" s="90"/>
-      <c r="AU29" s="90"/>
-      <c r="AV29" s="90"/>
-      <c r="AW29" s="90"/>
-      <c r="AX29" s="90"/>
-      <c r="AY29" s="90"/>
-      <c r="AZ29" s="90"/>
-      <c r="BA29" s="90"/>
-      <c r="BB29" s="90"/>
-      <c r="BC29" s="90"/>
-      <c r="BD29" s="90"/>
-      <c r="BE29" s="96"/>
+      <c r="P29" s="85"/>
+      <c r="Q29" s="85"/>
+      <c r="R29" s="85"/>
+      <c r="S29" s="85"/>
+      <c r="T29" s="85"/>
+      <c r="U29" s="85"/>
+      <c r="V29" s="85"/>
+      <c r="W29" s="85"/>
+      <c r="X29" s="85"/>
+      <c r="Y29" s="85"/>
+      <c r="Z29" s="85"/>
+      <c r="AA29" s="85"/>
+      <c r="AB29" s="85"/>
+      <c r="AC29" s="85"/>
+      <c r="AD29" s="85"/>
+      <c r="AE29" s="85"/>
+      <c r="AF29" s="85"/>
+      <c r="AG29" s="85"/>
+      <c r="AH29" s="85"/>
+      <c r="AI29" s="85"/>
+      <c r="AJ29" s="85"/>
+      <c r="AK29" s="85"/>
+      <c r="AL29" s="85"/>
+      <c r="AM29" s="85"/>
+      <c r="AN29" s="85"/>
+      <c r="AO29" s="85"/>
+      <c r="AP29" s="93"/>
+      <c r="AQ29" s="84"/>
+      <c r="AR29" s="85"/>
+      <c r="AS29" s="85"/>
+      <c r="AT29" s="85"/>
+      <c r="AU29" s="85"/>
+      <c r="AV29" s="85"/>
+      <c r="AW29" s="85"/>
+      <c r="AX29" s="85"/>
+      <c r="AY29" s="85"/>
+      <c r="AZ29" s="85"/>
+      <c r="BA29" s="85"/>
+      <c r="BB29" s="85"/>
+      <c r="BC29" s="85"/>
+      <c r="BD29" s="85"/>
+      <c r="BE29" s="86"/>
     </row>
     <row r="30" spans="1:57" ht="15" customHeight="1">
-      <c r="A30" s="84"/>
-      <c r="B30" s="85"/>
-      <c r="C30" s="85"/>
-      <c r="D30" s="85"/>
-      <c r="E30" s="85"/>
-      <c r="F30" s="85"/>
-      <c r="G30" s="86"/>
+      <c r="A30" s="104"/>
+      <c r="B30" s="105"/>
+      <c r="C30" s="105"/>
+      <c r="D30" s="105"/>
+      <c r="E30" s="105"/>
+      <c r="F30" s="105"/>
+      <c r="G30" s="106"/>
       <c r="H30" s="87"/>
       <c r="I30" s="88"/>
       <c r="J30" s="88"/>
@@ -66770,57 +66738,57 @@
       <c r="M30" s="88"/>
       <c r="N30" s="89"/>
       <c r="O30" s="87"/>
-      <c r="P30" s="90"/>
-      <c r="Q30" s="90"/>
-      <c r="R30" s="90"/>
-      <c r="S30" s="90"/>
-      <c r="T30" s="90"/>
-      <c r="U30" s="90"/>
-      <c r="V30" s="90"/>
-      <c r="W30" s="90"/>
-      <c r="X30" s="90"/>
-      <c r="Y30" s="90"/>
-      <c r="Z30" s="90"/>
-      <c r="AA30" s="90"/>
-      <c r="AB30" s="90"/>
-      <c r="AC30" s="90"/>
-      <c r="AD30" s="90"/>
-      <c r="AE30" s="90"/>
-      <c r="AF30" s="90"/>
-      <c r="AG30" s="90"/>
-      <c r="AH30" s="90"/>
-      <c r="AI30" s="90"/>
-      <c r="AJ30" s="90"/>
-      <c r="AK30" s="90"/>
-      <c r="AL30" s="90"/>
-      <c r="AM30" s="90"/>
-      <c r="AN30" s="90"/>
-      <c r="AO30" s="90"/>
-      <c r="AP30" s="91"/>
-      <c r="AQ30" s="95"/>
-      <c r="AR30" s="90"/>
-      <c r="AS30" s="90"/>
-      <c r="AT30" s="90"/>
-      <c r="AU30" s="90"/>
-      <c r="AV30" s="90"/>
-      <c r="AW30" s="90"/>
-      <c r="AX30" s="90"/>
-      <c r="AY30" s="90"/>
-      <c r="AZ30" s="90"/>
-      <c r="BA30" s="90"/>
-      <c r="BB30" s="90"/>
-      <c r="BC30" s="90"/>
-      <c r="BD30" s="90"/>
-      <c r="BE30" s="96"/>
+      <c r="P30" s="85"/>
+      <c r="Q30" s="85"/>
+      <c r="R30" s="85"/>
+      <c r="S30" s="85"/>
+      <c r="T30" s="85"/>
+      <c r="U30" s="85"/>
+      <c r="V30" s="85"/>
+      <c r="W30" s="85"/>
+      <c r="X30" s="85"/>
+      <c r="Y30" s="85"/>
+      <c r="Z30" s="85"/>
+      <c r="AA30" s="85"/>
+      <c r="AB30" s="85"/>
+      <c r="AC30" s="85"/>
+      <c r="AD30" s="85"/>
+      <c r="AE30" s="85"/>
+      <c r="AF30" s="85"/>
+      <c r="AG30" s="85"/>
+      <c r="AH30" s="85"/>
+      <c r="AI30" s="85"/>
+      <c r="AJ30" s="85"/>
+      <c r="AK30" s="85"/>
+      <c r="AL30" s="85"/>
+      <c r="AM30" s="85"/>
+      <c r="AN30" s="85"/>
+      <c r="AO30" s="85"/>
+      <c r="AP30" s="93"/>
+      <c r="AQ30" s="84"/>
+      <c r="AR30" s="85"/>
+      <c r="AS30" s="85"/>
+      <c r="AT30" s="85"/>
+      <c r="AU30" s="85"/>
+      <c r="AV30" s="85"/>
+      <c r="AW30" s="85"/>
+      <c r="AX30" s="85"/>
+      <c r="AY30" s="85"/>
+      <c r="AZ30" s="85"/>
+      <c r="BA30" s="85"/>
+      <c r="BB30" s="85"/>
+      <c r="BC30" s="85"/>
+      <c r="BD30" s="85"/>
+      <c r="BE30" s="86"/>
     </row>
     <row r="31" spans="1:57" ht="15" customHeight="1">
-      <c r="A31" s="84"/>
-      <c r="B31" s="85"/>
-      <c r="C31" s="85"/>
-      <c r="D31" s="85"/>
-      <c r="E31" s="85"/>
-      <c r="F31" s="85"/>
-      <c r="G31" s="86"/>
+      <c r="A31" s="104"/>
+      <c r="B31" s="105"/>
+      <c r="C31" s="105"/>
+      <c r="D31" s="105"/>
+      <c r="E31" s="105"/>
+      <c r="F31" s="105"/>
+      <c r="G31" s="106"/>
       <c r="H31" s="87"/>
       <c r="I31" s="88"/>
       <c r="J31" s="88"/>
@@ -66829,57 +66797,57 @@
       <c r="M31" s="88"/>
       <c r="N31" s="89"/>
       <c r="O31" s="87"/>
-      <c r="P31" s="90"/>
-      <c r="Q31" s="90"/>
-      <c r="R31" s="90"/>
-      <c r="S31" s="90"/>
-      <c r="T31" s="90"/>
-      <c r="U31" s="90"/>
-      <c r="V31" s="90"/>
-      <c r="W31" s="90"/>
-      <c r="X31" s="90"/>
-      <c r="Y31" s="90"/>
-      <c r="Z31" s="90"/>
-      <c r="AA31" s="90"/>
-      <c r="AB31" s="90"/>
-      <c r="AC31" s="90"/>
-      <c r="AD31" s="90"/>
-      <c r="AE31" s="90"/>
-      <c r="AF31" s="90"/>
-      <c r="AG31" s="90"/>
-      <c r="AH31" s="90"/>
-      <c r="AI31" s="90"/>
-      <c r="AJ31" s="90"/>
-      <c r="AK31" s="90"/>
-      <c r="AL31" s="90"/>
-      <c r="AM31" s="90"/>
-      <c r="AN31" s="90"/>
-      <c r="AO31" s="90"/>
-      <c r="AP31" s="91"/>
-      <c r="AQ31" s="95"/>
-      <c r="AR31" s="90"/>
-      <c r="AS31" s="90"/>
-      <c r="AT31" s="90"/>
-      <c r="AU31" s="90"/>
-      <c r="AV31" s="90"/>
-      <c r="AW31" s="90"/>
-      <c r="AX31" s="90"/>
-      <c r="AY31" s="90"/>
-      <c r="AZ31" s="90"/>
-      <c r="BA31" s="90"/>
-      <c r="BB31" s="90"/>
-      <c r="BC31" s="90"/>
-      <c r="BD31" s="90"/>
-      <c r="BE31" s="96"/>
+      <c r="P31" s="85"/>
+      <c r="Q31" s="85"/>
+      <c r="R31" s="85"/>
+      <c r="S31" s="85"/>
+      <c r="T31" s="85"/>
+      <c r="U31" s="85"/>
+      <c r="V31" s="85"/>
+      <c r="W31" s="85"/>
+      <c r="X31" s="85"/>
+      <c r="Y31" s="85"/>
+      <c r="Z31" s="85"/>
+      <c r="AA31" s="85"/>
+      <c r="AB31" s="85"/>
+      <c r="AC31" s="85"/>
+      <c r="AD31" s="85"/>
+      <c r="AE31" s="85"/>
+      <c r="AF31" s="85"/>
+      <c r="AG31" s="85"/>
+      <c r="AH31" s="85"/>
+      <c r="AI31" s="85"/>
+      <c r="AJ31" s="85"/>
+      <c r="AK31" s="85"/>
+      <c r="AL31" s="85"/>
+      <c r="AM31" s="85"/>
+      <c r="AN31" s="85"/>
+      <c r="AO31" s="85"/>
+      <c r="AP31" s="93"/>
+      <c r="AQ31" s="84"/>
+      <c r="AR31" s="85"/>
+      <c r="AS31" s="85"/>
+      <c r="AT31" s="85"/>
+      <c r="AU31" s="85"/>
+      <c r="AV31" s="85"/>
+      <c r="AW31" s="85"/>
+      <c r="AX31" s="85"/>
+      <c r="AY31" s="85"/>
+      <c r="AZ31" s="85"/>
+      <c r="BA31" s="85"/>
+      <c r="BB31" s="85"/>
+      <c r="BC31" s="85"/>
+      <c r="BD31" s="85"/>
+      <c r="BE31" s="86"/>
     </row>
     <row r="32" spans="1:57" ht="15" customHeight="1">
-      <c r="A32" s="84"/>
-      <c r="B32" s="85"/>
-      <c r="C32" s="85"/>
-      <c r="D32" s="85"/>
-      <c r="E32" s="85"/>
-      <c r="F32" s="85"/>
-      <c r="G32" s="86"/>
+      <c r="A32" s="104"/>
+      <c r="B32" s="105"/>
+      <c r="C32" s="105"/>
+      <c r="D32" s="105"/>
+      <c r="E32" s="105"/>
+      <c r="F32" s="105"/>
+      <c r="G32" s="106"/>
       <c r="H32" s="87"/>
       <c r="I32" s="88"/>
       <c r="J32" s="88"/>
@@ -66888,57 +66856,57 @@
       <c r="M32" s="88"/>
       <c r="N32" s="89"/>
       <c r="O32" s="87"/>
-      <c r="P32" s="90"/>
-      <c r="Q32" s="90"/>
-      <c r="R32" s="90"/>
-      <c r="S32" s="90"/>
-      <c r="T32" s="90"/>
-      <c r="U32" s="90"/>
-      <c r="V32" s="90"/>
-      <c r="W32" s="90"/>
-      <c r="X32" s="90"/>
-      <c r="Y32" s="90"/>
-      <c r="Z32" s="90"/>
-      <c r="AA32" s="90"/>
-      <c r="AB32" s="90"/>
-      <c r="AC32" s="90"/>
-      <c r="AD32" s="90"/>
-      <c r="AE32" s="90"/>
-      <c r="AF32" s="90"/>
-      <c r="AG32" s="90"/>
-      <c r="AH32" s="90"/>
-      <c r="AI32" s="90"/>
-      <c r="AJ32" s="90"/>
-      <c r="AK32" s="90"/>
-      <c r="AL32" s="90"/>
-      <c r="AM32" s="90"/>
-      <c r="AN32" s="90"/>
-      <c r="AO32" s="90"/>
-      <c r="AP32" s="91"/>
-      <c r="AQ32" s="95"/>
-      <c r="AR32" s="90"/>
-      <c r="AS32" s="90"/>
-      <c r="AT32" s="90"/>
-      <c r="AU32" s="90"/>
-      <c r="AV32" s="90"/>
-      <c r="AW32" s="90"/>
-      <c r="AX32" s="90"/>
-      <c r="AY32" s="90"/>
-      <c r="AZ32" s="90"/>
-      <c r="BA32" s="90"/>
-      <c r="BB32" s="90"/>
-      <c r="BC32" s="90"/>
-      <c r="BD32" s="90"/>
-      <c r="BE32" s="96"/>
+      <c r="P32" s="85"/>
+      <c r="Q32" s="85"/>
+      <c r="R32" s="85"/>
+      <c r="S32" s="85"/>
+      <c r="T32" s="85"/>
+      <c r="U32" s="85"/>
+      <c r="V32" s="85"/>
+      <c r="W32" s="85"/>
+      <c r="X32" s="85"/>
+      <c r="Y32" s="85"/>
+      <c r="Z32" s="85"/>
+      <c r="AA32" s="85"/>
+      <c r="AB32" s="85"/>
+      <c r="AC32" s="85"/>
+      <c r="AD32" s="85"/>
+      <c r="AE32" s="85"/>
+      <c r="AF32" s="85"/>
+      <c r="AG32" s="85"/>
+      <c r="AH32" s="85"/>
+      <c r="AI32" s="85"/>
+      <c r="AJ32" s="85"/>
+      <c r="AK32" s="85"/>
+      <c r="AL32" s="85"/>
+      <c r="AM32" s="85"/>
+      <c r="AN32" s="85"/>
+      <c r="AO32" s="85"/>
+      <c r="AP32" s="93"/>
+      <c r="AQ32" s="84"/>
+      <c r="AR32" s="85"/>
+      <c r="AS32" s="85"/>
+      <c r="AT32" s="85"/>
+      <c r="AU32" s="85"/>
+      <c r="AV32" s="85"/>
+      <c r="AW32" s="85"/>
+      <c r="AX32" s="85"/>
+      <c r="AY32" s="85"/>
+      <c r="AZ32" s="85"/>
+      <c r="BA32" s="85"/>
+      <c r="BB32" s="85"/>
+      <c r="BC32" s="85"/>
+      <c r="BD32" s="85"/>
+      <c r="BE32" s="86"/>
     </row>
     <row r="33" spans="1:57" ht="15" customHeight="1">
-      <c r="A33" s="84"/>
-      <c r="B33" s="85"/>
-      <c r="C33" s="85"/>
-      <c r="D33" s="85"/>
-      <c r="E33" s="85"/>
-      <c r="F33" s="85"/>
-      <c r="G33" s="86"/>
+      <c r="A33" s="104"/>
+      <c r="B33" s="105"/>
+      <c r="C33" s="105"/>
+      <c r="D33" s="105"/>
+      <c r="E33" s="105"/>
+      <c r="F33" s="105"/>
+      <c r="G33" s="106"/>
       <c r="H33" s="87"/>
       <c r="I33" s="88"/>
       <c r="J33" s="88"/>
@@ -66947,57 +66915,57 @@
       <c r="M33" s="88"/>
       <c r="N33" s="89"/>
       <c r="O33" s="87"/>
-      <c r="P33" s="90"/>
-      <c r="Q33" s="90"/>
-      <c r="R33" s="90"/>
-      <c r="S33" s="90"/>
-      <c r="T33" s="90"/>
-      <c r="U33" s="90"/>
-      <c r="V33" s="90"/>
-      <c r="W33" s="90"/>
-      <c r="X33" s="90"/>
-      <c r="Y33" s="90"/>
-      <c r="Z33" s="90"/>
-      <c r="AA33" s="90"/>
-      <c r="AB33" s="90"/>
-      <c r="AC33" s="90"/>
-      <c r="AD33" s="90"/>
-      <c r="AE33" s="90"/>
-      <c r="AF33" s="90"/>
-      <c r="AG33" s="90"/>
-      <c r="AH33" s="90"/>
-      <c r="AI33" s="90"/>
-      <c r="AJ33" s="90"/>
-      <c r="AK33" s="90"/>
-      <c r="AL33" s="90"/>
-      <c r="AM33" s="90"/>
-      <c r="AN33" s="90"/>
-      <c r="AO33" s="90"/>
-      <c r="AP33" s="91"/>
-      <c r="AQ33" s="95"/>
-      <c r="AR33" s="90"/>
-      <c r="AS33" s="90"/>
-      <c r="AT33" s="90"/>
-      <c r="AU33" s="90"/>
-      <c r="AV33" s="90"/>
-      <c r="AW33" s="90"/>
-      <c r="AX33" s="90"/>
-      <c r="AY33" s="90"/>
-      <c r="AZ33" s="90"/>
-      <c r="BA33" s="90"/>
-      <c r="BB33" s="90"/>
-      <c r="BC33" s="90"/>
-      <c r="BD33" s="90"/>
-      <c r="BE33" s="96"/>
+      <c r="P33" s="85"/>
+      <c r="Q33" s="85"/>
+      <c r="R33" s="85"/>
+      <c r="S33" s="85"/>
+      <c r="T33" s="85"/>
+      <c r="U33" s="85"/>
+      <c r="V33" s="85"/>
+      <c r="W33" s="85"/>
+      <c r="X33" s="85"/>
+      <c r="Y33" s="85"/>
+      <c r="Z33" s="85"/>
+      <c r="AA33" s="85"/>
+      <c r="AB33" s="85"/>
+      <c r="AC33" s="85"/>
+      <c r="AD33" s="85"/>
+      <c r="AE33" s="85"/>
+      <c r="AF33" s="85"/>
+      <c r="AG33" s="85"/>
+      <c r="AH33" s="85"/>
+      <c r="AI33" s="85"/>
+      <c r="AJ33" s="85"/>
+      <c r="AK33" s="85"/>
+      <c r="AL33" s="85"/>
+      <c r="AM33" s="85"/>
+      <c r="AN33" s="85"/>
+      <c r="AO33" s="85"/>
+      <c r="AP33" s="93"/>
+      <c r="AQ33" s="84"/>
+      <c r="AR33" s="85"/>
+      <c r="AS33" s="85"/>
+      <c r="AT33" s="85"/>
+      <c r="AU33" s="85"/>
+      <c r="AV33" s="85"/>
+      <c r="AW33" s="85"/>
+      <c r="AX33" s="85"/>
+      <c r="AY33" s="85"/>
+      <c r="AZ33" s="85"/>
+      <c r="BA33" s="85"/>
+      <c r="BB33" s="85"/>
+      <c r="BC33" s="85"/>
+      <c r="BD33" s="85"/>
+      <c r="BE33" s="86"/>
     </row>
     <row r="34" spans="1:57" ht="15" customHeight="1">
-      <c r="A34" s="84"/>
-      <c r="B34" s="85"/>
-      <c r="C34" s="85"/>
-      <c r="D34" s="85"/>
-      <c r="E34" s="85"/>
-      <c r="F34" s="85"/>
-      <c r="G34" s="86"/>
+      <c r="A34" s="104"/>
+      <c r="B34" s="105"/>
+      <c r="C34" s="105"/>
+      <c r="D34" s="105"/>
+      <c r="E34" s="105"/>
+      <c r="F34" s="105"/>
+      <c r="G34" s="106"/>
       <c r="H34" s="87"/>
       <c r="I34" s="88"/>
       <c r="J34" s="88"/>
@@ -67006,110 +66974,219 @@
       <c r="M34" s="88"/>
       <c r="N34" s="89"/>
       <c r="O34" s="87"/>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="90"/>
-      <c r="S34" s="90"/>
-      <c r="T34" s="90"/>
-      <c r="U34" s="90"/>
-      <c r="V34" s="90"/>
-      <c r="W34" s="90"/>
-      <c r="X34" s="90"/>
-      <c r="Y34" s="90"/>
-      <c r="Z34" s="90"/>
-      <c r="AA34" s="90"/>
-      <c r="AB34" s="90"/>
-      <c r="AC34" s="90"/>
-      <c r="AD34" s="90"/>
-      <c r="AE34" s="90"/>
-      <c r="AF34" s="90"/>
-      <c r="AG34" s="90"/>
-      <c r="AH34" s="90"/>
-      <c r="AI34" s="90"/>
-      <c r="AJ34" s="90"/>
-      <c r="AK34" s="90"/>
-      <c r="AL34" s="90"/>
-      <c r="AM34" s="90"/>
-      <c r="AN34" s="90"/>
-      <c r="AO34" s="90"/>
-      <c r="AP34" s="91"/>
-      <c r="AQ34" s="95"/>
-      <c r="AR34" s="90"/>
-      <c r="AS34" s="90"/>
-      <c r="AT34" s="90"/>
-      <c r="AU34" s="90"/>
-      <c r="AV34" s="90"/>
-      <c r="AW34" s="90"/>
-      <c r="AX34" s="90"/>
-      <c r="AY34" s="90"/>
-      <c r="AZ34" s="90"/>
-      <c r="BA34" s="90"/>
-      <c r="BB34" s="90"/>
-      <c r="BC34" s="90"/>
-      <c r="BD34" s="90"/>
-      <c r="BE34" s="96"/>
+      <c r="P34" s="85"/>
+      <c r="Q34" s="85"/>
+      <c r="R34" s="85"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="85"/>
+      <c r="V34" s="85"/>
+      <c r="W34" s="85"/>
+      <c r="X34" s="85"/>
+      <c r="Y34" s="85"/>
+      <c r="Z34" s="85"/>
+      <c r="AA34" s="85"/>
+      <c r="AB34" s="85"/>
+      <c r="AC34" s="85"/>
+      <c r="AD34" s="85"/>
+      <c r="AE34" s="85"/>
+      <c r="AF34" s="85"/>
+      <c r="AG34" s="85"/>
+      <c r="AH34" s="85"/>
+      <c r="AI34" s="85"/>
+      <c r="AJ34" s="85"/>
+      <c r="AK34" s="85"/>
+      <c r="AL34" s="85"/>
+      <c r="AM34" s="85"/>
+      <c r="AN34" s="85"/>
+      <c r="AO34" s="85"/>
+      <c r="AP34" s="93"/>
+      <c r="AQ34" s="84"/>
+      <c r="AR34" s="85"/>
+      <c r="AS34" s="85"/>
+      <c r="AT34" s="85"/>
+      <c r="AU34" s="85"/>
+      <c r="AV34" s="85"/>
+      <c r="AW34" s="85"/>
+      <c r="AX34" s="85"/>
+      <c r="AY34" s="85"/>
+      <c r="AZ34" s="85"/>
+      <c r="BA34" s="85"/>
+      <c r="BB34" s="85"/>
+      <c r="BC34" s="85"/>
+      <c r="BD34" s="85"/>
+      <c r="BE34" s="86"/>
     </row>
     <row r="35" spans="1:57" ht="15" customHeight="1" thickBot="1">
-      <c r="A35" s="101"/>
-      <c r="B35" s="102"/>
-      <c r="C35" s="102"/>
-      <c r="D35" s="102"/>
-      <c r="E35" s="102"/>
-      <c r="F35" s="102"/>
-      <c r="G35" s="103"/>
-      <c r="H35" s="97"/>
-      <c r="I35" s="98"/>
-      <c r="J35" s="98"/>
-      <c r="K35" s="98"/>
-      <c r="L35" s="98"/>
-      <c r="M35" s="98"/>
-      <c r="N35" s="99"/>
-      <c r="O35" s="97"/>
-      <c r="P35" s="93"/>
-      <c r="Q35" s="93"/>
-      <c r="R35" s="93"/>
-      <c r="S35" s="93"/>
-      <c r="T35" s="93"/>
-      <c r="U35" s="93"/>
-      <c r="V35" s="93"/>
-      <c r="W35" s="93"/>
-      <c r="X35" s="93"/>
-      <c r="Y35" s="93"/>
-      <c r="Z35" s="93"/>
-      <c r="AA35" s="93"/>
-      <c r="AB35" s="93"/>
-      <c r="AC35" s="93"/>
-      <c r="AD35" s="93"/>
-      <c r="AE35" s="93"/>
-      <c r="AF35" s="93"/>
-      <c r="AG35" s="93"/>
-      <c r="AH35" s="93"/>
-      <c r="AI35" s="93"/>
-      <c r="AJ35" s="93"/>
-      <c r="AK35" s="93"/>
-      <c r="AL35" s="93"/>
-      <c r="AM35" s="93"/>
-      <c r="AN35" s="93"/>
-      <c r="AO35" s="93"/>
-      <c r="AP35" s="100"/>
-      <c r="AQ35" s="92"/>
-      <c r="AR35" s="93"/>
-      <c r="AS35" s="93"/>
-      <c r="AT35" s="93"/>
-      <c r="AU35" s="93"/>
-      <c r="AV35" s="93"/>
-      <c r="AW35" s="93"/>
-      <c r="AX35" s="93"/>
-      <c r="AY35" s="93"/>
-      <c r="AZ35" s="93"/>
-      <c r="BA35" s="93"/>
-      <c r="BB35" s="93"/>
-      <c r="BC35" s="93"/>
-      <c r="BD35" s="93"/>
-      <c r="BE35" s="94"/>
+      <c r="A35" s="125"/>
+      <c r="B35" s="126"/>
+      <c r="C35" s="126"/>
+      <c r="D35" s="126"/>
+      <c r="E35" s="126"/>
+      <c r="F35" s="126"/>
+      <c r="G35" s="127"/>
+      <c r="H35" s="131"/>
+      <c r="I35" s="132"/>
+      <c r="J35" s="132"/>
+      <c r="K35" s="132"/>
+      <c r="L35" s="132"/>
+      <c r="M35" s="132"/>
+      <c r="N35" s="133"/>
+      <c r="O35" s="131"/>
+      <c r="P35" s="129"/>
+      <c r="Q35" s="129"/>
+      <c r="R35" s="129"/>
+      <c r="S35" s="129"/>
+      <c r="T35" s="129"/>
+      <c r="U35" s="129"/>
+      <c r="V35" s="129"/>
+      <c r="W35" s="129"/>
+      <c r="X35" s="129"/>
+      <c r="Y35" s="129"/>
+      <c r="Z35" s="129"/>
+      <c r="AA35" s="129"/>
+      <c r="AB35" s="129"/>
+      <c r="AC35" s="129"/>
+      <c r="AD35" s="129"/>
+      <c r="AE35" s="129"/>
+      <c r="AF35" s="129"/>
+      <c r="AG35" s="129"/>
+      <c r="AH35" s="129"/>
+      <c r="AI35" s="129"/>
+      <c r="AJ35" s="129"/>
+      <c r="AK35" s="129"/>
+      <c r="AL35" s="129"/>
+      <c r="AM35" s="129"/>
+      <c r="AN35" s="129"/>
+      <c r="AO35" s="129"/>
+      <c r="AP35" s="134"/>
+      <c r="AQ35" s="128"/>
+      <c r="AR35" s="129"/>
+      <c r="AS35" s="129"/>
+      <c r="AT35" s="129"/>
+      <c r="AU35" s="129"/>
+      <c r="AV35" s="129"/>
+      <c r="AW35" s="129"/>
+      <c r="AX35" s="129"/>
+      <c r="AY35" s="129"/>
+      <c r="AZ35" s="129"/>
+      <c r="BA35" s="129"/>
+      <c r="BB35" s="129"/>
+      <c r="BC35" s="129"/>
+      <c r="BD35" s="129"/>
+      <c r="BE35" s="130"/>
     </row>
   </sheetData>
   <mergeCells count="133">
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="O19:AP19"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AQ35:BE35"/>
+    <mergeCell ref="AQ33:BE33"/>
+    <mergeCell ref="AQ34:BE34"/>
+    <mergeCell ref="AQ32:BE32"/>
+    <mergeCell ref="AQ31:BE31"/>
+    <mergeCell ref="O27:AP27"/>
+    <mergeCell ref="AQ27:BE27"/>
+    <mergeCell ref="H30:N30"/>
+    <mergeCell ref="O30:AP30"/>
+    <mergeCell ref="AQ30:BE30"/>
+    <mergeCell ref="AQ28:BE28"/>
+    <mergeCell ref="H28:N28"/>
+    <mergeCell ref="O28:AP28"/>
+    <mergeCell ref="H35:N35"/>
+    <mergeCell ref="O35:AP35"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="H33:N33"/>
+    <mergeCell ref="H34:N34"/>
+    <mergeCell ref="O34:AP34"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="O33:AP33"/>
+    <mergeCell ref="O32:AP32"/>
+    <mergeCell ref="H31:N31"/>
+    <mergeCell ref="O31:AP31"/>
+    <mergeCell ref="H27:N27"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="H32:N32"/>
+    <mergeCell ref="H29:N29"/>
+    <mergeCell ref="O29:AP29"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:AP20"/>
+    <mergeCell ref="AQ17:BE17"/>
+    <mergeCell ref="H26:N26"/>
+    <mergeCell ref="O26:AP26"/>
+    <mergeCell ref="AQ26:BE26"/>
+    <mergeCell ref="AQ19:BE19"/>
+    <mergeCell ref="H25:N25"/>
+    <mergeCell ref="H24:N24"/>
+    <mergeCell ref="O24:AP24"/>
+    <mergeCell ref="O25:AP25"/>
+    <mergeCell ref="AQ25:BE25"/>
+    <mergeCell ref="H22:N22"/>
+    <mergeCell ref="AQ24:BE24"/>
+    <mergeCell ref="H23:N23"/>
+    <mergeCell ref="O23:AP23"/>
+    <mergeCell ref="AQ23:BE23"/>
+    <mergeCell ref="AQ20:BE20"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:AP21"/>
+    <mergeCell ref="AQ18:BE18"/>
+    <mergeCell ref="AQ21:BE21"/>
+    <mergeCell ref="O22:AP22"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="H4:N4"/>
+    <mergeCell ref="O4:AP4"/>
+    <mergeCell ref="AQ4:BE4"/>
+    <mergeCell ref="H13:N13"/>
+    <mergeCell ref="O13:AP13"/>
+    <mergeCell ref="AQ13:BE13"/>
+    <mergeCell ref="H14:N14"/>
+    <mergeCell ref="O14:AP14"/>
+    <mergeCell ref="AQ14:BE14"/>
+    <mergeCell ref="AQ16:BE16"/>
+    <mergeCell ref="H15:N15"/>
+    <mergeCell ref="O18:AP18"/>
+    <mergeCell ref="H9:N9"/>
+    <mergeCell ref="O9:AP9"/>
+    <mergeCell ref="AQ9:BE9"/>
+    <mergeCell ref="H10:N10"/>
+    <mergeCell ref="O10:AP10"/>
+    <mergeCell ref="AQ10:BE10"/>
+    <mergeCell ref="H11:N11"/>
+    <mergeCell ref="O11:AP11"/>
+    <mergeCell ref="AQ11:BE11"/>
+    <mergeCell ref="H16:N16"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="O15:AP15"/>
+    <mergeCell ref="A1:BE1"/>
+    <mergeCell ref="H3:N3"/>
+    <mergeCell ref="O3:AP3"/>
+    <mergeCell ref="AQ3:BE3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
     <mergeCell ref="AQ22:BE22"/>
     <mergeCell ref="AQ29:BE29"/>
     <mergeCell ref="H17:N17"/>
@@ -67134,115 +67211,6 @@
     <mergeCell ref="A9:G9"/>
     <mergeCell ref="O16:AP16"/>
     <mergeCell ref="O17:AP17"/>
-    <mergeCell ref="A1:BE1"/>
-    <mergeCell ref="H3:N3"/>
-    <mergeCell ref="O3:AP3"/>
-    <mergeCell ref="AQ3:BE3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="O15:AP15"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="H4:N4"/>
-    <mergeCell ref="O4:AP4"/>
-    <mergeCell ref="AQ4:BE4"/>
-    <mergeCell ref="H13:N13"/>
-    <mergeCell ref="O13:AP13"/>
-    <mergeCell ref="AQ13:BE13"/>
-    <mergeCell ref="H14:N14"/>
-    <mergeCell ref="O14:AP14"/>
-    <mergeCell ref="AQ14:BE14"/>
-    <mergeCell ref="AQ16:BE16"/>
-    <mergeCell ref="H15:N15"/>
-    <mergeCell ref="O18:AP18"/>
-    <mergeCell ref="H9:N9"/>
-    <mergeCell ref="O9:AP9"/>
-    <mergeCell ref="AQ9:BE9"/>
-    <mergeCell ref="H10:N10"/>
-    <mergeCell ref="O10:AP10"/>
-    <mergeCell ref="AQ10:BE10"/>
-    <mergeCell ref="H11:N11"/>
-    <mergeCell ref="O11:AP11"/>
-    <mergeCell ref="AQ11:BE11"/>
-    <mergeCell ref="H16:N16"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:AP20"/>
-    <mergeCell ref="AQ17:BE17"/>
-    <mergeCell ref="H26:N26"/>
-    <mergeCell ref="O26:AP26"/>
-    <mergeCell ref="AQ26:BE26"/>
-    <mergeCell ref="AQ19:BE19"/>
-    <mergeCell ref="H25:N25"/>
-    <mergeCell ref="H24:N24"/>
-    <mergeCell ref="O24:AP24"/>
-    <mergeCell ref="O25:AP25"/>
-    <mergeCell ref="AQ25:BE25"/>
-    <mergeCell ref="H22:N22"/>
-    <mergeCell ref="AQ24:BE24"/>
-    <mergeCell ref="H23:N23"/>
-    <mergeCell ref="O23:AP23"/>
-    <mergeCell ref="AQ23:BE23"/>
-    <mergeCell ref="AQ20:BE20"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:AP21"/>
-    <mergeCell ref="AQ18:BE18"/>
-    <mergeCell ref="AQ21:BE21"/>
-    <mergeCell ref="O22:AP22"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="H33:N33"/>
-    <mergeCell ref="H34:N34"/>
-    <mergeCell ref="O34:AP34"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="O33:AP33"/>
-    <mergeCell ref="O32:AP32"/>
-    <mergeCell ref="H31:N31"/>
-    <mergeCell ref="O31:AP31"/>
-    <mergeCell ref="H27:N27"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="H32:N32"/>
-    <mergeCell ref="H29:N29"/>
-    <mergeCell ref="O29:AP29"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="O19:AP19"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="AQ35:BE35"/>
-    <mergeCell ref="AQ33:BE33"/>
-    <mergeCell ref="AQ34:BE34"/>
-    <mergeCell ref="AQ32:BE32"/>
-    <mergeCell ref="AQ31:BE31"/>
-    <mergeCell ref="O27:AP27"/>
-    <mergeCell ref="AQ27:BE27"/>
-    <mergeCell ref="H30:N30"/>
-    <mergeCell ref="O30:AP30"/>
-    <mergeCell ref="AQ30:BE30"/>
-    <mergeCell ref="AQ28:BE28"/>
-    <mergeCell ref="H28:N28"/>
-    <mergeCell ref="O28:AP28"/>
-    <mergeCell ref="H35:N35"/>
-    <mergeCell ref="O35:AP35"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A20:G20"/>
   </mergeCells>
   <phoneticPr fontId="5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
